--- a/data/BAN.MI.xlsx
+++ b/data/BAN.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1475" uniqueCount="1475">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1476" uniqueCount="1476">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -38,19 +38,19 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">3.6691300868988</t>
+    <t xml:space="preserve">3.66912961006165</t>
   </si>
   <si>
     <t xml:space="preserve">BAN.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">3.68330264091492</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.59039354324341</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.46283984184265</t>
+    <t xml:space="preserve">3.68330216407776</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.59039330482483</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.46283936500549</t>
   </si>
   <si>
     <t xml:space="preserve">3.41874718666077</t>
@@ -62,7 +62,7 @@
     <t xml:space="preserve">3.44551777839661</t>
   </si>
   <si>
-    <t xml:space="preserve">3.46441411972046</t>
+    <t xml:space="preserve">3.46441459655762</t>
   </si>
   <si>
     <t xml:space="preserve">3.45181632041931</t>
@@ -71,10 +71,10 @@
     <t xml:space="preserve">3.43134450912476</t>
   </si>
   <si>
-    <t xml:space="preserve">3.38410329818726</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.40929913520813</t>
+    <t xml:space="preserve">3.3841028213501</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.40929889678955</t>
   </si>
   <si>
     <t xml:space="preserve">3.11639809608459</t>
@@ -95,10 +95,10 @@
     <t xml:space="preserve">3.19356036186218</t>
   </si>
   <si>
-    <t xml:space="preserve">3.13372015953064</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.22820425033569</t>
+    <t xml:space="preserve">3.13372039794922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.22820448875427</t>
   </si>
   <si>
     <t xml:space="preserve">3.16678977012634</t>
@@ -110,31 +110,31 @@
     <t xml:space="preserve">3.07073140144348</t>
   </si>
   <si>
-    <t xml:space="preserve">3.1494677066803</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.05025911331177</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.92900490760803</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.91325783729553</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.83452033996582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.82664728164673</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.75263452529907</t>
+    <t xml:space="preserve">3.14946746826172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.0502598285675</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.92900466918945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.91325807571411</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.8345205783844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.82664704322815</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.75263476371765</t>
   </si>
   <si>
     <t xml:space="preserve">2.75420928001404</t>
   </si>
   <si>
-    <t xml:space="preserve">2.755784034729</t>
+    <t xml:space="preserve">2.75578451156616</t>
   </si>
   <si>
     <t xml:space="preserve">2.89436101913452</t>
@@ -149,67 +149,67 @@
     <t xml:space="preserve">2.99356913566589</t>
   </si>
   <si>
-    <t xml:space="preserve">3.05970740318298</t>
+    <t xml:space="preserve">3.05970788002014</t>
   </si>
   <si>
     <t xml:space="preserve">3.11009955406189</t>
   </si>
   <si>
-    <t xml:space="preserve">3.06915616989136</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.96364903450012</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.99199438095093</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.00774145126343</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.97624683380127</t>
+    <t xml:space="preserve">3.06915640830994</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.96364879608154</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.99199390411377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.00774121284485</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.97624707221985</t>
   </si>
   <si>
     <t xml:space="preserve">3.06285738945007</t>
   </si>
   <si>
-    <t xml:space="preserve">3.1179735660553</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.18096232414246</t>
+    <t xml:space="preserve">3.11797332763672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.18096256256104</t>
   </si>
   <si>
     <t xml:space="preserve">3.10222578048706</t>
   </si>
   <si>
-    <t xml:space="preserve">3.13686966896057</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.23292899131775</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.33843541145325</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.30694055557251</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.24395155906677</t>
+    <t xml:space="preserve">3.13686990737915</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.23292875289917</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.33843564987183</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.30694103240967</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.24395203590393</t>
   </si>
   <si>
     <t xml:space="preserve">3.24237704277039</t>
   </si>
   <si>
-    <t xml:space="preserve">3.12584686279297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.19670987129211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.2030086517334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.10380029678345</t>
+    <t xml:space="preserve">3.12584638595581</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.19670963287354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.20300841331482</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.10380053520203</t>
   </si>
   <si>
     <t xml:space="preserve">3.11324882507324</t>
@@ -227,52 +227,52 @@
     <t xml:space="preserve">2.96049952507019</t>
   </si>
   <si>
-    <t xml:space="preserve">3.09435176849365</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.96837329864502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.86286568641663</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.87388920783997</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.91010856628418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.98569536209106</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.00144267082214</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.01561546325684</t>
+    <t xml:space="preserve">3.09435224533081</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.9683735370636</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.86286592483521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.87388944625854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.9101083278656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.98569560050964</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.00144290924072</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.01561522483826</t>
   </si>
   <si>
     <t xml:space="preserve">2.92742991447449</t>
   </si>
   <si>
-    <t xml:space="preserve">2.9211311340332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.85814237594604</t>
+    <t xml:space="preserve">2.92113137245178</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.85814189910889</t>
   </si>
   <si>
     <t xml:space="preserve">2.814049243927</t>
   </si>
   <si>
-    <t xml:space="preserve">2.84081983566284</t>
+    <t xml:space="preserve">2.84082007408142</t>
   </si>
   <si>
     <t xml:space="preserve">2.80145144462585</t>
   </si>
   <si>
-    <t xml:space="preserve">2.72901368141174</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.65185213088989</t>
+    <t xml:space="preserve">2.72901344299316</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.65185141563416</t>
   </si>
   <si>
     <t xml:space="preserve">2.68177151679993</t>
@@ -281,166 +281,166 @@
     <t xml:space="preserve">2.71484112739563</t>
   </si>
   <si>
-    <t xml:space="preserve">2.76365756988525</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.77940511703491</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.72428965568542</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.59043741226196</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.53532147407532</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.49437832832336</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.48020601272583</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.51957440376282</t>
+    <t xml:space="preserve">2.76365852355957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.77940535545349</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.724289894104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.59043717384338</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.53532123565674</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.49437856674194</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.48020577430725</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.51957416534424</t>
   </si>
   <si>
     <t xml:space="preserve">2.60572743415833</t>
   </si>
   <si>
-    <t xml:space="preserve">2.58784651756287</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.56021285057068</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.56183791160583</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.60897827148438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.59272313117981</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.58134436607361</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.60085082054138</t>
+    <t xml:space="preserve">2.58784627914429</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.5602126121521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.56183767318726</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.60897850990295</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.59272289276123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.58134460449219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.60085105895996</t>
   </si>
   <si>
     <t xml:space="preserve">2.72114014625549</t>
   </si>
   <si>
-    <t xml:space="preserve">2.82029747962952</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.80404210090637</t>
+    <t xml:space="preserve">2.82029724121094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.80404233932495</t>
   </si>
   <si>
     <t xml:space="preserve">2.68212723731995</t>
   </si>
   <si>
-    <t xml:space="preserve">2.71463799476624</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.44642496109009</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.39765930175781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.50331854820251</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.47568511962891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.51957416534424</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.52770161628723</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.50819540023804</t>
+    <t xml:space="preserve">2.71463775634766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.44642543792725</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.39765954017639</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.50331878662109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.47568488121033</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.51957392692566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.52770185470581</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.50819516181946</t>
   </si>
   <si>
     <t xml:space="preserve">2.40578699111938</t>
   </si>
   <si>
-    <t xml:space="preserve">2.19446802139282</t>
+    <t xml:space="preserve">2.19446754455566</t>
   </si>
   <si>
     <t xml:space="preserve">2.2351062297821</t>
   </si>
   <si>
-    <t xml:space="preserve">2.29525065422058</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.27411866188049</t>
+    <t xml:space="preserve">2.29525089263916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.27411890029907</t>
   </si>
   <si>
     <t xml:space="preserve">2.35702133178711</t>
   </si>
   <si>
-    <t xml:space="preserve">2.37327599525452</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.29199981689453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.19284224510193</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.22535300254822</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.28387188911438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.30500364303589</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.33101272583008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.33588862419128</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.33263826370239</t>
+    <t xml:space="preserve">2.37327647209167</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.29200005531311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.19284248352051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.22535276412964</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.28387212753296</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.30500388145447</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.3310124874115</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.33588910102844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.33263778686523</t>
   </si>
   <si>
     <t xml:space="preserve">2.3196337223053</t>
   </si>
   <si>
-    <t xml:space="preserve">2.38140392303467</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.53582978248596</t>
+    <t xml:space="preserve">2.38140416145325</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.5358293056488</t>
   </si>
   <si>
     <t xml:space="preserve">2.54395723342896</t>
   </si>
   <si>
-    <t xml:space="preserve">2.56834030151367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.89669728279114</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.83817887306213</t>
+    <t xml:space="preserve">2.56834006309509</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.89669752120972</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.83817839622498</t>
   </si>
   <si>
     <t xml:space="preserve">2.81217002868652</t>
   </si>
   <si>
-    <t xml:space="preserve">2.59597444534302</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.57646751403809</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.57321667671204</t>
+    <t xml:space="preserve">2.59597396850586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.57646775245667</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.57321643829346</t>
   </si>
   <si>
     <t xml:space="preserve">2.56671452522278</t>
@@ -449,40 +449,40 @@
     <t xml:space="preserve">2.53257846832275</t>
   </si>
   <si>
-    <t xml:space="preserve">2.5374550819397</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.63661241531372</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.63011050224304</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.64636564254761</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.65286755561829</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.63823771476746</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.64148902893066</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.69188070297241</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.75690150260925</t>
+    <t xml:space="preserve">2.53745532035828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.6366126537323</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.63011026382446</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.64636540412903</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.65286779403687</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.63823795318604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.64148879051208</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.69188046455383</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.75690197944641</t>
   </si>
   <si>
     <t xml:space="preserve">2.79266333580017</t>
   </si>
   <si>
-    <t xml:space="preserve">2.76340389251709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.73089289665222</t>
+    <t xml:space="preserve">2.76340413093567</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.7308931350708</t>
   </si>
   <si>
     <t xml:space="preserve">2.65449333190918</t>
@@ -491,16 +491,16 @@
     <t xml:space="preserve">2.65774416923523</t>
   </si>
   <si>
-    <t xml:space="preserve">2.742271900177</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.76828026771545</t>
+    <t xml:space="preserve">2.74227213859558</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.76828002929688</t>
   </si>
   <si>
     <t xml:space="preserve">2.70651030540466</t>
   </si>
   <si>
-    <t xml:space="preserve">2.72764253616333</t>
+    <t xml:space="preserve">2.72764229774475</t>
   </si>
   <si>
     <t xml:space="preserve">2.74064660072327</t>
@@ -512,37 +512,37 @@
     <t xml:space="preserve">2.80079126358032</t>
   </si>
   <si>
-    <t xml:space="preserve">2.69513130187988</t>
+    <t xml:space="preserve">2.69513154029846</t>
   </si>
   <si>
     <t xml:space="preserve">2.66749739646912</t>
   </si>
   <si>
-    <t xml:space="preserve">2.64799094200134</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.62523365020752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.59759998321533</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.61710619926453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.66587209701538</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.63336157798767</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.68862962722778</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.60247611999512</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.67725038528442</t>
+    <t xml:space="preserve">2.64799118041992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.62523412704468</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.59759974479675</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.61710596084595</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.6658718585968</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.63336133956909</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.6886293888092</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.6024763584137</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.67725086212158</t>
   </si>
   <si>
     <t xml:space="preserve">2.70976138114929</t>
@@ -557,16 +557,16 @@
     <t xml:space="preserve">2.72276544570923</t>
   </si>
   <si>
-    <t xml:space="preserve">2.82842540740967</t>
+    <t xml:space="preserve">2.82842516899109</t>
   </si>
   <si>
     <t xml:space="preserve">2.74389743804932</t>
   </si>
   <si>
-    <t xml:space="preserve">2.7617781162262</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.73902130126953</t>
+    <t xml:space="preserve">2.76177859306335</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.73902082443237</t>
   </si>
   <si>
     <t xml:space="preserve">2.70488476753235</t>
@@ -575,31 +575,31 @@
     <t xml:space="preserve">2.69025492668152</t>
   </si>
   <si>
-    <t xml:space="preserve">2.61222958564758</t>
+    <t xml:space="preserve">2.61222887039185</t>
   </si>
   <si>
     <t xml:space="preserve">2.73251891136169</t>
   </si>
   <si>
-    <t xml:space="preserve">2.67562532424927</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.62360811233521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.59434795379639</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.55371022224426</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.55045938491821</t>
+    <t xml:space="preserve">2.67562508583069</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.62360835075378</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.5943489074707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.55371046066284</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.55045914649963</t>
   </si>
   <si>
     <t xml:space="preserve">2.51307201385498</t>
   </si>
   <si>
-    <t xml:space="preserve">2.46755743026733</t>
+    <t xml:space="preserve">2.46755719184875</t>
   </si>
   <si>
     <t xml:space="preserve">2.50169348716736</t>
@@ -611,22 +611,22 @@
     <t xml:space="preserve">2.63173580169678</t>
   </si>
   <si>
-    <t xml:space="preserve">2.65611863136292</t>
+    <t xml:space="preserve">2.65611886978149</t>
   </si>
   <si>
     <t xml:space="preserve">2.66912293434143</t>
   </si>
   <si>
-    <t xml:space="preserve">2.72439098358154</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.78291058540344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.77153158187866</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.77803349494934</t>
+    <t xml:space="preserve">2.72439122200012</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.78291034698486</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.77153134346008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.77803373336792</t>
   </si>
   <si>
     <t xml:space="preserve">2.70000815391541</t>
@@ -635,34 +635,34 @@
     <t xml:space="preserve">2.7731568813324</t>
   </si>
   <si>
-    <t xml:space="preserve">2.76502966880798</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.71788907051086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.74552273750305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.77965927124023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.74714851379395</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.60410189628601</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.62685942649841</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.64961624145508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.69350576400757</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.69838261604309</t>
+    <t xml:space="preserve">2.7650294303894</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.71788883209229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.74552297592163</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.77965903282166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.7471489906311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.60410165786743</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.62685918807983</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.64961647987366</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.69350647926331</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.69838285446167</t>
   </si>
   <si>
     <t xml:space="preserve">2.92270588874817</t>
@@ -671,13 +671,13 @@
     <t xml:space="preserve">2.88531875610352</t>
   </si>
   <si>
-    <t xml:space="preserve">2.99910593032837</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.97472333908081</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.96984672546387</t>
+    <t xml:space="preserve">2.99910616874695</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.97472286224365</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.96984648704529</t>
   </si>
   <si>
     <t xml:space="preserve">2.96334409713745</t>
@@ -686,28 +686,28 @@
     <t xml:space="preserve">2.94221234321594</t>
   </si>
   <si>
-    <t xml:space="preserve">2.93408489227295</t>
+    <t xml:space="preserve">2.93408441543579</t>
   </si>
   <si>
     <t xml:space="preserve">2.89832282066345</t>
   </si>
   <si>
-    <t xml:space="preserve">2.89182090759277</t>
+    <t xml:space="preserve">2.89182066917419</t>
   </si>
   <si>
     <t xml:space="preserve">2.87881684303284</t>
   </si>
   <si>
-    <t xml:space="preserve">2.87556600570679</t>
+    <t xml:space="preserve">2.87556529045105</t>
   </si>
   <si>
     <t xml:space="preserve">2.84468054771423</t>
   </si>
   <si>
-    <t xml:space="preserve">2.82192301750183</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.8495569229126</t>
+    <t xml:space="preserve">2.82192254066467</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.84955739974976</t>
   </si>
   <si>
     <t xml:space="preserve">2.91945505142212</t>
@@ -719,19 +719,19 @@
     <t xml:space="preserve">2.9909782409668</t>
   </si>
   <si>
-    <t xml:space="preserve">2.9145781993866</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.91620373725891</t>
+    <t xml:space="preserve">2.91457843780518</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.91620421409607</t>
   </si>
   <si>
     <t xml:space="preserve">2.95846772193909</t>
   </si>
   <si>
-    <t xml:space="preserve">2.95684218406677</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.95196533203125</t>
+    <t xml:space="preserve">2.95684242248535</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.95196557044983</t>
   </si>
   <si>
     <t xml:space="preserve">3.0494978427887</t>
@@ -740,55 +740,55 @@
     <t xml:space="preserve">3.0559995174408</t>
   </si>
   <si>
-    <t xml:space="preserve">2.99585509300232</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.97959971427917</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.00723385810852</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.09645915031433</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.11628699302673</t>
+    <t xml:space="preserve">2.99585485458374</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.97959923744202</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.00723361968994</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.09645938873291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.11628746986389</t>
   </si>
   <si>
     <t xml:space="preserve">3.16916155815125</t>
   </si>
   <si>
-    <t xml:space="preserve">3.13941979408264</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.14437699317932</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.18898963928223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.18072772026062</t>
+    <t xml:space="preserve">3.13941955566406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.14437675476074</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.18898940086365</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.1807279586792</t>
   </si>
   <si>
     <t xml:space="preserve">3.24847316741943</t>
   </si>
   <si>
-    <t xml:space="preserve">3.21707916259766</t>
+    <t xml:space="preserve">3.21707940101624</t>
   </si>
   <si>
     <t xml:space="preserve">3.16750955581665</t>
   </si>
   <si>
-    <t xml:space="preserve">3.15429091453552</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.17081427574158</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.07663106918335</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.07497882843018</t>
+    <t xml:space="preserve">3.15429067611694</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.170814037323</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.07663130760193</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.0749785900116</t>
   </si>
   <si>
     <t xml:space="preserve">2.98244881629944</t>
@@ -797,46 +797,46 @@
     <t xml:space="preserve">3.05845594406128</t>
   </si>
   <si>
-    <t xml:space="preserve">3.06506490707397</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.03367066383362</t>
+    <t xml:space="preserve">3.06506514549255</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.03367042541504</t>
   </si>
   <si>
     <t xml:space="preserve">3.02540946006775</t>
   </si>
   <si>
-    <t xml:space="preserve">2.99401521682739</t>
+    <t xml:space="preserve">2.99401545524597</t>
   </si>
   <si>
     <t xml:space="preserve">2.99071025848389</t>
   </si>
   <si>
-    <t xml:space="preserve">2.99897193908691</t>
+    <t xml:space="preserve">2.99897217750549</t>
   </si>
   <si>
     <t xml:space="preserve">2.93783593177795</t>
   </si>
   <si>
-    <t xml:space="preserve">2.95601177215576</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.07993578910828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.0881974697113</t>
+    <t xml:space="preserve">2.95601153373718</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.07993602752686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.08819723129272</t>
   </si>
   <si>
     <t xml:space="preserve">3.08654522895813</t>
   </si>
   <si>
-    <t xml:space="preserve">3.10802555084229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.11133003234863</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.14768147468567</t>
+    <t xml:space="preserve">3.10802578926086</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.11133050918579</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.14768171310425</t>
   </si>
   <si>
     <t xml:space="preserve">3.16420459747314</t>
@@ -851,94 +851,94 @@
     <t xml:space="preserve">3.23029780387878</t>
   </si>
   <si>
-    <t xml:space="preserve">3.23360228538513</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.25343036651611</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.29473853111267</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.3079571723938</t>
+    <t xml:space="preserve">3.23360276222229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.25343012809753</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.29473829269409</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.30795741081238</t>
   </si>
   <si>
     <t xml:space="preserve">3.27160596847534</t>
   </si>
   <si>
-    <t xml:space="preserve">3.29639077186584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.22368836402893</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.25012540817261</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.19394659996033</t>
+    <t xml:space="preserve">3.29639053344727</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.22368860244751</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.25012564659119</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.19394636154175</t>
   </si>
   <si>
     <t xml:space="preserve">3.26334428787231</t>
   </si>
   <si>
-    <t xml:space="preserve">3.09811162948608</t>
+    <t xml:space="preserve">3.0981113910675</t>
   </si>
   <si>
     <t xml:space="preserve">3.15924763679504</t>
   </si>
   <si>
-    <t xml:space="preserve">3.17246580123901</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.17411851882935</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.15098595619202</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.05184650421143</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.05680322647095</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.08489298820496</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.12785339355469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.03201866149902</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.09480738639832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.07332682609558</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.09150242805481</t>
+    <t xml:space="preserve">3.17246627807617</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.17411875724792</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.15098571777344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.05184674263</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.05680370330811</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.08489322662354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.12785363197327</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.0320188999176</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.09480690956116</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.073326587677</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.09150266647339</t>
   </si>
   <si>
     <t xml:space="preserve">3.13115787506104</t>
   </si>
   <si>
-    <t xml:space="preserve">3.10967803001404</t>
+    <t xml:space="preserve">3.10967779159546</t>
   </si>
   <si>
     <t xml:space="preserve">3.10472083091736</t>
   </si>
   <si>
-    <t xml:space="preserve">3.12124419212341</t>
+    <t xml:space="preserve">3.12124443054199</t>
   </si>
   <si>
     <t xml:space="preserve">3.13611507415771</t>
   </si>
   <si>
-    <t xml:space="preserve">3.14602899551392</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.12950611114502</t>
+    <t xml:space="preserve">3.1460292339325</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.12950587272644</t>
   </si>
   <si>
     <t xml:space="preserve">3.14107203483582</t>
@@ -947,40 +947,40 @@
     <t xml:space="preserve">3.15759515762329</t>
   </si>
   <si>
-    <t xml:space="preserve">3.18403267860413</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.10637307167053</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.08158826828003</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.10141611099243</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.10306859016418</t>
+    <t xml:space="preserve">3.18403220176697</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.10637331008911</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.08158850669861</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.10141658782959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.10306882858276</t>
   </si>
   <si>
     <t xml:space="preserve">3.12289667129517</t>
   </si>
   <si>
-    <t xml:space="preserve">3.08985018730164</t>
+    <t xml:space="preserve">3.08984994888306</t>
   </si>
   <si>
     <t xml:space="preserve">2.94940233230591</t>
   </si>
   <si>
-    <t xml:space="preserve">2.93287897109985</t>
+    <t xml:space="preserve">2.93287873268127</t>
   </si>
   <si>
     <t xml:space="preserve">2.83704376220703</t>
   </si>
   <si>
-    <t xml:space="preserve">2.88165688514709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.90809416770935</t>
+    <t xml:space="preserve">2.88165664672852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.90809392929077</t>
   </si>
   <si>
     <t xml:space="preserve">2.9113986492157</t>
@@ -995,7 +995,7 @@
     <t xml:space="preserve">2.96592545509338</t>
   </si>
   <si>
-    <t xml:space="preserve">2.88496160507202</t>
+    <t xml:space="preserve">2.8849618434906</t>
   </si>
   <si>
     <t xml:space="preserve">2.84034895896912</t>
@@ -1004,13 +1004,13 @@
     <t xml:space="preserve">2.82878255844116</t>
   </si>
   <si>
-    <t xml:space="preserve">2.81225943565369</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.88000416755676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.75112318992615</t>
+    <t xml:space="preserve">2.81225919723511</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.8800048828125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.75112295150757</t>
   </si>
   <si>
     <t xml:space="preserve">2.80895471572876</t>
@@ -1019,16 +1019,16 @@
     <t xml:space="preserve">2.79243111610413</t>
   </si>
   <si>
-    <t xml:space="preserve">2.81391096115112</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.85852456092834</t>
+    <t xml:space="preserve">2.81391143798828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.85852432250977</t>
   </si>
   <si>
     <t xml:space="preserve">2.97418689727783</t>
   </si>
   <si>
-    <t xml:space="preserve">2.97088289260864</t>
+    <t xml:space="preserve">2.97088241577148</t>
   </si>
   <si>
     <t xml:space="preserve">3.01549530029297</t>
@@ -1037,34 +1037,34 @@
     <t xml:space="preserve">3.05515098571777</t>
   </si>
   <si>
-    <t xml:space="preserve">3.04028058052063</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.07002234458923</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.06341290473938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.023756980896</t>
+    <t xml:space="preserve">3.04028034210205</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.07002210617065</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.0634126663208</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.02375674247742</t>
   </si>
   <si>
     <t xml:space="preserve">3.0369758605957</t>
   </si>
   <si>
-    <t xml:space="preserve">3.0287139415741</t>
+    <t xml:space="preserve">3.02871370315552</t>
   </si>
   <si>
     <t xml:space="preserve">3.0534987449646</t>
   </si>
   <si>
-    <t xml:space="preserve">3.07828378677368</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.11050415039062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.06919574737549</t>
+    <t xml:space="preserve">3.07828330993652</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.11050391197205</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.06919550895691</t>
   </si>
   <si>
     <t xml:space="preserve">3.1559431552887</t>
@@ -1073,127 +1073,130 @@
     <t xml:space="preserve">3.21790528297424</t>
   </si>
   <si>
+    <t xml:space="preserve">3.17659687995911</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.19312024116516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.25508260726929</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.22203612327576</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.96179437637329</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.9783182144165</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.92461752891541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.87504768371582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.13528919219971</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.07745718955994</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.05267238616943</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.03614926338196</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.92048668861389</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.08571934700012</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.01962637901306</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.02788782119751</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.0485417842865</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.04441094398499</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.15181231498718</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.3376989364624</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.25095176696777</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.2757363319397</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.28399848937988</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.24682068824768</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.18485903739929</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.2437379360199</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.20177483558655</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.21016716957092</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.18918561935425</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.22275638580322</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.16400837898254</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.08847498893738</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.12204504013062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.14302682876587</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.20597100257874</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.25632667541504</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.24793434143066</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.10526037216187</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.07168936729431</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.18498992919922</t>
+  </si>
+  <si>
     <t xml:space="preserve">3.17659711837769</t>
   </si>
   <si>
-    <t xml:space="preserve">3.19312047958374</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.25508236885071</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.22203636169434</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.96179485321045</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.97831797599792</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.92461752891541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.87504744529724</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.13528895378113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.07745742797852</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.05267238616943</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.03614950180054</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.92048645019531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.08571910858154</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.0196259021759</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.02788734436035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.04854202270508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.04441094398499</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.15181231498718</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.3376989364624</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.25095152854919</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.27573680877686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.28399801254272</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.24682116508484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.18485879898071</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.2437379360199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.20177507400513</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.21016764640808</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.18918561935425</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.22275590896606</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.16400814056396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.08847498893738</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.12204527854919</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.14302682876587</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.20597100257874</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.25632691383362</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.24793410301208</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.10525989532471</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.07168960571289</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.18498992919922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.11365246772766</t>
+    <t xml:space="preserve">3.11365270614624</t>
   </si>
   <si>
     <t xml:space="preserve">3.1262412071228</t>
@@ -1202,10 +1205,10 @@
     <t xml:space="preserve">3.1388304233551</t>
   </si>
   <si>
-    <t xml:space="preserve">3.14722275733948</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.15561532974243</t>
+    <t xml:space="preserve">3.14722299575806</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.15561580657959</t>
   </si>
   <si>
     <t xml:space="preserve">3.1724009513855</t>
@@ -1220,10 +1223,10 @@
     <t xml:space="preserve">3.16820478439331</t>
   </si>
   <si>
-    <t xml:space="preserve">3.10945653915405</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.15981197357178</t>
+    <t xml:space="preserve">3.10945630073547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.1598117351532</t>
   </si>
   <si>
     <t xml:space="preserve">3.19338250160217</t>
@@ -1232,277 +1235,277 @@
     <t xml:space="preserve">3.21436381340027</t>
   </si>
   <si>
-    <t xml:space="preserve">3.23534536361694</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.26471948623657</t>
+    <t xml:space="preserve">3.23534560203552</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.26471924781799</t>
   </si>
   <si>
     <t xml:space="preserve">3.32346749305725</t>
   </si>
   <si>
-    <t xml:space="preserve">3.31087827682495</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.27730798721313</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.35703802108765</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.42417812347412</t>
+    <t xml:space="preserve">3.31087875366211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.27730822563171</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.35703778266907</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.4241783618927</t>
   </si>
   <si>
     <t xml:space="preserve">3.49131941795349</t>
   </si>
   <si>
-    <t xml:space="preserve">3.43257117271423</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.54167485237122</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.44935655593872</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.48292660713196</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.51649713516235</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.47453427314758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.4577488899231</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.3864119052887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.37801957130432</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.4703381061554</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.302485704422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.31927108764648</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.29829001426697</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.34025263786316</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.27311205863953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.28150463104248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.39900088310242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.57524561882019</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.58783435821533</t>
+    <t xml:space="preserve">3.43257141113281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.54167461395264</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.4493567943573</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.48292684555054</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.51649689674377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.474534034729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.45774912834167</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.38641166687012</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.37801933288574</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.47033786773682</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.30248594284058</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.31927084922791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.29828953742981</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.34025287628174</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.27311182022095</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.28150486946106</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.399001121521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.57524538040161</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.58783411979675</t>
   </si>
   <si>
     <t xml:space="preserve">3.55006766319275</t>
   </si>
   <si>
-    <t xml:space="preserve">3.57944178581238</t>
+    <t xml:space="preserve">3.57944130897522</t>
   </si>
   <si>
     <t xml:space="preserve">3.58363747596741</t>
   </si>
   <si>
-    <t xml:space="preserve">3.66336703300476</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.55845999717712</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.56685280799866</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.62140440940857</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.78086352348328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.88577103614807</t>
+    <t xml:space="preserve">3.66336727142334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.55845975875854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.56685256958008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.62140464782715</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.78086400032043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.88577127456665</t>
   </si>
   <si>
     <t xml:space="preserve">3.72211575508118</t>
   </si>
   <si>
-    <t xml:space="preserve">3.76407837867737</t>
+    <t xml:space="preserve">3.76407861709595</t>
   </si>
   <si>
     <t xml:space="preserve">3.68434882164001</t>
   </si>
   <si>
-    <t xml:space="preserve">3.79764914512634</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.82702326774597</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.80184507369995</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.83961176872253</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.91934180259705</t>
+    <t xml:space="preserve">3.79764938354492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.82702374458313</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.80184555053711</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.83961248397827</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.91934156417847</t>
   </si>
   <si>
     <t xml:space="preserve">3.91094923019409</t>
   </si>
   <si>
-    <t xml:space="preserve">3.94451951980591</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.06621170043945</t>
+    <t xml:space="preserve">3.94451928138733</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.06621217727661</t>
   </si>
   <si>
     <t xml:space="preserve">4.02005290985107</t>
   </si>
   <si>
-    <t xml:space="preserve">3.92773342132568</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.86898612976074</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.81863069534302</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.86059308052063</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.79345273971558</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.86479020118713</t>
+    <t xml:space="preserve">3.92773413658142</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.86898684501648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.8186309337616</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.86059284210205</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.793452501297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.86478996276855</t>
   </si>
   <si>
     <t xml:space="preserve">3.87737894058228</t>
   </si>
   <si>
-    <t xml:space="preserve">3.73470401763916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.84380841255188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.69274187088013</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.90255665779114</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.95291233062744</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.99067902565002</t>
+    <t xml:space="preserve">3.73470425605774</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.84380793571472</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.69274210929871</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.90255641937256</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.95291209220886</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.99067854881287</t>
   </si>
   <si>
     <t xml:space="preserve">4.00326776504517</t>
   </si>
   <si>
-    <t xml:space="preserve">3.91514539718628</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.87318205833435</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.85220098495483</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.66756367683411</t>
+    <t xml:space="preserve">3.91514563560486</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.87318158149719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.85220122337341</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.66756391525269</t>
   </si>
   <si>
     <t xml:space="preserve">3.6759569644928</t>
   </si>
   <si>
-    <t xml:space="preserve">3.59203100204468</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.53328251838684</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.70532989501953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.64238619804382</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.77666759490967</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.71791958808899</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.64658212661743</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.70113444328308</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.68015265464783</t>
+    <t xml:space="preserve">3.59203052520752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.53328227996826</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.70533037185669</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.6423864364624</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.77666735649109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.71791934967041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.64658236503601</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.7011342048645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.68015313148499</t>
   </si>
   <si>
     <t xml:space="preserve">3.8060417175293</t>
   </si>
   <si>
-    <t xml:space="preserve">3.78506088256836</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.69693803787231</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.73050880432129</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.74729299545288</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.65077877044678</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.65917181968689</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.8563973903656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.8941638469696</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.93612694740295</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.00746393203735</t>
+    <t xml:space="preserve">3.78505992889404</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.69693779945374</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.73050856590271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.74729323387146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.6507785320282</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.65917158126831</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.85639762878418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.89416360855103</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.93612742424011</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.00746440887451</t>
   </si>
   <si>
     <t xml:space="preserve">4.08719348907471</t>
   </si>
   <si>
-    <t xml:space="preserve">4.11237096786499</t>
+    <t xml:space="preserve">4.11237144470215</t>
   </si>
   <si>
     <t xml:space="preserve">4.17111921310425</t>
   </si>
   <si>
-    <t xml:space="preserve">4.19629716873169</t>
+    <t xml:space="preserve">4.19629669189453</t>
   </si>
   <si>
     <t xml:space="preserve">4.2382607460022</t>
@@ -1511,37 +1514,37 @@
     <t xml:space="preserve">4.18790435791016</t>
   </si>
   <si>
-    <t xml:space="preserve">4.09978246688843</t>
+    <t xml:space="preserve">4.09978294372559</t>
   </si>
   <si>
     <t xml:space="preserve">4.09558629989624</t>
   </si>
   <si>
-    <t xml:space="preserve">4.07880115509033</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.14594173431396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.09139060974121</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.08299732208252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.06201648712158</t>
+    <t xml:space="preserve">4.07880067825317</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.14594221115112</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.09138965606689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.08299684524536</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.06201601028442</t>
   </si>
   <si>
     <t xml:space="preserve">4.26343822479248</t>
   </si>
   <si>
-    <t xml:space="preserve">4.39771938323975</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.52360820770264</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.49843072891235</t>
+    <t xml:space="preserve">4.3977198600769</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.52360868453979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.49843120574951</t>
   </si>
   <si>
     <t xml:space="preserve">4.58235645294189</t>
@@ -1553,7 +1556,7 @@
     <t xml:space="preserve">4.6243200302124</t>
   </si>
   <si>
-    <t xml:space="preserve">4.67467546463013</t>
+    <t xml:space="preserve">4.67467594146729</t>
   </si>
   <si>
     <t xml:space="preserve">4.69985294342041</t>
@@ -1571,118 +1574,115 @@
     <t xml:space="preserve">4.44807529449463</t>
   </si>
   <si>
-    <t xml:space="preserve">4.43968200683594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.47325325012207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.49003839492798</t>
+    <t xml:space="preserve">4.43968296051025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.47325229644775</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.49003791809082</t>
   </si>
   <si>
     <t xml:space="preserve">4.54878616333008</t>
   </si>
   <si>
-    <t xml:space="preserve">4.59914255142212</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.61592674255371</t>
+    <t xml:space="preserve">4.59914112091064</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.61592769622803</t>
   </si>
   <si>
     <t xml:space="preserve">4.60753440856934</t>
   </si>
   <si>
-    <t xml:space="preserve">4.40611171722412</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.53200149536133</t>
+    <t xml:space="preserve">4.40611219406128</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.53200101852417</t>
   </si>
   <si>
     <t xml:space="preserve">4.75860118865967</t>
   </si>
   <si>
-    <t xml:space="preserve">4.80895662307739</t>
+    <t xml:space="preserve">4.80895614624023</t>
   </si>
   <si>
     <t xml:space="preserve">4.74181604385376</t>
   </si>
   <si>
-    <t xml:space="preserve">4.69146060943604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.65789079666138</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.50682306289673</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.5403938293457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.46485996246338</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.41450548171997</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.38932704925537</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.38093423843384</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.34736347198486</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.46764707565308</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.5191969871521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.3989143371582</t>
+    <t xml:space="preserve">4.69146013259888</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.65789031982422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.50682353973389</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.54039287567139</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.46486043930054</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.41450452804565</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.38932657241821</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.380934715271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.34736394882202</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.46764612197876</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.51919651031494</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.39891338348389</t>
   </si>
   <si>
     <t xml:space="preserve">4.37313938140869</t>
   </si>
   <si>
-    <t xml:space="preserve">4.30440616607666</t>
+    <t xml:space="preserve">4.3044056892395</t>
   </si>
   <si>
     <t xml:space="preserve">4.27003908157349</t>
   </si>
   <si>
-    <t xml:space="preserve">4.33018064498901</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.31299734115601</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.38173007965088</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.34736442565918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.44187211990356</t>
+    <t xml:space="preserve">4.33018112182617</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.31299781799316</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.38173055648804</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.44187164306641</t>
   </si>
   <si>
     <t xml:space="preserve">4.45905542373657</t>
   </si>
   <si>
-    <t xml:space="preserve">4.35595560073853</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.39032125473022</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.45046281814575</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.41609716415405</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.23137712478638</t>
+    <t xml:space="preserve">4.35595607757568</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.39032220840454</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.45046329498291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.41609668731689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.23137760162354</t>
   </si>
   <si>
     <t xml:space="preserve">4.26574325561523</t>
@@ -1691,46 +1691,46 @@
     <t xml:space="preserve">4.13257360458374</t>
   </si>
   <si>
-    <t xml:space="preserve">4.0466570854187</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.08531951904297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.98222017288208</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.0337700843811</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.94785332679749</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.99081134796143</t>
+    <t xml:space="preserve">4.04665660858154</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.08531904220581</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.98221945762634</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.03376913070679</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.94785356521606</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.99081182479858</t>
   </si>
   <si>
     <t xml:space="preserve">3.98651552200317</t>
   </si>
   <si>
-    <t xml:space="preserve">3.94355750083923</t>
+    <t xml:space="preserve">3.94355773925781</t>
   </si>
   <si>
     <t xml:space="preserve">3.96503615379333</t>
   </si>
   <si>
-    <t xml:space="preserve">3.96074056625366</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.01229047775269</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.9263744354248</t>
+    <t xml:space="preserve">3.96074151992798</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.01229095458984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.92637419700623</t>
   </si>
   <si>
     <t xml:space="preserve">4.07243156433105</t>
   </si>
   <si>
-    <t xml:space="preserve">4.08961534500122</t>
+    <t xml:space="preserve">4.08961582183838</t>
   </si>
   <si>
     <t xml:space="preserve">4.11109399795532</t>
@@ -1739,7 +1739,7 @@
     <t xml:space="preserve">4.26144790649414</t>
   </si>
   <si>
-    <t xml:space="preserve">4.32158851623535</t>
+    <t xml:space="preserve">4.32158946990967</t>
   </si>
   <si>
     <t xml:space="preserve">4.295814037323</t>
@@ -1751,55 +1751,55 @@
     <t xml:space="preserve">3.84045767784119</t>
   </si>
   <si>
-    <t xml:space="preserve">3.87482500076294</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.88771200180054</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.00369882583618</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.02088117599487</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.93496584892273</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.8662326335907</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.77172470092773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.71587896347046</t>
+    <t xml:space="preserve">3.87482452392578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.88771224021912</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.00369834899902</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.02088165283203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.93496561050415</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.86623239517212</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.77172446250916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.71587920188904</t>
   </si>
   <si>
     <t xml:space="preserve">3.70299196243286</t>
   </si>
   <si>
-    <t xml:space="preserve">3.67721748352051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.68580842018127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.70728754997253</t>
+    <t xml:space="preserve">3.67721700668335</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.68580865859985</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.70728778839111</t>
   </si>
   <si>
     <t xml:space="preserve">3.66432952880859</t>
   </si>
   <si>
-    <t xml:space="preserve">3.66003394126892</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.72017526626587</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.81468319892883</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.9521484375</t>
+    <t xml:space="preserve">3.66003370285034</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.72017574310303</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.81468296051025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.95214867591858</t>
   </si>
   <si>
     <t xml:space="preserve">3.85764098167419</t>
@@ -1808,28 +1808,28 @@
     <t xml:space="preserve">3.78461241722107</t>
   </si>
   <si>
-    <t xml:space="preserve">3.8447539806366</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.78031659126282</t>
+    <t xml:space="preserve">3.84475374221802</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.7803168296814</t>
   </si>
   <si>
     <t xml:space="preserve">3.69440054893494</t>
   </si>
   <si>
-    <t xml:space="preserve">3.73306226730347</t>
+    <t xml:space="preserve">3.73306250572205</t>
   </si>
   <si>
     <t xml:space="preserve">3.71158361434937</t>
   </si>
   <si>
-    <t xml:space="preserve">3.59989213943481</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.75454139709473</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.65144205093384</t>
+    <t xml:space="preserve">3.59989237785339</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.75454163551331</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.65144181251526</t>
   </si>
   <si>
     <t xml:space="preserve">3.72447061538696</t>
@@ -1844,55 +1844,55 @@
     <t xml:space="preserve">3.66862487792969</t>
   </si>
   <si>
-    <t xml:space="preserve">3.6729211807251</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.6170756816864</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.57411742210388</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.64285016059875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.65573763847351</t>
+    <t xml:space="preserve">3.67292094230652</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.61707592010498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.5741171836853</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.64284992218018</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.65573787689209</t>
   </si>
   <si>
     <t xml:space="preserve">3.62996292114258</t>
   </si>
   <si>
-    <t xml:space="preserve">3.96933245658875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.95644521713257</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.90059924125671</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.9306697845459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.0165867805481</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.09820699691772</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.14116477966309</t>
+    <t xml:space="preserve">3.96933197975159</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.95644474029541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.90059971809387</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.93067026138306</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.01658630371094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.09820652008057</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.14116525650024</t>
   </si>
   <si>
     <t xml:space="preserve">4.24426460266113</t>
   </si>
   <si>
-    <t xml:space="preserve">4.24856090545654</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.4332799911499</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.4246883392334</t>
+    <t xml:space="preserve">4.24855995178223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.43328046798706</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.42468881607056</t>
   </si>
   <si>
     <t xml:space="preserve">4.58792972564697</t>
@@ -1901,31 +1901,31 @@
     <t xml:space="preserve">4.57933807373047</t>
   </si>
   <si>
-    <t xml:space="preserve">4.49342155456543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.55356311798096</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.48482990264893</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.53638029098511</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.59652137756348</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.7769455909729</t>
+    <t xml:space="preserve">4.49342107772827</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.55356359481812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.48483037948608</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.53637981414795</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.59652090072632</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.77694511413574</t>
   </si>
   <si>
     <t xml:space="preserve">4.81131172180176</t>
   </si>
   <si>
-    <t xml:space="preserve">4.69962072372437</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.64807081222534</t>
+    <t xml:space="preserve">4.69961977005005</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.64807033538818</t>
   </si>
   <si>
     <t xml:space="preserve">4.72539520263672</t>
@@ -1934,40 +1934,40 @@
     <t xml:space="preserve">4.71680402755737</t>
   </si>
   <si>
-    <t xml:space="preserve">4.6910285949707</t>
+    <t xml:space="preserve">4.69102907180786</t>
   </si>
   <si>
     <t xml:space="preserve">4.6824369430542</t>
   </si>
   <si>
-    <t xml:space="preserve">4.70821285247803</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.67384624481201</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.5621542930603</t>
+    <t xml:space="preserve">4.70821189880371</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.67384576797485</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.56215476989746</t>
   </si>
   <si>
     <t xml:space="preserve">4.50201320648193</t>
   </si>
   <si>
-    <t xml:space="preserve">4.54497098922729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.51060438156128</t>
+    <t xml:space="preserve">4.54497194290161</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.51060485839844</t>
   </si>
   <si>
     <t xml:space="preserve">4.5277886390686</t>
   </si>
   <si>
-    <t xml:space="preserve">4.76835441589355</t>
+    <t xml:space="preserve">4.7683539390564</t>
   </si>
   <si>
     <t xml:space="preserve">4.66525411605835</t>
   </si>
   <si>
-    <t xml:space="preserve">4.61370420455933</t>
+    <t xml:space="preserve">4.61370468139648</t>
   </si>
   <si>
     <t xml:space="preserve">4.73398780822754</t>
@@ -1976,7 +1976,7 @@
     <t xml:space="preserve">4.639479637146</t>
   </si>
   <si>
-    <t xml:space="preserve">4.23567295074463</t>
+    <t xml:space="preserve">4.23567199707031</t>
   </si>
   <si>
     <t xml:space="preserve">4.15834856033325</t>
@@ -1994,28 +1994,28 @@
     <t xml:space="preserve">4.11538982391357</t>
   </si>
   <si>
-    <t xml:space="preserve">3.7502453327179</t>
+    <t xml:space="preserve">3.75024557113647</t>
   </si>
   <si>
     <t xml:space="preserve">3.47101783752441</t>
   </si>
   <si>
-    <t xml:space="preserve">3.36362218856812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.31207275390625</t>
+    <t xml:space="preserve">3.36362242698669</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.31207299232483</t>
   </si>
   <si>
     <t xml:space="preserve">3.16601490974426</t>
   </si>
   <si>
-    <t xml:space="preserve">3.22186040878296</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.80516672134399</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.91685771942139</t>
+    <t xml:space="preserve">3.22186088562012</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.80516695976257</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.91685795783997</t>
   </si>
   <si>
     <t xml:space="preserve">2.86530804634094</t>
@@ -2027,25 +2027,25 @@
     <t xml:space="preserve">2.73213791847229</t>
   </si>
   <si>
-    <t xml:space="preserve">2.66770076751709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.80087065696716</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.61185479164124</t>
+    <t xml:space="preserve">2.66770052909851</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.80087089538574</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.61185503005981</t>
   </si>
   <si>
     <t xml:space="preserve">2.72354626655579</t>
   </si>
   <si>
-    <t xml:space="preserve">2.92115354537964</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.8137583732605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.70206713676453</t>
+    <t xml:space="preserve">2.92115378379822</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.81375861167908</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.70206689834595</t>
   </si>
   <si>
     <t xml:space="preserve">2.65910911560059</t>
@@ -2063,67 +2063,67 @@
     <t xml:space="preserve">2.70636320114136</t>
   </si>
   <si>
-    <t xml:space="preserve">2.71065855026245</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.85242080688477</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.89108300209045</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.92974495887756</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.0070698261261</t>
+    <t xml:space="preserve">2.71065878868103</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.85242033004761</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.89108324050903</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.92974543571472</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.00707006454468</t>
   </si>
   <si>
     <t xml:space="preserve">2.96411156654358</t>
   </si>
   <si>
-    <t xml:space="preserve">2.93833708763123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.9426326751709</t>
+    <t xml:space="preserve">2.93833684921265</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.94263243675232</t>
   </si>
   <si>
     <t xml:space="preserve">2.98129487037659</t>
   </si>
   <si>
-    <t xml:space="preserve">3.01136589050293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.94692850112915</t>
+    <t xml:space="preserve">3.01136612892151</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.94692873954773</t>
   </si>
   <si>
     <t xml:space="preserve">2.97699928283691</t>
   </si>
   <si>
-    <t xml:space="preserve">2.95122408866882</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.10587358474731</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.04143643379211</t>
+    <t xml:space="preserve">2.9512243270874</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.10587382316589</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.04143667221069</t>
   </si>
   <si>
     <t xml:space="preserve">3.05002784729004</t>
   </si>
   <si>
-    <t xml:space="preserve">3.08439445495605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.13164830207825</t>
+    <t xml:space="preserve">3.08439421653748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.13164854049683</t>
   </si>
   <si>
     <t xml:space="preserve">3.03284502029419</t>
   </si>
   <si>
-    <t xml:space="preserve">3.09298634529114</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.19178986549377</t>
+    <t xml:space="preserve">3.09298610687256</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.1917896270752</t>
   </si>
   <si>
     <t xml:space="preserve">3.24763560295105</t>
@@ -2132,13 +2132,13 @@
     <t xml:space="preserve">3.16171932220459</t>
   </si>
   <si>
-    <t xml:space="preserve">3.14883160591125</t>
+    <t xml:space="preserve">3.14883184432983</t>
   </si>
   <si>
     <t xml:space="preserve">3.18319845199585</t>
   </si>
   <si>
-    <t xml:space="preserve">3.13594460487366</t>
+    <t xml:space="preserve">3.13594436645508</t>
   </si>
   <si>
     <t xml:space="preserve">3.11876130104065</t>
@@ -2150,13 +2150,13 @@
     <t xml:space="preserve">3.38510155677795</t>
   </si>
   <si>
-    <t xml:space="preserve">3.43665146827698</t>
+    <t xml:space="preserve">3.4366512298584</t>
   </si>
   <si>
     <t xml:space="preserve">3.48390507698059</t>
   </si>
   <si>
-    <t xml:space="preserve">3.46242642402649</t>
+    <t xml:space="preserve">3.46242618560791</t>
   </si>
   <si>
     <t xml:space="preserve">3.47960948944092</t>
@@ -2168,46 +2168,46 @@
     <t xml:space="preserve">3.29488945007324</t>
   </si>
   <si>
-    <t xml:space="preserve">3.19608569145203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.38080549240112</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.37651014328003</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.35073518753052</t>
+    <t xml:space="preserve">3.19608592987061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.3808057308197</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.37650966644287</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.35073494911194</t>
   </si>
   <si>
     <t xml:space="preserve">3.3722140789032</t>
   </si>
   <si>
-    <t xml:space="preserve">3.42806005477905</t>
+    <t xml:space="preserve">3.42805981636047</t>
   </si>
   <si>
     <t xml:space="preserve">3.44094729423523</t>
   </si>
   <si>
-    <t xml:space="preserve">3.44524312019348</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.75857472419739</t>
+    <t xml:space="preserve">3.44524335861206</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.75857448577881</t>
   </si>
   <si>
     <t xml:space="preserve">3.71435570716858</t>
   </si>
   <si>
-    <t xml:space="preserve">3.63034105300903</t>
+    <t xml:space="preserve">3.63034081459045</t>
   </si>
   <si>
     <t xml:space="preserve">3.58170080184937</t>
   </si>
   <si>
-    <t xml:space="preserve">3.51979470252991</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.50210738182068</t>
+    <t xml:space="preserve">3.51979494094849</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.5021071434021</t>
   </si>
   <si>
     <t xml:space="preserve">3.43135762214661</t>
@@ -2216,7 +2216,7 @@
     <t xml:space="preserve">3.44904518127441</t>
   </si>
   <si>
-    <t xml:space="preserve">3.36060786247253</t>
+    <t xml:space="preserve">3.36060762405396</t>
   </si>
   <si>
     <t xml:space="preserve">3.38713908195496</t>
@@ -2231,7 +2231,7 @@
     <t xml:space="preserve">3.33849883079529</t>
   </si>
   <si>
-    <t xml:space="preserve">3.31638932228088</t>
+    <t xml:space="preserve">3.31638956069946</t>
   </si>
   <si>
     <t xml:space="preserve">3.27217102050781</t>
@@ -2243,16 +2243,16 @@
     <t xml:space="preserve">3.22795248031616</t>
   </si>
   <si>
-    <t xml:space="preserve">3.09529662132263</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.18373394012451</t>
+    <t xml:space="preserve">3.09529685974121</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.18373370170593</t>
   </si>
   <si>
     <t xml:space="preserve">3.25448369979858</t>
   </si>
   <si>
-    <t xml:space="preserve">3.20584297180176</t>
+    <t xml:space="preserve">3.20584321022034</t>
   </si>
   <si>
     <t xml:space="preserve">3.1660463809967</t>
@@ -2264,7 +2264,7 @@
     <t xml:space="preserve">3.13951516151428</t>
   </si>
   <si>
-    <t xml:space="preserve">3.10414052009583</t>
+    <t xml:space="preserve">3.1041407585144</t>
   </si>
   <si>
     <t xml:space="preserve">3.09971904754639</t>
@@ -2276,34 +2276,34 @@
     <t xml:space="preserve">3.04665637016296</t>
   </si>
   <si>
-    <t xml:space="preserve">3.07760953903198</t>
+    <t xml:space="preserve">3.0776093006134</t>
   </si>
   <si>
     <t xml:space="preserve">3.05992197990417</t>
   </si>
   <si>
-    <t xml:space="preserve">2.98032832145691</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.96264123916626</t>
+    <t xml:space="preserve">2.98032879829407</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.96264100074768</t>
   </si>
   <si>
     <t xml:space="preserve">2.94495368003845</t>
   </si>
   <si>
-    <t xml:space="preserve">2.93611025810242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.09087514877319</t>
+    <t xml:space="preserve">2.93611001968384</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.09087491035461</t>
   </si>
   <si>
     <t xml:space="preserve">3.06876564025879</t>
   </si>
   <si>
-    <t xml:space="preserve">3.05550026893616</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.98475027084351</t>
+    <t xml:space="preserve">3.05550003051758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.98475050926208</t>
   </si>
   <si>
     <t xml:space="preserve">2.9051570892334</t>
@@ -2324,7 +2324,7 @@
     <t xml:space="preserve">2.81229829788208</t>
   </si>
   <si>
-    <t xml:space="preserve">2.84767317771912</t>
+    <t xml:space="preserve">2.84767293930054</t>
   </si>
   <si>
     <t xml:space="preserve">2.82998585700989</t>
@@ -2345,7 +2345,7 @@
     <t xml:space="preserve">2.80787658691406</t>
   </si>
   <si>
-    <t xml:space="preserve">2.75923562049866</t>
+    <t xml:space="preserve">2.75923609733582</t>
   </si>
   <si>
     <t xml:space="preserve">2.7238609790802</t>
@@ -2357,7 +2357,7 @@
     <t xml:space="preserve">2.6840648651123</t>
   </si>
   <si>
-    <t xml:space="preserve">2.63542413711548</t>
+    <t xml:space="preserve">2.6354238986969</t>
   </si>
   <si>
     <t xml:space="preserve">2.61773705482483</t>
@@ -2381,13 +2381,13 @@
     <t xml:space="preserve">2.5735182762146</t>
   </si>
   <si>
-    <t xml:space="preserve">2.97148466110229</t>
+    <t xml:space="preserve">2.97148489952087</t>
   </si>
   <si>
     <t xml:space="preserve">2.95379757881165</t>
   </si>
   <si>
-    <t xml:space="preserve">3.00243782997131</t>
+    <t xml:space="preserve">3.00243806838989</t>
   </si>
   <si>
     <t xml:space="preserve">3.17931199073792</t>
@@ -2402,7 +2402,7 @@
     <t xml:space="preserve">3.28985834121704</t>
   </si>
   <si>
-    <t xml:space="preserve">3.29870200157166</t>
+    <t xml:space="preserve">3.29870223999023</t>
   </si>
   <si>
     <t xml:space="preserve">3.47999787330627</t>
@@ -2420,10 +2420,10 @@
     <t xml:space="preserve">3.49326372146606</t>
   </si>
   <si>
-    <t xml:space="preserve">3.51095104217529</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.44462299346924</t>
+    <t xml:space="preserve">3.51095080375671</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.44462323188782</t>
   </si>
   <si>
     <t xml:space="preserve">3.42693591117859</t>
@@ -2438,25 +2438,25 @@
     <t xml:space="preserve">3.72320008277893</t>
   </si>
   <si>
-    <t xml:space="preserve">3.74973082542419</t>
+    <t xml:space="preserve">3.74973058700562</t>
   </si>
   <si>
     <t xml:space="preserve">3.80279350280762</t>
   </si>
   <si>
-    <t xml:space="preserve">3.65687251091003</t>
+    <t xml:space="preserve">3.65687203407288</t>
   </si>
   <si>
     <t xml:space="preserve">3.66129374504089</t>
   </si>
   <si>
-    <t xml:space="preserve">3.65245032310486</t>
+    <t xml:space="preserve">3.65245056152344</t>
   </si>
   <si>
     <t xml:space="preserve">3.62591910362244</t>
   </si>
   <si>
-    <t xml:space="preserve">3.60823130607605</t>
+    <t xml:space="preserve">3.60823154449463</t>
   </si>
   <si>
     <t xml:space="preserve">3.54632616043091</t>
@@ -2468,7 +2468,7 @@
     <t xml:space="preserve">3.57285690307617</t>
   </si>
   <si>
-    <t xml:space="preserve">3.5065290927887</t>
+    <t xml:space="preserve">3.50652885437012</t>
   </si>
   <si>
     <t xml:space="preserve">3.5905442237854</t>
@@ -2477,13 +2477,13 @@
     <t xml:space="preserve">3.57727885246277</t>
   </si>
   <si>
-    <t xml:space="preserve">3.74530911445618</t>
+    <t xml:space="preserve">3.7453088760376</t>
   </si>
   <si>
     <t xml:space="preserve">3.74088740348816</t>
   </si>
   <si>
-    <t xml:space="preserve">3.73204350471497</t>
+    <t xml:space="preserve">3.73204326629639</t>
   </si>
   <si>
     <t xml:space="preserve">3.70551252365112</t>
@@ -2492,25 +2492,25 @@
     <t xml:space="preserve">3.77626180648804</t>
   </si>
   <si>
-    <t xml:space="preserve">3.83816814422607</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.68340349197388</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.76741862297058</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.78068399429321</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.76299643516541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.7718403339386</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.71877813339233</t>
+    <t xml:space="preserve">3.83816862106323</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.6834032535553</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.767418384552</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.78068375587463</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.76299667358398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.77184009552002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.71877789497375</t>
   </si>
   <si>
     <t xml:space="preserve">3.68782496452332</t>
@@ -2519,43 +2519,43 @@
     <t xml:space="preserve">3.61707544326782</t>
   </si>
   <si>
-    <t xml:space="preserve">3.59938836097717</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.66571593284607</t>
+    <t xml:space="preserve">3.59938812255859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.66571617126465</t>
   </si>
   <si>
     <t xml:space="preserve">3.7099347114563</t>
   </si>
   <si>
-    <t xml:space="preserve">3.78510642051697</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.92660546302795</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.93987083435059</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.99735474586487</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.01079893112183</t>
+    <t xml:space="preserve">3.78510618209839</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.9266049861908</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.93987035751343</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.99735450744629</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.01079845428467</t>
   </si>
   <si>
     <t xml:space="preserve">4.09594440460205</t>
   </si>
   <si>
-    <t xml:space="preserve">4.17212772369385</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.16316413879395</t>
+    <t xml:space="preserve">4.17212724685669</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.1631646156311</t>
   </si>
   <si>
     <t xml:space="preserve">4.13627576828003</t>
   </si>
   <si>
-    <t xml:space="preserve">4.19901514053345</t>
+    <t xml:space="preserve">4.19901466369629</t>
   </si>
   <si>
     <t xml:space="preserve">4.14075756072998</t>
@@ -2564,22 +2564,22 @@
     <t xml:space="preserve">4.10490655899048</t>
   </si>
   <si>
-    <t xml:space="preserve">4.06905603408813</t>
+    <t xml:space="preserve">4.06905651092529</t>
   </si>
   <si>
     <t xml:space="preserve">4.03320503234863</t>
   </si>
   <si>
-    <t xml:space="preserve">3.9794294834137</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.028724193573</t>
+    <t xml:space="preserve">3.97942924499512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.02872371673584</t>
   </si>
   <si>
     <t xml:space="preserve">4.05561256408691</t>
   </si>
   <si>
-    <t xml:space="preserve">4.08698129653931</t>
+    <t xml:space="preserve">4.08698177337646</t>
   </si>
   <si>
     <t xml:space="preserve">3.97494792938232</t>
@@ -2597,13 +2597,13 @@
     <t xml:space="preserve">3.98839139938354</t>
   </si>
   <si>
-    <t xml:space="preserve">3.95254158973694</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.96598553657532</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.04216861724854</t>
+    <t xml:space="preserve">3.95254135131836</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.96598529815674</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.04216814041138</t>
   </si>
   <si>
     <t xml:space="preserve">4.07801914215088</t>
@@ -2621,13 +2621,13 @@
     <t xml:space="preserve">4.10938835144043</t>
   </si>
   <si>
-    <t xml:space="preserve">4.06009292602539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.19453287124634</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.21245908737183</t>
+    <t xml:space="preserve">4.06009340286255</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.1945333480835</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.21245861053467</t>
   </si>
   <si>
     <t xml:space="preserve">4.14972019195557</t>
@@ -2648,7 +2648,7 @@
     <t xml:space="preserve">4.20797777175903</t>
   </si>
   <si>
-    <t xml:space="preserve">4.230384349823</t>
+    <t xml:space="preserve">4.23038387298584</t>
   </si>
   <si>
     <t xml:space="preserve">4.25727224349976</t>
@@ -2657,19 +2657,19 @@
     <t xml:space="preserve">4.20349645614624</t>
   </si>
   <si>
-    <t xml:space="preserve">3.92565369606018</t>
+    <t xml:space="preserve">3.9256534576416</t>
   </si>
   <si>
     <t xml:space="preserve">3.90772819519043</t>
   </si>
   <si>
-    <t xml:space="preserve">3.88084006309509</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.87635827064514</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.80913829803467</t>
+    <t xml:space="preserve">3.88084030151367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.87635850906372</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.80913805961609</t>
   </si>
   <si>
     <t xml:space="preserve">3.71503043174744</t>
@@ -2678,37 +2678,37 @@
     <t xml:space="preserve">3.66573548316956</t>
   </si>
   <si>
-    <t xml:space="preserve">3.83154535293579</t>
+    <t xml:space="preserve">3.83154487609863</t>
   </si>
   <si>
     <t xml:space="preserve">3.93461561203003</t>
   </si>
   <si>
-    <t xml:space="preserve">3.94357848167419</t>
+    <t xml:space="preserve">3.94357872009277</t>
   </si>
   <si>
     <t xml:space="preserve">4.04664897918701</t>
   </si>
   <si>
-    <t xml:space="preserve">3.99287343025208</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.98391127586365</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.02424287796021</t>
+    <t xml:space="preserve">3.9928731918335</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.98391103744507</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.02424240112305</t>
   </si>
   <si>
     <t xml:space="preserve">3.85395193099976</t>
   </si>
   <si>
-    <t xml:space="preserve">3.93013453483582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.97046685218811</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.10042524337769</t>
+    <t xml:space="preserve">3.93013477325439</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.97046661376953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.10042572021484</t>
   </si>
   <si>
     <t xml:space="preserve">4.15420150756836</t>
@@ -2720,19 +2720,19 @@
     <t xml:space="preserve">4.22590303421021</t>
   </si>
   <si>
-    <t xml:space="preserve">4.26623582839966</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.24382877349854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.13179492950439</t>
+    <t xml:space="preserve">4.2662353515625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.24382829666138</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.13179540634155</t>
   </si>
   <si>
     <t xml:space="preserve">4.1273136138916</t>
   </si>
   <si>
-    <t xml:space="preserve">4.24830913543701</t>
+    <t xml:space="preserve">4.24830961227417</t>
   </si>
   <si>
     <t xml:space="preserve">4.19005250930786</t>
@@ -2744,7 +2744,7 @@
     <t xml:space="preserve">4.40515661239624</t>
   </si>
   <si>
-    <t xml:space="preserve">4.43652534484863</t>
+    <t xml:space="preserve">4.43652582168579</t>
   </si>
   <si>
     <t xml:space="preserve">4.48133897781372</t>
@@ -2753,28 +2753,28 @@
     <t xml:space="preserve">4.53511571884155</t>
   </si>
   <si>
-    <t xml:space="preserve">4.55304050445557</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.56200361251831</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.50822687149048</t>
+    <t xml:space="preserve">4.55304098129272</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.56200408935547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.50822782516479</t>
   </si>
   <si>
     <t xml:space="preserve">4.45445108413696</t>
   </si>
   <si>
-    <t xml:space="preserve">4.43204498291016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.49926471710205</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.49030256271362</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.51718997955322</t>
+    <t xml:space="preserve">4.432044506073</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.49926519393921</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.49030208587646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.51719045639038</t>
   </si>
   <si>
     <t xml:space="preserve">4.63370513916016</t>
@@ -2786,13 +2786,13 @@
     <t xml:space="preserve">4.47685766220093</t>
   </si>
   <si>
-    <t xml:space="preserve">4.57096576690674</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.61577939987183</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.64266681671143</t>
+    <t xml:space="preserve">4.5709662437439</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.61577987670898</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.64266729354858</t>
   </si>
   <si>
     <t xml:space="preserve">4.39171266555786</t>
@@ -2801,13 +2801,13 @@
     <t xml:space="preserve">4.44996976852417</t>
   </si>
   <si>
-    <t xml:space="preserve">4.27519750595093</t>
+    <t xml:space="preserve">4.27519798278809</t>
   </si>
   <si>
     <t xml:space="preserve">4.58889150619507</t>
   </si>
   <si>
-    <t xml:space="preserve">4.66059303283691</t>
+    <t xml:space="preserve">4.66059255599976</t>
   </si>
   <si>
     <t xml:space="preserve">4.65163040161133</t>
@@ -2816,10 +2816,10 @@
     <t xml:space="preserve">4.71436929702759</t>
   </si>
   <si>
-    <t xml:space="preserve">4.75918197631836</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.7681450843811</t>
+    <t xml:space="preserve">4.75918245315552</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.76814556121826</t>
   </si>
   <si>
     <t xml:space="preserve">4.89362239837646</t>
@@ -2828,31 +2828,31 @@
     <t xml:space="preserve">4.92051076889038</t>
   </si>
   <si>
-    <t xml:space="preserve">4.88465929031372</t>
+    <t xml:space="preserve">4.88465976715088</t>
   </si>
   <si>
     <t xml:space="preserve">5.05495071411133</t>
   </si>
   <si>
-    <t xml:space="preserve">5.01909971237183</t>
+    <t xml:space="preserve">5.01910018920898</t>
   </si>
   <si>
     <t xml:space="preserve">5.14457702636719</t>
   </si>
   <si>
-    <t xml:space="preserve">5.31486845016479</t>
+    <t xml:space="preserve">5.31486797332764</t>
   </si>
   <si>
     <t xml:space="preserve">5.37760734558105</t>
   </si>
   <si>
-    <t xml:space="preserve">5.35968208312988</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.16250324249268</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.04598808288574</t>
+    <t xml:space="preserve">5.35968160629272</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.16250276565552</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.0459885597229</t>
   </si>
   <si>
     <t xml:space="preserve">5.15354013442993</t>
@@ -2864,16 +2864,16 @@
     <t xml:space="preserve">5.27901697158813</t>
   </si>
   <si>
-    <t xml:space="preserve">5.51204776763916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.4761962890625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.50308465957642</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.29694318771362</t>
+    <t xml:space="preserve">5.512047290802</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.47619676589966</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.50308418273926</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.29694271087646</t>
   </si>
   <si>
     <t xml:space="preserve">5.19835376739502</t>
@@ -2882,19 +2882,19 @@
     <t xml:space="preserve">5.18042850494385</t>
   </si>
   <si>
-    <t xml:space="preserve">5.07287549972534</t>
+    <t xml:space="preserve">5.0728759765625</t>
   </si>
   <si>
     <t xml:space="preserve">5.09080123901367</t>
   </si>
   <si>
-    <t xml:space="preserve">4.99221229553223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.75021982192993</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.80399560928345</t>
+    <t xml:space="preserve">4.99221277236938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.75022029876709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.80399608612061</t>
   </si>
   <si>
     <t xml:space="preserve">4.92947340011597</t>
@@ -2912,16 +2912,16 @@
     <t xml:space="preserve">4.86673450469971</t>
   </si>
   <si>
-    <t xml:space="preserve">5.03702592849731</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.95636129379272</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.79503345489502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.74125719070435</t>
+    <t xml:space="preserve">5.03702545166016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.95636177062988</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.79503297805786</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.7412576675415</t>
   </si>
   <si>
     <t xml:space="preserve">4.70540618896484</t>
@@ -2930,22 +2930,22 @@
     <t xml:space="preserve">4.52615308761597</t>
   </si>
   <si>
-    <t xml:space="preserve">4.41860055923462</t>
+    <t xml:space="preserve">4.41860008239746</t>
   </si>
   <si>
     <t xml:space="preserve">4.36482429504395</t>
   </si>
   <si>
-    <t xml:space="preserve">4.23934698104858</t>
+    <t xml:space="preserve">4.23934650421143</t>
   </si>
   <si>
     <t xml:space="preserve">4.85777187347412</t>
   </si>
   <si>
-    <t xml:space="preserve">4.91154813766479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.96532392501831</t>
+    <t xml:space="preserve">4.91154766082764</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.96532440185547</t>
   </si>
   <si>
     <t xml:space="preserve">5.11768960952759</t>
@@ -2960,13 +2960,13 @@
     <t xml:space="preserve">5.42242097854614</t>
   </si>
   <si>
-    <t xml:space="preserve">5.28798007965088</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.43138360977173</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.55686092376709</t>
+    <t xml:space="preserve">5.28798055648804</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.43138313293457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.55686044692993</t>
   </si>
   <si>
     <t xml:space="preserve">5.62856245040894</t>
@@ -2975,7 +2975,7 @@
     <t xml:space="preserve">5.52100944519043</t>
   </si>
   <si>
-    <t xml:space="preserve">5.61959981918335</t>
+    <t xml:space="preserve">5.61959934234619</t>
   </si>
   <si>
     <t xml:space="preserve">5.53893518447876</t>
@@ -2984,7 +2984,7 @@
     <t xml:space="preserve">5.37441253662109</t>
   </si>
   <si>
-    <t xml:space="preserve">5.47495365142822</t>
+    <t xml:space="preserve">5.47495412826538</t>
   </si>
   <si>
     <t xml:space="preserve">5.46581411361694</t>
@@ -2993,7 +2993,7 @@
     <t xml:space="preserve">5.48409461975098</t>
   </si>
   <si>
-    <t xml:space="preserve">5.63947725296021</t>
+    <t xml:space="preserve">5.63947677612305</t>
   </si>
   <si>
     <t xml:space="preserve">5.75829935073853</t>
@@ -3008,10 +3008,10 @@
     <t xml:space="preserve">5.62119674682617</t>
   </si>
   <si>
-    <t xml:space="preserve">5.41097354888916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.40183305740356</t>
+    <t xml:space="preserve">5.410973072052</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.40183258056641</t>
   </si>
   <si>
     <t xml:space="preserve">5.63033676147461</t>
@@ -3026,7 +3026,7 @@
     <t xml:space="preserve">5.84056043624878</t>
   </si>
   <si>
-    <t xml:space="preserve">5.88626146316528</t>
+    <t xml:space="preserve">5.88626098632812</t>
   </si>
   <si>
     <t xml:space="preserve">5.93196201324463</t>
@@ -3038,22 +3038,22 @@
     <t xml:space="preserve">5.97766304016113</t>
   </si>
   <si>
-    <t xml:space="preserve">5.95938205718994</t>
+    <t xml:space="preserve">5.9593825340271</t>
   </si>
   <si>
     <t xml:space="preserve">6.04164409637451</t>
   </si>
   <si>
-    <t xml:space="preserve">5.87712144851685</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.07820510864258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.9136815071106</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.68517780303955</t>
+    <t xml:space="preserve">5.87712097167969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.07820463180542</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.91368103027344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.68517732620239</t>
   </si>
   <si>
     <t xml:space="preserve">5.785719871521</t>
@@ -3062,10 +3062,10 @@
     <t xml:space="preserve">5.7308783531189</t>
   </si>
   <si>
-    <t xml:space="preserve">5.67603778839111</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.69431829452515</t>
+    <t xml:space="preserve">5.67603731155396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.69431781768799</t>
   </si>
   <si>
     <t xml:space="preserve">5.66689729690552</t>
@@ -3077,10 +3077,10 @@
     <t xml:space="preserve">5.42011308670044</t>
   </si>
   <si>
-    <t xml:space="preserve">5.33785152435303</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.20988988876343</t>
+    <t xml:space="preserve">5.33785200119019</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.20988941192627</t>
   </si>
   <si>
     <t xml:space="preserve">5.34699201583862</t>
@@ -3095,13 +3095,13 @@
     <t xml:space="preserve">5.36527252197266</t>
   </si>
   <si>
-    <t xml:space="preserve">5.28301095962524</t>
+    <t xml:space="preserve">5.2830114364624</t>
   </si>
   <si>
     <t xml:space="preserve">5.2281699180603</t>
   </si>
   <si>
-    <t xml:space="preserve">5.21902990341187</t>
+    <t xml:space="preserve">5.21902942657471</t>
   </si>
   <si>
     <t xml:space="preserve">5.15504837036133</t>
@@ -3131,16 +3131,16 @@
     <t xml:space="preserve">5.07278776168823</t>
   </si>
   <si>
-    <t xml:space="preserve">5.02708673477173</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.0453667640686</t>
+    <t xml:space="preserve">5.02708625793457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.04536724090576</t>
   </si>
   <si>
     <t xml:space="preserve">4.99052572250366</t>
   </si>
   <si>
-    <t xml:space="preserve">5.0088062286377</t>
+    <t xml:space="preserve">5.00880575180054</t>
   </si>
   <si>
     <t xml:space="preserve">5.0545072555542</t>
@@ -3149,10 +3149,10 @@
     <t xml:space="preserve">5.44753360748291</t>
   </si>
   <si>
-    <t xml:space="preserve">5.16418933868408</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.14590835571289</t>
+    <t xml:space="preserve">5.16418886184692</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.14590883255005</t>
   </si>
   <si>
     <t xml:space="preserve">4.94482469558716</t>
@@ -3167,13 +3167,13 @@
     <t xml:space="preserve">4.8808445930481</t>
   </si>
   <si>
-    <t xml:space="preserve">4.85342311859131</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.826003074646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.73460149765015</t>
+    <t xml:space="preserve">4.85342359542847</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.82600355148315</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.73460102081299</t>
   </si>
   <si>
     <t xml:space="preserve">4.75288152694702</t>
@@ -3182,7 +3182,7 @@
     <t xml:space="preserve">4.69804096221924</t>
   </si>
   <si>
-    <t xml:space="preserve">4.57921934127808</t>
+    <t xml:space="preserve">4.57921886444092</t>
   </si>
   <si>
     <t xml:space="preserve">4.71632099151611</t>
@@ -3194,7 +3194,7 @@
     <t xml:space="preserve">4.84428358078003</t>
   </si>
   <si>
-    <t xml:space="preserve">4.80772256851196</t>
+    <t xml:space="preserve">4.80772304534912</t>
   </si>
   <si>
     <t xml:space="preserve">4.57007837295532</t>
@@ -3203,7 +3203,7 @@
     <t xml:space="preserve">4.72546148300171</t>
   </si>
   <si>
-    <t xml:space="preserve">4.6889009475708</t>
+    <t xml:space="preserve">4.68890047073364</t>
   </si>
   <si>
     <t xml:space="preserve">4.67062044143677</t>
@@ -3218,10 +3218,10 @@
     <t xml:space="preserve">4.56093835830688</t>
   </si>
   <si>
-    <t xml:space="preserve">4.58835887908936</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.55179834365845</t>
+    <t xml:space="preserve">4.58835935592651</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.55179786682129</t>
   </si>
   <si>
     <t xml:space="preserve">4.48781728744507</t>
@@ -3236,7 +3236,7 @@
     <t xml:space="preserve">4.50152778625488</t>
   </si>
   <si>
-    <t xml:space="preserve">4.49695777893066</t>
+    <t xml:space="preserve">4.49695730209351</t>
   </si>
   <si>
     <t xml:space="preserve">4.40555620193481</t>
@@ -3245,7 +3245,7 @@
     <t xml:space="preserve">4.43297624588013</t>
   </si>
   <si>
-    <t xml:space="preserve">4.45582723617554</t>
+    <t xml:space="preserve">4.45582675933838</t>
   </si>
   <si>
     <t xml:space="preserve">4.36899518966675</t>
@@ -3281,10 +3281,10 @@
     <t xml:space="preserve">5.19160890579224</t>
   </si>
   <si>
-    <t xml:space="preserve">5.25559043884277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.38355207443237</t>
+    <t xml:space="preserve">5.25559091567993</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.38355255126953</t>
   </si>
   <si>
     <t xml:space="preserve">4.97224569320679</t>
@@ -3305,10 +3305,10 @@
     <t xml:space="preserve">5.09106779098511</t>
   </si>
   <si>
-    <t xml:space="preserve">4.98138570785522</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.92654514312744</t>
+    <t xml:space="preserve">4.98138523101807</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.92654466629028</t>
   </si>
   <si>
     <t xml:space="preserve">5.06364727020264</t>
@@ -3332,7 +3332,7 @@
     <t xml:space="preserve">5.31957197189331</t>
   </si>
   <si>
-    <t xml:space="preserve">5.27241277694702</t>
+    <t xml:space="preserve">5.27241230010986</t>
   </si>
   <si>
     <t xml:space="preserve">5.23468494415283</t>
@@ -3344,13 +3344,13 @@
     <t xml:space="preserve">5.02718353271484</t>
   </si>
   <si>
-    <t xml:space="preserve">4.99888849258423</t>
+    <t xml:space="preserve">4.99888801574707</t>
   </si>
   <si>
     <t xml:space="preserve">5.01775217056274</t>
   </si>
   <si>
-    <t xml:space="preserve">5.16866207122803</t>
+    <t xml:space="preserve">5.16866159439087</t>
   </si>
   <si>
     <t xml:space="preserve">5.1403660774231</t>
@@ -3380,10 +3380,10 @@
     <t xml:space="preserve">5.26298046112061</t>
   </si>
   <si>
-    <t xml:space="preserve">5.37616300582886</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.17809295654297</t>
+    <t xml:space="preserve">5.3761625289917</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.17809343338013</t>
   </si>
   <si>
     <t xml:space="preserve">5.21582126617432</t>
@@ -3392,7 +3392,7 @@
     <t xml:space="preserve">5.10263824462891</t>
   </si>
   <si>
-    <t xml:space="preserve">5.14979839324951</t>
+    <t xml:space="preserve">5.14979791641235</t>
   </si>
   <si>
     <t xml:space="preserve">5.09320688247681</t>
@@ -3407,7 +3407,7 @@
     <t xml:space="preserve">5.03661584854126</t>
   </si>
   <si>
-    <t xml:space="preserve">5.06491136550903</t>
+    <t xml:space="preserve">5.06491088867188</t>
   </si>
   <si>
     <t xml:space="preserve">4.95172882080078</t>
@@ -3422,7 +3422,7 @@
     <t xml:space="preserve">4.91400146484375</t>
   </si>
   <si>
-    <t xml:space="preserve">4.90456914901733</t>
+    <t xml:space="preserve">4.90456962585449</t>
   </si>
   <si>
     <t xml:space="preserve">4.77252340316772</t>
@@ -3434,16 +3434,16 @@
     <t xml:space="preserve">4.72536420822144</t>
   </si>
   <si>
-    <t xml:space="preserve">4.9611611366272</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.8574104309082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.8008189201355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.51786327362061</t>
+    <t xml:space="preserve">4.96116065979004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.85740995407104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.80081939697266</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.51786279678345</t>
   </si>
   <si>
     <t xml:space="preserve">4.50843143463135</t>
@@ -3455,7 +3455,7 @@
     <t xml:space="preserve">4.54615879058838</t>
   </si>
   <si>
-    <t xml:space="preserve">4.6216139793396</t>
+    <t xml:space="preserve">4.62161350250244</t>
   </si>
   <si>
     <t xml:space="preserve">4.54144287109375</t>
@@ -3470,7 +3470,7 @@
     <t xml:space="preserve">4.56030654907227</t>
   </si>
   <si>
-    <t xml:space="preserve">4.47541952133179</t>
+    <t xml:space="preserve">4.47541999816895</t>
   </si>
   <si>
     <t xml:space="preserve">4.47070360183716</t>
@@ -3488,7 +3488,7 @@
     <t xml:space="preserve">4.50371503829956</t>
   </si>
   <si>
-    <t xml:space="preserve">4.51314687728882</t>
+    <t xml:space="preserve">4.51314735412598</t>
   </si>
   <si>
     <t xml:space="preserve">4.63576126098633</t>
@@ -3497,13 +3497,13 @@
     <t xml:space="preserve">4.65934085845947</t>
   </si>
   <si>
-    <t xml:space="preserve">4.62632942199707</t>
+    <t xml:space="preserve">4.62632989883423</t>
   </si>
   <si>
     <t xml:space="preserve">4.64519357681274</t>
   </si>
   <si>
-    <t xml:space="preserve">4.67820453643799</t>
+    <t xml:space="preserve">4.67820501327515</t>
   </si>
   <si>
     <t xml:space="preserve">4.71593236923218</t>
@@ -3521,7 +3521,7 @@
     <t xml:space="preserve">4.73479604721069</t>
   </si>
   <si>
-    <t xml:space="preserve">4.60274982452393</t>
+    <t xml:space="preserve">4.60275030136108</t>
   </si>
   <si>
     <t xml:space="preserve">4.57445430755615</t>
@@ -3536,7 +3536,7 @@
     <t xml:space="preserve">4.34337377548218</t>
   </si>
   <si>
-    <t xml:space="preserve">4.41411256790161</t>
+    <t xml:space="preserve">4.41411209106445</t>
   </si>
   <si>
     <t xml:space="preserve">4.3952488899231</t>
@@ -3578,31 +3578,31 @@
     <t xml:space="preserve">4.27263498306274</t>
   </si>
   <si>
-    <t xml:space="preserve">4.2349066734314</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.1122932434082</t>
+    <t xml:space="preserve">4.23490715026855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.11229276657104</t>
   </si>
   <si>
     <t xml:space="preserve">4.0887131690979</t>
   </si>
   <si>
-    <t xml:space="preserve">4.0557017326355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.10757684707642</t>
+    <t xml:space="preserve">4.05570220947266</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.10757732391357</t>
   </si>
   <si>
     <t xml:space="preserve">4.03683805465698</t>
   </si>
   <si>
-    <t xml:space="preserve">3.86234831809998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.00854253768921</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.99910998344421</t>
+    <t xml:space="preserve">3.86234855651855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.00854206085205</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.99911022186279</t>
   </si>
   <si>
     <t xml:space="preserve">4.07456541061401</t>
@@ -3620,7 +3620,7 @@
     <t xml:space="preserve">4.15473651885986</t>
   </si>
   <si>
-    <t xml:space="preserve">4.18303155899048</t>
+    <t xml:space="preserve">4.18303203582764</t>
   </si>
   <si>
     <t xml:space="preserve">4.27735042572021</t>
@@ -3638,7 +3638,7 @@
     <t xml:space="preserve">4.24905490875244</t>
   </si>
   <si>
-    <t xml:space="preserve">4.26791906356812</t>
+    <t xml:space="preserve">4.26791858673096</t>
   </si>
   <si>
     <t xml:space="preserve">4.39053297042847</t>
@@ -3647,7 +3647,7 @@
     <t xml:space="preserve">4.37166976928711</t>
   </si>
   <si>
-    <t xml:space="preserve">4.35752105712891</t>
+    <t xml:space="preserve">4.35752153396606</t>
   </si>
   <si>
     <t xml:space="preserve">4.35280513763428</t>
@@ -3683,19 +3683,19 @@
     <t xml:space="preserve">4.23962306976318</t>
   </si>
   <si>
-    <t xml:space="preserve">4.20189523696899</t>
+    <t xml:space="preserve">4.20189571380615</t>
   </si>
   <si>
     <t xml:space="preserve">4.12644052505493</t>
   </si>
   <si>
-    <t xml:space="preserve">4.0226902961731</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.15002012252808</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.92837142944336</t>
+    <t xml:space="preserve">4.02268981933594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.15002059936523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.92837166786194</t>
   </si>
   <si>
     <t xml:space="preserve">4.04626989364624</t>
@@ -3704,16 +3704,16 @@
     <t xml:space="preserve">3.96138286590576</t>
   </si>
   <si>
-    <t xml:space="preserve">4.06041765213013</t>
+    <t xml:space="preserve">4.06041717529297</t>
   </si>
   <si>
     <t xml:space="preserve">4.01797485351562</t>
   </si>
   <si>
-    <t xml:space="preserve">3.90007615089417</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.94251942634583</t>
+    <t xml:space="preserve">3.90007638931274</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.94251894950867</t>
   </si>
   <si>
     <t xml:space="preserve">3.89535999298096</t>
@@ -3731,7 +3731,7 @@
     <t xml:space="preserve">3.88121199607849</t>
   </si>
   <si>
-    <t xml:space="preserve">3.84348440170288</t>
+    <t xml:space="preserve">3.84348464012146</t>
   </si>
   <si>
     <t xml:space="preserve">3.81990528106689</t>
@@ -3749,10 +3749,10 @@
     <t xml:space="preserve">3.75388216972351</t>
   </si>
   <si>
-    <t xml:space="preserve">3.72558665275574</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.76331400871277</t>
+    <t xml:space="preserve">3.72558641433716</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.76331377029419</t>
   </si>
   <si>
     <t xml:space="preserve">3.735018491745</t>
@@ -3761,7 +3761,7 @@
     <t xml:space="preserve">3.71615481376648</t>
   </si>
   <si>
-    <t xml:space="preserve">3.58410835266113</t>
+    <t xml:space="preserve">3.58410859107971</t>
   </si>
   <si>
     <t xml:space="preserve">3.76442790031433</t>
@@ -4437,6 +4437,9 @@
   </si>
   <si>
     <t xml:space="preserve">6.94000005722046</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.90000009536743</t>
   </si>
 </sst>
 </file>
@@ -21017,7 +21020,7 @@
         <v>3.78500008583069</v>
       </c>
       <c r="G625" t="s">
-        <v>353</v>
+        <v>393</v>
       </c>
       <c r="H625" t="s">
         <v>9</v>
@@ -21043,7 +21046,7 @@
         <v>3.71000003814697</v>
       </c>
       <c r="G626" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="H626" t="s">
         <v>9</v>
@@ -21069,7 +21072,7 @@
         <v>3.72499990463257</v>
       </c>
       <c r="G627" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="H627" t="s">
         <v>9</v>
@@ -21095,7 +21098,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G628" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="H628" t="s">
         <v>9</v>
@@ -21121,7 +21124,7 @@
         <v>3.75</v>
       </c>
       <c r="G629" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="H629" t="s">
         <v>9</v>
@@ -21147,7 +21150,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G630" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="H630" t="s">
         <v>9</v>
@@ -21173,7 +21176,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G631" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="H631" t="s">
         <v>9</v>
@@ -21199,7 +21202,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G632" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="H632" t="s">
         <v>9</v>
@@ -21225,7 +21228,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G633" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="H633" t="s">
         <v>9</v>
@@ -21277,7 +21280,7 @@
         <v>3.67499995231628</v>
       </c>
       <c r="G635" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="H635" t="s">
         <v>9</v>
@@ -21303,7 +21306,7 @@
         <v>3.73499989509583</v>
       </c>
       <c r="G636" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="H636" t="s">
         <v>9</v>
@@ -21329,7 +21332,7 @@
         <v>3.77500009536743</v>
       </c>
       <c r="G637" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="H637" t="s">
         <v>9</v>
@@ -21355,7 +21358,7 @@
         <v>3.70499992370605</v>
       </c>
       <c r="G638" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="H638" t="s">
         <v>9</v>
@@ -21381,7 +21384,7 @@
         <v>3.76500010490417</v>
       </c>
       <c r="G639" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="H639" t="s">
         <v>9</v>
@@ -21407,7 +21410,7 @@
         <v>3.8050000667572</v>
       </c>
       <c r="G640" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="H640" t="s">
         <v>9</v>
@@ -21433,7 +21436,7 @@
         <v>3.8050000667572</v>
       </c>
       <c r="G641" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="H641" t="s">
         <v>9</v>
@@ -21459,7 +21462,7 @@
         <v>3.8050000667572</v>
       </c>
       <c r="G642" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="H642" t="s">
         <v>9</v>
@@ -21485,7 +21488,7 @@
         <v>3.75</v>
       </c>
       <c r="G643" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="H643" t="s">
         <v>9</v>
@@ -21537,7 +21540,7 @@
         <v>3.82999992370605</v>
       </c>
       <c r="G645" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="H645" t="s">
         <v>9</v>
@@ -21563,7 +21566,7 @@
         <v>3.82999992370605</v>
       </c>
       <c r="G646" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="H646" t="s">
         <v>9</v>
@@ -21615,7 +21618,7 @@
         <v>3.8050000667572</v>
       </c>
       <c r="G648" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="H648" t="s">
         <v>9</v>
@@ -21667,7 +21670,7 @@
         <v>3.85500001907349</v>
       </c>
       <c r="G650" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="H650" t="s">
         <v>9</v>
@@ -21693,7 +21696,7 @@
         <v>3.89000010490417</v>
       </c>
       <c r="G651" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="H651" t="s">
         <v>9</v>
@@ -21719,7 +21722,7 @@
         <v>3.96000003814697</v>
       </c>
       <c r="G652" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="H652" t="s">
         <v>9</v>
@@ -21745,7 +21748,7 @@
         <v>3.9449999332428</v>
       </c>
       <c r="G653" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="H653" t="s">
         <v>9</v>
@@ -21771,7 +21774,7 @@
         <v>3.90499997138977</v>
       </c>
       <c r="G654" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="H654" t="s">
         <v>9</v>
@@ -21797,7 +21800,7 @@
         <v>4</v>
       </c>
       <c r="G655" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="H655" t="s">
         <v>9</v>
@@ -21823,7 +21826,7 @@
         <v>4.07999992370605</v>
       </c>
       <c r="G656" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="H656" t="s">
         <v>9</v>
@@ -21849,7 +21852,7 @@
         <v>4.15999984741211</v>
       </c>
       <c r="G657" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="H657" t="s">
         <v>9</v>
@@ -21875,7 +21878,7 @@
         <v>4.07999992370605</v>
       </c>
       <c r="G658" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="H658" t="s">
         <v>9</v>
@@ -21901,7 +21904,7 @@
         <v>4.09000015258789</v>
       </c>
       <c r="G659" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="H659" t="s">
         <v>9</v>
@@ -21927,7 +21930,7 @@
         <v>4.21999979019165</v>
       </c>
       <c r="G660" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="H660" t="s">
         <v>9</v>
@@ -21953,7 +21956,7 @@
         <v>4.1100001335144</v>
       </c>
       <c r="G661" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="H661" t="s">
         <v>9</v>
@@ -21979,7 +21982,7 @@
         <v>4.15000009536743</v>
       </c>
       <c r="G662" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="H662" t="s">
         <v>9</v>
@@ -22005,7 +22008,7 @@
         <v>4.19000005722046</v>
       </c>
       <c r="G663" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="H663" t="s">
         <v>9</v>
@@ -22031,7 +22034,7 @@
         <v>4.19000005722046</v>
       </c>
       <c r="G664" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="H664" t="s">
         <v>9</v>
@@ -22057,7 +22060,7 @@
         <v>4.1399998664856</v>
       </c>
       <c r="G665" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="H665" t="s">
         <v>9</v>
@@ -22083,7 +22086,7 @@
         <v>4.11999988555908</v>
       </c>
       <c r="G666" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="H666" t="s">
         <v>9</v>
@@ -22109,7 +22112,7 @@
         <v>4.03499984741211</v>
       </c>
       <c r="G667" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="H667" t="s">
         <v>9</v>
@@ -22135,7 +22138,7 @@
         <v>4</v>
       </c>
       <c r="G668" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="H668" t="s">
         <v>9</v>
@@ -22161,7 +22164,7 @@
         <v>4.02500009536743</v>
       </c>
       <c r="G669" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="H669" t="s">
         <v>9</v>
@@ -22187,7 +22190,7 @@
         <v>4.13500022888184</v>
       </c>
       <c r="G670" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="H670" t="s">
         <v>9</v>
@@ -22213,7 +22216,7 @@
         <v>4.09000015258789</v>
       </c>
       <c r="G671" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="H671" t="s">
         <v>9</v>
@@ -22239,7 +22242,7 @@
         <v>3.9449999332428</v>
       </c>
       <c r="G672" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="H672" t="s">
         <v>9</v>
@@ -22265,7 +22268,7 @@
         <v>3.93499994277954</v>
       </c>
       <c r="G673" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="H673" t="s">
         <v>9</v>
@@ -22291,7 +22294,7 @@
         <v>3.95499992370605</v>
       </c>
       <c r="G674" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="H674" t="s">
         <v>9</v>
@@ -22317,7 +22320,7 @@
         <v>3.9300000667572</v>
       </c>
       <c r="G675" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="H675" t="s">
         <v>9</v>
@@ -22343,7 +22346,7 @@
         <v>3.98000001907349</v>
       </c>
       <c r="G676" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="H676" t="s">
         <v>9</v>
@@ -22369,7 +22372,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G677" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="H677" t="s">
         <v>9</v>
@@ -22395,7 +22398,7 @@
         <v>3.95499992370605</v>
       </c>
       <c r="G678" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="H678" t="s">
         <v>9</v>
@@ -22421,7 +22424,7 @@
         <v>3.91000008583069</v>
       </c>
       <c r="G679" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="H679" t="s">
         <v>9</v>
@@ -22447,7 +22450,7 @@
         <v>3.9300000667572</v>
       </c>
       <c r="G680" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="H680" t="s">
         <v>9</v>
@@ -22473,7 +22476,7 @@
         <v>4</v>
       </c>
       <c r="G681" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="H681" t="s">
         <v>9</v>
@@ -22499,7 +22502,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G682" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="H682" t="s">
         <v>9</v>
@@ -22525,7 +22528,7 @@
         <v>4.26000022888184</v>
       </c>
       <c r="G683" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="H683" t="s">
         <v>9</v>
@@ -22551,7 +22554,7 @@
         <v>4.27500009536743</v>
       </c>
       <c r="G684" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="H684" t="s">
         <v>9</v>
@@ -22577,7 +22580,7 @@
         <v>4.23000001907349</v>
       </c>
       <c r="G685" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="H685" t="s">
         <v>9</v>
@@ -22603,7 +22606,7 @@
         <v>4.2649998664856</v>
       </c>
       <c r="G686" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="H686" t="s">
         <v>9</v>
@@ -22629,7 +22632,7 @@
         <v>4.26999998092651</v>
       </c>
       <c r="G687" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="H687" t="s">
         <v>9</v>
@@ -22655,7 +22658,7 @@
         <v>4.36499977111816</v>
       </c>
       <c r="G688" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="H688" t="s">
         <v>9</v>
@@ -22681,7 +22684,7 @@
         <v>4.23999977111816</v>
       </c>
       <c r="G689" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="H689" t="s">
         <v>9</v>
@@ -22707,7 +22710,7 @@
         <v>4.25</v>
       </c>
       <c r="G690" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="H690" t="s">
         <v>9</v>
@@ -22733,7 +22736,7 @@
         <v>4.31500005722046</v>
       </c>
       <c r="G691" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="H691" t="s">
         <v>9</v>
@@ -22759,7 +22762,7 @@
         <v>4.50500011444092</v>
       </c>
       <c r="G692" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="H692" t="s">
         <v>9</v>
@@ -22785,7 +22788,7 @@
         <v>4.63000011444092</v>
       </c>
       <c r="G693" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="H693" t="s">
         <v>9</v>
@@ -22811,7 +22814,7 @@
         <v>4.43499994277954</v>
       </c>
       <c r="G694" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="H694" t="s">
         <v>9</v>
@@ -22837,7 +22840,7 @@
         <v>4.4850001335144</v>
       </c>
       <c r="G695" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="H695" t="s">
         <v>9</v>
@@ -22863,7 +22866,7 @@
         <v>4.3899998664856</v>
       </c>
       <c r="G696" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="H696" t="s">
         <v>9</v>
@@ -22889,7 +22892,7 @@
         <v>4.52500009536743</v>
       </c>
       <c r="G697" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="H697" t="s">
         <v>9</v>
@@ -22915,7 +22918,7 @@
         <v>4.50500011444092</v>
       </c>
       <c r="G698" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="H698" t="s">
         <v>9</v>
@@ -22941,7 +22944,7 @@
         <v>4.55999994277954</v>
       </c>
       <c r="G699" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="H699" t="s">
         <v>9</v>
@@ -22967,7 +22970,7 @@
         <v>4.53000020980835</v>
       </c>
       <c r="G700" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="H700" t="s">
         <v>9</v>
@@ -22993,7 +22996,7 @@
         <v>4.57499980926514</v>
       </c>
       <c r="G701" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="H701" t="s">
         <v>9</v>
@@ -23019,7 +23022,7 @@
         <v>4.67000007629395</v>
       </c>
       <c r="G702" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="H702" t="s">
         <v>9</v>
@@ -23045,7 +23048,7 @@
         <v>4.65999984741211</v>
       </c>
       <c r="G703" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="H703" t="s">
         <v>9</v>
@@ -23071,7 +23074,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G704" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="H704" t="s">
         <v>9</v>
@@ -23097,7 +23100,7 @@
         <v>4.84499979019165</v>
       </c>
       <c r="G705" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="H705" t="s">
         <v>9</v>
@@ -23123,7 +23126,7 @@
         <v>4.78999996185303</v>
       </c>
       <c r="G706" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="H706" t="s">
         <v>9</v>
@@ -23149,7 +23152,7 @@
         <v>4.67999982833862</v>
       </c>
       <c r="G707" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="H707" t="s">
         <v>9</v>
@@ -23175,7 +23178,7 @@
         <v>4.63000011444092</v>
       </c>
       <c r="G708" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="H708" t="s">
         <v>9</v>
@@ -23201,7 +23204,7 @@
         <v>4.6100001335144</v>
       </c>
       <c r="G709" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="H709" t="s">
         <v>9</v>
@@ -23227,7 +23230,7 @@
         <v>4.55000019073486</v>
       </c>
       <c r="G710" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="H710" t="s">
         <v>9</v>
@@ -23253,7 +23256,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G711" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="H711" t="s">
         <v>9</v>
@@ -23279,7 +23282,7 @@
         <v>4.51999998092651</v>
       </c>
       <c r="G712" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="H712" t="s">
         <v>9</v>
@@ -23305,7 +23308,7 @@
         <v>4.60500001907349</v>
       </c>
       <c r="G713" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="H713" t="s">
         <v>9</v>
@@ -23331,7 +23334,7 @@
         <v>4.61999988555908</v>
       </c>
       <c r="G714" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="H714" t="s">
         <v>9</v>
@@ -23357,7 +23360,7 @@
         <v>4.57499980926514</v>
       </c>
       <c r="G715" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="H715" t="s">
         <v>9</v>
@@ -23383,7 +23386,7 @@
         <v>4.44999980926514</v>
       </c>
       <c r="G716" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="H716" t="s">
         <v>9</v>
@@ -23409,7 +23412,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G717" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="H717" t="s">
         <v>9</v>
@@ -23435,7 +23438,7 @@
         <v>4.57999992370605</v>
       </c>
       <c r="G718" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="H718" t="s">
         <v>9</v>
@@ -23461,7 +23464,7 @@
         <v>4.53000020980835</v>
       </c>
       <c r="G719" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="H719" t="s">
         <v>9</v>
@@ -23487,7 +23490,7 @@
         <v>4.4850001335144</v>
       </c>
       <c r="G720" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="H720" t="s">
         <v>9</v>
@@ -23513,7 +23516,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G721" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="H721" t="s">
         <v>9</v>
@@ -23539,7 +23542,7 @@
         <v>4.55000019073486</v>
       </c>
       <c r="G722" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="H722" t="s">
         <v>9</v>
@@ -23565,7 +23568,7 @@
         <v>4.65000009536743</v>
       </c>
       <c r="G723" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="H723" t="s">
         <v>9</v>
@@ -23591,7 +23594,7 @@
         <v>4.71000003814697</v>
       </c>
       <c r="G724" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="H724" t="s">
         <v>9</v>
@@ -23617,7 +23620,7 @@
         <v>4.75500011444092</v>
       </c>
       <c r="G725" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="H725" t="s">
         <v>9</v>
@@ -23643,7 +23646,7 @@
         <v>4.76999998092651</v>
       </c>
       <c r="G726" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="H726" t="s">
         <v>9</v>
@@ -23669,7 +23672,7 @@
         <v>4.76999998092651</v>
       </c>
       <c r="G727" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="H727" t="s">
         <v>9</v>
@@ -23695,7 +23698,7 @@
         <v>4.66499996185303</v>
       </c>
       <c r="G728" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="H728" t="s">
         <v>9</v>
@@ -23721,7 +23724,7 @@
         <v>4.61499977111816</v>
       </c>
       <c r="G729" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="H729" t="s">
         <v>9</v>
@@ -23747,7 +23750,7 @@
         <v>4.67000007629395</v>
       </c>
       <c r="G730" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="H730" t="s">
         <v>9</v>
@@ -23773,7 +23776,7 @@
         <v>4.59000015258789</v>
       </c>
       <c r="G731" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="H731" t="s">
         <v>9</v>
@@ -23799,7 +23802,7 @@
         <v>4.57999992370605</v>
       </c>
       <c r="G732" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="H732" t="s">
         <v>9</v>
@@ -23825,7 +23828,7 @@
         <v>4.57999992370605</v>
       </c>
       <c r="G733" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="H733" t="s">
         <v>9</v>
@@ -23851,7 +23854,7 @@
         <v>4.4850001335144</v>
       </c>
       <c r="G734" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="H734" t="s">
         <v>9</v>
@@ -23877,7 +23880,7 @@
         <v>4.43499994277954</v>
       </c>
       <c r="G735" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="H735" t="s">
         <v>9</v>
@@ -23903,7 +23906,7 @@
         <v>4.36999988555908</v>
       </c>
       <c r="G736" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="H736" t="s">
         <v>9</v>
@@ -23929,7 +23932,7 @@
         <v>4.38000011444092</v>
       </c>
       <c r="G737" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="H737" t="s">
         <v>9</v>
@@ -23955,7 +23958,7 @@
         <v>4.28000020980835</v>
       </c>
       <c r="G738" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="H738" t="s">
         <v>9</v>
@@ -23981,7 +23984,7 @@
         <v>4.25</v>
       </c>
       <c r="G739" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="H739" t="s">
         <v>9</v>
@@ -24007,7 +24010,7 @@
         <v>4.23999977111816</v>
       </c>
       <c r="G740" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="H740" t="s">
         <v>9</v>
@@ -24033,7 +24036,7 @@
         <v>4.21000003814697</v>
       </c>
       <c r="G741" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="H741" t="s">
         <v>9</v>
@@ -24059,7 +24062,7 @@
         <v>4.3899998664856</v>
       </c>
       <c r="G742" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="H742" t="s">
         <v>9</v>
@@ -24085,7 +24088,7 @@
         <v>4.41499996185303</v>
       </c>
       <c r="G743" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="H743" t="s">
         <v>9</v>
@@ -24111,7 +24114,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G744" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="H744" t="s">
         <v>9</v>
@@ -24137,7 +24140,7 @@
         <v>4.34000015258789</v>
       </c>
       <c r="G745" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="H745" t="s">
         <v>9</v>
@@ -24163,7 +24166,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G746" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="H746" t="s">
         <v>9</v>
@@ -24189,7 +24192,7 @@
         <v>4.55000019073486</v>
       </c>
       <c r="G747" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="H747" t="s">
         <v>9</v>
@@ -24215,7 +24218,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G748" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="H748" t="s">
         <v>9</v>
@@ -24241,7 +24244,7 @@
         <v>4.5</v>
       </c>
       <c r="G749" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="H749" t="s">
         <v>9</v>
@@ -24267,7 +24270,7 @@
         <v>4.42999982833862</v>
       </c>
       <c r="G750" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="H750" t="s">
         <v>9</v>
@@ -24293,7 +24296,7 @@
         <v>4.41499996185303</v>
       </c>
       <c r="G751" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="H751" t="s">
         <v>9</v>
@@ -24319,7 +24322,7 @@
         <v>4.34499979019165</v>
       </c>
       <c r="G752" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="H752" t="s">
         <v>9</v>
@@ -24345,7 +24348,7 @@
         <v>4.43499994277954</v>
       </c>
       <c r="G753" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="H753" t="s">
         <v>9</v>
@@ -24371,7 +24374,7 @@
         <v>4.42999982833862</v>
       </c>
       <c r="G754" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="H754" t="s">
         <v>9</v>
@@ -24397,7 +24400,7 @@
         <v>4.42999982833862</v>
       </c>
       <c r="G755" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="H755" t="s">
         <v>9</v>
@@ -24423,7 +24426,7 @@
         <v>4.40999984741211</v>
       </c>
       <c r="G756" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="H756" t="s">
         <v>9</v>
@@ -24449,7 +24452,7 @@
         <v>4.38500022888184</v>
       </c>
       <c r="G757" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="H757" t="s">
         <v>9</v>
@@ -24475,7 +24478,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G758" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="H758" t="s">
         <v>9</v>
@@ -24501,7 +24504,7 @@
         <v>4.44999980926514</v>
       </c>
       <c r="G759" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="H759" t="s">
         <v>9</v>
@@ -24527,7 +24530,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G760" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="H760" t="s">
         <v>9</v>
@@ -24553,7 +24556,7 @@
         <v>4.38000011444092</v>
       </c>
       <c r="G761" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="H761" t="s">
         <v>9</v>
@@ -24579,7 +24582,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G762" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="H762" t="s">
         <v>9</v>
@@ -24605,7 +24608,7 @@
         <v>4.42999982833862</v>
       </c>
       <c r="G763" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="H763" t="s">
         <v>9</v>
@@ -24631,7 +24634,7 @@
         <v>4.55000019073486</v>
       </c>
       <c r="G764" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="H764" t="s">
         <v>9</v>
@@ -24657,7 +24660,7 @@
         <v>4.53499984741211</v>
       </c>
       <c r="G765" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="H765" t="s">
         <v>9</v>
@@ -24683,7 +24686,7 @@
         <v>4.51000022888184</v>
       </c>
       <c r="G766" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="H766" t="s">
         <v>9</v>
@@ -24709,7 +24712,7 @@
         <v>4.40500020980835</v>
       </c>
       <c r="G767" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="H767" t="s">
         <v>9</v>
@@ -24735,7 +24738,7 @@
         <v>4.44999980926514</v>
       </c>
       <c r="G768" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="H768" t="s">
         <v>9</v>
@@ -24761,7 +24764,7 @@
         <v>4.44999980926514</v>
       </c>
       <c r="G769" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="H769" t="s">
         <v>9</v>
@@ -24787,7 +24790,7 @@
         <v>4.44500017166138</v>
       </c>
       <c r="G770" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="H770" t="s">
         <v>9</v>
@@ -24813,7 +24816,7 @@
         <v>4.46500015258789</v>
       </c>
       <c r="G771" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="H771" t="s">
         <v>9</v>
@@ -24839,7 +24842,7 @@
         <v>4.42999982833862</v>
       </c>
       <c r="G772" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="H772" t="s">
         <v>9</v>
@@ -24865,7 +24868,7 @@
         <v>4.34999990463257</v>
       </c>
       <c r="G773" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="H773" t="s">
         <v>9</v>
@@ -24891,7 +24894,7 @@
         <v>4.28000020980835</v>
       </c>
       <c r="G774" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="H774" t="s">
         <v>9</v>
@@ -24917,7 +24920,7 @@
         <v>4.3600001335144</v>
       </c>
       <c r="G775" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="H775" t="s">
         <v>9</v>
@@ -24943,7 +24946,7 @@
         <v>4.5</v>
       </c>
       <c r="G776" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="H776" t="s">
         <v>9</v>
@@ -24969,7 +24972,7 @@
         <v>4.63000011444092</v>
       </c>
       <c r="G777" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="H777" t="s">
         <v>9</v>
@@ -24995,7 +24998,7 @@
         <v>4.59499979019165</v>
       </c>
       <c r="G778" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="H778" t="s">
         <v>9</v>
@@ -25021,7 +25024,7 @@
         <v>4.65000009536743</v>
       </c>
       <c r="G779" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="H779" t="s">
         <v>9</v>
@@ -25047,7 +25050,7 @@
         <v>4.6399998664856</v>
       </c>
       <c r="G780" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="H780" t="s">
         <v>9</v>
@@ -25073,7 +25076,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G781" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="H781" t="s">
         <v>9</v>
@@ -25099,7 +25102,7 @@
         <v>4.69000005722046</v>
       </c>
       <c r="G782" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="H782" t="s">
         <v>9</v>
@@ -25125,7 +25128,7 @@
         <v>4.77500009536743</v>
       </c>
       <c r="G783" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="H783" t="s">
         <v>9</v>
@@ -25151,7 +25154,7 @@
         <v>4.78999996185303</v>
       </c>
       <c r="G784" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="H784" t="s">
         <v>9</v>
@@ -25177,7 +25180,7 @@
         <v>4.86999988555908</v>
       </c>
       <c r="G785" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="H785" t="s">
         <v>9</v>
@@ -25203,7 +25206,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G786" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="H786" t="s">
         <v>9</v>
@@ -25229,7 +25232,7 @@
         <v>4.96999979019165</v>
       </c>
       <c r="G787" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="H787" t="s">
         <v>9</v>
@@ -25255,7 +25258,7 @@
         <v>5</v>
       </c>
       <c r="G788" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="H788" t="s">
         <v>9</v>
@@ -25281,7 +25284,7 @@
         <v>5.05000019073486</v>
       </c>
       <c r="G789" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="H789" t="s">
         <v>9</v>
@@ -25307,7 +25310,7 @@
         <v>4.98999977111816</v>
       </c>
       <c r="G790" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="H790" t="s">
         <v>9</v>
@@ -25333,7 +25336,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G791" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="H791" t="s">
         <v>9</v>
@@ -25359,7 +25362,7 @@
         <v>4.88500022888184</v>
       </c>
       <c r="G792" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="H792" t="s">
         <v>9</v>
@@ -25385,7 +25388,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G793" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="H793" t="s">
         <v>9</v>
@@ -25411,7 +25414,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G794" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="H794" t="s">
         <v>9</v>
@@ -25437,7 +25440,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G795" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="H795" t="s">
         <v>9</v>
@@ -25463,7 +25466,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G796" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="H796" t="s">
         <v>9</v>
@@ -25489,7 +25492,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G797" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="H797" t="s">
         <v>9</v>
@@ -25515,7 +25518,7 @@
         <v>4.8600001335144</v>
       </c>
       <c r="G798" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="H798" t="s">
         <v>9</v>
@@ -25541,7 +25544,7 @@
         <v>4.88500022888184</v>
       </c>
       <c r="G799" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="H799" t="s">
         <v>9</v>
@@ -25567,7 +25570,7 @@
         <v>4.94000005722046</v>
       </c>
       <c r="G800" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="H800" t="s">
         <v>9</v>
@@ -25593,7 +25596,7 @@
         <v>4.875</v>
       </c>
       <c r="G801" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="H801" t="s">
         <v>9</v>
@@ -25619,7 +25622,7 @@
         <v>4.86499977111816</v>
       </c>
       <c r="G802" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="H802" t="s">
         <v>9</v>
@@ -25645,7 +25648,7 @@
         <v>4.8600001335144</v>
       </c>
       <c r="G803" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="H803" t="s">
         <v>9</v>
@@ -25671,7 +25674,7 @@
         <v>4.84000015258789</v>
       </c>
       <c r="G804" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="H804" t="s">
         <v>9</v>
@@ -25697,7 +25700,7 @@
         <v>4.8600001335144</v>
       </c>
       <c r="G805" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="H805" t="s">
         <v>9</v>
@@ -25723,7 +25726,7 @@
         <v>5.07999992370605</v>
       </c>
       <c r="G806" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="H806" t="s">
         <v>9</v>
@@ -25749,7 +25752,7 @@
         <v>5.23999977111816</v>
       </c>
       <c r="G807" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="H807" t="s">
         <v>9</v>
@@ -25775,7 +25778,7 @@
         <v>5.3899998664856</v>
       </c>
       <c r="G808" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="H808" t="s">
         <v>9</v>
@@ -25801,7 +25804,7 @@
         <v>5.3600001335144</v>
       </c>
       <c r="G809" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="H809" t="s">
         <v>9</v>
@@ -25827,7 +25830,7 @@
         <v>5.46000003814697</v>
       </c>
       <c r="G810" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="H810" t="s">
         <v>9</v>
@@ -25853,7 +25856,7 @@
         <v>5.34000015258789</v>
       </c>
       <c r="G811" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="H811" t="s">
         <v>9</v>
@@ -25879,7 +25882,7 @@
         <v>5.46000003814697</v>
       </c>
       <c r="G812" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="H812" t="s">
         <v>9</v>
@@ -25905,7 +25908,7 @@
         <v>5.51000022888184</v>
       </c>
       <c r="G813" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="H813" t="s">
         <v>9</v>
@@ -25931,7 +25934,7 @@
         <v>5.57000017166138</v>
       </c>
       <c r="G814" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="H814" t="s">
         <v>9</v>
@@ -25957,7 +25960,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G815" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="H815" t="s">
         <v>9</v>
@@ -25983,7 +25986,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G816" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="H816" t="s">
         <v>9</v>
@@ -26009,7 +26012,7 @@
         <v>5.57000017166138</v>
       </c>
       <c r="G817" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="H817" t="s">
         <v>9</v>
@@ -26035,7 +26038,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G818" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="H818" t="s">
         <v>9</v>
@@ -26061,7 +26064,7 @@
         <v>5.57999992370605</v>
       </c>
       <c r="G819" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="H819" t="s">
         <v>9</v>
@@ -26087,7 +26090,7 @@
         <v>5.55999994277954</v>
       </c>
       <c r="G820" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="H820" t="s">
         <v>9</v>
@@ -26113,7 +26116,7 @@
         <v>5.51999998092651</v>
       </c>
       <c r="G821" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="H821" t="s">
         <v>9</v>
@@ -26139,7 +26142,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G822" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="H822" t="s">
         <v>9</v>
@@ -26165,7 +26168,7 @@
         <v>5.28999996185303</v>
       </c>
       <c r="G823" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="H823" t="s">
         <v>9</v>
@@ -26191,7 +26194,7 @@
         <v>5.32999992370605</v>
       </c>
       <c r="G824" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="H824" t="s">
         <v>9</v>
@@ -26217,7 +26220,7 @@
         <v>5.34999990463257</v>
       </c>
       <c r="G825" t="s">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="H825" t="s">
         <v>9</v>
@@ -26243,7 +26246,7 @@
         <v>5.42000007629395</v>
       </c>
       <c r="G826" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="H826" t="s">
         <v>9</v>
@@ -26269,7 +26272,7 @@
         <v>5.42000007629395</v>
       </c>
       <c r="G827" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="H827" t="s">
         <v>9</v>
@@ -26295,7 +26298,7 @@
         <v>5.48000001907349</v>
       </c>
       <c r="G828" t="s">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="H828" t="s">
         <v>9</v>
@@ -26321,7 +26324,7 @@
         <v>5.5</v>
       </c>
       <c r="G829" t="s">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="H829" t="s">
         <v>9</v>
@@ -26347,7 +26350,7 @@
         <v>5.48999977111816</v>
       </c>
       <c r="G830" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="H830" t="s">
         <v>9</v>
@@ -26373,7 +26376,7 @@
         <v>5.5</v>
       </c>
       <c r="G831" t="s">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="H831" t="s">
         <v>9</v>
@@ -26399,7 +26402,7 @@
         <v>5.5</v>
       </c>
       <c r="G832" t="s">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="H832" t="s">
         <v>9</v>
@@ -26425,7 +26428,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G833" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="H833" t="s">
         <v>9</v>
@@ -26451,7 +26454,7 @@
         <v>5.25</v>
       </c>
       <c r="G834" t="s">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="H834" t="s">
         <v>9</v>
@@ -26477,7 +26480,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G835" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="H835" t="s">
         <v>9</v>
@@ -26503,7 +26506,7 @@
         <v>5.46000003814697</v>
       </c>
       <c r="G836" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="H836" t="s">
         <v>9</v>
@@ -26529,7 +26532,7 @@
         <v>5.51000022888184</v>
       </c>
       <c r="G837" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="H837" t="s">
         <v>9</v>
@@ -26555,7 +26558,7 @@
         <v>5.67000007629395</v>
       </c>
       <c r="G838" t="s">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="H838" t="s">
         <v>9</v>
@@ -26581,7 +26584,7 @@
         <v>5.73000001907349</v>
       </c>
       <c r="G839" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="H839" t="s">
         <v>9</v>
@@ -26607,7 +26610,7 @@
         <v>5.65000009536743</v>
       </c>
       <c r="G840" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="H840" t="s">
         <v>9</v>
@@ -26633,7 +26636,7 @@
         <v>5.59000015258789</v>
       </c>
       <c r="G841" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="H841" t="s">
         <v>9</v>
@@ -26659,7 +26662,7 @@
         <v>5.55000019073486</v>
       </c>
       <c r="G842" t="s">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="H842" t="s">
         <v>9</v>
@@ -26685,7 +26688,7 @@
         <v>5.55000019073486</v>
       </c>
       <c r="G843" t="s">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="H843" t="s">
         <v>9</v>
@@ -26711,7 +26714,7 @@
         <v>5.46000003814697</v>
       </c>
       <c r="G844" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="H844" t="s">
         <v>9</v>
@@ -26737,7 +26740,7 @@
         <v>5.36999988555908</v>
       </c>
       <c r="G845" t="s">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="H845" t="s">
         <v>9</v>
@@ -26763,7 +26766,7 @@
         <v>5.46000003814697</v>
       </c>
       <c r="G846" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="H846" t="s">
         <v>9</v>
@@ -26789,7 +26792,7 @@
         <v>5.40999984741211</v>
       </c>
       <c r="G847" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="H847" t="s">
         <v>9</v>
@@ -26815,7 +26818,7 @@
         <v>5.48999977111816</v>
       </c>
       <c r="G848" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="H848" t="s">
         <v>9</v>
@@ -26841,7 +26844,7 @@
         <v>5.42000007629395</v>
       </c>
       <c r="G849" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="H849" t="s">
         <v>9</v>
@@ -26867,7 +26870,7 @@
         <v>5.32000017166138</v>
       </c>
       <c r="G850" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="H850" t="s">
         <v>9</v>
@@ -26893,7 +26896,7 @@
         <v>5.34000015258789</v>
       </c>
       <c r="G851" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="H851" t="s">
         <v>9</v>
@@ -26919,7 +26922,7 @@
         <v>5.32000017166138</v>
       </c>
       <c r="G852" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="H852" t="s">
         <v>9</v>
@@ -26945,7 +26948,7 @@
         <v>5.34999990463257</v>
       </c>
       <c r="G853" t="s">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="H853" t="s">
         <v>9</v>
@@ -26971,7 +26974,7 @@
         <v>5.26000022888184</v>
       </c>
       <c r="G854" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="H854" t="s">
         <v>9</v>
@@ -26997,7 +27000,7 @@
         <v>5.26000022888184</v>
       </c>
       <c r="G855" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="H855" t="s">
         <v>9</v>
@@ -27023,7 +27026,7 @@
         <v>5.23000001907349</v>
       </c>
       <c r="G856" t="s">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="H856" t="s">
         <v>9</v>
@@ -27049,7 +27052,7 @@
         <v>5.21999979019165</v>
       </c>
       <c r="G857" t="s">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="H857" t="s">
         <v>9</v>
@@ -27075,7 +27078,7 @@
         <v>5.17999982833862</v>
       </c>
       <c r="G858" t="s">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="H858" t="s">
         <v>9</v>
@@ -27101,7 +27104,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G859" t="s">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="H859" t="s">
         <v>9</v>
@@ -27127,7 +27130,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G860" t="s">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="H860" t="s">
         <v>9</v>
@@ -27153,7 +27156,7 @@
         <v>5.26000022888184</v>
       </c>
       <c r="G861" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="H861" t="s">
         <v>9</v>
@@ -27179,7 +27182,7 @@
         <v>5.11999988555908</v>
       </c>
       <c r="G862" t="s">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="H862" t="s">
         <v>9</v>
@@ -27205,7 +27208,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G863" t="s">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="H863" t="s">
         <v>9</v>
@@ -27231,7 +27234,7 @@
         <v>5.09000015258789</v>
       </c>
       <c r="G864" t="s">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="H864" t="s">
         <v>9</v>
@@ -27257,7 +27260,7 @@
         <v>5.01000022888184</v>
       </c>
       <c r="G865" t="s">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="H865" t="s">
         <v>9</v>
@@ -27283,7 +27286,7 @@
         <v>4.96999979019165</v>
       </c>
       <c r="G866" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="H866" t="s">
         <v>9</v>
@@ -27309,7 +27312,7 @@
         <v>5.03999996185303</v>
       </c>
       <c r="G867" t="s">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="H867" t="s">
         <v>9</v>
@@ -27335,7 +27338,7 @@
         <v>5.01999998092651</v>
       </c>
       <c r="G868" t="s">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="H868" t="s">
         <v>9</v>
@@ -27361,7 +27364,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G869" t="s">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="H869" t="s">
         <v>9</v>
@@ -27387,7 +27390,7 @@
         <v>5.05999994277954</v>
       </c>
       <c r="G870" t="s">
-        <v>549</v>
+        <v>540</v>
       </c>
       <c r="H870" t="s">
         <v>9</v>
@@ -27465,7 +27468,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G873" t="s">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="H873" t="s">
         <v>9</v>
@@ -27491,7 +27494,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G874" t="s">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="H874" t="s">
         <v>9</v>
@@ -27517,7 +27520,7 @@
         <v>5.09000015258789</v>
       </c>
       <c r="G875" t="s">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="H875" t="s">
         <v>9</v>
@@ -27621,7 +27624,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G879" t="s">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="H879" t="s">
         <v>9</v>
@@ -27699,7 +27702,7 @@
         <v>5.11999988555908</v>
       </c>
       <c r="G882" t="s">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="H882" t="s">
         <v>9</v>
@@ -27725,7 +27728,7 @@
         <v>5.05999994277954</v>
       </c>
       <c r="G883" t="s">
-        <v>549</v>
+        <v>540</v>
       </c>
       <c r="H883" t="s">
         <v>9</v>
@@ -28271,7 +28274,7 @@
         <v>4.96999979019165</v>
       </c>
       <c r="G904" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="H904" t="s">
         <v>9</v>
@@ -30247,7 +30250,7 @@
         <v>5.05999994277954</v>
       </c>
       <c r="G980" t="s">
-        <v>549</v>
+        <v>540</v>
       </c>
       <c r="H980" t="s">
         <v>9</v>
@@ -30273,7 +30276,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G981" t="s">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="H981" t="s">
         <v>9</v>
@@ -30325,7 +30328,7 @@
         <v>5.26000022888184</v>
       </c>
       <c r="G983" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="H983" t="s">
         <v>9</v>
@@ -30429,7 +30432,7 @@
         <v>5.26000022888184</v>
       </c>
       <c r="G987" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="H987" t="s">
         <v>9</v>
@@ -30455,7 +30458,7 @@
         <v>5.11999988555908</v>
       </c>
       <c r="G988" t="s">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="H988" t="s">
         <v>9</v>
@@ -31157,7 +31160,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G1015" t="s">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="H1015" t="s">
         <v>9</v>
@@ -31287,7 +31290,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G1020" t="s">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="H1020" t="s">
         <v>9</v>
@@ -31807,7 +31810,7 @@
         <v>5.01000022888184</v>
       </c>
       <c r="G1040" t="s">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="H1040" t="s">
         <v>9</v>
@@ -31911,7 +31914,7 @@
         <v>5.11999988555908</v>
       </c>
       <c r="G1044" t="s">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="H1044" t="s">
         <v>9</v>
@@ -69541,7 +69544,7 @@
     </row>
     <row r="2492">
       <c r="A2492" s="1" t="n">
-        <v>45947.6495833333</v>
+        <v>45947.2916666667</v>
       </c>
       <c r="B2492" t="n">
         <v>31626</v>
@@ -69562,6 +69565,32 @@
         <v>1474</v>
       </c>
       <c r="H2492" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2493">
+      <c r="A2493" s="1" t="n">
+        <v>45950.6493287037</v>
+      </c>
+      <c r="B2493" t="n">
+        <v>18823</v>
+      </c>
+      <c r="C2493" t="n">
+        <v>7.03000020980835</v>
+      </c>
+      <c r="D2493" t="n">
+        <v>6.71999979019165</v>
+      </c>
+      <c r="E2493" t="n">
+        <v>6.71999979019165</v>
+      </c>
+      <c r="F2493" t="n">
+        <v>6.90000009536743</v>
+      </c>
+      <c r="G2493" t="s">
+        <v>1475</v>
+      </c>
+      <c r="H2493" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/BAN.MI.xlsx
+++ b/data/BAN.MI.xlsx
@@ -44,79 +44,79 @@
     <t xml:space="preserve">BAN.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">3.6833028793335</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.59039282798767</t>
+    <t xml:space="preserve">3.68330216407776</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.59039354324341</t>
   </si>
   <si>
     <t xml:space="preserve">3.46283960342407</t>
   </si>
   <si>
-    <t xml:space="preserve">3.41874766349792</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.35733222961426</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.44551777839661</t>
+    <t xml:space="preserve">3.41874718666077</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.35733270645142</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.44551753997803</t>
   </si>
   <si>
     <t xml:space="preserve">3.46441459655762</t>
   </si>
   <si>
-    <t xml:space="preserve">3.45181679725647</t>
+    <t xml:space="preserve">3.45181632041931</t>
   </si>
   <si>
     <t xml:space="preserve">3.43134474754333</t>
   </si>
   <si>
-    <t xml:space="preserve">3.38410258293152</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.40929889678955</t>
+    <t xml:space="preserve">3.38410329818726</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.40929841995239</t>
   </si>
   <si>
     <t xml:space="preserve">3.11639809608459</t>
   </si>
   <si>
-    <t xml:space="preserve">3.24080228805542</t>
+    <t xml:space="preserve">3.240802526474</t>
   </si>
   <si>
     <t xml:space="preserve">3.29119372367859</t>
   </si>
   <si>
-    <t xml:space="preserve">3.21245670318604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.26757311820984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.19356036186218</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.13372015953064</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.22820448875427</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.16678953170776</t>
+    <t xml:space="preserve">3.21245718002319</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.2675724029541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.19356060028076</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.13372039794922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.22820401191711</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.16678977012634</t>
   </si>
   <si>
     <t xml:space="preserve">3.17308878898621</t>
   </si>
   <si>
-    <t xml:space="preserve">3.0707311630249</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.14946746826172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.05025935173035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.92900466918945</t>
+    <t xml:space="preserve">3.07073068618774</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.14946794509888</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.0502598285675</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.92900514602661</t>
   </si>
   <si>
     <t xml:space="preserve">2.91325759887695</t>
@@ -125,25 +125,25 @@
     <t xml:space="preserve">2.83452081680298</t>
   </si>
   <si>
-    <t xml:space="preserve">2.82664680480957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.75263500213623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.75420904159546</t>
+    <t xml:space="preserve">2.82664704322815</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.75263476371765</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.75420928001404</t>
   </si>
   <si>
     <t xml:space="preserve">2.755784034729</t>
   </si>
   <si>
-    <t xml:space="preserve">2.89436078071594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.98254585266113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.96207451820374</t>
+    <t xml:space="preserve">2.89436054229736</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.98254609107971</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.96207427978516</t>
   </si>
   <si>
     <t xml:space="preserve">2.99356913566589</t>
@@ -155,55 +155,55 @@
     <t xml:space="preserve">3.11009931564331</t>
   </si>
   <si>
-    <t xml:space="preserve">3.06915640830994</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.96364903450012</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.99199438095093</t>
+    <t xml:space="preserve">3.06915616989136</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.96364855766296</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.99199461936951</t>
   </si>
   <si>
     <t xml:space="preserve">3.00774168968201</t>
   </si>
   <si>
-    <t xml:space="preserve">2.97624683380127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.06285762786865</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.11797332763672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.18096232414246</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.10222578048706</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.13686990737915</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.23292875289917</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.33843541145325</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.30694055557251</t>
+    <t xml:space="preserve">2.97624707221985</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.06285715103149</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.11797308921814</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.18096208572388</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.10222601890564</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.13687014579773</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.23292827606201</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.33843517303467</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.30694079399109</t>
   </si>
   <si>
     <t xml:space="preserve">3.24395132064819</t>
   </si>
   <si>
-    <t xml:space="preserve">3.24237704277039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.12584710121155</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.19670987129211</t>
+    <t xml:space="preserve">3.24237680435181</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.12584662437439</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.19670915603638</t>
   </si>
   <si>
     <t xml:space="preserve">3.20300841331482</t>
@@ -215,40 +215,40 @@
     <t xml:space="preserve">3.11324906349182</t>
   </si>
   <si>
-    <t xml:space="preserve">3.14159417152405</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.04711008071899</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.99986839294434</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.96049928665161</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.09435224533081</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.96837329864502</t>
+    <t xml:space="preserve">3.14159393310547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.04710984230042</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.9998676776886</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.96049976348877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.09435176849365</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.9683735370636</t>
   </si>
   <si>
     <t xml:space="preserve">2.86286568641663</t>
   </si>
   <si>
-    <t xml:space="preserve">2.87388968467712</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.91010785102844</t>
+    <t xml:space="preserve">2.87388944625854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.91010808944702</t>
   </si>
   <si>
     <t xml:space="preserve">2.98569560050964</t>
   </si>
   <si>
-    <t xml:space="preserve">3.00144290924072</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.01561546325684</t>
+    <t xml:space="preserve">3.00144267082214</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.01561522483826</t>
   </si>
   <si>
     <t xml:space="preserve">2.92743039131165</t>
@@ -257,25 +257,25 @@
     <t xml:space="preserve">2.92113137245178</t>
   </si>
   <si>
-    <t xml:space="preserve">2.85814189910889</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.81404948234558</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.84082007408142</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.80145168304443</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.72901391983032</t>
+    <t xml:space="preserve">2.85814213752747</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.814049243927</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.8408203125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.80145120620728</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.72901368141174</t>
   </si>
   <si>
     <t xml:space="preserve">2.65185189247131</t>
   </si>
   <si>
-    <t xml:space="preserve">2.68177199363708</t>
+    <t xml:space="preserve">2.68177151679993</t>
   </si>
   <si>
     <t xml:space="preserve">2.71484088897705</t>
@@ -284,25 +284,25 @@
     <t xml:space="preserve">2.76365804672241</t>
   </si>
   <si>
-    <t xml:space="preserve">2.77940535545349</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.72428965568542</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.59043741226196</t>
+    <t xml:space="preserve">2.77940511703491</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.72428941726685</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.59043669700623</t>
   </si>
   <si>
     <t xml:space="preserve">2.53532147407532</t>
   </si>
   <si>
-    <t xml:space="preserve">2.49437856674194</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.48020601272583</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.51957440376282</t>
+    <t xml:space="preserve">2.49437832832336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.48020577430725</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.51957392692566</t>
   </si>
   <si>
     <t xml:space="preserve">2.6057276725769</t>
@@ -311,22 +311,22 @@
     <t xml:space="preserve">2.58784627914429</t>
   </si>
   <si>
-    <t xml:space="preserve">2.56021237373352</t>
+    <t xml:space="preserve">2.5602126121521</t>
   </si>
   <si>
     <t xml:space="preserve">2.56183791160583</t>
   </si>
   <si>
-    <t xml:space="preserve">2.6089780330658</t>
+    <t xml:space="preserve">2.60897827148438</t>
   </si>
   <si>
     <t xml:space="preserve">2.59272336959839</t>
   </si>
   <si>
-    <t xml:space="preserve">2.58134436607361</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.60085105895996</t>
+    <t xml:space="preserve">2.58134460449219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.6008505821228</t>
   </si>
   <si>
     <t xml:space="preserve">2.72114014625549</t>
@@ -335,34 +335,34 @@
     <t xml:space="preserve">2.82029747962952</t>
   </si>
   <si>
-    <t xml:space="preserve">2.80404210090637</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.68212747573853</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.71463799476624</t>
+    <t xml:space="preserve">2.80404257774353</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.68212723731995</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.71463775634766</t>
   </si>
   <si>
     <t xml:space="preserve">2.44642519950867</t>
   </si>
   <si>
-    <t xml:space="preserve">2.39765882492065</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.50331878662109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.47568488121033</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.52770161628723</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.50819540023804</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.40578699111938</t>
+    <t xml:space="preserve">2.39765930175781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.50331830978394</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.47568464279175</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.52770185470581</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.50819563865662</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.40578651428223</t>
   </si>
   <si>
     <t xml:space="preserve">2.19446778297424</t>
@@ -374,154 +374,154 @@
     <t xml:space="preserve">2.29525089263916</t>
   </si>
   <si>
-    <t xml:space="preserve">2.27411866188049</t>
+    <t xml:space="preserve">2.27411890029907</t>
   </si>
   <si>
     <t xml:space="preserve">2.35702109336853</t>
   </si>
   <si>
-    <t xml:space="preserve">2.3732762336731</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.29199957847595</t>
+    <t xml:space="preserve">2.37327647209167</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.29199934005737</t>
   </si>
   <si>
     <t xml:space="preserve">2.19284224510193</t>
   </si>
   <si>
-    <t xml:space="preserve">2.22535300254822</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.28387188911438</t>
+    <t xml:space="preserve">2.22535276412964</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.28387236595154</t>
   </si>
   <si>
     <t xml:space="preserve">2.30500388145447</t>
   </si>
   <si>
-    <t xml:space="preserve">2.3310124874115</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.33588886260986</t>
+    <t xml:space="preserve">2.33101224899292</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.3358895778656</t>
   </si>
   <si>
     <t xml:space="preserve">2.33263802528381</t>
   </si>
   <si>
-    <t xml:space="preserve">2.31963396072388</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.38140416145325</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.5358293056488</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.54395723342896</t>
+    <t xml:space="preserve">2.3196337223053</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.38140392303467</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.53582954406738</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.54395771026611</t>
   </si>
   <si>
     <t xml:space="preserve">2.56834030151367</t>
   </si>
   <si>
-    <t xml:space="preserve">2.89669752120972</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.83817863464355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.81216979026794</t>
+    <t xml:space="preserve">2.89669704437256</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.83817839622498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.81217002868652</t>
   </si>
   <si>
     <t xml:space="preserve">2.59597420692444</t>
   </si>
   <si>
-    <t xml:space="preserve">2.57646799087524</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.57321667671204</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.56671476364136</t>
+    <t xml:space="preserve">2.57646751403809</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.57321643829346</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.56671452522278</t>
   </si>
   <si>
     <t xml:space="preserve">2.53257822990417</t>
   </si>
   <si>
-    <t xml:space="preserve">2.5374550819397</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.63661241531372</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.63011050224304</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.64636540412903</t>
+    <t xml:space="preserve">2.53745484352112</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.63661217689514</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.63011026382446</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.64636564254761</t>
   </si>
   <si>
     <t xml:space="preserve">2.65286803245544</t>
   </si>
   <si>
-    <t xml:space="preserve">2.63823795318604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.64148902893066</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.69188094139099</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.75690150260925</t>
+    <t xml:space="preserve">2.63823771476746</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.64148926734924</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.69188070297241</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.75690174102783</t>
   </si>
   <si>
     <t xml:space="preserve">2.79266357421875</t>
   </si>
   <si>
-    <t xml:space="preserve">2.76340389251709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.7308931350708</t>
+    <t xml:space="preserve">2.76340413093567</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.73089337348938</t>
   </si>
   <si>
     <t xml:space="preserve">2.65449333190918</t>
   </si>
   <si>
-    <t xml:space="preserve">2.65774440765381</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.74227237701416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.76828074455261</t>
+    <t xml:space="preserve">2.65774416923523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.74227213859558</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.76828050613403</t>
   </si>
   <si>
     <t xml:space="preserve">2.70651006698608</t>
   </si>
   <si>
-    <t xml:space="preserve">2.72764158248901</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.74064636230469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.76990604400635</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.80079126358032</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.69513130187988</t>
+    <t xml:space="preserve">2.72764205932617</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.74064660072327</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.76990580558777</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.8007915019989</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.69513201713562</t>
   </si>
   <si>
     <t xml:space="preserve">2.66749787330627</t>
   </si>
   <si>
-    <t xml:space="preserve">2.64799094200134</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.62523365020752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.59759974479675</t>
+    <t xml:space="preserve">2.64799118041992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.6252338886261</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.59759950637817</t>
   </si>
   <si>
     <t xml:space="preserve">2.61710619926453</t>
@@ -533,58 +533,58 @@
     <t xml:space="preserve">2.63336157798767</t>
   </si>
   <si>
-    <t xml:space="preserve">2.6886293888092</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.6024763584137</t>
+    <t xml:space="preserve">2.68862962722778</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.60247611999512</t>
   </si>
   <si>
     <t xml:space="preserve">2.67725086212158</t>
   </si>
   <si>
-    <t xml:space="preserve">2.70976161956787</t>
+    <t xml:space="preserve">2.70976185798645</t>
   </si>
   <si>
     <t xml:space="preserve">2.7552764415741</t>
   </si>
   <si>
-    <t xml:space="preserve">2.72601628303528</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.72276544570923</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.82842516899109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.7438976764679</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.7617781162262</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.73902082443237</t>
+    <t xml:space="preserve">2.72601675987244</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.72276568412781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.82842540740967</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.74389719963074</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.76177835464478</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.73902106285095</t>
   </si>
   <si>
     <t xml:space="preserve">2.70488500595093</t>
   </si>
   <si>
-    <t xml:space="preserve">2.69025540351868</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.61222910881042</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.73251891136169</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.67562508583069</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.62360787391663</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.5943489074707</t>
+    <t xml:space="preserve">2.69025468826294</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.612229347229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.73251867294312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.67562484741211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.62360811233521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.59434866905212</t>
   </si>
   <si>
     <t xml:space="preserve">2.55371022224426</t>
@@ -596,16 +596,16 @@
     <t xml:space="preserve">2.51307201385498</t>
   </si>
   <si>
-    <t xml:space="preserve">2.46755743026733</t>
+    <t xml:space="preserve">2.46755719184875</t>
   </si>
   <si>
     <t xml:space="preserve">2.50169348716736</t>
   </si>
   <si>
-    <t xml:space="preserve">2.58459544181824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.63173604011536</t>
+    <t xml:space="preserve">2.58459520339966</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.63173580169678</t>
   </si>
   <si>
     <t xml:space="preserve">2.65611886978149</t>
@@ -614,70 +614,70 @@
     <t xml:space="preserve">2.66912317276001</t>
   </si>
   <si>
-    <t xml:space="preserve">2.72439098358154</t>
+    <t xml:space="preserve">2.72439122200012</t>
   </si>
   <si>
     <t xml:space="preserve">2.78291034698486</t>
   </si>
   <si>
-    <t xml:space="preserve">2.77153182029724</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.77803349494934</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.70000839233398</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.77315711975098</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.76502919197083</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.71788930892944</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.74552297592163</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.77965950965881</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.74714851379395</t>
+    <t xml:space="preserve">2.77153158187866</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.77803373336792</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.70000791549683</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.77315735816956</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.7650294303894</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.71788907051086</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.74552273750305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.77965927124023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.74714875221252</t>
   </si>
   <si>
     <t xml:space="preserve">2.60410189628601</t>
   </si>
   <si>
-    <t xml:space="preserve">2.62685966491699</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.64961647987366</t>
+    <t xml:space="preserve">2.62685894966125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.64961695671082</t>
   </si>
   <si>
     <t xml:space="preserve">2.69350600242615</t>
   </si>
   <si>
-    <t xml:space="preserve">2.69838261604309</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.92270612716675</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.88531899452209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.99910616874695</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.97472310066223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.96984624862671</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.96334457397461</t>
+    <t xml:space="preserve">2.69838237762451</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.92270565032959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.88531851768494</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.99910593032837</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.97472333908081</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.96984648704529</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.96334433555603</t>
   </si>
   <si>
     <t xml:space="preserve">2.94221210479736</t>
@@ -692,22 +692,22 @@
     <t xml:space="preserve">2.89182114601135</t>
   </si>
   <si>
-    <t xml:space="preserve">2.87881660461426</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.87556529045105</t>
+    <t xml:space="preserve">2.87881684303284</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.87556576728821</t>
   </si>
   <si>
     <t xml:space="preserve">2.84468030929565</t>
   </si>
   <si>
-    <t xml:space="preserve">2.82192277908325</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.84955716133118</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.91945481300354</t>
+    <t xml:space="preserve">2.82192301750183</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.84955739974976</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.9194552898407</t>
   </si>
   <si>
     <t xml:space="preserve">2.9259569644928</t>
@@ -716,22 +716,22 @@
     <t xml:space="preserve">2.99097871780396</t>
   </si>
   <si>
-    <t xml:space="preserve">2.91457867622375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.91620397567749</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.95846796035767</t>
+    <t xml:space="preserve">2.91457796096802</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.91620373725891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.95846772193909</t>
   </si>
   <si>
     <t xml:space="preserve">2.95684218406677</t>
   </si>
   <si>
-    <t xml:space="preserve">2.95196557044983</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.0494978427887</t>
+    <t xml:space="preserve">2.95196580886841</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.04949736595154</t>
   </si>
   <si>
     <t xml:space="preserve">3.0559995174408</t>
@@ -740,16 +740,16 @@
     <t xml:space="preserve">2.99585509300232</t>
   </si>
   <si>
-    <t xml:space="preserve">2.97959923744202</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.00723361968994</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.09645938873291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.11628723144531</t>
+    <t xml:space="preserve">2.97959971427917</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.00723385810852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.09645962715149</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.11628699302673</t>
   </si>
   <si>
     <t xml:space="preserve">3.16916179656982</t>
@@ -758,43 +758,43 @@
     <t xml:space="preserve">3.13941979408264</t>
   </si>
   <si>
-    <t xml:space="preserve">3.14437675476074</t>
+    <t xml:space="preserve">3.14437651634216</t>
   </si>
   <si>
     <t xml:space="preserve">3.18898940086365</t>
   </si>
   <si>
-    <t xml:space="preserve">3.18072772026062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.24847340583801</t>
+    <t xml:space="preserve">3.18072748184204</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.24847316741943</t>
   </si>
   <si>
     <t xml:space="preserve">3.21707916259766</t>
   </si>
   <si>
-    <t xml:space="preserve">3.16750979423523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.15429091453552</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.17081427574158</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.07663154602051</t>
+    <t xml:space="preserve">3.16750931739807</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.15429067611694</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.17081379890442</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.07663130760193</t>
   </si>
   <si>
     <t xml:space="preserve">3.07497882843018</t>
   </si>
   <si>
-    <t xml:space="preserve">2.98244857788086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.05845546722412</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.06506490707397</t>
+    <t xml:space="preserve">2.98244881629944</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.05845594406128</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.06506514549255</t>
   </si>
   <si>
     <t xml:space="preserve">3.03367066383362</t>
@@ -803,10 +803,10 @@
     <t xml:space="preserve">3.02540922164917</t>
   </si>
   <si>
-    <t xml:space="preserve">2.99401497840881</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.99071025848389</t>
+    <t xml:space="preserve">2.99401521682739</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.99071002006531</t>
   </si>
   <si>
     <t xml:space="preserve">2.99897217750549</t>
@@ -818,43 +818,43 @@
     <t xml:space="preserve">2.95601153373718</t>
   </si>
   <si>
-    <t xml:space="preserve">3.07993626594543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.08819794654846</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.08654522895813</t>
+    <t xml:space="preserve">3.07993602752686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.0881974697113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.08654546737671</t>
   </si>
   <si>
     <t xml:space="preserve">3.10802555084229</t>
   </si>
   <si>
-    <t xml:space="preserve">3.11133027076721</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.14768171310425</t>
+    <t xml:space="preserve">3.11133074760437</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.14768147468567</t>
   </si>
   <si>
     <t xml:space="preserve">3.16420483589172</t>
   </si>
   <si>
-    <t xml:space="preserve">3.20551300048828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.21377444267273</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.23029780387878</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.23360252380371</t>
+    <t xml:space="preserve">3.2055127620697</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.21377491950989</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.23029804229736</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.23360228538513</t>
   </si>
   <si>
     <t xml:space="preserve">3.25343012809753</t>
   </si>
   <si>
-    <t xml:space="preserve">3.29473805427551</t>
+    <t xml:space="preserve">3.29473829269409</t>
   </si>
   <si>
     <t xml:space="preserve">3.3079571723938</t>
@@ -866,7 +866,7 @@
     <t xml:space="preserve">3.29639077186584</t>
   </si>
   <si>
-    <t xml:space="preserve">3.22368788719177</t>
+    <t xml:space="preserve">3.22368812561035</t>
   </si>
   <si>
     <t xml:space="preserve">3.25012564659119</t>
@@ -878,34 +878,34 @@
     <t xml:space="preserve">3.26334404945374</t>
   </si>
   <si>
-    <t xml:space="preserve">3.09811186790466</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.15924739837646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.17246580123901</t>
+    <t xml:space="preserve">3.09811162948608</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.15924787521362</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.17246627807617</t>
   </si>
   <si>
     <t xml:space="preserve">3.17411875724792</t>
   </si>
   <si>
-    <t xml:space="preserve">3.15098595619202</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.05184650421143</t>
+    <t xml:space="preserve">3.15098643302917</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.05184626579285</t>
   </si>
   <si>
     <t xml:space="preserve">3.05680370330811</t>
   </si>
   <si>
-    <t xml:space="preserve">3.08489274978638</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.12785363197327</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.03201866149902</t>
+    <t xml:space="preserve">3.08489322662354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.12785339355469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.0320188999176</t>
   </si>
   <si>
     <t xml:space="preserve">3.09480690956116</t>
@@ -914,10 +914,10 @@
     <t xml:space="preserve">3.073326587677</t>
   </si>
   <si>
-    <t xml:space="preserve">3.09150266647339</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.13115859031677</t>
+    <t xml:space="preserve">3.09150218963623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.13115787506104</t>
   </si>
   <si>
     <t xml:space="preserve">3.10967779159546</t>
@@ -926,34 +926,34 @@
     <t xml:space="preserve">3.10472106933594</t>
   </si>
   <si>
-    <t xml:space="preserve">3.12124443054199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.13611507415771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.1460292339325</t>
+    <t xml:space="preserve">3.12124419212341</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.13611531257629</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.14602875709534</t>
   </si>
   <si>
     <t xml:space="preserve">3.12950587272644</t>
   </si>
   <si>
-    <t xml:space="preserve">3.14107227325439</t>
+    <t xml:space="preserve">3.14107203483582</t>
   </si>
   <si>
     <t xml:space="preserve">3.15759539604187</t>
   </si>
   <si>
-    <t xml:space="preserve">3.18403291702271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.10637331008911</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.08158850669861</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.10141634941101</t>
+    <t xml:space="preserve">3.18403267860413</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.10637307167053</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.08158826828003</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.10141587257385</t>
   </si>
   <si>
     <t xml:space="preserve">3.10306882858276</t>
@@ -965,10 +965,10 @@
     <t xml:space="preserve">3.08984994888306</t>
   </si>
   <si>
-    <t xml:space="preserve">2.94940233230591</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.93287920951843</t>
+    <t xml:space="preserve">2.94940209388733</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.93287873268127</t>
   </si>
   <si>
     <t xml:space="preserve">2.83704400062561</t>
@@ -977,16 +977,16 @@
     <t xml:space="preserve">2.88165688514709</t>
   </si>
   <si>
-    <t xml:space="preserve">2.90809392929077</t>
+    <t xml:space="preserve">2.90809416770935</t>
   </si>
   <si>
     <t xml:space="preserve">2.91139888763428</t>
   </si>
   <si>
-    <t xml:space="preserve">2.94609785079956</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.9411404132843</t>
+    <t xml:space="preserve">2.94609761238098</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.94114065170288</t>
   </si>
   <si>
     <t xml:space="preserve">2.96592569351196</t>
@@ -995,16 +995,16 @@
     <t xml:space="preserve">2.88496160507202</t>
   </si>
   <si>
-    <t xml:space="preserve">2.84034824371338</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.82878232002258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.81225943565369</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.88000464439392</t>
+    <t xml:space="preserve">2.84034848213196</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.82878255844116</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.81225895881653</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.88000440597534</t>
   </si>
   <si>
     <t xml:space="preserve">2.75112295150757</t>
@@ -1013,13 +1013,13 @@
     <t xml:space="preserve">2.80895471572876</t>
   </si>
   <si>
-    <t xml:space="preserve">2.79243111610413</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.8139111995697</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.85852432250977</t>
+    <t xml:space="preserve">2.79243135452271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.81391143798828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.85852456092834</t>
   </si>
   <si>
     <t xml:space="preserve">2.97418713569641</t>
@@ -1028,7 +1028,7 @@
     <t xml:space="preserve">2.97088217735291</t>
   </si>
   <si>
-    <t xml:space="preserve">3.01549553871155</t>
+    <t xml:space="preserve">3.01549530029297</t>
   </si>
   <si>
     <t xml:space="preserve">3.05515098571777</t>
@@ -1037,16 +1037,16 @@
     <t xml:space="preserve">3.04028058052063</t>
   </si>
   <si>
-    <t xml:space="preserve">3.07002210617065</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.06341290473938</t>
+    <t xml:space="preserve">3.07002186775208</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.0634126663208</t>
   </si>
   <si>
     <t xml:space="preserve">3.02375721931458</t>
   </si>
   <si>
-    <t xml:space="preserve">3.0369758605957</t>
+    <t xml:space="preserve">3.03697538375854</t>
   </si>
   <si>
     <t xml:space="preserve">3.0287139415741</t>
@@ -1055,46 +1055,46 @@
     <t xml:space="preserve">3.05349898338318</t>
   </si>
   <si>
-    <t xml:space="preserve">3.07828402519226</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.1105043888092</t>
+    <t xml:space="preserve">3.07828378677368</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.11050415039062</t>
   </si>
   <si>
     <t xml:space="preserve">3.06919574737549</t>
   </si>
   <si>
-    <t xml:space="preserve">3.1559431552887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.21790504455566</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.17659735679626</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.19312047958374</t>
+    <t xml:space="preserve">3.15594291687012</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.21790528297424</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.17659687995911</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.19312024116516</t>
   </si>
   <si>
     <t xml:space="preserve">3.25508260726929</t>
   </si>
   <si>
-    <t xml:space="preserve">3.22203612327576</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.96179437637329</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.97831773757935</t>
+    <t xml:space="preserve">3.22203636169434</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.96179509162903</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.97831797599792</t>
   </si>
   <si>
     <t xml:space="preserve">2.92461729049683</t>
   </si>
   <si>
-    <t xml:space="preserve">2.87504768371582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.13528895378113</t>
+    <t xml:space="preserve">2.8750479221344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.13528919219971</t>
   </si>
   <si>
     <t xml:space="preserve">3.07745742797852</t>
@@ -1103,13 +1103,13 @@
     <t xml:space="preserve">3.05267262458801</t>
   </si>
   <si>
-    <t xml:space="preserve">3.03614926338196</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.92048668861389</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.08571887016296</t>
+    <t xml:space="preserve">3.03614974021912</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.92048645019531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.08571910858154</t>
   </si>
   <si>
     <t xml:space="preserve">3.01962614059448</t>
@@ -1118,58 +1118,58 @@
     <t xml:space="preserve">3.02788758277893</t>
   </si>
   <si>
-    <t xml:space="preserve">3.04854202270508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.04441094398499</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.15181255340576</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.3376989364624</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.25095152854919</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.27573704719543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.28399801254272</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.24682140350342</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.18485879898071</t>
+    <t xml:space="preserve">3.0485417842865</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.04441070556641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.15181231498718</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.33769869804382</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.25095176696777</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.27573680877686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.2839982509613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.24682116508484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.18485856056213</t>
   </si>
   <si>
     <t xml:space="preserve">3.2437379360199</t>
   </si>
   <si>
-    <t xml:space="preserve">3.20177507400513</t>
+    <t xml:space="preserve">3.20177483558655</t>
   </si>
   <si>
     <t xml:space="preserve">3.2101674079895</t>
   </si>
   <si>
-    <t xml:space="preserve">3.18918609619141</t>
+    <t xml:space="preserve">3.18918585777283</t>
   </si>
   <si>
     <t xml:space="preserve">3.22275638580322</t>
   </si>
   <si>
-    <t xml:space="preserve">3.16400837898254</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.0884747505188</t>
+    <t xml:space="preserve">3.16400790214539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.08847498893738</t>
   </si>
   <si>
     <t xml:space="preserve">3.12204527854919</t>
   </si>
   <si>
-    <t xml:space="preserve">3.14302682876587</t>
+    <t xml:space="preserve">3.14302659034729</t>
   </si>
   <si>
     <t xml:space="preserve">3.20597100257874</t>
@@ -1178,7 +1178,7 @@
     <t xml:space="preserve">3.25632667541504</t>
   </si>
   <si>
-    <t xml:space="preserve">3.24793410301208</t>
+    <t xml:space="preserve">3.24793434143066</t>
   </si>
   <si>
     <t xml:space="preserve">3.10525989532471</t>
@@ -1193,28 +1193,28 @@
     <t xml:space="preserve">3.11365246772766</t>
   </si>
   <si>
-    <t xml:space="preserve">3.1262412071228</t>
+    <t xml:space="preserve">3.12624144554138</t>
   </si>
   <si>
     <t xml:space="preserve">3.1388304233551</t>
   </si>
   <si>
-    <t xml:space="preserve">3.14722299575806</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.15561580657959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.1724009513855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.08427858352661</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.13463377952576</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.16820454597473</t>
+    <t xml:space="preserve">3.14722323417664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.15561556816101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.17240071296692</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.08427882194519</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.13463401794434</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.16820478439331</t>
   </si>
   <si>
     <t xml:space="preserve">3.10945653915405</t>
@@ -1223,10 +1223,10 @@
     <t xml:space="preserve">3.15981197357178</t>
   </si>
   <si>
-    <t xml:space="preserve">3.19338250160217</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.21436405181885</t>
+    <t xml:space="preserve">3.19338226318359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.21436381340027</t>
   </si>
   <si>
     <t xml:space="preserve">3.23534536361694</t>
@@ -1235,10 +1235,10 @@
     <t xml:space="preserve">3.26471948623657</t>
   </si>
   <si>
-    <t xml:space="preserve">3.32346749305725</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.31087827682495</t>
+    <t xml:space="preserve">3.32346773147583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.31087851524353</t>
   </si>
   <si>
     <t xml:space="preserve">3.27730822563171</t>
@@ -1247,7 +1247,7 @@
     <t xml:space="preserve">3.35703778266907</t>
   </si>
   <si>
-    <t xml:space="preserve">3.42417883872986</t>
+    <t xml:space="preserve">3.42417860031128</t>
   </si>
   <si>
     <t xml:space="preserve">3.49131917953491</t>
@@ -1259,16 +1259,16 @@
     <t xml:space="preserve">3.54167485237122</t>
   </si>
   <si>
-    <t xml:space="preserve">3.44935655593872</t>
+    <t xml:space="preserve">3.44935631752014</t>
   </si>
   <si>
     <t xml:space="preserve">3.48292684555054</t>
   </si>
   <si>
-    <t xml:space="preserve">3.51649761199951</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.47453451156616</t>
+    <t xml:space="preserve">3.51649713516235</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.47453427314758</t>
   </si>
   <si>
     <t xml:space="preserve">3.4577488899231</t>
@@ -1277,13 +1277,13 @@
     <t xml:space="preserve">3.3864119052887</t>
   </si>
   <si>
-    <t xml:space="preserve">3.37801933288574</t>
+    <t xml:space="preserve">3.37801957130432</t>
   </si>
   <si>
     <t xml:space="preserve">3.4703381061554</t>
   </si>
   <si>
-    <t xml:space="preserve">3.30248618125916</t>
+    <t xml:space="preserve">3.30248594284058</t>
   </si>
   <si>
     <t xml:space="preserve">3.31927108764648</t>
@@ -1292,13 +1292,13 @@
     <t xml:space="preserve">3.29828977584839</t>
   </si>
   <si>
-    <t xml:space="preserve">3.34025287628174</t>
+    <t xml:space="preserve">3.34025263786316</t>
   </si>
   <si>
     <t xml:space="preserve">3.27311229705811</t>
   </si>
   <si>
-    <t xml:space="preserve">3.28150486946106</t>
+    <t xml:space="preserve">3.28150463104248</t>
   </si>
   <si>
     <t xml:space="preserve">3.399001121521</t>
@@ -1310,7 +1310,7 @@
     <t xml:space="preserve">3.58783459663391</t>
   </si>
   <si>
-    <t xml:space="preserve">3.55006790161133</t>
+    <t xml:space="preserve">3.55006742477417</t>
   </si>
   <si>
     <t xml:space="preserve">3.5794415473938</t>
@@ -1319,25 +1319,25 @@
     <t xml:space="preserve">3.58363819122314</t>
   </si>
   <si>
-    <t xml:space="preserve">3.66336727142334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.5584602355957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.56685280799866</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.62140488624573</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.78086423873901</t>
+    <t xml:space="preserve">3.66336750984192</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.55845975875854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.56685256958008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.62140464782715</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.78086376190186</t>
   </si>
   <si>
     <t xml:space="preserve">3.88577175140381</t>
   </si>
   <si>
-    <t xml:space="preserve">3.72211575508118</t>
+    <t xml:space="preserve">3.72211599349976</t>
   </si>
   <si>
     <t xml:space="preserve">3.76407885551453</t>
@@ -1346,25 +1346,25 @@
     <t xml:space="preserve">3.68434906005859</t>
   </si>
   <si>
-    <t xml:space="preserve">3.79764986038208</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.82702326774597</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.80184602737427</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.83961224555969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.91934180259705</t>
+    <t xml:space="preserve">3.7976496219635</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.82702350616455</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.80184555053711</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.83961248397827</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.91934156417847</t>
   </si>
   <si>
     <t xml:space="preserve">3.91094899177551</t>
   </si>
   <si>
-    <t xml:space="preserve">3.94451904296875</t>
+    <t xml:space="preserve">3.94451951980591</t>
   </si>
   <si>
     <t xml:space="preserve">4.06621217727661</t>
@@ -1373,49 +1373,49 @@
     <t xml:space="preserve">4.02005290985107</t>
   </si>
   <si>
-    <t xml:space="preserve">3.92773413658142</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.8689866065979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.8186309337616</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.86059331893921</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.79345297813416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.86478996276855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.87737846374512</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.73470449447632</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.84380865097046</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.69274163246155</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.90255665779114</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.9529116153717</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.99067854881287</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.00326824188232</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.91514587402344</t>
+    <t xml:space="preserve">3.92773389816284</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.86898612976074</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.81863069534302</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.86059379577637</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.793452501297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.86478972434998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.8773787021637</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.73470497131348</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.8438081741333</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.69274210929871</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.9025571346283</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.95291233062744</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.99067902565002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.00326776504517</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.91514539718628</t>
   </si>
   <si>
     <t xml:space="preserve">3.87318229675293</t>
@@ -1424,82 +1424,82 @@
     <t xml:space="preserve">3.85220122337341</t>
   </si>
   <si>
-    <t xml:space="preserve">3.66756367683411</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.6759569644928</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.59203052520752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.53328251838684</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.70533084869385</t>
+    <t xml:space="preserve">3.66756391525269</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.67595672607422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.5920307636261</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.53328275680542</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.70533061027527</t>
   </si>
   <si>
     <t xml:space="preserve">3.6423864364624</t>
   </si>
   <si>
-    <t xml:space="preserve">3.77666807174683</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.71791958808899</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.64658260345459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.7011342048645</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.68015289306641</t>
+    <t xml:space="preserve">3.77666759490967</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.71791887283325</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.64658212661743</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.70113396644592</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.68015313148499</t>
   </si>
   <si>
     <t xml:space="preserve">3.80604147911072</t>
   </si>
   <si>
-    <t xml:space="preserve">3.78505992889404</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.69693851470947</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.73050880432129</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.7472939491272</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.65077877044678</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.65917158126831</t>
+    <t xml:space="preserve">3.78506064414978</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.69693803787231</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.73050832748413</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.74729418754578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.6507785320282</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.65917134284973</t>
   </si>
   <si>
     <t xml:space="preserve">3.85639715194702</t>
   </si>
   <si>
-    <t xml:space="preserve">3.89416432380676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.93612742424011</t>
+    <t xml:space="preserve">3.89416360855103</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.93612694740295</t>
   </si>
   <si>
     <t xml:space="preserve">4.00746393203735</t>
   </si>
   <si>
-    <t xml:space="preserve">4.08719348907471</t>
+    <t xml:space="preserve">4.08719396591187</t>
   </si>
   <si>
     <t xml:space="preserve">4.11237144470215</t>
   </si>
   <si>
-    <t xml:space="preserve">4.17111921310425</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.19629764556885</t>
+    <t xml:space="preserve">4.17111968994141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.19629716873169</t>
   </si>
   <si>
     <t xml:space="preserve">4.2382607460022</t>
@@ -1508,79 +1508,79 @@
     <t xml:space="preserve">4.18790435791016</t>
   </si>
   <si>
-    <t xml:space="preserve">4.09978294372559</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.09558629989624</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.07880163192749</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.14594221115112</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.09139013290405</t>
+    <t xml:space="preserve">4.09978246688843</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.0955867767334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.07880067825317</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.14594173431396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.09138965606689</t>
   </si>
   <si>
     <t xml:space="preserve">4.08299684524536</t>
   </si>
   <si>
-    <t xml:space="preserve">4.06201553344727</t>
+    <t xml:space="preserve">4.06201648712158</t>
   </si>
   <si>
     <t xml:space="preserve">4.26343822479248</t>
   </si>
   <si>
-    <t xml:space="preserve">4.39771938323975</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.52360868453979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.49843120574951</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.58235692977905</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.4816460609436</t>
+    <t xml:space="preserve">4.3977198600769</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.52360820770264</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.49843072891235</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.58235645294189</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.48164558410645</t>
   </si>
   <si>
     <t xml:space="preserve">4.62431955337524</t>
   </si>
   <si>
-    <t xml:space="preserve">4.67467546463013</t>
+    <t xml:space="preserve">4.67467498779297</t>
   </si>
   <si>
     <t xml:space="preserve">4.69985246658325</t>
   </si>
   <si>
-    <t xml:space="preserve">4.6830677986145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.66628217697144</t>
+    <t xml:space="preserve">4.68306732177734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.66628265380859</t>
   </si>
   <si>
     <t xml:space="preserve">4.63271236419678</t>
   </si>
   <si>
-    <t xml:space="preserve">4.44807529449463</t>
+    <t xml:space="preserve">4.44807577133179</t>
   </si>
   <si>
     <t xml:space="preserve">4.4396824836731</t>
   </si>
   <si>
-    <t xml:space="preserve">4.47325277328491</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.49003744125366</t>
+    <t xml:space="preserve">4.47325229644775</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.49003887176514</t>
   </si>
   <si>
     <t xml:space="preserve">4.54878616333008</t>
   </si>
   <si>
-    <t xml:space="preserve">4.59914112091064</t>
+    <t xml:space="preserve">4.59914207458496</t>
   </si>
   <si>
     <t xml:space="preserve">4.61592721939087</t>
@@ -1589,22 +1589,22 @@
     <t xml:space="preserve">4.60753440856934</t>
   </si>
   <si>
-    <t xml:space="preserve">4.40611267089844</t>
+    <t xml:space="preserve">4.40611171722412</t>
   </si>
   <si>
     <t xml:space="preserve">4.53200101852417</t>
   </si>
   <si>
-    <t xml:space="preserve">4.75860071182251</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.80895614624023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.7418155670166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.69146013259888</t>
+    <t xml:space="preserve">4.75860166549683</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.80895709991455</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.74181604385376</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.69146108627319</t>
   </si>
   <si>
     <t xml:space="preserve">4.65788984298706</t>
@@ -1616,22 +1616,22 @@
     <t xml:space="preserve">4.5403938293457</t>
   </si>
   <si>
-    <t xml:space="preserve">4.4648609161377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.41450452804565</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.38932704925537</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.38093423843384</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.34736394882202</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.46764659881592</t>
+    <t xml:space="preserve">4.46486043930054</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.41450500488281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.38932752609253</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.38093376159668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.34736347198486</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.46764707565308</t>
   </si>
   <si>
     <t xml:space="preserve">4.51919651031494</t>
@@ -1640,10 +1640,10 @@
     <t xml:space="preserve">4.39891386032104</t>
   </si>
   <si>
-    <t xml:space="preserve">4.37313890457153</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.30440616607666</t>
+    <t xml:space="preserve">4.37313842773438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.3044056892395</t>
   </si>
   <si>
     <t xml:space="preserve">4.27003955841064</t>
@@ -1658,82 +1658,79 @@
     <t xml:space="preserve">4.38173055648804</t>
   </si>
   <si>
-    <t xml:space="preserve">4.34736347198486</t>
-  </si>
-  <si>
     <t xml:space="preserve">4.44187211990356</t>
   </si>
   <si>
-    <t xml:space="preserve">4.45905494689941</t>
+    <t xml:space="preserve">4.45905542373657</t>
   </si>
   <si>
     <t xml:space="preserve">4.35595560073853</t>
   </si>
   <si>
-    <t xml:space="preserve">4.39032220840454</t>
+    <t xml:space="preserve">4.3903226852417</t>
   </si>
   <si>
     <t xml:space="preserve">4.45046329498291</t>
   </si>
   <si>
-    <t xml:space="preserve">4.41609621047974</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.23137712478638</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.26574325561523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.13257360458374</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.04665660858154</t>
+    <t xml:space="preserve">4.41609668731689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.23137664794922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.26574373245239</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.13257265090942</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.0466570854187</t>
   </si>
   <si>
     <t xml:space="preserve">4.08531951904297</t>
   </si>
   <si>
-    <t xml:space="preserve">3.98222064971924</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.0337700843811</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.94785284996033</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.99081134796143</t>
+    <t xml:space="preserve">3.9822199344635</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.03376960754395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.94785332679749</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.99081158638</t>
   </si>
   <si>
     <t xml:space="preserve">3.98651552200317</t>
   </si>
   <si>
-    <t xml:space="preserve">3.94355702400208</t>
+    <t xml:space="preserve">3.94355773925781</t>
   </si>
   <si>
     <t xml:space="preserve">3.96503615379333</t>
   </si>
   <si>
-    <t xml:space="preserve">3.96074104309082</t>
+    <t xml:space="preserve">3.96074056625366</t>
   </si>
   <si>
     <t xml:space="preserve">4.01229047775269</t>
   </si>
   <si>
-    <t xml:space="preserve">3.9263744354248</t>
+    <t xml:space="preserve">3.92637419700623</t>
   </si>
   <si>
     <t xml:space="preserve">4.07243204116821</t>
   </si>
   <si>
-    <t xml:space="preserve">4.08961534500122</t>
+    <t xml:space="preserve">4.08961486816406</t>
   </si>
   <si>
     <t xml:space="preserve">4.11109399795532</t>
   </si>
   <si>
-    <t xml:space="preserve">4.26144742965698</t>
+    <t xml:space="preserve">4.2614483833313</t>
   </si>
   <si>
     <t xml:space="preserve">4.32158899307251</t>
@@ -1745,7 +1742,7 @@
     <t xml:space="preserve">4.02947378158569</t>
   </si>
   <si>
-    <t xml:space="preserve">3.84045815467834</t>
+    <t xml:space="preserve">3.84045767784119</t>
   </si>
   <si>
     <t xml:space="preserve">3.87482452392578</t>
@@ -1754,40 +1751,40 @@
     <t xml:space="preserve">3.88771200180054</t>
   </si>
   <si>
-    <t xml:space="preserve">4.00369930267334</t>
+    <t xml:space="preserve">4.00369882583618</t>
   </si>
   <si>
     <t xml:space="preserve">4.02088212966919</t>
   </si>
   <si>
-    <t xml:space="preserve">3.93496584892273</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.8662326335907</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.77172517776489</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.71587944030762</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.70299196243286</t>
+    <t xml:space="preserve">3.93496561050415</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.86623287200928</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.77172493934631</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.71587920188904</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.70299172401428</t>
   </si>
   <si>
     <t xml:space="preserve">3.67721724510193</t>
   </si>
   <si>
-    <t xml:space="preserve">3.68580842018127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.70728778839111</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.66432976722717</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.66003394126892</t>
+    <t xml:space="preserve">3.6858081817627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.70728754997253</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.66432952880859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.6600341796875</t>
   </si>
   <si>
     <t xml:space="preserve">3.72017502784729</t>
@@ -1796,31 +1793,31 @@
     <t xml:space="preserve">3.81468319892883</t>
   </si>
   <si>
-    <t xml:space="preserve">3.95214939117432</t>
+    <t xml:space="preserve">3.9521484375</t>
   </si>
   <si>
     <t xml:space="preserve">3.85764098167419</t>
   </si>
   <si>
-    <t xml:space="preserve">3.78461313247681</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.8447539806366</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.7803168296814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.69440102577209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.73306250572205</t>
+    <t xml:space="preserve">3.78461265563965</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.84475374221802</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.78031659126282</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.69440031051636</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.73306226730347</t>
   </si>
   <si>
     <t xml:space="preserve">3.71158385276794</t>
   </si>
   <si>
-    <t xml:space="preserve">3.59989261627197</t>
+    <t xml:space="preserve">3.59989237785339</t>
   </si>
   <si>
     <t xml:space="preserve">3.75454163551331</t>
@@ -1832,91 +1829,91 @@
     <t xml:space="preserve">3.72447109222412</t>
   </si>
   <si>
-    <t xml:space="preserve">3.78890800476074</t>
+    <t xml:space="preserve">3.78890776634216</t>
   </si>
   <si>
     <t xml:space="preserve">3.64714622497559</t>
   </si>
   <si>
-    <t xml:space="preserve">3.66862559318542</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.67292141914368</t>
+    <t xml:space="preserve">3.66862535476685</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.6729211807251</t>
   </si>
   <si>
     <t xml:space="preserve">3.6170756816864</t>
   </si>
   <si>
-    <t xml:space="preserve">3.57411742210388</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.64285063743591</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.65573811531067</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.62996292114258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.96933245658875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.95644521713257</t>
+    <t xml:space="preserve">3.5741171836853</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.64284992218018</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.65573835372925</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.629962682724</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.96933221817017</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.95644450187683</t>
   </si>
   <si>
     <t xml:space="preserve">3.90059924125671</t>
   </si>
   <si>
-    <t xml:space="preserve">3.9306697845459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.01658630371094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.09820699691772</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.14116477966309</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.24426460266113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.24856090545654</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.43328046798706</t>
+    <t xml:space="preserve">3.93067002296448</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.01658582687378</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.09820652008057</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.14116525650024</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.24426412582397</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.24855995178223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.4332799911499</t>
   </si>
   <si>
     <t xml:space="preserve">4.4246883392334</t>
   </si>
   <si>
-    <t xml:space="preserve">4.58792924880981</t>
+    <t xml:space="preserve">4.58792972564697</t>
   </si>
   <si>
     <t xml:space="preserve">4.57933759689331</t>
   </si>
   <si>
-    <t xml:space="preserve">4.49342203140259</t>
+    <t xml:space="preserve">4.49342155456543</t>
   </si>
   <si>
     <t xml:space="preserve">4.55356311798096</t>
   </si>
   <si>
-    <t xml:space="preserve">4.48482990264893</t>
+    <t xml:space="preserve">4.48482942581177</t>
   </si>
   <si>
     <t xml:space="preserve">4.53637981414795</t>
   </si>
   <si>
-    <t xml:space="preserve">4.59652090072632</t>
+    <t xml:space="preserve">4.59652137756348</t>
   </si>
   <si>
     <t xml:space="preserve">4.77694511413574</t>
   </si>
   <si>
-    <t xml:space="preserve">4.81131219863892</t>
+    <t xml:space="preserve">4.81131172180176</t>
   </si>
   <si>
     <t xml:space="preserve">4.69962072372437</t>
@@ -1931,13 +1928,13 @@
     <t xml:space="preserve">4.71680355072021</t>
   </si>
   <si>
-    <t xml:space="preserve">4.6910285949707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.6824369430542</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.70821237564087</t>
+    <t xml:space="preserve">4.69102907180786</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.68243741989136</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.70821285247803</t>
   </si>
   <si>
     <t xml:space="preserve">4.67384624481201</t>
@@ -1949,52 +1946,52 @@
     <t xml:space="preserve">4.50201320648193</t>
   </si>
   <si>
-    <t xml:space="preserve">4.54497098922729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.51060438156128</t>
+    <t xml:space="preserve">4.54497146606445</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.51060485839844</t>
   </si>
   <si>
     <t xml:space="preserve">4.52778768539429</t>
   </si>
   <si>
-    <t xml:space="preserve">4.7683539390564</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.66525363922119</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.61370420455933</t>
+    <t xml:space="preserve">4.76835346221924</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.66525411605835</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.61370468139648</t>
   </si>
   <si>
     <t xml:space="preserve">4.73398733139038</t>
   </si>
   <si>
-    <t xml:space="preserve">4.63947916030884</t>
+    <t xml:space="preserve">4.639479637146</t>
   </si>
   <si>
     <t xml:space="preserve">4.23567247390747</t>
   </si>
   <si>
-    <t xml:space="preserve">4.15834808349609</t>
+    <t xml:space="preserve">4.15834856033325</t>
   </si>
   <si>
     <t xml:space="preserve">4.20130634307861</t>
   </si>
   <si>
-    <t xml:space="preserve">4.36454725265503</t>
+    <t xml:space="preserve">4.36454677581787</t>
   </si>
   <si>
     <t xml:space="preserve">4.60511302947998</t>
   </si>
   <si>
-    <t xml:space="preserve">4.11538982391357</t>
+    <t xml:space="preserve">4.11539030075073</t>
   </si>
   <si>
     <t xml:space="preserve">3.75024557113647</t>
   </si>
   <si>
-    <t xml:space="preserve">3.47101783752441</t>
+    <t xml:space="preserve">3.47101759910583</t>
   </si>
   <si>
     <t xml:space="preserve">3.36362266540527</t>
@@ -2006,58 +2003,58 @@
     <t xml:space="preserve">3.16601490974426</t>
   </si>
   <si>
-    <t xml:space="preserve">3.22186064720154</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.80516695976257</t>
+    <t xml:space="preserve">3.22186040878296</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.80516624450684</t>
   </si>
   <si>
     <t xml:space="preserve">2.91685771942139</t>
   </si>
   <si>
-    <t xml:space="preserve">2.86530828475952</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.8867871761322</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.73213815689087</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.66770052909851</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.80087065696716</t>
+    <t xml:space="preserve">2.86530804634094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.88678693771362</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.73213791847229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.66770076751709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.80087113380432</t>
   </si>
   <si>
     <t xml:space="preserve">2.61185479164124</t>
   </si>
   <si>
-    <t xml:space="preserve">2.72354602813721</t>
+    <t xml:space="preserve">2.72354626655579</t>
   </si>
   <si>
     <t xml:space="preserve">2.92115378379822</t>
   </si>
   <si>
-    <t xml:space="preserve">2.81375813484192</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.70206713676453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.65910887718201</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.84382891654968</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.76650428771973</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.78798365592957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.70636320114136</t>
+    <t xml:space="preserve">2.8137583732605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.70206737518311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.65910911560059</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.84382915496826</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.76650452613831</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.78798317909241</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.7063627243042</t>
   </si>
   <si>
     <t xml:space="preserve">2.71065855026245</t>
@@ -2066,25 +2063,25 @@
     <t xml:space="preserve">2.85242056846619</t>
   </si>
   <si>
-    <t xml:space="preserve">2.89108300209045</t>
+    <t xml:space="preserve">2.89108276367188</t>
   </si>
   <si>
     <t xml:space="preserve">2.92974519729614</t>
   </si>
   <si>
-    <t xml:space="preserve">3.0070698261261</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.96411156654358</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.93833684921265</t>
+    <t xml:space="preserve">3.00706958770752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.96411228179932</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.93833708763123</t>
   </si>
   <si>
     <t xml:space="preserve">2.9426326751709</t>
   </si>
   <si>
-    <t xml:space="preserve">2.98129487037659</t>
+    <t xml:space="preserve">2.98129510879517</t>
   </si>
   <si>
     <t xml:space="preserve">3.01136565208435</t>
@@ -2099,142 +2096,142 @@
     <t xml:space="preserve">2.95122408866882</t>
   </si>
   <si>
-    <t xml:space="preserve">3.10587358474731</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.04143619537354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.05002784729004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.08439421653748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.13164830207825</t>
+    <t xml:space="preserve">3.10587334632874</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.04143643379211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.05002808570862</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.08439469337463</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.13164854049683</t>
   </si>
   <si>
     <t xml:space="preserve">3.03284478187561</t>
   </si>
   <si>
-    <t xml:space="preserve">3.09298634529114</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.19178986549377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.24763560295105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.16171884536743</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.14883184432983</t>
+    <t xml:space="preserve">3.09298610687256</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.19179010391235</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.24763512611389</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.16171956062317</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.14883160591125</t>
   </si>
   <si>
     <t xml:space="preserve">3.18319845199585</t>
   </si>
   <si>
-    <t xml:space="preserve">3.13594460487366</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.11876106262207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.30777668952942</t>
+    <t xml:space="preserve">3.1359441280365</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.11876130104065</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.30777645111084</t>
   </si>
   <si>
     <t xml:space="preserve">3.38510179519653</t>
   </si>
   <si>
-    <t xml:space="preserve">3.43665146827698</t>
+    <t xml:space="preserve">3.4366512298584</t>
   </si>
   <si>
     <t xml:space="preserve">3.48390531539917</t>
   </si>
   <si>
-    <t xml:space="preserve">3.46242642402649</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.47960948944092</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.31636881828308</t>
+    <t xml:space="preserve">3.46242666244507</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.4796097278595</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.31636834144592</t>
   </si>
   <si>
     <t xml:space="preserve">3.29488968849182</t>
   </si>
   <si>
-    <t xml:space="preserve">3.19608545303345</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.3808057308197</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.37651014328003</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.3507354259491</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.37221431732178</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.42806005477905</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.44094753265381</t>
+    <t xml:space="preserve">3.19608569145203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.38080596923828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.37650990486145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.35073518753052</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.37221384048462</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.42805957794189</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.44094729423523</t>
   </si>
   <si>
     <t xml:space="preserve">3.44524312019348</t>
   </si>
   <si>
-    <t xml:space="preserve">3.75857472419739</t>
+    <t xml:space="preserve">3.75857448577881</t>
   </si>
   <si>
     <t xml:space="preserve">3.71435594558716</t>
   </si>
   <si>
-    <t xml:space="preserve">3.63034105300903</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.58170080184937</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.51979494094849</t>
+    <t xml:space="preserve">3.63034129142761</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.58170104026794</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.51979470252991</t>
   </si>
   <si>
     <t xml:space="preserve">3.50210738182068</t>
   </si>
   <si>
-    <t xml:space="preserve">3.43135762214661</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.44904541969299</t>
+    <t xml:space="preserve">3.43135786056519</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.44904494285583</t>
   </si>
   <si>
     <t xml:space="preserve">3.36060810089111</t>
   </si>
   <si>
-    <t xml:space="preserve">3.38713932037354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.4180920124054</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.32081151008606</t>
+    <t xml:space="preserve">3.38713884353638</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.41809225082397</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.32081127166748</t>
   </si>
   <si>
     <t xml:space="preserve">3.33849883079529</t>
   </si>
   <si>
-    <t xml:space="preserve">3.31638956069946</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.27217078208923</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.28101444244385</t>
+    <t xml:space="preserve">3.31638979911804</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.27217125892639</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.28101468086243</t>
   </si>
   <si>
     <t xml:space="preserve">3.22795248031616</t>
@@ -2246,34 +2243,34 @@
     <t xml:space="preserve">3.18373394012451</t>
   </si>
   <si>
-    <t xml:space="preserve">3.25448322296143</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.20584321022034</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.1660463809967</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.15720272064209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.13951516151428</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.10414028167725</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.09971880912781</t>
+    <t xml:space="preserve">3.25448369979858</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.20584297180176</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.16604661941528</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.15720248222351</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.13951539993286</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.10414052009583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.09971857070923</t>
   </si>
   <si>
     <t xml:space="preserve">3.04223465919495</t>
   </si>
   <si>
-    <t xml:space="preserve">3.04665613174438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.07760953903198</t>
+    <t xml:space="preserve">3.04665637016296</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.0776093006134</t>
   </si>
   <si>
     <t xml:space="preserve">3.05992197990417</t>
@@ -2282,7 +2279,7 @@
     <t xml:space="preserve">2.98032855987549</t>
   </si>
   <si>
-    <t xml:space="preserve">2.96264123916626</t>
+    <t xml:space="preserve">2.96264147758484</t>
   </si>
   <si>
     <t xml:space="preserve">2.94495368003845</t>
@@ -2294,10 +2291,10 @@
     <t xml:space="preserve">3.09087514877319</t>
   </si>
   <si>
-    <t xml:space="preserve">3.06876564025879</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.05550026893616</t>
+    <t xml:space="preserve">3.06876587867737</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.05550003051758</t>
   </si>
   <si>
     <t xml:space="preserve">2.98475050926208</t>
@@ -2306,10 +2303,10 @@
     <t xml:space="preserve">2.90515732765198</t>
   </si>
   <si>
-    <t xml:space="preserve">2.83440780639648</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.86978244781494</t>
+    <t xml:space="preserve">2.83440756797791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.86978220939636</t>
   </si>
   <si>
     <t xml:space="preserve">2.80345439910889</t>
@@ -2321,52 +2318,52 @@
     <t xml:space="preserve">2.81229853630066</t>
   </si>
   <si>
-    <t xml:space="preserve">2.84767317771912</t>
+    <t xml:space="preserve">2.84767293930054</t>
   </si>
   <si>
     <t xml:space="preserve">2.82998561859131</t>
   </si>
   <si>
-    <t xml:space="preserve">2.79461097717285</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.91842269897461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.82114219665527</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.79903268814087</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.80787658691406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.75923585891724</t>
+    <t xml:space="preserve">2.79461073875427</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.91842293739319</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.82114195823669</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.79903292655945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.80787634849548</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.75923609733582</t>
   </si>
   <si>
     <t xml:space="preserve">2.72386121749878</t>
   </si>
   <si>
-    <t xml:space="preserve">2.71501731872559</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.6840648651123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.63542413711548</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.61773705482483</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.58236169815063</t>
+    <t xml:space="preserve">2.71501755714417</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.68406462669373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.63542437553406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.61773681640625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.58236217498779</t>
   </si>
   <si>
     <t xml:space="preserve">2.54698705673218</t>
   </si>
   <si>
-    <t xml:space="preserve">2.56467461585999</t>
+    <t xml:space="preserve">2.56467437744141</t>
   </si>
   <si>
     <t xml:space="preserve">2.5514087677002</t>
@@ -2378,7 +2375,7 @@
     <t xml:space="preserve">2.5735182762146</t>
   </si>
   <si>
-    <t xml:space="preserve">2.97148489952087</t>
+    <t xml:space="preserve">2.97148466110229</t>
   </si>
   <si>
     <t xml:space="preserve">2.95379734039307</t>
@@ -2390,22 +2387,22 @@
     <t xml:space="preserve">3.17931199073792</t>
   </si>
   <si>
-    <t xml:space="preserve">3.17046856880188</t>
+    <t xml:space="preserve">3.1704683303833</t>
   </si>
   <si>
     <t xml:space="preserve">3.19257760047913</t>
   </si>
   <si>
-    <t xml:space="preserve">3.28985810279846</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.29870200157166</t>
+    <t xml:space="preserve">3.28985857963562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.29870223999023</t>
   </si>
   <si>
     <t xml:space="preserve">3.47999811172485</t>
   </si>
   <si>
-    <t xml:space="preserve">3.41367053985596</t>
+    <t xml:space="preserve">3.4136700630188</t>
   </si>
   <si>
     <t xml:space="preserve">3.48442006111145</t>
@@ -2414,40 +2411,40 @@
     <t xml:space="preserve">3.45788884162903</t>
   </si>
   <si>
-    <t xml:space="preserve">3.49326372146606</t>
+    <t xml:space="preserve">3.49326348304749</t>
   </si>
   <si>
     <t xml:space="preserve">3.51095080375671</t>
   </si>
   <si>
-    <t xml:space="preserve">3.44462323188782</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.42693614959717</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.55516958236694</t>
+    <t xml:space="preserve">3.44462299346924</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.42693567276001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.55516934394836</t>
   </si>
   <si>
     <t xml:space="preserve">3.6789813041687</t>
   </si>
   <si>
-    <t xml:space="preserve">3.72320032119751</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.74973130226135</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.80279397964478</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.65687251091003</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.66129398345947</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.65245032310486</t>
+    <t xml:space="preserve">3.72320008277893</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.74973058700562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.80279326438904</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.65687227249146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.66129374504089</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.65245056152344</t>
   </si>
   <si>
     <t xml:space="preserve">3.62591886520386</t>
@@ -2462,10 +2459,10 @@
     <t xml:space="preserve">3.53748202323914</t>
   </si>
   <si>
-    <t xml:space="preserve">3.57285690307617</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.50652933120728</t>
+    <t xml:space="preserve">3.57285714149475</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.5065290927887</t>
   </si>
   <si>
     <t xml:space="preserve">3.5905442237854</t>
@@ -2474,232 +2471,235 @@
     <t xml:space="preserve">3.57727885246277</t>
   </si>
   <si>
-    <t xml:space="preserve">3.74530959129333</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.74088716506958</t>
+    <t xml:space="preserve">3.74530911445618</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.74088764190674</t>
   </si>
   <si>
     <t xml:space="preserve">3.73204374313354</t>
   </si>
   <si>
-    <t xml:space="preserve">3.70551300048828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.77626252174377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.83816862106323</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.6834032535553</t>
+    <t xml:space="preserve">3.70551252365112</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.7762622833252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.83816814422607</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.68340277671814</t>
   </si>
   <si>
     <t xml:space="preserve">3.76741862297058</t>
   </si>
   <si>
-    <t xml:space="preserve">3.78068423271179</t>
+    <t xml:space="preserve">3.78068447113037</t>
   </si>
   <si>
     <t xml:space="preserve">3.76299691200256</t>
   </si>
   <si>
-    <t xml:space="preserve">3.77184057235718</t>
+    <t xml:space="preserve">3.77184009552002</t>
   </si>
   <si>
     <t xml:space="preserve">3.71877813339233</t>
   </si>
   <si>
-    <t xml:space="preserve">3.68782496452332</t>
+    <t xml:space="preserve">3.68782520294189</t>
   </si>
   <si>
     <t xml:space="preserve">3.59938812255859</t>
   </si>
   <si>
-    <t xml:space="preserve">3.66571569442749</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.70993447303772</t>
+    <t xml:space="preserve">3.66571593284607</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.70993423461914</t>
   </si>
   <si>
     <t xml:space="preserve">3.78510618209839</t>
   </si>
   <si>
-    <t xml:space="preserve">3.92660546302795</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.93987131118774</t>
+    <t xml:space="preserve">3.92660522460938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.93987083435059</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.99735426902771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.01079845428467</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.09594440460205</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.17212724685669</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.16316413879395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.13627576828003</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.19901466369629</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.14075756072998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.10490655899048</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.06905603408813</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.03320550918579</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.9794294834137</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.02872371673584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.05561208724976</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.08698177337646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.97494792938232</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.00183629989624</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.01528024673462</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.96150398254395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.98839163780212</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.95254135131836</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.96598529815674</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.04216861724854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.07801914215088</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.11835050582886</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.17660760879517</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.11386966705322</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.10938835144043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.06009340286255</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.1945333480835</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.21245861053467</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.14972019195557</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.12283229827881</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.03768634796143</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.01976203918457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.06457471847534</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.20797777175903</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.230384349823</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.25727224349976</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.20349597930908</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.92565321922302</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.90772819519043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.88083982467651</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.87635850906372</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.80913829803467</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.71503043174744</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.66573596000671</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.83154535293579</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.93461537361145</t>
   </si>
   <si>
     <t xml:space="preserve">3.99735474586487</t>
   </si>
   <si>
-    <t xml:space="preserve">4.01079893112183</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.09594440460205</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.17212772369385</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.16316413879395</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.13627576828003</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.19901514053345</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.14075756072998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.10490655899048</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.06905603408813</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.03320503234863</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.9794294834137</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.028724193573</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.05561256408691</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.08698129653931</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.97494792938232</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.00183582305908</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.01528024673462</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.96150398254395</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.98839139938354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.95254158973694</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.96598553657532</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.04216861724854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.07801914215088</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.11835098266602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.17660808563232</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.11386966705322</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.10938835144043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.06009292602539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.19453287124634</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.21245908737183</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.14972019195557</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.12283182144165</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.03768682479858</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.01976108551025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.06457471847534</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.20797777175903</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.230384349823</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.25727224349976</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.20349645614624</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.92565369606018</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.90772819519043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.88084006309509</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.87635827064514</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.80913829803467</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.71503043174744</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.66573548316956</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.83154535293579</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.93461561203003</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.94357848167419</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.04664897918701</t>
+    <t xml:space="preserve">3.94357872009277</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.04664945602417</t>
   </si>
   <si>
     <t xml:space="preserve">3.99287343025208</t>
   </si>
   <si>
-    <t xml:space="preserve">3.98391127586365</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.02424287796021</t>
+    <t xml:space="preserve">3.98391079902649</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.02424240112305</t>
   </si>
   <si>
     <t xml:space="preserve">3.85395193099976</t>
   </si>
   <si>
-    <t xml:space="preserve">3.93013453483582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.97046685218811</t>
+    <t xml:space="preserve">3.93013501167297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.97046661376953</t>
   </si>
   <si>
     <t xml:space="preserve">4.10042524337769</t>
@@ -2708,25 +2708,25 @@
     <t xml:space="preserve">4.15420150756836</t>
   </si>
   <si>
-    <t xml:space="preserve">4.0914626121521</t>
+    <t xml:space="preserve">4.09146308898926</t>
   </si>
   <si>
     <t xml:space="preserve">4.22590303421021</t>
   </si>
   <si>
-    <t xml:space="preserve">4.26623582839966</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.24382877349854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.13179492950439</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.1273136138916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.24830913543701</t>
+    <t xml:space="preserve">4.26623487472534</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.24382829666138</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.13179445266724</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.12731313705444</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.24830961227417</t>
   </si>
   <si>
     <t xml:space="preserve">4.19005250930786</t>
@@ -2735,25 +2735,25 @@
     <t xml:space="preserve">4.29312324523926</t>
   </si>
   <si>
-    <t xml:space="preserve">4.40515661239624</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.43652534484863</t>
+    <t xml:space="preserve">4.40515613555908</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.43652582168579</t>
   </si>
   <si>
     <t xml:space="preserve">4.48133897781372</t>
   </si>
   <si>
-    <t xml:space="preserve">4.53511571884155</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.55304050445557</t>
+    <t xml:space="preserve">4.53511524200439</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.55304002761841</t>
   </si>
   <si>
     <t xml:space="preserve">4.56200361251831</t>
   </si>
   <si>
-    <t xml:space="preserve">4.50822687149048</t>
+    <t xml:space="preserve">4.50822734832764</t>
   </si>
   <si>
     <t xml:space="preserve">4.45445108413696</t>
@@ -2765,19 +2765,19 @@
     <t xml:space="preserve">4.49926471710205</t>
   </si>
   <si>
-    <t xml:space="preserve">4.49030256271362</t>
+    <t xml:space="preserve">4.49030208587646</t>
   </si>
   <si>
     <t xml:space="preserve">4.51718997955322</t>
   </si>
   <si>
-    <t xml:space="preserve">4.63370513916016</t>
+    <t xml:space="preserve">4.633704662323</t>
   </si>
   <si>
     <t xml:space="preserve">4.59785413742065</t>
   </si>
   <si>
-    <t xml:space="preserve">4.47685766220093</t>
+    <t xml:space="preserve">4.47685813903809</t>
   </si>
   <si>
     <t xml:space="preserve">4.57096576690674</t>
@@ -2789,16 +2789,16 @@
     <t xml:space="preserve">4.64266681671143</t>
   </si>
   <si>
-    <t xml:space="preserve">4.39171266555786</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.44996976852417</t>
+    <t xml:space="preserve">4.3917121887207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.44997024536133</t>
   </si>
   <si>
     <t xml:space="preserve">4.27519750595093</t>
   </si>
   <si>
-    <t xml:space="preserve">4.58889150619507</t>
+    <t xml:space="preserve">4.58889198303223</t>
   </si>
   <si>
     <t xml:space="preserve">4.66059303283691</t>
@@ -2810,37 +2810,37 @@
     <t xml:space="preserve">4.71436929702759</t>
   </si>
   <si>
-    <t xml:space="preserve">4.75918197631836</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.7681450843811</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.89362239837646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.92051076889038</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.88465929031372</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.05495071411133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.01909971237183</t>
+    <t xml:space="preserve">4.75918245315552</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.76814460754395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.89362287521362</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.92051029205322</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.88465976715088</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.05495023727417</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.01910018920898</t>
   </si>
   <si>
     <t xml:space="preserve">5.14457702636719</t>
   </si>
   <si>
-    <t xml:space="preserve">5.31486845016479</t>
+    <t xml:space="preserve">5.31486797332764</t>
   </si>
   <si>
     <t xml:space="preserve">5.37760734558105</t>
   </si>
   <si>
-    <t xml:space="preserve">5.35968208312988</t>
+    <t xml:space="preserve">5.35968160629272</t>
   </si>
   <si>
     <t xml:space="preserve">5.16250324249268</t>
@@ -2849,13 +2849,13 @@
     <t xml:space="preserve">5.04598808288574</t>
   </si>
   <si>
-    <t xml:space="preserve">5.15354013442993</t>
+    <t xml:space="preserve">5.15354061126709</t>
   </si>
   <si>
     <t xml:space="preserve">5.26109218597412</t>
   </si>
   <si>
-    <t xml:space="preserve">5.27901697158813</t>
+    <t xml:space="preserve">5.27901744842529</t>
   </si>
   <si>
     <t xml:space="preserve">5.51204776763916</t>
@@ -2864,13 +2864,13 @@
     <t xml:space="preserve">5.4761962890625</t>
   </si>
   <si>
-    <t xml:space="preserve">5.50308465957642</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.29694318771362</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.19835376739502</t>
+    <t xml:space="preserve">5.50308418273926</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.29694366455078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.19835329055786</t>
   </si>
   <si>
     <t xml:space="preserve">5.18042850494385</t>
@@ -2879,25 +2879,25 @@
     <t xml:space="preserve">5.07287549972534</t>
   </si>
   <si>
-    <t xml:space="preserve">5.09080123901367</t>
+    <t xml:space="preserve">5.09080171585083</t>
   </si>
   <si>
     <t xml:space="preserve">4.99221229553223</t>
   </si>
   <si>
-    <t xml:space="preserve">4.75021982192993</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.80399560928345</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.92947340011597</t>
+    <t xml:space="preserve">4.75022029876709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.80399608612061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.92947292327881</t>
   </si>
   <si>
     <t xml:space="preserve">4.83984661102295</t>
   </si>
   <si>
-    <t xml:space="preserve">4.97428703308105</t>
+    <t xml:space="preserve">4.9742865562439</t>
   </si>
   <si>
     <t xml:space="preserve">4.90258502960205</t>
@@ -2906,13 +2906,13 @@
     <t xml:space="preserve">4.86673450469971</t>
   </si>
   <si>
-    <t xml:space="preserve">5.03702592849731</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.95636129379272</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.79503345489502</t>
+    <t xml:space="preserve">5.03702545166016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.95636177062988</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.79503297805786</t>
   </si>
   <si>
     <t xml:space="preserve">4.74125719070435</t>
@@ -2933,13 +2933,13 @@
     <t xml:space="preserve">4.23934698104858</t>
   </si>
   <si>
-    <t xml:space="preserve">4.85777187347412</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.91154813766479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.96532392501831</t>
+    <t xml:space="preserve">4.85777139663696</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.91154766082764</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.96532440185547</t>
   </si>
   <si>
     <t xml:space="preserve">5.11768960952759</t>
@@ -2957,19 +2957,19 @@
     <t xml:space="preserve">5.28798007965088</t>
   </si>
   <si>
-    <t xml:space="preserve">5.43138360977173</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.55686092376709</t>
+    <t xml:space="preserve">5.43138265609741</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.55686044692993</t>
   </si>
   <si>
     <t xml:space="preserve">5.62856245040894</t>
   </si>
   <si>
-    <t xml:space="preserve">5.52100944519043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.61959981918335</t>
+    <t xml:space="preserve">5.52100992202759</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.61959934234619</t>
   </si>
   <si>
     <t xml:space="preserve">5.53893518447876</t>
@@ -2984,7 +2984,7 @@
     <t xml:space="preserve">5.46581411361694</t>
   </si>
   <si>
-    <t xml:space="preserve">5.48409461975098</t>
+    <t xml:space="preserve">5.48409414291382</t>
   </si>
   <si>
     <t xml:space="preserve">5.63947725296021</t>
@@ -2993,7 +2993,7 @@
     <t xml:space="preserve">5.75829935073853</t>
   </si>
   <si>
-    <t xml:space="preserve">5.80399990081787</t>
+    <t xml:space="preserve">5.80399942398071</t>
   </si>
   <si>
     <t xml:space="preserve">5.65775728225708</t>
@@ -3002,19 +3002,19 @@
     <t xml:space="preserve">5.62119674682617</t>
   </si>
   <si>
-    <t xml:space="preserve">5.41097354888916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.40183305740356</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.63033676147461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.61205625534058</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.82227993011475</t>
+    <t xml:space="preserve">5.410973072052</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.40183258056641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.63033628463745</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.61205673217773</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.8222804069519</t>
   </si>
   <si>
     <t xml:space="preserve">5.84056043624878</t>
@@ -3032,16 +3032,16 @@
     <t xml:space="preserve">5.97766304016113</t>
   </si>
   <si>
-    <t xml:space="preserve">5.95938205718994</t>
+    <t xml:space="preserve">5.9593825340271</t>
   </si>
   <si>
     <t xml:space="preserve">6.04164409637451</t>
   </si>
   <si>
-    <t xml:space="preserve">5.87712144851685</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.07820510864258</t>
+    <t xml:space="preserve">5.87712097167969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.07820463180542</t>
   </si>
   <si>
     <t xml:space="preserve">5.9136815071106</t>
@@ -3056,25 +3056,25 @@
     <t xml:space="preserve">5.7308783531189</t>
   </si>
   <si>
-    <t xml:space="preserve">5.67603778839111</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.69431829452515</t>
+    <t xml:space="preserve">5.67603826522827</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.69431781768799</t>
   </si>
   <si>
     <t xml:space="preserve">5.66689729690552</t>
   </si>
   <si>
-    <t xml:space="preserve">5.42925310134888</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.42011308670044</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.33785152435303</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.20988988876343</t>
+    <t xml:space="preserve">5.42925357818604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.4201135635376</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.33785200119019</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.20988941192627</t>
   </si>
   <si>
     <t xml:space="preserve">5.34699201583862</t>
@@ -3086,10 +3086,10 @@
     <t xml:space="preserve">5.39269304275513</t>
   </si>
   <si>
-    <t xml:space="preserve">5.36527252197266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.28301095962524</t>
+    <t xml:space="preserve">5.3652720451355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.2830114364624</t>
   </si>
   <si>
     <t xml:space="preserve">5.2281699180603</t>
@@ -3098,7 +3098,7 @@
     <t xml:space="preserve">5.21902990341187</t>
   </si>
   <si>
-    <t xml:space="preserve">5.15504837036133</t>
+    <t xml:space="preserve">5.15504884719849</t>
   </si>
   <si>
     <t xml:space="preserve">5.10020780563354</t>
@@ -3107,7 +3107,7 @@
     <t xml:space="preserve">5.10934782028198</t>
   </si>
   <si>
-    <t xml:space="preserve">5.08192729949951</t>
+    <t xml:space="preserve">5.08192777633667</t>
   </si>
   <si>
     <t xml:space="preserve">5.03622674942017</t>
@@ -3122,10 +3122,10 @@
     <t xml:space="preserve">5.13676834106445</t>
   </si>
   <si>
-    <t xml:space="preserve">5.07278776168823</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.02708673477173</t>
+    <t xml:space="preserve">5.07278728485107</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.02708625793457</t>
   </si>
   <si>
     <t xml:space="preserve">5.0453667640686</t>
@@ -3143,10 +3143,10 @@
     <t xml:space="preserve">5.44753360748291</t>
   </si>
   <si>
-    <t xml:space="preserve">5.16418933868408</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.14590835571289</t>
+    <t xml:space="preserve">5.16418886184692</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.14590883255005</t>
   </si>
   <si>
     <t xml:space="preserve">4.94482469558716</t>
@@ -3155,43 +3155,43 @@
     <t xml:space="preserve">4.93568515777588</t>
   </si>
   <si>
-    <t xml:space="preserve">4.89912414550781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.8808445930481</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.85342311859131</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.826003074646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.73460149765015</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.75288152694702</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.69804096221924</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.57921934127808</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.71632099151611</t>
+    <t xml:space="preserve">4.89912462234497</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.88084411621094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.85342359542847</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.82600355148315</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.73460102081299</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.75288200378418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.69804048538208</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.57921886444092</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.71632146835327</t>
   </si>
   <si>
     <t xml:space="preserve">4.67976045608521</t>
   </si>
   <si>
-    <t xml:space="preserve">4.84428358078003</t>
+    <t xml:space="preserve">4.84428310394287</t>
   </si>
   <si>
     <t xml:space="preserve">4.80772256851196</t>
   </si>
   <si>
-    <t xml:space="preserve">4.57007837295532</t>
+    <t xml:space="preserve">4.57007884979248</t>
   </si>
   <si>
     <t xml:space="preserve">4.72546148300171</t>
@@ -3221,7 +3221,7 @@
     <t xml:space="preserve">4.48781728744507</t>
   </si>
   <si>
-    <t xml:space="preserve">4.53808784484863</t>
+    <t xml:space="preserve">4.53808832168579</t>
   </si>
   <si>
     <t xml:space="preserve">4.46953678131104</t>
@@ -3233,28 +3233,28 @@
     <t xml:space="preserve">4.49695777893066</t>
   </si>
   <si>
-    <t xml:space="preserve">4.40555620193481</t>
+    <t xml:space="preserve">4.40555572509766</t>
   </si>
   <si>
     <t xml:space="preserve">4.43297624588013</t>
   </si>
   <si>
-    <t xml:space="preserve">4.45582723617554</t>
+    <t xml:space="preserve">4.45582675933838</t>
   </si>
   <si>
     <t xml:space="preserve">4.36899518966675</t>
   </si>
   <si>
-    <t xml:space="preserve">4.29130411148071</t>
+    <t xml:space="preserve">4.29130363464355</t>
   </si>
   <si>
     <t xml:space="preserve">4.20447206497192</t>
   </si>
   <si>
-    <t xml:space="preserve">4.47867727279663</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.48324728012085</t>
+    <t xml:space="preserve">4.47867679595947</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.48324775695801</t>
   </si>
   <si>
     <t xml:space="preserve">4.79858255386353</t>
@@ -3263,7 +3263,7 @@
     <t xml:space="preserve">4.87170362472534</t>
   </si>
   <si>
-    <t xml:space="preserve">4.83514356613159</t>
+    <t xml:space="preserve">4.83514308929443</t>
   </si>
   <si>
     <t xml:space="preserve">5.17332887649536</t>
@@ -3272,13 +3272,13 @@
     <t xml:space="preserve">5.32871150970459</t>
   </si>
   <si>
-    <t xml:space="preserve">5.19160890579224</t>
+    <t xml:space="preserve">5.19160938262939</t>
   </si>
   <si>
     <t xml:space="preserve">5.25559043884277</t>
   </si>
   <si>
-    <t xml:space="preserve">5.38355207443237</t>
+    <t xml:space="preserve">5.38355302810669</t>
   </si>
   <si>
     <t xml:space="preserve">4.97224569320679</t>
@@ -3302,7 +3302,7 @@
     <t xml:space="preserve">4.98138570785522</t>
   </si>
   <si>
-    <t xml:space="preserve">4.92654514312744</t>
+    <t xml:space="preserve">4.92654466629028</t>
   </si>
   <si>
     <t xml:space="preserve">5.06364727020264</t>
@@ -3320,13 +3320,13 @@
     <t xml:space="preserve">5.23730993270874</t>
   </si>
   <si>
-    <t xml:space="preserve">5.27387094497681</t>
+    <t xml:space="preserve">5.27387046813965</t>
   </si>
   <si>
     <t xml:space="preserve">5.31957197189331</t>
   </si>
   <si>
-    <t xml:space="preserve">5.27241277694702</t>
+    <t xml:space="preserve">5.27241230010986</t>
   </si>
   <si>
     <t xml:space="preserve">5.23468494415283</t>
@@ -3338,13 +3338,13 @@
     <t xml:space="preserve">5.02718353271484</t>
   </si>
   <si>
-    <t xml:space="preserve">4.99888849258423</t>
+    <t xml:space="preserve">4.99888801574707</t>
   </si>
   <si>
     <t xml:space="preserve">5.01775217056274</t>
   </si>
   <si>
-    <t xml:space="preserve">5.16866207122803</t>
+    <t xml:space="preserve">5.16866159439087</t>
   </si>
   <si>
     <t xml:space="preserve">5.1403660774231</t>
@@ -3374,10 +3374,10 @@
     <t xml:space="preserve">5.26298046112061</t>
   </si>
   <si>
-    <t xml:space="preserve">5.37616300582886</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.17809295654297</t>
+    <t xml:space="preserve">5.3761625289917</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.17809343338013</t>
   </si>
   <si>
     <t xml:space="preserve">5.21582126617432</t>
@@ -3386,7 +3386,7 @@
     <t xml:space="preserve">5.10263824462891</t>
   </si>
   <si>
-    <t xml:space="preserve">5.14979839324951</t>
+    <t xml:space="preserve">5.14979791641235</t>
   </si>
   <si>
     <t xml:space="preserve">5.09320688247681</t>
@@ -3401,7 +3401,7 @@
     <t xml:space="preserve">5.03661584854126</t>
   </si>
   <si>
-    <t xml:space="preserve">5.06491136550903</t>
+    <t xml:space="preserve">5.06491088867188</t>
   </si>
   <si>
     <t xml:space="preserve">4.95172882080078</t>
@@ -3416,7 +3416,7 @@
     <t xml:space="preserve">4.91400146484375</t>
   </si>
   <si>
-    <t xml:space="preserve">4.90456914901733</t>
+    <t xml:space="preserve">4.90456962585449</t>
   </si>
   <si>
     <t xml:space="preserve">4.77252340316772</t>
@@ -3428,16 +3428,16 @@
     <t xml:space="preserve">4.72536420822144</t>
   </si>
   <si>
-    <t xml:space="preserve">4.9611611366272</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.8574104309082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.8008189201355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.51786327362061</t>
+    <t xml:space="preserve">4.96116065979004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.85740995407104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.80081939697266</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.51786279678345</t>
   </si>
   <si>
     <t xml:space="preserve">4.50843143463135</t>
@@ -3449,7 +3449,7 @@
     <t xml:space="preserve">4.54615879058838</t>
   </si>
   <si>
-    <t xml:space="preserve">4.6216139793396</t>
+    <t xml:space="preserve">4.62161350250244</t>
   </si>
   <si>
     <t xml:space="preserve">4.54144287109375</t>
@@ -3464,7 +3464,7 @@
     <t xml:space="preserve">4.56030654907227</t>
   </si>
   <si>
-    <t xml:space="preserve">4.47541952133179</t>
+    <t xml:space="preserve">4.47541999816895</t>
   </si>
   <si>
     <t xml:space="preserve">4.47070360183716</t>
@@ -3482,7 +3482,7 @@
     <t xml:space="preserve">4.50371503829956</t>
   </si>
   <si>
-    <t xml:space="preserve">4.51314687728882</t>
+    <t xml:space="preserve">4.51314735412598</t>
   </si>
   <si>
     <t xml:space="preserve">4.63576126098633</t>
@@ -3491,13 +3491,13 @@
     <t xml:space="preserve">4.65934085845947</t>
   </si>
   <si>
-    <t xml:space="preserve">4.62632942199707</t>
+    <t xml:space="preserve">4.62632989883423</t>
   </si>
   <si>
     <t xml:space="preserve">4.64519357681274</t>
   </si>
   <si>
-    <t xml:space="preserve">4.67820453643799</t>
+    <t xml:space="preserve">4.67820501327515</t>
   </si>
   <si>
     <t xml:space="preserve">4.71593236923218</t>
@@ -3515,7 +3515,7 @@
     <t xml:space="preserve">4.73479604721069</t>
   </si>
   <si>
-    <t xml:space="preserve">4.60274982452393</t>
+    <t xml:space="preserve">4.60275030136108</t>
   </si>
   <si>
     <t xml:space="preserve">4.57445430755615</t>
@@ -3530,7 +3530,7 @@
     <t xml:space="preserve">4.34337377548218</t>
   </si>
   <si>
-    <t xml:space="preserve">4.41411256790161</t>
+    <t xml:space="preserve">4.41411209106445</t>
   </si>
   <si>
     <t xml:space="preserve">4.3952488899231</t>
@@ -3572,31 +3572,31 @@
     <t xml:space="preserve">4.27263498306274</t>
   </si>
   <si>
-    <t xml:space="preserve">4.2349066734314</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.1122932434082</t>
+    <t xml:space="preserve">4.23490715026855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.11229276657104</t>
   </si>
   <si>
     <t xml:space="preserve">4.0887131690979</t>
   </si>
   <si>
-    <t xml:space="preserve">4.0557017326355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.10757684707642</t>
+    <t xml:space="preserve">4.05570220947266</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.10757732391357</t>
   </si>
   <si>
     <t xml:space="preserve">4.03683805465698</t>
   </si>
   <si>
-    <t xml:space="preserve">3.86234831809998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.00854253768921</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.99910998344421</t>
+    <t xml:space="preserve">3.86234855651855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.00854206085205</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.99911022186279</t>
   </si>
   <si>
     <t xml:space="preserve">4.07456541061401</t>
@@ -3614,7 +3614,7 @@
     <t xml:space="preserve">4.15473651885986</t>
   </si>
   <si>
-    <t xml:space="preserve">4.18303155899048</t>
+    <t xml:space="preserve">4.18303203582764</t>
   </si>
   <si>
     <t xml:space="preserve">4.27735042572021</t>
@@ -3632,7 +3632,7 @@
     <t xml:space="preserve">4.24905490875244</t>
   </si>
   <si>
-    <t xml:space="preserve">4.26791906356812</t>
+    <t xml:space="preserve">4.26791858673096</t>
   </si>
   <si>
     <t xml:space="preserve">4.39053297042847</t>
@@ -3641,7 +3641,7 @@
     <t xml:space="preserve">4.37166976928711</t>
   </si>
   <si>
-    <t xml:space="preserve">4.35752105712891</t>
+    <t xml:space="preserve">4.35752153396606</t>
   </si>
   <si>
     <t xml:space="preserve">4.35280513763428</t>
@@ -3677,19 +3677,19 @@
     <t xml:space="preserve">4.23962306976318</t>
   </si>
   <si>
-    <t xml:space="preserve">4.20189523696899</t>
+    <t xml:space="preserve">4.20189571380615</t>
   </si>
   <si>
     <t xml:space="preserve">4.12644052505493</t>
   </si>
   <si>
-    <t xml:space="preserve">4.0226902961731</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.15002012252808</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.92837142944336</t>
+    <t xml:space="preserve">4.02268981933594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.15002059936523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.92837166786194</t>
   </si>
   <si>
     <t xml:space="preserve">4.04626989364624</t>
@@ -3698,16 +3698,16 @@
     <t xml:space="preserve">3.96138286590576</t>
   </si>
   <si>
-    <t xml:space="preserve">4.06041765213013</t>
+    <t xml:space="preserve">4.06041717529297</t>
   </si>
   <si>
     <t xml:space="preserve">4.01797485351562</t>
   </si>
   <si>
-    <t xml:space="preserve">3.90007615089417</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.94251942634583</t>
+    <t xml:space="preserve">3.90007638931274</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.94251894950867</t>
   </si>
   <si>
     <t xml:space="preserve">3.89535999298096</t>
@@ -3725,7 +3725,7 @@
     <t xml:space="preserve">3.88121199607849</t>
   </si>
   <si>
-    <t xml:space="preserve">3.84348440170288</t>
+    <t xml:space="preserve">3.84348464012146</t>
   </si>
   <si>
     <t xml:space="preserve">3.81990528106689</t>
@@ -3743,10 +3743,10 @@
     <t xml:space="preserve">3.75388216972351</t>
   </si>
   <si>
-    <t xml:space="preserve">3.72558665275574</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.76331400871277</t>
+    <t xml:space="preserve">3.72558641433716</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.76331377029419</t>
   </si>
   <si>
     <t xml:space="preserve">3.735018491745</t>
@@ -3755,7 +3755,7 @@
     <t xml:space="preserve">3.71615481376648</t>
   </si>
   <si>
-    <t xml:space="preserve">3.58410835266113</t>
+    <t xml:space="preserve">3.58410859107971</t>
   </si>
   <si>
     <t xml:space="preserve">3.76442790031433</t>
@@ -27396,7 +27396,7 @@
         <v>5.05999994277954</v>
       </c>
       <c r="G870" t="s">
-        <v>548</v>
+        <v>538</v>
       </c>
       <c r="H870" t="s">
         <v>9</v>
@@ -27422,7 +27422,7 @@
         <v>5.17000007629395</v>
       </c>
       <c r="G871" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="H871" t="s">
         <v>9</v>
@@ -27448,7 +27448,7 @@
         <v>5.19000005722046</v>
       </c>
       <c r="G872" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="H872" t="s">
         <v>9</v>
@@ -27552,7 +27552,7 @@
         <v>5.07000017166138</v>
       </c>
       <c r="G876" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="H876" t="s">
         <v>9</v>
@@ -27578,7 +27578,7 @@
         <v>5.1100001335144</v>
       </c>
       <c r="G877" t="s">
-        <v>552</v>
+        <v>551</v>
       </c>
       <c r="H877" t="s">
         <v>9</v>
@@ -27604,7 +27604,7 @@
         <v>5.17999982833862</v>
       </c>
       <c r="G878" t="s">
-        <v>553</v>
+        <v>552</v>
       </c>
       <c r="H878" t="s">
         <v>9</v>
@@ -27656,7 +27656,7 @@
         <v>5.1399998664856</v>
       </c>
       <c r="G880" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="H880" t="s">
         <v>9</v>
@@ -27682,7 +27682,7 @@
         <v>5.1399998664856</v>
       </c>
       <c r="G881" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="H881" t="s">
         <v>9</v>
@@ -27734,7 +27734,7 @@
         <v>5.05999994277954</v>
       </c>
       <c r="G883" t="s">
-        <v>548</v>
+        <v>538</v>
       </c>
       <c r="H883" t="s">
         <v>9</v>
@@ -27760,7 +27760,7 @@
         <v>4.92500019073486</v>
       </c>
       <c r="G884" t="s">
-        <v>555</v>
+        <v>554</v>
       </c>
       <c r="H884" t="s">
         <v>9</v>
@@ -27786,7 +27786,7 @@
         <v>4.96500015258789</v>
       </c>
       <c r="G885" t="s">
-        <v>556</v>
+        <v>555</v>
       </c>
       <c r="H885" t="s">
         <v>9</v>
@@ -27812,7 +27812,7 @@
         <v>4.80999994277954</v>
       </c>
       <c r="G886" t="s">
-        <v>557</v>
+        <v>556</v>
       </c>
       <c r="H886" t="s">
         <v>9</v>
@@ -27838,7 +27838,7 @@
         <v>4.71000003814697</v>
       </c>
       <c r="G887" t="s">
-        <v>558</v>
+        <v>557</v>
       </c>
       <c r="H887" t="s">
         <v>9</v>
@@ -27864,7 +27864,7 @@
         <v>4.75500011444092</v>
       </c>
       <c r="G888" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="H888" t="s">
         <v>9</v>
@@ -27890,7 +27890,7 @@
         <v>4.63500022888184</v>
       </c>
       <c r="G889" t="s">
-        <v>560</v>
+        <v>559</v>
       </c>
       <c r="H889" t="s">
         <v>9</v>
@@ -27916,7 +27916,7 @@
         <v>4.69500017166138</v>
       </c>
       <c r="G890" t="s">
-        <v>561</v>
+        <v>560</v>
       </c>
       <c r="H890" t="s">
         <v>9</v>
@@ -27942,7 +27942,7 @@
         <v>4.59499979019165</v>
       </c>
       <c r="G891" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
       <c r="H891" t="s">
         <v>9</v>
@@ -27968,7 +27968,7 @@
         <v>4.64499998092651</v>
       </c>
       <c r="G892" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="H892" t="s">
         <v>9</v>
@@ -27994,7 +27994,7 @@
         <v>4.6399998664856</v>
       </c>
       <c r="G893" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="H893" t="s">
         <v>9</v>
@@ -28020,7 +28020,7 @@
         <v>4.59000015258789</v>
       </c>
       <c r="G894" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="H894" t="s">
         <v>9</v>
@@ -28046,7 +28046,7 @@
         <v>4.61499977111816</v>
       </c>
       <c r="G895" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="H895" t="s">
         <v>9</v>
@@ -28072,7 +28072,7 @@
         <v>4.6100001335144</v>
       </c>
       <c r="G896" t="s">
-        <v>567</v>
+        <v>566</v>
       </c>
       <c r="H896" t="s">
         <v>9</v>
@@ -28098,7 +28098,7 @@
         <v>4.67000007629395</v>
       </c>
       <c r="G897" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="H897" t="s">
         <v>9</v>
@@ -28124,7 +28124,7 @@
         <v>4.64499998092651</v>
       </c>
       <c r="G898" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="H898" t="s">
         <v>9</v>
@@ -28150,7 +28150,7 @@
         <v>4.57000017166138</v>
       </c>
       <c r="G899" t="s">
-        <v>569</v>
+        <v>568</v>
       </c>
       <c r="H899" t="s">
         <v>9</v>
@@ -28176,7 +28176,7 @@
         <v>4.59499979019165</v>
       </c>
       <c r="G900" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
       <c r="H900" t="s">
         <v>9</v>
@@ -28202,7 +28202,7 @@
         <v>4.73999977111816</v>
       </c>
       <c r="G901" t="s">
-        <v>570</v>
+        <v>569</v>
       </c>
       <c r="H901" t="s">
         <v>9</v>
@@ -28228,7 +28228,7 @@
         <v>4.76000022888184</v>
       </c>
       <c r="G902" t="s">
-        <v>571</v>
+        <v>570</v>
       </c>
       <c r="H902" t="s">
         <v>9</v>
@@ -28254,7 +28254,7 @@
         <v>4.78499984741211</v>
       </c>
       <c r="G903" t="s">
-        <v>572</v>
+        <v>571</v>
       </c>
       <c r="H903" t="s">
         <v>9</v>
@@ -28306,7 +28306,7 @@
         <v>4.96000003814697</v>
       </c>
       <c r="G905" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="H905" t="s">
         <v>9</v>
@@ -28332,7 +28332,7 @@
         <v>5.03000020980835</v>
       </c>
       <c r="G906" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="H906" t="s">
         <v>9</v>
@@ -28358,7 +28358,7 @@
         <v>5</v>
       </c>
       <c r="G907" t="s">
-        <v>575</v>
+        <v>574</v>
       </c>
       <c r="H907" t="s">
         <v>9</v>
@@ -28384,7 +28384,7 @@
         <v>4.69000005722046</v>
       </c>
       <c r="G908" t="s">
-        <v>576</v>
+        <v>575</v>
       </c>
       <c r="H908" t="s">
         <v>9</v>
@@ -28410,7 +28410,7 @@
         <v>4.46999979019165</v>
       </c>
       <c r="G909" t="s">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="H909" t="s">
         <v>9</v>
@@ -28436,7 +28436,7 @@
         <v>4.51000022888184</v>
       </c>
       <c r="G910" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="H910" t="s">
         <v>9</v>
@@ -28462,7 +28462,7 @@
         <v>4.52500009536743</v>
       </c>
       <c r="G911" t="s">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="H911" t="s">
         <v>9</v>
@@ -28488,7 +28488,7 @@
         <v>4.73999977111816</v>
       </c>
       <c r="G912" t="s">
-        <v>570</v>
+        <v>569</v>
       </c>
       <c r="H912" t="s">
         <v>9</v>
@@ -28514,7 +28514,7 @@
         <v>4.65999984741211</v>
       </c>
       <c r="G913" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="H913" t="s">
         <v>9</v>
@@ -28540,7 +28540,7 @@
         <v>4.67999982833862</v>
       </c>
       <c r="G914" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="H914" t="s">
         <v>9</v>
@@ -28566,7 +28566,7 @@
         <v>4.57999992370605</v>
       </c>
       <c r="G915" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="H915" t="s">
         <v>9</v>
@@ -28592,7 +28592,7 @@
         <v>4.52500009536743</v>
       </c>
       <c r="G916" t="s">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="H916" t="s">
         <v>9</v>
@@ -28618,7 +28618,7 @@
         <v>4.5</v>
       </c>
       <c r="G917" t="s">
-        <v>583</v>
+        <v>582</v>
       </c>
       <c r="H917" t="s">
         <v>9</v>
@@ -28644,7 +28644,7 @@
         <v>4.3899998664856</v>
       </c>
       <c r="G918" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="H918" t="s">
         <v>9</v>
@@ -28670,7 +28670,7 @@
         <v>4.32499980926514</v>
       </c>
       <c r="G919" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="H919" t="s">
         <v>9</v>
@@ -28696,7 +28696,7 @@
         <v>4.30999994277954</v>
       </c>
       <c r="G920" t="s">
-        <v>586</v>
+        <v>585</v>
       </c>
       <c r="H920" t="s">
         <v>9</v>
@@ -28722,7 +28722,7 @@
         <v>4.28000020980835</v>
       </c>
       <c r="G921" t="s">
-        <v>587</v>
+        <v>586</v>
       </c>
       <c r="H921" t="s">
         <v>9</v>
@@ -28748,7 +28748,7 @@
         <v>4.28999996185303</v>
       </c>
       <c r="G922" t="s">
-        <v>588</v>
+        <v>587</v>
       </c>
       <c r="H922" t="s">
         <v>9</v>
@@ -28774,7 +28774,7 @@
         <v>4.31500005722046</v>
       </c>
       <c r="G923" t="s">
-        <v>589</v>
+        <v>588</v>
       </c>
       <c r="H923" t="s">
         <v>9</v>
@@ -28800,7 +28800,7 @@
         <v>4.2649998664856</v>
       </c>
       <c r="G924" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="H924" t="s">
         <v>9</v>
@@ -28826,7 +28826,7 @@
         <v>4.26000022888184</v>
       </c>
       <c r="G925" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="H925" t="s">
         <v>9</v>
@@ -28852,7 +28852,7 @@
         <v>4.32999992370605</v>
       </c>
       <c r="G926" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="H926" t="s">
         <v>9</v>
@@ -28878,7 +28878,7 @@
         <v>4.44000005722046</v>
       </c>
       <c r="G927" t="s">
-        <v>593</v>
+        <v>592</v>
       </c>
       <c r="H927" t="s">
         <v>9</v>
@@ -28904,7 +28904,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G928" t="s">
-        <v>594</v>
+        <v>593</v>
       </c>
       <c r="H928" t="s">
         <v>9</v>
@@ -28930,7 +28930,7 @@
         <v>4.48999977111816</v>
       </c>
       <c r="G929" t="s">
-        <v>595</v>
+        <v>594</v>
       </c>
       <c r="H929" t="s">
         <v>9</v>
@@ -28956,7 +28956,7 @@
         <v>4.40500020980835</v>
       </c>
       <c r="G930" t="s">
-        <v>596</v>
+        <v>595</v>
       </c>
       <c r="H930" t="s">
         <v>9</v>
@@ -28982,7 +28982,7 @@
         <v>4.47499990463257</v>
       </c>
       <c r="G931" t="s">
-        <v>597</v>
+        <v>596</v>
       </c>
       <c r="H931" t="s">
         <v>9</v>
@@ -29008,7 +29008,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G932" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="H932" t="s">
         <v>9</v>
@@ -29034,7 +29034,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G933" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="H933" t="s">
         <v>9</v>
@@ -29060,7 +29060,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G934" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="H934" t="s">
         <v>9</v>
@@ -29086,7 +29086,7 @@
         <v>4.34499979019165</v>
       </c>
       <c r="G935" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="H935" t="s">
         <v>9</v>
@@ -29112,7 +29112,7 @@
         <v>4.32000017166138</v>
       </c>
       <c r="G936" t="s">
-        <v>601</v>
+        <v>600</v>
       </c>
       <c r="H936" t="s">
         <v>9</v>
@@ -29138,7 +29138,7 @@
         <v>4.19000005722046</v>
       </c>
       <c r="G937" t="s">
-        <v>602</v>
+        <v>601</v>
       </c>
       <c r="H937" t="s">
         <v>9</v>
@@ -29164,7 +29164,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G938" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="H938" t="s">
         <v>9</v>
@@ -29190,7 +29190,7 @@
         <v>4.36999988555908</v>
       </c>
       <c r="G939" t="s">
-        <v>603</v>
+        <v>602</v>
       </c>
       <c r="H939" t="s">
         <v>9</v>
@@ -29216,7 +29216,7 @@
         <v>4.28000020980835</v>
       </c>
       <c r="G940" t="s">
-        <v>587</v>
+        <v>586</v>
       </c>
       <c r="H940" t="s">
         <v>9</v>
@@ -29242,7 +29242,7 @@
         <v>4.25</v>
       </c>
       <c r="G941" t="s">
-        <v>604</v>
+        <v>603</v>
       </c>
       <c r="H941" t="s">
         <v>9</v>
@@ -29268,7 +29268,7 @@
         <v>4.25</v>
       </c>
       <c r="G942" t="s">
-        <v>604</v>
+        <v>603</v>
       </c>
       <c r="H942" t="s">
         <v>9</v>
@@ -29294,7 +29294,7 @@
         <v>4.30999994277954</v>
       </c>
       <c r="G943" t="s">
-        <v>586</v>
+        <v>585</v>
       </c>
       <c r="H943" t="s">
         <v>9</v>
@@ -29320,7 +29320,7 @@
         <v>4.33500003814697</v>
       </c>
       <c r="G944" t="s">
-        <v>605</v>
+        <v>604</v>
       </c>
       <c r="H944" t="s">
         <v>9</v>
@@ -29346,7 +29346,7 @@
         <v>4.47499990463257</v>
       </c>
       <c r="G945" t="s">
-        <v>597</v>
+        <v>596</v>
       </c>
       <c r="H945" t="s">
         <v>9</v>
@@ -29372,7 +29372,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G946" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="H946" t="s">
         <v>9</v>
@@ -29398,7 +29398,7 @@
         <v>4.40999984741211</v>
       </c>
       <c r="G947" t="s">
-        <v>606</v>
+        <v>605</v>
       </c>
       <c r="H947" t="s">
         <v>9</v>
@@ -29424,7 +29424,7 @@
         <v>4.24499988555908</v>
       </c>
       <c r="G948" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="H948" t="s">
         <v>9</v>
@@ -29450,7 +29450,7 @@
         <v>4.25</v>
       </c>
       <c r="G949" t="s">
-        <v>604</v>
+        <v>603</v>
       </c>
       <c r="H949" t="s">
         <v>9</v>
@@ -29476,7 +29476,7 @@
         <v>4.26000022888184</v>
       </c>
       <c r="G950" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="H950" t="s">
         <v>9</v>
@@ -29502,7 +29502,7 @@
         <v>4.26999998092651</v>
       </c>
       <c r="G951" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="H951" t="s">
         <v>9</v>
@@ -29528,7 +29528,7 @@
         <v>4.27500009536743</v>
       </c>
       <c r="G952" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="H952" t="s">
         <v>9</v>
@@ -29554,7 +29554,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G953" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="H953" t="s">
         <v>9</v>
@@ -29580,7 +29580,7 @@
         <v>4.32000017166138</v>
       </c>
       <c r="G954" t="s">
-        <v>601</v>
+        <v>600</v>
       </c>
       <c r="H954" t="s">
         <v>9</v>
@@ -29606,7 +29606,7 @@
         <v>4.21000003814697</v>
       </c>
       <c r="G955" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
       <c r="H955" t="s">
         <v>9</v>
@@ -29632,7 +29632,7 @@
         <v>4.15999984741211</v>
       </c>
       <c r="G956" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="H956" t="s">
         <v>9</v>
@@ -29658,7 +29658,7 @@
         <v>4.23999977111816</v>
       </c>
       <c r="G957" t="s">
-        <v>612</v>
+        <v>611</v>
       </c>
       <c r="H957" t="s">
         <v>9</v>
@@ -29684,7 +29684,7 @@
         <v>4.25500011444092</v>
       </c>
       <c r="G958" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
       <c r="H958" t="s">
         <v>9</v>
@@ -29710,7 +29710,7 @@
         <v>4.33500003814697</v>
       </c>
       <c r="G959" t="s">
-        <v>605</v>
+        <v>604</v>
       </c>
       <c r="H959" t="s">
         <v>9</v>
@@ -29736,7 +29736,7 @@
         <v>4.22499990463257</v>
       </c>
       <c r="G960" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
       <c r="H960" t="s">
         <v>9</v>
@@ -29762,7 +29762,7 @@
         <v>4.26999998092651</v>
       </c>
       <c r="G961" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="H961" t="s">
         <v>9</v>
@@ -29788,7 +29788,7 @@
         <v>4.34499979019165</v>
       </c>
       <c r="G962" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="H962" t="s">
         <v>9</v>
@@ -29814,7 +29814,7 @@
         <v>4.28999996185303</v>
       </c>
       <c r="G963" t="s">
-        <v>588</v>
+        <v>587</v>
       </c>
       <c r="H963" t="s">
         <v>9</v>
@@ -29840,7 +29840,7 @@
         <v>4.28000020980835</v>
       </c>
       <c r="G964" t="s">
-        <v>587</v>
+        <v>586</v>
       </c>
       <c r="H964" t="s">
         <v>9</v>
@@ -29866,7 +29866,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G965" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="H965" t="s">
         <v>9</v>
@@ -29892,7 +29892,7 @@
         <v>4.61999988555908</v>
       </c>
       <c r="G966" t="s">
-        <v>615</v>
+        <v>614</v>
       </c>
       <c r="H966" t="s">
         <v>9</v>
@@ -29918,7 +29918,7 @@
         <v>4.60500001907349</v>
       </c>
       <c r="G967" t="s">
-        <v>616</v>
+        <v>615</v>
       </c>
       <c r="H967" t="s">
         <v>9</v>
@@ -29944,7 +29944,7 @@
         <v>4.53999996185303</v>
       </c>
       <c r="G968" t="s">
-        <v>617</v>
+        <v>616</v>
       </c>
       <c r="H968" t="s">
         <v>9</v>
@@ -29970,7 +29970,7 @@
         <v>4.57499980926514</v>
       </c>
       <c r="G969" t="s">
-        <v>618</v>
+        <v>617</v>
       </c>
       <c r="H969" t="s">
         <v>9</v>
@@ -29996,7 +29996,7 @@
         <v>4.57999992370605</v>
       </c>
       <c r="G970" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="H970" t="s">
         <v>9</v>
@@ -30022,7 +30022,7 @@
         <v>4.61499977111816</v>
       </c>
       <c r="G971" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="H971" t="s">
         <v>9</v>
@@ -30048,7 +30048,7 @@
         <v>4.67000007629395</v>
       </c>
       <c r="G972" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="H972" t="s">
         <v>9</v>
@@ -30074,7 +30074,7 @@
         <v>4.67500019073486</v>
       </c>
       <c r="G973" t="s">
-        <v>619</v>
+        <v>618</v>
       </c>
       <c r="H973" t="s">
         <v>9</v>
@@ -30100,7 +30100,7 @@
         <v>4.67000007629395</v>
       </c>
       <c r="G974" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="H974" t="s">
         <v>9</v>
@@ -30126,7 +30126,7 @@
         <v>4.76999998092651</v>
       </c>
       <c r="G975" t="s">
-        <v>620</v>
+        <v>619</v>
       </c>
       <c r="H975" t="s">
         <v>9</v>
@@ -30152,7 +30152,7 @@
         <v>4.82000017166138</v>
       </c>
       <c r="G976" t="s">
-        <v>621</v>
+        <v>620</v>
       </c>
       <c r="H976" t="s">
         <v>9</v>
@@ -30178,7 +30178,7 @@
         <v>4.94000005722046</v>
       </c>
       <c r="G977" t="s">
-        <v>622</v>
+        <v>621</v>
       </c>
       <c r="H977" t="s">
         <v>9</v>
@@ -30204,7 +30204,7 @@
         <v>4.94500017166138</v>
       </c>
       <c r="G978" t="s">
-        <v>623</v>
+        <v>622</v>
       </c>
       <c r="H978" t="s">
         <v>9</v>
@@ -30230,7 +30230,7 @@
         <v>5.15999984741211</v>
       </c>
       <c r="G979" t="s">
-        <v>624</v>
+        <v>623</v>
       </c>
       <c r="H979" t="s">
         <v>9</v>
@@ -30256,7 +30256,7 @@
         <v>5.05999994277954</v>
       </c>
       <c r="G980" t="s">
-        <v>548</v>
+        <v>538</v>
       </c>
       <c r="H980" t="s">
         <v>9</v>
@@ -30308,7 +30308,7 @@
         <v>5.15000009536743</v>
       </c>
       <c r="G982" t="s">
-        <v>625</v>
+        <v>624</v>
       </c>
       <c r="H982" t="s">
         <v>9</v>
@@ -30360,7 +30360,7 @@
         <v>5.34000015258789</v>
       </c>
       <c r="G984" t="s">
-        <v>626</v>
+        <v>625</v>
       </c>
       <c r="H984" t="s">
         <v>9</v>
@@ -30386,7 +30386,7 @@
         <v>5.32999992370605</v>
       </c>
       <c r="G985" t="s">
-        <v>627</v>
+        <v>626</v>
       </c>
       <c r="H985" t="s">
         <v>9</v>
@@ -30412,7 +30412,7 @@
         <v>5.23000001907349</v>
       </c>
       <c r="G986" t="s">
-        <v>628</v>
+        <v>627</v>
       </c>
       <c r="H986" t="s">
         <v>9</v>
@@ -30490,7 +30490,7 @@
         <v>5.19000005722046</v>
       </c>
       <c r="G989" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="H989" t="s">
         <v>9</v>
@@ -30516,7 +30516,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G990" t="s">
-        <v>629</v>
+        <v>628</v>
       </c>
       <c r="H990" t="s">
         <v>9</v>
@@ -30542,7 +30542,7 @@
         <v>5.15999984741211</v>
       </c>
       <c r="G991" t="s">
-        <v>624</v>
+        <v>623</v>
       </c>
       <c r="H991" t="s">
         <v>9</v>
@@ -30568,7 +30568,7 @@
         <v>5.15000009536743</v>
       </c>
       <c r="G992" t="s">
-        <v>625</v>
+        <v>624</v>
       </c>
       <c r="H992" t="s">
         <v>9</v>
@@ -30594,7 +30594,7 @@
         <v>5.21999979019165</v>
       </c>
       <c r="G993" t="s">
-        <v>630</v>
+        <v>629</v>
       </c>
       <c r="H993" t="s">
         <v>9</v>
@@ -30620,7 +30620,7 @@
         <v>5.28000020980835</v>
       </c>
       <c r="G994" t="s">
-        <v>631</v>
+        <v>630</v>
       </c>
       <c r="H994" t="s">
         <v>9</v>
@@ -30646,7 +30646,7 @@
         <v>5.34999990463257</v>
       </c>
       <c r="G995" t="s">
-        <v>632</v>
+        <v>631</v>
       </c>
       <c r="H995" t="s">
         <v>9</v>
@@ -30672,7 +30672,7 @@
         <v>5.55999994277954</v>
       </c>
       <c r="G996" t="s">
-        <v>633</v>
+        <v>632</v>
       </c>
       <c r="H996" t="s">
         <v>9</v>
@@ -30698,7 +30698,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G997" t="s">
-        <v>634</v>
+        <v>633</v>
       </c>
       <c r="H997" t="s">
         <v>9</v>
@@ -30724,7 +30724,7 @@
         <v>5.46999979019165</v>
       </c>
       <c r="G998" t="s">
-        <v>635</v>
+        <v>634</v>
       </c>
       <c r="H998" t="s">
         <v>9</v>
@@ -30750,7 +30750,7 @@
         <v>5.40999984741211</v>
       </c>
       <c r="G999" t="s">
-        <v>636</v>
+        <v>635</v>
       </c>
       <c r="H999" t="s">
         <v>9</v>
@@ -30776,7 +30776,7 @@
         <v>5.5</v>
       </c>
       <c r="G1000" t="s">
-        <v>637</v>
+        <v>636</v>
       </c>
       <c r="H1000" t="s">
         <v>9</v>
@@ -30802,7 +30802,7 @@
         <v>5.48999977111816</v>
       </c>
       <c r="G1001" t="s">
-        <v>638</v>
+        <v>637</v>
       </c>
       <c r="H1001" t="s">
         <v>9</v>
@@ -30828,7 +30828,7 @@
         <v>5.46000003814697</v>
       </c>
       <c r="G1002" t="s">
-        <v>639</v>
+        <v>638</v>
       </c>
       <c r="H1002" t="s">
         <v>9</v>
@@ -30854,7 +30854,7 @@
         <v>5.46000003814697</v>
       </c>
       <c r="G1003" t="s">
-        <v>639</v>
+        <v>638</v>
       </c>
       <c r="H1003" t="s">
         <v>9</v>
@@ -30880,7 +30880,7 @@
         <v>5.44999980926514</v>
       </c>
       <c r="G1004" t="s">
-        <v>640</v>
+        <v>639</v>
       </c>
       <c r="H1004" t="s">
         <v>9</v>
@@ -30906,7 +30906,7 @@
         <v>5.48000001907349</v>
       </c>
       <c r="G1005" t="s">
-        <v>641</v>
+        <v>640</v>
       </c>
       <c r="H1005" t="s">
         <v>9</v>
@@ -30932,7 +30932,7 @@
         <v>5.44000005722046</v>
       </c>
       <c r="G1006" t="s">
-        <v>642</v>
+        <v>641</v>
       </c>
       <c r="H1006" t="s">
         <v>9</v>
@@ -30958,7 +30958,7 @@
         <v>5.23000001907349</v>
       </c>
       <c r="G1007" t="s">
-        <v>628</v>
+        <v>627</v>
       </c>
       <c r="H1007" t="s">
         <v>9</v>
@@ -30984,7 +30984,7 @@
         <v>5.30999994277954</v>
       </c>
       <c r="G1008" t="s">
-        <v>643</v>
+        <v>642</v>
       </c>
       <c r="H1008" t="s">
         <v>9</v>
@@ -31010,7 +31010,7 @@
         <v>5.28000020980835</v>
       </c>
       <c r="G1009" t="s">
-        <v>631</v>
+        <v>630</v>
       </c>
       <c r="H1009" t="s">
         <v>9</v>
@@ -31036,7 +31036,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G1010" t="s">
-        <v>629</v>
+        <v>628</v>
       </c>
       <c r="H1010" t="s">
         <v>9</v>
@@ -31062,7 +31062,7 @@
         <v>5.23999977111816</v>
       </c>
       <c r="G1011" t="s">
-        <v>644</v>
+        <v>643</v>
       </c>
       <c r="H1011" t="s">
         <v>9</v>
@@ -31088,7 +31088,7 @@
         <v>5.28999996185303</v>
       </c>
       <c r="G1012" t="s">
-        <v>645</v>
+        <v>644</v>
       </c>
       <c r="H1012" t="s">
         <v>9</v>
@@ -31114,7 +31114,7 @@
         <v>5.25</v>
       </c>
       <c r="G1013" t="s">
-        <v>646</v>
+        <v>645</v>
       </c>
       <c r="H1013" t="s">
         <v>9</v>
@@ -31140,7 +31140,7 @@
         <v>5.28000020980835</v>
       </c>
       <c r="G1014" t="s">
-        <v>631</v>
+        <v>630</v>
       </c>
       <c r="H1014" t="s">
         <v>9</v>
@@ -31192,7 +31192,7 @@
         <v>5.28999996185303</v>
       </c>
       <c r="G1016" t="s">
-        <v>645</v>
+        <v>644</v>
       </c>
       <c r="H1016" t="s">
         <v>9</v>
@@ -31218,7 +31218,7 @@
         <v>5.28999996185303</v>
       </c>
       <c r="G1017" t="s">
-        <v>645</v>
+        <v>644</v>
       </c>
       <c r="H1017" t="s">
         <v>9</v>
@@ -31244,7 +31244,7 @@
         <v>5.21999979019165</v>
       </c>
       <c r="G1018" t="s">
-        <v>630</v>
+        <v>629</v>
       </c>
       <c r="H1018" t="s">
         <v>9</v>
@@ -31270,7 +31270,7 @@
         <v>5.26999998092651</v>
       </c>
       <c r="G1019" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
       <c r="H1019" t="s">
         <v>9</v>
@@ -31322,7 +31322,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G1021" t="s">
-        <v>629</v>
+        <v>628</v>
       </c>
       <c r="H1021" t="s">
         <v>9</v>
@@ -31348,7 +31348,7 @@
         <v>5.48000001907349</v>
       </c>
       <c r="G1022" t="s">
-        <v>641</v>
+        <v>640</v>
       </c>
       <c r="H1022" t="s">
         <v>9</v>
@@ -31374,7 +31374,7 @@
         <v>5.55000019073486</v>
       </c>
       <c r="G1023" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="H1023" t="s">
         <v>9</v>
@@ -31400,7 +31400,7 @@
         <v>5.46000003814697</v>
       </c>
       <c r="G1024" t="s">
-        <v>639</v>
+        <v>638</v>
       </c>
       <c r="H1024" t="s">
         <v>9</v>
@@ -31426,7 +31426,7 @@
         <v>5.42999982833862</v>
       </c>
       <c r="G1025" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="H1025" t="s">
         <v>9</v>
@@ -31452,7 +31452,7 @@
         <v>5.36999988555908</v>
       </c>
       <c r="G1026" t="s">
-        <v>650</v>
+        <v>649</v>
       </c>
       <c r="H1026" t="s">
         <v>9</v>
@@ -31478,7 +31478,7 @@
         <v>5.5</v>
       </c>
       <c r="G1027" t="s">
-        <v>637</v>
+        <v>636</v>
       </c>
       <c r="H1027" t="s">
         <v>9</v>
@@ -31504,7 +31504,7 @@
         <v>5.51000022888184</v>
       </c>
       <c r="G1028" t="s">
-        <v>651</v>
+        <v>650</v>
       </c>
       <c r="H1028" t="s">
         <v>9</v>
@@ -31530,7 +31530,7 @@
         <v>5.44000005722046</v>
       </c>
       <c r="G1029" t="s">
-        <v>642</v>
+        <v>641</v>
       </c>
       <c r="H1029" t="s">
         <v>9</v>
@@ -31556,7 +31556,7 @@
         <v>5.44000005722046</v>
       </c>
       <c r="G1030" t="s">
-        <v>642</v>
+        <v>641</v>
       </c>
       <c r="H1030" t="s">
         <v>9</v>
@@ -31582,7 +31582,7 @@
         <v>5.28999996185303</v>
       </c>
       <c r="G1031" t="s">
-        <v>645</v>
+        <v>644</v>
       </c>
       <c r="H1031" t="s">
         <v>9</v>
@@ -31608,7 +31608,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G1032" t="s">
-        <v>652</v>
+        <v>651</v>
       </c>
       <c r="H1032" t="s">
         <v>9</v>
@@ -31634,7 +31634,7 @@
         <v>5.15000009536743</v>
       </c>
       <c r="G1033" t="s">
-        <v>625</v>
+        <v>624</v>
       </c>
       <c r="H1033" t="s">
         <v>9</v>
@@ -31660,7 +31660,7 @@
         <v>5.28000020980835</v>
       </c>
       <c r="G1034" t="s">
-        <v>631</v>
+        <v>630</v>
       </c>
       <c r="H1034" t="s">
         <v>9</v>
@@ -31686,7 +31686,7 @@
         <v>5.17999982833862</v>
       </c>
       <c r="G1035" t="s">
-        <v>553</v>
+        <v>552</v>
       </c>
       <c r="H1035" t="s">
         <v>9</v>
@@ -31712,7 +31712,7 @@
         <v>4.92999982833862</v>
       </c>
       <c r="G1036" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="H1036" t="s">
         <v>9</v>
@@ -31738,7 +31738,7 @@
         <v>4.84000015258789</v>
       </c>
       <c r="G1037" t="s">
-        <v>654</v>
+        <v>653</v>
       </c>
       <c r="H1037" t="s">
         <v>9</v>
@@ -31764,7 +31764,7 @@
         <v>4.8899998664856</v>
       </c>
       <c r="G1038" t="s">
-        <v>655</v>
+        <v>654</v>
       </c>
       <c r="H1038" t="s">
         <v>9</v>
@@ -31790,7 +31790,7 @@
         <v>5.03000020980835</v>
       </c>
       <c r="G1039" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="H1039" t="s">
         <v>9</v>
@@ -31842,7 +31842,7 @@
         <v>5.07999992370605</v>
       </c>
       <c r="G1041" t="s">
-        <v>656</v>
+        <v>655</v>
       </c>
       <c r="H1041" t="s">
         <v>9</v>
@@ -31868,7 +31868,7 @@
         <v>4.96000003814697</v>
       </c>
       <c r="G1042" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="H1042" t="s">
         <v>9</v>
@@ -31894,7 +31894,7 @@
         <v>4.92999982833862</v>
       </c>
       <c r="G1043" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="H1043" t="s">
         <v>9</v>
@@ -31946,7 +31946,7 @@
         <v>5.21999979019165</v>
       </c>
       <c r="G1045" t="s">
-        <v>630</v>
+        <v>629</v>
       </c>
       <c r="H1045" t="s">
         <v>9</v>
@@ -31972,7 +31972,7 @@
         <v>5.15000009536743</v>
       </c>
       <c r="G1046" t="s">
-        <v>625</v>
+        <v>624</v>
       </c>
       <c r="H1046" t="s">
         <v>9</v>
@@ -31998,7 +31998,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G1047" t="s">
-        <v>652</v>
+        <v>651</v>
       </c>
       <c r="H1047" t="s">
         <v>9</v>
@@ -32024,7 +32024,7 @@
         <v>5.42999982833862</v>
       </c>
       <c r="G1048" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="H1048" t="s">
         <v>9</v>
@@ -32050,7 +32050,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G1049" t="s">
-        <v>652</v>
+        <v>651</v>
       </c>
       <c r="H1049" t="s">
         <v>9</v>
@@ -32076,7 +32076,7 @@
         <v>5.3600001335144</v>
       </c>
       <c r="G1050" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="H1050" t="s">
         <v>9</v>
@@ -32102,7 +32102,7 @@
         <v>5.34999990463257</v>
       </c>
       <c r="G1051" t="s">
-        <v>632</v>
+        <v>631</v>
       </c>
       <c r="H1051" t="s">
         <v>9</v>
@@ -32128,7 +32128,7 @@
         <v>5.34999990463257</v>
       </c>
       <c r="G1052" t="s">
-        <v>632</v>
+        <v>631</v>
       </c>
       <c r="H1052" t="s">
         <v>9</v>
@@ -32154,7 +32154,7 @@
         <v>4.80999994277954</v>
       </c>
       <c r="G1053" t="s">
-        <v>557</v>
+        <v>556</v>
       </c>
       <c r="H1053" t="s">
         <v>9</v>
@@ -32180,7 +32180,7 @@
         <v>4.78999996185303</v>
       </c>
       <c r="G1054" t="s">
-        <v>658</v>
+        <v>657</v>
       </c>
       <c r="H1054" t="s">
         <v>9</v>
@@ -32206,7 +32206,7 @@
         <v>4.80999994277954</v>
       </c>
       <c r="G1055" t="s">
-        <v>557</v>
+        <v>556</v>
       </c>
       <c r="H1055" t="s">
         <v>9</v>
@@ -32232,7 +32232,7 @@
         <v>4.6399998664856</v>
       </c>
       <c r="G1056" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="H1056" t="s">
         <v>9</v>
@@ -32258,7 +32258,7 @@
         <v>4.5</v>
       </c>
       <c r="G1057" t="s">
-        <v>583</v>
+        <v>582</v>
       </c>
       <c r="H1057" t="s">
         <v>9</v>
@@ -32284,7 +32284,7 @@
         <v>4.5</v>
       </c>
       <c r="G1058" t="s">
-        <v>583</v>
+        <v>582</v>
       </c>
       <c r="H1058" t="s">
         <v>9</v>
@@ -32310,7 +32310,7 @@
         <v>4.36499977111816</v>
       </c>
       <c r="G1059" t="s">
-        <v>659</v>
+        <v>658</v>
       </c>
       <c r="H1059" t="s">
         <v>9</v>
@@ -32336,7 +32336,7 @@
         <v>4.27500009536743</v>
       </c>
       <c r="G1060" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="H1060" t="s">
         <v>9</v>
@@ -32362,7 +32362,7 @@
         <v>4.03999996185303</v>
       </c>
       <c r="G1061" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
       <c r="H1061" t="s">
         <v>9</v>
@@ -32388,7 +32388,7 @@
         <v>3.91499996185303</v>
       </c>
       <c r="G1062" t="s">
-        <v>661</v>
+        <v>660</v>
       </c>
       <c r="H1062" t="s">
         <v>9</v>
@@ -32414,7 +32414,7 @@
         <v>3.85500001907349</v>
       </c>
       <c r="G1063" t="s">
-        <v>662</v>
+        <v>661</v>
       </c>
       <c r="H1063" t="s">
         <v>9</v>
@@ -32440,7 +32440,7 @@
         <v>3.68499994277954</v>
       </c>
       <c r="G1064" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="H1064" t="s">
         <v>9</v>
@@ -32466,7 +32466,7 @@
         <v>3.75</v>
       </c>
       <c r="G1065" t="s">
-        <v>664</v>
+        <v>663</v>
       </c>
       <c r="H1065" t="s">
         <v>9</v>
@@ -32492,7 +32492,7 @@
         <v>3.26500010490417</v>
       </c>
       <c r="G1066" t="s">
-        <v>665</v>
+        <v>664</v>
       </c>
       <c r="H1066" t="s">
         <v>9</v>
@@ -32518,7 +32518,7 @@
         <v>3.39499998092651</v>
       </c>
       <c r="G1067" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
       <c r="H1067" t="s">
         <v>9</v>
@@ -32544,7 +32544,7 @@
         <v>3.33500003814697</v>
       </c>
       <c r="G1068" t="s">
-        <v>667</v>
+        <v>666</v>
       </c>
       <c r="H1068" t="s">
         <v>9</v>
@@ -32570,7 +32570,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G1069" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="H1069" t="s">
         <v>9</v>
@@ -32596,7 +32596,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G1070" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="H1070" t="s">
         <v>9</v>
@@ -32622,7 +32622,7 @@
         <v>3.10500001907349</v>
       </c>
       <c r="G1071" t="s">
-        <v>670</v>
+        <v>669</v>
       </c>
       <c r="H1071" t="s">
         <v>9</v>
@@ -32648,7 +32648,7 @@
         <v>3.25999999046326</v>
       </c>
       <c r="G1072" t="s">
-        <v>671</v>
+        <v>670</v>
       </c>
       <c r="H1072" t="s">
         <v>9</v>
@@ -32674,7 +32674,7 @@
         <v>3.03999996185303</v>
       </c>
       <c r="G1073" t="s">
-        <v>672</v>
+        <v>671</v>
       </c>
       <c r="H1073" t="s">
         <v>9</v>
@@ -32700,7 +32700,7 @@
         <v>3.17000007629395</v>
       </c>
       <c r="G1074" t="s">
-        <v>673</v>
+        <v>672</v>
       </c>
       <c r="H1074" t="s">
         <v>9</v>
@@ -32726,7 +32726,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G1075" t="s">
-        <v>674</v>
+        <v>673</v>
       </c>
       <c r="H1075" t="s">
         <v>9</v>
@@ -32752,7 +32752,7 @@
         <v>3.27500009536743</v>
       </c>
       <c r="G1076" t="s">
-        <v>675</v>
+        <v>674</v>
       </c>
       <c r="H1076" t="s">
         <v>9</v>
@@ -32778,7 +32778,7 @@
         <v>3.14499998092651</v>
       </c>
       <c r="G1077" t="s">
-        <v>676</v>
+        <v>675</v>
       </c>
       <c r="H1077" t="s">
         <v>9</v>
@@ -32804,7 +32804,7 @@
         <v>3.09500002861023</v>
       </c>
       <c r="G1078" t="s">
-        <v>677</v>
+        <v>676</v>
       </c>
       <c r="H1078" t="s">
         <v>9</v>
@@ -32830,7 +32830,7 @@
         <v>3.30999994277954</v>
       </c>
       <c r="G1079" t="s">
-        <v>678</v>
+        <v>677</v>
       </c>
       <c r="H1079" t="s">
         <v>9</v>
@@ -32856,7 +32856,7 @@
         <v>3.22000002861023</v>
       </c>
       <c r="G1080" t="s">
-        <v>679</v>
+        <v>678</v>
       </c>
       <c r="H1080" t="s">
         <v>9</v>
@@ -32882,7 +32882,7 @@
         <v>3.24499988555908</v>
       </c>
       <c r="G1081" t="s">
-        <v>680</v>
+        <v>679</v>
       </c>
       <c r="H1081" t="s">
         <v>9</v>
@@ -32908,7 +32908,7 @@
         <v>3.15000009536743</v>
       </c>
       <c r="G1082" t="s">
-        <v>681</v>
+        <v>680</v>
       </c>
       <c r="H1082" t="s">
         <v>9</v>
@@ -32934,7 +32934,7 @@
         <v>3.15499997138977</v>
       </c>
       <c r="G1083" t="s">
-        <v>682</v>
+        <v>681</v>
       </c>
       <c r="H1083" t="s">
         <v>9</v>
@@ -32960,7 +32960,7 @@
         <v>3.3199999332428</v>
       </c>
       <c r="G1084" t="s">
-        <v>683</v>
+        <v>682</v>
       </c>
       <c r="H1084" t="s">
         <v>9</v>
@@ -32986,7 +32986,7 @@
         <v>3.36500000953674</v>
       </c>
       <c r="G1085" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="H1085" t="s">
         <v>9</v>
@@ -33012,7 +33012,7 @@
         <v>3.41000008583069</v>
       </c>
       <c r="G1086" t="s">
-        <v>685</v>
+        <v>684</v>
       </c>
       <c r="H1086" t="s">
         <v>9</v>
@@ -33038,7 +33038,7 @@
         <v>3.5</v>
       </c>
       <c r="G1087" t="s">
-        <v>686</v>
+        <v>685</v>
       </c>
       <c r="H1087" t="s">
         <v>9</v>
@@ -33064,7 +33064,7 @@
         <v>3.45000004768372</v>
       </c>
       <c r="G1088" t="s">
-        <v>687</v>
+        <v>686</v>
       </c>
       <c r="H1088" t="s">
         <v>9</v>
@@ -33090,7 +33090,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G1089" t="s">
-        <v>674</v>
+        <v>673</v>
       </c>
       <c r="H1089" t="s">
         <v>9</v>
@@ -33116,7 +33116,7 @@
         <v>3.42000007629395</v>
       </c>
       <c r="G1090" t="s">
-        <v>688</v>
+        <v>687</v>
       </c>
       <c r="H1090" t="s">
         <v>9</v>
@@ -33142,7 +33142,7 @@
         <v>3.42499995231628</v>
       </c>
       <c r="G1091" t="s">
-        <v>689</v>
+        <v>688</v>
       </c>
       <c r="H1091" t="s">
         <v>9</v>
@@ -33168,7 +33168,7 @@
         <v>3.47000002861023</v>
       </c>
       <c r="G1092" t="s">
-        <v>690</v>
+        <v>689</v>
       </c>
       <c r="H1092" t="s">
         <v>9</v>
@@ -33194,7 +33194,7 @@
         <v>3.47000002861023</v>
       </c>
       <c r="G1093" t="s">
-        <v>690</v>
+        <v>689</v>
       </c>
       <c r="H1093" t="s">
         <v>9</v>
@@ -33220,7 +33220,7 @@
         <v>3.45000004768372</v>
       </c>
       <c r="G1094" t="s">
-        <v>687</v>
+        <v>686</v>
       </c>
       <c r="H1094" t="s">
         <v>9</v>
@@ -33246,7 +33246,7 @@
         <v>3.50500011444092</v>
       </c>
       <c r="G1095" t="s">
-        <v>691</v>
+        <v>690</v>
       </c>
       <c r="H1095" t="s">
         <v>9</v>
@@ -33272,7 +33272,7 @@
         <v>3.42499995231628</v>
       </c>
       <c r="G1096" t="s">
-        <v>689</v>
+        <v>688</v>
       </c>
       <c r="H1096" t="s">
         <v>9</v>
@@ -33298,7 +33298,7 @@
         <v>3.4300000667572</v>
       </c>
       <c r="G1097" t="s">
-        <v>692</v>
+        <v>691</v>
       </c>
       <c r="H1097" t="s">
         <v>9</v>
@@ -33324,7 +33324,7 @@
         <v>3.45000004768372</v>
       </c>
       <c r="G1098" t="s">
-        <v>687</v>
+        <v>686</v>
       </c>
       <c r="H1098" t="s">
         <v>9</v>
@@ -33350,7 +33350,7 @@
         <v>3.46499991416931</v>
       </c>
       <c r="G1099" t="s">
-        <v>693</v>
+        <v>692</v>
       </c>
       <c r="H1099" t="s">
         <v>9</v>
@@ -33376,7 +33376,7 @@
         <v>3.43499994277954</v>
       </c>
       <c r="G1100" t="s">
-        <v>694</v>
+        <v>693</v>
       </c>
       <c r="H1100" t="s">
         <v>9</v>
@@ -33402,7 +33402,7 @@
         <v>3.42499995231628</v>
       </c>
       <c r="G1101" t="s">
-        <v>689</v>
+        <v>688</v>
       </c>
       <c r="H1101" t="s">
         <v>9</v>
@@ -33428,7 +33428,7 @@
         <v>3.42499995231628</v>
       </c>
       <c r="G1102" t="s">
-        <v>689</v>
+        <v>688</v>
       </c>
       <c r="H1102" t="s">
         <v>9</v>
@@ -33454,7 +33454,7 @@
         <v>3.61500000953674</v>
       </c>
       <c r="G1103" t="s">
-        <v>695</v>
+        <v>694</v>
       </c>
       <c r="H1103" t="s">
         <v>9</v>
@@ -33480,7 +33480,7 @@
         <v>3.53999996185303</v>
       </c>
       <c r="G1104" t="s">
-        <v>696</v>
+        <v>695</v>
       </c>
       <c r="H1104" t="s">
         <v>9</v>
@@ -33506,7 +33506,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G1105" t="s">
-        <v>697</v>
+        <v>696</v>
       </c>
       <c r="H1105" t="s">
         <v>9</v>
@@ -33532,7 +33532,7 @@
         <v>3.58999991416931</v>
       </c>
       <c r="G1106" t="s">
-        <v>698</v>
+        <v>697</v>
       </c>
       <c r="H1106" t="s">
         <v>9</v>
@@ -33558,7 +33558,7 @@
         <v>3.64499998092651</v>
       </c>
       <c r="G1107" t="s">
-        <v>699</v>
+        <v>698</v>
       </c>
       <c r="H1107" t="s">
         <v>9</v>
@@ -33584,7 +33584,7 @@
         <v>3.5</v>
       </c>
       <c r="G1108" t="s">
-        <v>686</v>
+        <v>685</v>
       </c>
       <c r="H1108" t="s">
         <v>9</v>
@@ -33610,7 +33610,7 @@
         <v>3.5</v>
       </c>
       <c r="G1109" t="s">
-        <v>686</v>
+        <v>685</v>
       </c>
       <c r="H1109" t="s">
         <v>9</v>
@@ -33636,7 +33636,7 @@
         <v>3.52999997138977</v>
       </c>
       <c r="G1110" t="s">
-        <v>700</v>
+        <v>699</v>
       </c>
       <c r="H1110" t="s">
         <v>9</v>
@@ -33662,7 +33662,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G1111" t="s">
-        <v>701</v>
+        <v>700</v>
       </c>
       <c r="H1111" t="s">
         <v>9</v>
@@ -33688,7 +33688,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G1112" t="s">
-        <v>697</v>
+        <v>696</v>
       </c>
       <c r="H1112" t="s">
         <v>9</v>
@@ -33714,7 +33714,7 @@
         <v>3.71499991416931</v>
       </c>
       <c r="G1113" t="s">
-        <v>702</v>
+        <v>701</v>
       </c>
       <c r="H1113" t="s">
         <v>9</v>
@@ -33740,7 +33740,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G1114" t="s">
-        <v>703</v>
+        <v>702</v>
       </c>
       <c r="H1114" t="s">
         <v>9</v>
@@ -33766,7 +33766,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G1115" t="s">
-        <v>704</v>
+        <v>703</v>
       </c>
       <c r="H1115" t="s">
         <v>9</v>
@@ -33792,7 +33792,7 @@
         <v>3.75</v>
       </c>
       <c r="G1116" t="s">
-        <v>664</v>
+        <v>663</v>
       </c>
       <c r="H1116" t="s">
         <v>9</v>
@@ -33818,7 +33818,7 @@
         <v>3.66499996185303</v>
       </c>
       <c r="G1117" t="s">
-        <v>705</v>
+        <v>704</v>
       </c>
       <c r="H1117" t="s">
         <v>9</v>
@@ -33844,7 +33844,7 @@
         <v>3.70499992370605</v>
       </c>
       <c r="G1118" t="s">
-        <v>706</v>
+        <v>705</v>
       </c>
       <c r="H1118" t="s">
         <v>9</v>
@@ -33870,7 +33870,7 @@
         <v>3.65000009536743</v>
       </c>
       <c r="G1119" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="H1119" t="s">
         <v>9</v>
@@ -33896,7 +33896,7 @@
         <v>3.63000011444092</v>
       </c>
       <c r="G1120" t="s">
-        <v>708</v>
+        <v>707</v>
       </c>
       <c r="H1120" t="s">
         <v>9</v>
@@ -33922,7 +33922,7 @@
         <v>3.75</v>
       </c>
       <c r="G1121" t="s">
-        <v>664</v>
+        <v>663</v>
       </c>
       <c r="H1121" t="s">
         <v>9</v>
@@ -33948,7 +33948,7 @@
         <v>3.84999990463257</v>
       </c>
       <c r="G1122" t="s">
-        <v>709</v>
+        <v>708</v>
       </c>
       <c r="H1122" t="s">
         <v>9</v>
@@ -33974,7 +33974,7 @@
         <v>3.94000005722046</v>
       </c>
       <c r="G1123" t="s">
-        <v>710</v>
+        <v>709</v>
       </c>
       <c r="H1123" t="s">
         <v>9</v>
@@ -34000,7 +34000,7 @@
         <v>4</v>
       </c>
       <c r="G1124" t="s">
-        <v>711</v>
+        <v>710</v>
       </c>
       <c r="H1124" t="s">
         <v>9</v>
@@ -34026,7 +34026,7 @@
         <v>4.05499982833862</v>
       </c>
       <c r="G1125" t="s">
-        <v>712</v>
+        <v>711</v>
       </c>
       <c r="H1125" t="s">
         <v>9</v>
@@ -34052,7 +34052,7 @@
         <v>4.03000020980835</v>
       </c>
       <c r="G1126" t="s">
-        <v>713</v>
+        <v>712</v>
       </c>
       <c r="H1126" t="s">
         <v>9</v>
@@ -34078,7 +34078,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G1127" t="s">
-        <v>714</v>
+        <v>713</v>
       </c>
       <c r="H1127" t="s">
         <v>9</v>
@@ -34104,7 +34104,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G1128" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="H1128" t="s">
         <v>9</v>
@@ -34130,7 +34130,7 @@
         <v>3.83500003814697</v>
       </c>
       <c r="G1129" t="s">
-        <v>716</v>
+        <v>715</v>
       </c>
       <c r="H1129" t="s">
         <v>9</v>
@@ -34156,7 +34156,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G1130" t="s">
-        <v>717</v>
+        <v>716</v>
       </c>
       <c r="H1130" t="s">
         <v>9</v>
@@ -34182,7 +34182,7 @@
         <v>3.91499996185303</v>
       </c>
       <c r="G1131" t="s">
-        <v>661</v>
+        <v>660</v>
       </c>
       <c r="H1131" t="s">
         <v>9</v>
@@ -34208,7 +34208,7 @@
         <v>3.93499994277954</v>
       </c>
       <c r="G1132" t="s">
-        <v>718</v>
+        <v>717</v>
       </c>
       <c r="H1132" t="s">
         <v>9</v>
@@ -34234,7 +34234,7 @@
         <v>3.9300000667572</v>
       </c>
       <c r="G1133" t="s">
-        <v>719</v>
+        <v>718</v>
       </c>
       <c r="H1133" t="s">
         <v>9</v>
@@ -34260,7 +34260,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G1134" t="s">
-        <v>720</v>
+        <v>719</v>
       </c>
       <c r="H1134" t="s">
         <v>9</v>
@@ -34286,7 +34286,7 @@
         <v>3.92499995231628</v>
       </c>
       <c r="G1135" t="s">
-        <v>721</v>
+        <v>720</v>
       </c>
       <c r="H1135" t="s">
         <v>9</v>
@@ -34312,7 +34312,7 @@
         <v>3.94000005722046</v>
       </c>
       <c r="G1136" t="s">
-        <v>710</v>
+        <v>709</v>
       </c>
       <c r="H1136" t="s">
         <v>9</v>
@@ -34338,7 +34338,7 @@
         <v>3.93499994277954</v>
       </c>
       <c r="G1137" t="s">
-        <v>718</v>
+        <v>717</v>
       </c>
       <c r="H1137" t="s">
         <v>9</v>
@@ -34364,7 +34364,7 @@
         <v>3.91499996185303</v>
       </c>
       <c r="G1138" t="s">
-        <v>661</v>
+        <v>660</v>
       </c>
       <c r="H1138" t="s">
         <v>9</v>
@@ -34390,7 +34390,7 @@
         <v>3.99000000953674</v>
       </c>
       <c r="G1139" t="s">
-        <v>722</v>
+        <v>721</v>
       </c>
       <c r="H1139" t="s">
         <v>9</v>
@@ -34416,7 +34416,7 @@
         <v>4.00500011444092</v>
       </c>
       <c r="G1140" t="s">
-        <v>723</v>
+        <v>722</v>
       </c>
       <c r="H1140" t="s">
         <v>9</v>
@@ -34442,7 +34442,7 @@
         <v>4.01000022888184</v>
       </c>
       <c r="G1141" t="s">
-        <v>724</v>
+        <v>723</v>
       </c>
       <c r="H1141" t="s">
         <v>9</v>
@@ -34468,7 +34468,7 @@
         <v>4</v>
       </c>
       <c r="G1142" t="s">
-        <v>711</v>
+        <v>710</v>
       </c>
       <c r="H1142" t="s">
         <v>9</v>
@@ -34494,7 +34494,7 @@
         <v>4.26999998092651</v>
       </c>
       <c r="G1143" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="H1143" t="s">
         <v>9</v>
@@ -34520,7 +34520,7 @@
         <v>4.21000003814697</v>
       </c>
       <c r="G1144" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
       <c r="H1144" t="s">
         <v>9</v>
@@ -34546,7 +34546,7 @@
         <v>4.25</v>
       </c>
       <c r="G1145" t="s">
-        <v>725</v>
+        <v>724</v>
       </c>
       <c r="H1145" t="s">
         <v>9</v>
@@ -34572,7 +34572,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G1146" t="s">
-        <v>726</v>
+        <v>725</v>
       </c>
       <c r="H1146" t="s">
         <v>9</v>
@@ -34598,7 +34598,7 @@
         <v>4.10500001907349</v>
       </c>
       <c r="G1147" t="s">
-        <v>727</v>
+        <v>726</v>
       </c>
       <c r="H1147" t="s">
         <v>9</v>
@@ -34624,7 +34624,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G1148" t="s">
-        <v>728</v>
+        <v>727</v>
       </c>
       <c r="H1148" t="s">
         <v>9</v>
@@ -34650,7 +34650,7 @@
         <v>3.98000001907349</v>
       </c>
       <c r="G1149" t="s">
-        <v>729</v>
+        <v>728</v>
       </c>
       <c r="H1149" t="s">
         <v>9</v>
@@ -34676,7 +34676,7 @@
         <v>3.96000003814697</v>
       </c>
       <c r="G1150" t="s">
-        <v>730</v>
+        <v>729</v>
       </c>
       <c r="H1150" t="s">
         <v>9</v>
@@ -34702,7 +34702,7 @@
         <v>3.88000011444092</v>
       </c>
       <c r="G1151" t="s">
-        <v>731</v>
+        <v>730</v>
       </c>
       <c r="H1151" t="s">
         <v>9</v>
@@ -34728,7 +34728,7 @@
         <v>3.88000011444092</v>
       </c>
       <c r="G1152" t="s">
-        <v>731</v>
+        <v>730</v>
       </c>
       <c r="H1152" t="s">
         <v>9</v>
@@ -34754,7 +34754,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G1153" t="s">
-        <v>732</v>
+        <v>731</v>
       </c>
       <c r="H1153" t="s">
         <v>9</v>
@@ -34780,7 +34780,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G1154" t="s">
-        <v>733</v>
+        <v>732</v>
       </c>
       <c r="H1154" t="s">
         <v>9</v>
@@ -34806,7 +34806,7 @@
         <v>3.82999992370605</v>
       </c>
       <c r="G1155" t="s">
-        <v>734</v>
+        <v>733</v>
       </c>
       <c r="H1155" t="s">
         <v>9</v>
@@ -34832,7 +34832,7 @@
         <v>3.86500000953674</v>
       </c>
       <c r="G1156" t="s">
-        <v>735</v>
+        <v>734</v>
       </c>
       <c r="H1156" t="s">
         <v>9</v>
@@ -34858,7 +34858,7 @@
         <v>3.75500011444092</v>
       </c>
       <c r="G1157" t="s">
-        <v>736</v>
+        <v>735</v>
       </c>
       <c r="H1157" t="s">
         <v>9</v>
@@ -34884,7 +34884,7 @@
         <v>3.77500009536743</v>
       </c>
       <c r="G1158" t="s">
-        <v>737</v>
+        <v>736</v>
       </c>
       <c r="H1158" t="s">
         <v>9</v>
@@ -34910,7 +34910,7 @@
         <v>3.75</v>
       </c>
       <c r="G1159" t="s">
-        <v>738</v>
+        <v>737</v>
       </c>
       <c r="H1159" t="s">
         <v>9</v>
@@ -34936,7 +34936,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G1160" t="s">
-        <v>739</v>
+        <v>738</v>
       </c>
       <c r="H1160" t="s">
         <v>9</v>
@@ -34962,7 +34962,7 @@
         <v>3.71000003814697</v>
       </c>
       <c r="G1161" t="s">
-        <v>740</v>
+        <v>739</v>
       </c>
       <c r="H1161" t="s">
         <v>9</v>
@@ -34988,7 +34988,7 @@
         <v>3.65000009536743</v>
       </c>
       <c r="G1162" t="s">
-        <v>741</v>
+        <v>740</v>
       </c>
       <c r="H1162" t="s">
         <v>9</v>
@@ -35014,7 +35014,7 @@
         <v>3.65000009536743</v>
       </c>
       <c r="G1163" t="s">
-        <v>741</v>
+        <v>740</v>
       </c>
       <c r="H1163" t="s">
         <v>9</v>
@@ -35040,7 +35040,7 @@
         <v>3.5</v>
       </c>
       <c r="G1164" t="s">
-        <v>742</v>
+        <v>741</v>
       </c>
       <c r="H1164" t="s">
         <v>9</v>
@@ -35066,7 +35066,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G1165" t="s">
-        <v>739</v>
+        <v>738</v>
       </c>
       <c r="H1165" t="s">
         <v>9</v>
@@ -35092,7 +35092,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G1166" t="s">
-        <v>739</v>
+        <v>738</v>
       </c>
       <c r="H1166" t="s">
         <v>9</v>
@@ -35118,7 +35118,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G1167" t="s">
-        <v>743</v>
+        <v>742</v>
       </c>
       <c r="H1167" t="s">
         <v>9</v>
@@ -35144,7 +35144,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G1168" t="s">
-        <v>744</v>
+        <v>743</v>
       </c>
       <c r="H1168" t="s">
         <v>9</v>
@@ -35170,7 +35170,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G1169" t="s">
-        <v>743</v>
+        <v>742</v>
       </c>
       <c r="H1169" t="s">
         <v>9</v>
@@ -35196,7 +35196,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G1170" t="s">
-        <v>743</v>
+        <v>742</v>
       </c>
       <c r="H1170" t="s">
         <v>9</v>
@@ -35222,7 +35222,7 @@
         <v>3.625</v>
       </c>
       <c r="G1171" t="s">
-        <v>745</v>
+        <v>744</v>
       </c>
       <c r="H1171" t="s">
         <v>9</v>
@@ -35248,7 +35248,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G1172" t="s">
-        <v>743</v>
+        <v>742</v>
       </c>
       <c r="H1172" t="s">
         <v>9</v>
@@ -35274,7 +35274,7 @@
         <v>3.57999992370605</v>
       </c>
       <c r="G1173" t="s">
-        <v>746</v>
+        <v>745</v>
       </c>
       <c r="H1173" t="s">
         <v>9</v>
@@ -35300,7 +35300,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G1174" t="s">
-        <v>743</v>
+        <v>742</v>
       </c>
       <c r="H1174" t="s">
         <v>9</v>
@@ -35326,7 +35326,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G1175" t="s">
-        <v>743</v>
+        <v>742</v>
       </c>
       <c r="H1175" t="s">
         <v>9</v>
@@ -35352,7 +35352,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G1176" t="s">
-        <v>743</v>
+        <v>742</v>
       </c>
       <c r="H1176" t="s">
         <v>9</v>
@@ -35378,7 +35378,7 @@
         <v>3.5699999332428</v>
       </c>
       <c r="G1177" t="s">
-        <v>747</v>
+        <v>746</v>
       </c>
       <c r="H1177" t="s">
         <v>9</v>
@@ -35404,7 +35404,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G1178" t="s">
-        <v>748</v>
+        <v>747</v>
       </c>
       <c r="H1178" t="s">
         <v>9</v>
@@ -35430,7 +35430,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G1179" t="s">
-        <v>748</v>
+        <v>747</v>
       </c>
       <c r="H1179" t="s">
         <v>9</v>
@@ -35456,7 +35456,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G1180" t="s">
-        <v>748</v>
+        <v>747</v>
       </c>
       <c r="H1180" t="s">
         <v>9</v>
@@ -35482,7 +35482,7 @@
         <v>3.50999999046326</v>
       </c>
       <c r="G1181" t="s">
-        <v>749</v>
+        <v>748</v>
       </c>
       <c r="H1181" t="s">
         <v>9</v>
@@ -35508,7 +35508,7 @@
         <v>3.50500011444092</v>
       </c>
       <c r="G1182" t="s">
-        <v>750</v>
+        <v>749</v>
       </c>
       <c r="H1182" t="s">
         <v>9</v>
@@ -35534,7 +35534,7 @@
         <v>3.44000005722046</v>
       </c>
       <c r="G1183" t="s">
-        <v>751</v>
+        <v>750</v>
       </c>
       <c r="H1183" t="s">
         <v>9</v>
@@ -35560,7 +35560,7 @@
         <v>3.5</v>
       </c>
       <c r="G1184" t="s">
-        <v>742</v>
+        <v>741</v>
       </c>
       <c r="H1184" t="s">
         <v>9</v>
@@ -35586,7 +35586,7 @@
         <v>3.4449999332428</v>
       </c>
       <c r="G1185" t="s">
-        <v>752</v>
+        <v>751</v>
       </c>
       <c r="H1185" t="s">
         <v>9</v>
@@ -35612,7 +35612,7 @@
         <v>3.48000001907349</v>
       </c>
       <c r="G1186" t="s">
-        <v>753</v>
+        <v>752</v>
       </c>
       <c r="H1186" t="s">
         <v>9</v>
@@ -35638,7 +35638,7 @@
         <v>3.46000003814697</v>
       </c>
       <c r="G1187" t="s">
-        <v>754</v>
+        <v>753</v>
       </c>
       <c r="H1187" t="s">
         <v>9</v>
@@ -35664,7 +35664,7 @@
         <v>3.36999988555908</v>
       </c>
       <c r="G1188" t="s">
-        <v>755</v>
+        <v>754</v>
       </c>
       <c r="H1188" t="s">
         <v>9</v>
@@ -35690,7 +35690,7 @@
         <v>3.34999990463257</v>
       </c>
       <c r="G1189" t="s">
-        <v>756</v>
+        <v>755</v>
       </c>
       <c r="H1189" t="s">
         <v>9</v>
@@ -35716,7 +35716,7 @@
         <v>3.32999992370605</v>
       </c>
       <c r="G1190" t="s">
-        <v>757</v>
+        <v>756</v>
       </c>
       <c r="H1190" t="s">
         <v>9</v>
@@ -35742,7 +35742,7 @@
         <v>3.32999992370605</v>
       </c>
       <c r="G1191" t="s">
-        <v>757</v>
+        <v>756</v>
       </c>
       <c r="H1191" t="s">
         <v>9</v>
@@ -35768,7 +35768,7 @@
         <v>3.3199999332428</v>
       </c>
       <c r="G1192" t="s">
-        <v>758</v>
+        <v>757</v>
       </c>
       <c r="H1192" t="s">
         <v>9</v>
@@ -35794,7 +35794,7 @@
         <v>3.3199999332428</v>
       </c>
       <c r="G1193" t="s">
-        <v>758</v>
+        <v>757</v>
       </c>
       <c r="H1193" t="s">
         <v>9</v>
@@ -35820,7 +35820,7 @@
         <v>3.49499988555908</v>
       </c>
       <c r="G1194" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="H1194" t="s">
         <v>9</v>
@@ -35846,7 +35846,7 @@
         <v>3.47000002861023</v>
       </c>
       <c r="G1195" t="s">
-        <v>760</v>
+        <v>759</v>
       </c>
       <c r="H1195" t="s">
         <v>9</v>
@@ -35872,7 +35872,7 @@
         <v>3.44000005722046</v>
       </c>
       <c r="G1196" t="s">
-        <v>751</v>
+        <v>750</v>
       </c>
       <c r="H1196" t="s">
         <v>9</v>
@@ -35898,7 +35898,7 @@
         <v>3.45499992370605</v>
       </c>
       <c r="G1197" t="s">
-        <v>761</v>
+        <v>760</v>
       </c>
       <c r="H1197" t="s">
         <v>9</v>
@@ -35924,7 +35924,7 @@
         <v>3.375</v>
       </c>
       <c r="G1198" t="s">
-        <v>762</v>
+        <v>761</v>
       </c>
       <c r="H1198" t="s">
         <v>9</v>
@@ -35950,7 +35950,7 @@
         <v>3.28500008583069</v>
       </c>
       <c r="G1199" t="s">
-        <v>763</v>
+        <v>762</v>
       </c>
       <c r="H1199" t="s">
         <v>9</v>
@@ -35976,7 +35976,7 @@
         <v>3.20499992370605</v>
       </c>
       <c r="G1200" t="s">
-        <v>764</v>
+        <v>763</v>
       </c>
       <c r="H1200" t="s">
         <v>9</v>
@@ -36002,7 +36002,7 @@
         <v>3.20499992370605</v>
       </c>
       <c r="G1201" t="s">
-        <v>764</v>
+        <v>763</v>
       </c>
       <c r="H1201" t="s">
         <v>9</v>
@@ -36028,7 +36028,7 @@
         <v>3.24499988555908</v>
       </c>
       <c r="G1202" t="s">
-        <v>765</v>
+        <v>764</v>
       </c>
       <c r="H1202" t="s">
         <v>9</v>
@@ -36054,7 +36054,7 @@
         <v>3.17000007629395</v>
       </c>
       <c r="G1203" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="H1203" t="s">
         <v>9</v>
@@ -36080,7 +36080,7 @@
         <v>3.14000010490417</v>
       </c>
       <c r="G1204" t="s">
-        <v>767</v>
+        <v>766</v>
       </c>
       <c r="H1204" t="s">
         <v>9</v>
@@ -36106,7 +36106,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G1205" t="s">
-        <v>768</v>
+        <v>767</v>
       </c>
       <c r="H1205" t="s">
         <v>9</v>
@@ -36132,7 +36132,7 @@
         <v>3.22000002861023</v>
       </c>
       <c r="G1206" t="s">
-        <v>769</v>
+        <v>768</v>
       </c>
       <c r="H1206" t="s">
         <v>9</v>
@@ -36158,7 +36158,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G1207" t="s">
-        <v>770</v>
+        <v>769</v>
       </c>
       <c r="H1207" t="s">
         <v>9</v>
@@ -36184,7 +36184,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G1208" t="s">
-        <v>771</v>
+        <v>770</v>
       </c>
       <c r="H1208" t="s">
         <v>9</v>
@@ -36210,7 +36210,7 @@
         <v>3.22000002861023</v>
       </c>
       <c r="G1209" t="s">
-        <v>769</v>
+        <v>768</v>
       </c>
       <c r="H1209" t="s">
         <v>9</v>
@@ -36236,7 +36236,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G1210" t="s">
-        <v>770</v>
+        <v>769</v>
       </c>
       <c r="H1210" t="s">
         <v>9</v>
@@ -36262,7 +36262,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G1211" t="s">
-        <v>772</v>
+        <v>771</v>
       </c>
       <c r="H1211" t="s">
         <v>9</v>
@@ -36288,7 +36288,7 @@
         <v>3.34999990463257</v>
       </c>
       <c r="G1212" t="s">
-        <v>756</v>
+        <v>755</v>
       </c>
       <c r="H1212" t="s">
         <v>9</v>
@@ -36314,7 +36314,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G1213" t="s">
-        <v>772</v>
+        <v>771</v>
       </c>
       <c r="H1213" t="s">
         <v>9</v>
@@ -36340,7 +36340,7 @@
         <v>3.47000002861023</v>
       </c>
       <c r="G1214" t="s">
-        <v>760</v>
+        <v>759</v>
       </c>
       <c r="H1214" t="s">
         <v>9</v>
@@ -36366,7 +36366,7 @@
         <v>3.34999990463257</v>
       </c>
       <c r="G1215" t="s">
-        <v>756</v>
+        <v>755</v>
       </c>
       <c r="H1215" t="s">
         <v>9</v>
@@ -36392,7 +36392,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G1216" t="s">
-        <v>770</v>
+        <v>769</v>
       </c>
       <c r="H1216" t="s">
         <v>9</v>
@@ -36418,7 +36418,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G1217" t="s">
-        <v>770</v>
+        <v>769</v>
       </c>
       <c r="H1217" t="s">
         <v>9</v>
@@ -36444,7 +36444,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G1218" t="s">
-        <v>770</v>
+        <v>769</v>
       </c>
       <c r="H1218" t="s">
         <v>9</v>
@@ -36470,7 +36470,7 @@
         <v>3.19000005722046</v>
       </c>
       <c r="G1219" t="s">
-        <v>773</v>
+        <v>772</v>
       </c>
       <c r="H1219" t="s">
         <v>9</v>
@@ -36496,7 +36496,7 @@
         <v>3.16499996185303</v>
       </c>
       <c r="G1220" t="s">
-        <v>774</v>
+        <v>773</v>
       </c>
       <c r="H1220" t="s">
         <v>9</v>
@@ -36522,7 +36522,7 @@
         <v>3.17499995231628</v>
       </c>
       <c r="G1221" t="s">
-        <v>775</v>
+        <v>774</v>
       </c>
       <c r="H1221" t="s">
         <v>9</v>
@@ -36548,7 +36548,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G1222" t="s">
-        <v>776</v>
+        <v>775</v>
       </c>
       <c r="H1222" t="s">
         <v>9</v>
@@ -36574,7 +36574,7 @@
         <v>3.07999992370605</v>
       </c>
       <c r="G1223" t="s">
-        <v>777</v>
+        <v>776</v>
       </c>
       <c r="H1223" t="s">
         <v>9</v>
@@ -36600,7 +36600,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G1224" t="s">
-        <v>778</v>
+        <v>777</v>
       </c>
       <c r="H1224" t="s">
         <v>9</v>
@@ -36626,7 +36626,7 @@
         <v>3.03500008583069</v>
       </c>
       <c r="G1225" t="s">
-        <v>779</v>
+        <v>778</v>
       </c>
       <c r="H1225" t="s">
         <v>9</v>
@@ -36652,7 +36652,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G1226" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
       <c r="H1226" t="s">
         <v>9</v>
@@ -36678,7 +36678,7 @@
         <v>2.96000003814697</v>
       </c>
       <c r="G1227" t="s">
-        <v>781</v>
+        <v>780</v>
       </c>
       <c r="H1227" t="s">
         <v>9</v>
@@ -36704,7 +36704,7 @@
         <v>2.92000007629395</v>
       </c>
       <c r="G1228" t="s">
-        <v>782</v>
+        <v>781</v>
       </c>
       <c r="H1228" t="s">
         <v>9</v>
@@ -36730,7 +36730,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G1229" t="s">
-        <v>783</v>
+        <v>782</v>
       </c>
       <c r="H1229" t="s">
         <v>9</v>
@@ -36756,7 +36756,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G1230" t="s">
-        <v>784</v>
+        <v>783</v>
       </c>
       <c r="H1230" t="s">
         <v>9</v>
@@ -36782,7 +36782,7 @@
         <v>2.88499999046326</v>
       </c>
       <c r="G1231" t="s">
-        <v>785</v>
+        <v>784</v>
       </c>
       <c r="H1231" t="s">
         <v>9</v>
@@ -36808,7 +36808,7 @@
         <v>2.92000007629395</v>
       </c>
       <c r="G1232" t="s">
-        <v>782</v>
+        <v>781</v>
       </c>
       <c r="H1232" t="s">
         <v>9</v>
@@ -36834,7 +36834,7 @@
         <v>2.8199999332428</v>
       </c>
       <c r="G1233" t="s">
-        <v>786</v>
+        <v>785</v>
       </c>
       <c r="H1233" t="s">
         <v>9</v>
@@ -36860,7 +36860,7 @@
         <v>2.91000008583069</v>
       </c>
       <c r="G1234" t="s">
-        <v>787</v>
+        <v>786</v>
       </c>
       <c r="H1234" t="s">
         <v>9</v>
@@ -36886,7 +36886,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G1235" t="s">
-        <v>772</v>
+        <v>771</v>
       </c>
       <c r="H1235" t="s">
         <v>9</v>
@@ -36912,7 +36912,7 @@
         <v>3.32999992370605</v>
       </c>
       <c r="G1236" t="s">
-        <v>757</v>
+        <v>756</v>
       </c>
       <c r="H1236" t="s">
         <v>9</v>
@@ -36938,7 +36938,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G1237" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="H1237" t="s">
         <v>9</v>
@@ -36964,7 +36964,7 @@
         <v>3.33999991416931</v>
       </c>
       <c r="G1238" t="s">
-        <v>789</v>
+        <v>788</v>
       </c>
       <c r="H1238" t="s">
         <v>9</v>
@@ -36990,7 +36990,7 @@
         <v>3.32999992370605</v>
       </c>
       <c r="G1239" t="s">
-        <v>757</v>
+        <v>756</v>
       </c>
       <c r="H1239" t="s">
         <v>9</v>
@@ -37016,7 +37016,7 @@
         <v>3.39499998092651</v>
       </c>
       <c r="G1240" t="s">
-        <v>790</v>
+        <v>789</v>
       </c>
       <c r="H1240" t="s">
         <v>9</v>
@@ -37042,7 +37042,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G1241" t="s">
-        <v>748</v>
+        <v>747</v>
       </c>
       <c r="H1241" t="s">
         <v>9</v>
@@ -37068,7 +37068,7 @@
         <v>3.625</v>
       </c>
       <c r="G1242" t="s">
-        <v>745</v>
+        <v>744</v>
       </c>
       <c r="H1242" t="s">
         <v>9</v>
@@ -37094,7 +37094,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G1243" t="s">
-        <v>743</v>
+        <v>742</v>
       </c>
       <c r="H1243" t="s">
         <v>9</v>
@@ -37120,7 +37120,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G1244" t="s">
-        <v>743</v>
+        <v>742</v>
       </c>
       <c r="H1244" t="s">
         <v>9</v>
@@ -37146,7 +37146,7 @@
         <v>3.57999992370605</v>
       </c>
       <c r="G1245" t="s">
-        <v>746</v>
+        <v>745</v>
       </c>
       <c r="H1245" t="s">
         <v>9</v>
@@ -37172,7 +37172,7 @@
         <v>3.59500002861023</v>
       </c>
       <c r="G1246" t="s">
-        <v>791</v>
+        <v>790</v>
       </c>
       <c r="H1246" t="s">
         <v>9</v>
@@ -37198,7 +37198,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G1247" t="s">
-        <v>743</v>
+        <v>742</v>
       </c>
       <c r="H1247" t="s">
         <v>9</v>
@@ -37224,7 +37224,7 @@
         <v>3.58500003814697</v>
       </c>
       <c r="G1248" t="s">
-        <v>792</v>
+        <v>791</v>
       </c>
       <c r="H1248" t="s">
         <v>9</v>
@@ -37250,7 +37250,7 @@
         <v>3.58500003814697</v>
       </c>
       <c r="G1249" t="s">
-        <v>792</v>
+        <v>791</v>
       </c>
       <c r="H1249" t="s">
         <v>9</v>
@@ -37276,7 +37276,7 @@
         <v>3.60999989509583</v>
       </c>
       <c r="G1250" t="s">
-        <v>793</v>
+        <v>792</v>
       </c>
       <c r="H1250" t="s">
         <v>9</v>
@@ -37302,7 +37302,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G1251" t="s">
-        <v>743</v>
+        <v>742</v>
       </c>
       <c r="H1251" t="s">
         <v>9</v>
@@ -37328,7 +37328,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G1252" t="s">
-        <v>794</v>
+        <v>793</v>
       </c>
       <c r="H1252" t="s">
         <v>9</v>
@@ -37354,7 +37354,7 @@
         <v>3.73000001907349</v>
       </c>
       <c r="G1253" t="s">
-        <v>795</v>
+        <v>794</v>
       </c>
       <c r="H1253" t="s">
         <v>9</v>
@@ -37380,7 +37380,7 @@
         <v>3.75</v>
       </c>
       <c r="G1254" t="s">
-        <v>738</v>
+        <v>737</v>
       </c>
       <c r="H1254" t="s">
         <v>9</v>
@@ -37406,7 +37406,7 @@
         <v>3.82999992370605</v>
       </c>
       <c r="G1255" t="s">
-        <v>734</v>
+        <v>733</v>
       </c>
       <c r="H1255" t="s">
         <v>9</v>
@@ -37432,7 +37432,7 @@
         <v>3.93499994277954</v>
       </c>
       <c r="G1256" t="s">
-        <v>796</v>
+        <v>795</v>
       </c>
       <c r="H1256" t="s">
         <v>9</v>
@@ -37458,7 +37458,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G1257" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
       <c r="H1257" t="s">
         <v>9</v>
@@ -37484,7 +37484,7 @@
         <v>3.94000005722046</v>
       </c>
       <c r="G1258" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
       <c r="H1258" t="s">
         <v>9</v>
@@ -37510,7 +37510,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G1259" t="s">
-        <v>732</v>
+        <v>731</v>
       </c>
       <c r="H1259" t="s">
         <v>9</v>
@@ -37536,7 +37536,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G1260" t="s">
-        <v>732</v>
+        <v>731</v>
       </c>
       <c r="H1260" t="s">
         <v>9</v>
@@ -37562,7 +37562,7 @@
         <v>3.91000008583069</v>
       </c>
       <c r="G1261" t="s">
-        <v>799</v>
+        <v>798</v>
       </c>
       <c r="H1261" t="s">
         <v>9</v>
@@ -37588,7 +37588,7 @@
         <v>3.95000004768372</v>
       </c>
       <c r="G1262" t="s">
-        <v>800</v>
+        <v>799</v>
       </c>
       <c r="H1262" t="s">
         <v>9</v>
@@ -37614,7 +37614,7 @@
         <v>3.97000002861023</v>
       </c>
       <c r="G1263" t="s">
-        <v>801</v>
+        <v>800</v>
       </c>
       <c r="H1263" t="s">
         <v>9</v>
@@ -37640,7 +37640,7 @@
         <v>3.89499998092651</v>
       </c>
       <c r="G1264" t="s">
-        <v>802</v>
+        <v>801</v>
       </c>
       <c r="H1264" t="s">
         <v>9</v>
@@ -37666,7 +37666,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G1265" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
       <c r="H1265" t="s">
         <v>9</v>
@@ -37692,7 +37692,7 @@
         <v>3.95000004768372</v>
       </c>
       <c r="G1266" t="s">
-        <v>800</v>
+        <v>799</v>
       </c>
       <c r="H1266" t="s">
         <v>9</v>
@@ -37718,7 +37718,7 @@
         <v>3.875</v>
       </c>
       <c r="G1267" t="s">
-        <v>803</v>
+        <v>802</v>
       </c>
       <c r="H1267" t="s">
         <v>9</v>
@@ -37744,7 +37744,7 @@
         <v>4.01999998092651</v>
       </c>
       <c r="G1268" t="s">
-        <v>804</v>
+        <v>803</v>
       </c>
       <c r="H1268" t="s">
         <v>9</v>
@@ -37770,7 +37770,7 @@
         <v>4.15999984741211</v>
       </c>
       <c r="G1269" t="s">
-        <v>805</v>
+        <v>804</v>
       </c>
       <c r="H1269" t="s">
         <v>9</v>
@@ -37796,7 +37796,7 @@
         <v>4.15999984741211</v>
       </c>
       <c r="G1270" t="s">
-        <v>805</v>
+        <v>804</v>
       </c>
       <c r="H1270" t="s">
         <v>9</v>
@@ -37822,7 +37822,7 @@
         <v>4.25</v>
       </c>
       <c r="G1271" t="s">
-        <v>725</v>
+        <v>724</v>
       </c>
       <c r="H1271" t="s">
         <v>9</v>
@@ -37848,7 +37848,7 @@
         <v>4.21000003814697</v>
       </c>
       <c r="G1272" t="s">
-        <v>806</v>
+        <v>805</v>
       </c>
       <c r="H1272" t="s">
         <v>9</v>
@@ -37874,7 +37874,7 @@
         <v>4.23999977111816</v>
       </c>
       <c r="G1273" t="s">
-        <v>807</v>
+        <v>806</v>
       </c>
       <c r="H1273" t="s">
         <v>9</v>
@@ -37900,7 +37900,7 @@
         <v>4.23999977111816</v>
       </c>
       <c r="G1274" t="s">
-        <v>807</v>
+        <v>806</v>
       </c>
       <c r="H1274" t="s">
         <v>9</v>
@@ -37926,7 +37926,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G1275" t="s">
-        <v>808</v>
+        <v>807</v>
       </c>
       <c r="H1275" t="s">
         <v>9</v>
@@ -37952,7 +37952,7 @@
         <v>4.21000003814697</v>
       </c>
       <c r="G1276" t="s">
-        <v>806</v>
+        <v>805</v>
       </c>
       <c r="H1276" t="s">
         <v>9</v>
@@ -37978,7 +37978,7 @@
         <v>4.13500022888184</v>
       </c>
       <c r="G1277" t="s">
-        <v>809</v>
+        <v>808</v>
       </c>
       <c r="H1277" t="s">
         <v>9</v>
@@ -38004,7 +38004,7 @@
         <v>4.1399998664856</v>
       </c>
       <c r="G1278" t="s">
-        <v>810</v>
+        <v>809</v>
       </c>
       <c r="H1278" t="s">
         <v>9</v>
@@ -38030,7 +38030,7 @@
         <v>4.13000011444092</v>
       </c>
       <c r="G1279" t="s">
-        <v>811</v>
+        <v>810</v>
       </c>
       <c r="H1279" t="s">
         <v>9</v>
@@ -38056,7 +38056,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G1280" t="s">
-        <v>812</v>
+        <v>811</v>
       </c>
       <c r="H1280" t="s">
         <v>9</v>
@@ -38082,7 +38082,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G1281" t="s">
-        <v>812</v>
+        <v>811</v>
       </c>
       <c r="H1281" t="s">
         <v>9</v>
@@ -38108,7 +38108,7 @@
         <v>4.07999992370605</v>
       </c>
       <c r="G1282" t="s">
-        <v>813</v>
+        <v>812</v>
       </c>
       <c r="H1282" t="s">
         <v>9</v>
@@ -38134,7 +38134,7 @@
         <v>4.01000022888184</v>
       </c>
       <c r="G1283" t="s">
-        <v>814</v>
+        <v>813</v>
       </c>
       <c r="H1283" t="s">
         <v>9</v>
@@ -38160,7 +38160,7 @@
         <v>4</v>
       </c>
       <c r="G1284" t="s">
-        <v>815</v>
+        <v>814</v>
       </c>
       <c r="H1284" t="s">
         <v>9</v>
@@ -38186,7 +38186,7 @@
         <v>4</v>
       </c>
       <c r="G1285" t="s">
-        <v>815</v>
+        <v>814</v>
       </c>
       <c r="H1285" t="s">
         <v>9</v>
@@ -38212,7 +38212,7 @@
         <v>3.98000001907349</v>
       </c>
       <c r="G1286" t="s">
-        <v>729</v>
+        <v>728</v>
       </c>
       <c r="H1286" t="s">
         <v>9</v>
@@ -38238,7 +38238,7 @@
         <v>3.97000002861023</v>
       </c>
       <c r="G1287" t="s">
-        <v>801</v>
+        <v>800</v>
       </c>
       <c r="H1287" t="s">
         <v>9</v>
@@ -38264,7 +38264,7 @@
         <v>4.03999996185303</v>
       </c>
       <c r="G1288" t="s">
-        <v>816</v>
+        <v>815</v>
       </c>
       <c r="H1288" t="s">
         <v>9</v>
@@ -38290,7 +38290,7 @@
         <v>3.98000001907349</v>
       </c>
       <c r="G1289" t="s">
-        <v>729</v>
+        <v>728</v>
       </c>
       <c r="H1289" t="s">
         <v>9</v>
@@ -38316,7 +38316,7 @@
         <v>3.94000005722046</v>
       </c>
       <c r="G1290" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
       <c r="H1290" t="s">
         <v>9</v>
@@ -38342,7 +38342,7 @@
         <v>3.94000005722046</v>
       </c>
       <c r="G1291" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
       <c r="H1291" t="s">
         <v>9</v>
@@ -38368,7 +38368,7 @@
         <v>4</v>
       </c>
       <c r="G1292" t="s">
-        <v>815</v>
+        <v>814</v>
       </c>
       <c r="H1292" t="s">
         <v>9</v>
@@ -38394,7 +38394,7 @@
         <v>4.01000022888184</v>
       </c>
       <c r="G1293" t="s">
-        <v>814</v>
+        <v>813</v>
       </c>
       <c r="H1293" t="s">
         <v>9</v>
@@ -38420,7 +38420,7 @@
         <v>4</v>
       </c>
       <c r="G1294" t="s">
-        <v>815</v>
+        <v>814</v>
       </c>
       <c r="H1294" t="s">
         <v>9</v>
@@ -38446,7 +38446,7 @@
         <v>3.96499991416931</v>
       </c>
       <c r="G1295" t="s">
-        <v>817</v>
+        <v>816</v>
       </c>
       <c r="H1295" t="s">
         <v>9</v>
@@ -38472,7 +38472,7 @@
         <v>4.01999998092651</v>
       </c>
       <c r="G1296" t="s">
-        <v>804</v>
+        <v>803</v>
       </c>
       <c r="H1296" t="s">
         <v>9</v>
@@ -38498,7 +38498,7 @@
         <v>4.05999994277954</v>
       </c>
       <c r="G1297" t="s">
-        <v>818</v>
+        <v>817</v>
       </c>
       <c r="H1297" t="s">
         <v>9</v>
@@ -38524,7 +38524,7 @@
         <v>4.04500007629395</v>
       </c>
       <c r="G1298" t="s">
-        <v>819</v>
+        <v>818</v>
       </c>
       <c r="H1298" t="s">
         <v>9</v>
@@ -38550,7 +38550,7 @@
         <v>4.03999996185303</v>
       </c>
       <c r="G1299" t="s">
-        <v>816</v>
+        <v>815</v>
       </c>
       <c r="H1299" t="s">
         <v>9</v>
@@ -38576,7 +38576,7 @@
         <v>4.07999992370605</v>
       </c>
       <c r="G1300" t="s">
-        <v>813</v>
+        <v>812</v>
       </c>
       <c r="H1300" t="s">
         <v>9</v>
@@ -38602,7 +38602,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G1301" t="s">
-        <v>728</v>
+        <v>727</v>
       </c>
       <c r="H1301" t="s">
         <v>9</v>
@@ -38628,7 +38628,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G1302" t="s">
-        <v>728</v>
+        <v>727</v>
       </c>
       <c r="H1302" t="s">
         <v>9</v>
@@ -38654,7 +38654,7 @@
         <v>4</v>
       </c>
       <c r="G1303" t="s">
-        <v>815</v>
+        <v>814</v>
       </c>
       <c r="H1303" t="s">
         <v>9</v>
@@ -38680,7 +38680,7 @@
         <v>4.04500007629395</v>
       </c>
       <c r="G1304" t="s">
-        <v>819</v>
+        <v>818</v>
       </c>
       <c r="H1304" t="s">
         <v>9</v>
@@ -38706,7 +38706,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G1305" t="s">
-        <v>812</v>
+        <v>811</v>
       </c>
       <c r="H1305" t="s">
         <v>9</v>
@@ -38732,7 +38732,7 @@
         <v>4.15999984741211</v>
       </c>
       <c r="G1306" t="s">
-        <v>805</v>
+        <v>804</v>
       </c>
       <c r="H1306" t="s">
         <v>9</v>
@@ -38758,7 +38758,7 @@
         <v>4.2350001335144</v>
       </c>
       <c r="G1307" t="s">
-        <v>820</v>
+        <v>819</v>
       </c>
       <c r="H1307" t="s">
         <v>9</v>
@@ -38784,7 +38784,7 @@
         <v>4.23000001907349</v>
       </c>
       <c r="G1308" t="s">
-        <v>821</v>
+        <v>820</v>
       </c>
       <c r="H1308" t="s">
         <v>9</v>
@@ -38810,7 +38810,7 @@
         <v>4.21999979019165</v>
       </c>
       <c r="G1309" t="s">
-        <v>822</v>
+        <v>821</v>
       </c>
       <c r="H1309" t="s">
         <v>9</v>
@@ -38836,7 +38836,7 @@
         <v>4.19000005722046</v>
       </c>
       <c r="G1310" t="s">
-        <v>823</v>
+        <v>822</v>
       </c>
       <c r="H1310" t="s">
         <v>9</v>
@@ -38862,7 +38862,7 @@
         <v>4.23000001907349</v>
       </c>
       <c r="G1311" t="s">
-        <v>821</v>
+        <v>820</v>
       </c>
       <c r="H1311" t="s">
         <v>9</v>
@@ -38888,7 +38888,7 @@
         <v>4.26999998092651</v>
       </c>
       <c r="G1312" t="s">
-        <v>824</v>
+        <v>823</v>
       </c>
       <c r="H1312" t="s">
         <v>9</v>
@@ -38914,7 +38914,7 @@
         <v>4.34000015258789</v>
       </c>
       <c r="G1313" t="s">
-        <v>825</v>
+        <v>824</v>
       </c>
       <c r="H1313" t="s">
         <v>9</v>
@@ -38940,7 +38940,7 @@
         <v>4.19000005722046</v>
       </c>
       <c r="G1314" t="s">
-        <v>823</v>
+        <v>822</v>
       </c>
       <c r="H1314" t="s">
         <v>9</v>
@@ -38966,7 +38966,7 @@
         <v>4.16499996185303</v>
       </c>
       <c r="G1315" t="s">
-        <v>826</v>
+        <v>825</v>
       </c>
       <c r="H1315" t="s">
         <v>9</v>
@@ -38992,7 +38992,7 @@
         <v>4.23999977111816</v>
       </c>
       <c r="G1316" t="s">
-        <v>807</v>
+        <v>806</v>
       </c>
       <c r="H1316" t="s">
         <v>9</v>
@@ -39018,7 +39018,7 @@
         <v>4.26000022888184</v>
       </c>
       <c r="G1317" t="s">
-        <v>827</v>
+        <v>826</v>
       </c>
       <c r="H1317" t="s">
         <v>9</v>
@@ -39044,7 +39044,7 @@
         <v>4.23000001907349</v>
       </c>
       <c r="G1318" t="s">
-        <v>821</v>
+        <v>820</v>
       </c>
       <c r="H1318" t="s">
         <v>9</v>
@@ -39070,7 +39070,7 @@
         <v>4.27500009536743</v>
       </c>
       <c r="G1319" t="s">
-        <v>828</v>
+        <v>827</v>
       </c>
       <c r="H1319" t="s">
         <v>9</v>
@@ -39096,7 +39096,7 @@
         <v>4.27500009536743</v>
       </c>
       <c r="G1320" t="s">
-        <v>828</v>
+        <v>827</v>
       </c>
       <c r="H1320" t="s">
         <v>9</v>
@@ -39122,7 +39122,7 @@
         <v>4.25500011444092</v>
       </c>
       <c r="G1321" t="s">
-        <v>829</v>
+        <v>828</v>
       </c>
       <c r="H1321" t="s">
         <v>9</v>
@@ -39148,7 +39148,7 @@
         <v>4.2649998664856</v>
       </c>
       <c r="G1322" t="s">
-        <v>830</v>
+        <v>829</v>
       </c>
       <c r="H1322" t="s">
         <v>9</v>
@@ -39174,7 +39174,7 @@
         <v>4.20499992370605</v>
       </c>
       <c r="G1323" t="s">
-        <v>831</v>
+        <v>830</v>
       </c>
       <c r="H1323" t="s">
         <v>9</v>
@@ -39200,7 +39200,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G1324" t="s">
-        <v>726</v>
+        <v>725</v>
       </c>
       <c r="H1324" t="s">
         <v>9</v>
@@ -39226,7 +39226,7 @@
         <v>4.21000003814697</v>
       </c>
       <c r="G1325" t="s">
-        <v>806</v>
+        <v>805</v>
       </c>
       <c r="H1325" t="s">
         <v>9</v>
@@ -39252,7 +39252,7 @@
         <v>4.17000007629395</v>
       </c>
       <c r="G1326" t="s">
-        <v>832</v>
+        <v>831</v>
       </c>
       <c r="H1326" t="s">
         <v>9</v>
@@ -39278,7 +39278,7 @@
         <v>4.25500011444092</v>
       </c>
       <c r="G1327" t="s">
-        <v>829</v>
+        <v>828</v>
       </c>
       <c r="H1327" t="s">
         <v>9</v>
@@ -39304,7 +39304,7 @@
         <v>4.13000011444092</v>
       </c>
       <c r="G1328" t="s">
-        <v>811</v>
+        <v>810</v>
       </c>
       <c r="H1328" t="s">
         <v>9</v>
@@ -39330,7 +39330,7 @@
         <v>4.09000015258789</v>
       </c>
       <c r="G1329" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
       <c r="H1329" t="s">
         <v>9</v>
@@ -39356,7 +39356,7 @@
         <v>4.01999998092651</v>
       </c>
       <c r="G1330" t="s">
-        <v>804</v>
+        <v>803</v>
       </c>
       <c r="H1330" t="s">
         <v>9</v>
@@ -39382,7 +39382,7 @@
         <v>4.01000022888184</v>
       </c>
       <c r="G1331" t="s">
-        <v>814</v>
+        <v>813</v>
       </c>
       <c r="H1331" t="s">
         <v>9</v>
@@ -39408,7 +39408,7 @@
         <v>4.07000017166138</v>
       </c>
       <c r="G1332" t="s">
-        <v>833</v>
+        <v>832</v>
       </c>
       <c r="H1332" t="s">
         <v>9</v>
@@ -39434,7 +39434,7 @@
         <v>4.19000005722046</v>
       </c>
       <c r="G1333" t="s">
-        <v>823</v>
+        <v>822</v>
       </c>
       <c r="H1333" t="s">
         <v>9</v>
@@ -39460,7 +39460,7 @@
         <v>4.21000003814697</v>
       </c>
       <c r="G1334" t="s">
-        <v>806</v>
+        <v>805</v>
       </c>
       <c r="H1334" t="s">
         <v>9</v>
@@ -39486,7 +39486,7 @@
         <v>4.14499998092651</v>
       </c>
       <c r="G1335" t="s">
-        <v>834</v>
+        <v>833</v>
       </c>
       <c r="H1335" t="s">
         <v>9</v>
@@ -39512,7 +39512,7 @@
         <v>4.15999984741211</v>
       </c>
       <c r="G1336" t="s">
-        <v>805</v>
+        <v>804</v>
       </c>
       <c r="H1336" t="s">
         <v>9</v>
@@ -39538,7 +39538,7 @@
         <v>4.19500017166138</v>
       </c>
       <c r="G1337" t="s">
-        <v>835</v>
+        <v>834</v>
       </c>
       <c r="H1337" t="s">
         <v>9</v>
@@ -39564,7 +39564,7 @@
         <v>4.17000007629395</v>
       </c>
       <c r="G1338" t="s">
-        <v>832</v>
+        <v>831</v>
       </c>
       <c r="H1338" t="s">
         <v>9</v>
@@ -39590,7 +39590,7 @@
         <v>4.28000020980835</v>
       </c>
       <c r="G1339" t="s">
-        <v>836</v>
+        <v>835</v>
       </c>
       <c r="H1339" t="s">
         <v>9</v>
@@ -39616,7 +39616,7 @@
         <v>4.34000015258789</v>
       </c>
       <c r="G1340" t="s">
-        <v>825</v>
+        <v>824</v>
       </c>
       <c r="H1340" t="s">
         <v>9</v>
@@ -39642,7 +39642,7 @@
         <v>4.44000005722046</v>
       </c>
       <c r="G1341" t="s">
-        <v>837</v>
+        <v>836</v>
       </c>
       <c r="H1341" t="s">
         <v>9</v>
@@ -39668,7 +39668,7 @@
         <v>4.45499992370605</v>
       </c>
       <c r="G1342" t="s">
-        <v>838</v>
+        <v>837</v>
       </c>
       <c r="H1342" t="s">
         <v>9</v>
@@ -39694,7 +39694,7 @@
         <v>4.51999998092651</v>
       </c>
       <c r="G1343" t="s">
-        <v>839</v>
+        <v>838</v>
       </c>
       <c r="H1343" t="s">
         <v>9</v>
@@ -39720,7 +39720,7 @@
         <v>4.47499990463257</v>
       </c>
       <c r="G1344" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="H1344" t="s">
         <v>9</v>
@@ -39746,7 +39746,7 @@
         <v>4.57000017166138</v>
       </c>
       <c r="G1345" t="s">
-        <v>841</v>
+        <v>840</v>
       </c>
       <c r="H1345" t="s">
         <v>9</v>
@@ -39772,7 +39772,7 @@
         <v>4.65500020980835</v>
       </c>
       <c r="G1346" t="s">
-        <v>842</v>
+        <v>841</v>
       </c>
       <c r="H1346" t="s">
         <v>9</v>
@@ -39798,7 +39798,7 @@
         <v>4.64499998092651</v>
       </c>
       <c r="G1347" t="s">
-        <v>843</v>
+        <v>842</v>
       </c>
       <c r="H1347" t="s">
         <v>9</v>
@@ -39824,7 +39824,7 @@
         <v>4.61499977111816</v>
       </c>
       <c r="G1348" t="s">
-        <v>844</v>
+        <v>843</v>
       </c>
       <c r="H1348" t="s">
         <v>9</v>
@@ -39850,7 +39850,7 @@
         <v>4.68499994277954</v>
       </c>
       <c r="G1349" t="s">
-        <v>845</v>
+        <v>844</v>
       </c>
       <c r="H1349" t="s">
         <v>9</v>
@@ -39876,7 +39876,7 @@
         <v>4.61499977111816</v>
       </c>
       <c r="G1350" t="s">
-        <v>844</v>
+        <v>843</v>
       </c>
       <c r="H1350" t="s">
         <v>9</v>
@@ -39902,7 +39902,7 @@
         <v>4.61999988555908</v>
       </c>
       <c r="G1351" t="s">
-        <v>846</v>
+        <v>845</v>
       </c>
       <c r="H1351" t="s">
         <v>9</v>
@@ -39928,7 +39928,7 @@
         <v>4.57999992370605</v>
       </c>
       <c r="G1352" t="s">
-        <v>847</v>
+        <v>846</v>
       </c>
       <c r="H1352" t="s">
         <v>9</v>
@@ -39954,7 +39954,7 @@
         <v>4.57000017166138</v>
       </c>
       <c r="G1353" t="s">
-        <v>841</v>
+        <v>840</v>
       </c>
       <c r="H1353" t="s">
         <v>9</v>
@@ -39980,7 +39980,7 @@
         <v>4.53999996185303</v>
       </c>
       <c r="G1354" t="s">
-        <v>848</v>
+        <v>847</v>
       </c>
       <c r="H1354" t="s">
         <v>9</v>
@@ -40006,7 +40006,7 @@
         <v>4.5</v>
       </c>
       <c r="G1355" t="s">
-        <v>849</v>
+        <v>848</v>
       </c>
       <c r="H1355" t="s">
         <v>9</v>
@@ -40032,7 +40032,7 @@
         <v>4.44000005722046</v>
       </c>
       <c r="G1356" t="s">
-        <v>850</v>
+        <v>849</v>
       </c>
       <c r="H1356" t="s">
         <v>9</v>
@@ -40058,7 +40058,7 @@
         <v>4.49499988555908</v>
       </c>
       <c r="G1357" t="s">
-        <v>851</v>
+        <v>850</v>
       </c>
       <c r="H1357" t="s">
         <v>9</v>
@@ -40084,7 +40084,7 @@
         <v>4.52500009536743</v>
       </c>
       <c r="G1358" t="s">
-        <v>852</v>
+        <v>851</v>
       </c>
       <c r="H1358" t="s">
         <v>9</v>
@@ -40110,7 +40110,7 @@
         <v>4.55999994277954</v>
       </c>
       <c r="G1359" t="s">
-        <v>853</v>
+        <v>852</v>
       </c>
       <c r="H1359" t="s">
         <v>9</v>
@@ -40136,7 +40136,7 @@
         <v>4.5</v>
       </c>
       <c r="G1360" t="s">
-        <v>849</v>
+        <v>848</v>
       </c>
       <c r="H1360" t="s">
         <v>9</v>
@@ -40162,7 +40162,7 @@
         <v>4.5</v>
       </c>
       <c r="G1361" t="s">
-        <v>849</v>
+        <v>848</v>
       </c>
       <c r="H1361" t="s">
         <v>9</v>
@@ -40188,7 +40188,7 @@
         <v>4.5</v>
       </c>
       <c r="G1362" t="s">
-        <v>849</v>
+        <v>848</v>
       </c>
       <c r="H1362" t="s">
         <v>9</v>
@@ -40214,7 +40214,7 @@
         <v>4.43499994277954</v>
       </c>
       <c r="G1363" t="s">
-        <v>854</v>
+        <v>853</v>
       </c>
       <c r="H1363" t="s">
         <v>9</v>
@@ -40240,7 +40240,7 @@
         <v>4.46500015258789</v>
       </c>
       <c r="G1364" t="s">
-        <v>855</v>
+        <v>854</v>
       </c>
       <c r="H1364" t="s">
         <v>9</v>
@@ -40266,7 +40266,7 @@
         <v>4.48000001907349</v>
       </c>
       <c r="G1365" t="s">
-        <v>856</v>
+        <v>855</v>
       </c>
       <c r="H1365" t="s">
         <v>9</v>
@@ -40292,7 +40292,7 @@
         <v>4.44000005722046</v>
       </c>
       <c r="G1366" t="s">
-        <v>850</v>
+        <v>849</v>
       </c>
       <c r="H1366" t="s">
         <v>9</v>
@@ -40318,7 +40318,7 @@
         <v>4.42000007629395</v>
       </c>
       <c r="G1367" t="s">
-        <v>857</v>
+        <v>856</v>
       </c>
       <c r="H1367" t="s">
         <v>9</v>
@@ -40344,7 +40344,7 @@
         <v>4.44999980926514</v>
       </c>
       <c r="G1368" t="s">
-        <v>858</v>
+        <v>857</v>
       </c>
       <c r="H1368" t="s">
         <v>9</v>
@@ -40370,7 +40370,7 @@
         <v>4.40999984741211</v>
       </c>
       <c r="G1369" t="s">
-        <v>859</v>
+        <v>858</v>
       </c>
       <c r="H1369" t="s">
         <v>9</v>
@@ -40396,7 +40396,7 @@
         <v>4.42000007629395</v>
       </c>
       <c r="G1370" t="s">
-        <v>857</v>
+        <v>856</v>
       </c>
       <c r="H1370" t="s">
         <v>9</v>
@@ -40422,7 +40422,7 @@
         <v>4.42500019073486</v>
       </c>
       <c r="G1371" t="s">
-        <v>860</v>
+        <v>859</v>
       </c>
       <c r="H1371" t="s">
         <v>9</v>
@@ -40448,7 +40448,7 @@
         <v>4.42500019073486</v>
       </c>
       <c r="G1372" t="s">
-        <v>860</v>
+        <v>859</v>
       </c>
       <c r="H1372" t="s">
         <v>9</v>
@@ -40474,7 +40474,7 @@
         <v>4.47499990463257</v>
       </c>
       <c r="G1373" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="H1373" t="s">
         <v>9</v>
@@ -40500,7 +40500,7 @@
         <v>4.51000022888184</v>
       </c>
       <c r="G1374" t="s">
-        <v>861</v>
+        <v>860</v>
       </c>
       <c r="H1374" t="s">
         <v>9</v>
@@ -40526,7 +40526,7 @@
         <v>4.55000019073486</v>
       </c>
       <c r="G1375" t="s">
-        <v>862</v>
+        <v>861</v>
       </c>
       <c r="H1375" t="s">
         <v>9</v>
@@ -40552,7 +40552,7 @@
         <v>4.59499979019165</v>
       </c>
       <c r="G1376" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="H1376" t="s">
         <v>9</v>
@@ -40578,7 +40578,7 @@
         <v>4.65999984741211</v>
       </c>
       <c r="G1377" t="s">
-        <v>864</v>
+        <v>863</v>
       </c>
       <c r="H1377" t="s">
         <v>9</v>
@@ -40604,7 +40604,7 @@
         <v>4.57999992370605</v>
       </c>
       <c r="G1378" t="s">
-        <v>847</v>
+        <v>846</v>
       </c>
       <c r="H1378" t="s">
         <v>9</v>
@@ -40630,7 +40630,7 @@
         <v>4.57999992370605</v>
       </c>
       <c r="G1379" t="s">
-        <v>847</v>
+        <v>846</v>
       </c>
       <c r="H1379" t="s">
         <v>9</v>
@@ -40656,7 +40656,7 @@
         <v>4.59000015258789</v>
       </c>
       <c r="G1380" t="s">
-        <v>865</v>
+        <v>864</v>
       </c>
       <c r="H1380" t="s">
         <v>9</v>
@@ -40682,7 +40682,7 @@
         <v>4.58500003814697</v>
       </c>
       <c r="G1381" t="s">
-        <v>866</v>
+        <v>865</v>
       </c>
       <c r="H1381" t="s">
         <v>9</v>
@@ -40708,7 +40708,7 @@
         <v>4.53000020980835</v>
       </c>
       <c r="G1382" t="s">
-        <v>867</v>
+        <v>866</v>
       </c>
       <c r="H1382" t="s">
         <v>9</v>
@@ -40734,7 +40734,7 @@
         <v>4.59000015258789</v>
       </c>
       <c r="G1383" t="s">
-        <v>865</v>
+        <v>864</v>
       </c>
       <c r="H1383" t="s">
         <v>9</v>
@@ -40760,7 +40760,7 @@
         <v>4.67999982833862</v>
       </c>
       <c r="G1384" t="s">
-        <v>868</v>
+        <v>867</v>
       </c>
       <c r="H1384" t="s">
         <v>9</v>
@@ -40786,7 +40786,7 @@
         <v>4.67999982833862</v>
       </c>
       <c r="G1385" t="s">
-        <v>868</v>
+        <v>867</v>
       </c>
       <c r="H1385" t="s">
         <v>9</v>
@@ -40812,7 +40812,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G1386" t="s">
-        <v>869</v>
+        <v>868</v>
       </c>
       <c r="H1386" t="s">
         <v>9</v>
@@ -40838,7 +40838,7 @@
         <v>4.63000011444092</v>
       </c>
       <c r="G1387" t="s">
-        <v>870</v>
+        <v>869</v>
       </c>
       <c r="H1387" t="s">
         <v>9</v>
@@ -40864,7 +40864,7 @@
         <v>4.63000011444092</v>
       </c>
       <c r="G1388" t="s">
-        <v>870</v>
+        <v>869</v>
       </c>
       <c r="H1388" t="s">
         <v>9</v>
@@ -40890,7 +40890,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G1389" t="s">
-        <v>871</v>
+        <v>870</v>
       </c>
       <c r="H1389" t="s">
         <v>9</v>
@@ -40916,7 +40916,7 @@
         <v>4.59499979019165</v>
       </c>
       <c r="G1390" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="H1390" t="s">
         <v>9</v>
@@ -40942,7 +40942,7 @@
         <v>4.50500011444092</v>
       </c>
       <c r="G1391" t="s">
-        <v>872</v>
+        <v>871</v>
       </c>
       <c r="H1391" t="s">
         <v>9</v>
@@ -40968,7 +40968,7 @@
         <v>4.4850001335144</v>
       </c>
       <c r="G1392" t="s">
-        <v>873</v>
+        <v>872</v>
       </c>
       <c r="H1392" t="s">
         <v>9</v>
@@ -40994,7 +40994,7 @@
         <v>4.53499984741211</v>
       </c>
       <c r="G1393" t="s">
-        <v>874</v>
+        <v>873</v>
       </c>
       <c r="H1393" t="s">
         <v>9</v>
@@ -41020,7 +41020,7 @@
         <v>4.67999982833862</v>
       </c>
       <c r="G1394" t="s">
-        <v>868</v>
+        <v>867</v>
       </c>
       <c r="H1394" t="s">
         <v>9</v>
@@ -41046,7 +41046,7 @@
         <v>4.69500017166138</v>
       </c>
       <c r="G1395" t="s">
-        <v>875</v>
+        <v>874</v>
       </c>
       <c r="H1395" t="s">
         <v>9</v>
@@ -41072,7 +41072,7 @@
         <v>4.71999979019165</v>
       </c>
       <c r="G1396" t="s">
-        <v>876</v>
+        <v>875</v>
       </c>
       <c r="H1396" t="s">
         <v>9</v>
@@ -41098,7 +41098,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G1397" t="s">
-        <v>869</v>
+        <v>868</v>
       </c>
       <c r="H1397" t="s">
         <v>9</v>
@@ -41124,7 +41124,7 @@
         <v>4.75</v>
       </c>
       <c r="G1398" t="s">
-        <v>877</v>
+        <v>876</v>
       </c>
       <c r="H1398" t="s">
         <v>9</v>
@@ -41150,7 +41150,7 @@
         <v>4.71999979019165</v>
       </c>
       <c r="G1399" t="s">
-        <v>876</v>
+        <v>875</v>
       </c>
       <c r="H1399" t="s">
         <v>9</v>
@@ -41176,7 +41176,7 @@
         <v>4.69000005722046</v>
       </c>
       <c r="G1400" t="s">
-        <v>878</v>
+        <v>877</v>
       </c>
       <c r="H1400" t="s">
         <v>9</v>
@@ -41202,7 +41202,7 @@
         <v>4.69500017166138</v>
       </c>
       <c r="G1401" t="s">
-        <v>875</v>
+        <v>874</v>
       </c>
       <c r="H1401" t="s">
         <v>9</v>
@@ -41228,7 +41228,7 @@
         <v>4.59000015258789</v>
       </c>
       <c r="G1402" t="s">
-        <v>865</v>
+        <v>864</v>
       </c>
       <c r="H1402" t="s">
         <v>9</v>
@@ -41254,7 +41254,7 @@
         <v>4.5</v>
       </c>
       <c r="G1403" t="s">
-        <v>849</v>
+        <v>848</v>
       </c>
       <c r="H1403" t="s">
         <v>9</v>
@@ -41280,7 +41280,7 @@
         <v>4.38000011444092</v>
       </c>
       <c r="G1404" t="s">
-        <v>879</v>
+        <v>878</v>
       </c>
       <c r="H1404" t="s">
         <v>9</v>
@@ -41306,7 +41306,7 @@
         <v>4.3600001335144</v>
       </c>
       <c r="G1405" t="s">
-        <v>880</v>
+        <v>879</v>
       </c>
       <c r="H1405" t="s">
         <v>9</v>
@@ -41332,7 +41332,7 @@
         <v>4.32999992370605</v>
       </c>
       <c r="G1406" t="s">
-        <v>881</v>
+        <v>880</v>
       </c>
       <c r="H1406" t="s">
         <v>9</v>
@@ -41358,7 +41358,7 @@
         <v>4.32499980926514</v>
       </c>
       <c r="G1407" t="s">
-        <v>882</v>
+        <v>881</v>
       </c>
       <c r="H1407" t="s">
         <v>9</v>
@@ -41384,7 +41384,7 @@
         <v>4.25</v>
       </c>
       <c r="G1408" t="s">
-        <v>883</v>
+        <v>882</v>
       </c>
       <c r="H1408" t="s">
         <v>9</v>
@@ -41410,7 +41410,7 @@
         <v>4.14499998092651</v>
       </c>
       <c r="G1409" t="s">
-        <v>884</v>
+        <v>883</v>
       </c>
       <c r="H1409" t="s">
         <v>9</v>
@@ -41436,7 +41436,7 @@
         <v>4.09000015258789</v>
       </c>
       <c r="G1410" t="s">
-        <v>885</v>
+        <v>884</v>
       </c>
       <c r="H1410" t="s">
         <v>9</v>
@@ -41462,7 +41462,7 @@
         <v>4.27500009536743</v>
       </c>
       <c r="G1411" t="s">
-        <v>886</v>
+        <v>885</v>
       </c>
       <c r="H1411" t="s">
         <v>9</v>
@@ -41488,7 +41488,7 @@
         <v>4.3899998664856</v>
       </c>
       <c r="G1412" t="s">
-        <v>887</v>
+        <v>886</v>
       </c>
       <c r="H1412" t="s">
         <v>9</v>
@@ -41514,7 +41514,7 @@
         <v>4.5</v>
       </c>
       <c r="G1413" t="s">
-        <v>849</v>
+        <v>848</v>
       </c>
       <c r="H1413" t="s">
         <v>9</v>
@@ -41540,7 +41540,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G1414" t="s">
-        <v>839</v>
+        <v>887</v>
       </c>
       <c r="H1414" t="s">
         <v>9</v>
@@ -41566,7 +41566,7 @@
         <v>4.32999992370605</v>
       </c>
       <c r="G1415" t="s">
-        <v>881</v>
+        <v>880</v>
       </c>
       <c r="H1415" t="s">
         <v>9</v>
@@ -41670,7 +41670,7 @@
         <v>4.5</v>
       </c>
       <c r="G1419" t="s">
-        <v>849</v>
+        <v>848</v>
       </c>
       <c r="H1419" t="s">
         <v>9</v>
@@ -41696,7 +41696,7 @@
         <v>4.50500011444092</v>
       </c>
       <c r="G1420" t="s">
-        <v>872</v>
+        <v>871</v>
       </c>
       <c r="H1420" t="s">
         <v>9</v>
@@ -41722,7 +41722,7 @@
         <v>4.44999980926514</v>
       </c>
       <c r="G1421" t="s">
-        <v>858</v>
+        <v>857</v>
       </c>
       <c r="H1421" t="s">
         <v>9</v>
@@ -41748,7 +41748,7 @@
         <v>4.44000005722046</v>
       </c>
       <c r="G1422" t="s">
-        <v>850</v>
+        <v>849</v>
       </c>
       <c r="H1422" t="s">
         <v>9</v>
@@ -41800,7 +41800,7 @@
         <v>4.5</v>
       </c>
       <c r="G1424" t="s">
-        <v>849</v>
+        <v>848</v>
       </c>
       <c r="H1424" t="s">
         <v>9</v>
@@ -41826,7 +41826,7 @@
         <v>4.46500015258789</v>
       </c>
       <c r="G1425" t="s">
-        <v>855</v>
+        <v>854</v>
       </c>
       <c r="H1425" t="s">
         <v>9</v>
@@ -41878,7 +41878,7 @@
         <v>4.51000022888184</v>
       </c>
       <c r="G1427" t="s">
-        <v>861</v>
+        <v>860</v>
       </c>
       <c r="H1427" t="s">
         <v>9</v>
@@ -41904,7 +41904,7 @@
         <v>4.5</v>
       </c>
       <c r="G1428" t="s">
-        <v>849</v>
+        <v>848</v>
       </c>
       <c r="H1428" t="s">
         <v>9</v>
@@ -41930,7 +41930,7 @@
         <v>4.43499994277954</v>
       </c>
       <c r="G1429" t="s">
-        <v>854</v>
+        <v>853</v>
       </c>
       <c r="H1429" t="s">
         <v>9</v>
@@ -41956,7 +41956,7 @@
         <v>4.3600001335144</v>
       </c>
       <c r="G1430" t="s">
-        <v>880</v>
+        <v>879</v>
       </c>
       <c r="H1430" t="s">
         <v>9</v>
@@ -41982,7 +41982,7 @@
         <v>4.42500019073486</v>
       </c>
       <c r="G1431" t="s">
-        <v>860</v>
+        <v>859</v>
       </c>
       <c r="H1431" t="s">
         <v>9</v>
@@ -42008,7 +42008,7 @@
         <v>4.38000011444092</v>
       </c>
       <c r="G1432" t="s">
-        <v>879</v>
+        <v>878</v>
       </c>
       <c r="H1432" t="s">
         <v>9</v>
@@ -42138,7 +42138,7 @@
         <v>4.49499988555908</v>
       </c>
       <c r="G1437" t="s">
-        <v>851</v>
+        <v>850</v>
       </c>
       <c r="H1437" t="s">
         <v>9</v>
@@ -42190,7 +42190,7 @@
         <v>4.44999980926514</v>
       </c>
       <c r="G1439" t="s">
-        <v>858</v>
+        <v>857</v>
       </c>
       <c r="H1439" t="s">
         <v>9</v>
@@ -42216,7 +42216,7 @@
         <v>4.48000001907349</v>
       </c>
       <c r="G1440" t="s">
-        <v>856</v>
+        <v>855</v>
       </c>
       <c r="H1440" t="s">
         <v>9</v>
@@ -42294,7 +42294,7 @@
         <v>4.44000005722046</v>
       </c>
       <c r="G1443" t="s">
-        <v>850</v>
+        <v>849</v>
       </c>
       <c r="H1443" t="s">
         <v>9</v>
@@ -42320,7 +42320,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G1444" t="s">
-        <v>871</v>
+        <v>870</v>
       </c>
       <c r="H1444" t="s">
         <v>9</v>
@@ -42346,7 +42346,7 @@
         <v>4.61499977111816</v>
       </c>
       <c r="G1445" t="s">
-        <v>844</v>
+        <v>843</v>
       </c>
       <c r="H1445" t="s">
         <v>9</v>
@@ -42372,7 +42372,7 @@
         <v>4.51000022888184</v>
       </c>
       <c r="G1446" t="s">
-        <v>861</v>
+        <v>860</v>
       </c>
       <c r="H1446" t="s">
         <v>9</v>
@@ -42398,7 +42398,7 @@
         <v>4.4850001335144</v>
       </c>
       <c r="G1447" t="s">
-        <v>873</v>
+        <v>872</v>
       </c>
       <c r="H1447" t="s">
         <v>9</v>
@@ -42424,7 +42424,7 @@
         <v>4.51000022888184</v>
       </c>
       <c r="G1448" t="s">
-        <v>861</v>
+        <v>860</v>
       </c>
       <c r="H1448" t="s">
         <v>9</v>
@@ -42450,7 +42450,7 @@
         <v>4.63000011444092</v>
       </c>
       <c r="G1449" t="s">
-        <v>870</v>
+        <v>869</v>
       </c>
       <c r="H1449" t="s">
         <v>9</v>
@@ -42502,7 +42502,7 @@
         <v>4.57000017166138</v>
       </c>
       <c r="G1451" t="s">
-        <v>841</v>
+        <v>840</v>
       </c>
       <c r="H1451" t="s">
         <v>9</v>
@@ -42554,7 +42554,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G1453" t="s">
-        <v>869</v>
+        <v>868</v>
       </c>
       <c r="H1453" t="s">
         <v>9</v>
@@ -42606,7 +42606,7 @@
         <v>4.58500003814697</v>
       </c>
       <c r="G1455" t="s">
-        <v>866</v>
+        <v>865</v>
       </c>
       <c r="H1455" t="s">
         <v>9</v>
@@ -42736,7 +42736,7 @@
         <v>4.57999992370605</v>
       </c>
       <c r="G1460" t="s">
-        <v>847</v>
+        <v>846</v>
       </c>
       <c r="H1460" t="s">
         <v>9</v>
@@ -42814,7 +42814,7 @@
         <v>4.55000019073486</v>
       </c>
       <c r="G1463" t="s">
-        <v>862</v>
+        <v>861</v>
       </c>
       <c r="H1463" t="s">
         <v>9</v>
@@ -42840,7 +42840,7 @@
         <v>4.58500003814697</v>
       </c>
       <c r="G1464" t="s">
-        <v>866</v>
+        <v>865</v>
       </c>
       <c r="H1464" t="s">
         <v>9</v>
@@ -42866,7 +42866,7 @@
         <v>4.69000005722046</v>
       </c>
       <c r="G1465" t="s">
-        <v>878</v>
+        <v>877</v>
       </c>
       <c r="H1465" t="s">
         <v>9</v>
@@ -42918,7 +42918,7 @@
         <v>4.69500017166138</v>
       </c>
       <c r="G1467" t="s">
-        <v>875</v>
+        <v>874</v>
       </c>
       <c r="H1467" t="s">
         <v>9</v>
@@ -42944,7 +42944,7 @@
         <v>4.68499994277954</v>
       </c>
       <c r="G1468" t="s">
-        <v>845</v>
+        <v>844</v>
       </c>
       <c r="H1468" t="s">
         <v>9</v>
@@ -43022,7 +43022,7 @@
         <v>4.71999979019165</v>
       </c>
       <c r="G1471" t="s">
-        <v>876</v>
+        <v>875</v>
       </c>
       <c r="H1471" t="s">
         <v>9</v>
@@ -43048,7 +43048,7 @@
         <v>4.71999979019165</v>
       </c>
       <c r="G1472" t="s">
-        <v>876</v>
+        <v>875</v>
       </c>
       <c r="H1472" t="s">
         <v>9</v>
@@ -45648,7 +45648,7 @@
         <v>4.71999979019165</v>
       </c>
       <c r="G1572" t="s">
-        <v>876</v>
+        <v>875</v>
       </c>
       <c r="H1572" t="s">
         <v>9</v>
@@ -69862,7 +69862,7 @@
     </row>
     <row r="2504">
       <c r="A2504" s="1" t="n">
-        <v>45965.6912615741</v>
+        <v>45965.3333333333</v>
       </c>
       <c r="B2504" t="n">
         <v>27069</v>
@@ -69883,6 +69883,32 @@
         <v>1477</v>
       </c>
       <c r="H2504" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2505">
+      <c r="A2505" s="1" t="n">
+        <v>45966.6912847222</v>
+      </c>
+      <c r="B2505" t="n">
+        <v>49562</v>
+      </c>
+      <c r="C2505" t="n">
+        <v>7.03000020980835</v>
+      </c>
+      <c r="D2505" t="n">
+        <v>6.75</v>
+      </c>
+      <c r="E2505" t="n">
+        <v>6.76000022888184</v>
+      </c>
+      <c r="F2505" t="n">
+        <v>6.98999977111816</v>
+      </c>
+      <c r="G2505" t="s">
+        <v>1471</v>
+      </c>
+      <c r="H2505" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/BAN.MI.xlsx
+++ b/data/BAN.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1484" uniqueCount="1484">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1485" uniqueCount="1485">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -38,28 +38,28 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">3.66912961006165</t>
+    <t xml:space="preserve">3.66912984848022</t>
   </si>
   <si>
     <t xml:space="preserve">BAN.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">3.68330192565918</t>
+    <t xml:space="preserve">3.68330240249634</t>
   </si>
   <si>
     <t xml:space="preserve">3.59039354324341</t>
   </si>
   <si>
-    <t xml:space="preserve">3.46283912658691</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.41874694824219</t>
+    <t xml:space="preserve">3.46283960342407</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.41874647140503</t>
   </si>
   <si>
     <t xml:space="preserve">3.35733246803284</t>
   </si>
   <si>
-    <t xml:space="preserve">3.44551682472229</t>
+    <t xml:space="preserve">3.44551777839661</t>
   </si>
   <si>
     <t xml:space="preserve">3.46441459655762</t>
@@ -74,55 +74,55 @@
     <t xml:space="preserve">3.3841028213501</t>
   </si>
   <si>
-    <t xml:space="preserve">3.40929841995239</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.11639833450317</t>
+    <t xml:space="preserve">3.40929889678955</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.11639857292175</t>
   </si>
   <si>
     <t xml:space="preserve">3.240802526474</t>
   </si>
   <si>
-    <t xml:space="preserve">3.29119348526001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.21245718002319</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.26757264137268</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.19356060028076</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.1337206363678</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.22820448875427</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.16678977012634</t>
+    <t xml:space="preserve">3.29119396209717</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.21245694160461</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.2675724029541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.19356036186218</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.13372015953064</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.22820425033569</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.16678953170776</t>
   </si>
   <si>
     <t xml:space="preserve">3.17308878898621</t>
   </si>
   <si>
-    <t xml:space="preserve">3.07073068618774</t>
+    <t xml:space="preserve">3.07073092460632</t>
   </si>
   <si>
     <t xml:space="preserve">3.1494677066803</t>
   </si>
   <si>
-    <t xml:space="preserve">3.0502598285675</t>
+    <t xml:space="preserve">3.05025959014893</t>
   </si>
   <si>
     <t xml:space="preserve">2.92900490760803</t>
   </si>
   <si>
-    <t xml:space="preserve">2.91325759887695</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.83452081680298</t>
+    <t xml:space="preserve">2.91325783729553</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.8345205783844</t>
   </si>
   <si>
     <t xml:space="preserve">2.82664728164673</t>
@@ -131,22 +131,22 @@
     <t xml:space="preserve">2.75263476371765</t>
   </si>
   <si>
-    <t xml:space="preserve">2.75420928001404</t>
+    <t xml:space="preserve">2.75420951843262</t>
   </si>
   <si>
     <t xml:space="preserve">2.75578427314758</t>
   </si>
   <si>
-    <t xml:space="preserve">2.89436101913452</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.98254609107971</t>
+    <t xml:space="preserve">2.89436054229736</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.98254561424255</t>
   </si>
   <si>
     <t xml:space="preserve">2.96207427978516</t>
   </si>
   <si>
-    <t xml:space="preserve">2.99356889724731</t>
+    <t xml:space="preserve">2.99356913566589</t>
   </si>
   <si>
     <t xml:space="preserve">3.05970788002014</t>
@@ -155,16 +155,16 @@
     <t xml:space="preserve">3.11009931564331</t>
   </si>
   <si>
-    <t xml:space="preserve">3.06915616989136</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.9636492729187</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.99199461936951</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.00774121284485</t>
+    <t xml:space="preserve">3.06915640830994</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.96364903450012</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.99199390411377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.00774145126343</t>
   </si>
   <si>
     <t xml:space="preserve">2.97624707221985</t>
@@ -176,67 +176,67 @@
     <t xml:space="preserve">3.11797285079956</t>
   </si>
   <si>
-    <t xml:space="preserve">3.1809618473053</t>
+    <t xml:space="preserve">3.18096232414246</t>
   </si>
   <si>
     <t xml:space="preserve">3.10222578048706</t>
   </si>
   <si>
-    <t xml:space="preserve">3.13686943054199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.23292851448059</t>
+    <t xml:space="preserve">3.13686990737915</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.23292875289917</t>
   </si>
   <si>
     <t xml:space="preserve">3.33843564987183</t>
   </si>
   <si>
-    <t xml:space="preserve">3.30694031715393</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.24395155906677</t>
+    <t xml:space="preserve">3.30694055557251</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.24395179748535</t>
   </si>
   <si>
     <t xml:space="preserve">3.24237704277039</t>
   </si>
   <si>
-    <t xml:space="preserve">3.12584686279297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.19670939445496</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.2030086517334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.10380029678345</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.11324882507324</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.14159417152405</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.04711008071899</t>
+    <t xml:space="preserve">3.12584662437439</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.19671010971069</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.20300889015198</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.10380005836487</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.11324858665466</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.14159393310547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.04710960388184</t>
   </si>
   <si>
     <t xml:space="preserve">2.99986815452576</t>
   </si>
   <si>
-    <t xml:space="preserve">2.96049952507019</t>
+    <t xml:space="preserve">2.96049928665161</t>
   </si>
   <si>
     <t xml:space="preserve">3.09435224533081</t>
   </si>
   <si>
-    <t xml:space="preserve">2.96837306022644</t>
+    <t xml:space="preserve">2.9683735370636</t>
   </si>
   <si>
     <t xml:space="preserve">2.86286616325378</t>
   </si>
   <si>
-    <t xml:space="preserve">2.87388896942139</t>
+    <t xml:space="preserve">2.87388920783997</t>
   </si>
   <si>
     <t xml:space="preserve">2.9101083278656</t>
@@ -245,19 +245,19 @@
     <t xml:space="preserve">2.98569560050964</t>
   </si>
   <si>
-    <t xml:space="preserve">3.00144267082214</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.01561546325684</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.92743015289307</t>
+    <t xml:space="preserve">3.0014431476593</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.01561522483826</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.92743039131165</t>
   </si>
   <si>
     <t xml:space="preserve">2.92113137245178</t>
   </si>
   <si>
-    <t xml:space="preserve">2.85814213752747</t>
+    <t xml:space="preserve">2.85814237594604</t>
   </si>
   <si>
     <t xml:space="preserve">2.81404948234558</t>
@@ -266,16 +266,16 @@
     <t xml:space="preserve">2.84081983566284</t>
   </si>
   <si>
-    <t xml:space="preserve">2.80145168304443</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.72901368141174</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.65185213088989</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.68177151679993</t>
+    <t xml:space="preserve">2.80145192146301</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.72901391983032</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.65185236930847</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.68177175521851</t>
   </si>
   <si>
     <t xml:space="preserve">2.71484136581421</t>
@@ -284,49 +284,49 @@
     <t xml:space="preserve">2.76365780830383</t>
   </si>
   <si>
-    <t xml:space="preserve">2.77940487861633</t>
+    <t xml:space="preserve">2.77940559387207</t>
   </si>
   <si>
     <t xml:space="preserve">2.72428965568542</t>
   </si>
   <si>
-    <t xml:space="preserve">2.5904369354248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.53532147407532</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.49437832832336</t>
+    <t xml:space="preserve">2.59043717384338</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.53532123565674</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.49437856674194</t>
   </si>
   <si>
     <t xml:space="preserve">2.48020577430725</t>
   </si>
   <si>
-    <t xml:space="preserve">2.51957416534424</t>
+    <t xml:space="preserve">2.51957440376282</t>
   </si>
   <si>
     <t xml:space="preserve">2.60572743415833</t>
   </si>
   <si>
-    <t xml:space="preserve">2.58784651756287</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.56021237373352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.56183815002441</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.60897850990295</t>
+    <t xml:space="preserve">2.58784627914429</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.5602126121521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.56183767318726</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.60897827148438</t>
   </si>
   <si>
     <t xml:space="preserve">2.59272289276123</t>
   </si>
   <si>
-    <t xml:space="preserve">2.58134436607361</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.60085082054138</t>
+    <t xml:space="preserve">2.58134412765503</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.60085105895996</t>
   </si>
   <si>
     <t xml:space="preserve">2.72114014625549</t>
@@ -338,7 +338,7 @@
     <t xml:space="preserve">2.80404233932495</t>
   </si>
   <si>
-    <t xml:space="preserve">2.68212723731995</t>
+    <t xml:space="preserve">2.6821277141571</t>
   </si>
   <si>
     <t xml:space="preserve">2.71463775634766</t>
@@ -347,49 +347,46 @@
     <t xml:space="preserve">2.44642496109009</t>
   </si>
   <si>
-    <t xml:space="preserve">2.39765930175781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.50331854820251</t>
+    <t xml:space="preserve">2.39765954017639</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.50331902503967</t>
   </si>
   <si>
     <t xml:space="preserve">2.47568464279175</t>
   </si>
   <si>
-    <t xml:space="preserve">2.51957392692566</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.52770209312439</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.50819563865662</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.40578699111938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.19446778297424</t>
+    <t xml:space="preserve">2.52770185470581</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.50819540023804</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.40578675270081</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.19446802139282</t>
   </si>
   <si>
     <t xml:space="preserve">2.23510599136353</t>
   </si>
   <si>
-    <t xml:space="preserve">2.29525065422058</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.27411913871765</t>
+    <t xml:space="preserve">2.29525089263916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.27411890029907</t>
   </si>
   <si>
     <t xml:space="preserve">2.35702109336853</t>
   </si>
   <si>
-    <t xml:space="preserve">2.3732762336731</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.29199957847595</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.19284224510193</t>
+    <t xml:space="preserve">2.37327647209167</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.29199934005737</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.19284248352051</t>
   </si>
   <si>
     <t xml:space="preserve">2.2253532409668</t>
@@ -401,7 +398,7 @@
     <t xml:space="preserve">2.30500411987305</t>
   </si>
   <si>
-    <t xml:space="preserve">2.33101224899292</t>
+    <t xml:space="preserve">2.3310124874115</t>
   </si>
   <si>
     <t xml:space="preserve">2.33588910102844</t>
@@ -410,43 +407,43 @@
     <t xml:space="preserve">2.33263778686523</t>
   </si>
   <si>
-    <t xml:space="preserve">2.31963396072388</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.38140416145325</t>
+    <t xml:space="preserve">2.3196337223053</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.38140392303467</t>
   </si>
   <si>
     <t xml:space="preserve">2.53582954406738</t>
   </si>
   <si>
-    <t xml:space="preserve">2.54395699501038</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.56834030151367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.89669752120972</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.83817863464355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.8121702671051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.59597396850586</t>
+    <t xml:space="preserve">2.54395723342896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.56834006309509</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.89669728279114</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.83817839622498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.81216979026794</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.59597444534302</t>
   </si>
   <si>
     <t xml:space="preserve">2.57646775245667</t>
   </si>
   <si>
-    <t xml:space="preserve">2.57321691513062</t>
+    <t xml:space="preserve">2.57321667671204</t>
   </si>
   <si>
     <t xml:space="preserve">2.56671452522278</t>
   </si>
   <si>
-    <t xml:space="preserve">2.53257846832275</t>
+    <t xml:space="preserve">2.53257822990417</t>
   </si>
   <si>
     <t xml:space="preserve">2.53745484352112</t>
@@ -455,19 +452,19 @@
     <t xml:space="preserve">2.6366126537323</t>
   </si>
   <si>
-    <t xml:space="preserve">2.63011026382446</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.64636516571045</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.65286731719971</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.63823819160461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.64148902893066</t>
+    <t xml:space="preserve">2.63011050224304</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.64636588096619</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.65286779403687</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.63823771476746</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.64148950576782</t>
   </si>
   <si>
     <t xml:space="preserve">2.69188070297241</t>
@@ -479,67 +476,67 @@
     <t xml:space="preserve">2.79266357421875</t>
   </si>
   <si>
-    <t xml:space="preserve">2.76340389251709</t>
+    <t xml:space="preserve">2.76340365409851</t>
   </si>
   <si>
     <t xml:space="preserve">2.7308931350708</t>
   </si>
   <si>
-    <t xml:space="preserve">2.65449357032776</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.65774440765381</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.74227213859558</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.76828026771545</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.70651006698608</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.72764205932617</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.74064683914185</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.76990580558777</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.80079102516174</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.69513201713562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.66749739646912</t>
+    <t xml:space="preserve">2.65449333190918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.65774416923523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.742271900177</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.76828050613403</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.70651030540466</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.72764229774475</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.74064636230469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.76990604400635</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.80079126358032</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.69513154029846</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.6674976348877</t>
   </si>
   <si>
     <t xml:space="preserve">2.64799118041992</t>
   </si>
   <si>
-    <t xml:space="preserve">2.6252338886261</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.59759974479675</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.61710643768311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.6658718585968</t>
+    <t xml:space="preserve">2.62523412704468</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.59759998321533</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.61710572242737</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.66587209701538</t>
   </si>
   <si>
     <t xml:space="preserve">2.63336110115051</t>
   </si>
   <si>
-    <t xml:space="preserve">2.68862962722778</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.60247611999512</t>
+    <t xml:space="preserve">2.68862986564636</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.6024763584137</t>
   </si>
   <si>
     <t xml:space="preserve">2.67725086212158</t>
@@ -548,16 +545,16 @@
     <t xml:space="preserve">2.70976138114929</t>
   </si>
   <si>
-    <t xml:space="preserve">2.75527620315552</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.72601699829102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.72276568412781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.82842516899109</t>
+    <t xml:space="preserve">2.7552764415741</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.72601675987244</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.72276592254639</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.82842540740967</t>
   </si>
   <si>
     <t xml:space="preserve">2.7438976764679</t>
@@ -566,19 +563,19 @@
     <t xml:space="preserve">2.76177835464478</t>
   </si>
   <si>
-    <t xml:space="preserve">2.73902130126953</t>
+    <t xml:space="preserve">2.73902058601379</t>
   </si>
   <si>
     <t xml:space="preserve">2.70488476753235</t>
   </si>
   <si>
-    <t xml:space="preserve">2.6902551651001</t>
+    <t xml:space="preserve">2.69025492668152</t>
   </si>
   <si>
     <t xml:space="preserve">2.61222982406616</t>
   </si>
   <si>
-    <t xml:space="preserve">2.73251867294312</t>
+    <t xml:space="preserve">2.73251891136169</t>
   </si>
   <si>
     <t xml:space="preserve">2.67562508583069</t>
@@ -587,16 +584,16 @@
     <t xml:space="preserve">2.62360811233521</t>
   </si>
   <si>
-    <t xml:space="preserve">2.59434866905212</t>
+    <t xml:space="preserve">2.59434843063354</t>
   </si>
   <si>
     <t xml:space="preserve">2.55371022224426</t>
   </si>
   <si>
-    <t xml:space="preserve">2.55045962333679</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.51307201385498</t>
+    <t xml:space="preserve">2.55045914649963</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.5130717754364</t>
   </si>
   <si>
     <t xml:space="preserve">2.46755719184875</t>
@@ -605,64 +602,64 @@
     <t xml:space="preserve">2.50169324874878</t>
   </si>
   <si>
-    <t xml:space="preserve">2.58459520339966</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.63173604011536</t>
+    <t xml:space="preserve">2.58459544181824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.6317355632782</t>
   </si>
   <si>
     <t xml:space="preserve">2.65611863136292</t>
   </si>
   <si>
-    <t xml:space="preserve">2.66912269592285</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.72439122200012</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.78291010856628</t>
+    <t xml:space="preserve">2.66912293434143</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.72439098358154</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.78291058540344</t>
   </si>
   <si>
     <t xml:space="preserve">2.77153158187866</t>
   </si>
   <si>
-    <t xml:space="preserve">2.7780339717865</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.70000815391541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.7731568813324</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.7650294303894</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.71788930892944</t>
+    <t xml:space="preserve">2.77803349494934</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.70000839233398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.77315735816956</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.76502966880798</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.71788883209229</t>
   </si>
   <si>
     <t xml:space="preserve">2.74552297592163</t>
   </si>
   <si>
-    <t xml:space="preserve">2.77965950965881</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.74714827537537</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.60410189628601</t>
+    <t xml:space="preserve">2.77965927124023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.74714875221252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.60410165786743</t>
   </si>
   <si>
     <t xml:space="preserve">2.62685918807983</t>
   </si>
   <si>
-    <t xml:space="preserve">2.64961671829224</t>
+    <t xml:space="preserve">2.64961647987366</t>
   </si>
   <si>
     <t xml:space="preserve">2.69350576400757</t>
   </si>
   <si>
-    <t xml:space="preserve">2.69838285446167</t>
+    <t xml:space="preserve">2.69838237762451</t>
   </si>
   <si>
     <t xml:space="preserve">2.92270588874817</t>
@@ -677,25 +674,25 @@
     <t xml:space="preserve">2.97472310066223</t>
   </si>
   <si>
-    <t xml:space="preserve">2.96984624862671</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.96334385871887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.94221258163452</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.93408489227295</t>
+    <t xml:space="preserve">2.96984648704529</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.96334433555603</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.94221210479736</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.93408465385437</t>
   </si>
   <si>
     <t xml:space="preserve">2.89832329750061</t>
   </si>
   <si>
-    <t xml:space="preserve">2.89182090759277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.87881684303284</t>
+    <t xml:space="preserve">2.89182138442993</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.87881636619568</t>
   </si>
   <si>
     <t xml:space="preserve">2.87556576728821</t>
@@ -707,19 +704,19 @@
     <t xml:space="preserve">2.82192325592041</t>
   </si>
   <si>
-    <t xml:space="preserve">2.8495569229126</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.91945505142212</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.92595720291138</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.99097847938538</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.9145781993866</t>
+    <t xml:space="preserve">2.84955716133118</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.91945481300354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.92595672607422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.99097871780396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.91457843780518</t>
   </si>
   <si>
     <t xml:space="preserve">2.91620397567749</t>
@@ -731,100 +728,100 @@
     <t xml:space="preserve">2.95684218406677</t>
   </si>
   <si>
-    <t xml:space="preserve">2.95196580886841</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.04949760437012</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.05599927902222</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.99585509300232</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.97959971427917</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.00723385810852</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.09645938873291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.11628746986389</t>
+    <t xml:space="preserve">2.95196533203125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.0494978427887</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.0559995174408</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.99585485458374</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.9795994758606</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.00723361968994</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.09645962715149</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.11628699302673</t>
   </si>
   <si>
     <t xml:space="preserve">3.16916155815125</t>
   </si>
   <si>
-    <t xml:space="preserve">3.13941979408264</t>
+    <t xml:space="preserve">3.13941955566406</t>
   </si>
   <si>
     <t xml:space="preserve">3.14437675476074</t>
   </si>
   <si>
-    <t xml:space="preserve">3.18898940086365</t>
+    <t xml:space="preserve">3.18898987770081</t>
   </si>
   <si>
     <t xml:space="preserve">3.18072772026062</t>
   </si>
   <si>
-    <t xml:space="preserve">3.24847316741943</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.21707940101624</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.16750931739807</t>
+    <t xml:space="preserve">3.24847292900085</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.21707892417908</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.16750979423523</t>
   </si>
   <si>
     <t xml:space="preserve">3.15429091453552</t>
   </si>
   <si>
-    <t xml:space="preserve">3.17081427574158</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.07663130760193</t>
+    <t xml:space="preserve">3.170814037323</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.07663154602051</t>
   </si>
   <si>
     <t xml:space="preserve">3.07497906684875</t>
   </si>
   <si>
-    <t xml:space="preserve">2.98244881629944</t>
+    <t xml:space="preserve">2.98244857788086</t>
   </si>
   <si>
     <t xml:space="preserve">3.0584557056427</t>
   </si>
   <si>
-    <t xml:space="preserve">3.06506490707397</t>
+    <t xml:space="preserve">3.06506514549255</t>
   </si>
   <si>
     <t xml:space="preserve">3.03367114067078</t>
   </si>
   <si>
-    <t xml:space="preserve">3.02540898323059</t>
+    <t xml:space="preserve">3.02540969848633</t>
   </si>
   <si>
     <t xml:space="preserve">2.99401497840881</t>
   </si>
   <si>
-    <t xml:space="preserve">2.99071049690247</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.99897193908691</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.93783593177795</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.95601153373718</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.07993578910828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.08819770812988</t>
+    <t xml:space="preserve">2.99071025848389</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.99897217750549</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.93783617019653</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.95601177215576</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.07993602752686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.0881974697113</t>
   </si>
   <si>
     <t xml:space="preserve">3.08654522895813</t>
@@ -833,55 +830,55 @@
     <t xml:space="preserve">3.10802578926086</t>
   </si>
   <si>
-    <t xml:space="preserve">3.11133027076721</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.14768123626709</t>
+    <t xml:space="preserve">3.11133050918579</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.14768147468567</t>
   </si>
   <si>
     <t xml:space="preserve">3.16420459747314</t>
   </si>
   <si>
-    <t xml:space="preserve">3.2055127620697</t>
+    <t xml:space="preserve">3.20551300048828</t>
   </si>
   <si>
     <t xml:space="preserve">3.21377444267273</t>
   </si>
   <si>
-    <t xml:space="preserve">3.23029756546021</t>
+    <t xml:space="preserve">3.23029804229736</t>
   </si>
   <si>
     <t xml:space="preserve">3.23360228538513</t>
   </si>
   <si>
-    <t xml:space="preserve">3.25343012809753</t>
+    <t xml:space="preserve">3.25343060493469</t>
   </si>
   <si>
     <t xml:space="preserve">3.29473829269409</t>
   </si>
   <si>
-    <t xml:space="preserve">3.3079571723938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.27160620689392</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.29639077186584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.22368812561035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.25012540817261</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.19394636154175</t>
+    <t xml:space="preserve">3.30795741081238</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.27160573005676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.29639053344727</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.22368836402893</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.25012564659119</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.19394659996033</t>
   </si>
   <si>
     <t xml:space="preserve">3.26334428787231</t>
   </si>
   <si>
-    <t xml:space="preserve">3.09811210632324</t>
+    <t xml:space="preserve">3.0981113910675</t>
   </si>
   <si>
     <t xml:space="preserve">3.15924763679504</t>
@@ -893,43 +890,43 @@
     <t xml:space="preserve">3.17411851882935</t>
   </si>
   <si>
-    <t xml:space="preserve">3.15098595619202</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.05184650421143</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.05680370330811</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.08489298820496</t>
+    <t xml:space="preserve">3.15098571777344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.05184626579285</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.05680346488953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.08489274978638</t>
   </si>
   <si>
     <t xml:space="preserve">3.12785339355469</t>
   </si>
   <si>
-    <t xml:space="preserve">3.03201842308044</t>
+    <t xml:space="preserve">3.0320188999176</t>
   </si>
   <si>
     <t xml:space="preserve">3.09480690956116</t>
   </si>
   <si>
-    <t xml:space="preserve">3.073326587677</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.09150218963623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.13115811347961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.10967779159546</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.10472106933594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.12124395370483</t>
+    <t xml:space="preserve">3.07332682609558</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.09150242805481</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.13115787506104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.10967755317688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.10472059249878</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.12124419212341</t>
   </si>
   <si>
     <t xml:space="preserve">3.13611507415771</t>
@@ -938,10 +935,10 @@
     <t xml:space="preserve">3.1460292339325</t>
   </si>
   <si>
-    <t xml:space="preserve">3.12950611114502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.14107203483582</t>
+    <t xml:space="preserve">3.12950563430786</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.14107227325439</t>
   </si>
   <si>
     <t xml:space="preserve">3.15759539604187</t>
@@ -950,112 +947,112 @@
     <t xml:space="preserve">3.18403267860413</t>
   </si>
   <si>
-    <t xml:space="preserve">3.10637331008911</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.08158850669861</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.10141611099243</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.10306882858276</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.12289643287659</t>
+    <t xml:space="preserve">3.10637307167053</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.08158826828003</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.10141634941101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.10306906700134</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.12289667129517</t>
   </si>
   <si>
     <t xml:space="preserve">3.08984994888306</t>
   </si>
   <si>
-    <t xml:space="preserve">2.94940209388733</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.93287873268127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.83704423904419</t>
+    <t xml:space="preserve">2.94940185546875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.93287920951843</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.83704400062561</t>
   </si>
   <si>
     <t xml:space="preserve">2.88165688514709</t>
   </si>
   <si>
-    <t xml:space="preserve">2.90809416770935</t>
+    <t xml:space="preserve">2.90809392929077</t>
   </si>
   <si>
     <t xml:space="preserve">2.91139888763428</t>
   </si>
   <si>
-    <t xml:space="preserve">2.94609761238098</t>
+    <t xml:space="preserve">2.94609785079956</t>
   </si>
   <si>
     <t xml:space="preserve">2.94114089012146</t>
   </si>
   <si>
-    <t xml:space="preserve">2.96592569351196</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.8849618434906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.84034848213196</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.82878232002258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.81225895881653</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.88000464439392</t>
+    <t xml:space="preserve">2.96592545509338</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.88496160507202</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.84034872055054</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.82878255844116</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.81225943565369</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.88000416755676</t>
   </si>
   <si>
     <t xml:space="preserve">2.75112295150757</t>
   </si>
   <si>
-    <t xml:space="preserve">2.80895471572876</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.79243111610413</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.81391143798828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.85852456092834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.97418713569641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.97088241577148</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.01549553871155</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.05515146255493</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.04028034210205</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.07002234458923</t>
+    <t xml:space="preserve">2.8089542388916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.79243135452271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.81391167640686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.85852432250977</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.97418689727783</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.97088217735291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.01549530029297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.05515170097351</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.04028058052063</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.07002210617065</t>
   </si>
   <si>
     <t xml:space="preserve">3.06341242790222</t>
   </si>
   <si>
-    <t xml:space="preserve">3.02375721931458</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.03697562217712</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.0287139415741</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.0534987449646</t>
+    <t xml:space="preserve">3.023756980896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.03697538375854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.02871370315552</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.05349898338318</t>
   </si>
   <si>
     <t xml:space="preserve">3.07828378677368</t>
@@ -1067,10 +1064,10 @@
     <t xml:space="preserve">3.06919574737549</t>
   </si>
   <si>
-    <t xml:space="preserve">3.15594291687012</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.21790504455566</t>
+    <t xml:space="preserve">3.15594267845154</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.21790552139282</t>
   </si>
   <si>
     <t xml:space="preserve">3.17659711837769</t>
@@ -1079,25 +1076,25 @@
     <t xml:space="preserve">3.19312047958374</t>
   </si>
   <si>
-    <t xml:space="preserve">3.25508284568787</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.22203612327576</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.96179485321045</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.97831845283508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.92461705207825</t>
+    <t xml:space="preserve">3.25508260726929</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.22203588485718</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.96179461479187</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.9783182144165</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.92461729049683</t>
   </si>
   <si>
     <t xml:space="preserve">2.87504768371582</t>
   </si>
   <si>
-    <t xml:space="preserve">3.13528919219971</t>
+    <t xml:space="preserve">3.13528895378113</t>
   </si>
   <si>
     <t xml:space="preserve">3.07745742797852</t>
@@ -1106,16 +1103,16 @@
     <t xml:space="preserve">3.05267262458801</t>
   </si>
   <si>
-    <t xml:space="preserve">3.03614950180054</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.92048645019531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.08571887016296</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.01962637901306</t>
+    <t xml:space="preserve">3.03614926338196</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.92048692703247</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.08571910858154</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.01962614059448</t>
   </si>
   <si>
     <t xml:space="preserve">3.02788782119751</t>
@@ -1124,34 +1121,34 @@
     <t xml:space="preserve">3.0485417842865</t>
   </si>
   <si>
-    <t xml:space="preserve">3.04441070556641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.15181231498718</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.33769869804382</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.25095176696777</t>
+    <t xml:space="preserve">3.04441094398499</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.15181183815002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.3376989364624</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.25095152854919</t>
   </si>
   <si>
     <t xml:space="preserve">3.27573657035828</t>
   </si>
   <si>
-    <t xml:space="preserve">3.28399848937988</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.24682116508484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.18485879898071</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.2437379360199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.20177531242371</t>
+    <t xml:space="preserve">3.2839982509613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.24682092666626</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.18485903739929</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.24373769760132</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.20177459716797</t>
   </si>
   <si>
     <t xml:space="preserve">3.2101674079895</t>
@@ -1163,7 +1160,7 @@
     <t xml:space="preserve">3.22275638580322</t>
   </si>
   <si>
-    <t xml:space="preserve">3.16400837898254</t>
+    <t xml:space="preserve">3.16400814056396</t>
   </si>
   <si>
     <t xml:space="preserve">3.08847498893738</t>
@@ -1175,76 +1172,79 @@
     <t xml:space="preserve">3.14302659034729</t>
   </si>
   <si>
-    <t xml:space="preserve">3.20597124099731</t>
+    <t xml:space="preserve">3.20597076416016</t>
   </si>
   <si>
     <t xml:space="preserve">3.25632691383362</t>
   </si>
   <si>
-    <t xml:space="preserve">3.24793457984924</t>
+    <t xml:space="preserve">3.24793410301208</t>
   </si>
   <si>
     <t xml:space="preserve">3.10526013374329</t>
   </si>
   <si>
-    <t xml:space="preserve">3.07168984413147</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.18498969078064</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.11365246772766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.12624144554138</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.13883018493652</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.14722299575806</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.15561532974243</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.17240047454834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.08427858352661</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.13463377952576</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.16820454597473</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.10945653915405</t>
+    <t xml:space="preserve">3.07168960571289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.18498945236206</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.17659735679626</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.11365270614624</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.1262412071228</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.1388304233551</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.14722275733948</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.15561556816101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.1724009513855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.08427834510803</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.13463401794434</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.16820430755615</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.10945630073547</t>
   </si>
   <si>
     <t xml:space="preserve">3.15981197357178</t>
   </si>
   <si>
-    <t xml:space="preserve">3.19338226318359</t>
+    <t xml:space="preserve">3.19338250160217</t>
   </si>
   <si>
     <t xml:space="preserve">3.21436381340027</t>
   </si>
   <si>
-    <t xml:space="preserve">3.23534536361694</t>
+    <t xml:space="preserve">3.23534560203552</t>
   </si>
   <si>
     <t xml:space="preserve">3.26471948623657</t>
   </si>
   <si>
-    <t xml:space="preserve">3.32346773147583</t>
+    <t xml:space="preserve">3.32346749305725</t>
   </si>
   <si>
     <t xml:space="preserve">3.31087851524353</t>
   </si>
   <si>
-    <t xml:space="preserve">3.27730798721313</t>
+    <t xml:space="preserve">3.27730822563171</t>
   </si>
   <si>
     <t xml:space="preserve">3.35703778266907</t>
@@ -1256,34 +1256,34 @@
     <t xml:space="preserve">3.49131941795349</t>
   </si>
   <si>
-    <t xml:space="preserve">3.43257141113281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.54167532920837</t>
+    <t xml:space="preserve">3.43257117271423</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.54167461395264</t>
   </si>
   <si>
     <t xml:space="preserve">3.44935655593872</t>
   </si>
   <si>
-    <t xml:space="preserve">3.48292684555054</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.51649713516235</t>
+    <t xml:space="preserve">3.48292636871338</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.51649737358093</t>
   </si>
   <si>
     <t xml:space="preserve">3.47453427314758</t>
   </si>
   <si>
-    <t xml:space="preserve">3.4577488899231</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.38641214370728</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.37801909446716</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.4703381061554</t>
+    <t xml:space="preserve">3.45774912834167</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.3864119052887</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.37801957130432</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.47033786773682</t>
   </si>
   <si>
     <t xml:space="preserve">3.30248594284058</t>
@@ -1292,13 +1292,13 @@
     <t xml:space="preserve">3.31927108764648</t>
   </si>
   <si>
-    <t xml:space="preserve">3.29829001426697</t>
+    <t xml:space="preserve">3.29828977584839</t>
   </si>
   <si>
     <t xml:space="preserve">3.34025263786316</t>
   </si>
   <si>
-    <t xml:space="preserve">3.27311205863953</t>
+    <t xml:space="preserve">3.27311182022095</t>
   </si>
   <si>
     <t xml:space="preserve">3.28150463104248</t>
@@ -1307,55 +1307,55 @@
     <t xml:space="preserve">3.399001121521</t>
   </si>
   <si>
-    <t xml:space="preserve">3.57524561882019</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.58783411979675</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.55006790161133</t>
+    <t xml:space="preserve">3.57524585723877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.58783483505249</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.55006766319275</t>
   </si>
   <si>
     <t xml:space="preserve">3.57944130897522</t>
   </si>
   <si>
-    <t xml:space="preserve">3.58363842964172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.66336727142334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.55845975875854</t>
+    <t xml:space="preserve">3.58363771438599</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.66336750984192</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.55845999717712</t>
   </si>
   <si>
     <t xml:space="preserve">3.56685304641724</t>
   </si>
   <si>
-    <t xml:space="preserve">3.62140417098999</t>
+    <t xml:space="preserve">3.62140440940857</t>
   </si>
   <si>
     <t xml:space="preserve">3.78086376190186</t>
   </si>
   <si>
-    <t xml:space="preserve">3.88577127456665</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.72211575508118</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.76407909393311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.68434882164001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.7976496219635</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.82702326774597</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.80184531211853</t>
+    <t xml:space="preserve">3.88577151298523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.7221155166626</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.76407861709595</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.68434929847717</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.79764914512634</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.82702374458313</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.80184555053711</t>
   </si>
   <si>
     <t xml:space="preserve">3.83961224555969</t>
@@ -1364,79 +1364,79 @@
     <t xml:space="preserve">3.91934180259705</t>
   </si>
   <si>
-    <t xml:space="preserve">3.91094923019409</t>
+    <t xml:space="preserve">3.91094946861267</t>
   </si>
   <si>
     <t xml:space="preserve">3.94451928138733</t>
   </si>
   <si>
-    <t xml:space="preserve">4.06621217727661</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.02005290985107</t>
+    <t xml:space="preserve">4.06621170043945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.02005243301392</t>
   </si>
   <si>
     <t xml:space="preserve">3.927734375</t>
   </si>
   <si>
-    <t xml:space="preserve">3.86898565292358</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.81863045692444</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.86059403419495</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.79345226287842</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.8647894859314</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.87737846374512</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.73470449447632</t>
+    <t xml:space="preserve">3.8689866065979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.8186309337616</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.86059355735779</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.79345273971558</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.86478996276855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.8773787021637</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.73470425605774</t>
   </si>
   <si>
     <t xml:space="preserve">3.8438081741333</t>
   </si>
   <si>
-    <t xml:space="preserve">3.69274234771729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.9025571346283</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.95291233062744</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.99067878723145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.00326824188232</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.91514539718628</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.87318253517151</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.85220122337341</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.66756415367126</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.67595624923706</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.59203124046326</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.53328275680542</t>
+    <t xml:space="preserve">3.69274163246155</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.90255665779114</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.95291209220886</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.9906792640686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.00326776504517</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.91514468193054</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.87318158149719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.85220074653625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.66756367683411</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.67595648765564</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.59203100204468</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.53328251838684</t>
   </si>
   <si>
     <t xml:space="preserve">3.70533061027527</t>
@@ -1445,58 +1445,58 @@
     <t xml:space="preserve">3.64238619804382</t>
   </si>
   <si>
-    <t xml:space="preserve">3.77666783332825</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.71791911125183</t>
+    <t xml:space="preserve">3.77666759490967</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.71791934967041</t>
   </si>
   <si>
     <t xml:space="preserve">3.64658236503601</t>
   </si>
   <si>
-    <t xml:space="preserve">3.70113396644592</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.68015360832214</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.80604195594788</t>
+    <t xml:space="preserve">3.7011342048645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.68015289306641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.8060417175293</t>
   </si>
   <si>
     <t xml:space="preserve">3.7850604057312</t>
   </si>
   <si>
-    <t xml:space="preserve">3.69693827629089</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.73050832748413</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.74729371070862</t>
+    <t xml:space="preserve">3.69693779945374</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.73050856590271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.74729323387146</t>
   </si>
   <si>
     <t xml:space="preserve">3.6507785320282</t>
   </si>
   <si>
-    <t xml:space="preserve">3.65917158126831</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.85639667510986</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.89416408538818</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.93612766265869</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.0074634552002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.08719396591187</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.11237096786499</t>
+    <t xml:space="preserve">3.65917134284973</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.85639715194702</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.89416337013245</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.9361264705658</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.00746393203735</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.08719348907471</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.11237144470215</t>
   </si>
   <si>
     <t xml:space="preserve">4.17111921310425</t>
@@ -1508,40 +1508,40 @@
     <t xml:space="preserve">4.2382607460022</t>
   </si>
   <si>
-    <t xml:space="preserve">4.18790435791016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.09978342056274</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.09558629989624</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.07880067825317</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.14594125747681</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.09138965606689</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.08299732208252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.06201601028442</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.26343822479248</t>
+    <t xml:space="preserve">4.18790483474731</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.09978246688843</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.09558582305908</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.07880115509033</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.14594221115112</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.09139013290405</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.0829963684082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.06201553344727</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.26343774795532</t>
   </si>
   <si>
     <t xml:space="preserve">4.39771938323975</t>
   </si>
   <si>
-    <t xml:space="preserve">4.52360820770264</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.4984302520752</t>
+    <t xml:space="preserve">4.52360916137695</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.49843072891235</t>
   </si>
   <si>
     <t xml:space="preserve">4.58235692977905</t>
@@ -1562,16 +1562,16 @@
     <t xml:space="preserve">4.6830677986145</t>
   </si>
   <si>
-    <t xml:space="preserve">4.66628217697144</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.63271236419678</t>
+    <t xml:space="preserve">4.66628265380859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.63271188735962</t>
   </si>
   <si>
     <t xml:space="preserve">4.44807529449463</t>
   </si>
   <si>
-    <t xml:space="preserve">4.43968200683594</t>
+    <t xml:space="preserve">4.4396824836731</t>
   </si>
   <si>
     <t xml:space="preserve">4.47325277328491</t>
@@ -1580,19 +1580,19 @@
     <t xml:space="preserve">4.49003839492798</t>
   </si>
   <si>
-    <t xml:space="preserve">4.54878568649292</t>
+    <t xml:space="preserve">4.54878616333008</t>
   </si>
   <si>
     <t xml:space="preserve">4.59914207458496</t>
   </si>
   <si>
-    <t xml:space="preserve">4.61592674255371</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.60753488540649</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.40611267089844</t>
+    <t xml:space="preserve">4.61592721939087</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.60753440856934</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.40611219406128</t>
   </si>
   <si>
     <t xml:space="preserve">4.53200149536133</t>
@@ -1601,13 +1601,13 @@
     <t xml:space="preserve">4.75860166549683</t>
   </si>
   <si>
-    <t xml:space="preserve">4.80895709991455</t>
+    <t xml:space="preserve">4.80895662307739</t>
   </si>
   <si>
     <t xml:space="preserve">4.74181604385376</t>
   </si>
   <si>
-    <t xml:space="preserve">4.69146060943604</t>
+    <t xml:space="preserve">4.69145965576172</t>
   </si>
   <si>
     <t xml:space="preserve">4.65789031982422</t>
@@ -1616,13 +1616,13 @@
     <t xml:space="preserve">4.50682353973389</t>
   </si>
   <si>
-    <t xml:space="preserve">4.54039287567139</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.46486043930054</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.41450500488281</t>
+    <t xml:space="preserve">4.54039335250854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.4648609161377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.41450452804565</t>
   </si>
   <si>
     <t xml:space="preserve">4.38932704925537</t>
@@ -1631,7 +1631,7 @@
     <t xml:space="preserve">4.38093423843384</t>
   </si>
   <si>
-    <t xml:space="preserve">4.34736347198486</t>
+    <t xml:space="preserve">4.34736394882202</t>
   </si>
   <si>
     <t xml:space="preserve">4.46764659881592</t>
@@ -1640,55 +1640,55 @@
     <t xml:space="preserve">4.51919651031494</t>
   </si>
   <si>
-    <t xml:space="preserve">4.39891386032104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.37313842773438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.30440664291382</t>
+    <t xml:space="preserve">4.3989143371582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.37313938140869</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.30440616607666</t>
   </si>
   <si>
     <t xml:space="preserve">4.27003860473633</t>
   </si>
   <si>
-    <t xml:space="preserve">4.33018112182617</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.31299781799316</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.3817310333252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.34736394882202</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.44187164306641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.45905494689941</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.35595607757568</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.3903226852417</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.45046329498291</t>
+    <t xml:space="preserve">4.33018064498901</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.31299686431885</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.38173007965088</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.34736442565918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.44187211990356</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.45905542373657</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.35595512390137</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.39032173156738</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.45046377182007</t>
   </si>
   <si>
     <t xml:space="preserve">4.41609716415405</t>
   </si>
   <si>
-    <t xml:space="preserve">4.23137712478638</t>
+    <t xml:space="preserve">4.23137760162354</t>
   </si>
   <si>
     <t xml:space="preserve">4.26574325561523</t>
   </si>
   <si>
-    <t xml:space="preserve">4.13257312774658</t>
+    <t xml:space="preserve">4.13257360458374</t>
   </si>
   <si>
     <t xml:space="preserve">4.0466570854187</t>
@@ -1697,13 +1697,13 @@
     <t xml:space="preserve">4.08531951904297</t>
   </si>
   <si>
-    <t xml:space="preserve">3.98221945762634</t>
+    <t xml:space="preserve">3.9822199344635</t>
   </si>
   <si>
     <t xml:space="preserve">4.03376960754395</t>
   </si>
   <si>
-    <t xml:space="preserve">3.94785284996033</t>
+    <t xml:space="preserve">3.94785308837891</t>
   </si>
   <si>
     <t xml:space="preserve">3.99081134796143</t>
@@ -1715,10 +1715,10 @@
     <t xml:space="preserve">3.94355750083923</t>
   </si>
   <si>
-    <t xml:space="preserve">3.96503639221191</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.96074032783508</t>
+    <t xml:space="preserve">3.96503663063049</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.9607412815094</t>
   </si>
   <si>
     <t xml:space="preserve">4.01229047775269</t>
@@ -1730,34 +1730,34 @@
     <t xml:space="preserve">4.07243156433105</t>
   </si>
   <si>
-    <t xml:space="preserve">4.08961534500122</t>
+    <t xml:space="preserve">4.08961582183838</t>
   </si>
   <si>
     <t xml:space="preserve">4.11109399795532</t>
   </si>
   <si>
-    <t xml:space="preserve">4.26144742965698</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.32158899307251</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.295814037323</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.02947425842285</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.84045720100403</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.87482452392578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.8877124786377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.00369882583618</t>
+    <t xml:space="preserve">4.26144790649414</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.32158946990967</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.29581451416016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.02947378158569</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.84045743942261</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.87482500076294</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.88771200180054</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.00369930267334</t>
   </si>
   <si>
     <t xml:space="preserve">4.02088212966919</t>
@@ -1766,7 +1766,7 @@
     <t xml:space="preserve">3.93496584892273</t>
   </si>
   <si>
-    <t xml:space="preserve">3.86623287200928</t>
+    <t xml:space="preserve">3.86623215675354</t>
   </si>
   <si>
     <t xml:space="preserve">3.77172470092773</t>
@@ -1778,7 +1778,7 @@
     <t xml:space="preserve">3.70299196243286</t>
   </si>
   <si>
-    <t xml:space="preserve">3.67721772193909</t>
+    <t xml:space="preserve">3.67721700668335</t>
   </si>
   <si>
     <t xml:space="preserve">3.68580842018127</t>
@@ -1787,64 +1787,64 @@
     <t xml:space="preserve">3.70728731155396</t>
   </si>
   <si>
-    <t xml:space="preserve">3.66432929039001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.66003394126892</t>
+    <t xml:space="preserve">3.66432952880859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.6600341796875</t>
   </si>
   <si>
     <t xml:space="preserve">3.72017502784729</t>
   </si>
   <si>
-    <t xml:space="preserve">3.81468319892883</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.95214939117432</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.85764050483704</t>
+    <t xml:space="preserve">3.81468272209167</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.9521484375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.85764122009277</t>
   </si>
   <si>
     <t xml:space="preserve">3.78461265563965</t>
   </si>
   <si>
-    <t xml:space="preserve">3.84475326538086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.78031706809998</t>
+    <t xml:space="preserve">3.8447539806366</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.78031659126282</t>
   </si>
   <si>
     <t xml:space="preserve">3.69440054893494</t>
   </si>
   <si>
-    <t xml:space="preserve">3.73306250572205</t>
+    <t xml:space="preserve">3.73306226730347</t>
   </si>
   <si>
     <t xml:space="preserve">3.71158361434937</t>
   </si>
   <si>
-    <t xml:space="preserve">3.59989237785339</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.75454187393188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.65144228935242</t>
+    <t xml:space="preserve">3.59989213943481</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.75454139709473</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.65144181251526</t>
   </si>
   <si>
     <t xml:space="preserve">3.72447085380554</t>
   </si>
   <si>
-    <t xml:space="preserve">3.78890776634216</t>
+    <t xml:space="preserve">3.78890824317932</t>
   </si>
   <si>
     <t xml:space="preserve">3.64714598655701</t>
   </si>
   <si>
-    <t xml:space="preserve">3.66862559318542</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.67292094230652</t>
+    <t xml:space="preserve">3.66862511634827</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.6729211807251</t>
   </si>
   <si>
     <t xml:space="preserve">3.61707592010498</t>
@@ -1859,49 +1859,49 @@
     <t xml:space="preserve">3.65573787689209</t>
   </si>
   <si>
-    <t xml:space="preserve">3.629962682724</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.96933197975159</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.95644450187683</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.90059947967529</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.93067002296448</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.0165867805481</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.09820699691772</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.14116477966309</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.24426364898682</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.24856090545654</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.43328046798706</t>
+    <t xml:space="preserve">3.62996292114258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.96933221817017</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.95644426345825</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.90059924125671</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.9306697845459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.01658630371094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.09820652008057</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.14116525650024</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.24426507949829</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.24855995178223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.43327951431274</t>
   </si>
   <si>
     <t xml:space="preserve">4.42468881607056</t>
   </si>
   <si>
-    <t xml:space="preserve">4.58792972564697</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.57933807373047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.49342155456543</t>
+    <t xml:space="preserve">4.58793020248413</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.57933759689331</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.49342107772827</t>
   </si>
   <si>
     <t xml:space="preserve">4.55356311798096</t>
@@ -1910,16 +1910,16 @@
     <t xml:space="preserve">4.48482990264893</t>
   </si>
   <si>
-    <t xml:space="preserve">4.53637981414795</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.59652137756348</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.77694511413574</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.81131172180176</t>
+    <t xml:space="preserve">4.53637933731079</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.59652090072632</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.7769455909729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.81131219863892</t>
   </si>
   <si>
     <t xml:space="preserve">4.69962072372437</t>
@@ -1928,22 +1928,22 @@
     <t xml:space="preserve">4.64807033538818</t>
   </si>
   <si>
-    <t xml:space="preserve">4.72539520263672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.71680450439453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.69102954864502</t>
+    <t xml:space="preserve">4.72539615631104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.71680355072021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.6910285949707</t>
   </si>
   <si>
     <t xml:space="preserve">4.68243789672852</t>
   </si>
   <si>
-    <t xml:space="preserve">4.70821237564087</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.67384576797485</t>
+    <t xml:space="preserve">4.70821189880371</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.67384624481201</t>
   </si>
   <si>
     <t xml:space="preserve">4.5621542930603</t>
@@ -1952,28 +1952,28 @@
     <t xml:space="preserve">4.50201320648193</t>
   </si>
   <si>
-    <t xml:space="preserve">4.54497098922729</t>
+    <t xml:space="preserve">4.54497146606445</t>
   </si>
   <si>
     <t xml:space="preserve">4.51060485839844</t>
   </si>
   <si>
-    <t xml:space="preserve">4.52778768539429</t>
+    <t xml:space="preserve">4.5277886390686</t>
   </si>
   <si>
     <t xml:space="preserve">4.7683539390564</t>
   </si>
   <si>
-    <t xml:space="preserve">4.66525411605835</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.61370420455933</t>
+    <t xml:space="preserve">4.66525363922119</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.61370468139648</t>
   </si>
   <si>
     <t xml:space="preserve">4.73398733139038</t>
   </si>
   <si>
-    <t xml:space="preserve">4.63947916030884</t>
+    <t xml:space="preserve">4.639479637146</t>
   </si>
   <si>
     <t xml:space="preserve">4.23567295074463</t>
@@ -1982,7 +1982,7 @@
     <t xml:space="preserve">4.15834856033325</t>
   </si>
   <si>
-    <t xml:space="preserve">4.20130586624146</t>
+    <t xml:space="preserve">4.20130634307861</t>
   </si>
   <si>
     <t xml:space="preserve">4.36454725265503</t>
@@ -1994,28 +1994,28 @@
     <t xml:space="preserve">4.11539030075073</t>
   </si>
   <si>
-    <t xml:space="preserve">3.75024557113647</t>
+    <t xml:space="preserve">3.7502453327179</t>
   </si>
   <si>
     <t xml:space="preserve">3.47101783752441</t>
   </si>
   <si>
-    <t xml:space="preserve">3.36362242698669</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.31207275390625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.16601490974426</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.22186064720154</t>
+    <t xml:space="preserve">3.36362218856812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.31207299232483</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.16601514816284</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.22186040878296</t>
   </si>
   <si>
     <t xml:space="preserve">2.80516672134399</t>
   </si>
   <si>
-    <t xml:space="preserve">2.91685795783997</t>
+    <t xml:space="preserve">2.91685771942139</t>
   </si>
   <si>
     <t xml:space="preserve">2.86530804634094</t>
@@ -2024,82 +2024,82 @@
     <t xml:space="preserve">2.88678693771362</t>
   </si>
   <si>
-    <t xml:space="preserve">2.73213815689087</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.66770029067993</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.80087089538574</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.61185503005981</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.72354602813721</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.92115378379822</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.81375813484192</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.70206713676453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.65910911560059</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.84382915496826</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.76650452613831</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.78798317909241</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.7063627243042</t>
+    <t xml:space="preserve">2.73213768005371</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.66770052909851</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.80087065696716</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.61185526847839</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.72354626655579</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.92115354537964</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.8137583732605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.70206689834595</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.65910887718201</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.84382891654968</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.76650476455688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.78798341751099</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.70636296272278</t>
   </si>
   <si>
     <t xml:space="preserve">2.71065878868103</t>
   </si>
   <si>
-    <t xml:space="preserve">2.85242056846619</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.89108300209045</t>
+    <t xml:space="preserve">2.85242080688477</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.89108276367188</t>
   </si>
   <si>
     <t xml:space="preserve">2.92974543571472</t>
   </si>
   <si>
-    <t xml:space="preserve">3.00707006454468</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.96411180496216</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.93833708763123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.94263291358948</t>
+    <t xml:space="preserve">3.0070698261261</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.96411156654358</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.93833684921265</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.94263243675232</t>
   </si>
   <si>
     <t xml:space="preserve">2.98129510879517</t>
   </si>
   <si>
-    <t xml:space="preserve">3.01136565208435</t>
+    <t xml:space="preserve">3.01136612892151</t>
   </si>
   <si>
     <t xml:space="preserve">2.94692873954773</t>
   </si>
   <si>
-    <t xml:space="preserve">2.97699928283691</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.9512243270874</t>
+    <t xml:space="preserve">2.97699904441833</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.95122408866882</t>
   </si>
   <si>
     <t xml:space="preserve">3.10587358474731</t>
@@ -2108,19 +2108,19 @@
     <t xml:space="preserve">3.04143643379211</t>
   </si>
   <si>
-    <t xml:space="preserve">3.05002784729004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.08439469337463</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.13164854049683</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.03284502029419</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.09298634529114</t>
+    <t xml:space="preserve">3.05002808570862</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.08439445495605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.13164830207825</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.03284478187561</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.09298610687256</t>
   </si>
   <si>
     <t xml:space="preserve">3.19178986549377</t>
@@ -2129,37 +2129,37 @@
     <t xml:space="preserve">3.24763536453247</t>
   </si>
   <si>
-    <t xml:space="preserve">3.16171932220459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.14883160591125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.18319845199585</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.13594460487366</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.11876130104065</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.30777668952942</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.38510179519653</t>
+    <t xml:space="preserve">3.16171908378601</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.14883184432983</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.18319797515869</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.13594436645508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.11876106262207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.307776927948</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.38510155677795</t>
   </si>
   <si>
     <t xml:space="preserve">3.4366512298584</t>
   </si>
   <si>
-    <t xml:space="preserve">3.48390531539917</t>
+    <t xml:space="preserve">3.48390507698059</t>
   </si>
   <si>
     <t xml:space="preserve">3.46242642402649</t>
   </si>
   <si>
-    <t xml:space="preserve">3.47960996627808</t>
+    <t xml:space="preserve">3.47960948944092</t>
   </si>
   <si>
     <t xml:space="preserve">3.31636834144592</t>
@@ -2171,13 +2171,13 @@
     <t xml:space="preserve">3.19608569145203</t>
   </si>
   <si>
-    <t xml:space="preserve">3.3808057308197</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.37651014328003</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.35073518753052</t>
+    <t xml:space="preserve">3.38080549240112</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.37650990486145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.35073494911194</t>
   </si>
   <si>
     <t xml:space="preserve">3.3722140789032</t>
@@ -2192,13 +2192,13 @@
     <t xml:space="preserve">3.44524312019348</t>
   </si>
   <si>
-    <t xml:space="preserve">3.75857496261597</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.71435618400574</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.63034129142761</t>
+    <t xml:space="preserve">3.75857448577881</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.71435570716858</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.63034105300903</t>
   </si>
   <si>
     <t xml:space="preserve">3.58170104026794</t>
@@ -2210,7 +2210,7 @@
     <t xml:space="preserve">3.50210738182068</t>
   </si>
   <si>
-    <t xml:space="preserve">3.43135786056519</t>
+    <t xml:space="preserve">3.43135762214661</t>
   </si>
   <si>
     <t xml:space="preserve">3.44904518127441</t>
@@ -2222,7 +2222,7 @@
     <t xml:space="preserve">3.38713908195496</t>
   </si>
   <si>
-    <t xml:space="preserve">3.41809225082397</t>
+    <t xml:space="preserve">3.4180920124054</t>
   </si>
   <si>
     <t xml:space="preserve">3.32081151008606</t>
@@ -2231,31 +2231,31 @@
     <t xml:space="preserve">3.33849883079529</t>
   </si>
   <si>
-    <t xml:space="preserve">3.31638956069946</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.27217102050781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.28101468086243</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.22795271873474</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.09529685974121</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.18373394012451</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.25448369979858</t>
+    <t xml:space="preserve">3.31638932228088</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.27217078208923</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.28101491928101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.22795224189758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.09529662132263</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.18373346328735</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.25448346138</t>
   </si>
   <si>
     <t xml:space="preserve">3.20584297180176</t>
   </si>
   <si>
-    <t xml:space="preserve">3.1660463809967</t>
+    <t xml:space="preserve">3.16604661941528</t>
   </si>
   <si>
     <t xml:space="preserve">3.15720248222351</t>
@@ -2267,7 +2267,7 @@
     <t xml:space="preserve">3.10414052009583</t>
   </si>
   <si>
-    <t xml:space="preserve">3.09971857070923</t>
+    <t xml:space="preserve">3.09971904754639</t>
   </si>
   <si>
     <t xml:space="preserve">3.04223465919495</t>
@@ -2276,16 +2276,16 @@
     <t xml:space="preserve">3.04665637016296</t>
   </si>
   <si>
-    <t xml:space="preserve">3.0776093006134</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.0599217414856</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.98032855987549</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.96264123916626</t>
+    <t xml:space="preserve">3.07760953903198</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.05992197990417</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.98032832145691</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.96264100074768</t>
   </si>
   <si>
     <t xml:space="preserve">2.94495368003845</t>
@@ -2294,34 +2294,34 @@
     <t xml:space="preserve">2.93611001968384</t>
   </si>
   <si>
-    <t xml:space="preserve">3.09087491035461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.06876587867737</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.05550003051758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.98475074768066</t>
+    <t xml:space="preserve">3.09087467193604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.06876540184021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.05550026893616</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.98475050926208</t>
   </si>
   <si>
     <t xml:space="preserve">2.9051570892334</t>
   </si>
   <si>
-    <t xml:space="preserve">2.83440756797791</t>
+    <t xml:space="preserve">2.83440732955933</t>
   </si>
   <si>
     <t xml:space="preserve">2.86978220939636</t>
   </si>
   <si>
-    <t xml:space="preserve">2.80345439910889</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.77692341804504</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.81229853630066</t>
+    <t xml:space="preserve">2.80345463752747</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.7769238948822</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.81229829788208</t>
   </si>
   <si>
     <t xml:space="preserve">2.84767317771912</t>
@@ -2333,13 +2333,13 @@
     <t xml:space="preserve">2.79461097717285</t>
   </si>
   <si>
-    <t xml:space="preserve">2.91842269897461</t>
+    <t xml:space="preserve">2.91842293739319</t>
   </si>
   <si>
     <t xml:space="preserve">2.82114243507385</t>
   </si>
   <si>
-    <t xml:space="preserve">2.79903268814087</t>
+    <t xml:space="preserve">2.79903292655945</t>
   </si>
   <si>
     <t xml:space="preserve">2.80787634849548</t>
@@ -2348,22 +2348,22 @@
     <t xml:space="preserve">2.75923585891724</t>
   </si>
   <si>
-    <t xml:space="preserve">2.7238609790802</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.71501755714417</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.68406462669373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.63542437553406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.61773681640625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.58236193656921</t>
+    <t xml:space="preserve">2.72386121749878</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.71501731872559</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.6840648651123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.63542413711548</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.61773705482483</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.58236169815063</t>
   </si>
   <si>
     <t xml:space="preserve">2.54698729515076</t>
@@ -2372,7 +2372,7 @@
     <t xml:space="preserve">2.56467461585999</t>
   </si>
   <si>
-    <t xml:space="preserve">2.5514087677002</t>
+    <t xml:space="preserve">2.55140900611877</t>
   </si>
   <si>
     <t xml:space="preserve">2.49392461776733</t>
@@ -2384,16 +2384,16 @@
     <t xml:space="preserve">2.97148466110229</t>
   </si>
   <si>
-    <t xml:space="preserve">2.95379734039307</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.00243806838989</t>
+    <t xml:space="preserve">2.95379757881165</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.00243782997131</t>
   </si>
   <si>
     <t xml:space="preserve">3.17931199073792</t>
   </si>
   <si>
-    <t xml:space="preserve">3.1704683303833</t>
+    <t xml:space="preserve">3.17046856880188</t>
   </si>
   <si>
     <t xml:space="preserve">3.19257760047913</t>
@@ -2411,19 +2411,19 @@
     <t xml:space="preserve">3.4136700630188</t>
   </si>
   <si>
-    <t xml:space="preserve">3.48442006111145</t>
+    <t xml:space="preserve">3.48441982269287</t>
   </si>
   <si>
     <t xml:space="preserve">3.45788884162903</t>
   </si>
   <si>
-    <t xml:space="preserve">3.49326348304749</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.51095080375671</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.44462299346924</t>
+    <t xml:space="preserve">3.49326372146606</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.51095104217529</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.44462323188782</t>
   </si>
   <si>
     <t xml:space="preserve">3.42693567276001</t>
@@ -2432,37 +2432,37 @@
     <t xml:space="preserve">3.55516934394836</t>
   </si>
   <si>
-    <t xml:space="preserve">3.6789813041687</t>
+    <t xml:space="preserve">3.67898154258728</t>
   </si>
   <si>
     <t xml:space="preserve">3.72320032119751</t>
   </si>
   <si>
-    <t xml:space="preserve">3.74973082542419</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.80279350280762</t>
+    <t xml:space="preserve">3.74973106384277</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.80279326438904</t>
   </si>
   <si>
     <t xml:space="preserve">3.65687227249146</t>
   </si>
   <si>
-    <t xml:space="preserve">3.66129422187805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.65245032310486</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.62591886520386</t>
+    <t xml:space="preserve">3.66129398345947</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.65245079994202</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.62591934204102</t>
   </si>
   <si>
     <t xml:space="preserve">3.60823178291321</t>
   </si>
   <si>
-    <t xml:space="preserve">3.54632592201233</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.53748202323914</t>
+    <t xml:space="preserve">3.54632616043091</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.53748226165771</t>
   </si>
   <si>
     <t xml:space="preserve">3.57285690307617</t>
@@ -2471,49 +2471,49 @@
     <t xml:space="preserve">3.50652885437012</t>
   </si>
   <si>
-    <t xml:space="preserve">3.5905442237854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.57727909088135</t>
+    <t xml:space="preserve">3.59054446220398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.57727861404419</t>
   </si>
   <si>
     <t xml:space="preserve">3.74530935287476</t>
   </si>
   <si>
-    <t xml:space="preserve">3.74088764190674</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.73204398155212</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.70551252365112</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.77626252174377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.83816838264465</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.68340301513672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.76741862297058</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.78068375587463</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.76299667358398</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.77184009552002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.71877789497375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.68782544136047</t>
+    <t xml:space="preserve">3.74088740348816</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.73204326629639</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.7055127620697</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.77626180648804</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.83816814422607</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.68340349197388</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.76741886138916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.78068399429321</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.76299643516541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.77184057235718</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.71877813339233</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.68782496452332</t>
   </si>
   <si>
     <t xml:space="preserve">3.6170756816864</t>
@@ -2528,31 +2528,31 @@
     <t xml:space="preserve">3.70993447303772</t>
   </si>
   <si>
-    <t xml:space="preserve">3.78510665893555</t>
+    <t xml:space="preserve">3.78510594367981</t>
   </si>
   <si>
     <t xml:space="preserve">3.92660522460938</t>
   </si>
   <si>
-    <t xml:space="preserve">3.93987035751343</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.99735426902771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.01079845428467</t>
+    <t xml:space="preserve">3.93987107276917</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.99735474586487</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.01079893112183</t>
   </si>
   <si>
     <t xml:space="preserve">4.09594440460205</t>
   </si>
   <si>
-    <t xml:space="preserve">4.17212724685669</t>
+    <t xml:space="preserve">4.17212677001953</t>
   </si>
   <si>
     <t xml:space="preserve">4.16316413879395</t>
   </si>
   <si>
-    <t xml:space="preserve">4.13627576828003</t>
+    <t xml:space="preserve">4.13627624511719</t>
   </si>
   <si>
     <t xml:space="preserve">4.19901466369629</t>
@@ -2567,7 +2567,7 @@
     <t xml:space="preserve">4.06905603408813</t>
   </si>
   <si>
-    <t xml:space="preserve">4.03320550918579</t>
+    <t xml:space="preserve">4.03320503234863</t>
   </si>
   <si>
     <t xml:space="preserve">3.9794294834137</t>
@@ -2576,13 +2576,13 @@
     <t xml:space="preserve">4.02872371673584</t>
   </si>
   <si>
-    <t xml:space="preserve">4.05561208724976</t>
+    <t xml:space="preserve">4.05561256408691</t>
   </si>
   <si>
     <t xml:space="preserve">4.08698177337646</t>
   </si>
   <si>
-    <t xml:space="preserve">3.97494792938232</t>
+    <t xml:space="preserve">3.97494769096375</t>
   </si>
   <si>
     <t xml:space="preserve">4.00183629989624</t>
@@ -2591,34 +2591,34 @@
     <t xml:space="preserve">4.01528024673462</t>
   </si>
   <si>
-    <t xml:space="preserve">3.96150398254395</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.98839163780212</t>
+    <t xml:space="preserve">3.96150374412537</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.9883918762207</t>
   </si>
   <si>
     <t xml:space="preserve">3.95254135131836</t>
   </si>
   <si>
-    <t xml:space="preserve">3.96598529815674</t>
+    <t xml:space="preserve">3.96598553657532</t>
   </si>
   <si>
     <t xml:space="preserve">4.04216861724854</t>
   </si>
   <si>
-    <t xml:space="preserve">4.07801914215088</t>
+    <t xml:space="preserve">4.07801866531372</t>
   </si>
   <si>
     <t xml:space="preserve">4.11835050582886</t>
   </si>
   <si>
-    <t xml:space="preserve">4.17660760879517</t>
+    <t xml:space="preserve">4.17660856246948</t>
   </si>
   <si>
     <t xml:space="preserve">4.11386966705322</t>
   </si>
   <si>
-    <t xml:space="preserve">4.10938835144043</t>
+    <t xml:space="preserve">4.10938787460327</t>
   </si>
   <si>
     <t xml:space="preserve">4.06009340286255</t>
@@ -2633,16 +2633,16 @@
     <t xml:space="preserve">4.14972019195557</t>
   </si>
   <si>
-    <t xml:space="preserve">4.12283229827881</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.03768634796143</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.01976203918457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.06457471847534</t>
+    <t xml:space="preserve">4.12283182144165</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.03768682479858</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.01976108551025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.06457424163818</t>
   </si>
   <si>
     <t xml:space="preserve">4.20797777175903</t>
@@ -2654,10 +2654,10 @@
     <t xml:space="preserve">4.25727224349976</t>
   </si>
   <si>
-    <t xml:space="preserve">4.20349597930908</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.92565321922302</t>
+    <t xml:space="preserve">4.20349645614624</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.92565369606018</t>
   </si>
   <si>
     <t xml:space="preserve">3.90772819519043</t>
@@ -2666,25 +2666,25 @@
     <t xml:space="preserve">3.88083982467651</t>
   </si>
   <si>
-    <t xml:space="preserve">3.87635850906372</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.80913829803467</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.71503043174744</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.66573596000671</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.83154535293579</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.93461537361145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.99735474586487</t>
+    <t xml:space="preserve">3.87635827064514</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.80913805961609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.71503019332886</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.66573572158813</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.83154511451721</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.93461585044861</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.99735498428345</t>
   </si>
   <si>
     <t xml:space="preserve">3.94357872009277</t>
@@ -2693,10 +2693,10 @@
     <t xml:space="preserve">4.04664945602417</t>
   </si>
   <si>
-    <t xml:space="preserve">3.99287343025208</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.98391079902649</t>
+    <t xml:space="preserve">3.99287366867065</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.98391056060791</t>
   </si>
   <si>
     <t xml:space="preserve">4.02424240112305</t>
@@ -2705,13 +2705,13 @@
     <t xml:space="preserve">3.85395193099976</t>
   </si>
   <si>
-    <t xml:space="preserve">3.93013501167297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.97046661376953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.10042524337769</t>
+    <t xml:space="preserve">3.93013453483582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.97046685218811</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.10042572021484</t>
   </si>
   <si>
     <t xml:space="preserve">4.15420150756836</t>
@@ -2723,70 +2723,70 @@
     <t xml:space="preserve">4.22590303421021</t>
   </si>
   <si>
-    <t xml:space="preserve">4.26623487472534</t>
+    <t xml:space="preserve">4.2662353515625</t>
   </si>
   <si>
     <t xml:space="preserve">4.24382829666138</t>
   </si>
   <si>
-    <t xml:space="preserve">4.13179445266724</t>
+    <t xml:space="preserve">4.13179540634155</t>
   </si>
   <si>
     <t xml:space="preserve">4.12731313705444</t>
   </si>
   <si>
-    <t xml:space="preserve">4.24830961227417</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.19005250930786</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.29312324523926</t>
+    <t xml:space="preserve">4.24830913543701</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.19005298614502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.2931227684021</t>
   </si>
   <si>
     <t xml:space="preserve">4.40515613555908</t>
   </si>
   <si>
-    <t xml:space="preserve">4.43652582168579</t>
+    <t xml:space="preserve">4.43652534484863</t>
   </si>
   <si>
     <t xml:space="preserve">4.48133897781372</t>
   </si>
   <si>
-    <t xml:space="preserve">4.53511524200439</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.55304002761841</t>
+    <t xml:space="preserve">4.53511571884155</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.55304098129272</t>
   </si>
   <si>
     <t xml:space="preserve">4.56200361251831</t>
   </si>
   <si>
-    <t xml:space="preserve">4.50822734832764</t>
+    <t xml:space="preserve">4.50822782516479</t>
   </si>
   <si>
     <t xml:space="preserve">4.45445108413696</t>
   </si>
   <si>
-    <t xml:space="preserve">4.43204498291016</t>
+    <t xml:space="preserve">4.432044506073</t>
   </si>
   <si>
     <t xml:space="preserve">4.49926471710205</t>
   </si>
   <si>
-    <t xml:space="preserve">4.49030208587646</t>
+    <t xml:space="preserve">4.49030256271362</t>
   </si>
   <si>
     <t xml:space="preserve">4.51718997955322</t>
   </si>
   <si>
-    <t xml:space="preserve">4.633704662323</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.59785413742065</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.47685813903809</t>
+    <t xml:space="preserve">4.63370513916016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.59785461425781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.47685766220093</t>
   </si>
   <si>
     <t xml:space="preserve">4.57096576690674</t>
@@ -2795,37 +2795,37 @@
     <t xml:space="preserve">4.61577939987183</t>
   </si>
   <si>
-    <t xml:space="preserve">4.64266681671143</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.3917121887207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.44997024536133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.27519750595093</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.58889198303223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.66059303283691</t>
+    <t xml:space="preserve">4.64266777038574</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.39171266555786</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.44996976852417</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.27519798278809</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.58889150619507</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.66059255599976</t>
   </si>
   <si>
     <t xml:space="preserve">4.65163040161133</t>
   </si>
   <si>
-    <t xml:space="preserve">4.71436929702759</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.75918245315552</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.76814460754395</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.89362287521362</t>
+    <t xml:space="preserve">4.71436882019043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.75918197631836</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.76814556121826</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.89362239837646</t>
   </si>
   <si>
     <t xml:space="preserve">4.92051029205322</t>
@@ -2843,13 +2843,13 @@
     <t xml:space="preserve">5.14457702636719</t>
   </si>
   <si>
-    <t xml:space="preserve">5.31486797332764</t>
+    <t xml:space="preserve">5.31486845016479</t>
   </si>
   <si>
     <t xml:space="preserve">5.37760734558105</t>
   </si>
   <si>
-    <t xml:space="preserve">5.35968160629272</t>
+    <t xml:space="preserve">5.35968208312988</t>
   </si>
   <si>
     <t xml:space="preserve">5.16250324249268</t>
@@ -2858,55 +2858,55 @@
     <t xml:space="preserve">5.04598808288574</t>
   </si>
   <si>
-    <t xml:space="preserve">5.15354061126709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.26109218597412</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.27901744842529</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.51204776763916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.4761962890625</t>
+    <t xml:space="preserve">5.15354013442993</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.26109266281128</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.27901697158813</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.512047290802</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.47619676589966</t>
   </si>
   <si>
     <t xml:space="preserve">5.50308418273926</t>
   </si>
   <si>
-    <t xml:space="preserve">5.29694366455078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.19835329055786</t>
+    <t xml:space="preserve">5.29694318771362</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.19835376739502</t>
   </si>
   <si>
     <t xml:space="preserve">5.18042850494385</t>
   </si>
   <si>
-    <t xml:space="preserve">5.07287549972534</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.09080171585083</t>
+    <t xml:space="preserve">5.0728759765625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.09080123901367</t>
   </si>
   <si>
     <t xml:space="preserve">4.99221229553223</t>
   </si>
   <si>
-    <t xml:space="preserve">4.75022029876709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.80399608612061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.92947292327881</t>
+    <t xml:space="preserve">4.75021982192993</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.80399560928345</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.92947340011597</t>
   </si>
   <si>
     <t xml:space="preserve">4.83984661102295</t>
   </si>
   <si>
-    <t xml:space="preserve">4.9742865562439</t>
+    <t xml:space="preserve">4.97428703308105</t>
   </si>
   <si>
     <t xml:space="preserve">4.90258502960205</t>
@@ -2930,25 +2930,25 @@
     <t xml:space="preserve">4.70540618896484</t>
   </si>
   <si>
-    <t xml:space="preserve">4.52615308761597</t>
+    <t xml:space="preserve">4.52615261077881</t>
   </si>
   <si>
     <t xml:space="preserve">4.41860055923462</t>
   </si>
   <si>
-    <t xml:space="preserve">4.36482429504395</t>
+    <t xml:space="preserve">4.3648247718811</t>
   </si>
   <si>
     <t xml:space="preserve">4.23934698104858</t>
   </si>
   <si>
-    <t xml:space="preserve">4.85777139663696</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.91154766082764</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.96532440185547</t>
+    <t xml:space="preserve">4.85777187347412</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.91154813766479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.96532392501831</t>
   </si>
   <si>
     <t xml:space="preserve">5.11768960952759</t>
@@ -2957,22 +2957,22 @@
     <t xml:space="preserve">5.22524166107178</t>
   </si>
   <si>
-    <t xml:space="preserve">5.30590581893921</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.42242097854614</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.28798007965088</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.43138265609741</t>
+    <t xml:space="preserve">5.30590629577637</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.42242050170898</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.28798055648804</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.43138313293457</t>
   </si>
   <si>
     <t xml:space="preserve">5.55686044692993</t>
   </si>
   <si>
-    <t xml:space="preserve">5.62856245040894</t>
+    <t xml:space="preserve">5.62856292724609</t>
   </si>
   <si>
     <t xml:space="preserve">5.52100992202759</t>
@@ -2981,7 +2981,7 @@
     <t xml:space="preserve">5.61959934234619</t>
   </si>
   <si>
-    <t xml:space="preserve">5.53893518447876</t>
+    <t xml:space="preserve">5.53893566131592</t>
   </si>
   <si>
     <t xml:space="preserve">5.37441253662109</t>
@@ -2993,7 +2993,7 @@
     <t xml:space="preserve">5.46581411361694</t>
   </si>
   <si>
-    <t xml:space="preserve">5.48409414291382</t>
+    <t xml:space="preserve">5.48409461975098</t>
   </si>
   <si>
     <t xml:space="preserve">5.63947725296021</t>
@@ -3002,7 +3002,7 @@
     <t xml:space="preserve">5.75829935073853</t>
   </si>
   <si>
-    <t xml:space="preserve">5.80399942398071</t>
+    <t xml:space="preserve">5.80399990081787</t>
   </si>
   <si>
     <t xml:space="preserve">5.65775728225708</t>
@@ -3011,19 +3011,19 @@
     <t xml:space="preserve">5.62119674682617</t>
   </si>
   <si>
-    <t xml:space="preserve">5.410973072052</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.40183258056641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.63033628463745</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.61205673217773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.8222804069519</t>
+    <t xml:space="preserve">5.41097354888916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.40183305740356</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.63033676147461</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.61205625534058</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.82227993011475</t>
   </si>
   <si>
     <t xml:space="preserve">5.84056043624878</t>
@@ -3041,16 +3041,16 @@
     <t xml:space="preserve">5.97766304016113</t>
   </si>
   <si>
-    <t xml:space="preserve">5.9593825340271</t>
+    <t xml:space="preserve">5.95938205718994</t>
   </si>
   <si>
     <t xml:space="preserve">6.04164409637451</t>
   </si>
   <si>
-    <t xml:space="preserve">5.87712097167969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.07820463180542</t>
+    <t xml:space="preserve">5.87712144851685</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.07820510864258</t>
   </si>
   <si>
     <t xml:space="preserve">5.9136815071106</t>
@@ -3065,25 +3065,25 @@
     <t xml:space="preserve">5.7308783531189</t>
   </si>
   <si>
-    <t xml:space="preserve">5.67603826522827</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.69431781768799</t>
+    <t xml:space="preserve">5.67603778839111</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.69431829452515</t>
   </si>
   <si>
     <t xml:space="preserve">5.66689729690552</t>
   </si>
   <si>
-    <t xml:space="preserve">5.42925357818604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.4201135635376</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.33785200119019</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.20988941192627</t>
+    <t xml:space="preserve">5.42925310134888</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.42011308670044</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.33785152435303</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.20988988876343</t>
   </si>
   <si>
     <t xml:space="preserve">5.34699201583862</t>
@@ -3095,10 +3095,10 @@
     <t xml:space="preserve">5.39269304275513</t>
   </si>
   <si>
-    <t xml:space="preserve">5.3652720451355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.2830114364624</t>
+    <t xml:space="preserve">5.36527252197266</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.28301095962524</t>
   </si>
   <si>
     <t xml:space="preserve">5.2281699180603</t>
@@ -3107,7 +3107,7 @@
     <t xml:space="preserve">5.21902990341187</t>
   </si>
   <si>
-    <t xml:space="preserve">5.15504884719849</t>
+    <t xml:space="preserve">5.15504837036133</t>
   </si>
   <si>
     <t xml:space="preserve">5.10020780563354</t>
@@ -3116,7 +3116,7 @@
     <t xml:space="preserve">5.10934782028198</t>
   </si>
   <si>
-    <t xml:space="preserve">5.08192777633667</t>
+    <t xml:space="preserve">5.08192729949951</t>
   </si>
   <si>
     <t xml:space="preserve">5.03622674942017</t>
@@ -3131,10 +3131,10 @@
     <t xml:space="preserve">5.13676834106445</t>
   </si>
   <si>
-    <t xml:space="preserve">5.07278728485107</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.02708625793457</t>
+    <t xml:space="preserve">5.07278776168823</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.02708673477173</t>
   </si>
   <si>
     <t xml:space="preserve">5.0453667640686</t>
@@ -3152,10 +3152,10 @@
     <t xml:space="preserve">5.44753360748291</t>
   </si>
   <si>
-    <t xml:space="preserve">5.16418886184692</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.14590883255005</t>
+    <t xml:space="preserve">5.16418933868408</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.14590835571289</t>
   </si>
   <si>
     <t xml:space="preserve">4.94482469558716</t>
@@ -3164,43 +3164,43 @@
     <t xml:space="preserve">4.93568515777588</t>
   </si>
   <si>
-    <t xml:space="preserve">4.89912462234497</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.88084411621094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.85342359542847</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.82600355148315</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.73460102081299</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.75288200378418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.69804048538208</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.57921886444092</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.71632146835327</t>
+    <t xml:space="preserve">4.89912414550781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.8808445930481</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.85342311859131</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.826003074646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.73460149765015</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.75288152694702</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.69804096221924</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.57921934127808</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.71632099151611</t>
   </si>
   <si>
     <t xml:space="preserve">4.67976045608521</t>
   </si>
   <si>
-    <t xml:space="preserve">4.84428310394287</t>
+    <t xml:space="preserve">4.84428358078003</t>
   </si>
   <si>
     <t xml:space="preserve">4.80772256851196</t>
   </si>
   <si>
-    <t xml:space="preserve">4.57007884979248</t>
+    <t xml:space="preserve">4.57007837295532</t>
   </si>
   <si>
     <t xml:space="preserve">4.72546148300171</t>
@@ -3230,7 +3230,7 @@
     <t xml:space="preserve">4.48781728744507</t>
   </si>
   <si>
-    <t xml:space="preserve">4.53808832168579</t>
+    <t xml:space="preserve">4.53808784484863</t>
   </si>
   <si>
     <t xml:space="preserve">4.46953678131104</t>
@@ -3242,28 +3242,28 @@
     <t xml:space="preserve">4.49695777893066</t>
   </si>
   <si>
-    <t xml:space="preserve">4.40555572509766</t>
+    <t xml:space="preserve">4.40555620193481</t>
   </si>
   <si>
     <t xml:space="preserve">4.43297624588013</t>
   </si>
   <si>
-    <t xml:space="preserve">4.45582675933838</t>
+    <t xml:space="preserve">4.45582723617554</t>
   </si>
   <si>
     <t xml:space="preserve">4.36899518966675</t>
   </si>
   <si>
-    <t xml:space="preserve">4.29130363464355</t>
+    <t xml:space="preserve">4.29130411148071</t>
   </si>
   <si>
     <t xml:space="preserve">4.20447206497192</t>
   </si>
   <si>
-    <t xml:space="preserve">4.47867679595947</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.48324775695801</t>
+    <t xml:space="preserve">4.47867727279663</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.48324728012085</t>
   </si>
   <si>
     <t xml:space="preserve">4.79858255386353</t>
@@ -3272,7 +3272,7 @@
     <t xml:space="preserve">4.87170362472534</t>
   </si>
   <si>
-    <t xml:space="preserve">4.83514308929443</t>
+    <t xml:space="preserve">4.83514356613159</t>
   </si>
   <si>
     <t xml:space="preserve">5.17332887649536</t>
@@ -3281,13 +3281,13 @@
     <t xml:space="preserve">5.32871150970459</t>
   </si>
   <si>
-    <t xml:space="preserve">5.19160938262939</t>
+    <t xml:space="preserve">5.19160890579224</t>
   </si>
   <si>
     <t xml:space="preserve">5.25559043884277</t>
   </si>
   <si>
-    <t xml:space="preserve">5.38355302810669</t>
+    <t xml:space="preserve">5.38355207443237</t>
   </si>
   <si>
     <t xml:space="preserve">4.97224569320679</t>
@@ -3311,7 +3311,7 @@
     <t xml:space="preserve">4.98138570785522</t>
   </si>
   <si>
-    <t xml:space="preserve">4.92654466629028</t>
+    <t xml:space="preserve">4.92654514312744</t>
   </si>
   <si>
     <t xml:space="preserve">5.06364727020264</t>
@@ -3329,13 +3329,13 @@
     <t xml:space="preserve">5.23730993270874</t>
   </si>
   <si>
-    <t xml:space="preserve">5.27387046813965</t>
+    <t xml:space="preserve">5.27387094497681</t>
   </si>
   <si>
     <t xml:space="preserve">5.31957197189331</t>
   </si>
   <si>
-    <t xml:space="preserve">5.27241230010986</t>
+    <t xml:space="preserve">5.27241277694702</t>
   </si>
   <si>
     <t xml:space="preserve">5.23468494415283</t>
@@ -3347,13 +3347,13 @@
     <t xml:space="preserve">5.02718353271484</t>
   </si>
   <si>
-    <t xml:space="preserve">4.99888801574707</t>
+    <t xml:space="preserve">4.99888849258423</t>
   </si>
   <si>
     <t xml:space="preserve">5.01775217056274</t>
   </si>
   <si>
-    <t xml:space="preserve">5.16866159439087</t>
+    <t xml:space="preserve">5.16866207122803</t>
   </si>
   <si>
     <t xml:space="preserve">5.1403660774231</t>
@@ -3383,10 +3383,10 @@
     <t xml:space="preserve">5.26298046112061</t>
   </si>
   <si>
-    <t xml:space="preserve">5.3761625289917</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.17809343338013</t>
+    <t xml:space="preserve">5.37616300582886</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.17809295654297</t>
   </si>
   <si>
     <t xml:space="preserve">5.21582126617432</t>
@@ -3395,7 +3395,7 @@
     <t xml:space="preserve">5.10263824462891</t>
   </si>
   <si>
-    <t xml:space="preserve">5.14979791641235</t>
+    <t xml:space="preserve">5.14979839324951</t>
   </si>
   <si>
     <t xml:space="preserve">5.09320688247681</t>
@@ -3410,7 +3410,7 @@
     <t xml:space="preserve">5.03661584854126</t>
   </si>
   <si>
-    <t xml:space="preserve">5.06491088867188</t>
+    <t xml:space="preserve">5.06491136550903</t>
   </si>
   <si>
     <t xml:space="preserve">4.95172882080078</t>
@@ -3425,7 +3425,7 @@
     <t xml:space="preserve">4.91400146484375</t>
   </si>
   <si>
-    <t xml:space="preserve">4.90456962585449</t>
+    <t xml:space="preserve">4.90456914901733</t>
   </si>
   <si>
     <t xml:space="preserve">4.77252340316772</t>
@@ -3437,16 +3437,16 @@
     <t xml:space="preserve">4.72536420822144</t>
   </si>
   <si>
-    <t xml:space="preserve">4.96116065979004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.85740995407104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.80081939697266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.51786279678345</t>
+    <t xml:space="preserve">4.9611611366272</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.8574104309082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.8008189201355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.51786327362061</t>
   </si>
   <si>
     <t xml:space="preserve">4.50843143463135</t>
@@ -3458,7 +3458,7 @@
     <t xml:space="preserve">4.54615879058838</t>
   </si>
   <si>
-    <t xml:space="preserve">4.62161350250244</t>
+    <t xml:space="preserve">4.6216139793396</t>
   </si>
   <si>
     <t xml:space="preserve">4.54144287109375</t>
@@ -3473,7 +3473,7 @@
     <t xml:space="preserve">4.56030654907227</t>
   </si>
   <si>
-    <t xml:space="preserve">4.47541999816895</t>
+    <t xml:space="preserve">4.47541952133179</t>
   </si>
   <si>
     <t xml:space="preserve">4.47070360183716</t>
@@ -3491,7 +3491,7 @@
     <t xml:space="preserve">4.50371503829956</t>
   </si>
   <si>
-    <t xml:space="preserve">4.51314735412598</t>
+    <t xml:space="preserve">4.51314687728882</t>
   </si>
   <si>
     <t xml:space="preserve">4.63576126098633</t>
@@ -3500,13 +3500,13 @@
     <t xml:space="preserve">4.65934085845947</t>
   </si>
   <si>
-    <t xml:space="preserve">4.62632989883423</t>
+    <t xml:space="preserve">4.62632942199707</t>
   </si>
   <si>
     <t xml:space="preserve">4.64519357681274</t>
   </si>
   <si>
-    <t xml:space="preserve">4.67820501327515</t>
+    <t xml:space="preserve">4.67820453643799</t>
   </si>
   <si>
     <t xml:space="preserve">4.71593236923218</t>
@@ -3524,7 +3524,7 @@
     <t xml:space="preserve">4.73479604721069</t>
   </si>
   <si>
-    <t xml:space="preserve">4.60275030136108</t>
+    <t xml:space="preserve">4.60274982452393</t>
   </si>
   <si>
     <t xml:space="preserve">4.57445430755615</t>
@@ -3539,7 +3539,7 @@
     <t xml:space="preserve">4.34337377548218</t>
   </si>
   <si>
-    <t xml:space="preserve">4.41411209106445</t>
+    <t xml:space="preserve">4.41411256790161</t>
   </si>
   <si>
     <t xml:space="preserve">4.3952488899231</t>
@@ -3581,31 +3581,31 @@
     <t xml:space="preserve">4.27263498306274</t>
   </si>
   <si>
-    <t xml:space="preserve">4.23490715026855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.11229276657104</t>
+    <t xml:space="preserve">4.2349066734314</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.1122932434082</t>
   </si>
   <si>
     <t xml:space="preserve">4.0887131690979</t>
   </si>
   <si>
-    <t xml:space="preserve">4.05570220947266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.10757732391357</t>
+    <t xml:space="preserve">4.0557017326355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.10757684707642</t>
   </si>
   <si>
     <t xml:space="preserve">4.03683805465698</t>
   </si>
   <si>
-    <t xml:space="preserve">3.86234855651855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.00854206085205</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.99911022186279</t>
+    <t xml:space="preserve">3.86234831809998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.00854253768921</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.99910998344421</t>
   </si>
   <si>
     <t xml:space="preserve">4.07456541061401</t>
@@ -3623,7 +3623,7 @@
     <t xml:space="preserve">4.15473651885986</t>
   </si>
   <si>
-    <t xml:space="preserve">4.18303203582764</t>
+    <t xml:space="preserve">4.18303155899048</t>
   </si>
   <si>
     <t xml:space="preserve">4.27735042572021</t>
@@ -3641,7 +3641,7 @@
     <t xml:space="preserve">4.24905490875244</t>
   </si>
   <si>
-    <t xml:space="preserve">4.26791858673096</t>
+    <t xml:space="preserve">4.26791906356812</t>
   </si>
   <si>
     <t xml:space="preserve">4.39053297042847</t>
@@ -3650,7 +3650,7 @@
     <t xml:space="preserve">4.37166976928711</t>
   </si>
   <si>
-    <t xml:space="preserve">4.35752153396606</t>
+    <t xml:space="preserve">4.35752105712891</t>
   </si>
   <si>
     <t xml:space="preserve">4.35280513763428</t>
@@ -3686,19 +3686,19 @@
     <t xml:space="preserve">4.23962306976318</t>
   </si>
   <si>
-    <t xml:space="preserve">4.20189571380615</t>
+    <t xml:space="preserve">4.20189523696899</t>
   </si>
   <si>
     <t xml:space="preserve">4.12644052505493</t>
   </si>
   <si>
-    <t xml:space="preserve">4.02268981933594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.15002059936523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.92837166786194</t>
+    <t xml:space="preserve">4.0226902961731</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.15002012252808</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.92837142944336</t>
   </si>
   <si>
     <t xml:space="preserve">4.04626989364624</t>
@@ -3707,16 +3707,16 @@
     <t xml:space="preserve">3.96138286590576</t>
   </si>
   <si>
-    <t xml:space="preserve">4.06041717529297</t>
+    <t xml:space="preserve">4.06041765213013</t>
   </si>
   <si>
     <t xml:space="preserve">4.01797485351562</t>
   </si>
   <si>
-    <t xml:space="preserve">3.90007638931274</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.94251894950867</t>
+    <t xml:space="preserve">3.90007615089417</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.94251942634583</t>
   </si>
   <si>
     <t xml:space="preserve">3.89535999298096</t>
@@ -3734,7 +3734,7 @@
     <t xml:space="preserve">3.88121199607849</t>
   </si>
   <si>
-    <t xml:space="preserve">3.84348464012146</t>
+    <t xml:space="preserve">3.84348440170288</t>
   </si>
   <si>
     <t xml:space="preserve">3.81990528106689</t>
@@ -3752,10 +3752,10 @@
     <t xml:space="preserve">3.75388216972351</t>
   </si>
   <si>
-    <t xml:space="preserve">3.72558641433716</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.76331377029419</t>
+    <t xml:space="preserve">3.72558665275574</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.76331400871277</t>
   </si>
   <si>
     <t xml:space="preserve">3.735018491745</t>
@@ -3764,7 +3764,7 @@
     <t xml:space="preserve">3.71615481376648</t>
   </si>
   <si>
-    <t xml:space="preserve">3.58410859107971</t>
+    <t xml:space="preserve">3.58410835266113</t>
   </si>
   <si>
     <t xml:space="preserve">3.76442790031433</t>
@@ -4464,6 +4464,9 @@
   </si>
   <si>
     <t xml:space="preserve">7.30999994277954</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.32999992370605</t>
   </si>
 </sst>
 </file>
@@ -7940,7 +7943,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G121" t="s">
-        <v>114</v>
+        <v>96</v>
       </c>
       <c r="H121" t="s">
         <v>9</v>
@@ -7966,7 +7969,7 @@
         <v>3.10999989509583</v>
       </c>
       <c r="G122" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="H122" t="s">
         <v>9</v>
@@ -7992,7 +7995,7 @@
         <v>3.08599996566772</v>
       </c>
       <c r="G123" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="H123" t="s">
         <v>9</v>
@@ -8018,7 +8021,7 @@
         <v>2.96000003814697</v>
       </c>
       <c r="G124" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="H124" t="s">
         <v>9</v>
@@ -8044,7 +8047,7 @@
         <v>2.70000004768372</v>
       </c>
       <c r="G125" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="H125" t="s">
         <v>9</v>
@@ -8070,7 +8073,7 @@
         <v>2.75</v>
       </c>
       <c r="G126" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="H126" t="s">
         <v>9</v>
@@ -8096,7 +8099,7 @@
         <v>2.82399988174438</v>
       </c>
       <c r="G127" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="H127" t="s">
         <v>9</v>
@@ -8122,7 +8125,7 @@
         <v>2.79800009727478</v>
       </c>
       <c r="G128" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="H128" t="s">
         <v>9</v>
@@ -8148,7 +8151,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G129" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="H129" t="s">
         <v>9</v>
@@ -8174,7 +8177,7 @@
         <v>2.92000007629395</v>
       </c>
       <c r="G130" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="H130" t="s">
         <v>9</v>
@@ -8200,7 +8203,7 @@
         <v>2.8199999332428</v>
       </c>
       <c r="G131" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="H131" t="s">
         <v>9</v>
@@ -8226,7 +8229,7 @@
         <v>2.69799995422363</v>
       </c>
       <c r="G132" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="H132" t="s">
         <v>9</v>
@@ -8252,7 +8255,7 @@
         <v>2.73799991607666</v>
       </c>
       <c r="G133" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="H133" t="s">
         <v>9</v>
@@ -8278,7 +8281,7 @@
         <v>2.80999994277954</v>
       </c>
       <c r="G134" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="H134" t="s">
         <v>9</v>
@@ -8304,7 +8307,7 @@
         <v>2.83599996566772</v>
       </c>
       <c r="G135" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="H135" t="s">
         <v>9</v>
@@ -8330,7 +8333,7 @@
         <v>2.86800003051758</v>
       </c>
       <c r="G136" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="H136" t="s">
         <v>9</v>
@@ -8356,7 +8359,7 @@
         <v>2.87400007247925</v>
       </c>
       <c r="G137" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="H137" t="s">
         <v>9</v>
@@ -8382,7 +8385,7 @@
         <v>2.86999988555908</v>
       </c>
       <c r="G138" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="H138" t="s">
         <v>9</v>
@@ -8408,7 +8411,7 @@
         <v>2.85400009155273</v>
       </c>
       <c r="G139" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="H139" t="s">
         <v>9</v>
@@ -8434,7 +8437,7 @@
         <v>2.85400009155273</v>
       </c>
       <c r="G140" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="H140" t="s">
         <v>9</v>
@@ -8460,7 +8463,7 @@
         <v>2.9300000667572</v>
       </c>
       <c r="G141" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="H141" t="s">
         <v>9</v>
@@ -8486,7 +8489,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G142" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="H142" t="s">
         <v>9</v>
@@ -8512,7 +8515,7 @@
         <v>3.13000011444092</v>
       </c>
       <c r="G143" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="H143" t="s">
         <v>9</v>
@@ -8538,7 +8541,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G144" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="H144" t="s">
         <v>9</v>
@@ -8590,7 +8593,7 @@
         <v>3.56399989128113</v>
       </c>
       <c r="G146" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="H146" t="s">
         <v>9</v>
@@ -8616,7 +8619,7 @@
         <v>3.49200010299683</v>
       </c>
       <c r="G147" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="H147" t="s">
         <v>9</v>
@@ -8668,7 +8671,7 @@
         <v>3.46000003814697</v>
       </c>
       <c r="G149" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="H149" t="s">
         <v>9</v>
@@ -8694,7 +8697,7 @@
         <v>3.19400000572205</v>
       </c>
       <c r="G150" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="H150" t="s">
         <v>9</v>
@@ -8720,7 +8723,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G151" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="H151" t="s">
         <v>9</v>
@@ -8824,7 +8827,7 @@
         <v>3.17000007629395</v>
       </c>
       <c r="G155" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="H155" t="s">
         <v>9</v>
@@ -8850,7 +8853,7 @@
         <v>3.17000007629395</v>
       </c>
       <c r="G156" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="H156" t="s">
         <v>9</v>
@@ -8876,7 +8879,7 @@
         <v>3.16599988937378</v>
       </c>
       <c r="G157" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="H157" t="s">
         <v>9</v>
@@ -8902,7 +8905,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G158" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="H158" t="s">
         <v>9</v>
@@ -8928,7 +8931,7 @@
         <v>3.15799999237061</v>
       </c>
       <c r="G159" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="H159" t="s">
         <v>9</v>
@@ -8954,7 +8957,7 @@
         <v>3.1159999370575</v>
       </c>
       <c r="G160" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="H160" t="s">
         <v>9</v>
@@ -8980,7 +8983,7 @@
         <v>3.10999989509583</v>
       </c>
       <c r="G161" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="H161" t="s">
         <v>9</v>
@@ -9006,7 +9009,7 @@
         <v>3.12199997901917</v>
       </c>
       <c r="G162" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="H162" t="s">
         <v>9</v>
@@ -9032,7 +9035,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G163" t="s">
-        <v>114</v>
+        <v>96</v>
       </c>
       <c r="H163" t="s">
         <v>9</v>
@@ -9058,7 +9061,7 @@
         <v>3.10999989509583</v>
       </c>
       <c r="G164" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="H164" t="s">
         <v>9</v>
@@ -9084,7 +9087,7 @@
         <v>3.10999989509583</v>
       </c>
       <c r="G165" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="H165" t="s">
         <v>9</v>
@@ -9110,7 +9113,7 @@
         <v>3.24399995803833</v>
       </c>
       <c r="G166" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="H166" t="s">
         <v>9</v>
@@ -9136,7 +9139,7 @@
         <v>3.23600006103516</v>
       </c>
       <c r="G167" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="H167" t="s">
         <v>9</v>
@@ -9162,7 +9165,7 @@
         <v>3.24399995803833</v>
       </c>
       <c r="G168" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="H168" t="s">
         <v>9</v>
@@ -9188,7 +9191,7 @@
         <v>3.25600004196167</v>
       </c>
       <c r="G169" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="H169" t="s">
         <v>9</v>
@@ -9214,7 +9217,7 @@
         <v>3.26399993896484</v>
       </c>
       <c r="G170" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="H170" t="s">
         <v>9</v>
@@ -9240,7 +9243,7 @@
         <v>3.24600005149841</v>
       </c>
       <c r="G171" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="H171" t="s">
         <v>9</v>
@@ -9266,7 +9269,7 @@
         <v>3.25</v>
       </c>
       <c r="G172" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="H172" t="s">
         <v>9</v>
@@ -9292,7 +9295,7 @@
         <v>3.31200003623962</v>
       </c>
       <c r="G173" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="H173" t="s">
         <v>9</v>
@@ -9318,7 +9321,7 @@
         <v>3.39199995994568</v>
       </c>
       <c r="G174" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="H174" t="s">
         <v>9</v>
@@ -9344,7 +9347,7 @@
         <v>3.43600010871887</v>
       </c>
       <c r="G175" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="H175" t="s">
         <v>9</v>
@@ -9370,7 +9373,7 @@
         <v>3.43600010871887</v>
       </c>
       <c r="G176" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="H176" t="s">
         <v>9</v>
@@ -9422,7 +9425,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G178" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="H178" t="s">
         <v>9</v>
@@ -9448,7 +9451,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G179" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="H179" t="s">
         <v>9</v>
@@ -9474,7 +9477,7 @@
         <v>3.26600003242493</v>
       </c>
       <c r="G180" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="H180" t="s">
         <v>9</v>
@@ -9500,7 +9503,7 @@
         <v>3.26999998092651</v>
       </c>
       <c r="G181" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="H181" t="s">
         <v>9</v>
@@ -9526,7 +9529,7 @@
         <v>3.37400007247925</v>
       </c>
       <c r="G182" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="H182" t="s">
         <v>9</v>
@@ -9552,7 +9555,7 @@
         <v>3.40599989891052</v>
       </c>
       <c r="G183" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="H183" t="s">
         <v>9</v>
@@ -9578,7 +9581,7 @@
         <v>3.32999992370605</v>
       </c>
       <c r="G184" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="H184" t="s">
         <v>9</v>
@@ -9604,7 +9607,7 @@
         <v>3.35599994659424</v>
       </c>
       <c r="G185" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="H185" t="s">
         <v>9</v>
@@ -9630,7 +9633,7 @@
         <v>3.37199997901917</v>
       </c>
       <c r="G186" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="H186" t="s">
         <v>9</v>
@@ -9656,7 +9659,7 @@
         <v>3.40799999237061</v>
       </c>
       <c r="G187" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="H187" t="s">
         <v>9</v>
@@ -9682,7 +9685,7 @@
         <v>3.44600009918213</v>
       </c>
       <c r="G188" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="H188" t="s">
         <v>9</v>
@@ -9708,7 +9711,7 @@
         <v>3.32999992370605</v>
       </c>
       <c r="G189" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="H189" t="s">
         <v>9</v>
@@ -9734,7 +9737,7 @@
         <v>3.31599998474121</v>
       </c>
       <c r="G190" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="H190" t="s">
         <v>9</v>
@@ -9760,7 +9763,7 @@
         <v>3.28200006484985</v>
       </c>
       <c r="G191" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="H191" t="s">
         <v>9</v>
@@ -9786,7 +9789,7 @@
         <v>3.25799989700317</v>
       </c>
       <c r="G192" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="H192" t="s">
         <v>9</v>
@@ -9812,7 +9815,7 @@
         <v>3.23000001907349</v>
       </c>
       <c r="G193" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="H193" t="s">
         <v>9</v>
@@ -9838,7 +9841,7 @@
         <v>3.19600009918213</v>
       </c>
       <c r="G194" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="H194" t="s">
         <v>9</v>
@@ -9890,7 +9893,7 @@
         <v>3.22000002861023</v>
       </c>
       <c r="G196" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="H196" t="s">
         <v>9</v>
@@ -9968,7 +9971,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G199" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="H199" t="s">
         <v>9</v>
@@ -9994,7 +9997,7 @@
         <v>3.24000000953674</v>
       </c>
       <c r="G200" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="H200" t="s">
         <v>9</v>
@@ -10020,7 +10023,7 @@
         <v>3.30800008773804</v>
       </c>
       <c r="G201" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="H201" t="s">
         <v>9</v>
@@ -10046,7 +10049,7 @@
         <v>3.20199990272522</v>
       </c>
       <c r="G202" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="H202" t="s">
         <v>9</v>
@@ -10072,7 +10075,7 @@
         <v>3.26999998092651</v>
       </c>
       <c r="G203" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="H203" t="s">
         <v>9</v>
@@ -10098,7 +10101,7 @@
         <v>3.29399991035461</v>
       </c>
       <c r="G204" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="H204" t="s">
         <v>9</v>
@@ -10124,7 +10127,7 @@
         <v>3.33400011062622</v>
       </c>
       <c r="G205" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="H205" t="s">
         <v>9</v>
@@ -10150,7 +10153,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G206" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="H206" t="s">
         <v>9</v>
@@ -10176,7 +10179,7 @@
         <v>3.39000010490417</v>
       </c>
       <c r="G207" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="H207" t="s">
         <v>9</v>
@@ -10202,7 +10205,7 @@
         <v>3.35400009155273</v>
       </c>
       <c r="G208" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="H208" t="s">
         <v>9</v>
@@ -10228,7 +10231,7 @@
         <v>3.34999990463257</v>
       </c>
       <c r="G209" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="H209" t="s">
         <v>9</v>
@@ -10254,7 +10257,7 @@
         <v>3.48000001907349</v>
       </c>
       <c r="G210" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="H210" t="s">
         <v>9</v>
@@ -10280,7 +10283,7 @@
         <v>3.37599992752075</v>
       </c>
       <c r="G211" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="H211" t="s">
         <v>9</v>
@@ -10306,7 +10309,7 @@
         <v>3.37400007247925</v>
       </c>
       <c r="G212" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="H212" t="s">
         <v>9</v>
@@ -10332,7 +10335,7 @@
         <v>3.39800000190735</v>
       </c>
       <c r="G213" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="H213" t="s">
         <v>9</v>
@@ -10358,7 +10361,7 @@
         <v>3.36999988555908</v>
       </c>
       <c r="G214" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="H214" t="s">
         <v>9</v>
@@ -10384,7 +10387,7 @@
         <v>3.36999988555908</v>
       </c>
       <c r="G215" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="H215" t="s">
         <v>9</v>
@@ -10410,7 +10413,7 @@
         <v>3.32800006866455</v>
       </c>
       <c r="G216" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="H216" t="s">
         <v>9</v>
@@ -10436,7 +10439,7 @@
         <v>3.30999994277954</v>
       </c>
       <c r="G217" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="H217" t="s">
         <v>9</v>
@@ -10462,7 +10465,7 @@
         <v>3.25</v>
       </c>
       <c r="G218" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="H218" t="s">
         <v>9</v>
@@ -10488,7 +10491,7 @@
         <v>3.10999989509583</v>
       </c>
       <c r="G219" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="H219" t="s">
         <v>9</v>
@@ -10514,7 +10517,7 @@
         <v>3.21399998664856</v>
       </c>
       <c r="G220" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="H220" t="s">
         <v>9</v>
@@ -10540,7 +10543,7 @@
         <v>3.34999990463257</v>
       </c>
       <c r="G221" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="H221" t="s">
         <v>9</v>
@@ -10566,7 +10569,7 @@
         <v>3.36199998855591</v>
       </c>
       <c r="G222" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="H222" t="s">
         <v>9</v>
@@ -10618,7 +10621,7 @@
         <v>3.34999990463257</v>
       </c>
       <c r="G224" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="H224" t="s">
         <v>9</v>
@@ -10644,7 +10647,7 @@
         <v>3.29200005531311</v>
       </c>
       <c r="G225" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="H225" t="s">
         <v>9</v>
@@ -10670,7 +10673,7 @@
         <v>3.2279999256134</v>
       </c>
       <c r="G226" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="H226" t="s">
         <v>9</v>
@@ -10696,7 +10699,7 @@
         <v>3.23000001907349</v>
       </c>
       <c r="G227" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="H227" t="s">
         <v>9</v>
@@ -10722,7 +10725,7 @@
         <v>3.19199991226196</v>
       </c>
       <c r="G228" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="H228" t="s">
         <v>9</v>
@@ -10800,7 +10803,7 @@
         <v>3.14199995994568</v>
       </c>
       <c r="G231" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="H231" t="s">
         <v>9</v>
@@ -10826,7 +10829,7 @@
         <v>3.13000011444092</v>
       </c>
       <c r="G232" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="H232" t="s">
         <v>9</v>
@@ -10852,7 +10855,7 @@
         <v>3.13800001144409</v>
       </c>
       <c r="G233" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="H233" t="s">
         <v>9</v>
@@ -10878,7 +10881,7 @@
         <v>3.09200000762939</v>
       </c>
       <c r="G234" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="H234" t="s">
         <v>9</v>
@@ -10904,7 +10907,7 @@
         <v>3.03600001335144</v>
       </c>
       <c r="G235" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="H235" t="s">
         <v>9</v>
@@ -10930,7 +10933,7 @@
         <v>3.03600001335144</v>
       </c>
       <c r="G236" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="H236" t="s">
         <v>9</v>
@@ -10956,7 +10959,7 @@
         <v>2.96000003814697</v>
       </c>
       <c r="G237" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="H237" t="s">
         <v>9</v>
@@ -10982,7 +10985,7 @@
         <v>3.07800006866455</v>
       </c>
       <c r="G238" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="H238" t="s">
         <v>9</v>
@@ -11034,7 +11037,7 @@
         <v>3.23000001907349</v>
       </c>
       <c r="G240" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="H240" t="s">
         <v>9</v>
@@ -11086,7 +11089,7 @@
         <v>3.19199991226196</v>
       </c>
       <c r="G242" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="H242" t="s">
         <v>9</v>
@@ -11112,7 +11115,7 @@
         <v>3.19199991226196</v>
       </c>
       <c r="G243" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="H243" t="s">
         <v>9</v>
@@ -11138,7 +11141,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G244" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="H244" t="s">
         <v>9</v>
@@ -11164,7 +11167,7 @@
         <v>3.23799991607666</v>
       </c>
       <c r="G245" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="H245" t="s">
         <v>9</v>
@@ -11190,7 +11193,7 @@
         <v>3.17000007629395</v>
       </c>
       <c r="G246" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="H246" t="s">
         <v>9</v>
@@ -11216,7 +11219,7 @@
         <v>3.24000000953674</v>
       </c>
       <c r="G247" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="H247" t="s">
         <v>9</v>
@@ -11242,7 +11245,7 @@
         <v>3.24000000953674</v>
       </c>
       <c r="G248" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="H248" t="s">
         <v>9</v>
@@ -11268,7 +11271,7 @@
         <v>3.25</v>
       </c>
       <c r="G249" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="H249" t="s">
         <v>9</v>
@@ -11320,7 +11323,7 @@
         <v>3.24000000953674</v>
       </c>
       <c r="G251" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="H251" t="s">
         <v>9</v>
@@ -11346,7 +11349,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G252" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="H252" t="s">
         <v>9</v>
@@ -11372,7 +11375,7 @@
         <v>3.26799988746643</v>
       </c>
       <c r="G253" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="H253" t="s">
         <v>9</v>
@@ -11398,7 +11401,7 @@
         <v>3.28399991989136</v>
       </c>
       <c r="G254" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="H254" t="s">
         <v>9</v>
@@ -11424,7 +11427,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G255" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="H255" t="s">
         <v>9</v>
@@ -11450,7 +11453,7 @@
         <v>3.30999994277954</v>
       </c>
       <c r="G256" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="H256" t="s">
         <v>9</v>
@@ -11476,7 +11479,7 @@
         <v>3.35199999809265</v>
       </c>
       <c r="G257" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="H257" t="s">
         <v>9</v>
@@ -11502,7 +11505,7 @@
         <v>3.46000003814697</v>
       </c>
       <c r="G258" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="H258" t="s">
         <v>9</v>
@@ -11528,7 +11531,7 @@
         <v>3.46000003814697</v>
       </c>
       <c r="G259" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="H259" t="s">
         <v>9</v>
@@ -11554,7 +11557,7 @@
         <v>3.42400002479553</v>
       </c>
       <c r="G260" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="H260" t="s">
         <v>9</v>
@@ -11580,7 +11583,7 @@
         <v>3.41000008583069</v>
       </c>
       <c r="G261" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="H261" t="s">
         <v>9</v>
@@ -11606,7 +11609,7 @@
         <v>3.41799998283386</v>
       </c>
       <c r="G262" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="H262" t="s">
         <v>9</v>
@@ -11632,7 +11635,7 @@
         <v>3.32200002670288</v>
       </c>
       <c r="G263" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="H263" t="s">
         <v>9</v>
@@ -11658,7 +11661,7 @@
         <v>3.35199999809265</v>
       </c>
       <c r="G264" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="H264" t="s">
         <v>9</v>
@@ -11684,7 +11687,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G265" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="H265" t="s">
         <v>9</v>
@@ -11710,7 +11713,7 @@
         <v>3.36999988555908</v>
       </c>
       <c r="G266" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="H266" t="s">
         <v>9</v>
@@ -11736,7 +11739,7 @@
         <v>3.41199994087219</v>
       </c>
       <c r="G267" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="H267" t="s">
         <v>9</v>
@@ -11762,7 +11765,7 @@
         <v>3.40199995040894</v>
       </c>
       <c r="G268" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="H268" t="s">
         <v>9</v>
@@ -11788,7 +11791,7 @@
         <v>3.40199995040894</v>
       </c>
       <c r="G269" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="H269" t="s">
         <v>9</v>
@@ -11814,7 +11817,7 @@
         <v>3.34400010108948</v>
       </c>
       <c r="G270" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="H270" t="s">
         <v>9</v>
@@ -11866,7 +11869,7 @@
         <v>3.30800008773804</v>
       </c>
       <c r="G272" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="H272" t="s">
         <v>9</v>
@@ -11970,7 +11973,7 @@
         <v>3.26999998092651</v>
       </c>
       <c r="G276" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="H276" t="s">
         <v>9</v>
@@ -11996,7 +11999,7 @@
         <v>3.23600006103516</v>
       </c>
       <c r="G277" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="H277" t="s">
         <v>9</v>
@@ -12022,7 +12025,7 @@
         <v>3.25</v>
       </c>
       <c r="G278" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="H278" t="s">
         <v>9</v>
@@ -12048,7 +12051,7 @@
         <v>3.23000001907349</v>
       </c>
       <c r="G279" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="H279" t="s">
         <v>9</v>
@@ -12074,7 +12077,7 @@
         <v>3.25799989700317</v>
       </c>
       <c r="G280" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="H280" t="s">
         <v>9</v>
@@ -12152,7 +12155,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G283" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="H283" t="s">
         <v>9</v>
@@ -12178,7 +12181,7 @@
         <v>3.36999988555908</v>
       </c>
       <c r="G284" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="H284" t="s">
         <v>9</v>
@@ -12204,7 +12207,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G285" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="H285" t="s">
         <v>9</v>
@@ -12230,7 +12233,7 @@
         <v>3.37800002098083</v>
       </c>
       <c r="G286" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="H286" t="s">
         <v>9</v>
@@ -12256,7 +12259,7 @@
         <v>3.37400007247925</v>
       </c>
       <c r="G287" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="H287" t="s">
         <v>9</v>
@@ -12282,7 +12285,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G288" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="H288" t="s">
         <v>9</v>
@@ -12308,7 +12311,7 @@
         <v>3.42000007629395</v>
       </c>
       <c r="G289" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="H289" t="s">
         <v>9</v>
@@ -12334,7 +12337,7 @@
         <v>3.38000011444092</v>
       </c>
       <c r="G290" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="H290" t="s">
         <v>9</v>
@@ -12386,7 +12389,7 @@
         <v>3.30999994277954</v>
       </c>
       <c r="G292" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="H292" t="s">
         <v>9</v>
@@ -12412,7 +12415,7 @@
         <v>3.34999990463257</v>
       </c>
       <c r="G293" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="H293" t="s">
         <v>9</v>
@@ -12438,7 +12441,7 @@
         <v>3.34999990463257</v>
       </c>
       <c r="G294" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="H294" t="s">
         <v>9</v>
@@ -12464,7 +12467,7 @@
         <v>3.26999998092651</v>
       </c>
       <c r="G295" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="H295" t="s">
         <v>9</v>
@@ -12490,7 +12493,7 @@
         <v>3.29399991035461</v>
       </c>
       <c r="G296" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="H296" t="s">
         <v>9</v>
@@ -12542,7 +12545,7 @@
         <v>3.24600005149841</v>
       </c>
       <c r="G298" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="H298" t="s">
         <v>9</v>
@@ -12594,7 +12597,7 @@
         <v>3.2039999961853</v>
       </c>
       <c r="G300" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="H300" t="s">
         <v>9</v>
@@ -12620,7 +12623,7 @@
         <v>3.23200011253357</v>
       </c>
       <c r="G301" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="H301" t="s">
         <v>9</v>
@@ -12646,7 +12649,7 @@
         <v>3.25999999046326</v>
       </c>
       <c r="G302" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="H302" t="s">
         <v>9</v>
@@ -12672,7 +12675,7 @@
         <v>3.28200006484985</v>
       </c>
       <c r="G303" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="H303" t="s">
         <v>9</v>
@@ -12698,7 +12701,7 @@
         <v>3.25</v>
       </c>
       <c r="G304" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="H304" t="s">
         <v>9</v>
@@ -12724,7 +12727,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G305" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="H305" t="s">
         <v>9</v>
@@ -12750,7 +12753,7 @@
         <v>3.31399989128113</v>
       </c>
       <c r="G306" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="H306" t="s">
         <v>9</v>
@@ -12776,7 +12779,7 @@
         <v>3.31599998474121</v>
       </c>
       <c r="G307" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="H307" t="s">
         <v>9</v>
@@ -12802,7 +12805,7 @@
         <v>3.28399991989136</v>
       </c>
       <c r="G308" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="H308" t="s">
         <v>9</v>
@@ -12828,7 +12831,7 @@
         <v>3.29200005531311</v>
       </c>
       <c r="G309" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="H309" t="s">
         <v>9</v>
@@ -12854,7 +12857,7 @@
         <v>3.29399991035461</v>
       </c>
       <c r="G310" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="H310" t="s">
         <v>9</v>
@@ -12880,7 +12883,7 @@
         <v>3.3199999332428</v>
       </c>
       <c r="G311" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="H311" t="s">
         <v>9</v>
@@ -12906,7 +12909,7 @@
         <v>3.35400009155273</v>
       </c>
       <c r="G312" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="H312" t="s">
         <v>9</v>
@@ -12958,7 +12961,7 @@
         <v>3.59599995613098</v>
       </c>
       <c r="G314" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="H314" t="s">
         <v>9</v>
@@ -12984,7 +12987,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G315" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="H315" t="s">
         <v>9</v>
@@ -13010,7 +13013,7 @@
         <v>3.69000005722046</v>
       </c>
       <c r="G316" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="H316" t="s">
         <v>9</v>
@@ -13036,7 +13039,7 @@
         <v>3.66000008583069</v>
       </c>
       <c r="G317" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="H317" t="s">
         <v>9</v>
@@ -13062,7 +13065,7 @@
         <v>3.65400004386902</v>
       </c>
       <c r="G318" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="H318" t="s">
         <v>9</v>
@@ -13088,7 +13091,7 @@
         <v>3.66000008583069</v>
       </c>
       <c r="G319" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="H319" t="s">
         <v>9</v>
@@ -13114,7 +13117,7 @@
         <v>3.64599990844727</v>
       </c>
       <c r="G320" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="H320" t="s">
         <v>9</v>
@@ -13140,7 +13143,7 @@
         <v>3.61999988555908</v>
       </c>
       <c r="G321" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="H321" t="s">
         <v>9</v>
@@ -13166,7 +13169,7 @@
         <v>3.61999988555908</v>
       </c>
       <c r="G322" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="H322" t="s">
         <v>9</v>
@@ -13192,7 +13195,7 @@
         <v>3.60999989509583</v>
       </c>
       <c r="G323" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="H323" t="s">
         <v>9</v>
@@ -13218,7 +13221,7 @@
         <v>3.59599995613098</v>
       </c>
       <c r="G324" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="H324" t="s">
         <v>9</v>
@@ -13244,7 +13247,7 @@
         <v>3.56599998474121</v>
       </c>
       <c r="G325" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="H325" t="s">
         <v>9</v>
@@ -13270,7 +13273,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G326" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="H326" t="s">
         <v>9</v>
@@ -13296,7 +13299,7 @@
         <v>3.55800008773804</v>
       </c>
       <c r="G327" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="H327" t="s">
         <v>9</v>
@@ -13322,7 +13325,7 @@
         <v>3.55800008773804</v>
       </c>
       <c r="G328" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="H328" t="s">
         <v>9</v>
@@ -13348,7 +13351,7 @@
         <v>3.54200005531311</v>
       </c>
       <c r="G329" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="H329" t="s">
         <v>9</v>
@@ -13374,7 +13377,7 @@
         <v>3.53800010681152</v>
       </c>
       <c r="G330" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="H330" t="s">
         <v>9</v>
@@ -13400,7 +13403,7 @@
         <v>3.5</v>
       </c>
       <c r="G331" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="H331" t="s">
         <v>9</v>
@@ -13426,7 +13429,7 @@
         <v>3.47199988365173</v>
       </c>
       <c r="G332" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="H332" t="s">
         <v>9</v>
@@ -13452,7 +13455,7 @@
         <v>3.50600004196167</v>
       </c>
       <c r="G333" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="H333" t="s">
         <v>9</v>
@@ -13478,7 +13481,7 @@
         <v>3.59200000762939</v>
       </c>
       <c r="G334" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="H334" t="s">
         <v>9</v>
@@ -13504,7 +13507,7 @@
         <v>3.59200000762939</v>
       </c>
       <c r="G335" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="H335" t="s">
         <v>9</v>
@@ -13530,7 +13533,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G336" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="H336" t="s">
         <v>9</v>
@@ -13556,7 +13559,7 @@
         <v>3.61999988555908</v>
       </c>
       <c r="G337" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="H337" t="s">
         <v>9</v>
@@ -13582,7 +13585,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G338" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="H338" t="s">
         <v>9</v>
@@ -13608,7 +13611,7 @@
         <v>3.59200000762939</v>
       </c>
       <c r="G339" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="H339" t="s">
         <v>9</v>
@@ -13634,7 +13637,7 @@
         <v>3.58599996566772</v>
       </c>
       <c r="G340" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="H340" t="s">
         <v>9</v>
@@ -13660,7 +13663,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G341" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="H341" t="s">
         <v>9</v>
@@ -13686,7 +13689,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G342" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="H342" t="s">
         <v>9</v>
@@ -13712,7 +13715,7 @@
         <v>3.58800005912781</v>
       </c>
       <c r="G343" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="H343" t="s">
         <v>9</v>
@@ -13738,7 +13741,7 @@
         <v>3.61999988555908</v>
       </c>
       <c r="G344" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="H344" t="s">
         <v>9</v>
@@ -13764,7 +13767,7 @@
         <v>3.64000010490417</v>
       </c>
       <c r="G345" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="H345" t="s">
         <v>9</v>
@@ -13790,7 +13793,7 @@
         <v>3.63800001144409</v>
       </c>
       <c r="G346" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="H346" t="s">
         <v>9</v>
@@ -13816,7 +13819,7 @@
         <v>3.63199996948242</v>
       </c>
       <c r="G347" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="H347" t="s">
         <v>9</v>
@@ -13842,7 +13845,7 @@
         <v>3.61999988555908</v>
       </c>
       <c r="G348" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="H348" t="s">
         <v>9</v>
@@ -13868,7 +13871,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G349" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="H349" t="s">
         <v>9</v>
@@ -13894,7 +13897,7 @@
         <v>3.75200009346008</v>
       </c>
       <c r="G350" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="H350" t="s">
         <v>9</v>
@@ -13920,7 +13923,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G351" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="H351" t="s">
         <v>9</v>
@@ -13946,7 +13949,7 @@
         <v>3.68600010871887</v>
       </c>
       <c r="G352" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="H352" t="s">
         <v>9</v>
@@ -13972,7 +13975,7 @@
         <v>3.66599988937378</v>
       </c>
       <c r="G353" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="H353" t="s">
         <v>9</v>
@@ -13998,7 +14001,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G354" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="H354" t="s">
         <v>9</v>
@@ -14024,7 +14027,7 @@
         <v>3.74799990653992</v>
       </c>
       <c r="G355" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="H355" t="s">
         <v>9</v>
@@ -14050,7 +14053,7 @@
         <v>3.7720000743866</v>
       </c>
       <c r="G356" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="H356" t="s">
         <v>9</v>
@@ -14076,7 +14079,7 @@
         <v>3.83599996566772</v>
       </c>
       <c r="G357" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="H357" t="s">
         <v>9</v>
@@ -14102,7 +14105,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G358" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="H358" t="s">
         <v>9</v>
@@ -14128,7 +14131,7 @@
         <v>3.80599999427795</v>
       </c>
       <c r="G359" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="H359" t="s">
         <v>9</v>
@@ -14154,7 +14157,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G360" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="H360" t="s">
         <v>9</v>
@@ -14180,7 +14183,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G361" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="H361" t="s">
         <v>9</v>
@@ -14206,7 +14209,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G362" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="H362" t="s">
         <v>9</v>
@@ -14232,7 +14235,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G363" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="H363" t="s">
         <v>9</v>
@@ -14258,7 +14261,7 @@
         <v>3.84999990463257</v>
       </c>
       <c r="G364" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="H364" t="s">
         <v>9</v>
@@ -14284,7 +14287,7 @@
         <v>3.93199992179871</v>
       </c>
       <c r="G365" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="H365" t="s">
         <v>9</v>
@@ -14310,7 +14313,7 @@
         <v>3.89400005340576</v>
       </c>
       <c r="G366" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="H366" t="s">
         <v>9</v>
@@ -14336,7 +14339,7 @@
         <v>3.83400011062622</v>
       </c>
       <c r="G367" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="H367" t="s">
         <v>9</v>
@@ -14362,7 +14365,7 @@
         <v>3.83400011062622</v>
       </c>
       <c r="G368" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="H368" t="s">
         <v>9</v>
@@ -14388,7 +14391,7 @@
         <v>3.81800007820129</v>
       </c>
       <c r="G369" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="H369" t="s">
         <v>9</v>
@@ -14414,7 +14417,7 @@
         <v>3.83800005912781</v>
       </c>
       <c r="G370" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="H370" t="s">
         <v>9</v>
@@ -14440,7 +14443,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G371" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="H371" t="s">
         <v>9</v>
@@ -14466,7 +14469,7 @@
         <v>3.72399997711182</v>
       </c>
       <c r="G372" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="H372" t="s">
         <v>9</v>
@@ -14492,7 +14495,7 @@
         <v>3.72199988365173</v>
       </c>
       <c r="G373" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="H373" t="s">
         <v>9</v>
@@ -14518,7 +14521,7 @@
         <v>3.60999989509583</v>
       </c>
       <c r="G374" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="H374" t="s">
         <v>9</v>
@@ -14544,7 +14547,7 @@
         <v>3.70199990272522</v>
       </c>
       <c r="G375" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="H375" t="s">
         <v>9</v>
@@ -14570,7 +14573,7 @@
         <v>3.71000003814697</v>
       </c>
       <c r="G376" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="H376" t="s">
         <v>9</v>
@@ -14596,7 +14599,7 @@
         <v>3.67199993133545</v>
       </c>
       <c r="G377" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="H377" t="s">
         <v>9</v>
@@ -14622,7 +14625,7 @@
         <v>3.66199994087219</v>
       </c>
       <c r="G378" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="H378" t="s">
         <v>9</v>
@@ -14648,7 +14651,7 @@
         <v>3.62400007247925</v>
       </c>
       <c r="G379" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="H379" t="s">
         <v>9</v>
@@ -14674,7 +14677,7 @@
         <v>3.66199994087219</v>
       </c>
       <c r="G380" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="H380" t="s">
         <v>9</v>
@@ -14700,7 +14703,7 @@
         <v>3.61999988555908</v>
       </c>
       <c r="G381" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="H381" t="s">
         <v>9</v>
@@ -14726,7 +14729,7 @@
         <v>3.63000011444092</v>
       </c>
       <c r="G382" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="H382" t="s">
         <v>9</v>
@@ -14752,7 +14755,7 @@
         <v>3.55599999427795</v>
       </c>
       <c r="G383" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="H383" t="s">
         <v>9</v>
@@ -14778,7 +14781,7 @@
         <v>3.57800006866455</v>
       </c>
       <c r="G384" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="H384" t="s">
         <v>9</v>
@@ -14804,7 +14807,7 @@
         <v>3.7279999256134</v>
       </c>
       <c r="G385" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="H385" t="s">
         <v>9</v>
@@ -14830,7 +14833,7 @@
         <v>3.73799991607666</v>
       </c>
       <c r="G386" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="H386" t="s">
         <v>9</v>
@@ -14856,7 +14859,7 @@
         <v>3.73600006103516</v>
       </c>
       <c r="G387" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="H387" t="s">
         <v>9</v>
@@ -14882,7 +14885,7 @@
         <v>3.76200008392334</v>
       </c>
       <c r="G388" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="H388" t="s">
         <v>9</v>
@@ -14908,7 +14911,7 @@
         <v>3.76600003242493</v>
       </c>
       <c r="G389" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="H389" t="s">
         <v>9</v>
@@ -14934,7 +14937,7 @@
         <v>3.80999994277954</v>
       </c>
       <c r="G390" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="H390" t="s">
         <v>9</v>
@@ -14960,7 +14963,7 @@
         <v>3.82999992370605</v>
       </c>
       <c r="G391" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="H391" t="s">
         <v>9</v>
@@ -14986,7 +14989,7 @@
         <v>3.88000011444092</v>
       </c>
       <c r="G392" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="H392" t="s">
         <v>9</v>
@@ -15012,7 +15015,7 @@
         <v>3.89000010490417</v>
       </c>
       <c r="G393" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="H393" t="s">
         <v>9</v>
@@ -15038,7 +15041,7 @@
         <v>3.91000008583069</v>
       </c>
       <c r="G394" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="H394" t="s">
         <v>9</v>
@@ -15064,7 +15067,7 @@
         <v>3.91400003433228</v>
       </c>
       <c r="G395" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="H395" t="s">
         <v>9</v>
@@ -15090,7 +15093,7 @@
         <v>3.93799996376038</v>
       </c>
       <c r="G396" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="H396" t="s">
         <v>9</v>
@@ -15116,7 +15119,7 @@
         <v>3.98799991607666</v>
       </c>
       <c r="G397" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="H397" t="s">
         <v>9</v>
@@ -15142,7 +15145,7 @@
         <v>4.00400018692017</v>
       </c>
       <c r="G398" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="H398" t="s">
         <v>9</v>
@@ -15168,7 +15171,7 @@
         <v>3.96000003814697</v>
       </c>
       <c r="G399" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="H399" t="s">
         <v>9</v>
@@ -15194,7 +15197,7 @@
         <v>3.99000000953674</v>
       </c>
       <c r="G400" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="H400" t="s">
         <v>9</v>
@@ -15220,7 +15223,7 @@
         <v>3.90199995040894</v>
       </c>
       <c r="G401" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="H401" t="s">
         <v>9</v>
@@ -15246,7 +15249,7 @@
         <v>3.93400001525879</v>
       </c>
       <c r="G402" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="H402" t="s">
         <v>9</v>
@@ -15272,7 +15275,7 @@
         <v>3.8659999370575</v>
       </c>
       <c r="G403" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="H403" t="s">
         <v>9</v>
@@ -15298,7 +15301,7 @@
         <v>3.84999990463257</v>
       </c>
       <c r="G404" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="H404" t="s">
         <v>9</v>
@@ -15324,7 +15327,7 @@
         <v>3.95000004768372</v>
       </c>
       <c r="G405" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="H405" t="s">
         <v>9</v>
@@ -15350,7 +15353,7 @@
         <v>3.75</v>
       </c>
       <c r="G406" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="H406" t="s">
         <v>9</v>
@@ -15376,7 +15379,7 @@
         <v>3.82399988174438</v>
       </c>
       <c r="G407" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="H407" t="s">
         <v>9</v>
@@ -15402,7 +15405,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G408" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="H408" t="s">
         <v>9</v>
@@ -15428,7 +15431,7 @@
         <v>3.84200000762939</v>
       </c>
       <c r="G409" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="H409" t="s">
         <v>9</v>
@@ -15454,7 +15457,7 @@
         <v>3.81399989128113</v>
       </c>
       <c r="G410" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="H410" t="s">
         <v>9</v>
@@ -15480,7 +15483,7 @@
         <v>3.75</v>
       </c>
       <c r="G411" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="H411" t="s">
         <v>9</v>
@@ -15506,7 +15509,7 @@
         <v>3.75</v>
       </c>
       <c r="G412" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="H412" t="s">
         <v>9</v>
@@ -15532,7 +15535,7 @@
         <v>3.69400000572205</v>
       </c>
       <c r="G413" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="H413" t="s">
         <v>9</v>
@@ -15558,7 +15561,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G414" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="H414" t="s">
         <v>9</v>
@@ -15584,7 +15587,7 @@
         <v>3.73399996757507</v>
       </c>
       <c r="G415" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="H415" t="s">
         <v>9</v>
@@ -15610,7 +15613,7 @@
         <v>3.84999990463257</v>
       </c>
       <c r="G416" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="H416" t="s">
         <v>9</v>
@@ -15636,7 +15639,7 @@
         <v>3.78600001335144</v>
       </c>
       <c r="G417" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="H417" t="s">
         <v>9</v>
@@ -15662,7 +15665,7 @@
         <v>3.7720000743866</v>
       </c>
       <c r="G418" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="H418" t="s">
         <v>9</v>
@@ -15688,7 +15691,7 @@
         <v>3.76600003242493</v>
       </c>
       <c r="G419" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="H419" t="s">
         <v>9</v>
@@ -15714,7 +15717,7 @@
         <v>3.71000003814697</v>
       </c>
       <c r="G420" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="H420" t="s">
         <v>9</v>
@@ -15740,7 +15743,7 @@
         <v>3.67000007629395</v>
       </c>
       <c r="G421" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="H421" t="s">
         <v>9</v>
@@ -15766,7 +15769,7 @@
         <v>3.69400000572205</v>
       </c>
       <c r="G422" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="H422" t="s">
         <v>9</v>
@@ -15792,7 +15795,7 @@
         <v>3.74600005149841</v>
       </c>
       <c r="G423" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="H423" t="s">
         <v>9</v>
@@ -15818,7 +15821,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G424" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="H424" t="s">
         <v>9</v>
@@ -15844,7 +15847,7 @@
         <v>3.74200010299683</v>
       </c>
       <c r="G425" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="H425" t="s">
         <v>9</v>
@@ -15870,7 +15873,7 @@
         <v>3.7279999256134</v>
       </c>
       <c r="G426" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="H426" t="s">
         <v>9</v>
@@ -15896,7 +15899,7 @@
         <v>3.75</v>
       </c>
       <c r="G427" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="H427" t="s">
         <v>9</v>
@@ -15922,7 +15925,7 @@
         <v>3.78999996185303</v>
       </c>
       <c r="G428" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="H428" t="s">
         <v>9</v>
@@ -15948,7 +15951,7 @@
         <v>3.76399993896484</v>
       </c>
       <c r="G429" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="H429" t="s">
         <v>9</v>
@@ -15974,7 +15977,7 @@
         <v>3.75799989700317</v>
       </c>
       <c r="G430" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="H430" t="s">
         <v>9</v>
@@ -16000,7 +16003,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G431" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="H431" t="s">
         <v>9</v>
@@ -16026,7 +16029,7 @@
         <v>3.77800011634827</v>
       </c>
       <c r="G432" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="H432" t="s">
         <v>9</v>
@@ -16052,7 +16055,7 @@
         <v>3.7960000038147</v>
       </c>
       <c r="G433" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="H433" t="s">
         <v>9</v>
@@ -16078,7 +16081,7 @@
         <v>3.80800008773804</v>
       </c>
       <c r="G434" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="H434" t="s">
         <v>9</v>
@@ -16104,7 +16107,7 @@
         <v>3.78800010681152</v>
       </c>
       <c r="G435" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="H435" t="s">
         <v>9</v>
@@ -16130,7 +16133,7 @@
         <v>3.80999994277954</v>
       </c>
       <c r="G436" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="H436" t="s">
         <v>9</v>
@@ -16156,7 +16159,7 @@
         <v>3.80200004577637</v>
       </c>
       <c r="G437" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="H437" t="s">
         <v>9</v>
@@ -16182,7 +16185,7 @@
         <v>3.82200002670288</v>
       </c>
       <c r="G438" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="H438" t="s">
         <v>9</v>
@@ -16208,7 +16211,7 @@
         <v>3.84999990463257</v>
       </c>
       <c r="G439" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="H439" t="s">
         <v>9</v>
@@ -16234,7 +16237,7 @@
         <v>3.89000010490417</v>
       </c>
       <c r="G440" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="H440" t="s">
         <v>9</v>
@@ -16260,7 +16263,7 @@
         <v>3.83800005912781</v>
       </c>
       <c r="G441" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="H441" t="s">
         <v>9</v>
@@ -16286,7 +16289,7 @@
         <v>3.81800007820129</v>
       </c>
       <c r="G442" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="H442" t="s">
         <v>9</v>
@@ -16312,7 +16315,7 @@
         <v>3.85400009155273</v>
       </c>
       <c r="G443" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="H443" t="s">
         <v>9</v>
@@ -16338,7 +16341,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G444" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="H444" t="s">
         <v>9</v>
@@ -16364,7 +16367,7 @@
         <v>3.73000001907349</v>
       </c>
       <c r="G445" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="H445" t="s">
         <v>9</v>
@@ -16390,7 +16393,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G446" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="H446" t="s">
         <v>9</v>
@@ -16416,7 +16419,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G447" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="H447" t="s">
         <v>9</v>
@@ -16442,7 +16445,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G448" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="H448" t="s">
         <v>9</v>
@@ -16468,7 +16471,7 @@
         <v>3.82999992370605</v>
       </c>
       <c r="G449" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="H449" t="s">
         <v>9</v>
@@ -16494,7 +16497,7 @@
         <v>3.75399994850159</v>
       </c>
       <c r="G450" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="H450" t="s">
         <v>9</v>
@@ -16520,7 +16523,7 @@
         <v>3.75600004196167</v>
       </c>
       <c r="G451" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="H451" t="s">
         <v>9</v>
@@ -16546,7 +16549,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G452" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="H452" t="s">
         <v>9</v>
@@ -16572,7 +16575,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G453" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="H453" t="s">
         <v>9</v>
@@ -16598,7 +16601,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G454" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="H454" t="s">
         <v>9</v>
@@ -16624,7 +16627,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G455" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="H455" t="s">
         <v>9</v>
@@ -16650,7 +16653,7 @@
         <v>3.73399996757507</v>
       </c>
       <c r="G456" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="H456" t="s">
         <v>9</v>
@@ -16676,7 +16679,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G457" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="H457" t="s">
         <v>9</v>
@@ -16702,7 +16705,7 @@
         <v>3.77800011634827</v>
       </c>
       <c r="G458" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="H458" t="s">
         <v>9</v>
@@ -16728,7 +16731,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G459" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="H459" t="s">
         <v>9</v>
@@ -16754,7 +16757,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G460" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="H460" t="s">
         <v>9</v>
@@ -16780,7 +16783,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G461" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="H461" t="s">
         <v>9</v>
@@ -16806,7 +16809,7 @@
         <v>3.75</v>
       </c>
       <c r="G462" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="H462" t="s">
         <v>9</v>
@@ -16832,7 +16835,7 @@
         <v>3.75</v>
       </c>
       <c r="G463" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="H463" t="s">
         <v>9</v>
@@ -16858,7 +16861,7 @@
         <v>3.67000007629395</v>
       </c>
       <c r="G464" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="H464" t="s">
         <v>9</v>
@@ -16884,7 +16887,7 @@
         <v>3.5699999332428</v>
       </c>
       <c r="G465" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="H465" t="s">
         <v>9</v>
@@ -16910,7 +16913,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G466" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="H466" t="s">
         <v>9</v>
@@ -16936,7 +16939,7 @@
         <v>3.43400001525879</v>
       </c>
       <c r="G467" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="H467" t="s">
         <v>9</v>
@@ -16962,7 +16965,7 @@
         <v>3.48799991607666</v>
       </c>
       <c r="G468" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="H468" t="s">
         <v>9</v>
@@ -16988,7 +16991,7 @@
         <v>3.51999998092651</v>
       </c>
       <c r="G469" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="H469" t="s">
         <v>9</v>
@@ -17014,7 +17017,7 @@
         <v>3.51999998092651</v>
       </c>
       <c r="G470" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="H470" t="s">
         <v>9</v>
@@ -17040,7 +17043,7 @@
         <v>3.5239999294281</v>
       </c>
       <c r="G471" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="H471" t="s">
         <v>9</v>
@@ -17066,7 +17069,7 @@
         <v>3.57800006866455</v>
       </c>
       <c r="G472" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="H472" t="s">
         <v>9</v>
@@ -17092,7 +17095,7 @@
         <v>3.56599998474121</v>
       </c>
       <c r="G473" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="H473" t="s">
         <v>9</v>
@@ -17118,7 +17121,7 @@
         <v>3.55999994277954</v>
       </c>
       <c r="G474" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="H474" t="s">
         <v>9</v>
@@ -17144,7 +17147,7 @@
         <v>3.58999991416931</v>
       </c>
       <c r="G475" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="H475" t="s">
         <v>9</v>
@@ -17170,7 +17173,7 @@
         <v>3.49200010299683</v>
       </c>
       <c r="G476" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="H476" t="s">
         <v>9</v>
@@ -17196,7 +17199,7 @@
         <v>3.43799996376038</v>
       </c>
       <c r="G477" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="H477" t="s">
         <v>9</v>
@@ -17222,7 +17225,7 @@
         <v>3.42400002479553</v>
       </c>
       <c r="G478" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="H478" t="s">
         <v>9</v>
@@ -17248,7 +17251,7 @@
         <v>3.40400004386902</v>
       </c>
       <c r="G479" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="H479" t="s">
         <v>9</v>
@@ -17274,7 +17277,7 @@
         <v>3.48600006103516</v>
       </c>
       <c r="G480" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="H480" t="s">
         <v>9</v>
@@ -17300,7 +17303,7 @@
         <v>3.32999992370605</v>
       </c>
       <c r="G481" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="H481" t="s">
         <v>9</v>
@@ -17326,7 +17329,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G482" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="H482" t="s">
         <v>9</v>
@@ -17352,7 +17355,7 @@
         <v>3.38000011444092</v>
       </c>
       <c r="G483" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="H483" t="s">
         <v>9</v>
@@ -17378,7 +17381,7 @@
         <v>3.40599989891052</v>
       </c>
       <c r="G484" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="H484" t="s">
         <v>9</v>
@@ -17404,7 +17407,7 @@
         <v>3.46000003814697</v>
       </c>
       <c r="G485" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="H485" t="s">
         <v>9</v>
@@ -17430,7 +17433,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G486" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="H486" t="s">
         <v>9</v>
@@ -17456,7 +17459,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G487" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="H487" t="s">
         <v>9</v>
@@ -17482,7 +17485,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G488" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="H488" t="s">
         <v>9</v>
@@ -17508,7 +17511,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G489" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="H489" t="s">
         <v>9</v>
@@ -17534,7 +17537,7 @@
         <v>3.55999994277954</v>
       </c>
       <c r="G490" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="H490" t="s">
         <v>9</v>
@@ -17560,7 +17563,7 @@
         <v>3.59599995613098</v>
       </c>
       <c r="G491" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="H491" t="s">
         <v>9</v>
@@ -17586,7 +17589,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G492" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="H492" t="s">
         <v>9</v>
@@ -17612,7 +17615,7 @@
         <v>3.65000009536743</v>
       </c>
       <c r="G493" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="H493" t="s">
         <v>9</v>
@@ -17638,7 +17641,7 @@
         <v>3.69799995422363</v>
       </c>
       <c r="G494" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="H494" t="s">
         <v>9</v>
@@ -17664,7 +17667,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G495" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="H495" t="s">
         <v>9</v>
@@ -17690,7 +17693,7 @@
         <v>3.65000009536743</v>
       </c>
       <c r="G496" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="H496" t="s">
         <v>9</v>
@@ -17716,7 +17719,7 @@
         <v>3.65000009536743</v>
       </c>
       <c r="G497" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="H497" t="s">
         <v>9</v>
@@ -17742,7 +17745,7 @@
         <v>3.67000007629395</v>
       </c>
       <c r="G498" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="H498" t="s">
         <v>9</v>
@@ -17768,7 +17771,7 @@
         <v>3.71000003814697</v>
       </c>
       <c r="G499" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="H499" t="s">
         <v>9</v>
@@ -17794,7 +17797,7 @@
         <v>3.70199990272522</v>
       </c>
       <c r="G500" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="H500" t="s">
         <v>9</v>
@@ -17820,7 +17823,7 @@
         <v>3.71600008010864</v>
       </c>
       <c r="G501" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="H501" t="s">
         <v>9</v>
@@ -17846,7 +17849,7 @@
         <v>3.70799994468689</v>
       </c>
       <c r="G502" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="H502" t="s">
         <v>9</v>
@@ -17872,7 +17875,7 @@
         <v>3.66000008583069</v>
       </c>
       <c r="G503" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="H503" t="s">
         <v>9</v>
@@ -17898,7 +17901,7 @@
         <v>3.67600011825562</v>
       </c>
       <c r="G504" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="H504" t="s">
         <v>9</v>
@@ -17924,7 +17927,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G505" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="H505" t="s">
         <v>9</v>
@@ -17950,7 +17953,7 @@
         <v>3.65000009536743</v>
       </c>
       <c r="G506" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="H506" t="s">
         <v>9</v>
@@ -17976,7 +17979,7 @@
         <v>3.65000009536743</v>
       </c>
       <c r="G507" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="H507" t="s">
         <v>9</v>
@@ -18002,7 +18005,7 @@
         <v>3.66599988937378</v>
       </c>
       <c r="G508" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="H508" t="s">
         <v>9</v>
@@ -18028,7 +18031,7 @@
         <v>3.69600009918213</v>
       </c>
       <c r="G509" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="H509" t="s">
         <v>9</v>
@@ -18054,7 +18057,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G510" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="H510" t="s">
         <v>9</v>
@@ -18080,7 +18083,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G511" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="H511" t="s">
         <v>9</v>
@@ -18106,7 +18109,7 @@
         <v>3.7260000705719</v>
       </c>
       <c r="G512" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="H512" t="s">
         <v>9</v>
@@ -18132,7 +18135,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G513" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="H513" t="s">
         <v>9</v>
@@ -18158,7 +18161,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G514" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="H514" t="s">
         <v>9</v>
@@ -18184,7 +18187,7 @@
         <v>3.76500010490417</v>
       </c>
       <c r="G515" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="H515" t="s">
         <v>9</v>
@@ -18210,7 +18213,7 @@
         <v>3.71499991416931</v>
       </c>
       <c r="G516" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="H516" t="s">
         <v>9</v>
@@ -18236,7 +18239,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G517" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="H517" t="s">
         <v>9</v>
@@ -18262,7 +18265,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G518" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="H518" t="s">
         <v>9</v>
@@ -18288,7 +18291,7 @@
         <v>3.8199999332428</v>
       </c>
       <c r="G519" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="H519" t="s">
         <v>9</v>
@@ -18314,7 +18317,7 @@
         <v>3.8199999332428</v>
       </c>
       <c r="G520" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="H520" t="s">
         <v>9</v>
@@ -18340,7 +18343,7 @@
         <v>3.91000008583069</v>
       </c>
       <c r="G521" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="H521" t="s">
         <v>9</v>
@@ -18366,7 +18369,7 @@
         <v>3.89499998092651</v>
       </c>
       <c r="G522" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="H522" t="s">
         <v>9</v>
@@ -18392,7 +18395,7 @@
         <v>3.82999992370605</v>
       </c>
       <c r="G523" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="H523" t="s">
         <v>9</v>
@@ -18418,7 +18421,7 @@
         <v>3.84999990463257</v>
       </c>
       <c r="G524" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="H524" t="s">
         <v>9</v>
@@ -18444,7 +18447,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G525" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="H525" t="s">
         <v>9</v>
@@ -18470,7 +18473,7 @@
         <v>3.84500002861023</v>
       </c>
       <c r="G526" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="H526" t="s">
         <v>9</v>
@@ -18496,7 +18499,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G527" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="H527" t="s">
         <v>9</v>
@@ -18522,7 +18525,7 @@
         <v>3.86500000953674</v>
       </c>
       <c r="G528" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="H528" t="s">
         <v>9</v>
@@ -18548,7 +18551,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G529" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="H529" t="s">
         <v>9</v>
@@ -18574,7 +18577,7 @@
         <v>3.94000005722046</v>
       </c>
       <c r="G530" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="H530" t="s">
         <v>9</v>
@@ -18600,7 +18603,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G531" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="H531" t="s">
         <v>9</v>
@@ -18626,7 +18629,7 @@
         <v>3.71000003814697</v>
       </c>
       <c r="G532" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="H532" t="s">
         <v>9</v>
@@ -18652,7 +18655,7 @@
         <v>3.75</v>
       </c>
       <c r="G533" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="H533" t="s">
         <v>9</v>
@@ -18678,7 +18681,7 @@
         <v>3.73000001907349</v>
       </c>
       <c r="G534" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="H534" t="s">
         <v>9</v>
@@ -18704,7 +18707,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G535" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="H535" t="s">
         <v>9</v>
@@ -18730,7 +18733,7 @@
         <v>3.65000009536743</v>
       </c>
       <c r="G536" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="H536" t="s">
         <v>9</v>
@@ -18756,7 +18759,7 @@
         <v>3.58500003814697</v>
       </c>
       <c r="G537" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="H537" t="s">
         <v>9</v>
@@ -18782,7 +18785,7 @@
         <v>3.60500001907349</v>
       </c>
       <c r="G538" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="H538" t="s">
         <v>9</v>
@@ -18808,7 +18811,7 @@
         <v>3.58500003814697</v>
       </c>
       <c r="G539" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="H539" t="s">
         <v>9</v>
@@ -18834,7 +18837,7 @@
         <v>3.53999996185303</v>
       </c>
       <c r="G540" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="H540" t="s">
         <v>9</v>
@@ -18860,7 +18863,7 @@
         <v>3.51999998092651</v>
       </c>
       <c r="G541" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="H541" t="s">
         <v>9</v>
@@ -18886,7 +18889,7 @@
         <v>3.48000001907349</v>
       </c>
       <c r="G542" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="H542" t="s">
         <v>9</v>
@@ -18912,7 +18915,7 @@
         <v>3.53999996185303</v>
       </c>
       <c r="G543" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="H543" t="s">
         <v>9</v>
@@ -18938,7 +18941,7 @@
         <v>3.63000011444092</v>
       </c>
       <c r="G544" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="H544" t="s">
         <v>9</v>
@@ -18964,7 +18967,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G545" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="H545" t="s">
         <v>9</v>
@@ -18990,7 +18993,7 @@
         <v>3.79500007629395</v>
       </c>
       <c r="G546" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="H546" t="s">
         <v>9</v>
@@ -19016,7 +19019,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G547" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="H547" t="s">
         <v>9</v>
@@ -19042,7 +19045,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G548" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="H548" t="s">
         <v>9</v>
@@ -19068,7 +19071,7 @@
         <v>3.72499990463257</v>
       </c>
       <c r="G549" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="H549" t="s">
         <v>9</v>
@@ -19094,7 +19097,7 @@
         <v>3.72499990463257</v>
       </c>
       <c r="G550" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="H550" t="s">
         <v>9</v>
@@ -19120,7 +19123,7 @@
         <v>3.6949999332428</v>
       </c>
       <c r="G551" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="H551" t="s">
         <v>9</v>
@@ -19146,7 +19149,7 @@
         <v>3.67499995231628</v>
       </c>
       <c r="G552" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="H552" t="s">
         <v>9</v>
@@ -19172,7 +19175,7 @@
         <v>3.63000011444092</v>
       </c>
       <c r="G553" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="H553" t="s">
         <v>9</v>
@@ -19198,7 +19201,7 @@
         <v>3.5699999332428</v>
       </c>
       <c r="G554" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="H554" t="s">
         <v>9</v>
@@ -19224,7 +19227,7 @@
         <v>3.53500008583069</v>
       </c>
       <c r="G555" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="H555" t="s">
         <v>9</v>
@@ -19250,7 +19253,7 @@
         <v>3.53999996185303</v>
       </c>
       <c r="G556" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="H556" t="s">
         <v>9</v>
@@ -19276,7 +19279,7 @@
         <v>3.51999998092651</v>
       </c>
       <c r="G557" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="H557" t="s">
         <v>9</v>
@@ -19302,7 +19305,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G558" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="H558" t="s">
         <v>9</v>
@@ -19328,7 +19331,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G559" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="H559" t="s">
         <v>9</v>
@@ -19354,7 +19357,7 @@
         <v>3.73499989509583</v>
       </c>
       <c r="G560" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="H560" t="s">
         <v>9</v>
@@ -19380,7 +19383,7 @@
         <v>3.73000001907349</v>
       </c>
       <c r="G561" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="H561" t="s">
         <v>9</v>
@@ -19406,7 +19409,7 @@
         <v>3.65499997138977</v>
       </c>
       <c r="G562" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="H562" t="s">
         <v>9</v>
@@ -19432,7 +19435,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G563" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="H563" t="s">
         <v>9</v>
@@ -19458,7 +19461,7 @@
         <v>3.67499995231628</v>
       </c>
       <c r="G564" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="H564" t="s">
         <v>9</v>
@@ -19484,7 +19487,7 @@
         <v>3.65499997138977</v>
       </c>
       <c r="G565" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="H565" t="s">
         <v>9</v>
@@ -19510,7 +19513,7 @@
         <v>3.71499991416931</v>
       </c>
       <c r="G566" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="H566" t="s">
         <v>9</v>
@@ -19536,7 +19539,7 @@
         <v>3.66499996185303</v>
       </c>
       <c r="G567" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="H567" t="s">
         <v>9</v>
@@ -19562,7 +19565,7 @@
         <v>3.69000005722046</v>
       </c>
       <c r="G568" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="H568" t="s">
         <v>9</v>
@@ -19588,7 +19591,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G569" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="H569" t="s">
         <v>9</v>
@@ -19614,7 +19617,7 @@
         <v>3.69000005722046</v>
       </c>
       <c r="G570" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="H570" t="s">
         <v>9</v>
@@ -19640,7 +19643,7 @@
         <v>3.68499994277954</v>
       </c>
       <c r="G571" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="H571" t="s">
         <v>9</v>
@@ -19666,7 +19669,7 @@
         <v>3.65000009536743</v>
       </c>
       <c r="G572" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="H572" t="s">
         <v>9</v>
@@ -19692,7 +19695,7 @@
         <v>3.69000005722046</v>
       </c>
       <c r="G573" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="H573" t="s">
         <v>9</v>
@@ -19718,7 +19721,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G574" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="H574" t="s">
         <v>9</v>
@@ -19744,7 +19747,7 @@
         <v>3.69000005722046</v>
       </c>
       <c r="G575" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="H575" t="s">
         <v>9</v>
@@ -19770,7 +19773,7 @@
         <v>3.67000007629395</v>
       </c>
       <c r="G576" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="H576" t="s">
         <v>9</v>
@@ -19796,7 +19799,7 @@
         <v>3.65499997138977</v>
       </c>
       <c r="G577" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="H577" t="s">
         <v>9</v>
@@ -19822,7 +19825,7 @@
         <v>3.73499989509583</v>
       </c>
       <c r="G578" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="H578" t="s">
         <v>9</v>
@@ -19848,7 +19851,7 @@
         <v>3.80999994277954</v>
       </c>
       <c r="G579" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="H579" t="s">
         <v>9</v>
@@ -19874,7 +19877,7 @@
         <v>3.79500007629395</v>
       </c>
       <c r="G580" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="H580" t="s">
         <v>9</v>
@@ -19900,7 +19903,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G581" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="H581" t="s">
         <v>9</v>
@@ -19926,7 +19929,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G582" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="H582" t="s">
         <v>9</v>
@@ -19952,7 +19955,7 @@
         <v>3.80999994277954</v>
       </c>
       <c r="G583" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="H583" t="s">
         <v>9</v>
@@ -19978,7 +19981,7 @@
         <v>3.81500005722046</v>
       </c>
       <c r="G584" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="H584" t="s">
         <v>9</v>
@@ -20004,7 +20007,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G585" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="H585" t="s">
         <v>9</v>
@@ -20030,7 +20033,7 @@
         <v>3.79500007629395</v>
       </c>
       <c r="G586" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="H586" t="s">
         <v>9</v>
@@ -20056,7 +20059,7 @@
         <v>3.78999996185303</v>
       </c>
       <c r="G587" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="H587" t="s">
         <v>9</v>
@@ -20082,7 +20085,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G588" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="H588" t="s">
         <v>9</v>
@@ -20108,7 +20111,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G589" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="H589" t="s">
         <v>9</v>
@@ -20134,7 +20137,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G590" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="H590" t="s">
         <v>9</v>
@@ -20160,7 +20163,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G591" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="H591" t="s">
         <v>9</v>
@@ -20186,7 +20189,7 @@
         <v>3.88000011444092</v>
       </c>
       <c r="G592" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="H592" t="s">
         <v>9</v>
@@ -20212,7 +20215,7 @@
         <v>3.88000011444092</v>
       </c>
       <c r="G593" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="H593" t="s">
         <v>9</v>
@@ -20238,7 +20241,7 @@
         <v>3.86500000953674</v>
       </c>
       <c r="G594" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="H594" t="s">
         <v>9</v>
@@ -20264,7 +20267,7 @@
         <v>3.81500005722046</v>
       </c>
       <c r="G595" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="H595" t="s">
         <v>9</v>
@@ -20290,7 +20293,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G596" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="H596" t="s">
         <v>9</v>
@@ -20316,7 +20319,7 @@
         <v>3.95000004768372</v>
       </c>
       <c r="G597" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="H597" t="s">
         <v>9</v>
@@ -20342,7 +20345,7 @@
         <v>4.03999996185303</v>
       </c>
       <c r="G598" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="H598" t="s">
         <v>9</v>
@@ -20368,7 +20371,7 @@
         <v>3.99000000953674</v>
       </c>
       <c r="G599" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="H599" t="s">
         <v>9</v>
@@ -20394,7 +20397,7 @@
         <v>3.93499994277954</v>
       </c>
       <c r="G600" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="H600" t="s">
         <v>9</v>
@@ -20420,7 +20423,7 @@
         <v>3.96499991416931</v>
       </c>
       <c r="G601" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="H601" t="s">
         <v>9</v>
@@ -20446,7 +20449,7 @@
         <v>3.96000003814697</v>
       </c>
       <c r="G602" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="H602" t="s">
         <v>9</v>
@@ -20472,7 +20475,7 @@
         <v>3.97499990463257</v>
       </c>
       <c r="G603" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="H603" t="s">
         <v>9</v>
@@ -20498,7 +20501,7 @@
         <v>3.9300000667572</v>
       </c>
       <c r="G604" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="H604" t="s">
         <v>9</v>
@@ -20524,7 +20527,7 @@
         <v>3.85500001907349</v>
       </c>
       <c r="G605" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="H605" t="s">
         <v>9</v>
@@ -20550,7 +20553,7 @@
         <v>3.9300000667572</v>
       </c>
       <c r="G606" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="H606" t="s">
         <v>9</v>
@@ -20576,7 +20579,7 @@
         <v>3.84500002861023</v>
       </c>
       <c r="G607" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="H607" t="s">
         <v>9</v>
@@ -20602,7 +20605,7 @@
         <v>3.86500000953674</v>
       </c>
       <c r="G608" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="H608" t="s">
         <v>9</v>
@@ -20628,7 +20631,7 @@
         <v>3.81500005722046</v>
       </c>
       <c r="G609" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="H609" t="s">
         <v>9</v>
@@ -20654,7 +20657,7 @@
         <v>3.82500004768372</v>
       </c>
       <c r="G610" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="H610" t="s">
         <v>9</v>
@@ -20680,7 +20683,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G611" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="H611" t="s">
         <v>9</v>
@@ -20706,7 +20709,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G612" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="H612" t="s">
         <v>9</v>
@@ -20732,7 +20735,7 @@
         <v>3.76999998092651</v>
       </c>
       <c r="G613" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="H613" t="s">
         <v>9</v>
@@ -20758,7 +20761,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G614" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="H614" t="s">
         <v>9</v>
@@ -20784,7 +20787,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G615" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="H615" t="s">
         <v>9</v>
@@ -20810,7 +20813,7 @@
         <v>3.74499988555908</v>
       </c>
       <c r="G616" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="H616" t="s">
         <v>9</v>
@@ -20836,7 +20839,7 @@
         <v>3.8199999332428</v>
       </c>
       <c r="G617" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="H617" t="s">
         <v>9</v>
@@ -20862,7 +20865,7 @@
         <v>3.88000011444092</v>
       </c>
       <c r="G618" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="H618" t="s">
         <v>9</v>
@@ -20888,7 +20891,7 @@
         <v>3.86999988555908</v>
       </c>
       <c r="G619" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="H619" t="s">
         <v>9</v>
@@ -20914,7 +20917,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G620" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="H620" t="s">
         <v>9</v>
@@ -20940,7 +20943,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G621" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="H621" t="s">
         <v>9</v>
@@ -20966,7 +20969,7 @@
         <v>3.66000008583069</v>
       </c>
       <c r="G622" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="H622" t="s">
         <v>9</v>
@@ -20992,7 +20995,7 @@
         <v>3.79500007629395</v>
       </c>
       <c r="G623" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="H623" t="s">
         <v>9</v>
@@ -21018,7 +21021,7 @@
         <v>3.79500007629395</v>
       </c>
       <c r="G624" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="H624" t="s">
         <v>9</v>
@@ -21044,7 +21047,7 @@
         <v>3.78500008583069</v>
       </c>
       <c r="G625" t="s">
-        <v>353</v>
+        <v>392</v>
       </c>
       <c r="H625" t="s">
         <v>9</v>
@@ -21278,7 +21281,7 @@
         <v>3.76999998092651</v>
       </c>
       <c r="G634" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="H634" t="s">
         <v>9</v>
@@ -21538,7 +21541,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G644" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="H644" t="s">
         <v>9</v>
@@ -21616,7 +21619,7 @@
         <v>3.81500005722046</v>
       </c>
       <c r="G647" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="H647" t="s">
         <v>9</v>
@@ -21668,7 +21671,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G649" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="H649" t="s">
         <v>9</v>
@@ -70010,7 +70013,7 @@
     </row>
     <row r="2509">
       <c r="A2509" s="1" t="n">
-        <v>45972.6910763889</v>
+        <v>45972.3333333333</v>
       </c>
       <c r="B2509" t="n">
         <v>94576</v>
@@ -70031,6 +70034,32 @@
         <v>1483</v>
       </c>
       <c r="H2509" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2510">
+      <c r="A2510" s="1" t="n">
+        <v>45973.6911342593</v>
+      </c>
+      <c r="B2510" t="n">
+        <v>89562</v>
+      </c>
+      <c r="C2510" t="n">
+        <v>7.57999992370605</v>
+      </c>
+      <c r="D2510" t="n">
+        <v>7.21999979019165</v>
+      </c>
+      <c r="E2510" t="n">
+        <v>7.57999992370605</v>
+      </c>
+      <c r="F2510" t="n">
+        <v>7.32999992370605</v>
+      </c>
+      <c r="G2510" t="s">
+        <v>1484</v>
+      </c>
+      <c r="H2510" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/BAN.MI.xlsx
+++ b/data/BAN.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1486" uniqueCount="1486">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1487" uniqueCount="1487">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -44,61 +44,61 @@
     <t xml:space="preserve">BAN.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">3.68330311775208</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.59039282798767</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.46283960342407</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.41874718666077</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.35733270645142</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.44551801681519</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.46441411972046</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.45181655883789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.43134498596191</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.38410329818726</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.40929841995239</t>
+    <t xml:space="preserve">3.68330264091492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.59039306640625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.46283936500549</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.41874694824219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.35733246803284</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.44551753997803</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.4644148349762</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.45181703567505</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.43134474754333</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.38410258293152</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.40929889678955</t>
   </si>
   <si>
     <t xml:space="preserve">3.11639809608459</t>
   </si>
   <si>
-    <t xml:space="preserve">3.240802526474</t>
+    <t xml:space="preserve">3.24080228805542</t>
   </si>
   <si>
     <t xml:space="preserve">3.29119372367859</t>
   </si>
   <si>
-    <t xml:space="preserve">3.21245670318604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.26757287979126</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.19356036186218</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.13372015953064</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.22820448875427</t>
+    <t xml:space="preserve">3.21245622634888</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.26757264137268</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.19356060028076</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.1337206363678</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.22820425033569</t>
   </si>
   <si>
     <t xml:space="preserve">3.16678977012634</t>
@@ -110,16 +110,16 @@
     <t xml:space="preserve">3.0707311630249</t>
   </si>
   <si>
-    <t xml:space="preserve">3.14946722984314</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.05025911331177</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.92900538444519</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.91325783729553</t>
+    <t xml:space="preserve">3.1494677066803</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.05025959014893</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.92900490760803</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.91325712203979</t>
   </si>
   <si>
     <t xml:space="preserve">2.83452081680298</t>
@@ -128,7 +128,7 @@
     <t xml:space="preserve">2.82664728164673</t>
   </si>
   <si>
-    <t xml:space="preserve">2.75263500213623</t>
+    <t xml:space="preserve">2.75263476371765</t>
   </si>
   <si>
     <t xml:space="preserve">2.75420928001404</t>
@@ -137,16 +137,16 @@
     <t xml:space="preserve">2.75578451156616</t>
   </si>
   <si>
-    <t xml:space="preserve">2.89436054229736</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.98254585266113</t>
+    <t xml:space="preserve">2.89436078071594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.98254609107971</t>
   </si>
   <si>
     <t xml:space="preserve">2.96207427978516</t>
   </si>
   <si>
-    <t xml:space="preserve">2.99356913566589</t>
+    <t xml:space="preserve">2.99356889724731</t>
   </si>
   <si>
     <t xml:space="preserve">3.05970788002014</t>
@@ -155,25 +155,25 @@
     <t xml:space="preserve">3.11009955406189</t>
   </si>
   <si>
-    <t xml:space="preserve">3.06915616989136</t>
+    <t xml:space="preserve">3.06915640830994</t>
   </si>
   <si>
     <t xml:space="preserve">2.96364879608154</t>
   </si>
   <si>
-    <t xml:space="preserve">2.99199414253235</t>
+    <t xml:space="preserve">2.99199438095093</t>
   </si>
   <si>
     <t xml:space="preserve">3.00774145126343</t>
   </si>
   <si>
-    <t xml:space="preserve">2.97624683380127</t>
+    <t xml:space="preserve">2.97624659538269</t>
   </si>
   <si>
     <t xml:space="preserve">3.06285762786865</t>
   </si>
   <si>
-    <t xml:space="preserve">3.11797308921814</t>
+    <t xml:space="preserve">3.11797332763672</t>
   </si>
   <si>
     <t xml:space="preserve">3.18096256256104</t>
@@ -188,70 +188,70 @@
     <t xml:space="preserve">3.23292875289917</t>
   </si>
   <si>
-    <t xml:space="preserve">3.33843588829041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.30694055557251</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.24395179748535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.24237704277039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.12584662437439</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.19670987129211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.2030086517334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.10380029678345</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.11324906349182</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.14159393310547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.04710960388184</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.99986815452576</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.96049976348877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.09435224533081</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.96837306022644</t>
+    <t xml:space="preserve">3.33843541145325</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.30694079399109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.24395155906677</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.24237728118896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.12584686279297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.19670939445496</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.20300841331482</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.10380053520203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.11324882507324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.14159417152405</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.04710984230042</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.99986791610718</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.96049952507019</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.09435200691223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.96837329864502</t>
   </si>
   <si>
     <t xml:space="preserve">2.86286568641663</t>
   </si>
   <si>
-    <t xml:space="preserve">2.87388920783997</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.9101083278656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.98569583892822</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.00144267082214</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.01561546325684</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.92743015289307</t>
+    <t xml:space="preserve">2.87388944625854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.91010785102844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.98569536209106</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.00144290924072</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.01561570167542</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.92742991447449</t>
   </si>
   <si>
     <t xml:space="preserve">2.92113137245178</t>
@@ -260,31 +260,31 @@
     <t xml:space="preserve">2.85814189910889</t>
   </si>
   <si>
-    <t xml:space="preserve">2.81404948234558</t>
+    <t xml:space="preserve">2.814049243927</t>
   </si>
   <si>
     <t xml:space="preserve">2.84081983566284</t>
   </si>
   <si>
-    <t xml:space="preserve">2.80145144462585</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.7290141582489</t>
+    <t xml:space="preserve">2.80145168304443</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.72901368141174</t>
   </si>
   <si>
     <t xml:space="preserve">2.65185189247131</t>
   </si>
   <si>
-    <t xml:space="preserve">2.68177127838135</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.71484136581421</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.76365780830383</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.77940487861633</t>
+    <t xml:space="preserve">2.68177199363708</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.71484088897705</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.76365804672241</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.77940535545349</t>
   </si>
   <si>
     <t xml:space="preserve">2.72428965568542</t>
@@ -296,22 +296,22 @@
     <t xml:space="preserve">2.5353217124939</t>
   </si>
   <si>
-    <t xml:space="preserve">2.49437856674194</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.48020601272583</t>
+    <t xml:space="preserve">2.49437832832336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.48020553588867</t>
   </si>
   <si>
     <t xml:space="preserve">2.51957416534424</t>
   </si>
   <si>
-    <t xml:space="preserve">2.60572743415833</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.58784627914429</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.5602126121521</t>
+    <t xml:space="preserve">2.6057276725769</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.58784675598145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.56021213531494</t>
   </si>
   <si>
     <t xml:space="preserve">2.56183791160583</t>
@@ -320,58 +320,58 @@
     <t xml:space="preserve">2.60897850990295</t>
   </si>
   <si>
-    <t xml:space="preserve">2.59272313117981</t>
+    <t xml:space="preserve">2.59272360801697</t>
   </si>
   <si>
     <t xml:space="preserve">2.58134412765503</t>
   </si>
   <si>
-    <t xml:space="preserve">2.60085082054138</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.72113990783691</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.8202977180481</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.80404257774353</t>
+    <t xml:space="preserve">2.60085105895996</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.72114038467407</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.82029795646667</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.80404210090637</t>
   </si>
   <si>
     <t xml:space="preserve">2.68212747573853</t>
   </si>
   <si>
-    <t xml:space="preserve">2.71463799476624</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.44642519950867</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.39765954017639</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.50331878662109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.47568464279175</t>
+    <t xml:space="preserve">2.71463775634766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.44642496109009</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.39765930175781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.50331902503967</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.47568488121033</t>
   </si>
   <si>
     <t xml:space="preserve">2.52770185470581</t>
   </si>
   <si>
-    <t xml:space="preserve">2.50819563865662</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.40578675270081</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.19446778297424</t>
+    <t xml:space="preserve">2.50819540023804</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.40578699111938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.19446802139282</t>
   </si>
   <si>
     <t xml:space="preserve">2.23510599136353</t>
   </si>
   <si>
-    <t xml:space="preserve">2.29525113105774</t>
+    <t xml:space="preserve">2.29525089263916</t>
   </si>
   <si>
     <t xml:space="preserve">2.27411890029907</t>
@@ -380,64 +380,64 @@
     <t xml:space="preserve">2.35702085494995</t>
   </si>
   <si>
-    <t xml:space="preserve">2.37327647209167</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.29199981689453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.19284200668335</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.22535300254822</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.28387236595154</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.30500411987305</t>
+    <t xml:space="preserve">2.37327694892883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.29199934005737</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.19284248352051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.22535276412964</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.28387212753296</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.30500364303589</t>
   </si>
   <si>
     <t xml:space="preserve">2.3310124874115</t>
   </si>
   <si>
-    <t xml:space="preserve">2.33588886260986</t>
+    <t xml:space="preserve">2.33588933944702</t>
   </si>
   <si>
     <t xml:space="preserve">2.33263778686523</t>
   </si>
   <si>
-    <t xml:space="preserve">2.3196337223053</t>
+    <t xml:space="preserve">2.31963396072388</t>
   </si>
   <si>
     <t xml:space="preserve">2.38140392303467</t>
   </si>
   <si>
-    <t xml:space="preserve">2.5358293056488</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.54395699501038</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.56833982467651</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.89669728279114</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.83817863464355</t>
+    <t xml:space="preserve">2.53582906723022</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.54395723342896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.56834030151367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.8966977596283</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.83817839622498</t>
   </si>
   <si>
     <t xml:space="preserve">2.81217002868652</t>
   </si>
   <si>
-    <t xml:space="preserve">2.59597396850586</t>
+    <t xml:space="preserve">2.59597420692444</t>
   </si>
   <si>
     <t xml:space="preserve">2.57646799087524</t>
   </si>
   <si>
-    <t xml:space="preserve">2.57321643829346</t>
+    <t xml:space="preserve">2.57321619987488</t>
   </si>
   <si>
     <t xml:space="preserve">2.56671452522278</t>
@@ -446,7 +446,7 @@
     <t xml:space="preserve">2.53257822990417</t>
   </si>
   <si>
-    <t xml:space="preserve">2.53745484352112</t>
+    <t xml:space="preserve">2.5374550819397</t>
   </si>
   <si>
     <t xml:space="preserve">2.63661241531372</t>
@@ -455,67 +455,67 @@
     <t xml:space="preserve">2.63011050224304</t>
   </si>
   <si>
-    <t xml:space="preserve">2.64636564254761</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.65286803245544</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.63823819160461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.64148902893066</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.69188046455383</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.75690197944641</t>
+    <t xml:space="preserve">2.64636540412903</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.65286755561829</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.63823771476746</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.64148926734924</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.69188070297241</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.75690174102783</t>
   </si>
   <si>
     <t xml:space="preserve">2.79266333580017</t>
   </si>
   <si>
-    <t xml:space="preserve">2.76340365409851</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.73089289665222</t>
+    <t xml:space="preserve">2.76340389251709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.7308931350708</t>
   </si>
   <si>
     <t xml:space="preserve">2.65449357032776</t>
   </si>
   <si>
-    <t xml:space="preserve">2.65774416923523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.74227213859558</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.76828002929688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.70651030540466</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.72764253616333</t>
+    <t xml:space="preserve">2.65774440765381</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.742271900177</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.76828074455261</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.70651006698608</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.72764205932617</t>
   </si>
   <si>
     <t xml:space="preserve">2.74064660072327</t>
   </si>
   <si>
-    <t xml:space="preserve">2.76990604400635</t>
+    <t xml:space="preserve">2.76990628242493</t>
   </si>
   <si>
     <t xml:space="preserve">2.80079126358032</t>
   </si>
   <si>
-    <t xml:space="preserve">2.69513177871704</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.66749787330627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.6479914188385</t>
+    <t xml:space="preserve">2.69513154029846</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.6674976348877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.64799118041992</t>
   </si>
   <si>
     <t xml:space="preserve">2.62523365020752</t>
@@ -524,100 +524,100 @@
     <t xml:space="preserve">2.59759950637817</t>
   </si>
   <si>
-    <t xml:space="preserve">2.61710596084595</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.66587209701538</t>
+    <t xml:space="preserve">2.61710619926453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.66587233543396</t>
   </si>
   <si>
     <t xml:space="preserve">2.63336157798767</t>
   </si>
   <si>
-    <t xml:space="preserve">2.68862962722778</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.60247588157654</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.67725086212158</t>
+    <t xml:space="preserve">2.6886293888092</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.6024763584137</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.67725038528442</t>
   </si>
   <si>
     <t xml:space="preserve">2.70976138114929</t>
   </si>
   <si>
-    <t xml:space="preserve">2.75527620315552</t>
+    <t xml:space="preserve">2.7552764415741</t>
   </si>
   <si>
     <t xml:space="preserve">2.72601675987244</t>
   </si>
   <si>
-    <t xml:space="preserve">2.72276544570923</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.82842516899109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.74389743804932</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.76177859306335</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.73902082443237</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.70488452911377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.69025492668152</t>
+    <t xml:space="preserve">2.72276568412781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.82842493057251</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.7438976764679</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.76177835464478</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.73902058601379</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.70488524436951</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.6902551651001</t>
   </si>
   <si>
     <t xml:space="preserve">2.612229347229</t>
   </si>
   <si>
-    <t xml:space="preserve">2.73251891136169</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.67562508583069</t>
+    <t xml:space="preserve">2.73251867294312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.67562532424927</t>
   </si>
   <si>
     <t xml:space="preserve">2.62360811233521</t>
   </si>
   <si>
-    <t xml:space="preserve">2.59434843063354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.55371022224426</t>
+    <t xml:space="preserve">2.59434866905212</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.55371046066284</t>
   </si>
   <si>
     <t xml:space="preserve">2.55045938491821</t>
   </si>
   <si>
-    <t xml:space="preserve">2.51307201385498</t>
+    <t xml:space="preserve">2.51307225227356</t>
   </si>
   <si>
     <t xml:space="preserve">2.46755719184875</t>
   </si>
   <si>
-    <t xml:space="preserve">2.50169324874878</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.58459544181824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.6317355632782</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.65611886978149</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.66912341117859</t>
+    <t xml:space="preserve">2.50169372558594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.58459520339966</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.63173580169678</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.65611863136292</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.66912317276001</t>
   </si>
   <si>
     <t xml:space="preserve">2.72439098358154</t>
   </si>
   <si>
-    <t xml:space="preserve">2.78291034698486</t>
+    <t xml:space="preserve">2.78291058540344</t>
   </si>
   <si>
     <t xml:space="preserve">2.77153182029724</t>
@@ -626,40 +626,40 @@
     <t xml:space="preserve">2.77803349494934</t>
   </si>
   <si>
-    <t xml:space="preserve">2.70000815391541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.7731568813324</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.7650294303894</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.71788883209229</t>
+    <t xml:space="preserve">2.70000791549683</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.77315711975098</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.76502966880798</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.71788930892944</t>
   </si>
   <si>
     <t xml:space="preserve">2.74552297592163</t>
   </si>
   <si>
-    <t xml:space="preserve">2.77965903282166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.74714875221252</t>
+    <t xml:space="preserve">2.77965927124023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.74714851379395</t>
   </si>
   <si>
     <t xml:space="preserve">2.60410189628601</t>
   </si>
   <si>
-    <t xml:space="preserve">2.62685942649841</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.64961671829224</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.69350600242615</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.69838309288025</t>
+    <t xml:space="preserve">2.62685918807983</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.64961647987366</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.69350624084473</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.69838261604309</t>
   </si>
   <si>
     <t xml:space="preserve">2.92270612716675</t>
@@ -668,10 +668,10 @@
     <t xml:space="preserve">2.88531875610352</t>
   </si>
   <si>
-    <t xml:space="preserve">2.99910593032837</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.97472286224365</t>
+    <t xml:space="preserve">2.99910640716553</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.97472310066223</t>
   </si>
   <si>
     <t xml:space="preserve">2.96984624862671</t>
@@ -686,16 +686,16 @@
     <t xml:space="preserve">2.93408465385437</t>
   </si>
   <si>
-    <t xml:space="preserve">2.89832282066345</t>
+    <t xml:space="preserve">2.89832329750061</t>
   </si>
   <si>
     <t xml:space="preserve">2.89182090759277</t>
   </si>
   <si>
-    <t xml:space="preserve">2.87881660461426</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.87556576728821</t>
+    <t xml:space="preserve">2.87881636619568</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.87556552886963</t>
   </si>
   <si>
     <t xml:space="preserve">2.84468078613281</t>
@@ -707,10 +707,10 @@
     <t xml:space="preserve">2.84955716133118</t>
   </si>
   <si>
-    <t xml:space="preserve">2.91945505142212</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.9259569644928</t>
+    <t xml:space="preserve">2.91945457458496</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.92595672607422</t>
   </si>
   <si>
     <t xml:space="preserve">2.99097847938538</t>
@@ -719,10 +719,10 @@
     <t xml:space="preserve">2.91457843780518</t>
   </si>
   <si>
-    <t xml:space="preserve">2.91620373725891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.95846772193909</t>
+    <t xml:space="preserve">2.91620397567749</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.95846748352051</t>
   </si>
   <si>
     <t xml:space="preserve">2.95684218406677</t>
@@ -740,25 +740,25 @@
     <t xml:space="preserve">2.99585509300232</t>
   </si>
   <si>
-    <t xml:space="preserve">2.97959971427917</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.0072340965271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.09645915031433</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.11628746986389</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.1691620349884</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.13942003250122</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.14437699317932</t>
+    <t xml:space="preserve">2.9795994758606</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.00723338127136</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.09645891189575</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.11628723144531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.16916179656982</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.13941979408264</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.14437675476074</t>
   </si>
   <si>
     <t xml:space="preserve">3.18898940086365</t>
@@ -770,16 +770,16 @@
     <t xml:space="preserve">3.24847340583801</t>
   </si>
   <si>
-    <t xml:space="preserve">3.21707963943481</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.16750955581665</t>
+    <t xml:space="preserve">3.21707940101624</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.16750979423523</t>
   </si>
   <si>
     <t xml:space="preserve">3.15429091453552</t>
   </si>
   <si>
-    <t xml:space="preserve">3.17081427574158</t>
+    <t xml:space="preserve">3.170814037323</t>
   </si>
   <si>
     <t xml:space="preserve">3.07663130760193</t>
@@ -791,52 +791,52 @@
     <t xml:space="preserve">2.98244857788086</t>
   </si>
   <si>
-    <t xml:space="preserve">3.0584557056427</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.06506514549255</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.0336709022522</t>
+    <t xml:space="preserve">3.05845546722412</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.06506538391113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.03367066383362</t>
   </si>
   <si>
     <t xml:space="preserve">3.02540922164917</t>
   </si>
   <si>
-    <t xml:space="preserve">2.99401521682739</t>
+    <t xml:space="preserve">2.99401497840881</t>
   </si>
   <si>
     <t xml:space="preserve">2.99071025848389</t>
   </si>
   <si>
-    <t xml:space="preserve">2.99897217750549</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.93783569335938</t>
+    <t xml:space="preserve">2.99897193908691</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.93783593177795</t>
   </si>
   <si>
     <t xml:space="preserve">2.9560112953186</t>
   </si>
   <si>
-    <t xml:space="preserve">3.07993578910828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.0881974697113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.08654546737671</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.10802555084229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.11133027076721</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.14768171310425</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.16420483589172</t>
+    <t xml:space="preserve">3.07993626594543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.08819794654846</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.08654522895813</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.10802531242371</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.11132979393005</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.14768123626709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.16420459747314</t>
   </si>
   <si>
     <t xml:space="preserve">3.2055127620697</t>
@@ -845,34 +845,34 @@
     <t xml:space="preserve">3.21377444267273</t>
   </si>
   <si>
-    <t xml:space="preserve">3.23029804229736</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.23360276222229</t>
+    <t xml:space="preserve">3.23029780387878</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.23360252380371</t>
   </si>
   <si>
     <t xml:space="preserve">3.25343012809753</t>
   </si>
   <si>
-    <t xml:space="preserve">3.29473853111267</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.3079571723938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.27160596847534</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.29639077186584</t>
+    <t xml:space="preserve">3.29473829269409</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.30795741081238</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.27160620689392</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.29639101028442</t>
   </si>
   <si>
     <t xml:space="preserve">3.22368836402893</t>
   </si>
   <si>
-    <t xml:space="preserve">3.25012588500977</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.19394636154175</t>
+    <t xml:space="preserve">3.25012564659119</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.19394659996033</t>
   </si>
   <si>
     <t xml:space="preserve">3.26334452629089</t>
@@ -881,52 +881,52 @@
     <t xml:space="preserve">3.09811162948608</t>
   </si>
   <si>
-    <t xml:space="preserve">3.15924739837646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.17246627807617</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.17411875724792</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.1509861946106</t>
+    <t xml:space="preserve">3.15924763679504</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.17246603965759</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.17411828041077</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.15098547935486</t>
   </si>
   <si>
     <t xml:space="preserve">3.05184650421143</t>
   </si>
   <si>
-    <t xml:space="preserve">3.05680346488953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.08489322662354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.12785339355469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.03201866149902</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.09480667114258</t>
+    <t xml:space="preserve">3.05680298805237</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.08489298820496</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.12785363197327</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.03201842308044</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.09480690956116</t>
   </si>
   <si>
     <t xml:space="preserve">3.073326587677</t>
   </si>
   <si>
-    <t xml:space="preserve">3.09150266647339</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.13115835189819</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.10967803001404</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.10472106933594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.12124443054199</t>
+    <t xml:space="preserve">3.09150218963623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.13115811347961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.10967779159546</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.10472083091736</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.12124419212341</t>
   </si>
   <si>
     <t xml:space="preserve">3.13611507415771</t>
@@ -935,10 +935,10 @@
     <t xml:space="preserve">3.1460292339325</t>
   </si>
   <si>
-    <t xml:space="preserve">3.12950587272644</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.14107227325439</t>
+    <t xml:space="preserve">3.12950611114502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.14107203483582</t>
   </si>
   <si>
     <t xml:space="preserve">3.15759515762329</t>
@@ -950,19 +950,19 @@
     <t xml:space="preserve">3.10637331008911</t>
   </si>
   <si>
-    <t xml:space="preserve">3.08158826828003</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.10141611099243</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.10306859016418</t>
+    <t xml:space="preserve">3.08158850669861</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.10141634941101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.10306882858276</t>
   </si>
   <si>
     <t xml:space="preserve">3.12289643287659</t>
   </si>
   <si>
-    <t xml:space="preserve">3.08984994888306</t>
+    <t xml:space="preserve">3.08985018730164</t>
   </si>
   <si>
     <t xml:space="preserve">2.94940233230591</t>
@@ -971,82 +971,82 @@
     <t xml:space="preserve">2.93287897109985</t>
   </si>
   <si>
-    <t xml:space="preserve">2.83704423904419</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.88165712356567</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.90809416770935</t>
+    <t xml:space="preserve">2.83704400062561</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.88165688514709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.90809392929077</t>
   </si>
   <si>
     <t xml:space="preserve">2.91139888763428</t>
   </si>
   <si>
-    <t xml:space="preserve">2.94609761238098</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.94114065170288</t>
+    <t xml:space="preserve">2.94609785079956</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.9411404132843</t>
   </si>
   <si>
     <t xml:space="preserve">2.96592569351196</t>
   </si>
   <si>
-    <t xml:space="preserve">2.8849618434906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.84034872055054</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.82878232002258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.81225895881653</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.8800048828125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.75112318992615</t>
+    <t xml:space="preserve">2.88496160507202</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.84034848213196</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.82878255844116</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.81225919723511</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.88000440597534</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.75112271308899</t>
   </si>
   <si>
     <t xml:space="preserve">2.80895447731018</t>
   </si>
   <si>
-    <t xml:space="preserve">2.79243111610413</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.8139111995697</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.85852408409119</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.97418713569641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.97088241577148</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.01549530029297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.05515074729919</t>
+    <t xml:space="preserve">2.79243135452271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.81391167640686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.85852432250977</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.97418689727783</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.97088265419006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.01549553871155</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.05515122413635</t>
   </si>
   <si>
     <t xml:space="preserve">3.04028058052063</t>
   </si>
   <si>
-    <t xml:space="preserve">3.07002234458923</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.06341242790222</t>
+    <t xml:space="preserve">3.07002186775208</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.06341290473938</t>
   </si>
   <si>
     <t xml:space="preserve">3.023756980896</t>
   </si>
   <si>
-    <t xml:space="preserve">3.0369758605957</t>
+    <t xml:space="preserve">3.03697562217712</t>
   </si>
   <si>
     <t xml:space="preserve">3.0287139415741</t>
@@ -1055,37 +1055,37 @@
     <t xml:space="preserve">3.05349898338318</t>
   </si>
   <si>
-    <t xml:space="preserve">3.07828402519226</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.1105043888092</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.06919574737549</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.1559431552887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.21790528297424</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.17659735679626</t>
+    <t xml:space="preserve">3.07828378677368</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.11050415039062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.06919550895691</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.15594291687012</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.21790504455566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.17659711837769</t>
   </si>
   <si>
     <t xml:space="preserve">3.19312047958374</t>
   </si>
   <si>
-    <t xml:space="preserve">3.25508284568787</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.22203588485718</t>
+    <t xml:space="preserve">3.25508260726929</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.22203612327576</t>
   </si>
   <si>
     <t xml:space="preserve">2.96179485321045</t>
   </si>
   <si>
-    <t xml:space="preserve">2.97831797599792</t>
+    <t xml:space="preserve">2.97831773757935</t>
   </si>
   <si>
     <t xml:space="preserve">2.92461729049683</t>
@@ -1100,19 +1100,19 @@
     <t xml:space="preserve">3.07745766639709</t>
   </si>
   <si>
-    <t xml:space="preserve">3.05267310142517</t>
+    <t xml:space="preserve">3.05267262458801</t>
   </si>
   <si>
     <t xml:space="preserve">3.03614950180054</t>
   </si>
   <si>
-    <t xml:space="preserve">2.92048716545105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.08571934700012</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.01962637901306</t>
+    <t xml:space="preserve">2.92048668861389</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.08571887016296</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.01962614059448</t>
   </si>
   <si>
     <t xml:space="preserve">3.02788758277893</t>
@@ -1121,25 +1121,25 @@
     <t xml:space="preserve">3.04854202270508</t>
   </si>
   <si>
-    <t xml:space="preserve">3.04441118240356</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.15181255340576</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.3376989364624</t>
+    <t xml:space="preserve">3.04441094398499</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.15181231498718</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.33769941329956</t>
   </si>
   <si>
     <t xml:space="preserve">3.25095200538635</t>
   </si>
   <si>
-    <t xml:space="preserve">3.27573657035828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.2839982509613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.24682140350342</t>
+    <t xml:space="preserve">3.27573680877686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.28399801254272</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.24682116508484</t>
   </si>
   <si>
     <t xml:space="preserve">3.18485879898071</t>
@@ -1151,16 +1151,16 @@
     <t xml:space="preserve">3.20177507400513</t>
   </si>
   <si>
-    <t xml:space="preserve">3.21016764640808</t>
+    <t xml:space="preserve">3.2101674079895</t>
   </si>
   <si>
     <t xml:space="preserve">3.18918633460999</t>
   </si>
   <si>
-    <t xml:space="preserve">3.22275614738464</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.16400814056396</t>
+    <t xml:space="preserve">3.2227566242218</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.16400837898254</t>
   </si>
   <si>
     <t xml:space="preserve">3.08847498893738</t>
@@ -1169,28 +1169,28 @@
     <t xml:space="preserve">3.12204527854919</t>
   </si>
   <si>
-    <t xml:space="preserve">3.14302659034729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.20597100257874</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.25632667541504</t>
+    <t xml:space="preserve">3.14302635192871</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.20597124099731</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.25632691383362</t>
   </si>
   <si>
     <t xml:space="preserve">3.24793410301208</t>
   </si>
   <si>
-    <t xml:space="preserve">3.10525989532471</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.07168960571289</t>
+    <t xml:space="preserve">3.10526013374329</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.07168984413147</t>
   </si>
   <si>
     <t xml:space="preserve">3.18498969078064</t>
   </si>
   <si>
-    <t xml:space="preserve">3.11365246772766</t>
+    <t xml:space="preserve">3.11365294456482</t>
   </si>
   <si>
     <t xml:space="preserve">3.12624168395996</t>
@@ -1199,37 +1199,37 @@
     <t xml:space="preserve">3.1388304233551</t>
   </si>
   <si>
-    <t xml:space="preserve">3.14722275733948</t>
+    <t xml:space="preserve">3.14722323417664</t>
   </si>
   <si>
     <t xml:space="preserve">3.15561556816101</t>
   </si>
   <si>
-    <t xml:space="preserve">3.17240071296692</t>
+    <t xml:space="preserve">3.1724009513855</t>
   </si>
   <si>
     <t xml:space="preserve">3.08427858352661</t>
   </si>
   <si>
-    <t xml:space="preserve">3.13463377952576</t>
+    <t xml:space="preserve">3.13463425636292</t>
   </si>
   <si>
     <t xml:space="preserve">3.16820454597473</t>
   </si>
   <si>
-    <t xml:space="preserve">3.10945630073547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.15981197357178</t>
+    <t xml:space="preserve">3.10945606231689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.15981221199036</t>
   </si>
   <si>
     <t xml:space="preserve">3.19338250160217</t>
   </si>
   <si>
-    <t xml:space="preserve">3.21436357498169</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.23534536361694</t>
+    <t xml:space="preserve">3.21436381340027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.23534560203552</t>
   </si>
   <si>
     <t xml:space="preserve">3.26471948623657</t>
@@ -1238,10 +1238,10 @@
     <t xml:space="preserve">3.32346773147583</t>
   </si>
   <si>
-    <t xml:space="preserve">3.31087827682495</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.27730822563171</t>
+    <t xml:space="preserve">3.31087875366211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.27730846405029</t>
   </si>
   <si>
     <t xml:space="preserve">3.35703802108765</t>
@@ -1250,91 +1250,91 @@
     <t xml:space="preserve">3.42417860031128</t>
   </si>
   <si>
-    <t xml:space="preserve">3.49131941795349</t>
+    <t xml:space="preserve">3.49131894111633</t>
   </si>
   <si>
     <t xml:space="preserve">3.43257141113281</t>
   </si>
   <si>
-    <t xml:space="preserve">3.54167485237122</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.44935631752014</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.48292708396912</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.51649761199951</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.47453379631042</t>
+    <t xml:space="preserve">3.54167437553406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.44935655593872</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.48292684555054</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.51649689674377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.474534034729</t>
   </si>
   <si>
     <t xml:space="preserve">3.4577488899231</t>
   </si>
   <si>
-    <t xml:space="preserve">3.38641214370728</t>
+    <t xml:space="preserve">3.38641166687012</t>
   </si>
   <si>
     <t xml:space="preserve">3.37801933288574</t>
   </si>
   <si>
-    <t xml:space="preserve">3.47033786773682</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.30248594284058</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.31927108764648</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.29829025268555</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.34025263786316</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.27311182022095</t>
+    <t xml:space="preserve">3.4703381061554</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.30248618125916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.31927084922791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.29828977584839</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.34025287628174</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.27311205863953</t>
   </si>
   <si>
     <t xml:space="preserve">3.28150463104248</t>
   </si>
   <si>
-    <t xml:space="preserve">3.39900088310242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.57524538040161</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.58783459663391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.55006718635559</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.5794415473938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.58363795280457</t>
+    <t xml:space="preserve">3.399001121521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.57524561882019</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.58783435821533</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.55006766319275</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.57944178581238</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.58363771438599</t>
   </si>
   <si>
     <t xml:space="preserve">3.66336750984192</t>
   </si>
   <si>
-    <t xml:space="preserve">3.55845999717712</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.56685280799866</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.62140488624573</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.78086400032043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.88577151298523</t>
+    <t xml:space="preserve">3.55845952033997</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.56685256958008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.62140512466431</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.78086352348328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.88577127456665</t>
   </si>
   <si>
     <t xml:space="preserve">3.72211527824402</t>
@@ -1346,49 +1346,49 @@
     <t xml:space="preserve">3.68434882164001</t>
   </si>
   <si>
-    <t xml:space="preserve">3.79764890670776</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.82702302932739</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.80184531211853</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.83961200714111</t>
+    <t xml:space="preserve">3.79764914512634</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.82702326774597</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.80184578895569</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.83961224555969</t>
   </si>
   <si>
     <t xml:space="preserve">3.91934180259705</t>
   </si>
   <si>
-    <t xml:space="preserve">3.91094970703125</t>
+    <t xml:space="preserve">3.91094875335693</t>
   </si>
   <si>
     <t xml:space="preserve">3.94451951980591</t>
   </si>
   <si>
-    <t xml:space="preserve">4.06621217727661</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.02005243301392</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.927734375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.86898612976074</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.81863021850586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.86059355735779</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.793452501297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.86478972434998</t>
+    <t xml:space="preserve">4.06621170043945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.02005290985107</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.92773461341858</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.86898636817932</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.81863045692444</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.86059379577637</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.79345273971558</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.86478996276855</t>
   </si>
   <si>
     <t xml:space="preserve">3.8773787021637</t>
@@ -1397,37 +1397,37 @@
     <t xml:space="preserve">3.73470449447632</t>
   </si>
   <si>
-    <t xml:space="preserve">3.84380841255188</t>
+    <t xml:space="preserve">3.84380793571472</t>
   </si>
   <si>
     <t xml:space="preserve">3.69274163246155</t>
   </si>
   <si>
-    <t xml:space="preserve">3.90255641937256</t>
+    <t xml:space="preserve">3.90255618095398</t>
   </si>
   <si>
     <t xml:space="preserve">3.95291209220886</t>
   </si>
   <si>
-    <t xml:space="preserve">3.9906792640686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.00326728820801</t>
+    <t xml:space="preserve">3.99067807197571</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.00326776504517</t>
   </si>
   <si>
     <t xml:space="preserve">3.9151451587677</t>
   </si>
   <si>
-    <t xml:space="preserve">3.87318301200867</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.85220170021057</t>
+    <t xml:space="preserve">3.87318205833435</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.85220122337341</t>
   </si>
   <si>
     <t xml:space="preserve">3.66756391525269</t>
   </si>
   <si>
-    <t xml:space="preserve">3.67595672607422</t>
+    <t xml:space="preserve">3.67595648765564</t>
   </si>
   <si>
     <t xml:space="preserve">3.5920307636261</t>
@@ -1436,79 +1436,79 @@
     <t xml:space="preserve">3.53328275680542</t>
   </si>
   <si>
-    <t xml:space="preserve">3.70533037185669</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.64238667488098</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.77666759490967</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.71791958808899</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.64658188819885</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.70113468170166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.68015313148499</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.80604195594788</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.7850604057312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.69693779945374</t>
+    <t xml:space="preserve">3.70533084869385</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.64238619804382</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.77666783332825</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.71791911125183</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.64658212661743</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.70113396644592</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.68015265464783</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.80604124069214</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.78506016731262</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.69693803787231</t>
   </si>
   <si>
     <t xml:space="preserve">3.73050856590271</t>
   </si>
   <si>
-    <t xml:space="preserve">3.7472939491272</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.65077900886536</t>
+    <t xml:space="preserve">3.74729347229004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.6507785320282</t>
   </si>
   <si>
     <t xml:space="preserve">3.65917158126831</t>
   </si>
   <si>
-    <t xml:space="preserve">3.85639691352844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.89416360855103</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.9361264705658</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.00746393203735</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.08719396591187</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.11237144470215</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.17111968994141</t>
+    <t xml:space="preserve">3.85639643669128</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.8941638469696</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.93612694740295</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.0074634552002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.08719348907471</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.11237096786499</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.17111921310425</t>
   </si>
   <si>
     <t xml:space="preserve">4.19629716873169</t>
   </si>
   <si>
-    <t xml:space="preserve">4.2382607460022</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.18790483474731</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.09978246688843</t>
+    <t xml:space="preserve">4.23826026916504</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.18790435791016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.09978199005127</t>
   </si>
   <si>
     <t xml:space="preserve">4.09558629989624</t>
@@ -1520,7 +1520,7 @@
     <t xml:space="preserve">4.14594173431396</t>
   </si>
   <si>
-    <t xml:space="preserve">4.09138965606689</t>
+    <t xml:space="preserve">4.09139013290405</t>
   </si>
   <si>
     <t xml:space="preserve">4.08299732208252</t>
@@ -1535,40 +1535,40 @@
     <t xml:space="preserve">4.39771938323975</t>
   </si>
   <si>
-    <t xml:space="preserve">4.52360868453979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.49843120574951</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.58235645294189</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.48164558410645</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.62431955337524</t>
+    <t xml:space="preserve">4.52360820770264</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.49843072891235</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.58235692977905</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.4816460609436</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.6243200302124</t>
   </si>
   <si>
     <t xml:space="preserve">4.67467498779297</t>
   </si>
   <si>
-    <t xml:space="preserve">4.69985294342041</t>
+    <t xml:space="preserve">4.69985342025757</t>
   </si>
   <si>
     <t xml:space="preserve">4.6830677986145</t>
   </si>
   <si>
-    <t xml:space="preserve">4.66628217697144</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.63271188735962</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.44807529449463</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.43968296051025</t>
+    <t xml:space="preserve">4.66628265380859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.63271236419678</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.44807577133179</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.4396824836731</t>
   </si>
   <si>
     <t xml:space="preserve">4.47325277328491</t>
@@ -1577,19 +1577,19 @@
     <t xml:space="preserve">4.49003839492798</t>
   </si>
   <si>
-    <t xml:space="preserve">4.54878616333008</t>
+    <t xml:space="preserve">4.54878664016724</t>
   </si>
   <si>
     <t xml:space="preserve">4.5991415977478</t>
   </si>
   <si>
-    <t xml:space="preserve">4.61592721939087</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.60753393173218</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.40611171722412</t>
+    <t xml:space="preserve">4.61592674255371</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.60753440856934</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.40611219406128</t>
   </si>
   <si>
     <t xml:space="preserve">4.53200101852417</t>
@@ -1598,10 +1598,10 @@
     <t xml:space="preserve">4.75860166549683</t>
   </si>
   <si>
-    <t xml:space="preserve">4.80895709991455</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.74181604385376</t>
+    <t xml:space="preserve">4.80895614624023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.7418155670166</t>
   </si>
   <si>
     <t xml:space="preserve">4.69146108627319</t>
@@ -1613,7 +1613,7 @@
     <t xml:space="preserve">4.50682353973389</t>
   </si>
   <si>
-    <t xml:space="preserve">4.5403938293457</t>
+    <t xml:space="preserve">4.54039335250854</t>
   </si>
   <si>
     <t xml:space="preserve">4.46485996246338</t>
@@ -1634,7 +1634,7 @@
     <t xml:space="preserve">4.46764707565308</t>
   </si>
   <si>
-    <t xml:space="preserve">4.51919651031494</t>
+    <t xml:space="preserve">4.5191969871521</t>
   </si>
   <si>
     <t xml:space="preserve">4.39891386032104</t>
@@ -1646,13 +1646,13 @@
     <t xml:space="preserve">4.30440616607666</t>
   </si>
   <si>
-    <t xml:space="preserve">4.27003955841064</t>
+    <t xml:space="preserve">4.27003860473633</t>
   </si>
   <si>
     <t xml:space="preserve">4.33018064498901</t>
   </si>
   <si>
-    <t xml:space="preserve">4.31299686431885</t>
+    <t xml:space="preserve">4.31299734115601</t>
   </si>
   <si>
     <t xml:space="preserve">4.38173055648804</t>
@@ -1661,10 +1661,10 @@
     <t xml:space="preserve">4.44187164306641</t>
   </si>
   <si>
-    <t xml:space="preserve">4.45905494689941</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.35595560073853</t>
+    <t xml:space="preserve">4.45905542373657</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.35595512390137</t>
   </si>
   <si>
     <t xml:space="preserve">4.39032220840454</t>
@@ -1673,7 +1673,7 @@
     <t xml:space="preserve">4.45046329498291</t>
   </si>
   <si>
-    <t xml:space="preserve">4.41609668731689</t>
+    <t xml:space="preserve">4.41609621047974</t>
   </si>
   <si>
     <t xml:space="preserve">4.23137712478638</t>
@@ -1688,64 +1688,64 @@
     <t xml:space="preserve">4.04665660858154</t>
   </si>
   <si>
-    <t xml:space="preserve">4.08531951904297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.98221945762634</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.03376913070679</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.94785332679749</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.99081110954285</t>
+    <t xml:space="preserve">4.08531904220581</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.98222064971924</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.03376960754395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.94785237312317</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.99081087112427</t>
   </si>
   <si>
     <t xml:space="preserve">3.98651552200317</t>
   </si>
   <si>
-    <t xml:space="preserve">3.94355773925781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.96503686904907</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.96074032783508</t>
+    <t xml:space="preserve">3.94355750083923</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.96503615379333</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.96074056625366</t>
   </si>
   <si>
     <t xml:space="preserve">4.01229095458984</t>
   </si>
   <si>
-    <t xml:space="preserve">3.92637419700623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.07243204116821</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.08961534500122</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.11109495162964</t>
+    <t xml:space="preserve">3.9263744354248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.07243156433105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.08961486816406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.11109399795532</t>
   </si>
   <si>
     <t xml:space="preserve">4.26144790649414</t>
   </si>
   <si>
-    <t xml:space="preserve">4.32158899307251</t>
+    <t xml:space="preserve">4.32158946990967</t>
   </si>
   <si>
     <t xml:space="preserve">4.295814037323</t>
   </si>
   <si>
-    <t xml:space="preserve">4.02947330474854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.84045791625977</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.87482452392578</t>
+    <t xml:space="preserve">4.02947378158569</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.84045767784119</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.87482476234436</t>
   </si>
   <si>
     <t xml:space="preserve">3.88771176338196</t>
@@ -1754,73 +1754,73 @@
     <t xml:space="preserve">4.00369882583618</t>
   </si>
   <si>
-    <t xml:space="preserve">4.02088212966919</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.93496608734131</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.86623287200928</t>
+    <t xml:space="preserve">4.02088165283203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.93496584892273</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.8662326335907</t>
   </si>
   <si>
     <t xml:space="preserve">3.77172470092773</t>
   </si>
   <si>
-    <t xml:space="preserve">3.71587920188904</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.7029914855957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.67721700668335</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.68580842018127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.70728754997253</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.66432929039001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.66003394126892</t>
+    <t xml:space="preserve">3.71587896347046</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.70299172401428</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.67721724510193</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.68580913543701</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.70728802680969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.66432976722717</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.66003370285034</t>
   </si>
   <si>
     <t xml:space="preserve">3.72017478942871</t>
   </si>
   <si>
-    <t xml:space="preserve">3.81468272209167</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.95214891433716</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.85764098167419</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.78461217880249</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.84475350379944</t>
+    <t xml:space="preserve">3.81468319892883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.95214939117432</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.85764074325562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.78461241722107</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.8447539806366</t>
   </si>
   <si>
     <t xml:space="preserve">3.78031635284424</t>
   </si>
   <si>
-    <t xml:space="preserve">3.69440031051636</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.73306226730347</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.71158361434937</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.59989261627197</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.75454163551331</t>
+    <t xml:space="preserve">3.69440007209778</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.73306250572205</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.71158337593079</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.59989213943481</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.75454187393188</t>
   </si>
   <si>
     <t xml:space="preserve">3.65144228935242</t>
@@ -1829,28 +1829,28 @@
     <t xml:space="preserve">3.72447085380554</t>
   </si>
   <si>
-    <t xml:space="preserve">3.78890824317932</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.64714646339417</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.66862535476685</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.67292165756226</t>
+    <t xml:space="preserve">3.78890800476074</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.64714598655701</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.66862511634827</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.6729211807251</t>
   </si>
   <si>
     <t xml:space="preserve">3.6170756816864</t>
   </si>
   <si>
-    <t xml:space="preserve">3.57411742210388</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.64285039901733</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.65573787689209</t>
+    <t xml:space="preserve">3.57411694526672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.64284992218018</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.65573811531067</t>
   </si>
   <si>
     <t xml:space="preserve">3.62996292114258</t>
@@ -1859,7 +1859,7 @@
     <t xml:space="preserve">3.96933245658875</t>
   </si>
   <si>
-    <t xml:space="preserve">3.95644474029541</t>
+    <t xml:space="preserve">3.95644521713257</t>
   </si>
   <si>
     <t xml:space="preserve">3.90059924125671</t>
@@ -1871,28 +1871,28 @@
     <t xml:space="preserve">4.01658582687378</t>
   </si>
   <si>
-    <t xml:space="preserve">4.09820652008057</t>
+    <t xml:space="preserve">4.09820699691772</t>
   </si>
   <si>
     <t xml:space="preserve">4.14116477966309</t>
   </si>
   <si>
-    <t xml:space="preserve">4.24426412582397</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.24855995178223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.43328046798706</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.42468881607056</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.58793020248413</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.57933759689331</t>
+    <t xml:space="preserve">4.24426460266113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.24856090545654</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.4332799911499</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.4246883392334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.58792972564697</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.57933807373047</t>
   </si>
   <si>
     <t xml:space="preserve">4.49342155456543</t>
@@ -1907,16 +1907,16 @@
     <t xml:space="preserve">4.53637981414795</t>
   </si>
   <si>
-    <t xml:space="preserve">4.59652137756348</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.77694463729858</t>
+    <t xml:space="preserve">4.59652090072632</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.77694511413574</t>
   </si>
   <si>
     <t xml:space="preserve">4.81131172180176</t>
   </si>
   <si>
-    <t xml:space="preserve">4.69962072372437</t>
+    <t xml:space="preserve">4.69962024688721</t>
   </si>
   <si>
     <t xml:space="preserve">4.64807033538818</t>
@@ -1937,7 +1937,7 @@
     <t xml:space="preserve">4.70821189880371</t>
   </si>
   <si>
-    <t xml:space="preserve">4.67384576797485</t>
+    <t xml:space="preserve">4.67384624481201</t>
   </si>
   <si>
     <t xml:space="preserve">4.5621542930603</t>
@@ -1946,91 +1946,91 @@
     <t xml:space="preserve">4.50201272964478</t>
   </si>
   <si>
-    <t xml:space="preserve">4.54497146606445</t>
+    <t xml:space="preserve">4.54497098922729</t>
   </si>
   <si>
     <t xml:space="preserve">4.51060485839844</t>
   </si>
   <si>
-    <t xml:space="preserve">4.52778768539429</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.7683539390564</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.66525411605835</t>
+    <t xml:space="preserve">4.52778816223145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.76835346221924</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.66525363922119</t>
   </si>
   <si>
     <t xml:space="preserve">4.61370468139648</t>
   </si>
   <si>
-    <t xml:space="preserve">4.73398733139038</t>
+    <t xml:space="preserve">4.73398780822754</t>
   </si>
   <si>
     <t xml:space="preserve">4.639479637146</t>
   </si>
   <si>
-    <t xml:space="preserve">4.23567247390747</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.15834808349609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.20130634307861</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.36454677581787</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.60511302947998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.11538982391357</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.75024580955505</t>
+    <t xml:space="preserve">4.23567295074463</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.15834856033325</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.20130586624146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.36454725265503</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.60511255264282</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.11539030075073</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.75024557113647</t>
   </si>
   <si>
     <t xml:space="preserve">3.47101783752441</t>
   </si>
   <si>
-    <t xml:space="preserve">3.36362266540527</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.31207275390625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.16601514816284</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.22186040878296</t>
+    <t xml:space="preserve">3.36362242698669</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.31207299232483</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.16601538658142</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.22186064720154</t>
   </si>
   <si>
     <t xml:space="preserve">2.80516672134399</t>
   </si>
   <si>
-    <t xml:space="preserve">2.91685771942139</t>
+    <t xml:space="preserve">2.91685819625854</t>
   </si>
   <si>
     <t xml:space="preserve">2.86530804634094</t>
   </si>
   <si>
-    <t xml:space="preserve">2.8867871761322</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.73213791847229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.66770052909851</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.80087065696716</t>
+    <t xml:space="preserve">2.88678693771362</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.73213815689087</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.66770076751709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.80087089538574</t>
   </si>
   <si>
     <t xml:space="preserve">2.61185479164124</t>
   </si>
   <si>
-    <t xml:space="preserve">2.72354674339294</t>
+    <t xml:space="preserve">2.72354602813721</t>
   </si>
   <si>
     <t xml:space="preserve">2.92115330696106</t>
@@ -2048,34 +2048,34 @@
     <t xml:space="preserve">2.84382891654968</t>
   </si>
   <si>
-    <t xml:space="preserve">2.76650428771973</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.78798317909241</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.70636296272278</t>
+    <t xml:space="preserve">2.76650452613831</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.78798341751099</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.7063627243042</t>
   </si>
   <si>
     <t xml:space="preserve">2.71065878868103</t>
   </si>
   <si>
-    <t xml:space="preserve">2.85242080688477</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.89108300209045</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.9297456741333</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.00706958770752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.96411180496216</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.93833684921265</t>
+    <t xml:space="preserve">2.85242056846619</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.89108276367188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.92974519729614</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.0070698261261</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.96411156654358</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.9383373260498</t>
   </si>
   <si>
     <t xml:space="preserve">2.9426326751709</t>
@@ -2084,16 +2084,16 @@
     <t xml:space="preserve">2.98129510879517</t>
   </si>
   <si>
-    <t xml:space="preserve">3.01136589050293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.94692850112915</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.97699928283691</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.95122456550598</t>
+    <t xml:space="preserve">3.01136565208435</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.94692873954773</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.97699904441833</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.9512243270874</t>
   </si>
   <si>
     <t xml:space="preserve">3.10587382316589</t>
@@ -2102,94 +2102,94 @@
     <t xml:space="preserve">3.04143643379211</t>
   </si>
   <si>
-    <t xml:space="preserve">3.05002808570862</t>
+    <t xml:space="preserve">3.0500283241272</t>
   </si>
   <si>
     <t xml:space="preserve">3.08439469337463</t>
   </si>
   <si>
-    <t xml:space="preserve">3.13164830207825</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.03284502029419</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.09298634529114</t>
+    <t xml:space="preserve">3.13164854049683</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.03284454345703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.09298610687256</t>
   </si>
   <si>
     <t xml:space="preserve">3.1917896270752</t>
   </si>
   <si>
-    <t xml:space="preserve">3.24763536453247</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.16171932220459</t>
+    <t xml:space="preserve">3.24763560295105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.16171908378601</t>
   </si>
   <si>
     <t xml:space="preserve">3.14883160591125</t>
   </si>
   <si>
-    <t xml:space="preserve">3.18319821357727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.13594460487366</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.11876106262207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.307776927948</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.38510179519653</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.4366512298584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.48390555381775</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.46242642402649</t>
+    <t xml:space="preserve">3.18319797515869</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.13594436645508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.11876130104065</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.30777668952942</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.38510155677795</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.43665146827698</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.48390531539917</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.46242618560791</t>
   </si>
   <si>
     <t xml:space="preserve">3.47960948944092</t>
   </si>
   <si>
-    <t xml:space="preserve">3.31636810302734</t>
+    <t xml:space="preserve">3.3163685798645</t>
   </si>
   <si>
     <t xml:space="preserve">3.29488921165466</t>
   </si>
   <si>
-    <t xml:space="preserve">3.19608592987061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.38080596923828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.37651014328003</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.35073494911194</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.3722140789032</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.42805957794189</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.44094705581665</t>
+    <t xml:space="preserve">3.19608616828918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.3808057308197</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.37650990486145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.35073518753052</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.37221431732178</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.42805981636047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.44094729423523</t>
   </si>
   <si>
     <t xml:space="preserve">3.44524312019348</t>
   </si>
   <si>
-    <t xml:space="preserve">3.75857472419739</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.71435570716858</t>
+    <t xml:space="preserve">3.75857496261597</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.71435594558716</t>
   </si>
   <si>
     <t xml:space="preserve">3.63034105300903</t>
@@ -2207,7 +2207,7 @@
     <t xml:space="preserve">3.43135786056519</t>
   </si>
   <si>
-    <t xml:space="preserve">3.44904518127441</t>
+    <t xml:space="preserve">3.44904541969299</t>
   </si>
   <si>
     <t xml:space="preserve">3.36060786247253</t>
@@ -2216,25 +2216,25 @@
     <t xml:space="preserve">3.38713932037354</t>
   </si>
   <si>
-    <t xml:space="preserve">3.41809225082397</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.32081127166748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.33849883079529</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.31638956069946</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.27217078208923</t>
+    <t xml:space="preserve">3.4180920124054</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.32081151008606</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.33849859237671</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.31638932228088</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.27217102050781</t>
   </si>
   <si>
     <t xml:space="preserve">3.28101468086243</t>
   </si>
   <si>
-    <t xml:space="preserve">3.22795271873474</t>
+    <t xml:space="preserve">3.22795224189758</t>
   </si>
   <si>
     <t xml:space="preserve">3.09529685974121</t>
@@ -2246,7 +2246,7 @@
     <t xml:space="preserve">3.25448346138</t>
   </si>
   <si>
-    <t xml:space="preserve">3.20584321022034</t>
+    <t xml:space="preserve">3.20584297180176</t>
   </si>
   <si>
     <t xml:space="preserve">3.1660463809967</t>
@@ -2255,10 +2255,10 @@
     <t xml:space="preserve">3.15720272064209</t>
   </si>
   <si>
-    <t xml:space="preserve">3.13951516151428</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.10414028167725</t>
+    <t xml:space="preserve">3.13951539993286</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.1041407585144</t>
   </si>
   <si>
     <t xml:space="preserve">3.09971857070923</t>
@@ -2270,13 +2270,13 @@
     <t xml:space="preserve">3.04665637016296</t>
   </si>
   <si>
-    <t xml:space="preserve">3.0776093006134</t>
+    <t xml:space="preserve">3.07760953903198</t>
   </si>
   <si>
     <t xml:space="preserve">3.05992221832275</t>
   </si>
   <si>
-    <t xml:space="preserve">2.98032832145691</t>
+    <t xml:space="preserve">2.98032855987549</t>
   </si>
   <si>
     <t xml:space="preserve">2.96264100074768</t>
@@ -2288,16 +2288,16 @@
     <t xml:space="preserve">2.93611001968384</t>
   </si>
   <si>
-    <t xml:space="preserve">3.09087467193604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.06876587867737</t>
+    <t xml:space="preserve">3.09087514877319</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.06876564025879</t>
   </si>
   <si>
     <t xml:space="preserve">3.05550003051758</t>
   </si>
   <si>
-    <t xml:space="preserve">2.98475050926208</t>
+    <t xml:space="preserve">2.98475027084351</t>
   </si>
   <si>
     <t xml:space="preserve">2.9051570892334</t>
@@ -2306,43 +2306,43 @@
     <t xml:space="preserve">2.83440756797791</t>
   </si>
   <si>
-    <t xml:space="preserve">2.86978197097778</t>
+    <t xml:space="preserve">2.86978244781494</t>
   </si>
   <si>
     <t xml:space="preserve">2.80345463752747</t>
   </si>
   <si>
-    <t xml:space="preserve">2.77692341804504</t>
+    <t xml:space="preserve">2.77692365646362</t>
   </si>
   <si>
     <t xml:space="preserve">2.81229829788208</t>
   </si>
   <si>
-    <t xml:space="preserve">2.84767317771912</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.82998585700989</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.79461097717285</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.91842246055603</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.82114195823669</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.79903292655945</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.80787634849548</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.75923562049866</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.7238609790802</t>
+    <t xml:space="preserve">2.8476734161377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.82998561859131</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.79461073875427</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.91842269897461</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.82114219665527</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.79903268814087</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.80787658691406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.75923609733582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.72386121749878</t>
   </si>
   <si>
     <t xml:space="preserve">2.71501755714417</t>
@@ -2354,13 +2354,13 @@
     <t xml:space="preserve">2.63542413711548</t>
   </si>
   <si>
-    <t xml:space="preserve">2.61773705482483</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.58236193656921</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.54698705673218</t>
+    <t xml:space="preserve">2.61773681640625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.58236169815063</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.54698729515076</t>
   </si>
   <si>
     <t xml:space="preserve">2.56467485427856</t>
@@ -2375,16 +2375,16 @@
     <t xml:space="preserve">2.5735182762146</t>
   </si>
   <si>
-    <t xml:space="preserve">2.97148513793945</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.95379757881165</t>
+    <t xml:space="preserve">2.97148466110229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.95379781723022</t>
   </si>
   <si>
     <t xml:space="preserve">3.00243782997131</t>
   </si>
   <si>
-    <t xml:space="preserve">3.17931222915649</t>
+    <t xml:space="preserve">3.17931199073792</t>
   </si>
   <si>
     <t xml:space="preserve">3.1704683303833</t>
@@ -2393,25 +2393,25 @@
     <t xml:space="preserve">3.19257736206055</t>
   </si>
   <si>
-    <t xml:space="preserve">3.28985857963562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.29870223999023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.47999787330627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.4136700630188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.48442006111145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.45788860321045</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.49326348304749</t>
+    <t xml:space="preserve">3.28985834121704</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.29870200157166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.47999811172485</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.41367030143738</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.48441982269287</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.45788884162903</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.49326395988464</t>
   </si>
   <si>
     <t xml:space="preserve">3.51095080375671</t>
@@ -2420,7 +2420,7 @@
     <t xml:space="preserve">3.44462299346924</t>
   </si>
   <si>
-    <t xml:space="preserve">3.42693567276001</t>
+    <t xml:space="preserve">3.42693591117859</t>
   </si>
   <si>
     <t xml:space="preserve">3.55516934394836</t>
@@ -2429,10 +2429,10 @@
     <t xml:space="preserve">3.67898106575012</t>
   </si>
   <si>
-    <t xml:space="preserve">3.72319960594177</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.74973082542419</t>
+    <t xml:space="preserve">3.72320032119751</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.74973058700562</t>
   </si>
   <si>
     <t xml:space="preserve">3.80279350280762</t>
@@ -2456,10 +2456,10 @@
     <t xml:space="preserve">3.54632592201233</t>
   </si>
   <si>
-    <t xml:space="preserve">3.53748226165771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.57285714149475</t>
+    <t xml:space="preserve">3.53748202323914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.57285690307617</t>
   </si>
   <si>
     <t xml:space="preserve">3.5065290927887</t>
@@ -2468,73 +2468,73 @@
     <t xml:space="preserve">3.5905442237854</t>
   </si>
   <si>
-    <t xml:space="preserve">3.57727861404419</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.74530911445618</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.74088764190674</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.73204374313354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.70551252365112</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.7762622833252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.83816838264465</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.68340373039246</t>
+    <t xml:space="preserve">3.57727885246277</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.74530935287476</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.74088740348816</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.73204326629639</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.70551228523254</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.77626204490662</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.83816862106323</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.68340301513672</t>
   </si>
   <si>
     <t xml:space="preserve">3.76741862297058</t>
   </si>
   <si>
-    <t xml:space="preserve">3.78068423271179</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.76299667358398</t>
+    <t xml:space="preserve">3.78068375587463</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.76299691200256</t>
   </si>
   <si>
     <t xml:space="preserve">3.7718403339386</t>
   </si>
   <si>
-    <t xml:space="preserve">3.71877813339233</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.68782496452332</t>
+    <t xml:space="preserve">3.71877789497375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.68782520294189</t>
   </si>
   <si>
     <t xml:space="preserve">3.59938812255859</t>
   </si>
   <si>
-    <t xml:space="preserve">3.66571545600891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.70993447303772</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.78510570526123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.92660570144653</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.93987083435059</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.99735498428345</t>
+    <t xml:space="preserve">3.66571593284607</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.7099347114563</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.78510594367981</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.92660546302795</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.93987035751343</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.99735426902771</t>
   </si>
   <si>
     <t xml:space="preserve">4.01079893112183</t>
   </si>
   <si>
-    <t xml:space="preserve">4.09594440460205</t>
+    <t xml:space="preserve">4.09594392776489</t>
   </si>
   <si>
     <t xml:space="preserve">4.17212724685669</t>
@@ -2546,7 +2546,7 @@
     <t xml:space="preserve">4.13627576828003</t>
   </si>
   <si>
-    <t xml:space="preserve">4.19901466369629</t>
+    <t xml:space="preserve">4.19901514053345</t>
   </si>
   <si>
     <t xml:space="preserve">4.14075756072998</t>
@@ -2555,25 +2555,25 @@
     <t xml:space="preserve">4.10490703582764</t>
   </si>
   <si>
-    <t xml:space="preserve">4.06905555725098</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.03320503234863</t>
+    <t xml:space="preserve">4.06905603408813</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.03320550918579</t>
   </si>
   <si>
     <t xml:space="preserve">3.9794294834137</t>
   </si>
   <si>
-    <t xml:space="preserve">4.02872371673584</t>
+    <t xml:space="preserve">4.028724193573</t>
   </si>
   <si>
     <t xml:space="preserve">4.05561208724976</t>
   </si>
   <si>
-    <t xml:space="preserve">4.08698129653931</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.97494769096375</t>
+    <t xml:space="preserve">4.08698081970215</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.97494792938232</t>
   </si>
   <si>
     <t xml:space="preserve">4.00183629989624</t>
@@ -2582,25 +2582,25 @@
     <t xml:space="preserve">4.01528024673462</t>
   </si>
   <si>
-    <t xml:space="preserve">3.96150374412537</t>
+    <t xml:space="preserve">3.96150398254395</t>
   </si>
   <si>
     <t xml:space="preserve">3.9883918762207</t>
   </si>
   <si>
-    <t xml:space="preserve">3.95254135131836</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.96598553657532</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.04216861724854</t>
+    <t xml:space="preserve">3.95254111289978</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.96598505973816</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.04216814041138</t>
   </si>
   <si>
     <t xml:space="preserve">4.07801914215088</t>
   </si>
   <si>
-    <t xml:space="preserve">4.11835050582886</t>
+    <t xml:space="preserve">4.11835098266602</t>
   </si>
   <si>
     <t xml:space="preserve">4.17660808563232</t>
@@ -2612,82 +2612,82 @@
     <t xml:space="preserve">4.10938787460327</t>
   </si>
   <si>
-    <t xml:space="preserve">4.06009340286255</t>
+    <t xml:space="preserve">4.06009387969971</t>
   </si>
   <si>
     <t xml:space="preserve">4.1945333480835</t>
   </si>
   <si>
-    <t xml:space="preserve">4.21245908737183</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.14972019195557</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.12283182144165</t>
+    <t xml:space="preserve">4.21245861053467</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.14972066879272</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.12283229827881</t>
   </si>
   <si>
     <t xml:space="preserve">4.03768682479858</t>
   </si>
   <si>
-    <t xml:space="preserve">4.01976108551025</t>
+    <t xml:space="preserve">4.01976156234741</t>
   </si>
   <si>
     <t xml:space="preserve">4.06457471847534</t>
   </si>
   <si>
-    <t xml:space="preserve">4.20797777175903</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.23038387298584</t>
+    <t xml:space="preserve">4.20797729492188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.230384349823</t>
   </si>
   <si>
     <t xml:space="preserve">4.25727224349976</t>
   </si>
   <si>
-    <t xml:space="preserve">4.20349597930908</t>
+    <t xml:space="preserve">4.20349645614624</t>
   </si>
   <si>
     <t xml:space="preserve">3.92565321922302</t>
   </si>
   <si>
-    <t xml:space="preserve">3.90772771835327</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.88084006309509</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.87635850906372</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.80913805961609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.71503019332886</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.66573596000671</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.83154535293579</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.93461585044861</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.94357872009277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.04664945602417</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.99287366867065</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.98391103744507</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.02424240112305</t>
+    <t xml:space="preserve">3.90772795677185</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.88083958625793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.87635803222656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.80913829803467</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.71503043174744</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.66573572158813</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.83154511451721</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.93461608886719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.94357848167419</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.04664897918701</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.99287295341492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.98391079902649</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.02424287796021</t>
   </si>
   <si>
     <t xml:space="preserve">3.85395193099976</t>
@@ -2696,16 +2696,16 @@
     <t xml:space="preserve">3.93013501167297</t>
   </si>
   <si>
-    <t xml:space="preserve">3.97046637535095</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.10042572021484</t>
+    <t xml:space="preserve">3.97046589851379</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.10042524337769</t>
   </si>
   <si>
     <t xml:space="preserve">4.15420198440552</t>
   </si>
   <si>
-    <t xml:space="preserve">4.09146308898926</t>
+    <t xml:space="preserve">4.0914626121521</t>
   </si>
   <si>
     <t xml:space="preserve">4.22590351104736</t>
@@ -2714,31 +2714,31 @@
     <t xml:space="preserve">4.2662353515625</t>
   </si>
   <si>
-    <t xml:space="preserve">4.24382781982422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.13179492950439</t>
+    <t xml:space="preserve">4.24382877349854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.13179540634155</t>
   </si>
   <si>
     <t xml:space="preserve">4.1273136138916</t>
   </si>
   <si>
-    <t xml:space="preserve">4.24830913543701</t>
+    <t xml:space="preserve">4.24830961227417</t>
   </si>
   <si>
     <t xml:space="preserve">4.19005250930786</t>
   </si>
   <si>
-    <t xml:space="preserve">4.2931227684021</t>
+    <t xml:space="preserve">4.29312324523926</t>
   </si>
   <si>
     <t xml:space="preserve">4.40515661239624</t>
   </si>
   <si>
-    <t xml:space="preserve">4.43652582168579</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.48133897781372</t>
+    <t xml:space="preserve">4.43652534484863</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.48133945465088</t>
   </si>
   <si>
     <t xml:space="preserve">4.53511524200439</t>
@@ -2747,19 +2747,19 @@
     <t xml:space="preserve">4.55304098129272</t>
   </si>
   <si>
-    <t xml:space="preserve">4.56200361251831</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.50822782516479</t>
+    <t xml:space="preserve">4.56200313568115</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.50822734832764</t>
   </si>
   <si>
     <t xml:space="preserve">4.45445108413696</t>
   </si>
   <si>
-    <t xml:space="preserve">4.43204498291016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.49926519393921</t>
+    <t xml:space="preserve">4.432044506073</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.49926471710205</t>
   </si>
   <si>
     <t xml:space="preserve">4.49030208587646</t>
@@ -2768,22 +2768,22 @@
     <t xml:space="preserve">4.51718950271606</t>
   </si>
   <si>
-    <t xml:space="preserve">4.63370513916016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.59785461425781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.47685718536377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.57096576690674</t>
+    <t xml:space="preserve">4.633704662323</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.59785413742065</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.47685766220093</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.5709662437439</t>
   </si>
   <si>
     <t xml:space="preserve">4.61577939987183</t>
   </si>
   <si>
-    <t xml:space="preserve">4.64266729354858</t>
+    <t xml:space="preserve">4.64266681671143</t>
   </si>
   <si>
     <t xml:space="preserve">4.39171266555786</t>
@@ -2807,10 +2807,10 @@
     <t xml:space="preserve">4.71436929702759</t>
   </si>
   <si>
-    <t xml:space="preserve">4.75918245315552</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.76814556121826</t>
+    <t xml:space="preserve">4.75918197631836</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.7681450843811</t>
   </si>
   <si>
     <t xml:space="preserve">4.89362287521362</t>
@@ -2825,10 +2825,10 @@
     <t xml:space="preserve">5.05495071411133</t>
   </si>
   <si>
-    <t xml:space="preserve">5.01910018920898</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.14457702636719</t>
+    <t xml:space="preserve">5.01909971237183</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.14457750320435</t>
   </si>
   <si>
     <t xml:space="preserve">5.31486845016479</t>
@@ -2837,25 +2837,25 @@
     <t xml:space="preserve">5.37760734558105</t>
   </si>
   <si>
-    <t xml:space="preserve">5.35968208312988</t>
+    <t xml:space="preserve">5.35968160629272</t>
   </si>
   <si>
     <t xml:space="preserve">5.16250324249268</t>
   </si>
   <si>
-    <t xml:space="preserve">5.0459885597229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.15354061126709</t>
+    <t xml:space="preserve">5.04598808288574</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.15354013442993</t>
   </si>
   <si>
     <t xml:space="preserve">5.26109218597412</t>
   </si>
   <si>
-    <t xml:space="preserve">5.27901744842529</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.512047290802</t>
+    <t xml:space="preserve">5.27901697158813</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.51204776763916</t>
   </si>
   <si>
     <t xml:space="preserve">5.47619676589966</t>
@@ -2864,16 +2864,16 @@
     <t xml:space="preserve">5.50308465957642</t>
   </si>
   <si>
-    <t xml:space="preserve">5.29694271087646</t>
+    <t xml:space="preserve">5.29694318771362</t>
   </si>
   <si>
     <t xml:space="preserve">5.19835329055786</t>
   </si>
   <si>
-    <t xml:space="preserve">5.18042898178101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.0728759765625</t>
+    <t xml:space="preserve">5.18042850494385</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.07287549972534</t>
   </si>
   <si>
     <t xml:space="preserve">5.09080123901367</t>
@@ -2882,13 +2882,13 @@
     <t xml:space="preserve">4.99221229553223</t>
   </si>
   <si>
-    <t xml:space="preserve">4.75021934509277</t>
+    <t xml:space="preserve">4.75021982192993</t>
   </si>
   <si>
     <t xml:space="preserve">4.80399560928345</t>
   </si>
   <si>
-    <t xml:space="preserve">4.92947292327881</t>
+    <t xml:space="preserve">4.92947340011597</t>
   </si>
   <si>
     <t xml:space="preserve">4.83984661102295</t>
@@ -2903,22 +2903,22 @@
     <t xml:space="preserve">4.86673450469971</t>
   </si>
   <si>
-    <t xml:space="preserve">5.037024974823</t>
+    <t xml:space="preserve">5.03702592849731</t>
   </si>
   <si>
     <t xml:space="preserve">4.95636177062988</t>
   </si>
   <si>
-    <t xml:space="preserve">4.79503297805786</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.74125671386719</t>
+    <t xml:space="preserve">4.79503345489502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.74125719070435</t>
   </si>
   <si>
     <t xml:space="preserve">4.70540618896484</t>
   </si>
   <si>
-    <t xml:space="preserve">4.52615261077881</t>
+    <t xml:space="preserve">4.52615308761597</t>
   </si>
   <si>
     <t xml:space="preserve">4.41860055923462</t>
@@ -2927,13 +2927,13 @@
     <t xml:space="preserve">4.3648247718811</t>
   </si>
   <si>
-    <t xml:space="preserve">4.23934698104858</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.85777187347412</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.91154766082764</t>
+    <t xml:space="preserve">4.23934745788574</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.85777139663696</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.91154813766479</t>
   </si>
   <si>
     <t xml:space="preserve">4.96532392501831</t>
@@ -2945,25 +2945,25 @@
     <t xml:space="preserve">5.22524166107178</t>
   </si>
   <si>
-    <t xml:space="preserve">5.30590581893921</t>
+    <t xml:space="preserve">5.30590534210205</t>
   </si>
   <si>
     <t xml:space="preserve">5.42242050170898</t>
   </si>
   <si>
-    <t xml:space="preserve">5.28798055648804</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.43138313293457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.55686044692993</t>
+    <t xml:space="preserve">5.28798007965088</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.43138360977173</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.55686092376709</t>
   </si>
   <si>
     <t xml:space="preserve">5.62856245040894</t>
   </si>
   <si>
-    <t xml:space="preserve">5.52100992202759</t>
+    <t xml:space="preserve">5.52100944519043</t>
   </si>
   <si>
     <t xml:space="preserve">5.61959934234619</t>
@@ -2975,7 +2975,7 @@
     <t xml:space="preserve">5.37441253662109</t>
   </si>
   <si>
-    <t xml:space="preserve">5.47495365142822</t>
+    <t xml:space="preserve">5.47495412826538</t>
   </si>
   <si>
     <t xml:space="preserve">5.46581411361694</t>
@@ -2984,16 +2984,16 @@
     <t xml:space="preserve">5.48409461975098</t>
   </si>
   <si>
-    <t xml:space="preserve">5.63947677612305</t>
+    <t xml:space="preserve">5.63947725296021</t>
   </si>
   <si>
     <t xml:space="preserve">5.75829935073853</t>
   </si>
   <si>
-    <t xml:space="preserve">5.80399942398071</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.65775775909424</t>
+    <t xml:space="preserve">5.80399990081787</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.65775728225708</t>
   </si>
   <si>
     <t xml:space="preserve">5.62119674682617</t>
@@ -3002,25 +3002,25 @@
     <t xml:space="preserve">5.410973072052</t>
   </si>
   <si>
-    <t xml:space="preserve">5.40183258056641</t>
+    <t xml:space="preserve">5.40183305740356</t>
   </si>
   <si>
     <t xml:space="preserve">5.63033676147461</t>
   </si>
   <si>
-    <t xml:space="preserve">5.61205673217773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.8222804069519</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.84056091308594</t>
+    <t xml:space="preserve">5.61205625534058</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.82227993011475</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.84056043624878</t>
   </si>
   <si>
     <t xml:space="preserve">5.88626146316528</t>
   </si>
   <si>
-    <t xml:space="preserve">5.93196153640747</t>
+    <t xml:space="preserve">5.93196201324463</t>
   </si>
   <si>
     <t xml:space="preserve">5.90454149246216</t>
@@ -3050,13 +3050,13 @@
     <t xml:space="preserve">5.785719871521</t>
   </si>
   <si>
-    <t xml:space="preserve">5.7308783531189</t>
+    <t xml:space="preserve">5.73087882995605</t>
   </si>
   <si>
     <t xml:space="preserve">5.67603778839111</t>
   </si>
   <si>
-    <t xml:space="preserve">5.69431781768799</t>
+    <t xml:space="preserve">5.69431829452515</t>
   </si>
   <si>
     <t xml:space="preserve">5.66689729690552</t>
@@ -3068,16 +3068,16 @@
     <t xml:space="preserve">5.42011308670044</t>
   </si>
   <si>
-    <t xml:space="preserve">5.33785200119019</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.20988941192627</t>
+    <t xml:space="preserve">5.33785152435303</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.20988988876343</t>
   </si>
   <si>
     <t xml:space="preserve">5.34699201583862</t>
   </si>
   <si>
-    <t xml:space="preserve">5.31043148040771</t>
+    <t xml:space="preserve">5.31043100357056</t>
   </si>
   <si>
     <t xml:space="preserve">5.39269304275513</t>
@@ -3101,7 +3101,7 @@
     <t xml:space="preserve">5.10020780563354</t>
   </si>
   <si>
-    <t xml:space="preserve">5.10934782028198</t>
+    <t xml:space="preserve">5.10934829711914</t>
   </si>
   <si>
     <t xml:space="preserve">5.08192729949951</t>
@@ -3113,25 +3113,25 @@
     <t xml:space="preserve">5.01794624328613</t>
   </si>
   <si>
-    <t xml:space="preserve">5.11848831176758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.13676786422729</t>
+    <t xml:space="preserve">5.11848783493042</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.13676834106445</t>
   </si>
   <si>
     <t xml:space="preserve">5.07278728485107</t>
   </si>
   <si>
-    <t xml:space="preserve">5.02708625793457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.0453667640686</t>
+    <t xml:space="preserve">5.02708673477173</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.04536628723145</t>
   </si>
   <si>
     <t xml:space="preserve">4.99052619934082</t>
   </si>
   <si>
-    <t xml:space="preserve">5.00880575180054</t>
+    <t xml:space="preserve">5.00880670547485</t>
   </si>
   <si>
     <t xml:space="preserve">5.0545072555542</t>
@@ -3143,7 +3143,7 @@
     <t xml:space="preserve">5.16418886184692</t>
   </si>
   <si>
-    <t xml:space="preserve">5.14590930938721</t>
+    <t xml:space="preserve">5.14590835571289</t>
   </si>
   <si>
     <t xml:space="preserve">4.94482469558716</t>
@@ -3155,19 +3155,19 @@
     <t xml:space="preserve">4.89912414550781</t>
   </si>
   <si>
-    <t xml:space="preserve">4.8808445930481</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.85342359542847</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.82600355148315</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.73460102081299</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.75288200378418</t>
+    <t xml:space="preserve">4.88084411621094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.85342311859131</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.826003074646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.73460149765015</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.75288152694702</t>
   </si>
   <si>
     <t xml:space="preserve">4.69804096221924</t>
@@ -3176,16 +3176,16 @@
     <t xml:space="preserve">4.57921886444092</t>
   </si>
   <si>
-    <t xml:space="preserve">4.71632146835327</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.67975997924805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.84428310394287</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.80772304534912</t>
+    <t xml:space="preserve">4.71632099151611</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.67976045608521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.84428358078003</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.80772256851196</t>
   </si>
   <si>
     <t xml:space="preserve">4.57007837295532</t>
@@ -3197,7 +3197,7 @@
     <t xml:space="preserve">4.6889009475708</t>
   </si>
   <si>
-    <t xml:space="preserve">4.67062044143677</t>
+    <t xml:space="preserve">4.67062091827393</t>
   </si>
   <si>
     <t xml:space="preserve">4.6431999206543</t>
@@ -3206,10 +3206,10 @@
     <t xml:space="preserve">4.63405990600586</t>
   </si>
   <si>
-    <t xml:space="preserve">4.56093835830688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.58835935592651</t>
+    <t xml:space="preserve">4.56093788146973</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.58835887908936</t>
   </si>
   <si>
     <t xml:space="preserve">4.55179834365845</t>
@@ -3218,7 +3218,7 @@
     <t xml:space="preserve">4.48781728744507</t>
   </si>
   <si>
-    <t xml:space="preserve">4.53808832168579</t>
+    <t xml:space="preserve">4.53808784484863</t>
   </si>
   <si>
     <t xml:space="preserve">4.46953678131104</t>
@@ -3227,418 +3227,421 @@
     <t xml:space="preserve">4.50152778625488</t>
   </si>
   <si>
-    <t xml:space="preserve">4.49695730209351</t>
+    <t xml:space="preserve">4.49695777893066</t>
   </si>
   <si>
     <t xml:space="preserve">4.40555620193481</t>
   </si>
   <si>
+    <t xml:space="preserve">4.43297672271729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.45582723617554</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.36899518966675</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.29130363464355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.20447254180908</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.47867774963379</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.48324728012085</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.79858207702637</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.87170362472534</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.83514308929443</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.17332887649536</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.32871150970459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.19160890579224</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.25559091567993</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.38355207443237</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.97224569320679</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.18246936798096</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.81686305999756</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.9996657371521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.96310567855835</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.09106731414795</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.98138570785522</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.92654466629028</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.06364727020264</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.30129146575928</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.20074987411499</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.12762832641602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.23730993270874</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.27387094497681</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.31957149505615</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.27241277694702</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.23468494415283</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.25354862213135</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.02718353271484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.99888849258423</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.01775217056274</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.16866207122803</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.1403660774231</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.18752527236938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.24411678314209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.35729885101318</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.39502620697021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.30070781707764</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.32900333404541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.1969575881958</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.26298046112061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.37616300582886</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.17809295654297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.21582126617432</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.10263824462891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.14979839324951</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.09320688247681</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.12150239944458</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.07434320449829</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.03661584854126</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.06491136550903</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.95172882080078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.93286514282227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.89513778686523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.91400146484375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.90456914901733</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.77252340316772</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.76309156417847</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.72536420822144</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.9611611366272</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.8574104309082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.8008189201355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.51786327362061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.50843143463135</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.55559015274048</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.54615879058838</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.6216139793396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.54144287109375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.56502246856689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.52729511260986</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.56030654907227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.47541952133179</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.47070360183716</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.4848518371582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.45655584335327</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.59331798553467</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.50371503829956</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.51314687728882</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.63576126098633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.65934085845947</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.62632942199707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.64519357681274</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.67820453643799</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.71593236923218</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.6310453414917</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.69706869125366</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.71121597290039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.73479604721069</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.60274982452393</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.57445430755615</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.42354488372803</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.37638473510742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.34337377548218</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.41411256790161</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.3952488899231</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.4942831993103</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.44712448120117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.38110113143921</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.36695337295532</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.33865737915039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.26320266723633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.28206634521484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.32922601699829</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.3245096206665</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.31036233901978</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.28678226470947</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.27263498306274</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.2349066734314</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.1122932434082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.0887131690979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.0557017326355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.10757684707642</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.03683805465698</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.86234831809998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.00854253768921</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.99910998344421</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.07456541061401</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.10286092758179</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.13587284088135</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.2254753112793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.15473651885986</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.18303155899048</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.27735042572021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.29149866104126</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.45183944702148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.22075939178467</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.24905490875244</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.26791906356812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.39053297042847</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.37166976928711</t>
+  </si>
+  <si>
     <t xml:space="preserve">4.43297624588013</t>
   </si>
   <si>
-    <t xml:space="preserve">4.45582628250122</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.36899518966675</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.29130411148071</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.20447206497192</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.47867727279663</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.48324728012085</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.79858255386353</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.87170362472534</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.83514308929443</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.17332887649536</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.32871150970459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.19160890579224</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.25559091567993</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.38355255126953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.97224569320679</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.18246936798096</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.81686305999756</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.9996657371521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.96310520172119</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.09106779098511</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.98138570785522</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.92654466629028</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.06364727020264</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.30129098892212</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.20074987411499</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.12762832641602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.23730993270874</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.27387046813965</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.31957197189331</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.27241230010986</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.23468494415283</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.25354862213135</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.02718353271484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.99888801574707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.01775217056274</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.16866159439087</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.1403660774231</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.18752527236938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.24411678314209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.35729885101318</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.39502620697021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.30070781707764</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.32900333404541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.1969575881958</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.26298046112061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.3761625289917</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.17809343338013</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.21582126617432</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.10263824462891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.14979791641235</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.09320688247681</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.12150239944458</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.07434320449829</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.03661584854126</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.06491088867188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.95172882080078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.93286514282227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.89513778686523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.91400146484375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.90456962585449</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.77252340316772</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.76309156417847</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.72536420822144</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.96116065979004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.85740995407104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.80081939697266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.51786279678345</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.50843143463135</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.55559015274048</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.54615879058838</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.62161350250244</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.54144287109375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.56502246856689</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.52729511260986</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.56030654907227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.47541999816895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.47070360183716</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.4848518371582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.45655584335327</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.59331798553467</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.50371503829956</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.51314735412598</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.63576126098633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.65934085845947</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.62632989883423</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.64519357681274</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.67820501327515</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.71593236923218</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.6310453414917</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.69706869125366</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.71121597290039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.73479604721069</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.60275030136108</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.57445430755615</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.42354488372803</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.37638473510742</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.34337377548218</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.41411209106445</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.3952488899231</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.4942831993103</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.44712448120117</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.38110113143921</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.36695337295532</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.33865737915039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.26320266723633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.28206634521484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.32922601699829</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.3245096206665</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.31036233901978</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.28678226470947</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.27263498306274</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.23490715026855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.11229276657104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.0887131690979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.05570220947266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.10757732391357</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.03683805465698</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.86234855651855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.00854206085205</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.99911022186279</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.07456541061401</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.10286092758179</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.13587284088135</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.2254753112793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.15473651885986</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.18303203582764</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.27735042572021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.29149866104126</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.45183944702148</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.22075939178467</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.24905490875244</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.26791858673096</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.39053297042847</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.37166976928711</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.35752153396606</t>
+    <t xml:space="preserve">4.35752105712891</t>
   </si>
   <si>
     <t xml:space="preserve">4.35280513763428</t>
@@ -3674,19 +3677,19 @@
     <t xml:space="preserve">4.23962306976318</t>
   </si>
   <si>
-    <t xml:space="preserve">4.20189571380615</t>
+    <t xml:space="preserve">4.20189523696899</t>
   </si>
   <si>
     <t xml:space="preserve">4.12644052505493</t>
   </si>
   <si>
-    <t xml:space="preserve">4.02268981933594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.15002059936523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.92837166786194</t>
+    <t xml:space="preserve">4.0226902961731</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.15002012252808</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.92837142944336</t>
   </si>
   <si>
     <t xml:space="preserve">4.04626989364624</t>
@@ -3695,16 +3698,16 @@
     <t xml:space="preserve">3.96138286590576</t>
   </si>
   <si>
-    <t xml:space="preserve">4.06041717529297</t>
+    <t xml:space="preserve">4.06041765213013</t>
   </si>
   <si>
     <t xml:space="preserve">4.01797485351562</t>
   </si>
   <si>
-    <t xml:space="preserve">3.90007638931274</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.94251894950867</t>
+    <t xml:space="preserve">3.90007615089417</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.94251942634583</t>
   </si>
   <si>
     <t xml:space="preserve">3.89535999298096</t>
@@ -3722,7 +3725,7 @@
     <t xml:space="preserve">3.88121199607849</t>
   </si>
   <si>
-    <t xml:space="preserve">3.84348464012146</t>
+    <t xml:space="preserve">3.84348440170288</t>
   </si>
   <si>
     <t xml:space="preserve">3.81990528106689</t>
@@ -3740,10 +3743,10 @@
     <t xml:space="preserve">3.75388216972351</t>
   </si>
   <si>
-    <t xml:space="preserve">3.72558641433716</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.76331377029419</t>
+    <t xml:space="preserve">3.72558665275574</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.76331400871277</t>
   </si>
   <si>
     <t xml:space="preserve">3.735018491745</t>
@@ -3752,7 +3755,7 @@
     <t xml:space="preserve">3.71615481376648</t>
   </si>
   <si>
-    <t xml:space="preserve">3.58410859107971</t>
+    <t xml:space="preserve">3.58410835266113</t>
   </si>
   <si>
     <t xml:space="preserve">3.76442790031433</t>
@@ -57580,7 +57583,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G2030" t="s">
-        <v>1073</v>
+        <v>1208</v>
       </c>
       <c r="H2030" t="s">
         <v>9</v>
@@ -57606,7 +57609,7 @@
         <v>4.61999988555908</v>
       </c>
       <c r="G2031" t="s">
-        <v>1208</v>
+        <v>1209</v>
       </c>
       <c r="H2031" t="s">
         <v>9</v>
@@ -57658,7 +57661,7 @@
         <v>4.61999988555908</v>
       </c>
       <c r="G2033" t="s">
-        <v>1208</v>
+        <v>1209</v>
       </c>
       <c r="H2033" t="s">
         <v>9</v>
@@ -57788,7 +57791,7 @@
         <v>4.61499977111816</v>
       </c>
       <c r="G2038" t="s">
-        <v>1209</v>
+        <v>1210</v>
       </c>
       <c r="H2038" t="s">
         <v>9</v>
@@ -57814,7 +57817,7 @@
         <v>4.55499982833862</v>
       </c>
       <c r="G2039" t="s">
-        <v>1210</v>
+        <v>1211</v>
       </c>
       <c r="H2039" t="s">
         <v>9</v>
@@ -57840,7 +57843,7 @@
         <v>4.88500022888184</v>
       </c>
       <c r="G2040" t="s">
-        <v>1211</v>
+        <v>1212</v>
       </c>
       <c r="H2040" t="s">
         <v>9</v>
@@ -57892,7 +57895,7 @@
         <v>4.75</v>
       </c>
       <c r="G2042" t="s">
-        <v>1212</v>
+        <v>1213</v>
       </c>
       <c r="H2042" t="s">
         <v>9</v>
@@ -57944,7 +57947,7 @@
         <v>4.75</v>
       </c>
       <c r="G2044" t="s">
-        <v>1212</v>
+        <v>1213</v>
       </c>
       <c r="H2044" t="s">
         <v>9</v>
@@ -58022,7 +58025,7 @@
         <v>4.76999998092651</v>
       </c>
       <c r="G2047" t="s">
-        <v>1213</v>
+        <v>1214</v>
       </c>
       <c r="H2047" t="s">
         <v>9</v>
@@ -58048,7 +58051,7 @@
         <v>4.67000007629395</v>
       </c>
       <c r="G2048" t="s">
-        <v>1214</v>
+        <v>1215</v>
       </c>
       <c r="H2048" t="s">
         <v>9</v>
@@ -58074,7 +58077,7 @@
         <v>4.71000003814697</v>
       </c>
       <c r="G2049" t="s">
-        <v>1215</v>
+        <v>1216</v>
       </c>
       <c r="H2049" t="s">
         <v>9</v>
@@ -58126,7 +58129,7 @@
         <v>4.55999994277954</v>
       </c>
       <c r="G2051" t="s">
-        <v>1216</v>
+        <v>1217</v>
       </c>
       <c r="H2051" t="s">
         <v>9</v>
@@ -58438,7 +58441,7 @@
         <v>4.5</v>
       </c>
       <c r="G2063" t="s">
-        <v>1217</v>
+        <v>1218</v>
       </c>
       <c r="H2063" t="s">
         <v>9</v>
@@ -58464,7 +58467,7 @@
         <v>4.6100001335144</v>
       </c>
       <c r="G2064" t="s">
-        <v>1218</v>
+        <v>1219</v>
       </c>
       <c r="H2064" t="s">
         <v>9</v>
@@ -58516,7 +58519,7 @@
         <v>4.61999988555908</v>
       </c>
       <c r="G2066" t="s">
-        <v>1208</v>
+        <v>1209</v>
       </c>
       <c r="H2066" t="s">
         <v>9</v>
@@ -58542,7 +58545,7 @@
         <v>4.5</v>
       </c>
       <c r="G2067" t="s">
-        <v>1217</v>
+        <v>1218</v>
       </c>
       <c r="H2067" t="s">
         <v>9</v>
@@ -58568,7 +58571,7 @@
         <v>4.49499988555908</v>
       </c>
       <c r="G2068" t="s">
-        <v>1219</v>
+        <v>1220</v>
       </c>
       <c r="H2068" t="s">
         <v>9</v>
@@ -58646,7 +58649,7 @@
         <v>4.45499992370605</v>
       </c>
       <c r="G2071" t="s">
-        <v>1220</v>
+        <v>1221</v>
       </c>
       <c r="H2071" t="s">
         <v>9</v>
@@ -58672,7 +58675,7 @@
         <v>4.375</v>
       </c>
       <c r="G2072" t="s">
-        <v>1221</v>
+        <v>1222</v>
       </c>
       <c r="H2072" t="s">
         <v>9</v>
@@ -58698,7 +58701,7 @@
         <v>4.2649998664856</v>
       </c>
       <c r="G2073" t="s">
-        <v>1222</v>
+        <v>1223</v>
       </c>
       <c r="H2073" t="s">
         <v>9</v>
@@ -58750,7 +58753,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G2075" t="s">
-        <v>1223</v>
+        <v>1224</v>
       </c>
       <c r="H2075" t="s">
         <v>9</v>
@@ -58854,7 +58857,7 @@
         <v>4.16499996185303</v>
       </c>
       <c r="G2079" t="s">
-        <v>1224</v>
+        <v>1225</v>
       </c>
       <c r="H2079" t="s">
         <v>9</v>
@@ -58906,7 +58909,7 @@
         <v>4.28999996185303</v>
       </c>
       <c r="G2081" t="s">
-        <v>1225</v>
+        <v>1226</v>
       </c>
       <c r="H2081" t="s">
         <v>9</v>
@@ -58932,7 +58935,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G2082" t="s">
-        <v>1226</v>
+        <v>1227</v>
       </c>
       <c r="H2082" t="s">
         <v>9</v>
@@ -59010,7 +59013,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G2085" t="s">
-        <v>1226</v>
+        <v>1227</v>
       </c>
       <c r="H2085" t="s">
         <v>9</v>
@@ -59036,7 +59039,7 @@
         <v>4.2649998664856</v>
       </c>
       <c r="G2086" t="s">
-        <v>1222</v>
+        <v>1223</v>
       </c>
       <c r="H2086" t="s">
         <v>9</v>
@@ -59088,7 +59091,7 @@
         <v>4.30499982833862</v>
       </c>
       <c r="G2088" t="s">
-        <v>1227</v>
+        <v>1228</v>
       </c>
       <c r="H2088" t="s">
         <v>9</v>
@@ -59114,7 +59117,7 @@
         <v>4.26000022888184</v>
       </c>
       <c r="G2089" t="s">
-        <v>1228</v>
+        <v>1229</v>
       </c>
       <c r="H2089" t="s">
         <v>9</v>
@@ -59140,7 +59143,7 @@
         <v>4.13500022888184</v>
       </c>
       <c r="G2090" t="s">
-        <v>1229</v>
+        <v>1230</v>
       </c>
       <c r="H2090" t="s">
         <v>9</v>
@@ -59166,7 +59169,7 @@
         <v>4.17999982833862</v>
       </c>
       <c r="G2091" t="s">
-        <v>1230</v>
+        <v>1231</v>
       </c>
       <c r="H2091" t="s">
         <v>9</v>
@@ -59192,7 +59195,7 @@
         <v>4.13000011444092</v>
       </c>
       <c r="G2092" t="s">
-        <v>1231</v>
+        <v>1232</v>
       </c>
       <c r="H2092" t="s">
         <v>9</v>
@@ -59218,7 +59221,7 @@
         <v>4.11999988555908</v>
       </c>
       <c r="G2093" t="s">
-        <v>1232</v>
+        <v>1233</v>
       </c>
       <c r="H2093" t="s">
         <v>9</v>
@@ -59244,7 +59247,7 @@
         <v>4.15500020980835</v>
       </c>
       <c r="G2094" t="s">
-        <v>1233</v>
+        <v>1234</v>
       </c>
       <c r="H2094" t="s">
         <v>9</v>
@@ -59270,7 +59273,7 @@
         <v>4.15500020980835</v>
       </c>
       <c r="G2095" t="s">
-        <v>1233</v>
+        <v>1234</v>
       </c>
       <c r="H2095" t="s">
         <v>9</v>
@@ -59296,7 +59299,7 @@
         <v>4.11999988555908</v>
       </c>
       <c r="G2096" t="s">
-        <v>1232</v>
+        <v>1233</v>
       </c>
       <c r="H2096" t="s">
         <v>9</v>
@@ -59322,7 +59325,7 @@
         <v>4.1399998664856</v>
       </c>
       <c r="G2097" t="s">
-        <v>1234</v>
+        <v>1235</v>
       </c>
       <c r="H2097" t="s">
         <v>9</v>
@@ -59348,7 +59351,7 @@
         <v>4.11499977111816</v>
       </c>
       <c r="G2098" t="s">
-        <v>1235</v>
+        <v>1236</v>
       </c>
       <c r="H2098" t="s">
         <v>9</v>
@@ -59374,7 +59377,7 @@
         <v>4.07499980926514</v>
       </c>
       <c r="G2099" t="s">
-        <v>1236</v>
+        <v>1237</v>
       </c>
       <c r="H2099" t="s">
         <v>9</v>
@@ -59400,7 +59403,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G2100" t="s">
-        <v>1237</v>
+        <v>1238</v>
       </c>
       <c r="H2100" t="s">
         <v>9</v>
@@ -59426,7 +59429,7 @@
         <v>4.01000022888184</v>
       </c>
       <c r="G2101" t="s">
-        <v>1238</v>
+        <v>1239</v>
       </c>
       <c r="H2101" t="s">
         <v>9</v>
@@ -59452,7 +59455,7 @@
         <v>3.9300000667572</v>
       </c>
       <c r="G2102" t="s">
-        <v>1239</v>
+        <v>1240</v>
       </c>
       <c r="H2102" t="s">
         <v>9</v>
@@ -59478,7 +59481,7 @@
         <v>3.97000002861023</v>
       </c>
       <c r="G2103" t="s">
-        <v>1240</v>
+        <v>1241</v>
       </c>
       <c r="H2103" t="s">
         <v>9</v>
@@ -59504,7 +59507,7 @@
         <v>3.98000001907349</v>
       </c>
       <c r="G2104" t="s">
-        <v>1241</v>
+        <v>1242</v>
       </c>
       <c r="H2104" t="s">
         <v>9</v>
@@ -59530,7 +59533,7 @@
         <v>3.95000004768372</v>
       </c>
       <c r="G2105" t="s">
-        <v>1242</v>
+        <v>1243</v>
       </c>
       <c r="H2105" t="s">
         <v>9</v>
@@ -59556,7 +59559,7 @@
         <v>3.99000000953674</v>
       </c>
       <c r="G2106" t="s">
-        <v>1243</v>
+        <v>1244</v>
       </c>
       <c r="H2106" t="s">
         <v>9</v>
@@ -59582,7 +59585,7 @@
         <v>3.96000003814697</v>
       </c>
       <c r="G2107" t="s">
-        <v>1244</v>
+        <v>1245</v>
       </c>
       <c r="H2107" t="s">
         <v>9</v>
@@ -59608,7 +59611,7 @@
         <v>3.94000005722046</v>
       </c>
       <c r="G2108" t="s">
-        <v>1245</v>
+        <v>1246</v>
       </c>
       <c r="H2108" t="s">
         <v>9</v>
@@ -59634,7 +59637,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G2109" t="s">
-        <v>1246</v>
+        <v>1247</v>
       </c>
       <c r="H2109" t="s">
         <v>9</v>
@@ -59660,7 +59663,7 @@
         <v>3.9300000667572</v>
       </c>
       <c r="G2110" t="s">
-        <v>1239</v>
+        <v>1240</v>
       </c>
       <c r="H2110" t="s">
         <v>9</v>
@@ -59686,7 +59689,7 @@
         <v>3.97000002861023</v>
       </c>
       <c r="G2111" t="s">
-        <v>1240</v>
+        <v>1241</v>
       </c>
       <c r="H2111" t="s">
         <v>9</v>
@@ -59712,7 +59715,7 @@
         <v>3.94000005722046</v>
       </c>
       <c r="G2112" t="s">
-        <v>1245</v>
+        <v>1246</v>
       </c>
       <c r="H2112" t="s">
         <v>9</v>
@@ -59738,7 +59741,7 @@
         <v>3.96000003814697</v>
       </c>
       <c r="G2113" t="s">
-        <v>1244</v>
+        <v>1245</v>
       </c>
       <c r="H2113" t="s">
         <v>9</v>
@@ -59764,7 +59767,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G2114" t="s">
-        <v>1247</v>
+        <v>1248</v>
       </c>
       <c r="H2114" t="s">
         <v>9</v>
@@ -59790,7 +59793,7 @@
         <v>3.82999992370605</v>
       </c>
       <c r="G2115" t="s">
-        <v>1248</v>
+        <v>1249</v>
       </c>
       <c r="H2115" t="s">
         <v>9</v>
@@ -59816,7 +59819,7 @@
         <v>3.78999996185303</v>
       </c>
       <c r="G2116" t="s">
-        <v>1249</v>
+        <v>1250</v>
       </c>
       <c r="H2116" t="s">
         <v>9</v>
@@ -59842,7 +59845,7 @@
         <v>3.80999994277954</v>
       </c>
       <c r="G2117" t="s">
-        <v>1244</v>
+        <v>1245</v>
       </c>
       <c r="H2117" t="s">
         <v>9</v>
@@ -59868,7 +59871,7 @@
         <v>3.84999990463257</v>
       </c>
       <c r="G2118" t="s">
-        <v>1250</v>
+        <v>1251</v>
       </c>
       <c r="H2118" t="s">
         <v>9</v>
@@ -59894,7 +59897,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G2119" t="s">
-        <v>1247</v>
+        <v>1248</v>
       </c>
       <c r="H2119" t="s">
         <v>9</v>
@@ -59920,7 +59923,7 @@
         <v>3.82999992370605</v>
       </c>
       <c r="G2120" t="s">
-        <v>1248</v>
+        <v>1249</v>
       </c>
       <c r="H2120" t="s">
         <v>9</v>
@@ -59946,7 +59949,7 @@
         <v>3.84999990463257</v>
       </c>
       <c r="G2121" t="s">
-        <v>1250</v>
+        <v>1251</v>
       </c>
       <c r="H2121" t="s">
         <v>9</v>
@@ -59972,7 +59975,7 @@
         <v>3.78999996185303</v>
       </c>
       <c r="G2122" t="s">
-        <v>1249</v>
+        <v>1250</v>
       </c>
       <c r="H2122" t="s">
         <v>9</v>
@@ -59998,7 +60001,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G2123" t="s">
-        <v>1251</v>
+        <v>1252</v>
       </c>
       <c r="H2123" t="s">
         <v>9</v>
@@ -60024,7 +60027,7 @@
         <v>3.76999998092651</v>
       </c>
       <c r="G2124" t="s">
-        <v>1252</v>
+        <v>1253</v>
       </c>
       <c r="H2124" t="s">
         <v>9</v>
@@ -60050,7 +60053,7 @@
         <v>3.78999996185303</v>
       </c>
       <c r="G2125" t="s">
-        <v>1249</v>
+        <v>1250</v>
       </c>
       <c r="H2125" t="s">
         <v>9</v>
@@ -60076,7 +60079,7 @@
         <v>3.75</v>
       </c>
       <c r="G2126" t="s">
-        <v>1253</v>
+        <v>1254</v>
       </c>
       <c r="H2126" t="s">
         <v>9</v>
@@ -60102,7 +60105,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G2127" t="s">
-        <v>1254</v>
+        <v>1255</v>
       </c>
       <c r="H2127" t="s">
         <v>9</v>
@@ -60128,7 +60131,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G2128" t="s">
-        <v>1255</v>
+        <v>1256</v>
       </c>
       <c r="H2128" t="s">
         <v>9</v>
@@ -60154,7 +60157,7 @@
         <v>3.67000007629395</v>
       </c>
       <c r="G2129" t="s">
-        <v>1256</v>
+        <v>1257</v>
       </c>
       <c r="H2129" t="s">
         <v>9</v>
@@ -60180,7 +60183,7 @@
         <v>3.67000007629395</v>
       </c>
       <c r="G2130" t="s">
-        <v>1256</v>
+        <v>1257</v>
       </c>
       <c r="H2130" t="s">
         <v>9</v>
@@ -60206,7 +60209,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G2131" t="s">
-        <v>1255</v>
+        <v>1256</v>
       </c>
       <c r="H2131" t="s">
         <v>9</v>
@@ -60232,7 +60235,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G2132" t="s">
-        <v>1257</v>
+        <v>1258</v>
       </c>
       <c r="H2132" t="s">
         <v>9</v>
@@ -60258,7 +60261,7 @@
         <v>3.75</v>
       </c>
       <c r="G2133" t="s">
-        <v>1253</v>
+        <v>1254</v>
       </c>
       <c r="H2133" t="s">
         <v>9</v>
@@ -60284,7 +60287,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G2134" t="s">
-        <v>1255</v>
+        <v>1256</v>
       </c>
       <c r="H2134" t="s">
         <v>9</v>
@@ -60310,7 +60313,7 @@
         <v>3.76999998092651</v>
       </c>
       <c r="G2135" t="s">
-        <v>1252</v>
+        <v>1253</v>
       </c>
       <c r="H2135" t="s">
         <v>9</v>
@@ -60336,7 +60339,7 @@
         <v>3.71000003814697</v>
       </c>
       <c r="G2136" t="s">
-        <v>1258</v>
+        <v>1259</v>
       </c>
       <c r="H2136" t="s">
         <v>9</v>
@@ -60362,7 +60365,7 @@
         <v>3.69000005722046</v>
       </c>
       <c r="G2137" t="s">
-        <v>1259</v>
+        <v>1260</v>
       </c>
       <c r="H2137" t="s">
         <v>9</v>
@@ -60388,7 +60391,7 @@
         <v>3.69000005722046</v>
       </c>
       <c r="G2138" t="s">
-        <v>1259</v>
+        <v>1260</v>
       </c>
       <c r="H2138" t="s">
         <v>9</v>
@@ -60414,7 +60417,7 @@
         <v>3.69000005722046</v>
       </c>
       <c r="G2139" t="s">
-        <v>1259</v>
+        <v>1260</v>
       </c>
       <c r="H2139" t="s">
         <v>9</v>
@@ -60440,7 +60443,7 @@
         <v>3.69000005722046</v>
       </c>
       <c r="G2140" t="s">
-        <v>1259</v>
+        <v>1260</v>
       </c>
       <c r="H2140" t="s">
         <v>9</v>
@@ -60466,7 +60469,7 @@
         <v>3.66000008583069</v>
       </c>
       <c r="G2141" t="s">
-        <v>1260</v>
+        <v>1261</v>
       </c>
       <c r="H2141" t="s">
         <v>9</v>
@@ -60492,7 +60495,7 @@
         <v>3.65000009536743</v>
       </c>
       <c r="G2142" t="s">
-        <v>1261</v>
+        <v>1262</v>
       </c>
       <c r="H2142" t="s">
         <v>9</v>
@@ -60518,7 +60521,7 @@
         <v>3.73000001907349</v>
       </c>
       <c r="G2143" t="s">
-        <v>1262</v>
+        <v>1263</v>
       </c>
       <c r="H2143" t="s">
         <v>9</v>
@@ -60544,7 +60547,7 @@
         <v>3.69000005722046</v>
       </c>
       <c r="G2144" t="s">
-        <v>1259</v>
+        <v>1260</v>
       </c>
       <c r="H2144" t="s">
         <v>9</v>
@@ -60570,7 +60573,7 @@
         <v>3.66000008583069</v>
       </c>
       <c r="G2145" t="s">
-        <v>1260</v>
+        <v>1261</v>
       </c>
       <c r="H2145" t="s">
         <v>9</v>
@@ -60596,7 +60599,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G2146" t="s">
-        <v>1263</v>
+        <v>1264</v>
       </c>
       <c r="H2146" t="s">
         <v>9</v>
@@ -60622,7 +60625,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G2147" t="s">
-        <v>1255</v>
+        <v>1256</v>
       </c>
       <c r="H2147" t="s">
         <v>9</v>
@@ -60648,7 +60651,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G2148" t="s">
-        <v>1255</v>
+        <v>1256</v>
       </c>
       <c r="H2148" t="s">
         <v>9</v>
@@ -60674,7 +60677,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G2149" t="s">
-        <v>1255</v>
+        <v>1256</v>
       </c>
       <c r="H2149" t="s">
         <v>9</v>
@@ -60700,7 +60703,7 @@
         <v>3.69000005722046</v>
       </c>
       <c r="G2150" t="s">
-        <v>1259</v>
+        <v>1260</v>
       </c>
       <c r="H2150" t="s">
         <v>9</v>
@@ -60726,7 +60729,7 @@
         <v>3.66000008583069</v>
       </c>
       <c r="G2151" t="s">
-        <v>1260</v>
+        <v>1261</v>
       </c>
       <c r="H2151" t="s">
         <v>9</v>
@@ -60752,7 +60755,7 @@
         <v>3.69000005722046</v>
       </c>
       <c r="G2152" t="s">
-        <v>1259</v>
+        <v>1260</v>
       </c>
       <c r="H2152" t="s">
         <v>9</v>
@@ -60778,7 +60781,7 @@
         <v>3.64000010490417</v>
       </c>
       <c r="G2153" t="s">
-        <v>1264</v>
+        <v>1265</v>
       </c>
       <c r="H2153" t="s">
         <v>9</v>
@@ -60804,7 +60807,7 @@
         <v>3.66000008583069</v>
       </c>
       <c r="G2154" t="s">
-        <v>1260</v>
+        <v>1261</v>
       </c>
       <c r="H2154" t="s">
         <v>9</v>
@@ -60830,7 +60833,7 @@
         <v>3.63000011444092</v>
       </c>
       <c r="G2155" t="s">
-        <v>1265</v>
+        <v>1266</v>
       </c>
       <c r="H2155" t="s">
         <v>9</v>
@@ -60856,7 +60859,7 @@
         <v>3.65000009536743</v>
       </c>
       <c r="G2156" t="s">
-        <v>1261</v>
+        <v>1262</v>
       </c>
       <c r="H2156" t="s">
         <v>9</v>
@@ -60882,7 +60885,7 @@
         <v>3.63000011444092</v>
       </c>
       <c r="G2157" t="s">
-        <v>1265</v>
+        <v>1266</v>
       </c>
       <c r="H2157" t="s">
         <v>9</v>
@@ -60908,7 +60911,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G2158" t="s">
-        <v>1266</v>
+        <v>1267</v>
       </c>
       <c r="H2158" t="s">
         <v>9</v>
@@ -60934,7 +60937,7 @@
         <v>3.47000002861023</v>
       </c>
       <c r="G2159" t="s">
-        <v>1267</v>
+        <v>1268</v>
       </c>
       <c r="H2159" t="s">
         <v>9</v>
@@ -60960,7 +60963,7 @@
         <v>3.4300000667572</v>
       </c>
       <c r="G2160" t="s">
-        <v>1268</v>
+        <v>1269</v>
       </c>
       <c r="H2160" t="s">
         <v>9</v>
@@ -60986,7 +60989,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G2161" t="s">
-        <v>1269</v>
+        <v>1270</v>
       </c>
       <c r="H2161" t="s">
         <v>9</v>
@@ -61012,7 +61015,7 @@
         <v>3.45000004768372</v>
       </c>
       <c r="G2162" t="s">
-        <v>1270</v>
+        <v>1271</v>
       </c>
       <c r="H2162" t="s">
         <v>9</v>
@@ -61038,7 +61041,7 @@
         <v>3.52999997138977</v>
       </c>
       <c r="G2163" t="s">
-        <v>1271</v>
+        <v>1272</v>
       </c>
       <c r="H2163" t="s">
         <v>9</v>
@@ -61064,7 +61067,7 @@
         <v>3.45000004768372</v>
       </c>
       <c r="G2164" t="s">
-        <v>1270</v>
+        <v>1271</v>
       </c>
       <c r="H2164" t="s">
         <v>9</v>
@@ -61090,7 +61093,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G2165" t="s">
-        <v>1269</v>
+        <v>1270</v>
       </c>
       <c r="H2165" t="s">
         <v>9</v>
@@ -61116,7 +61119,7 @@
         <v>3.47000002861023</v>
       </c>
       <c r="G2166" t="s">
-        <v>1267</v>
+        <v>1268</v>
       </c>
       <c r="H2166" t="s">
         <v>9</v>
@@ -61142,7 +61145,7 @@
         <v>3.38000011444092</v>
       </c>
       <c r="G2167" t="s">
-        <v>1272</v>
+        <v>1273</v>
       </c>
       <c r="H2167" t="s">
         <v>9</v>
@@ -61168,7 +61171,7 @@
         <v>3.33999991416931</v>
       </c>
       <c r="G2168" t="s">
-        <v>1273</v>
+        <v>1274</v>
       </c>
       <c r="H2168" t="s">
         <v>9</v>
@@ -61194,7 +61197,7 @@
         <v>3.44000005722046</v>
       </c>
       <c r="G2169" t="s">
-        <v>1274</v>
+        <v>1275</v>
       </c>
       <c r="H2169" t="s">
         <v>9</v>
@@ -61220,7 +61223,7 @@
         <v>3.32999992370605</v>
       </c>
       <c r="G2170" t="s">
-        <v>1275</v>
+        <v>1276</v>
       </c>
       <c r="H2170" t="s">
         <v>9</v>
@@ -61246,7 +61249,7 @@
         <v>3.33999991416931</v>
       </c>
       <c r="G2171" t="s">
-        <v>1273</v>
+        <v>1274</v>
       </c>
       <c r="H2171" t="s">
         <v>9</v>
@@ -61272,7 +61275,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G2172" t="s">
-        <v>1269</v>
+        <v>1270</v>
       </c>
       <c r="H2172" t="s">
         <v>9</v>
@@ -61298,7 +61301,7 @@
         <v>3.45000004768372</v>
       </c>
       <c r="G2173" t="s">
-        <v>1270</v>
+        <v>1271</v>
       </c>
       <c r="H2173" t="s">
         <v>9</v>
@@ -61324,7 +61327,7 @@
         <v>3.5699999332428</v>
       </c>
       <c r="G2174" t="s">
-        <v>1276</v>
+        <v>1277</v>
       </c>
       <c r="H2174" t="s">
         <v>9</v>
@@ -61350,7 +61353,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G2175" t="s">
-        <v>1277</v>
+        <v>1278</v>
       </c>
       <c r="H2175" t="s">
         <v>9</v>
@@ -61376,7 +61379,7 @@
         <v>3.53999996185303</v>
       </c>
       <c r="G2176" t="s">
-        <v>1278</v>
+        <v>1279</v>
       </c>
       <c r="H2176" t="s">
         <v>9</v>
@@ -61402,7 +61405,7 @@
         <v>3.49000000953674</v>
       </c>
       <c r="G2177" t="s">
-        <v>1279</v>
+        <v>1280</v>
       </c>
       <c r="H2177" t="s">
         <v>9</v>
@@ -61428,7 +61431,7 @@
         <v>3.49000000953674</v>
       </c>
       <c r="G2178" t="s">
-        <v>1279</v>
+        <v>1280</v>
       </c>
       <c r="H2178" t="s">
         <v>9</v>
@@ -61454,7 +61457,7 @@
         <v>3.4300000667572</v>
       </c>
       <c r="G2179" t="s">
-        <v>1268</v>
+        <v>1269</v>
       </c>
       <c r="H2179" t="s">
         <v>9</v>
@@ -61480,7 +61483,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G2180" t="s">
-        <v>1280</v>
+        <v>1281</v>
       </c>
       <c r="H2180" t="s">
         <v>9</v>
@@ -61506,7 +61509,7 @@
         <v>3.3199999332428</v>
       </c>
       <c r="G2181" t="s">
-        <v>1281</v>
+        <v>1282</v>
       </c>
       <c r="H2181" t="s">
         <v>9</v>
@@ -61532,7 +61535,7 @@
         <v>3.38000011444092</v>
       </c>
       <c r="G2182" t="s">
-        <v>1272</v>
+        <v>1273</v>
       </c>
       <c r="H2182" t="s">
         <v>9</v>
@@ -61558,7 +61561,7 @@
         <v>3.32999992370605</v>
       </c>
       <c r="G2183" t="s">
-        <v>1275</v>
+        <v>1276</v>
       </c>
       <c r="H2183" t="s">
         <v>9</v>
@@ -61584,7 +61587,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G2184" t="s">
-        <v>1282</v>
+        <v>1283</v>
       </c>
       <c r="H2184" t="s">
         <v>9</v>
@@ -61610,7 +61613,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G2185" t="s">
-        <v>1282</v>
+        <v>1283</v>
       </c>
       <c r="H2185" t="s">
         <v>9</v>
@@ -61636,7 +61639,7 @@
         <v>3.32999992370605</v>
       </c>
       <c r="G2186" t="s">
-        <v>1275</v>
+        <v>1276</v>
       </c>
       <c r="H2186" t="s">
         <v>9</v>
@@ -61662,7 +61665,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G2187" t="s">
-        <v>1282</v>
+        <v>1283</v>
       </c>
       <c r="H2187" t="s">
         <v>9</v>
@@ -61688,7 +61691,7 @@
         <v>3.04999995231628</v>
       </c>
       <c r="G2188" t="s">
-        <v>1283</v>
+        <v>1284</v>
       </c>
       <c r="H2188" t="s">
         <v>9</v>
@@ -61714,7 +61717,7 @@
         <v>3.32999992370605</v>
       </c>
       <c r="G2189" t="s">
-        <v>1275</v>
+        <v>1276</v>
       </c>
       <c r="H2189" t="s">
         <v>9</v>
@@ -61740,7 +61743,7 @@
         <v>3.17000007629395</v>
       </c>
       <c r="G2190" t="s">
-        <v>1284</v>
+        <v>1285</v>
       </c>
       <c r="H2190" t="s">
         <v>9</v>
@@ -61766,7 +61769,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G2191" t="s">
-        <v>1285</v>
+        <v>1286</v>
       </c>
       <c r="H2191" t="s">
         <v>9</v>
@@ -61792,7 +61795,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G2192" t="s">
-        <v>1285</v>
+        <v>1286</v>
       </c>
       <c r="H2192" t="s">
         <v>9</v>
@@ -61818,7 +61821,7 @@
         <v>3.14000010490417</v>
       </c>
       <c r="G2193" t="s">
-        <v>1286</v>
+        <v>1287</v>
       </c>
       <c r="H2193" t="s">
         <v>9</v>
@@ -61844,7 +61847,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G2194" t="s">
-        <v>1287</v>
+        <v>1288</v>
       </c>
       <c r="H2194" t="s">
         <v>9</v>
@@ -61870,7 +61873,7 @@
         <v>3.15000009536743</v>
       </c>
       <c r="G2195" t="s">
-        <v>1288</v>
+        <v>1289</v>
       </c>
       <c r="H2195" t="s">
         <v>9</v>
@@ -61896,7 +61899,7 @@
         <v>3.08999991416931</v>
       </c>
       <c r="G2196" t="s">
-        <v>1289</v>
+        <v>1290</v>
       </c>
       <c r="H2196" t="s">
         <v>9</v>
@@ -61922,7 +61925,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G2197" t="s">
-        <v>1290</v>
+        <v>1291</v>
       </c>
       <c r="H2197" t="s">
         <v>9</v>
@@ -61948,7 +61951,7 @@
         <v>3.07999992370605</v>
       </c>
       <c r="G2198" t="s">
-        <v>1291</v>
+        <v>1292</v>
       </c>
       <c r="H2198" t="s">
         <v>9</v>
@@ -61974,7 +61977,7 @@
         <v>3.14000010490417</v>
       </c>
       <c r="G2199" t="s">
-        <v>1286</v>
+        <v>1287</v>
       </c>
       <c r="H2199" t="s">
         <v>9</v>
@@ -62000,7 +62003,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G2200" t="s">
-        <v>1292</v>
+        <v>1293</v>
       </c>
       <c r="H2200" t="s">
         <v>9</v>
@@ -62026,7 +62029,7 @@
         <v>3.13000011444092</v>
       </c>
       <c r="G2201" t="s">
-        <v>1293</v>
+        <v>1294</v>
       </c>
       <c r="H2201" t="s">
         <v>9</v>
@@ -62052,7 +62055,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G2202" t="s">
-        <v>1292</v>
+        <v>1293</v>
       </c>
       <c r="H2202" t="s">
         <v>9</v>
@@ -62078,7 +62081,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G2203" t="s">
-        <v>1294</v>
+        <v>1295</v>
       </c>
       <c r="H2203" t="s">
         <v>9</v>
@@ -62104,7 +62107,7 @@
         <v>3.08999991416931</v>
       </c>
       <c r="G2204" t="s">
-        <v>1289</v>
+        <v>1290</v>
       </c>
       <c r="H2204" t="s">
         <v>9</v>
@@ -62130,7 +62133,7 @@
         <v>3.03999996185303</v>
       </c>
       <c r="G2205" t="s">
-        <v>1295</v>
+        <v>1296</v>
       </c>
       <c r="H2205" t="s">
         <v>9</v>
@@ -62156,7 +62159,7 @@
         <v>3.05999994277954</v>
       </c>
       <c r="G2206" t="s">
-        <v>1296</v>
+        <v>1297</v>
       </c>
       <c r="H2206" t="s">
         <v>9</v>
@@ -62182,7 +62185,7 @@
         <v>3.07999992370605</v>
       </c>
       <c r="G2207" t="s">
-        <v>1291</v>
+        <v>1292</v>
       </c>
       <c r="H2207" t="s">
         <v>9</v>
@@ -62208,7 +62211,7 @@
         <v>3.04999995231628</v>
       </c>
       <c r="G2208" t="s">
-        <v>1283</v>
+        <v>1284</v>
       </c>
       <c r="H2208" t="s">
         <v>9</v>
@@ -62234,7 +62237,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G2209" t="s">
-        <v>1290</v>
+        <v>1291</v>
       </c>
       <c r="H2209" t="s">
         <v>9</v>
@@ -62260,7 +62263,7 @@
         <v>3.08999991416931</v>
       </c>
       <c r="G2210" t="s">
-        <v>1289</v>
+        <v>1290</v>
       </c>
       <c r="H2210" t="s">
         <v>9</v>
@@ -62286,7 +62289,7 @@
         <v>3.08999991416931</v>
       </c>
       <c r="G2211" t="s">
-        <v>1289</v>
+        <v>1290</v>
       </c>
       <c r="H2211" t="s">
         <v>9</v>
@@ -62312,7 +62315,7 @@
         <v>3.08999991416931</v>
       </c>
       <c r="G2212" t="s">
-        <v>1289</v>
+        <v>1290</v>
       </c>
       <c r="H2212" t="s">
         <v>9</v>
@@ -62338,7 +62341,7 @@
         <v>3.08999991416931</v>
       </c>
       <c r="G2213" t="s">
-        <v>1289</v>
+        <v>1290</v>
       </c>
       <c r="H2213" t="s">
         <v>9</v>
@@ -62364,7 +62367,7 @@
         <v>3.05999994277954</v>
       </c>
       <c r="G2214" t="s">
-        <v>1296</v>
+        <v>1297</v>
       </c>
       <c r="H2214" t="s">
         <v>9</v>
@@ -62390,7 +62393,7 @@
         <v>2.9300000667572</v>
       </c>
       <c r="G2215" t="s">
-        <v>1297</v>
+        <v>1298</v>
       </c>
       <c r="H2215" t="s">
         <v>9</v>
@@ -62416,7 +62419,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G2216" t="s">
-        <v>1298</v>
+        <v>1299</v>
       </c>
       <c r="H2216" t="s">
         <v>9</v>
@@ -62442,7 +62445,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G2217" t="s">
-        <v>1299</v>
+        <v>1300</v>
       </c>
       <c r="H2217" t="s">
         <v>9</v>
@@ -62468,7 +62471,7 @@
         <v>2.96000003814697</v>
       </c>
       <c r="G2218" t="s">
-        <v>1300</v>
+        <v>1301</v>
       </c>
       <c r="H2218" t="s">
         <v>9</v>
@@ -62494,7 +62497,7 @@
         <v>2.97000002861023</v>
       </c>
       <c r="G2219" t="s">
-        <v>1301</v>
+        <v>1302</v>
       </c>
       <c r="H2219" t="s">
         <v>9</v>
@@ -62520,7 +62523,7 @@
         <v>3</v>
       </c>
       <c r="G2220" t="s">
-        <v>1302</v>
+        <v>1303</v>
       </c>
       <c r="H2220" t="s">
         <v>9</v>
@@ -62546,7 +62549,7 @@
         <v>3.02999997138977</v>
       </c>
       <c r="G2221" t="s">
-        <v>1303</v>
+        <v>1304</v>
       </c>
       <c r="H2221" t="s">
         <v>9</v>
@@ -62572,7 +62575,7 @@
         <v>3.04999995231628</v>
       </c>
       <c r="G2222" t="s">
-        <v>1283</v>
+        <v>1284</v>
       </c>
       <c r="H2222" t="s">
         <v>9</v>
@@ -62598,7 +62601,7 @@
         <v>3.07999992370605</v>
       </c>
       <c r="G2223" t="s">
-        <v>1291</v>
+        <v>1292</v>
       </c>
       <c r="H2223" t="s">
         <v>9</v>
@@ -62624,7 +62627,7 @@
         <v>3.13000011444092</v>
       </c>
       <c r="G2224" t="s">
-        <v>1293</v>
+        <v>1294</v>
       </c>
       <c r="H2224" t="s">
         <v>9</v>
@@ -62650,7 +62653,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G2225" t="s">
-        <v>1292</v>
+        <v>1293</v>
       </c>
       <c r="H2225" t="s">
         <v>9</v>
@@ -62676,7 +62679,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G2226" t="s">
-        <v>1304</v>
+        <v>1305</v>
       </c>
       <c r="H2226" t="s">
         <v>9</v>
@@ -62702,7 +62705,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G2227" t="s">
-        <v>1282</v>
+        <v>1283</v>
       </c>
       <c r="H2227" t="s">
         <v>9</v>
@@ -62728,7 +62731,7 @@
         <v>3.33999991416931</v>
       </c>
       <c r="G2228" t="s">
-        <v>1273</v>
+        <v>1274</v>
       </c>
       <c r="H2228" t="s">
         <v>9</v>
@@ -62754,7 +62757,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G2229" t="s">
-        <v>1305</v>
+        <v>1306</v>
       </c>
       <c r="H2229" t="s">
         <v>9</v>
@@ -62780,7 +62783,7 @@
         <v>3.3199999332428</v>
       </c>
       <c r="G2230" t="s">
-        <v>1281</v>
+        <v>1282</v>
       </c>
       <c r="H2230" t="s">
         <v>9</v>
@@ -62806,7 +62809,7 @@
         <v>3.34999990463257</v>
       </c>
       <c r="G2231" t="s">
-        <v>1306</v>
+        <v>1307</v>
       </c>
       <c r="H2231" t="s">
         <v>9</v>
@@ -62832,7 +62835,7 @@
         <v>3.44000005722046</v>
       </c>
       <c r="G2232" t="s">
-        <v>1274</v>
+        <v>1275</v>
       </c>
       <c r="H2232" t="s">
         <v>9</v>
@@ -62858,7 +62861,7 @@
         <v>3.38000011444092</v>
       </c>
       <c r="G2233" t="s">
-        <v>1272</v>
+        <v>1273</v>
       </c>
       <c r="H2233" t="s">
         <v>9</v>
@@ -62884,7 +62887,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G2234" t="s">
-        <v>1305</v>
+        <v>1306</v>
       </c>
       <c r="H2234" t="s">
         <v>9</v>
@@ -62910,7 +62913,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G2235" t="s">
-        <v>1280</v>
+        <v>1281</v>
       </c>
       <c r="H2235" t="s">
         <v>9</v>
@@ -62936,7 +62939,7 @@
         <v>3.41000008583069</v>
       </c>
       <c r="G2236" t="s">
-        <v>1307</v>
+        <v>1308</v>
       </c>
       <c r="H2236" t="s">
         <v>9</v>
@@ -62962,7 +62965,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G2237" t="s">
-        <v>1280</v>
+        <v>1281</v>
       </c>
       <c r="H2237" t="s">
         <v>9</v>
@@ -62988,7 +62991,7 @@
         <v>3.30999994277954</v>
       </c>
       <c r="G2238" t="s">
-        <v>1308</v>
+        <v>1309</v>
       </c>
       <c r="H2238" t="s">
         <v>9</v>
@@ -63014,7 +63017,7 @@
         <v>3.39000010490417</v>
       </c>
       <c r="G2239" t="s">
-        <v>1309</v>
+        <v>1310</v>
       </c>
       <c r="H2239" t="s">
         <v>9</v>
@@ -63040,7 +63043,7 @@
         <v>3.36999988555908</v>
       </c>
       <c r="G2240" t="s">
-        <v>1310</v>
+        <v>1311</v>
       </c>
       <c r="H2240" t="s">
         <v>9</v>
@@ -63066,7 +63069,7 @@
         <v>3.45000004768372</v>
       </c>
       <c r="G2241" t="s">
-        <v>1270</v>
+        <v>1271</v>
       </c>
       <c r="H2241" t="s">
         <v>9</v>
@@ -63092,7 +63095,7 @@
         <v>3.39000010490417</v>
       </c>
       <c r="G2242" t="s">
-        <v>1309</v>
+        <v>1310</v>
       </c>
       <c r="H2242" t="s">
         <v>9</v>
@@ -63118,7 +63121,7 @@
         <v>3.46000003814697</v>
       </c>
       <c r="G2243" t="s">
-        <v>1311</v>
+        <v>1312</v>
       </c>
       <c r="H2243" t="s">
         <v>9</v>
@@ -63144,7 +63147,7 @@
         <v>3.5699999332428</v>
       </c>
       <c r="G2244" t="s">
-        <v>1276</v>
+        <v>1277</v>
       </c>
       <c r="H2244" t="s">
         <v>9</v>
@@ -63170,7 +63173,7 @@
         <v>3.60999989509583</v>
       </c>
       <c r="G2245" t="s">
-        <v>1312</v>
+        <v>1313</v>
       </c>
       <c r="H2245" t="s">
         <v>9</v>
@@ -63196,7 +63199,7 @@
         <v>3.82999992370605</v>
       </c>
       <c r="G2246" t="s">
-        <v>1248</v>
+        <v>1249</v>
       </c>
       <c r="H2246" t="s">
         <v>9</v>
@@ -63222,7 +63225,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G2247" t="s">
-        <v>1313</v>
+        <v>1314</v>
       </c>
       <c r="H2247" t="s">
         <v>9</v>
@@ -63248,7 +63251,7 @@
         <v>5.28000020980835</v>
       </c>
       <c r="G2248" t="s">
-        <v>1314</v>
+        <v>1315</v>
       </c>
       <c r="H2248" t="s">
         <v>9</v>
@@ -63274,7 +63277,7 @@
         <v>5.32000017166138</v>
       </c>
       <c r="G2249" t="s">
-        <v>1315</v>
+        <v>1316</v>
       </c>
       <c r="H2249" t="s">
         <v>9</v>
@@ -63300,7 +63303,7 @@
         <v>5.26000022888184</v>
       </c>
       <c r="G2250" t="s">
-        <v>1316</v>
+        <v>1317</v>
       </c>
       <c r="H2250" t="s">
         <v>9</v>
@@ -63326,7 +63329,7 @@
         <v>5.34000015258789</v>
       </c>
       <c r="G2251" t="s">
-        <v>1317</v>
+        <v>1318</v>
       </c>
       <c r="H2251" t="s">
         <v>9</v>
@@ -63352,7 +63355,7 @@
         <v>5.6399998664856</v>
       </c>
       <c r="G2252" t="s">
-        <v>1318</v>
+        <v>1319</v>
       </c>
       <c r="H2252" t="s">
         <v>9</v>
@@ -63378,7 +63381,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G2253" t="s">
-        <v>1319</v>
+        <v>1320</v>
       </c>
       <c r="H2253" t="s">
         <v>9</v>
@@ -63404,7 +63407,7 @@
         <v>5.84000015258789</v>
       </c>
       <c r="G2254" t="s">
-        <v>1320</v>
+        <v>1321</v>
       </c>
       <c r="H2254" t="s">
         <v>9</v>
@@ -63430,7 +63433,7 @@
         <v>6.34000015258789</v>
       </c>
       <c r="G2255" t="s">
-        <v>1321</v>
+        <v>1322</v>
       </c>
       <c r="H2255" t="s">
         <v>9</v>
@@ -63456,7 +63459,7 @@
         <v>6.42000007629395</v>
       </c>
       <c r="G2256" t="s">
-        <v>1322</v>
+        <v>1323</v>
       </c>
       <c r="H2256" t="s">
         <v>9</v>
@@ -63482,7 +63485,7 @@
         <v>6.71999979019165</v>
       </c>
       <c r="G2257" t="s">
-        <v>1323</v>
+        <v>1324</v>
       </c>
       <c r="H2257" t="s">
         <v>9</v>
@@ -63508,7 +63511,7 @@
         <v>6.3600001335144</v>
       </c>
       <c r="G2258" t="s">
-        <v>1324</v>
+        <v>1325</v>
       </c>
       <c r="H2258" t="s">
         <v>9</v>
@@ -63534,7 +63537,7 @@
         <v>6.5</v>
       </c>
       <c r="G2259" t="s">
-        <v>1325</v>
+        <v>1326</v>
       </c>
       <c r="H2259" t="s">
         <v>9</v>
@@ -63560,7 +63563,7 @@
         <v>6.59999990463257</v>
       </c>
       <c r="G2260" t="s">
-        <v>1326</v>
+        <v>1327</v>
       </c>
       <c r="H2260" t="s">
         <v>9</v>
@@ -63586,7 +63589,7 @@
         <v>6.84000015258789</v>
       </c>
       <c r="G2261" t="s">
-        <v>1327</v>
+        <v>1328</v>
       </c>
       <c r="H2261" t="s">
         <v>9</v>
@@ -63612,7 +63615,7 @@
         <v>6.84000015258789</v>
       </c>
       <c r="G2262" t="s">
-        <v>1327</v>
+        <v>1328</v>
       </c>
       <c r="H2262" t="s">
         <v>9</v>
@@ -63638,7 +63641,7 @@
         <v>6.98000001907349</v>
       </c>
       <c r="G2263" t="s">
-        <v>1328</v>
+        <v>1329</v>
       </c>
       <c r="H2263" t="s">
         <v>9</v>
@@ -63664,7 +63667,7 @@
         <v>6.82000017166138</v>
       </c>
       <c r="G2264" t="s">
-        <v>1329</v>
+        <v>1330</v>
       </c>
       <c r="H2264" t="s">
         <v>9</v>
@@ -63690,7 +63693,7 @@
         <v>6.90000009536743</v>
       </c>
       <c r="G2265" t="s">
-        <v>1330</v>
+        <v>1331</v>
       </c>
       <c r="H2265" t="s">
         <v>9</v>
@@ -63716,7 +63719,7 @@
         <v>6.98000001907349</v>
       </c>
       <c r="G2266" t="s">
-        <v>1328</v>
+        <v>1329</v>
       </c>
       <c r="H2266" t="s">
         <v>9</v>
@@ -63742,7 +63745,7 @@
         <v>6.92000007629395</v>
       </c>
       <c r="G2267" t="s">
-        <v>1331</v>
+        <v>1332</v>
       </c>
       <c r="H2267" t="s">
         <v>9</v>
@@ -63768,7 +63771,7 @@
         <v>6.84000015258789</v>
       </c>
       <c r="G2268" t="s">
-        <v>1327</v>
+        <v>1328</v>
       </c>
       <c r="H2268" t="s">
         <v>9</v>
@@ -63794,7 +63797,7 @@
         <v>7.07999992370605</v>
       </c>
       <c r="G2269" t="s">
-        <v>1332</v>
+        <v>1333</v>
       </c>
       <c r="H2269" t="s">
         <v>9</v>
@@ -63820,7 +63823,7 @@
         <v>7.19999980926514</v>
       </c>
       <c r="G2270" t="s">
-        <v>1333</v>
+        <v>1334</v>
       </c>
       <c r="H2270" t="s">
         <v>9</v>
@@ -63846,7 +63849,7 @@
         <v>7.09999990463257</v>
       </c>
       <c r="G2271" t="s">
-        <v>1334</v>
+        <v>1335</v>
       </c>
       <c r="H2271" t="s">
         <v>9</v>
@@ -63872,7 +63875,7 @@
         <v>7.26000022888184</v>
       </c>
       <c r="G2272" t="s">
-        <v>1335</v>
+        <v>1336</v>
       </c>
       <c r="H2272" t="s">
         <v>9</v>
@@ -63898,7 +63901,7 @@
         <v>7.40000009536743</v>
       </c>
       <c r="G2273" t="s">
-        <v>1336</v>
+        <v>1337</v>
       </c>
       <c r="H2273" t="s">
         <v>9</v>
@@ -63924,7 +63927,7 @@
         <v>7.51999998092651</v>
       </c>
       <c r="G2274" t="s">
-        <v>1337</v>
+        <v>1338</v>
       </c>
       <c r="H2274" t="s">
         <v>9</v>
@@ -63950,7 +63953,7 @@
         <v>7.40000009536743</v>
       </c>
       <c r="G2275" t="s">
-        <v>1336</v>
+        <v>1337</v>
       </c>
       <c r="H2275" t="s">
         <v>9</v>
@@ -63976,7 +63979,7 @@
         <v>7.46000003814697</v>
       </c>
       <c r="G2276" t="s">
-        <v>1338</v>
+        <v>1339</v>
       </c>
       <c r="H2276" t="s">
         <v>9</v>
@@ -64002,7 +64005,7 @@
         <v>7.48000001907349</v>
       </c>
       <c r="G2277" t="s">
-        <v>1339</v>
+        <v>1340</v>
       </c>
       <c r="H2277" t="s">
         <v>9</v>
@@ -64028,7 +64031,7 @@
         <v>7.67999982833862</v>
       </c>
       <c r="G2278" t="s">
-        <v>1340</v>
+        <v>1341</v>
       </c>
       <c r="H2278" t="s">
         <v>9</v>
@@ -64054,7 +64057,7 @@
         <v>8.10000038146973</v>
       </c>
       <c r="G2279" t="s">
-        <v>1341</v>
+        <v>1342</v>
       </c>
       <c r="H2279" t="s">
         <v>9</v>
@@ -64080,7 +64083,7 @@
         <v>7.59999990463257</v>
       </c>
       <c r="G2280" t="s">
-        <v>1342</v>
+        <v>1343</v>
       </c>
       <c r="H2280" t="s">
         <v>9</v>
@@ -64106,7 +64109,7 @@
         <v>7.6399998664856</v>
       </c>
       <c r="G2281" t="s">
-        <v>1343</v>
+        <v>1344</v>
       </c>
       <c r="H2281" t="s">
         <v>9</v>
@@ -64132,7 +64135,7 @@
         <v>7.71999979019165</v>
       </c>
       <c r="G2282" t="s">
-        <v>1344</v>
+        <v>1345</v>
       </c>
       <c r="H2282" t="s">
         <v>9</v>
@@ -64158,7 +64161,7 @@
         <v>7.59999990463257</v>
       </c>
       <c r="G2283" t="s">
-        <v>1342</v>
+        <v>1343</v>
       </c>
       <c r="H2283" t="s">
         <v>9</v>
@@ -64184,7 +64187,7 @@
         <v>7.48000001907349</v>
       </c>
       <c r="G2284" t="s">
-        <v>1339</v>
+        <v>1340</v>
       </c>
       <c r="H2284" t="s">
         <v>9</v>
@@ -64210,7 +64213,7 @@
         <v>7.46000003814697</v>
       </c>
       <c r="G2285" t="s">
-        <v>1338</v>
+        <v>1339</v>
       </c>
       <c r="H2285" t="s">
         <v>9</v>
@@ -64236,7 +64239,7 @@
         <v>7.90000009536743</v>
       </c>
       <c r="G2286" t="s">
-        <v>1345</v>
+        <v>1346</v>
       </c>
       <c r="H2286" t="s">
         <v>9</v>
@@ -64262,7 +64265,7 @@
         <v>7.6399998664856</v>
       </c>
       <c r="G2287" t="s">
-        <v>1343</v>
+        <v>1344</v>
       </c>
       <c r="H2287" t="s">
         <v>9</v>
@@ -64288,7 +64291,7 @@
         <v>7.8600001335144</v>
       </c>
       <c r="G2288" t="s">
-        <v>1346</v>
+        <v>1347</v>
       </c>
       <c r="H2288" t="s">
         <v>9</v>
@@ -64314,7 +64317,7 @@
         <v>7.8600001335144</v>
       </c>
       <c r="G2289" t="s">
-        <v>1346</v>
+        <v>1347</v>
       </c>
       <c r="H2289" t="s">
         <v>9</v>
@@ -64340,7 +64343,7 @@
         <v>7.73999977111816</v>
       </c>
       <c r="G2290" t="s">
-        <v>1347</v>
+        <v>1348</v>
       </c>
       <c r="H2290" t="s">
         <v>9</v>
@@ -64366,7 +64369,7 @@
         <v>7.69999980926514</v>
       </c>
       <c r="G2291" t="s">
-        <v>1348</v>
+        <v>1349</v>
       </c>
       <c r="H2291" t="s">
         <v>9</v>
@@ -64392,7 +64395,7 @@
         <v>7.90000009536743</v>
       </c>
       <c r="G2292" t="s">
-        <v>1345</v>
+        <v>1346</v>
       </c>
       <c r="H2292" t="s">
         <v>9</v>
@@ -64418,7 +64421,7 @@
         <v>7.5</v>
       </c>
       <c r="G2293" t="s">
-        <v>1349</v>
+        <v>1350</v>
       </c>
       <c r="H2293" t="s">
         <v>9</v>
@@ -64444,7 +64447,7 @@
         <v>7.38000011444092</v>
       </c>
       <c r="G2294" t="s">
-        <v>1350</v>
+        <v>1351</v>
       </c>
       <c r="H2294" t="s">
         <v>9</v>
@@ -64470,7 +64473,7 @@
         <v>7.61999988555908</v>
       </c>
       <c r="G2295" t="s">
-        <v>1351</v>
+        <v>1352</v>
       </c>
       <c r="H2295" t="s">
         <v>9</v>
@@ -64496,7 +64499,7 @@
         <v>7.71999979019165</v>
       </c>
       <c r="G2296" t="s">
-        <v>1344</v>
+        <v>1345</v>
       </c>
       <c r="H2296" t="s">
         <v>9</v>
@@ -64522,7 +64525,7 @@
         <v>7.55999994277954</v>
       </c>
       <c r="G2297" t="s">
-        <v>1352</v>
+        <v>1353</v>
       </c>
       <c r="H2297" t="s">
         <v>9</v>
@@ -64548,7 +64551,7 @@
         <v>7.46000003814697</v>
       </c>
       <c r="G2298" t="s">
-        <v>1338</v>
+        <v>1339</v>
       </c>
       <c r="H2298" t="s">
         <v>9</v>
@@ -64574,7 +64577,7 @@
         <v>7.59999990463257</v>
       </c>
       <c r="G2299" t="s">
-        <v>1342</v>
+        <v>1343</v>
       </c>
       <c r="H2299" t="s">
         <v>9</v>
@@ -64600,7 +64603,7 @@
         <v>7.48000001907349</v>
       </c>
       <c r="G2300" t="s">
-        <v>1339</v>
+        <v>1340</v>
       </c>
       <c r="H2300" t="s">
         <v>9</v>
@@ -64626,7 +64629,7 @@
         <v>7.42000007629395</v>
       </c>
       <c r="G2301" t="s">
-        <v>1353</v>
+        <v>1354</v>
       </c>
       <c r="H2301" t="s">
         <v>9</v>
@@ -64652,7 +64655,7 @@
         <v>7.3600001335144</v>
       </c>
       <c r="G2302" t="s">
-        <v>1354</v>
+        <v>1355</v>
       </c>
       <c r="H2302" t="s">
         <v>9</v>
@@ -64678,7 +64681,7 @@
         <v>7.34000015258789</v>
       </c>
       <c r="G2303" t="s">
-        <v>1355</v>
+        <v>1356</v>
       </c>
       <c r="H2303" t="s">
         <v>9</v>
@@ -64704,7 +64707,7 @@
         <v>7.42000007629395</v>
       </c>
       <c r="G2304" t="s">
-        <v>1353</v>
+        <v>1354</v>
       </c>
       <c r="H2304" t="s">
         <v>9</v>
@@ -64730,7 +64733,7 @@
         <v>7.21999979019165</v>
       </c>
       <c r="G2305" t="s">
-        <v>1356</v>
+        <v>1357</v>
       </c>
       <c r="H2305" t="s">
         <v>9</v>
@@ -64756,7 +64759,7 @@
         <v>7.34000015258789</v>
       </c>
       <c r="G2306" t="s">
-        <v>1355</v>
+        <v>1356</v>
       </c>
       <c r="H2306" t="s">
         <v>9</v>
@@ -64782,7 +64785,7 @@
         <v>7.21999979019165</v>
       </c>
       <c r="G2307" t="s">
-        <v>1356</v>
+        <v>1357</v>
       </c>
       <c r="H2307" t="s">
         <v>9</v>
@@ -64808,7 +64811,7 @@
         <v>7.6399998664856</v>
       </c>
       <c r="G2308" t="s">
-        <v>1343</v>
+        <v>1344</v>
       </c>
       <c r="H2308" t="s">
         <v>9</v>
@@ -64834,7 +64837,7 @@
         <v>7.76000022888184</v>
       </c>
       <c r="G2309" t="s">
-        <v>1357</v>
+        <v>1358</v>
       </c>
       <c r="H2309" t="s">
         <v>9</v>
@@ -64860,7 +64863,7 @@
         <v>7.6399998664856</v>
       </c>
       <c r="G2310" t="s">
-        <v>1343</v>
+        <v>1344</v>
       </c>
       <c r="H2310" t="s">
         <v>9</v>
@@ -64886,7 +64889,7 @@
         <v>7.73999977111816</v>
       </c>
       <c r="G2311" t="s">
-        <v>1347</v>
+        <v>1348</v>
       </c>
       <c r="H2311" t="s">
         <v>9</v>
@@ -64912,7 +64915,7 @@
         <v>7.71999979019165</v>
       </c>
       <c r="G2312" t="s">
-        <v>1344</v>
+        <v>1345</v>
       </c>
       <c r="H2312" t="s">
         <v>9</v>
@@ -64938,7 +64941,7 @@
         <v>7.6399998664856</v>
       </c>
       <c r="G2313" t="s">
-        <v>1343</v>
+        <v>1344</v>
       </c>
       <c r="H2313" t="s">
         <v>9</v>
@@ -64964,7 +64967,7 @@
         <v>7.59999990463257</v>
       </c>
       <c r="G2314" t="s">
-        <v>1342</v>
+        <v>1343</v>
       </c>
       <c r="H2314" t="s">
         <v>9</v>
@@ -64990,7 +64993,7 @@
         <v>7.84000015258789</v>
       </c>
       <c r="G2315" t="s">
-        <v>1358</v>
+        <v>1359</v>
       </c>
       <c r="H2315" t="s">
         <v>9</v>
@@ -65016,7 +65019,7 @@
         <v>7.69999980926514</v>
       </c>
       <c r="G2316" t="s">
-        <v>1348</v>
+        <v>1349</v>
       </c>
       <c r="H2316" t="s">
         <v>9</v>
@@ -65042,7 +65045,7 @@
         <v>7.40000009536743</v>
       </c>
       <c r="G2317" t="s">
-        <v>1336</v>
+        <v>1337</v>
       </c>
       <c r="H2317" t="s">
         <v>9</v>
@@ -65068,7 +65071,7 @@
         <v>7.90000009536743</v>
       </c>
       <c r="G2318" t="s">
-        <v>1345</v>
+        <v>1346</v>
       </c>
       <c r="H2318" t="s">
         <v>9</v>
@@ -65094,7 +65097,7 @@
         <v>7.90000009536743</v>
       </c>
       <c r="G2319" t="s">
-        <v>1345</v>
+        <v>1346</v>
       </c>
       <c r="H2319" t="s">
         <v>9</v>
@@ -65120,7 +65123,7 @@
         <v>8.60000038146973</v>
       </c>
       <c r="G2320" t="s">
-        <v>1359</v>
+        <v>1360</v>
       </c>
       <c r="H2320" t="s">
         <v>9</v>
@@ -65146,7 +65149,7 @@
         <v>8.77999973297119</v>
       </c>
       <c r="G2321" t="s">
-        <v>1360</v>
+        <v>1361</v>
       </c>
       <c r="H2321" t="s">
         <v>9</v>
@@ -65172,7 +65175,7 @@
         <v>8.60000038146973</v>
       </c>
       <c r="G2322" t="s">
-        <v>1359</v>
+        <v>1360</v>
       </c>
       <c r="H2322" t="s">
         <v>9</v>
@@ -65198,7 +65201,7 @@
         <v>8.72000026702881</v>
       </c>
       <c r="G2323" t="s">
-        <v>1361</v>
+        <v>1362</v>
       </c>
       <c r="H2323" t="s">
         <v>9</v>
@@ -65224,7 +65227,7 @@
         <v>8.61999988555908</v>
       </c>
       <c r="G2324" t="s">
-        <v>1362</v>
+        <v>1363</v>
       </c>
       <c r="H2324" t="s">
         <v>9</v>
@@ -65250,7 +65253,7 @@
         <v>8.5</v>
       </c>
       <c r="G2325" t="s">
-        <v>1363</v>
+        <v>1364</v>
       </c>
       <c r="H2325" t="s">
         <v>9</v>
@@ -65276,7 +65279,7 @@
         <v>8.46000003814697</v>
       </c>
       <c r="G2326" t="s">
-        <v>1364</v>
+        <v>1365</v>
       </c>
       <c r="H2326" t="s">
         <v>9</v>
@@ -65302,7 +65305,7 @@
         <v>8.31999969482422</v>
       </c>
       <c r="G2327" t="s">
-        <v>1365</v>
+        <v>1366</v>
       </c>
       <c r="H2327" t="s">
         <v>9</v>
@@ -65328,7 +65331,7 @@
         <v>8.22000026702881</v>
       </c>
       <c r="G2328" t="s">
-        <v>1366</v>
+        <v>1367</v>
       </c>
       <c r="H2328" t="s">
         <v>9</v>
@@ -65354,7 +65357,7 @@
         <v>8.02000045776367</v>
       </c>
       <c r="G2329" t="s">
-        <v>1367</v>
+        <v>1368</v>
       </c>
       <c r="H2329" t="s">
         <v>9</v>
@@ -65380,7 +65383,7 @@
         <v>7.8600001335144</v>
       </c>
       <c r="G2330" t="s">
-        <v>1346</v>
+        <v>1347</v>
       </c>
       <c r="H2330" t="s">
         <v>9</v>
@@ -65406,7 +65409,7 @@
         <v>7.92000007629395</v>
       </c>
       <c r="G2331" t="s">
-        <v>1368</v>
+        <v>1369</v>
       </c>
       <c r="H2331" t="s">
         <v>9</v>
@@ -65432,7 +65435,7 @@
         <v>8.10000038146973</v>
       </c>
       <c r="G2332" t="s">
-        <v>1341</v>
+        <v>1342</v>
       </c>
       <c r="H2332" t="s">
         <v>9</v>
@@ -65458,7 +65461,7 @@
         <v>7.6399998664856</v>
       </c>
       <c r="G2333" t="s">
-        <v>1343</v>
+        <v>1344</v>
       </c>
       <c r="H2333" t="s">
         <v>9</v>
@@ -65484,7 +65487,7 @@
         <v>7.61999988555908</v>
       </c>
       <c r="G2334" t="s">
-        <v>1351</v>
+        <v>1352</v>
       </c>
       <c r="H2334" t="s">
         <v>9</v>
@@ -65510,7 +65513,7 @@
         <v>7.48000001907349</v>
       </c>
       <c r="G2335" t="s">
-        <v>1339</v>
+        <v>1340</v>
       </c>
       <c r="H2335" t="s">
         <v>9</v>
@@ -65536,7 +65539,7 @@
         <v>7.32000017166138</v>
       </c>
       <c r="G2336" t="s">
-        <v>1369</v>
+        <v>1370</v>
       </c>
       <c r="H2336" t="s">
         <v>9</v>
@@ -65562,7 +65565,7 @@
         <v>7.05999994277954</v>
       </c>
       <c r="G2337" t="s">
-        <v>1370</v>
+        <v>1371</v>
       </c>
       <c r="H2337" t="s">
         <v>9</v>
@@ -65588,7 +65591,7 @@
         <v>6.88000011444092</v>
       </c>
       <c r="G2338" t="s">
-        <v>1371</v>
+        <v>1372</v>
       </c>
       <c r="H2338" t="s">
         <v>9</v>
@@ -65614,7 +65617,7 @@
         <v>7</v>
       </c>
       <c r="G2339" t="s">
-        <v>1372</v>
+        <v>1373</v>
       </c>
       <c r="H2339" t="s">
         <v>9</v>
@@ -65640,7 +65643,7 @@
         <v>7.09999990463257</v>
       </c>
       <c r="G2340" t="s">
-        <v>1334</v>
+        <v>1335</v>
       </c>
       <c r="H2340" t="s">
         <v>9</v>
@@ -65666,7 +65669,7 @@
         <v>7.5</v>
       </c>
       <c r="G2341" t="s">
-        <v>1349</v>
+        <v>1350</v>
       </c>
       <c r="H2341" t="s">
         <v>9</v>
@@ -65692,7 +65695,7 @@
         <v>7.57999992370605</v>
       </c>
       <c r="G2342" t="s">
-        <v>1373</v>
+        <v>1374</v>
       </c>
       <c r="H2342" t="s">
         <v>9</v>
@@ -65718,7 +65721,7 @@
         <v>7.59999990463257</v>
       </c>
       <c r="G2343" t="s">
-        <v>1342</v>
+        <v>1343</v>
       </c>
       <c r="H2343" t="s">
         <v>9</v>
@@ -65744,7 +65747,7 @@
         <v>7.59999990463257</v>
       </c>
       <c r="G2344" t="s">
-        <v>1342</v>
+        <v>1343</v>
       </c>
       <c r="H2344" t="s">
         <v>9</v>
@@ -65770,7 +65773,7 @@
         <v>7.55999994277954</v>
       </c>
       <c r="G2345" t="s">
-        <v>1352</v>
+        <v>1353</v>
       </c>
       <c r="H2345" t="s">
         <v>9</v>
@@ -65796,7 +65799,7 @@
         <v>7.57999992370605</v>
       </c>
       <c r="G2346" t="s">
-        <v>1373</v>
+        <v>1374</v>
       </c>
       <c r="H2346" t="s">
         <v>9</v>
@@ -65822,7 +65825,7 @@
         <v>7.5</v>
       </c>
       <c r="G2347" t="s">
-        <v>1349</v>
+        <v>1350</v>
       </c>
       <c r="H2347" t="s">
         <v>9</v>
@@ -65848,7 +65851,7 @@
         <v>7.69999980926514</v>
       </c>
       <c r="G2348" t="s">
-        <v>1348</v>
+        <v>1349</v>
       </c>
       <c r="H2348" t="s">
         <v>9</v>
@@ -65874,7 +65877,7 @@
         <v>7.59999990463257</v>
       </c>
       <c r="G2349" t="s">
-        <v>1342</v>
+        <v>1343</v>
       </c>
       <c r="H2349" t="s">
         <v>9</v>
@@ -65900,7 +65903,7 @@
         <v>7.67999982833862</v>
       </c>
       <c r="G2350" t="s">
-        <v>1340</v>
+        <v>1341</v>
       </c>
       <c r="H2350" t="s">
         <v>9</v>
@@ -65926,7 +65929,7 @@
         <v>7.80000019073486</v>
       </c>
       <c r="G2351" t="s">
-        <v>1374</v>
+        <v>1375</v>
       </c>
       <c r="H2351" t="s">
         <v>9</v>
@@ -65952,7 +65955,7 @@
         <v>7.73999977111816</v>
       </c>
       <c r="G2352" t="s">
-        <v>1347</v>
+        <v>1348</v>
       </c>
       <c r="H2352" t="s">
         <v>9</v>
@@ -65978,7 +65981,7 @@
         <v>8.14000034332275</v>
       </c>
       <c r="G2353" t="s">
-        <v>1375</v>
+        <v>1376</v>
       </c>
       <c r="H2353" t="s">
         <v>9</v>
@@ -66004,7 +66007,7 @@
         <v>8.11999988555908</v>
       </c>
       <c r="G2354" t="s">
-        <v>1376</v>
+        <v>1377</v>
       </c>
       <c r="H2354" t="s">
         <v>9</v>
@@ -66030,7 +66033,7 @@
         <v>7.80000019073486</v>
       </c>
       <c r="G2355" t="s">
-        <v>1374</v>
+        <v>1375</v>
       </c>
       <c r="H2355" t="s">
         <v>9</v>
@@ -66056,7 +66059,7 @@
         <v>7.57999992370605</v>
       </c>
       <c r="G2356" t="s">
-        <v>1373</v>
+        <v>1374</v>
       </c>
       <c r="H2356" t="s">
         <v>9</v>
@@ -66082,7 +66085,7 @@
         <v>7.34000015258789</v>
       </c>
       <c r="G2357" t="s">
-        <v>1355</v>
+        <v>1356</v>
       </c>
       <c r="H2357" t="s">
         <v>9</v>
@@ -66108,7 +66111,7 @@
         <v>7.55999994277954</v>
       </c>
       <c r="G2358" t="s">
-        <v>1352</v>
+        <v>1353</v>
       </c>
       <c r="H2358" t="s">
         <v>9</v>
@@ -66134,7 +66137,7 @@
         <v>7.44999980926514</v>
       </c>
       <c r="G2359" t="s">
-        <v>1377</v>
+        <v>1378</v>
       </c>
       <c r="H2359" t="s">
         <v>9</v>
@@ -66160,7 +66163,7 @@
         <v>7.78999996185303</v>
       </c>
       <c r="G2360" t="s">
-        <v>1378</v>
+        <v>1379</v>
       </c>
       <c r="H2360" t="s">
         <v>9</v>
@@ -66186,7 +66189,7 @@
         <v>7.65000009536743</v>
       </c>
       <c r="G2361" t="s">
-        <v>1379</v>
+        <v>1380</v>
       </c>
       <c r="H2361" t="s">
         <v>9</v>
@@ -66212,7 +66215,7 @@
         <v>7.90000009536743</v>
       </c>
       <c r="G2362" t="s">
-        <v>1345</v>
+        <v>1346</v>
       </c>
       <c r="H2362" t="s">
         <v>9</v>
@@ -66238,7 +66241,7 @@
         <v>8</v>
       </c>
       <c r="G2363" t="s">
-        <v>1380</v>
+        <v>1381</v>
       </c>
       <c r="H2363" t="s">
         <v>9</v>
@@ -66264,7 +66267,7 @@
         <v>8.03999996185303</v>
       </c>
       <c r="G2364" t="s">
-        <v>1381</v>
+        <v>1382</v>
       </c>
       <c r="H2364" t="s">
         <v>9</v>
@@ -66290,7 +66293,7 @@
         <v>7.82000017166138</v>
       </c>
       <c r="G2365" t="s">
-        <v>1382</v>
+        <v>1383</v>
       </c>
       <c r="H2365" t="s">
         <v>9</v>
@@ -66316,7 +66319,7 @@
         <v>8.03999996185303</v>
       </c>
       <c r="G2366" t="s">
-        <v>1381</v>
+        <v>1382</v>
       </c>
       <c r="H2366" t="s">
         <v>9</v>
@@ -66342,7 +66345,7 @@
         <v>8.05000019073486</v>
       </c>
       <c r="G2367" t="s">
-        <v>1383</v>
+        <v>1384</v>
       </c>
       <c r="H2367" t="s">
         <v>9</v>
@@ -66368,7 +66371,7 @@
         <v>8.05000019073486</v>
       </c>
       <c r="G2368" t="s">
-        <v>1383</v>
+        <v>1384</v>
       </c>
       <c r="H2368" t="s">
         <v>9</v>
@@ -66394,7 +66397,7 @@
         <v>8.13000011444092</v>
       </c>
       <c r="G2369" t="s">
-        <v>1384</v>
+        <v>1385</v>
       </c>
       <c r="H2369" t="s">
         <v>9</v>
@@ -66420,7 +66423,7 @@
         <v>8.0600004196167</v>
       </c>
       <c r="G2370" t="s">
-        <v>1385</v>
+        <v>1386</v>
       </c>
       <c r="H2370" t="s">
         <v>9</v>
@@ -66446,7 +66449,7 @@
         <v>7.86999988555908</v>
       </c>
       <c r="G2371" t="s">
-        <v>1386</v>
+        <v>1387</v>
       </c>
       <c r="H2371" t="s">
         <v>9</v>
@@ -66472,7 +66475,7 @@
         <v>7.40000009536743</v>
       </c>
       <c r="G2372" t="s">
-        <v>1387</v>
+        <v>1388</v>
       </c>
       <c r="H2372" t="s">
         <v>9</v>
@@ -66498,7 +66501,7 @@
         <v>7.53999996185303</v>
       </c>
       <c r="G2373" t="s">
-        <v>1388</v>
+        <v>1389</v>
       </c>
       <c r="H2373" t="s">
         <v>9</v>
@@ -66524,7 +66527,7 @@
         <v>7.59000015258789</v>
       </c>
       <c r="G2374" t="s">
-        <v>1389</v>
+        <v>1390</v>
       </c>
       <c r="H2374" t="s">
         <v>9</v>
@@ -66550,7 +66553,7 @@
         <v>7.6399998664856</v>
       </c>
       <c r="G2375" t="s">
-        <v>1390</v>
+        <v>1391</v>
       </c>
       <c r="H2375" t="s">
         <v>9</v>
@@ -66576,7 +66579,7 @@
         <v>7.63000011444092</v>
       </c>
       <c r="G2376" t="s">
-        <v>1391</v>
+        <v>1392</v>
       </c>
       <c r="H2376" t="s">
         <v>9</v>
@@ -66602,7 +66605,7 @@
         <v>7.90999984741211</v>
       </c>
       <c r="G2377" t="s">
-        <v>1392</v>
+        <v>1393</v>
       </c>
       <c r="H2377" t="s">
         <v>9</v>
@@ -66628,7 +66631,7 @@
         <v>7.96000003814697</v>
       </c>
       <c r="G2378" t="s">
-        <v>1393</v>
+        <v>1394</v>
       </c>
       <c r="H2378" t="s">
         <v>9</v>
@@ -66654,7 +66657,7 @@
         <v>7.98999977111816</v>
       </c>
       <c r="G2379" t="s">
-        <v>1394</v>
+        <v>1395</v>
       </c>
       <c r="H2379" t="s">
         <v>9</v>
@@ -66680,7 +66683,7 @@
         <v>8.35999965667725</v>
       </c>
       <c r="G2380" t="s">
-        <v>1395</v>
+        <v>1396</v>
       </c>
       <c r="H2380" t="s">
         <v>9</v>
@@ -66706,7 +66709,7 @@
         <v>8.53999996185303</v>
       </c>
       <c r="G2381" t="s">
-        <v>1396</v>
+        <v>1397</v>
       </c>
       <c r="H2381" t="s">
         <v>9</v>
@@ -66732,7 +66735,7 @@
         <v>8.47000026702881</v>
       </c>
       <c r="G2382" t="s">
-        <v>1397</v>
+        <v>1398</v>
       </c>
       <c r="H2382" t="s">
         <v>9</v>
@@ -66758,7 +66761,7 @@
         <v>8.52000045776367</v>
       </c>
       <c r="G2383" t="s">
-        <v>1398</v>
+        <v>1399</v>
       </c>
       <c r="H2383" t="s">
         <v>9</v>
@@ -66784,7 +66787,7 @@
         <v>8.36999988555908</v>
       </c>
       <c r="G2384" t="s">
-        <v>1399</v>
+        <v>1400</v>
       </c>
       <c r="H2384" t="s">
         <v>9</v>
@@ -66810,7 +66813,7 @@
         <v>8.67000007629395</v>
       </c>
       <c r="G2385" t="s">
-        <v>1400</v>
+        <v>1401</v>
       </c>
       <c r="H2385" t="s">
         <v>9</v>
@@ -66836,7 +66839,7 @@
         <v>8.59000015258789</v>
       </c>
       <c r="G2386" t="s">
-        <v>1401</v>
+        <v>1402</v>
       </c>
       <c r="H2386" t="s">
         <v>9</v>
@@ -66862,7 +66865,7 @@
         <v>8.52999973297119</v>
       </c>
       <c r="G2387" t="s">
-        <v>1402</v>
+        <v>1403</v>
       </c>
       <c r="H2387" t="s">
         <v>9</v>
@@ -66888,7 +66891,7 @@
         <v>8.65999984741211</v>
       </c>
       <c r="G2388" t="s">
-        <v>1403</v>
+        <v>1404</v>
       </c>
       <c r="H2388" t="s">
         <v>9</v>
@@ -66914,7 +66917,7 @@
         <v>8.64999961853027</v>
       </c>
       <c r="G2389" t="s">
-        <v>1404</v>
+        <v>1405</v>
       </c>
       <c r="H2389" t="s">
         <v>9</v>
@@ -66940,7 +66943,7 @@
         <v>8.82999992370605</v>
       </c>
       <c r="G2390" t="s">
-        <v>1405</v>
+        <v>1406</v>
       </c>
       <c r="H2390" t="s">
         <v>9</v>
@@ -66966,7 +66969,7 @@
         <v>8.8100004196167</v>
       </c>
       <c r="G2391" t="s">
-        <v>1406</v>
+        <v>1407</v>
       </c>
       <c r="H2391" t="s">
         <v>9</v>
@@ -66992,7 +66995,7 @@
         <v>8.55000019073486</v>
       </c>
       <c r="G2392" t="s">
-        <v>1407</v>
+        <v>1408</v>
       </c>
       <c r="H2392" t="s">
         <v>9</v>
@@ -67018,7 +67021,7 @@
         <v>8.52000045776367</v>
       </c>
       <c r="G2393" t="s">
-        <v>1398</v>
+        <v>1399</v>
       </c>
       <c r="H2393" t="s">
         <v>9</v>
@@ -67044,7 +67047,7 @@
         <v>8.52000045776367</v>
       </c>
       <c r="G2394" t="s">
-        <v>1398</v>
+        <v>1399</v>
       </c>
       <c r="H2394" t="s">
         <v>9</v>
@@ -67070,7 +67073,7 @@
         <v>8.42000007629395</v>
       </c>
       <c r="G2395" t="s">
-        <v>1408</v>
+        <v>1409</v>
       </c>
       <c r="H2395" t="s">
         <v>9</v>
@@ -67096,7 +67099,7 @@
         <v>8.63000011444092</v>
       </c>
       <c r="G2396" t="s">
-        <v>1409</v>
+        <v>1410</v>
       </c>
       <c r="H2396" t="s">
         <v>9</v>
@@ -67122,7 +67125,7 @@
         <v>8.57999992370605</v>
       </c>
       <c r="G2397" t="s">
-        <v>1410</v>
+        <v>1411</v>
       </c>
       <c r="H2397" t="s">
         <v>9</v>
@@ -67148,7 +67151,7 @@
         <v>8.55000019073486</v>
       </c>
       <c r="G2398" t="s">
-        <v>1407</v>
+        <v>1408</v>
       </c>
       <c r="H2398" t="s">
         <v>9</v>
@@ -67174,7 +67177,7 @@
         <v>8.78999996185303</v>
       </c>
       <c r="G2399" t="s">
-        <v>1411</v>
+        <v>1412</v>
       </c>
       <c r="H2399" t="s">
         <v>9</v>
@@ -67200,7 +67203,7 @@
         <v>8.56999969482422</v>
       </c>
       <c r="G2400" t="s">
-        <v>1412</v>
+        <v>1413</v>
       </c>
       <c r="H2400" t="s">
         <v>9</v>
@@ -67226,7 +67229,7 @@
         <v>8.53999996185303</v>
       </c>
       <c r="G2401" t="s">
-        <v>1396</v>
+        <v>1397</v>
       </c>
       <c r="H2401" t="s">
         <v>9</v>
@@ -67252,7 +67255,7 @@
         <v>8.56999969482422</v>
       </c>
       <c r="G2402" t="s">
-        <v>1412</v>
+        <v>1413</v>
       </c>
       <c r="H2402" t="s">
         <v>9</v>
@@ -67278,7 +67281,7 @@
         <v>8</v>
       </c>
       <c r="G2403" t="s">
-        <v>1413</v>
+        <v>1414</v>
       </c>
       <c r="H2403" t="s">
         <v>9</v>
@@ -67304,7 +67307,7 @@
         <v>7.82000017166138</v>
       </c>
       <c r="G2404" t="s">
-        <v>1414</v>
+        <v>1415</v>
       </c>
       <c r="H2404" t="s">
         <v>9</v>
@@ -67330,7 +67333,7 @@
         <v>7.69999980926514</v>
       </c>
       <c r="G2405" t="s">
-        <v>1415</v>
+        <v>1416</v>
       </c>
       <c r="H2405" t="s">
         <v>9</v>
@@ -67356,7 +67359,7 @@
         <v>7.65000009536743</v>
       </c>
       <c r="G2406" t="s">
-        <v>1416</v>
+        <v>1417</v>
       </c>
       <c r="H2406" t="s">
         <v>9</v>
@@ -67382,7 +67385,7 @@
         <v>7.57999992370605</v>
       </c>
       <c r="G2407" t="s">
-        <v>1417</v>
+        <v>1418</v>
       </c>
       <c r="H2407" t="s">
         <v>9</v>
@@ -67408,7 +67411,7 @@
         <v>7.59999990463257</v>
       </c>
       <c r="G2408" t="s">
-        <v>1418</v>
+        <v>1419</v>
       </c>
       <c r="H2408" t="s">
         <v>9</v>
@@ -67434,7 +67437,7 @@
         <v>7.82000017166138</v>
       </c>
       <c r="G2409" t="s">
-        <v>1414</v>
+        <v>1415</v>
       </c>
       <c r="H2409" t="s">
         <v>9</v>
@@ -67460,7 +67463,7 @@
         <v>7.75</v>
       </c>
       <c r="G2410" t="s">
-        <v>1419</v>
+        <v>1420</v>
       </c>
       <c r="H2410" t="s">
         <v>9</v>
@@ -67486,7 +67489,7 @@
         <v>7.69000005722046</v>
       </c>
       <c r="G2411" t="s">
-        <v>1420</v>
+        <v>1421</v>
       </c>
       <c r="H2411" t="s">
         <v>9</v>
@@ -67512,7 +67515,7 @@
         <v>7.76999998092651</v>
       </c>
       <c r="G2412" t="s">
-        <v>1421</v>
+        <v>1422</v>
       </c>
       <c r="H2412" t="s">
         <v>9</v>
@@ -67538,7 +67541,7 @@
         <v>8.02000045776367</v>
       </c>
       <c r="G2413" t="s">
-        <v>1422</v>
+        <v>1423</v>
       </c>
       <c r="H2413" t="s">
         <v>9</v>
@@ -67564,7 +67567,7 @@
         <v>7.90999984741211</v>
       </c>
       <c r="G2414" t="s">
-        <v>1392</v>
+        <v>1393</v>
       </c>
       <c r="H2414" t="s">
         <v>9</v>
@@ -67590,7 +67593,7 @@
         <v>7.84999990463257</v>
       </c>
       <c r="G2415" t="s">
-        <v>1423</v>
+        <v>1424</v>
       </c>
       <c r="H2415" t="s">
         <v>9</v>
@@ -67616,7 +67619,7 @@
         <v>7.73999977111816</v>
       </c>
       <c r="G2416" t="s">
-        <v>1424</v>
+        <v>1425</v>
       </c>
       <c r="H2416" t="s">
         <v>9</v>
@@ -67642,7 +67645,7 @@
         <v>7.80000019073486</v>
       </c>
       <c r="G2417" t="s">
-        <v>1425</v>
+        <v>1426</v>
       </c>
       <c r="H2417" t="s">
         <v>9</v>
@@ -67668,7 +67671,7 @@
         <v>7.65999984741211</v>
       </c>
       <c r="G2418" t="s">
-        <v>1426</v>
+        <v>1427</v>
       </c>
       <c r="H2418" t="s">
         <v>9</v>
@@ -67694,7 +67697,7 @@
         <v>7.69999980926514</v>
       </c>
       <c r="G2419" t="s">
-        <v>1415</v>
+        <v>1416</v>
       </c>
       <c r="H2419" t="s">
         <v>9</v>
@@ -67720,7 +67723,7 @@
         <v>7.65000009536743</v>
       </c>
       <c r="G2420" t="s">
-        <v>1416</v>
+        <v>1417</v>
       </c>
       <c r="H2420" t="s">
         <v>9</v>
@@ -67746,7 +67749,7 @@
         <v>7.63000011444092</v>
       </c>
       <c r="G2421" t="s">
-        <v>1391</v>
+        <v>1392</v>
       </c>
       <c r="H2421" t="s">
         <v>9</v>
@@ -67772,7 +67775,7 @@
         <v>7.6100001335144</v>
       </c>
       <c r="G2422" t="s">
-        <v>1427</v>
+        <v>1428</v>
       </c>
       <c r="H2422" t="s">
         <v>9</v>
@@ -67798,7 +67801,7 @@
         <v>7.48000001907349</v>
       </c>
       <c r="G2423" t="s">
-        <v>1428</v>
+        <v>1429</v>
       </c>
       <c r="H2423" t="s">
         <v>9</v>
@@ -67824,7 +67827,7 @@
         <v>7.55999994277954</v>
       </c>
       <c r="G2424" t="s">
-        <v>1429</v>
+        <v>1430</v>
       </c>
       <c r="H2424" t="s">
         <v>9</v>
@@ -67850,7 +67853,7 @@
         <v>7.55999994277954</v>
       </c>
       <c r="G2425" t="s">
-        <v>1429</v>
+        <v>1430</v>
       </c>
       <c r="H2425" t="s">
         <v>9</v>
@@ -67876,7 +67879,7 @@
         <v>7.53999996185303</v>
       </c>
       <c r="G2426" t="s">
-        <v>1388</v>
+        <v>1389</v>
       </c>
       <c r="H2426" t="s">
         <v>9</v>
@@ -67902,7 +67905,7 @@
         <v>7.59999990463257</v>
       </c>
       <c r="G2427" t="s">
-        <v>1418</v>
+        <v>1419</v>
       </c>
       <c r="H2427" t="s">
         <v>9</v>
@@ -67928,7 +67931,7 @@
         <v>7.80000019073486</v>
       </c>
       <c r="G2428" t="s">
-        <v>1425</v>
+        <v>1426</v>
       </c>
       <c r="H2428" t="s">
         <v>9</v>
@@ -67954,7 +67957,7 @@
         <v>7.6399998664856</v>
       </c>
       <c r="G2429" t="s">
-        <v>1390</v>
+        <v>1391</v>
       </c>
       <c r="H2429" t="s">
         <v>9</v>
@@ -67980,7 +67983,7 @@
         <v>7.57000017166138</v>
       </c>
       <c r="G2430" t="s">
-        <v>1430</v>
+        <v>1431</v>
       </c>
       <c r="H2430" t="s">
         <v>9</v>
@@ -68006,7 +68009,7 @@
         <v>7.67999982833862</v>
       </c>
       <c r="G2431" t="s">
-        <v>1431</v>
+        <v>1432</v>
       </c>
       <c r="H2431" t="s">
         <v>9</v>
@@ -68032,7 +68035,7 @@
         <v>7.65999984741211</v>
       </c>
       <c r="G2432" t="s">
-        <v>1426</v>
+        <v>1427</v>
       </c>
       <c r="H2432" t="s">
         <v>9</v>
@@ -68058,7 +68061,7 @@
         <v>7.59999990463257</v>
       </c>
       <c r="G2433" t="s">
-        <v>1418</v>
+        <v>1419</v>
       </c>
       <c r="H2433" t="s">
         <v>9</v>
@@ -68084,7 +68087,7 @@
         <v>7.46000003814697</v>
       </c>
       <c r="G2434" t="s">
-        <v>1432</v>
+        <v>1433</v>
       </c>
       <c r="H2434" t="s">
         <v>9</v>
@@ -68110,7 +68113,7 @@
         <v>7.42000007629395</v>
       </c>
       <c r="G2435" t="s">
-        <v>1433</v>
+        <v>1434</v>
       </c>
       <c r="H2435" t="s">
         <v>9</v>
@@ -68136,7 +68139,7 @@
         <v>7.42999982833862</v>
       </c>
       <c r="G2436" t="s">
-        <v>1434</v>
+        <v>1435</v>
       </c>
       <c r="H2436" t="s">
         <v>9</v>
@@ -68162,7 +68165,7 @@
         <v>7.1399998664856</v>
       </c>
       <c r="G2437" t="s">
-        <v>1435</v>
+        <v>1436</v>
       </c>
       <c r="H2437" t="s">
         <v>9</v>
@@ -68188,7 +68191,7 @@
         <v>7.17999982833862</v>
       </c>
       <c r="G2438" t="s">
-        <v>1436</v>
+        <v>1437</v>
       </c>
       <c r="H2438" t="s">
         <v>9</v>
@@ -68214,7 +68217,7 @@
         <v>6.92000007629395</v>
       </c>
       <c r="G2439" t="s">
-        <v>1437</v>
+        <v>1438</v>
       </c>
       <c r="H2439" t="s">
         <v>9</v>
@@ -68240,7 +68243,7 @@
         <v>6.67999982833862</v>
       </c>
       <c r="G2440" t="s">
-        <v>1438</v>
+        <v>1439</v>
       </c>
       <c r="H2440" t="s">
         <v>9</v>
@@ -68266,7 +68269,7 @@
         <v>6.8899998664856</v>
       </c>
       <c r="G2441" t="s">
-        <v>1439</v>
+        <v>1440</v>
       </c>
       <c r="H2441" t="s">
         <v>9</v>
@@ -68292,7 +68295,7 @@
         <v>6.82000017166138</v>
       </c>
       <c r="G2442" t="s">
-        <v>1440</v>
+        <v>1441</v>
       </c>
       <c r="H2442" t="s">
         <v>9</v>
@@ -68318,7 +68321,7 @@
         <v>6.65999984741211</v>
       </c>
       <c r="G2443" t="s">
-        <v>1441</v>
+        <v>1442</v>
       </c>
       <c r="H2443" t="s">
         <v>9</v>
@@ -68344,7 +68347,7 @@
         <v>6.61999988555908</v>
       </c>
       <c r="G2444" t="s">
-        <v>1442</v>
+        <v>1443</v>
       </c>
       <c r="H2444" t="s">
         <v>9</v>
@@ -68370,7 +68373,7 @@
         <v>6.48000001907349</v>
       </c>
       <c r="G2445" t="s">
-        <v>1443</v>
+        <v>1444</v>
       </c>
       <c r="H2445" t="s">
         <v>9</v>
@@ -68396,7 +68399,7 @@
         <v>6.36999988555908</v>
       </c>
       <c r="G2446" t="s">
-        <v>1444</v>
+        <v>1445</v>
       </c>
       <c r="H2446" t="s">
         <v>9</v>
@@ -68422,7 +68425,7 @@
         <v>6.48999977111816</v>
       </c>
       <c r="G2447" t="s">
-        <v>1445</v>
+        <v>1446</v>
       </c>
       <c r="H2447" t="s">
         <v>9</v>
@@ -68448,7 +68451,7 @@
         <v>6.5</v>
       </c>
       <c r="G2448" t="s">
-        <v>1446</v>
+        <v>1447</v>
       </c>
       <c r="H2448" t="s">
         <v>9</v>
@@ -68474,7 +68477,7 @@
         <v>6.51999998092651</v>
       </c>
       <c r="G2449" t="s">
-        <v>1447</v>
+        <v>1448</v>
       </c>
       <c r="H2449" t="s">
         <v>9</v>
@@ -68500,7 +68503,7 @@
         <v>6.55000019073486</v>
       </c>
       <c r="G2450" t="s">
-        <v>1448</v>
+        <v>1449</v>
       </c>
       <c r="H2450" t="s">
         <v>9</v>
@@ -68526,7 +68529,7 @@
         <v>6.75</v>
       </c>
       <c r="G2451" t="s">
-        <v>1449</v>
+        <v>1450</v>
       </c>
       <c r="H2451" t="s">
         <v>9</v>
@@ -68552,7 +68555,7 @@
         <v>6.98000001907349</v>
       </c>
       <c r="G2452" t="s">
-        <v>1450</v>
+        <v>1451</v>
       </c>
       <c r="H2452" t="s">
         <v>9</v>
@@ -68578,7 +68581,7 @@
         <v>7</v>
       </c>
       <c r="G2453" t="s">
-        <v>1451</v>
+        <v>1452</v>
       </c>
       <c r="H2453" t="s">
         <v>9</v>
@@ -68604,7 +68607,7 @@
         <v>6.84000015258789</v>
       </c>
       <c r="G2454" t="s">
-        <v>1452</v>
+        <v>1453</v>
       </c>
       <c r="H2454" t="s">
         <v>9</v>
@@ -68630,7 +68633,7 @@
         <v>6.61999988555908</v>
       </c>
       <c r="G2455" t="s">
-        <v>1442</v>
+        <v>1443</v>
       </c>
       <c r="H2455" t="s">
         <v>9</v>
@@ -68656,7 +68659,7 @@
         <v>6.65999984741211</v>
       </c>
       <c r="G2456" t="s">
-        <v>1441</v>
+        <v>1442</v>
       </c>
       <c r="H2456" t="s">
         <v>9</v>
@@ -68682,7 +68685,7 @@
         <v>6.48999977111816</v>
       </c>
       <c r="G2457" t="s">
-        <v>1445</v>
+        <v>1446</v>
       </c>
       <c r="H2457" t="s">
         <v>9</v>
@@ -68708,7 +68711,7 @@
         <v>6.5</v>
       </c>
       <c r="G2458" t="s">
-        <v>1446</v>
+        <v>1447</v>
       </c>
       <c r="H2458" t="s">
         <v>9</v>
@@ -68734,7 +68737,7 @@
         <v>6.36999988555908</v>
       </c>
       <c r="G2459" t="s">
-        <v>1444</v>
+        <v>1445</v>
       </c>
       <c r="H2459" t="s">
         <v>9</v>
@@ -68760,7 +68763,7 @@
         <v>6.65000009536743</v>
       </c>
       <c r="G2460" t="s">
-        <v>1453</v>
+        <v>1454</v>
       </c>
       <c r="H2460" t="s">
         <v>9</v>
@@ -68786,7 +68789,7 @@
         <v>6.84999990463257</v>
       </c>
       <c r="G2461" t="s">
-        <v>1454</v>
+        <v>1455</v>
       </c>
       <c r="H2461" t="s">
         <v>9</v>
@@ -68812,7 +68815,7 @@
         <v>6.92000007629395</v>
       </c>
       <c r="G2462" t="s">
-        <v>1437</v>
+        <v>1438</v>
       </c>
       <c r="H2462" t="s">
         <v>9</v>
@@ -68838,7 +68841,7 @@
         <v>6.82000017166138</v>
       </c>
       <c r="G2463" t="s">
-        <v>1440</v>
+        <v>1441</v>
       </c>
       <c r="H2463" t="s">
         <v>9</v>
@@ -68864,7 +68867,7 @@
         <v>6.76999998092651</v>
       </c>
       <c r="G2464" t="s">
-        <v>1455</v>
+        <v>1456</v>
       </c>
       <c r="H2464" t="s">
         <v>9</v>
@@ -68890,7 +68893,7 @@
         <v>7.6100001335144</v>
       </c>
       <c r="G2465" t="s">
-        <v>1427</v>
+        <v>1428</v>
       </c>
       <c r="H2465" t="s">
         <v>9</v>
@@ -68916,7 +68919,7 @@
         <v>7.69999980926514</v>
       </c>
       <c r="G2466" t="s">
-        <v>1415</v>
+        <v>1416</v>
       </c>
       <c r="H2466" t="s">
         <v>9</v>
@@ -68942,7 +68945,7 @@
         <v>7.5</v>
       </c>
       <c r="G2467" t="s">
-        <v>1456</v>
+        <v>1457</v>
       </c>
       <c r="H2467" t="s">
         <v>9</v>
@@ -68968,7 +68971,7 @@
         <v>7.42999982833862</v>
       </c>
       <c r="G2468" t="s">
-        <v>1434</v>
+        <v>1435</v>
       </c>
       <c r="H2468" t="s">
         <v>9</v>
@@ -68994,7 +68997,7 @@
         <v>7.40000009536743</v>
       </c>
       <c r="G2469" t="s">
-        <v>1387</v>
+        <v>1388</v>
       </c>
       <c r="H2469" t="s">
         <v>9</v>
@@ -69020,7 +69023,7 @@
         <v>7.26000022888184</v>
       </c>
       <c r="G2470" t="s">
-        <v>1457</v>
+        <v>1458</v>
       </c>
       <c r="H2470" t="s">
         <v>9</v>
@@ -69046,7 +69049,7 @@
         <v>7.1399998664856</v>
       </c>
       <c r="G2471" t="s">
-        <v>1435</v>
+        <v>1436</v>
       </c>
       <c r="H2471" t="s">
         <v>9</v>
@@ -69072,7 +69075,7 @@
         <v>7.05000019073486</v>
       </c>
       <c r="G2472" t="s">
-        <v>1458</v>
+        <v>1459</v>
       </c>
       <c r="H2472" t="s">
         <v>9</v>
@@ -69098,7 +69101,7 @@
         <v>7.15000009536743</v>
       </c>
       <c r="G2473" t="s">
-        <v>1459</v>
+        <v>1460</v>
       </c>
       <c r="H2473" t="s">
         <v>9</v>
@@ -69124,7 +69127,7 @@
         <v>7.15999984741211</v>
       </c>
       <c r="G2474" t="s">
-        <v>1460</v>
+        <v>1461</v>
       </c>
       <c r="H2474" t="s">
         <v>9</v>
@@ -69150,7 +69153,7 @@
         <v>7.01999998092651</v>
       </c>
       <c r="G2475" t="s">
-        <v>1461</v>
+        <v>1462</v>
       </c>
       <c r="H2475" t="s">
         <v>9</v>
@@ -69176,7 +69179,7 @@
         <v>6.96999979019165</v>
       </c>
       <c r="G2476" t="s">
-        <v>1462</v>
+        <v>1463</v>
       </c>
       <c r="H2476" t="s">
         <v>9</v>
@@ -69202,7 +69205,7 @@
         <v>6.92000007629395</v>
       </c>
       <c r="G2477" t="s">
-        <v>1437</v>
+        <v>1438</v>
       </c>
       <c r="H2477" t="s">
         <v>9</v>
@@ -69228,7 +69231,7 @@
         <v>7.03000020980835</v>
       </c>
       <c r="G2478" t="s">
-        <v>1463</v>
+        <v>1464</v>
       </c>
       <c r="H2478" t="s">
         <v>9</v>
@@ -69254,7 +69257,7 @@
         <v>7.05000019073486</v>
       </c>
       <c r="G2479" t="s">
-        <v>1458</v>
+        <v>1459</v>
       </c>
       <c r="H2479" t="s">
         <v>9</v>
@@ -69280,7 +69283,7 @@
         <v>7</v>
       </c>
       <c r="G2480" t="s">
-        <v>1451</v>
+        <v>1452</v>
       </c>
       <c r="H2480" t="s">
         <v>9</v>
@@ -69306,7 +69309,7 @@
         <v>6.96000003814697</v>
       </c>
       <c r="G2481" t="s">
-        <v>1464</v>
+        <v>1465</v>
       </c>
       <c r="H2481" t="s">
         <v>9</v>
@@ -69332,7 +69335,7 @@
         <v>7.03999996185303</v>
       </c>
       <c r="G2482" t="s">
-        <v>1465</v>
+        <v>1466</v>
       </c>
       <c r="H2482" t="s">
         <v>9</v>
@@ -69358,7 +69361,7 @@
         <v>7.17999982833862</v>
       </c>
       <c r="G2483" t="s">
-        <v>1436</v>
+        <v>1437</v>
       </c>
       <c r="H2483" t="s">
         <v>9</v>
@@ -69384,7 +69387,7 @@
         <v>7.1399998664856</v>
       </c>
       <c r="G2484" t="s">
-        <v>1435</v>
+        <v>1436</v>
       </c>
       <c r="H2484" t="s">
         <v>9</v>
@@ -69410,7 +69413,7 @@
         <v>7.07999992370605</v>
       </c>
       <c r="G2485" t="s">
-        <v>1466</v>
+        <v>1467</v>
       </c>
       <c r="H2485" t="s">
         <v>9</v>
@@ -69436,7 +69439,7 @@
         <v>7.21000003814697</v>
       </c>
       <c r="G2486" t="s">
-        <v>1467</v>
+        <v>1468</v>
       </c>
       <c r="H2486" t="s">
         <v>9</v>
@@ -69462,7 +69465,7 @@
         <v>6.86999988555908</v>
       </c>
       <c r="G2487" t="s">
-        <v>1468</v>
+        <v>1469</v>
       </c>
       <c r="H2487" t="s">
         <v>9</v>
@@ -69488,7 +69491,7 @@
         <v>7.05000019073486</v>
       </c>
       <c r="G2488" t="s">
-        <v>1458</v>
+        <v>1459</v>
       </c>
       <c r="H2488" t="s">
         <v>9</v>
@@ -69514,7 +69517,7 @@
         <v>7.09000015258789</v>
       </c>
       <c r="G2489" t="s">
-        <v>1469</v>
+        <v>1470</v>
       </c>
       <c r="H2489" t="s">
         <v>9</v>
@@ -69540,7 +69543,7 @@
         <v>7</v>
       </c>
       <c r="G2490" t="s">
-        <v>1451</v>
+        <v>1452</v>
       </c>
       <c r="H2490" t="s">
         <v>9</v>
@@ -69566,7 +69569,7 @@
         <v>6.98999977111816</v>
       </c>
       <c r="G2491" t="s">
-        <v>1470</v>
+        <v>1471</v>
       </c>
       <c r="H2491" t="s">
         <v>9</v>
@@ -69592,7 +69595,7 @@
         <v>6.94000005722046</v>
       </c>
       <c r="G2492" t="s">
-        <v>1471</v>
+        <v>1472</v>
       </c>
       <c r="H2492" t="s">
         <v>9</v>
@@ -69618,7 +69621,7 @@
         <v>6.90000009536743</v>
       </c>
       <c r="G2493" t="s">
-        <v>1472</v>
+        <v>1473</v>
       </c>
       <c r="H2493" t="s">
         <v>9</v>
@@ -69644,7 +69647,7 @@
         <v>7</v>
       </c>
       <c r="G2494" t="s">
-        <v>1451</v>
+        <v>1452</v>
       </c>
       <c r="H2494" t="s">
         <v>9</v>
@@ -69670,7 +69673,7 @@
         <v>7.11999988555908</v>
       </c>
       <c r="G2495" t="s">
-        <v>1473</v>
+        <v>1474</v>
       </c>
       <c r="H2495" t="s">
         <v>9</v>
@@ -69696,7 +69699,7 @@
         <v>7.17999982833862</v>
       </c>
       <c r="G2496" t="s">
-        <v>1436</v>
+        <v>1437</v>
       </c>
       <c r="H2496" t="s">
         <v>9</v>
@@ -69722,7 +69725,7 @@
         <v>7.15000009536743</v>
       </c>
       <c r="G2497" t="s">
-        <v>1459</v>
+        <v>1460</v>
       </c>
       <c r="H2497" t="s">
         <v>9</v>
@@ -69748,7 +69751,7 @@
         <v>7.07999992370605</v>
       </c>
       <c r="G2498" t="s">
-        <v>1466</v>
+        <v>1467</v>
       </c>
       <c r="H2498" t="s">
         <v>9</v>
@@ -69774,7 +69777,7 @@
         <v>7.05000019073486</v>
       </c>
       <c r="G2499" t="s">
-        <v>1458</v>
+        <v>1459</v>
       </c>
       <c r="H2499" t="s">
         <v>9</v>
@@ -69800,7 +69803,7 @@
         <v>6.8600001335144</v>
       </c>
       <c r="G2500" t="s">
-        <v>1474</v>
+        <v>1475</v>
       </c>
       <c r="H2500" t="s">
         <v>9</v>
@@ -69826,7 +69829,7 @@
         <v>6.98000001907349</v>
       </c>
       <c r="G2501" t="s">
-        <v>1450</v>
+        <v>1451</v>
       </c>
       <c r="H2501" t="s">
         <v>9</v>
@@ -69852,7 +69855,7 @@
         <v>6.8899998664856</v>
       </c>
       <c r="G2502" t="s">
-        <v>1439</v>
+        <v>1440</v>
       </c>
       <c r="H2502" t="s">
         <v>9</v>
@@ -69878,7 +69881,7 @@
         <v>6.92999982833862</v>
       </c>
       <c r="G2503" t="s">
-        <v>1475</v>
+        <v>1476</v>
       </c>
       <c r="H2503" t="s">
         <v>9</v>
@@ -69904,7 +69907,7 @@
         <v>6.80999994277954</v>
       </c>
       <c r="G2504" t="s">
-        <v>1476</v>
+        <v>1477</v>
       </c>
       <c r="H2504" t="s">
         <v>9</v>
@@ -69930,7 +69933,7 @@
         <v>6.98999977111816</v>
       </c>
       <c r="G2505" t="s">
-        <v>1470</v>
+        <v>1471</v>
       </c>
       <c r="H2505" t="s">
         <v>9</v>
@@ -69956,7 +69959,7 @@
         <v>6.82999992370605</v>
       </c>
       <c r="G2506" t="s">
-        <v>1477</v>
+        <v>1478</v>
       </c>
       <c r="H2506" t="s">
         <v>9</v>
@@ -69982,7 +69985,7 @@
         <v>6.8899998664856</v>
       </c>
       <c r="G2507" t="s">
-        <v>1439</v>
+        <v>1440</v>
       </c>
       <c r="H2507" t="s">
         <v>9</v>
@@ -70008,7 +70011,7 @@
         <v>7.09999990463257</v>
       </c>
       <c r="G2508" t="s">
-        <v>1478</v>
+        <v>1479</v>
       </c>
       <c r="H2508" t="s">
         <v>9</v>
@@ -70034,7 +70037,7 @@
         <v>7.30999994277954</v>
       </c>
       <c r="G2509" t="s">
-        <v>1479</v>
+        <v>1480</v>
       </c>
       <c r="H2509" t="s">
         <v>9</v>
@@ -70060,7 +70063,7 @@
         <v>7.32999992370605</v>
       </c>
       <c r="G2510" t="s">
-        <v>1480</v>
+        <v>1481</v>
       </c>
       <c r="H2510" t="s">
         <v>9</v>
@@ -70086,7 +70089,7 @@
         <v>7.30000019073486</v>
       </c>
       <c r="G2511" t="s">
-        <v>1481</v>
+        <v>1482</v>
       </c>
       <c r="H2511" t="s">
         <v>9</v>
@@ -70112,7 +70115,7 @@
         <v>6.88000011444092</v>
       </c>
       <c r="G2512" t="s">
-        <v>1482</v>
+        <v>1483</v>
       </c>
       <c r="H2512" t="s">
         <v>9</v>
@@ -70138,7 +70141,7 @@
         <v>6.63000011444092</v>
       </c>
       <c r="G2513" t="s">
-        <v>1483</v>
+        <v>1484</v>
       </c>
       <c r="H2513" t="s">
         <v>9</v>
@@ -70164,7 +70167,7 @@
         <v>6.57000017166138</v>
       </c>
       <c r="G2514" t="s">
-        <v>1484</v>
+        <v>1485</v>
       </c>
       <c r="H2514" t="s">
         <v>9</v>
@@ -70190,7 +70193,7 @@
         <v>6.63000011444092</v>
       </c>
       <c r="G2515" t="s">
-        <v>1483</v>
+        <v>1484</v>
       </c>
       <c r="H2515" t="s">
         <v>9</v>
@@ -70216,7 +70219,7 @@
         <v>6.76000022888184</v>
       </c>
       <c r="G2516" t="s">
-        <v>1485</v>
+        <v>1486</v>
       </c>
       <c r="H2516" t="s">
         <v>9</v>
@@ -70242,7 +70245,7 @@
         <v>6.86999988555908</v>
       </c>
       <c r="G2517" t="s">
-        <v>1468</v>
+        <v>1469</v>
       </c>
       <c r="H2517" t="s">
         <v>9</v>
@@ -70268,7 +70271,7 @@
         <v>6.92000007629395</v>
       </c>
       <c r="G2518" t="s">
-        <v>1437</v>
+        <v>1438</v>
       </c>
       <c r="H2518" t="s">
         <v>9</v>
@@ -70294,7 +70297,7 @@
         <v>6.84999990463257</v>
       </c>
       <c r="G2519" t="s">
-        <v>1454</v>
+        <v>1455</v>
       </c>
       <c r="H2519" t="s">
         <v>9</v>
@@ -70302,7 +70305,7 @@
     </row>
     <row r="2520">
       <c r="A2520" s="1" t="n">
-        <v>45987.6913078704</v>
+        <v>45987.3333333333</v>
       </c>
       <c r="B2520" t="n">
         <v>23648</v>
@@ -70320,9 +70323,35 @@
         <v>6.84999990463257</v>
       </c>
       <c r="G2520" t="s">
-        <v>1454</v>
+        <v>1455</v>
       </c>
       <c r="H2520" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2521">
+      <c r="A2521" s="1" t="n">
+        <v>45988.6910648148</v>
+      </c>
+      <c r="B2521" t="n">
+        <v>17473</v>
+      </c>
+      <c r="C2521" t="n">
+        <v>7</v>
+      </c>
+      <c r="D2521" t="n">
+        <v>6.84000015258789</v>
+      </c>
+      <c r="E2521" t="n">
+        <v>6.92000007629395</v>
+      </c>
+      <c r="F2521" t="n">
+        <v>6.86999988555908</v>
+      </c>
+      <c r="G2521" t="s">
+        <v>1469</v>
+      </c>
+      <c r="H2521" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/BAN.MI.xlsx
+++ b/data/BAN.MI.xlsx
@@ -38,94 +38,94 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">3.66912961006165</t>
+    <t xml:space="preserve">3.6691300868988</t>
   </si>
   <si>
     <t xml:space="preserve">BAN.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">3.68330216407776</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.59039306640625</t>
+    <t xml:space="preserve">3.68330240249634</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.59039378166199</t>
   </si>
   <si>
     <t xml:space="preserve">3.46283960342407</t>
   </si>
   <si>
-    <t xml:space="preserve">3.41874718666077</t>
+    <t xml:space="preserve">3.41874694824219</t>
   </si>
   <si>
     <t xml:space="preserve">3.35733246803284</t>
   </si>
   <si>
-    <t xml:space="preserve">3.44551801681519</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.46441435813904</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.45181679725647</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.43134498596191</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.38410258293152</t>
+    <t xml:space="preserve">3.44551753997803</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.46441459655762</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.45181655883789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.43134450912476</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.3841028213501</t>
   </si>
   <si>
     <t xml:space="preserve">3.40929865837097</t>
   </si>
   <si>
-    <t xml:space="preserve">3.11639857292175</t>
+    <t xml:space="preserve">3.11639833450317</t>
   </si>
   <si>
     <t xml:space="preserve">3.24080228805542</t>
   </si>
   <si>
-    <t xml:space="preserve">3.29119348526001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.21245694160461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.26757287979126</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.1935601234436</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.13372015953064</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.22820448875427</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.16678953170776</t>
+    <t xml:space="preserve">3.29119324684143</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.21245718002319</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.26757264137268</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.19356036186218</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.1337206363678</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.22820425033569</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.16678929328918</t>
   </si>
   <si>
     <t xml:space="preserve">3.17308902740479</t>
   </si>
   <si>
-    <t xml:space="preserve">3.0707311630249</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.14946746826172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.05025959014893</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.92900514602661</t>
+    <t xml:space="preserve">3.07073092460632</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.1494677066803</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.0502598285675</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.92900466918945</t>
   </si>
   <si>
     <t xml:space="preserve">2.91325759887695</t>
   </si>
   <si>
-    <t xml:space="preserve">2.8345205783844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.82664704322815</t>
+    <t xml:space="preserve">2.83452081680298</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.82664680480957</t>
   </si>
   <si>
     <t xml:space="preserve">2.75263476371765</t>
@@ -137,16 +137,16 @@
     <t xml:space="preserve">2.75578427314758</t>
   </si>
   <si>
-    <t xml:space="preserve">2.89436054229736</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.98254585266113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.96207451820374</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.99356937408447</t>
+    <t xml:space="preserve">2.89436078071594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.98254561424255</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.96207427978516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.99356889724731</t>
   </si>
   <si>
     <t xml:space="preserve">3.05970788002014</t>
@@ -158,16 +158,16 @@
     <t xml:space="preserve">3.06915640830994</t>
   </si>
   <si>
-    <t xml:space="preserve">2.96364903450012</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.99199438095093</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.00774168968201</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.97624707221985</t>
+    <t xml:space="preserve">2.9636492729187</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.99199414253235</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.00774192810059</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.97624731063843</t>
   </si>
   <si>
     <t xml:space="preserve">3.06285738945007</t>
@@ -176,76 +176,76 @@
     <t xml:space="preserve">3.11797308921814</t>
   </si>
   <si>
-    <t xml:space="preserve">3.18096232414246</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.10222601890564</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.13686966896057</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.23292875289917</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.33843564987183</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.30694055557251</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.24395155906677</t>
+    <t xml:space="preserve">3.18096208572388</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.10222578048706</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.13686990737915</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.23292803764343</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.33843588829041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.30694079399109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.24395132064819</t>
   </si>
   <si>
     <t xml:space="preserve">3.24237704277039</t>
   </si>
   <si>
-    <t xml:space="preserve">3.12584686279297</t>
+    <t xml:space="preserve">3.12584662437439</t>
   </si>
   <si>
     <t xml:space="preserve">3.19670987129211</t>
   </si>
   <si>
-    <t xml:space="preserve">3.2030086517334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.10380005836487</t>
+    <t xml:space="preserve">3.20300817489624</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.10380029678345</t>
   </si>
   <si>
     <t xml:space="preserve">3.11324906349182</t>
   </si>
   <si>
-    <t xml:space="preserve">3.14159345626831</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.04711008071899</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.99986839294434</t>
+    <t xml:space="preserve">3.14159393310547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.04710984230042</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.99986815452576</t>
   </si>
   <si>
     <t xml:space="preserve">2.96049952507019</t>
   </si>
   <si>
-    <t xml:space="preserve">3.09435176849365</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.96837306022644</t>
+    <t xml:space="preserve">3.09435224533081</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.96837329864502</t>
   </si>
   <si>
     <t xml:space="preserve">2.86286616325378</t>
   </si>
   <si>
-    <t xml:space="preserve">2.87388968467712</t>
+    <t xml:space="preserve">2.87388944625854</t>
   </si>
   <si>
     <t xml:space="preserve">2.9101083278656</t>
   </si>
   <si>
-    <t xml:space="preserve">2.98569560050964</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.00144290924072</t>
+    <t xml:space="preserve">2.98569536209106</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.00144267082214</t>
   </si>
   <si>
     <t xml:space="preserve">3.01561522483826</t>
@@ -257,49 +257,49 @@
     <t xml:space="preserve">2.9211311340332</t>
   </si>
   <si>
-    <t xml:space="preserve">2.85814237594604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.81404948234558</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.84081959724426</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.80145144462585</t>
+    <t xml:space="preserve">2.85814213752747</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.814049243927</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.84081983566284</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.80145120620728</t>
   </si>
   <si>
     <t xml:space="preserve">2.72901368141174</t>
   </si>
   <si>
-    <t xml:space="preserve">2.65185213088989</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.68177199363708</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.71484136581421</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.76365756988525</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.77940511703491</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.72428917884827</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.59043741226196</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.5353217124939</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.49437785148621</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.48020601272583</t>
+    <t xml:space="preserve">2.65185189247131</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.68177151679993</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.71484112739563</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.76365804672241</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.77940535545349</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.72428941726685</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.5904369354248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.53532147407532</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.49437832832336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.48020553588867</t>
   </si>
   <si>
     <t xml:space="preserve">2.51957440376282</t>
@@ -308,16 +308,16 @@
     <t xml:space="preserve">2.6057276725769</t>
   </si>
   <si>
-    <t xml:space="preserve">2.58784675598145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.56021213531494</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.56183791160583</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.6089780330658</t>
+    <t xml:space="preserve">2.58784651756287</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.56021237373352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.56183815002441</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.60897827148438</t>
   </si>
   <si>
     <t xml:space="preserve">2.59272313117981</t>
@@ -329,7 +329,7 @@
     <t xml:space="preserve">2.60085082054138</t>
   </si>
   <si>
-    <t xml:space="preserve">2.72113966941833</t>
+    <t xml:space="preserve">2.72113990783691</t>
   </si>
   <si>
     <t xml:space="preserve">2.82029747962952</t>
@@ -338,19 +338,19 @@
     <t xml:space="preserve">2.80404233932495</t>
   </si>
   <si>
-    <t xml:space="preserve">2.68212699890137</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.71463799476624</t>
+    <t xml:space="preserve">2.68212723731995</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.71463751792908</t>
   </si>
   <si>
     <t xml:space="preserve">2.44642519950867</t>
   </si>
   <si>
-    <t xml:space="preserve">2.39765930175781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.50331878662109</t>
+    <t xml:space="preserve">2.39765954017639</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.50331854820251</t>
   </si>
   <si>
     <t xml:space="preserve">2.47568488121033</t>
@@ -359,19 +359,19 @@
     <t xml:space="preserve">2.51957416534424</t>
   </si>
   <si>
-    <t xml:space="preserve">2.52770185470581</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.50819540023804</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.40578675270081</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.19446802139282</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.23510575294495</t>
+    <t xml:space="preserve">2.52770209312439</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.50819563865662</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.40578699111938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.19446778297424</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.2351062297821</t>
   </si>
   <si>
     <t xml:space="preserve">2.29525065422058</t>
@@ -380,37 +380,37 @@
     <t xml:space="preserve">2.27411890029907</t>
   </si>
   <si>
-    <t xml:space="preserve">2.35702085494995</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.37327599525452</t>
+    <t xml:space="preserve">2.35702109336853</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.37327647209167</t>
   </si>
   <si>
     <t xml:space="preserve">2.29200005531311</t>
   </si>
   <si>
-    <t xml:space="preserve">2.19284200668335</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.22535276412964</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.2838716506958</t>
+    <t xml:space="preserve">2.19284224510193</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.22535300254822</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.28387188911438</t>
   </si>
   <si>
     <t xml:space="preserve">2.30500388145447</t>
   </si>
   <si>
-    <t xml:space="preserve">2.33101272583008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.33588933944702</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.33263802528381</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.3196337223053</t>
+    <t xml:space="preserve">2.33101224899292</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.33588910102844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.33263778686523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.31963396072388</t>
   </si>
   <si>
     <t xml:space="preserve">2.38140392303467</t>
@@ -422,79 +422,79 @@
     <t xml:space="preserve">2.54395723342896</t>
   </si>
   <si>
-    <t xml:space="preserve">2.56834053993225</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.89669728279114</t>
+    <t xml:space="preserve">2.56834006309509</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.8966977596283</t>
   </si>
   <si>
     <t xml:space="preserve">2.83817863464355</t>
   </si>
   <si>
-    <t xml:space="preserve">2.81217002868652</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.59597420692444</t>
+    <t xml:space="preserve">2.81216955184937</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.59597373008728</t>
   </si>
   <si>
     <t xml:space="preserve">2.57646775245667</t>
   </si>
   <si>
-    <t xml:space="preserve">2.57321667671204</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.56671452522278</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.53257822990417</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.53745460510254</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.6366126537323</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.63011026382446</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.64636564254761</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.65286755561829</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.63823771476746</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.64148926734924</t>
+    <t xml:space="preserve">2.57321691513062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.56671476364136</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.53257846832275</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.5374550819397</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.63661241531372</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.63011074066162</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.64636540412903</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.65286779403687</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.63823819160461</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.64148902893066</t>
   </si>
   <si>
     <t xml:space="preserve">2.69188070297241</t>
   </si>
   <si>
-    <t xml:space="preserve">2.75690174102783</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.79266357421875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.76340413093567</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.7308931350708</t>
+    <t xml:space="preserve">2.75690150260925</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.79266333580017</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.76340389251709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.73089337348938</t>
   </si>
   <si>
     <t xml:space="preserve">2.65449333190918</t>
   </si>
   <si>
-    <t xml:space="preserve">2.65774416923523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.742271900177</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.76828050613403</t>
+    <t xml:space="preserve">2.65774440765381</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.74227213859558</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.76828026771545</t>
   </si>
   <si>
     <t xml:space="preserve">2.70651006698608</t>
@@ -503,19 +503,19 @@
     <t xml:space="preserve">2.72764229774475</t>
   </si>
   <si>
-    <t xml:space="preserve">2.74064636230469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.76990556716919</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.8007915019989</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.69513201713562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.6674976348877</t>
+    <t xml:space="preserve">2.74064660072327</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.76990580558777</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.80079126358032</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.69513177871704</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.66749739646912</t>
   </si>
   <si>
     <t xml:space="preserve">2.64799094200134</t>
@@ -527,13 +527,13 @@
     <t xml:space="preserve">2.59759974479675</t>
   </si>
   <si>
-    <t xml:space="preserve">2.61710643768311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.66587209701538</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.63336133956909</t>
+    <t xml:space="preserve">2.61710619926453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.66587162017822</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.63336110115051</t>
   </si>
   <si>
     <t xml:space="preserve">2.68862962722778</t>
@@ -545,7 +545,7 @@
     <t xml:space="preserve">2.67725086212158</t>
   </si>
   <si>
-    <t xml:space="preserve">2.70976114273071</t>
+    <t xml:space="preserve">2.70976161956787</t>
   </si>
   <si>
     <t xml:space="preserve">2.7552764415741</t>
@@ -554,7 +554,7 @@
     <t xml:space="preserve">2.72601652145386</t>
   </si>
   <si>
-    <t xml:space="preserve">2.72276544570923</t>
+    <t xml:space="preserve">2.72276568412781</t>
   </si>
   <si>
     <t xml:space="preserve">2.82842516899109</t>
@@ -572,13 +572,13 @@
     <t xml:space="preserve">2.70488476753235</t>
   </si>
   <si>
-    <t xml:space="preserve">2.6902551651001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.61222958564758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.73251867294312</t>
+    <t xml:space="preserve">2.69025468826294</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.612229347229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.73251891136169</t>
   </si>
   <si>
     <t xml:space="preserve">2.67562532424927</t>
@@ -587,40 +587,40 @@
     <t xml:space="preserve">2.62360811233521</t>
   </si>
   <si>
-    <t xml:space="preserve">2.59434843063354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.55371022224426</t>
+    <t xml:space="preserve">2.59434866905212</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.55370998382568</t>
   </si>
   <si>
     <t xml:space="preserve">2.55045938491821</t>
   </si>
   <si>
-    <t xml:space="preserve">2.51307225227356</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.46755766868591</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.50169372558594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.58459544181824</t>
+    <t xml:space="preserve">2.51307201385498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.46755695343018</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.50169348716736</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.58459520339966</t>
   </si>
   <si>
     <t xml:space="preserve">2.63173580169678</t>
   </si>
   <si>
-    <t xml:space="preserve">2.65611910820007</t>
+    <t xml:space="preserve">2.65611886978149</t>
   </si>
   <si>
     <t xml:space="preserve">2.66912293434143</t>
   </si>
   <si>
-    <t xml:space="preserve">2.72439074516296</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.78291034698486</t>
+    <t xml:space="preserve">2.72439122200012</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.78291058540344</t>
   </si>
   <si>
     <t xml:space="preserve">2.77153158187866</t>
@@ -629,19 +629,19 @@
     <t xml:space="preserve">2.77803373336792</t>
   </si>
   <si>
-    <t xml:space="preserve">2.70000839233398</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.7731568813324</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.76502919197083</t>
+    <t xml:space="preserve">2.70000863075256</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.77315735816956</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.7650294303894</t>
   </si>
   <si>
     <t xml:space="preserve">2.71788907051086</t>
   </si>
   <si>
-    <t xml:space="preserve">2.74552297592163</t>
+    <t xml:space="preserve">2.74552321434021</t>
   </si>
   <si>
     <t xml:space="preserve">2.77965927124023</t>
@@ -650,7 +650,7 @@
     <t xml:space="preserve">2.74714851379395</t>
   </si>
   <si>
-    <t xml:space="preserve">2.60410165786743</t>
+    <t xml:space="preserve">2.60410141944885</t>
   </si>
   <si>
     <t xml:space="preserve">2.62685918807983</t>
@@ -665,52 +665,52 @@
     <t xml:space="preserve">2.69838237762451</t>
   </si>
   <si>
-    <t xml:space="preserve">2.92270588874817</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.88531851768494</t>
+    <t xml:space="preserve">2.92270565032959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.88531827926636</t>
   </si>
   <si>
     <t xml:space="preserve">2.99910616874695</t>
   </si>
   <si>
-    <t xml:space="preserve">2.97472286224365</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.96984624862671</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.96334385871887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.94221234321594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.93408417701721</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.89832305908203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.89182066917419</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.87881684303284</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.87556552886963</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.84468030929565</t>
+    <t xml:space="preserve">2.97472310066223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.96984648704529</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.96334409713745</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.94221210479736</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.93408441543579</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.89832282066345</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.89182090759277</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.87881660461426</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.87556576728821</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.84468054771423</t>
   </si>
   <si>
     <t xml:space="preserve">2.82192325592041</t>
   </si>
   <si>
-    <t xml:space="preserve">2.84955739974976</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.91945457458496</t>
+    <t xml:space="preserve">2.84955716133118</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.91945505142212</t>
   </si>
   <si>
     <t xml:space="preserve">2.9259569644928</t>
@@ -719,25 +719,25 @@
     <t xml:space="preserve">2.99097847938538</t>
   </si>
   <si>
-    <t xml:space="preserve">2.91457796096802</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.91620373725891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.95846748352051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.95684194564819</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.95196533203125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.04949760437012</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.0559995174408</t>
+    <t xml:space="preserve">2.91457843780518</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.91620397567749</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.95846796035767</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.95684218406677</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.95196604728699</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.04949736595154</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.05599975585938</t>
   </si>
   <si>
     <t xml:space="preserve">2.99585485458374</t>
@@ -746,13 +746,13 @@
     <t xml:space="preserve">2.9795994758606</t>
   </si>
   <si>
-    <t xml:space="preserve">3.00723338127136</t>
+    <t xml:space="preserve">3.00723361968994</t>
   </si>
   <si>
     <t xml:space="preserve">3.09645915031433</t>
   </si>
   <si>
-    <t xml:space="preserve">3.11628699302673</t>
+    <t xml:space="preserve">3.11628723144531</t>
   </si>
   <si>
     <t xml:space="preserve">3.16916155815125</t>
@@ -761,58 +761,58 @@
     <t xml:space="preserve">3.13941979408264</t>
   </si>
   <si>
-    <t xml:space="preserve">3.14437651634216</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.18898916244507</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.18072772026062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.24847316741943</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.21707892417908</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.16750931739807</t>
+    <t xml:space="preserve">3.14437675476074</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.18898963928223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.1807279586792</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.24847340583801</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.21707940101624</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.16750955581665</t>
   </si>
   <si>
     <t xml:space="preserve">3.15429067611694</t>
   </si>
   <si>
-    <t xml:space="preserve">3.170814037323</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.07663130760193</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.07497882843018</t>
+    <t xml:space="preserve">3.17081451416016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.07663154602051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.07497930526733</t>
   </si>
   <si>
     <t xml:space="preserve">2.98244857788086</t>
   </si>
   <si>
-    <t xml:space="preserve">3.0584557056427</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.06506538391113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.0336709022522</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.02540898323059</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.99401521682739</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.99071073532104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.99897217750549</t>
+    <t xml:space="preserve">3.05845594406128</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.06506514549255</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.03367066383362</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.02540946006775</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.99401497840881</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.99071025848389</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.99897193908691</t>
   </si>
   <si>
     <t xml:space="preserve">2.93783593177795</t>
@@ -821,7 +821,7 @@
     <t xml:space="preserve">2.95601177215576</t>
   </si>
   <si>
-    <t xml:space="preserve">3.07993578910828</t>
+    <t xml:space="preserve">3.07993626594543</t>
   </si>
   <si>
     <t xml:space="preserve">3.08819770812988</t>
@@ -833,52 +833,52 @@
     <t xml:space="preserve">3.10802555084229</t>
   </si>
   <si>
-    <t xml:space="preserve">3.11133027076721</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.14768147468567</t>
+    <t xml:space="preserve">3.11133003234863</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.14768123626709</t>
   </si>
   <si>
     <t xml:space="preserve">3.16420459747314</t>
   </si>
   <si>
-    <t xml:space="preserve">3.20551300048828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.21377420425415</t>
+    <t xml:space="preserve">3.2055127620697</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.21377444267273</t>
   </si>
   <si>
     <t xml:space="preserve">3.23029756546021</t>
   </si>
   <si>
-    <t xml:space="preserve">3.23360276222229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.25343036651611</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.29473853111267</t>
+    <t xml:space="preserve">3.23360228538513</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.25343012809753</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.29473829269409</t>
   </si>
   <si>
     <t xml:space="preserve">3.3079571723938</t>
   </si>
   <si>
-    <t xml:space="preserve">3.27160573005676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.29639077186584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.22368836402893</t>
+    <t xml:space="preserve">3.27160596847534</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.29639101028442</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.22368812561035</t>
   </si>
   <si>
     <t xml:space="preserve">3.25012564659119</t>
   </si>
   <si>
-    <t xml:space="preserve">3.19394636154175</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.26334381103516</t>
+    <t xml:space="preserve">3.19394659996033</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.26334428787231</t>
   </si>
   <si>
     <t xml:space="preserve">3.09811162948608</t>
@@ -890,28 +890,28 @@
     <t xml:space="preserve">3.17246627807617</t>
   </si>
   <si>
-    <t xml:space="preserve">3.17411875724792</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.15098571777344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.05184650421143</t>
+    <t xml:space="preserve">3.17411851882935</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.15098595619202</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.05184674263</t>
   </si>
   <si>
     <t xml:space="preserve">3.05680322647095</t>
   </si>
   <si>
-    <t xml:space="preserve">3.08489274978638</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.12785387039185</t>
+    <t xml:space="preserve">3.08489298820496</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.12785363197327</t>
   </si>
   <si>
     <t xml:space="preserve">3.03201866149902</t>
   </si>
   <si>
-    <t xml:space="preserve">3.09480667114258</t>
+    <t xml:space="preserve">3.09480714797974</t>
   </si>
   <si>
     <t xml:space="preserve">3.073326587677</t>
@@ -932,28 +932,28 @@
     <t xml:space="preserve">3.12124443054199</t>
   </si>
   <si>
-    <t xml:space="preserve">3.13611507415771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.1460292339325</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.12950539588928</t>
+    <t xml:space="preserve">3.13611483573914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.14602899551392</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.12950587272644</t>
   </si>
   <si>
     <t xml:space="preserve">3.14107203483582</t>
   </si>
   <si>
-    <t xml:space="preserve">3.15759515762329</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.18403291702271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.10637331008911</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.08158826828003</t>
+    <t xml:space="preserve">3.15759539604187</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.18403267860413</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.10637307167053</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.08158850669861</t>
   </si>
   <si>
     <t xml:space="preserve">3.10141611099243</t>
@@ -965,7 +965,7 @@
     <t xml:space="preserve">3.12289667129517</t>
   </si>
   <si>
-    <t xml:space="preserve">3.08984994888306</t>
+    <t xml:space="preserve">3.08985018730164</t>
   </si>
   <si>
     <t xml:space="preserve">2.94940233230591</t>
@@ -974,16 +974,16 @@
     <t xml:space="preserve">2.93287873268127</t>
   </si>
   <si>
-    <t xml:space="preserve">2.83704423904419</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.88165688514709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.90809392929077</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.9113986492157</t>
+    <t xml:space="preserve">2.83704447746277</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.88165664672852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.90809416770935</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.91139912605286</t>
   </si>
   <si>
     <t xml:space="preserve">2.94609761238098</t>
@@ -992,16 +992,16 @@
     <t xml:space="preserve">2.94114065170288</t>
   </si>
   <si>
-    <t xml:space="preserve">2.96592569351196</t>
+    <t xml:space="preserve">2.9659252166748</t>
   </si>
   <si>
     <t xml:space="preserve">2.88496160507202</t>
   </si>
   <si>
-    <t xml:space="preserve">2.84034848213196</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.828782081604</t>
+    <t xml:space="preserve">2.84034872055054</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.82878255844116</t>
   </si>
   <si>
     <t xml:space="preserve">2.81225919723511</t>
@@ -1013,52 +1013,52 @@
     <t xml:space="preserve">2.75112271308899</t>
   </si>
   <si>
-    <t xml:space="preserve">2.80895495414734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.79243135452271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.81391143798828</t>
+    <t xml:space="preserve">2.80895471572876</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.79243159294128</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.8139111995697</t>
   </si>
   <si>
     <t xml:space="preserve">2.85852432250977</t>
   </si>
   <si>
-    <t xml:space="preserve">2.97418689727783</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.97088241577148</t>
+    <t xml:space="preserve">2.97418713569641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.97088217735291</t>
   </si>
   <si>
     <t xml:space="preserve">3.01549553871155</t>
   </si>
   <si>
-    <t xml:space="preserve">3.05515098571777</t>
+    <t xml:space="preserve">3.05515122413635</t>
   </si>
   <si>
     <t xml:space="preserve">3.04028010368347</t>
   </si>
   <si>
-    <t xml:space="preserve">3.07002210617065</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.0634126663208</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.023756980896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.03697562217712</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.0287139415741</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.05349898338318</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.07828402519226</t>
+    <t xml:space="preserve">3.07002234458923</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.06341290473938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.02375721931458</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.03697538375854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.02871370315552</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.0534987449646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.0782835483551</t>
   </si>
   <si>
     <t xml:space="preserve">3.11050415039062</t>
@@ -1067,97 +1067,97 @@
     <t xml:space="preserve">3.06919574737549</t>
   </si>
   <si>
-    <t xml:space="preserve">3.1559431552887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.21790504455566</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.17659711837769</t>
+    <t xml:space="preserve">3.15594291687012</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.21790528297424</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.17659687995911</t>
   </si>
   <si>
     <t xml:space="preserve">3.19312024116516</t>
   </si>
   <si>
-    <t xml:space="preserve">3.25508284568787</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.22203612327576</t>
+    <t xml:space="preserve">3.25508260726929</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.22203636169434</t>
   </si>
   <si>
     <t xml:space="preserve">2.96179461479187</t>
   </si>
   <si>
-    <t xml:space="preserve">2.97831797599792</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.92461752891541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.87504768371582</t>
+    <t xml:space="preserve">2.9783182144165</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.92461729049683</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.87504744529724</t>
   </si>
   <si>
     <t xml:space="preserve">3.13528919219971</t>
   </si>
   <si>
-    <t xml:space="preserve">3.07745742797852</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.05267286300659</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.03614902496338</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.92048692703247</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.08571910858154</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.01962614059448</t>
+    <t xml:space="preserve">3.07745766639709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.05267262458801</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.03614950180054</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.92048668861389</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.08571887016296</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.01962566375732</t>
   </si>
   <si>
     <t xml:space="preserve">3.02788782119751</t>
   </si>
   <si>
-    <t xml:space="preserve">3.0485417842865</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.04441118240356</t>
+    <t xml:space="preserve">3.04854202270508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.04441094398499</t>
   </si>
   <si>
     <t xml:space="preserve">3.15181231498718</t>
   </si>
   <si>
-    <t xml:space="preserve">3.3376989364624</t>
+    <t xml:space="preserve">3.33769869804382</t>
   </si>
   <si>
     <t xml:space="preserve">3.25095152854919</t>
   </si>
   <si>
-    <t xml:space="preserve">3.27573657035828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.28399848937988</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.24682116508484</t>
+    <t xml:space="preserve">3.27573680877686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.2839982509613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.24682092666626</t>
   </si>
   <si>
     <t xml:space="preserve">3.18485879898071</t>
   </si>
   <si>
-    <t xml:space="preserve">3.2437379360199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.20177507400513</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.21016764640808</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.18918609619141</t>
+    <t xml:space="preserve">3.24373769760132</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.20177483558655</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.21016716957092</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.18918561935425</t>
   </si>
   <si>
     <t xml:space="preserve">3.22275614738464</t>
@@ -1166,7 +1166,7 @@
     <t xml:space="preserve">3.16400837898254</t>
   </si>
   <si>
-    <t xml:space="preserve">3.0884747505188</t>
+    <t xml:space="preserve">3.08847498893738</t>
   </si>
   <si>
     <t xml:space="preserve">3.12204527854919</t>
@@ -1175,37 +1175,37 @@
     <t xml:space="preserve">3.14302659034729</t>
   </si>
   <si>
-    <t xml:space="preserve">3.20597100257874</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.25632667541504</t>
+    <t xml:space="preserve">3.20597124099731</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.25632691383362</t>
   </si>
   <si>
     <t xml:space="preserve">3.24793410301208</t>
   </si>
   <si>
-    <t xml:space="preserve">3.10525989532471</t>
+    <t xml:space="preserve">3.10526013374329</t>
   </si>
   <si>
     <t xml:space="preserve">3.07168960571289</t>
   </si>
   <si>
-    <t xml:space="preserve">3.18498969078064</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.11365270614624</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.12624168395996</t>
+    <t xml:space="preserve">3.1849901676178</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.11365246772766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.1262412071228</t>
   </si>
   <si>
     <t xml:space="preserve">3.1388304233551</t>
   </si>
   <si>
-    <t xml:space="preserve">3.14722323417664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.15561580657959</t>
+    <t xml:space="preserve">3.14722299575806</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.15561532974243</t>
   </si>
   <si>
     <t xml:space="preserve">3.1724009513855</t>
@@ -1217,10 +1217,10 @@
     <t xml:space="preserve">3.13463401794434</t>
   </si>
   <si>
-    <t xml:space="preserve">3.16820430755615</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.10945653915405</t>
+    <t xml:space="preserve">3.16820454597473</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.10945606231689</t>
   </si>
   <si>
     <t xml:space="preserve">3.15981197357178</t>
@@ -1235,82 +1235,82 @@
     <t xml:space="preserve">3.23534536361694</t>
   </si>
   <si>
-    <t xml:space="preserve">3.26471948623657</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.32346773147583</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.31087851524353</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.27730846405029</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.35703802108765</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.4241783618927</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.49131941795349</t>
+    <t xml:space="preserve">3.26471924781799</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.32346749305725</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.31087827682495</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.27730774879456</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.35703754425049</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.42417860031128</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.49131917953491</t>
   </si>
   <si>
     <t xml:space="preserve">3.43257141113281</t>
   </si>
   <si>
-    <t xml:space="preserve">3.54167485237122</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.44935655593872</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.4829273223877</t>
+    <t xml:space="preserve">3.54167509078979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.44935703277588</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.48292684555054</t>
   </si>
   <si>
     <t xml:space="preserve">3.51649737358093</t>
   </si>
   <si>
-    <t xml:space="preserve">3.47453379631042</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.45774936676025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.3864119052887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.37801957130432</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.4703381061554</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.302485704422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.31927108764648</t>
+    <t xml:space="preserve">3.47453427314758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.45774865150452</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.38641214370728</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.37801909446716</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.47033834457397</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.30248618125916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.31927132606506</t>
   </si>
   <si>
     <t xml:space="preserve">3.29828977584839</t>
   </si>
   <si>
-    <t xml:space="preserve">3.34025263786316</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.27311182022095</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.2815043926239</t>
+    <t xml:space="preserve">3.34025287628174</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.27311205863953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.28150510787964</t>
   </si>
   <si>
     <t xml:space="preserve">3.399001121521</t>
   </si>
   <si>
-    <t xml:space="preserve">3.57524561882019</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.58783483505249</t>
+    <t xml:space="preserve">3.57524538040161</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.58783388137817</t>
   </si>
   <si>
     <t xml:space="preserve">3.55006742477417</t>
@@ -1319,46 +1319,46 @@
     <t xml:space="preserve">3.57944178581238</t>
   </si>
   <si>
-    <t xml:space="preserve">3.58363795280457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.66336727142334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.55845975875854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.5668523311615</t>
+    <t xml:space="preserve">3.58363819122314</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.66336750984192</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.55845999717712</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.56685304641724</t>
   </si>
   <si>
     <t xml:space="preserve">3.62140464782715</t>
   </si>
   <si>
-    <t xml:space="preserve">3.78086400032043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.88577127456665</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.7221155166626</t>
+    <t xml:space="preserve">3.78086423873901</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.88577079772949</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.72211575508118</t>
   </si>
   <si>
     <t xml:space="preserve">3.76407861709595</t>
   </si>
   <si>
-    <t xml:space="preserve">3.68434882164001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.79764890670776</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.82702326774597</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.80184578895569</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.83961224555969</t>
+    <t xml:space="preserve">3.68434858322144</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.79764938354492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.82702374458313</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.80184555053711</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.83961200714111</t>
   </si>
   <si>
     <t xml:space="preserve">3.91934180259705</t>
@@ -1367,118 +1367,118 @@
     <t xml:space="preserve">3.91094875335693</t>
   </si>
   <si>
-    <t xml:space="preserve">3.94451951980591</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.06621122360229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.02005243301392</t>
+    <t xml:space="preserve">3.94451975822449</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.06621217727661</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.02005290985107</t>
   </si>
   <si>
     <t xml:space="preserve">3.92773389816284</t>
   </si>
   <si>
-    <t xml:space="preserve">3.86898612976074</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.8186309337616</t>
+    <t xml:space="preserve">3.86898636817932</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.81863045692444</t>
   </si>
   <si>
     <t xml:space="preserve">3.86059331893921</t>
   </si>
   <si>
-    <t xml:space="preserve">3.79345297813416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.86479020118713</t>
+    <t xml:space="preserve">3.793452501297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.8647894859314</t>
   </si>
   <si>
     <t xml:space="preserve">3.8773787021637</t>
   </si>
   <si>
-    <t xml:space="preserve">3.7347047328949</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.84380888938904</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.69274210929871</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.90255641937256</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.95291209220886</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.99067878723145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.00326728820801</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.9151451587677</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.87318181991577</t>
+    <t xml:space="preserve">3.73470449447632</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.8438081741333</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.69274187088013</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.9025571346283</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.95291185379028</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.99067854881287</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.00326824188232</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.91514587402344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.87318205833435</t>
   </si>
   <si>
     <t xml:space="preserve">3.85220098495483</t>
   </si>
   <si>
-    <t xml:space="preserve">3.66756391525269</t>
+    <t xml:space="preserve">3.66756367683411</t>
   </si>
   <si>
     <t xml:space="preserve">3.67595648765564</t>
   </si>
   <si>
-    <t xml:space="preserve">3.59203052520752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.53328227996826</t>
+    <t xml:space="preserve">3.59203100204468</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.53328251838684</t>
   </si>
   <si>
     <t xml:space="preserve">3.70533037185669</t>
   </si>
   <si>
-    <t xml:space="preserve">3.6423864364624</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.77666735649109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.71791911125183</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.64658212661743</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.70113444328308</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.68015313148499</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.8060417175293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.78506064414978</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.69693779945374</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.73050880432129</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.7472939491272</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.6507785320282</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.65917110443115</t>
+    <t xml:space="preserve">3.64238619804382</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.77666759490967</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.71791934967041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.64658236503601</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.7011342048645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.68015265464783</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.80604147911072</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.78505992889404</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.69693803787231</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.73050832748413</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.74729371070862</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.65077877044678</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.65917134284973</t>
   </si>
   <si>
     <t xml:space="preserve">3.85639691352844</t>
@@ -1487,10 +1487,10 @@
     <t xml:space="preserve">3.89416408538818</t>
   </si>
   <si>
-    <t xml:space="preserve">3.93612694740295</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.00746393203735</t>
+    <t xml:space="preserve">3.93612718582153</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.0074634552002</t>
   </si>
   <si>
     <t xml:space="preserve">4.08719396591187</t>
@@ -1499,7 +1499,7 @@
     <t xml:space="preserve">4.11237144470215</t>
   </si>
   <si>
-    <t xml:space="preserve">4.17111921310425</t>
+    <t xml:space="preserve">4.17111968994141</t>
   </si>
   <si>
     <t xml:space="preserve">4.19629716873169</t>
@@ -1508,67 +1508,67 @@
     <t xml:space="preserve">4.2382607460022</t>
   </si>
   <si>
-    <t xml:space="preserve">4.18790435791016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.09978294372559</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.0955867767334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.07880067825317</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.14594125747681</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.09138965606689</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.08299684524536</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.06201648712158</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.26343822479248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.39771938323975</t>
+    <t xml:space="preserve">4.18790483474731</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.09978246688843</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.09558582305908</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.07880115509033</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.14594173431396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.09139013290405</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.08299732208252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.06201553344727</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.26343774795532</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.39771890640259</t>
   </si>
   <si>
     <t xml:space="preserve">4.52360868453979</t>
   </si>
   <si>
-    <t xml:space="preserve">4.4984302520752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.58235692977905</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.48164558410645</t>
+    <t xml:space="preserve">4.49843072891235</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.58235645294189</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.4816460609436</t>
   </si>
   <si>
     <t xml:space="preserve">4.62431955337524</t>
   </si>
   <si>
-    <t xml:space="preserve">4.67467546463013</t>
+    <t xml:space="preserve">4.67467594146729</t>
   </si>
   <si>
     <t xml:space="preserve">4.69985294342041</t>
   </si>
   <si>
-    <t xml:space="preserve">4.68306827545166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.66628265380859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.63271236419678</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.44807529449463</t>
+    <t xml:space="preserve">4.6830677986145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.66628217697144</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.63271188735962</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.44807577133179</t>
   </si>
   <si>
     <t xml:space="preserve">4.4396824836731</t>
@@ -1580,70 +1580,70 @@
     <t xml:space="preserve">4.49003791809082</t>
   </si>
   <si>
-    <t xml:space="preserve">4.54878616333008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.5991415977478</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.61592721939087</t>
+    <t xml:space="preserve">4.54878711700439</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.59914112091064</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.61592817306519</t>
   </si>
   <si>
     <t xml:space="preserve">4.60753440856934</t>
   </si>
   <si>
-    <t xml:space="preserve">4.40611219406128</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.53200101852417</t>
+    <t xml:space="preserve">4.40611267089844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.53200054168701</t>
   </si>
   <si>
     <t xml:space="preserve">4.75860118865967</t>
   </si>
   <si>
-    <t xml:space="preserve">4.80895614624023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.74181604385376</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.69146013259888</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.6578893661499</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.50682353973389</t>
+    <t xml:space="preserve">4.80895709991455</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.74181699752808</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.69146060943604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.65789031982422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.50682306289673</t>
   </si>
   <si>
     <t xml:space="preserve">4.54039335250854</t>
   </si>
   <si>
-    <t xml:space="preserve">4.4648609161377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.41450500488281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.38932657241821</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.38093423843384</t>
+    <t xml:space="preserve">4.46486043930054</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.41450548171997</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.38932704925537</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.380934715271</t>
   </si>
   <si>
     <t xml:space="preserve">4.34736347198486</t>
   </si>
   <si>
-    <t xml:space="preserve">4.46764707565308</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.51919651031494</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.39891338348389</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.37313890457153</t>
+    <t xml:space="preserve">4.46764659881592</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.5191969871521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.39891386032104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.37313842773438</t>
   </si>
   <si>
     <t xml:space="preserve">4.30440616607666</t>
@@ -1652,7 +1652,7 @@
     <t xml:space="preserve">4.27003908157349</t>
   </si>
   <si>
-    <t xml:space="preserve">4.33018016815186</t>
+    <t xml:space="preserve">4.33018064498901</t>
   </si>
   <si>
     <t xml:space="preserve">4.31299781799316</t>
@@ -1661,85 +1661,85 @@
     <t xml:space="preserve">4.38173055648804</t>
   </si>
   <si>
-    <t xml:space="preserve">4.44187164306641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.45905590057373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.35595560073853</t>
+    <t xml:space="preserve">4.44187116622925</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.45905494689941</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.35595607757568</t>
   </si>
   <si>
     <t xml:space="preserve">4.39032220840454</t>
   </si>
   <si>
-    <t xml:space="preserve">4.45046281814575</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.41609716415405</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.23137664794922</t>
+    <t xml:space="preserve">4.45046377182007</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.41609668731689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.23137712478638</t>
   </si>
   <si>
     <t xml:space="preserve">4.26574373245239</t>
   </si>
   <si>
-    <t xml:space="preserve">4.13257312774658</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.04665660858154</t>
+    <t xml:space="preserve">4.13257265090942</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.0466570854187</t>
   </si>
   <si>
     <t xml:space="preserve">4.08531904220581</t>
   </si>
   <si>
-    <t xml:space="preserve">3.98222041130066</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.0337700843811</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.94785284996033</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.99081158638</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.98651552200317</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.94355773925781</t>
+    <t xml:space="preserve">3.9822199344635</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.03376960754395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.94785237312317</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.99081087112427</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.98651576042175</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.94355702400208</t>
   </si>
   <si>
     <t xml:space="preserve">3.96503591537476</t>
   </si>
   <si>
-    <t xml:space="preserve">3.96074080467224</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.01229095458984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.92637419700623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.07243156433105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.08961582183838</t>
+    <t xml:space="preserve">3.9607412815094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.01229000091553</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.9263744354248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.07243204116821</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.08961534500122</t>
   </si>
   <si>
     <t xml:space="preserve">4.11109447479248</t>
   </si>
   <si>
-    <t xml:space="preserve">4.2614483833313</t>
+    <t xml:space="preserve">4.26144790649414</t>
   </si>
   <si>
     <t xml:space="preserve">4.32158946990967</t>
   </si>
   <si>
-    <t xml:space="preserve">4.295814037323</t>
+    <t xml:space="preserve">4.29581356048584</t>
   </si>
   <si>
     <t xml:space="preserve">4.02947378158569</t>
@@ -1748,22 +1748,22 @@
     <t xml:space="preserve">3.84045767784119</t>
   </si>
   <si>
-    <t xml:space="preserve">3.87482500076294</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.88771152496338</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.00369834899902</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.02088165283203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.93496632575989</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.86623239517212</t>
+    <t xml:space="preserve">3.87482452392578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.88771200180054</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.00369882583618</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.02088212966919</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.93496584892273</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.86623287200928</t>
   </si>
   <si>
     <t xml:space="preserve">3.77172470092773</t>
@@ -1772,7 +1772,7 @@
     <t xml:space="preserve">3.71587920188904</t>
   </si>
   <si>
-    <t xml:space="preserve">3.70299172401428</t>
+    <t xml:space="preserve">3.70299196243286</t>
   </si>
   <si>
     <t xml:space="preserve">3.67721700668335</t>
@@ -1781,28 +1781,28 @@
     <t xml:space="preserve">3.68580842018127</t>
   </si>
   <si>
-    <t xml:space="preserve">3.70728754997253</t>
+    <t xml:space="preserve">3.70728778839111</t>
   </si>
   <si>
     <t xml:space="preserve">3.66432952880859</t>
   </si>
   <si>
-    <t xml:space="preserve">3.6600341796875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.72017526626587</t>
+    <t xml:space="preserve">3.66003394126892</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.72017478942871</t>
   </si>
   <si>
     <t xml:space="preserve">3.81468319892883</t>
   </si>
   <si>
-    <t xml:space="preserve">3.95214891433716</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.85764122009277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.78461241722107</t>
+    <t xml:space="preserve">3.95214939117432</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.85764098167419</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.78461289405823</t>
   </si>
   <si>
     <t xml:space="preserve">3.84475350379944</t>
@@ -1811,70 +1811,70 @@
     <t xml:space="preserve">3.7803168296814</t>
   </si>
   <si>
-    <t xml:space="preserve">3.69440031051636</t>
+    <t xml:space="preserve">3.69440054893494</t>
   </si>
   <si>
     <t xml:space="preserve">3.73306250572205</t>
   </si>
   <si>
-    <t xml:space="preserve">3.71158385276794</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.59989237785339</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.75454139709473</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.65144181251526</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.72447085380554</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.78890800476074</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.64714598655701</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.66862559318542</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.67292141914368</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.61707520484924</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.57411742210388</t>
+    <t xml:space="preserve">3.71158361434937</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.59989261627197</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.75454187393188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.65144205093384</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.72447061538696</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.78890776634216</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.64714670181274</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.66862535476685</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.67292094230652</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.61707544326782</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.5741171836853</t>
   </si>
   <si>
     <t xml:space="preserve">3.64284992218018</t>
   </si>
   <si>
-    <t xml:space="preserve">3.65573763847351</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.62996292114258</t>
+    <t xml:space="preserve">3.65573811531067</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.629962682724</t>
   </si>
   <si>
     <t xml:space="preserve">3.96933197975159</t>
   </si>
   <si>
-    <t xml:space="preserve">3.95644521713257</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.90059924125671</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.9306697845459</t>
+    <t xml:space="preserve">3.95644497871399</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.90059900283813</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.93067002296448</t>
   </si>
   <si>
     <t xml:space="preserve">4.01658630371094</t>
   </si>
   <si>
-    <t xml:space="preserve">4.09820699691772</t>
+    <t xml:space="preserve">4.09820652008057</t>
   </si>
   <si>
     <t xml:space="preserve">4.14116525650024</t>
@@ -1883,19 +1883,19 @@
     <t xml:space="preserve">4.24426412582397</t>
   </si>
   <si>
-    <t xml:space="preserve">4.24856042861938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.43328046798706</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.4246883392334</t>
+    <t xml:space="preserve">4.24855995178223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.4332799911499</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.42468929290771</t>
   </si>
   <si>
     <t xml:space="preserve">4.58793020248413</t>
   </si>
   <si>
-    <t xml:space="preserve">4.57933712005615</t>
+    <t xml:space="preserve">4.57933759689331</t>
   </si>
   <si>
     <t xml:space="preserve">4.49342155456543</t>
@@ -1904,16 +1904,16 @@
     <t xml:space="preserve">4.55356311798096</t>
   </si>
   <si>
-    <t xml:space="preserve">4.48482990264893</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.53638029098511</t>
+    <t xml:space="preserve">4.48482942581177</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.53637933731079</t>
   </si>
   <si>
     <t xml:space="preserve">4.59652090072632</t>
   </si>
   <si>
-    <t xml:space="preserve">4.77694511413574</t>
+    <t xml:space="preserve">4.7769455909729</t>
   </si>
   <si>
     <t xml:space="preserve">4.81131172180176</t>
@@ -1931,46 +1931,46 @@
     <t xml:space="preserve">4.71680402755737</t>
   </si>
   <si>
-    <t xml:space="preserve">4.69102907180786</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.68243741989136</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.70821237564087</t>
+    <t xml:space="preserve">4.69102954864502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.68243789672852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.70821189880371</t>
   </si>
   <si>
     <t xml:space="preserve">4.67384576797485</t>
   </si>
   <si>
-    <t xml:space="preserve">4.56215476989746</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.50201272964478</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.54497146606445</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.51060485839844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.52778816223145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.76835346221924</t>
+    <t xml:space="preserve">4.5621542930603</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.50201320648193</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.54497194290161</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.51060438156128</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.52778768539429</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.7683539390564</t>
   </si>
   <si>
     <t xml:space="preserve">4.66525411605835</t>
   </si>
   <si>
-    <t xml:space="preserve">4.61370420455933</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.73398685455322</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.639479637146</t>
+    <t xml:space="preserve">4.61370468139648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.73398733139038</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.63947916030884</t>
   </si>
   <si>
     <t xml:space="preserve">4.23567247390747</t>
@@ -1979,19 +1979,19 @@
     <t xml:space="preserve">4.15834856033325</t>
   </si>
   <si>
-    <t xml:space="preserve">4.20130586624146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.36454677581787</t>
+    <t xml:space="preserve">4.2013053894043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.36454725265503</t>
   </si>
   <si>
     <t xml:space="preserve">4.60511255264282</t>
   </si>
   <si>
-    <t xml:space="preserve">4.11538982391357</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.75024557113647</t>
+    <t xml:space="preserve">4.11539030075073</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.75024580955505</t>
   </si>
   <si>
     <t xml:space="preserve">3.47101783752441</t>
@@ -2000,13 +2000,13 @@
     <t xml:space="preserve">3.36362266540527</t>
   </si>
   <si>
-    <t xml:space="preserve">3.31207275390625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.16601514816284</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.22186088562012</t>
+    <t xml:space="preserve">3.31207251548767</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.16601490974426</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.22186064720154</t>
   </si>
   <si>
     <t xml:space="preserve">2.80516672134399</t>
@@ -2015,7 +2015,7 @@
     <t xml:space="preserve">2.91685771942139</t>
   </si>
   <si>
-    <t xml:space="preserve">2.86530780792236</t>
+    <t xml:space="preserve">2.86530804634094</t>
   </si>
   <si>
     <t xml:space="preserve">2.8867871761322</t>
@@ -2024,10 +2024,10 @@
     <t xml:space="preserve">2.73213791847229</t>
   </si>
   <si>
-    <t xml:space="preserve">2.66770076751709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.80087065696716</t>
+    <t xml:space="preserve">2.66770052909851</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.80087089538574</t>
   </si>
   <si>
     <t xml:space="preserve">2.61185503005981</t>
@@ -2039,22 +2039,22 @@
     <t xml:space="preserve">2.92115378379822</t>
   </si>
   <si>
-    <t xml:space="preserve">2.8137583732605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.70206713676453</t>
+    <t xml:space="preserve">2.81375813484192</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.70206689834595</t>
   </si>
   <si>
     <t xml:space="preserve">2.65910911560059</t>
   </si>
   <si>
-    <t xml:space="preserve">2.84382891654968</t>
+    <t xml:space="preserve">2.84382915496826</t>
   </si>
   <si>
     <t xml:space="preserve">2.76650452613831</t>
   </si>
   <si>
-    <t xml:space="preserve">2.78798341751099</t>
+    <t xml:space="preserve">2.78798317909241</t>
   </si>
   <si>
     <t xml:space="preserve">2.70636320114136</t>
@@ -2066,13 +2066,13 @@
     <t xml:space="preserve">2.85242056846619</t>
   </si>
   <si>
-    <t xml:space="preserve">2.89108300209045</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.92974543571472</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.0070698261261</t>
+    <t xml:space="preserve">2.89108324050903</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.92974519729614</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.00707006454468</t>
   </si>
   <si>
     <t xml:space="preserve">2.96411180496216</t>
@@ -2081,55 +2081,55 @@
     <t xml:space="preserve">2.93833708763123</t>
   </si>
   <si>
-    <t xml:space="preserve">2.94263243675232</t>
+    <t xml:space="preserve">2.9426326751709</t>
   </si>
   <si>
     <t xml:space="preserve">2.98129487037659</t>
   </si>
   <si>
-    <t xml:space="preserve">3.01136612892151</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.94692850112915</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.97699928283691</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.95122456550598</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.10587358474731</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.04143643379211</t>
+    <t xml:space="preserve">3.01136589050293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.94692873954773</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.97699904441833</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.9512243270874</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.10587382316589</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.04143619537354</t>
   </si>
   <si>
     <t xml:space="preserve">3.05002784729004</t>
   </si>
   <si>
-    <t xml:space="preserve">3.08439469337463</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.13164830207825</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.03284478187561</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.09298634529114</t>
+    <t xml:space="preserve">3.08439445495605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.13164854049683</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.03284502029419</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.09298610687256</t>
   </si>
   <si>
     <t xml:space="preserve">3.19178986549377</t>
   </si>
   <si>
-    <t xml:space="preserve">3.24763584136963</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.16171932220459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.14883160591125</t>
+    <t xml:space="preserve">3.24763536453247</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.16171908378601</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.14883184432983</t>
   </si>
   <si>
     <t xml:space="preserve">3.18319821357727</t>
@@ -2138,34 +2138,34 @@
     <t xml:space="preserve">3.13594436645508</t>
   </si>
   <si>
-    <t xml:space="preserve">3.11876130104065</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.307776927948</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.38510203361511</t>
+    <t xml:space="preserve">3.11876106262207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.30777668952942</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.38510179519653</t>
   </si>
   <si>
     <t xml:space="preserve">3.43665146827698</t>
   </si>
   <si>
-    <t xml:space="preserve">3.48390507698059</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.46242666244507</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.47960948944092</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.31636834144592</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.29488921165466</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.19608592987061</t>
+    <t xml:space="preserve">3.48390531539917</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.46242642402649</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.4796097278595</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.3163685798645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.29488945007324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.19608569145203</t>
   </si>
   <si>
     <t xml:space="preserve">3.3808057308197</t>
@@ -2177,34 +2177,34 @@
     <t xml:space="preserve">3.35073518753052</t>
   </si>
   <si>
-    <t xml:space="preserve">3.3722140789032</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.42805957794189</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.44094705581665</t>
+    <t xml:space="preserve">3.37221431732178</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.42805933952332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.44094729423523</t>
   </si>
   <si>
     <t xml:space="preserve">3.44524312019348</t>
   </si>
   <si>
-    <t xml:space="preserve">3.75857448577881</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.71435570716858</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.63034105300903</t>
+    <t xml:space="preserve">3.75857472419739</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.71435594558716</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.63034081459045</t>
   </si>
   <si>
     <t xml:space="preserve">3.58170080184937</t>
   </si>
   <si>
-    <t xml:space="preserve">3.51979470252991</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.50210738182068</t>
+    <t xml:space="preserve">3.51979494094849</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.5021071434021</t>
   </si>
   <si>
     <t xml:space="preserve">3.43135762214661</t>
@@ -2213,25 +2213,25 @@
     <t xml:space="preserve">3.44904518127441</t>
   </si>
   <si>
-    <t xml:space="preserve">3.36060786247253</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.38713908195496</t>
+    <t xml:space="preserve">3.36060762405396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.38713932037354</t>
   </si>
   <si>
     <t xml:space="preserve">3.4180920124054</t>
   </si>
   <si>
-    <t xml:space="preserve">3.32081127166748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.33849859237671</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.31638979911804</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.27217078208923</t>
+    <t xml:space="preserve">3.32081151008606</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.33849883079529</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.31638956069946</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.27217102050781</t>
   </si>
   <si>
     <t xml:space="preserve">3.28101468086243</t>
@@ -2261,7 +2261,7 @@
     <t xml:space="preserve">3.13951516151428</t>
   </si>
   <si>
-    <t xml:space="preserve">3.10414052009583</t>
+    <t xml:space="preserve">3.10414028167725</t>
   </si>
   <si>
     <t xml:space="preserve">3.09971880912781</t>
@@ -2276,22 +2276,22 @@
     <t xml:space="preserve">3.07760953903198</t>
   </si>
   <si>
-    <t xml:space="preserve">3.05992197990417</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.98032832145691</t>
+    <t xml:space="preserve">3.05992221832275</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.98032855987549</t>
   </si>
   <si>
     <t xml:space="preserve">2.96264100074768</t>
   </si>
   <si>
-    <t xml:space="preserve">2.94495368003845</t>
+    <t xml:space="preserve">2.94495344161987</t>
   </si>
   <si>
     <t xml:space="preserve">2.93611001968384</t>
   </si>
   <si>
-    <t xml:space="preserve">3.09087467193604</t>
+    <t xml:space="preserve">3.09087491035461</t>
   </si>
   <si>
     <t xml:space="preserve">3.06876564025879</t>
@@ -2303,10 +2303,10 @@
     <t xml:space="preserve">2.98475050926208</t>
   </si>
   <si>
-    <t xml:space="preserve">2.90515732765198</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.83440732955933</t>
+    <t xml:space="preserve">2.90515756607056</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.83440756797791</t>
   </si>
   <si>
     <t xml:space="preserve">2.86978220939636</t>
@@ -2315,7 +2315,7 @@
     <t xml:space="preserve">2.80345463752747</t>
   </si>
   <si>
-    <t xml:space="preserve">2.77692341804504</t>
+    <t xml:space="preserve">2.77692365646362</t>
   </si>
   <si>
     <t xml:space="preserve">2.81229829788208</t>
@@ -2324,7 +2324,7 @@
     <t xml:space="preserve">2.84767317771912</t>
   </si>
   <si>
-    <t xml:space="preserve">2.82998585700989</t>
+    <t xml:space="preserve">2.82998561859131</t>
   </si>
   <si>
     <t xml:space="preserve">2.79461097717285</t>
@@ -2333,16 +2333,16 @@
     <t xml:space="preserve">2.91842269897461</t>
   </si>
   <si>
-    <t xml:space="preserve">2.82114195823669</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.79903292655945</t>
+    <t xml:space="preserve">2.82114219665527</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.79903268814087</t>
   </si>
   <si>
     <t xml:space="preserve">2.80787634849548</t>
   </si>
   <si>
-    <t xml:space="preserve">2.75923562049866</t>
+    <t xml:space="preserve">2.75923585891724</t>
   </si>
   <si>
     <t xml:space="preserve">2.7238609790802</t>
@@ -2351,13 +2351,13 @@
     <t xml:space="preserve">2.71501755714417</t>
   </si>
   <si>
-    <t xml:space="preserve">2.6840648651123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.63542437553406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.61773681640625</t>
+    <t xml:space="preserve">2.68406462669373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.63542413711548</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.61773705482483</t>
   </si>
   <si>
     <t xml:space="preserve">2.58236217498779</t>
@@ -2366,16 +2366,16 @@
     <t xml:space="preserve">2.54698729515076</t>
   </si>
   <si>
-    <t xml:space="preserve">2.56467437744141</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.55140900611877</t>
+    <t xml:space="preserve">2.56467461585999</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.5514087677002</t>
   </si>
   <si>
     <t xml:space="preserve">2.49392485618591</t>
   </si>
   <si>
-    <t xml:space="preserve">2.5735182762146</t>
+    <t xml:space="preserve">2.57351803779602</t>
   </si>
   <si>
     <t xml:space="preserve">2.97148489952087</t>
@@ -2387,28 +2387,28 @@
     <t xml:space="preserve">3.00243782997131</t>
   </si>
   <si>
-    <t xml:space="preserve">3.17931222915649</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.17046809196472</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.19257736206055</t>
+    <t xml:space="preserve">3.17931199073792</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.17046856880188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.19257760047913</t>
   </si>
   <si>
     <t xml:space="preserve">3.28985834121704</t>
   </si>
   <si>
-    <t xml:space="preserve">3.29870200157166</t>
+    <t xml:space="preserve">3.29870223999023</t>
   </si>
   <si>
     <t xml:space="preserve">3.47999787330627</t>
   </si>
   <si>
-    <t xml:space="preserve">3.4136700630188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.48442029953003</t>
+    <t xml:space="preserve">3.41367030143738</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.48442006111145</t>
   </si>
   <si>
     <t xml:space="preserve">3.45788860321045</t>
@@ -2423,37 +2423,37 @@
     <t xml:space="preserve">3.44462299346924</t>
   </si>
   <si>
-    <t xml:space="preserve">3.42693567276001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.55516934394836</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.6789813041687</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.72319960594177</t>
+    <t xml:space="preserve">3.42693591117859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.55516958236694</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.67898106575012</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.72319984436035</t>
   </si>
   <si>
     <t xml:space="preserve">3.74973058700562</t>
   </si>
   <si>
-    <t xml:space="preserve">3.80279326438904</t>
+    <t xml:space="preserve">3.80279350280762</t>
   </si>
   <si>
     <t xml:space="preserve">3.65687251091003</t>
   </si>
   <si>
-    <t xml:space="preserve">3.66129374504089</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.65245056152344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.62591910362244</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.60823154449463</t>
+    <t xml:space="preserve">3.66129398345947</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.65245032310486</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.62591886520386</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.60823202133179</t>
   </si>
   <si>
     <t xml:space="preserve">3.54632592201233</t>
@@ -2465,7 +2465,7 @@
     <t xml:space="preserve">3.57285690307617</t>
   </si>
   <si>
-    <t xml:space="preserve">3.5065290927887</t>
+    <t xml:space="preserve">3.50652933120728</t>
   </si>
   <si>
     <t xml:space="preserve">3.59054446220398</t>
@@ -2477,10 +2477,10 @@
     <t xml:space="preserve">3.74530911445618</t>
   </si>
   <si>
-    <t xml:space="preserve">3.74088740348816</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.73204374313354</t>
+    <t xml:space="preserve">3.74088716506958</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.73204350471497</t>
   </si>
   <si>
     <t xml:space="preserve">3.7055127620697</t>
@@ -2489,40 +2489,40 @@
     <t xml:space="preserve">3.7762622833252</t>
   </si>
   <si>
-    <t xml:space="preserve">3.83816838264465</t>
+    <t xml:space="preserve">3.8381679058075</t>
   </si>
   <si>
     <t xml:space="preserve">3.6834032535553</t>
   </si>
   <si>
-    <t xml:space="preserve">3.76741886138916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.78068423271179</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.76299643516541</t>
+    <t xml:space="preserve">3.76741862297058</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.78068375587463</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.76299691200256</t>
   </si>
   <si>
     <t xml:space="preserve">3.7718403339386</t>
   </si>
   <si>
-    <t xml:space="preserve">3.71877813339233</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.68782496452332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.6170756816864</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.59938812255859</t>
+    <t xml:space="preserve">3.71877789497375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.68782520294189</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.61707592010498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.59938788414001</t>
   </si>
   <si>
     <t xml:space="preserve">3.66571569442749</t>
   </si>
   <si>
-    <t xml:space="preserve">3.70993447303772</t>
+    <t xml:space="preserve">3.7099347114563</t>
   </si>
   <si>
     <t xml:space="preserve">3.78510594367981</t>
@@ -2543,7 +2543,7 @@
     <t xml:space="preserve">4.09594440460205</t>
   </si>
   <si>
-    <t xml:space="preserve">4.17212724685669</t>
+    <t xml:space="preserve">4.17212677001953</t>
   </si>
   <si>
     <t xml:space="preserve">4.16316413879395</t>
@@ -2561,10 +2561,10 @@
     <t xml:space="preserve">4.10490703582764</t>
   </si>
   <si>
-    <t xml:space="preserve">4.06905555725098</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.03320503234863</t>
+    <t xml:space="preserve">4.06905603408813</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.03320550918579</t>
   </si>
   <si>
     <t xml:space="preserve">3.9794294834137</t>
@@ -2573,7 +2573,7 @@
     <t xml:space="preserve">4.02872371673584</t>
   </si>
   <si>
-    <t xml:space="preserve">4.05561208724976</t>
+    <t xml:space="preserve">4.05561256408691</t>
   </si>
   <si>
     <t xml:space="preserve">4.08698129653931</t>
@@ -2588,19 +2588,19 @@
     <t xml:space="preserve">4.01528024673462</t>
   </si>
   <si>
-    <t xml:space="preserve">3.96150374412537</t>
+    <t xml:space="preserve">3.96150422096252</t>
   </si>
   <si>
     <t xml:space="preserve">3.9883918762207</t>
   </si>
   <si>
-    <t xml:space="preserve">3.95254135131836</t>
+    <t xml:space="preserve">3.9525408744812</t>
   </si>
   <si>
     <t xml:space="preserve">3.96598553657532</t>
   </si>
   <si>
-    <t xml:space="preserve">4.04216861724854</t>
+    <t xml:space="preserve">4.04216814041138</t>
   </si>
   <si>
     <t xml:space="preserve">4.07801914215088</t>
@@ -2609,7 +2609,7 @@
     <t xml:space="preserve">4.11835050582886</t>
   </si>
   <si>
-    <t xml:space="preserve">4.17660808563232</t>
+    <t xml:space="preserve">4.17660856246948</t>
   </si>
   <si>
     <t xml:space="preserve">4.11386966705322</t>
@@ -2621,10 +2621,10 @@
     <t xml:space="preserve">4.06009340286255</t>
   </si>
   <si>
-    <t xml:space="preserve">4.1945333480835</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.21245908737183</t>
+    <t xml:space="preserve">4.19453382492065</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.21245861053467</t>
   </si>
   <si>
     <t xml:space="preserve">4.14972019195557</t>
@@ -2639,10 +2639,10 @@
     <t xml:space="preserve">4.01976108551025</t>
   </si>
   <si>
-    <t xml:space="preserve">4.06457471847534</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.20797777175903</t>
+    <t xml:space="preserve">4.06457424163818</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.20797729492188</t>
   </si>
   <si>
     <t xml:space="preserve">4.23038387298584</t>
@@ -2651,52 +2651,52 @@
     <t xml:space="preserve">4.25727224349976</t>
   </si>
   <si>
-    <t xml:space="preserve">4.20349597930908</t>
+    <t xml:space="preserve">4.20349645614624</t>
   </si>
   <si>
     <t xml:space="preserve">3.92565321922302</t>
   </si>
   <si>
-    <t xml:space="preserve">3.90772771835327</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.88084006309509</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.87635850906372</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.80913805961609</t>
+    <t xml:space="preserve">3.90772819519043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.88083982467651</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.87635803222656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.80913853645325</t>
   </si>
   <si>
     <t xml:space="preserve">3.71503019332886</t>
   </si>
   <si>
-    <t xml:space="preserve">3.66573596000671</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.83154535293579</t>
+    <t xml:space="preserve">3.66573572158813</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.83154511451721</t>
   </si>
   <si>
     <t xml:space="preserve">3.93461585044861</t>
   </si>
   <si>
-    <t xml:space="preserve">3.94357872009277</t>
+    <t xml:space="preserve">3.94357824325562</t>
   </si>
   <si>
     <t xml:space="preserve">4.04664945602417</t>
   </si>
   <si>
-    <t xml:space="preserve">3.99287366867065</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.98391103744507</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.02424240112305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.85395193099976</t>
+    <t xml:space="preserve">3.99287271499634</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.98391056060791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.02424192428589</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.85395169258118</t>
   </si>
   <si>
     <t xml:space="preserve">3.93013501167297</t>
@@ -2705,13 +2705,13 @@
     <t xml:space="preserve">3.97046637535095</t>
   </si>
   <si>
-    <t xml:space="preserve">4.10042572021484</t>
+    <t xml:space="preserve">4.10042524337769</t>
   </si>
   <si>
     <t xml:space="preserve">4.15420198440552</t>
   </si>
   <si>
-    <t xml:space="preserve">4.09146308898926</t>
+    <t xml:space="preserve">4.0914626121521</t>
   </si>
   <si>
     <t xml:space="preserve">4.22590351104736</t>
@@ -2720,7 +2720,7 @@
     <t xml:space="preserve">4.2662353515625</t>
   </si>
   <si>
-    <t xml:space="preserve">4.24382781982422</t>
+    <t xml:space="preserve">4.24382829666138</t>
   </si>
   <si>
     <t xml:space="preserve">4.13179492950439</t>
@@ -2735,7 +2735,7 @@
     <t xml:space="preserve">4.19005250930786</t>
   </si>
   <si>
-    <t xml:space="preserve">4.2931227684021</t>
+    <t xml:space="preserve">4.29312324523926</t>
   </si>
   <si>
     <t xml:space="preserve">4.40515661239624</t>
@@ -2744,7 +2744,7 @@
     <t xml:space="preserve">4.43652582168579</t>
   </si>
   <si>
-    <t xml:space="preserve">4.48133897781372</t>
+    <t xml:space="preserve">4.48133945465088</t>
   </si>
   <si>
     <t xml:space="preserve">4.53511524200439</t>
@@ -2753,7 +2753,7 @@
     <t xml:space="preserve">4.55304098129272</t>
   </si>
   <si>
-    <t xml:space="preserve">4.56200361251831</t>
+    <t xml:space="preserve">4.56200313568115</t>
   </si>
   <si>
     <t xml:space="preserve">4.50822782516479</t>
@@ -2762,31 +2762,31 @@
     <t xml:space="preserve">4.45445108413696</t>
   </si>
   <si>
-    <t xml:space="preserve">4.43204498291016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.49926519393921</t>
+    <t xml:space="preserve">4.432044506073</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.49926471710205</t>
   </si>
   <si>
     <t xml:space="preserve">4.49030208587646</t>
   </si>
   <si>
-    <t xml:space="preserve">4.51718950271606</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.63370513916016</t>
+    <t xml:space="preserve">4.51718997955322</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.633704662323</t>
   </si>
   <si>
     <t xml:space="preserve">4.59785461425781</t>
   </si>
   <si>
-    <t xml:space="preserve">4.47685718536377</t>
+    <t xml:space="preserve">4.47685766220093</t>
   </si>
   <si>
     <t xml:space="preserve">4.57096576690674</t>
   </si>
   <si>
-    <t xml:space="preserve">4.61577939987183</t>
+    <t xml:space="preserve">4.61577987670898</t>
   </si>
   <si>
     <t xml:space="preserve">4.64266729354858</t>
@@ -2801,10 +2801,10 @@
     <t xml:space="preserve">4.27519798278809</t>
   </si>
   <si>
-    <t xml:space="preserve">4.58889102935791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.66059303283691</t>
+    <t xml:space="preserve">4.58889150619507</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.66059255599976</t>
   </si>
   <si>
     <t xml:space="preserve">4.65163040161133</t>
@@ -2813,7 +2813,7 @@
     <t xml:space="preserve">4.71436929702759</t>
   </si>
   <si>
-    <t xml:space="preserve">4.75918245315552</t>
+    <t xml:space="preserve">4.75918197631836</t>
   </si>
   <si>
     <t xml:space="preserve">4.76814556121826</t>
@@ -2822,7 +2822,7 @@
     <t xml:space="preserve">4.89362287521362</t>
   </si>
   <si>
-    <t xml:space="preserve">4.92051029205322</t>
+    <t xml:space="preserve">4.92050981521606</t>
   </si>
   <si>
     <t xml:space="preserve">4.88465976715088</t>
@@ -2831,7 +2831,7 @@
     <t xml:space="preserve">5.05495071411133</t>
   </si>
   <si>
-    <t xml:space="preserve">5.01910018920898</t>
+    <t xml:space="preserve">5.01909971237183</t>
   </si>
   <si>
     <t xml:space="preserve">5.14457702636719</t>
@@ -2840,7 +2840,7 @@
     <t xml:space="preserve">5.31486845016479</t>
   </si>
   <si>
-    <t xml:space="preserve">5.37760734558105</t>
+    <t xml:space="preserve">5.3776068687439</t>
   </si>
   <si>
     <t xml:space="preserve">5.35968208312988</t>
@@ -2849,10 +2849,10 @@
     <t xml:space="preserve">5.16250324249268</t>
   </si>
   <si>
-    <t xml:space="preserve">5.0459885597229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.15354061126709</t>
+    <t xml:space="preserve">5.04598808288574</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.15354013442993</t>
   </si>
   <si>
     <t xml:space="preserve">5.26109218597412</t>
@@ -2870,10 +2870,10 @@
     <t xml:space="preserve">5.50308465957642</t>
   </si>
   <si>
-    <t xml:space="preserve">5.29694271087646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.19835329055786</t>
+    <t xml:space="preserve">5.29694318771362</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.19835376739502</t>
   </si>
   <si>
     <t xml:space="preserve">5.18042898178101</t>
@@ -2882,16 +2882,16 @@
     <t xml:space="preserve">5.0728759765625</t>
   </si>
   <si>
-    <t xml:space="preserve">5.09080123901367</t>
+    <t xml:space="preserve">5.09080171585083</t>
   </si>
   <si>
     <t xml:space="preserve">4.99221229553223</t>
   </si>
   <si>
-    <t xml:space="preserve">4.75021934509277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.80399560928345</t>
+    <t xml:space="preserve">4.75021982192993</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.80399608612061</t>
   </si>
   <si>
     <t xml:space="preserve">4.92947292327881</t>
@@ -2909,7 +2909,7 @@
     <t xml:space="preserve">4.86673450469971</t>
   </si>
   <si>
-    <t xml:space="preserve">5.037024974823</t>
+    <t xml:space="preserve">5.03702545166016</t>
   </si>
   <si>
     <t xml:space="preserve">4.95636177062988</t>
@@ -2939,13 +2939,13 @@
     <t xml:space="preserve">4.85777187347412</t>
   </si>
   <si>
-    <t xml:space="preserve">4.91154766082764</t>
+    <t xml:space="preserve">4.91154861450195</t>
   </si>
   <si>
     <t xml:space="preserve">4.96532392501831</t>
   </si>
   <si>
-    <t xml:space="preserve">5.11768960952759</t>
+    <t xml:space="preserve">5.11768913269043</t>
   </si>
   <si>
     <t xml:space="preserve">5.22524166107178</t>
@@ -2969,7 +2969,7 @@
     <t xml:space="preserve">5.62856245040894</t>
   </si>
   <si>
-    <t xml:space="preserve">5.52100992202759</t>
+    <t xml:space="preserve">5.52100944519043</t>
   </si>
   <si>
     <t xml:space="preserve">5.61959934234619</t>
@@ -2981,25 +2981,25 @@
     <t xml:space="preserve">5.37441253662109</t>
   </si>
   <si>
-    <t xml:space="preserve">5.47495365142822</t>
+    <t xml:space="preserve">5.47495412826538</t>
   </si>
   <si>
     <t xml:space="preserve">5.46581411361694</t>
   </si>
   <si>
-    <t xml:space="preserve">5.48409461975098</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.63947677612305</t>
+    <t xml:space="preserve">5.48409414291382</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.63947725296021</t>
   </si>
   <si>
     <t xml:space="preserve">5.75829935073853</t>
   </si>
   <si>
-    <t xml:space="preserve">5.80399942398071</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.65775775909424</t>
+    <t xml:space="preserve">5.80399990081787</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.65775728225708</t>
   </si>
   <si>
     <t xml:space="preserve">5.62119674682617</t>
@@ -3008,10 +3008,10 @@
     <t xml:space="preserve">5.410973072052</t>
   </si>
   <si>
-    <t xml:space="preserve">5.40183258056641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.63033676147461</t>
+    <t xml:space="preserve">5.40183305740356</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.63033628463745</t>
   </si>
   <si>
     <t xml:space="preserve">5.61205673217773</t>
@@ -3020,16 +3020,16 @@
     <t xml:space="preserve">5.8222804069519</t>
   </si>
   <si>
-    <t xml:space="preserve">5.84056091308594</t>
+    <t xml:space="preserve">5.84056043624878</t>
   </si>
   <si>
     <t xml:space="preserve">5.88626146316528</t>
   </si>
   <si>
-    <t xml:space="preserve">5.93196153640747</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.90454149246216</t>
+    <t xml:space="preserve">5.93196201324463</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.90454196929932</t>
   </si>
   <si>
     <t xml:space="preserve">5.97766304016113</t>
@@ -3038,7 +3038,7 @@
     <t xml:space="preserve">5.9593825340271</t>
   </si>
   <si>
-    <t xml:space="preserve">6.04164409637451</t>
+    <t xml:space="preserve">6.04164361953735</t>
   </si>
   <si>
     <t xml:space="preserve">5.87712097167969</t>
@@ -3047,7 +3047,7 @@
     <t xml:space="preserve">6.07820463180542</t>
   </si>
   <si>
-    <t xml:space="preserve">5.9136815071106</t>
+    <t xml:space="preserve">5.91368198394775</t>
   </si>
   <si>
     <t xml:space="preserve">5.68517780303955</t>
@@ -3062,7 +3062,7 @@
     <t xml:space="preserve">5.67603778839111</t>
   </si>
   <si>
-    <t xml:space="preserve">5.69431781768799</t>
+    <t xml:space="preserve">5.69431829452515</t>
   </si>
   <si>
     <t xml:space="preserve">5.66689729690552</t>
@@ -3077,7 +3077,7 @@
     <t xml:space="preserve">5.33785200119019</t>
   </si>
   <si>
-    <t xml:space="preserve">5.20988941192627</t>
+    <t xml:space="preserve">5.20988988876343</t>
   </si>
   <si>
     <t xml:space="preserve">5.34699201583862</t>
@@ -3098,7 +3098,7 @@
     <t xml:space="preserve">5.2281699180603</t>
   </si>
   <si>
-    <t xml:space="preserve">5.21902990341187</t>
+    <t xml:space="preserve">5.21902942657471</t>
   </si>
   <si>
     <t xml:space="preserve">5.15504884719849</t>
@@ -3107,22 +3107,22 @@
     <t xml:space="preserve">5.10020780563354</t>
   </si>
   <si>
-    <t xml:space="preserve">5.10934782028198</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.08192729949951</t>
+    <t xml:space="preserve">5.10934829711914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.08192777633667</t>
   </si>
   <si>
     <t xml:space="preserve">5.03622674942017</t>
   </si>
   <si>
-    <t xml:space="preserve">5.01794624328613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.11848831176758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.13676786422729</t>
+    <t xml:space="preserve">5.01794576644897</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.11848783493042</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.13676834106445</t>
   </si>
   <si>
     <t xml:space="preserve">5.07278728485107</t>
@@ -3137,19 +3137,19 @@
     <t xml:space="preserve">4.99052619934082</t>
   </si>
   <si>
-    <t xml:space="preserve">5.00880575180054</t>
+    <t xml:space="preserve">5.00880670547485</t>
   </si>
   <si>
     <t xml:space="preserve">5.0545072555542</t>
   </si>
   <si>
-    <t xml:space="preserve">5.44753408432007</t>
+    <t xml:space="preserve">5.44753360748291</t>
   </si>
   <si>
     <t xml:space="preserve">5.16418886184692</t>
   </si>
   <si>
-    <t xml:space="preserve">5.14590930938721</t>
+    <t xml:space="preserve">5.14590835571289</t>
   </si>
   <si>
     <t xml:space="preserve">4.94482469558716</t>
@@ -3158,22 +3158,22 @@
     <t xml:space="preserve">4.93568515777588</t>
   </si>
   <si>
-    <t xml:space="preserve">4.89912414550781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.8808445930481</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.85342359542847</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.82600355148315</t>
+    <t xml:space="preserve">4.89912462234497</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.88084411621094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.85342311859131</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.826003074646</t>
   </si>
   <si>
     <t xml:space="preserve">4.73460102081299</t>
   </si>
   <si>
-    <t xml:space="preserve">4.75288200378418</t>
+    <t xml:space="preserve">4.75288152694702</t>
   </si>
   <si>
     <t xml:space="preserve">4.69804096221924</t>
@@ -3182,28 +3182,28 @@
     <t xml:space="preserve">4.57921886444092</t>
   </si>
   <si>
-    <t xml:space="preserve">4.71632146835327</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.67975997924805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.84428310394287</t>
+    <t xml:space="preserve">4.71632099151611</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.67976045608521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.84428358078003</t>
   </si>
   <si>
     <t xml:space="preserve">4.80772304534912</t>
   </si>
   <si>
-    <t xml:space="preserve">4.57007837295532</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.72546148300171</t>
+    <t xml:space="preserve">4.57007884979248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.72546100616455</t>
   </si>
   <si>
     <t xml:space="preserve">4.6889009475708</t>
   </si>
   <si>
-    <t xml:space="preserve">4.67062044143677</t>
+    <t xml:space="preserve">4.67062091827393</t>
   </si>
   <si>
     <t xml:space="preserve">4.6431999206543</t>
@@ -3215,7 +3215,7 @@
     <t xml:space="preserve">4.56093835830688</t>
   </si>
   <si>
-    <t xml:space="preserve">4.58835935592651</t>
+    <t xml:space="preserve">4.58835887908936</t>
   </si>
   <si>
     <t xml:space="preserve">4.55179834365845</t>
@@ -3233,22 +3233,22 @@
     <t xml:space="preserve">4.50152778625488</t>
   </si>
   <si>
-    <t xml:space="preserve">4.49695730209351</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.40555620193481</t>
+    <t xml:space="preserve">4.49695777893066</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.40555572509766</t>
   </si>
   <si>
     <t xml:space="preserve">4.43297624588013</t>
   </si>
   <si>
-    <t xml:space="preserve">4.45582628250122</t>
+    <t xml:space="preserve">4.45582675933838</t>
   </si>
   <si>
     <t xml:space="preserve">4.36899518966675</t>
   </si>
   <si>
-    <t xml:space="preserve">4.29130411148071</t>
+    <t xml:space="preserve">4.29130363464355</t>
   </si>
   <si>
     <t xml:space="preserve">4.20447206497192</t>
@@ -3275,10 +3275,10 @@
     <t xml:space="preserve">5.32871150970459</t>
   </si>
   <si>
-    <t xml:space="preserve">5.19160890579224</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.25559091567993</t>
+    <t xml:space="preserve">5.19160938262939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.25559043884277</t>
   </si>
   <si>
     <t xml:space="preserve">5.38355255126953</t>
@@ -3305,13 +3305,13 @@
     <t xml:space="preserve">4.98138570785522</t>
   </si>
   <si>
-    <t xml:space="preserve">4.92654466629028</t>
+    <t xml:space="preserve">4.92654418945312</t>
   </si>
   <si>
     <t xml:space="preserve">5.06364727020264</t>
   </si>
   <si>
-    <t xml:space="preserve">5.30129098892212</t>
+    <t xml:space="preserve">5.30129146575928</t>
   </si>
   <si>
     <t xml:space="preserve">5.20074987411499</t>
@@ -3323,13 +3323,13 @@
     <t xml:space="preserve">5.23730993270874</t>
   </si>
   <si>
-    <t xml:space="preserve">5.27387046813965</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.31957197189331</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.27241230010986</t>
+    <t xml:space="preserve">5.27387094497681</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.31957149505615</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.27241277694702</t>
   </si>
   <si>
     <t xml:space="preserve">5.23468494415283</t>
@@ -3341,13 +3341,13 @@
     <t xml:space="preserve">5.02718353271484</t>
   </si>
   <si>
-    <t xml:space="preserve">4.99888801574707</t>
+    <t xml:space="preserve">4.99888849258423</t>
   </si>
   <si>
     <t xml:space="preserve">5.01775217056274</t>
   </si>
   <si>
-    <t xml:space="preserve">5.16866159439087</t>
+    <t xml:space="preserve">5.16866207122803</t>
   </si>
   <si>
     <t xml:space="preserve">5.1403660774231</t>
@@ -3377,10 +3377,10 @@
     <t xml:space="preserve">5.26298046112061</t>
   </si>
   <si>
-    <t xml:space="preserve">5.3761625289917</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.17809343338013</t>
+    <t xml:space="preserve">5.37616300582886</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.17809295654297</t>
   </si>
   <si>
     <t xml:space="preserve">5.21582126617432</t>
@@ -3389,7 +3389,7 @@
     <t xml:space="preserve">5.10263824462891</t>
   </si>
   <si>
-    <t xml:space="preserve">5.14979791641235</t>
+    <t xml:space="preserve">5.14979839324951</t>
   </si>
   <si>
     <t xml:space="preserve">5.09320688247681</t>
@@ -3404,7 +3404,7 @@
     <t xml:space="preserve">5.03661584854126</t>
   </si>
   <si>
-    <t xml:space="preserve">5.06491088867188</t>
+    <t xml:space="preserve">5.06491136550903</t>
   </si>
   <si>
     <t xml:space="preserve">4.95172882080078</t>
@@ -3419,7 +3419,7 @@
     <t xml:space="preserve">4.91400146484375</t>
   </si>
   <si>
-    <t xml:space="preserve">4.90456962585449</t>
+    <t xml:space="preserve">4.90456914901733</t>
   </si>
   <si>
     <t xml:space="preserve">4.77252340316772</t>
@@ -3431,16 +3431,16 @@
     <t xml:space="preserve">4.72536420822144</t>
   </si>
   <si>
-    <t xml:space="preserve">4.96116065979004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.85740995407104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.80081939697266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.51786279678345</t>
+    <t xml:space="preserve">4.9611611366272</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.8574104309082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.8008189201355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.51786327362061</t>
   </si>
   <si>
     <t xml:space="preserve">4.50843143463135</t>
@@ -3452,7 +3452,7 @@
     <t xml:space="preserve">4.54615879058838</t>
   </si>
   <si>
-    <t xml:space="preserve">4.62161350250244</t>
+    <t xml:space="preserve">4.6216139793396</t>
   </si>
   <si>
     <t xml:space="preserve">4.54144287109375</t>
@@ -3467,7 +3467,7 @@
     <t xml:space="preserve">4.56030654907227</t>
   </si>
   <si>
-    <t xml:space="preserve">4.47541999816895</t>
+    <t xml:space="preserve">4.47541952133179</t>
   </si>
   <si>
     <t xml:space="preserve">4.47070360183716</t>
@@ -3485,7 +3485,7 @@
     <t xml:space="preserve">4.50371503829956</t>
   </si>
   <si>
-    <t xml:space="preserve">4.51314735412598</t>
+    <t xml:space="preserve">4.51314687728882</t>
   </si>
   <si>
     <t xml:space="preserve">4.63576126098633</t>
@@ -3494,13 +3494,13 @@
     <t xml:space="preserve">4.65934085845947</t>
   </si>
   <si>
-    <t xml:space="preserve">4.62632989883423</t>
+    <t xml:space="preserve">4.62632942199707</t>
   </si>
   <si>
     <t xml:space="preserve">4.64519357681274</t>
   </si>
   <si>
-    <t xml:space="preserve">4.67820501327515</t>
+    <t xml:space="preserve">4.67820453643799</t>
   </si>
   <si>
     <t xml:space="preserve">4.71593236923218</t>
@@ -3518,7 +3518,7 @@
     <t xml:space="preserve">4.73479604721069</t>
   </si>
   <si>
-    <t xml:space="preserve">4.60275030136108</t>
+    <t xml:space="preserve">4.60274982452393</t>
   </si>
   <si>
     <t xml:space="preserve">4.57445430755615</t>
@@ -3533,7 +3533,7 @@
     <t xml:space="preserve">4.34337377548218</t>
   </si>
   <si>
-    <t xml:space="preserve">4.41411209106445</t>
+    <t xml:space="preserve">4.41411256790161</t>
   </si>
   <si>
     <t xml:space="preserve">4.3952488899231</t>
@@ -3575,31 +3575,31 @@
     <t xml:space="preserve">4.27263498306274</t>
   </si>
   <si>
-    <t xml:space="preserve">4.23490715026855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.11229276657104</t>
+    <t xml:space="preserve">4.2349066734314</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.1122932434082</t>
   </si>
   <si>
     <t xml:space="preserve">4.0887131690979</t>
   </si>
   <si>
-    <t xml:space="preserve">4.05570220947266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.10757732391357</t>
+    <t xml:space="preserve">4.0557017326355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.10757684707642</t>
   </si>
   <si>
     <t xml:space="preserve">4.03683805465698</t>
   </si>
   <si>
-    <t xml:space="preserve">3.86234855651855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.00854206085205</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.99911022186279</t>
+    <t xml:space="preserve">3.86234831809998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.00854253768921</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.99910998344421</t>
   </si>
   <si>
     <t xml:space="preserve">4.07456541061401</t>
@@ -3617,7 +3617,7 @@
     <t xml:space="preserve">4.15473651885986</t>
   </si>
   <si>
-    <t xml:space="preserve">4.18303203582764</t>
+    <t xml:space="preserve">4.18303155899048</t>
   </si>
   <si>
     <t xml:space="preserve">4.27735042572021</t>
@@ -3635,7 +3635,7 @@
     <t xml:space="preserve">4.24905490875244</t>
   </si>
   <si>
-    <t xml:space="preserve">4.26791858673096</t>
+    <t xml:space="preserve">4.26791906356812</t>
   </si>
   <si>
     <t xml:space="preserve">4.39053297042847</t>
@@ -3644,7 +3644,7 @@
     <t xml:space="preserve">4.37166976928711</t>
   </si>
   <si>
-    <t xml:space="preserve">4.35752153396606</t>
+    <t xml:space="preserve">4.35752105712891</t>
   </si>
   <si>
     <t xml:space="preserve">4.35280513763428</t>
@@ -3680,19 +3680,19 @@
     <t xml:space="preserve">4.23962306976318</t>
   </si>
   <si>
-    <t xml:space="preserve">4.20189571380615</t>
+    <t xml:space="preserve">4.20189523696899</t>
   </si>
   <si>
     <t xml:space="preserve">4.12644052505493</t>
   </si>
   <si>
-    <t xml:space="preserve">4.02268981933594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.15002059936523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.92837166786194</t>
+    <t xml:space="preserve">4.0226902961731</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.15002012252808</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.92837142944336</t>
   </si>
   <si>
     <t xml:space="preserve">4.04626989364624</t>
@@ -3701,16 +3701,16 @@
     <t xml:space="preserve">3.96138286590576</t>
   </si>
   <si>
-    <t xml:space="preserve">4.06041717529297</t>
+    <t xml:space="preserve">4.06041765213013</t>
   </si>
   <si>
     <t xml:space="preserve">4.01797485351562</t>
   </si>
   <si>
-    <t xml:space="preserve">3.90007638931274</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.94251894950867</t>
+    <t xml:space="preserve">3.90007615089417</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.94251942634583</t>
   </si>
   <si>
     <t xml:space="preserve">3.89535999298096</t>
@@ -3728,7 +3728,7 @@
     <t xml:space="preserve">3.88121199607849</t>
   </si>
   <si>
-    <t xml:space="preserve">3.84348464012146</t>
+    <t xml:space="preserve">3.84348440170288</t>
   </si>
   <si>
     <t xml:space="preserve">3.81990528106689</t>
@@ -3746,10 +3746,10 @@
     <t xml:space="preserve">3.75388216972351</t>
   </si>
   <si>
-    <t xml:space="preserve">3.72558641433716</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.76331377029419</t>
+    <t xml:space="preserve">3.72558665275574</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.76331400871277</t>
   </si>
   <si>
     <t xml:space="preserve">3.735018491745</t>
@@ -3758,7 +3758,7 @@
     <t xml:space="preserve">3.71615481376648</t>
   </si>
   <si>
-    <t xml:space="preserve">3.58410859107971</t>
+    <t xml:space="preserve">3.58410835266113</t>
   </si>
   <si>
     <t xml:space="preserve">3.76442790031433</t>
@@ -70606,7 +70606,7 @@
     </row>
     <row r="2531">
       <c r="A2531" s="1" t="n">
-        <v>46002.6918518519</v>
+        <v>46002.3333333333</v>
       </c>
       <c r="B2531" t="n">
         <v>58184</v>
@@ -70627,6 +70627,32 @@
         <v>1491</v>
       </c>
       <c r="H2531" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2532">
+      <c r="A2532" s="1" t="n">
+        <v>46003.6911689815</v>
+      </c>
+      <c r="B2532" t="n">
+        <v>40963</v>
+      </c>
+      <c r="C2532" t="n">
+        <v>7.44999980926514</v>
+      </c>
+      <c r="D2532" t="n">
+        <v>7.26999998092651</v>
+      </c>
+      <c r="E2532" t="n">
+        <v>7.36999988555908</v>
+      </c>
+      <c r="F2532" t="n">
+        <v>7.32999992370605</v>
+      </c>
+      <c r="G2532" t="s">
+        <v>1482</v>
+      </c>
+      <c r="H2532" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/BAN.MI.xlsx
+++ b/data/BAN.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1491" uniqueCount="1491">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1492" uniqueCount="1492">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -47,28 +47,28 @@
     <t xml:space="preserve">3.68330240249634</t>
   </si>
   <si>
-    <t xml:space="preserve">3.59039258956909</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.46283960342407</t>
+    <t xml:space="preserve">3.59039282798767</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.46283984184265</t>
   </si>
   <si>
     <t xml:space="preserve">3.41874718666077</t>
   </si>
   <si>
-    <t xml:space="preserve">3.35733246803284</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.44551777839661</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.46441459655762</t>
+    <t xml:space="preserve">3.35733294487</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.44551730155945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.46441435813904</t>
   </si>
   <si>
     <t xml:space="preserve">3.45181632041931</t>
   </si>
   <si>
-    <t xml:space="preserve">3.43134498596191</t>
+    <t xml:space="preserve">3.43134474754333</t>
   </si>
   <si>
     <t xml:space="preserve">3.38410258293152</t>
@@ -80,37 +80,37 @@
     <t xml:space="preserve">3.11639833450317</t>
   </si>
   <si>
-    <t xml:space="preserve">3.24080181121826</t>
+    <t xml:space="preserve">3.240802526474</t>
   </si>
   <si>
     <t xml:space="preserve">3.29119372367859</t>
   </si>
   <si>
-    <t xml:space="preserve">3.21245670318604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.26757287979126</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.19356036186218</t>
+    <t xml:space="preserve">3.21245694160461</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.2675724029541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.19356060028076</t>
   </si>
   <si>
     <t xml:space="preserve">3.13372039794922</t>
   </si>
   <si>
-    <t xml:space="preserve">3.22820425033569</t>
+    <t xml:space="preserve">3.22820448875427</t>
   </si>
   <si>
     <t xml:space="preserve">3.16678953170776</t>
   </si>
   <si>
-    <t xml:space="preserve">3.17308855056763</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.07073092460632</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.14946746826172</t>
+    <t xml:space="preserve">3.17308878898621</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.0707311630249</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.14946794509888</t>
   </si>
   <si>
     <t xml:space="preserve">3.0502598285675</t>
@@ -119,7 +119,7 @@
     <t xml:space="preserve">2.92900490760803</t>
   </si>
   <si>
-    <t xml:space="preserve">2.91325759887695</t>
+    <t xml:space="preserve">2.91325783729553</t>
   </si>
   <si>
     <t xml:space="preserve">2.83452081680298</t>
@@ -128,121 +128,121 @@
     <t xml:space="preserve">2.82664752006531</t>
   </si>
   <si>
-    <t xml:space="preserve">2.75263500213623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.75420928001404</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.755784034729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.89436101913452</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.98254609107971</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.96207451820374</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.99356889724731</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.05970788002014</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.11009955406189</t>
+    <t xml:space="preserve">2.75263428688049</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.75420951843262</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.75578427314758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.8943612575531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.98254585266113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.96207404136658</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.99356913566589</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.05970740318298</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.11009931564331</t>
   </si>
   <si>
     <t xml:space="preserve">3.06915616989136</t>
   </si>
   <si>
-    <t xml:space="preserve">2.96364879608154</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.99199414253235</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.00774168968201</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.97624683380127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.06285762786865</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.11797332763672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.18096232414246</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.1022253036499</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.13687014579773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.23292875289917</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.33843517303467</t>
+    <t xml:space="preserve">2.9636492729187</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.99199438095093</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.00774121284485</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.97624659538269</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.06285738945007</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.11797285079956</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.18096256256104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.10222578048706</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.13686990737915</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.23292899131775</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.33843564987183</t>
   </si>
   <si>
     <t xml:space="preserve">3.30694055557251</t>
   </si>
   <si>
-    <t xml:space="preserve">3.24395132064819</t>
+    <t xml:space="preserve">3.24395203590393</t>
   </si>
   <si>
     <t xml:space="preserve">3.24237728118896</t>
   </si>
   <si>
-    <t xml:space="preserve">3.12584686279297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.19670915603638</t>
+    <t xml:space="preserve">3.12584662437439</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.19670939445496</t>
   </si>
   <si>
     <t xml:space="preserve">3.2030086517334</t>
   </si>
   <si>
-    <t xml:space="preserve">3.10380029678345</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.11324882507324</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.14159417152405</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.04711008071899</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.99986791610718</t>
+    <t xml:space="preserve">3.10380053520203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.11324858665466</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.14159393310547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.04710984230042</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.9998676776886</t>
   </si>
   <si>
     <t xml:space="preserve">2.96049976348877</t>
   </si>
   <si>
-    <t xml:space="preserve">3.09435224533081</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.96837329864502</t>
+    <t xml:space="preserve">3.09435200691223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.9683735370636</t>
   </si>
   <si>
     <t xml:space="preserve">2.86286616325378</t>
   </si>
   <si>
-    <t xml:space="preserve">2.87388944625854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.91010856628418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.98569536209106</t>
+    <t xml:space="preserve">2.87388920783997</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.9101083278656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.98569512367249</t>
   </si>
   <si>
     <t xml:space="preserve">3.00144267082214</t>
@@ -260,7 +260,7 @@
     <t xml:space="preserve">2.85814213752747</t>
   </si>
   <si>
-    <t xml:space="preserve">2.81404948234558</t>
+    <t xml:space="preserve">2.81404900550842</t>
   </si>
   <si>
     <t xml:space="preserve">2.84082007408142</t>
@@ -272,22 +272,22 @@
     <t xml:space="preserve">2.72901368141174</t>
   </si>
   <si>
-    <t xml:space="preserve">2.65185165405273</t>
+    <t xml:space="preserve">2.65185141563416</t>
   </si>
   <si>
     <t xml:space="preserve">2.68177151679993</t>
   </si>
   <si>
-    <t xml:space="preserve">2.71484112739563</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.76365733146667</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.77940535545349</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.724289894104</t>
+    <t xml:space="preserve">2.71484088897705</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.76365756988525</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.77940511703491</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.72428941726685</t>
   </si>
   <si>
     <t xml:space="preserve">2.59043717384338</t>
@@ -302,16 +302,16 @@
     <t xml:space="preserve">2.48020577430725</t>
   </si>
   <si>
-    <t xml:space="preserve">2.51957416534424</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.60572743415833</t>
+    <t xml:space="preserve">2.51957392692566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.60572719573975</t>
   </si>
   <si>
     <t xml:space="preserve">2.58784651756287</t>
   </si>
   <si>
-    <t xml:space="preserve">2.5602126121521</t>
+    <t xml:space="preserve">2.56021237373352</t>
   </si>
   <si>
     <t xml:space="preserve">2.56183815002441</t>
@@ -320,67 +320,67 @@
     <t xml:space="preserve">2.60897850990295</t>
   </si>
   <si>
-    <t xml:space="preserve">2.59272289276123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.58134460449219</t>
+    <t xml:space="preserve">2.59272313117981</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.58134436607361</t>
   </si>
   <si>
     <t xml:space="preserve">2.6008505821228</t>
   </si>
   <si>
-    <t xml:space="preserve">2.72114038467407</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.82029747962952</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.80404210090637</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.6821277141571</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.71463823318481</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.44642519950867</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.39765906333923</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.50331854820251</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.47568464279175</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.52770161628723</t>
+    <t xml:space="preserve">2.72114014625549</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.8202977180481</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.80404233932495</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.68212723731995</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.71463799476624</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.44642567634583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.39765930175781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.50331902503967</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.47568488121033</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.52770137786865</t>
   </si>
   <si>
     <t xml:space="preserve">2.50819540023804</t>
   </si>
   <si>
-    <t xml:space="preserve">2.40578722953796</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.19446754455566</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.23510599136353</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.29525065422058</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.27411913871765</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.35702133178711</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.37327647209167</t>
+    <t xml:space="preserve">2.40578699111938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.1944682598114</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.2351062297821</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.29525089263916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.27411890029907</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.35702085494995</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.37327599525452</t>
   </si>
   <si>
     <t xml:space="preserve">2.29199957847595</t>
@@ -389,10 +389,10 @@
     <t xml:space="preserve">2.19284224510193</t>
   </si>
   <si>
-    <t xml:space="preserve">2.22535276412964</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.28387188911438</t>
+    <t xml:space="preserve">2.2253532409668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.28387236595154</t>
   </si>
   <si>
     <t xml:space="preserve">2.30500388145447</t>
@@ -401,10 +401,10 @@
     <t xml:space="preserve">2.3310124874115</t>
   </si>
   <si>
-    <t xml:space="preserve">2.33588886260986</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.33263778686523</t>
+    <t xml:space="preserve">2.33588910102844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.33263802528381</t>
   </si>
   <si>
     <t xml:space="preserve">2.3196337223053</t>
@@ -413,25 +413,25 @@
     <t xml:space="preserve">2.38140392303467</t>
   </si>
   <si>
-    <t xml:space="preserve">2.53582978248596</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.54395723342896</t>
+    <t xml:space="preserve">2.5358293056488</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.54395747184753</t>
   </si>
   <si>
     <t xml:space="preserve">2.56834030151367</t>
   </si>
   <si>
-    <t xml:space="preserve">2.89669752120972</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.83817863464355</t>
+    <t xml:space="preserve">2.89669728279114</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.83817839622498</t>
   </si>
   <si>
     <t xml:space="preserve">2.81217002868652</t>
   </si>
   <si>
-    <t xml:space="preserve">2.59597396850586</t>
+    <t xml:space="preserve">2.59597420692444</t>
   </si>
   <si>
     <t xml:space="preserve">2.57646775245667</t>
@@ -440,76 +440,76 @@
     <t xml:space="preserve">2.57321643829346</t>
   </si>
   <si>
-    <t xml:space="preserve">2.56671452522278</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.53257846832275</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.5374550819397</t>
+    <t xml:space="preserve">2.56671500205994</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.53257822990417</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.53745484352112</t>
   </si>
   <si>
     <t xml:space="preserve">2.6366126537323</t>
   </si>
   <si>
-    <t xml:space="preserve">2.63011050224304</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.64636540412903</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.65286803245544</t>
+    <t xml:space="preserve">2.63011026382446</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.64636564254761</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.65286755561829</t>
   </si>
   <si>
     <t xml:space="preserve">2.63823795318604</t>
   </si>
   <si>
-    <t xml:space="preserve">2.64148879051208</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.69188022613525</t>
+    <t xml:space="preserve">2.64148926734924</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.69188070297241</t>
   </si>
   <si>
     <t xml:space="preserve">2.75690174102783</t>
   </si>
   <si>
-    <t xml:space="preserve">2.79266381263733</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.76340436935425</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.7308931350708</t>
+    <t xml:space="preserve">2.79266333580017</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.76340389251709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.73089337348938</t>
   </si>
   <si>
     <t xml:space="preserve">2.65449333190918</t>
   </si>
   <si>
-    <t xml:space="preserve">2.65774416923523</t>
+    <t xml:space="preserve">2.65774440765381</t>
   </si>
   <si>
     <t xml:space="preserve">2.74227213859558</t>
   </si>
   <si>
-    <t xml:space="preserve">2.76828026771545</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.70651054382324</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.72764229774475</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.74064612388611</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.76990628242493</t>
+    <t xml:space="preserve">2.76828050613403</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.70651006698608</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.72764205932617</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.74064636230469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.76990604400635</t>
   </si>
   <si>
     <t xml:space="preserve">2.8007915019989</t>
   </si>
   <si>
-    <t xml:space="preserve">2.69513130187988</t>
+    <t xml:space="preserve">2.69513154029846</t>
   </si>
   <si>
     <t xml:space="preserve">2.6674976348877</t>
@@ -521,37 +521,37 @@
     <t xml:space="preserve">2.62523365020752</t>
   </si>
   <si>
-    <t xml:space="preserve">2.59759974479675</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.61710619926453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.66587209701538</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.63336133956909</t>
+    <t xml:space="preserve">2.59759950637817</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.61710643768311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.6658718585968</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.63336110115051</t>
   </si>
   <si>
     <t xml:space="preserve">2.6886293888092</t>
   </si>
   <si>
-    <t xml:space="preserve">2.60247611999512</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.67725086212158</t>
+    <t xml:space="preserve">2.6024763584137</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.677250623703</t>
   </si>
   <si>
     <t xml:space="preserve">2.70976161956787</t>
   </si>
   <si>
-    <t xml:space="preserve">2.75527620315552</t>
+    <t xml:space="preserve">2.7552764415741</t>
   </si>
   <si>
     <t xml:space="preserve">2.72601675987244</t>
   </si>
   <si>
-    <t xml:space="preserve">2.72276592254639</t>
+    <t xml:space="preserve">2.72276544570923</t>
   </si>
   <si>
     <t xml:space="preserve">2.82842516899109</t>
@@ -560,43 +560,43 @@
     <t xml:space="preserve">2.74389743804932</t>
   </si>
   <si>
-    <t xml:space="preserve">2.76177787780762</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.73902106285095</t>
+    <t xml:space="preserve">2.76177835464478</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.73902058601379</t>
   </si>
   <si>
     <t xml:space="preserve">2.70488476753235</t>
   </si>
   <si>
-    <t xml:space="preserve">2.6902551651001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.612229347229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.73251867294312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.67562484741211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.62360858917236</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.59434843063354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.55371069908142</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.55045914649963</t>
+    <t xml:space="preserve">2.69025444984436</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.61222958564758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.73251891136169</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.67562532424927</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.62360811233521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.59434866905212</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.55371046066284</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.55045938491821</t>
   </si>
   <si>
     <t xml:space="preserve">2.51307201385498</t>
   </si>
   <si>
-    <t xml:space="preserve">2.46755719184875</t>
+    <t xml:space="preserve">2.46755695343018</t>
   </si>
   <si>
     <t xml:space="preserve">2.50169324874878</t>
@@ -614,94 +614,94 @@
     <t xml:space="preserve">2.66912293434143</t>
   </si>
   <si>
-    <t xml:space="preserve">2.72439098358154</t>
+    <t xml:space="preserve">2.7243914604187</t>
   </si>
   <si>
     <t xml:space="preserve">2.78291034698486</t>
   </si>
   <si>
-    <t xml:space="preserve">2.77153182029724</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.77803325653076</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.70000839233398</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.77315711975098</t>
+    <t xml:space="preserve">2.77153158187866</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.77803349494934</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.70000815391541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.7731568813324</t>
   </si>
   <si>
     <t xml:space="preserve">2.7650294303894</t>
   </si>
   <si>
-    <t xml:space="preserve">2.71788930892944</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.74552297592163</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.77965903282166</t>
+    <t xml:space="preserve">2.71788907051086</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.74552321434021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.77965974807739</t>
   </si>
   <si>
     <t xml:space="preserve">2.74714875221252</t>
   </si>
   <si>
-    <t xml:space="preserve">2.60410189628601</t>
+    <t xml:space="preserve">2.60410213470459</t>
   </si>
   <si>
     <t xml:space="preserve">2.62685942649841</t>
   </si>
   <si>
-    <t xml:space="preserve">2.64961624145508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.69350600242615</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.69838261604309</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.92270565032959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.88531851768494</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.99910616874695</t>
+    <t xml:space="preserve">2.64961671829224</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.69350552558899</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.69838237762451</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.92270588874817</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.88531875610352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.99910593032837</t>
   </si>
   <si>
     <t xml:space="preserve">2.97472310066223</t>
   </si>
   <si>
-    <t xml:space="preserve">2.96984648704529</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.96334409713745</t>
+    <t xml:space="preserve">2.96984624862671</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.96334433555603</t>
   </si>
   <si>
     <t xml:space="preserve">2.94221234321594</t>
   </si>
   <si>
-    <t xml:space="preserve">2.93408489227295</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.89832305908203</t>
+    <t xml:space="preserve">2.93408465385437</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.89832282066345</t>
   </si>
   <si>
     <t xml:space="preserve">2.89182114601135</t>
   </si>
   <si>
-    <t xml:space="preserve">2.87881660461426</t>
+    <t xml:space="preserve">2.87881684303284</t>
   </si>
   <si>
     <t xml:space="preserve">2.87556576728821</t>
   </si>
   <si>
-    <t xml:space="preserve">2.84468030929565</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.82192325592041</t>
+    <t xml:space="preserve">2.84468054771423</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.82192277908325</t>
   </si>
   <si>
     <t xml:space="preserve">2.84955716133118</t>
@@ -710,10 +710,10 @@
     <t xml:space="preserve">2.91945481300354</t>
   </si>
   <si>
-    <t xml:space="preserve">2.92595672607422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.9909782409668</t>
+    <t xml:space="preserve">2.9259569644928</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.99097847938538</t>
   </si>
   <si>
     <t xml:space="preserve">2.9145781993866</t>
@@ -725,28 +725,28 @@
     <t xml:space="preserve">2.95846772193909</t>
   </si>
   <si>
-    <t xml:space="preserve">2.95684242248535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.95196580886841</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.0494978427887</t>
+    <t xml:space="preserve">2.95684218406677</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.95196557044983</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.04949760437012</t>
   </si>
   <si>
     <t xml:space="preserve">3.05599975585938</t>
   </si>
   <si>
-    <t xml:space="preserve">2.99585509300232</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.97959995269775</t>
+    <t xml:space="preserve">2.9958553314209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.9795994758606</t>
   </si>
   <si>
     <t xml:space="preserve">3.00723361968994</t>
   </si>
   <si>
-    <t xml:space="preserve">3.09645938873291</t>
+    <t xml:space="preserve">3.09645962715149</t>
   </si>
   <si>
     <t xml:space="preserve">3.11628723144531</t>
@@ -758,13 +758,13 @@
     <t xml:space="preserve">3.13941979408264</t>
   </si>
   <si>
-    <t xml:space="preserve">3.14437651634216</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.18898963928223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.1807279586792</t>
+    <t xml:space="preserve">3.14437675476074</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.18898940086365</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.18072772026062</t>
   </si>
   <si>
     <t xml:space="preserve">3.24847316741943</t>
@@ -773,49 +773,49 @@
     <t xml:space="preserve">3.21707916259766</t>
   </si>
   <si>
-    <t xml:space="preserve">3.16750955581665</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.1542911529541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.170814037323</t>
+    <t xml:space="preserve">3.16750931739807</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.15429091453552</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.17081379890442</t>
   </si>
   <si>
     <t xml:space="preserve">3.07663154602051</t>
   </si>
   <si>
-    <t xml:space="preserve">3.07497906684875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.98244881629944</t>
+    <t xml:space="preserve">3.07497882843018</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.98244857788086</t>
   </si>
   <si>
     <t xml:space="preserve">3.0584557056427</t>
   </si>
   <si>
-    <t xml:space="preserve">3.06506490707397</t>
+    <t xml:space="preserve">3.06506514549255</t>
   </si>
   <si>
     <t xml:space="preserve">3.03367066383362</t>
   </si>
   <si>
-    <t xml:space="preserve">3.02540898323059</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.99401497840881</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.99071025848389</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.99897217750549</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.93783569335938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.95601177215576</t>
+    <t xml:space="preserve">3.02540922164917</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.99401521682739</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.99071049690247</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.99897193908691</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.93783617019653</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.9560112953186</t>
   </si>
   <si>
     <t xml:space="preserve">3.07993602752686</t>
@@ -824,10 +824,10 @@
     <t xml:space="preserve">3.08819770812988</t>
   </si>
   <si>
-    <t xml:space="preserve">3.08654522895813</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.10802555084229</t>
+    <t xml:space="preserve">3.08654594421387</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.10802531242371</t>
   </si>
   <si>
     <t xml:space="preserve">3.11133050918579</t>
@@ -836,28 +836,28 @@
     <t xml:space="preserve">3.14768123626709</t>
   </si>
   <si>
-    <t xml:space="preserve">3.16420459747314</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.2055127620697</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.21377468109131</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.23029804229736</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.23360252380371</t>
+    <t xml:space="preserve">3.16420435905457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.20551323890686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.21377444267273</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.23029780387878</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.23360228538513</t>
   </si>
   <si>
     <t xml:space="preserve">3.25343012809753</t>
   </si>
   <si>
-    <t xml:space="preserve">3.29473853111267</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.3079571723938</t>
+    <t xml:space="preserve">3.29473829269409</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.30795741081238</t>
   </si>
   <si>
     <t xml:space="preserve">3.27160573005676</t>
@@ -869,64 +869,64 @@
     <t xml:space="preserve">3.22368812561035</t>
   </si>
   <si>
-    <t xml:space="preserve">3.25012588500977</t>
+    <t xml:space="preserve">3.25012564659119</t>
   </si>
   <si>
     <t xml:space="preserve">3.19394636154175</t>
   </si>
   <si>
-    <t xml:space="preserve">3.26334452629089</t>
+    <t xml:space="preserve">3.26334404945374</t>
   </si>
   <si>
     <t xml:space="preserve">3.0981113910675</t>
   </si>
   <si>
-    <t xml:space="preserve">3.15924787521362</t>
+    <t xml:space="preserve">3.15924763679504</t>
   </si>
   <si>
     <t xml:space="preserve">3.17246627807617</t>
   </si>
   <si>
-    <t xml:space="preserve">3.17411851882935</t>
+    <t xml:space="preserve">3.17411875724792</t>
   </si>
   <si>
     <t xml:space="preserve">3.1509861946106</t>
   </si>
   <si>
-    <t xml:space="preserve">3.05184650421143</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.05680346488953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.08489298820496</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.12785339355469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.03201866149902</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.09480667114258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.07332706451416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.09150242805481</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.13115811347961</t>
+    <t xml:space="preserve">3.05184626579285</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.05680370330811</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.08489322662354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.12785363197327</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.0320188999176</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.09480714797974</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.073326587677</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.09150218963623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.13115835189819</t>
   </si>
   <si>
     <t xml:space="preserve">3.10967779159546</t>
   </si>
   <si>
-    <t xml:space="preserve">3.10472106933594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.12124466896057</t>
+    <t xml:space="preserve">3.10472083091736</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.12124419212341</t>
   </si>
   <si>
     <t xml:space="preserve">3.13611507415771</t>
@@ -938,22 +938,22 @@
     <t xml:space="preserve">3.12950611114502</t>
   </si>
   <si>
-    <t xml:space="preserve">3.14107179641724</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.15759515762329</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.18403267860413</t>
+    <t xml:space="preserve">3.14107227325439</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.15759539604187</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.18403244018555</t>
   </si>
   <si>
     <t xml:space="preserve">3.10637307167053</t>
   </si>
   <si>
-    <t xml:space="preserve">3.08158850669861</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.10141611099243</t>
+    <t xml:space="preserve">3.08158826828003</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.10141634941101</t>
   </si>
   <si>
     <t xml:space="preserve">3.10306859016418</t>
@@ -962,25 +962,25 @@
     <t xml:space="preserve">3.12289643287659</t>
   </si>
   <si>
-    <t xml:space="preserve">3.08984994888306</t>
+    <t xml:space="preserve">3.08984971046448</t>
   </si>
   <si>
     <t xml:space="preserve">2.94940209388733</t>
   </si>
   <si>
-    <t xml:space="preserve">2.93287897109985</t>
+    <t xml:space="preserve">2.93287873268127</t>
   </si>
   <si>
     <t xml:space="preserve">2.83704400062561</t>
   </si>
   <si>
-    <t xml:space="preserve">2.88165712356567</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.90809392929077</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.91139912605286</t>
+    <t xml:space="preserve">2.88165736198425</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.90809416770935</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.9113986492157</t>
   </si>
   <si>
     <t xml:space="preserve">2.94609761238098</t>
@@ -992,19 +992,19 @@
     <t xml:space="preserve">2.96592545509338</t>
   </si>
   <si>
-    <t xml:space="preserve">2.88496160507202</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.84034848213196</t>
+    <t xml:space="preserve">2.8849618434906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.84034872055054</t>
   </si>
   <si>
     <t xml:space="preserve">2.82878255844116</t>
   </si>
   <si>
-    <t xml:space="preserve">2.81225967407227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.88000440597534</t>
+    <t xml:space="preserve">2.81225919723511</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.88000464439392</t>
   </si>
   <si>
     <t xml:space="preserve">2.75112295150757</t>
@@ -1016,10 +1016,10 @@
     <t xml:space="preserve">2.79243135452271</t>
   </si>
   <si>
-    <t xml:space="preserve">2.81391167640686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.85852408409119</t>
+    <t xml:space="preserve">2.81391143798828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.85852456092834</t>
   </si>
   <si>
     <t xml:space="preserve">2.97418713569641</t>
@@ -1028,13 +1028,13 @@
     <t xml:space="preserve">2.97088241577148</t>
   </si>
   <si>
-    <t xml:space="preserve">3.01549553871155</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.05515122413635</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.04028058052063</t>
+    <t xml:space="preserve">3.01549530029297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.05515098571777</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.04028081893921</t>
   </si>
   <si>
     <t xml:space="preserve">3.07002210617065</t>
@@ -1043,7 +1043,7 @@
     <t xml:space="preserve">3.0634126663208</t>
   </si>
   <si>
-    <t xml:space="preserve">3.023756980896</t>
+    <t xml:space="preserve">3.02375721931458</t>
   </si>
   <si>
     <t xml:space="preserve">3.0369758605957</t>
@@ -1052,7 +1052,7 @@
     <t xml:space="preserve">3.02871370315552</t>
   </si>
   <si>
-    <t xml:space="preserve">3.05349898338318</t>
+    <t xml:space="preserve">3.0534987449646</t>
   </si>
   <si>
     <t xml:space="preserve">3.07828378677368</t>
@@ -1064,16 +1064,16 @@
     <t xml:space="preserve">3.06919598579407</t>
   </si>
   <si>
-    <t xml:space="preserve">3.15594291687012</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.21790480613708</t>
+    <t xml:space="preserve">3.1559431552887</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.21790528297424</t>
   </si>
   <si>
     <t xml:space="preserve">3.17659711837769</t>
   </si>
   <si>
-    <t xml:space="preserve">3.19312047958374</t>
+    <t xml:space="preserve">3.19312000274658</t>
   </si>
   <si>
     <t xml:space="preserve">3.25508260726929</t>
@@ -1082,40 +1082,40 @@
     <t xml:space="preserve">3.22203636169434</t>
   </si>
   <si>
-    <t xml:space="preserve">2.96179485321045</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.97831797599792</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.92461705207825</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.87504744529724</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.13528895378113</t>
+    <t xml:space="preserve">2.96179533004761</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.97831773757935</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.92461729049683</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.8750479221344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.13528919219971</t>
   </si>
   <si>
     <t xml:space="preserve">3.07745742797852</t>
   </si>
   <si>
-    <t xml:space="preserve">3.05267238616943</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.03614926338196</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.92048692703247</t>
+    <t xml:space="preserve">3.05267262458801</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.03614950180054</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.92048645019531</t>
   </si>
   <si>
     <t xml:space="preserve">3.08571910858154</t>
   </si>
   <si>
-    <t xml:space="preserve">3.01962637901306</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.02788782119751</t>
+    <t xml:space="preserve">3.01962614059448</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.02788758277893</t>
   </si>
   <si>
     <t xml:space="preserve">3.0485417842865</t>
@@ -1124,46 +1124,46 @@
     <t xml:space="preserve">3.04441094398499</t>
   </si>
   <si>
-    <t xml:space="preserve">3.15181183815002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.33769917488098</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.25095152854919</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.2757363319397</t>
+    <t xml:space="preserve">3.15181255340576</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.3376989364624</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.25095176696777</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.27573657035828</t>
   </si>
   <si>
     <t xml:space="preserve">3.28399801254272</t>
   </si>
   <si>
-    <t xml:space="preserve">3.24682116508484</t>
+    <t xml:space="preserve">3.24682140350342</t>
   </si>
   <si>
     <t xml:space="preserve">3.18485856056213</t>
   </si>
   <si>
-    <t xml:space="preserve">3.24373745918274</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.20177483558655</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.21016764640808</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.18918609619141</t>
+    <t xml:space="preserve">3.2437379360199</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.20177507400513</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.2101674079895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.18918585777283</t>
   </si>
   <si>
     <t xml:space="preserve">3.22275614738464</t>
   </si>
   <si>
-    <t xml:space="preserve">3.16400837898254</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.08847522735596</t>
+    <t xml:space="preserve">3.16400814056396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.08847498893738</t>
   </si>
   <si>
     <t xml:space="preserve">3.12204551696777</t>
@@ -1175,10 +1175,10 @@
     <t xml:space="preserve">3.20597100257874</t>
   </si>
   <si>
-    <t xml:space="preserve">3.25632691383362</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.24793410301208</t>
+    <t xml:space="preserve">3.2563271522522</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.24793386459351</t>
   </si>
   <si>
     <t xml:space="preserve">3.10526013374329</t>
@@ -1187,10 +1187,10 @@
     <t xml:space="preserve">3.07168984413147</t>
   </si>
   <si>
-    <t xml:space="preserve">3.18498969078064</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.11365270614624</t>
+    <t xml:space="preserve">3.18498992919922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.11365246772766</t>
   </si>
   <si>
     <t xml:space="preserve">3.1262412071228</t>
@@ -1199,7 +1199,7 @@
     <t xml:space="preserve">3.1388304233551</t>
   </si>
   <si>
-    <t xml:space="preserve">3.14722275733948</t>
+    <t xml:space="preserve">3.14722323417664</t>
   </si>
   <si>
     <t xml:space="preserve">3.15561556816101</t>
@@ -1208,67 +1208,67 @@
     <t xml:space="preserve">3.17240071296692</t>
   </si>
   <si>
-    <t xml:space="preserve">3.08427834510803</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.13463425636292</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.16820430755615</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.10945606231689</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.1598117351532</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.19338226318359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.21436357498169</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.23534536361694</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.26471948623657</t>
+    <t xml:space="preserve">3.08427858352661</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.13463377952576</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.16820478439331</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.10945653915405</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.15981197357178</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.19338202476501</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.21436333656311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.23534512519836</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.26471924781799</t>
   </si>
   <si>
     <t xml:space="preserve">3.32346773147583</t>
   </si>
   <si>
-    <t xml:space="preserve">3.31087851524353</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.27730798721313</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.35703778266907</t>
+    <t xml:space="preserve">3.31087827682495</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.27730846405029</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.35703802108765</t>
   </si>
   <si>
     <t xml:space="preserve">3.42417860031128</t>
   </si>
   <si>
-    <t xml:space="preserve">3.49131941795349</t>
+    <t xml:space="preserve">3.49131894111633</t>
   </si>
   <si>
     <t xml:space="preserve">3.43257117271423</t>
   </si>
   <si>
-    <t xml:space="preserve">3.54167485237122</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.44935655593872</t>
+    <t xml:space="preserve">3.54167461395264</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.44935631752014</t>
   </si>
   <si>
     <t xml:space="preserve">3.48292660713196</t>
   </si>
   <si>
-    <t xml:space="preserve">3.51649737358093</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.474534034729</t>
+    <t xml:space="preserve">3.51649713516235</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.47453427314758</t>
   </si>
   <si>
     <t xml:space="preserve">3.45774912834167</t>
@@ -1280,46 +1280,46 @@
     <t xml:space="preserve">3.37801957130432</t>
   </si>
   <si>
-    <t xml:space="preserve">3.47033786773682</t>
+    <t xml:space="preserve">3.47033834457397</t>
   </si>
   <si>
     <t xml:space="preserve">3.30248594284058</t>
   </si>
   <si>
-    <t xml:space="preserve">3.31927084922791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.29828977584839</t>
+    <t xml:space="preserve">3.31927108764648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.29829001426697</t>
   </si>
   <si>
     <t xml:space="preserve">3.34025263786316</t>
   </si>
   <si>
-    <t xml:space="preserve">3.27311182022095</t>
+    <t xml:space="preserve">3.27311205863953</t>
   </si>
   <si>
     <t xml:space="preserve">3.28150463104248</t>
   </si>
   <si>
-    <t xml:space="preserve">3.399001121521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.57524561882019</t>
+    <t xml:space="preserve">3.39900135993958</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.57524585723877</t>
   </si>
   <si>
     <t xml:space="preserve">3.58783435821533</t>
   </si>
   <si>
-    <t xml:space="preserve">3.55006766319275</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.5794415473938</t>
+    <t xml:space="preserve">3.55006742477417</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.57944130897522</t>
   </si>
   <si>
     <t xml:space="preserve">3.58363795280457</t>
   </si>
   <si>
-    <t xml:space="preserve">3.66336679458618</t>
+    <t xml:space="preserve">3.66336750984192</t>
   </si>
   <si>
     <t xml:space="preserve">3.55845999717712</t>
@@ -1328,124 +1328,124 @@
     <t xml:space="preserve">3.56685256958008</t>
   </si>
   <si>
-    <t xml:space="preserve">3.62140417098999</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.78086423873901</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.88577103614807</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.72211599349976</t>
+    <t xml:space="preserve">3.62140464782715</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.78086352348328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.88577127456665</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.7221155166626</t>
   </si>
   <si>
     <t xml:space="preserve">3.76407885551453</t>
   </si>
   <si>
-    <t xml:space="preserve">3.68434882164001</t>
+    <t xml:space="preserve">3.68434858322144</t>
   </si>
   <si>
     <t xml:space="preserve">3.79764914512634</t>
   </si>
   <si>
-    <t xml:space="preserve">3.82702374458313</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.80184507369995</t>
+    <t xml:space="preserve">3.82702326774597</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.80184578895569</t>
   </si>
   <si>
     <t xml:space="preserve">3.83961224555969</t>
   </si>
   <si>
-    <t xml:space="preserve">3.91934180259705</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.91094946861267</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.94451904296875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.06621170043945</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.02005243301392</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.92773365974426</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.86898636817932</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.81863069534302</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.86059355735779</t>
+    <t xml:space="preserve">3.91934204101562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.91094899177551</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.94451999664307</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.06621217727661</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.02005290985107</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.92773389816284</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.86898612976074</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.8186309337616</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.86059379577637</t>
   </si>
   <si>
     <t xml:space="preserve">3.79345273971558</t>
   </si>
   <si>
-    <t xml:space="preserve">3.86478996276855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.87737822532654</t>
+    <t xml:space="preserve">3.8647894859314</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.8773787021637</t>
   </si>
   <si>
     <t xml:space="preserve">3.73470425605774</t>
   </si>
   <si>
-    <t xml:space="preserve">3.84380793571472</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.69274187088013</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.90255618095398</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.95291209220886</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.9906792640686</t>
+    <t xml:space="preserve">3.84380865097046</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.69274139404297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.90255665779114</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.95291185379028</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.99067902565002</t>
   </si>
   <si>
     <t xml:space="preserve">4.00326776504517</t>
   </si>
   <si>
-    <t xml:space="preserve">3.91514539718628</t>
+    <t xml:space="preserve">3.91514587402344</t>
   </si>
   <si>
     <t xml:space="preserve">3.87318229675293</t>
   </si>
   <si>
-    <t xml:space="preserve">3.85220098495483</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.66756391525269</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.67595672607422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.59203100204468</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.53328227996826</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.70533037185669</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.6423864364624</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.77666735649109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.71791934967041</t>
+    <t xml:space="preserve">3.85220074653625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.66756367683411</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.67595624923706</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.59203052520752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.53328251838684</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.70533061027527</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.64238595962524</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.77666783332825</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.71791911125183</t>
   </si>
   <si>
     <t xml:space="preserve">3.64658212661743</t>
@@ -1454,55 +1454,55 @@
     <t xml:space="preserve">3.70113444328308</t>
   </si>
   <si>
-    <t xml:space="preserve">3.68015289306641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.80604147911072</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.78506016731262</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.69693779945374</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.73050832748413</t>
+    <t xml:space="preserve">3.68015265464783</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.80604195594788</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.7850604057312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.69693851470947</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.73050856590271</t>
   </si>
   <si>
     <t xml:space="preserve">3.7472939491272</t>
   </si>
   <si>
-    <t xml:space="preserve">3.65077805519104</t>
+    <t xml:space="preserve">3.65077900886536</t>
   </si>
   <si>
     <t xml:space="preserve">3.65917158126831</t>
   </si>
   <si>
-    <t xml:space="preserve">3.8563973903656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.8941638469696</t>
+    <t xml:space="preserve">3.85639715194702</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.89416408538818</t>
   </si>
   <si>
     <t xml:space="preserve">3.93612694740295</t>
   </si>
   <si>
-    <t xml:space="preserve">4.0074634552002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.08719348907471</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.11237144470215</t>
+    <t xml:space="preserve">4.00746393203735</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.08719396591187</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.11237096786499</t>
   </si>
   <si>
     <t xml:space="preserve">4.17111921310425</t>
   </si>
   <si>
-    <t xml:space="preserve">4.19629716873169</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.23825979232788</t>
+    <t xml:space="preserve">4.19629764556885</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.2382607460022</t>
   </si>
   <si>
     <t xml:space="preserve">4.18790483474731</t>
@@ -1511,10 +1511,10 @@
     <t xml:space="preserve">4.09978246688843</t>
   </si>
   <si>
-    <t xml:space="preserve">4.09558629989624</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.07880115509033</t>
+    <t xml:space="preserve">4.0955867767334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.07880067825317</t>
   </si>
   <si>
     <t xml:space="preserve">4.14594173431396</t>
@@ -1526,7 +1526,7 @@
     <t xml:space="preserve">4.08299732208252</t>
   </si>
   <si>
-    <t xml:space="preserve">4.06201553344727</t>
+    <t xml:space="preserve">4.06201601028442</t>
   </si>
   <si>
     <t xml:space="preserve">4.26343774795532</t>
@@ -1535,37 +1535,37 @@
     <t xml:space="preserve">4.39771938323975</t>
   </si>
   <si>
-    <t xml:space="preserve">4.52360868453979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.49843120574951</t>
+    <t xml:space="preserve">4.52360820770264</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.4984302520752</t>
   </si>
   <si>
     <t xml:space="preserve">4.58235645294189</t>
   </si>
   <si>
-    <t xml:space="preserve">4.4816460609436</t>
+    <t xml:space="preserve">4.48164558410645</t>
   </si>
   <si>
     <t xml:space="preserve">4.62431955337524</t>
   </si>
   <si>
-    <t xml:space="preserve">4.67467594146729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.69985294342041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.6830677986145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.66628217697144</t>
+    <t xml:space="preserve">4.67467546463013</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.69985246658325</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.68306732177734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.66628265380859</t>
   </si>
   <si>
     <t xml:space="preserve">4.63271236419678</t>
   </si>
   <si>
-    <t xml:space="preserve">4.44807577133179</t>
+    <t xml:space="preserve">4.44807529449463</t>
   </si>
   <si>
     <t xml:space="preserve">4.4396824836731</t>
@@ -1574,10 +1574,10 @@
     <t xml:space="preserve">4.47325277328491</t>
   </si>
   <si>
-    <t xml:space="preserve">4.49003791809082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.54878664016724</t>
+    <t xml:space="preserve">4.49003839492798</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.54878568649292</t>
   </si>
   <si>
     <t xml:space="preserve">4.5991415977478</t>
@@ -1586,10 +1586,10 @@
     <t xml:space="preserve">4.61592721939087</t>
   </si>
   <si>
-    <t xml:space="preserve">4.60753440856934</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.40611219406128</t>
+    <t xml:space="preserve">4.60753393173218</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.40611171722412</t>
   </si>
   <si>
     <t xml:space="preserve">4.53200101852417</t>
@@ -1598,16 +1598,16 @@
     <t xml:space="preserve">4.75860118865967</t>
   </si>
   <si>
-    <t xml:space="preserve">4.80895662307739</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.74181604385376</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.69146013259888</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.65788984298706</t>
+    <t xml:space="preserve">4.80895709991455</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.7418155670166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.69146108627319</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.65789031982422</t>
   </si>
   <si>
     <t xml:space="preserve">4.50682306289673</t>
@@ -1622,16 +1622,16 @@
     <t xml:space="preserve">4.41450500488281</t>
   </si>
   <si>
-    <t xml:space="preserve">4.38932657241821</t>
+    <t xml:space="preserve">4.38932704925537</t>
   </si>
   <si>
     <t xml:space="preserve">4.38093423843384</t>
   </si>
   <si>
-    <t xml:space="preserve">4.34736442565918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.46764659881592</t>
+    <t xml:space="preserve">4.34736347198486</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.46764707565308</t>
   </si>
   <si>
     <t xml:space="preserve">4.51919651031494</t>
@@ -1640,16 +1640,16 @@
     <t xml:space="preserve">4.39891386032104</t>
   </si>
   <si>
-    <t xml:space="preserve">4.37313938140869</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.30440616607666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.27003860473633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.33018112182617</t>
+    <t xml:space="preserve">4.37313890457153</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.3044056892395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.27003955841064</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.33018064498901</t>
   </si>
   <si>
     <t xml:space="preserve">4.31299734115601</t>
@@ -1658,28 +1658,28 @@
     <t xml:space="preserve">4.38173055648804</t>
   </si>
   <si>
-    <t xml:space="preserve">4.44187259674072</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.45905542373657</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.35595607757568</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.39032173156738</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.45046377182007</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.41609716415405</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.23137760162354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.26574373245239</t>
+    <t xml:space="preserve">4.44187211990356</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.45905494689941</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.35595512390137</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.39032220840454</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.45046281814575</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.41609668731689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.23137664794922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.26574325561523</t>
   </si>
   <si>
     <t xml:space="preserve">4.13257312774658</t>
@@ -1688,22 +1688,22 @@
     <t xml:space="preserve">4.0466570854187</t>
   </si>
   <si>
-    <t xml:space="preserve">4.08531951904297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.98221945762634</t>
+    <t xml:space="preserve">4.08531904220581</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.9822199344635</t>
   </si>
   <si>
     <t xml:space="preserve">4.03376960754395</t>
   </si>
   <si>
-    <t xml:space="preserve">3.94785308837891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.99081182479858</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.98651528358459</t>
+    <t xml:space="preserve">3.94785332679749</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.99081110954285</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.98651599884033</t>
   </si>
   <si>
     <t xml:space="preserve">3.94355773925781</t>
@@ -1712,19 +1712,19 @@
     <t xml:space="preserve">3.96503615379333</t>
   </si>
   <si>
-    <t xml:space="preserve">3.9607412815094</t>
+    <t xml:space="preserve">3.9607400894165</t>
   </si>
   <si>
     <t xml:space="preserve">4.01229047775269</t>
   </si>
   <si>
-    <t xml:space="preserve">3.92637419700623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.07243156433105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.08961534500122</t>
+    <t xml:space="preserve">3.9263744354248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.07243204116821</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.08961486816406</t>
   </si>
   <si>
     <t xml:space="preserve">4.11109447479248</t>
@@ -1739,46 +1739,46 @@
     <t xml:space="preserve">4.295814037323</t>
   </si>
   <si>
-    <t xml:space="preserve">4.02947330474854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.84045767784119</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.87482476234436</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.88771176338196</t>
+    <t xml:space="preserve">4.02947378158569</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.84045720100403</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.87482452392578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.88771200180054</t>
   </si>
   <si>
     <t xml:space="preserve">4.00369882583618</t>
   </si>
   <si>
-    <t xml:space="preserve">4.02088117599487</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.93496584892273</t>
+    <t xml:space="preserve">4.02088165283203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.93496561050415</t>
   </si>
   <si>
     <t xml:space="preserve">3.86623287200928</t>
   </si>
   <si>
-    <t xml:space="preserve">3.77172493934631</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.71587944030762</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.70299172401428</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.67721724510193</t>
+    <t xml:space="preserve">3.77172446250916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.71587920188904</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.70299196243286</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.67721700668335</t>
   </si>
   <si>
     <t xml:space="preserve">3.68580842018127</t>
   </si>
   <si>
-    <t xml:space="preserve">3.70728731155396</t>
+    <t xml:space="preserve">3.70728754997253</t>
   </si>
   <si>
     <t xml:space="preserve">3.66432929039001</t>
@@ -1793,10 +1793,10 @@
     <t xml:space="preserve">3.81468319892883</t>
   </si>
   <si>
-    <t xml:space="preserve">3.95214939117432</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.85764122009277</t>
+    <t xml:space="preserve">3.95214891433716</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.85764098167419</t>
   </si>
   <si>
     <t xml:space="preserve">3.78461241722107</t>
@@ -1805,16 +1805,16 @@
     <t xml:space="preserve">3.84475326538086</t>
   </si>
   <si>
-    <t xml:space="preserve">3.7803168296814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.69440054893494</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.73306250572205</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.71158337593079</t>
+    <t xml:space="preserve">3.78031706809998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.69440031051636</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.73306226730347</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.71158385276794</t>
   </si>
   <si>
     <t xml:space="preserve">3.59989237785339</t>
@@ -1823,67 +1823,67 @@
     <t xml:space="preserve">3.75454163551331</t>
   </si>
   <si>
-    <t xml:space="preserve">3.65144181251526</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.72447061538696</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.78890824317932</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.64714646339417</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.66862535476685</t>
+    <t xml:space="preserve">3.65144205093384</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.72447109222412</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.78890800476074</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.64714598655701</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.66862559318542</t>
   </si>
   <si>
     <t xml:space="preserve">3.67292141914368</t>
   </si>
   <si>
-    <t xml:space="preserve">3.61707544326782</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.57411742210388</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.64285016059875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.65573763847351</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.62996292114258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.96933221817017</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.95644474029541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.90059924125671</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.93067026138306</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.0165867805481</t>
+    <t xml:space="preserve">3.6170756816864</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.5741171836853</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.64284992218018</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.65573835372925</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.629962682724</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.96933174133301</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.95644450187683</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.90059876441956</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.93067002296448</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.01658630371094</t>
   </si>
   <si>
     <t xml:space="preserve">4.09820652008057</t>
   </si>
   <si>
-    <t xml:space="preserve">4.14116477966309</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.24426460266113</t>
+    <t xml:space="preserve">4.14116525650024</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.24426412582397</t>
   </si>
   <si>
     <t xml:space="preserve">4.24856042861938</t>
   </si>
   <si>
-    <t xml:space="preserve">4.4332799911499</t>
+    <t xml:space="preserve">4.43328046798706</t>
   </si>
   <si>
     <t xml:space="preserve">4.4246883392334</t>
@@ -1901,16 +1901,16 @@
     <t xml:space="preserve">4.55356311798096</t>
   </si>
   <si>
-    <t xml:space="preserve">4.48482990264893</t>
+    <t xml:space="preserve">4.48482942581177</t>
   </si>
   <si>
     <t xml:space="preserve">4.53638029098511</t>
   </si>
   <si>
-    <t xml:space="preserve">4.59652090072632</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.77694463729858</t>
+    <t xml:space="preserve">4.59652137756348</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.7769455909729</t>
   </si>
   <si>
     <t xml:space="preserve">4.81131172180176</t>
@@ -1919,55 +1919,55 @@
     <t xml:space="preserve">4.69962072372437</t>
   </si>
   <si>
-    <t xml:space="preserve">4.64807033538818</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.72539615631104</t>
+    <t xml:space="preserve">4.64807081222534</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.72539520263672</t>
   </si>
   <si>
     <t xml:space="preserve">4.71680402755737</t>
   </si>
   <si>
-    <t xml:space="preserve">4.6910285949707</t>
+    <t xml:space="preserve">4.69102907180786</t>
   </si>
   <si>
     <t xml:space="preserve">4.68243741989136</t>
   </si>
   <si>
-    <t xml:space="preserve">4.70821142196655</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.67384576797485</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.56215476989746</t>
+    <t xml:space="preserve">4.70821285247803</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.67384624481201</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.5621542930603</t>
   </si>
   <si>
     <t xml:space="preserve">4.50201320648193</t>
   </si>
   <si>
-    <t xml:space="preserve">4.54497194290161</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.51060485839844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.5277886390686</t>
+    <t xml:space="preserve">4.54497146606445</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.51060438156128</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.52778816223145</t>
   </si>
   <si>
     <t xml:space="preserve">4.7683539390564</t>
   </si>
   <si>
-    <t xml:space="preserve">4.66525363922119</t>
+    <t xml:space="preserve">4.66525459289551</t>
   </si>
   <si>
     <t xml:space="preserve">4.61370420455933</t>
   </si>
   <si>
-    <t xml:space="preserve">4.73398685455322</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.63947916030884</t>
+    <t xml:space="preserve">4.73398733139038</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.639479637146</t>
   </si>
   <si>
     <t xml:space="preserve">4.23567247390747</t>
@@ -1982,31 +1982,31 @@
     <t xml:space="preserve">4.36454677581787</t>
   </si>
   <si>
-    <t xml:space="preserve">4.60511255264282</t>
+    <t xml:space="preserve">4.60511302947998</t>
   </si>
   <si>
     <t xml:space="preserve">4.11538982391357</t>
   </si>
   <si>
-    <t xml:space="preserve">3.75024509429932</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.47101783752441</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.36362242698669</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.31207299232483</t>
+    <t xml:space="preserve">3.7502453327179</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.47101759910583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.36362266540527</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.31207251548767</t>
   </si>
   <si>
     <t xml:space="preserve">3.16601490974426</t>
   </si>
   <si>
-    <t xml:space="preserve">3.22186040878296</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.80516672134399</t>
+    <t xml:space="preserve">3.22186064720154</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.80516624450684</t>
   </si>
   <si>
     <t xml:space="preserve">2.91685771942139</t>
@@ -2024,25 +2024,25 @@
     <t xml:space="preserve">2.66770052909851</t>
   </si>
   <si>
-    <t xml:space="preserve">2.80087089538574</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.61185503005981</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.72354626655579</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.92115330696106</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.81375861167908</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.70206689834595</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.65910887718201</t>
+    <t xml:space="preserve">2.80087113380432</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.61185479164124</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.72354602813721</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.92115378379822</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.8137583732605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.70206713676453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.65910935401917</t>
   </si>
   <si>
     <t xml:space="preserve">2.84382891654968</t>
@@ -2051,10 +2051,10 @@
     <t xml:space="preserve">2.76650452613831</t>
   </si>
   <si>
-    <t xml:space="preserve">2.78798341751099</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.70636320114136</t>
+    <t xml:space="preserve">2.78798317909241</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.7063627243042</t>
   </si>
   <si>
     <t xml:space="preserve">2.71065878868103</t>
@@ -2063,31 +2063,31 @@
     <t xml:space="preserve">2.85242056846619</t>
   </si>
   <si>
-    <t xml:space="preserve">2.89108300209045</t>
+    <t xml:space="preserve">2.89108276367188</t>
   </si>
   <si>
     <t xml:space="preserve">2.92974519729614</t>
   </si>
   <si>
-    <t xml:space="preserve">3.00707006454468</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.96411156654358</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.93833684921265</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.9426326751709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.98129487037659</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.01136589050293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.94692850112915</t>
+    <t xml:space="preserve">3.00706958770752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.96411204338074</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.93833708763123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.94263243675232</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.98129510879517</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.01136565208435</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.94692826271057</t>
   </si>
   <si>
     <t xml:space="preserve">2.97699904441833</t>
@@ -2102,34 +2102,34 @@
     <t xml:space="preserve">3.04143643379211</t>
   </si>
   <si>
-    <t xml:space="preserve">3.05002808570862</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.08439445495605</t>
+    <t xml:space="preserve">3.05002784729004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.08439469337463</t>
   </si>
   <si>
     <t xml:space="preserve">3.13164854049683</t>
   </si>
   <si>
-    <t xml:space="preserve">3.03284478187561</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.09298634529114</t>
+    <t xml:space="preserve">3.03284502029419</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.09298610687256</t>
   </si>
   <si>
     <t xml:space="preserve">3.19179010391235</t>
   </si>
   <si>
-    <t xml:space="preserve">3.24763560295105</t>
+    <t xml:space="preserve">3.24763536453247</t>
   </si>
   <si>
     <t xml:space="preserve">3.16171956062317</t>
   </si>
   <si>
-    <t xml:space="preserve">3.14883184432983</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.18319821357727</t>
+    <t xml:space="preserve">3.14883160591125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.18319845199585</t>
   </si>
   <si>
     <t xml:space="preserve">3.13594436645508</t>
@@ -2141,16 +2141,16 @@
     <t xml:space="preserve">3.30777668952942</t>
   </si>
   <si>
-    <t xml:space="preserve">3.38510155677795</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.43665146827698</t>
+    <t xml:space="preserve">3.38510179519653</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.4366512298584</t>
   </si>
   <si>
     <t xml:space="preserve">3.48390531539917</t>
   </si>
   <si>
-    <t xml:space="preserve">3.46242642402649</t>
+    <t xml:space="preserve">3.46242666244507</t>
   </si>
   <si>
     <t xml:space="preserve">3.4796097278595</t>
@@ -2159,19 +2159,19 @@
     <t xml:space="preserve">3.31636834144592</t>
   </si>
   <si>
-    <t xml:space="preserve">3.29488945007324</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.19608592987061</t>
+    <t xml:space="preserve">3.29488968849182</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.19608569145203</t>
   </si>
   <si>
     <t xml:space="preserve">3.38080596923828</t>
   </si>
   <si>
-    <t xml:space="preserve">3.37650990486145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.35073494911194</t>
+    <t xml:space="preserve">3.37651014328003</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.35073518753052</t>
   </si>
   <si>
     <t xml:space="preserve">3.37221384048462</t>
@@ -2180,10 +2180,10 @@
     <t xml:space="preserve">3.42805981636047</t>
   </si>
   <si>
-    <t xml:space="preserve">3.44094729423523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.44524312019348</t>
+    <t xml:space="preserve">3.44094705581665</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.44524335861206</t>
   </si>
   <si>
     <t xml:space="preserve">3.75857472419739</t>
@@ -2192,43 +2192,43 @@
     <t xml:space="preserve">3.71435594558716</t>
   </si>
   <si>
-    <t xml:space="preserve">3.63034081459045</t>
+    <t xml:space="preserve">3.63034129142761</t>
   </si>
   <si>
     <t xml:space="preserve">3.58170080184937</t>
   </si>
   <si>
-    <t xml:space="preserve">3.51979470252991</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.50210738182068</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.43135762214661</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.44904541969299</t>
+    <t xml:space="preserve">3.51979494094849</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.5021071434021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.43135786056519</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.44904518127441</t>
   </si>
   <si>
     <t xml:space="preserve">3.36060786247253</t>
   </si>
   <si>
-    <t xml:space="preserve">3.38713908195496</t>
+    <t xml:space="preserve">3.38713884353638</t>
   </si>
   <si>
     <t xml:space="preserve">3.4180920124054</t>
   </si>
   <si>
-    <t xml:space="preserve">3.32081174850464</t>
+    <t xml:space="preserve">3.32081127166748</t>
   </si>
   <si>
     <t xml:space="preserve">3.33849883079529</t>
   </si>
   <si>
-    <t xml:space="preserve">3.31638932228088</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.27217102050781</t>
+    <t xml:space="preserve">3.31638956069946</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.27217125892639</t>
   </si>
   <si>
     <t xml:space="preserve">3.28101468086243</t>
@@ -2240,16 +2240,16 @@
     <t xml:space="preserve">3.09529662132263</t>
   </si>
   <si>
-    <t xml:space="preserve">3.18373370170593</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.25448369979858</t>
+    <t xml:space="preserve">3.18373394012451</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.25448346138</t>
   </si>
   <si>
     <t xml:space="preserve">3.20584321022034</t>
   </si>
   <si>
-    <t xml:space="preserve">3.1660463809967</t>
+    <t xml:space="preserve">3.16604661941528</t>
   </si>
   <si>
     <t xml:space="preserve">3.15720272064209</t>
@@ -2258,16 +2258,16 @@
     <t xml:space="preserve">3.13951516151428</t>
   </si>
   <si>
-    <t xml:space="preserve">3.10414052009583</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.09971904754639</t>
+    <t xml:space="preserve">3.10414028167725</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.09971880912781</t>
   </si>
   <si>
     <t xml:space="preserve">3.04223465919495</t>
   </si>
   <si>
-    <t xml:space="preserve">3.04665637016296</t>
+    <t xml:space="preserve">3.04665613174438</t>
   </si>
   <si>
     <t xml:space="preserve">3.07760953903198</t>
@@ -2276,10 +2276,10 @@
     <t xml:space="preserve">3.05992197990417</t>
   </si>
   <si>
-    <t xml:space="preserve">2.98032832145691</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.96264100074768</t>
+    <t xml:space="preserve">2.98032855987549</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.96264147758484</t>
   </si>
   <si>
     <t xml:space="preserve">2.94495368003845</t>
@@ -2288,76 +2288,76 @@
     <t xml:space="preserve">2.93611001968384</t>
   </si>
   <si>
-    <t xml:space="preserve">3.09087491035461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.06876564025879</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.05550026893616</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.98475050926208</t>
+    <t xml:space="preserve">3.09087514877319</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.06876587867737</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.05550003051758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.98475074768066</t>
   </si>
   <si>
     <t xml:space="preserve">2.9051570892334</t>
   </si>
   <si>
-    <t xml:space="preserve">2.83440732955933</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.86978220939636</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.80345463752747</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.77692365646362</t>
+    <t xml:space="preserve">2.83440756797791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.86978244781494</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.80345439910889</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.77692341804504</t>
   </si>
   <si>
     <t xml:space="preserve">2.81229829788208</t>
   </si>
   <si>
-    <t xml:space="preserve">2.84767317771912</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.82998609542847</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.79461073875427</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.91842293739319</t>
+    <t xml:space="preserve">2.84767270088196</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.82998561859131</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.79461097717285</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.91842269897461</t>
   </si>
   <si>
     <t xml:space="preserve">2.82114219665527</t>
   </si>
   <si>
-    <t xml:space="preserve">2.79903268814087</t>
+    <t xml:space="preserve">2.79903292655945</t>
   </si>
   <si>
     <t xml:space="preserve">2.80787634849548</t>
   </si>
   <si>
-    <t xml:space="preserve">2.75923585891724</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.7238609790802</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.71501755714417</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.68406462669373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.63542413711548</t>
+    <t xml:space="preserve">2.75923609733582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.72386121749878</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.71501779556274</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.68406438827515</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.63542437553406</t>
   </si>
   <si>
     <t xml:space="preserve">2.61773681640625</t>
   </si>
   <si>
-    <t xml:space="preserve">2.58236169815063</t>
+    <t xml:space="preserve">2.58236193656921</t>
   </si>
   <si>
     <t xml:space="preserve">2.54698705673218</t>
@@ -2369,22 +2369,22 @@
     <t xml:space="preserve">2.55140900611877</t>
   </si>
   <si>
-    <t xml:space="preserve">2.49392485618591</t>
+    <t xml:space="preserve">2.49392461776733</t>
   </si>
   <si>
     <t xml:space="preserve">2.5735182762146</t>
   </si>
   <si>
-    <t xml:space="preserve">2.97148466110229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.95379734039307</t>
+    <t xml:space="preserve">2.97148489952087</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.95379710197449</t>
   </si>
   <si>
     <t xml:space="preserve">3.00243782997131</t>
   </si>
   <si>
-    <t xml:space="preserve">3.17931222915649</t>
+    <t xml:space="preserve">3.17931199073792</t>
   </si>
   <si>
     <t xml:space="preserve">3.17046856880188</t>
@@ -2399,58 +2399,58 @@
     <t xml:space="preserve">3.29870223999023</t>
   </si>
   <si>
-    <t xml:space="preserve">3.47999787330627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.41367030143738</t>
+    <t xml:space="preserve">3.47999811172485</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.4136700630188</t>
   </si>
   <si>
     <t xml:space="preserve">3.48442006111145</t>
   </si>
   <si>
-    <t xml:space="preserve">3.45788908004761</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.49326372146606</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.51095104217529</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.44462323188782</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.42693567276001</t>
+    <t xml:space="preserve">3.45788884162903</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.49326348304749</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.51095080375671</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.44462299346924</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.42693591117859</t>
   </si>
   <si>
     <t xml:space="preserve">3.55516958236694</t>
   </si>
   <si>
-    <t xml:space="preserve">3.67898154258728</t>
+    <t xml:space="preserve">3.67898106575012</t>
   </si>
   <si>
     <t xml:space="preserve">3.72320008277893</t>
   </si>
   <si>
-    <t xml:space="preserve">3.74973058700562</t>
+    <t xml:space="preserve">3.74973082542419</t>
   </si>
   <si>
     <t xml:space="preserve">3.80279326438904</t>
   </si>
   <si>
-    <t xml:space="preserve">3.65687203407288</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.66129374504089</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.65245056152344</t>
+    <t xml:space="preserve">3.65687227249146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.66129398345947</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.65245032310486</t>
   </si>
   <si>
     <t xml:space="preserve">3.62591910362244</t>
   </si>
   <si>
-    <t xml:space="preserve">3.60823154449463</t>
+    <t xml:space="preserve">3.60823178291321</t>
   </si>
   <si>
     <t xml:space="preserve">3.54632592201233</t>
@@ -2459,7 +2459,7 @@
     <t xml:space="preserve">3.53748202323914</t>
   </si>
   <si>
-    <t xml:space="preserve">3.57285666465759</t>
+    <t xml:space="preserve">3.57285690307617</t>
   </si>
   <si>
     <t xml:space="preserve">3.5065290927887</t>
@@ -2471,7 +2471,7 @@
     <t xml:space="preserve">3.57727885246277</t>
   </si>
   <si>
-    <t xml:space="preserve">3.74530935287476</t>
+    <t xml:space="preserve">3.74530911445618</t>
   </si>
   <si>
     <t xml:space="preserve">3.74088764190674</t>
@@ -2483,13 +2483,13 @@
     <t xml:space="preserve">3.70551252365112</t>
   </si>
   <si>
-    <t xml:space="preserve">3.77626180648804</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.8381679058075</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.6834032535553</t>
+    <t xml:space="preserve">3.77626252174377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.83816814422607</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.68340301513672</t>
   </si>
   <si>
     <t xml:space="preserve">3.76741862297058</t>
@@ -2498,19 +2498,19 @@
     <t xml:space="preserve">3.78068399429321</t>
   </si>
   <si>
-    <t xml:space="preserve">3.76299643516541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.7718403339386</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.71877789497375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.68782496452332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.59938836097717</t>
+    <t xml:space="preserve">3.76299691200256</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.77184009552002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.71877813339233</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.68782520294189</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.59938812255859</t>
   </si>
   <si>
     <t xml:space="preserve">3.66571569442749</t>
@@ -2519,22 +2519,22 @@
     <t xml:space="preserve">3.70993447303772</t>
   </si>
   <si>
-    <t xml:space="preserve">3.78510618209839</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.9266049861908</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.93987059593201</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.99735474586487</t>
+    <t xml:space="preserve">3.78510642051697</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.92660522460938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.93987035751343</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.99735426902771</t>
   </si>
   <si>
     <t xml:space="preserve">4.01079893112183</t>
   </si>
   <si>
-    <t xml:space="preserve">4.09594440460205</t>
+    <t xml:space="preserve">4.09594392776489</t>
   </si>
   <si>
     <t xml:space="preserve">4.17212724685669</t>
@@ -2546,7 +2546,7 @@
     <t xml:space="preserve">4.13627576828003</t>
   </si>
   <si>
-    <t xml:space="preserve">4.19901514053345</t>
+    <t xml:space="preserve">4.19901466369629</t>
   </si>
   <si>
     <t xml:space="preserve">4.14075756072998</t>
@@ -2558,25 +2558,25 @@
     <t xml:space="preserve">4.06905603408813</t>
   </si>
   <si>
-    <t xml:space="preserve">4.03320503234863</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.97942924499512</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.028724193573</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.05561256408691</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.08698129653931</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.97494745254517</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.00183582305908</t>
+    <t xml:space="preserve">4.03320550918579</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.9794294834137</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.02872371673584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.05561208724976</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.08698177337646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.97494792938232</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.00183629989624</t>
   </si>
   <si>
     <t xml:space="preserve">4.01528024673462</t>
@@ -2585,19 +2585,19 @@
     <t xml:space="preserve">3.96150398254395</t>
   </si>
   <si>
-    <t xml:space="preserve">3.98839139938354</t>
+    <t xml:space="preserve">3.98839211463928</t>
   </si>
   <si>
     <t xml:space="preserve">3.95254135131836</t>
   </si>
   <si>
-    <t xml:space="preserve">3.9659857749939</t>
+    <t xml:space="preserve">3.96598529815674</t>
   </si>
   <si>
     <t xml:space="preserve">4.04216861724854</t>
   </si>
   <si>
-    <t xml:space="preserve">4.07801866531372</t>
+    <t xml:space="preserve">4.07801914215088</t>
   </si>
   <si>
     <t xml:space="preserve">4.11835050582886</t>
@@ -2609,7 +2609,7 @@
     <t xml:space="preserve">4.11386966705322</t>
   </si>
   <si>
-    <t xml:space="preserve">4.10938835144043</t>
+    <t xml:space="preserve">4.10938787460327</t>
   </si>
   <si>
     <t xml:space="preserve">4.06009340286255</t>
@@ -2627,16 +2627,16 @@
     <t xml:space="preserve">4.12283182144165</t>
   </si>
   <si>
-    <t xml:space="preserve">4.03768682479858</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.01976108551025</t>
+    <t xml:space="preserve">4.03768634796143</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.01976156234741</t>
   </si>
   <si>
     <t xml:space="preserve">4.06457471847534</t>
   </si>
   <si>
-    <t xml:space="preserve">4.20797777175903</t>
+    <t xml:space="preserve">4.20797729492188</t>
   </si>
   <si>
     <t xml:space="preserve">4.230384349823</t>
@@ -2648,10 +2648,10 @@
     <t xml:space="preserve">4.20349645614624</t>
   </si>
   <si>
-    <t xml:space="preserve">3.9256534576416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.90772819519043</t>
+    <t xml:space="preserve">3.92565321922302</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.90772795677185</t>
   </si>
   <si>
     <t xml:space="preserve">3.88083982467651</t>
@@ -2660,34 +2660,34 @@
     <t xml:space="preserve">3.87635850906372</t>
   </si>
   <si>
-    <t xml:space="preserve">3.80913829803467</t>
+    <t xml:space="preserve">3.80913853645325</t>
   </si>
   <si>
     <t xml:space="preserve">3.71503019332886</t>
   </si>
   <si>
-    <t xml:space="preserve">3.66573548316956</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.83154511451721</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.93461561203003</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.99735498428345</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.94357824325562</t>
+    <t xml:space="preserve">3.66573596000671</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.83154487609863</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.93461537361145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.99735522270203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.94357872009277</t>
   </si>
   <si>
     <t xml:space="preserve">4.04664897918701</t>
   </si>
   <si>
-    <t xml:space="preserve">3.9928731918335</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.98391103744507</t>
+    <t xml:space="preserve">3.99287295341492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.98391079902649</t>
   </si>
   <si>
     <t xml:space="preserve">4.02424240112305</t>
@@ -2696,31 +2696,31 @@
     <t xml:space="preserve">3.85395193099976</t>
   </si>
   <si>
-    <t xml:space="preserve">3.93013429641724</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.97046709060669</t>
+    <t xml:space="preserve">3.93013501167297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.97046661376953</t>
   </si>
   <si>
     <t xml:space="preserve">4.10042572021484</t>
   </si>
   <si>
-    <t xml:space="preserve">4.15420198440552</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.0914626121521</t>
+    <t xml:space="preserve">4.15420150756836</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.09146308898926</t>
   </si>
   <si>
     <t xml:space="preserve">4.22590303421021</t>
   </si>
   <si>
-    <t xml:space="preserve">4.2662353515625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.24382877349854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.13179492950439</t>
+    <t xml:space="preserve">4.26623487472534</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.24382829666138</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.13179445266724</t>
   </si>
   <si>
     <t xml:space="preserve">4.1273136138916</t>
@@ -2735,13 +2735,13 @@
     <t xml:space="preserve">4.29312324523926</t>
   </si>
   <si>
-    <t xml:space="preserve">4.40515661239624</t>
+    <t xml:space="preserve">4.40515613555908</t>
   </si>
   <si>
     <t xml:space="preserve">4.43652582168579</t>
   </si>
   <si>
-    <t xml:space="preserve">4.48133945465088</t>
+    <t xml:space="preserve">4.48133897781372</t>
   </si>
   <si>
     <t xml:space="preserve">4.53511571884155</t>
@@ -2750,7 +2750,7 @@
     <t xml:space="preserve">4.55304050445557</t>
   </si>
   <si>
-    <t xml:space="preserve">4.56200408935547</t>
+    <t xml:space="preserve">4.56200361251831</t>
   </si>
   <si>
     <t xml:space="preserve">4.50822734832764</t>
@@ -2762,16 +2762,16 @@
     <t xml:space="preserve">4.43204498291016</t>
   </si>
   <si>
-    <t xml:space="preserve">4.49926471710205</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.49030256271362</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.51719045639038</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.63370513916016</t>
+    <t xml:space="preserve">4.49926424026489</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.49030208587646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.51718997955322</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.633704662323</t>
   </si>
   <si>
     <t xml:space="preserve">4.59785413742065</t>
@@ -2780,25 +2780,25 @@
     <t xml:space="preserve">4.47685813903809</t>
   </si>
   <si>
-    <t xml:space="preserve">4.5709662437439</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.61577987670898</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.64266729354858</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.3917121887207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.44996976852417</t>
+    <t xml:space="preserve">4.57096576690674</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.61577939987183</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.64266681671143</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.39171266555786</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.44997024536133</t>
   </si>
   <si>
     <t xml:space="preserve">4.27519750595093</t>
   </si>
   <si>
-    <t xml:space="preserve">4.58889150619507</t>
+    <t xml:space="preserve">4.58889198303223</t>
   </si>
   <si>
     <t xml:space="preserve">4.66059303283691</t>
@@ -2807,7 +2807,7 @@
     <t xml:space="preserve">4.65163040161133</t>
   </si>
   <si>
-    <t xml:space="preserve">4.71436929702759</t>
+    <t xml:space="preserve">4.71436882019043</t>
   </si>
   <si>
     <t xml:space="preserve">4.75918245315552</t>
@@ -2819,16 +2819,16 @@
     <t xml:space="preserve">4.89362287521362</t>
   </si>
   <si>
-    <t xml:space="preserve">4.92051076889038</t>
+    <t xml:space="preserve">4.92051029205322</t>
   </si>
   <si>
     <t xml:space="preserve">4.88465976715088</t>
   </si>
   <si>
-    <t xml:space="preserve">5.05495071411133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.01910018920898</t>
+    <t xml:space="preserve">5.05495023727417</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.01909971237183</t>
   </si>
   <si>
     <t xml:space="preserve">5.14457702636719</t>
@@ -2837,37 +2837,37 @@
     <t xml:space="preserve">5.31486845016479</t>
   </si>
   <si>
-    <t xml:space="preserve">5.3776068687439</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.35968208312988</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.16250276565552</t>
+    <t xml:space="preserve">5.37760734558105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.35968160629272</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.16250324249268</t>
   </si>
   <si>
     <t xml:space="preserve">5.04598808288574</t>
   </si>
   <si>
-    <t xml:space="preserve">5.15354013442993</t>
+    <t xml:space="preserve">5.15354061126709</t>
   </si>
   <si>
     <t xml:space="preserve">5.26109218597412</t>
   </si>
   <si>
-    <t xml:space="preserve">5.27901697158813</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.512047290802</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.4761962890625</t>
+    <t xml:space="preserve">5.27901744842529</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.51204776763916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.47619676589966</t>
   </si>
   <si>
     <t xml:space="preserve">5.50308465957642</t>
   </si>
   <si>
-    <t xml:space="preserve">5.29694271087646</t>
+    <t xml:space="preserve">5.29694366455078</t>
   </si>
   <si>
     <t xml:space="preserve">5.19835376739502</t>
@@ -2876,28 +2876,28 @@
     <t xml:space="preserve">5.18042802810669</t>
   </si>
   <si>
-    <t xml:space="preserve">5.0728759765625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.09080123901367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.99221277236938</t>
+    <t xml:space="preserve">5.07287549972534</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.09080171585083</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.99221181869507</t>
   </si>
   <si>
     <t xml:space="preserve">4.75022029876709</t>
   </si>
   <si>
-    <t xml:space="preserve">4.80399608612061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.92947340011597</t>
+    <t xml:space="preserve">4.80399560928345</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.92947292327881</t>
   </si>
   <si>
     <t xml:space="preserve">4.83984661102295</t>
   </si>
   <si>
-    <t xml:space="preserve">4.97428703308105</t>
+    <t xml:space="preserve">4.9742865562439</t>
   </si>
   <si>
     <t xml:space="preserve">4.90258502960205</t>
@@ -2906,10 +2906,10 @@
     <t xml:space="preserve">4.86673450469971</t>
   </si>
   <si>
-    <t xml:space="preserve">5.03702592849731</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.95636129379272</t>
+    <t xml:space="preserve">5.03702545166016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.95636177062988</t>
   </si>
   <si>
     <t xml:space="preserve">4.79503345489502</t>
@@ -2918,22 +2918,22 @@
     <t xml:space="preserve">4.74125719070435</t>
   </si>
   <si>
-    <t xml:space="preserve">4.705406665802</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.52615308761597</t>
+    <t xml:space="preserve">4.70540618896484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.52615261077881</t>
   </si>
   <si>
     <t xml:space="preserve">4.41860055923462</t>
   </si>
   <si>
-    <t xml:space="preserve">4.36482429504395</t>
+    <t xml:space="preserve">4.3648247718811</t>
   </si>
   <si>
     <t xml:space="preserve">4.23934698104858</t>
   </si>
   <si>
-    <t xml:space="preserve">4.85777187347412</t>
+    <t xml:space="preserve">4.85777139663696</t>
   </si>
   <si>
     <t xml:space="preserve">4.91154813766479</t>
@@ -2954,19 +2954,19 @@
     <t xml:space="preserve">5.42242050170898</t>
   </si>
   <si>
-    <t xml:space="preserve">5.28798007965088</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.43138313293457</t>
+    <t xml:space="preserve">5.28798055648804</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.43138265609741</t>
   </si>
   <si>
     <t xml:space="preserve">5.55686044692993</t>
   </si>
   <si>
-    <t xml:space="preserve">5.62856245040894</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.52100944519043</t>
+    <t xml:space="preserve">5.62856197357178</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.52100992202759</t>
   </si>
   <si>
     <t xml:space="preserve">5.61959934234619</t>
@@ -2984,10 +2984,10 @@
     <t xml:space="preserve">5.46581411361694</t>
   </si>
   <si>
-    <t xml:space="preserve">5.48409461975098</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.63947677612305</t>
+    <t xml:space="preserve">5.48409414291382</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.63947725296021</t>
   </si>
   <si>
     <t xml:space="preserve">5.75829935073853</t>
@@ -3005,28 +3005,28 @@
     <t xml:space="preserve">5.410973072052</t>
   </si>
   <si>
-    <t xml:space="preserve">5.40183258056641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.63033676147461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.61205625534058</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.82227993011475</t>
+    <t xml:space="preserve">5.40183305740356</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.63033628463745</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.61205673217773</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.8222804069519</t>
   </si>
   <si>
     <t xml:space="preserve">5.84056043624878</t>
   </si>
   <si>
-    <t xml:space="preserve">5.88626098632812</t>
+    <t xml:space="preserve">5.88626146316528</t>
   </si>
   <si>
     <t xml:space="preserve">5.93196201324463</t>
   </si>
   <si>
-    <t xml:space="preserve">5.90454149246216</t>
+    <t xml:space="preserve">5.90454196929932</t>
   </si>
   <si>
     <t xml:space="preserve">5.97766304016113</t>
@@ -3035,7 +3035,7 @@
     <t xml:space="preserve">5.9593825340271</t>
   </si>
   <si>
-    <t xml:space="preserve">6.04164409637451</t>
+    <t xml:space="preserve">6.04164361953735</t>
   </si>
   <si>
     <t xml:space="preserve">5.87712097167969</t>
@@ -3044,10 +3044,10 @@
     <t xml:space="preserve">6.07820463180542</t>
   </si>
   <si>
-    <t xml:space="preserve">5.91368103027344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.68517732620239</t>
+    <t xml:space="preserve">5.91368198394775</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.68517780303955</t>
   </si>
   <si>
     <t xml:space="preserve">5.785719871521</t>
@@ -3056,16 +3056,16 @@
     <t xml:space="preserve">5.7308783531189</t>
   </si>
   <si>
-    <t xml:space="preserve">5.67603731155396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.69431781768799</t>
+    <t xml:space="preserve">5.67603778839111</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.69431829452515</t>
   </si>
   <si>
     <t xml:space="preserve">5.66689729690552</t>
   </si>
   <si>
-    <t xml:space="preserve">5.42925310134888</t>
+    <t xml:space="preserve">5.42925357818604</t>
   </si>
   <si>
     <t xml:space="preserve">5.42011308670044</t>
@@ -3074,7 +3074,7 @@
     <t xml:space="preserve">5.33785200119019</t>
   </si>
   <si>
-    <t xml:space="preserve">5.20988941192627</t>
+    <t xml:space="preserve">5.20988988876343</t>
   </si>
   <si>
     <t xml:space="preserve">5.34699201583862</t>
@@ -3086,7 +3086,7 @@
     <t xml:space="preserve">5.39269304275513</t>
   </si>
   <si>
-    <t xml:space="preserve">5.36527252197266</t>
+    <t xml:space="preserve">5.3652720451355</t>
   </si>
   <si>
     <t xml:space="preserve">5.2830114364624</t>
@@ -3098,43 +3098,43 @@
     <t xml:space="preserve">5.21902942657471</t>
   </si>
   <si>
-    <t xml:space="preserve">5.15504837036133</t>
+    <t xml:space="preserve">5.15504884719849</t>
   </si>
   <si>
     <t xml:space="preserve">5.10020780563354</t>
   </si>
   <si>
-    <t xml:space="preserve">5.10934782028198</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.08192729949951</t>
+    <t xml:space="preserve">5.10934829711914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.08192777633667</t>
   </si>
   <si>
     <t xml:space="preserve">5.03622674942017</t>
   </si>
   <si>
-    <t xml:space="preserve">5.01794624328613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.11848831176758</t>
+    <t xml:space="preserve">5.01794576644897</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.11848783493042</t>
   </si>
   <si>
     <t xml:space="preserve">5.13676834106445</t>
   </si>
   <si>
-    <t xml:space="preserve">5.07278776168823</t>
+    <t xml:space="preserve">5.07278728485107</t>
   </si>
   <si>
     <t xml:space="preserve">5.02708625793457</t>
   </si>
   <si>
-    <t xml:space="preserve">5.04536724090576</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.99052572250366</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.00880575180054</t>
+    <t xml:space="preserve">5.0453667640686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.99052619934082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.00880670547485</t>
   </si>
   <si>
     <t xml:space="preserve">5.0545072555542</t>
@@ -3146,7 +3146,7 @@
     <t xml:space="preserve">5.16418886184692</t>
   </si>
   <si>
-    <t xml:space="preserve">5.14590883255005</t>
+    <t xml:space="preserve">5.14590835571289</t>
   </si>
   <si>
     <t xml:space="preserve">4.94482469558716</t>
@@ -3155,16 +3155,16 @@
     <t xml:space="preserve">4.93568515777588</t>
   </si>
   <si>
-    <t xml:space="preserve">4.89912414550781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.8808445930481</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.85342359542847</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.82600355148315</t>
+    <t xml:space="preserve">4.89912462234497</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.88084411621094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.85342311859131</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.826003074646</t>
   </si>
   <si>
     <t xml:space="preserve">4.73460102081299</t>
@@ -3191,16 +3191,16 @@
     <t xml:space="preserve">4.80772304534912</t>
   </si>
   <si>
-    <t xml:space="preserve">4.57007837295532</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.72546148300171</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.68890047073364</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.67062044143677</t>
+    <t xml:space="preserve">4.57007884979248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.72546100616455</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.6889009475708</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.67062091827393</t>
   </si>
   <si>
     <t xml:space="preserve">4.6431999206543</t>
@@ -3212,16 +3212,16 @@
     <t xml:space="preserve">4.56093835830688</t>
   </si>
   <si>
-    <t xml:space="preserve">4.58835935592651</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.55179786682129</t>
+    <t xml:space="preserve">4.58835887908936</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.55179834365845</t>
   </si>
   <si>
     <t xml:space="preserve">4.48781728744507</t>
   </si>
   <si>
-    <t xml:space="preserve">4.53808784484863</t>
+    <t xml:space="preserve">4.53808832168579</t>
   </si>
   <si>
     <t xml:space="preserve">4.46953678131104</t>
@@ -3230,10 +3230,10 @@
     <t xml:space="preserve">4.50152778625488</t>
   </si>
   <si>
-    <t xml:space="preserve">4.49695730209351</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.40555620193481</t>
+    <t xml:space="preserve">4.49695777893066</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.40555572509766</t>
   </si>
   <si>
     <t xml:space="preserve">4.43297624588013</t>
@@ -3245,7 +3245,7 @@
     <t xml:space="preserve">4.36899518966675</t>
   </si>
   <si>
-    <t xml:space="preserve">4.29130411148071</t>
+    <t xml:space="preserve">4.29130363464355</t>
   </si>
   <si>
     <t xml:space="preserve">4.20447206497192</t>
@@ -3263,7 +3263,7 @@
     <t xml:space="preserve">4.87170362472534</t>
   </si>
   <si>
-    <t xml:space="preserve">4.83514356613159</t>
+    <t xml:space="preserve">4.83514308929443</t>
   </si>
   <si>
     <t xml:space="preserve">5.17332887649536</t>
@@ -3272,10 +3272,10 @@
     <t xml:space="preserve">5.32871150970459</t>
   </si>
   <si>
-    <t xml:space="preserve">5.19160890579224</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.25559091567993</t>
+    <t xml:space="preserve">5.19160938262939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.25559043884277</t>
   </si>
   <si>
     <t xml:space="preserve">5.38355255126953</t>
@@ -3299,10 +3299,10 @@
     <t xml:space="preserve">5.09106779098511</t>
   </si>
   <si>
-    <t xml:space="preserve">4.98138523101807</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.92654466629028</t>
+    <t xml:space="preserve">4.98138570785522</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.92654418945312</t>
   </si>
   <si>
     <t xml:space="preserve">5.06364727020264</t>
@@ -3311,7 +3311,7 @@
     <t xml:space="preserve">5.30129146575928</t>
   </si>
   <si>
-    <t xml:space="preserve">5.20074939727783</t>
+    <t xml:space="preserve">5.20074987411499</t>
   </si>
   <si>
     <t xml:space="preserve">5.12762832641602</t>
@@ -3323,10 +3323,10 @@
     <t xml:space="preserve">5.27387094497681</t>
   </si>
   <si>
-    <t xml:space="preserve">5.31957197189331</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.27241230010986</t>
+    <t xml:space="preserve">5.31957149505615</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.27241277694702</t>
   </si>
   <si>
     <t xml:space="preserve">5.23468494415283</t>
@@ -3338,13 +3338,13 @@
     <t xml:space="preserve">5.02718353271484</t>
   </si>
   <si>
-    <t xml:space="preserve">4.99888801574707</t>
+    <t xml:space="preserve">4.99888849258423</t>
   </si>
   <si>
     <t xml:space="preserve">5.01775217056274</t>
   </si>
   <si>
-    <t xml:space="preserve">5.16866159439087</t>
+    <t xml:space="preserve">5.16866207122803</t>
   </si>
   <si>
     <t xml:space="preserve">5.1403660774231</t>
@@ -3374,10 +3374,10 @@
     <t xml:space="preserve">5.26298046112061</t>
   </si>
   <si>
-    <t xml:space="preserve">5.3761625289917</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.17809343338013</t>
+    <t xml:space="preserve">5.37616300582886</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.17809295654297</t>
   </si>
   <si>
     <t xml:space="preserve">5.21582126617432</t>
@@ -3386,7 +3386,7 @@
     <t xml:space="preserve">5.10263824462891</t>
   </si>
   <si>
-    <t xml:space="preserve">5.14979791641235</t>
+    <t xml:space="preserve">5.14979839324951</t>
   </si>
   <si>
     <t xml:space="preserve">5.09320688247681</t>
@@ -3401,7 +3401,7 @@
     <t xml:space="preserve">5.03661584854126</t>
   </si>
   <si>
-    <t xml:space="preserve">5.06491088867188</t>
+    <t xml:space="preserve">5.06491136550903</t>
   </si>
   <si>
     <t xml:space="preserve">4.95172882080078</t>
@@ -3416,7 +3416,7 @@
     <t xml:space="preserve">4.91400146484375</t>
   </si>
   <si>
-    <t xml:space="preserve">4.90456962585449</t>
+    <t xml:space="preserve">4.90456914901733</t>
   </si>
   <si>
     <t xml:space="preserve">4.77252340316772</t>
@@ -3428,16 +3428,16 @@
     <t xml:space="preserve">4.72536420822144</t>
   </si>
   <si>
-    <t xml:space="preserve">4.96116065979004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.85740995407104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.80081939697266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.51786279678345</t>
+    <t xml:space="preserve">4.9611611366272</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.8574104309082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.8008189201355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.51786327362061</t>
   </si>
   <si>
     <t xml:space="preserve">4.50843143463135</t>
@@ -3449,7 +3449,7 @@
     <t xml:space="preserve">4.54615879058838</t>
   </si>
   <si>
-    <t xml:space="preserve">4.62161350250244</t>
+    <t xml:space="preserve">4.6216139793396</t>
   </si>
   <si>
     <t xml:space="preserve">4.54144287109375</t>
@@ -3464,7 +3464,7 @@
     <t xml:space="preserve">4.56030654907227</t>
   </si>
   <si>
-    <t xml:space="preserve">4.47541999816895</t>
+    <t xml:space="preserve">4.47541952133179</t>
   </si>
   <si>
     <t xml:space="preserve">4.47070360183716</t>
@@ -3482,7 +3482,7 @@
     <t xml:space="preserve">4.50371503829956</t>
   </si>
   <si>
-    <t xml:space="preserve">4.51314735412598</t>
+    <t xml:space="preserve">4.51314687728882</t>
   </si>
   <si>
     <t xml:space="preserve">4.63576126098633</t>
@@ -3491,13 +3491,13 @@
     <t xml:space="preserve">4.65934085845947</t>
   </si>
   <si>
-    <t xml:space="preserve">4.62632989883423</t>
+    <t xml:space="preserve">4.62632942199707</t>
   </si>
   <si>
     <t xml:space="preserve">4.64519357681274</t>
   </si>
   <si>
-    <t xml:space="preserve">4.67820501327515</t>
+    <t xml:space="preserve">4.67820453643799</t>
   </si>
   <si>
     <t xml:space="preserve">4.71593236923218</t>
@@ -3515,7 +3515,7 @@
     <t xml:space="preserve">4.73479604721069</t>
   </si>
   <si>
-    <t xml:space="preserve">4.60275030136108</t>
+    <t xml:space="preserve">4.60274982452393</t>
   </si>
   <si>
     <t xml:space="preserve">4.57445430755615</t>
@@ -3530,7 +3530,7 @@
     <t xml:space="preserve">4.34337377548218</t>
   </si>
   <si>
-    <t xml:space="preserve">4.41411209106445</t>
+    <t xml:space="preserve">4.41411256790161</t>
   </si>
   <si>
     <t xml:space="preserve">4.3952488899231</t>
@@ -3572,31 +3572,31 @@
     <t xml:space="preserve">4.27263498306274</t>
   </si>
   <si>
-    <t xml:space="preserve">4.23490715026855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.11229276657104</t>
+    <t xml:space="preserve">4.2349066734314</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.1122932434082</t>
   </si>
   <si>
     <t xml:space="preserve">4.0887131690979</t>
   </si>
   <si>
-    <t xml:space="preserve">4.05570220947266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.10757732391357</t>
+    <t xml:space="preserve">4.0557017326355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.10757684707642</t>
   </si>
   <si>
     <t xml:space="preserve">4.03683805465698</t>
   </si>
   <si>
-    <t xml:space="preserve">3.86234855651855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.00854206085205</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.99911022186279</t>
+    <t xml:space="preserve">3.86234831809998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.00854253768921</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.99910998344421</t>
   </si>
   <si>
     <t xml:space="preserve">4.07456541061401</t>
@@ -3614,7 +3614,7 @@
     <t xml:space="preserve">4.15473651885986</t>
   </si>
   <si>
-    <t xml:space="preserve">4.18303203582764</t>
+    <t xml:space="preserve">4.18303155899048</t>
   </si>
   <si>
     <t xml:space="preserve">4.27735042572021</t>
@@ -3632,7 +3632,7 @@
     <t xml:space="preserve">4.24905490875244</t>
   </si>
   <si>
-    <t xml:space="preserve">4.26791858673096</t>
+    <t xml:space="preserve">4.26791906356812</t>
   </si>
   <si>
     <t xml:space="preserve">4.39053297042847</t>
@@ -3641,7 +3641,7 @@
     <t xml:space="preserve">4.37166976928711</t>
   </si>
   <si>
-    <t xml:space="preserve">4.35752153396606</t>
+    <t xml:space="preserve">4.35752105712891</t>
   </si>
   <si>
     <t xml:space="preserve">4.35280513763428</t>
@@ -3677,19 +3677,19 @@
     <t xml:space="preserve">4.23962306976318</t>
   </si>
   <si>
-    <t xml:space="preserve">4.20189571380615</t>
+    <t xml:space="preserve">4.20189523696899</t>
   </si>
   <si>
     <t xml:space="preserve">4.12644052505493</t>
   </si>
   <si>
-    <t xml:space="preserve">4.02268981933594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.15002059936523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.92837166786194</t>
+    <t xml:space="preserve">4.0226902961731</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.15002012252808</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.92837142944336</t>
   </si>
   <si>
     <t xml:space="preserve">4.04626989364624</t>
@@ -3698,16 +3698,16 @@
     <t xml:space="preserve">3.96138286590576</t>
   </si>
   <si>
-    <t xml:space="preserve">4.06041717529297</t>
+    <t xml:space="preserve">4.06041765213013</t>
   </si>
   <si>
     <t xml:space="preserve">4.01797485351562</t>
   </si>
   <si>
-    <t xml:space="preserve">3.90007638931274</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.94251894950867</t>
+    <t xml:space="preserve">3.90007615089417</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.94251942634583</t>
   </si>
   <si>
     <t xml:space="preserve">3.89535999298096</t>
@@ -3725,7 +3725,7 @@
     <t xml:space="preserve">3.88121199607849</t>
   </si>
   <si>
-    <t xml:space="preserve">3.84348464012146</t>
+    <t xml:space="preserve">3.84348440170288</t>
   </si>
   <si>
     <t xml:space="preserve">3.81990528106689</t>
@@ -3743,10 +3743,10 @@
     <t xml:space="preserve">3.75388216972351</t>
   </si>
   <si>
-    <t xml:space="preserve">3.72558641433716</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.76331377029419</t>
+    <t xml:space="preserve">3.72558665275574</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.76331400871277</t>
   </si>
   <si>
     <t xml:space="preserve">3.735018491745</t>
@@ -3755,7 +3755,7 @@
     <t xml:space="preserve">3.71615481376648</t>
   </si>
   <si>
-    <t xml:space="preserve">3.58410859107971</t>
+    <t xml:space="preserve">3.58410835266113</t>
   </si>
   <si>
     <t xml:space="preserve">3.76442790031433</t>
@@ -4485,6 +4485,9 @@
   </si>
   <si>
     <t xml:space="preserve">7.34999990463257</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.34000015258789</t>
   </si>
 </sst>
 </file>
@@ -70655,7 +70658,7 @@
     </row>
     <row r="2533">
       <c r="A2533" s="1" t="n">
-        <v>46006.6911921296</v>
+        <v>46006.3333333333</v>
       </c>
       <c r="B2533" t="n">
         <v>41895</v>
@@ -70676,6 +70679,32 @@
         <v>1481</v>
       </c>
       <c r="H2533" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2534">
+      <c r="A2534" s="1" t="n">
+        <v>46007.6911111111</v>
+      </c>
+      <c r="B2534" t="n">
+        <v>50114</v>
+      </c>
+      <c r="C2534" t="n">
+        <v>7.3899998664856</v>
+      </c>
+      <c r="D2534" t="n">
+        <v>7.23000001907349</v>
+      </c>
+      <c r="E2534" t="n">
+        <v>7.32999992370605</v>
+      </c>
+      <c r="F2534" t="n">
+        <v>7.34000015258789</v>
+      </c>
+      <c r="G2534" t="s">
+        <v>1491</v>
+      </c>
+      <c r="H2534" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/BAN.MI.xlsx
+++ b/data/BAN.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1496" uniqueCount="1496">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1495" uniqueCount="1495">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -38,145 +38,145 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">3.66912937164307</t>
+    <t xml:space="preserve">3.66912984848022</t>
   </si>
   <si>
     <t xml:space="preserve">BAN.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">3.68330192565918</t>
+    <t xml:space="preserve">3.6833028793335</t>
   </si>
   <si>
     <t xml:space="preserve">3.59039330482483</t>
   </si>
   <si>
-    <t xml:space="preserve">3.46283936500549</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.41874694824219</t>
+    <t xml:space="preserve">3.46283960342407</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.41874670982361</t>
   </si>
   <si>
     <t xml:space="preserve">3.35733246803284</t>
   </si>
   <si>
-    <t xml:space="preserve">3.44551777839661</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.46441459655762</t>
+    <t xml:space="preserve">3.44551730155945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.4644148349762</t>
   </si>
   <si>
     <t xml:space="preserve">3.45181632041931</t>
   </si>
   <si>
-    <t xml:space="preserve">3.43134450912476</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.38410258293152</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.40929841995239</t>
+    <t xml:space="preserve">3.43134474754333</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.3841028213501</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.40929865837097</t>
   </si>
   <si>
     <t xml:space="preserve">3.11639833450317</t>
   </si>
   <si>
-    <t xml:space="preserve">3.240802526474</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.29119324684143</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.21245718002319</t>
+    <t xml:space="preserve">3.24080228805542</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.29119348526001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.21245694160461</t>
   </si>
   <si>
     <t xml:space="preserve">3.26757287979126</t>
   </si>
   <si>
-    <t xml:space="preserve">3.19356036186218</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.13372015953064</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.22820425033569</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.16678977012634</t>
+    <t xml:space="preserve">3.1935601234436</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.13372039794922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.22820448875427</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.16678953170776</t>
   </si>
   <si>
     <t xml:space="preserve">3.17308902740479</t>
   </si>
   <si>
-    <t xml:space="preserve">3.0707311630249</t>
+    <t xml:space="preserve">3.07073092460632</t>
   </si>
   <si>
     <t xml:space="preserve">3.1494677066803</t>
   </si>
   <si>
-    <t xml:space="preserve">3.0502598285675</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.92900466918945</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.91325783729553</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.83452081680298</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.82664728164673</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.75263500213623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.75420928001404</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.755784034729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.89436078071594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.98254561424255</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.96207451820374</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.99356889724731</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.05970788002014</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.11009955406189</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.06915640830994</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.96364879608154</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.99199414253235</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.00774168968201</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.97624707221985</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.06285738945007</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.11797261238098</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.18096232414246</t>
+    <t xml:space="preserve">3.05025959014893</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.92900490760803</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.91325736045837</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.83452105522156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.82664704322815</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.75263476371765</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.75420904159546</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.75578427314758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.89436101913452</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.98254585266113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.96207427978516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.99356913566589</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.05970764160156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.11009931564331</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.06915593147278</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.96364903450012</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.99199438095093</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.00774145126343</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.97624659538269</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.06285786628723</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.11797285079956</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.18096256256104</t>
   </si>
   <si>
     <t xml:space="preserve">3.10222578048706</t>
@@ -185,28 +185,28 @@
     <t xml:space="preserve">3.13686990737915</t>
   </si>
   <si>
-    <t xml:space="preserve">3.23292899131775</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.33843588829041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.30694079399109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.24395203590393</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.24237704277039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.12584662437439</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.19670963287354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.2030086517334</t>
+    <t xml:space="preserve">3.23292851448059</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.33843541145325</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.30694127082825</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.24395179748535</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.24237656593323</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.12584686279297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.19670987129211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.20300841331482</t>
   </si>
   <si>
     <t xml:space="preserve">3.10380029678345</t>
@@ -215,13 +215,13 @@
     <t xml:space="preserve">3.11324882507324</t>
   </si>
   <si>
-    <t xml:space="preserve">3.14159369468689</t>
+    <t xml:space="preserve">3.14159417152405</t>
   </si>
   <si>
     <t xml:space="preserve">3.04710984230042</t>
   </si>
   <si>
-    <t xml:space="preserve">2.99986791610718</t>
+    <t xml:space="preserve">2.99986815452576</t>
   </si>
   <si>
     <t xml:space="preserve">2.96049976348877</t>
@@ -236,22 +236,22 @@
     <t xml:space="preserve">2.86286592483521</t>
   </si>
   <si>
-    <t xml:space="preserve">2.87388968467712</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.91010856628418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.98569512367249</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.0014431476593</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.01561546325684</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.92742991447449</t>
+    <t xml:space="preserve">2.87388920783997</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.9101083278656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.98569560050964</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.00144267082214</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.01561522483826</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.92743015289307</t>
   </si>
   <si>
     <t xml:space="preserve">2.92113137245178</t>
@@ -260,40 +260,40 @@
     <t xml:space="preserve">2.85814213752747</t>
   </si>
   <si>
-    <t xml:space="preserve">2.81404948234558</t>
+    <t xml:space="preserve">2.814049243927</t>
   </si>
   <si>
     <t xml:space="preserve">2.84081983566284</t>
   </si>
   <si>
-    <t xml:space="preserve">2.80145144462585</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.72901368141174</t>
+    <t xml:space="preserve">2.80145192146301</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.72901391983032</t>
   </si>
   <si>
     <t xml:space="preserve">2.65185189247131</t>
   </si>
   <si>
-    <t xml:space="preserve">2.68177175521851</t>
+    <t xml:space="preserve">2.68177223205566</t>
   </si>
   <si>
     <t xml:space="preserve">2.71484112739563</t>
   </si>
   <si>
-    <t xml:space="preserve">2.76365804672241</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.77940511703491</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.72428965568542</t>
+    <t xml:space="preserve">2.76365780830383</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.77940535545349</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.724289894104</t>
   </si>
   <si>
     <t xml:space="preserve">2.59043741226196</t>
   </si>
   <si>
-    <t xml:space="preserve">2.5353217124939</t>
+    <t xml:space="preserve">2.53532099723816</t>
   </si>
   <si>
     <t xml:space="preserve">2.49437832832336</t>
@@ -302,34 +302,34 @@
     <t xml:space="preserve">2.48020577430725</t>
   </si>
   <si>
-    <t xml:space="preserve">2.51957440376282</t>
+    <t xml:space="preserve">2.51957416534424</t>
   </si>
   <si>
     <t xml:space="preserve">2.60572743415833</t>
   </si>
   <si>
-    <t xml:space="preserve">2.58784627914429</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.56021237373352</t>
+    <t xml:space="preserve">2.58784651756287</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.5602126121521</t>
   </si>
   <si>
     <t xml:space="preserve">2.56183791160583</t>
   </si>
   <si>
-    <t xml:space="preserve">2.60897874832153</t>
+    <t xml:space="preserve">2.60897827148438</t>
   </si>
   <si>
     <t xml:space="preserve">2.59272313117981</t>
   </si>
   <si>
-    <t xml:space="preserve">2.58134436607361</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.6008505821228</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.72113990783691</t>
+    <t xml:space="preserve">2.58134460449219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.60085105895996</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.72114014625549</t>
   </si>
   <si>
     <t xml:space="preserve">2.82029747962952</t>
@@ -338,127 +338,127 @@
     <t xml:space="preserve">2.80404233932495</t>
   </si>
   <si>
-    <t xml:space="preserve">2.68212747573853</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.71463775634766</t>
+    <t xml:space="preserve">2.68212723731995</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.71463799476624</t>
   </si>
   <si>
     <t xml:space="preserve">2.44642496109009</t>
   </si>
   <si>
-    <t xml:space="preserve">2.39765954017639</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.50331878662109</t>
+    <t xml:space="preserve">2.39765906333923</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.50331854820251</t>
   </si>
   <si>
     <t xml:space="preserve">2.47568488121033</t>
   </si>
   <si>
-    <t xml:space="preserve">2.52770185470581</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.50819516181946</t>
+    <t xml:space="preserve">2.52770161628723</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.50819563865662</t>
   </si>
   <si>
     <t xml:space="preserve">2.40578699111938</t>
   </si>
   <si>
-    <t xml:space="preserve">2.19446754455566</t>
+    <t xml:space="preserve">2.19446802139282</t>
   </si>
   <si>
     <t xml:space="preserve">2.23510599136353</t>
   </si>
   <si>
-    <t xml:space="preserve">2.29525113105774</t>
+    <t xml:space="preserve">2.29525065422058</t>
   </si>
   <si>
     <t xml:space="preserve">2.27411890029907</t>
   </si>
   <si>
-    <t xml:space="preserve">2.35702085494995</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.37327599525452</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.29199957847595</t>
+    <t xml:space="preserve">2.35702109336853</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.3732762336731</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.29200005531311</t>
   </si>
   <si>
     <t xml:space="preserve">2.19284248352051</t>
   </si>
   <si>
-    <t xml:space="preserve">2.22535252571106</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.28387188911438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.30500388145447</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.3310124874115</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.33588933944702</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.33263826370239</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.31963419914246</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.38140368461609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.53582906723022</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.54395723342896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.56834006309509</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.89669728279114</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.83817839622498</t>
+    <t xml:space="preserve">2.22535276412964</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.2838716506958</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.30500411987305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.33101272583008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.33588886260986</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.33263802528381</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.3196337223053</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.38140416145325</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.5358293056488</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.54395699501038</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.56834030151367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.8966977596283</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.83817863464355</t>
   </si>
   <si>
     <t xml:space="preserve">2.81217002868652</t>
   </si>
   <si>
-    <t xml:space="preserve">2.59597396850586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.57646799087524</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.57321619987488</t>
+    <t xml:space="preserve">2.59597420692444</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.57646751403809</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.57321667671204</t>
   </si>
   <si>
     <t xml:space="preserve">2.56671452522278</t>
   </si>
   <si>
-    <t xml:space="preserve">2.53257822990417</t>
+    <t xml:space="preserve">2.53257846832275</t>
   </si>
   <si>
     <t xml:space="preserve">2.53745484352112</t>
   </si>
   <si>
-    <t xml:space="preserve">2.63661217689514</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.63011074066162</t>
+    <t xml:space="preserve">2.63661241531372</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.63011050224304</t>
   </si>
   <si>
     <t xml:space="preserve">2.64636564254761</t>
   </si>
   <si>
-    <t xml:space="preserve">2.65286779403687</t>
+    <t xml:space="preserve">2.65286755561829</t>
   </si>
   <si>
     <t xml:space="preserve">2.63823795318604</t>
@@ -470,73 +470,73 @@
     <t xml:space="preserve">2.69188070297241</t>
   </si>
   <si>
-    <t xml:space="preserve">2.75690197944641</t>
+    <t xml:space="preserve">2.75690174102783</t>
   </si>
   <si>
     <t xml:space="preserve">2.79266357421875</t>
   </si>
   <si>
-    <t xml:space="preserve">2.76340413093567</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.7308931350708</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.65449357032776</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.65774416923523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.742271900177</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.76828026771545</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.70651030540466</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.72764205932617</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.74064636230469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.76990604400635</t>
+    <t xml:space="preserve">2.76340436935425</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.73089337348938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.65449333190918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.65774440765381</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.74227213859558</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.76828050613403</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.70651054382324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.72764229774475</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.74064660072327</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.76990580558777</t>
   </si>
   <si>
     <t xml:space="preserve">2.80079126358032</t>
   </si>
   <si>
-    <t xml:space="preserve">2.69513201713562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.6674976348877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.64799094200134</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.62523365020752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.59759950637817</t>
+    <t xml:space="preserve">2.69513177871704</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.66749739646912</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.64799118041992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.6252338886261</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.59759974479675</t>
   </si>
   <si>
     <t xml:space="preserve">2.61710572242737</t>
   </si>
   <si>
-    <t xml:space="preserve">2.6658718585968</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.63336133956909</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.68862962722778</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.60247611999512</t>
+    <t xml:space="preserve">2.66587233543396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.63336157798767</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.6886293888092</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.6024763584137</t>
   </si>
   <si>
     <t xml:space="preserve">2.677250623703</t>
@@ -548,7 +548,7 @@
     <t xml:space="preserve">2.75527620315552</t>
   </si>
   <si>
-    <t xml:space="preserve">2.72601652145386</t>
+    <t xml:space="preserve">2.72601675987244</t>
   </si>
   <si>
     <t xml:space="preserve">2.72276520729065</t>
@@ -557,7 +557,7 @@
     <t xml:space="preserve">2.82842516899109</t>
   </si>
   <si>
-    <t xml:space="preserve">2.74389743804932</t>
+    <t xml:space="preserve">2.7438976764679</t>
   </si>
   <si>
     <t xml:space="preserve">2.7617781162262</t>
@@ -566,19 +566,19 @@
     <t xml:space="preserve">2.73902082443237</t>
   </si>
   <si>
-    <t xml:space="preserve">2.70488500595093</t>
+    <t xml:space="preserve">2.70488476753235</t>
   </si>
   <si>
     <t xml:space="preserve">2.69025492668152</t>
   </si>
   <si>
-    <t xml:space="preserve">2.612229347229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.73251843452454</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.67562532424927</t>
+    <t xml:space="preserve">2.61222982406616</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.73251891136169</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.67562508583069</t>
   </si>
   <si>
     <t xml:space="preserve">2.62360811233521</t>
@@ -587,10 +587,10 @@
     <t xml:space="preserve">2.59434866905212</t>
   </si>
   <si>
-    <t xml:space="preserve">2.55371022224426</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.55045914649963</t>
+    <t xml:space="preserve">2.55371046066284</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.55045938491821</t>
   </si>
   <si>
     <t xml:space="preserve">2.51307201385498</t>
@@ -599,10 +599,10 @@
     <t xml:space="preserve">2.46755695343018</t>
   </si>
   <si>
-    <t xml:space="preserve">2.50169372558594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.58459544181824</t>
+    <t xml:space="preserve">2.50169348716736</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.58459568023682</t>
   </si>
   <si>
     <t xml:space="preserve">2.63173580169678</t>
@@ -611,7 +611,7 @@
     <t xml:space="preserve">2.65611886978149</t>
   </si>
   <si>
-    <t xml:space="preserve">2.66912293434143</t>
+    <t xml:space="preserve">2.66912269592285</t>
   </si>
   <si>
     <t xml:space="preserve">2.72439122200012</t>
@@ -626,22 +626,22 @@
     <t xml:space="preserve">2.77803373336792</t>
   </si>
   <si>
-    <t xml:space="preserve">2.70000839233398</t>
+    <t xml:space="preserve">2.70000791549683</t>
   </si>
   <si>
     <t xml:space="preserve">2.7731568813324</t>
   </si>
   <si>
-    <t xml:space="preserve">2.7650294303894</t>
+    <t xml:space="preserve">2.76502966880798</t>
   </si>
   <si>
     <t xml:space="preserve">2.71788907051086</t>
   </si>
   <si>
-    <t xml:space="preserve">2.74552321434021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.77965927124023</t>
+    <t xml:space="preserve">2.74552297592163</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.77965903282166</t>
   </si>
   <si>
     <t xml:space="preserve">2.74714875221252</t>
@@ -653,13 +653,13 @@
     <t xml:space="preserve">2.62685918807983</t>
   </si>
   <si>
-    <t xml:space="preserve">2.64961695671082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.69350647926331</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.69838285446167</t>
+    <t xml:space="preserve">2.64961647987366</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.69350624084473</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.69838237762451</t>
   </si>
   <si>
     <t xml:space="preserve">2.92270588874817</t>
@@ -668,58 +668,58 @@
     <t xml:space="preserve">2.88531875610352</t>
   </si>
   <si>
-    <t xml:space="preserve">2.99910593032837</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.97472286224365</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.96984624862671</t>
+    <t xml:space="preserve">2.99910616874695</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.97472310066223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.96984672546387</t>
   </si>
   <si>
     <t xml:space="preserve">2.96334433555603</t>
   </si>
   <si>
-    <t xml:space="preserve">2.94221234321594</t>
+    <t xml:space="preserve">2.94221210479736</t>
   </si>
   <si>
     <t xml:space="preserve">2.93408441543579</t>
   </si>
   <si>
-    <t xml:space="preserve">2.89832329750061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.89182066917419</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.87881684303284</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.87556600570679</t>
+    <t xml:space="preserve">2.89832305908203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.89182114601135</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.87881660461426</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.87556576728821</t>
   </si>
   <si>
     <t xml:space="preserve">2.84468030929565</t>
   </si>
   <si>
-    <t xml:space="preserve">2.82192301750183</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.84955739974976</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.91945481300354</t>
+    <t xml:space="preserve">2.82192325592041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.84955716133118</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.91945457458496</t>
   </si>
   <si>
     <t xml:space="preserve">2.9259569644928</t>
   </si>
   <si>
-    <t xml:space="preserve">2.99097847938538</t>
+    <t xml:space="preserve">2.9909782409668</t>
   </si>
   <si>
     <t xml:space="preserve">2.91457867622375</t>
   </si>
   <si>
-    <t xml:space="preserve">2.91620373725891</t>
+    <t xml:space="preserve">2.91620397567749</t>
   </si>
   <si>
     <t xml:space="preserve">2.95846796035767</t>
@@ -728,58 +728,58 @@
     <t xml:space="preserve">2.95684218406677</t>
   </si>
   <si>
-    <t xml:space="preserve">2.95196533203125</t>
+    <t xml:space="preserve">2.95196509361267</t>
   </si>
   <si>
     <t xml:space="preserve">3.04949760437012</t>
   </si>
   <si>
-    <t xml:space="preserve">3.0559995174408</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.99585461616516</t>
+    <t xml:space="preserve">3.05599999427795</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.99585509300232</t>
   </si>
   <si>
     <t xml:space="preserve">2.97959971427917</t>
   </si>
   <si>
-    <t xml:space="preserve">3.00723385810852</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.09645938873291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.11628723144531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.1691620349884</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.13941955566406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.14437675476074</t>
+    <t xml:space="preserve">3.00723361968994</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.09645915031433</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.11628699302673</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.16916131973267</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.13941979408264</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.14437699317932</t>
   </si>
   <si>
     <t xml:space="preserve">3.18898940086365</t>
   </si>
   <si>
-    <t xml:space="preserve">3.18072772026062</t>
+    <t xml:space="preserve">3.1807279586792</t>
   </si>
   <si>
     <t xml:space="preserve">3.24847340583801</t>
   </si>
   <si>
-    <t xml:space="preserve">3.21707916259766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.16750931739807</t>
+    <t xml:space="preserve">3.21707940101624</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.16750955581665</t>
   </si>
   <si>
     <t xml:space="preserve">3.15429091453552</t>
   </si>
   <si>
-    <t xml:space="preserve">3.170814037323</t>
+    <t xml:space="preserve">3.17081379890442</t>
   </si>
   <si>
     <t xml:space="preserve">3.07663130760193</t>
@@ -788,7 +788,7 @@
     <t xml:space="preserve">3.07497882843018</t>
   </si>
   <si>
-    <t xml:space="preserve">2.98244833946228</t>
+    <t xml:space="preserve">2.98244857788086</t>
   </si>
   <si>
     <t xml:space="preserve">3.0584557056427</t>
@@ -797,7 +797,7 @@
     <t xml:space="preserve">3.06506514549255</t>
   </si>
   <si>
-    <t xml:space="preserve">3.03367066383362</t>
+    <t xml:space="preserve">3.03367114067078</t>
   </si>
   <si>
     <t xml:space="preserve">3.02540922164917</t>
@@ -806,19 +806,19 @@
     <t xml:space="preserve">2.99401497840881</t>
   </si>
   <si>
-    <t xml:space="preserve">2.99071002006531</t>
+    <t xml:space="preserve">2.99071025848389</t>
   </si>
   <si>
     <t xml:space="preserve">2.99897193908691</t>
   </si>
   <si>
-    <t xml:space="preserve">2.93783569335938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.9560112953186</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.0799355506897</t>
+    <t xml:space="preserve">2.93783593177795</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.95601153373718</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.07993602752686</t>
   </si>
   <si>
     <t xml:space="preserve">3.08819770812988</t>
@@ -827,49 +827,49 @@
     <t xml:space="preserve">3.08654546737671</t>
   </si>
   <si>
-    <t xml:space="preserve">3.10802555084229</t>
+    <t xml:space="preserve">3.10802578926086</t>
   </si>
   <si>
     <t xml:space="preserve">3.11133027076721</t>
   </si>
   <si>
-    <t xml:space="preserve">3.14768147468567</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.16420435905457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.20551347732544</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.21377420425415</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.23029780387878</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.23360252380371</t>
+    <t xml:space="preserve">3.14768123626709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.16420459747314</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.20551300048828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.21377468109131</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.23029804229736</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.23360228538513</t>
   </si>
   <si>
     <t xml:space="preserve">3.25343036651611</t>
   </si>
   <si>
-    <t xml:space="preserve">3.29473829269409</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.30795693397522</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.27160573005676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.29639101028442</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.22368860244751</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.25012564659119</t>
+    <t xml:space="preserve">3.29473853111267</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.30795741081238</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.27160596847534</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.29639029502869</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.22368812561035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.25012540817261</t>
   </si>
   <si>
     <t xml:space="preserve">3.19394659996033</t>
@@ -878,49 +878,49 @@
     <t xml:space="preserve">3.26334404945374</t>
   </si>
   <si>
-    <t xml:space="preserve">3.09811162948608</t>
+    <t xml:space="preserve">3.0981113910675</t>
   </si>
   <si>
     <t xml:space="preserve">3.15924763679504</t>
   </si>
   <si>
-    <t xml:space="preserve">3.17246603965759</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.17411875724792</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.1509861946106</t>
+    <t xml:space="preserve">3.17246627807617</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.17411851882935</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.15098595619202</t>
   </si>
   <si>
     <t xml:space="preserve">3.05184650421143</t>
   </si>
   <si>
-    <t xml:space="preserve">3.05680370330811</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.08489274978638</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.12785363197327</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.03201842308044</t>
+    <t xml:space="preserve">3.05680346488953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.08489298820496</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.12785339355469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.0320188999176</t>
   </si>
   <si>
     <t xml:space="preserve">3.09480690956116</t>
   </si>
   <si>
-    <t xml:space="preserve">3.07332634925842</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.09150242805481</t>
+    <t xml:space="preserve">3.07332682609558</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.09150266647339</t>
   </si>
   <si>
     <t xml:space="preserve">3.13115811347961</t>
   </si>
   <si>
-    <t xml:space="preserve">3.10967803001404</t>
+    <t xml:space="preserve">3.10967779159546</t>
   </si>
   <si>
     <t xml:space="preserve">3.10472106933594</t>
@@ -935,22 +935,22 @@
     <t xml:space="preserve">3.1460292339325</t>
   </si>
   <si>
-    <t xml:space="preserve">3.12950563430786</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.14107227325439</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.15759515762329</t>
+    <t xml:space="preserve">3.12950587272644</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.14107203483582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.15759539604187</t>
   </si>
   <si>
     <t xml:space="preserve">3.18403267860413</t>
   </si>
   <si>
-    <t xml:space="preserve">3.10637354850769</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.08158826828003</t>
+    <t xml:space="preserve">3.10637307167053</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.08158850669861</t>
   </si>
   <si>
     <t xml:space="preserve">3.10141634941101</t>
@@ -959,7 +959,7 @@
     <t xml:space="preserve">3.10306859016418</t>
   </si>
   <si>
-    <t xml:space="preserve">3.12289643287659</t>
+    <t xml:space="preserve">3.12289667129517</t>
   </si>
   <si>
     <t xml:space="preserve">3.08984971046448</t>
@@ -968,16 +968,16 @@
     <t xml:space="preserve">2.94940209388733</t>
   </si>
   <si>
-    <t xml:space="preserve">2.93287873268127</t>
+    <t xml:space="preserve">2.93287897109985</t>
   </si>
   <si>
     <t xml:space="preserve">2.83704400062561</t>
   </si>
   <si>
-    <t xml:space="preserve">2.88165664672852</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.90809416770935</t>
+    <t xml:space="preserve">2.88165688514709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.90809392929077</t>
   </si>
   <si>
     <t xml:space="preserve">2.9113986492157</t>
@@ -986,7 +986,7 @@
     <t xml:space="preserve">2.9460973739624</t>
   </si>
   <si>
-    <t xml:space="preserve">2.94114017486572</t>
+    <t xml:space="preserve">2.94114065170288</t>
   </si>
   <si>
     <t xml:space="preserve">2.96592545509338</t>
@@ -995,28 +995,28 @@
     <t xml:space="preserve">2.88496208190918</t>
   </si>
   <si>
-    <t xml:space="preserve">2.84034872055054</t>
+    <t xml:space="preserve">2.84034895896912</t>
   </si>
   <si>
     <t xml:space="preserve">2.82878255844116</t>
   </si>
   <si>
-    <t xml:space="preserve">2.81225919723511</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.8800048828125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.75112271308899</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.80895447731018</t>
+    <t xml:space="preserve">2.81225943565369</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.88000440597534</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.75112295150757</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.80895495414734</t>
   </si>
   <si>
     <t xml:space="preserve">2.79243135452271</t>
   </si>
   <si>
-    <t xml:space="preserve">2.8139111995697</t>
+    <t xml:space="preserve">2.81391167640686</t>
   </si>
   <si>
     <t xml:space="preserve">2.85852432250977</t>
@@ -1025,82 +1025,82 @@
     <t xml:space="preserve">2.97418689727783</t>
   </si>
   <si>
-    <t xml:space="preserve">2.97088265419006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.01549553871155</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.05515098571777</t>
+    <t xml:space="preserve">2.97088217735291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.01549530029297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.05515146255493</t>
   </si>
   <si>
     <t xml:space="preserve">3.04027986526489</t>
   </si>
   <si>
-    <t xml:space="preserve">3.07002234458923</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.06341290473938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.02375674247742</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.03697562217712</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.02871370315552</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.0534987449646</t>
+    <t xml:space="preserve">3.07002210617065</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.06341242790222</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.023756980896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.03697514533997</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.0287139415741</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.05349922180176</t>
   </si>
   <si>
     <t xml:space="preserve">3.0782835483551</t>
   </si>
   <si>
-    <t xml:space="preserve">3.1105043888092</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.06919574737549</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.15594363212585</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.21790528297424</t>
+    <t xml:space="preserve">3.11050415039062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.06919598579407</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.1559431552887</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.21790504455566</t>
   </si>
   <si>
     <t xml:space="preserve">3.17659711837769</t>
   </si>
   <si>
-    <t xml:space="preserve">3.19312047958374</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.25508308410645</t>
+    <t xml:space="preserve">3.19312071800232</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.25508284568787</t>
   </si>
   <si>
     <t xml:space="preserve">3.22203612327576</t>
   </si>
   <si>
-    <t xml:space="preserve">2.96179461479187</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.97831773757935</t>
+    <t xml:space="preserve">2.96179437637329</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.97831797599792</t>
   </si>
   <si>
     <t xml:space="preserve">2.92461729049683</t>
   </si>
   <si>
-    <t xml:space="preserve">2.87504768371582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.13528943061829</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.07745695114136</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.05267238616943</t>
+    <t xml:space="preserve">2.87504744529724</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.13528919219971</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.07745766639709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.05267214775085</t>
   </si>
   <si>
     <t xml:space="preserve">3.03614926338196</t>
@@ -1115,43 +1115,43 @@
     <t xml:space="preserve">3.01962614059448</t>
   </si>
   <si>
-    <t xml:space="preserve">3.02788734436035</t>
+    <t xml:space="preserve">3.02788758277893</t>
   </si>
   <si>
     <t xml:space="preserve">3.0485417842865</t>
   </si>
   <si>
-    <t xml:space="preserve">3.04441070556641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.15181231498718</t>
+    <t xml:space="preserve">3.04441142082214</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.1518120765686</t>
   </si>
   <si>
     <t xml:space="preserve">3.3376989364624</t>
   </si>
   <si>
-    <t xml:space="preserve">3.25095176696777</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.27573680877686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.28399848937988</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.24682116508484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.18485903739929</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.2437379360199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.20177483558655</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.2101674079895</t>
+    <t xml:space="preserve">3.25095152854919</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.2757363319397</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.28399872779846</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.24682068824768</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.18485856056213</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.24373769760132</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.20177459716797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.21016764640808</t>
   </si>
   <si>
     <t xml:space="preserve">3.18918585777283</t>
@@ -1160,46 +1160,46 @@
     <t xml:space="preserve">3.22275614738464</t>
   </si>
   <si>
-    <t xml:space="preserve">3.16400837898254</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.08847451210022</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.12204504013062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.14302682876587</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.20597171783447</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.2563271522522</t>
+    <t xml:space="preserve">3.16400814056396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.0884747505188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.12204551696777</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.14302659034729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.20597100257874</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.25632667541504</t>
   </si>
   <si>
     <t xml:space="preserve">3.24793410301208</t>
   </si>
   <si>
-    <t xml:space="preserve">3.10526013374329</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.07168936729431</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.1849901676178</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.17659687995911</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.11365246772766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.1262412071228</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.13883018493652</t>
+    <t xml:space="preserve">3.10525989532471</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.07168960571289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.18498945236206</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.17659735679626</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.11365270614624</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.12624168395996</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.1388304233551</t>
   </si>
   <si>
     <t xml:space="preserve">3.14722299575806</t>
@@ -1211,7 +1211,7 @@
     <t xml:space="preserve">3.1724009513855</t>
   </si>
   <si>
-    <t xml:space="preserve">3.08427858352661</t>
+    <t xml:space="preserve">3.08427834510803</t>
   </si>
   <si>
     <t xml:space="preserve">3.13463401794434</t>
@@ -1223,22 +1223,22 @@
     <t xml:space="preserve">3.10945630073547</t>
   </si>
   <si>
-    <t xml:space="preserve">3.15981197357178</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.19338250160217</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.21436357498169</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.23534560203552</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.26471924781799</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.32346749305725</t>
+    <t xml:space="preserve">3.15981221199036</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.19338226318359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.21436381340027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.23534512519836</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.26471948623657</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.32346796989441</t>
   </si>
   <si>
     <t xml:space="preserve">3.31087851524353</t>
@@ -1247,124 +1247,124 @@
     <t xml:space="preserve">3.27730822563171</t>
   </si>
   <si>
-    <t xml:space="preserve">3.35703825950623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.42417860031128</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.49131917953491</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.43257141113281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.54167509078979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.44935655593872</t>
+    <t xml:space="preserve">3.35703778266907</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.4241783618927</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.49131965637207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.43257117271423</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.54167485237122</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.44935631752014</t>
   </si>
   <si>
     <t xml:space="preserve">3.48292684555054</t>
   </si>
   <si>
-    <t xml:space="preserve">3.51649761199951</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.47453427314758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.45774912834167</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.3864119052887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.37801957130432</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.47033786773682</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.302485704422</t>
+    <t xml:space="preserve">3.51649737358093</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.474534034729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.4577488899231</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.38641214370728</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.3780198097229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.4703381061554</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.30248594284058</t>
   </si>
   <si>
     <t xml:space="preserve">3.31927108764648</t>
   </si>
   <si>
-    <t xml:space="preserve">3.29828977584839</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.34025287628174</t>
+    <t xml:space="preserve">3.29828953742981</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.34025311470032</t>
   </si>
   <si>
     <t xml:space="preserve">3.27311205863953</t>
   </si>
   <si>
-    <t xml:space="preserve">3.28150463104248</t>
+    <t xml:space="preserve">3.2815043926239</t>
   </si>
   <si>
     <t xml:space="preserve">3.39900088310242</t>
   </si>
   <si>
-    <t xml:space="preserve">3.57524561882019</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.58783435821533</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.55006766319275</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.57944202423096</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.58363819122314</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.66336750984192</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.55845999717712</t>
+    <t xml:space="preserve">3.57524585723877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.58783459663391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.55006814002991</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.57944130897522</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.58363795280457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.6633677482605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.55845975875854</t>
   </si>
   <si>
     <t xml:space="preserve">3.56685256958008</t>
   </si>
   <si>
-    <t xml:space="preserve">3.62140488624573</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.78086447715759</t>
+    <t xml:space="preserve">3.62140417098999</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.78086400032043</t>
   </si>
   <si>
     <t xml:space="preserve">3.88577151298523</t>
   </si>
   <si>
-    <t xml:space="preserve">3.72211575508118</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.76407909393311</t>
+    <t xml:space="preserve">3.72211599349976</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.76407885551453</t>
   </si>
   <si>
     <t xml:space="preserve">3.68434906005859</t>
   </si>
   <si>
-    <t xml:space="preserve">3.79764938354492</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.82702350616455</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.80184602737427</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.83961200714111</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.91934204101562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.91094875335693</t>
+    <t xml:space="preserve">3.79764914512634</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.82702302932739</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.80184555053711</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.83961176872253</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.91934132575989</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.91094899177551</t>
   </si>
   <si>
     <t xml:space="preserve">3.94451951980591</t>
@@ -1373,46 +1373,46 @@
     <t xml:space="preserve">4.06621170043945</t>
   </si>
   <si>
-    <t xml:space="preserve">4.02005290985107</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.927734375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.86898636817932</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.81863141059875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.86059403419495</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.79345273971558</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.86479020118713</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.87737846374512</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.73470449447632</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.84380865097046</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.69274210929871</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.9025571346283</t>
+    <t xml:space="preserve">4.02005243301392</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.92773342132568</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.86898612976074</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.81863069534302</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.86059331893921</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.79345297813416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.86478996276855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.8773787021637</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.73470425605774</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.84380841255188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.69274163246155</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.90255641937256</t>
   </si>
   <si>
     <t xml:space="preserve">3.95291209220886</t>
   </si>
   <si>
-    <t xml:space="preserve">3.99067878723145</t>
+    <t xml:space="preserve">3.9906792640686</t>
   </si>
   <si>
     <t xml:space="preserve">4.00326824188232</t>
@@ -1421,16 +1421,16 @@
     <t xml:space="preserve">3.91514563560486</t>
   </si>
   <si>
-    <t xml:space="preserve">3.87318181991577</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.85220098495483</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.66756415367126</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.6759569644928</t>
+    <t xml:space="preserve">3.87318205833435</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.85220122337341</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.66756391525269</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.67595672607422</t>
   </si>
   <si>
     <t xml:space="preserve">3.5920307636261</t>
@@ -1439,58 +1439,58 @@
     <t xml:space="preserve">3.53328251838684</t>
   </si>
   <si>
-    <t xml:space="preserve">3.70533037185669</t>
+    <t xml:space="preserve">3.70533013343811</t>
   </si>
   <si>
     <t xml:space="preserve">3.6423864364624</t>
   </si>
   <si>
-    <t xml:space="preserve">3.77666831016541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.71791958808899</t>
+    <t xml:space="preserve">3.77666807174683</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.71791934967041</t>
   </si>
   <si>
     <t xml:space="preserve">3.64658236503601</t>
   </si>
   <si>
-    <t xml:space="preserve">3.70113444328308</t>
+    <t xml:space="preserve">3.70113396644592</t>
   </si>
   <si>
     <t xml:space="preserve">3.68015313148499</t>
   </si>
   <si>
-    <t xml:space="preserve">3.80604195594788</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.78506016731262</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.69693875312805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.73050856590271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.74729347229004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.65077900886536</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.65917158126831</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.85639691352844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.8941638469696</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.93612694740295</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.00746393203735</t>
+    <t xml:space="preserve">3.80604147911072</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.78506088256836</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.69693779945374</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.73050832748413</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.74729371070862</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.6507785320282</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.65917086601257</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.85639715194702</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.89416360855103</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.93612766265869</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.0074634552002</t>
   </si>
   <si>
     <t xml:space="preserve">4.08719396591187</t>
@@ -1499,7 +1499,7 @@
     <t xml:space="preserve">4.11237192153931</t>
   </si>
   <si>
-    <t xml:space="preserve">4.17111968994141</t>
+    <t xml:space="preserve">4.17111921310425</t>
   </si>
   <si>
     <t xml:space="preserve">4.19629716873169</t>
@@ -1508,13 +1508,13 @@
     <t xml:space="preserve">4.23826026916504</t>
   </si>
   <si>
-    <t xml:space="preserve">4.18790483474731</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.09978294372559</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.09558582305908</t>
+    <t xml:space="preserve">4.18790435791016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.09978246688843</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.0955867767334</t>
   </si>
   <si>
     <t xml:space="preserve">4.07880115509033</t>
@@ -1526,37 +1526,37 @@
     <t xml:space="preserve">4.09139013290405</t>
   </si>
   <si>
-    <t xml:space="preserve">4.08299684524536</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.06201648712158</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.26343822479248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.39771938323975</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.52360820770264</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.4984302520752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.58235645294189</t>
+    <t xml:space="preserve">4.08299732208252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.06201601028442</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.26343774795532</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.3977198600769</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.52360916137695</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.49843120574951</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.58235692977905</t>
   </si>
   <si>
     <t xml:space="preserve">4.48164558410645</t>
   </si>
   <si>
-    <t xml:space="preserve">4.62431907653809</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.67467546463013</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.69985246658325</t>
+    <t xml:space="preserve">4.62431955337524</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.67467498779297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.69985294342041</t>
   </si>
   <si>
     <t xml:space="preserve">4.6830677986145</t>
@@ -1565,46 +1565,46 @@
     <t xml:space="preserve">4.66628217697144</t>
   </si>
   <si>
-    <t xml:space="preserve">4.63271284103394</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.44807529449463</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.4396824836731</t>
+    <t xml:space="preserve">4.63271188735962</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.44807481765747</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.43968200683594</t>
   </si>
   <si>
     <t xml:space="preserve">4.47325277328491</t>
   </si>
   <si>
-    <t xml:space="preserve">4.49003791809082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.54878664016724</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.59914112091064</t>
+    <t xml:space="preserve">4.49003839492798</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.54878616333008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.59914207458496</t>
   </si>
   <si>
     <t xml:space="preserve">4.61592674255371</t>
   </si>
   <si>
-    <t xml:space="preserve">4.60753488540649</t>
+    <t xml:space="preserve">4.60753440856934</t>
   </si>
   <si>
     <t xml:space="preserve">4.40611219406128</t>
   </si>
   <si>
-    <t xml:space="preserve">4.53200101852417</t>
+    <t xml:space="preserve">4.53200149536133</t>
   </si>
   <si>
     <t xml:space="preserve">4.75860118865967</t>
   </si>
   <si>
-    <t xml:space="preserve">4.80895709991455</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.7418155670166</t>
+    <t xml:space="preserve">4.80895662307739</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.74181604385376</t>
   </si>
   <si>
     <t xml:space="preserve">4.69146060943604</t>
@@ -1613,13 +1613,13 @@
     <t xml:space="preserve">4.65788984298706</t>
   </si>
   <si>
-    <t xml:space="preserve">4.50682401657104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.54039335250854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.46486043930054</t>
+    <t xml:space="preserve">4.50682306289673</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.5403938293457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.4648609161377</t>
   </si>
   <si>
     <t xml:space="preserve">4.41450500488281</t>
@@ -1628,7 +1628,7 @@
     <t xml:space="preserve">4.38932704925537</t>
   </si>
   <si>
-    <t xml:space="preserve">4.38093423843384</t>
+    <t xml:space="preserve">4.38093376159668</t>
   </si>
   <si>
     <t xml:space="preserve">4.34736394882202</t>
@@ -1640,16 +1640,16 @@
     <t xml:space="preserve">4.51919651031494</t>
   </si>
   <si>
-    <t xml:space="preserve">4.39891338348389</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.37313890457153</t>
+    <t xml:space="preserve">4.39891386032104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.37313938140869</t>
   </si>
   <si>
     <t xml:space="preserve">4.30440616607666</t>
   </si>
   <si>
-    <t xml:space="preserve">4.27003955841064</t>
+    <t xml:space="preserve">4.27003908157349</t>
   </si>
   <si>
     <t xml:space="preserve">4.33018064498901</t>
@@ -1661,67 +1661,67 @@
     <t xml:space="preserve">4.38173055648804</t>
   </si>
   <si>
-    <t xml:space="preserve">4.44187164306641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.45905494689941</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.35595560073853</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.3903226852417</t>
+    <t xml:space="preserve">4.44187211990356</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.45905542373657</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.35595512390137</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.39032220840454</t>
   </si>
   <si>
     <t xml:space="preserve">4.45046329498291</t>
   </si>
   <si>
-    <t xml:space="preserve">4.41609668731689</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.23137712478638</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.26574325561523</t>
+    <t xml:space="preserve">4.41609716415405</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.23137664794922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.26574373245239</t>
   </si>
   <si>
     <t xml:space="preserve">4.13257312774658</t>
   </si>
   <si>
-    <t xml:space="preserve">4.04665660858154</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.08531951904297</t>
+    <t xml:space="preserve">4.0466570854187</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.08531999588013</t>
   </si>
   <si>
     <t xml:space="preserve">3.98222041130066</t>
   </si>
   <si>
-    <t xml:space="preserve">4.03376960754395</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.94785284996033</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.99081158638</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.98651552200317</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.94355726242065</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.96503591537476</t>
+    <t xml:space="preserve">4.03376913070679</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.94785308837891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.99081134796143</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.98651528358459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.94355773925781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.96503615379333</t>
   </si>
   <si>
     <t xml:space="preserve">3.96074080467224</t>
   </si>
   <si>
-    <t xml:space="preserve">4.01229095458984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.92637419700623</t>
+    <t xml:space="preserve">4.01229000091553</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.9263744354248</t>
   </si>
   <si>
     <t xml:space="preserve">4.07243156433105</t>
@@ -1730,7 +1730,7 @@
     <t xml:space="preserve">4.08961534500122</t>
   </si>
   <si>
-    <t xml:space="preserve">4.11109447479248</t>
+    <t xml:space="preserve">4.11109399795532</t>
   </si>
   <si>
     <t xml:space="preserve">4.26144790649414</t>
@@ -1739,154 +1739,154 @@
     <t xml:space="preserve">4.32158899307251</t>
   </si>
   <si>
-    <t xml:space="preserve">4.29581451416016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.02947378158569</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.84045791625977</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.87482452392578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.88771224021912</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.00369834899902</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.02088212966919</t>
+    <t xml:space="preserve">4.295814037323</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.02947425842285</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.84045720100403</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.87482500076294</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.88771176338196</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.00369882583618</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.02088117599487</t>
   </si>
   <si>
     <t xml:space="preserve">3.93496608734131</t>
   </si>
   <si>
-    <t xml:space="preserve">3.86623334884644</t>
+    <t xml:space="preserve">3.86623311042786</t>
   </si>
   <si>
     <t xml:space="preserve">3.77172493934631</t>
   </si>
   <si>
-    <t xml:space="preserve">3.71587944030762</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.70299196243286</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.67721724510193</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.68580865859985</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.70728778839111</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.66432976722717</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.66003394126892</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.72017478942871</t>
+    <t xml:space="preserve">3.71587920188904</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.70299172401428</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.67721700668335</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.68580842018127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.70728731155396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.66432905197144</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.6600341796875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.72017502784729</t>
   </si>
   <si>
     <t xml:space="preserve">3.81468319892883</t>
   </si>
   <si>
-    <t xml:space="preserve">3.95214939117432</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.85764098167419</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.78461313247681</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.84475350379944</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.7803168296814</t>
+    <t xml:space="preserve">3.95214891433716</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.85764145851135</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.78461217880249</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.8447539806366</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.78031659126282</t>
   </si>
   <si>
     <t xml:space="preserve">3.69440078735352</t>
   </si>
   <si>
-    <t xml:space="preserve">3.73306274414062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.71158409118652</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.59989261627197</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.75454187393188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.65144205093384</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.72447109222412</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.78890800476074</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.64714670181274</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.668625831604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.6729211807251</t>
+    <t xml:space="preserve">3.73306250572205</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.71158337593079</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.59989237785339</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.75454163551331</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.65144181251526</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.72447085380554</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.78890776634216</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.64714622497559</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.66862535476685</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.67292141914368</t>
   </si>
   <si>
     <t xml:space="preserve">3.6170756816864</t>
   </si>
   <si>
-    <t xml:space="preserve">3.5741171836853</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.64285039901733</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.65573811531067</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.62996292114258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.96933197975159</t>
+    <t xml:space="preserve">3.57411766052246</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.64284992218018</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.65573787689209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.629962682724</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.96933221817017</t>
   </si>
   <si>
     <t xml:space="preserve">3.95644521713257</t>
   </si>
   <si>
-    <t xml:space="preserve">3.90059924125671</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.9306697845459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.01658630371094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.09820747375488</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.1411657333374</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.24426460266113</t>
+    <t xml:space="preserve">3.90059900283813</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.93066954612732</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.0165867805481</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.09820699691772</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.14116477966309</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.24426412582397</t>
   </si>
   <si>
     <t xml:space="preserve">4.24856042861938</t>
   </si>
   <si>
-    <t xml:space="preserve">4.43328046798706</t>
+    <t xml:space="preserve">4.4332799911499</t>
   </si>
   <si>
     <t xml:space="preserve">4.4246883392334</t>
@@ -1901,79 +1901,79 @@
     <t xml:space="preserve">4.49342155456543</t>
   </si>
   <si>
-    <t xml:space="preserve">4.55356311798096</t>
+    <t xml:space="preserve">4.55356216430664</t>
   </si>
   <si>
     <t xml:space="preserve">4.48482942581177</t>
   </si>
   <si>
-    <t xml:space="preserve">4.53637981414795</t>
+    <t xml:space="preserve">4.53638029098511</t>
   </si>
   <si>
     <t xml:space="preserve">4.59652090072632</t>
   </si>
   <si>
-    <t xml:space="preserve">4.77694463729858</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.8113112449646</t>
+    <t xml:space="preserve">4.77694511413574</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.81131219863892</t>
   </si>
   <si>
     <t xml:space="preserve">4.69962072372437</t>
   </si>
   <si>
-    <t xml:space="preserve">4.64807033538818</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.72539520263672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.71680402755737</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.6910285949707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.68243741989136</t>
+    <t xml:space="preserve">4.64807081222534</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.72539567947388</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.71680355072021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.69102907180786</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.68243789672852</t>
   </si>
   <si>
     <t xml:space="preserve">4.70821189880371</t>
   </si>
   <si>
-    <t xml:space="preserve">4.67384576797485</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.5621542930603</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.50201320648193</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.54497146606445</t>
+    <t xml:space="preserve">4.6738452911377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.56215476989746</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.50201368331909</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.54497098922729</t>
   </si>
   <si>
     <t xml:space="preserve">4.51060485839844</t>
   </si>
   <si>
-    <t xml:space="preserve">4.52778768539429</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.76835346221924</t>
+    <t xml:space="preserve">4.5277886390686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.7683539390564</t>
   </si>
   <si>
     <t xml:space="preserve">4.66525363922119</t>
   </si>
   <si>
-    <t xml:space="preserve">4.61370468139648</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.73398685455322</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.63947916030884</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.23567199707031</t>
+    <t xml:space="preserve">4.61370420455933</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.73398733139038</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.639479637146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.23567247390747</t>
   </si>
   <si>
     <t xml:space="preserve">4.15834856033325</t>
@@ -1982,13 +1982,13 @@
     <t xml:space="preserve">4.20130634307861</t>
   </si>
   <si>
-    <t xml:space="preserve">4.36454725265503</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.60511255264282</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.11539030075073</t>
+    <t xml:space="preserve">4.36454677581787</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.60511302947998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.11538982391357</t>
   </si>
   <si>
     <t xml:space="preserve">3.75024580955505</t>
@@ -1997,55 +1997,55 @@
     <t xml:space="preserve">3.47101783752441</t>
   </si>
   <si>
-    <t xml:space="preserve">3.36362290382385</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.31207299232483</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.16601467132568</t>
+    <t xml:space="preserve">3.36362242698669</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.31207275390625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.16601514816284</t>
   </si>
   <si>
     <t xml:space="preserve">3.22186064720154</t>
   </si>
   <si>
-    <t xml:space="preserve">2.80516695976257</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.91685771942139</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.86530804634094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.88678741455078</t>
+    <t xml:space="preserve">2.80516672134399</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.91685795783997</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.86530828475952</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.8867871761322</t>
   </si>
   <si>
     <t xml:space="preserve">2.73213815689087</t>
   </si>
   <si>
-    <t xml:space="preserve">2.66770052909851</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.80087089538574</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.61185479164124</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.72354650497437</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.92115354537964</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.81375813484192</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.70206737518311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.65910911560059</t>
+    <t xml:space="preserve">2.66770076751709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.80087065696716</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.61185503005981</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.72354626655579</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.92115378379822</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.8137583732605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.70206713676453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.65910863876343</t>
   </si>
   <si>
     <t xml:space="preserve">2.84382891654968</t>
@@ -2060,22 +2060,22 @@
     <t xml:space="preserve">2.70636296272278</t>
   </si>
   <si>
-    <t xml:space="preserve">2.71065902709961</t>
+    <t xml:space="preserve">2.71065855026245</t>
   </si>
   <si>
     <t xml:space="preserve">2.85242056846619</t>
   </si>
   <si>
-    <t xml:space="preserve">2.89108300209045</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.9297456741333</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.00706958770752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.96411156654358</t>
+    <t xml:space="preserve">2.89108276367188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.92974519729614</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.0070698261261</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.96411180496216</t>
   </si>
   <si>
     <t xml:space="preserve">2.93833708763123</t>
@@ -2087,7 +2087,7 @@
     <t xml:space="preserve">2.98129534721375</t>
   </si>
   <si>
-    <t xml:space="preserve">3.01136612892151</t>
+    <t xml:space="preserve">3.01136565208435</t>
   </si>
   <si>
     <t xml:space="preserve">2.94692850112915</t>
@@ -2096,7 +2096,7 @@
     <t xml:space="preserve">2.97699904441833</t>
   </si>
   <si>
-    <t xml:space="preserve">2.95122456550598</t>
+    <t xml:space="preserve">2.9512243270874</t>
   </si>
   <si>
     <t xml:space="preserve">3.10587358474731</t>
@@ -2105,22 +2105,22 @@
     <t xml:space="preserve">3.04143619537354</t>
   </si>
   <si>
-    <t xml:space="preserve">3.05002760887146</t>
+    <t xml:space="preserve">3.05002808570862</t>
   </si>
   <si>
     <t xml:space="preserve">3.08439445495605</t>
   </si>
   <si>
-    <t xml:space="preserve">3.13164830207825</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.03284502029419</t>
+    <t xml:space="preserve">3.13164877891541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.03284478187561</t>
   </si>
   <si>
     <t xml:space="preserve">3.09298610687256</t>
   </si>
   <si>
-    <t xml:space="preserve">3.1917896270752</t>
+    <t xml:space="preserve">3.19179010391235</t>
   </si>
   <si>
     <t xml:space="preserve">3.24763560295105</t>
@@ -2129,25 +2129,25 @@
     <t xml:space="preserve">3.16171908378601</t>
   </si>
   <si>
-    <t xml:space="preserve">3.14883160591125</t>
+    <t xml:space="preserve">3.14883184432983</t>
   </si>
   <si>
     <t xml:space="preserve">3.18319821357727</t>
   </si>
   <si>
-    <t xml:space="preserve">3.13594460487366</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.11876106262207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.30777668952942</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.38510203361511</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.43665146827698</t>
+    <t xml:space="preserve">3.13594484329224</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.11876130104065</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.307776927948</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.38510179519653</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.4366512298584</t>
   </si>
   <si>
     <t xml:space="preserve">3.48390531539917</t>
@@ -2165,10 +2165,10 @@
     <t xml:space="preserve">3.29488945007324</t>
   </si>
   <si>
-    <t xml:space="preserve">3.19608569145203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.3808057308197</t>
+    <t xml:space="preserve">3.19608592987061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.38080549240112</t>
   </si>
   <si>
     <t xml:space="preserve">3.37650990486145</t>
@@ -2180,7 +2180,7 @@
     <t xml:space="preserve">3.3722140789032</t>
   </si>
   <si>
-    <t xml:space="preserve">3.42805981636047</t>
+    <t xml:space="preserve">3.42805957794189</t>
   </si>
   <si>
     <t xml:space="preserve">3.44094729423523</t>
@@ -2189,13 +2189,13 @@
     <t xml:space="preserve">3.44524312019348</t>
   </si>
   <si>
-    <t xml:space="preserve">3.75857496261597</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.71435594558716</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.63034081459045</t>
+    <t xml:space="preserve">3.75857448577881</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.71435618400574</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.63034105300903</t>
   </si>
   <si>
     <t xml:space="preserve">3.58170080184937</t>
@@ -2204,7 +2204,7 @@
     <t xml:space="preserve">3.51979494094849</t>
   </si>
   <si>
-    <t xml:space="preserve">3.50210738182068</t>
+    <t xml:space="preserve">3.50210762023926</t>
   </si>
   <si>
     <t xml:space="preserve">3.43135786056519</t>
@@ -2213,13 +2213,13 @@
     <t xml:space="preserve">3.44904518127441</t>
   </si>
   <si>
-    <t xml:space="preserve">3.36060786247253</t>
+    <t xml:space="preserve">3.36060810089111</t>
   </si>
   <si>
     <t xml:space="preserve">3.38713908195496</t>
   </si>
   <si>
-    <t xml:space="preserve">3.41809225082397</t>
+    <t xml:space="preserve">3.4180920124054</t>
   </si>
   <si>
     <t xml:space="preserve">3.32081127166748</t>
@@ -2228,7 +2228,7 @@
     <t xml:space="preserve">3.33849883079529</t>
   </si>
   <si>
-    <t xml:space="preserve">3.31638979911804</t>
+    <t xml:space="preserve">3.31638932228088</t>
   </si>
   <si>
     <t xml:space="preserve">3.27217078208923</t>
@@ -2240,7 +2240,7 @@
     <t xml:space="preserve">3.22795271873474</t>
   </si>
   <si>
-    <t xml:space="preserve">3.09529685974121</t>
+    <t xml:space="preserve">3.09529662132263</t>
   </si>
   <si>
     <t xml:space="preserve">3.18373370170593</t>
@@ -2261,10 +2261,10 @@
     <t xml:space="preserve">3.13951516151428</t>
   </si>
   <si>
-    <t xml:space="preserve">3.10414028167725</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.09971857070923</t>
+    <t xml:space="preserve">3.10414052009583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.09971880912781</t>
   </si>
   <si>
     <t xml:space="preserve">3.04223465919495</t>
@@ -2273,7 +2273,7 @@
     <t xml:space="preserve">3.04665637016296</t>
   </si>
   <si>
-    <t xml:space="preserve">3.07760953903198</t>
+    <t xml:space="preserve">3.0776093006134</t>
   </si>
   <si>
     <t xml:space="preserve">3.05992197990417</t>
@@ -2282,7 +2282,7 @@
     <t xml:space="preserve">2.98032832145691</t>
   </si>
   <si>
-    <t xml:space="preserve">2.96264123916626</t>
+    <t xml:space="preserve">2.9626407623291</t>
   </si>
   <si>
     <t xml:space="preserve">2.94495368003845</t>
@@ -2303,7 +2303,7 @@
     <t xml:space="preserve">2.98475050926208</t>
   </si>
   <si>
-    <t xml:space="preserve">2.90515732765198</t>
+    <t xml:space="preserve">2.9051570892334</t>
   </si>
   <si>
     <t xml:space="preserve">2.83440756797791</t>
@@ -2324,10 +2324,10 @@
     <t xml:space="preserve">2.84767317771912</t>
   </si>
   <si>
-    <t xml:space="preserve">2.82998561859131</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.79461073875427</t>
+    <t xml:space="preserve">2.82998609542847</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.79461121559143</t>
   </si>
   <si>
     <t xml:space="preserve">2.91842269897461</t>
@@ -2336,13 +2336,13 @@
     <t xml:space="preserve">2.82114195823669</t>
   </si>
   <si>
-    <t xml:space="preserve">2.79903292655945</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.80787634849548</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.75923562049866</t>
+    <t xml:space="preserve">2.79903268814087</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.8078761100769</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.75923609733582</t>
   </si>
   <si>
     <t xml:space="preserve">2.72386121749878</t>
@@ -2354,7 +2354,7 @@
     <t xml:space="preserve">2.68406462669373</t>
   </si>
   <si>
-    <t xml:space="preserve">2.63542437553406</t>
+    <t xml:space="preserve">2.63542413711548</t>
   </si>
   <si>
     <t xml:space="preserve">2.61773705482483</t>
@@ -2366,13 +2366,13 @@
     <t xml:space="preserve">2.54698729515076</t>
   </si>
   <si>
-    <t xml:space="preserve">2.56467461585999</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.55140900611877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.49392461776733</t>
+    <t xml:space="preserve">2.56467437744141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.5514087677002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.49392485618591</t>
   </si>
   <si>
     <t xml:space="preserve">2.5735182762146</t>
@@ -2381,10 +2381,10 @@
     <t xml:space="preserve">2.97148489952087</t>
   </si>
   <si>
-    <t xml:space="preserve">2.95379734039307</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.00243782997131</t>
+    <t xml:space="preserve">2.95379757881165</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.00243806838989</t>
   </si>
   <si>
     <t xml:space="preserve">3.17931222915649</t>
@@ -2393,19 +2393,19 @@
     <t xml:space="preserve">3.1704683303833</t>
   </si>
   <si>
-    <t xml:space="preserve">3.19257760047913</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.28985810279846</t>
+    <t xml:space="preserve">3.19257736206055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.28985857963562</t>
   </si>
   <si>
     <t xml:space="preserve">3.29870200157166</t>
   </si>
   <si>
-    <t xml:space="preserve">3.47999811172485</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.41367030143738</t>
+    <t xml:space="preserve">3.4799976348877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.4136700630188</t>
   </si>
   <si>
     <t xml:space="preserve">3.48442006111145</t>
@@ -2414,37 +2414,37 @@
     <t xml:space="preserve">3.45788884162903</t>
   </si>
   <si>
-    <t xml:space="preserve">3.49326372146606</t>
+    <t xml:space="preserve">3.49326348304749</t>
   </si>
   <si>
     <t xml:space="preserve">3.51095104217529</t>
   </si>
   <si>
-    <t xml:space="preserve">3.44462323188782</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.42693591117859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.55516934394836</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.67898106575012</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.72320032119751</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.74973106384277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.80279397964478</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.65687227249146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.66129398345947</t>
+    <t xml:space="preserve">3.44462299346924</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.42693543434143</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.55516958236694</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.67898154258728</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.72320008277893</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.74973082542419</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.80279350280762</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.65687251091003</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.66129374504089</t>
   </si>
   <si>
     <t xml:space="preserve">3.65245032310486</t>
@@ -2456,7 +2456,7 @@
     <t xml:space="preserve">3.60823178291321</t>
   </si>
   <si>
-    <t xml:space="preserve">3.54632592201233</t>
+    <t xml:space="preserve">3.54632616043091</t>
   </si>
   <si>
     <t xml:space="preserve">3.53748226165771</t>
@@ -2465,19 +2465,19 @@
     <t xml:space="preserve">3.57285714149475</t>
   </si>
   <si>
-    <t xml:space="preserve">3.50652933120728</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.59054446220398</t>
+    <t xml:space="preserve">3.5065290927887</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.5905442237854</t>
   </si>
   <si>
     <t xml:space="preserve">3.57727885246277</t>
   </si>
   <si>
-    <t xml:space="preserve">3.74530959129333</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.74088740348816</t>
+    <t xml:space="preserve">3.74530911445618</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.74088764190674</t>
   </si>
   <si>
     <t xml:space="preserve">3.73204374313354</t>
@@ -2486,7 +2486,7 @@
     <t xml:space="preserve">3.7055127620697</t>
   </si>
   <si>
-    <t xml:space="preserve">3.7762622833252</t>
+    <t xml:space="preserve">3.77626204490662</t>
   </si>
   <si>
     <t xml:space="preserve">3.83816838264465</t>
@@ -2495,34 +2495,34 @@
     <t xml:space="preserve">3.68340349197388</t>
   </si>
   <si>
-    <t xml:space="preserve">3.76741862297058</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.78068375587463</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.76299691200256</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.77184057235718</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.71877789497375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.68782496452332</t>
+    <t xml:space="preserve">3.76741886138916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.78068399429321</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.76299667358398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.77183985710144</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.71877813339233</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.68782544136047</t>
   </si>
   <si>
     <t xml:space="preserve">3.59938812255859</t>
   </si>
   <si>
-    <t xml:space="preserve">3.66571545600891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.7099347114563</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.78510618209839</t>
+    <t xml:space="preserve">3.66571569442749</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.70993423461914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.78510594367981</t>
   </si>
   <si>
     <t xml:space="preserve">3.92660522460938</t>
@@ -2531,7 +2531,7 @@
     <t xml:space="preserve">3.93987083435059</t>
   </si>
   <si>
-    <t xml:space="preserve">3.99735498428345</t>
+    <t xml:space="preserve">3.99735474586487</t>
   </si>
   <si>
     <t xml:space="preserve">4.01079893112183</t>
@@ -2540,10 +2540,10 @@
     <t xml:space="preserve">4.09594440460205</t>
   </si>
   <si>
-    <t xml:space="preserve">4.17212724685669</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.16316413879395</t>
+    <t xml:space="preserve">4.17212677001953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.1631646156311</t>
   </si>
   <si>
     <t xml:space="preserve">4.13627576828003</t>
@@ -2561,49 +2561,49 @@
     <t xml:space="preserve">4.06905603408813</t>
   </si>
   <si>
-    <t xml:space="preserve">4.03320503234863</t>
+    <t xml:space="preserve">4.03320550918579</t>
   </si>
   <si>
     <t xml:space="preserve">3.9794294834137</t>
   </si>
   <si>
-    <t xml:space="preserve">4.02872371673584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.05561256408691</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.08698177337646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.97494769096375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.00183582305908</t>
+    <t xml:space="preserve">4.028724193573</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.0556116104126</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.08698129653931</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.97494792938232</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.00183629989624</t>
   </si>
   <si>
     <t xml:space="preserve">4.01528024673462</t>
   </si>
   <si>
-    <t xml:space="preserve">3.96150374412537</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.98839139938354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.95254135131836</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.96598553657532</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.04216814041138</t>
+    <t xml:space="preserve">3.96150398254395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.98839163780212</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.9525408744812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.96598529815674</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.04216861724854</t>
   </si>
   <si>
     <t xml:space="preserve">4.07801914215088</t>
   </si>
   <si>
-    <t xml:space="preserve">4.11835098266602</t>
+    <t xml:space="preserve">4.11835050582886</t>
   </si>
   <si>
     <t xml:space="preserve">4.17660808563232</t>
@@ -2618,13 +2618,13 @@
     <t xml:space="preserve">4.06009340286255</t>
   </si>
   <si>
-    <t xml:space="preserve">4.1945333480835</t>
+    <t xml:space="preserve">4.19453287124634</t>
   </si>
   <si>
     <t xml:space="preserve">4.21245861053467</t>
   </si>
   <si>
-    <t xml:space="preserve">4.14972019195557</t>
+    <t xml:space="preserve">4.14972066879272</t>
   </si>
   <si>
     <t xml:space="preserve">4.12283182144165</t>
@@ -2633,13 +2633,13 @@
     <t xml:space="preserve">4.03768682479858</t>
   </si>
   <si>
-    <t xml:space="preserve">4.01976108551025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.06457471847534</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.20797777175903</t>
+    <t xml:space="preserve">4.01976156234741</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.06457424163818</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.20797729492188</t>
   </si>
   <si>
     <t xml:space="preserve">4.23038387298584</t>
@@ -2648,16 +2648,16 @@
     <t xml:space="preserve">4.25727224349976</t>
   </si>
   <si>
-    <t xml:space="preserve">4.20349597930908</t>
+    <t xml:space="preserve">4.20349645614624</t>
   </si>
   <si>
     <t xml:space="preserve">3.92565369606018</t>
   </si>
   <si>
-    <t xml:space="preserve">3.90772819519043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.88084006309509</t>
+    <t xml:space="preserve">3.90772795677185</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.88083982467651</t>
   </si>
   <si>
     <t xml:space="preserve">3.87635850906372</t>
@@ -2666,13 +2666,13 @@
     <t xml:space="preserve">3.80913805961609</t>
   </si>
   <si>
-    <t xml:space="preserve">3.71503043174744</t>
+    <t xml:space="preserve">3.71503019332886</t>
   </si>
   <si>
     <t xml:space="preserve">3.66573572158813</t>
   </si>
   <si>
-    <t xml:space="preserve">3.83154487609863</t>
+    <t xml:space="preserve">3.83154511451721</t>
   </si>
   <si>
     <t xml:space="preserve">3.93461585044861</t>
@@ -2681,73 +2681,73 @@
     <t xml:space="preserve">3.94357872009277</t>
   </si>
   <si>
-    <t xml:space="preserve">4.04664897918701</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.9928731918335</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.98391103744507</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.02424240112305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.85395193099976</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.93013453483582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.97046685218811</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.10042572021484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.15420150756836</t>
+    <t xml:space="preserve">4.04664945602417</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.99287343025208</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.98391079902649</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.02424287796021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.85395216941833</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.93013501167297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.97046613693237</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.10042524337769</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.15420246124268</t>
   </si>
   <si>
     <t xml:space="preserve">4.09146308898926</t>
   </si>
   <si>
-    <t xml:space="preserve">4.22590303421021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.2662353515625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.24382781982422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.13179540634155</t>
+    <t xml:space="preserve">4.22590351104736</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.26623487472534</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.24382829666138</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.13179492950439</t>
   </si>
   <si>
     <t xml:space="preserve">4.1273136138916</t>
   </si>
   <si>
-    <t xml:space="preserve">4.24830913543701</t>
+    <t xml:space="preserve">4.24830961227417</t>
   </si>
   <si>
     <t xml:space="preserve">4.19005250930786</t>
   </si>
   <si>
-    <t xml:space="preserve">4.29312324523926</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.40515661239624</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.43652534484863</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.48133897781372</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.53511571884155</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.55304098129272</t>
+    <t xml:space="preserve">4.2931227684021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.40515613555908</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.43652582168579</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.48133945465088</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.53511524200439</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.55304050445557</t>
   </si>
   <si>
     <t xml:space="preserve">4.56200361251831</t>
@@ -2759,10 +2759,10 @@
     <t xml:space="preserve">4.45445108413696</t>
   </si>
   <si>
-    <t xml:space="preserve">4.432044506073</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.49926519393921</t>
+    <t xml:space="preserve">4.43204498291016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.49926471710205</t>
   </si>
   <si>
     <t xml:space="preserve">4.49030208587646</t>
@@ -2771,13 +2771,13 @@
     <t xml:space="preserve">4.51718997955322</t>
   </si>
   <si>
-    <t xml:space="preserve">4.63370513916016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.59785413742065</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.47685718536377</t>
+    <t xml:space="preserve">4.633704662323</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.59785461425781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.47685766220093</t>
   </si>
   <si>
     <t xml:space="preserve">4.57096576690674</t>
@@ -2786,13 +2786,13 @@
     <t xml:space="preserve">4.61577939987183</t>
   </si>
   <si>
-    <t xml:space="preserve">4.64266729354858</t>
+    <t xml:space="preserve">4.64266681671143</t>
   </si>
   <si>
     <t xml:space="preserve">4.39171266555786</t>
   </si>
   <si>
-    <t xml:space="preserve">4.44996976852417</t>
+    <t xml:space="preserve">4.44997024536133</t>
   </si>
   <si>
     <t xml:space="preserve">4.27519798278809</t>
@@ -2801,19 +2801,19 @@
     <t xml:space="preserve">4.58889150619507</t>
   </si>
   <si>
-    <t xml:space="preserve">4.66059255599976</t>
+    <t xml:space="preserve">4.66059303283691</t>
   </si>
   <si>
     <t xml:space="preserve">4.65163040161133</t>
   </si>
   <si>
-    <t xml:space="preserve">4.71436929702759</t>
+    <t xml:space="preserve">4.71436882019043</t>
   </si>
   <si>
     <t xml:space="preserve">4.75918245315552</t>
   </si>
   <si>
-    <t xml:space="preserve">4.76814556121826</t>
+    <t xml:space="preserve">4.7681450843811</t>
   </si>
   <si>
     <t xml:space="preserve">4.89362239837646</t>
@@ -2822,16 +2822,16 @@
     <t xml:space="preserve">4.92051029205322</t>
   </si>
   <si>
-    <t xml:space="preserve">4.88465929031372</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.05495023727417</t>
+    <t xml:space="preserve">4.88465976715088</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.05495071411133</t>
   </si>
   <si>
     <t xml:space="preserve">5.01910018920898</t>
   </si>
   <si>
-    <t xml:space="preserve">5.14457654953003</t>
+    <t xml:space="preserve">5.14457750320435</t>
   </si>
   <si>
     <t xml:space="preserve">5.31486845016479</t>
@@ -2840,7 +2840,7 @@
     <t xml:space="preserve">5.37760734558105</t>
   </si>
   <si>
-    <t xml:space="preserve">5.35968208312988</t>
+    <t xml:space="preserve">5.35968160629272</t>
   </si>
   <si>
     <t xml:space="preserve">5.16250324249268</t>
@@ -2852,25 +2852,25 @@
     <t xml:space="preserve">5.15354061126709</t>
   </si>
   <si>
-    <t xml:space="preserve">5.26109266281128</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.27901744842529</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.512047290802</t>
+    <t xml:space="preserve">5.26109218597412</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.27901792526245</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.51204776763916</t>
   </si>
   <si>
     <t xml:space="preserve">5.47619676589966</t>
   </si>
   <si>
-    <t xml:space="preserve">5.50308418273926</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.29694271087646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.19835376739502</t>
+    <t xml:space="preserve">5.50308465957642</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.29694318771362</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.19835329055786</t>
   </si>
   <si>
     <t xml:space="preserve">5.18042898178101</t>
@@ -2882,13 +2882,13 @@
     <t xml:space="preserve">5.09080123901367</t>
   </si>
   <si>
-    <t xml:space="preserve">4.99221229553223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.75021982192993</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.80399560928345</t>
+    <t xml:space="preserve">4.99221181869507</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.75021934509277</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.80399608612061</t>
   </si>
   <si>
     <t xml:space="preserve">4.92947292327881</t>
@@ -2897,7 +2897,7 @@
     <t xml:space="preserve">4.83984661102295</t>
   </si>
   <si>
-    <t xml:space="preserve">4.97428703308105</t>
+    <t xml:space="preserve">4.9742865562439</t>
   </si>
   <si>
     <t xml:space="preserve">4.90258502960205</t>
@@ -2912,43 +2912,43 @@
     <t xml:space="preserve">4.95636177062988</t>
   </si>
   <si>
-    <t xml:space="preserve">4.79503297805786</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.74125719070435</t>
+    <t xml:space="preserve">4.79503345489502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.74125671386719</t>
   </si>
   <si>
     <t xml:space="preserve">4.70540618896484</t>
   </si>
   <si>
-    <t xml:space="preserve">4.52615308761597</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.41860055923462</t>
+    <t xml:space="preserve">4.52615261077881</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.41860008239746</t>
   </si>
   <si>
     <t xml:space="preserve">4.3648247718811</t>
   </si>
   <si>
-    <t xml:space="preserve">4.23934698104858</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.85777187347412</t>
+    <t xml:space="preserve">4.23934745788574</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.85777139663696</t>
   </si>
   <si>
     <t xml:space="preserve">4.91154766082764</t>
   </si>
   <si>
-    <t xml:space="preserve">4.96532392501831</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.11768913269043</t>
+    <t xml:space="preserve">4.96532440185547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.11768960952759</t>
   </si>
   <si>
     <t xml:space="preserve">5.22524166107178</t>
   </si>
   <si>
-    <t xml:space="preserve">5.30590581893921</t>
+    <t xml:space="preserve">5.30590629577637</t>
   </si>
   <si>
     <t xml:space="preserve">5.42242097854614</t>
@@ -2957,13 +2957,13 @@
     <t xml:space="preserve">5.28798055648804</t>
   </si>
   <si>
-    <t xml:space="preserve">5.43138313293457</t>
+    <t xml:space="preserve">5.43138265609741</t>
   </si>
   <si>
     <t xml:space="preserve">5.55686044692993</t>
   </si>
   <si>
-    <t xml:space="preserve">5.62856292724609</t>
+    <t xml:space="preserve">5.62856245040894</t>
   </si>
   <si>
     <t xml:space="preserve">5.52100992202759</t>
@@ -2978,22 +2978,22 @@
     <t xml:space="preserve">5.37441253662109</t>
   </si>
   <si>
-    <t xml:space="preserve">5.47495412826538</t>
+    <t xml:space="preserve">5.47495365142822</t>
   </si>
   <si>
     <t xml:space="preserve">5.46581411361694</t>
   </si>
   <si>
-    <t xml:space="preserve">5.48409461975098</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.63947677612305</t>
+    <t xml:space="preserve">5.48409414291382</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.63947725296021</t>
   </si>
   <si>
     <t xml:space="preserve">5.75829935073853</t>
   </si>
   <si>
-    <t xml:space="preserve">5.80399990081787</t>
+    <t xml:space="preserve">5.80399942398071</t>
   </si>
   <si>
     <t xml:space="preserve">5.65775728225708</t>
@@ -3008,19 +3008,19 @@
     <t xml:space="preserve">5.40183258056641</t>
   </si>
   <si>
-    <t xml:space="preserve">5.63033676147461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.61205625534058</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.82227993011475</t>
+    <t xml:space="preserve">5.63033628463745</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.61205673217773</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.8222804069519</t>
   </si>
   <si>
     <t xml:space="preserve">5.84056043624878</t>
   </si>
   <si>
-    <t xml:space="preserve">5.88626098632812</t>
+    <t xml:space="preserve">5.88626146316528</t>
   </si>
   <si>
     <t xml:space="preserve">5.93196201324463</t>
@@ -3044,10 +3044,10 @@
     <t xml:space="preserve">6.07820463180542</t>
   </si>
   <si>
-    <t xml:space="preserve">5.91368103027344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.68517732620239</t>
+    <t xml:space="preserve">5.9136815071106</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.68517780303955</t>
   </si>
   <si>
     <t xml:space="preserve">5.785719871521</t>
@@ -3056,7 +3056,7 @@
     <t xml:space="preserve">5.7308783531189</t>
   </si>
   <si>
-    <t xml:space="preserve">5.67603731155396</t>
+    <t xml:space="preserve">5.67603826522827</t>
   </si>
   <si>
     <t xml:space="preserve">5.69431781768799</t>
@@ -3065,10 +3065,10 @@
     <t xml:space="preserve">5.66689729690552</t>
   </si>
   <si>
-    <t xml:space="preserve">5.42925310134888</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.42011308670044</t>
+    <t xml:space="preserve">5.42925357818604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.4201135635376</t>
   </si>
   <si>
     <t xml:space="preserve">5.33785200119019</t>
@@ -3086,7 +3086,7 @@
     <t xml:space="preserve">5.39269304275513</t>
   </si>
   <si>
-    <t xml:space="preserve">5.36527252197266</t>
+    <t xml:space="preserve">5.3652720451355</t>
   </si>
   <si>
     <t xml:space="preserve">5.2830114364624</t>
@@ -3095,10 +3095,10 @@
     <t xml:space="preserve">5.2281699180603</t>
   </si>
   <si>
-    <t xml:space="preserve">5.21902942657471</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.15504837036133</t>
+    <t xml:space="preserve">5.21902990341187</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.15504884719849</t>
   </si>
   <si>
     <t xml:space="preserve">5.10020780563354</t>
@@ -3107,7 +3107,7 @@
     <t xml:space="preserve">5.10934782028198</t>
   </si>
   <si>
-    <t xml:space="preserve">5.08192729949951</t>
+    <t xml:space="preserve">5.08192777633667</t>
   </si>
   <si>
     <t xml:space="preserve">5.03622674942017</t>
@@ -3122,19 +3122,19 @@
     <t xml:space="preserve">5.13676834106445</t>
   </si>
   <si>
-    <t xml:space="preserve">5.07278776168823</t>
+    <t xml:space="preserve">5.07278728485107</t>
   </si>
   <si>
     <t xml:space="preserve">5.02708625793457</t>
   </si>
   <si>
-    <t xml:space="preserve">5.04536724090576</t>
+    <t xml:space="preserve">5.0453667640686</t>
   </si>
   <si>
     <t xml:space="preserve">4.99052572250366</t>
   </si>
   <si>
-    <t xml:space="preserve">5.00880575180054</t>
+    <t xml:space="preserve">5.0088062286377</t>
   </si>
   <si>
     <t xml:space="preserve">5.0545072555542</t>
@@ -3155,10 +3155,10 @@
     <t xml:space="preserve">4.93568515777588</t>
   </si>
   <si>
-    <t xml:space="preserve">4.89912414550781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.8808445930481</t>
+    <t xml:space="preserve">4.89912462234497</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.88084411621094</t>
   </si>
   <si>
     <t xml:space="preserve">4.85342359542847</t>
@@ -3170,34 +3170,34 @@
     <t xml:space="preserve">4.73460102081299</t>
   </si>
   <si>
-    <t xml:space="preserve">4.75288152694702</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.69804096221924</t>
+    <t xml:space="preserve">4.75288200378418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.69804048538208</t>
   </si>
   <si>
     <t xml:space="preserve">4.57921886444092</t>
   </si>
   <si>
-    <t xml:space="preserve">4.71632099151611</t>
+    <t xml:space="preserve">4.71632146835327</t>
   </si>
   <si>
     <t xml:space="preserve">4.67976045608521</t>
   </si>
   <si>
-    <t xml:space="preserve">4.84428358078003</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.80772304534912</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.57007837295532</t>
+    <t xml:space="preserve">4.84428310394287</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.80772256851196</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.57007884979248</t>
   </si>
   <si>
     <t xml:space="preserve">4.72546148300171</t>
   </si>
   <si>
-    <t xml:space="preserve">4.68890047073364</t>
+    <t xml:space="preserve">4.6889009475708</t>
   </si>
   <si>
     <t xml:space="preserve">4.67062044143677</t>
@@ -3212,16 +3212,16 @@
     <t xml:space="preserve">4.56093835830688</t>
   </si>
   <si>
-    <t xml:space="preserve">4.58835935592651</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.55179786682129</t>
+    <t xml:space="preserve">4.58835887908936</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.55179834365845</t>
   </si>
   <si>
     <t xml:space="preserve">4.48781728744507</t>
   </si>
   <si>
-    <t xml:space="preserve">4.53808784484863</t>
+    <t xml:space="preserve">4.53808832168579</t>
   </si>
   <si>
     <t xml:space="preserve">4.46953678131104</t>
@@ -3230,10 +3230,10 @@
     <t xml:space="preserve">4.50152778625488</t>
   </si>
   <si>
-    <t xml:space="preserve">4.49695730209351</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.40555620193481</t>
+    <t xml:space="preserve">4.49695777893066</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.40555572509766</t>
   </si>
   <si>
     <t xml:space="preserve">4.43297624588013</t>
@@ -3245,16 +3245,16 @@
     <t xml:space="preserve">4.36899518966675</t>
   </si>
   <si>
-    <t xml:space="preserve">4.29130411148071</t>
+    <t xml:space="preserve">4.29130363464355</t>
   </si>
   <si>
     <t xml:space="preserve">4.20447206497192</t>
   </si>
   <si>
-    <t xml:space="preserve">4.47867727279663</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.48324728012085</t>
+    <t xml:space="preserve">4.47867679595947</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.48324775695801</t>
   </si>
   <si>
     <t xml:space="preserve">4.79858255386353</t>
@@ -3263,7 +3263,7 @@
     <t xml:space="preserve">4.87170362472534</t>
   </si>
   <si>
-    <t xml:space="preserve">4.83514356613159</t>
+    <t xml:space="preserve">4.83514308929443</t>
   </si>
   <si>
     <t xml:space="preserve">5.17332887649536</t>
@@ -3272,13 +3272,13 @@
     <t xml:space="preserve">5.32871150970459</t>
   </si>
   <si>
-    <t xml:space="preserve">5.19160890579224</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.25559091567993</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.38355255126953</t>
+    <t xml:space="preserve">5.19160938262939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.25559043884277</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.38355302810669</t>
   </si>
   <si>
     <t xml:space="preserve">4.97224569320679</t>
@@ -3299,7 +3299,7 @@
     <t xml:space="preserve">5.09106779098511</t>
   </si>
   <si>
-    <t xml:space="preserve">4.98138523101807</t>
+    <t xml:space="preserve">4.98138570785522</t>
   </si>
   <si>
     <t xml:space="preserve">4.92654466629028</t>
@@ -3320,7 +3320,7 @@
     <t xml:space="preserve">5.23730993270874</t>
   </si>
   <si>
-    <t xml:space="preserve">5.27387094497681</t>
+    <t xml:space="preserve">5.27387046813965</t>
   </si>
   <si>
     <t xml:space="preserve">5.31957197189331</t>
@@ -4497,9 +4497,6 @@
   </si>
   <si>
     <t xml:space="preserve">7.44000005722046</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.48999977111816</t>
   </si>
 </sst>
 </file>
@@ -70956,13 +70953,13 @@
     </row>
     <row r="2544">
       <c r="A2544" s="1" t="n">
-        <v>46028.6871412037</v>
+        <v>46028.3333333333</v>
       </c>
       <c r="B2544" t="n">
-        <v>30771</v>
+        <v>32899</v>
       </c>
       <c r="C2544" t="n">
-        <v>7.48999977111816</v>
+        <v>7.5</v>
       </c>
       <c r="D2544" t="n">
         <v>7.3600001335144</v>
@@ -70971,12 +70968,38 @@
         <v>7.48999977111816</v>
       </c>
       <c r="F2544" t="n">
-        <v>7.48999977111816</v>
+        <v>7.5</v>
       </c>
       <c r="G2544" t="s">
-        <v>1495</v>
+        <v>1457</v>
       </c>
       <c r="H2544" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2545">
+      <c r="A2545" s="1" t="n">
+        <v>46029.691099537</v>
+      </c>
+      <c r="B2545" t="n">
+        <v>89251</v>
+      </c>
+      <c r="C2545" t="n">
+        <v>7.65000009536743</v>
+      </c>
+      <c r="D2545" t="n">
+        <v>7.3899998664856</v>
+      </c>
+      <c r="E2545" t="n">
+        <v>7.51000022888184</v>
+      </c>
+      <c r="F2545" t="n">
+        <v>7.48000001907349</v>
+      </c>
+      <c r="G2545" t="s">
+        <v>1429</v>
+      </c>
+      <c r="H2545" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/BAN.MI.xlsx
+++ b/data/BAN.MI.xlsx
@@ -38,49 +38,49 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">3.66912984848022</t>
+    <t xml:space="preserve">3.6691300868988</t>
   </si>
   <si>
     <t xml:space="preserve">BAN.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">3.6833028793335</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.59039330482483</t>
+    <t xml:space="preserve">3.68330240249634</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.59039306640625</t>
   </si>
   <si>
     <t xml:space="preserve">3.46283960342407</t>
   </si>
   <si>
-    <t xml:space="preserve">3.41874670982361</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.35733246803284</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.44551730155945</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.4644148349762</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.45181632041931</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.43134474754333</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.3841028213501</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.40929865837097</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.11639833450317</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.24080228805542</t>
+    <t xml:space="preserve">3.41874718666077</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.35733294487</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.44551753997803</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.46441459655762</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.45181655883789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.43134498596191</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.38410305976868</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.40929841995239</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.11639809608459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.24080276489258</t>
   </si>
   <si>
     <t xml:space="preserve">3.29119348526001</t>
@@ -89,37 +89,37 @@
     <t xml:space="preserve">3.21245694160461</t>
   </si>
   <si>
-    <t xml:space="preserve">3.26757287979126</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.1935601234436</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.13372039794922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.22820448875427</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.16678953170776</t>
+    <t xml:space="preserve">3.26757264137268</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.19356060028076</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.1337206363678</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.22820425033569</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.16678977012634</t>
   </si>
   <si>
     <t xml:space="preserve">3.17308902740479</t>
   </si>
   <si>
-    <t xml:space="preserve">3.07073092460632</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.1494677066803</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.05025959014893</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.92900490760803</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.91325736045837</t>
+    <t xml:space="preserve">3.07073163986206</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.14946794509888</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.05025935173035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.92900443077087</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.91325783729553</t>
   </si>
   <si>
     <t xml:space="preserve">2.83452105522156</t>
@@ -128,22 +128,22 @@
     <t xml:space="preserve">2.82664704322815</t>
   </si>
   <si>
-    <t xml:space="preserve">2.75263476371765</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.75420904159546</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.75578427314758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.89436101913452</t>
+    <t xml:space="preserve">2.75263500213623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.75420951843262</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.755784034729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.89436078071594</t>
   </si>
   <si>
     <t xml:space="preserve">2.98254585266113</t>
   </si>
   <si>
-    <t xml:space="preserve">2.96207427978516</t>
+    <t xml:space="preserve">2.96207475662231</t>
   </si>
   <si>
     <t xml:space="preserve">2.99356913566589</t>
@@ -155,7 +155,7 @@
     <t xml:space="preserve">3.11009931564331</t>
   </si>
   <si>
-    <t xml:space="preserve">3.06915593147278</t>
+    <t xml:space="preserve">3.06915616989136</t>
   </si>
   <si>
     <t xml:space="preserve">2.96364903450012</t>
@@ -164,16 +164,16 @@
     <t xml:space="preserve">2.99199438095093</t>
   </si>
   <si>
-    <t xml:space="preserve">3.00774145126343</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.97624659538269</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.06285786628723</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.11797285079956</t>
+    <t xml:space="preserve">3.00774168968201</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.97624731063843</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.06285715103149</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.11797308921814</t>
   </si>
   <si>
     <t xml:space="preserve">3.18096256256104</t>
@@ -188,16 +188,16 @@
     <t xml:space="preserve">3.23292851448059</t>
   </si>
   <si>
-    <t xml:space="preserve">3.33843541145325</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.30694127082825</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.24395179748535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.24237656593323</t>
+    <t xml:space="preserve">3.33843564987183</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.30694103240967</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.24395155906677</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.24237704277039</t>
   </si>
   <si>
     <t xml:space="preserve">3.12584686279297</t>
@@ -206,19 +206,19 @@
     <t xml:space="preserve">3.19670987129211</t>
   </si>
   <si>
-    <t xml:space="preserve">3.20300841331482</t>
+    <t xml:space="preserve">3.2030086517334</t>
   </si>
   <si>
     <t xml:space="preserve">3.10380029678345</t>
   </si>
   <si>
-    <t xml:space="preserve">3.11324882507324</t>
+    <t xml:space="preserve">3.11324906349182</t>
   </si>
   <si>
     <t xml:space="preserve">3.14159417152405</t>
   </si>
   <si>
-    <t xml:space="preserve">3.04710984230042</t>
+    <t xml:space="preserve">3.04710960388184</t>
   </si>
   <si>
     <t xml:space="preserve">2.99986815452576</t>
@@ -233,7 +233,7 @@
     <t xml:space="preserve">2.96837329864502</t>
   </si>
   <si>
-    <t xml:space="preserve">2.86286592483521</t>
+    <t xml:space="preserve">2.86286616325378</t>
   </si>
   <si>
     <t xml:space="preserve">2.87388920783997</t>
@@ -242,10 +242,10 @@
     <t xml:space="preserve">2.9101083278656</t>
   </si>
   <si>
-    <t xml:space="preserve">2.98569560050964</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.00144267082214</t>
+    <t xml:space="preserve">2.98569583892822</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.00144290924072</t>
   </si>
   <si>
     <t xml:space="preserve">3.01561522483826</t>
@@ -254,58 +254,58 @@
     <t xml:space="preserve">2.92743015289307</t>
   </si>
   <si>
-    <t xml:space="preserve">2.92113137245178</t>
+    <t xml:space="preserve">2.9211311340332</t>
   </si>
   <si>
     <t xml:space="preserve">2.85814213752747</t>
   </si>
   <si>
-    <t xml:space="preserve">2.814049243927</t>
+    <t xml:space="preserve">2.81404900550842</t>
   </si>
   <si>
     <t xml:space="preserve">2.84081983566284</t>
   </si>
   <si>
-    <t xml:space="preserve">2.80145192146301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.72901391983032</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.65185189247131</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.68177223205566</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.71484112739563</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.76365780830383</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.77940535545349</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.724289894104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.59043741226196</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.53532099723816</t>
+    <t xml:space="preserve">2.80145120620728</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.72901368141174</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.65185165405273</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.68177151679993</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.71484136581421</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.76365756988525</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.77940511703491</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.72428941726685</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.59043717384338</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.5353217124939</t>
   </si>
   <si>
     <t xml:space="preserve">2.49437832832336</t>
   </si>
   <si>
-    <t xml:space="preserve">2.48020577430725</t>
+    <t xml:space="preserve">2.48020601272583</t>
   </si>
   <si>
     <t xml:space="preserve">2.51957416534424</t>
   </si>
   <si>
-    <t xml:space="preserve">2.60572743415833</t>
+    <t xml:space="preserve">2.60572719573975</t>
   </si>
   <si>
     <t xml:space="preserve">2.58784651756287</t>
@@ -314,61 +314,64 @@
     <t xml:space="preserve">2.5602126121521</t>
   </si>
   <si>
-    <t xml:space="preserve">2.56183791160583</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.60897827148438</t>
+    <t xml:space="preserve">2.56183815002441</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.60897850990295</t>
   </si>
   <si>
     <t xml:space="preserve">2.59272313117981</t>
   </si>
   <si>
-    <t xml:space="preserve">2.58134460449219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.60085105895996</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.72114014625549</t>
+    <t xml:space="preserve">2.58134436607361</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.60085082054138</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.72113990783691</t>
   </si>
   <si>
     <t xml:space="preserve">2.82029747962952</t>
   </si>
   <si>
-    <t xml:space="preserve">2.80404233932495</t>
+    <t xml:space="preserve">2.80404186248779</t>
   </si>
   <si>
     <t xml:space="preserve">2.68212723731995</t>
   </si>
   <si>
-    <t xml:space="preserve">2.71463799476624</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.44642496109009</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.39765906333923</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.50331854820251</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.47568488121033</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.52770161628723</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.50819563865662</t>
+    <t xml:space="preserve">2.71463775634766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.44642543792725</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.39765954017639</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.50331878662109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.47568464279175</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.51957392692566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.52770185470581</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.50819540023804</t>
   </si>
   <si>
     <t xml:space="preserve">2.40578699111938</t>
   </si>
   <si>
-    <t xml:space="preserve">2.19446802139282</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.23510599136353</t>
+    <t xml:space="preserve">2.19446754455566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.23510646820068</t>
   </si>
   <si>
     <t xml:space="preserve">2.29525065422058</t>
@@ -377,37 +380,37 @@
     <t xml:space="preserve">2.27411890029907</t>
   </si>
   <si>
-    <t xml:space="preserve">2.35702109336853</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.3732762336731</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.29200005531311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.19284248352051</t>
+    <t xml:space="preserve">2.35702061653137</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.37327599525452</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.29199981689453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.19284224510193</t>
   </si>
   <si>
     <t xml:space="preserve">2.22535276412964</t>
   </si>
   <si>
-    <t xml:space="preserve">2.2838716506958</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.30500411987305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.33101272583008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.33588886260986</t>
+    <t xml:space="preserve">2.28387212753296</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.30500388145447</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.3310124874115</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.33588910102844</t>
   </si>
   <si>
     <t xml:space="preserve">2.33263802528381</t>
   </si>
   <si>
-    <t xml:space="preserve">2.3196337223053</t>
+    <t xml:space="preserve">2.31963348388672</t>
   </si>
   <si>
     <t xml:space="preserve">2.38140416145325</t>
@@ -416,85 +419,85 @@
     <t xml:space="preserve">2.5358293056488</t>
   </si>
   <si>
-    <t xml:space="preserve">2.54395699501038</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.56834030151367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.8966977596283</t>
+    <t xml:space="preserve">2.54395747184753</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.56834006309509</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.89669728279114</t>
   </si>
   <si>
     <t xml:space="preserve">2.83817863464355</t>
   </si>
   <si>
-    <t xml:space="preserve">2.81217002868652</t>
+    <t xml:space="preserve">2.81216979026794</t>
   </si>
   <si>
     <t xml:space="preserve">2.59597420692444</t>
   </si>
   <si>
-    <t xml:space="preserve">2.57646751403809</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.57321667671204</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.56671452522278</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.53257846832275</t>
+    <t xml:space="preserve">2.57646775245667</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.57321643829346</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.56671476364136</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.53257822990417</t>
   </si>
   <si>
     <t xml:space="preserve">2.53745484352112</t>
   </si>
   <si>
-    <t xml:space="preserve">2.63661241531372</t>
+    <t xml:space="preserve">2.63661217689514</t>
   </si>
   <si>
     <t xml:space="preserve">2.63011050224304</t>
   </si>
   <si>
-    <t xml:space="preserve">2.64636564254761</t>
+    <t xml:space="preserve">2.64636588096619</t>
   </si>
   <si>
     <t xml:space="preserve">2.65286755561829</t>
   </si>
   <si>
-    <t xml:space="preserve">2.63823795318604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.64148926734924</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.69188070297241</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.75690174102783</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.79266357421875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.76340436935425</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.73089337348938</t>
+    <t xml:space="preserve">2.63823819160461</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.64148879051208</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.69188046455383</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.75690150260925</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.79266381263733</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.76340389251709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.73089361190796</t>
   </si>
   <si>
     <t xml:space="preserve">2.65449333190918</t>
   </si>
   <si>
-    <t xml:space="preserve">2.65774440765381</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.74227213859558</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.76828050613403</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.70651054382324</t>
+    <t xml:space="preserve">2.65774416923523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.74227166175842</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.76828026771545</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.70651030540466</t>
   </si>
   <si>
     <t xml:space="preserve">2.72764229774475</t>
@@ -506,28 +509,28 @@
     <t xml:space="preserve">2.76990580558777</t>
   </si>
   <si>
-    <t xml:space="preserve">2.80079126358032</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.69513177871704</t>
+    <t xml:space="preserve">2.8007915019989</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.69513130187988</t>
   </si>
   <si>
     <t xml:space="preserve">2.66749739646912</t>
   </si>
   <si>
-    <t xml:space="preserve">2.64799118041992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.6252338886261</t>
+    <t xml:space="preserve">2.64799094200134</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.62523365020752</t>
   </si>
   <si>
     <t xml:space="preserve">2.59759974479675</t>
   </si>
   <si>
-    <t xml:space="preserve">2.61710572242737</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.66587233543396</t>
+    <t xml:space="preserve">2.61710619926453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.66587209701538</t>
   </si>
   <si>
     <t xml:space="preserve">2.63336157798767</t>
@@ -542,25 +545,25 @@
     <t xml:space="preserve">2.677250623703</t>
   </si>
   <si>
-    <t xml:space="preserve">2.70976114273071</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.75527620315552</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.72601675987244</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.72276520729065</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.82842516899109</t>
+    <t xml:space="preserve">2.70976161956787</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.7552764415741</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.72601652145386</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.72276568412781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.82842540740967</t>
   </si>
   <si>
     <t xml:space="preserve">2.7438976764679</t>
   </si>
   <si>
-    <t xml:space="preserve">2.7617781162262</t>
+    <t xml:space="preserve">2.76177835464478</t>
   </si>
   <si>
     <t xml:space="preserve">2.73902082443237</t>
@@ -572,7 +575,7 @@
     <t xml:space="preserve">2.69025492668152</t>
   </si>
   <si>
-    <t xml:space="preserve">2.61222982406616</t>
+    <t xml:space="preserve">2.612229347229</t>
   </si>
   <si>
     <t xml:space="preserve">2.73251891136169</t>
@@ -584,19 +587,19 @@
     <t xml:space="preserve">2.62360811233521</t>
   </si>
   <si>
-    <t xml:space="preserve">2.59434866905212</t>
+    <t xml:space="preserve">2.59434843063354</t>
   </si>
   <si>
     <t xml:space="preserve">2.55371046066284</t>
   </si>
   <si>
-    <t xml:space="preserve">2.55045938491821</t>
+    <t xml:space="preserve">2.55045890808105</t>
   </si>
   <si>
     <t xml:space="preserve">2.51307201385498</t>
   </si>
   <si>
-    <t xml:space="preserve">2.46755695343018</t>
+    <t xml:space="preserve">2.46755743026733</t>
   </si>
   <si>
     <t xml:space="preserve">2.50169348716736</t>
@@ -611,13 +614,13 @@
     <t xml:space="preserve">2.65611886978149</t>
   </si>
   <si>
-    <t xml:space="preserve">2.66912269592285</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.72439122200012</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.78291034698486</t>
+    <t xml:space="preserve">2.66912317276001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.72439098358154</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.78291010856628</t>
   </si>
   <si>
     <t xml:space="preserve">2.77153158187866</t>
@@ -626,37 +629,37 @@
     <t xml:space="preserve">2.77803373336792</t>
   </si>
   <si>
-    <t xml:space="preserve">2.70000791549683</t>
+    <t xml:space="preserve">2.70000839233398</t>
   </si>
   <si>
     <t xml:space="preserve">2.7731568813324</t>
   </si>
   <si>
-    <t xml:space="preserve">2.76502966880798</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.71788907051086</t>
+    <t xml:space="preserve">2.7650294303894</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.71788954734802</t>
   </si>
   <si>
     <t xml:space="preserve">2.74552297592163</t>
   </si>
   <si>
-    <t xml:space="preserve">2.77965903282166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.74714875221252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.60410189628601</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.62685918807983</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.64961647987366</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.69350624084473</t>
+    <t xml:space="preserve">2.77965927124023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.74714851379395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.60410165786743</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.62685942649841</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.64961671829224</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.69350600242615</t>
   </si>
   <si>
     <t xml:space="preserve">2.69838237762451</t>
@@ -665,16 +668,16 @@
     <t xml:space="preserve">2.92270588874817</t>
   </si>
   <si>
-    <t xml:space="preserve">2.88531875610352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.99910616874695</t>
+    <t xml:space="preserve">2.88531899452209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.99910593032837</t>
   </si>
   <si>
     <t xml:space="preserve">2.97472310066223</t>
   </si>
   <si>
-    <t xml:space="preserve">2.96984672546387</t>
+    <t xml:space="preserve">2.96984648704529</t>
   </si>
   <si>
     <t xml:space="preserve">2.96334433555603</t>
@@ -683,88 +686,88 @@
     <t xml:space="preserve">2.94221210479736</t>
   </si>
   <si>
-    <t xml:space="preserve">2.93408441543579</t>
+    <t xml:space="preserve">2.93408465385437</t>
   </si>
   <si>
     <t xml:space="preserve">2.89832305908203</t>
   </si>
   <si>
-    <t xml:space="preserve">2.89182114601135</t>
+    <t xml:space="preserve">2.89182066917419</t>
   </si>
   <si>
     <t xml:space="preserve">2.87881660461426</t>
   </si>
   <si>
-    <t xml:space="preserve">2.87556576728821</t>
+    <t xml:space="preserve">2.87556600570679</t>
   </si>
   <si>
     <t xml:space="preserve">2.84468030929565</t>
   </si>
   <si>
-    <t xml:space="preserve">2.82192325592041</t>
+    <t xml:space="preserve">2.82192277908325</t>
   </si>
   <si>
     <t xml:space="preserve">2.84955716133118</t>
   </si>
   <si>
-    <t xml:space="preserve">2.91945457458496</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.9259569644928</t>
+    <t xml:space="preserve">2.91945505142212</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.92595720291138</t>
   </si>
   <si>
     <t xml:space="preserve">2.9909782409668</t>
   </si>
   <si>
-    <t xml:space="preserve">2.91457867622375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.91620397567749</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.95846796035767</t>
+    <t xml:space="preserve">2.91457796096802</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.91620373725891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.95846772193909</t>
   </si>
   <si>
     <t xml:space="preserve">2.95684218406677</t>
   </si>
   <si>
-    <t xml:space="preserve">2.95196509361267</t>
+    <t xml:space="preserve">2.95196533203125</t>
   </si>
   <si>
     <t xml:space="preserve">3.04949760437012</t>
   </si>
   <si>
-    <t xml:space="preserve">3.05599999427795</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.99585509300232</t>
+    <t xml:space="preserve">3.05599975585938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.99585485458374</t>
   </si>
   <si>
     <t xml:space="preserve">2.97959971427917</t>
   </si>
   <si>
-    <t xml:space="preserve">3.00723361968994</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.09645915031433</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.11628699302673</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.16916131973267</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.13941979408264</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.14437699317932</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.18898940086365</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.1807279586792</t>
+    <t xml:space="preserve">3.00723385810852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.09645938873291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.11628746986389</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.1691620349884</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.13941955566406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.14437675476074</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.18898963928223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.18072772026062</t>
   </si>
   <si>
     <t xml:space="preserve">3.24847340583801</t>
@@ -773,13 +776,13 @@
     <t xml:space="preserve">3.21707940101624</t>
   </si>
   <si>
-    <t xml:space="preserve">3.16750955581665</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.15429091453552</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.17081379890442</t>
+    <t xml:space="preserve">3.16750931739807</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.15429067611694</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.17081427574158</t>
   </si>
   <si>
     <t xml:space="preserve">3.07663130760193</t>
@@ -794,22 +797,22 @@
     <t xml:space="preserve">3.0584557056427</t>
   </si>
   <si>
-    <t xml:space="preserve">3.06506514549255</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.03367114067078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.02540922164917</t>
+    <t xml:space="preserve">3.06506490707397</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.0336709022522</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.02540946006775</t>
   </si>
   <si>
     <t xml:space="preserve">2.99401497840881</t>
   </si>
   <si>
-    <t xml:space="preserve">2.99071025848389</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.99897193908691</t>
+    <t xml:space="preserve">2.99071002006531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.99897217750549</t>
   </si>
   <si>
     <t xml:space="preserve">2.93783593177795</t>
@@ -818,7 +821,7 @@
     <t xml:space="preserve">2.95601153373718</t>
   </si>
   <si>
-    <t xml:space="preserve">3.07993602752686</t>
+    <t xml:space="preserve">3.07993578910828</t>
   </si>
   <si>
     <t xml:space="preserve">3.08819770812988</t>
@@ -827,13 +830,13 @@
     <t xml:space="preserve">3.08654546737671</t>
   </si>
   <si>
-    <t xml:space="preserve">3.10802578926086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.11133027076721</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.14768123626709</t>
+    <t xml:space="preserve">3.10802602767944</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.11133050918579</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.14768147468567</t>
   </si>
   <si>
     <t xml:space="preserve">3.16420459747314</t>
@@ -842,10 +845,10 @@
     <t xml:space="preserve">3.20551300048828</t>
   </si>
   <si>
-    <t xml:space="preserve">3.21377468109131</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.23029804229736</t>
+    <t xml:space="preserve">3.21377420425415</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.23029780387878</t>
   </si>
   <si>
     <t xml:space="preserve">3.23360228538513</t>
@@ -854,73 +857,73 @@
     <t xml:space="preserve">3.25343036651611</t>
   </si>
   <si>
-    <t xml:space="preserve">3.29473853111267</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.30795741081238</t>
+    <t xml:space="preserve">3.29473829269409</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.3079571723938</t>
   </si>
   <si>
     <t xml:space="preserve">3.27160596847534</t>
   </si>
   <si>
-    <t xml:space="preserve">3.29639029502869</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.22368812561035</t>
+    <t xml:space="preserve">3.29639053344727</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.22368836402893</t>
   </si>
   <si>
     <t xml:space="preserve">3.25012540817261</t>
   </si>
   <si>
-    <t xml:space="preserve">3.19394659996033</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.26334404945374</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.0981113910675</t>
+    <t xml:space="preserve">3.19394683837891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.26334452629089</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.09811162948608</t>
   </si>
   <si>
     <t xml:space="preserve">3.15924763679504</t>
   </si>
   <si>
-    <t xml:space="preserve">3.17246627807617</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.17411851882935</t>
+    <t xml:space="preserve">3.17246603965759</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.1741189956665</t>
   </si>
   <si>
     <t xml:space="preserve">3.15098595619202</t>
   </si>
   <si>
-    <t xml:space="preserve">3.05184650421143</t>
+    <t xml:space="preserve">3.05184626579285</t>
   </si>
   <si>
     <t xml:space="preserve">3.05680346488953</t>
   </si>
   <si>
-    <t xml:space="preserve">3.08489298820496</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.12785339355469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.0320188999176</t>
+    <t xml:space="preserve">3.08489274978638</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.12785363197327</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.03201842308044</t>
   </si>
   <si>
     <t xml:space="preserve">3.09480690956116</t>
   </si>
   <si>
-    <t xml:space="preserve">3.07332682609558</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.09150266647339</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.13115811347961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.10967779159546</t>
+    <t xml:space="preserve">3.073326587677</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.09150242805481</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.13115787506104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.10967803001404</t>
   </si>
   <si>
     <t xml:space="preserve">3.10472106933594</t>
@@ -932,7 +935,7 @@
     <t xml:space="preserve">3.13611507415771</t>
   </si>
   <si>
-    <t xml:space="preserve">3.1460292339325</t>
+    <t xml:space="preserve">3.14602899551392</t>
   </si>
   <si>
     <t xml:space="preserve">3.12950587272644</t>
@@ -944,22 +947,22 @@
     <t xml:space="preserve">3.15759539604187</t>
   </si>
   <si>
-    <t xml:space="preserve">3.18403267860413</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.10637307167053</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.08158850669861</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.10141634941101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.10306859016418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.12289667129517</t>
+    <t xml:space="preserve">3.18403291702271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.10637331008911</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.08158826828003</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.10141611099243</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.10306882858276</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.12289643287659</t>
   </si>
   <si>
     <t xml:space="preserve">3.08984971046448</t>
@@ -971,19 +974,19 @@
     <t xml:space="preserve">2.93287897109985</t>
   </si>
   <si>
-    <t xml:space="preserve">2.83704400062561</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.88165688514709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.90809392929077</t>
+    <t xml:space="preserve">2.83704376220703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.88165664672852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.90809416770935</t>
   </si>
   <si>
     <t xml:space="preserve">2.9113986492157</t>
   </si>
   <si>
-    <t xml:space="preserve">2.9460973739624</t>
+    <t xml:space="preserve">2.94609761238098</t>
   </si>
   <si>
     <t xml:space="preserve">2.94114065170288</t>
@@ -992,76 +995,76 @@
     <t xml:space="preserve">2.96592545509338</t>
   </si>
   <si>
-    <t xml:space="preserve">2.88496208190918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.84034895896912</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.82878255844116</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.81225943565369</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.88000440597534</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.75112295150757</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.80895495414734</t>
+    <t xml:space="preserve">2.88496160507202</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.84034872055054</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.82878232002258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.81225919723511</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.88000464439392</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.75112318992615</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.80895471572876</t>
   </si>
   <si>
     <t xml:space="preserve">2.79243135452271</t>
   </si>
   <si>
-    <t xml:space="preserve">2.81391167640686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.85852432250977</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.97418689727783</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.97088217735291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.01549530029297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.05515146255493</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.04027986526489</t>
+    <t xml:space="preserve">2.81391143798828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.85852456092834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.97418713569641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.97088241577148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.01549577713013</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.05515074729919</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.04028010368347</t>
   </si>
   <si>
     <t xml:space="preserve">3.07002210617065</t>
   </si>
   <si>
-    <t xml:space="preserve">3.06341242790222</t>
+    <t xml:space="preserve">3.0634126663208</t>
   </si>
   <si>
     <t xml:space="preserve">3.023756980896</t>
   </si>
   <si>
-    <t xml:space="preserve">3.03697514533997</t>
+    <t xml:space="preserve">3.03697538375854</t>
   </si>
   <si>
     <t xml:space="preserve">3.0287139415741</t>
   </si>
   <si>
-    <t xml:space="preserve">3.05349922180176</t>
+    <t xml:space="preserve">3.0534987449646</t>
   </si>
   <si>
     <t xml:space="preserve">3.0782835483551</t>
   </si>
   <si>
-    <t xml:space="preserve">3.11050415039062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.06919598579407</t>
+    <t xml:space="preserve">3.1105043888092</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.06919550895691</t>
   </si>
   <si>
     <t xml:space="preserve">3.1559431552887</t>
@@ -1073,16 +1076,16 @@
     <t xml:space="preserve">3.17659711837769</t>
   </si>
   <si>
-    <t xml:space="preserve">3.19312071800232</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.25508284568787</t>
+    <t xml:space="preserve">3.19312047958374</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.25508260726929</t>
   </si>
   <si>
     <t xml:space="preserve">3.22203612327576</t>
   </si>
   <si>
-    <t xml:space="preserve">2.96179437637329</t>
+    <t xml:space="preserve">2.96179485321045</t>
   </si>
   <si>
     <t xml:space="preserve">2.97831797599792</t>
@@ -1091,73 +1094,73 @@
     <t xml:space="preserve">2.92461729049683</t>
   </si>
   <si>
-    <t xml:space="preserve">2.87504744529724</t>
+    <t xml:space="preserve">2.87504768371582</t>
   </si>
   <si>
     <t xml:space="preserve">3.13528919219971</t>
   </si>
   <si>
-    <t xml:space="preserve">3.07745766639709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.05267214775085</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.03614926338196</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.92048668861389</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.08571910858154</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.01962614059448</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.02788758277893</t>
+    <t xml:space="preserve">3.07745742797852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.05267238616943</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.03614974021912</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.92048645019531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.08571934700012</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.0196259021759</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.02788782119751</t>
   </si>
   <si>
     <t xml:space="preserve">3.0485417842865</t>
   </si>
   <si>
-    <t xml:space="preserve">3.04441142082214</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.1518120765686</t>
+    <t xml:space="preserve">3.04441094398499</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.15181231498718</t>
   </si>
   <si>
     <t xml:space="preserve">3.3376989364624</t>
   </si>
   <si>
-    <t xml:space="preserve">3.25095152854919</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.2757363319397</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.28399872779846</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.24682068824768</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.18485856056213</t>
+    <t xml:space="preserve">3.25095176696777</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.27573680877686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.2839982509613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.24682092666626</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.18485879898071</t>
   </si>
   <si>
     <t xml:space="preserve">3.24373769760132</t>
   </si>
   <si>
-    <t xml:space="preserve">3.20177459716797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.21016764640808</t>
+    <t xml:space="preserve">3.20177507400513</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.2101674079895</t>
   </si>
   <si>
     <t xml:space="preserve">3.18918585777283</t>
   </si>
   <si>
-    <t xml:space="preserve">3.22275614738464</t>
+    <t xml:space="preserve">3.22275638580322</t>
   </si>
   <si>
     <t xml:space="preserve">3.16400814056396</t>
@@ -1166,46 +1169,43 @@
     <t xml:space="preserve">3.0884747505188</t>
   </si>
   <si>
-    <t xml:space="preserve">3.12204551696777</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.14302659034729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.20597100257874</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.25632667541504</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.24793410301208</t>
+    <t xml:space="preserve">3.12204527854919</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.14302682876587</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.20597124099731</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.2563271522522</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.24793434143066</t>
   </si>
   <si>
     <t xml:space="preserve">3.10525989532471</t>
   </si>
   <si>
-    <t xml:space="preserve">3.07168960571289</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.18498945236206</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.17659735679626</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.11365270614624</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.12624168395996</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.1388304233551</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.14722299575806</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.15561580657959</t>
+    <t xml:space="preserve">3.07168936729431</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.18498992919922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.11365246772766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.1262412071228</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.13883018493652</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.14722323417664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.15561556816101</t>
   </si>
   <si>
     <t xml:space="preserve">3.1724009513855</t>
@@ -1223,7 +1223,7 @@
     <t xml:space="preserve">3.10945630073547</t>
   </si>
   <si>
-    <t xml:space="preserve">3.15981221199036</t>
+    <t xml:space="preserve">3.15981197357178</t>
   </si>
   <si>
     <t xml:space="preserve">3.19338226318359</t>
@@ -1232,55 +1232,55 @@
     <t xml:space="preserve">3.21436381340027</t>
   </si>
   <si>
-    <t xml:space="preserve">3.23534512519836</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.26471948623657</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.32346796989441</t>
+    <t xml:space="preserve">3.23534560203552</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.26471924781799</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.32346725463867</t>
   </si>
   <si>
     <t xml:space="preserve">3.31087851524353</t>
   </si>
   <si>
-    <t xml:space="preserve">3.27730822563171</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.35703778266907</t>
+    <t xml:space="preserve">3.27730846405029</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.35703802108765</t>
   </si>
   <si>
     <t xml:space="preserve">3.4241783618927</t>
   </si>
   <si>
-    <t xml:space="preserve">3.49131965637207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.43257117271423</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.54167485237122</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.44935631752014</t>
+    <t xml:space="preserve">3.49131917953491</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.43257164955139</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.54167532920837</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.44935655593872</t>
   </si>
   <si>
     <t xml:space="preserve">3.48292684555054</t>
   </si>
   <si>
-    <t xml:space="preserve">3.51649737358093</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.474534034729</t>
+    <t xml:space="preserve">3.51649761199951</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.47453427314758</t>
   </si>
   <si>
     <t xml:space="preserve">3.4577488899231</t>
   </si>
   <si>
-    <t xml:space="preserve">3.38641214370728</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.3780198097229</t>
+    <t xml:space="preserve">3.3864119052887</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.37801957130432</t>
   </si>
   <si>
     <t xml:space="preserve">3.4703381061554</t>
@@ -1292,49 +1292,49 @@
     <t xml:space="preserve">3.31927108764648</t>
   </si>
   <si>
-    <t xml:space="preserve">3.29828953742981</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.34025311470032</t>
+    <t xml:space="preserve">3.29828977584839</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.34025287628174</t>
   </si>
   <si>
     <t xml:space="preserve">3.27311205863953</t>
   </si>
   <si>
-    <t xml:space="preserve">3.2815043926239</t>
+    <t xml:space="preserve">3.28150463104248</t>
   </si>
   <si>
     <t xml:space="preserve">3.39900088310242</t>
   </si>
   <si>
-    <t xml:space="preserve">3.57524585723877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.58783459663391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.55006814002991</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.57944130897522</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.58363795280457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.6633677482605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.55845975875854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.56685256958008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.62140417098999</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.78086400032043</t>
+    <t xml:space="preserve">3.57524561882019</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.58783435821533</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.55006766319275</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.57944178581238</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.58363819122314</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.66336750984192</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.5584602355957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.56685280799866</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.62140488624573</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.78086471557617</t>
   </si>
   <si>
     <t xml:space="preserve">3.88577151298523</t>
@@ -1346,88 +1346,88 @@
     <t xml:space="preserve">3.76407885551453</t>
   </si>
   <si>
-    <t xml:space="preserve">3.68434906005859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.79764914512634</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.82702302932739</t>
+    <t xml:space="preserve">3.68434882164001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.79764938354492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.82702350616455</t>
   </si>
   <si>
     <t xml:space="preserve">3.80184555053711</t>
   </si>
   <si>
-    <t xml:space="preserve">3.83961176872253</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.91934132575989</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.91094899177551</t>
+    <t xml:space="preserve">3.83961224555969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.9193422794342</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.91094923019409</t>
   </si>
   <si>
     <t xml:space="preserve">3.94451951980591</t>
   </si>
   <si>
-    <t xml:space="preserve">4.06621170043945</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.02005243301392</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.92773342132568</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.86898612976074</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.81863069534302</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.86059331893921</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.79345297813416</t>
+    <t xml:space="preserve">4.06621217727661</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.02005338668823</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.927734375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.8689866065979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.81863117218018</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.86059403419495</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.79345273971558</t>
   </si>
   <si>
     <t xml:space="preserve">3.86478996276855</t>
   </si>
   <si>
-    <t xml:space="preserve">3.8773787021637</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.73470425605774</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.84380841255188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.69274163246155</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.90255641937256</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.95291209220886</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.9906792640686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.00326824188232</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.91514563560486</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.87318205833435</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.85220122337341</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.66756391525269</t>
+    <t xml:space="preserve">3.87737846374512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.7347047328949</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.8438081741333</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.69274234771729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.90255665779114</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.95291185379028</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.99067902565002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.00326776504517</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.91514539718628</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.87318158149719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.85220074653625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.66756415367126</t>
   </si>
   <si>
     <t xml:space="preserve">3.67595672607422</t>
@@ -1436,10 +1436,10 @@
     <t xml:space="preserve">3.5920307636261</t>
   </si>
   <si>
-    <t xml:space="preserve">3.53328251838684</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.70533013343811</t>
+    <t xml:space="preserve">3.53328275680542</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.70533037185669</t>
   </si>
   <si>
     <t xml:space="preserve">3.6423864364624</t>
@@ -1448,61 +1448,61 @@
     <t xml:space="preserve">3.77666807174683</t>
   </si>
   <si>
-    <t xml:space="preserve">3.71791934967041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.64658236503601</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.70113396644592</t>
+    <t xml:space="preserve">3.71791958808899</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.64658260345459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.7011342048645</t>
   </si>
   <si>
     <t xml:space="preserve">3.68015313148499</t>
   </si>
   <si>
-    <t xml:space="preserve">3.80604147911072</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.78506088256836</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.69693779945374</t>
+    <t xml:space="preserve">3.80604219436646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.7850604057312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.69693875312805</t>
   </si>
   <si>
     <t xml:space="preserve">3.73050832748413</t>
   </si>
   <si>
-    <t xml:space="preserve">3.74729371070862</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.6507785320282</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.65917086601257</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.85639715194702</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.89416360855103</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.93612766265869</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.0074634552002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.08719396591187</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.11237192153931</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.17111921310425</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.19629716873169</t>
+    <t xml:space="preserve">3.74729347229004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.65077877044678</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.65917158126831</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.85639667510986</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.8941638469696</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.93612694740295</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.00746393203735</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.08719348907471</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.11237144470215</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.17111968994141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.19629764556885</t>
   </si>
   <si>
     <t xml:space="preserve">4.23826026916504</t>
@@ -1514,7 +1514,7 @@
     <t xml:space="preserve">4.09978246688843</t>
   </si>
   <si>
-    <t xml:space="preserve">4.0955867767334</t>
+    <t xml:space="preserve">4.09558582305908</t>
   </si>
   <si>
     <t xml:space="preserve">4.07880115509033</t>
@@ -1523,37 +1523,37 @@
     <t xml:space="preserve">4.14594173431396</t>
   </si>
   <si>
-    <t xml:space="preserve">4.09139013290405</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.08299732208252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.06201601028442</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.26343774795532</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.3977198600769</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.52360916137695</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.49843120574951</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.58235692977905</t>
+    <t xml:space="preserve">4.09139060974121</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.08299684524536</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.06201648712158</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.26343822479248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.39771938323975</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.52360773086548</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.49843072891235</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.58235645294189</t>
   </si>
   <si>
     <t xml:space="preserve">4.48164558410645</t>
   </si>
   <si>
-    <t xml:space="preserve">4.62431955337524</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.67467498779297</t>
+    <t xml:space="preserve">4.62431907653809</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.67467546463013</t>
   </si>
   <si>
     <t xml:space="preserve">4.69985294342041</t>
@@ -1562,28 +1562,28 @@
     <t xml:space="preserve">4.6830677986145</t>
   </si>
   <si>
-    <t xml:space="preserve">4.66628217697144</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.63271188735962</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.44807481765747</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.43968200683594</t>
+    <t xml:space="preserve">4.66628170013428</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.63271284103394</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.44807529449463</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.4396824836731</t>
   </si>
   <si>
     <t xml:space="preserve">4.47325277328491</t>
   </si>
   <si>
-    <t xml:space="preserve">4.49003839492798</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.54878616333008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.59914207458496</t>
+    <t xml:space="preserve">4.49003791809082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.54878664016724</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.5991415977478</t>
   </si>
   <si>
     <t xml:space="preserve">4.61592674255371</t>
@@ -1595,13 +1595,13 @@
     <t xml:space="preserve">4.40611219406128</t>
   </si>
   <si>
-    <t xml:space="preserve">4.53200149536133</t>
+    <t xml:space="preserve">4.53200101852417</t>
   </si>
   <si>
     <t xml:space="preserve">4.75860118865967</t>
   </si>
   <si>
-    <t xml:space="preserve">4.80895662307739</t>
+    <t xml:space="preserve">4.80895709991455</t>
   </si>
   <si>
     <t xml:space="preserve">4.74181604385376</t>
@@ -1613,13 +1613,13 @@
     <t xml:space="preserve">4.65788984298706</t>
   </si>
   <si>
-    <t xml:space="preserve">4.50682306289673</t>
+    <t xml:space="preserve">4.50682353973389</t>
   </si>
   <si>
     <t xml:space="preserve">4.5403938293457</t>
   </si>
   <si>
-    <t xml:space="preserve">4.4648609161377</t>
+    <t xml:space="preserve">4.46486043930054</t>
   </si>
   <si>
     <t xml:space="preserve">4.41450500488281</t>
@@ -1628,28 +1628,28 @@
     <t xml:space="preserve">4.38932704925537</t>
   </si>
   <si>
-    <t xml:space="preserve">4.38093376159668</t>
+    <t xml:space="preserve">4.38093423843384</t>
   </si>
   <si>
     <t xml:space="preserve">4.34736394882202</t>
   </si>
   <si>
-    <t xml:space="preserve">4.46764659881592</t>
+    <t xml:space="preserve">4.46764612197876</t>
   </si>
   <si>
     <t xml:space="preserve">4.51919651031494</t>
   </si>
   <si>
-    <t xml:space="preserve">4.39891386032104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.37313938140869</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.30440616607666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.27003908157349</t>
+    <t xml:space="preserve">4.39891338348389</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.37313890457153</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.3044056892395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.27003955841064</t>
   </si>
   <si>
     <t xml:space="preserve">4.33018064498901</t>
@@ -1661,67 +1661,67 @@
     <t xml:space="preserve">4.38173055648804</t>
   </si>
   <si>
-    <t xml:space="preserve">4.44187211990356</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.45905542373657</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.35595512390137</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.39032220840454</t>
+    <t xml:space="preserve">4.44187164306641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.45905494689941</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.35595560073853</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.3903226852417</t>
   </si>
   <si>
     <t xml:space="preserve">4.45046329498291</t>
   </si>
   <si>
-    <t xml:space="preserve">4.41609716415405</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.23137664794922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.26574373245239</t>
+    <t xml:space="preserve">4.41609668731689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.23137712478638</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.26574325561523</t>
   </si>
   <si>
     <t xml:space="preserve">4.13257312774658</t>
   </si>
   <si>
-    <t xml:space="preserve">4.0466570854187</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.08531999588013</t>
+    <t xml:space="preserve">4.04665660858154</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.08531951904297</t>
   </si>
   <si>
     <t xml:space="preserve">3.98222041130066</t>
   </si>
   <si>
-    <t xml:space="preserve">4.03376913070679</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.94785308837891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.99081134796143</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.98651528358459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.94355773925781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.96503615379333</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.96074080467224</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.01229000091553</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.9263744354248</t>
+    <t xml:space="preserve">4.03376960754395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.94785261154175</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.99081158638</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.98651552200317</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.94355726242065</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.96503567695618</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.96074104309082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.01229095458984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.92637419700623</t>
   </si>
   <si>
     <t xml:space="preserve">4.07243156433105</t>
@@ -1733,160 +1733,160 @@
     <t xml:space="preserve">4.11109399795532</t>
   </si>
   <si>
-    <t xml:space="preserve">4.26144790649414</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.32158899307251</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.295814037323</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.02947425842285</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.84045720100403</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.87482500076294</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.88771176338196</t>
+    <t xml:space="preserve">4.26144742965698</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.32158946990967</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.29581451416016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.02947378158569</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.84045767784119</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.87482452392578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.88771224021912</t>
   </si>
   <si>
     <t xml:space="preserve">4.00369882583618</t>
   </si>
   <si>
-    <t xml:space="preserve">4.02088117599487</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.93496608734131</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.86623311042786</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.77172493934631</t>
+    <t xml:space="preserve">4.02088212966919</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.93496561050415</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.86623334884644</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.77172470092773</t>
   </si>
   <si>
     <t xml:space="preserve">3.71587920188904</t>
   </si>
   <si>
-    <t xml:space="preserve">3.70299172401428</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.67721700668335</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.68580842018127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.70728731155396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.66432905197144</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.6600341796875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.72017502784729</t>
+    <t xml:space="preserve">3.70299196243286</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.67721724510193</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.68580889701843</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.70728802680969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.66432976722717</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.66003394126892</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.72017478942871</t>
   </si>
   <si>
     <t xml:space="preserve">3.81468319892883</t>
   </si>
   <si>
-    <t xml:space="preserve">3.95214891433716</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.85764145851135</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.78461217880249</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.8447539806366</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.78031659126282</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.69440078735352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.73306250572205</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.71158337593079</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.59989237785339</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.75454163551331</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.65144181251526</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.72447085380554</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.78890776634216</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.64714622497559</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.66862535476685</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.67292141914368</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.6170756816864</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.57411766052246</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.64284992218018</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.65573787689209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.629962682724</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.96933221817017</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.95644521713257</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.90059900283813</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.93066954612732</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.0165867805481</t>
+    <t xml:space="preserve">3.9521496295929</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.85764098167419</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.78461313247681</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.84475350379944</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.78031706809998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.69440054893494</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.73306274414062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.71158385276794</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.59989261627197</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.75454187393188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.65144205093384</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.72447109222412</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.78890800476074</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.64714670181274</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.66862559318542</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.6729211807251</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.61707592010498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.5741171836853</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.64285039901733</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.65573811531067</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.62996292114258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.96933197975159</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.95644497871399</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.90059924125671</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.93067026138306</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.01658630371094</t>
   </si>
   <si>
     <t xml:space="preserve">4.09820699691772</t>
   </si>
   <si>
-    <t xml:space="preserve">4.14116477966309</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.24426412582397</t>
+    <t xml:space="preserve">4.14116525650024</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.24426460266113</t>
   </si>
   <si>
     <t xml:space="preserve">4.24856042861938</t>
   </si>
   <si>
-    <t xml:space="preserve">4.4332799911499</t>
+    <t xml:space="preserve">4.43328046798706</t>
   </si>
   <si>
     <t xml:space="preserve">4.4246883392334</t>
@@ -1901,22 +1901,22 @@
     <t xml:space="preserve">4.49342155456543</t>
   </si>
   <si>
-    <t xml:space="preserve">4.55356216430664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.48482942581177</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.53638029098511</t>
+    <t xml:space="preserve">4.55356311798096</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.48482990264893</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.53637981414795</t>
   </si>
   <si>
     <t xml:space="preserve">4.59652090072632</t>
   </si>
   <si>
-    <t xml:space="preserve">4.77694511413574</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.81131219863892</t>
+    <t xml:space="preserve">4.77694463729858</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.81131172180176</t>
   </si>
   <si>
     <t xml:space="preserve">4.69962072372437</t>
@@ -1925,55 +1925,55 @@
     <t xml:space="preserve">4.64807081222534</t>
   </si>
   <si>
-    <t xml:space="preserve">4.72539567947388</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.71680355072021</t>
+    <t xml:space="preserve">4.72539520263672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.71680402755737</t>
   </si>
   <si>
     <t xml:space="preserve">4.69102907180786</t>
   </si>
   <si>
-    <t xml:space="preserve">4.68243789672852</t>
+    <t xml:space="preserve">4.6824369430542</t>
   </si>
   <si>
     <t xml:space="preserve">4.70821189880371</t>
   </si>
   <si>
-    <t xml:space="preserve">4.6738452911377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.56215476989746</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.50201368331909</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.54497098922729</t>
+    <t xml:space="preserve">4.67384576797485</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.5621542930603</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.50201320648193</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.54497146606445</t>
   </si>
   <si>
     <t xml:space="preserve">4.51060485839844</t>
   </si>
   <si>
-    <t xml:space="preserve">4.5277886390686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.7683539390564</t>
+    <t xml:space="preserve">4.52778768539429</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.76835346221924</t>
   </si>
   <si>
     <t xml:space="preserve">4.66525363922119</t>
   </si>
   <si>
-    <t xml:space="preserve">4.61370420455933</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.73398733139038</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.639479637146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.23567247390747</t>
+    <t xml:space="preserve">4.61370468139648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.73398685455322</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.63947916030884</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.23567199707031</t>
   </si>
   <si>
     <t xml:space="preserve">4.15834856033325</t>
@@ -1982,13 +1982,13 @@
     <t xml:space="preserve">4.20130634307861</t>
   </si>
   <si>
-    <t xml:space="preserve">4.36454677581787</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.60511302947998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.11538982391357</t>
+    <t xml:space="preserve">4.36454725265503</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.60511255264282</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.11539030075073</t>
   </si>
   <si>
     <t xml:space="preserve">3.75024580955505</t>
@@ -1997,25 +1997,25 @@
     <t xml:space="preserve">3.47101783752441</t>
   </si>
   <si>
-    <t xml:space="preserve">3.36362242698669</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.31207275390625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.16601514816284</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.22186064720154</t>
+    <t xml:space="preserve">3.36362266540527</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.31207299232483</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.16601467132568</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.22186088562012</t>
   </si>
   <si>
     <t xml:space="preserve">2.80516672134399</t>
   </si>
   <si>
-    <t xml:space="preserve">2.91685795783997</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.86530828475952</t>
+    <t xml:space="preserve">2.91685771942139</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.86530804634094</t>
   </si>
   <si>
     <t xml:space="preserve">2.8867871761322</t>
@@ -2024,10 +2024,10 @@
     <t xml:space="preserve">2.73213815689087</t>
   </si>
   <si>
-    <t xml:space="preserve">2.66770076751709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.80087065696716</t>
+    <t xml:space="preserve">2.66770052909851</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.80087113380432</t>
   </si>
   <si>
     <t xml:space="preserve">2.61185503005981</t>
@@ -2036,16 +2036,16 @@
     <t xml:space="preserve">2.72354626655579</t>
   </si>
   <si>
-    <t xml:space="preserve">2.92115378379822</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.8137583732605</t>
+    <t xml:space="preserve">2.92115354537964</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.81375813484192</t>
   </si>
   <si>
     <t xml:space="preserve">2.70206713676453</t>
   </si>
   <si>
-    <t xml:space="preserve">2.65910863876343</t>
+    <t xml:space="preserve">2.65910911560059</t>
   </si>
   <si>
     <t xml:space="preserve">2.84382891654968</t>
@@ -2060,16 +2060,16 @@
     <t xml:space="preserve">2.70636296272278</t>
   </si>
   <si>
-    <t xml:space="preserve">2.71065855026245</t>
+    <t xml:space="preserve">2.71065878868103</t>
   </si>
   <si>
     <t xml:space="preserve">2.85242056846619</t>
   </si>
   <si>
-    <t xml:space="preserve">2.89108276367188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.92974519729614</t>
+    <t xml:space="preserve">2.89108300209045</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.9297456741333</t>
   </si>
   <si>
     <t xml:space="preserve">3.0070698261261</t>
@@ -2081,13 +2081,13 @@
     <t xml:space="preserve">2.93833708763123</t>
   </si>
   <si>
-    <t xml:space="preserve">2.94263243675232</t>
+    <t xml:space="preserve">2.9426326751709</t>
   </si>
   <si>
     <t xml:space="preserve">2.98129534721375</t>
   </si>
   <si>
-    <t xml:space="preserve">3.01136565208435</t>
+    <t xml:space="preserve">3.01136612892151</t>
   </si>
   <si>
     <t xml:space="preserve">2.94692850112915</t>
@@ -2105,22 +2105,22 @@
     <t xml:space="preserve">3.04143619537354</t>
   </si>
   <si>
-    <t xml:space="preserve">3.05002808570862</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.08439445495605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.13164877891541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.03284478187561</t>
+    <t xml:space="preserve">3.05002760887146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.08439421653748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.13164830207825</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.03284502029419</t>
   </si>
   <si>
     <t xml:space="preserve">3.09298610687256</t>
   </si>
   <si>
-    <t xml:space="preserve">3.19179010391235</t>
+    <t xml:space="preserve">3.19178986549377</t>
   </si>
   <si>
     <t xml:space="preserve">3.24763560295105</t>
@@ -2135,19 +2135,19 @@
     <t xml:space="preserve">3.18319821357727</t>
   </si>
   <si>
-    <t xml:space="preserve">3.13594484329224</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.11876130104065</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.307776927948</t>
+    <t xml:space="preserve">3.13594436645508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.11876106262207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.30777668952942</t>
   </si>
   <si>
     <t xml:space="preserve">3.38510179519653</t>
   </si>
   <si>
-    <t xml:space="preserve">3.4366512298584</t>
+    <t xml:space="preserve">3.43665146827698</t>
   </si>
   <si>
     <t xml:space="preserve">3.48390531539917</t>
@@ -2165,10 +2165,10 @@
     <t xml:space="preserve">3.29488945007324</t>
   </si>
   <si>
-    <t xml:space="preserve">3.19608592987061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.38080549240112</t>
+    <t xml:space="preserve">3.19608569145203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.3808057308197</t>
   </si>
   <si>
     <t xml:space="preserve">3.37650990486145</t>
@@ -2180,22 +2180,22 @@
     <t xml:space="preserve">3.3722140789032</t>
   </si>
   <si>
-    <t xml:space="preserve">3.42805957794189</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.44094729423523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.44524312019348</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.75857448577881</t>
+    <t xml:space="preserve">3.42805981636047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.44094753265381</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.4452428817749</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.75857496261597</t>
   </si>
   <si>
     <t xml:space="preserve">3.71435618400574</t>
   </si>
   <si>
-    <t xml:space="preserve">3.63034105300903</t>
+    <t xml:space="preserve">3.63034081459045</t>
   </si>
   <si>
     <t xml:space="preserve">3.58170080184937</t>
@@ -2204,37 +2204,37 @@
     <t xml:space="preserve">3.51979494094849</t>
   </si>
   <si>
-    <t xml:space="preserve">3.50210762023926</t>
+    <t xml:space="preserve">3.5021071434021</t>
   </si>
   <si>
     <t xml:space="preserve">3.43135786056519</t>
   </si>
   <si>
-    <t xml:space="preserve">3.44904518127441</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.36060810089111</t>
+    <t xml:space="preserve">3.44904541969299</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.36060786247253</t>
   </si>
   <si>
     <t xml:space="preserve">3.38713908195496</t>
   </si>
   <si>
-    <t xml:space="preserve">3.4180920124054</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.32081127166748</t>
+    <t xml:space="preserve">3.41809225082397</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.32081151008606</t>
   </si>
   <si>
     <t xml:space="preserve">3.33849883079529</t>
   </si>
   <si>
-    <t xml:space="preserve">3.31638932228088</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.27217078208923</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.28101468086243</t>
+    <t xml:space="preserve">3.31638956069946</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.27217102050781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.28101444244385</t>
   </si>
   <si>
     <t xml:space="preserve">3.22795271873474</t>
@@ -2270,19 +2270,19 @@
     <t xml:space="preserve">3.04223465919495</t>
   </si>
   <si>
-    <t xml:space="preserve">3.04665637016296</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.0776093006134</t>
+    <t xml:space="preserve">3.04665613174438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.07760953903198</t>
   </si>
   <si>
     <t xml:space="preserve">3.05992197990417</t>
   </si>
   <si>
-    <t xml:space="preserve">2.98032832145691</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.9626407623291</t>
+    <t xml:space="preserve">2.98032855987549</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.96264123916626</t>
   </si>
   <si>
     <t xml:space="preserve">2.94495368003845</t>
@@ -2303,7 +2303,7 @@
     <t xml:space="preserve">2.98475050926208</t>
   </si>
   <si>
-    <t xml:space="preserve">2.9051570892334</t>
+    <t xml:space="preserve">2.90515732765198</t>
   </si>
   <si>
     <t xml:space="preserve">2.83440756797791</t>
@@ -2324,10 +2324,10 @@
     <t xml:space="preserve">2.84767317771912</t>
   </si>
   <si>
-    <t xml:space="preserve">2.82998609542847</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.79461121559143</t>
+    <t xml:space="preserve">2.82998561859131</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.79461073875427</t>
   </si>
   <si>
     <t xml:space="preserve">2.91842269897461</t>
@@ -2339,10 +2339,10 @@
     <t xml:space="preserve">2.79903268814087</t>
   </si>
   <si>
-    <t xml:space="preserve">2.8078761100769</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.75923609733582</t>
+    <t xml:space="preserve">2.80787634849548</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.75923585891724</t>
   </si>
   <si>
     <t xml:space="preserve">2.72386121749878</t>
@@ -2354,7 +2354,7 @@
     <t xml:space="preserve">2.68406462669373</t>
   </si>
   <si>
-    <t xml:space="preserve">2.63542413711548</t>
+    <t xml:space="preserve">2.63542437553406</t>
   </si>
   <si>
     <t xml:space="preserve">2.61773705482483</t>
@@ -2366,25 +2366,25 @@
     <t xml:space="preserve">2.54698729515076</t>
   </si>
   <si>
-    <t xml:space="preserve">2.56467437744141</t>
+    <t xml:space="preserve">2.56467461585999</t>
   </si>
   <si>
     <t xml:space="preserve">2.5514087677002</t>
   </si>
   <si>
-    <t xml:space="preserve">2.49392485618591</t>
+    <t xml:space="preserve">2.49392461776733</t>
   </si>
   <si>
     <t xml:space="preserve">2.5735182762146</t>
   </si>
   <si>
-    <t xml:space="preserve">2.97148489952087</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.95379757881165</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.00243806838989</t>
+    <t xml:space="preserve">2.97148466110229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.95379734039307</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.00243782997131</t>
   </si>
   <si>
     <t xml:space="preserve">3.17931222915649</t>
@@ -2393,19 +2393,19 @@
     <t xml:space="preserve">3.1704683303833</t>
   </si>
   <si>
-    <t xml:space="preserve">3.19257736206055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.28985857963562</t>
+    <t xml:space="preserve">3.19257760047913</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.28985810279846</t>
   </si>
   <si>
     <t xml:space="preserve">3.29870200157166</t>
   </si>
   <si>
-    <t xml:space="preserve">3.4799976348877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.4136700630188</t>
+    <t xml:space="preserve">3.47999811172485</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.41367030143738</t>
   </si>
   <si>
     <t xml:space="preserve">3.48442006111145</t>
@@ -2414,43 +2414,43 @@
     <t xml:space="preserve">3.45788884162903</t>
   </si>
   <si>
-    <t xml:space="preserve">3.49326348304749</t>
+    <t xml:space="preserve">3.49326395988464</t>
   </si>
   <si>
     <t xml:space="preserve">3.51095104217529</t>
   </si>
   <si>
-    <t xml:space="preserve">3.44462299346924</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.42693543434143</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.55516958236694</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.67898154258728</t>
+    <t xml:space="preserve">3.4446234703064</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.42693567276001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.55516934394836</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.6789813041687</t>
   </si>
   <si>
     <t xml:space="preserve">3.72320008277893</t>
   </si>
   <si>
-    <t xml:space="preserve">3.74973082542419</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.80279350280762</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.65687251091003</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.66129374504089</t>
+    <t xml:space="preserve">3.74973106384277</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.80279397964478</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.65687227249146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.66129398345947</t>
   </si>
   <si>
     <t xml:space="preserve">3.65245032310486</t>
   </si>
   <si>
-    <t xml:space="preserve">3.62591910362244</t>
+    <t xml:space="preserve">3.62591886520386</t>
   </si>
   <si>
     <t xml:space="preserve">3.60823178291321</t>
@@ -2462,22 +2462,22 @@
     <t xml:space="preserve">3.53748226165771</t>
   </si>
   <si>
-    <t xml:space="preserve">3.57285714149475</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.5065290927887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.5905442237854</t>
+    <t xml:space="preserve">3.57285690307617</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.50652933120728</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.59054446220398</t>
   </si>
   <si>
     <t xml:space="preserve">3.57727885246277</t>
   </si>
   <si>
-    <t xml:space="preserve">3.74530911445618</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.74088764190674</t>
+    <t xml:space="preserve">3.74530935287476</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.74088740348816</t>
   </si>
   <si>
     <t xml:space="preserve">3.73204374313354</t>
@@ -2486,61 +2486,61 @@
     <t xml:space="preserve">3.7055127620697</t>
   </si>
   <si>
-    <t xml:space="preserve">3.77626204490662</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.83816838264465</t>
+    <t xml:space="preserve">3.7762622833252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.83816862106323</t>
   </si>
   <si>
     <t xml:space="preserve">3.68340349197388</t>
   </si>
   <si>
-    <t xml:space="preserve">3.76741886138916</t>
+    <t xml:space="preserve">3.76741862297058</t>
   </si>
   <si>
     <t xml:space="preserve">3.78068399429321</t>
   </si>
   <si>
-    <t xml:space="preserve">3.76299667358398</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.77183985710144</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.71877813339233</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.68782544136047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.59938812255859</t>
+    <t xml:space="preserve">3.76299691200256</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.7718403339386</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.71877789497375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.68782496452332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.59938788414001</t>
   </si>
   <si>
     <t xml:space="preserve">3.66571569442749</t>
   </si>
   <si>
-    <t xml:space="preserve">3.70993423461914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.78510594367981</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.92660522460938</t>
+    <t xml:space="preserve">3.70993447303772</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.78510618209839</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.9266049861908</t>
   </si>
   <si>
     <t xml:space="preserve">3.93987083435059</t>
   </si>
   <si>
-    <t xml:space="preserve">3.99735474586487</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.01079893112183</t>
+    <t xml:space="preserve">3.99735450744629</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.01079845428467</t>
   </si>
   <si>
     <t xml:space="preserve">4.09594440460205</t>
   </si>
   <si>
-    <t xml:space="preserve">4.17212677001953</t>
+    <t xml:space="preserve">4.17212724685669</t>
   </si>
   <si>
     <t xml:space="preserve">4.1631646156311</t>
@@ -2555,31 +2555,31 @@
     <t xml:space="preserve">4.14075756072998</t>
   </si>
   <si>
-    <t xml:space="preserve">4.10490703582764</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.06905603408813</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.03320550918579</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.9794294834137</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.028724193573</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.0556116104126</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.08698129653931</t>
+    <t xml:space="preserve">4.10490655899048</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.06905651092529</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.03320503234863</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.97942924499512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.02872371673584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.05561256408691</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.08698177337646</t>
   </si>
   <si>
     <t xml:space="preserve">3.97494792938232</t>
   </si>
   <si>
-    <t xml:space="preserve">4.00183629989624</t>
+    <t xml:space="preserve">4.00183582305908</t>
   </si>
   <si>
     <t xml:space="preserve">4.01528024673462</t>
@@ -2588,22 +2588,22 @@
     <t xml:space="preserve">3.96150398254395</t>
   </si>
   <si>
-    <t xml:space="preserve">3.98839163780212</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.9525408744812</t>
+    <t xml:space="preserve">3.98839139938354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.95254135131836</t>
   </si>
   <si>
     <t xml:space="preserve">3.96598529815674</t>
   </si>
   <si>
-    <t xml:space="preserve">4.04216861724854</t>
+    <t xml:space="preserve">4.04216814041138</t>
   </si>
   <si>
     <t xml:space="preserve">4.07801914215088</t>
   </si>
   <si>
-    <t xml:space="preserve">4.11835050582886</t>
+    <t xml:space="preserve">4.11835098266602</t>
   </si>
   <si>
     <t xml:space="preserve">4.17660808563232</t>
@@ -2612,19 +2612,19 @@
     <t xml:space="preserve">4.11386966705322</t>
   </si>
   <si>
-    <t xml:space="preserve">4.10938787460327</t>
+    <t xml:space="preserve">4.10938835144043</t>
   </si>
   <si>
     <t xml:space="preserve">4.06009340286255</t>
   </si>
   <si>
-    <t xml:space="preserve">4.19453287124634</t>
+    <t xml:space="preserve">4.1945333480835</t>
   </si>
   <si>
     <t xml:space="preserve">4.21245861053467</t>
   </si>
   <si>
-    <t xml:space="preserve">4.14972066879272</t>
+    <t xml:space="preserve">4.14972019195557</t>
   </si>
   <si>
     <t xml:space="preserve">4.12283182144165</t>
@@ -2633,13 +2633,13 @@
     <t xml:space="preserve">4.03768682479858</t>
   </si>
   <si>
-    <t xml:space="preserve">4.01976156234741</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.06457424163818</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.20797729492188</t>
+    <t xml:space="preserve">4.01976108551025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.06457471847534</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.20797777175903</t>
   </si>
   <si>
     <t xml:space="preserve">4.23038387298584</t>
@@ -2651,13 +2651,13 @@
     <t xml:space="preserve">4.20349645614624</t>
   </si>
   <si>
-    <t xml:space="preserve">3.92565369606018</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.90772795677185</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.88083982467651</t>
+    <t xml:space="preserve">3.9256534576416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.90772819519043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.88084030151367</t>
   </si>
   <si>
     <t xml:space="preserve">3.87635850906372</t>
@@ -2666,61 +2666,61 @@
     <t xml:space="preserve">3.80913805961609</t>
   </si>
   <si>
-    <t xml:space="preserve">3.71503019332886</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.66573572158813</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.83154511451721</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.93461585044861</t>
+    <t xml:space="preserve">3.71503043174744</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.66573548316956</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.83154487609863</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.93461561203003</t>
   </si>
   <si>
     <t xml:space="preserve">3.94357872009277</t>
   </si>
   <si>
-    <t xml:space="preserve">4.04664945602417</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.99287343025208</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.98391079902649</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.02424287796021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.85395216941833</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.93013501167297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.97046613693237</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.10042524337769</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.15420246124268</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.09146308898926</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.22590351104736</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.26623487472534</t>
+    <t xml:space="preserve">4.04664897918701</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.9928731918335</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.98391103744507</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.02424240112305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.85395193099976</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.93013477325439</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.97046661376953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.10042572021484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.15420150756836</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.0914626121521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.22590303421021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.2662353515625</t>
   </si>
   <si>
     <t xml:space="preserve">4.24382829666138</t>
   </si>
   <si>
-    <t xml:space="preserve">4.13179492950439</t>
+    <t xml:space="preserve">4.13179540634155</t>
   </si>
   <si>
     <t xml:space="preserve">4.1273136138916</t>
@@ -2732,25 +2732,25 @@
     <t xml:space="preserve">4.19005250930786</t>
   </si>
   <si>
-    <t xml:space="preserve">4.2931227684021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.40515613555908</t>
+    <t xml:space="preserve">4.29312324523926</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.40515661239624</t>
   </si>
   <si>
     <t xml:space="preserve">4.43652582168579</t>
   </si>
   <si>
-    <t xml:space="preserve">4.48133945465088</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.53511524200439</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.55304050445557</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.56200361251831</t>
+    <t xml:space="preserve">4.48133897781372</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.53511571884155</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.55304098129272</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.56200408935547</t>
   </si>
   <si>
     <t xml:space="preserve">4.50822782516479</t>
@@ -2759,40 +2759,40 @@
     <t xml:space="preserve">4.45445108413696</t>
   </si>
   <si>
-    <t xml:space="preserve">4.43204498291016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.49926471710205</t>
+    <t xml:space="preserve">4.432044506073</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.49926519393921</t>
   </si>
   <si>
     <t xml:space="preserve">4.49030208587646</t>
   </si>
   <si>
-    <t xml:space="preserve">4.51718997955322</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.633704662323</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.59785461425781</t>
+    <t xml:space="preserve">4.51719045639038</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.63370513916016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.59785413742065</t>
   </si>
   <si>
     <t xml:space="preserve">4.47685766220093</t>
   </si>
   <si>
-    <t xml:space="preserve">4.57096576690674</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.61577939987183</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.64266681671143</t>
+    <t xml:space="preserve">4.5709662437439</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.61577987670898</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.64266729354858</t>
   </si>
   <si>
     <t xml:space="preserve">4.39171266555786</t>
   </si>
   <si>
-    <t xml:space="preserve">4.44997024536133</t>
+    <t xml:space="preserve">4.44996976852417</t>
   </si>
   <si>
     <t xml:space="preserve">4.27519798278809</t>
@@ -2801,25 +2801,25 @@
     <t xml:space="preserve">4.58889150619507</t>
   </si>
   <si>
-    <t xml:space="preserve">4.66059303283691</t>
+    <t xml:space="preserve">4.66059255599976</t>
   </si>
   <si>
     <t xml:space="preserve">4.65163040161133</t>
   </si>
   <si>
-    <t xml:space="preserve">4.71436882019043</t>
+    <t xml:space="preserve">4.71436929702759</t>
   </si>
   <si>
     <t xml:space="preserve">4.75918245315552</t>
   </si>
   <si>
-    <t xml:space="preserve">4.7681450843811</t>
+    <t xml:space="preserve">4.76814556121826</t>
   </si>
   <si>
     <t xml:space="preserve">4.89362239837646</t>
   </si>
   <si>
-    <t xml:space="preserve">4.92051029205322</t>
+    <t xml:space="preserve">4.92051076889038</t>
   </si>
   <si>
     <t xml:space="preserve">4.88465976715088</t>
@@ -2831,10 +2831,10 @@
     <t xml:space="preserve">5.01910018920898</t>
   </si>
   <si>
-    <t xml:space="preserve">5.14457750320435</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.31486845016479</t>
+    <t xml:space="preserve">5.14457702636719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.31486797332764</t>
   </si>
   <si>
     <t xml:space="preserve">5.37760734558105</t>
@@ -2843,37 +2843,37 @@
     <t xml:space="preserve">5.35968160629272</t>
   </si>
   <si>
-    <t xml:space="preserve">5.16250324249268</t>
+    <t xml:space="preserve">5.16250276565552</t>
   </si>
   <si>
     <t xml:space="preserve">5.0459885597229</t>
   </si>
   <si>
-    <t xml:space="preserve">5.15354061126709</t>
+    <t xml:space="preserve">5.15354013442993</t>
   </si>
   <si>
     <t xml:space="preserve">5.26109218597412</t>
   </si>
   <si>
-    <t xml:space="preserve">5.27901792526245</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.51204776763916</t>
+    <t xml:space="preserve">5.27901697158813</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.512047290802</t>
   </si>
   <si>
     <t xml:space="preserve">5.47619676589966</t>
   </si>
   <si>
-    <t xml:space="preserve">5.50308465957642</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.29694318771362</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.19835329055786</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.18042898178101</t>
+    <t xml:space="preserve">5.50308418273926</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.29694271087646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.19835376739502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.18042850494385</t>
   </si>
   <si>
     <t xml:space="preserve">5.0728759765625</t>
@@ -2882,22 +2882,22 @@
     <t xml:space="preserve">5.09080123901367</t>
   </si>
   <si>
-    <t xml:space="preserve">4.99221181869507</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.75021934509277</t>
+    <t xml:space="preserve">4.99221277236938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.75022029876709</t>
   </si>
   <si>
     <t xml:space="preserve">4.80399608612061</t>
   </si>
   <si>
-    <t xml:space="preserve">4.92947292327881</t>
+    <t xml:space="preserve">4.92947340011597</t>
   </si>
   <si>
     <t xml:space="preserve">4.83984661102295</t>
   </si>
   <si>
-    <t xml:space="preserve">4.9742865562439</t>
+    <t xml:space="preserve">4.97428703308105</t>
   </si>
   <si>
     <t xml:space="preserve">4.90258502960205</t>
@@ -2912,28 +2912,28 @@
     <t xml:space="preserve">4.95636177062988</t>
   </si>
   <si>
-    <t xml:space="preserve">4.79503345489502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.74125671386719</t>
+    <t xml:space="preserve">4.79503297805786</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.7412576675415</t>
   </si>
   <si>
     <t xml:space="preserve">4.70540618896484</t>
   </si>
   <si>
-    <t xml:space="preserve">4.52615261077881</t>
+    <t xml:space="preserve">4.52615308761597</t>
   </si>
   <si>
     <t xml:space="preserve">4.41860008239746</t>
   </si>
   <si>
-    <t xml:space="preserve">4.3648247718811</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.23934745788574</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.85777139663696</t>
+    <t xml:space="preserve">4.36482429504395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.23934650421143</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.85777187347412</t>
   </si>
   <si>
     <t xml:space="preserve">4.91154766082764</t>
@@ -2948,7 +2948,7 @@
     <t xml:space="preserve">5.22524166107178</t>
   </si>
   <si>
-    <t xml:space="preserve">5.30590629577637</t>
+    <t xml:space="preserve">5.30590581893921</t>
   </si>
   <si>
     <t xml:space="preserve">5.42242097854614</t>
@@ -2957,7 +2957,7 @@
     <t xml:space="preserve">5.28798055648804</t>
   </si>
   <si>
-    <t xml:space="preserve">5.43138265609741</t>
+    <t xml:space="preserve">5.43138313293457</t>
   </si>
   <si>
     <t xml:space="preserve">5.55686044692993</t>
@@ -2966,7 +2966,7 @@
     <t xml:space="preserve">5.62856245040894</t>
   </si>
   <si>
-    <t xml:space="preserve">5.52100992202759</t>
+    <t xml:space="preserve">5.52100944519043</t>
   </si>
   <si>
     <t xml:space="preserve">5.61959934234619</t>
@@ -2978,22 +2978,22 @@
     <t xml:space="preserve">5.37441253662109</t>
   </si>
   <si>
-    <t xml:space="preserve">5.47495365142822</t>
+    <t xml:space="preserve">5.47495412826538</t>
   </si>
   <si>
     <t xml:space="preserve">5.46581411361694</t>
   </si>
   <si>
-    <t xml:space="preserve">5.48409414291382</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.63947725296021</t>
+    <t xml:space="preserve">5.48409461975098</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.63947677612305</t>
   </si>
   <si>
     <t xml:space="preserve">5.75829935073853</t>
   </si>
   <si>
-    <t xml:space="preserve">5.80399942398071</t>
+    <t xml:space="preserve">5.80399990081787</t>
   </si>
   <si>
     <t xml:space="preserve">5.65775728225708</t>
@@ -3008,19 +3008,19 @@
     <t xml:space="preserve">5.40183258056641</t>
   </si>
   <si>
-    <t xml:space="preserve">5.63033628463745</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.61205673217773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.8222804069519</t>
+    <t xml:space="preserve">5.63033676147461</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.61205625534058</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.82227993011475</t>
   </si>
   <si>
     <t xml:space="preserve">5.84056043624878</t>
   </si>
   <si>
-    <t xml:space="preserve">5.88626146316528</t>
+    <t xml:space="preserve">5.88626098632812</t>
   </si>
   <si>
     <t xml:space="preserve">5.93196201324463</t>
@@ -3044,10 +3044,10 @@
     <t xml:space="preserve">6.07820463180542</t>
   </si>
   <si>
-    <t xml:space="preserve">5.9136815071106</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.68517780303955</t>
+    <t xml:space="preserve">5.91368103027344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.68517732620239</t>
   </si>
   <si>
     <t xml:space="preserve">5.785719871521</t>
@@ -3056,7 +3056,7 @@
     <t xml:space="preserve">5.7308783531189</t>
   </si>
   <si>
-    <t xml:space="preserve">5.67603826522827</t>
+    <t xml:space="preserve">5.67603731155396</t>
   </si>
   <si>
     <t xml:space="preserve">5.69431781768799</t>
@@ -3065,10 +3065,10 @@
     <t xml:space="preserve">5.66689729690552</t>
   </si>
   <si>
-    <t xml:space="preserve">5.42925357818604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.4201135635376</t>
+    <t xml:space="preserve">5.42925310134888</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.42011308670044</t>
   </si>
   <si>
     <t xml:space="preserve">5.33785200119019</t>
@@ -3086,7 +3086,7 @@
     <t xml:space="preserve">5.39269304275513</t>
   </si>
   <si>
-    <t xml:space="preserve">5.3652720451355</t>
+    <t xml:space="preserve">5.36527252197266</t>
   </si>
   <si>
     <t xml:space="preserve">5.2830114364624</t>
@@ -3095,10 +3095,10 @@
     <t xml:space="preserve">5.2281699180603</t>
   </si>
   <si>
-    <t xml:space="preserve">5.21902990341187</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.15504884719849</t>
+    <t xml:space="preserve">5.21902942657471</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.15504837036133</t>
   </si>
   <si>
     <t xml:space="preserve">5.10020780563354</t>
@@ -3107,7 +3107,7 @@
     <t xml:space="preserve">5.10934782028198</t>
   </si>
   <si>
-    <t xml:space="preserve">5.08192777633667</t>
+    <t xml:space="preserve">5.08192729949951</t>
   </si>
   <si>
     <t xml:space="preserve">5.03622674942017</t>
@@ -3122,19 +3122,19 @@
     <t xml:space="preserve">5.13676834106445</t>
   </si>
   <si>
-    <t xml:space="preserve">5.07278728485107</t>
+    <t xml:space="preserve">5.07278776168823</t>
   </si>
   <si>
     <t xml:space="preserve">5.02708625793457</t>
   </si>
   <si>
-    <t xml:space="preserve">5.0453667640686</t>
+    <t xml:space="preserve">5.04536724090576</t>
   </si>
   <si>
     <t xml:space="preserve">4.99052572250366</t>
   </si>
   <si>
-    <t xml:space="preserve">5.0088062286377</t>
+    <t xml:space="preserve">5.00880575180054</t>
   </si>
   <si>
     <t xml:space="preserve">5.0545072555542</t>
@@ -3155,10 +3155,10 @@
     <t xml:space="preserve">4.93568515777588</t>
   </si>
   <si>
-    <t xml:space="preserve">4.89912462234497</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.88084411621094</t>
+    <t xml:space="preserve">4.89912414550781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.8808445930481</t>
   </si>
   <si>
     <t xml:space="preserve">4.85342359542847</t>
@@ -3170,34 +3170,34 @@
     <t xml:space="preserve">4.73460102081299</t>
   </si>
   <si>
-    <t xml:space="preserve">4.75288200378418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.69804048538208</t>
+    <t xml:space="preserve">4.75288152694702</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.69804096221924</t>
   </si>
   <si>
     <t xml:space="preserve">4.57921886444092</t>
   </si>
   <si>
-    <t xml:space="preserve">4.71632146835327</t>
+    <t xml:space="preserve">4.71632099151611</t>
   </si>
   <si>
     <t xml:space="preserve">4.67976045608521</t>
   </si>
   <si>
-    <t xml:space="preserve">4.84428310394287</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.80772256851196</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.57007884979248</t>
+    <t xml:space="preserve">4.84428358078003</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.80772304534912</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.57007837295532</t>
   </si>
   <si>
     <t xml:space="preserve">4.72546148300171</t>
   </si>
   <si>
-    <t xml:space="preserve">4.6889009475708</t>
+    <t xml:space="preserve">4.68890047073364</t>
   </si>
   <si>
     <t xml:space="preserve">4.67062044143677</t>
@@ -3212,16 +3212,16 @@
     <t xml:space="preserve">4.56093835830688</t>
   </si>
   <si>
-    <t xml:space="preserve">4.58835887908936</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.55179834365845</t>
+    <t xml:space="preserve">4.58835935592651</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.55179786682129</t>
   </si>
   <si>
     <t xml:space="preserve">4.48781728744507</t>
   </si>
   <si>
-    <t xml:space="preserve">4.53808832168579</t>
+    <t xml:space="preserve">4.53808784484863</t>
   </si>
   <si>
     <t xml:space="preserve">4.46953678131104</t>
@@ -3230,10 +3230,10 @@
     <t xml:space="preserve">4.50152778625488</t>
   </si>
   <si>
-    <t xml:space="preserve">4.49695777893066</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.40555572509766</t>
+    <t xml:space="preserve">4.49695730209351</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.40555620193481</t>
   </si>
   <si>
     <t xml:space="preserve">4.43297624588013</t>
@@ -3245,16 +3245,16 @@
     <t xml:space="preserve">4.36899518966675</t>
   </si>
   <si>
-    <t xml:space="preserve">4.29130363464355</t>
+    <t xml:space="preserve">4.29130411148071</t>
   </si>
   <si>
     <t xml:space="preserve">4.20447206497192</t>
   </si>
   <si>
-    <t xml:space="preserve">4.47867679595947</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.48324775695801</t>
+    <t xml:space="preserve">4.47867727279663</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.48324728012085</t>
   </si>
   <si>
     <t xml:space="preserve">4.79858255386353</t>
@@ -3263,7 +3263,7 @@
     <t xml:space="preserve">4.87170362472534</t>
   </si>
   <si>
-    <t xml:space="preserve">4.83514308929443</t>
+    <t xml:space="preserve">4.83514356613159</t>
   </si>
   <si>
     <t xml:space="preserve">5.17332887649536</t>
@@ -3272,13 +3272,13 @@
     <t xml:space="preserve">5.32871150970459</t>
   </si>
   <si>
-    <t xml:space="preserve">5.19160938262939</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.25559043884277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.38355302810669</t>
+    <t xml:space="preserve">5.19160890579224</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.25559091567993</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.38355255126953</t>
   </si>
   <si>
     <t xml:space="preserve">4.97224569320679</t>
@@ -3299,7 +3299,7 @@
     <t xml:space="preserve">5.09106779098511</t>
   </si>
   <si>
-    <t xml:space="preserve">4.98138570785522</t>
+    <t xml:space="preserve">4.98138523101807</t>
   </si>
   <si>
     <t xml:space="preserve">4.92654466629028</t>
@@ -3320,7 +3320,7 @@
     <t xml:space="preserve">5.23730993270874</t>
   </si>
   <si>
-    <t xml:space="preserve">5.27387046813965</t>
+    <t xml:space="preserve">5.27387094497681</t>
   </si>
   <si>
     <t xml:space="preserve">5.31957197189331</t>
@@ -7973,7 +7973,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G121" t="s">
-        <v>96</v>
+        <v>114</v>
       </c>
       <c r="H121" t="s">
         <v>9</v>
@@ -7999,7 +7999,7 @@
         <v>3.10999989509583</v>
       </c>
       <c r="G122" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="H122" t="s">
         <v>9</v>
@@ -8025,7 +8025,7 @@
         <v>3.08599996566772</v>
       </c>
       <c r="G123" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="H123" t="s">
         <v>9</v>
@@ -8051,7 +8051,7 @@
         <v>2.96000003814697</v>
       </c>
       <c r="G124" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="H124" t="s">
         <v>9</v>
@@ -8077,7 +8077,7 @@
         <v>2.70000004768372</v>
       </c>
       <c r="G125" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="H125" t="s">
         <v>9</v>
@@ -8103,7 +8103,7 @@
         <v>2.75</v>
       </c>
       <c r="G126" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="H126" t="s">
         <v>9</v>
@@ -8129,7 +8129,7 @@
         <v>2.82399988174438</v>
       </c>
       <c r="G127" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="H127" t="s">
         <v>9</v>
@@ -8155,7 +8155,7 @@
         <v>2.79800009727478</v>
       </c>
       <c r="G128" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="H128" t="s">
         <v>9</v>
@@ -8181,7 +8181,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G129" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="H129" t="s">
         <v>9</v>
@@ -8207,7 +8207,7 @@
         <v>2.92000007629395</v>
       </c>
       <c r="G130" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="H130" t="s">
         <v>9</v>
@@ -8233,7 +8233,7 @@
         <v>2.8199999332428</v>
       </c>
       <c r="G131" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="H131" t="s">
         <v>9</v>
@@ -8259,7 +8259,7 @@
         <v>2.69799995422363</v>
       </c>
       <c r="G132" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="H132" t="s">
         <v>9</v>
@@ -8285,7 +8285,7 @@
         <v>2.73799991607666</v>
       </c>
       <c r="G133" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="H133" t="s">
         <v>9</v>
@@ -8311,7 +8311,7 @@
         <v>2.80999994277954</v>
       </c>
       <c r="G134" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="H134" t="s">
         <v>9</v>
@@ -8337,7 +8337,7 @@
         <v>2.83599996566772</v>
       </c>
       <c r="G135" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="H135" t="s">
         <v>9</v>
@@ -8363,7 +8363,7 @@
         <v>2.86800003051758</v>
       </c>
       <c r="G136" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="H136" t="s">
         <v>9</v>
@@ -8389,7 +8389,7 @@
         <v>2.87400007247925</v>
       </c>
       <c r="G137" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="H137" t="s">
         <v>9</v>
@@ -8415,7 +8415,7 @@
         <v>2.86999988555908</v>
       </c>
       <c r="G138" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="H138" t="s">
         <v>9</v>
@@ -8441,7 +8441,7 @@
         <v>2.85400009155273</v>
       </c>
       <c r="G139" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="H139" t="s">
         <v>9</v>
@@ -8467,7 +8467,7 @@
         <v>2.85400009155273</v>
       </c>
       <c r="G140" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="H140" t="s">
         <v>9</v>
@@ -8493,7 +8493,7 @@
         <v>2.9300000667572</v>
       </c>
       <c r="G141" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="H141" t="s">
         <v>9</v>
@@ -8519,7 +8519,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G142" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="H142" t="s">
         <v>9</v>
@@ -8545,7 +8545,7 @@
         <v>3.13000011444092</v>
       </c>
       <c r="G143" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="H143" t="s">
         <v>9</v>
@@ -8571,7 +8571,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G144" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="H144" t="s">
         <v>9</v>
@@ -8623,7 +8623,7 @@
         <v>3.56399989128113</v>
       </c>
       <c r="G146" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="H146" t="s">
         <v>9</v>
@@ -8649,7 +8649,7 @@
         <v>3.49200010299683</v>
       </c>
       <c r="G147" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="H147" t="s">
         <v>9</v>
@@ -8701,7 +8701,7 @@
         <v>3.46000003814697</v>
       </c>
       <c r="G149" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="H149" t="s">
         <v>9</v>
@@ -8727,7 +8727,7 @@
         <v>3.19400000572205</v>
       </c>
       <c r="G150" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="H150" t="s">
         <v>9</v>
@@ -8753,7 +8753,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G151" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="H151" t="s">
         <v>9</v>
@@ -8857,7 +8857,7 @@
         <v>3.17000007629395</v>
       </c>
       <c r="G155" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="H155" t="s">
         <v>9</v>
@@ -8883,7 +8883,7 @@
         <v>3.17000007629395</v>
       </c>
       <c r="G156" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="H156" t="s">
         <v>9</v>
@@ -8909,7 +8909,7 @@
         <v>3.16599988937378</v>
       </c>
       <c r="G157" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="H157" t="s">
         <v>9</v>
@@ -8935,7 +8935,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G158" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="H158" t="s">
         <v>9</v>
@@ -8961,7 +8961,7 @@
         <v>3.15799999237061</v>
       </c>
       <c r="G159" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="H159" t="s">
         <v>9</v>
@@ -8987,7 +8987,7 @@
         <v>3.1159999370575</v>
       </c>
       <c r="G160" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="H160" t="s">
         <v>9</v>
@@ -9013,7 +9013,7 @@
         <v>3.10999989509583</v>
       </c>
       <c r="G161" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="H161" t="s">
         <v>9</v>
@@ -9039,7 +9039,7 @@
         <v>3.12199997901917</v>
       </c>
       <c r="G162" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="H162" t="s">
         <v>9</v>
@@ -9065,7 +9065,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G163" t="s">
-        <v>96</v>
+        <v>114</v>
       </c>
       <c r="H163" t="s">
         <v>9</v>
@@ -9091,7 +9091,7 @@
         <v>3.10999989509583</v>
       </c>
       <c r="G164" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="H164" t="s">
         <v>9</v>
@@ -9117,7 +9117,7 @@
         <v>3.10999989509583</v>
       </c>
       <c r="G165" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="H165" t="s">
         <v>9</v>
@@ -9143,7 +9143,7 @@
         <v>3.24399995803833</v>
       </c>
       <c r="G166" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="H166" t="s">
         <v>9</v>
@@ -9169,7 +9169,7 @@
         <v>3.23600006103516</v>
       </c>
       <c r="G167" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="H167" t="s">
         <v>9</v>
@@ -9195,7 +9195,7 @@
         <v>3.24399995803833</v>
       </c>
       <c r="G168" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="H168" t="s">
         <v>9</v>
@@ -9221,7 +9221,7 @@
         <v>3.25600004196167</v>
       </c>
       <c r="G169" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="H169" t="s">
         <v>9</v>
@@ -9247,7 +9247,7 @@
         <v>3.26399993896484</v>
       </c>
       <c r="G170" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="H170" t="s">
         <v>9</v>
@@ -9273,7 +9273,7 @@
         <v>3.24600005149841</v>
       </c>
       <c r="G171" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="H171" t="s">
         <v>9</v>
@@ -9299,7 +9299,7 @@
         <v>3.25</v>
       </c>
       <c r="G172" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="H172" t="s">
         <v>9</v>
@@ -9325,7 +9325,7 @@
         <v>3.31200003623962</v>
       </c>
       <c r="G173" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="H173" t="s">
         <v>9</v>
@@ -9351,7 +9351,7 @@
         <v>3.39199995994568</v>
       </c>
       <c r="G174" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="H174" t="s">
         <v>9</v>
@@ -9377,7 +9377,7 @@
         <v>3.43600010871887</v>
       </c>
       <c r="G175" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="H175" t="s">
         <v>9</v>
@@ -9403,7 +9403,7 @@
         <v>3.43600010871887</v>
       </c>
       <c r="G176" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="H176" t="s">
         <v>9</v>
@@ -9455,7 +9455,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G178" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="H178" t="s">
         <v>9</v>
@@ -9481,7 +9481,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G179" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="H179" t="s">
         <v>9</v>
@@ -9507,7 +9507,7 @@
         <v>3.26600003242493</v>
       </c>
       <c r="G180" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="H180" t="s">
         <v>9</v>
@@ -9533,7 +9533,7 @@
         <v>3.26999998092651</v>
       </c>
       <c r="G181" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="H181" t="s">
         <v>9</v>
@@ -9559,7 +9559,7 @@
         <v>3.37400007247925</v>
       </c>
       <c r="G182" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="H182" t="s">
         <v>9</v>
@@ -9585,7 +9585,7 @@
         <v>3.40599989891052</v>
       </c>
       <c r="G183" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="H183" t="s">
         <v>9</v>
@@ -9611,7 +9611,7 @@
         <v>3.32999992370605</v>
       </c>
       <c r="G184" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="H184" t="s">
         <v>9</v>
@@ -9637,7 +9637,7 @@
         <v>3.35599994659424</v>
       </c>
       <c r="G185" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="H185" t="s">
         <v>9</v>
@@ -9663,7 +9663,7 @@
         <v>3.37199997901917</v>
       </c>
       <c r="G186" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="H186" t="s">
         <v>9</v>
@@ -9689,7 +9689,7 @@
         <v>3.40799999237061</v>
       </c>
       <c r="G187" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="H187" t="s">
         <v>9</v>
@@ -9715,7 +9715,7 @@
         <v>3.44600009918213</v>
       </c>
       <c r="G188" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="H188" t="s">
         <v>9</v>
@@ -9741,7 +9741,7 @@
         <v>3.32999992370605</v>
       </c>
       <c r="G189" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="H189" t="s">
         <v>9</v>
@@ -9767,7 +9767,7 @@
         <v>3.31599998474121</v>
       </c>
       <c r="G190" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="H190" t="s">
         <v>9</v>
@@ -9793,7 +9793,7 @@
         <v>3.28200006484985</v>
       </c>
       <c r="G191" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="H191" t="s">
         <v>9</v>
@@ -9819,7 +9819,7 @@
         <v>3.25799989700317</v>
       </c>
       <c r="G192" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="H192" t="s">
         <v>9</v>
@@ -9845,7 +9845,7 @@
         <v>3.23000001907349</v>
       </c>
       <c r="G193" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="H193" t="s">
         <v>9</v>
@@ -9871,7 +9871,7 @@
         <v>3.19600009918213</v>
       </c>
       <c r="G194" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="H194" t="s">
         <v>9</v>
@@ -9923,7 +9923,7 @@
         <v>3.22000002861023</v>
       </c>
       <c r="G196" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="H196" t="s">
         <v>9</v>
@@ -10001,7 +10001,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G199" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="H199" t="s">
         <v>9</v>
@@ -10027,7 +10027,7 @@
         <v>3.24000000953674</v>
       </c>
       <c r="G200" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="H200" t="s">
         <v>9</v>
@@ -10053,7 +10053,7 @@
         <v>3.30800008773804</v>
       </c>
       <c r="G201" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="H201" t="s">
         <v>9</v>
@@ -10079,7 +10079,7 @@
         <v>3.20199990272522</v>
       </c>
       <c r="G202" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="H202" t="s">
         <v>9</v>
@@ -10105,7 +10105,7 @@
         <v>3.26999998092651</v>
       </c>
       <c r="G203" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="H203" t="s">
         <v>9</v>
@@ -10131,7 +10131,7 @@
         <v>3.29399991035461</v>
       </c>
       <c r="G204" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="H204" t="s">
         <v>9</v>
@@ -10157,7 +10157,7 @@
         <v>3.33400011062622</v>
       </c>
       <c r="G205" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="H205" t="s">
         <v>9</v>
@@ -10183,7 +10183,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G206" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="H206" t="s">
         <v>9</v>
@@ -10209,7 +10209,7 @@
         <v>3.39000010490417</v>
       </c>
       <c r="G207" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="H207" t="s">
         <v>9</v>
@@ -10235,7 +10235,7 @@
         <v>3.35400009155273</v>
       </c>
       <c r="G208" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="H208" t="s">
         <v>9</v>
@@ -10261,7 +10261,7 @@
         <v>3.34999990463257</v>
       </c>
       <c r="G209" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="H209" t="s">
         <v>9</v>
@@ -10287,7 +10287,7 @@
         <v>3.48000001907349</v>
       </c>
       <c r="G210" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="H210" t="s">
         <v>9</v>
@@ -10313,7 +10313,7 @@
         <v>3.37599992752075</v>
       </c>
       <c r="G211" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="H211" t="s">
         <v>9</v>
@@ -10339,7 +10339,7 @@
         <v>3.37400007247925</v>
       </c>
       <c r="G212" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="H212" t="s">
         <v>9</v>
@@ -10365,7 +10365,7 @@
         <v>3.39800000190735</v>
       </c>
       <c r="G213" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="H213" t="s">
         <v>9</v>
@@ -10391,7 +10391,7 @@
         <v>3.36999988555908</v>
       </c>
       <c r="G214" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="H214" t="s">
         <v>9</v>
@@ -10417,7 +10417,7 @@
         <v>3.36999988555908</v>
       </c>
       <c r="G215" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="H215" t="s">
         <v>9</v>
@@ -10443,7 +10443,7 @@
         <v>3.32800006866455</v>
       </c>
       <c r="G216" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="H216" t="s">
         <v>9</v>
@@ -10469,7 +10469,7 @@
         <v>3.30999994277954</v>
       </c>
       <c r="G217" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="H217" t="s">
         <v>9</v>
@@ -10495,7 +10495,7 @@
         <v>3.25</v>
       </c>
       <c r="G218" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="H218" t="s">
         <v>9</v>
@@ -10521,7 +10521,7 @@
         <v>3.10999989509583</v>
       </c>
       <c r="G219" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="H219" t="s">
         <v>9</v>
@@ -10547,7 +10547,7 @@
         <v>3.21399998664856</v>
       </c>
       <c r="G220" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="H220" t="s">
         <v>9</v>
@@ -10573,7 +10573,7 @@
         <v>3.34999990463257</v>
       </c>
       <c r="G221" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="H221" t="s">
         <v>9</v>
@@ -10599,7 +10599,7 @@
         <v>3.36199998855591</v>
       </c>
       <c r="G222" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="H222" t="s">
         <v>9</v>
@@ -10651,7 +10651,7 @@
         <v>3.34999990463257</v>
       </c>
       <c r="G224" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="H224" t="s">
         <v>9</v>
@@ -10677,7 +10677,7 @@
         <v>3.29200005531311</v>
       </c>
       <c r="G225" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="H225" t="s">
         <v>9</v>
@@ -10703,7 +10703,7 @@
         <v>3.2279999256134</v>
       </c>
       <c r="G226" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="H226" t="s">
         <v>9</v>
@@ -10729,7 +10729,7 @@
         <v>3.23000001907349</v>
       </c>
       <c r="G227" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="H227" t="s">
         <v>9</v>
@@ -10755,7 +10755,7 @@
         <v>3.19199991226196</v>
       </c>
       <c r="G228" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="H228" t="s">
         <v>9</v>
@@ -10833,7 +10833,7 @@
         <v>3.14199995994568</v>
       </c>
       <c r="G231" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="H231" t="s">
         <v>9</v>
@@ -10859,7 +10859,7 @@
         <v>3.13000011444092</v>
       </c>
       <c r="G232" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="H232" t="s">
         <v>9</v>
@@ -10885,7 +10885,7 @@
         <v>3.13800001144409</v>
       </c>
       <c r="G233" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="H233" t="s">
         <v>9</v>
@@ -10911,7 +10911,7 @@
         <v>3.09200000762939</v>
       </c>
       <c r="G234" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="H234" t="s">
         <v>9</v>
@@ -10937,7 +10937,7 @@
         <v>3.03600001335144</v>
       </c>
       <c r="G235" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="H235" t="s">
         <v>9</v>
@@ -10963,7 +10963,7 @@
         <v>3.03600001335144</v>
       </c>
       <c r="G236" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="H236" t="s">
         <v>9</v>
@@ -10989,7 +10989,7 @@
         <v>2.96000003814697</v>
       </c>
       <c r="G237" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="H237" t="s">
         <v>9</v>
@@ -11015,7 +11015,7 @@
         <v>3.07800006866455</v>
       </c>
       <c r="G238" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="H238" t="s">
         <v>9</v>
@@ -11067,7 +11067,7 @@
         <v>3.23000001907349</v>
       </c>
       <c r="G240" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="H240" t="s">
         <v>9</v>
@@ -11119,7 +11119,7 @@
         <v>3.19199991226196</v>
       </c>
       <c r="G242" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="H242" t="s">
         <v>9</v>
@@ -11145,7 +11145,7 @@
         <v>3.19199991226196</v>
       </c>
       <c r="G243" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="H243" t="s">
         <v>9</v>
@@ -11171,7 +11171,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G244" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="H244" t="s">
         <v>9</v>
@@ -11197,7 +11197,7 @@
         <v>3.23799991607666</v>
       </c>
       <c r="G245" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="H245" t="s">
         <v>9</v>
@@ -11223,7 +11223,7 @@
         <v>3.17000007629395</v>
       </c>
       <c r="G246" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="H246" t="s">
         <v>9</v>
@@ -11249,7 +11249,7 @@
         <v>3.24000000953674</v>
       </c>
       <c r="G247" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="H247" t="s">
         <v>9</v>
@@ -11275,7 +11275,7 @@
         <v>3.24000000953674</v>
       </c>
       <c r="G248" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="H248" t="s">
         <v>9</v>
@@ -11301,7 +11301,7 @@
         <v>3.25</v>
       </c>
       <c r="G249" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="H249" t="s">
         <v>9</v>
@@ -11353,7 +11353,7 @@
         <v>3.24000000953674</v>
       </c>
       <c r="G251" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="H251" t="s">
         <v>9</v>
@@ -11379,7 +11379,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G252" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="H252" t="s">
         <v>9</v>
@@ -11405,7 +11405,7 @@
         <v>3.26799988746643</v>
       </c>
       <c r="G253" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="H253" t="s">
         <v>9</v>
@@ -11431,7 +11431,7 @@
         <v>3.28399991989136</v>
       </c>
       <c r="G254" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="H254" t="s">
         <v>9</v>
@@ -11457,7 +11457,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G255" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="H255" t="s">
         <v>9</v>
@@ -11483,7 +11483,7 @@
         <v>3.30999994277954</v>
       </c>
       <c r="G256" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="H256" t="s">
         <v>9</v>
@@ -11509,7 +11509,7 @@
         <v>3.35199999809265</v>
       </c>
       <c r="G257" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="H257" t="s">
         <v>9</v>
@@ -11535,7 +11535,7 @@
         <v>3.46000003814697</v>
       </c>
       <c r="G258" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="H258" t="s">
         <v>9</v>
@@ -11561,7 +11561,7 @@
         <v>3.46000003814697</v>
       </c>
       <c r="G259" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="H259" t="s">
         <v>9</v>
@@ -11587,7 +11587,7 @@
         <v>3.42400002479553</v>
       </c>
       <c r="G260" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="H260" t="s">
         <v>9</v>
@@ -11613,7 +11613,7 @@
         <v>3.41000008583069</v>
       </c>
       <c r="G261" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="H261" t="s">
         <v>9</v>
@@ -11639,7 +11639,7 @@
         <v>3.41799998283386</v>
       </c>
       <c r="G262" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="H262" t="s">
         <v>9</v>
@@ -11665,7 +11665,7 @@
         <v>3.32200002670288</v>
       </c>
       <c r="G263" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="H263" t="s">
         <v>9</v>
@@ -11691,7 +11691,7 @@
         <v>3.35199999809265</v>
       </c>
       <c r="G264" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="H264" t="s">
         <v>9</v>
@@ -11717,7 +11717,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G265" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="H265" t="s">
         <v>9</v>
@@ -11743,7 +11743,7 @@
         <v>3.36999988555908</v>
       </c>
       <c r="G266" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="H266" t="s">
         <v>9</v>
@@ -11769,7 +11769,7 @@
         <v>3.41199994087219</v>
       </c>
       <c r="G267" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="H267" t="s">
         <v>9</v>
@@ -11795,7 +11795,7 @@
         <v>3.40199995040894</v>
       </c>
       <c r="G268" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="H268" t="s">
         <v>9</v>
@@ -11821,7 +11821,7 @@
         <v>3.40199995040894</v>
       </c>
       <c r="G269" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="H269" t="s">
         <v>9</v>
@@ -11847,7 +11847,7 @@
         <v>3.34400010108948</v>
       </c>
       <c r="G270" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="H270" t="s">
         <v>9</v>
@@ -11899,7 +11899,7 @@
         <v>3.30800008773804</v>
       </c>
       <c r="G272" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="H272" t="s">
         <v>9</v>
@@ -12003,7 +12003,7 @@
         <v>3.26999998092651</v>
       </c>
       <c r="G276" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="H276" t="s">
         <v>9</v>
@@ -12029,7 +12029,7 @@
         <v>3.23600006103516</v>
       </c>
       <c r="G277" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="H277" t="s">
         <v>9</v>
@@ -12055,7 +12055,7 @@
         <v>3.25</v>
       </c>
       <c r="G278" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="H278" t="s">
         <v>9</v>
@@ -12081,7 +12081,7 @@
         <v>3.23000001907349</v>
       </c>
       <c r="G279" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="H279" t="s">
         <v>9</v>
@@ -12107,7 +12107,7 @@
         <v>3.25799989700317</v>
       </c>
       <c r="G280" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="H280" t="s">
         <v>9</v>
@@ -12185,7 +12185,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G283" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="H283" t="s">
         <v>9</v>
@@ -12211,7 +12211,7 @@
         <v>3.36999988555908</v>
       </c>
       <c r="G284" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="H284" t="s">
         <v>9</v>
@@ -12237,7 +12237,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G285" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="H285" t="s">
         <v>9</v>
@@ -12263,7 +12263,7 @@
         <v>3.37800002098083</v>
       </c>
       <c r="G286" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="H286" t="s">
         <v>9</v>
@@ -12289,7 +12289,7 @@
         <v>3.37400007247925</v>
       </c>
       <c r="G287" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="H287" t="s">
         <v>9</v>
@@ -12315,7 +12315,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G288" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="H288" t="s">
         <v>9</v>
@@ -12341,7 +12341,7 @@
         <v>3.42000007629395</v>
       </c>
       <c r="G289" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="H289" t="s">
         <v>9</v>
@@ -12367,7 +12367,7 @@
         <v>3.38000011444092</v>
       </c>
       <c r="G290" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="H290" t="s">
         <v>9</v>
@@ -12419,7 +12419,7 @@
         <v>3.30999994277954</v>
       </c>
       <c r="G292" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="H292" t="s">
         <v>9</v>
@@ -12445,7 +12445,7 @@
         <v>3.34999990463257</v>
       </c>
       <c r="G293" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="H293" t="s">
         <v>9</v>
@@ -12471,7 +12471,7 @@
         <v>3.34999990463257</v>
       </c>
       <c r="G294" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="H294" t="s">
         <v>9</v>
@@ -12497,7 +12497,7 @@
         <v>3.26999998092651</v>
       </c>
       <c r="G295" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="H295" t="s">
         <v>9</v>
@@ -12523,7 +12523,7 @@
         <v>3.29399991035461</v>
       </c>
       <c r="G296" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="H296" t="s">
         <v>9</v>
@@ -12575,7 +12575,7 @@
         <v>3.24600005149841</v>
       </c>
       <c r="G298" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="H298" t="s">
         <v>9</v>
@@ -12627,7 +12627,7 @@
         <v>3.2039999961853</v>
       </c>
       <c r="G300" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="H300" t="s">
         <v>9</v>
@@ -12653,7 +12653,7 @@
         <v>3.23200011253357</v>
       </c>
       <c r="G301" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="H301" t="s">
         <v>9</v>
@@ -12679,7 +12679,7 @@
         <v>3.25999999046326</v>
       </c>
       <c r="G302" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="H302" t="s">
         <v>9</v>
@@ -12705,7 +12705,7 @@
         <v>3.28200006484985</v>
       </c>
       <c r="G303" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="H303" t="s">
         <v>9</v>
@@ -12731,7 +12731,7 @@
         <v>3.25</v>
       </c>
       <c r="G304" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="H304" t="s">
         <v>9</v>
@@ -12757,7 +12757,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G305" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="H305" t="s">
         <v>9</v>
@@ -12783,7 +12783,7 @@
         <v>3.31399989128113</v>
       </c>
       <c r="G306" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="H306" t="s">
         <v>9</v>
@@ -12809,7 +12809,7 @@
         <v>3.31599998474121</v>
       </c>
       <c r="G307" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="H307" t="s">
         <v>9</v>
@@ -12835,7 +12835,7 @@
         <v>3.28399991989136</v>
       </c>
       <c r="G308" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="H308" t="s">
         <v>9</v>
@@ -12861,7 +12861,7 @@
         <v>3.29200005531311</v>
       </c>
       <c r="G309" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="H309" t="s">
         <v>9</v>
@@ -12887,7 +12887,7 @@
         <v>3.29399991035461</v>
       </c>
       <c r="G310" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="H310" t="s">
         <v>9</v>
@@ -12913,7 +12913,7 @@
         <v>3.3199999332428</v>
       </c>
       <c r="G311" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="H311" t="s">
         <v>9</v>
@@ -12939,7 +12939,7 @@
         <v>3.35400009155273</v>
       </c>
       <c r="G312" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="H312" t="s">
         <v>9</v>
@@ -12991,7 +12991,7 @@
         <v>3.59599995613098</v>
       </c>
       <c r="G314" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="H314" t="s">
         <v>9</v>
@@ -13017,7 +13017,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G315" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="H315" t="s">
         <v>9</v>
@@ -13043,7 +13043,7 @@
         <v>3.69000005722046</v>
       </c>
       <c r="G316" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="H316" t="s">
         <v>9</v>
@@ -13069,7 +13069,7 @@
         <v>3.66000008583069</v>
       </c>
       <c r="G317" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="H317" t="s">
         <v>9</v>
@@ -13095,7 +13095,7 @@
         <v>3.65400004386902</v>
       </c>
       <c r="G318" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="H318" t="s">
         <v>9</v>
@@ -13121,7 +13121,7 @@
         <v>3.66000008583069</v>
       </c>
       <c r="G319" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="H319" t="s">
         <v>9</v>
@@ -13147,7 +13147,7 @@
         <v>3.64599990844727</v>
       </c>
       <c r="G320" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="H320" t="s">
         <v>9</v>
@@ -13173,7 +13173,7 @@
         <v>3.61999988555908</v>
       </c>
       <c r="G321" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="H321" t="s">
         <v>9</v>
@@ -13199,7 +13199,7 @@
         <v>3.61999988555908</v>
       </c>
       <c r="G322" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="H322" t="s">
         <v>9</v>
@@ -13225,7 +13225,7 @@
         <v>3.60999989509583</v>
       </c>
       <c r="G323" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="H323" t="s">
         <v>9</v>
@@ -13251,7 +13251,7 @@
         <v>3.59599995613098</v>
       </c>
       <c r="G324" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="H324" t="s">
         <v>9</v>
@@ -13277,7 +13277,7 @@
         <v>3.56599998474121</v>
       </c>
       <c r="G325" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="H325" t="s">
         <v>9</v>
@@ -13303,7 +13303,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G326" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="H326" t="s">
         <v>9</v>
@@ -13329,7 +13329,7 @@
         <v>3.55800008773804</v>
       </c>
       <c r="G327" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="H327" t="s">
         <v>9</v>
@@ -13355,7 +13355,7 @@
         <v>3.55800008773804</v>
       </c>
       <c r="G328" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="H328" t="s">
         <v>9</v>
@@ -13381,7 +13381,7 @@
         <v>3.54200005531311</v>
       </c>
       <c r="G329" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="H329" t="s">
         <v>9</v>
@@ -13407,7 +13407,7 @@
         <v>3.53800010681152</v>
       </c>
       <c r="G330" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="H330" t="s">
         <v>9</v>
@@ -13433,7 +13433,7 @@
         <v>3.5</v>
       </c>
       <c r="G331" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="H331" t="s">
         <v>9</v>
@@ -13459,7 +13459,7 @@
         <v>3.47199988365173</v>
       </c>
       <c r="G332" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="H332" t="s">
         <v>9</v>
@@ -13485,7 +13485,7 @@
         <v>3.50600004196167</v>
       </c>
       <c r="G333" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="H333" t="s">
         <v>9</v>
@@ -13511,7 +13511,7 @@
         <v>3.59200000762939</v>
       </c>
       <c r="G334" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="H334" t="s">
         <v>9</v>
@@ -13537,7 +13537,7 @@
         <v>3.59200000762939</v>
       </c>
       <c r="G335" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="H335" t="s">
         <v>9</v>
@@ -13563,7 +13563,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G336" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="H336" t="s">
         <v>9</v>
@@ -13589,7 +13589,7 @@
         <v>3.61999988555908</v>
       </c>
       <c r="G337" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="H337" t="s">
         <v>9</v>
@@ -13615,7 +13615,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G338" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="H338" t="s">
         <v>9</v>
@@ -13641,7 +13641,7 @@
         <v>3.59200000762939</v>
       </c>
       <c r="G339" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="H339" t="s">
         <v>9</v>
@@ -13667,7 +13667,7 @@
         <v>3.58599996566772</v>
       </c>
       <c r="G340" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="H340" t="s">
         <v>9</v>
@@ -13693,7 +13693,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G341" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="H341" t="s">
         <v>9</v>
@@ -13719,7 +13719,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G342" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="H342" t="s">
         <v>9</v>
@@ -13745,7 +13745,7 @@
         <v>3.58800005912781</v>
       </c>
       <c r="G343" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="H343" t="s">
         <v>9</v>
@@ -13771,7 +13771,7 @@
         <v>3.61999988555908</v>
       </c>
       <c r="G344" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="H344" t="s">
         <v>9</v>
@@ -13797,7 +13797,7 @@
         <v>3.64000010490417</v>
       </c>
       <c r="G345" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="H345" t="s">
         <v>9</v>
@@ -13823,7 +13823,7 @@
         <v>3.63800001144409</v>
       </c>
       <c r="G346" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="H346" t="s">
         <v>9</v>
@@ -13849,7 +13849,7 @@
         <v>3.63199996948242</v>
       </c>
       <c r="G347" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="H347" t="s">
         <v>9</v>
@@ -13875,7 +13875,7 @@
         <v>3.61999988555908</v>
       </c>
       <c r="G348" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="H348" t="s">
         <v>9</v>
@@ -13901,7 +13901,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G349" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="H349" t="s">
         <v>9</v>
@@ -13927,7 +13927,7 @@
         <v>3.75200009346008</v>
       </c>
       <c r="G350" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="H350" t="s">
         <v>9</v>
@@ -13953,7 +13953,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G351" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="H351" t="s">
         <v>9</v>
@@ -13979,7 +13979,7 @@
         <v>3.68600010871887</v>
       </c>
       <c r="G352" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="H352" t="s">
         <v>9</v>
@@ -14005,7 +14005,7 @@
         <v>3.66599988937378</v>
       </c>
       <c r="G353" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="H353" t="s">
         <v>9</v>
@@ -14031,7 +14031,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G354" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="H354" t="s">
         <v>9</v>
@@ -14057,7 +14057,7 @@
         <v>3.74799990653992</v>
       </c>
       <c r="G355" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="H355" t="s">
         <v>9</v>
@@ -14083,7 +14083,7 @@
         <v>3.7720000743866</v>
       </c>
       <c r="G356" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="H356" t="s">
         <v>9</v>
@@ -14109,7 +14109,7 @@
         <v>3.83599996566772</v>
       </c>
       <c r="G357" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="H357" t="s">
         <v>9</v>
@@ -14135,7 +14135,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G358" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="H358" t="s">
         <v>9</v>
@@ -14161,7 +14161,7 @@
         <v>3.80599999427795</v>
       </c>
       <c r="G359" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="H359" t="s">
         <v>9</v>
@@ -14187,7 +14187,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G360" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="H360" t="s">
         <v>9</v>
@@ -14213,7 +14213,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G361" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="H361" t="s">
         <v>9</v>
@@ -14239,7 +14239,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G362" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="H362" t="s">
         <v>9</v>
@@ -14265,7 +14265,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G363" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="H363" t="s">
         <v>9</v>
@@ -14291,7 +14291,7 @@
         <v>3.84999990463257</v>
       </c>
       <c r="G364" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="H364" t="s">
         <v>9</v>
@@ -14317,7 +14317,7 @@
         <v>3.93199992179871</v>
       </c>
       <c r="G365" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="H365" t="s">
         <v>9</v>
@@ -14343,7 +14343,7 @@
         <v>3.89400005340576</v>
       </c>
       <c r="G366" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="H366" t="s">
         <v>9</v>
@@ -14369,7 +14369,7 @@
         <v>3.83400011062622</v>
       </c>
       <c r="G367" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="H367" t="s">
         <v>9</v>
@@ -14395,7 +14395,7 @@
         <v>3.83400011062622</v>
       </c>
       <c r="G368" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="H368" t="s">
         <v>9</v>
@@ -14421,7 +14421,7 @@
         <v>3.81800007820129</v>
       </c>
       <c r="G369" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="H369" t="s">
         <v>9</v>
@@ -14447,7 +14447,7 @@
         <v>3.83800005912781</v>
       </c>
       <c r="G370" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="H370" t="s">
         <v>9</v>
@@ -14473,7 +14473,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G371" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="H371" t="s">
         <v>9</v>
@@ -14499,7 +14499,7 @@
         <v>3.72399997711182</v>
       </c>
       <c r="G372" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="H372" t="s">
         <v>9</v>
@@ -14525,7 +14525,7 @@
         <v>3.72199988365173</v>
       </c>
       <c r="G373" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="H373" t="s">
         <v>9</v>
@@ -14551,7 +14551,7 @@
         <v>3.60999989509583</v>
       </c>
       <c r="G374" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="H374" t="s">
         <v>9</v>
@@ -14577,7 +14577,7 @@
         <v>3.70199990272522</v>
       </c>
       <c r="G375" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="H375" t="s">
         <v>9</v>
@@ -14603,7 +14603,7 @@
         <v>3.71000003814697</v>
       </c>
       <c r="G376" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="H376" t="s">
         <v>9</v>
@@ -14629,7 +14629,7 @@
         <v>3.67199993133545</v>
       </c>
       <c r="G377" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="H377" t="s">
         <v>9</v>
@@ -14655,7 +14655,7 @@
         <v>3.66199994087219</v>
       </c>
       <c r="G378" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="H378" t="s">
         <v>9</v>
@@ -14681,7 +14681,7 @@
         <v>3.62400007247925</v>
       </c>
       <c r="G379" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="H379" t="s">
         <v>9</v>
@@ -14707,7 +14707,7 @@
         <v>3.66199994087219</v>
       </c>
       <c r="G380" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="H380" t="s">
         <v>9</v>
@@ -14733,7 +14733,7 @@
         <v>3.61999988555908</v>
       </c>
       <c r="G381" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="H381" t="s">
         <v>9</v>
@@ -14759,7 +14759,7 @@
         <v>3.63000011444092</v>
       </c>
       <c r="G382" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="H382" t="s">
         <v>9</v>
@@ -14785,7 +14785,7 @@
         <v>3.55599999427795</v>
       </c>
       <c r="G383" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="H383" t="s">
         <v>9</v>
@@ -14811,7 +14811,7 @@
         <v>3.57800006866455</v>
       </c>
       <c r="G384" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="H384" t="s">
         <v>9</v>
@@ -14837,7 +14837,7 @@
         <v>3.7279999256134</v>
       </c>
       <c r="G385" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="H385" t="s">
         <v>9</v>
@@ -14863,7 +14863,7 @@
         <v>3.73799991607666</v>
       </c>
       <c r="G386" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="H386" t="s">
         <v>9</v>
@@ -14889,7 +14889,7 @@
         <v>3.73600006103516</v>
       </c>
       <c r="G387" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="H387" t="s">
         <v>9</v>
@@ -14915,7 +14915,7 @@
         <v>3.76200008392334</v>
       </c>
       <c r="G388" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="H388" t="s">
         <v>9</v>
@@ -14941,7 +14941,7 @@
         <v>3.76600003242493</v>
       </c>
       <c r="G389" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="H389" t="s">
         <v>9</v>
@@ -14967,7 +14967,7 @@
         <v>3.80999994277954</v>
       </c>
       <c r="G390" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="H390" t="s">
         <v>9</v>
@@ -14993,7 +14993,7 @@
         <v>3.82999992370605</v>
       </c>
       <c r="G391" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="H391" t="s">
         <v>9</v>
@@ -15019,7 +15019,7 @@
         <v>3.88000011444092</v>
       </c>
       <c r="G392" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="H392" t="s">
         <v>9</v>
@@ -15045,7 +15045,7 @@
         <v>3.89000010490417</v>
       </c>
       <c r="G393" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="H393" t="s">
         <v>9</v>
@@ -15071,7 +15071,7 @@
         <v>3.91000008583069</v>
       </c>
       <c r="G394" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="H394" t="s">
         <v>9</v>
@@ -15097,7 +15097,7 @@
         <v>3.91400003433228</v>
       </c>
       <c r="G395" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="H395" t="s">
         <v>9</v>
@@ -15123,7 +15123,7 @@
         <v>3.93799996376038</v>
       </c>
       <c r="G396" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="H396" t="s">
         <v>9</v>
@@ -15149,7 +15149,7 @@
         <v>3.98799991607666</v>
       </c>
       <c r="G397" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="H397" t="s">
         <v>9</v>
@@ -15175,7 +15175,7 @@
         <v>4.00400018692017</v>
       </c>
       <c r="G398" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="H398" t="s">
         <v>9</v>
@@ -15201,7 +15201,7 @@
         <v>3.96000003814697</v>
       </c>
       <c r="G399" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="H399" t="s">
         <v>9</v>
@@ -15227,7 +15227,7 @@
         <v>3.99000000953674</v>
       </c>
       <c r="G400" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="H400" t="s">
         <v>9</v>
@@ -15253,7 +15253,7 @@
         <v>3.90199995040894</v>
       </c>
       <c r="G401" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="H401" t="s">
         <v>9</v>
@@ -15279,7 +15279,7 @@
         <v>3.93400001525879</v>
       </c>
       <c r="G402" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="H402" t="s">
         <v>9</v>
@@ -15305,7 +15305,7 @@
         <v>3.8659999370575</v>
       </c>
       <c r="G403" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="H403" t="s">
         <v>9</v>
@@ -15331,7 +15331,7 @@
         <v>3.84999990463257</v>
       </c>
       <c r="G404" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="H404" t="s">
         <v>9</v>
@@ -15357,7 +15357,7 @@
         <v>3.95000004768372</v>
       </c>
       <c r="G405" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="H405" t="s">
         <v>9</v>
@@ -15383,7 +15383,7 @@
         <v>3.75</v>
       </c>
       <c r="G406" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="H406" t="s">
         <v>9</v>
@@ -15409,7 +15409,7 @@
         <v>3.82399988174438</v>
       </c>
       <c r="G407" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="H407" t="s">
         <v>9</v>
@@ -15435,7 +15435,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G408" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="H408" t="s">
         <v>9</v>
@@ -15461,7 +15461,7 @@
         <v>3.84200000762939</v>
       </c>
       <c r="G409" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="H409" t="s">
         <v>9</v>
@@ -15487,7 +15487,7 @@
         <v>3.81399989128113</v>
       </c>
       <c r="G410" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="H410" t="s">
         <v>9</v>
@@ -15513,7 +15513,7 @@
         <v>3.75</v>
       </c>
       <c r="G411" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="H411" t="s">
         <v>9</v>
@@ -15539,7 +15539,7 @@
         <v>3.75</v>
       </c>
       <c r="G412" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="H412" t="s">
         <v>9</v>
@@ -15565,7 +15565,7 @@
         <v>3.69400000572205</v>
       </c>
       <c r="G413" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="H413" t="s">
         <v>9</v>
@@ -15591,7 +15591,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G414" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="H414" t="s">
         <v>9</v>
@@ -15617,7 +15617,7 @@
         <v>3.73399996757507</v>
       </c>
       <c r="G415" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="H415" t="s">
         <v>9</v>
@@ -15643,7 +15643,7 @@
         <v>3.84999990463257</v>
       </c>
       <c r="G416" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="H416" t="s">
         <v>9</v>
@@ -15669,7 +15669,7 @@
         <v>3.78600001335144</v>
       </c>
       <c r="G417" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="H417" t="s">
         <v>9</v>
@@ -15695,7 +15695,7 @@
         <v>3.7720000743866</v>
       </c>
       <c r="G418" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="H418" t="s">
         <v>9</v>
@@ -15721,7 +15721,7 @@
         <v>3.76600003242493</v>
       </c>
       <c r="G419" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="H419" t="s">
         <v>9</v>
@@ -15747,7 +15747,7 @@
         <v>3.71000003814697</v>
       </c>
       <c r="G420" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="H420" t="s">
         <v>9</v>
@@ -15773,7 +15773,7 @@
         <v>3.67000007629395</v>
       </c>
       <c r="G421" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="H421" t="s">
         <v>9</v>
@@ -15799,7 +15799,7 @@
         <v>3.69400000572205</v>
       </c>
       <c r="G422" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="H422" t="s">
         <v>9</v>
@@ -15825,7 +15825,7 @@
         <v>3.74600005149841</v>
       </c>
       <c r="G423" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="H423" t="s">
         <v>9</v>
@@ -15851,7 +15851,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G424" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="H424" t="s">
         <v>9</v>
@@ -15877,7 +15877,7 @@
         <v>3.74200010299683</v>
       </c>
       <c r="G425" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="H425" t="s">
         <v>9</v>
@@ -15903,7 +15903,7 @@
         <v>3.7279999256134</v>
       </c>
       <c r="G426" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="H426" t="s">
         <v>9</v>
@@ -15929,7 +15929,7 @@
         <v>3.75</v>
       </c>
       <c r="G427" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="H427" t="s">
         <v>9</v>
@@ -15955,7 +15955,7 @@
         <v>3.78999996185303</v>
       </c>
       <c r="G428" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="H428" t="s">
         <v>9</v>
@@ -15981,7 +15981,7 @@
         <v>3.76399993896484</v>
       </c>
       <c r="G429" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="H429" t="s">
         <v>9</v>
@@ -16007,7 +16007,7 @@
         <v>3.75799989700317</v>
       </c>
       <c r="G430" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="H430" t="s">
         <v>9</v>
@@ -16033,7 +16033,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G431" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="H431" t="s">
         <v>9</v>
@@ -16059,7 +16059,7 @@
         <v>3.77800011634827</v>
       </c>
       <c r="G432" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="H432" t="s">
         <v>9</v>
@@ -16085,7 +16085,7 @@
         <v>3.7960000038147</v>
       </c>
       <c r="G433" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="H433" t="s">
         <v>9</v>
@@ -16111,7 +16111,7 @@
         <v>3.80800008773804</v>
       </c>
       <c r="G434" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="H434" t="s">
         <v>9</v>
@@ -16137,7 +16137,7 @@
         <v>3.78800010681152</v>
       </c>
       <c r="G435" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="H435" t="s">
         <v>9</v>
@@ -16163,7 +16163,7 @@
         <v>3.80999994277954</v>
       </c>
       <c r="G436" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="H436" t="s">
         <v>9</v>
@@ -16189,7 +16189,7 @@
         <v>3.80200004577637</v>
       </c>
       <c r="G437" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="H437" t="s">
         <v>9</v>
@@ -16215,7 +16215,7 @@
         <v>3.82200002670288</v>
       </c>
       <c r="G438" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="H438" t="s">
         <v>9</v>
@@ -16241,7 +16241,7 @@
         <v>3.84999990463257</v>
       </c>
       <c r="G439" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="H439" t="s">
         <v>9</v>
@@ -16267,7 +16267,7 @@
         <v>3.89000010490417</v>
       </c>
       <c r="G440" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="H440" t="s">
         <v>9</v>
@@ -16293,7 +16293,7 @@
         <v>3.83800005912781</v>
       </c>
       <c r="G441" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="H441" t="s">
         <v>9</v>
@@ -16319,7 +16319,7 @@
         <v>3.81800007820129</v>
       </c>
       <c r="G442" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="H442" t="s">
         <v>9</v>
@@ -16345,7 +16345,7 @@
         <v>3.85400009155273</v>
       </c>
       <c r="G443" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="H443" t="s">
         <v>9</v>
@@ -16371,7 +16371,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G444" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="H444" t="s">
         <v>9</v>
@@ -16397,7 +16397,7 @@
         <v>3.73000001907349</v>
       </c>
       <c r="G445" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="H445" t="s">
         <v>9</v>
@@ -16423,7 +16423,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G446" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="H446" t="s">
         <v>9</v>
@@ -16449,7 +16449,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G447" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="H447" t="s">
         <v>9</v>
@@ -16475,7 +16475,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G448" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="H448" t="s">
         <v>9</v>
@@ -16501,7 +16501,7 @@
         <v>3.82999992370605</v>
       </c>
       <c r="G449" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="H449" t="s">
         <v>9</v>
@@ -16527,7 +16527,7 @@
         <v>3.75399994850159</v>
       </c>
       <c r="G450" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="H450" t="s">
         <v>9</v>
@@ -16553,7 +16553,7 @@
         <v>3.75600004196167</v>
       </c>
       <c r="G451" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="H451" t="s">
         <v>9</v>
@@ -16579,7 +16579,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G452" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="H452" t="s">
         <v>9</v>
@@ -16605,7 +16605,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G453" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="H453" t="s">
         <v>9</v>
@@ -16631,7 +16631,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G454" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="H454" t="s">
         <v>9</v>
@@ -16657,7 +16657,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G455" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="H455" t="s">
         <v>9</v>
@@ -16683,7 +16683,7 @@
         <v>3.73399996757507</v>
       </c>
       <c r="G456" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="H456" t="s">
         <v>9</v>
@@ -16709,7 +16709,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G457" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="H457" t="s">
         <v>9</v>
@@ -16735,7 +16735,7 @@
         <v>3.77800011634827</v>
       </c>
       <c r="G458" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="H458" t="s">
         <v>9</v>
@@ -16761,7 +16761,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G459" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="H459" t="s">
         <v>9</v>
@@ -16787,7 +16787,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G460" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="H460" t="s">
         <v>9</v>
@@ -16813,7 +16813,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G461" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="H461" t="s">
         <v>9</v>
@@ -16839,7 +16839,7 @@
         <v>3.75</v>
       </c>
       <c r="G462" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="H462" t="s">
         <v>9</v>
@@ -16865,7 +16865,7 @@
         <v>3.75</v>
       </c>
       <c r="G463" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="H463" t="s">
         <v>9</v>
@@ -16891,7 +16891,7 @@
         <v>3.67000007629395</v>
       </c>
       <c r="G464" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="H464" t="s">
         <v>9</v>
@@ -16917,7 +16917,7 @@
         <v>3.5699999332428</v>
       </c>
       <c r="G465" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="H465" t="s">
         <v>9</v>
@@ -16943,7 +16943,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G466" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="H466" t="s">
         <v>9</v>
@@ -16969,7 +16969,7 @@
         <v>3.43400001525879</v>
       </c>
       <c r="G467" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="H467" t="s">
         <v>9</v>
@@ -16995,7 +16995,7 @@
         <v>3.48799991607666</v>
       </c>
       <c r="G468" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="H468" t="s">
         <v>9</v>
@@ -17021,7 +17021,7 @@
         <v>3.51999998092651</v>
       </c>
       <c r="G469" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="H469" t="s">
         <v>9</v>
@@ -17047,7 +17047,7 @@
         <v>3.51999998092651</v>
       </c>
       <c r="G470" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="H470" t="s">
         <v>9</v>
@@ -17073,7 +17073,7 @@
         <v>3.5239999294281</v>
       </c>
       <c r="G471" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="H471" t="s">
         <v>9</v>
@@ -17099,7 +17099,7 @@
         <v>3.57800006866455</v>
       </c>
       <c r="G472" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="H472" t="s">
         <v>9</v>
@@ -17125,7 +17125,7 @@
         <v>3.56599998474121</v>
       </c>
       <c r="G473" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="H473" t="s">
         <v>9</v>
@@ -17151,7 +17151,7 @@
         <v>3.55999994277954</v>
       </c>
       <c r="G474" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="H474" t="s">
         <v>9</v>
@@ -17177,7 +17177,7 @@
         <v>3.58999991416931</v>
       </c>
       <c r="G475" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="H475" t="s">
         <v>9</v>
@@ -17203,7 +17203,7 @@
         <v>3.49200010299683</v>
       </c>
       <c r="G476" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="H476" t="s">
         <v>9</v>
@@ -17229,7 +17229,7 @@
         <v>3.43799996376038</v>
       </c>
       <c r="G477" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="H477" t="s">
         <v>9</v>
@@ -17255,7 +17255,7 @@
         <v>3.42400002479553</v>
       </c>
       <c r="G478" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="H478" t="s">
         <v>9</v>
@@ -17281,7 +17281,7 @@
         <v>3.40400004386902</v>
       </c>
       <c r="G479" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="H479" t="s">
         <v>9</v>
@@ -17307,7 +17307,7 @@
         <v>3.48600006103516</v>
       </c>
       <c r="G480" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="H480" t="s">
         <v>9</v>
@@ -17333,7 +17333,7 @@
         <v>3.32999992370605</v>
       </c>
       <c r="G481" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="H481" t="s">
         <v>9</v>
@@ -17359,7 +17359,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G482" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="H482" t="s">
         <v>9</v>
@@ -17385,7 +17385,7 @@
         <v>3.38000011444092</v>
       </c>
       <c r="G483" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="H483" t="s">
         <v>9</v>
@@ -17411,7 +17411,7 @@
         <v>3.40599989891052</v>
       </c>
       <c r="G484" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="H484" t="s">
         <v>9</v>
@@ -17437,7 +17437,7 @@
         <v>3.46000003814697</v>
       </c>
       <c r="G485" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="H485" t="s">
         <v>9</v>
@@ -17463,7 +17463,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G486" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="H486" t="s">
         <v>9</v>
@@ -17489,7 +17489,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G487" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="H487" t="s">
         <v>9</v>
@@ -17515,7 +17515,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G488" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="H488" t="s">
         <v>9</v>
@@ -17541,7 +17541,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G489" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="H489" t="s">
         <v>9</v>
@@ -17567,7 +17567,7 @@
         <v>3.55999994277954</v>
       </c>
       <c r="G490" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="H490" t="s">
         <v>9</v>
@@ -17593,7 +17593,7 @@
         <v>3.59599995613098</v>
       </c>
       <c r="G491" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="H491" t="s">
         <v>9</v>
@@ -17619,7 +17619,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G492" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="H492" t="s">
         <v>9</v>
@@ -17645,7 +17645,7 @@
         <v>3.65000009536743</v>
       </c>
       <c r="G493" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="H493" t="s">
         <v>9</v>
@@ -17671,7 +17671,7 @@
         <v>3.69799995422363</v>
       </c>
       <c r="G494" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="H494" t="s">
         <v>9</v>
@@ -17697,7 +17697,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G495" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="H495" t="s">
         <v>9</v>
@@ -17723,7 +17723,7 @@
         <v>3.65000009536743</v>
       </c>
       <c r="G496" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="H496" t="s">
         <v>9</v>
@@ -17749,7 +17749,7 @@
         <v>3.65000009536743</v>
       </c>
       <c r="G497" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="H497" t="s">
         <v>9</v>
@@ -17775,7 +17775,7 @@
         <v>3.67000007629395</v>
       </c>
       <c r="G498" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="H498" t="s">
         <v>9</v>
@@ -17801,7 +17801,7 @@
         <v>3.71000003814697</v>
       </c>
       <c r="G499" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="H499" t="s">
         <v>9</v>
@@ -17827,7 +17827,7 @@
         <v>3.70199990272522</v>
       </c>
       <c r="G500" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="H500" t="s">
         <v>9</v>
@@ -17853,7 +17853,7 @@
         <v>3.71600008010864</v>
       </c>
       <c r="G501" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="H501" t="s">
         <v>9</v>
@@ -17879,7 +17879,7 @@
         <v>3.70799994468689</v>
       </c>
       <c r="G502" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="H502" t="s">
         <v>9</v>
@@ -17905,7 +17905,7 @@
         <v>3.66000008583069</v>
       </c>
       <c r="G503" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="H503" t="s">
         <v>9</v>
@@ -17931,7 +17931,7 @@
         <v>3.67600011825562</v>
       </c>
       <c r="G504" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="H504" t="s">
         <v>9</v>
@@ -17957,7 +17957,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G505" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="H505" t="s">
         <v>9</v>
@@ -17983,7 +17983,7 @@
         <v>3.65000009536743</v>
       </c>
       <c r="G506" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="H506" t="s">
         <v>9</v>
@@ -18009,7 +18009,7 @@
         <v>3.65000009536743</v>
       </c>
       <c r="G507" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="H507" t="s">
         <v>9</v>
@@ -18035,7 +18035,7 @@
         <v>3.66599988937378</v>
       </c>
       <c r="G508" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="H508" t="s">
         <v>9</v>
@@ -18061,7 +18061,7 @@
         <v>3.69600009918213</v>
       </c>
       <c r="G509" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="H509" t="s">
         <v>9</v>
@@ -18087,7 +18087,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G510" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="H510" t="s">
         <v>9</v>
@@ -18113,7 +18113,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G511" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="H511" t="s">
         <v>9</v>
@@ -18139,7 +18139,7 @@
         <v>3.7260000705719</v>
       </c>
       <c r="G512" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="H512" t="s">
         <v>9</v>
@@ -18165,7 +18165,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G513" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="H513" t="s">
         <v>9</v>
@@ -18191,7 +18191,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G514" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="H514" t="s">
         <v>9</v>
@@ -18217,7 +18217,7 @@
         <v>3.76500010490417</v>
       </c>
       <c r="G515" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="H515" t="s">
         <v>9</v>
@@ -18243,7 +18243,7 @@
         <v>3.71499991416931</v>
       </c>
       <c r="G516" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="H516" t="s">
         <v>9</v>
@@ -18269,7 +18269,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G517" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="H517" t="s">
         <v>9</v>
@@ -18295,7 +18295,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G518" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="H518" t="s">
         <v>9</v>
@@ -18321,7 +18321,7 @@
         <v>3.8199999332428</v>
       </c>
       <c r="G519" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="H519" t="s">
         <v>9</v>
@@ -18347,7 +18347,7 @@
         <v>3.8199999332428</v>
       </c>
       <c r="G520" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="H520" t="s">
         <v>9</v>
@@ -18373,7 +18373,7 @@
         <v>3.91000008583069</v>
       </c>
       <c r="G521" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="H521" t="s">
         <v>9</v>
@@ -18399,7 +18399,7 @@
         <v>3.89499998092651</v>
       </c>
       <c r="G522" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="H522" t="s">
         <v>9</v>
@@ -18425,7 +18425,7 @@
         <v>3.82999992370605</v>
       </c>
       <c r="G523" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="H523" t="s">
         <v>9</v>
@@ -18451,7 +18451,7 @@
         <v>3.84999990463257</v>
       </c>
       <c r="G524" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="H524" t="s">
         <v>9</v>
@@ -18477,7 +18477,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G525" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="H525" t="s">
         <v>9</v>
@@ -18503,7 +18503,7 @@
         <v>3.84500002861023</v>
       </c>
       <c r="G526" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="H526" t="s">
         <v>9</v>
@@ -18529,7 +18529,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G527" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="H527" t="s">
         <v>9</v>
@@ -18555,7 +18555,7 @@
         <v>3.86500000953674</v>
       </c>
       <c r="G528" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="H528" t="s">
         <v>9</v>
@@ -18581,7 +18581,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G529" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="H529" t="s">
         <v>9</v>
@@ -18607,7 +18607,7 @@
         <v>3.94000005722046</v>
       </c>
       <c r="G530" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="H530" t="s">
         <v>9</v>
@@ -18633,7 +18633,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G531" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="H531" t="s">
         <v>9</v>
@@ -18659,7 +18659,7 @@
         <v>3.71000003814697</v>
       </c>
       <c r="G532" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="H532" t="s">
         <v>9</v>
@@ -18685,7 +18685,7 @@
         <v>3.75</v>
       </c>
       <c r="G533" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="H533" t="s">
         <v>9</v>
@@ -18711,7 +18711,7 @@
         <v>3.73000001907349</v>
       </c>
       <c r="G534" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="H534" t="s">
         <v>9</v>
@@ -18737,7 +18737,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G535" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="H535" t="s">
         <v>9</v>
@@ -18763,7 +18763,7 @@
         <v>3.65000009536743</v>
       </c>
       <c r="G536" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="H536" t="s">
         <v>9</v>
@@ -18789,7 +18789,7 @@
         <v>3.58500003814697</v>
       </c>
       <c r="G537" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="H537" t="s">
         <v>9</v>
@@ -18815,7 +18815,7 @@
         <v>3.60500001907349</v>
       </c>
       <c r="G538" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="H538" t="s">
         <v>9</v>
@@ -18841,7 +18841,7 @@
         <v>3.58500003814697</v>
       </c>
       <c r="G539" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="H539" t="s">
         <v>9</v>
@@ -18867,7 +18867,7 @@
         <v>3.53999996185303</v>
       </c>
       <c r="G540" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="H540" t="s">
         <v>9</v>
@@ -18893,7 +18893,7 @@
         <v>3.51999998092651</v>
       </c>
       <c r="G541" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="H541" t="s">
         <v>9</v>
@@ -18919,7 +18919,7 @@
         <v>3.48000001907349</v>
       </c>
       <c r="G542" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="H542" t="s">
         <v>9</v>
@@ -18945,7 +18945,7 @@
         <v>3.53999996185303</v>
       </c>
       <c r="G543" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="H543" t="s">
         <v>9</v>
@@ -18971,7 +18971,7 @@
         <v>3.63000011444092</v>
       </c>
       <c r="G544" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="H544" t="s">
         <v>9</v>
@@ -18997,7 +18997,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G545" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="H545" t="s">
         <v>9</v>
@@ -19023,7 +19023,7 @@
         <v>3.79500007629395</v>
       </c>
       <c r="G546" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="H546" t="s">
         <v>9</v>
@@ -19049,7 +19049,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G547" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="H547" t="s">
         <v>9</v>
@@ -19075,7 +19075,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G548" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="H548" t="s">
         <v>9</v>
@@ -19101,7 +19101,7 @@
         <v>3.72499990463257</v>
       </c>
       <c r="G549" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="H549" t="s">
         <v>9</v>
@@ -19127,7 +19127,7 @@
         <v>3.72499990463257</v>
       </c>
       <c r="G550" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="H550" t="s">
         <v>9</v>
@@ -19153,7 +19153,7 @@
         <v>3.6949999332428</v>
       </c>
       <c r="G551" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="H551" t="s">
         <v>9</v>
@@ -19179,7 +19179,7 @@
         <v>3.67499995231628</v>
       </c>
       <c r="G552" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="H552" t="s">
         <v>9</v>
@@ -19205,7 +19205,7 @@
         <v>3.63000011444092</v>
       </c>
       <c r="G553" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="H553" t="s">
         <v>9</v>
@@ -19231,7 +19231,7 @@
         <v>3.5699999332428</v>
       </c>
       <c r="G554" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="H554" t="s">
         <v>9</v>
@@ -19257,7 +19257,7 @@
         <v>3.53500008583069</v>
       </c>
       <c r="G555" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="H555" t="s">
         <v>9</v>
@@ -19283,7 +19283,7 @@
         <v>3.53999996185303</v>
       </c>
       <c r="G556" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="H556" t="s">
         <v>9</v>
@@ -19309,7 +19309,7 @@
         <v>3.51999998092651</v>
       </c>
       <c r="G557" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="H557" t="s">
         <v>9</v>
@@ -19335,7 +19335,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G558" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="H558" t="s">
         <v>9</v>
@@ -19361,7 +19361,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G559" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="H559" t="s">
         <v>9</v>
@@ -19387,7 +19387,7 @@
         <v>3.73499989509583</v>
       </c>
       <c r="G560" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="H560" t="s">
         <v>9</v>
@@ -19413,7 +19413,7 @@
         <v>3.73000001907349</v>
       </c>
       <c r="G561" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="H561" t="s">
         <v>9</v>
@@ -19439,7 +19439,7 @@
         <v>3.65499997138977</v>
       </c>
       <c r="G562" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="H562" t="s">
         <v>9</v>
@@ -19465,7 +19465,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G563" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="H563" t="s">
         <v>9</v>
@@ -19491,7 +19491,7 @@
         <v>3.67499995231628</v>
       </c>
       <c r="G564" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="H564" t="s">
         <v>9</v>
@@ -19517,7 +19517,7 @@
         <v>3.65499997138977</v>
       </c>
       <c r="G565" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="H565" t="s">
         <v>9</v>
@@ -19543,7 +19543,7 @@
         <v>3.71499991416931</v>
       </c>
       <c r="G566" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="H566" t="s">
         <v>9</v>
@@ -19569,7 +19569,7 @@
         <v>3.66499996185303</v>
       </c>
       <c r="G567" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="H567" t="s">
         <v>9</v>
@@ -19595,7 +19595,7 @@
         <v>3.69000005722046</v>
       </c>
       <c r="G568" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="H568" t="s">
         <v>9</v>
@@ -19621,7 +19621,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G569" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="H569" t="s">
         <v>9</v>
@@ -19647,7 +19647,7 @@
         <v>3.69000005722046</v>
       </c>
       <c r="G570" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="H570" t="s">
         <v>9</v>
@@ -19673,7 +19673,7 @@
         <v>3.68499994277954</v>
       </c>
       <c r="G571" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="H571" t="s">
         <v>9</v>
@@ -19699,7 +19699,7 @@
         <v>3.65000009536743</v>
       </c>
       <c r="G572" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="H572" t="s">
         <v>9</v>
@@ -19725,7 +19725,7 @@
         <v>3.69000005722046</v>
       </c>
       <c r="G573" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="H573" t="s">
         <v>9</v>
@@ -19751,7 +19751,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G574" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="H574" t="s">
         <v>9</v>
@@ -19777,7 +19777,7 @@
         <v>3.69000005722046</v>
       </c>
       <c r="G575" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="H575" t="s">
         <v>9</v>
@@ -19803,7 +19803,7 @@
         <v>3.67000007629395</v>
       </c>
       <c r="G576" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="H576" t="s">
         <v>9</v>
@@ -19829,7 +19829,7 @@
         <v>3.65499997138977</v>
       </c>
       <c r="G577" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="H577" t="s">
         <v>9</v>
@@ -19855,7 +19855,7 @@
         <v>3.73499989509583</v>
       </c>
       <c r="G578" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="H578" t="s">
         <v>9</v>
@@ -19881,7 +19881,7 @@
         <v>3.80999994277954</v>
       </c>
       <c r="G579" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="H579" t="s">
         <v>9</v>
@@ -19907,7 +19907,7 @@
         <v>3.79500007629395</v>
       </c>
       <c r="G580" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="H580" t="s">
         <v>9</v>
@@ -19933,7 +19933,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G581" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="H581" t="s">
         <v>9</v>
@@ -19959,7 +19959,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G582" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="H582" t="s">
         <v>9</v>
@@ -19985,7 +19985,7 @@
         <v>3.80999994277954</v>
       </c>
       <c r="G583" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="H583" t="s">
         <v>9</v>
@@ -20011,7 +20011,7 @@
         <v>3.81500005722046</v>
       </c>
       <c r="G584" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="H584" t="s">
         <v>9</v>
@@ -20037,7 +20037,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G585" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="H585" t="s">
         <v>9</v>
@@ -20063,7 +20063,7 @@
         <v>3.79500007629395</v>
       </c>
       <c r="G586" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="H586" t="s">
         <v>9</v>
@@ -20089,7 +20089,7 @@
         <v>3.78999996185303</v>
       </c>
       <c r="G587" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="H587" t="s">
         <v>9</v>
@@ -20115,7 +20115,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G588" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="H588" t="s">
         <v>9</v>
@@ -20141,7 +20141,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G589" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="H589" t="s">
         <v>9</v>
@@ -20167,7 +20167,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G590" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="H590" t="s">
         <v>9</v>
@@ -20193,7 +20193,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G591" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="H591" t="s">
         <v>9</v>
@@ -20219,7 +20219,7 @@
         <v>3.88000011444092</v>
       </c>
       <c r="G592" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="H592" t="s">
         <v>9</v>
@@ -20245,7 +20245,7 @@
         <v>3.88000011444092</v>
       </c>
       <c r="G593" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="H593" t="s">
         <v>9</v>
@@ -20271,7 +20271,7 @@
         <v>3.86500000953674</v>
       </c>
       <c r="G594" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="H594" t="s">
         <v>9</v>
@@ -20297,7 +20297,7 @@
         <v>3.81500005722046</v>
       </c>
       <c r="G595" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="H595" t="s">
         <v>9</v>
@@ -20323,7 +20323,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G596" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="H596" t="s">
         <v>9</v>
@@ -20349,7 +20349,7 @@
         <v>3.95000004768372</v>
       </c>
       <c r="G597" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="H597" t="s">
         <v>9</v>
@@ -20375,7 +20375,7 @@
         <v>4.03999996185303</v>
       </c>
       <c r="G598" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="H598" t="s">
         <v>9</v>
@@ -20401,7 +20401,7 @@
         <v>3.99000000953674</v>
       </c>
       <c r="G599" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="H599" t="s">
         <v>9</v>
@@ -20427,7 +20427,7 @@
         <v>3.93499994277954</v>
       </c>
       <c r="G600" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="H600" t="s">
         <v>9</v>
@@ -20453,7 +20453,7 @@
         <v>3.96499991416931</v>
       </c>
       <c r="G601" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="H601" t="s">
         <v>9</v>
@@ -20479,7 +20479,7 @@
         <v>3.96000003814697</v>
       </c>
       <c r="G602" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="H602" t="s">
         <v>9</v>
@@ -20505,7 +20505,7 @@
         <v>3.97499990463257</v>
       </c>
       <c r="G603" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="H603" t="s">
         <v>9</v>
@@ -20531,7 +20531,7 @@
         <v>3.9300000667572</v>
       </c>
       <c r="G604" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="H604" t="s">
         <v>9</v>
@@ -20557,7 +20557,7 @@
         <v>3.85500001907349</v>
       </c>
       <c r="G605" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="H605" t="s">
         <v>9</v>
@@ -20583,7 +20583,7 @@
         <v>3.9300000667572</v>
       </c>
       <c r="G606" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="H606" t="s">
         <v>9</v>
@@ -20609,7 +20609,7 @@
         <v>3.84500002861023</v>
       </c>
       <c r="G607" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="H607" t="s">
         <v>9</v>
@@ -20635,7 +20635,7 @@
         <v>3.86500000953674</v>
       </c>
       <c r="G608" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="H608" t="s">
         <v>9</v>
@@ -20661,7 +20661,7 @@
         <v>3.81500005722046</v>
       </c>
       <c r="G609" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="H609" t="s">
         <v>9</v>
@@ -20687,7 +20687,7 @@
         <v>3.82500004768372</v>
       </c>
       <c r="G610" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="H610" t="s">
         <v>9</v>
@@ -20713,7 +20713,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G611" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="H611" t="s">
         <v>9</v>
@@ -20739,7 +20739,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G612" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="H612" t="s">
         <v>9</v>
@@ -20765,7 +20765,7 @@
         <v>3.76999998092651</v>
       </c>
       <c r="G613" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="H613" t="s">
         <v>9</v>
@@ -20791,7 +20791,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G614" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="H614" t="s">
         <v>9</v>
@@ -20817,7 +20817,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G615" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="H615" t="s">
         <v>9</v>
@@ -20843,7 +20843,7 @@
         <v>3.74499988555908</v>
       </c>
       <c r="G616" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="H616" t="s">
         <v>9</v>
@@ -20869,7 +20869,7 @@
         <v>3.8199999332428</v>
       </c>
       <c r="G617" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="H617" t="s">
         <v>9</v>
@@ -20895,7 +20895,7 @@
         <v>3.88000011444092</v>
       </c>
       <c r="G618" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="H618" t="s">
         <v>9</v>
@@ -20921,7 +20921,7 @@
         <v>3.86999988555908</v>
       </c>
       <c r="G619" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="H619" t="s">
         <v>9</v>
@@ -20947,7 +20947,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G620" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="H620" t="s">
         <v>9</v>
@@ -20973,7 +20973,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G621" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="H621" t="s">
         <v>9</v>
@@ -20999,7 +20999,7 @@
         <v>3.66000008583069</v>
       </c>
       <c r="G622" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="H622" t="s">
         <v>9</v>
@@ -21025,7 +21025,7 @@
         <v>3.79500007629395</v>
       </c>
       <c r="G623" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="H623" t="s">
         <v>9</v>
@@ -21051,7 +21051,7 @@
         <v>3.79500007629395</v>
       </c>
       <c r="G624" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="H624" t="s">
         <v>9</v>
@@ -21077,7 +21077,7 @@
         <v>3.78500008583069</v>
       </c>
       <c r="G625" t="s">
-        <v>392</v>
+        <v>353</v>
       </c>
       <c r="H625" t="s">
         <v>9</v>
@@ -21311,7 +21311,7 @@
         <v>3.76999998092651</v>
       </c>
       <c r="G634" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="H634" t="s">
         <v>9</v>
@@ -21571,7 +21571,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G644" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="H644" t="s">
         <v>9</v>
@@ -21649,7 +21649,7 @@
         <v>3.81500005722046</v>
       </c>
       <c r="G647" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="H647" t="s">
         <v>9</v>
@@ -21701,7 +21701,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G649" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="H649" t="s">
         <v>9</v>
@@ -70979,7 +70979,7 @@
     </row>
     <row r="2545">
       <c r="A2545" s="1" t="n">
-        <v>46029.691099537</v>
+        <v>46029.3333333333</v>
       </c>
       <c r="B2545" t="n">
         <v>89251</v>
@@ -71000,6 +71000,32 @@
         <v>1429</v>
       </c>
       <c r="H2545" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2546">
+      <c r="A2546" s="1" t="n">
+        <v>46030.6909722222</v>
+      </c>
+      <c r="B2546" t="n">
+        <v>81910</v>
+      </c>
+      <c r="C2546" t="n">
+        <v>7.6399998664856</v>
+      </c>
+      <c r="D2546" t="n">
+        <v>7.42999982833862</v>
+      </c>
+      <c r="E2546" t="n">
+        <v>7.42999982833862</v>
+      </c>
+      <c r="F2546" t="n">
+        <v>7.59999990463257</v>
+      </c>
+      <c r="G2546" t="s">
+        <v>1419</v>
+      </c>
+      <c r="H2546" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/BAN.MI.xlsx
+++ b/data/BAN.MI.xlsx
@@ -38,25 +38,25 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">3.66912937164307</t>
+    <t xml:space="preserve">3.66913032531738</t>
   </si>
   <si>
     <t xml:space="preserve">BAN.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">3.68330311775208</t>
+    <t xml:space="preserve">3.68330240249634</t>
   </si>
   <si>
     <t xml:space="preserve">3.59039306640625</t>
   </si>
   <si>
-    <t xml:space="preserve">3.46283960342407</t>
+    <t xml:space="preserve">3.46283984184265</t>
   </si>
   <si>
     <t xml:space="preserve">3.41874718666077</t>
   </si>
   <si>
-    <t xml:space="preserve">3.35733222961426</t>
+    <t xml:space="preserve">3.35733294487</t>
   </si>
   <si>
     <t xml:space="preserve">3.44551753997803</t>
@@ -68,55 +68,55 @@
     <t xml:space="preserve">3.45181655883789</t>
   </si>
   <si>
-    <t xml:space="preserve">3.43134450912476</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.38410305976868</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.40929841995239</t>
+    <t xml:space="preserve">3.43134474754333</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.38410258293152</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.40929865837097</t>
   </si>
   <si>
     <t xml:space="preserve">3.11639809608459</t>
   </si>
   <si>
-    <t xml:space="preserve">3.24080276489258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.29119348526001</t>
+    <t xml:space="preserve">3.240802526474</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.29119372367859</t>
   </si>
   <si>
     <t xml:space="preserve">3.21245694160461</t>
   </si>
   <si>
-    <t xml:space="preserve">3.26757287979126</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.1935601234436</t>
+    <t xml:space="preserve">3.26757264137268</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.19356036186218</t>
   </si>
   <si>
     <t xml:space="preserve">3.13372039794922</t>
   </si>
   <si>
-    <t xml:space="preserve">3.22820425033569</t>
+    <t xml:space="preserve">3.22820448875427</t>
   </si>
   <si>
     <t xml:space="preserve">3.16678953170776</t>
   </si>
   <si>
-    <t xml:space="preserve">3.17308926582336</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.0707311630249</t>
+    <t xml:space="preserve">3.17308855056763</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.07073163986206</t>
   </si>
   <si>
     <t xml:space="preserve">3.14946746826172</t>
   </si>
   <si>
-    <t xml:space="preserve">3.05025935173035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.92900490760803</t>
+    <t xml:space="preserve">3.05025911331177</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.92900466918945</t>
   </si>
   <si>
     <t xml:space="preserve">2.91325759887695</t>
@@ -125,22 +125,22 @@
     <t xml:space="preserve">2.83452081680298</t>
   </si>
   <si>
-    <t xml:space="preserve">2.82664704322815</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.75263500213623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.75420928001404</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.75578427314758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.89436054229736</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.98254585266113</t>
+    <t xml:space="preserve">2.82664728164673</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.75263476371765</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.75420951843262</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.75578451156616</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.89436078071594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.98254632949829</t>
   </si>
   <si>
     <t xml:space="preserve">2.96207427978516</t>
@@ -149,10 +149,10 @@
     <t xml:space="preserve">2.99356889724731</t>
   </si>
   <si>
-    <t xml:space="preserve">3.05970764160156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.11009955406189</t>
+    <t xml:space="preserve">3.05970811843872</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.11009931564331</t>
   </si>
   <si>
     <t xml:space="preserve">3.06915616989136</t>
@@ -164,55 +164,55 @@
     <t xml:space="preserve">2.99199414253235</t>
   </si>
   <si>
-    <t xml:space="preserve">3.00774145126343</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.97624683380127</t>
+    <t xml:space="preserve">3.00774192810059</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.97624707221985</t>
   </si>
   <si>
     <t xml:space="preserve">3.06285762786865</t>
   </si>
   <si>
-    <t xml:space="preserve">3.11797285079956</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.18096256256104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.10222578048706</t>
+    <t xml:space="preserve">3.11797308921814</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.18096232414246</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.10222601890564</t>
   </si>
   <si>
     <t xml:space="preserve">3.13686990737915</t>
   </si>
   <si>
-    <t xml:space="preserve">3.23292851448059</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.33843541145325</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.30694079399109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.24395155906677</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.24237680435181</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.12584662437439</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.19670987129211</t>
+    <t xml:space="preserve">3.23292875289917</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.33843564987183</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.30694103240967</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.24395179748535</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.24237728118896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.12584686279297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.19670963287354</t>
   </si>
   <si>
     <t xml:space="preserve">3.2030086517334</t>
   </si>
   <si>
-    <t xml:space="preserve">3.10380005836487</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.11324906349182</t>
+    <t xml:space="preserve">3.10380029678345</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.11324882507324</t>
   </si>
   <si>
     <t xml:space="preserve">3.14159393310547</t>
@@ -221,28 +221,28 @@
     <t xml:space="preserve">3.04710960388184</t>
   </si>
   <si>
-    <t xml:space="preserve">2.99986791610718</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.96049976348877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.09435200691223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.9683735370636</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.86286616325378</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.87388944625854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.9101083278656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.98569560050964</t>
+    <t xml:space="preserve">2.9998676776886</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.96049928665161</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.09435224533081</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.96837329864502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.86286592483521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.87388968467712</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.91010785102844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.98569536209106</t>
   </si>
   <si>
     <t xml:space="preserve">3.00144290924072</t>
@@ -251,22 +251,22 @@
     <t xml:space="preserve">3.01561522483826</t>
   </si>
   <si>
-    <t xml:space="preserve">2.92743015289307</t>
+    <t xml:space="preserve">2.92743039131165</t>
   </si>
   <si>
     <t xml:space="preserve">2.92113137245178</t>
   </si>
   <si>
-    <t xml:space="preserve">2.85814213752747</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.81404972076416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.84081983566284</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.80145168304443</t>
+    <t xml:space="preserve">2.85814189910889</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.814049243927</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.84082007408142</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.80145144462585</t>
   </si>
   <si>
     <t xml:space="preserve">2.72901368141174</t>
@@ -275,19 +275,19 @@
     <t xml:space="preserve">2.65185165405273</t>
   </si>
   <si>
-    <t xml:space="preserve">2.68177151679993</t>
+    <t xml:space="preserve">2.68177175521851</t>
   </si>
   <si>
     <t xml:space="preserve">2.71484136581421</t>
   </si>
   <si>
-    <t xml:space="preserve">2.76365780830383</t>
+    <t xml:space="preserve">2.76365756988525</t>
   </si>
   <si>
     <t xml:space="preserve">2.77940535545349</t>
   </si>
   <si>
-    <t xml:space="preserve">2.72428965568542</t>
+    <t xml:space="preserve">2.724289894104</t>
   </si>
   <si>
     <t xml:space="preserve">2.59043717384338</t>
@@ -296,7 +296,7 @@
     <t xml:space="preserve">2.5353217124939</t>
   </si>
   <si>
-    <t xml:space="preserve">2.49437808990479</t>
+    <t xml:space="preserve">2.49437832832336</t>
   </si>
   <si>
     <t xml:space="preserve">2.48020577430725</t>
@@ -305,7 +305,7 @@
     <t xml:space="preserve">2.51957440376282</t>
   </si>
   <si>
-    <t xml:space="preserve">2.60572743415833</t>
+    <t xml:space="preserve">2.6057276725769</t>
   </si>
   <si>
     <t xml:space="preserve">2.58784627914429</t>
@@ -314,10 +314,10 @@
     <t xml:space="preserve">2.5602126121521</t>
   </si>
   <si>
-    <t xml:space="preserve">2.56183791160583</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.60897874832153</t>
+    <t xml:space="preserve">2.56183767318726</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.60897850990295</t>
   </si>
   <si>
     <t xml:space="preserve">2.59272313117981</t>
@@ -329,19 +329,19 @@
     <t xml:space="preserve">2.60085105895996</t>
   </si>
   <si>
-    <t xml:space="preserve">2.72114014625549</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.82029747962952</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.80404233932495</t>
+    <t xml:space="preserve">2.72114038467407</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.8202977180481</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.80404257774353</t>
   </si>
   <si>
     <t xml:space="preserve">2.68212747573853</t>
   </si>
   <si>
-    <t xml:space="preserve">2.71463799476624</t>
+    <t xml:space="preserve">2.71463775634766</t>
   </si>
   <si>
     <t xml:space="preserve">2.44642543792725</t>
@@ -356,22 +356,22 @@
     <t xml:space="preserve">2.47568488121033</t>
   </si>
   <si>
-    <t xml:space="preserve">2.51957416534424</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.52770185470581</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.5081958770752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.40578699111938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.19446754455566</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.23510599136353</t>
+    <t xml:space="preserve">2.51957392692566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.52770161628723</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.50819540023804</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.40578722953796</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.19446778297424</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.2351062297821</t>
   </si>
   <si>
     <t xml:space="preserve">2.29525089263916</t>
@@ -380,46 +380,46 @@
     <t xml:space="preserve">2.27411913871765</t>
   </si>
   <si>
-    <t xml:space="preserve">2.35702085494995</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.3732762336731</t>
+    <t xml:space="preserve">2.35702133178711</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.37327647209167</t>
   </si>
   <si>
     <t xml:space="preserve">2.29199981689453</t>
   </si>
   <si>
-    <t xml:space="preserve">2.19284224510193</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.22535276412964</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.28387236595154</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.30500411987305</t>
+    <t xml:space="preserve">2.19284248352051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.22535300254822</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.28387212753296</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.30500388145447</t>
   </si>
   <si>
     <t xml:space="preserve">2.33101224899292</t>
   </si>
   <si>
-    <t xml:space="preserve">2.33588910102844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.33263826370239</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.3196337223053</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.38140392303467</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.53582906723022</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.5439567565918</t>
+    <t xml:space="preserve">2.33588886260986</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.33263754844666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.31963348388672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.38140416145325</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.5358293056488</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.54395699501038</t>
   </si>
   <si>
     <t xml:space="preserve">2.56834030151367</t>
@@ -431,127 +431,127 @@
     <t xml:space="preserve">2.83817839622498</t>
   </si>
   <si>
-    <t xml:space="preserve">2.81216979026794</t>
+    <t xml:space="preserve">2.81217002868652</t>
   </si>
   <si>
     <t xml:space="preserve">2.59597396850586</t>
   </si>
   <si>
-    <t xml:space="preserve">2.57646799087524</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.57321643829346</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.5667142868042</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.53257822990417</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.53745484352112</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.63661241531372</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.63011050224304</t>
+    <t xml:space="preserve">2.57646775245667</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.57321667671204</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.56671476364136</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.53257846832275</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.5374550819397</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.6366126537323</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.63011026382446</t>
   </si>
   <si>
     <t xml:space="preserve">2.64636564254761</t>
   </si>
   <si>
-    <t xml:space="preserve">2.65286779403687</t>
+    <t xml:space="preserve">2.65286755561829</t>
   </si>
   <si>
     <t xml:space="preserve">2.63823819160461</t>
   </si>
   <si>
-    <t xml:space="preserve">2.64148926734924</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.69188046455383</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.75690174102783</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.79266381263733</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.76340413093567</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.73089289665222</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.6544930934906</t>
+    <t xml:space="preserve">2.64148902893066</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.69188022613525</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.75690150260925</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.79266357421875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.76340389251709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.7308931350708</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.65449333190918</t>
   </si>
   <si>
     <t xml:space="preserve">2.65774440765381</t>
   </si>
   <si>
-    <t xml:space="preserve">2.74227166175842</t>
+    <t xml:space="preserve">2.742271900177</t>
   </si>
   <si>
     <t xml:space="preserve">2.76828026771545</t>
   </si>
   <si>
-    <t xml:space="preserve">2.70651030540466</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.72764182090759</t>
+    <t xml:space="preserve">2.70651006698608</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.72764205932617</t>
   </si>
   <si>
     <t xml:space="preserve">2.74064660072327</t>
   </si>
   <si>
-    <t xml:space="preserve">2.76990628242493</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.80079126358032</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.69513177871704</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.66749739646912</t>
+    <t xml:space="preserve">2.76990604400635</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.8007915019989</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.69513130187988</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.6674976348877</t>
   </si>
   <si>
     <t xml:space="preserve">2.64799118041992</t>
   </si>
   <si>
-    <t xml:space="preserve">2.62523365020752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.59759998321533</t>
+    <t xml:space="preserve">2.6252338886261</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.59759950637817</t>
   </si>
   <si>
     <t xml:space="preserve">2.61710619926453</t>
   </si>
   <si>
-    <t xml:space="preserve">2.6658718585968</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.63336181640625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.68862962722778</t>
+    <t xml:space="preserve">2.66587162017822</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.63336157798767</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.6886293888092</t>
   </si>
   <si>
     <t xml:space="preserve">2.6024763584137</t>
   </si>
   <si>
-    <t xml:space="preserve">2.677250623703</t>
+    <t xml:space="preserve">2.67725038528442</t>
   </si>
   <si>
     <t xml:space="preserve">2.70976138114929</t>
   </si>
   <si>
-    <t xml:space="preserve">2.7552764415741</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.72601699829102</t>
+    <t xml:space="preserve">2.75527620315552</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.72601675987244</t>
   </si>
   <si>
     <t xml:space="preserve">2.72276520729065</t>
@@ -560,31 +560,31 @@
     <t xml:space="preserve">2.82842540740967</t>
   </si>
   <si>
-    <t xml:space="preserve">2.7438976764679</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.7617781162262</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.73902058601379</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.70488476753235</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.69025492668152</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.61222982406616</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.73251867294312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.67562508583069</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.62360835075378</t>
+    <t xml:space="preserve">2.74389743804932</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.76177835464478</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.73902082443237</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.70488452911377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.69025468826294</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.61222958564758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.73251891136169</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.67562532424927</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.62360811233521</t>
   </si>
   <si>
     <t xml:space="preserve">2.59434843063354</t>
@@ -593,13 +593,13 @@
     <t xml:space="preserve">2.55371022224426</t>
   </si>
   <si>
-    <t xml:space="preserve">2.55045890808105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.51307201385498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.46755695343018</t>
+    <t xml:space="preserve">2.55045914649963</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.5130717754364</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.46755719184875</t>
   </si>
   <si>
     <t xml:space="preserve">2.50169324874878</t>
@@ -614,70 +614,70 @@
     <t xml:space="preserve">2.65611863136292</t>
   </si>
   <si>
-    <t xml:space="preserve">2.66912269592285</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.72439122200012</t>
+    <t xml:space="preserve">2.66912293434143</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.72439098358154</t>
   </si>
   <si>
     <t xml:space="preserve">2.78291034698486</t>
   </si>
   <si>
-    <t xml:space="preserve">2.77153134346008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.7780339717865</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.70000839233398</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.77315735816956</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.7650294303894</t>
+    <t xml:space="preserve">2.77153158187866</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.77803373336792</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.70000815391541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.7731568813324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.76502966880798</t>
   </si>
   <si>
     <t xml:space="preserve">2.71788883209229</t>
   </si>
   <si>
-    <t xml:space="preserve">2.74552321434021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.77965903282166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.74714851379395</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.60410189628601</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.62685966491699</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.64961647987366</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.69350576400757</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.69838237762451</t>
+    <t xml:space="preserve">2.74552297592163</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.77965950965881</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.74714875221252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.60410213470459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.62685918807983</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.64961671829224</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.69350600242615</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.69838261604309</t>
   </si>
   <si>
     <t xml:space="preserve">2.92270588874817</t>
   </si>
   <si>
-    <t xml:space="preserve">2.88531875610352</t>
+    <t xml:space="preserve">2.88531851768494</t>
   </si>
   <si>
     <t xml:space="preserve">2.99910593032837</t>
   </si>
   <si>
-    <t xml:space="preserve">2.97472262382507</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.96984648704529</t>
+    <t xml:space="preserve">2.97472286224365</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.96984672546387</t>
   </si>
   <si>
     <t xml:space="preserve">2.96334433555603</t>
@@ -686,22 +686,22 @@
     <t xml:space="preserve">2.94221234321594</t>
   </si>
   <si>
-    <t xml:space="preserve">2.93408465385437</t>
+    <t xml:space="preserve">2.93408441543579</t>
   </si>
   <si>
     <t xml:space="preserve">2.89832305908203</t>
   </si>
   <si>
-    <t xml:space="preserve">2.89182090759277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.87881684303284</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.87556576728821</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.84468078613281</t>
+    <t xml:space="preserve">2.89182066917419</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.87881660461426</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.87556552886963</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.84468054771423</t>
   </si>
   <si>
     <t xml:space="preserve">2.82192301750183</t>
@@ -710,7 +710,7 @@
     <t xml:space="preserve">2.84955716133118</t>
   </si>
   <si>
-    <t xml:space="preserve">2.91945505142212</t>
+    <t xml:space="preserve">2.91945481300354</t>
   </si>
   <si>
     <t xml:space="preserve">2.9259569644928</t>
@@ -722,73 +722,73 @@
     <t xml:space="preserve">2.9145781993866</t>
   </si>
   <si>
-    <t xml:space="preserve">2.91620397567749</t>
+    <t xml:space="preserve">2.91620373725891</t>
   </si>
   <si>
     <t xml:space="preserve">2.95846772193909</t>
   </si>
   <si>
-    <t xml:space="preserve">2.95684218406677</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.95196580886841</t>
+    <t xml:space="preserve">2.95684242248535</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.95196557044983</t>
   </si>
   <si>
     <t xml:space="preserve">3.04949760437012</t>
   </si>
   <si>
-    <t xml:space="preserve">3.0559995174408</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.99585509300232</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.9795994758606</t>
+    <t xml:space="preserve">3.05599927902222</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.9958553314209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.97959971427917</t>
   </si>
   <si>
     <t xml:space="preserve">3.00723361968994</t>
   </si>
   <si>
-    <t xml:space="preserve">3.09645915031433</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.11628746986389</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.16916155815125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.13941955566406</t>
+    <t xml:space="preserve">3.09645938873291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.11628723144531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.16916179656982</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.13941979408264</t>
   </si>
   <si>
     <t xml:space="preserve">3.14437675476074</t>
   </si>
   <si>
-    <t xml:space="preserve">3.18898963928223</t>
+    <t xml:space="preserve">3.18898940086365</t>
   </si>
   <si>
     <t xml:space="preserve">3.18072772026062</t>
   </si>
   <si>
-    <t xml:space="preserve">3.24847340583801</t>
+    <t xml:space="preserve">3.24847316741943</t>
   </si>
   <si>
     <t xml:space="preserve">3.21707940101624</t>
   </si>
   <si>
-    <t xml:space="preserve">3.16750955581665</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.15429067611694</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.170814037323</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.07663106918335</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.07497882843018</t>
+    <t xml:space="preserve">3.16750931739807</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.15429091453552</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.17081427574158</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.07663154602051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.07497930526733</t>
   </si>
   <si>
     <t xml:space="preserve">2.98244857788086</t>
@@ -800,40 +800,40 @@
     <t xml:space="preserve">3.06506514549255</t>
   </si>
   <si>
-    <t xml:space="preserve">3.0336709022522</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.02540922164917</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.99401545524597</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.99071049690247</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.99897217750549</t>
+    <t xml:space="preserve">3.03367066383362</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.02540946006775</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.99401521682739</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.99071002006531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.99897193908691</t>
   </si>
   <si>
     <t xml:space="preserve">2.93783617019653</t>
   </si>
   <si>
-    <t xml:space="preserve">2.95601177215576</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.07993578910828</t>
+    <t xml:space="preserve">2.95601153373718</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.07993602752686</t>
   </si>
   <si>
     <t xml:space="preserve">3.08819723129272</t>
   </si>
   <si>
-    <t xml:space="preserve">3.08654546737671</t>
+    <t xml:space="preserve">3.08654522895813</t>
   </si>
   <si>
     <t xml:space="preserve">3.10802555084229</t>
   </si>
   <si>
-    <t xml:space="preserve">3.11133027076721</t>
+    <t xml:space="preserve">3.11133050918579</t>
   </si>
   <si>
     <t xml:space="preserve">3.14768147468567</t>
@@ -845,19 +845,19 @@
     <t xml:space="preserve">3.20551300048828</t>
   </si>
   <si>
-    <t xml:space="preserve">3.21377420425415</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.23029804229736</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.23360252380371</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.25343036651611</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.29473829269409</t>
+    <t xml:space="preserve">3.21377468109131</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.23029756546021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.23360228538513</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.25343012809753</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.29473853111267</t>
   </si>
   <si>
     <t xml:space="preserve">3.3079571723938</t>
@@ -878,19 +878,19 @@
     <t xml:space="preserve">3.19394636154175</t>
   </si>
   <si>
-    <t xml:space="preserve">3.26334404945374</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.09811186790466</t>
+    <t xml:space="preserve">3.26334452629089</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.0981113910675</t>
   </si>
   <si>
     <t xml:space="preserve">3.15924739837646</t>
   </si>
   <si>
-    <t xml:space="preserve">3.17246603965759</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.17411851882935</t>
+    <t xml:space="preserve">3.17246627807617</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.17411875724792</t>
   </si>
   <si>
     <t xml:space="preserve">3.15098595619202</t>
@@ -902,13 +902,13 @@
     <t xml:space="preserve">3.05680346488953</t>
   </si>
   <si>
-    <t xml:space="preserve">3.08489298820496</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.12785363197327</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.03201866149902</t>
+    <t xml:space="preserve">3.08489274978638</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.12785339355469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.0320188999176</t>
   </si>
   <si>
     <t xml:space="preserve">3.09480690956116</t>
@@ -920,25 +920,25 @@
     <t xml:space="preserve">3.09150242805481</t>
   </si>
   <si>
-    <t xml:space="preserve">3.13115835189819</t>
+    <t xml:space="preserve">3.13115787506104</t>
   </si>
   <si>
     <t xml:space="preserve">3.10967755317688</t>
   </si>
   <si>
-    <t xml:space="preserve">3.10472106933594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.12124419212341</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.13611507415771</t>
+    <t xml:space="preserve">3.10472083091736</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.12124443054199</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.13611531257629</t>
   </si>
   <si>
     <t xml:space="preserve">3.1460292339325</t>
   </si>
   <si>
-    <t xml:space="preserve">3.12950563430786</t>
+    <t xml:space="preserve">3.12950611114502</t>
   </si>
   <si>
     <t xml:space="preserve">3.14107203483582</t>
@@ -947,16 +947,16 @@
     <t xml:space="preserve">3.15759539604187</t>
   </si>
   <si>
-    <t xml:space="preserve">3.18403291702271</t>
+    <t xml:space="preserve">3.18403244018555</t>
   </si>
   <si>
     <t xml:space="preserve">3.10637307167053</t>
   </si>
   <si>
-    <t xml:space="preserve">3.08158826828003</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.10141611099243</t>
+    <t xml:space="preserve">3.08158874511719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.10141634941101</t>
   </si>
   <si>
     <t xml:space="preserve">3.10306859016418</t>
@@ -965,43 +965,43 @@
     <t xml:space="preserve">3.12289643287659</t>
   </si>
   <si>
-    <t xml:space="preserve">3.08985018730164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.94940233230591</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.93287897109985</t>
+    <t xml:space="preserve">3.08984994888306</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.94940209388733</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.93287873268127</t>
   </si>
   <si>
     <t xml:space="preserve">2.83704400062561</t>
   </si>
   <si>
-    <t xml:space="preserve">2.88165688514709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.90809416770935</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.9113986492157</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.94609761238098</t>
+    <t xml:space="preserve">2.88165664672852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.90809392929077</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.91139841079712</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.9460973739624</t>
   </si>
   <si>
     <t xml:space="preserve">2.94114065170288</t>
   </si>
   <si>
-    <t xml:space="preserve">2.96592545509338</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.88496160507202</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.84034848213196</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.82878232002258</t>
+    <t xml:space="preserve">2.96592569351196</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.8849618434906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.84034895896912</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.82878255844116</t>
   </si>
   <si>
     <t xml:space="preserve">2.81225895881653</t>
@@ -1010,28 +1010,28 @@
     <t xml:space="preserve">2.8800048828125</t>
   </si>
   <si>
-    <t xml:space="preserve">2.75112318992615</t>
+    <t xml:space="preserve">2.75112295150757</t>
   </si>
   <si>
     <t xml:space="preserve">2.80895471572876</t>
   </si>
   <si>
-    <t xml:space="preserve">2.79243111610413</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.8139111995697</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.85852432250977</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.97418689727783</t>
+    <t xml:space="preserve">2.79243135452271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.81391143798828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.85852408409119</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.97418713569641</t>
   </si>
   <si>
     <t xml:space="preserve">2.97088241577148</t>
   </si>
   <si>
-    <t xml:space="preserve">3.01549530029297</t>
+    <t xml:space="preserve">3.01549553871155</t>
   </si>
   <si>
     <t xml:space="preserve">3.05515098571777</t>
@@ -1040,109 +1040,109 @@
     <t xml:space="preserve">3.04028034210205</t>
   </si>
   <si>
-    <t xml:space="preserve">3.07002234458923</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.06341290473938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.02375674247742</t>
+    <t xml:space="preserve">3.07002210617065</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.0634126663208</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.023756980896</t>
   </si>
   <si>
     <t xml:space="preserve">3.03697562217712</t>
   </si>
   <si>
-    <t xml:space="preserve">3.02871370315552</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.05349898338318</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.07828402519226</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.1105043888092</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.06919550895691</t>
+    <t xml:space="preserve">3.0287139415741</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.0534987449646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.0782835483551</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.11050462722778</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.06919574737549</t>
   </si>
   <si>
     <t xml:space="preserve">3.1559431552887</t>
   </si>
   <si>
-    <t xml:space="preserve">3.21790504455566</t>
+    <t xml:space="preserve">3.21790552139282</t>
   </si>
   <si>
     <t xml:space="preserve">3.17659735679626</t>
   </si>
   <si>
-    <t xml:space="preserve">3.19312024116516</t>
+    <t xml:space="preserve">3.19312000274658</t>
   </si>
   <si>
     <t xml:space="preserve">3.25508260726929</t>
   </si>
   <si>
-    <t xml:space="preserve">3.22203612327576</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.96179485321045</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.97831773757935</t>
+    <t xml:space="preserve">3.22203636169434</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.96179461479187</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.9783182144165</t>
   </si>
   <si>
     <t xml:space="preserve">2.92461729049683</t>
   </si>
   <si>
-    <t xml:space="preserve">2.8750479221344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.13528919219971</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.07745718955994</t>
+    <t xml:space="preserve">2.87504744529724</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.13528895378113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.07745742797852</t>
   </si>
   <si>
     <t xml:space="preserve">3.05267262458801</t>
   </si>
   <si>
-    <t xml:space="preserve">3.03614926338196</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.92048692703247</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.08571910858154</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.01962614059448</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.02788758277893</t>
+    <t xml:space="preserve">3.03614950180054</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.92048668861389</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.08571934700012</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.01962637901306</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.02788782119751</t>
   </si>
   <si>
     <t xml:space="preserve">3.0485417842865</t>
   </si>
   <si>
-    <t xml:space="preserve">3.04441070556641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.15181255340576</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.3376989364624</t>
+    <t xml:space="preserve">3.04441094398499</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.15181231498718</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.33769869804382</t>
   </si>
   <si>
     <t xml:space="preserve">3.25095176696777</t>
   </si>
   <si>
-    <t xml:space="preserve">3.27573680877686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.28399801254272</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.24682116508484</t>
+    <t xml:space="preserve">3.27573657035828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.28399848937988</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.24682092666626</t>
   </si>
   <si>
     <t xml:space="preserve">3.18485879898071</t>
@@ -1151,7 +1151,7 @@
     <t xml:space="preserve">3.24373769760132</t>
   </si>
   <si>
-    <t xml:space="preserve">3.20177507400513</t>
+    <t xml:space="preserve">3.20177483558655</t>
   </si>
   <si>
     <t xml:space="preserve">3.21016764640808</t>
@@ -1175,31 +1175,31 @@
     <t xml:space="preserve">3.14302659034729</t>
   </si>
   <si>
-    <t xml:space="preserve">3.20597124099731</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.25632667541504</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.24793410301208</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.10525989532471</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.07168936729431</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.18498992919922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.11365246772766</t>
+    <t xml:space="preserve">3.20597100257874</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.25632691383362</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.24793386459351</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.10526013374329</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.07168984413147</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.18498969078064</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.11365270614624</t>
   </si>
   <si>
     <t xml:space="preserve">3.12624144554138</t>
   </si>
   <si>
-    <t xml:space="preserve">3.13883066177368</t>
+    <t xml:space="preserve">3.1388304233551</t>
   </si>
   <si>
     <t xml:space="preserve">3.14722299575806</t>
@@ -1214,49 +1214,49 @@
     <t xml:space="preserve">3.08427858352661</t>
   </si>
   <si>
-    <t xml:space="preserve">3.13463377952576</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.16820430755615</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.10945630073547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.15981197357178</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.19338226318359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.21436357498169</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.23534560203552</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.26471924781799</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.32346796989441</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.31087851524353</t>
+    <t xml:space="preserve">3.13463425636292</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.16820478439331</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.10945653915405</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.15981245040894</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.19338250160217</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.21436381340027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.23534536361694</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.26471948623657</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.32346773147583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.31087875366211</t>
   </si>
   <si>
     <t xml:space="preserve">3.27730846405029</t>
   </si>
   <si>
-    <t xml:space="preserve">3.35703802108765</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.42417860031128</t>
+    <t xml:space="preserve">3.35703778266907</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.42417883872986</t>
   </si>
   <si>
     <t xml:space="preserve">3.49131941795349</t>
   </si>
   <si>
-    <t xml:space="preserve">3.43257141113281</t>
+    <t xml:space="preserve">3.43257117271423</t>
   </si>
   <si>
     <t xml:space="preserve">3.54167485237122</t>
@@ -1268,7 +1268,7 @@
     <t xml:space="preserve">3.48292708396912</t>
   </si>
   <si>
-    <t xml:space="preserve">3.51649737358093</t>
+    <t xml:space="preserve">3.51649761199951</t>
   </si>
   <si>
     <t xml:space="preserve">3.474534034729</t>
@@ -1289,10 +1289,10 @@
     <t xml:space="preserve">3.30248594284058</t>
   </si>
   <si>
-    <t xml:space="preserve">3.31927084922791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.29829001426697</t>
+    <t xml:space="preserve">3.31927132606506</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.29828977584839</t>
   </si>
   <si>
     <t xml:space="preserve">3.34025263786316</t>
@@ -1304,121 +1304,121 @@
     <t xml:space="preserve">3.28150463104248</t>
   </si>
   <si>
-    <t xml:space="preserve">3.39900088310242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.57524514198303</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.58783388137817</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.55006694793701</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.5794415473938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.58363747596741</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.6633677482605</t>
+    <t xml:space="preserve">3.399001121521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.57524538040161</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.58783364295959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.55006742477417</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.57944130897522</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.58363771438599</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.66336727142334</t>
   </si>
   <si>
     <t xml:space="preserve">3.55845999717712</t>
   </si>
   <si>
-    <t xml:space="preserve">3.56685280799866</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.62140488624573</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.78086352348328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.88577103614807</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.72211575508118</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.76407909393311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.68434834480286</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.79764938354492</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.82702350616455</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.80184626579285</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.83961200714111</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.91934180259705</t>
+    <t xml:space="preserve">3.56685304641724</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.62140464782715</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.78086376190186</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.88577175140381</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.7221155166626</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.76407885551453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.68434882164001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.7976496219635</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.82702302932739</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.80184578895569</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.83961129188538</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.91934204101562</t>
   </si>
   <si>
     <t xml:space="preserve">3.91094923019409</t>
   </si>
   <si>
-    <t xml:space="preserve">3.94451951980591</t>
+    <t xml:space="preserve">3.94451928138733</t>
   </si>
   <si>
     <t xml:space="preserve">4.06621170043945</t>
   </si>
   <si>
-    <t xml:space="preserve">4.02005243301392</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.927734375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.86898636817932</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.81863117218018</t>
+    <t xml:space="preserve">4.02005290985107</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.92773413658142</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.8689866065979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.8186309337616</t>
   </si>
   <si>
     <t xml:space="preserve">3.86059355735779</t>
   </si>
   <si>
-    <t xml:space="preserve">3.79345345497131</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.86478924751282</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.87737822532654</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.73470401763916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.84380888938904</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.69274187088013</t>
+    <t xml:space="preserve">3.79345297813416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.86478996276855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.87737846374512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.73470497131348</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.84380793571472</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.69274163246155</t>
   </si>
   <si>
     <t xml:space="preserve">3.90255689620972</t>
   </si>
   <si>
-    <t xml:space="preserve">3.95291256904602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.99067878723145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.00326776504517</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.9151451587677</t>
+    <t xml:space="preserve">3.95291209220886</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.9906792640686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.00326824188232</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.91514563560486</t>
   </si>
   <si>
     <t xml:space="preserve">3.87318205833435</t>
@@ -1427,28 +1427,28 @@
     <t xml:space="preserve">3.85220122337341</t>
   </si>
   <si>
-    <t xml:space="preserve">3.66756367683411</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.67595624923706</t>
+    <t xml:space="preserve">3.66756391525269</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.67595648765564</t>
   </si>
   <si>
     <t xml:space="preserve">3.59203028678894</t>
   </si>
   <si>
-    <t xml:space="preserve">3.53328251838684</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.70533084869385</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.6423864364624</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.77666759490967</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.71791911125183</t>
+    <t xml:space="preserve">3.53328204154968</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.70533037185669</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.64238595962524</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.77666735649109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.71791958808899</t>
   </si>
   <si>
     <t xml:space="preserve">3.64658236503601</t>
@@ -1457,46 +1457,46 @@
     <t xml:space="preserve">3.70113444328308</t>
   </si>
   <si>
-    <t xml:space="preserve">3.68015265464783</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.80604147911072</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.7850604057312</t>
+    <t xml:space="preserve">3.68015289306641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.8060417175293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.78506016731262</t>
   </si>
   <si>
     <t xml:space="preserve">3.69693851470947</t>
   </si>
   <si>
-    <t xml:space="preserve">3.73050832748413</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.7472939491272</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.65077900886536</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.65917110443115</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.85639691352844</t>
+    <t xml:space="preserve">3.73050856590271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.74729418754578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.65077877044678</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.65917134284973</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.85639715194702</t>
   </si>
   <si>
     <t xml:space="preserve">3.89416408538818</t>
   </si>
   <si>
-    <t xml:space="preserve">3.9361264705658</t>
+    <t xml:space="preserve">3.93612694740295</t>
   </si>
   <si>
     <t xml:space="preserve">4.00746393203735</t>
   </si>
   <si>
-    <t xml:space="preserve">4.08719348907471</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.11237144470215</t>
+    <t xml:space="preserve">4.08719396591187</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.11237192153931</t>
   </si>
   <si>
     <t xml:space="preserve">4.17111921310425</t>
@@ -1505,7 +1505,7 @@
     <t xml:space="preserve">4.19629716873169</t>
   </si>
   <si>
-    <t xml:space="preserve">4.23826026916504</t>
+    <t xml:space="preserve">4.2382607460022</t>
   </si>
   <si>
     <t xml:space="preserve">4.18790483474731</t>
@@ -1517,22 +1517,22 @@
     <t xml:space="preserve">4.0955867767334</t>
   </si>
   <si>
-    <t xml:space="preserve">4.07880115509033</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.14594173431396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.09139060974121</t>
+    <t xml:space="preserve">4.07880020141602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.14594221115112</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.09139013290405</t>
   </si>
   <si>
     <t xml:space="preserve">4.08299684524536</t>
   </si>
   <si>
-    <t xml:space="preserve">4.06201601028442</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.26343774795532</t>
+    <t xml:space="preserve">4.06201553344727</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.26343822479248</t>
   </si>
   <si>
     <t xml:space="preserve">4.3977198600769</t>
@@ -1541,22 +1541,22 @@
     <t xml:space="preserve">4.52360868453979</t>
   </si>
   <si>
-    <t xml:space="preserve">4.49843072891235</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.58235692977905</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.4816460609436</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.62431955337524</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.67467498779297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.69985246658325</t>
+    <t xml:space="preserve">4.49843168258667</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.58235645294189</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.48164558410645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.6243200302124</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.67467594146729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.69985294342041</t>
   </si>
   <si>
     <t xml:space="preserve">4.6830677986145</t>
@@ -1571,7 +1571,7 @@
     <t xml:space="preserve">4.44807529449463</t>
   </si>
   <si>
-    <t xml:space="preserve">4.43968296051025</t>
+    <t xml:space="preserve">4.4396824836731</t>
   </si>
   <si>
     <t xml:space="preserve">4.47325277328491</t>
@@ -1586,13 +1586,13 @@
     <t xml:space="preserve">4.5991415977478</t>
   </si>
   <si>
-    <t xml:space="preserve">4.61592721939087</t>
+    <t xml:space="preserve">4.61592769622803</t>
   </si>
   <si>
     <t xml:space="preserve">4.60753440856934</t>
   </si>
   <si>
-    <t xml:space="preserve">4.40611219406128</t>
+    <t xml:space="preserve">4.40611267089844</t>
   </si>
   <si>
     <t xml:space="preserve">4.53200101852417</t>
@@ -1604,28 +1604,28 @@
     <t xml:space="preserve">4.80895709991455</t>
   </si>
   <si>
-    <t xml:space="preserve">4.7418155670166</t>
+    <t xml:space="preserve">4.74181604385376</t>
   </si>
   <si>
     <t xml:space="preserve">4.69146060943604</t>
   </si>
   <si>
-    <t xml:space="preserve">4.6578893661499</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.50682353973389</t>
+    <t xml:space="preserve">4.65789031982422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.50682401657104</t>
   </si>
   <si>
     <t xml:space="preserve">4.5403938293457</t>
   </si>
   <si>
-    <t xml:space="preserve">4.46486043930054</t>
+    <t xml:space="preserve">4.46485996246338</t>
   </si>
   <si>
     <t xml:space="preserve">4.41450500488281</t>
   </si>
   <si>
-    <t xml:space="preserve">4.38932704925537</t>
+    <t xml:space="preserve">4.38932752609253</t>
   </si>
   <si>
     <t xml:space="preserve">4.380934715271</t>
@@ -1634,28 +1634,28 @@
     <t xml:space="preserve">4.34736394882202</t>
   </si>
   <si>
-    <t xml:space="preserve">4.46764707565308</t>
+    <t xml:space="preserve">4.46764659881592</t>
   </si>
   <si>
     <t xml:space="preserve">4.51919651031494</t>
   </si>
   <si>
-    <t xml:space="preserve">4.39891386032104</t>
+    <t xml:space="preserve">4.39891338348389</t>
   </si>
   <si>
     <t xml:space="preserve">4.37313890457153</t>
   </si>
   <si>
-    <t xml:space="preserve">4.30440616607666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.27003955841064</t>
+    <t xml:space="preserve">4.3044056892395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.27003908157349</t>
   </si>
   <si>
     <t xml:space="preserve">4.33018064498901</t>
   </si>
   <si>
-    <t xml:space="preserve">4.31299686431885</t>
+    <t xml:space="preserve">4.31299734115601</t>
   </si>
   <si>
     <t xml:space="preserve">4.38173055648804</t>
@@ -1664,43 +1664,43 @@
     <t xml:space="preserve">4.44187164306641</t>
   </si>
   <si>
-    <t xml:space="preserve">4.45905494689941</t>
+    <t xml:space="preserve">4.45905542373657</t>
   </si>
   <si>
     <t xml:space="preserve">4.35595560073853</t>
   </si>
   <si>
-    <t xml:space="preserve">4.39032220840454</t>
+    <t xml:space="preserve">4.3903226852417</t>
   </si>
   <si>
     <t xml:space="preserve">4.45046329498291</t>
   </si>
   <si>
-    <t xml:space="preserve">4.41609668731689</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.23137712478638</t>
+    <t xml:space="preserve">4.41609716415405</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.23137664794922</t>
   </si>
   <si>
     <t xml:space="preserve">4.26574325561523</t>
   </si>
   <si>
-    <t xml:space="preserve">4.13257312774658</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.04665660858154</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.08531951904297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.98221945762634</t>
+    <t xml:space="preserve">4.13257360458374</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.0466570854187</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.08531904220581</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.9822199344635</t>
   </si>
   <si>
     <t xml:space="preserve">4.03376913070679</t>
   </si>
   <si>
-    <t xml:space="preserve">3.94785332679749</t>
+    <t xml:space="preserve">3.94785261154175</t>
   </si>
   <si>
     <t xml:space="preserve">3.99081110954285</t>
@@ -1712,37 +1712,37 @@
     <t xml:space="preserve">3.94355773925781</t>
   </si>
   <si>
-    <t xml:space="preserve">3.96503686904907</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.96074032783508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.01229095458984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.92637419700623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.07243204116821</t>
+    <t xml:space="preserve">3.96503615379333</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.96074056625366</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.01229047775269</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.92637467384338</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.07243156433105</t>
   </si>
   <si>
     <t xml:space="preserve">4.08961534500122</t>
   </si>
   <si>
-    <t xml:space="preserve">4.11109495162964</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.26144790649414</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.32158899307251</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.295814037323</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.02947330474854</t>
+    <t xml:space="preserve">4.11109399795532</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.26144742965698</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.32158946990967</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.29581451416016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.02947425842285</t>
   </si>
   <si>
     <t xml:space="preserve">3.84045791625977</t>
@@ -1751,7 +1751,7 @@
     <t xml:space="preserve">3.87482452392578</t>
   </si>
   <si>
-    <t xml:space="preserve">3.88771176338196</t>
+    <t xml:space="preserve">3.88771224021912</t>
   </si>
   <si>
     <t xml:space="preserve">4.00369882583618</t>
@@ -1760,100 +1760,100 @@
     <t xml:space="preserve">4.02088212966919</t>
   </si>
   <si>
-    <t xml:space="preserve">3.93496608734131</t>
+    <t xml:space="preserve">3.93496561050415</t>
   </si>
   <si>
     <t xml:space="preserve">3.86623287200928</t>
   </si>
   <si>
-    <t xml:space="preserve">3.77172470092773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.71587920188904</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.7029914855957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.67721700668335</t>
+    <t xml:space="preserve">3.77172446250916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.71587944030762</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.70299196243286</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.67721724510193</t>
   </si>
   <si>
     <t xml:space="preserve">3.68580842018127</t>
   </si>
   <si>
-    <t xml:space="preserve">3.70728754997253</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.66432929039001</t>
+    <t xml:space="preserve">3.70728802680969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.66433000564575</t>
   </si>
   <si>
     <t xml:space="preserve">3.66003394126892</t>
   </si>
   <si>
-    <t xml:space="preserve">3.72017478942871</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.81468272209167</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.95214891433716</t>
+    <t xml:space="preserve">3.72017502784729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.81468319892883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.95214915275574</t>
   </si>
   <si>
     <t xml:space="preserve">3.85764098167419</t>
   </si>
   <si>
-    <t xml:space="preserve">3.78461217880249</t>
+    <t xml:space="preserve">3.78461241722107</t>
   </si>
   <si>
     <t xml:space="preserve">3.84475350379944</t>
   </si>
   <si>
-    <t xml:space="preserve">3.78031635284424</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.69440031051636</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.73306226730347</t>
+    <t xml:space="preserve">3.78031659126282</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.69440054893494</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.73306250572205</t>
   </si>
   <si>
     <t xml:space="preserve">3.71158361434937</t>
   </si>
   <si>
-    <t xml:space="preserve">3.59989261627197</t>
+    <t xml:space="preserve">3.59989237785339</t>
   </si>
   <si>
     <t xml:space="preserve">3.75454163551331</t>
   </si>
   <si>
-    <t xml:space="preserve">3.65144228935242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.72447085380554</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.78890824317932</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.64714646339417</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.66862535476685</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.67292165756226</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.6170756816864</t>
+    <t xml:space="preserve">3.65144205093384</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.72447061538696</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.78890776634216</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.64714598655701</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.66862559318542</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.67292094230652</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.61707592010498</t>
   </si>
   <si>
     <t xml:space="preserve">3.57411742210388</t>
   </si>
   <si>
-    <t xml:space="preserve">3.64285039901733</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.65573787689209</t>
+    <t xml:space="preserve">3.64285016059875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.65573811531067</t>
   </si>
   <si>
     <t xml:space="preserve">3.62996292114258</t>
@@ -1871,7 +1871,7 @@
     <t xml:space="preserve">3.9306697845459</t>
   </si>
   <si>
-    <t xml:space="preserve">4.01658582687378</t>
+    <t xml:space="preserve">4.01658630371094</t>
   </si>
   <si>
     <t xml:space="preserve">4.09820652008057</t>
@@ -1880,10 +1880,10 @@
     <t xml:space="preserve">4.14116477966309</t>
   </si>
   <si>
-    <t xml:space="preserve">4.24426412582397</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.24855995178223</t>
+    <t xml:space="preserve">4.24426460266113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.24856042861938</t>
   </si>
   <si>
     <t xml:space="preserve">4.43328046798706</t>
@@ -1892,7 +1892,7 @@
     <t xml:space="preserve">4.42468881607056</t>
   </si>
   <si>
-    <t xml:space="preserve">4.58793020248413</t>
+    <t xml:space="preserve">4.58792972564697</t>
   </si>
   <si>
     <t xml:space="preserve">4.57933759689331</t>
@@ -1901,7 +1901,7 @@
     <t xml:space="preserve">4.49342155456543</t>
   </si>
   <si>
-    <t xml:space="preserve">4.55356359481812</t>
+    <t xml:space="preserve">4.55356311798096</t>
   </si>
   <si>
     <t xml:space="preserve">4.48482990264893</t>
@@ -1910,19 +1910,19 @@
     <t xml:space="preserve">4.53637981414795</t>
   </si>
   <si>
-    <t xml:space="preserve">4.59652137756348</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.77694463729858</t>
+    <t xml:space="preserve">4.59652090072632</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.77694511413574</t>
   </si>
   <si>
     <t xml:space="preserve">4.81131172180176</t>
   </si>
   <si>
-    <t xml:space="preserve">4.69962072372437</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.64807033538818</t>
+    <t xml:space="preserve">4.69962024688721</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.64807081222534</t>
   </si>
   <si>
     <t xml:space="preserve">4.72539520263672</t>
@@ -1934,7 +1934,7 @@
     <t xml:space="preserve">4.69102907180786</t>
   </si>
   <si>
-    <t xml:space="preserve">4.68243741989136</t>
+    <t xml:space="preserve">4.6824369430542</t>
   </si>
   <si>
     <t xml:space="preserve">4.70821189880371</t>
@@ -1943,13 +1943,13 @@
     <t xml:space="preserve">4.67384576797485</t>
   </si>
   <si>
-    <t xml:space="preserve">4.5621542930603</t>
+    <t xml:space="preserve">4.56215476989746</t>
   </si>
   <si>
     <t xml:space="preserve">4.50201272964478</t>
   </si>
   <si>
-    <t xml:space="preserve">4.54497146606445</t>
+    <t xml:space="preserve">4.54497098922729</t>
   </si>
   <si>
     <t xml:space="preserve">4.51060485839844</t>
@@ -1958,7 +1958,7 @@
     <t xml:space="preserve">4.52778768539429</t>
   </si>
   <si>
-    <t xml:space="preserve">4.7683539390564</t>
+    <t xml:space="preserve">4.76835346221924</t>
   </si>
   <si>
     <t xml:space="preserve">4.66525411605835</t>
@@ -1973,40 +1973,40 @@
     <t xml:space="preserve">4.639479637146</t>
   </si>
   <si>
-    <t xml:space="preserve">4.23567247390747</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.15834808349609</t>
+    <t xml:space="preserve">4.23567295074463</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.15834903717041</t>
   </si>
   <si>
     <t xml:space="preserve">4.20130634307861</t>
   </si>
   <si>
-    <t xml:space="preserve">4.36454677581787</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.60511302947998</t>
+    <t xml:space="preserve">4.36454725265503</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.60511255264282</t>
   </si>
   <si>
     <t xml:space="preserve">4.11538982391357</t>
   </si>
   <si>
-    <t xml:space="preserve">3.75024580955505</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.47101783752441</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.36362266540527</t>
+    <t xml:space="preserve">3.75024557113647</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.47101759910583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.36362242698669</t>
   </si>
   <si>
     <t xml:space="preserve">3.31207275390625</t>
   </si>
   <si>
-    <t xml:space="preserve">3.16601514816284</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.22186040878296</t>
+    <t xml:space="preserve">3.16601490974426</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.22186088562012</t>
   </si>
   <si>
     <t xml:space="preserve">2.80516672134399</t>
@@ -2018,25 +2018,25 @@
     <t xml:space="preserve">2.86530804634094</t>
   </si>
   <si>
-    <t xml:space="preserve">2.8867871761322</t>
+    <t xml:space="preserve">2.88678693771362</t>
   </si>
   <si>
     <t xml:space="preserve">2.73213791847229</t>
   </si>
   <si>
-    <t xml:space="preserve">2.66770052909851</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.80087065696716</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.61185479164124</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.72354674339294</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.92115330696106</t>
+    <t xml:space="preserve">2.66770029067993</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.80087089538574</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.61185503005981</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.72354626655579</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.92115354537964</t>
   </si>
   <si>
     <t xml:space="preserve">2.8137583732605</t>
@@ -2048,10 +2048,10 @@
     <t xml:space="preserve">2.65910911560059</t>
   </si>
   <si>
-    <t xml:space="preserve">2.84382891654968</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.76650428771973</t>
+    <t xml:space="preserve">2.84382915496826</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.76650452613831</t>
   </si>
   <si>
     <t xml:space="preserve">2.78798317909241</t>
@@ -2063,16 +2063,16 @@
     <t xml:space="preserve">2.71065878868103</t>
   </si>
   <si>
-    <t xml:space="preserve">2.85242080688477</t>
+    <t xml:space="preserve">2.85242033004761</t>
   </si>
   <si>
     <t xml:space="preserve">2.89108300209045</t>
   </si>
   <si>
-    <t xml:space="preserve">2.9297456741333</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.00706958770752</t>
+    <t xml:space="preserve">2.92974543571472</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.00707006454468</t>
   </si>
   <si>
     <t xml:space="preserve">2.96411180496216</t>
@@ -2093,10 +2093,10 @@
     <t xml:space="preserve">2.94692850112915</t>
   </si>
   <si>
-    <t xml:space="preserve">2.97699928283691</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.95122456550598</t>
+    <t xml:space="preserve">2.97699904441833</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.9512243270874</t>
   </si>
   <si>
     <t xml:space="preserve">3.10587382316589</t>
@@ -2105,13 +2105,13 @@
     <t xml:space="preserve">3.04143643379211</t>
   </si>
   <si>
-    <t xml:space="preserve">3.05002808570862</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.08439469337463</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.13164830207825</t>
+    <t xml:space="preserve">3.05002784729004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.08439445495605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.13164854049683</t>
   </si>
   <si>
     <t xml:space="preserve">3.03284502029419</t>
@@ -2123,16 +2123,16 @@
     <t xml:space="preserve">3.1917896270752</t>
   </si>
   <si>
-    <t xml:space="preserve">3.24763536453247</t>
+    <t xml:space="preserve">3.24763560295105</t>
   </si>
   <si>
     <t xml:space="preserve">3.16171932220459</t>
   </si>
   <si>
-    <t xml:space="preserve">3.14883160591125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.18319821357727</t>
+    <t xml:space="preserve">3.14883208274841</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.18319845199585</t>
   </si>
   <si>
     <t xml:space="preserve">3.13594460487366</t>
@@ -2141,7 +2141,7 @@
     <t xml:space="preserve">3.11876106262207</t>
   </si>
   <si>
-    <t xml:space="preserve">3.307776927948</t>
+    <t xml:space="preserve">3.30777668952942</t>
   </si>
   <si>
     <t xml:space="preserve">3.38510179519653</t>
@@ -2150,52 +2150,52 @@
     <t xml:space="preserve">3.4366512298584</t>
   </si>
   <si>
-    <t xml:space="preserve">3.48390555381775</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.46242642402649</t>
+    <t xml:space="preserve">3.48390507698059</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.46242666244507</t>
   </si>
   <si>
     <t xml:space="preserve">3.47960948944092</t>
   </si>
   <si>
-    <t xml:space="preserve">3.31636810302734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.29488921165466</t>
+    <t xml:space="preserve">3.31636834144592</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.29488945007324</t>
   </si>
   <si>
     <t xml:space="preserve">3.19608592987061</t>
   </si>
   <si>
-    <t xml:space="preserve">3.38080596923828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.37651014328003</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.35073494911194</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.3722140789032</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.42805957794189</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.44094705581665</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.44524312019348</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.75857472419739</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.71435570716858</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.63034105300903</t>
+    <t xml:space="preserve">3.3808057308197</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.37650990486145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.35073518753052</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.37221431732178</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.42805981636047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.44094753265381</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.4452428817749</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.75857448577881</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.71435618400574</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.63034081459045</t>
   </si>
   <si>
     <t xml:space="preserve">3.58170080184937</t>
@@ -2207,22 +2207,22 @@
     <t xml:space="preserve">3.50210738182068</t>
   </si>
   <si>
-    <t xml:space="preserve">3.43135786056519</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.44904518127441</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.36060786247253</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.38713932037354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.41809225082397</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.32081127166748</t>
+    <t xml:space="preserve">3.43135762214661</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.44904541969299</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.36060810089111</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.38713908195496</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.4180920124054</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.32081174850464</t>
   </si>
   <si>
     <t xml:space="preserve">3.33849883079529</t>
@@ -2231,7 +2231,7 @@
     <t xml:space="preserve">3.31638956069946</t>
   </si>
   <si>
-    <t xml:space="preserve">3.27217078208923</t>
+    <t xml:space="preserve">3.27217102050781</t>
   </si>
   <si>
     <t xml:space="preserve">3.28101468086243</t>
@@ -2246,22 +2246,22 @@
     <t xml:space="preserve">3.18373370170593</t>
   </si>
   <si>
-    <t xml:space="preserve">3.25448346138</t>
+    <t xml:space="preserve">3.25448369979858</t>
   </si>
   <si>
     <t xml:space="preserve">3.20584321022034</t>
   </si>
   <si>
-    <t xml:space="preserve">3.1660463809967</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.15720272064209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.13951516151428</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.10414028167725</t>
+    <t xml:space="preserve">3.16604614257812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.15720295906067</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.1395149230957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.10414052009583</t>
   </si>
   <si>
     <t xml:space="preserve">3.09971857070923</t>
@@ -2276,13 +2276,13 @@
     <t xml:space="preserve">3.0776093006134</t>
   </si>
   <si>
-    <t xml:space="preserve">3.05992221832275</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.98032832145691</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.96264100074768</t>
+    <t xml:space="preserve">3.05992197990417</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.98032855987549</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.96264123916626</t>
   </si>
   <si>
     <t xml:space="preserve">2.94495368003845</t>
@@ -2291,25 +2291,25 @@
     <t xml:space="preserve">2.93611001968384</t>
   </si>
   <si>
-    <t xml:space="preserve">3.09087467193604</t>
+    <t xml:space="preserve">3.09087491035461</t>
   </si>
   <si>
     <t xml:space="preserve">3.06876587867737</t>
   </si>
   <si>
-    <t xml:space="preserve">3.05550003051758</t>
+    <t xml:space="preserve">3.05550026893616</t>
   </si>
   <si>
     <t xml:space="preserve">2.98475050926208</t>
   </si>
   <si>
-    <t xml:space="preserve">2.9051570892334</t>
+    <t xml:space="preserve">2.90515732765198</t>
   </si>
   <si>
     <t xml:space="preserve">2.83440756797791</t>
   </si>
   <si>
-    <t xml:space="preserve">2.86978197097778</t>
+    <t xml:space="preserve">2.86978220939636</t>
   </si>
   <si>
     <t xml:space="preserve">2.80345463752747</t>
@@ -2327,22 +2327,22 @@
     <t xml:space="preserve">2.82998585700989</t>
   </si>
   <si>
-    <t xml:space="preserve">2.79461097717285</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.91842246055603</t>
+    <t xml:space="preserve">2.79461073875427</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.91842269897461</t>
   </si>
   <si>
     <t xml:space="preserve">2.82114195823669</t>
   </si>
   <si>
-    <t xml:space="preserve">2.79903292655945</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.80787634849548</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.75923562049866</t>
+    <t xml:space="preserve">2.79903244972229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.80787658691406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.75923585891724</t>
   </si>
   <si>
     <t xml:space="preserve">2.7238609790802</t>
@@ -2357,19 +2357,19 @@
     <t xml:space="preserve">2.63542413711548</t>
   </si>
   <si>
-    <t xml:space="preserve">2.61773705482483</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.58236193656921</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.54698705673218</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.56467485427856</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.55140900611877</t>
+    <t xml:space="preserve">2.61773681640625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.58236217498779</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.54698729515076</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.56467461585999</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.5514087677002</t>
   </si>
   <si>
     <t xml:space="preserve">2.49392485618591</t>
@@ -2378,7 +2378,7 @@
     <t xml:space="preserve">2.5735182762146</t>
   </si>
   <si>
-    <t xml:space="preserve">2.97148513793945</t>
+    <t xml:space="preserve">2.97148489952087</t>
   </si>
   <si>
     <t xml:space="preserve">2.95379757881165</t>
@@ -2387,7 +2387,7 @@
     <t xml:space="preserve">3.00243782997131</t>
   </si>
   <si>
-    <t xml:space="preserve">3.17931222915649</t>
+    <t xml:space="preserve">3.17931199073792</t>
   </si>
   <si>
     <t xml:space="preserve">3.1704683303833</t>
@@ -2396,7 +2396,7 @@
     <t xml:space="preserve">3.19257736206055</t>
   </si>
   <si>
-    <t xml:space="preserve">3.28985857963562</t>
+    <t xml:space="preserve">3.28985834121704</t>
   </si>
   <si>
     <t xml:space="preserve">3.29870223999023</t>
@@ -2411,7 +2411,7 @@
     <t xml:space="preserve">3.48442006111145</t>
   </si>
   <si>
-    <t xml:space="preserve">3.45788860321045</t>
+    <t xml:space="preserve">3.45788884162903</t>
   </si>
   <si>
     <t xml:space="preserve">3.49326348304749</t>
@@ -2420,7 +2420,7 @@
     <t xml:space="preserve">3.51095080375671</t>
   </si>
   <si>
-    <t xml:space="preserve">3.44462299346924</t>
+    <t xml:space="preserve">3.44462323188782</t>
   </si>
   <si>
     <t xml:space="preserve">3.42693567276001</t>
@@ -2429,10 +2429,10 @@
     <t xml:space="preserve">3.55516934394836</t>
   </si>
   <si>
-    <t xml:space="preserve">3.67898106575012</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.72319960594177</t>
+    <t xml:space="preserve">3.6789813041687</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.72320008277893</t>
   </si>
   <si>
     <t xml:space="preserve">3.74973082542419</t>
@@ -2444,40 +2444,40 @@
     <t xml:space="preserve">3.65687227249146</t>
   </si>
   <si>
-    <t xml:space="preserve">3.66129374504089</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.65245032310486</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.62591910362244</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.60823154449463</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.54632592201233</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.53748226165771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.57285714149475</t>
+    <t xml:space="preserve">3.66129398345947</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.65245008468628</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.62591886520386</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.60823178291321</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.54632616043091</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.53748202323914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.57285666465759</t>
   </si>
   <si>
     <t xml:space="preserve">3.5065290927887</t>
   </si>
   <si>
-    <t xml:space="preserve">3.5905442237854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.57727861404419</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.74530911445618</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.74088764190674</t>
+    <t xml:space="preserve">3.59054446220398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.57727885246277</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.74530935287476</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.74088716506958</t>
   </si>
   <si>
     <t xml:space="preserve">3.73204374313354</t>
@@ -2492,49 +2492,49 @@
     <t xml:space="preserve">3.83816838264465</t>
   </si>
   <si>
-    <t xml:space="preserve">3.68340373039246</t>
+    <t xml:space="preserve">3.68340349197388</t>
   </si>
   <si>
     <t xml:space="preserve">3.76741862297058</t>
   </si>
   <si>
-    <t xml:space="preserve">3.78068423271179</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.76299667358398</t>
+    <t xml:space="preserve">3.78068375587463</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.76299691200256</t>
   </si>
   <si>
     <t xml:space="preserve">3.7718403339386</t>
   </si>
   <si>
-    <t xml:space="preserve">3.71877813339233</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.68782496452332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.59938812255859</t>
+    <t xml:space="preserve">3.71877789497375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.68782520294189</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.59938788414001</t>
   </si>
   <si>
     <t xml:space="preserve">3.66571545600891</t>
   </si>
   <si>
-    <t xml:space="preserve">3.70993447303772</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.78510570526123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.92660570144653</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.93987083435059</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.99735498428345</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.01079893112183</t>
+    <t xml:space="preserve">3.7099347114563</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.78510618209839</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.9266049861908</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.93987035751343</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.99735450744629</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.01079845428467</t>
   </si>
   <si>
     <t xml:space="preserve">4.09594440460205</t>
@@ -2549,43 +2549,43 @@
     <t xml:space="preserve">4.13627576828003</t>
   </si>
   <si>
-    <t xml:space="preserve">4.19901466369629</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.14075756072998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.10490703582764</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.06905555725098</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.03320503234863</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.9794294834137</t>
+    <t xml:space="preserve">4.19901514053345</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.14075708389282</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.10490655899048</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.06905603408813</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.03320550918579</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.97942924499512</t>
   </si>
   <si>
     <t xml:space="preserve">4.02872371673584</t>
   </si>
   <si>
-    <t xml:space="preserve">4.05561208724976</t>
+    <t xml:space="preserve">4.05561256408691</t>
   </si>
   <si>
     <t xml:space="preserve">4.08698129653931</t>
   </si>
   <si>
-    <t xml:space="preserve">3.97494769096375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.00183629989624</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.01528024673462</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.96150374412537</t>
+    <t xml:space="preserve">3.97494792938232</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.00183582305908</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.01527976989746</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.96150398254395</t>
   </si>
   <si>
     <t xml:space="preserve">3.9883918762207</t>
@@ -2594,7 +2594,7 @@
     <t xml:space="preserve">3.95254135131836</t>
   </si>
   <si>
-    <t xml:space="preserve">3.96598553657532</t>
+    <t xml:space="preserve">3.96598529815674</t>
   </si>
   <si>
     <t xml:space="preserve">4.04216861724854</t>
@@ -2606,34 +2606,34 @@
     <t xml:space="preserve">4.11835050582886</t>
   </si>
   <si>
-    <t xml:space="preserve">4.17660808563232</t>
+    <t xml:space="preserve">4.17660760879517</t>
   </si>
   <si>
     <t xml:space="preserve">4.11386966705322</t>
   </si>
   <si>
-    <t xml:space="preserve">4.10938787460327</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.06009340286255</t>
+    <t xml:space="preserve">4.10938835144043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.06009387969971</t>
   </si>
   <si>
     <t xml:space="preserve">4.1945333480835</t>
   </si>
   <si>
-    <t xml:space="preserve">4.21245908737183</t>
+    <t xml:space="preserve">4.21245861053467</t>
   </si>
   <si>
     <t xml:space="preserve">4.14972019195557</t>
   </si>
   <si>
-    <t xml:space="preserve">4.12283182144165</t>
+    <t xml:space="preserve">4.12283229827881</t>
   </si>
   <si>
     <t xml:space="preserve">4.03768682479858</t>
   </si>
   <si>
-    <t xml:space="preserve">4.01976108551025</t>
+    <t xml:space="preserve">4.01976156234741</t>
   </si>
   <si>
     <t xml:space="preserve">4.06457471847534</t>
@@ -2648,34 +2648,34 @@
     <t xml:space="preserve">4.25727224349976</t>
   </si>
   <si>
-    <t xml:space="preserve">4.20349597930908</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.92565321922302</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.90772771835327</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.88084006309509</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.87635850906372</t>
+    <t xml:space="preserve">4.20349645614624</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.92565298080444</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.90772819519043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.88083982467651</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.87635803222656</t>
   </si>
   <si>
     <t xml:space="preserve">3.80913805961609</t>
   </si>
   <si>
-    <t xml:space="preserve">3.71503019332886</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.66573596000671</t>
+    <t xml:space="preserve">3.71503043174744</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.66573572158813</t>
   </si>
   <si>
     <t xml:space="preserve">3.83154535293579</t>
   </si>
   <si>
-    <t xml:space="preserve">3.93461585044861</t>
+    <t xml:space="preserve">3.93461561203003</t>
   </si>
   <si>
     <t xml:space="preserve">3.94357872009277</t>
@@ -2684,10 +2684,10 @@
     <t xml:space="preserve">4.04664945602417</t>
   </si>
   <si>
-    <t xml:space="preserve">3.99287366867065</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.98391103744507</t>
+    <t xml:space="preserve">3.9928731918335</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.98391056060791</t>
   </si>
   <si>
     <t xml:space="preserve">4.02424240112305</t>
@@ -2696,28 +2696,28 @@
     <t xml:space="preserve">3.85395193099976</t>
   </si>
   <si>
-    <t xml:space="preserve">3.93013501167297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.97046637535095</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.10042572021484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.15420198440552</t>
+    <t xml:space="preserve">3.93013477325439</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.97046661376953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.10042524337769</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.15420150756836</t>
   </si>
   <si>
     <t xml:space="preserve">4.09146308898926</t>
   </si>
   <si>
-    <t xml:space="preserve">4.22590351104736</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.2662353515625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.24382781982422</t>
+    <t xml:space="preserve">4.22590303421021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.26623487472534</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.24382829666138</t>
   </si>
   <si>
     <t xml:space="preserve">4.13179492950439</t>
@@ -2726,34 +2726,34 @@
     <t xml:space="preserve">4.1273136138916</t>
   </si>
   <si>
-    <t xml:space="preserve">4.24830913543701</t>
+    <t xml:space="preserve">4.24830961227417</t>
   </si>
   <si>
     <t xml:space="preserve">4.19005250930786</t>
   </si>
   <si>
-    <t xml:space="preserve">4.2931227684021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.40515661239624</t>
+    <t xml:space="preserve">4.29312324523926</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.40515613555908</t>
   </si>
   <si>
     <t xml:space="preserve">4.43652582168579</t>
   </si>
   <si>
-    <t xml:space="preserve">4.48133897781372</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.53511524200439</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.55304098129272</t>
+    <t xml:space="preserve">4.48133945465088</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.53511571884155</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.55304050445557</t>
   </si>
   <si>
     <t xml:space="preserve">4.56200361251831</t>
   </si>
   <si>
-    <t xml:space="preserve">4.50822782516479</t>
+    <t xml:space="preserve">4.50822734832764</t>
   </si>
   <si>
     <t xml:space="preserve">4.45445108413696</t>
@@ -2768,19 +2768,19 @@
     <t xml:space="preserve">4.49030208587646</t>
   </si>
   <si>
-    <t xml:space="preserve">4.51718950271606</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.63370513916016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.59785461425781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.47685718536377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.57096576690674</t>
+    <t xml:space="preserve">4.51718997955322</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.633704662323</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.59785413742065</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.47685813903809</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.5709662437439</t>
   </si>
   <si>
     <t xml:space="preserve">4.61577939987183</t>
@@ -2795,10 +2795,10 @@
     <t xml:space="preserve">4.44997024536133</t>
   </si>
   <si>
-    <t xml:space="preserve">4.27519798278809</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.58889102935791</t>
+    <t xml:space="preserve">4.27519750595093</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.58889198303223</t>
   </si>
   <si>
     <t xml:space="preserve">4.66059303283691</t>
@@ -2807,19 +2807,19 @@
     <t xml:space="preserve">4.65163040161133</t>
   </si>
   <si>
-    <t xml:space="preserve">4.71436929702759</t>
+    <t xml:space="preserve">4.71436977386475</t>
   </si>
   <si>
     <t xml:space="preserve">4.75918245315552</t>
   </si>
   <si>
-    <t xml:space="preserve">4.76814556121826</t>
+    <t xml:space="preserve">4.7681450843811</t>
   </si>
   <si>
     <t xml:space="preserve">4.89362287521362</t>
   </si>
   <si>
-    <t xml:space="preserve">4.92051029205322</t>
+    <t xml:space="preserve">4.92051076889038</t>
   </si>
   <si>
     <t xml:space="preserve">4.88465976715088</t>
@@ -2831,25 +2831,25 @@
     <t xml:space="preserve">5.01910018920898</t>
   </si>
   <si>
-    <t xml:space="preserve">5.14457702636719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.31486845016479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.37760734558105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.35968208312988</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.16250324249268</t>
+    <t xml:space="preserve">5.14457750320435</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.31486797332764</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.3776068687439</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.35968160629272</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.16250276565552</t>
   </si>
   <si>
     <t xml:space="preserve">5.0459885597229</t>
   </si>
   <si>
-    <t xml:space="preserve">5.15354061126709</t>
+    <t xml:space="preserve">5.15354013442993</t>
   </si>
   <si>
     <t xml:space="preserve">5.26109218597412</t>
@@ -2858,46 +2858,46 @@
     <t xml:space="preserve">5.27901744842529</t>
   </si>
   <si>
-    <t xml:space="preserve">5.512047290802</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.47619676589966</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.50308465957642</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.29694271087646</t>
+    <t xml:space="preserve">5.51204776763916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.4761962890625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.50308418273926</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.29694318771362</t>
   </si>
   <si>
     <t xml:space="preserve">5.19835329055786</t>
   </si>
   <si>
-    <t xml:space="preserve">5.18042898178101</t>
+    <t xml:space="preserve">5.18042802810669</t>
   </si>
   <si>
     <t xml:space="preserve">5.0728759765625</t>
   </si>
   <si>
-    <t xml:space="preserve">5.09080123901367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.99221229553223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.75021934509277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.80399560928345</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.92947292327881</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.83984661102295</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.9742865562439</t>
+    <t xml:space="preserve">5.09080171585083</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.99221277236938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.75022029876709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.80399608612061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.92947340011597</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.83984708786011</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.97428703308105</t>
   </si>
   <si>
     <t xml:space="preserve">4.90258502960205</t>
@@ -2906,7 +2906,7 @@
     <t xml:space="preserve">4.86673450469971</t>
   </si>
   <si>
-    <t xml:space="preserve">5.037024974823</t>
+    <t xml:space="preserve">5.03702545166016</t>
   </si>
   <si>
     <t xml:space="preserve">4.95636177062988</t>
@@ -2915,19 +2915,19 @@
     <t xml:space="preserve">4.79503297805786</t>
   </si>
   <si>
-    <t xml:space="preserve">4.74125671386719</t>
+    <t xml:space="preserve">4.74125719070435</t>
   </si>
   <si>
     <t xml:space="preserve">4.70540618896484</t>
   </si>
   <si>
-    <t xml:space="preserve">4.52615261077881</t>
+    <t xml:space="preserve">4.52615308761597</t>
   </si>
   <si>
     <t xml:space="preserve">4.41860055923462</t>
   </si>
   <si>
-    <t xml:space="preserve">4.3648247718811</t>
+    <t xml:space="preserve">4.36482429504395</t>
   </si>
   <si>
     <t xml:space="preserve">4.23934698104858</t>
@@ -2936,28 +2936,28 @@
     <t xml:space="preserve">4.85777187347412</t>
   </si>
   <si>
-    <t xml:space="preserve">4.91154766082764</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.96532392501831</t>
+    <t xml:space="preserve">4.91154813766479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.96532440185547</t>
   </si>
   <si>
     <t xml:space="preserve">5.11768960952759</t>
   </si>
   <si>
-    <t xml:space="preserve">5.22524166107178</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.30590581893921</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.42242050170898</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.28798055648804</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.43138313293457</t>
+    <t xml:space="preserve">5.22524118423462</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.30590534210205</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.42242097854614</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.28798007965088</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.43138265609741</t>
   </si>
   <si>
     <t xml:space="preserve">5.55686044692993</t>
@@ -71280,7 +71280,7 @@
     </row>
     <row r="2556">
       <c r="A2556" s="1" t="n">
-        <v>46044.6910185185</v>
+        <v>46044.3333333333</v>
       </c>
       <c r="B2556" t="n">
         <v>17631</v>
@@ -71301,6 +71301,32 @@
         <v>1499</v>
       </c>
       <c r="H2556" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2557">
+      <c r="A2557" s="1" t="n">
+        <v>46045.6912037037</v>
+      </c>
+      <c r="B2557" t="n">
+        <v>7509</v>
+      </c>
+      <c r="C2557" t="n">
+        <v>7.23000001907349</v>
+      </c>
+      <c r="D2557" t="n">
+        <v>7.11999988555908</v>
+      </c>
+      <c r="E2557" t="n">
+        <v>7.19999980926514</v>
+      </c>
+      <c r="F2557" t="n">
+        <v>7.15000009536743</v>
+      </c>
+      <c r="G2557" t="s">
+        <v>1460</v>
+      </c>
+      <c r="H2557" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/BAN.MI.xlsx
+++ b/data/BAN.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1500" uniqueCount="1500">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1501" uniqueCount="1501">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -38,13 +38,13 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">3.66913032531738</t>
+    <t xml:space="preserve">3.66912913322449</t>
   </si>
   <si>
     <t xml:space="preserve">BAN.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">3.68330240249634</t>
+    <t xml:space="preserve">3.68330264091492</t>
   </si>
   <si>
     <t xml:space="preserve">3.59039306640625</t>
@@ -56,22 +56,22 @@
     <t xml:space="preserve">3.41874718666077</t>
   </si>
   <si>
-    <t xml:space="preserve">3.35733294487</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.44551753997803</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.46441459655762</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.45181655883789</t>
+    <t xml:space="preserve">3.35733246803284</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.44551777839661</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.46441435813904</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.45181632041931</t>
   </si>
   <si>
     <t xml:space="preserve">3.43134474754333</t>
   </si>
   <si>
-    <t xml:space="preserve">3.38410258293152</t>
+    <t xml:space="preserve">3.38410329818726</t>
   </si>
   <si>
     <t xml:space="preserve">3.40929865837097</t>
@@ -80,46 +80,46 @@
     <t xml:space="preserve">3.11639809608459</t>
   </si>
   <si>
-    <t xml:space="preserve">3.240802526474</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.29119372367859</t>
+    <t xml:space="preserve">3.24080228805542</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.29119348526001</t>
   </si>
   <si>
     <t xml:space="preserve">3.21245694160461</t>
   </si>
   <si>
-    <t xml:space="preserve">3.26757264137268</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.19356036186218</t>
+    <t xml:space="preserve">3.26757287979126</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.1935601234436</t>
   </si>
   <si>
     <t xml:space="preserve">3.13372039794922</t>
   </si>
   <si>
-    <t xml:space="preserve">3.22820448875427</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.16678953170776</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.17308855056763</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.07073163986206</t>
+    <t xml:space="preserve">3.22820425033569</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.16678905487061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.17308926582336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.0707311630249</t>
   </si>
   <si>
     <t xml:space="preserve">3.14946746826172</t>
   </si>
   <si>
-    <t xml:space="preserve">3.05025911331177</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.92900466918945</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.91325759887695</t>
+    <t xml:space="preserve">3.05025935173035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.92900514602661</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.91325783729553</t>
   </si>
   <si>
     <t xml:space="preserve">2.83452081680298</t>
@@ -128,28 +128,28 @@
     <t xml:space="preserve">2.82664728164673</t>
   </si>
   <si>
-    <t xml:space="preserve">2.75263476371765</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.75420951843262</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.75578451156616</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.89436078071594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.98254632949829</t>
+    <t xml:space="preserve">2.75263500213623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.75420928001404</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.755784034729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.89436101913452</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.98254561424255</t>
   </si>
   <si>
     <t xml:space="preserve">2.96207427978516</t>
   </si>
   <si>
-    <t xml:space="preserve">2.99356889724731</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.05970811843872</t>
+    <t xml:space="preserve">2.99356913566589</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.05970764160156</t>
   </si>
   <si>
     <t xml:space="preserve">3.11009931564331</t>
@@ -158,16 +158,16 @@
     <t xml:space="preserve">3.06915616989136</t>
   </si>
   <si>
-    <t xml:space="preserve">2.9636492729187</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.99199414253235</t>
+    <t xml:space="preserve">2.96364903450012</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.99199438095093</t>
   </si>
   <si>
     <t xml:space="preserve">3.00774192810059</t>
   </si>
   <si>
-    <t xml:space="preserve">2.97624707221985</t>
+    <t xml:space="preserve">2.97624683380127</t>
   </si>
   <si>
     <t xml:space="preserve">3.06285762786865</t>
@@ -179,34 +179,34 @@
     <t xml:space="preserve">3.18096232414246</t>
   </si>
   <si>
-    <t xml:space="preserve">3.10222601890564</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.13686990737915</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.23292875289917</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.33843564987183</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.30694103240967</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.24395179748535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.24237728118896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.12584686279297</t>
+    <t xml:space="preserve">3.10222578048706</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.13686966896057</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.23292827606201</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.33843541145325</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.30694079399109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.24395132064819</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.24237704277039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.12584662437439</t>
   </si>
   <si>
     <t xml:space="preserve">3.19670963287354</t>
   </si>
   <si>
-    <t xml:space="preserve">3.2030086517334</t>
+    <t xml:space="preserve">3.20300889015198</t>
   </si>
   <si>
     <t xml:space="preserve">3.10380029678345</t>
@@ -215,13 +215,13 @@
     <t xml:space="preserve">3.11324882507324</t>
   </si>
   <si>
-    <t xml:space="preserve">3.14159393310547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.04710960388184</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.9998676776886</t>
+    <t xml:space="preserve">3.14159417152405</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.04710984230042</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.99986815452576</t>
   </si>
   <si>
     <t xml:space="preserve">2.96049928665161</t>
@@ -233,19 +233,19 @@
     <t xml:space="preserve">2.96837329864502</t>
   </si>
   <si>
-    <t xml:space="preserve">2.86286592483521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.87388968467712</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.91010785102844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.98569536209106</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.00144290924072</t>
+    <t xml:space="preserve">2.86286616325378</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.87388944625854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.91010808944702</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.98569560050964</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.00144267082214</t>
   </si>
   <si>
     <t xml:space="preserve">3.01561522483826</t>
@@ -254,7 +254,7 @@
     <t xml:space="preserve">2.92743039131165</t>
   </si>
   <si>
-    <t xml:space="preserve">2.92113137245178</t>
+    <t xml:space="preserve">2.92113089561462</t>
   </si>
   <si>
     <t xml:space="preserve">2.85814189910889</t>
@@ -263,94 +263,94 @@
     <t xml:space="preserve">2.814049243927</t>
   </si>
   <si>
-    <t xml:space="preserve">2.84082007408142</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.80145144462585</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.72901368141174</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.65185165405273</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.68177175521851</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.71484136581421</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.76365756988525</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.77940535545349</t>
+    <t xml:space="preserve">2.84081983566284</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.80145168304443</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.72901391983032</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.65185189247131</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.68177151679993</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.71484088897705</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.76365780830383</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.77940511703491</t>
   </si>
   <si>
     <t xml:space="preserve">2.724289894104</t>
   </si>
   <si>
-    <t xml:space="preserve">2.59043717384338</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.5353217124939</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.49437832832336</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.48020577430725</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.51957440376282</t>
+    <t xml:space="preserve">2.5904369354248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.53532123565674</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.49437880516052</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.48020553588867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.51957416534424</t>
   </si>
   <si>
     <t xml:space="preserve">2.6057276725769</t>
   </si>
   <si>
-    <t xml:space="preserve">2.58784627914429</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.5602126121521</t>
+    <t xml:space="preserve">2.58784651756287</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.56021213531494</t>
   </si>
   <si>
     <t xml:space="preserve">2.56183767318726</t>
   </si>
   <si>
-    <t xml:space="preserve">2.60897850990295</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.59272313117981</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.58134436607361</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.60085105895996</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.72114038467407</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.8202977180481</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.80404257774353</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.68212747573853</t>
+    <t xml:space="preserve">2.6089780330658</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.59272336959839</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.58134412765503</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.60085082054138</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.72113990783691</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.82029795646667</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.80404186248779</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.68212723731995</t>
   </si>
   <si>
     <t xml:space="preserve">2.71463775634766</t>
   </si>
   <si>
-    <t xml:space="preserve">2.44642543792725</t>
+    <t xml:space="preserve">2.44642496109009</t>
   </si>
   <si>
     <t xml:space="preserve">2.39765930175781</t>
   </si>
   <si>
-    <t xml:space="preserve">2.50331878662109</t>
+    <t xml:space="preserve">2.50331854820251</t>
   </si>
   <si>
     <t xml:space="preserve">2.47568488121033</t>
@@ -365,64 +365,64 @@
     <t xml:space="preserve">2.50819540023804</t>
   </si>
   <si>
-    <t xml:space="preserve">2.40578722953796</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.19446778297424</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.2351062297821</t>
+    <t xml:space="preserve">2.40578675270081</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.19446802139282</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.23510646820068</t>
   </si>
   <si>
     <t xml:space="preserve">2.29525089263916</t>
   </si>
   <si>
-    <t xml:space="preserve">2.27411913871765</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.35702133178711</t>
+    <t xml:space="preserve">2.27411890029907</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.35702109336853</t>
   </si>
   <si>
     <t xml:space="preserve">2.37327647209167</t>
   </si>
   <si>
-    <t xml:space="preserve">2.29199981689453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.19284248352051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.22535300254822</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.28387212753296</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.30500388145447</t>
+    <t xml:space="preserve">2.29199934005737</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.19284224510193</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.22535252571106</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.2838716506958</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.30500364303589</t>
   </si>
   <si>
     <t xml:space="preserve">2.33101224899292</t>
   </si>
   <si>
-    <t xml:space="preserve">2.33588886260986</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.33263754844666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.31963348388672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.38140416145325</t>
+    <t xml:space="preserve">2.3358895778656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.33263778686523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.3196337223053</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.38140392303467</t>
   </si>
   <si>
     <t xml:space="preserve">2.5358293056488</t>
   </si>
   <si>
-    <t xml:space="preserve">2.54395699501038</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.56834030151367</t>
+    <t xml:space="preserve">2.54395747184753</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.56834006309509</t>
   </si>
   <si>
     <t xml:space="preserve">2.89669752120972</t>
@@ -434,76 +434,76 @@
     <t xml:space="preserve">2.81217002868652</t>
   </si>
   <si>
-    <t xml:space="preserve">2.59597396850586</t>
+    <t xml:space="preserve">2.59597373008728</t>
   </si>
   <si>
     <t xml:space="preserve">2.57646775245667</t>
   </si>
   <si>
-    <t xml:space="preserve">2.57321667671204</t>
+    <t xml:space="preserve">2.57321619987488</t>
   </si>
   <si>
     <t xml:space="preserve">2.56671476364136</t>
   </si>
   <si>
-    <t xml:space="preserve">2.53257846832275</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.5374550819397</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.6366126537323</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.63011026382446</t>
+    <t xml:space="preserve">2.53257822990417</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.53745484352112</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.63661217689514</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.63011050224304</t>
   </si>
   <si>
     <t xml:space="preserve">2.64636564254761</t>
   </si>
   <si>
-    <t xml:space="preserve">2.65286755561829</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.63823819160461</t>
+    <t xml:space="preserve">2.65286803245544</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.63823771476746</t>
   </si>
   <si>
     <t xml:space="preserve">2.64148902893066</t>
   </si>
   <si>
-    <t xml:space="preserve">2.69188022613525</t>
+    <t xml:space="preserve">2.69188094139099</t>
   </si>
   <si>
     <t xml:space="preserve">2.75690150260925</t>
   </si>
   <si>
-    <t xml:space="preserve">2.79266357421875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.76340389251709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.7308931350708</t>
+    <t xml:space="preserve">2.79266381263733</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.76340365409851</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.73089337348938</t>
   </si>
   <si>
     <t xml:space="preserve">2.65449333190918</t>
   </si>
   <si>
-    <t xml:space="preserve">2.65774440765381</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.742271900177</t>
+    <t xml:space="preserve">2.65774416923523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.74227213859558</t>
   </si>
   <si>
     <t xml:space="preserve">2.76828026771545</t>
   </si>
   <si>
-    <t xml:space="preserve">2.70651006698608</t>
+    <t xml:space="preserve">2.70651054382324</t>
   </si>
   <si>
     <t xml:space="preserve">2.72764205932617</t>
   </si>
   <si>
-    <t xml:space="preserve">2.74064660072327</t>
+    <t xml:space="preserve">2.74064636230469</t>
   </si>
   <si>
     <t xml:space="preserve">2.76990604400635</t>
@@ -512,7 +512,7 @@
     <t xml:space="preserve">2.8007915019989</t>
   </si>
   <si>
-    <t xml:space="preserve">2.69513130187988</t>
+    <t xml:space="preserve">2.69513154029846</t>
   </si>
   <si>
     <t xml:space="preserve">2.6674976348877</t>
@@ -524,13 +524,13 @@
     <t xml:space="preserve">2.6252338886261</t>
   </si>
   <si>
-    <t xml:space="preserve">2.59759950637817</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.61710619926453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.66587162017822</t>
+    <t xml:space="preserve">2.59759974479675</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.61710596084595</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.66587209701538</t>
   </si>
   <si>
     <t xml:space="preserve">2.63336157798767</t>
@@ -542,10 +542,10 @@
     <t xml:space="preserve">2.6024763584137</t>
   </si>
   <si>
-    <t xml:space="preserve">2.67725038528442</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.70976138114929</t>
+    <t xml:space="preserve">2.677250623703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.70976161956787</t>
   </si>
   <si>
     <t xml:space="preserve">2.75527620315552</t>
@@ -557,7 +557,7 @@
     <t xml:space="preserve">2.72276520729065</t>
   </si>
   <si>
-    <t xml:space="preserve">2.82842540740967</t>
+    <t xml:space="preserve">2.82842516899109</t>
   </si>
   <si>
     <t xml:space="preserve">2.74389743804932</t>
@@ -566,196 +566,196 @@
     <t xml:space="preserve">2.76177835464478</t>
   </si>
   <si>
-    <t xml:space="preserve">2.73902082443237</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.70488452911377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.69025468826294</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.61222958564758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.73251891136169</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.67562532424927</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.62360811233521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.59434843063354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.55371022224426</t>
+    <t xml:space="preserve">2.73902058601379</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.70488476753235</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.6902551651001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.61222982406616</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.73251914978027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.67562484741211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.62360787391663</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.59434866905212</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.55371046066284</t>
   </si>
   <si>
     <t xml:space="preserve">2.55045914649963</t>
   </si>
   <si>
-    <t xml:space="preserve">2.5130717754364</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.46755719184875</t>
+    <t xml:space="preserve">2.51307201385498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.46755695343018</t>
   </si>
   <si>
     <t xml:space="preserve">2.50169324874878</t>
   </si>
   <si>
-    <t xml:space="preserve">2.58459520339966</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.63173580169678</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.65611863136292</t>
+    <t xml:space="preserve">2.58459544181824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.6317355632782</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.65611886978149</t>
   </si>
   <si>
     <t xml:space="preserve">2.66912293434143</t>
   </si>
   <si>
-    <t xml:space="preserve">2.72439098358154</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.78291034698486</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.77153158187866</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.77803373336792</t>
+    <t xml:space="preserve">2.72439122200012</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.78291058540344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.77153182029724</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.77803349494934</t>
   </si>
   <si>
     <t xml:space="preserve">2.70000815391541</t>
   </si>
   <si>
-    <t xml:space="preserve">2.7731568813324</t>
+    <t xml:space="preserve">2.77315735816956</t>
   </si>
   <si>
     <t xml:space="preserve">2.76502966880798</t>
   </si>
   <si>
-    <t xml:space="preserve">2.71788883209229</t>
+    <t xml:space="preserve">2.71788930892944</t>
   </si>
   <si>
     <t xml:space="preserve">2.74552297592163</t>
   </si>
   <si>
-    <t xml:space="preserve">2.77965950965881</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.74714875221252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.60410213470459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.62685918807983</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.64961671829224</t>
+    <t xml:space="preserve">2.77965927124023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.7471489906311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.60410165786743</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.62685942649841</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.64961647987366</t>
   </si>
   <si>
     <t xml:space="preserve">2.69350600242615</t>
   </si>
   <si>
-    <t xml:space="preserve">2.69838261604309</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.92270588874817</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.88531851768494</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.99910593032837</t>
+    <t xml:space="preserve">2.69838237762451</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.92270612716675</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.88531875610352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.99910616874695</t>
   </si>
   <si>
     <t xml:space="preserve">2.97472286224365</t>
   </si>
   <si>
-    <t xml:space="preserve">2.96984672546387</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.96334433555603</t>
+    <t xml:space="preserve">2.96984648704529</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.96334409713745</t>
   </si>
   <si>
     <t xml:space="preserve">2.94221234321594</t>
   </si>
   <si>
-    <t xml:space="preserve">2.93408441543579</t>
+    <t xml:space="preserve">2.93408465385437</t>
   </si>
   <si>
     <t xml:space="preserve">2.89832305908203</t>
   </si>
   <si>
-    <t xml:space="preserve">2.89182066917419</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.87881660461426</t>
+    <t xml:space="preserve">2.89182090759277</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.87881684303284</t>
   </si>
   <si>
     <t xml:space="preserve">2.87556552886963</t>
   </si>
   <si>
-    <t xml:space="preserve">2.84468054771423</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.82192301750183</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.84955716133118</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.91945481300354</t>
+    <t xml:space="preserve">2.84468030929565</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.82192277908325</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.8495569229126</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.91945505142212</t>
   </si>
   <si>
     <t xml:space="preserve">2.9259569644928</t>
   </si>
   <si>
-    <t xml:space="preserve">2.99097847938538</t>
+    <t xml:space="preserve">2.9909782409668</t>
   </si>
   <si>
     <t xml:space="preserve">2.9145781993866</t>
   </si>
   <si>
-    <t xml:space="preserve">2.91620373725891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.95846772193909</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.95684242248535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.95196557044983</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.04949760437012</t>
+    <t xml:space="preserve">2.91620349884033</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.95846796035767</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.95684194564819</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.95196533203125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.0494978427887</t>
   </si>
   <si>
     <t xml:space="preserve">3.05599927902222</t>
   </si>
   <si>
-    <t xml:space="preserve">2.9958553314209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.97959971427917</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.00723361968994</t>
+    <t xml:space="preserve">2.99585485458374</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.9795994758606</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.00723385810852</t>
   </si>
   <si>
     <t xml:space="preserve">3.09645938873291</t>
   </si>
   <si>
-    <t xml:space="preserve">3.11628723144531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.16916179656982</t>
+    <t xml:space="preserve">3.11628746986389</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.16916155815125</t>
   </si>
   <si>
     <t xml:space="preserve">3.13941979408264</t>
@@ -764,19 +764,19 @@
     <t xml:space="preserve">3.14437675476074</t>
   </si>
   <si>
-    <t xml:space="preserve">3.18898940086365</t>
+    <t xml:space="preserve">3.18898963928223</t>
   </si>
   <si>
     <t xml:space="preserve">3.18072772026062</t>
   </si>
   <si>
-    <t xml:space="preserve">3.24847316741943</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.21707940101624</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.16750931739807</t>
+    <t xml:space="preserve">3.24847340583801</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.21707916259766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.16750955581665</t>
   </si>
   <si>
     <t xml:space="preserve">3.15429091453552</t>
@@ -788,7 +788,7 @@
     <t xml:space="preserve">3.07663154602051</t>
   </si>
   <si>
-    <t xml:space="preserve">3.07497930526733</t>
+    <t xml:space="preserve">3.07497906684875</t>
   </si>
   <si>
     <t xml:space="preserve">2.98244857788086</t>
@@ -797,7 +797,7 @@
     <t xml:space="preserve">3.0584557056427</t>
   </si>
   <si>
-    <t xml:space="preserve">3.06506514549255</t>
+    <t xml:space="preserve">3.06506490707397</t>
   </si>
   <si>
     <t xml:space="preserve">3.03367066383362</t>
@@ -806,10 +806,10 @@
     <t xml:space="preserve">3.02540946006775</t>
   </si>
   <si>
-    <t xml:space="preserve">2.99401521682739</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.99071002006531</t>
+    <t xml:space="preserve">2.99401473999023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.99071049690247</t>
   </si>
   <si>
     <t xml:space="preserve">2.99897193908691</t>
@@ -818,43 +818,43 @@
     <t xml:space="preserve">2.93783617019653</t>
   </si>
   <si>
-    <t xml:space="preserve">2.95601153373718</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.07993602752686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.08819723129272</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.08654522895813</t>
+    <t xml:space="preserve">2.95601177215576</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.07993626594543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.0881974697113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.08654570579529</t>
   </si>
   <si>
     <t xml:space="preserve">3.10802555084229</t>
   </si>
   <si>
-    <t xml:space="preserve">3.11133050918579</t>
+    <t xml:space="preserve">3.11133027076721</t>
   </si>
   <si>
     <t xml:space="preserve">3.14768147468567</t>
   </si>
   <si>
-    <t xml:space="preserve">3.16420459747314</t>
+    <t xml:space="preserve">3.16420435905457</t>
   </si>
   <si>
     <t xml:space="preserve">3.20551300048828</t>
   </si>
   <si>
-    <t xml:space="preserve">3.21377468109131</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.23029756546021</t>
+    <t xml:space="preserve">3.21377444267273</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.23029804229736</t>
   </si>
   <si>
     <t xml:space="preserve">3.23360228538513</t>
   </si>
   <si>
-    <t xml:space="preserve">3.25343012809753</t>
+    <t xml:space="preserve">3.25343036651611</t>
   </si>
   <si>
     <t xml:space="preserve">3.29473853111267</t>
@@ -863,31 +863,31 @@
     <t xml:space="preserve">3.3079571723938</t>
   </si>
   <si>
-    <t xml:space="preserve">3.27160620689392</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.29639077186584</t>
+    <t xml:space="preserve">3.27160596847534</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.29639101028442</t>
   </si>
   <si>
     <t xml:space="preserve">3.22368836402893</t>
   </si>
   <si>
-    <t xml:space="preserve">3.25012564659119</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.19394636154175</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.26334452629089</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.0981113910675</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.15924739837646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.17246627807617</t>
+    <t xml:space="preserve">3.25012588500977</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.19394683837891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.26334404945374</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.09811162948608</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.15924763679504</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.17246580123901</t>
   </si>
   <si>
     <t xml:space="preserve">3.17411875724792</t>
@@ -896,49 +896,49 @@
     <t xml:space="preserve">3.15098595619202</t>
   </si>
   <si>
-    <t xml:space="preserve">3.05184650421143</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.05680346488953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.08489274978638</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.12785339355469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.0320188999176</t>
+    <t xml:space="preserve">3.05184674263</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.05680370330811</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.08489298820496</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.12785363197327</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.03201866149902</t>
   </si>
   <si>
     <t xml:space="preserve">3.09480690956116</t>
   </si>
   <si>
-    <t xml:space="preserve">3.073326587677</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.09150242805481</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.13115787506104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.10967755317688</t>
+    <t xml:space="preserve">3.07332682609558</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.09150266647339</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.13115835189819</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.10967779159546</t>
   </si>
   <si>
     <t xml:space="preserve">3.10472083091736</t>
   </si>
   <si>
-    <t xml:space="preserve">3.12124443054199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.13611531257629</t>
+    <t xml:space="preserve">3.12124395370483</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.13611507415771</t>
   </si>
   <si>
     <t xml:space="preserve">3.1460292339325</t>
   </si>
   <si>
-    <t xml:space="preserve">3.12950611114502</t>
+    <t xml:space="preserve">3.12950563430786</t>
   </si>
   <si>
     <t xml:space="preserve">3.14107203483582</t>
@@ -953,10 +953,10 @@
     <t xml:space="preserve">3.10637307167053</t>
   </si>
   <si>
-    <t xml:space="preserve">3.08158874511719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.10141634941101</t>
+    <t xml:space="preserve">3.08158826828003</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.10141587257385</t>
   </si>
   <si>
     <t xml:space="preserve">3.10306859016418</t>
@@ -968,61 +968,61 @@
     <t xml:space="preserve">3.08984994888306</t>
   </si>
   <si>
-    <t xml:space="preserve">2.94940209388733</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.93287873268127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.83704400062561</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.88165664672852</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.90809392929077</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.91139841079712</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.9460973739624</t>
+    <t xml:space="preserve">2.94940233230591</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.93287897109985</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.83704423904419</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.88165688514709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.90809416770935</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.91139888763428</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.94609761238098</t>
   </si>
   <si>
     <t xml:space="preserve">2.94114065170288</t>
   </si>
   <si>
-    <t xml:space="preserve">2.96592569351196</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.8849618434906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.84034895896912</t>
+    <t xml:space="preserve">2.96592545509338</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.88496160507202</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.84034872055054</t>
   </si>
   <si>
     <t xml:space="preserve">2.82878255844116</t>
   </si>
   <si>
-    <t xml:space="preserve">2.81225895881653</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.8800048828125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.75112295150757</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.80895471572876</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.79243135452271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.81391143798828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.85852408409119</t>
+    <t xml:space="preserve">2.81225919723511</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.88000440597534</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.75112318992615</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.80895447731018</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.79243159294128</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.8139111995697</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.85852456092834</t>
   </si>
   <si>
     <t xml:space="preserve">2.97418713569641</t>
@@ -1031,25 +1031,25 @@
     <t xml:space="preserve">2.97088241577148</t>
   </si>
   <si>
-    <t xml:space="preserve">3.01549553871155</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.05515098571777</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.04028034210205</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.07002210617065</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.0634126663208</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.023756980896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.03697562217712</t>
+    <t xml:space="preserve">3.01549577713013</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.05515122413635</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.04028010368347</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.07002186775208</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.06341290473938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.02375674247742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.0369758605957</t>
   </si>
   <si>
     <t xml:space="preserve">3.0287139415741</t>
@@ -1058,10 +1058,10 @@
     <t xml:space="preserve">3.0534987449646</t>
   </si>
   <si>
-    <t xml:space="preserve">3.0782835483551</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.11050462722778</t>
+    <t xml:space="preserve">3.07828378677368</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.11050415039062</t>
   </si>
   <si>
     <t xml:space="preserve">3.06919574737549</t>
@@ -1070,13 +1070,13 @@
     <t xml:space="preserve">3.1559431552887</t>
   </si>
   <si>
-    <t xml:space="preserve">3.21790552139282</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.17659735679626</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.19312000274658</t>
+    <t xml:space="preserve">3.21790504455566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.17659711837769</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.19312024116516</t>
   </si>
   <si>
     <t xml:space="preserve">3.25508260726929</t>
@@ -1088,16 +1088,16 @@
     <t xml:space="preserve">2.96179461479187</t>
   </si>
   <si>
-    <t xml:space="preserve">2.9783182144165</t>
+    <t xml:space="preserve">2.97831773757935</t>
   </si>
   <si>
     <t xml:space="preserve">2.92461729049683</t>
   </si>
   <si>
-    <t xml:space="preserve">2.87504744529724</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.13528895378113</t>
+    <t xml:space="preserve">2.87504768371582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.13528919219971</t>
   </si>
   <si>
     <t xml:space="preserve">3.07745742797852</t>
@@ -1109,13 +1109,13 @@
     <t xml:space="preserve">3.03614950180054</t>
   </si>
   <si>
-    <t xml:space="preserve">2.92048668861389</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.08571934700012</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.01962637901306</t>
+    <t xml:space="preserve">2.92048692703247</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.08571910858154</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.0196259021759</t>
   </si>
   <si>
     <t xml:space="preserve">3.02788782119751</t>
@@ -1124,25 +1124,25 @@
     <t xml:space="preserve">3.0485417842865</t>
   </si>
   <si>
-    <t xml:space="preserve">3.04441094398499</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.15181231498718</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.33769869804382</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.25095176696777</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.27573657035828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.28399848937988</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.24682092666626</t>
+    <t xml:space="preserve">3.04441070556641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.1518120765686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.33769917488098</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.25095200538635</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.27573680877686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.2839982509613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.24682116508484</t>
   </si>
   <si>
     <t xml:space="preserve">3.18485879898071</t>
@@ -1160,19 +1160,19 @@
     <t xml:space="preserve">3.18918609619141</t>
   </si>
   <si>
-    <t xml:space="preserve">3.22275638580322</t>
+    <t xml:space="preserve">3.22275614738464</t>
   </si>
   <si>
     <t xml:space="preserve">3.16400837898254</t>
   </si>
   <si>
-    <t xml:space="preserve">3.08847498893738</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.12204504013062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.14302659034729</t>
+    <t xml:space="preserve">3.0884747505188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.12204527854919</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.14302682876587</t>
   </si>
   <si>
     <t xml:space="preserve">3.20597100257874</t>
@@ -1181,16 +1181,16 @@
     <t xml:space="preserve">3.25632691383362</t>
   </si>
   <si>
-    <t xml:space="preserve">3.24793386459351</t>
+    <t xml:space="preserve">3.24793410301208</t>
   </si>
   <si>
     <t xml:space="preserve">3.10526013374329</t>
   </si>
   <si>
-    <t xml:space="preserve">3.07168984413147</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.18498969078064</t>
+    <t xml:space="preserve">3.07168960571289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.18498992919922</t>
   </si>
   <si>
     <t xml:space="preserve">3.11365270614624</t>
@@ -1199,31 +1199,31 @@
     <t xml:space="preserve">3.12624144554138</t>
   </si>
   <si>
-    <t xml:space="preserve">3.1388304233551</t>
+    <t xml:space="preserve">3.13883066177368</t>
   </si>
   <si>
     <t xml:space="preserve">3.14722299575806</t>
   </si>
   <si>
-    <t xml:space="preserve">3.15561556816101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.17240071296692</t>
+    <t xml:space="preserve">3.15561532974243</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.1724009513855</t>
   </si>
   <si>
     <t xml:space="preserve">3.08427858352661</t>
   </si>
   <si>
-    <t xml:space="preserve">3.13463425636292</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.16820478439331</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.10945653915405</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.15981245040894</t>
+    <t xml:space="preserve">3.13463377952576</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.16820430755615</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.10945630073547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.15981221199036</t>
   </si>
   <si>
     <t xml:space="preserve">3.19338250160217</t>
@@ -1235,70 +1235,70 @@
     <t xml:space="preserve">3.23534536361694</t>
   </si>
   <si>
-    <t xml:space="preserve">3.26471948623657</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.32346773147583</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.31087875366211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.27730846405029</t>
+    <t xml:space="preserve">3.26471924781799</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.32346749305725</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.31087851524353</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.27730822563171</t>
   </si>
   <si>
     <t xml:space="preserve">3.35703778266907</t>
   </si>
   <si>
-    <t xml:space="preserve">3.42417883872986</t>
+    <t xml:space="preserve">3.42417860031128</t>
   </si>
   <si>
     <t xml:space="preserve">3.49131941795349</t>
   </si>
   <si>
-    <t xml:space="preserve">3.43257117271423</t>
+    <t xml:space="preserve">3.43257164955139</t>
   </si>
   <si>
     <t xml:space="preserve">3.54167485237122</t>
   </si>
   <si>
-    <t xml:space="preserve">3.44935631752014</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.48292708396912</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.51649761199951</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.474534034729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.45774912834167</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.3864119052887</t>
+    <t xml:space="preserve">3.4493567943573</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.48292660713196</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.51649713516235</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.47453427314758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.45774865150452</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.38641214370728</t>
   </si>
   <si>
     <t xml:space="preserve">3.37801933288574</t>
   </si>
   <si>
-    <t xml:space="preserve">3.4703381061554</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.30248594284058</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.31927132606506</t>
+    <t xml:space="preserve">3.47033786773682</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.30248618125916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.31927108764648</t>
   </si>
   <si>
     <t xml:space="preserve">3.29828977584839</t>
   </si>
   <si>
-    <t xml:space="preserve">3.34025263786316</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.27311205863953</t>
+    <t xml:space="preserve">3.34025287628174</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.27311229705811</t>
   </si>
   <si>
     <t xml:space="preserve">3.28150463104248</t>
@@ -1307,34 +1307,34 @@
     <t xml:space="preserve">3.399001121521</t>
   </si>
   <si>
-    <t xml:space="preserve">3.57524538040161</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.58783364295959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.55006742477417</t>
+    <t xml:space="preserve">3.57524585723877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.58783411979675</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.55006766319275</t>
   </si>
   <si>
     <t xml:space="preserve">3.57944130897522</t>
   </si>
   <si>
-    <t xml:space="preserve">3.58363771438599</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.66336727142334</t>
+    <t xml:space="preserve">3.58363819122314</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.66336750984192</t>
   </si>
   <si>
     <t xml:space="preserve">3.55845999717712</t>
   </si>
   <si>
-    <t xml:space="preserve">3.56685304641724</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.62140464782715</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.78086376190186</t>
+    <t xml:space="preserve">3.56685209274292</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.62140488624573</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.78086400032043</t>
   </si>
   <si>
     <t xml:space="preserve">3.88577175140381</t>
@@ -1346,133 +1346,133 @@
     <t xml:space="preserve">3.76407885551453</t>
   </si>
   <si>
-    <t xml:space="preserve">3.68434882164001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.7976496219635</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.82702302932739</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.80184578895569</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.83961129188538</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.91934204101562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.91094923019409</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.94451928138733</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.06621170043945</t>
+    <t xml:space="preserve">3.68434906005859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.79764938354492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.82702326774597</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.80184602737427</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.83961224555969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.91934180259705</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.91094899177551</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.94451904296875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.06621217727661</t>
   </si>
   <si>
     <t xml:space="preserve">4.02005290985107</t>
   </si>
   <si>
-    <t xml:space="preserve">3.92773413658142</t>
+    <t xml:space="preserve">3.92773461341858</t>
   </si>
   <si>
     <t xml:space="preserve">3.8689866065979</t>
   </si>
   <si>
-    <t xml:space="preserve">3.8186309337616</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.86059355735779</t>
+    <t xml:space="preserve">3.81863045692444</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.86059331893921</t>
   </si>
   <si>
     <t xml:space="preserve">3.79345297813416</t>
   </si>
   <si>
-    <t xml:space="preserve">3.86478996276855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.87737846374512</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.73470497131348</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.84380793571472</t>
+    <t xml:space="preserve">3.86478972434998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.8773787021637</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.73470449447632</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.8438081741333</t>
   </si>
   <si>
     <t xml:space="preserve">3.69274163246155</t>
   </si>
   <si>
-    <t xml:space="preserve">3.90255689620972</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.95291209220886</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.9906792640686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.00326824188232</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.91514563560486</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.87318205833435</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.85220122337341</t>
+    <t xml:space="preserve">3.90255665779114</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.9529116153717</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.99067854881287</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.00326776504517</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.91514539718628</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.87318229675293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.85220074653625</t>
   </si>
   <si>
     <t xml:space="preserve">3.66756391525269</t>
   </si>
   <si>
-    <t xml:space="preserve">3.67595648765564</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.59203028678894</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.53328204154968</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.70533037185669</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.64238595962524</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.77666735649109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.71791958808899</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.64658236503601</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.70113444328308</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.68015289306641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.8060417175293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.78506016731262</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.69693851470947</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.73050856590271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.74729418754578</t>
+    <t xml:space="preserve">3.67595624923706</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.59203052520752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.53328251838684</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.70533084869385</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.64238619804382</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.77666807174683</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.71791911125183</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.64658188819885</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.70113396644592</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.68015265464783</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.80604195594788</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.78505969047546</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.69693827629089</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.73050832748413</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.74729371070862</t>
   </si>
   <si>
     <t xml:space="preserve">3.65077877044678</t>
@@ -1481,70 +1481,70 @@
     <t xml:space="preserve">3.65917134284973</t>
   </si>
   <si>
-    <t xml:space="preserve">3.85639715194702</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.89416408538818</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.93612694740295</t>
+    <t xml:space="preserve">3.85639667510986</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.8941638469696</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.93612742424011</t>
   </si>
   <si>
     <t xml:space="preserve">4.00746393203735</t>
   </si>
   <si>
-    <t xml:space="preserve">4.08719396591187</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.11237192153931</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.17111921310425</t>
+    <t xml:space="preserve">4.08719348907471</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.11237144470215</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.17111873626709</t>
   </si>
   <si>
     <t xml:space="preserve">4.19629716873169</t>
   </si>
   <si>
-    <t xml:space="preserve">4.2382607460022</t>
+    <t xml:space="preserve">4.23826026916504</t>
   </si>
   <si>
     <t xml:space="preserve">4.18790483474731</t>
   </si>
   <si>
-    <t xml:space="preserve">4.09978294372559</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.0955867767334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.07880020141602</t>
+    <t xml:space="preserve">4.09978246688843</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.09558629989624</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.07880115509033</t>
   </si>
   <si>
     <t xml:space="preserve">4.14594221115112</t>
   </si>
   <si>
-    <t xml:space="preserve">4.09139013290405</t>
+    <t xml:space="preserve">4.09139060974121</t>
   </si>
   <si>
     <t xml:space="preserve">4.08299684524536</t>
   </si>
   <si>
-    <t xml:space="preserve">4.06201553344727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.26343822479248</t>
+    <t xml:space="preserve">4.06201601028442</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.26343774795532</t>
   </si>
   <si>
     <t xml:space="preserve">4.3977198600769</t>
   </si>
   <si>
-    <t xml:space="preserve">4.52360868453979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.49843168258667</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.58235645294189</t>
+    <t xml:space="preserve">4.52360820770264</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.49843120574951</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.58235692977905</t>
   </si>
   <si>
     <t xml:space="preserve">4.48164558410645</t>
@@ -1553,10 +1553,10 @@
     <t xml:space="preserve">4.6243200302124</t>
   </si>
   <si>
-    <t xml:space="preserve">4.67467594146729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.69985294342041</t>
+    <t xml:space="preserve">4.67467546463013</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.69985342025757</t>
   </si>
   <si>
     <t xml:space="preserve">4.6830677986145</t>
@@ -1571,22 +1571,22 @@
     <t xml:space="preserve">4.44807529449463</t>
   </si>
   <si>
-    <t xml:space="preserve">4.4396824836731</t>
+    <t xml:space="preserve">4.43968296051025</t>
   </si>
   <si>
     <t xml:space="preserve">4.47325277328491</t>
   </si>
   <si>
-    <t xml:space="preserve">4.49003839492798</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.54878616333008</t>
+    <t xml:space="preserve">4.49003791809082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.54878664016724</t>
   </si>
   <si>
     <t xml:space="preserve">4.5991415977478</t>
   </si>
   <si>
-    <t xml:space="preserve">4.61592769622803</t>
+    <t xml:space="preserve">4.61592721939087</t>
   </si>
   <si>
     <t xml:space="preserve">4.60753440856934</t>
@@ -1595,19 +1595,19 @@
     <t xml:space="preserve">4.40611267089844</t>
   </si>
   <si>
-    <t xml:space="preserve">4.53200101852417</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.75860166549683</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.80895709991455</t>
+    <t xml:space="preserve">4.53200197219849</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.75860118865967</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.80895662307739</t>
   </si>
   <si>
     <t xml:space="preserve">4.74181604385376</t>
   </si>
   <si>
-    <t xml:space="preserve">4.69146060943604</t>
+    <t xml:space="preserve">4.69146013259888</t>
   </si>
   <si>
     <t xml:space="preserve">4.65789031982422</t>
@@ -1619,16 +1619,16 @@
     <t xml:space="preserve">4.5403938293457</t>
   </si>
   <si>
-    <t xml:space="preserve">4.46485996246338</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.41450500488281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.38932752609253</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.380934715271</t>
+    <t xml:space="preserve">4.4648609161377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.41450452804565</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.38932657241821</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.38093423843384</t>
   </si>
   <si>
     <t xml:space="preserve">4.34736394882202</t>
@@ -1637,16 +1637,16 @@
     <t xml:space="preserve">4.46764659881592</t>
   </si>
   <si>
-    <t xml:space="preserve">4.51919651031494</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.39891338348389</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.37313890457153</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.3044056892395</t>
+    <t xml:space="preserve">4.5191969871521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.39891386032104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.37313938140869</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.30440616607666</t>
   </si>
   <si>
     <t xml:space="preserve">4.27003908157349</t>
@@ -1658,10 +1658,10 @@
     <t xml:space="preserve">4.31299734115601</t>
   </si>
   <si>
-    <t xml:space="preserve">4.38173055648804</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.44187164306641</t>
+    <t xml:space="preserve">4.38173007965088</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.44187211990356</t>
   </si>
   <si>
     <t xml:space="preserve">4.45905542373657</t>
@@ -1670,46 +1670,46 @@
     <t xml:space="preserve">4.35595560073853</t>
   </si>
   <si>
-    <t xml:space="preserve">4.3903226852417</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.45046329498291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.41609716415405</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.23137664794922</t>
+    <t xml:space="preserve">4.39032220840454</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.45046281814575</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.41609668731689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.23137712478638</t>
   </si>
   <si>
     <t xml:space="preserve">4.26574325561523</t>
   </si>
   <si>
-    <t xml:space="preserve">4.13257360458374</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.0466570854187</t>
+    <t xml:space="preserve">4.13257312774658</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.04665660858154</t>
   </si>
   <si>
     <t xml:space="preserve">4.08531904220581</t>
   </si>
   <si>
-    <t xml:space="preserve">3.9822199344635</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.03376913070679</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.94785261154175</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.99081110954285</t>
+    <t xml:space="preserve">3.98222064971924</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.03376960754395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.94785284996033</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.99081134796143</t>
   </si>
   <si>
     <t xml:space="preserve">3.98651552200317</t>
   </si>
   <si>
-    <t xml:space="preserve">3.94355773925781</t>
+    <t xml:space="preserve">3.94355702400208</t>
   </si>
   <si>
     <t xml:space="preserve">3.96503615379333</t>
@@ -1721,13 +1721,13 @@
     <t xml:space="preserve">4.01229047775269</t>
   </si>
   <si>
-    <t xml:space="preserve">3.92637467384338</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.07243156433105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.08961534500122</t>
+    <t xml:space="preserve">3.9263744354248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.07243204116821</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.08961486816406</t>
   </si>
   <si>
     <t xml:space="preserve">4.11109399795532</t>
@@ -1736,22 +1736,22 @@
     <t xml:space="preserve">4.26144742965698</t>
   </si>
   <si>
-    <t xml:space="preserve">4.32158946990967</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.29581451416016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.02947425842285</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.84045791625977</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.87482452392578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.88771224021912</t>
+    <t xml:space="preserve">4.32158899307251</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.295814037323</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.02947378158569</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.84045767784119</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.87482404708862</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.88771200180054</t>
   </si>
   <si>
     <t xml:space="preserve">4.00369882583618</t>
@@ -1760,52 +1760,52 @@
     <t xml:space="preserve">4.02088212966919</t>
   </si>
   <si>
-    <t xml:space="preserve">3.93496561050415</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.86623287200928</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.77172446250916</t>
+    <t xml:space="preserve">3.93496632575989</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.8662326335907</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.77172493934631</t>
   </si>
   <si>
     <t xml:space="preserve">3.71587944030762</t>
   </si>
   <si>
-    <t xml:space="preserve">3.70299196243286</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.67721724510193</t>
+    <t xml:space="preserve">3.7029914855957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.67721700668335</t>
   </si>
   <si>
     <t xml:space="preserve">3.68580842018127</t>
   </si>
   <si>
-    <t xml:space="preserve">3.70728802680969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.66433000564575</t>
+    <t xml:space="preserve">3.70728778839111</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.66432952880859</t>
   </si>
   <si>
     <t xml:space="preserve">3.66003394126892</t>
   </si>
   <si>
-    <t xml:space="preserve">3.72017502784729</t>
+    <t xml:space="preserve">3.72017455101013</t>
   </si>
   <si>
     <t xml:space="preserve">3.81468319892883</t>
   </si>
   <si>
-    <t xml:space="preserve">3.95214915275574</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.85764098167419</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.78461241722107</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.84475350379944</t>
+    <t xml:space="preserve">3.95214891433716</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.85764050483704</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.78461265563965</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.8447539806366</t>
   </si>
   <si>
     <t xml:space="preserve">3.78031659126282</t>
@@ -1814,28 +1814,28 @@
     <t xml:space="preserve">3.69440054893494</t>
   </si>
   <si>
-    <t xml:space="preserve">3.73306250572205</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.71158361434937</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.59989237785339</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.75454163551331</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.65144205093384</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.72447061538696</t>
+    <t xml:space="preserve">3.73306202888489</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.71158409118652</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.59989213943481</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.75454187393188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.65144157409668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.72447085380554</t>
   </si>
   <si>
     <t xml:space="preserve">3.78890776634216</t>
   </si>
   <si>
-    <t xml:space="preserve">3.64714598655701</t>
+    <t xml:space="preserve">3.64714622497559</t>
   </si>
   <si>
     <t xml:space="preserve">3.66862559318542</t>
@@ -1844,7 +1844,7 @@
     <t xml:space="preserve">3.67292094230652</t>
   </si>
   <si>
-    <t xml:space="preserve">3.61707592010498</t>
+    <t xml:space="preserve">3.6170756816864</t>
   </si>
   <si>
     <t xml:space="preserve">3.57411742210388</t>
@@ -1856,7 +1856,7 @@
     <t xml:space="preserve">3.65573811531067</t>
   </si>
   <si>
-    <t xml:space="preserve">3.62996292114258</t>
+    <t xml:space="preserve">3.629962682724</t>
   </si>
   <si>
     <t xml:space="preserve">3.96933245658875</t>
@@ -1865,16 +1865,16 @@
     <t xml:space="preserve">3.95644474029541</t>
   </si>
   <si>
-    <t xml:space="preserve">3.90059924125671</t>
+    <t xml:space="preserve">3.90059876441956</t>
   </si>
   <si>
     <t xml:space="preserve">3.9306697845459</t>
   </si>
   <si>
-    <t xml:space="preserve">4.01658630371094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.09820652008057</t>
+    <t xml:space="preserve">4.0165867805481</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.09820699691772</t>
   </si>
   <si>
     <t xml:space="preserve">4.14116477966309</t>
@@ -1883,16 +1883,16 @@
     <t xml:space="preserve">4.24426460266113</t>
   </si>
   <si>
-    <t xml:space="preserve">4.24856042861938</t>
+    <t xml:space="preserve">4.24856090545654</t>
   </si>
   <si>
     <t xml:space="preserve">4.43328046798706</t>
   </si>
   <si>
-    <t xml:space="preserve">4.42468881607056</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.58792972564697</t>
+    <t xml:space="preserve">4.4246883392334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.58792924880981</t>
   </si>
   <si>
     <t xml:space="preserve">4.57933759689331</t>
@@ -1913,22 +1913,22 @@
     <t xml:space="preserve">4.59652090072632</t>
   </si>
   <si>
-    <t xml:space="preserve">4.77694511413574</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.81131172180176</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.69962024688721</t>
+    <t xml:space="preserve">4.7769455909729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.81131219863892</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.69962120056152</t>
   </si>
   <si>
     <t xml:space="preserve">4.64807081222534</t>
   </si>
   <si>
-    <t xml:space="preserve">4.72539520263672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.71680355072021</t>
+    <t xml:space="preserve">4.72539567947388</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.71680307388306</t>
   </si>
   <si>
     <t xml:space="preserve">4.69102907180786</t>
@@ -1937,7 +1937,7 @@
     <t xml:space="preserve">4.6824369430542</t>
   </si>
   <si>
-    <t xml:space="preserve">4.70821189880371</t>
+    <t xml:space="preserve">4.70821237564087</t>
   </si>
   <si>
     <t xml:space="preserve">4.67384576797485</t>
@@ -1946,28 +1946,28 @@
     <t xml:space="preserve">4.56215476989746</t>
   </si>
   <si>
-    <t xml:space="preserve">4.50201272964478</t>
+    <t xml:space="preserve">4.50201320648193</t>
   </si>
   <si>
     <t xml:space="preserve">4.54497098922729</t>
   </si>
   <si>
-    <t xml:space="preserve">4.51060485839844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.52778768539429</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.76835346221924</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.66525411605835</t>
+    <t xml:space="preserve">4.51060438156128</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.52778816223145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.76835441589355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.66525363922119</t>
   </si>
   <si>
     <t xml:space="preserve">4.61370468139648</t>
   </si>
   <si>
-    <t xml:space="preserve">4.73398733139038</t>
+    <t xml:space="preserve">4.73398780822754</t>
   </si>
   <si>
     <t xml:space="preserve">4.639479637146</t>
@@ -1976,7 +1976,7 @@
     <t xml:space="preserve">4.23567295074463</t>
   </si>
   <si>
-    <t xml:space="preserve">4.15834903717041</t>
+    <t xml:space="preserve">4.15834856033325</t>
   </si>
   <si>
     <t xml:space="preserve">4.20130634307861</t>
@@ -1985,7 +1985,7 @@
     <t xml:space="preserve">4.36454725265503</t>
   </si>
   <si>
-    <t xml:space="preserve">4.60511255264282</t>
+    <t xml:space="preserve">4.60511302947998</t>
   </si>
   <si>
     <t xml:space="preserve">4.11538982391357</t>
@@ -1994,7 +1994,7 @@
     <t xml:space="preserve">3.75024557113647</t>
   </si>
   <si>
-    <t xml:space="preserve">3.47101759910583</t>
+    <t xml:space="preserve">3.47101783752441</t>
   </si>
   <si>
     <t xml:space="preserve">3.36362242698669</t>
@@ -2006,10 +2006,10 @@
     <t xml:space="preserve">3.16601490974426</t>
   </si>
   <si>
-    <t xml:space="preserve">3.22186088562012</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.80516672134399</t>
+    <t xml:space="preserve">3.22186040878296</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.80516695976257</t>
   </si>
   <si>
     <t xml:space="preserve">2.91685771942139</t>
@@ -2024,13 +2024,13 @@
     <t xml:space="preserve">2.73213791847229</t>
   </si>
   <si>
-    <t xml:space="preserve">2.66770029067993</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.80087089538574</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.61185503005981</t>
+    <t xml:space="preserve">2.66770052909851</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.80087065696716</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.61185479164124</t>
   </si>
   <si>
     <t xml:space="preserve">2.72354626655579</t>
@@ -2039,7 +2039,7 @@
     <t xml:space="preserve">2.92115354537964</t>
   </si>
   <si>
-    <t xml:space="preserve">2.8137583732605</t>
+    <t xml:space="preserve">2.81375813484192</t>
   </si>
   <si>
     <t xml:space="preserve">2.70206713676453</t>
@@ -2048,22 +2048,22 @@
     <t xml:space="preserve">2.65910911560059</t>
   </si>
   <si>
-    <t xml:space="preserve">2.84382915496826</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.76650452613831</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.78798317909241</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.70636296272278</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.71065878868103</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.85242033004761</t>
+    <t xml:space="preserve">2.8438286781311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.76650428771973</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.78798341751099</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.70636320114136</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.71065855026245</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.85242056846619</t>
   </si>
   <si>
     <t xml:space="preserve">2.89108300209045</t>
@@ -2072,13 +2072,13 @@
     <t xml:space="preserve">2.92974543571472</t>
   </si>
   <si>
-    <t xml:space="preserve">3.00707006454468</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.96411180496216</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.93833684921265</t>
+    <t xml:space="preserve">3.0070698261261</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.96411156654358</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.93833708763123</t>
   </si>
   <si>
     <t xml:space="preserve">2.9426326751709</t>
@@ -2087,10 +2087,10 @@
     <t xml:space="preserve">2.98129510879517</t>
   </si>
   <si>
-    <t xml:space="preserve">3.01136589050293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.94692850112915</t>
+    <t xml:space="preserve">3.01136541366577</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.94692873954773</t>
   </si>
   <si>
     <t xml:space="preserve">2.97699904441833</t>
@@ -2111,25 +2111,25 @@
     <t xml:space="preserve">3.08439445495605</t>
   </si>
   <si>
-    <t xml:space="preserve">3.13164854049683</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.03284502029419</t>
+    <t xml:space="preserve">3.13164830207825</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.03284454345703</t>
   </si>
   <si>
     <t xml:space="preserve">3.09298634529114</t>
   </si>
   <si>
-    <t xml:space="preserve">3.1917896270752</t>
+    <t xml:space="preserve">3.19178986549377</t>
   </si>
   <si>
     <t xml:space="preserve">3.24763560295105</t>
   </si>
   <si>
-    <t xml:space="preserve">3.16171932220459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.14883208274841</t>
+    <t xml:space="preserve">3.16171908378601</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.14883184432983</t>
   </si>
   <si>
     <t xml:space="preserve">3.18319845199585</t>
@@ -2138,43 +2138,43 @@
     <t xml:space="preserve">3.13594460487366</t>
   </si>
   <si>
-    <t xml:space="preserve">3.11876106262207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.30777668952942</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.38510179519653</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.4366512298584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.48390507698059</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.46242666244507</t>
+    <t xml:space="preserve">3.11876130104065</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.307776927948</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.38510155677795</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.43665146827698</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.48390531539917</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.46242642402649</t>
   </si>
   <si>
     <t xml:space="preserve">3.47960948944092</t>
   </si>
   <si>
-    <t xml:space="preserve">3.31636834144592</t>
+    <t xml:space="preserve">3.3163685798645</t>
   </si>
   <si>
     <t xml:space="preserve">3.29488945007324</t>
   </si>
   <si>
-    <t xml:space="preserve">3.19608592987061</t>
+    <t xml:space="preserve">3.19608569145203</t>
   </si>
   <si>
     <t xml:space="preserve">3.3808057308197</t>
   </si>
   <si>
-    <t xml:space="preserve">3.37650990486145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.35073518753052</t>
+    <t xml:space="preserve">3.37651014328003</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.3507354259491</t>
   </si>
   <si>
     <t xml:space="preserve">3.37221431732178</t>
@@ -2186,16 +2186,16 @@
     <t xml:space="preserve">3.44094753265381</t>
   </si>
   <si>
-    <t xml:space="preserve">3.4452428817749</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.75857448577881</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.71435618400574</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.63034081459045</t>
+    <t xml:space="preserve">3.44524312019348</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.75857424736023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.71435594558716</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.63034105300903</t>
   </si>
   <si>
     <t xml:space="preserve">3.58170080184937</t>
@@ -2207,61 +2207,61 @@
     <t xml:space="preserve">3.50210738182068</t>
   </si>
   <si>
-    <t xml:space="preserve">3.43135762214661</t>
+    <t xml:space="preserve">3.43135786056519</t>
   </si>
   <si>
     <t xml:space="preserve">3.44904541969299</t>
   </si>
   <si>
-    <t xml:space="preserve">3.36060810089111</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.38713908195496</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.4180920124054</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.32081174850464</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.33849883079529</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.31638956069946</t>
+    <t xml:space="preserve">3.36060786247253</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.38713932037354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.41809177398682</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.32081151008606</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.33849859237671</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.31638932228088</t>
   </si>
   <si>
     <t xml:space="preserve">3.27217102050781</t>
   </si>
   <si>
-    <t xml:space="preserve">3.28101468086243</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.22795271873474</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.09529685974121</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.18373370170593</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.25448369979858</t>
+    <t xml:space="preserve">3.28101444244385</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.22795248031616</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.09529662132263</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.18373394012451</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.25448346138</t>
   </si>
   <si>
     <t xml:space="preserve">3.20584321022034</t>
   </si>
   <si>
-    <t xml:space="preserve">3.16604614257812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.15720295906067</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.1395149230957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.10414052009583</t>
+    <t xml:space="preserve">3.1660463809967</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.15720272064209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.13951516151428</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.1041407585144</t>
   </si>
   <si>
     <t xml:space="preserve">3.09971857070923</t>
@@ -2276,13 +2276,13 @@
     <t xml:space="preserve">3.0776093006134</t>
   </si>
   <si>
-    <t xml:space="preserve">3.05992197990417</t>
+    <t xml:space="preserve">3.05992221832275</t>
   </si>
   <si>
     <t xml:space="preserve">2.98032855987549</t>
   </si>
   <si>
-    <t xml:space="preserve">2.96264123916626</t>
+    <t xml:space="preserve">2.96264100074768</t>
   </si>
   <si>
     <t xml:space="preserve">2.94495368003845</t>
@@ -2291,19 +2291,19 @@
     <t xml:space="preserve">2.93611001968384</t>
   </si>
   <si>
-    <t xml:space="preserve">3.09087491035461</t>
+    <t xml:space="preserve">3.09087514877319</t>
   </si>
   <si>
     <t xml:space="preserve">3.06876587867737</t>
   </si>
   <si>
-    <t xml:space="preserve">3.05550026893616</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.98475050926208</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.90515732765198</t>
+    <t xml:space="preserve">3.05550003051758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.98475027084351</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.9051570892334</t>
   </si>
   <si>
     <t xml:space="preserve">2.83440756797791</t>
@@ -2327,16 +2327,16 @@
     <t xml:space="preserve">2.82998585700989</t>
   </si>
   <si>
-    <t xml:space="preserve">2.79461073875427</t>
+    <t xml:space="preserve">2.79461097717285</t>
   </si>
   <si>
     <t xml:space="preserve">2.91842269897461</t>
   </si>
   <si>
-    <t xml:space="preserve">2.82114195823669</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.79903244972229</t>
+    <t xml:space="preserve">2.82114219665527</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.79903268814087</t>
   </si>
   <si>
     <t xml:space="preserve">2.80787658691406</t>
@@ -2360,7 +2360,7 @@
     <t xml:space="preserve">2.61773681640625</t>
   </si>
   <si>
-    <t xml:space="preserve">2.58236217498779</t>
+    <t xml:space="preserve">2.58236193656921</t>
   </si>
   <si>
     <t xml:space="preserve">2.54698729515076</t>
@@ -2369,16 +2369,16 @@
     <t xml:space="preserve">2.56467461585999</t>
   </si>
   <si>
-    <t xml:space="preserve">2.5514087677002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.49392485618591</t>
+    <t xml:space="preserve">2.55140900611877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.49392461776733</t>
   </si>
   <si>
     <t xml:space="preserve">2.5735182762146</t>
   </si>
   <si>
-    <t xml:space="preserve">2.97148489952087</t>
+    <t xml:space="preserve">2.97148466110229</t>
   </si>
   <si>
     <t xml:space="preserve">2.95379757881165</t>
@@ -2390,10 +2390,10 @@
     <t xml:space="preserve">3.17931199073792</t>
   </si>
   <si>
-    <t xml:space="preserve">3.1704683303833</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.19257736206055</t>
+    <t xml:space="preserve">3.17046856880188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.19257760047913</t>
   </si>
   <si>
     <t xml:space="preserve">3.28985834121704</t>
@@ -2402,28 +2402,28 @@
     <t xml:space="preserve">3.29870223999023</t>
   </si>
   <si>
-    <t xml:space="preserve">3.47999787330627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.4136700630188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.48442006111145</t>
+    <t xml:space="preserve">3.47999811172485</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.41367030143738</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.48441982269287</t>
   </si>
   <si>
     <t xml:space="preserve">3.45788884162903</t>
   </si>
   <si>
-    <t xml:space="preserve">3.49326348304749</t>
+    <t xml:space="preserve">3.49326372146606</t>
   </si>
   <si>
     <t xml:space="preserve">3.51095080375671</t>
   </si>
   <si>
-    <t xml:space="preserve">3.44462323188782</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.42693567276001</t>
+    <t xml:space="preserve">3.44462299346924</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.42693614959717</t>
   </si>
   <si>
     <t xml:space="preserve">3.55516934394836</t>
@@ -2444,16 +2444,16 @@
     <t xml:space="preserve">3.65687227249146</t>
   </si>
   <si>
-    <t xml:space="preserve">3.66129398345947</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.65245008468628</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.62591886520386</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.60823178291321</t>
+    <t xml:space="preserve">3.66129374504089</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.65245032310486</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.62591910362244</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.60823154449463</t>
   </si>
   <si>
     <t xml:space="preserve">3.54632616043091</t>
@@ -2462,19 +2462,19 @@
     <t xml:space="preserve">3.53748202323914</t>
   </si>
   <si>
-    <t xml:space="preserve">3.57285666465759</t>
+    <t xml:space="preserve">3.57285690307617</t>
   </si>
   <si>
     <t xml:space="preserve">3.5065290927887</t>
   </si>
   <si>
-    <t xml:space="preserve">3.59054446220398</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.57727885246277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.74530935287476</t>
+    <t xml:space="preserve">3.5905442237854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.57727861404419</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.74530911445618</t>
   </si>
   <si>
     <t xml:space="preserve">3.74088716506958</t>
@@ -2486,7 +2486,7 @@
     <t xml:space="preserve">3.70551252365112</t>
   </si>
   <si>
-    <t xml:space="preserve">3.7762622833252</t>
+    <t xml:space="preserve">3.77626252174377</t>
   </si>
   <si>
     <t xml:space="preserve">3.83816838264465</t>
@@ -2507,13 +2507,13 @@
     <t xml:space="preserve">3.7718403339386</t>
   </si>
   <si>
-    <t xml:space="preserve">3.71877789497375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.68782520294189</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.59938788414001</t>
+    <t xml:space="preserve">3.71877813339233</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.68782496452332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.59938812255859</t>
   </si>
   <si>
     <t xml:space="preserve">3.66571545600891</t>
@@ -2522,22 +2522,22 @@
     <t xml:space="preserve">3.7099347114563</t>
   </si>
   <si>
-    <t xml:space="preserve">3.78510618209839</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.9266049861908</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.93987035751343</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.99735450744629</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.01079845428467</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.09594440460205</t>
+    <t xml:space="preserve">3.78510594367981</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.92660546302795</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.93987083435059</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.99735474586487</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.01079893112183</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.09594392776489</t>
   </si>
   <si>
     <t xml:space="preserve">4.17212724685669</t>
@@ -2546,10 +2546,10 @@
     <t xml:space="preserve">4.16316413879395</t>
   </si>
   <si>
-    <t xml:space="preserve">4.13627576828003</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.19901514053345</t>
+    <t xml:space="preserve">4.13627624511719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.19901466369629</t>
   </si>
   <si>
     <t xml:space="preserve">4.14075708389282</t>
@@ -2564,13 +2564,13 @@
     <t xml:space="preserve">4.03320550918579</t>
   </si>
   <si>
-    <t xml:space="preserve">3.97942924499512</t>
+    <t xml:space="preserve">3.9794294834137</t>
   </si>
   <si>
     <t xml:space="preserve">4.02872371673584</t>
   </si>
   <si>
-    <t xml:space="preserve">4.05561256408691</t>
+    <t xml:space="preserve">4.05561208724976</t>
   </si>
   <si>
     <t xml:space="preserve">4.08698129653931</t>
@@ -2579,10 +2579,10 @@
     <t xml:space="preserve">3.97494792938232</t>
   </si>
   <si>
-    <t xml:space="preserve">4.00183582305908</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.01527976989746</t>
+    <t xml:space="preserve">4.00183629989624</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.01528024673462</t>
   </si>
   <si>
     <t xml:space="preserve">3.96150398254395</t>
@@ -2591,10 +2591,10 @@
     <t xml:space="preserve">3.9883918762207</t>
   </si>
   <si>
-    <t xml:space="preserve">3.95254135131836</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.96598529815674</t>
+    <t xml:space="preserve">3.95254111289978</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.96598553657532</t>
   </si>
   <si>
     <t xml:space="preserve">4.04216861724854</t>
@@ -2603,25 +2603,25 @@
     <t xml:space="preserve">4.07801914215088</t>
   </si>
   <si>
-    <t xml:space="preserve">4.11835050582886</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.17660760879517</t>
+    <t xml:space="preserve">4.11835098266602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.17660808563232</t>
   </si>
   <si>
     <t xml:space="preserve">4.11386966705322</t>
   </si>
   <si>
-    <t xml:space="preserve">4.10938835144043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.06009387969971</t>
+    <t xml:space="preserve">4.10938787460327</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.06009340286255</t>
   </si>
   <si>
     <t xml:space="preserve">4.1945333480835</t>
   </si>
   <si>
-    <t xml:space="preserve">4.21245861053467</t>
+    <t xml:space="preserve">4.21245908737183</t>
   </si>
   <si>
     <t xml:space="preserve">4.14972019195557</t>
@@ -2636,13 +2636,13 @@
     <t xml:space="preserve">4.01976156234741</t>
   </si>
   <si>
-    <t xml:space="preserve">4.06457471847534</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.20797777175903</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.23038387298584</t>
+    <t xml:space="preserve">4.0645751953125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.20797729492188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.230384349823</t>
   </si>
   <si>
     <t xml:space="preserve">4.25727224349976</t>
@@ -2651,55 +2651,55 @@
     <t xml:space="preserve">4.20349645614624</t>
   </si>
   <si>
-    <t xml:space="preserve">3.92565298080444</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.90772819519043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.88083982467651</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.87635803222656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.80913805961609</t>
+    <t xml:space="preserve">3.92565321922302</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.90772795677185</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.88083958625793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.87635850906372</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.80913829803467</t>
   </si>
   <si>
     <t xml:space="preserve">3.71503043174744</t>
   </si>
   <si>
-    <t xml:space="preserve">3.66573572158813</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.83154535293579</t>
+    <t xml:space="preserve">3.66573596000671</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.83154511451721</t>
   </si>
   <si>
     <t xml:space="preserve">3.93461561203003</t>
   </si>
   <si>
-    <t xml:space="preserve">3.94357872009277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.04664945602417</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.9928731918335</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.98391056060791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.02424240112305</t>
+    <t xml:space="preserve">3.94357848167419</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.04664897918701</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.99287295341492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.98391032218933</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.02424287796021</t>
   </si>
   <si>
     <t xml:space="preserve">3.85395193099976</t>
   </si>
   <si>
-    <t xml:space="preserve">3.93013477325439</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.97046661376953</t>
+    <t xml:space="preserve">3.93013501167297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.97046637535095</t>
   </si>
   <si>
     <t xml:space="preserve">4.10042524337769</t>
@@ -2711,10 +2711,10 @@
     <t xml:space="preserve">4.09146308898926</t>
   </si>
   <si>
-    <t xml:space="preserve">4.22590303421021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.26623487472534</t>
+    <t xml:space="preserve">4.22590351104736</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.2662353515625</t>
   </si>
   <si>
     <t xml:space="preserve">4.24382829666138</t>
@@ -2738,37 +2738,37 @@
     <t xml:space="preserve">4.40515613555908</t>
   </si>
   <si>
-    <t xml:space="preserve">4.43652582168579</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.48133945465088</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.53511571884155</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.55304050445557</t>
+    <t xml:space="preserve">4.43652534484863</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.48133897781372</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.53511524200439</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.55304098129272</t>
   </si>
   <si>
     <t xml:space="preserve">4.56200361251831</t>
   </si>
   <si>
-    <t xml:space="preserve">4.50822734832764</t>
+    <t xml:space="preserve">4.50822687149048</t>
   </si>
   <si>
     <t xml:space="preserve">4.45445108413696</t>
   </si>
   <si>
-    <t xml:space="preserve">4.43204498291016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.49926519393921</t>
+    <t xml:space="preserve">4.432044506073</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.49926471710205</t>
   </si>
   <si>
     <t xml:space="preserve">4.49030208587646</t>
   </si>
   <si>
-    <t xml:space="preserve">4.51718997955322</t>
+    <t xml:space="preserve">4.51718950271606</t>
   </si>
   <si>
     <t xml:space="preserve">4.633704662323</t>
@@ -2786,7 +2786,7 @@
     <t xml:space="preserve">4.61577939987183</t>
   </si>
   <si>
-    <t xml:space="preserve">4.64266729354858</t>
+    <t xml:space="preserve">4.64266681671143</t>
   </si>
   <si>
     <t xml:space="preserve">4.39171266555786</t>
@@ -2798,16 +2798,16 @@
     <t xml:space="preserve">4.27519750595093</t>
   </si>
   <si>
-    <t xml:space="preserve">4.58889198303223</t>
+    <t xml:space="preserve">4.58889150619507</t>
   </si>
   <si>
     <t xml:space="preserve">4.66059303283691</t>
   </si>
   <si>
-    <t xml:space="preserve">4.65163040161133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.71436977386475</t>
+    <t xml:space="preserve">4.65162992477417</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.71436929702759</t>
   </si>
   <si>
     <t xml:space="preserve">4.75918245315552</t>
@@ -2825,28 +2825,28 @@
     <t xml:space="preserve">4.88465976715088</t>
   </si>
   <si>
-    <t xml:space="preserve">5.05495071411133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.01910018920898</t>
+    <t xml:space="preserve">5.05495023727417</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.01909971237183</t>
   </si>
   <si>
     <t xml:space="preserve">5.14457750320435</t>
   </si>
   <si>
-    <t xml:space="preserve">5.31486797332764</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.3776068687439</t>
+    <t xml:space="preserve">5.31486845016479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.37760734558105</t>
   </si>
   <si>
     <t xml:space="preserve">5.35968160629272</t>
   </si>
   <si>
-    <t xml:space="preserve">5.16250276565552</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.0459885597229</t>
+    <t xml:space="preserve">5.16250324249268</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.04598808288574</t>
   </si>
   <si>
     <t xml:space="preserve">5.15354013442993</t>
@@ -2861,10 +2861,10 @@
     <t xml:space="preserve">5.51204776763916</t>
   </si>
   <si>
-    <t xml:space="preserve">5.4761962890625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.50308418273926</t>
+    <t xml:space="preserve">5.47619676589966</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.50308465957642</t>
   </si>
   <si>
     <t xml:space="preserve">5.29694318771362</t>
@@ -2876,34 +2876,34 @@
     <t xml:space="preserve">5.18042802810669</t>
   </si>
   <si>
-    <t xml:space="preserve">5.0728759765625</t>
+    <t xml:space="preserve">5.07287549972534</t>
   </si>
   <si>
     <t xml:space="preserve">5.09080171585083</t>
   </si>
   <si>
-    <t xml:space="preserve">4.99221277236938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.75022029876709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.80399608612061</t>
+    <t xml:space="preserve">4.99221229553223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.75021982192993</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.80399560928345</t>
   </si>
   <si>
     <t xml:space="preserve">4.92947340011597</t>
   </si>
   <si>
-    <t xml:space="preserve">4.83984708786011</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.97428703308105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.90258502960205</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.86673450469971</t>
+    <t xml:space="preserve">4.83984661102295</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.9742865562439</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.90258550643921</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.86673402786255</t>
   </si>
   <si>
     <t xml:space="preserve">5.03702545166016</t>
@@ -2912,7 +2912,7 @@
     <t xml:space="preserve">4.95636177062988</t>
   </si>
   <si>
-    <t xml:space="preserve">4.79503297805786</t>
+    <t xml:space="preserve">4.79503345489502</t>
   </si>
   <si>
     <t xml:space="preserve">4.74125719070435</t>
@@ -2921,25 +2921,25 @@
     <t xml:space="preserve">4.70540618896484</t>
   </si>
   <si>
-    <t xml:space="preserve">4.52615308761597</t>
+    <t xml:space="preserve">4.52615261077881</t>
   </si>
   <si>
     <t xml:space="preserve">4.41860055923462</t>
   </si>
   <si>
-    <t xml:space="preserve">4.36482429504395</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.23934698104858</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.85777187347412</t>
+    <t xml:space="preserve">4.3648247718811</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.23934745788574</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.85777139663696</t>
   </si>
   <si>
     <t xml:space="preserve">4.91154813766479</t>
   </si>
   <si>
-    <t xml:space="preserve">4.96532440185547</t>
+    <t xml:space="preserve">4.96532392501831</t>
   </si>
   <si>
     <t xml:space="preserve">5.11768960952759</t>
@@ -2951,34 +2951,34 @@
     <t xml:space="preserve">5.30590534210205</t>
   </si>
   <si>
-    <t xml:space="preserve">5.42242097854614</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.28798007965088</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.43138265609741</t>
+    <t xml:space="preserve">5.42242050170898</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.28798055648804</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.43138313293457</t>
   </si>
   <si>
     <t xml:space="preserve">5.55686044692993</t>
   </si>
   <si>
-    <t xml:space="preserve">5.62856245040894</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.52100992202759</t>
+    <t xml:space="preserve">5.62856197357178</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.52100944519043</t>
   </si>
   <si>
     <t xml:space="preserve">5.61959934234619</t>
   </si>
   <si>
-    <t xml:space="preserve">5.53893518447876</t>
+    <t xml:space="preserve">5.53893566131592</t>
   </si>
   <si>
     <t xml:space="preserve">5.37441253662109</t>
   </si>
   <si>
-    <t xml:space="preserve">5.47495365142822</t>
+    <t xml:space="preserve">5.47495412826538</t>
   </si>
   <si>
     <t xml:space="preserve">5.46581411361694</t>
@@ -2987,16 +2987,16 @@
     <t xml:space="preserve">5.48409461975098</t>
   </si>
   <si>
-    <t xml:space="preserve">5.63947677612305</t>
+    <t xml:space="preserve">5.63947725296021</t>
   </si>
   <si>
     <t xml:space="preserve">5.75829935073853</t>
   </si>
   <si>
-    <t xml:space="preserve">5.80399942398071</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.65775775909424</t>
+    <t xml:space="preserve">5.80399990081787</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.65775728225708</t>
   </si>
   <si>
     <t xml:space="preserve">5.62119674682617</t>
@@ -3005,25 +3005,25 @@
     <t xml:space="preserve">5.410973072052</t>
   </si>
   <si>
-    <t xml:space="preserve">5.40183258056641</t>
+    <t xml:space="preserve">5.40183305740356</t>
   </si>
   <si>
     <t xml:space="preserve">5.63033676147461</t>
   </si>
   <si>
-    <t xml:space="preserve">5.61205673217773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.8222804069519</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.84056091308594</t>
+    <t xml:space="preserve">5.61205625534058</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.82227993011475</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.84056043624878</t>
   </si>
   <si>
     <t xml:space="preserve">5.88626146316528</t>
   </si>
   <si>
-    <t xml:space="preserve">5.93196153640747</t>
+    <t xml:space="preserve">5.93196201324463</t>
   </si>
   <si>
     <t xml:space="preserve">5.90454149246216</t>
@@ -3053,13 +3053,13 @@
     <t xml:space="preserve">5.785719871521</t>
   </si>
   <si>
-    <t xml:space="preserve">5.7308783531189</t>
+    <t xml:space="preserve">5.73087882995605</t>
   </si>
   <si>
     <t xml:space="preserve">5.67603778839111</t>
   </si>
   <si>
-    <t xml:space="preserve">5.69431781768799</t>
+    <t xml:space="preserve">5.69431829452515</t>
   </si>
   <si>
     <t xml:space="preserve">5.66689729690552</t>
@@ -3071,16 +3071,16 @@
     <t xml:space="preserve">5.42011308670044</t>
   </si>
   <si>
-    <t xml:space="preserve">5.33785200119019</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.20988941192627</t>
+    <t xml:space="preserve">5.33785152435303</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.20988988876343</t>
   </si>
   <si>
     <t xml:space="preserve">5.34699201583862</t>
   </si>
   <si>
-    <t xml:space="preserve">5.31043148040771</t>
+    <t xml:space="preserve">5.31043100357056</t>
   </si>
   <si>
     <t xml:space="preserve">5.39269304275513</t>
@@ -3104,7 +3104,7 @@
     <t xml:space="preserve">5.10020780563354</t>
   </si>
   <si>
-    <t xml:space="preserve">5.10934782028198</t>
+    <t xml:space="preserve">5.10934829711914</t>
   </si>
   <si>
     <t xml:space="preserve">5.08192729949951</t>
@@ -3116,25 +3116,25 @@
     <t xml:space="preserve">5.01794624328613</t>
   </si>
   <si>
-    <t xml:space="preserve">5.11848831176758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.13676786422729</t>
+    <t xml:space="preserve">5.11848783493042</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.13676834106445</t>
   </si>
   <si>
     <t xml:space="preserve">5.07278728485107</t>
   </si>
   <si>
-    <t xml:space="preserve">5.02708625793457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.0453667640686</t>
+    <t xml:space="preserve">5.02708673477173</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.04536628723145</t>
   </si>
   <si>
     <t xml:space="preserve">4.99052619934082</t>
   </si>
   <si>
-    <t xml:space="preserve">5.00880575180054</t>
+    <t xml:space="preserve">5.00880670547485</t>
   </si>
   <si>
     <t xml:space="preserve">5.0545072555542</t>
@@ -3146,7 +3146,7 @@
     <t xml:space="preserve">5.16418886184692</t>
   </si>
   <si>
-    <t xml:space="preserve">5.14590930938721</t>
+    <t xml:space="preserve">5.14590835571289</t>
   </si>
   <si>
     <t xml:space="preserve">4.94482469558716</t>
@@ -3158,19 +3158,19 @@
     <t xml:space="preserve">4.89912414550781</t>
   </si>
   <si>
-    <t xml:space="preserve">4.8808445930481</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.85342359542847</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.82600355148315</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.73460102081299</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.75288200378418</t>
+    <t xml:space="preserve">4.88084411621094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.85342311859131</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.826003074646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.73460149765015</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.75288152694702</t>
   </si>
   <si>
     <t xml:space="preserve">4.69804096221924</t>
@@ -3179,16 +3179,16 @@
     <t xml:space="preserve">4.57921886444092</t>
   </si>
   <si>
-    <t xml:space="preserve">4.71632146835327</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.67975997924805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.84428310394287</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.80772304534912</t>
+    <t xml:space="preserve">4.71632099151611</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.67976045608521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.84428358078003</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.80772256851196</t>
   </si>
   <si>
     <t xml:space="preserve">4.57007837295532</t>
@@ -3200,7 +3200,7 @@
     <t xml:space="preserve">4.6889009475708</t>
   </si>
   <si>
-    <t xml:space="preserve">4.67062044143677</t>
+    <t xml:space="preserve">4.67062091827393</t>
   </si>
   <si>
     <t xml:space="preserve">4.6431999206543</t>
@@ -3209,10 +3209,10 @@
     <t xml:space="preserve">4.63405990600586</t>
   </si>
   <si>
-    <t xml:space="preserve">4.56093835830688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.58835935592651</t>
+    <t xml:space="preserve">4.56093788146973</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.58835887908936</t>
   </si>
   <si>
     <t xml:space="preserve">4.55179834365845</t>
@@ -3221,7 +3221,7 @@
     <t xml:space="preserve">4.48781728744507</t>
   </si>
   <si>
-    <t xml:space="preserve">4.53808832168579</t>
+    <t xml:space="preserve">4.53808784484863</t>
   </si>
   <si>
     <t xml:space="preserve">4.46953678131104</t>
@@ -3230,418 +3230,421 @@
     <t xml:space="preserve">4.50152778625488</t>
   </si>
   <si>
-    <t xml:space="preserve">4.49695730209351</t>
+    <t xml:space="preserve">4.49695777893066</t>
   </si>
   <si>
     <t xml:space="preserve">4.40555620193481</t>
   </si>
   <si>
+    <t xml:space="preserve">4.43297672271729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.45582723617554</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.36899518966675</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.29130363464355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.20447254180908</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.47867774963379</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.48324728012085</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.79858207702637</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.87170362472534</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.83514308929443</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.17332887649536</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.32871150970459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.19160890579224</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.25559091567993</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.38355207443237</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.97224569320679</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.18246936798096</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.81686305999756</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.9996657371521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.96310567855835</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.09106731414795</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.98138570785522</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.92654466629028</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.06364727020264</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.30129146575928</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.20074987411499</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.12762832641602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.23730993270874</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.27387094497681</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.31957149505615</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.27241277694702</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.23468494415283</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.25354862213135</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.02718353271484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.99888849258423</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.01775217056274</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.16866207122803</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.1403660774231</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.18752527236938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.24411678314209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.35729885101318</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.39502620697021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.30070781707764</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.32900333404541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.1969575881958</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.26298046112061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.37616300582886</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.17809295654297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.21582126617432</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.10263824462891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.14979839324951</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.09320688247681</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.12150239944458</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.07434320449829</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.03661584854126</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.06491136550903</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.95172882080078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.93286514282227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.89513778686523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.91400146484375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.90456914901733</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.77252340316772</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.76309156417847</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.72536420822144</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.9611611366272</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.8574104309082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.8008189201355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.51786327362061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.50843143463135</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.55559015274048</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.54615879058838</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.6216139793396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.54144287109375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.56502246856689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.52729511260986</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.56030654907227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.47541952133179</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.47070360183716</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.4848518371582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.45655584335327</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.59331798553467</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.50371503829956</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.51314687728882</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.63576126098633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.65934085845947</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.62632942199707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.64519357681274</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.67820453643799</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.71593236923218</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.6310453414917</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.69706869125366</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.71121597290039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.73479604721069</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.60274982452393</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.57445430755615</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.42354488372803</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.37638473510742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.34337377548218</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.41411256790161</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.3952488899231</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.4942831993103</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.44712448120117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.38110113143921</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.36695337295532</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.33865737915039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.26320266723633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.28206634521484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.32922601699829</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.3245096206665</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.31036233901978</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.28678226470947</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.27263498306274</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.2349066734314</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.1122932434082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.0887131690979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.0557017326355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.10757684707642</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.03683805465698</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.86234831809998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.00854253768921</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.99910998344421</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.07456541061401</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.10286092758179</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.13587284088135</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.2254753112793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.15473651885986</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.18303155899048</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.27735042572021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.29149866104126</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.45183944702148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.22075939178467</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.24905490875244</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.26791906356812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.39053297042847</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.37166976928711</t>
+  </si>
+  <si>
     <t xml:space="preserve">4.43297624588013</t>
   </si>
   <si>
-    <t xml:space="preserve">4.45582628250122</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.36899518966675</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.29130411148071</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.20447206497192</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.47867727279663</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.48324728012085</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.79858255386353</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.87170362472534</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.83514308929443</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.17332887649536</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.32871150970459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.19160890579224</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.25559091567993</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.38355255126953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.97224569320679</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.18246936798096</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.81686305999756</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.9996657371521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.96310520172119</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.09106779098511</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.98138570785522</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.92654466629028</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.06364727020264</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.30129098892212</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.20074987411499</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.12762832641602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.23730993270874</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.27387046813965</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.31957197189331</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.27241230010986</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.23468494415283</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.25354862213135</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.02718353271484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.99888801574707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.01775217056274</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.16866159439087</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.1403660774231</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.18752527236938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.24411678314209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.35729885101318</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.39502620697021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.30070781707764</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.32900333404541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.1969575881958</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.26298046112061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.3761625289917</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.17809343338013</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.21582126617432</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.10263824462891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.14979791641235</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.09320688247681</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.12150239944458</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.07434320449829</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.03661584854126</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.06491088867188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.95172882080078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.93286514282227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.89513778686523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.91400146484375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.90456962585449</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.77252340316772</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.76309156417847</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.72536420822144</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.96116065979004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.85740995407104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.80081939697266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.51786279678345</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.50843143463135</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.55559015274048</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.54615879058838</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.62161350250244</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.54144287109375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.56502246856689</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.52729511260986</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.56030654907227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.47541999816895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.47070360183716</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.4848518371582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.45655584335327</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.59331798553467</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.50371503829956</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.51314735412598</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.63576126098633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.65934085845947</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.62632989883423</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.64519357681274</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.67820501327515</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.71593236923218</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.6310453414917</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.69706869125366</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.71121597290039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.73479604721069</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.60275030136108</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.57445430755615</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.42354488372803</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.37638473510742</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.34337377548218</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.41411209106445</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.3952488899231</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.4942831993103</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.44712448120117</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.38110113143921</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.36695337295532</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.33865737915039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.26320266723633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.28206634521484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.32922601699829</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.3245096206665</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.31036233901978</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.28678226470947</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.27263498306274</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.23490715026855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.11229276657104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.0887131690979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.05570220947266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.10757732391357</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.03683805465698</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.86234855651855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.00854206085205</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.99911022186279</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.07456541061401</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.10286092758179</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.13587284088135</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.2254753112793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.15473651885986</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.18303203582764</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.27735042572021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.29149866104126</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.45183944702148</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.22075939178467</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.24905490875244</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.26791858673096</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.39053297042847</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.37166976928711</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.35752153396606</t>
+    <t xml:space="preserve">4.35752105712891</t>
   </si>
   <si>
     <t xml:space="preserve">4.35280513763428</t>
@@ -3677,19 +3680,19 @@
     <t xml:space="preserve">4.23962306976318</t>
   </si>
   <si>
-    <t xml:space="preserve">4.20189571380615</t>
+    <t xml:space="preserve">4.20189523696899</t>
   </si>
   <si>
     <t xml:space="preserve">4.12644052505493</t>
   </si>
   <si>
-    <t xml:space="preserve">4.02268981933594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.15002059936523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.92837166786194</t>
+    <t xml:space="preserve">4.0226902961731</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.15002012252808</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.92837142944336</t>
   </si>
   <si>
     <t xml:space="preserve">4.04626989364624</t>
@@ -3698,16 +3701,16 @@
     <t xml:space="preserve">3.96138286590576</t>
   </si>
   <si>
-    <t xml:space="preserve">4.06041717529297</t>
+    <t xml:space="preserve">4.06041765213013</t>
   </si>
   <si>
     <t xml:space="preserve">4.01797485351562</t>
   </si>
   <si>
-    <t xml:space="preserve">3.90007638931274</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.94251894950867</t>
+    <t xml:space="preserve">3.90007615089417</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.94251942634583</t>
   </si>
   <si>
     <t xml:space="preserve">3.89535999298096</t>
@@ -3725,7 +3728,7 @@
     <t xml:space="preserve">3.88121199607849</t>
   </si>
   <si>
-    <t xml:space="preserve">3.84348464012146</t>
+    <t xml:space="preserve">3.84348440170288</t>
   </si>
   <si>
     <t xml:space="preserve">3.81990528106689</t>
@@ -3743,10 +3746,10 @@
     <t xml:space="preserve">3.75388216972351</t>
   </si>
   <si>
-    <t xml:space="preserve">3.72558641433716</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.76331377029419</t>
+    <t xml:space="preserve">3.72558665275574</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.76331400871277</t>
   </si>
   <si>
     <t xml:space="preserve">3.735018491745</t>
@@ -3755,7 +3758,7 @@
     <t xml:space="preserve">3.71615481376648</t>
   </si>
   <si>
-    <t xml:space="preserve">3.58410859107971</t>
+    <t xml:space="preserve">3.58410835266113</t>
   </si>
   <si>
     <t xml:space="preserve">3.76442790031433</t>
@@ -57622,7 +57625,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G2030" t="s">
-        <v>1074</v>
+        <v>1209</v>
       </c>
       <c r="H2030" t="s">
         <v>9</v>
@@ -57648,7 +57651,7 @@
         <v>4.61999988555908</v>
       </c>
       <c r="G2031" t="s">
-        <v>1209</v>
+        <v>1210</v>
       </c>
       <c r="H2031" t="s">
         <v>9</v>
@@ -57700,7 +57703,7 @@
         <v>4.61999988555908</v>
       </c>
       <c r="G2033" t="s">
-        <v>1209</v>
+        <v>1210</v>
       </c>
       <c r="H2033" t="s">
         <v>9</v>
@@ -57830,7 +57833,7 @@
         <v>4.61499977111816</v>
       </c>
       <c r="G2038" t="s">
-        <v>1210</v>
+        <v>1211</v>
       </c>
       <c r="H2038" t="s">
         <v>9</v>
@@ -57856,7 +57859,7 @@
         <v>4.55499982833862</v>
       </c>
       <c r="G2039" t="s">
-        <v>1211</v>
+        <v>1212</v>
       </c>
       <c r="H2039" t="s">
         <v>9</v>
@@ -57882,7 +57885,7 @@
         <v>4.88500022888184</v>
       </c>
       <c r="G2040" t="s">
-        <v>1212</v>
+        <v>1213</v>
       </c>
       <c r="H2040" t="s">
         <v>9</v>
@@ -57934,7 +57937,7 @@
         <v>4.75</v>
       </c>
       <c r="G2042" t="s">
-        <v>1213</v>
+        <v>1214</v>
       </c>
       <c r="H2042" t="s">
         <v>9</v>
@@ -57986,7 +57989,7 @@
         <v>4.75</v>
       </c>
       <c r="G2044" t="s">
-        <v>1213</v>
+        <v>1214</v>
       </c>
       <c r="H2044" t="s">
         <v>9</v>
@@ -58064,7 +58067,7 @@
         <v>4.76999998092651</v>
       </c>
       <c r="G2047" t="s">
-        <v>1214</v>
+        <v>1215</v>
       </c>
       <c r="H2047" t="s">
         <v>9</v>
@@ -58090,7 +58093,7 @@
         <v>4.67000007629395</v>
       </c>
       <c r="G2048" t="s">
-        <v>1215</v>
+        <v>1216</v>
       </c>
       <c r="H2048" t="s">
         <v>9</v>
@@ -58116,7 +58119,7 @@
         <v>4.71000003814697</v>
       </c>
       <c r="G2049" t="s">
-        <v>1216</v>
+        <v>1217</v>
       </c>
       <c r="H2049" t="s">
         <v>9</v>
@@ -58168,7 +58171,7 @@
         <v>4.55999994277954</v>
       </c>
       <c r="G2051" t="s">
-        <v>1217</v>
+        <v>1218</v>
       </c>
       <c r="H2051" t="s">
         <v>9</v>
@@ -58480,7 +58483,7 @@
         <v>4.5</v>
       </c>
       <c r="G2063" t="s">
-        <v>1218</v>
+        <v>1219</v>
       </c>
       <c r="H2063" t="s">
         <v>9</v>
@@ -58506,7 +58509,7 @@
         <v>4.6100001335144</v>
       </c>
       <c r="G2064" t="s">
-        <v>1219</v>
+        <v>1220</v>
       </c>
       <c r="H2064" t="s">
         <v>9</v>
@@ -58558,7 +58561,7 @@
         <v>4.61999988555908</v>
       </c>
       <c r="G2066" t="s">
-        <v>1209</v>
+        <v>1210</v>
       </c>
       <c r="H2066" t="s">
         <v>9</v>
@@ -58584,7 +58587,7 @@
         <v>4.5</v>
       </c>
       <c r="G2067" t="s">
-        <v>1218</v>
+        <v>1219</v>
       </c>
       <c r="H2067" t="s">
         <v>9</v>
@@ -58610,7 +58613,7 @@
         <v>4.49499988555908</v>
       </c>
       <c r="G2068" t="s">
-        <v>1220</v>
+        <v>1221</v>
       </c>
       <c r="H2068" t="s">
         <v>9</v>
@@ -58688,7 +58691,7 @@
         <v>4.45499992370605</v>
       </c>
       <c r="G2071" t="s">
-        <v>1221</v>
+        <v>1222</v>
       </c>
       <c r="H2071" t="s">
         <v>9</v>
@@ -58714,7 +58717,7 @@
         <v>4.375</v>
       </c>
       <c r="G2072" t="s">
-        <v>1222</v>
+        <v>1223</v>
       </c>
       <c r="H2072" t="s">
         <v>9</v>
@@ -58740,7 +58743,7 @@
         <v>4.2649998664856</v>
       </c>
       <c r="G2073" t="s">
-        <v>1223</v>
+        <v>1224</v>
       </c>
       <c r="H2073" t="s">
         <v>9</v>
@@ -58792,7 +58795,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G2075" t="s">
-        <v>1224</v>
+        <v>1225</v>
       </c>
       <c r="H2075" t="s">
         <v>9</v>
@@ -58896,7 +58899,7 @@
         <v>4.16499996185303</v>
       </c>
       <c r="G2079" t="s">
-        <v>1225</v>
+        <v>1226</v>
       </c>
       <c r="H2079" t="s">
         <v>9</v>
@@ -58948,7 +58951,7 @@
         <v>4.28999996185303</v>
       </c>
       <c r="G2081" t="s">
-        <v>1226</v>
+        <v>1227</v>
       </c>
       <c r="H2081" t="s">
         <v>9</v>
@@ -58974,7 +58977,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G2082" t="s">
-        <v>1227</v>
+        <v>1228</v>
       </c>
       <c r="H2082" t="s">
         <v>9</v>
@@ -59052,7 +59055,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G2085" t="s">
-        <v>1227</v>
+        <v>1228</v>
       </c>
       <c r="H2085" t="s">
         <v>9</v>
@@ -59078,7 +59081,7 @@
         <v>4.2649998664856</v>
       </c>
       <c r="G2086" t="s">
-        <v>1223</v>
+        <v>1224</v>
       </c>
       <c r="H2086" t="s">
         <v>9</v>
@@ -59130,7 +59133,7 @@
         <v>4.30499982833862</v>
       </c>
       <c r="G2088" t="s">
-        <v>1228</v>
+        <v>1229</v>
       </c>
       <c r="H2088" t="s">
         <v>9</v>
@@ -59156,7 +59159,7 @@
         <v>4.26000022888184</v>
       </c>
       <c r="G2089" t="s">
-        <v>1229</v>
+        <v>1230</v>
       </c>
       <c r="H2089" t="s">
         <v>9</v>
@@ -59182,7 +59185,7 @@
         <v>4.13500022888184</v>
       </c>
       <c r="G2090" t="s">
-        <v>1230</v>
+        <v>1231</v>
       </c>
       <c r="H2090" t="s">
         <v>9</v>
@@ -59208,7 +59211,7 @@
         <v>4.17999982833862</v>
       </c>
       <c r="G2091" t="s">
-        <v>1231</v>
+        <v>1232</v>
       </c>
       <c r="H2091" t="s">
         <v>9</v>
@@ -59234,7 +59237,7 @@
         <v>4.13000011444092</v>
       </c>
       <c r="G2092" t="s">
-        <v>1232</v>
+        <v>1233</v>
       </c>
       <c r="H2092" t="s">
         <v>9</v>
@@ -59260,7 +59263,7 @@
         <v>4.11999988555908</v>
       </c>
       <c r="G2093" t="s">
-        <v>1233</v>
+        <v>1234</v>
       </c>
       <c r="H2093" t="s">
         <v>9</v>
@@ -59286,7 +59289,7 @@
         <v>4.15500020980835</v>
       </c>
       <c r="G2094" t="s">
-        <v>1234</v>
+        <v>1235</v>
       </c>
       <c r="H2094" t="s">
         <v>9</v>
@@ -59312,7 +59315,7 @@
         <v>4.15500020980835</v>
       </c>
       <c r="G2095" t="s">
-        <v>1234</v>
+        <v>1235</v>
       </c>
       <c r="H2095" t="s">
         <v>9</v>
@@ -59338,7 +59341,7 @@
         <v>4.11999988555908</v>
       </c>
       <c r="G2096" t="s">
-        <v>1233</v>
+        <v>1234</v>
       </c>
       <c r="H2096" t="s">
         <v>9</v>
@@ -59364,7 +59367,7 @@
         <v>4.1399998664856</v>
       </c>
       <c r="G2097" t="s">
-        <v>1235</v>
+        <v>1236</v>
       </c>
       <c r="H2097" t="s">
         <v>9</v>
@@ -59390,7 +59393,7 @@
         <v>4.11499977111816</v>
       </c>
       <c r="G2098" t="s">
-        <v>1236</v>
+        <v>1237</v>
       </c>
       <c r="H2098" t="s">
         <v>9</v>
@@ -59416,7 +59419,7 @@
         <v>4.07499980926514</v>
       </c>
       <c r="G2099" t="s">
-        <v>1237</v>
+        <v>1238</v>
       </c>
       <c r="H2099" t="s">
         <v>9</v>
@@ -59442,7 +59445,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G2100" t="s">
-        <v>1238</v>
+        <v>1239</v>
       </c>
       <c r="H2100" t="s">
         <v>9</v>
@@ -59468,7 +59471,7 @@
         <v>4.01000022888184</v>
       </c>
       <c r="G2101" t="s">
-        <v>1239</v>
+        <v>1240</v>
       </c>
       <c r="H2101" t="s">
         <v>9</v>
@@ -59494,7 +59497,7 @@
         <v>3.9300000667572</v>
       </c>
       <c r="G2102" t="s">
-        <v>1240</v>
+        <v>1241</v>
       </c>
       <c r="H2102" t="s">
         <v>9</v>
@@ -59520,7 +59523,7 @@
         <v>3.97000002861023</v>
       </c>
       <c r="G2103" t="s">
-        <v>1241</v>
+        <v>1242</v>
       </c>
       <c r="H2103" t="s">
         <v>9</v>
@@ -59546,7 +59549,7 @@
         <v>3.98000001907349</v>
       </c>
       <c r="G2104" t="s">
-        <v>1242</v>
+        <v>1243</v>
       </c>
       <c r="H2104" t="s">
         <v>9</v>
@@ -59572,7 +59575,7 @@
         <v>3.95000004768372</v>
       </c>
       <c r="G2105" t="s">
-        <v>1243</v>
+        <v>1244</v>
       </c>
       <c r="H2105" t="s">
         <v>9</v>
@@ -59598,7 +59601,7 @@
         <v>3.99000000953674</v>
       </c>
       <c r="G2106" t="s">
-        <v>1244</v>
+        <v>1245</v>
       </c>
       <c r="H2106" t="s">
         <v>9</v>
@@ -59624,7 +59627,7 @@
         <v>3.96000003814697</v>
       </c>
       <c r="G2107" t="s">
-        <v>1245</v>
+        <v>1246</v>
       </c>
       <c r="H2107" t="s">
         <v>9</v>
@@ -59650,7 +59653,7 @@
         <v>3.94000005722046</v>
       </c>
       <c r="G2108" t="s">
-        <v>1246</v>
+        <v>1247</v>
       </c>
       <c r="H2108" t="s">
         <v>9</v>
@@ -59676,7 +59679,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G2109" t="s">
-        <v>1247</v>
+        <v>1248</v>
       </c>
       <c r="H2109" t="s">
         <v>9</v>
@@ -59702,7 +59705,7 @@
         <v>3.9300000667572</v>
       </c>
       <c r="G2110" t="s">
-        <v>1240</v>
+        <v>1241</v>
       </c>
       <c r="H2110" t="s">
         <v>9</v>
@@ -59728,7 +59731,7 @@
         <v>3.97000002861023</v>
       </c>
       <c r="G2111" t="s">
-        <v>1241</v>
+        <v>1242</v>
       </c>
       <c r="H2111" t="s">
         <v>9</v>
@@ -59754,7 +59757,7 @@
         <v>3.94000005722046</v>
       </c>
       <c r="G2112" t="s">
-        <v>1246</v>
+        <v>1247</v>
       </c>
       <c r="H2112" t="s">
         <v>9</v>
@@ -59780,7 +59783,7 @@
         <v>3.96000003814697</v>
       </c>
       <c r="G2113" t="s">
-        <v>1245</v>
+        <v>1246</v>
       </c>
       <c r="H2113" t="s">
         <v>9</v>
@@ -59806,7 +59809,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G2114" t="s">
-        <v>1248</v>
+        <v>1249</v>
       </c>
       <c r="H2114" t="s">
         <v>9</v>
@@ -59832,7 +59835,7 @@
         <v>3.82999992370605</v>
       </c>
       <c r="G2115" t="s">
-        <v>1249</v>
+        <v>1250</v>
       </c>
       <c r="H2115" t="s">
         <v>9</v>
@@ -59858,7 +59861,7 @@
         <v>3.78999996185303</v>
       </c>
       <c r="G2116" t="s">
-        <v>1250</v>
+        <v>1251</v>
       </c>
       <c r="H2116" t="s">
         <v>9</v>
@@ -59884,7 +59887,7 @@
         <v>3.80999994277954</v>
       </c>
       <c r="G2117" t="s">
-        <v>1245</v>
+        <v>1246</v>
       </c>
       <c r="H2117" t="s">
         <v>9</v>
@@ -59910,7 +59913,7 @@
         <v>3.84999990463257</v>
       </c>
       <c r="G2118" t="s">
-        <v>1251</v>
+        <v>1252</v>
       </c>
       <c r="H2118" t="s">
         <v>9</v>
@@ -59936,7 +59939,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G2119" t="s">
-        <v>1248</v>
+        <v>1249</v>
       </c>
       <c r="H2119" t="s">
         <v>9</v>
@@ -59962,7 +59965,7 @@
         <v>3.82999992370605</v>
       </c>
       <c r="G2120" t="s">
-        <v>1249</v>
+        <v>1250</v>
       </c>
       <c r="H2120" t="s">
         <v>9</v>
@@ -59988,7 +59991,7 @@
         <v>3.84999990463257</v>
       </c>
       <c r="G2121" t="s">
-        <v>1251</v>
+        <v>1252</v>
       </c>
       <c r="H2121" t="s">
         <v>9</v>
@@ -60014,7 +60017,7 @@
         <v>3.78999996185303</v>
       </c>
       <c r="G2122" t="s">
-        <v>1250</v>
+        <v>1251</v>
       </c>
       <c r="H2122" t="s">
         <v>9</v>
@@ -60040,7 +60043,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G2123" t="s">
-        <v>1252</v>
+        <v>1253</v>
       </c>
       <c r="H2123" t="s">
         <v>9</v>
@@ -60066,7 +60069,7 @@
         <v>3.76999998092651</v>
       </c>
       <c r="G2124" t="s">
-        <v>1253</v>
+        <v>1254</v>
       </c>
       <c r="H2124" t="s">
         <v>9</v>
@@ -60092,7 +60095,7 @@
         <v>3.78999996185303</v>
       </c>
       <c r="G2125" t="s">
-        <v>1250</v>
+        <v>1251</v>
       </c>
       <c r="H2125" t="s">
         <v>9</v>
@@ -60118,7 +60121,7 @@
         <v>3.75</v>
       </c>
       <c r="G2126" t="s">
-        <v>1254</v>
+        <v>1255</v>
       </c>
       <c r="H2126" t="s">
         <v>9</v>
@@ -60144,7 +60147,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G2127" t="s">
-        <v>1255</v>
+        <v>1256</v>
       </c>
       <c r="H2127" t="s">
         <v>9</v>
@@ -60170,7 +60173,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G2128" t="s">
-        <v>1256</v>
+        <v>1257</v>
       </c>
       <c r="H2128" t="s">
         <v>9</v>
@@ -60196,7 +60199,7 @@
         <v>3.67000007629395</v>
       </c>
       <c r="G2129" t="s">
-        <v>1257</v>
+        <v>1258</v>
       </c>
       <c r="H2129" t="s">
         <v>9</v>
@@ -60222,7 +60225,7 @@
         <v>3.67000007629395</v>
       </c>
       <c r="G2130" t="s">
-        <v>1257</v>
+        <v>1258</v>
       </c>
       <c r="H2130" t="s">
         <v>9</v>
@@ -60248,7 +60251,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G2131" t="s">
-        <v>1256</v>
+        <v>1257</v>
       </c>
       <c r="H2131" t="s">
         <v>9</v>
@@ -60274,7 +60277,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G2132" t="s">
-        <v>1258</v>
+        <v>1259</v>
       </c>
       <c r="H2132" t="s">
         <v>9</v>
@@ -60300,7 +60303,7 @@
         <v>3.75</v>
       </c>
       <c r="G2133" t="s">
-        <v>1254</v>
+        <v>1255</v>
       </c>
       <c r="H2133" t="s">
         <v>9</v>
@@ -60326,7 +60329,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G2134" t="s">
-        <v>1256</v>
+        <v>1257</v>
       </c>
       <c r="H2134" t="s">
         <v>9</v>
@@ -60352,7 +60355,7 @@
         <v>3.76999998092651</v>
       </c>
       <c r="G2135" t="s">
-        <v>1253</v>
+        <v>1254</v>
       </c>
       <c r="H2135" t="s">
         <v>9</v>
@@ -60378,7 +60381,7 @@
         <v>3.71000003814697</v>
       </c>
       <c r="G2136" t="s">
-        <v>1259</v>
+        <v>1260</v>
       </c>
       <c r="H2136" t="s">
         <v>9</v>
@@ -60404,7 +60407,7 @@
         <v>3.69000005722046</v>
       </c>
       <c r="G2137" t="s">
-        <v>1260</v>
+        <v>1261</v>
       </c>
       <c r="H2137" t="s">
         <v>9</v>
@@ -60430,7 +60433,7 @@
         <v>3.69000005722046</v>
       </c>
       <c r="G2138" t="s">
-        <v>1260</v>
+        <v>1261</v>
       </c>
       <c r="H2138" t="s">
         <v>9</v>
@@ -60456,7 +60459,7 @@
         <v>3.69000005722046</v>
       </c>
       <c r="G2139" t="s">
-        <v>1260</v>
+        <v>1261</v>
       </c>
       <c r="H2139" t="s">
         <v>9</v>
@@ -60482,7 +60485,7 @@
         <v>3.69000005722046</v>
       </c>
       <c r="G2140" t="s">
-        <v>1260</v>
+        <v>1261</v>
       </c>
       <c r="H2140" t="s">
         <v>9</v>
@@ -60508,7 +60511,7 @@
         <v>3.66000008583069</v>
       </c>
       <c r="G2141" t="s">
-        <v>1261</v>
+        <v>1262</v>
       </c>
       <c r="H2141" t="s">
         <v>9</v>
@@ -60534,7 +60537,7 @@
         <v>3.65000009536743</v>
       </c>
       <c r="G2142" t="s">
-        <v>1262</v>
+        <v>1263</v>
       </c>
       <c r="H2142" t="s">
         <v>9</v>
@@ -60560,7 +60563,7 @@
         <v>3.73000001907349</v>
       </c>
       <c r="G2143" t="s">
-        <v>1263</v>
+        <v>1264</v>
       </c>
       <c r="H2143" t="s">
         <v>9</v>
@@ -60586,7 +60589,7 @@
         <v>3.69000005722046</v>
       </c>
       <c r="G2144" t="s">
-        <v>1260</v>
+        <v>1261</v>
       </c>
       <c r="H2144" t="s">
         <v>9</v>
@@ -60612,7 +60615,7 @@
         <v>3.66000008583069</v>
       </c>
       <c r="G2145" t="s">
-        <v>1261</v>
+        <v>1262</v>
       </c>
       <c r="H2145" t="s">
         <v>9</v>
@@ -60638,7 +60641,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G2146" t="s">
-        <v>1264</v>
+        <v>1265</v>
       </c>
       <c r="H2146" t="s">
         <v>9</v>
@@ -60664,7 +60667,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G2147" t="s">
-        <v>1256</v>
+        <v>1257</v>
       </c>
       <c r="H2147" t="s">
         <v>9</v>
@@ -60690,7 +60693,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G2148" t="s">
-        <v>1256</v>
+        <v>1257</v>
       </c>
       <c r="H2148" t="s">
         <v>9</v>
@@ -60716,7 +60719,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G2149" t="s">
-        <v>1256</v>
+        <v>1257</v>
       </c>
       <c r="H2149" t="s">
         <v>9</v>
@@ -60742,7 +60745,7 @@
         <v>3.69000005722046</v>
       </c>
       <c r="G2150" t="s">
-        <v>1260</v>
+        <v>1261</v>
       </c>
       <c r="H2150" t="s">
         <v>9</v>
@@ -60768,7 +60771,7 @@
         <v>3.66000008583069</v>
       </c>
       <c r="G2151" t="s">
-        <v>1261</v>
+        <v>1262</v>
       </c>
       <c r="H2151" t="s">
         <v>9</v>
@@ -60794,7 +60797,7 @@
         <v>3.69000005722046</v>
       </c>
       <c r="G2152" t="s">
-        <v>1260</v>
+        <v>1261</v>
       </c>
       <c r="H2152" t="s">
         <v>9</v>
@@ -60820,7 +60823,7 @@
         <v>3.64000010490417</v>
       </c>
       <c r="G2153" t="s">
-        <v>1265</v>
+        <v>1266</v>
       </c>
       <c r="H2153" t="s">
         <v>9</v>
@@ -60846,7 +60849,7 @@
         <v>3.66000008583069</v>
       </c>
       <c r="G2154" t="s">
-        <v>1261</v>
+        <v>1262</v>
       </c>
       <c r="H2154" t="s">
         <v>9</v>
@@ -60872,7 +60875,7 @@
         <v>3.63000011444092</v>
       </c>
       <c r="G2155" t="s">
-        <v>1266</v>
+        <v>1267</v>
       </c>
       <c r="H2155" t="s">
         <v>9</v>
@@ -60898,7 +60901,7 @@
         <v>3.65000009536743</v>
       </c>
       <c r="G2156" t="s">
-        <v>1262</v>
+        <v>1263</v>
       </c>
       <c r="H2156" t="s">
         <v>9</v>
@@ -60924,7 +60927,7 @@
         <v>3.63000011444092</v>
       </c>
       <c r="G2157" t="s">
-        <v>1266</v>
+        <v>1267</v>
       </c>
       <c r="H2157" t="s">
         <v>9</v>
@@ -60950,7 +60953,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G2158" t="s">
-        <v>1267</v>
+        <v>1268</v>
       </c>
       <c r="H2158" t="s">
         <v>9</v>
@@ -60976,7 +60979,7 @@
         <v>3.47000002861023</v>
       </c>
       <c r="G2159" t="s">
-        <v>1268</v>
+        <v>1269</v>
       </c>
       <c r="H2159" t="s">
         <v>9</v>
@@ -61002,7 +61005,7 @@
         <v>3.4300000667572</v>
       </c>
       <c r="G2160" t="s">
-        <v>1269</v>
+        <v>1270</v>
       </c>
       <c r="H2160" t="s">
         <v>9</v>
@@ -61028,7 +61031,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G2161" t="s">
-        <v>1270</v>
+        <v>1271</v>
       </c>
       <c r="H2161" t="s">
         <v>9</v>
@@ -61054,7 +61057,7 @@
         <v>3.45000004768372</v>
       </c>
       <c r="G2162" t="s">
-        <v>1271</v>
+        <v>1272</v>
       </c>
       <c r="H2162" t="s">
         <v>9</v>
@@ -61080,7 +61083,7 @@
         <v>3.52999997138977</v>
       </c>
       <c r="G2163" t="s">
-        <v>1272</v>
+        <v>1273</v>
       </c>
       <c r="H2163" t="s">
         <v>9</v>
@@ -61106,7 +61109,7 @@
         <v>3.45000004768372</v>
       </c>
       <c r="G2164" t="s">
-        <v>1271</v>
+        <v>1272</v>
       </c>
       <c r="H2164" t="s">
         <v>9</v>
@@ -61132,7 +61135,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G2165" t="s">
-        <v>1270</v>
+        <v>1271</v>
       </c>
       <c r="H2165" t="s">
         <v>9</v>
@@ -61158,7 +61161,7 @@
         <v>3.47000002861023</v>
       </c>
       <c r="G2166" t="s">
-        <v>1268</v>
+        <v>1269</v>
       </c>
       <c r="H2166" t="s">
         <v>9</v>
@@ -61184,7 +61187,7 @@
         <v>3.38000011444092</v>
       </c>
       <c r="G2167" t="s">
-        <v>1273</v>
+        <v>1274</v>
       </c>
       <c r="H2167" t="s">
         <v>9</v>
@@ -61210,7 +61213,7 @@
         <v>3.33999991416931</v>
       </c>
       <c r="G2168" t="s">
-        <v>1274</v>
+        <v>1275</v>
       </c>
       <c r="H2168" t="s">
         <v>9</v>
@@ -61236,7 +61239,7 @@
         <v>3.44000005722046</v>
       </c>
       <c r="G2169" t="s">
-        <v>1275</v>
+        <v>1276</v>
       </c>
       <c r="H2169" t="s">
         <v>9</v>
@@ -61262,7 +61265,7 @@
         <v>3.32999992370605</v>
       </c>
       <c r="G2170" t="s">
-        <v>1276</v>
+        <v>1277</v>
       </c>
       <c r="H2170" t="s">
         <v>9</v>
@@ -61288,7 +61291,7 @@
         <v>3.33999991416931</v>
       </c>
       <c r="G2171" t="s">
-        <v>1274</v>
+        <v>1275</v>
       </c>
       <c r="H2171" t="s">
         <v>9</v>
@@ -61314,7 +61317,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G2172" t="s">
-        <v>1270</v>
+        <v>1271</v>
       </c>
       <c r="H2172" t="s">
         <v>9</v>
@@ -61340,7 +61343,7 @@
         <v>3.45000004768372</v>
       </c>
       <c r="G2173" t="s">
-        <v>1271</v>
+        <v>1272</v>
       </c>
       <c r="H2173" t="s">
         <v>9</v>
@@ -61366,7 +61369,7 @@
         <v>3.5699999332428</v>
       </c>
       <c r="G2174" t="s">
-        <v>1277</v>
+        <v>1278</v>
       </c>
       <c r="H2174" t="s">
         <v>9</v>
@@ -61392,7 +61395,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G2175" t="s">
-        <v>1278</v>
+        <v>1279</v>
       </c>
       <c r="H2175" t="s">
         <v>9</v>
@@ -61418,7 +61421,7 @@
         <v>3.53999996185303</v>
       </c>
       <c r="G2176" t="s">
-        <v>1279</v>
+        <v>1280</v>
       </c>
       <c r="H2176" t="s">
         <v>9</v>
@@ -61444,7 +61447,7 @@
         <v>3.49000000953674</v>
       </c>
       <c r="G2177" t="s">
-        <v>1280</v>
+        <v>1281</v>
       </c>
       <c r="H2177" t="s">
         <v>9</v>
@@ -61470,7 +61473,7 @@
         <v>3.49000000953674</v>
       </c>
       <c r="G2178" t="s">
-        <v>1280</v>
+        <v>1281</v>
       </c>
       <c r="H2178" t="s">
         <v>9</v>
@@ -61496,7 +61499,7 @@
         <v>3.4300000667572</v>
       </c>
       <c r="G2179" t="s">
-        <v>1269</v>
+        <v>1270</v>
       </c>
       <c r="H2179" t="s">
         <v>9</v>
@@ -61522,7 +61525,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G2180" t="s">
-        <v>1281</v>
+        <v>1282</v>
       </c>
       <c r="H2180" t="s">
         <v>9</v>
@@ -61548,7 +61551,7 @@
         <v>3.3199999332428</v>
       </c>
       <c r="G2181" t="s">
-        <v>1282</v>
+        <v>1283</v>
       </c>
       <c r="H2181" t="s">
         <v>9</v>
@@ -61574,7 +61577,7 @@
         <v>3.38000011444092</v>
       </c>
       <c r="G2182" t="s">
-        <v>1273</v>
+        <v>1274</v>
       </c>
       <c r="H2182" t="s">
         <v>9</v>
@@ -61600,7 +61603,7 @@
         <v>3.32999992370605</v>
       </c>
       <c r="G2183" t="s">
-        <v>1276</v>
+        <v>1277</v>
       </c>
       <c r="H2183" t="s">
         <v>9</v>
@@ -61626,7 +61629,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G2184" t="s">
-        <v>1283</v>
+        <v>1284</v>
       </c>
       <c r="H2184" t="s">
         <v>9</v>
@@ -61652,7 +61655,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G2185" t="s">
-        <v>1283</v>
+        <v>1284</v>
       </c>
       <c r="H2185" t="s">
         <v>9</v>
@@ -61678,7 +61681,7 @@
         <v>3.32999992370605</v>
       </c>
       <c r="G2186" t="s">
-        <v>1276</v>
+        <v>1277</v>
       </c>
       <c r="H2186" t="s">
         <v>9</v>
@@ -61704,7 +61707,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G2187" t="s">
-        <v>1283</v>
+        <v>1284</v>
       </c>
       <c r="H2187" t="s">
         <v>9</v>
@@ -61730,7 +61733,7 @@
         <v>3.04999995231628</v>
       </c>
       <c r="G2188" t="s">
-        <v>1284</v>
+        <v>1285</v>
       </c>
       <c r="H2188" t="s">
         <v>9</v>
@@ -61756,7 +61759,7 @@
         <v>3.32999992370605</v>
       </c>
       <c r="G2189" t="s">
-        <v>1276</v>
+        <v>1277</v>
       </c>
       <c r="H2189" t="s">
         <v>9</v>
@@ -61782,7 +61785,7 @@
         <v>3.17000007629395</v>
       </c>
       <c r="G2190" t="s">
-        <v>1285</v>
+        <v>1286</v>
       </c>
       <c r="H2190" t="s">
         <v>9</v>
@@ -61808,7 +61811,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G2191" t="s">
-        <v>1286</v>
+        <v>1287</v>
       </c>
       <c r="H2191" t="s">
         <v>9</v>
@@ -61834,7 +61837,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G2192" t="s">
-        <v>1286</v>
+        <v>1287</v>
       </c>
       <c r="H2192" t="s">
         <v>9</v>
@@ -61860,7 +61863,7 @@
         <v>3.14000010490417</v>
       </c>
       <c r="G2193" t="s">
-        <v>1287</v>
+        <v>1288</v>
       </c>
       <c r="H2193" t="s">
         <v>9</v>
@@ -61886,7 +61889,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G2194" t="s">
-        <v>1288</v>
+        <v>1289</v>
       </c>
       <c r="H2194" t="s">
         <v>9</v>
@@ -61912,7 +61915,7 @@
         <v>3.15000009536743</v>
       </c>
       <c r="G2195" t="s">
-        <v>1289</v>
+        <v>1290</v>
       </c>
       <c r="H2195" t="s">
         <v>9</v>
@@ -61938,7 +61941,7 @@
         <v>3.08999991416931</v>
       </c>
       <c r="G2196" t="s">
-        <v>1290</v>
+        <v>1291</v>
       </c>
       <c r="H2196" t="s">
         <v>9</v>
@@ -61964,7 +61967,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G2197" t="s">
-        <v>1291</v>
+        <v>1292</v>
       </c>
       <c r="H2197" t="s">
         <v>9</v>
@@ -61990,7 +61993,7 @@
         <v>3.07999992370605</v>
       </c>
       <c r="G2198" t="s">
-        <v>1292</v>
+        <v>1293</v>
       </c>
       <c r="H2198" t="s">
         <v>9</v>
@@ -62016,7 +62019,7 @@
         <v>3.14000010490417</v>
       </c>
       <c r="G2199" t="s">
-        <v>1287</v>
+        <v>1288</v>
       </c>
       <c r="H2199" t="s">
         <v>9</v>
@@ -62042,7 +62045,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G2200" t="s">
-        <v>1293</v>
+        <v>1294</v>
       </c>
       <c r="H2200" t="s">
         <v>9</v>
@@ -62068,7 +62071,7 @@
         <v>3.13000011444092</v>
       </c>
       <c r="G2201" t="s">
-        <v>1294</v>
+        <v>1295</v>
       </c>
       <c r="H2201" t="s">
         <v>9</v>
@@ -62094,7 +62097,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G2202" t="s">
-        <v>1293</v>
+        <v>1294</v>
       </c>
       <c r="H2202" t="s">
         <v>9</v>
@@ -62120,7 +62123,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G2203" t="s">
-        <v>1295</v>
+        <v>1296</v>
       </c>
       <c r="H2203" t="s">
         <v>9</v>
@@ -62146,7 +62149,7 @@
         <v>3.08999991416931</v>
       </c>
       <c r="G2204" t="s">
-        <v>1290</v>
+        <v>1291</v>
       </c>
       <c r="H2204" t="s">
         <v>9</v>
@@ -62172,7 +62175,7 @@
         <v>3.03999996185303</v>
       </c>
       <c r="G2205" t="s">
-        <v>1296</v>
+        <v>1297</v>
       </c>
       <c r="H2205" t="s">
         <v>9</v>
@@ -62198,7 +62201,7 @@
         <v>3.05999994277954</v>
       </c>
       <c r="G2206" t="s">
-        <v>1297</v>
+        <v>1298</v>
       </c>
       <c r="H2206" t="s">
         <v>9</v>
@@ -62224,7 +62227,7 @@
         <v>3.07999992370605</v>
       </c>
       <c r="G2207" t="s">
-        <v>1292</v>
+        <v>1293</v>
       </c>
       <c r="H2207" t="s">
         <v>9</v>
@@ -62250,7 +62253,7 @@
         <v>3.04999995231628</v>
       </c>
       <c r="G2208" t="s">
-        <v>1284</v>
+        <v>1285</v>
       </c>
       <c r="H2208" t="s">
         <v>9</v>
@@ -62276,7 +62279,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G2209" t="s">
-        <v>1291</v>
+        <v>1292</v>
       </c>
       <c r="H2209" t="s">
         <v>9</v>
@@ -62302,7 +62305,7 @@
         <v>3.08999991416931</v>
       </c>
       <c r="G2210" t="s">
-        <v>1290</v>
+        <v>1291</v>
       </c>
       <c r="H2210" t="s">
         <v>9</v>
@@ -62328,7 +62331,7 @@
         <v>3.08999991416931</v>
       </c>
       <c r="G2211" t="s">
-        <v>1290</v>
+        <v>1291</v>
       </c>
       <c r="H2211" t="s">
         <v>9</v>
@@ -62354,7 +62357,7 @@
         <v>3.08999991416931</v>
       </c>
       <c r="G2212" t="s">
-        <v>1290</v>
+        <v>1291</v>
       </c>
       <c r="H2212" t="s">
         <v>9</v>
@@ -62380,7 +62383,7 @@
         <v>3.08999991416931</v>
       </c>
       <c r="G2213" t="s">
-        <v>1290</v>
+        <v>1291</v>
       </c>
       <c r="H2213" t="s">
         <v>9</v>
@@ -62406,7 +62409,7 @@
         <v>3.05999994277954</v>
       </c>
       <c r="G2214" t="s">
-        <v>1297</v>
+        <v>1298</v>
       </c>
       <c r="H2214" t="s">
         <v>9</v>
@@ -62432,7 +62435,7 @@
         <v>2.9300000667572</v>
       </c>
       <c r="G2215" t="s">
-        <v>1298</v>
+        <v>1299</v>
       </c>
       <c r="H2215" t="s">
         <v>9</v>
@@ -62458,7 +62461,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G2216" t="s">
-        <v>1299</v>
+        <v>1300</v>
       </c>
       <c r="H2216" t="s">
         <v>9</v>
@@ -62484,7 +62487,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G2217" t="s">
-        <v>1300</v>
+        <v>1301</v>
       </c>
       <c r="H2217" t="s">
         <v>9</v>
@@ -62510,7 +62513,7 @@
         <v>2.96000003814697</v>
       </c>
       <c r="G2218" t="s">
-        <v>1301</v>
+        <v>1302</v>
       </c>
       <c r="H2218" t="s">
         <v>9</v>
@@ -62536,7 +62539,7 @@
         <v>2.97000002861023</v>
       </c>
       <c r="G2219" t="s">
-        <v>1302</v>
+        <v>1303</v>
       </c>
       <c r="H2219" t="s">
         <v>9</v>
@@ -62562,7 +62565,7 @@
         <v>3</v>
       </c>
       <c r="G2220" t="s">
-        <v>1303</v>
+        <v>1304</v>
       </c>
       <c r="H2220" t="s">
         <v>9</v>
@@ -62588,7 +62591,7 @@
         <v>3.02999997138977</v>
       </c>
       <c r="G2221" t="s">
-        <v>1304</v>
+        <v>1305</v>
       </c>
       <c r="H2221" t="s">
         <v>9</v>
@@ -62614,7 +62617,7 @@
         <v>3.04999995231628</v>
       </c>
       <c r="G2222" t="s">
-        <v>1284</v>
+        <v>1285</v>
       </c>
       <c r="H2222" t="s">
         <v>9</v>
@@ -62640,7 +62643,7 @@
         <v>3.07999992370605</v>
       </c>
       <c r="G2223" t="s">
-        <v>1292</v>
+        <v>1293</v>
       </c>
       <c r="H2223" t="s">
         <v>9</v>
@@ -62666,7 +62669,7 @@
         <v>3.13000011444092</v>
       </c>
       <c r="G2224" t="s">
-        <v>1294</v>
+        <v>1295</v>
       </c>
       <c r="H2224" t="s">
         <v>9</v>
@@ -62692,7 +62695,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G2225" t="s">
-        <v>1293</v>
+        <v>1294</v>
       </c>
       <c r="H2225" t="s">
         <v>9</v>
@@ -62718,7 +62721,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G2226" t="s">
-        <v>1305</v>
+        <v>1306</v>
       </c>
       <c r="H2226" t="s">
         <v>9</v>
@@ -62744,7 +62747,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G2227" t="s">
-        <v>1283</v>
+        <v>1284</v>
       </c>
       <c r="H2227" t="s">
         <v>9</v>
@@ -62770,7 +62773,7 @@
         <v>3.33999991416931</v>
       </c>
       <c r="G2228" t="s">
-        <v>1274</v>
+        <v>1275</v>
       </c>
       <c r="H2228" t="s">
         <v>9</v>
@@ -62796,7 +62799,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G2229" t="s">
-        <v>1306</v>
+        <v>1307</v>
       </c>
       <c r="H2229" t="s">
         <v>9</v>
@@ -62822,7 +62825,7 @@
         <v>3.3199999332428</v>
       </c>
       <c r="G2230" t="s">
-        <v>1282</v>
+        <v>1283</v>
       </c>
       <c r="H2230" t="s">
         <v>9</v>
@@ -62848,7 +62851,7 @@
         <v>3.34999990463257</v>
       </c>
       <c r="G2231" t="s">
-        <v>1307</v>
+        <v>1308</v>
       </c>
       <c r="H2231" t="s">
         <v>9</v>
@@ -62874,7 +62877,7 @@
         <v>3.44000005722046</v>
       </c>
       <c r="G2232" t="s">
-        <v>1275</v>
+        <v>1276</v>
       </c>
       <c r="H2232" t="s">
         <v>9</v>
@@ -62900,7 +62903,7 @@
         <v>3.38000011444092</v>
       </c>
       <c r="G2233" t="s">
-        <v>1273</v>
+        <v>1274</v>
       </c>
       <c r="H2233" t="s">
         <v>9</v>
@@ -62926,7 +62929,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G2234" t="s">
-        <v>1306</v>
+        <v>1307</v>
       </c>
       <c r="H2234" t="s">
         <v>9</v>
@@ -62952,7 +62955,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G2235" t="s">
-        <v>1281</v>
+        <v>1282</v>
       </c>
       <c r="H2235" t="s">
         <v>9</v>
@@ -62978,7 +62981,7 @@
         <v>3.41000008583069</v>
       </c>
       <c r="G2236" t="s">
-        <v>1308</v>
+        <v>1309</v>
       </c>
       <c r="H2236" t="s">
         <v>9</v>
@@ -63004,7 +63007,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G2237" t="s">
-        <v>1281</v>
+        <v>1282</v>
       </c>
       <c r="H2237" t="s">
         <v>9</v>
@@ -63030,7 +63033,7 @@
         <v>3.30999994277954</v>
       </c>
       <c r="G2238" t="s">
-        <v>1309</v>
+        <v>1310</v>
       </c>
       <c r="H2238" t="s">
         <v>9</v>
@@ -63056,7 +63059,7 @@
         <v>3.39000010490417</v>
       </c>
       <c r="G2239" t="s">
-        <v>1310</v>
+        <v>1311</v>
       </c>
       <c r="H2239" t="s">
         <v>9</v>
@@ -63082,7 +63085,7 @@
         <v>3.36999988555908</v>
       </c>
       <c r="G2240" t="s">
-        <v>1311</v>
+        <v>1312</v>
       </c>
       <c r="H2240" t="s">
         <v>9</v>
@@ -63108,7 +63111,7 @@
         <v>3.45000004768372</v>
       </c>
       <c r="G2241" t="s">
-        <v>1271</v>
+        <v>1272</v>
       </c>
       <c r="H2241" t="s">
         <v>9</v>
@@ -63134,7 +63137,7 @@
         <v>3.39000010490417</v>
       </c>
       <c r="G2242" t="s">
-        <v>1310</v>
+        <v>1311</v>
       </c>
       <c r="H2242" t="s">
         <v>9</v>
@@ -63160,7 +63163,7 @@
         <v>3.46000003814697</v>
       </c>
       <c r="G2243" t="s">
-        <v>1312</v>
+        <v>1313</v>
       </c>
       <c r="H2243" t="s">
         <v>9</v>
@@ -63186,7 +63189,7 @@
         <v>3.5699999332428</v>
       </c>
       <c r="G2244" t="s">
-        <v>1277</v>
+        <v>1278</v>
       </c>
       <c r="H2244" t="s">
         <v>9</v>
@@ -63212,7 +63215,7 @@
         <v>3.60999989509583</v>
       </c>
       <c r="G2245" t="s">
-        <v>1313</v>
+        <v>1314</v>
       </c>
       <c r="H2245" t="s">
         <v>9</v>
@@ -63238,7 +63241,7 @@
         <v>3.82999992370605</v>
       </c>
       <c r="G2246" t="s">
-        <v>1249</v>
+        <v>1250</v>
       </c>
       <c r="H2246" t="s">
         <v>9</v>
@@ -63264,7 +63267,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G2247" t="s">
-        <v>1314</v>
+        <v>1315</v>
       </c>
       <c r="H2247" t="s">
         <v>9</v>
@@ -63290,7 +63293,7 @@
         <v>5.28000020980835</v>
       </c>
       <c r="G2248" t="s">
-        <v>1315</v>
+        <v>1316</v>
       </c>
       <c r="H2248" t="s">
         <v>9</v>
@@ -63316,7 +63319,7 @@
         <v>5.32000017166138</v>
       </c>
       <c r="G2249" t="s">
-        <v>1316</v>
+        <v>1317</v>
       </c>
       <c r="H2249" t="s">
         <v>9</v>
@@ -63342,7 +63345,7 @@
         <v>5.26000022888184</v>
       </c>
       <c r="G2250" t="s">
-        <v>1317</v>
+        <v>1318</v>
       </c>
       <c r="H2250" t="s">
         <v>9</v>
@@ -63368,7 +63371,7 @@
         <v>5.34000015258789</v>
       </c>
       <c r="G2251" t="s">
-        <v>1318</v>
+        <v>1319</v>
       </c>
       <c r="H2251" t="s">
         <v>9</v>
@@ -63394,7 +63397,7 @@
         <v>5.6399998664856</v>
       </c>
       <c r="G2252" t="s">
-        <v>1319</v>
+        <v>1320</v>
       </c>
       <c r="H2252" t="s">
         <v>9</v>
@@ -63420,7 +63423,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G2253" t="s">
-        <v>1320</v>
+        <v>1321</v>
       </c>
       <c r="H2253" t="s">
         <v>9</v>
@@ -63446,7 +63449,7 @@
         <v>5.84000015258789</v>
       </c>
       <c r="G2254" t="s">
-        <v>1321</v>
+        <v>1322</v>
       </c>
       <c r="H2254" t="s">
         <v>9</v>
@@ -63472,7 +63475,7 @@
         <v>6.34000015258789</v>
       </c>
       <c r="G2255" t="s">
-        <v>1322</v>
+        <v>1323</v>
       </c>
       <c r="H2255" t="s">
         <v>9</v>
@@ -63498,7 +63501,7 @@
         <v>6.42000007629395</v>
       </c>
       <c r="G2256" t="s">
-        <v>1323</v>
+        <v>1324</v>
       </c>
       <c r="H2256" t="s">
         <v>9</v>
@@ -63524,7 +63527,7 @@
         <v>6.71999979019165</v>
       </c>
       <c r="G2257" t="s">
-        <v>1324</v>
+        <v>1325</v>
       </c>
       <c r="H2257" t="s">
         <v>9</v>
@@ -63550,7 +63553,7 @@
         <v>6.3600001335144</v>
       </c>
       <c r="G2258" t="s">
-        <v>1325</v>
+        <v>1326</v>
       </c>
       <c r="H2258" t="s">
         <v>9</v>
@@ -63576,7 +63579,7 @@
         <v>6.5</v>
       </c>
       <c r="G2259" t="s">
-        <v>1326</v>
+        <v>1327</v>
       </c>
       <c r="H2259" t="s">
         <v>9</v>
@@ -63602,7 +63605,7 @@
         <v>6.59999990463257</v>
       </c>
       <c r="G2260" t="s">
-        <v>1327</v>
+        <v>1328</v>
       </c>
       <c r="H2260" t="s">
         <v>9</v>
@@ -63628,7 +63631,7 @@
         <v>6.84000015258789</v>
       </c>
       <c r="G2261" t="s">
-        <v>1328</v>
+        <v>1329</v>
       </c>
       <c r="H2261" t="s">
         <v>9</v>
@@ -63654,7 +63657,7 @@
         <v>6.84000015258789</v>
       </c>
       <c r="G2262" t="s">
-        <v>1328</v>
+        <v>1329</v>
       </c>
       <c r="H2262" t="s">
         <v>9</v>
@@ -63680,7 +63683,7 @@
         <v>6.98000001907349</v>
       </c>
       <c r="G2263" t="s">
-        <v>1329</v>
+        <v>1330</v>
       </c>
       <c r="H2263" t="s">
         <v>9</v>
@@ -63706,7 +63709,7 @@
         <v>6.82000017166138</v>
       </c>
       <c r="G2264" t="s">
-        <v>1330</v>
+        <v>1331</v>
       </c>
       <c r="H2264" t="s">
         <v>9</v>
@@ -63732,7 +63735,7 @@
         <v>6.90000009536743</v>
       </c>
       <c r="G2265" t="s">
-        <v>1331</v>
+        <v>1332</v>
       </c>
       <c r="H2265" t="s">
         <v>9</v>
@@ -63758,7 +63761,7 @@
         <v>6.98000001907349</v>
       </c>
       <c r="G2266" t="s">
-        <v>1329</v>
+        <v>1330</v>
       </c>
       <c r="H2266" t="s">
         <v>9</v>
@@ -63784,7 +63787,7 @@
         <v>6.92000007629395</v>
       </c>
       <c r="G2267" t="s">
-        <v>1332</v>
+        <v>1333</v>
       </c>
       <c r="H2267" t="s">
         <v>9</v>
@@ -63810,7 +63813,7 @@
         <v>6.84000015258789</v>
       </c>
       <c r="G2268" t="s">
-        <v>1328</v>
+        <v>1329</v>
       </c>
       <c r="H2268" t="s">
         <v>9</v>
@@ -63836,7 +63839,7 @@
         <v>7.07999992370605</v>
       </c>
       <c r="G2269" t="s">
-        <v>1333</v>
+        <v>1334</v>
       </c>
       <c r="H2269" t="s">
         <v>9</v>
@@ -63862,7 +63865,7 @@
         <v>7.19999980926514</v>
       </c>
       <c r="G2270" t="s">
-        <v>1334</v>
+        <v>1335</v>
       </c>
       <c r="H2270" t="s">
         <v>9</v>
@@ -63888,7 +63891,7 @@
         <v>7.09999990463257</v>
       </c>
       <c r="G2271" t="s">
-        <v>1335</v>
+        <v>1336</v>
       </c>
       <c r="H2271" t="s">
         <v>9</v>
@@ -63914,7 +63917,7 @@
         <v>7.26000022888184</v>
       </c>
       <c r="G2272" t="s">
-        <v>1336</v>
+        <v>1337</v>
       </c>
       <c r="H2272" t="s">
         <v>9</v>
@@ -63940,7 +63943,7 @@
         <v>7.40000009536743</v>
       </c>
       <c r="G2273" t="s">
-        <v>1337</v>
+        <v>1338</v>
       </c>
       <c r="H2273" t="s">
         <v>9</v>
@@ -63966,7 +63969,7 @@
         <v>7.51999998092651</v>
       </c>
       <c r="G2274" t="s">
-        <v>1338</v>
+        <v>1339</v>
       </c>
       <c r="H2274" t="s">
         <v>9</v>
@@ -63992,7 +63995,7 @@
         <v>7.40000009536743</v>
       </c>
       <c r="G2275" t="s">
-        <v>1337</v>
+        <v>1338</v>
       </c>
       <c r="H2275" t="s">
         <v>9</v>
@@ -64018,7 +64021,7 @@
         <v>7.46000003814697</v>
       </c>
       <c r="G2276" t="s">
-        <v>1339</v>
+        <v>1340</v>
       </c>
       <c r="H2276" t="s">
         <v>9</v>
@@ -64044,7 +64047,7 @@
         <v>7.48000001907349</v>
       </c>
       <c r="G2277" t="s">
-        <v>1340</v>
+        <v>1341</v>
       </c>
       <c r="H2277" t="s">
         <v>9</v>
@@ -64070,7 +64073,7 @@
         <v>7.67999982833862</v>
       </c>
       <c r="G2278" t="s">
-        <v>1341</v>
+        <v>1342</v>
       </c>
       <c r="H2278" t="s">
         <v>9</v>
@@ -64096,7 +64099,7 @@
         <v>8.10000038146973</v>
       </c>
       <c r="G2279" t="s">
-        <v>1342</v>
+        <v>1343</v>
       </c>
       <c r="H2279" t="s">
         <v>9</v>
@@ -64122,7 +64125,7 @@
         <v>7.59999990463257</v>
       </c>
       <c r="G2280" t="s">
-        <v>1343</v>
+        <v>1344</v>
       </c>
       <c r="H2280" t="s">
         <v>9</v>
@@ -64148,7 +64151,7 @@
         <v>7.6399998664856</v>
       </c>
       <c r="G2281" t="s">
-        <v>1344</v>
+        <v>1345</v>
       </c>
       <c r="H2281" t="s">
         <v>9</v>
@@ -64174,7 +64177,7 @@
         <v>7.71999979019165</v>
       </c>
       <c r="G2282" t="s">
-        <v>1345</v>
+        <v>1346</v>
       </c>
       <c r="H2282" t="s">
         <v>9</v>
@@ -64200,7 +64203,7 @@
         <v>7.59999990463257</v>
       </c>
       <c r="G2283" t="s">
-        <v>1343</v>
+        <v>1344</v>
       </c>
       <c r="H2283" t="s">
         <v>9</v>
@@ -64226,7 +64229,7 @@
         <v>7.48000001907349</v>
       </c>
       <c r="G2284" t="s">
-        <v>1340</v>
+        <v>1341</v>
       </c>
       <c r="H2284" t="s">
         <v>9</v>
@@ -64252,7 +64255,7 @@
         <v>7.46000003814697</v>
       </c>
       <c r="G2285" t="s">
-        <v>1339</v>
+        <v>1340</v>
       </c>
       <c r="H2285" t="s">
         <v>9</v>
@@ -64278,7 +64281,7 @@
         <v>7.90000009536743</v>
       </c>
       <c r="G2286" t="s">
-        <v>1346</v>
+        <v>1347</v>
       </c>
       <c r="H2286" t="s">
         <v>9</v>
@@ -64304,7 +64307,7 @@
         <v>7.6399998664856</v>
       </c>
       <c r="G2287" t="s">
-        <v>1344</v>
+        <v>1345</v>
       </c>
       <c r="H2287" t="s">
         <v>9</v>
@@ -64330,7 +64333,7 @@
         <v>7.8600001335144</v>
       </c>
       <c r="G2288" t="s">
-        <v>1347</v>
+        <v>1348</v>
       </c>
       <c r="H2288" t="s">
         <v>9</v>
@@ -64356,7 +64359,7 @@
         <v>7.8600001335144</v>
       </c>
       <c r="G2289" t="s">
-        <v>1347</v>
+        <v>1348</v>
       </c>
       <c r="H2289" t="s">
         <v>9</v>
@@ -64382,7 +64385,7 @@
         <v>7.73999977111816</v>
       </c>
       <c r="G2290" t="s">
-        <v>1348</v>
+        <v>1349</v>
       </c>
       <c r="H2290" t="s">
         <v>9</v>
@@ -64408,7 +64411,7 @@
         <v>7.69999980926514</v>
       </c>
       <c r="G2291" t="s">
-        <v>1349</v>
+        <v>1350</v>
       </c>
       <c r="H2291" t="s">
         <v>9</v>
@@ -64434,7 +64437,7 @@
         <v>7.90000009536743</v>
       </c>
       <c r="G2292" t="s">
-        <v>1346</v>
+        <v>1347</v>
       </c>
       <c r="H2292" t="s">
         <v>9</v>
@@ -64460,7 +64463,7 @@
         <v>7.5</v>
       </c>
       <c r="G2293" t="s">
-        <v>1350</v>
+        <v>1351</v>
       </c>
       <c r="H2293" t="s">
         <v>9</v>
@@ -64486,7 +64489,7 @@
         <v>7.38000011444092</v>
       </c>
       <c r="G2294" t="s">
-        <v>1351</v>
+        <v>1352</v>
       </c>
       <c r="H2294" t="s">
         <v>9</v>
@@ -64512,7 +64515,7 @@
         <v>7.61999988555908</v>
       </c>
       <c r="G2295" t="s">
-        <v>1352</v>
+        <v>1353</v>
       </c>
       <c r="H2295" t="s">
         <v>9</v>
@@ -64538,7 +64541,7 @@
         <v>7.71999979019165</v>
       </c>
       <c r="G2296" t="s">
-        <v>1345</v>
+        <v>1346</v>
       </c>
       <c r="H2296" t="s">
         <v>9</v>
@@ -64564,7 +64567,7 @@
         <v>7.55999994277954</v>
       </c>
       <c r="G2297" t="s">
-        <v>1353</v>
+        <v>1354</v>
       </c>
       <c r="H2297" t="s">
         <v>9</v>
@@ -64590,7 +64593,7 @@
         <v>7.46000003814697</v>
       </c>
       <c r="G2298" t="s">
-        <v>1339</v>
+        <v>1340</v>
       </c>
       <c r="H2298" t="s">
         <v>9</v>
@@ -64616,7 +64619,7 @@
         <v>7.59999990463257</v>
       </c>
       <c r="G2299" t="s">
-        <v>1343</v>
+        <v>1344</v>
       </c>
       <c r="H2299" t="s">
         <v>9</v>
@@ -64642,7 +64645,7 @@
         <v>7.48000001907349</v>
       </c>
       <c r="G2300" t="s">
-        <v>1340</v>
+        <v>1341</v>
       </c>
       <c r="H2300" t="s">
         <v>9</v>
@@ -64668,7 +64671,7 @@
         <v>7.42000007629395</v>
       </c>
       <c r="G2301" t="s">
-        <v>1354</v>
+        <v>1355</v>
       </c>
       <c r="H2301" t="s">
         <v>9</v>
@@ -64694,7 +64697,7 @@
         <v>7.3600001335144</v>
       </c>
       <c r="G2302" t="s">
-        <v>1355</v>
+        <v>1356</v>
       </c>
       <c r="H2302" t="s">
         <v>9</v>
@@ -64720,7 +64723,7 @@
         <v>7.34000015258789</v>
       </c>
       <c r="G2303" t="s">
-        <v>1356</v>
+        <v>1357</v>
       </c>
       <c r="H2303" t="s">
         <v>9</v>
@@ -64746,7 +64749,7 @@
         <v>7.42000007629395</v>
       </c>
       <c r="G2304" t="s">
-        <v>1354</v>
+        <v>1355</v>
       </c>
       <c r="H2304" t="s">
         <v>9</v>
@@ -64772,7 +64775,7 @@
         <v>7.21999979019165</v>
       </c>
       <c r="G2305" t="s">
-        <v>1357</v>
+        <v>1358</v>
       </c>
       <c r="H2305" t="s">
         <v>9</v>
@@ -64798,7 +64801,7 @@
         <v>7.34000015258789</v>
       </c>
       <c r="G2306" t="s">
-        <v>1356</v>
+        <v>1357</v>
       </c>
       <c r="H2306" t="s">
         <v>9</v>
@@ -64824,7 +64827,7 @@
         <v>7.21999979019165</v>
       </c>
       <c r="G2307" t="s">
-        <v>1357</v>
+        <v>1358</v>
       </c>
       <c r="H2307" t="s">
         <v>9</v>
@@ -64850,7 +64853,7 @@
         <v>7.6399998664856</v>
       </c>
       <c r="G2308" t="s">
-        <v>1344</v>
+        <v>1345</v>
       </c>
       <c r="H2308" t="s">
         <v>9</v>
@@ -64876,7 +64879,7 @@
         <v>7.76000022888184</v>
       </c>
       <c r="G2309" t="s">
-        <v>1358</v>
+        <v>1359</v>
       </c>
       <c r="H2309" t="s">
         <v>9</v>
@@ -64902,7 +64905,7 @@
         <v>7.6399998664856</v>
       </c>
       <c r="G2310" t="s">
-        <v>1344</v>
+        <v>1345</v>
       </c>
       <c r="H2310" t="s">
         <v>9</v>
@@ -64928,7 +64931,7 @@
         <v>7.73999977111816</v>
       </c>
       <c r="G2311" t="s">
-        <v>1348</v>
+        <v>1349</v>
       </c>
       <c r="H2311" t="s">
         <v>9</v>
@@ -64954,7 +64957,7 @@
         <v>7.71999979019165</v>
       </c>
       <c r="G2312" t="s">
-        <v>1345</v>
+        <v>1346</v>
       </c>
       <c r="H2312" t="s">
         <v>9</v>
@@ -64980,7 +64983,7 @@
         <v>7.6399998664856</v>
       </c>
       <c r="G2313" t="s">
-        <v>1344</v>
+        <v>1345</v>
       </c>
       <c r="H2313" t="s">
         <v>9</v>
@@ -65006,7 +65009,7 @@
         <v>7.59999990463257</v>
       </c>
       <c r="G2314" t="s">
-        <v>1343</v>
+        <v>1344</v>
       </c>
       <c r="H2314" t="s">
         <v>9</v>
@@ -65032,7 +65035,7 @@
         <v>7.84000015258789</v>
       </c>
       <c r="G2315" t="s">
-        <v>1359</v>
+        <v>1360</v>
       </c>
       <c r="H2315" t="s">
         <v>9</v>
@@ -65058,7 +65061,7 @@
         <v>7.69999980926514</v>
       </c>
       <c r="G2316" t="s">
-        <v>1349</v>
+        <v>1350</v>
       </c>
       <c r="H2316" t="s">
         <v>9</v>
@@ -65084,7 +65087,7 @@
         <v>7.40000009536743</v>
       </c>
       <c r="G2317" t="s">
-        <v>1337</v>
+        <v>1338</v>
       </c>
       <c r="H2317" t="s">
         <v>9</v>
@@ -65110,7 +65113,7 @@
         <v>7.90000009536743</v>
       </c>
       <c r="G2318" t="s">
-        <v>1346</v>
+        <v>1347</v>
       </c>
       <c r="H2318" t="s">
         <v>9</v>
@@ -65136,7 +65139,7 @@
         <v>7.90000009536743</v>
       </c>
       <c r="G2319" t="s">
-        <v>1346</v>
+        <v>1347</v>
       </c>
       <c r="H2319" t="s">
         <v>9</v>
@@ -65162,7 +65165,7 @@
         <v>8.60000038146973</v>
       </c>
       <c r="G2320" t="s">
-        <v>1360</v>
+        <v>1361</v>
       </c>
       <c r="H2320" t="s">
         <v>9</v>
@@ -65188,7 +65191,7 @@
         <v>8.77999973297119</v>
       </c>
       <c r="G2321" t="s">
-        <v>1361</v>
+        <v>1362</v>
       </c>
       <c r="H2321" t="s">
         <v>9</v>
@@ -65214,7 +65217,7 @@
         <v>8.60000038146973</v>
       </c>
       <c r="G2322" t="s">
-        <v>1360</v>
+        <v>1361</v>
       </c>
       <c r="H2322" t="s">
         <v>9</v>
@@ -65240,7 +65243,7 @@
         <v>8.72000026702881</v>
       </c>
       <c r="G2323" t="s">
-        <v>1362</v>
+        <v>1363</v>
       </c>
       <c r="H2323" t="s">
         <v>9</v>
@@ -65266,7 +65269,7 @@
         <v>8.61999988555908</v>
       </c>
       <c r="G2324" t="s">
-        <v>1363</v>
+        <v>1364</v>
       </c>
       <c r="H2324" t="s">
         <v>9</v>
@@ -65292,7 +65295,7 @@
         <v>8.5</v>
       </c>
       <c r="G2325" t="s">
-        <v>1364</v>
+        <v>1365</v>
       </c>
       <c r="H2325" t="s">
         <v>9</v>
@@ -65318,7 +65321,7 @@
         <v>8.46000003814697</v>
       </c>
       <c r="G2326" t="s">
-        <v>1365</v>
+        <v>1366</v>
       </c>
       <c r="H2326" t="s">
         <v>9</v>
@@ -65344,7 +65347,7 @@
         <v>8.31999969482422</v>
       </c>
       <c r="G2327" t="s">
-        <v>1366</v>
+        <v>1367</v>
       </c>
       <c r="H2327" t="s">
         <v>9</v>
@@ -65370,7 +65373,7 @@
         <v>8.22000026702881</v>
       </c>
       <c r="G2328" t="s">
-        <v>1367</v>
+        <v>1368</v>
       </c>
       <c r="H2328" t="s">
         <v>9</v>
@@ -65396,7 +65399,7 @@
         <v>8.02000045776367</v>
       </c>
       <c r="G2329" t="s">
-        <v>1368</v>
+        <v>1369</v>
       </c>
       <c r="H2329" t="s">
         <v>9</v>
@@ -65422,7 +65425,7 @@
         <v>7.8600001335144</v>
       </c>
       <c r="G2330" t="s">
-        <v>1347</v>
+        <v>1348</v>
       </c>
       <c r="H2330" t="s">
         <v>9</v>
@@ -65448,7 +65451,7 @@
         <v>7.92000007629395</v>
       </c>
       <c r="G2331" t="s">
-        <v>1369</v>
+        <v>1370</v>
       </c>
       <c r="H2331" t="s">
         <v>9</v>
@@ -65474,7 +65477,7 @@
         <v>8.10000038146973</v>
       </c>
       <c r="G2332" t="s">
-        <v>1342</v>
+        <v>1343</v>
       </c>
       <c r="H2332" t="s">
         <v>9</v>
@@ -65500,7 +65503,7 @@
         <v>7.6399998664856</v>
       </c>
       <c r="G2333" t="s">
-        <v>1344</v>
+        <v>1345</v>
       </c>
       <c r="H2333" t="s">
         <v>9</v>
@@ -65526,7 +65529,7 @@
         <v>7.61999988555908</v>
       </c>
       <c r="G2334" t="s">
-        <v>1352</v>
+        <v>1353</v>
       </c>
       <c r="H2334" t="s">
         <v>9</v>
@@ -65552,7 +65555,7 @@
         <v>7.48000001907349</v>
       </c>
       <c r="G2335" t="s">
-        <v>1340</v>
+        <v>1341</v>
       </c>
       <c r="H2335" t="s">
         <v>9</v>
@@ -65578,7 +65581,7 @@
         <v>7.32000017166138</v>
       </c>
       <c r="G2336" t="s">
-        <v>1370</v>
+        <v>1371</v>
       </c>
       <c r="H2336" t="s">
         <v>9</v>
@@ -65604,7 +65607,7 @@
         <v>7.05999994277954</v>
       </c>
       <c r="G2337" t="s">
-        <v>1371</v>
+        <v>1372</v>
       </c>
       <c r="H2337" t="s">
         <v>9</v>
@@ -65630,7 +65633,7 @@
         <v>6.88000011444092</v>
       </c>
       <c r="G2338" t="s">
-        <v>1372</v>
+        <v>1373</v>
       </c>
       <c r="H2338" t="s">
         <v>9</v>
@@ -65656,7 +65659,7 @@
         <v>7</v>
       </c>
       <c r="G2339" t="s">
-        <v>1373</v>
+        <v>1374</v>
       </c>
       <c r="H2339" t="s">
         <v>9</v>
@@ -65682,7 +65685,7 @@
         <v>7.09999990463257</v>
       </c>
       <c r="G2340" t="s">
-        <v>1335</v>
+        <v>1336</v>
       </c>
       <c r="H2340" t="s">
         <v>9</v>
@@ -65708,7 +65711,7 @@
         <v>7.5</v>
       </c>
       <c r="G2341" t="s">
-        <v>1350</v>
+        <v>1351</v>
       </c>
       <c r="H2341" t="s">
         <v>9</v>
@@ -65734,7 +65737,7 @@
         <v>7.57999992370605</v>
       </c>
       <c r="G2342" t="s">
-        <v>1374</v>
+        <v>1375</v>
       </c>
       <c r="H2342" t="s">
         <v>9</v>
@@ -65760,7 +65763,7 @@
         <v>7.59999990463257</v>
       </c>
       <c r="G2343" t="s">
-        <v>1343</v>
+        <v>1344</v>
       </c>
       <c r="H2343" t="s">
         <v>9</v>
@@ -65786,7 +65789,7 @@
         <v>7.59999990463257</v>
       </c>
       <c r="G2344" t="s">
-        <v>1343</v>
+        <v>1344</v>
       </c>
       <c r="H2344" t="s">
         <v>9</v>
@@ -65812,7 +65815,7 @@
         <v>7.55999994277954</v>
       </c>
       <c r="G2345" t="s">
-        <v>1353</v>
+        <v>1354</v>
       </c>
       <c r="H2345" t="s">
         <v>9</v>
@@ -65838,7 +65841,7 @@
         <v>7.57999992370605</v>
       </c>
       <c r="G2346" t="s">
-        <v>1374</v>
+        <v>1375</v>
       </c>
       <c r="H2346" t="s">
         <v>9</v>
@@ -65864,7 +65867,7 @@
         <v>7.5</v>
       </c>
       <c r="G2347" t="s">
-        <v>1350</v>
+        <v>1351</v>
       </c>
       <c r="H2347" t="s">
         <v>9</v>
@@ -65890,7 +65893,7 @@
         <v>7.69999980926514</v>
       </c>
       <c r="G2348" t="s">
-        <v>1349</v>
+        <v>1350</v>
       </c>
       <c r="H2348" t="s">
         <v>9</v>
@@ -65916,7 +65919,7 @@
         <v>7.59999990463257</v>
       </c>
       <c r="G2349" t="s">
-        <v>1343</v>
+        <v>1344</v>
       </c>
       <c r="H2349" t="s">
         <v>9</v>
@@ -65942,7 +65945,7 @@
         <v>7.67999982833862</v>
       </c>
       <c r="G2350" t="s">
-        <v>1341</v>
+        <v>1342</v>
       </c>
       <c r="H2350" t="s">
         <v>9</v>
@@ -65968,7 +65971,7 @@
         <v>7.80000019073486</v>
       </c>
       <c r="G2351" t="s">
-        <v>1375</v>
+        <v>1376</v>
       </c>
       <c r="H2351" t="s">
         <v>9</v>
@@ -65994,7 +65997,7 @@
         <v>7.73999977111816</v>
       </c>
       <c r="G2352" t="s">
-        <v>1348</v>
+        <v>1349</v>
       </c>
       <c r="H2352" t="s">
         <v>9</v>
@@ -66020,7 +66023,7 @@
         <v>8.14000034332275</v>
       </c>
       <c r="G2353" t="s">
-        <v>1376</v>
+        <v>1377</v>
       </c>
       <c r="H2353" t="s">
         <v>9</v>
@@ -66046,7 +66049,7 @@
         <v>8.11999988555908</v>
       </c>
       <c r="G2354" t="s">
-        <v>1377</v>
+        <v>1378</v>
       </c>
       <c r="H2354" t="s">
         <v>9</v>
@@ -66072,7 +66075,7 @@
         <v>7.80000019073486</v>
       </c>
       <c r="G2355" t="s">
-        <v>1375</v>
+        <v>1376</v>
       </c>
       <c r="H2355" t="s">
         <v>9</v>
@@ -66098,7 +66101,7 @@
         <v>7.57999992370605</v>
       </c>
       <c r="G2356" t="s">
-        <v>1374</v>
+        <v>1375</v>
       </c>
       <c r="H2356" t="s">
         <v>9</v>
@@ -66124,7 +66127,7 @@
         <v>7.34000015258789</v>
       </c>
       <c r="G2357" t="s">
-        <v>1356</v>
+        <v>1357</v>
       </c>
       <c r="H2357" t="s">
         <v>9</v>
@@ -66150,7 +66153,7 @@
         <v>7.55999994277954</v>
       </c>
       <c r="G2358" t="s">
-        <v>1353</v>
+        <v>1354</v>
       </c>
       <c r="H2358" t="s">
         <v>9</v>
@@ -66176,7 +66179,7 @@
         <v>7.44999980926514</v>
       </c>
       <c r="G2359" t="s">
-        <v>1378</v>
+        <v>1379</v>
       </c>
       <c r="H2359" t="s">
         <v>9</v>
@@ -66202,7 +66205,7 @@
         <v>7.78999996185303</v>
       </c>
       <c r="G2360" t="s">
-        <v>1379</v>
+        <v>1380</v>
       </c>
       <c r="H2360" t="s">
         <v>9</v>
@@ -66228,7 +66231,7 @@
         <v>7.65000009536743</v>
       </c>
       <c r="G2361" t="s">
-        <v>1380</v>
+        <v>1381</v>
       </c>
       <c r="H2361" t="s">
         <v>9</v>
@@ -66254,7 +66257,7 @@
         <v>7.90000009536743</v>
       </c>
       <c r="G2362" t="s">
-        <v>1346</v>
+        <v>1347</v>
       </c>
       <c r="H2362" t="s">
         <v>9</v>
@@ -66280,7 +66283,7 @@
         <v>8</v>
       </c>
       <c r="G2363" t="s">
-        <v>1381</v>
+        <v>1382</v>
       </c>
       <c r="H2363" t="s">
         <v>9</v>
@@ -66306,7 +66309,7 @@
         <v>8.03999996185303</v>
       </c>
       <c r="G2364" t="s">
-        <v>1382</v>
+        <v>1383</v>
       </c>
       <c r="H2364" t="s">
         <v>9</v>
@@ -66332,7 +66335,7 @@
         <v>7.82000017166138</v>
       </c>
       <c r="G2365" t="s">
-        <v>1383</v>
+        <v>1384</v>
       </c>
       <c r="H2365" t="s">
         <v>9</v>
@@ -66358,7 +66361,7 @@
         <v>8.03999996185303</v>
       </c>
       <c r="G2366" t="s">
-        <v>1382</v>
+        <v>1383</v>
       </c>
       <c r="H2366" t="s">
         <v>9</v>
@@ -66384,7 +66387,7 @@
         <v>8.05000019073486</v>
       </c>
       <c r="G2367" t="s">
-        <v>1384</v>
+        <v>1385</v>
       </c>
       <c r="H2367" t="s">
         <v>9</v>
@@ -66410,7 +66413,7 @@
         <v>8.05000019073486</v>
       </c>
       <c r="G2368" t="s">
-        <v>1384</v>
+        <v>1385</v>
       </c>
       <c r="H2368" t="s">
         <v>9</v>
@@ -66436,7 +66439,7 @@
         <v>8.13000011444092</v>
       </c>
       <c r="G2369" t="s">
-        <v>1385</v>
+        <v>1386</v>
       </c>
       <c r="H2369" t="s">
         <v>9</v>
@@ -66462,7 +66465,7 @@
         <v>8.0600004196167</v>
       </c>
       <c r="G2370" t="s">
-        <v>1386</v>
+        <v>1387</v>
       </c>
       <c r="H2370" t="s">
         <v>9</v>
@@ -66488,7 +66491,7 @@
         <v>7.86999988555908</v>
       </c>
       <c r="G2371" t="s">
-        <v>1387</v>
+        <v>1388</v>
       </c>
       <c r="H2371" t="s">
         <v>9</v>
@@ -66514,7 +66517,7 @@
         <v>7.40000009536743</v>
       </c>
       <c r="G2372" t="s">
-        <v>1388</v>
+        <v>1389</v>
       </c>
       <c r="H2372" t="s">
         <v>9</v>
@@ -66540,7 +66543,7 @@
         <v>7.53999996185303</v>
       </c>
       <c r="G2373" t="s">
-        <v>1389</v>
+        <v>1390</v>
       </c>
       <c r="H2373" t="s">
         <v>9</v>
@@ -66566,7 +66569,7 @@
         <v>7.59000015258789</v>
       </c>
       <c r="G2374" t="s">
-        <v>1390</v>
+        <v>1391</v>
       </c>
       <c r="H2374" t="s">
         <v>9</v>
@@ -66592,7 +66595,7 @@
         <v>7.6399998664856</v>
       </c>
       <c r="G2375" t="s">
-        <v>1391</v>
+        <v>1392</v>
       </c>
       <c r="H2375" t="s">
         <v>9</v>
@@ -66618,7 +66621,7 @@
         <v>7.63000011444092</v>
       </c>
       <c r="G2376" t="s">
-        <v>1392</v>
+        <v>1393</v>
       </c>
       <c r="H2376" t="s">
         <v>9</v>
@@ -66644,7 +66647,7 @@
         <v>7.90999984741211</v>
       </c>
       <c r="G2377" t="s">
-        <v>1393</v>
+        <v>1394</v>
       </c>
       <c r="H2377" t="s">
         <v>9</v>
@@ -66670,7 +66673,7 @@
         <v>7.96000003814697</v>
       </c>
       <c r="G2378" t="s">
-        <v>1394</v>
+        <v>1395</v>
       </c>
       <c r="H2378" t="s">
         <v>9</v>
@@ -66696,7 +66699,7 @@
         <v>7.98999977111816</v>
       </c>
       <c r="G2379" t="s">
-        <v>1395</v>
+        <v>1396</v>
       </c>
       <c r="H2379" t="s">
         <v>9</v>
@@ -66722,7 +66725,7 @@
         <v>8.35999965667725</v>
       </c>
       <c r="G2380" t="s">
-        <v>1396</v>
+        <v>1397</v>
       </c>
       <c r="H2380" t="s">
         <v>9</v>
@@ -66748,7 +66751,7 @@
         <v>8.53999996185303</v>
       </c>
       <c r="G2381" t="s">
-        <v>1397</v>
+        <v>1398</v>
       </c>
       <c r="H2381" t="s">
         <v>9</v>
@@ -66774,7 +66777,7 @@
         <v>8.47000026702881</v>
       </c>
       <c r="G2382" t="s">
-        <v>1398</v>
+        <v>1399</v>
       </c>
       <c r="H2382" t="s">
         <v>9</v>
@@ -66800,7 +66803,7 @@
         <v>8.52000045776367</v>
       </c>
       <c r="G2383" t="s">
-        <v>1399</v>
+        <v>1400</v>
       </c>
       <c r="H2383" t="s">
         <v>9</v>
@@ -66826,7 +66829,7 @@
         <v>8.36999988555908</v>
       </c>
       <c r="G2384" t="s">
-        <v>1400</v>
+        <v>1401</v>
       </c>
       <c r="H2384" t="s">
         <v>9</v>
@@ -66852,7 +66855,7 @@
         <v>8.67000007629395</v>
       </c>
       <c r="G2385" t="s">
-        <v>1401</v>
+        <v>1402</v>
       </c>
       <c r="H2385" t="s">
         <v>9</v>
@@ -66878,7 +66881,7 @@
         <v>8.59000015258789</v>
       </c>
       <c r="G2386" t="s">
-        <v>1402</v>
+        <v>1403</v>
       </c>
       <c r="H2386" t="s">
         <v>9</v>
@@ -66904,7 +66907,7 @@
         <v>8.52999973297119</v>
       </c>
       <c r="G2387" t="s">
-        <v>1403</v>
+        <v>1404</v>
       </c>
       <c r="H2387" t="s">
         <v>9</v>
@@ -66930,7 +66933,7 @@
         <v>8.65999984741211</v>
       </c>
       <c r="G2388" t="s">
-        <v>1404</v>
+        <v>1405</v>
       </c>
       <c r="H2388" t="s">
         <v>9</v>
@@ -66956,7 +66959,7 @@
         <v>8.64999961853027</v>
       </c>
       <c r="G2389" t="s">
-        <v>1405</v>
+        <v>1406</v>
       </c>
       <c r="H2389" t="s">
         <v>9</v>
@@ -66982,7 +66985,7 @@
         <v>8.82999992370605</v>
       </c>
       <c r="G2390" t="s">
-        <v>1406</v>
+        <v>1407</v>
       </c>
       <c r="H2390" t="s">
         <v>9</v>
@@ -67008,7 +67011,7 @@
         <v>8.8100004196167</v>
       </c>
       <c r="G2391" t="s">
-        <v>1407</v>
+        <v>1408</v>
       </c>
       <c r="H2391" t="s">
         <v>9</v>
@@ -67034,7 +67037,7 @@
         <v>8.55000019073486</v>
       </c>
       <c r="G2392" t="s">
-        <v>1408</v>
+        <v>1409</v>
       </c>
       <c r="H2392" t="s">
         <v>9</v>
@@ -67060,7 +67063,7 @@
         <v>8.52000045776367</v>
       </c>
       <c r="G2393" t="s">
-        <v>1399</v>
+        <v>1400</v>
       </c>
       <c r="H2393" t="s">
         <v>9</v>
@@ -67086,7 +67089,7 @@
         <v>8.52000045776367</v>
       </c>
       <c r="G2394" t="s">
-        <v>1399</v>
+        <v>1400</v>
       </c>
       <c r="H2394" t="s">
         <v>9</v>
@@ -67112,7 +67115,7 @@
         <v>8.42000007629395</v>
       </c>
       <c r="G2395" t="s">
-        <v>1409</v>
+        <v>1410</v>
       </c>
       <c r="H2395" t="s">
         <v>9</v>
@@ -67138,7 +67141,7 @@
         <v>8.63000011444092</v>
       </c>
       <c r="G2396" t="s">
-        <v>1410</v>
+        <v>1411</v>
       </c>
       <c r="H2396" t="s">
         <v>9</v>
@@ -67164,7 +67167,7 @@
         <v>8.57999992370605</v>
       </c>
       <c r="G2397" t="s">
-        <v>1411</v>
+        <v>1412</v>
       </c>
       <c r="H2397" t="s">
         <v>9</v>
@@ -67190,7 +67193,7 @@
         <v>8.55000019073486</v>
       </c>
       <c r="G2398" t="s">
-        <v>1408</v>
+        <v>1409</v>
       </c>
       <c r="H2398" t="s">
         <v>9</v>
@@ -67216,7 +67219,7 @@
         <v>8.78999996185303</v>
       </c>
       <c r="G2399" t="s">
-        <v>1412</v>
+        <v>1413</v>
       </c>
       <c r="H2399" t="s">
         <v>9</v>
@@ -67242,7 +67245,7 @@
         <v>8.56999969482422</v>
       </c>
       <c r="G2400" t="s">
-        <v>1413</v>
+        <v>1414</v>
       </c>
       <c r="H2400" t="s">
         <v>9</v>
@@ -67268,7 +67271,7 @@
         <v>8.53999996185303</v>
       </c>
       <c r="G2401" t="s">
-        <v>1397</v>
+        <v>1398</v>
       </c>
       <c r="H2401" t="s">
         <v>9</v>
@@ -67294,7 +67297,7 @@
         <v>8.56999969482422</v>
       </c>
       <c r="G2402" t="s">
-        <v>1413</v>
+        <v>1414</v>
       </c>
       <c r="H2402" t="s">
         <v>9</v>
@@ -67320,7 +67323,7 @@
         <v>8</v>
       </c>
       <c r="G2403" t="s">
-        <v>1414</v>
+        <v>1415</v>
       </c>
       <c r="H2403" t="s">
         <v>9</v>
@@ -67346,7 +67349,7 @@
         <v>7.82000017166138</v>
       </c>
       <c r="G2404" t="s">
-        <v>1415</v>
+        <v>1416</v>
       </c>
       <c r="H2404" t="s">
         <v>9</v>
@@ -67372,7 +67375,7 @@
         <v>7.69999980926514</v>
       </c>
       <c r="G2405" t="s">
-        <v>1416</v>
+        <v>1417</v>
       </c>
       <c r="H2405" t="s">
         <v>9</v>
@@ -67398,7 +67401,7 @@
         <v>7.65000009536743</v>
       </c>
       <c r="G2406" t="s">
-        <v>1417</v>
+        <v>1418</v>
       </c>
       <c r="H2406" t="s">
         <v>9</v>
@@ -67424,7 +67427,7 @@
         <v>7.57999992370605</v>
       </c>
       <c r="G2407" t="s">
-        <v>1418</v>
+        <v>1419</v>
       </c>
       <c r="H2407" t="s">
         <v>9</v>
@@ -67450,7 +67453,7 @@
         <v>7.59999990463257</v>
       </c>
       <c r="G2408" t="s">
-        <v>1419</v>
+        <v>1420</v>
       </c>
       <c r="H2408" t="s">
         <v>9</v>
@@ -67476,7 +67479,7 @@
         <v>7.82000017166138</v>
       </c>
       <c r="G2409" t="s">
-        <v>1415</v>
+        <v>1416</v>
       </c>
       <c r="H2409" t="s">
         <v>9</v>
@@ -67502,7 +67505,7 @@
         <v>7.75</v>
       </c>
       <c r="G2410" t="s">
-        <v>1420</v>
+        <v>1421</v>
       </c>
       <c r="H2410" t="s">
         <v>9</v>
@@ -67528,7 +67531,7 @@
         <v>7.69000005722046</v>
       </c>
       <c r="G2411" t="s">
-        <v>1421</v>
+        <v>1422</v>
       </c>
       <c r="H2411" t="s">
         <v>9</v>
@@ -67554,7 +67557,7 @@
         <v>7.76999998092651</v>
       </c>
       <c r="G2412" t="s">
-        <v>1422</v>
+        <v>1423</v>
       </c>
       <c r="H2412" t="s">
         <v>9</v>
@@ -67580,7 +67583,7 @@
         <v>8.02000045776367</v>
       </c>
       <c r="G2413" t="s">
-        <v>1423</v>
+        <v>1424</v>
       </c>
       <c r="H2413" t="s">
         <v>9</v>
@@ -67606,7 +67609,7 @@
         <v>7.90999984741211</v>
       </c>
       <c r="G2414" t="s">
-        <v>1393</v>
+        <v>1394</v>
       </c>
       <c r="H2414" t="s">
         <v>9</v>
@@ -67632,7 +67635,7 @@
         <v>7.84999990463257</v>
       </c>
       <c r="G2415" t="s">
-        <v>1424</v>
+        <v>1425</v>
       </c>
       <c r="H2415" t="s">
         <v>9</v>
@@ -67658,7 +67661,7 @@
         <v>7.73999977111816</v>
       </c>
       <c r="G2416" t="s">
-        <v>1425</v>
+        <v>1426</v>
       </c>
       <c r="H2416" t="s">
         <v>9</v>
@@ -67684,7 +67687,7 @@
         <v>7.80000019073486</v>
       </c>
       <c r="G2417" t="s">
-        <v>1426</v>
+        <v>1427</v>
       </c>
       <c r="H2417" t="s">
         <v>9</v>
@@ -67710,7 +67713,7 @@
         <v>7.65999984741211</v>
       </c>
       <c r="G2418" t="s">
-        <v>1427</v>
+        <v>1428</v>
       </c>
       <c r="H2418" t="s">
         <v>9</v>
@@ -67736,7 +67739,7 @@
         <v>7.69999980926514</v>
       </c>
       <c r="G2419" t="s">
-        <v>1416</v>
+        <v>1417</v>
       </c>
       <c r="H2419" t="s">
         <v>9</v>
@@ -67762,7 +67765,7 @@
         <v>7.65000009536743</v>
       </c>
       <c r="G2420" t="s">
-        <v>1417</v>
+        <v>1418</v>
       </c>
       <c r="H2420" t="s">
         <v>9</v>
@@ -67788,7 +67791,7 @@
         <v>7.63000011444092</v>
       </c>
       <c r="G2421" t="s">
-        <v>1392</v>
+        <v>1393</v>
       </c>
       <c r="H2421" t="s">
         <v>9</v>
@@ -67814,7 +67817,7 @@
         <v>7.6100001335144</v>
       </c>
       <c r="G2422" t="s">
-        <v>1428</v>
+        <v>1429</v>
       </c>
       <c r="H2422" t="s">
         <v>9</v>
@@ -67840,7 +67843,7 @@
         <v>7.48000001907349</v>
       </c>
       <c r="G2423" t="s">
-        <v>1429</v>
+        <v>1430</v>
       </c>
       <c r="H2423" t="s">
         <v>9</v>
@@ -67866,7 +67869,7 @@
         <v>7.55999994277954</v>
       </c>
       <c r="G2424" t="s">
-        <v>1430</v>
+        <v>1431</v>
       </c>
       <c r="H2424" t="s">
         <v>9</v>
@@ -67892,7 +67895,7 @@
         <v>7.55999994277954</v>
       </c>
       <c r="G2425" t="s">
-        <v>1430</v>
+        <v>1431</v>
       </c>
       <c r="H2425" t="s">
         <v>9</v>
@@ -67918,7 +67921,7 @@
         <v>7.53999996185303</v>
       </c>
       <c r="G2426" t="s">
-        <v>1389</v>
+        <v>1390</v>
       </c>
       <c r="H2426" t="s">
         <v>9</v>
@@ -67944,7 +67947,7 @@
         <v>7.59999990463257</v>
       </c>
       <c r="G2427" t="s">
-        <v>1419</v>
+        <v>1420</v>
       </c>
       <c r="H2427" t="s">
         <v>9</v>
@@ -67970,7 +67973,7 @@
         <v>7.80000019073486</v>
       </c>
       <c r="G2428" t="s">
-        <v>1426</v>
+        <v>1427</v>
       </c>
       <c r="H2428" t="s">
         <v>9</v>
@@ -67996,7 +67999,7 @@
         <v>7.6399998664856</v>
       </c>
       <c r="G2429" t="s">
-        <v>1391</v>
+        <v>1392</v>
       </c>
       <c r="H2429" t="s">
         <v>9</v>
@@ -68022,7 +68025,7 @@
         <v>7.57000017166138</v>
       </c>
       <c r="G2430" t="s">
-        <v>1431</v>
+        <v>1432</v>
       </c>
       <c r="H2430" t="s">
         <v>9</v>
@@ -68048,7 +68051,7 @@
         <v>7.67999982833862</v>
       </c>
       <c r="G2431" t="s">
-        <v>1432</v>
+        <v>1433</v>
       </c>
       <c r="H2431" t="s">
         <v>9</v>
@@ -68074,7 +68077,7 @@
         <v>7.65999984741211</v>
       </c>
       <c r="G2432" t="s">
-        <v>1427</v>
+        <v>1428</v>
       </c>
       <c r="H2432" t="s">
         <v>9</v>
@@ -68100,7 +68103,7 @@
         <v>7.59999990463257</v>
       </c>
       <c r="G2433" t="s">
-        <v>1419</v>
+        <v>1420</v>
       </c>
       <c r="H2433" t="s">
         <v>9</v>
@@ -68126,7 +68129,7 @@
         <v>7.46000003814697</v>
       </c>
       <c r="G2434" t="s">
-        <v>1433</v>
+        <v>1434</v>
       </c>
       <c r="H2434" t="s">
         <v>9</v>
@@ -68152,7 +68155,7 @@
         <v>7.42000007629395</v>
       </c>
       <c r="G2435" t="s">
-        <v>1434</v>
+        <v>1435</v>
       </c>
       <c r="H2435" t="s">
         <v>9</v>
@@ -68178,7 +68181,7 @@
         <v>7.42999982833862</v>
       </c>
       <c r="G2436" t="s">
-        <v>1435</v>
+        <v>1436</v>
       </c>
       <c r="H2436" t="s">
         <v>9</v>
@@ -68204,7 +68207,7 @@
         <v>7.1399998664856</v>
       </c>
       <c r="G2437" t="s">
-        <v>1436</v>
+        <v>1437</v>
       </c>
       <c r="H2437" t="s">
         <v>9</v>
@@ -68230,7 +68233,7 @@
         <v>7.17999982833862</v>
       </c>
       <c r="G2438" t="s">
-        <v>1437</v>
+        <v>1438</v>
       </c>
       <c r="H2438" t="s">
         <v>9</v>
@@ -68256,7 +68259,7 @@
         <v>6.92000007629395</v>
       </c>
       <c r="G2439" t="s">
-        <v>1438</v>
+        <v>1439</v>
       </c>
       <c r="H2439" t="s">
         <v>9</v>
@@ -68282,7 +68285,7 @@
         <v>6.67999982833862</v>
       </c>
       <c r="G2440" t="s">
-        <v>1439</v>
+        <v>1440</v>
       </c>
       <c r="H2440" t="s">
         <v>9</v>
@@ -68308,7 +68311,7 @@
         <v>6.8899998664856</v>
       </c>
       <c r="G2441" t="s">
-        <v>1440</v>
+        <v>1441</v>
       </c>
       <c r="H2441" t="s">
         <v>9</v>
@@ -68334,7 +68337,7 @@
         <v>6.82000017166138</v>
       </c>
       <c r="G2442" t="s">
-        <v>1441</v>
+        <v>1442</v>
       </c>
       <c r="H2442" t="s">
         <v>9</v>
@@ -68360,7 +68363,7 @@
         <v>6.65999984741211</v>
       </c>
       <c r="G2443" t="s">
-        <v>1442</v>
+        <v>1443</v>
       </c>
       <c r="H2443" t="s">
         <v>9</v>
@@ -68386,7 +68389,7 @@
         <v>6.61999988555908</v>
       </c>
       <c r="G2444" t="s">
-        <v>1443</v>
+        <v>1444</v>
       </c>
       <c r="H2444" t="s">
         <v>9</v>
@@ -68412,7 +68415,7 @@
         <v>6.48000001907349</v>
       </c>
       <c r="G2445" t="s">
-        <v>1444</v>
+        <v>1445</v>
       </c>
       <c r="H2445" t="s">
         <v>9</v>
@@ -68438,7 +68441,7 @@
         <v>6.36999988555908</v>
       </c>
       <c r="G2446" t="s">
-        <v>1445</v>
+        <v>1446</v>
       </c>
       <c r="H2446" t="s">
         <v>9</v>
@@ -68464,7 +68467,7 @@
         <v>6.48999977111816</v>
       </c>
       <c r="G2447" t="s">
-        <v>1446</v>
+        <v>1447</v>
       </c>
       <c r="H2447" t="s">
         <v>9</v>
@@ -68490,7 +68493,7 @@
         <v>6.5</v>
       </c>
       <c r="G2448" t="s">
-        <v>1447</v>
+        <v>1448</v>
       </c>
       <c r="H2448" t="s">
         <v>9</v>
@@ -68516,7 +68519,7 @@
         <v>6.51999998092651</v>
       </c>
       <c r="G2449" t="s">
-        <v>1448</v>
+        <v>1449</v>
       </c>
       <c r="H2449" t="s">
         <v>9</v>
@@ -68542,7 +68545,7 @@
         <v>6.55000019073486</v>
       </c>
       <c r="G2450" t="s">
-        <v>1449</v>
+        <v>1450</v>
       </c>
       <c r="H2450" t="s">
         <v>9</v>
@@ -68568,7 +68571,7 @@
         <v>6.75</v>
       </c>
       <c r="G2451" t="s">
-        <v>1450</v>
+        <v>1451</v>
       </c>
       <c r="H2451" t="s">
         <v>9</v>
@@ -68594,7 +68597,7 @@
         <v>6.98000001907349</v>
       </c>
       <c r="G2452" t="s">
-        <v>1451</v>
+        <v>1452</v>
       </c>
       <c r="H2452" t="s">
         <v>9</v>
@@ -68620,7 +68623,7 @@
         <v>7</v>
       </c>
       <c r="G2453" t="s">
-        <v>1452</v>
+        <v>1453</v>
       </c>
       <c r="H2453" t="s">
         <v>9</v>
@@ -68646,7 +68649,7 @@
         <v>6.84000015258789</v>
       </c>
       <c r="G2454" t="s">
-        <v>1453</v>
+        <v>1454</v>
       </c>
       <c r="H2454" t="s">
         <v>9</v>
@@ -68672,7 +68675,7 @@
         <v>6.61999988555908</v>
       </c>
       <c r="G2455" t="s">
-        <v>1443</v>
+        <v>1444</v>
       </c>
       <c r="H2455" t="s">
         <v>9</v>
@@ -68698,7 +68701,7 @@
         <v>6.65999984741211</v>
       </c>
       <c r="G2456" t="s">
-        <v>1442</v>
+        <v>1443</v>
       </c>
       <c r="H2456" t="s">
         <v>9</v>
@@ -68724,7 +68727,7 @@
         <v>6.48999977111816</v>
       </c>
       <c r="G2457" t="s">
-        <v>1446</v>
+        <v>1447</v>
       </c>
       <c r="H2457" t="s">
         <v>9</v>
@@ -68750,7 +68753,7 @@
         <v>6.5</v>
       </c>
       <c r="G2458" t="s">
-        <v>1447</v>
+        <v>1448</v>
       </c>
       <c r="H2458" t="s">
         <v>9</v>
@@ -68776,7 +68779,7 @@
         <v>6.36999988555908</v>
       </c>
       <c r="G2459" t="s">
-        <v>1445</v>
+        <v>1446</v>
       </c>
       <c r="H2459" t="s">
         <v>9</v>
@@ -68802,7 +68805,7 @@
         <v>6.65000009536743</v>
       </c>
       <c r="G2460" t="s">
-        <v>1454</v>
+        <v>1455</v>
       </c>
       <c r="H2460" t="s">
         <v>9</v>
@@ -68828,7 +68831,7 @@
         <v>6.84999990463257</v>
       </c>
       <c r="G2461" t="s">
-        <v>1455</v>
+        <v>1456</v>
       </c>
       <c r="H2461" t="s">
         <v>9</v>
@@ -68854,7 +68857,7 @@
         <v>6.92000007629395</v>
       </c>
       <c r="G2462" t="s">
-        <v>1438</v>
+        <v>1439</v>
       </c>
       <c r="H2462" t="s">
         <v>9</v>
@@ -68880,7 +68883,7 @@
         <v>6.82000017166138</v>
       </c>
       <c r="G2463" t="s">
-        <v>1441</v>
+        <v>1442</v>
       </c>
       <c r="H2463" t="s">
         <v>9</v>
@@ -68906,7 +68909,7 @@
         <v>6.76999998092651</v>
       </c>
       <c r="G2464" t="s">
-        <v>1456</v>
+        <v>1457</v>
       </c>
       <c r="H2464" t="s">
         <v>9</v>
@@ -68932,7 +68935,7 @@
         <v>7.6100001335144</v>
       </c>
       <c r="G2465" t="s">
-        <v>1428</v>
+        <v>1429</v>
       </c>
       <c r="H2465" t="s">
         <v>9</v>
@@ -68958,7 +68961,7 @@
         <v>7.69999980926514</v>
       </c>
       <c r="G2466" t="s">
-        <v>1416</v>
+        <v>1417</v>
       </c>
       <c r="H2466" t="s">
         <v>9</v>
@@ -68984,7 +68987,7 @@
         <v>7.5</v>
       </c>
       <c r="G2467" t="s">
-        <v>1457</v>
+        <v>1458</v>
       </c>
       <c r="H2467" t="s">
         <v>9</v>
@@ -69010,7 +69013,7 @@
         <v>7.42999982833862</v>
       </c>
       <c r="G2468" t="s">
-        <v>1435</v>
+        <v>1436</v>
       </c>
       <c r="H2468" t="s">
         <v>9</v>
@@ -69036,7 +69039,7 @@
         <v>7.40000009536743</v>
       </c>
       <c r="G2469" t="s">
-        <v>1388</v>
+        <v>1389</v>
       </c>
       <c r="H2469" t="s">
         <v>9</v>
@@ -69062,7 +69065,7 @@
         <v>7.26000022888184</v>
       </c>
       <c r="G2470" t="s">
-        <v>1458</v>
+        <v>1459</v>
       </c>
       <c r="H2470" t="s">
         <v>9</v>
@@ -69088,7 +69091,7 @@
         <v>7.1399998664856</v>
       </c>
       <c r="G2471" t="s">
-        <v>1436</v>
+        <v>1437</v>
       </c>
       <c r="H2471" t="s">
         <v>9</v>
@@ -69114,7 +69117,7 @@
         <v>7.05000019073486</v>
       </c>
       <c r="G2472" t="s">
-        <v>1459</v>
+        <v>1460</v>
       </c>
       <c r="H2472" t="s">
         <v>9</v>
@@ -69140,7 +69143,7 @@
         <v>7.15000009536743</v>
       </c>
       <c r="G2473" t="s">
-        <v>1460</v>
+        <v>1461</v>
       </c>
       <c r="H2473" t="s">
         <v>9</v>
@@ -69166,7 +69169,7 @@
         <v>7.15999984741211</v>
       </c>
       <c r="G2474" t="s">
-        <v>1461</v>
+        <v>1462</v>
       </c>
       <c r="H2474" t="s">
         <v>9</v>
@@ -69192,7 +69195,7 @@
         <v>7.01999998092651</v>
       </c>
       <c r="G2475" t="s">
-        <v>1462</v>
+        <v>1463</v>
       </c>
       <c r="H2475" t="s">
         <v>9</v>
@@ -69218,7 +69221,7 @@
         <v>6.96999979019165</v>
       </c>
       <c r="G2476" t="s">
-        <v>1463</v>
+        <v>1464</v>
       </c>
       <c r="H2476" t="s">
         <v>9</v>
@@ -69244,7 +69247,7 @@
         <v>6.92000007629395</v>
       </c>
       <c r="G2477" t="s">
-        <v>1438</v>
+        <v>1439</v>
       </c>
       <c r="H2477" t="s">
         <v>9</v>
@@ -69270,7 +69273,7 @@
         <v>7.03000020980835</v>
       </c>
       <c r="G2478" t="s">
-        <v>1464</v>
+        <v>1465</v>
       </c>
       <c r="H2478" t="s">
         <v>9</v>
@@ -69296,7 +69299,7 @@
         <v>7.05000019073486</v>
       </c>
       <c r="G2479" t="s">
-        <v>1459</v>
+        <v>1460</v>
       </c>
       <c r="H2479" t="s">
         <v>9</v>
@@ -69322,7 +69325,7 @@
         <v>7</v>
       </c>
       <c r="G2480" t="s">
-        <v>1452</v>
+        <v>1453</v>
       </c>
       <c r="H2480" t="s">
         <v>9</v>
@@ -69348,7 +69351,7 @@
         <v>6.96000003814697</v>
       </c>
       <c r="G2481" t="s">
-        <v>1465</v>
+        <v>1466</v>
       </c>
       <c r="H2481" t="s">
         <v>9</v>
@@ -69374,7 +69377,7 @@
         <v>7.03999996185303</v>
       </c>
       <c r="G2482" t="s">
-        <v>1466</v>
+        <v>1467</v>
       </c>
       <c r="H2482" t="s">
         <v>9</v>
@@ -69400,7 +69403,7 @@
         <v>7.17999982833862</v>
       </c>
       <c r="G2483" t="s">
-        <v>1437</v>
+        <v>1438</v>
       </c>
       <c r="H2483" t="s">
         <v>9</v>
@@ -69426,7 +69429,7 @@
         <v>7.1399998664856</v>
       </c>
       <c r="G2484" t="s">
-        <v>1436</v>
+        <v>1437</v>
       </c>
       <c r="H2484" t="s">
         <v>9</v>
@@ -69452,7 +69455,7 @@
         <v>7.07999992370605</v>
       </c>
       <c r="G2485" t="s">
-        <v>1467</v>
+        <v>1468</v>
       </c>
       <c r="H2485" t="s">
         <v>9</v>
@@ -69478,7 +69481,7 @@
         <v>7.21000003814697</v>
       </c>
       <c r="G2486" t="s">
-        <v>1468</v>
+        <v>1469</v>
       </c>
       <c r="H2486" t="s">
         <v>9</v>
@@ -69504,7 +69507,7 @@
         <v>6.86999988555908</v>
       </c>
       <c r="G2487" t="s">
-        <v>1469</v>
+        <v>1470</v>
       </c>
       <c r="H2487" t="s">
         <v>9</v>
@@ -69530,7 +69533,7 @@
         <v>7.05000019073486</v>
       </c>
       <c r="G2488" t="s">
-        <v>1459</v>
+        <v>1460</v>
       </c>
       <c r="H2488" t="s">
         <v>9</v>
@@ -69556,7 +69559,7 @@
         <v>7.09000015258789</v>
       </c>
       <c r="G2489" t="s">
-        <v>1470</v>
+        <v>1471</v>
       </c>
       <c r="H2489" t="s">
         <v>9</v>
@@ -69582,7 +69585,7 @@
         <v>7</v>
       </c>
       <c r="G2490" t="s">
-        <v>1452</v>
+        <v>1453</v>
       </c>
       <c r="H2490" t="s">
         <v>9</v>
@@ -69608,7 +69611,7 @@
         <v>6.98999977111816</v>
       </c>
       <c r="G2491" t="s">
-        <v>1471</v>
+        <v>1472</v>
       </c>
       <c r="H2491" t="s">
         <v>9</v>
@@ -69634,7 +69637,7 @@
         <v>6.94000005722046</v>
       </c>
       <c r="G2492" t="s">
-        <v>1472</v>
+        <v>1473</v>
       </c>
       <c r="H2492" t="s">
         <v>9</v>
@@ -69660,7 +69663,7 @@
         <v>6.90000009536743</v>
       </c>
       <c r="G2493" t="s">
-        <v>1473</v>
+        <v>1474</v>
       </c>
       <c r="H2493" t="s">
         <v>9</v>
@@ -69686,7 +69689,7 @@
         <v>7</v>
       </c>
       <c r="G2494" t="s">
-        <v>1452</v>
+        <v>1453</v>
       </c>
       <c r="H2494" t="s">
         <v>9</v>
@@ -69712,7 +69715,7 @@
         <v>7.11999988555908</v>
       </c>
       <c r="G2495" t="s">
-        <v>1474</v>
+        <v>1475</v>
       </c>
       <c r="H2495" t="s">
         <v>9</v>
@@ -69738,7 +69741,7 @@
         <v>7.17999982833862</v>
       </c>
       <c r="G2496" t="s">
-        <v>1437</v>
+        <v>1438</v>
       </c>
       <c r="H2496" t="s">
         <v>9</v>
@@ -69764,7 +69767,7 @@
         <v>7.15000009536743</v>
       </c>
       <c r="G2497" t="s">
-        <v>1460</v>
+        <v>1461</v>
       </c>
       <c r="H2497" t="s">
         <v>9</v>
@@ -69790,7 +69793,7 @@
         <v>7.07999992370605</v>
       </c>
       <c r="G2498" t="s">
-        <v>1467</v>
+        <v>1468</v>
       </c>
       <c r="H2498" t="s">
         <v>9</v>
@@ -69816,7 +69819,7 @@
         <v>7.05000019073486</v>
       </c>
       <c r="G2499" t="s">
-        <v>1459</v>
+        <v>1460</v>
       </c>
       <c r="H2499" t="s">
         <v>9</v>
@@ -69842,7 +69845,7 @@
         <v>6.8600001335144</v>
       </c>
       <c r="G2500" t="s">
-        <v>1475</v>
+        <v>1476</v>
       </c>
       <c r="H2500" t="s">
         <v>9</v>
@@ -69868,7 +69871,7 @@
         <v>6.98000001907349</v>
       </c>
       <c r="G2501" t="s">
-        <v>1451</v>
+        <v>1452</v>
       </c>
       <c r="H2501" t="s">
         <v>9</v>
@@ -69894,7 +69897,7 @@
         <v>6.8899998664856</v>
       </c>
       <c r="G2502" t="s">
-        <v>1440</v>
+        <v>1441</v>
       </c>
       <c r="H2502" t="s">
         <v>9</v>
@@ -69920,7 +69923,7 @@
         <v>6.92999982833862</v>
       </c>
       <c r="G2503" t="s">
-        <v>1476</v>
+        <v>1477</v>
       </c>
       <c r="H2503" t="s">
         <v>9</v>
@@ -69946,7 +69949,7 @@
         <v>6.80999994277954</v>
       </c>
       <c r="G2504" t="s">
-        <v>1477</v>
+        <v>1478</v>
       </c>
       <c r="H2504" t="s">
         <v>9</v>
@@ -69972,7 +69975,7 @@
         <v>6.98999977111816</v>
       </c>
       <c r="G2505" t="s">
-        <v>1471</v>
+        <v>1472</v>
       </c>
       <c r="H2505" t="s">
         <v>9</v>
@@ -69998,7 +70001,7 @@
         <v>6.82999992370605</v>
       </c>
       <c r="G2506" t="s">
-        <v>1478</v>
+        <v>1479</v>
       </c>
       <c r="H2506" t="s">
         <v>9</v>
@@ -70024,7 +70027,7 @@
         <v>6.8899998664856</v>
       </c>
       <c r="G2507" t="s">
-        <v>1440</v>
+        <v>1441</v>
       </c>
       <c r="H2507" t="s">
         <v>9</v>
@@ -70050,7 +70053,7 @@
         <v>7.09999990463257</v>
       </c>
       <c r="G2508" t="s">
-        <v>1479</v>
+        <v>1480</v>
       </c>
       <c r="H2508" t="s">
         <v>9</v>
@@ -70076,7 +70079,7 @@
         <v>7.30999994277954</v>
       </c>
       <c r="G2509" t="s">
-        <v>1480</v>
+        <v>1481</v>
       </c>
       <c r="H2509" t="s">
         <v>9</v>
@@ -70102,7 +70105,7 @@
         <v>7.32999992370605</v>
       </c>
       <c r="G2510" t="s">
-        <v>1481</v>
+        <v>1482</v>
       </c>
       <c r="H2510" t="s">
         <v>9</v>
@@ -70128,7 +70131,7 @@
         <v>7.30000019073486</v>
       </c>
       <c r="G2511" t="s">
-        <v>1482</v>
+        <v>1483</v>
       </c>
       <c r="H2511" t="s">
         <v>9</v>
@@ -70154,7 +70157,7 @@
         <v>6.88000011444092</v>
       </c>
       <c r="G2512" t="s">
-        <v>1483</v>
+        <v>1484</v>
       </c>
       <c r="H2512" t="s">
         <v>9</v>
@@ -70180,7 +70183,7 @@
         <v>6.63000011444092</v>
       </c>
       <c r="G2513" t="s">
-        <v>1484</v>
+        <v>1485</v>
       </c>
       <c r="H2513" t="s">
         <v>9</v>
@@ -70206,7 +70209,7 @@
         <v>6.57000017166138</v>
       </c>
       <c r="G2514" t="s">
-        <v>1485</v>
+        <v>1486</v>
       </c>
       <c r="H2514" t="s">
         <v>9</v>
@@ -70232,7 +70235,7 @@
         <v>6.63000011444092</v>
       </c>
       <c r="G2515" t="s">
-        <v>1484</v>
+        <v>1485</v>
       </c>
       <c r="H2515" t="s">
         <v>9</v>
@@ -70258,7 +70261,7 @@
         <v>6.76000022888184</v>
       </c>
       <c r="G2516" t="s">
-        <v>1486</v>
+        <v>1487</v>
       </c>
       <c r="H2516" t="s">
         <v>9</v>
@@ -70284,7 +70287,7 @@
         <v>6.86999988555908</v>
       </c>
       <c r="G2517" t="s">
-        <v>1469</v>
+        <v>1470</v>
       </c>
       <c r="H2517" t="s">
         <v>9</v>
@@ -70310,7 +70313,7 @@
         <v>6.92000007629395</v>
       </c>
       <c r="G2518" t="s">
-        <v>1438</v>
+        <v>1439</v>
       </c>
       <c r="H2518" t="s">
         <v>9</v>
@@ -70336,7 +70339,7 @@
         <v>6.84999990463257</v>
       </c>
       <c r="G2519" t="s">
-        <v>1455</v>
+        <v>1456</v>
       </c>
       <c r="H2519" t="s">
         <v>9</v>
@@ -70362,7 +70365,7 @@
         <v>6.84999990463257</v>
       </c>
       <c r="G2520" t="s">
-        <v>1455</v>
+        <v>1456</v>
       </c>
       <c r="H2520" t="s">
         <v>9</v>
@@ -70388,7 +70391,7 @@
         <v>6.86999988555908</v>
       </c>
       <c r="G2521" t="s">
-        <v>1469</v>
+        <v>1470</v>
       </c>
       <c r="H2521" t="s">
         <v>9</v>
@@ -70414,7 +70417,7 @@
         <v>6.84000015258789</v>
       </c>
       <c r="G2522" t="s">
-        <v>1453</v>
+        <v>1454</v>
       </c>
       <c r="H2522" t="s">
         <v>9</v>
@@ -70440,7 +70443,7 @@
         <v>7.01999998092651</v>
       </c>
       <c r="G2523" t="s">
-        <v>1462</v>
+        <v>1463</v>
       </c>
       <c r="H2523" t="s">
         <v>9</v>
@@ -70466,7 +70469,7 @@
         <v>6.90999984741211</v>
       </c>
       <c r="G2524" t="s">
-        <v>1487</v>
+        <v>1488</v>
       </c>
       <c r="H2524" t="s">
         <v>9</v>
@@ -70492,7 +70495,7 @@
         <v>6.82999992370605</v>
       </c>
       <c r="G2525" t="s">
-        <v>1478</v>
+        <v>1479</v>
       </c>
       <c r="H2525" t="s">
         <v>9</v>
@@ -70518,7 +70521,7 @@
         <v>6.90000009536743</v>
       </c>
       <c r="G2526" t="s">
-        <v>1473</v>
+        <v>1474</v>
       </c>
       <c r="H2526" t="s">
         <v>9</v>
@@ -70544,7 +70547,7 @@
         <v>7.40000009536743</v>
       </c>
       <c r="G2527" t="s">
-        <v>1388</v>
+        <v>1389</v>
       </c>
       <c r="H2527" t="s">
         <v>9</v>
@@ -70570,7 +70573,7 @@
         <v>7.3600001335144</v>
       </c>
       <c r="G2528" t="s">
-        <v>1488</v>
+        <v>1489</v>
       </c>
       <c r="H2528" t="s">
         <v>9</v>
@@ -70596,7 +70599,7 @@
         <v>7.42999982833862</v>
       </c>
       <c r="G2529" t="s">
-        <v>1435</v>
+        <v>1436</v>
       </c>
       <c r="H2529" t="s">
         <v>9</v>
@@ -70622,7 +70625,7 @@
         <v>7.19000005722046</v>
       </c>
       <c r="G2530" t="s">
-        <v>1489</v>
+        <v>1490</v>
       </c>
       <c r="H2530" t="s">
         <v>9</v>
@@ -70648,7 +70651,7 @@
         <v>7.34999990463257</v>
       </c>
       <c r="G2531" t="s">
-        <v>1490</v>
+        <v>1491</v>
       </c>
       <c r="H2531" t="s">
         <v>9</v>
@@ -70674,7 +70677,7 @@
         <v>7.32999992370605</v>
       </c>
       <c r="G2532" t="s">
-        <v>1481</v>
+        <v>1482</v>
       </c>
       <c r="H2532" t="s">
         <v>9</v>
@@ -70700,7 +70703,7 @@
         <v>7.32999992370605</v>
       </c>
       <c r="G2533" t="s">
-        <v>1481</v>
+        <v>1482</v>
       </c>
       <c r="H2533" t="s">
         <v>9</v>
@@ -70726,7 +70729,7 @@
         <v>7.34000015258789</v>
       </c>
       <c r="G2534" t="s">
-        <v>1491</v>
+        <v>1492</v>
       </c>
       <c r="H2534" t="s">
         <v>9</v>
@@ -70752,7 +70755,7 @@
         <v>7.30999994277954</v>
       </c>
       <c r="G2535" t="s">
-        <v>1480</v>
+        <v>1481</v>
       </c>
       <c r="H2535" t="s">
         <v>9</v>
@@ -70778,7 +70781,7 @@
         <v>7.30000019073486</v>
       </c>
       <c r="G2536" t="s">
-        <v>1482</v>
+        <v>1483</v>
       </c>
       <c r="H2536" t="s">
         <v>9</v>
@@ -70804,7 +70807,7 @@
         <v>7.28999996185303</v>
       </c>
       <c r="G2537" t="s">
-        <v>1492</v>
+        <v>1493</v>
       </c>
       <c r="H2537" t="s">
         <v>9</v>
@@ -70830,7 +70833,7 @@
         <v>7.34000015258789</v>
       </c>
       <c r="G2538" t="s">
-        <v>1491</v>
+        <v>1492</v>
       </c>
       <c r="H2538" t="s">
         <v>9</v>
@@ -70856,7 +70859,7 @@
         <v>7.3600001335144</v>
       </c>
       <c r="G2539" t="s">
-        <v>1488</v>
+        <v>1489</v>
       </c>
       <c r="H2539" t="s">
         <v>9</v>
@@ -70882,7 +70885,7 @@
         <v>7.42999982833862</v>
       </c>
       <c r="G2540" t="s">
-        <v>1435</v>
+        <v>1436</v>
       </c>
       <c r="H2540" t="s">
         <v>9</v>
@@ -70908,7 +70911,7 @@
         <v>7.48000001907349</v>
       </c>
       <c r="G2541" t="s">
-        <v>1429</v>
+        <v>1430</v>
       </c>
       <c r="H2541" t="s">
         <v>9</v>
@@ -70934,7 +70937,7 @@
         <v>7.38000011444092</v>
       </c>
       <c r="G2542" t="s">
-        <v>1493</v>
+        <v>1494</v>
       </c>
       <c r="H2542" t="s">
         <v>9</v>
@@ -70960,7 +70963,7 @@
         <v>7.44000005722046</v>
       </c>
       <c r="G2543" t="s">
-        <v>1494</v>
+        <v>1495</v>
       </c>
       <c r="H2543" t="s">
         <v>9</v>
@@ -70986,7 +70989,7 @@
         <v>7.5</v>
       </c>
       <c r="G2544" t="s">
-        <v>1457</v>
+        <v>1458</v>
       </c>
       <c r="H2544" t="s">
         <v>9</v>
@@ -71012,7 +71015,7 @@
         <v>7.48000001907349</v>
       </c>
       <c r="G2545" t="s">
-        <v>1429</v>
+        <v>1430</v>
       </c>
       <c r="H2545" t="s">
         <v>9</v>
@@ -71038,7 +71041,7 @@
         <v>7.59999990463257</v>
       </c>
       <c r="G2546" t="s">
-        <v>1419</v>
+        <v>1420</v>
       </c>
       <c r="H2546" t="s">
         <v>9</v>
@@ -71064,7 +71067,7 @@
         <v>7.61999988555908</v>
       </c>
       <c r="G2547" t="s">
-        <v>1495</v>
+        <v>1496</v>
       </c>
       <c r="H2547" t="s">
         <v>9</v>
@@ -71090,7 +71093,7 @@
         <v>7.40999984741211</v>
       </c>
       <c r="G2548" t="s">
-        <v>1496</v>
+        <v>1497</v>
       </c>
       <c r="H2548" t="s">
         <v>9</v>
@@ -71116,7 +71119,7 @@
         <v>7.26000022888184</v>
       </c>
       <c r="G2549" t="s">
-        <v>1458</v>
+        <v>1459</v>
       </c>
       <c r="H2549" t="s">
         <v>9</v>
@@ -71142,7 +71145,7 @@
         <v>7.28999996185303</v>
       </c>
       <c r="G2550" t="s">
-        <v>1492</v>
+        <v>1493</v>
       </c>
       <c r="H2550" t="s">
         <v>9</v>
@@ -71168,7 +71171,7 @@
         <v>7.26999998092651</v>
       </c>
       <c r="G2551" t="s">
-        <v>1497</v>
+        <v>1498</v>
       </c>
       <c r="H2551" t="s">
         <v>9</v>
@@ -71194,7 +71197,7 @@
         <v>7.26000022888184</v>
       </c>
       <c r="G2552" t="s">
-        <v>1458</v>
+        <v>1459</v>
       </c>
       <c r="H2552" t="s">
         <v>9</v>
@@ -71220,7 +71223,7 @@
         <v>7.19000005722046</v>
       </c>
       <c r="G2553" t="s">
-        <v>1489</v>
+        <v>1490</v>
       </c>
       <c r="H2553" t="s">
         <v>9</v>
@@ -71246,7 +71249,7 @@
         <v>7.09999990463257</v>
       </c>
       <c r="G2554" t="s">
-        <v>1479</v>
+        <v>1480</v>
       </c>
       <c r="H2554" t="s">
         <v>9</v>
@@ -71272,7 +71275,7 @@
         <v>7.13000011444092</v>
       </c>
       <c r="G2555" t="s">
-        <v>1498</v>
+        <v>1499</v>
       </c>
       <c r="H2555" t="s">
         <v>9</v>
@@ -71298,7 +71301,7 @@
         <v>7.21999979019165</v>
       </c>
       <c r="G2556" t="s">
-        <v>1499</v>
+        <v>1500</v>
       </c>
       <c r="H2556" t="s">
         <v>9</v>
@@ -71306,7 +71309,7 @@
     </row>
     <row r="2557">
       <c r="A2557" s="1" t="n">
-        <v>46045.6912037037</v>
+        <v>46045.3333333333</v>
       </c>
       <c r="B2557" t="n">
         <v>7509</v>
@@ -71324,9 +71327,35 @@
         <v>7.15000009536743</v>
       </c>
       <c r="G2557" t="s">
-        <v>1460</v>
+        <v>1461</v>
       </c>
       <c r="H2557" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2558">
+      <c r="A2558" s="1" t="n">
+        <v>46048.6911921296</v>
+      </c>
+      <c r="B2558" t="n">
+        <v>17991</v>
+      </c>
+      <c r="C2558" t="n">
+        <v>7.21000003814697</v>
+      </c>
+      <c r="D2558" t="n">
+        <v>7.09999990463257</v>
+      </c>
+      <c r="E2558" t="n">
+        <v>7.21000003814697</v>
+      </c>
+      <c r="F2558" t="n">
+        <v>7.11999988555908</v>
+      </c>
+      <c r="G2558" t="s">
+        <v>1475</v>
+      </c>
+      <c r="H2558" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/BAN.MI.xlsx
+++ b/data/BAN.MI.xlsx
@@ -38,103 +38,103 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">3.66912961006165</t>
+    <t xml:space="preserve">3.66912984848022</t>
   </si>
   <si>
     <t xml:space="preserve">BAN.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">3.68330216407776</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.59039306640625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.46283984184265</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.41874718666077</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.35733246803284</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.44551753997803</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.46441435813904</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.45181608200073</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.43134498596191</t>
+    <t xml:space="preserve">3.68330240249634</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.59039258956909</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.46283912658691</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.41874694824219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.35733294487</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.44551801681519</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.46441459655762</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.45181632041931</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.43134474754333</t>
   </si>
   <si>
     <t xml:space="preserve">3.38410305976868</t>
   </si>
   <si>
-    <t xml:space="preserve">3.40929889678955</t>
+    <t xml:space="preserve">3.40929865837097</t>
   </si>
   <si>
     <t xml:space="preserve">3.11639857292175</t>
   </si>
   <si>
-    <t xml:space="preserve">3.24080300331116</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.29119324684143</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.21245718002319</t>
+    <t xml:space="preserve">3.240802526474</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.29119348526001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.21245670318604</t>
   </si>
   <si>
     <t xml:space="preserve">3.26757264137268</t>
   </si>
   <si>
-    <t xml:space="preserve">3.19356036186218</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.13372015953064</t>
+    <t xml:space="preserve">3.19356083869934</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.13372039794922</t>
   </si>
   <si>
     <t xml:space="preserve">3.22820425033569</t>
   </si>
   <si>
-    <t xml:space="preserve">3.16678977012634</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.17308878898621</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.0707311630249</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.14946794509888</t>
+    <t xml:space="preserve">3.16678929328918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.17308902740479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.07073140144348</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.1494677066803</t>
   </si>
   <si>
     <t xml:space="preserve">3.05025959014893</t>
   </si>
   <si>
-    <t xml:space="preserve">2.92900514602661</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.91325736045837</t>
+    <t xml:space="preserve">2.92900466918945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.91325759887695</t>
   </si>
   <si>
     <t xml:space="preserve">2.83452081680298</t>
   </si>
   <si>
-    <t xml:space="preserve">2.82664680480957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.75263476371765</t>
+    <t xml:space="preserve">2.82664728164673</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.75263500213623</t>
   </si>
   <si>
     <t xml:space="preserve">2.7542097568512</t>
   </si>
   <si>
-    <t xml:space="preserve">2.75578451156616</t>
+    <t xml:space="preserve">2.755784034729</t>
   </si>
   <si>
     <t xml:space="preserve">2.89436101913452</t>
@@ -143,37 +143,37 @@
     <t xml:space="preserve">2.98254585266113</t>
   </si>
   <si>
-    <t xml:space="preserve">2.96207404136658</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.99356913566589</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.05970788002014</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.11009931564331</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.06915593147278</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.96364903450012</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.99199390411377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.00774145126343</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.97624707221985</t>
+    <t xml:space="preserve">2.96207427978516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.99356889724731</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.05970764160156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.11009907722473</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.06915616989136</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.9636492729187</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.99199438095093</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.00774168968201</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.97624683380127</t>
   </si>
   <si>
     <t xml:space="preserve">3.06285762786865</t>
   </si>
   <si>
-    <t xml:space="preserve">3.11797285079956</t>
+    <t xml:space="preserve">3.11797308921814</t>
   </si>
   <si>
     <t xml:space="preserve">3.18096232414246</t>
@@ -185,43 +185,43 @@
     <t xml:space="preserve">3.13686990737915</t>
   </si>
   <si>
-    <t xml:space="preserve">3.23292875289917</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.33843588829041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.30694079399109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.24395155906677</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.24237704277039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.12584686279297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.19670987129211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.20300841331482</t>
+    <t xml:space="preserve">3.23292851448059</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.33843541145325</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.30694103240967</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.24395179748535</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.24237728118896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.12584638595581</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.19671010971069</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.2030086517334</t>
   </si>
   <si>
     <t xml:space="preserve">3.10380005836487</t>
   </si>
   <si>
-    <t xml:space="preserve">3.11324858665466</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.14159417152405</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.04711008071899</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.99986743927002</t>
+    <t xml:space="preserve">3.11324882507324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.14159393310547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.04710960388184</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.99986815452576</t>
   </si>
   <si>
     <t xml:space="preserve">2.96049952507019</t>
@@ -230,10 +230,10 @@
     <t xml:space="preserve">3.09435200691223</t>
   </si>
   <si>
-    <t xml:space="preserve">2.9683735370636</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.86286640167236</t>
+    <t xml:space="preserve">2.96837377548218</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.86286592483521</t>
   </si>
   <si>
     <t xml:space="preserve">2.87388944625854</t>
@@ -242,94 +242,94 @@
     <t xml:space="preserve">2.9101083278656</t>
   </si>
   <si>
-    <t xml:space="preserve">2.98569536209106</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.00144267082214</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.01561522483826</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.92743015289307</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.92113137245178</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.85814213752747</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.81404948234558</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.84081983566284</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.80145144462585</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.72901391983032</t>
+    <t xml:space="preserve">2.98569560050964</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.00144290924072</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.01561546325684</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.92742991447449</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.9211311340332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.85814166069031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.814049243927</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.84082007408142</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.80145120620728</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.7290141582489</t>
   </si>
   <si>
     <t xml:space="preserve">2.65185189247131</t>
   </si>
   <si>
-    <t xml:space="preserve">2.68177151679993</t>
+    <t xml:space="preserve">2.68177127838135</t>
   </si>
   <si>
     <t xml:space="preserve">2.71484112739563</t>
   </si>
   <si>
-    <t xml:space="preserve">2.76365828514099</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.77940511703491</t>
+    <t xml:space="preserve">2.76365780830383</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.77940535545349</t>
   </si>
   <si>
     <t xml:space="preserve">2.72428965568542</t>
   </si>
   <si>
-    <t xml:space="preserve">2.5904369354248</t>
+    <t xml:space="preserve">2.59043669700623</t>
   </si>
   <si>
     <t xml:space="preserve">2.5353217124939</t>
   </si>
   <si>
-    <t xml:space="preserve">2.49437856674194</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.48020553588867</t>
+    <t xml:space="preserve">2.49437880516052</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.48020601272583</t>
   </si>
   <si>
     <t xml:space="preserve">2.51957416534424</t>
   </si>
   <si>
-    <t xml:space="preserve">2.60572695732117</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.58784675598145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.56021237373352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.56183767318726</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.60897850990295</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.59272313117981</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.58134460449219</t>
+    <t xml:space="preserve">2.60572743415833</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.58784627914429</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.56021285057068</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.56183815002441</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.60897827148438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.59272265434265</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.58134436607361</t>
   </si>
   <si>
     <t xml:space="preserve">2.60085082054138</t>
   </si>
   <si>
-    <t xml:space="preserve">2.72113990783691</t>
+    <t xml:space="preserve">2.72114014625549</t>
   </si>
   <si>
     <t xml:space="preserve">2.82029747962952</t>
@@ -338,61 +338,61 @@
     <t xml:space="preserve">2.80404233932495</t>
   </si>
   <si>
-    <t xml:space="preserve">2.68212699890137</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.71463775634766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.44642543792725</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.39765930175781</t>
+    <t xml:space="preserve">2.68212723731995</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.71463751792908</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.44642519950867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.39765906333923</t>
   </si>
   <si>
     <t xml:space="preserve">2.50331854820251</t>
   </si>
   <si>
-    <t xml:space="preserve">2.47568464279175</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.52770161628723</t>
+    <t xml:space="preserve">2.47568488121033</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.52770185470581</t>
   </si>
   <si>
     <t xml:space="preserve">2.50819540023804</t>
   </si>
   <si>
-    <t xml:space="preserve">2.40578699111938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.1944682598114</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.2351062297821</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.29525065422058</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.27411913871765</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.35702133178711</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.3732762336731</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.29199981689453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.19284200668335</t>
+    <t xml:space="preserve">2.40578675270081</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.19446778297424</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.23510599136353</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.29525089263916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.27411890029907</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.35702085494995</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.37327647209167</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.29199957847595</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.19284248352051</t>
   </si>
   <si>
     <t xml:space="preserve">2.22535300254822</t>
   </si>
   <si>
-    <t xml:space="preserve">2.28387188911438</t>
+    <t xml:space="preserve">2.2838716506958</t>
   </si>
   <si>
     <t xml:space="preserve">2.30500364303589</t>
@@ -401,34 +401,34 @@
     <t xml:space="preserve">2.33101272583008</t>
   </si>
   <si>
-    <t xml:space="preserve">2.33588910102844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.33263778686523</t>
+    <t xml:space="preserve">2.3358895778656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.33263826370239</t>
   </si>
   <si>
     <t xml:space="preserve">2.31963396072388</t>
   </si>
   <si>
-    <t xml:space="preserve">2.38140416145325</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.53582954406738</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.54395771026611</t>
+    <t xml:space="preserve">2.38140392303467</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.5358293056488</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.54395747184753</t>
   </si>
   <si>
     <t xml:space="preserve">2.56834006309509</t>
   </si>
   <si>
-    <t xml:space="preserve">2.89669704437256</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.83817887306213</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.81216979026794</t>
+    <t xml:space="preserve">2.89669752120972</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.83817839622498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.81217002868652</t>
   </si>
   <si>
     <t xml:space="preserve">2.59597420692444</t>
@@ -437,7 +437,7 @@
     <t xml:space="preserve">2.57646799087524</t>
   </si>
   <si>
-    <t xml:space="preserve">2.57321643829346</t>
+    <t xml:space="preserve">2.57321667671204</t>
   </si>
   <si>
     <t xml:space="preserve">2.56671476364136</t>
@@ -446,61 +446,61 @@
     <t xml:space="preserve">2.53257822990417</t>
   </si>
   <si>
-    <t xml:space="preserve">2.5374550819397</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.63661241531372</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.63011026382446</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.64636564254761</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.65286803245544</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.63823795318604</t>
+    <t xml:space="preserve">2.53745460510254</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.63661217689514</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.63011074066162</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.64636516571045</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.65286779403687</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.63823819160461</t>
   </si>
   <si>
     <t xml:space="preserve">2.64148926734924</t>
   </si>
   <si>
-    <t xml:space="preserve">2.69188070297241</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.75690174102783</t>
+    <t xml:space="preserve">2.69188046455383</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.75690150260925</t>
   </si>
   <si>
     <t xml:space="preserve">2.79266357421875</t>
   </si>
   <si>
-    <t xml:space="preserve">2.76340413093567</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.73089337348938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.6544930934906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.65774416923523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.74227237701416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.76828026771545</t>
+    <t xml:space="preserve">2.76340365409851</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.7308931350708</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.65449357032776</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.65774393081665</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.742271900177</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.76828002929688</t>
   </si>
   <si>
     <t xml:space="preserve">2.70651030540466</t>
   </si>
   <si>
-    <t xml:space="preserve">2.72764229774475</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.74064636230469</t>
+    <t xml:space="preserve">2.72764253616333</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.74064683914185</t>
   </si>
   <si>
     <t xml:space="preserve">2.76990580558777</t>
@@ -509,46 +509,46 @@
     <t xml:space="preserve">2.80079126358032</t>
   </si>
   <si>
-    <t xml:space="preserve">2.69513177871704</t>
+    <t xml:space="preserve">2.69513154029846</t>
   </si>
   <si>
     <t xml:space="preserve">2.6674976348877</t>
   </si>
   <si>
-    <t xml:space="preserve">2.64799118041992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.62523341178894</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.59759974479675</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.61710596084595</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.6658718585968</t>
+    <t xml:space="preserve">2.64799094200134</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.62523365020752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.59759998321533</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.61710643768311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.66587209701538</t>
   </si>
   <si>
     <t xml:space="preserve">2.63336133956909</t>
   </si>
   <si>
-    <t xml:space="preserve">2.68862962722778</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.6024763584137</t>
+    <t xml:space="preserve">2.6886293888092</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.60247611999512</t>
   </si>
   <si>
     <t xml:space="preserve">2.677250623703</t>
   </si>
   <si>
-    <t xml:space="preserve">2.70976114273071</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.7552764415741</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.72601628303528</t>
+    <t xml:space="preserve">2.70976138114929</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.75527667999268</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.72601652145386</t>
   </si>
   <si>
     <t xml:space="preserve">2.72276568412781</t>
@@ -557,10 +557,10 @@
     <t xml:space="preserve">2.82842516899109</t>
   </si>
   <si>
-    <t xml:space="preserve">2.7438976764679</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.7617781162262</t>
+    <t xml:space="preserve">2.74389743804932</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.76177835464478</t>
   </si>
   <si>
     <t xml:space="preserve">2.73902082443237</t>
@@ -569,10 +569,10 @@
     <t xml:space="preserve">2.70488476753235</t>
   </si>
   <si>
-    <t xml:space="preserve">2.69025468826294</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.612229347229</t>
+    <t xml:space="preserve">2.6902551651001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.61222982406616</t>
   </si>
   <si>
     <t xml:space="preserve">2.73251867294312</t>
@@ -581,22 +581,22 @@
     <t xml:space="preserve">2.67562532424927</t>
   </si>
   <si>
-    <t xml:space="preserve">2.62360811233521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.59434843063354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.55371022224426</t>
+    <t xml:space="preserve">2.62360835075378</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.59434866905212</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.55371046066284</t>
   </si>
   <si>
     <t xml:space="preserve">2.55045938491821</t>
   </si>
   <si>
-    <t xml:space="preserve">2.51307201385498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.46755719184875</t>
+    <t xml:space="preserve">2.51307225227356</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.46755695343018</t>
   </si>
   <si>
     <t xml:space="preserve">2.50169348716736</t>
@@ -611,13 +611,13 @@
     <t xml:space="preserve">2.65611863136292</t>
   </si>
   <si>
-    <t xml:space="preserve">2.66912269592285</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.72439122200012</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.78291058540344</t>
+    <t xml:space="preserve">2.66912293434143</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.72439098358154</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.78291034698486</t>
   </si>
   <si>
     <t xml:space="preserve">2.77153182029724</t>
@@ -632,37 +632,37 @@
     <t xml:space="preserve">2.77315711975098</t>
   </si>
   <si>
-    <t xml:space="preserve">2.76502919197083</t>
+    <t xml:space="preserve">2.76502966880798</t>
   </si>
   <si>
     <t xml:space="preserve">2.71788907051086</t>
   </si>
   <si>
-    <t xml:space="preserve">2.74552273750305</t>
+    <t xml:space="preserve">2.74552297592163</t>
   </si>
   <si>
     <t xml:space="preserve">2.77965927124023</t>
   </si>
   <si>
-    <t xml:space="preserve">2.7471489906311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.60410165786743</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.62685942649841</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.64961624145508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.69350576400757</t>
+    <t xml:space="preserve">2.74714851379395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.60410141944885</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.62685918807983</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.64961695671082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.69350600242615</t>
   </si>
   <si>
     <t xml:space="preserve">2.69838261604309</t>
   </si>
   <si>
-    <t xml:space="preserve">2.92270565032959</t>
+    <t xml:space="preserve">2.92270612716675</t>
   </si>
   <si>
     <t xml:space="preserve">2.88531899452209</t>
@@ -671,13 +671,13 @@
     <t xml:space="preserve">2.99910593032837</t>
   </si>
   <si>
-    <t xml:space="preserve">2.97472286224365</t>
+    <t xml:space="preserve">2.97472310066223</t>
   </si>
   <si>
     <t xml:space="preserve">2.96984672546387</t>
   </si>
   <si>
-    <t xml:space="preserve">2.96334433555603</t>
+    <t xml:space="preserve">2.96334362030029</t>
   </si>
   <si>
     <t xml:space="preserve">2.94221210479736</t>
@@ -686,37 +686,37 @@
     <t xml:space="preserve">2.93408465385437</t>
   </si>
   <si>
-    <t xml:space="preserve">2.89832329750061</t>
+    <t xml:space="preserve">2.89832282066345</t>
   </si>
   <si>
     <t xml:space="preserve">2.89182114601135</t>
   </si>
   <si>
-    <t xml:space="preserve">2.87881660461426</t>
+    <t xml:space="preserve">2.87881684303284</t>
   </si>
   <si>
     <t xml:space="preserve">2.87556552886963</t>
   </si>
   <si>
-    <t xml:space="preserve">2.84468054771423</t>
+    <t xml:space="preserve">2.84468030929565</t>
   </si>
   <si>
     <t xml:space="preserve">2.82192301750183</t>
   </si>
   <si>
-    <t xml:space="preserve">2.84955739974976</t>
+    <t xml:space="preserve">2.84955716133118</t>
   </si>
   <si>
     <t xml:space="preserve">2.91945481300354</t>
   </si>
   <si>
-    <t xml:space="preserve">2.92595672607422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.9909782409668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.91457843780518</t>
+    <t xml:space="preserve">2.9259569644928</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.99097847938538</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.91457867622375</t>
   </si>
   <si>
     <t xml:space="preserve">2.91620397567749</t>
@@ -725,7 +725,7 @@
     <t xml:space="preserve">2.95846796035767</t>
   </si>
   <si>
-    <t xml:space="preserve">2.95684242248535</t>
+    <t xml:space="preserve">2.95684170722961</t>
   </si>
   <si>
     <t xml:space="preserve">2.95196557044983</t>
@@ -734,25 +734,25 @@
     <t xml:space="preserve">3.04949760437012</t>
   </si>
   <si>
-    <t xml:space="preserve">3.05599975585938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.99585485458374</t>
+    <t xml:space="preserve">3.0559995174408</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.99585509300232</t>
   </si>
   <si>
     <t xml:space="preserve">2.9795994758606</t>
   </si>
   <si>
-    <t xml:space="preserve">3.00723361968994</t>
+    <t xml:space="preserve">3.00723385810852</t>
   </si>
   <si>
     <t xml:space="preserve">3.09645938873291</t>
   </si>
   <si>
-    <t xml:space="preserve">3.11628699302673</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.16916179656982</t>
+    <t xml:space="preserve">3.11628746986389</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.1691620349884</t>
   </si>
   <si>
     <t xml:space="preserve">3.13941979408264</t>
@@ -761,25 +761,25 @@
     <t xml:space="preserve">3.14437651634216</t>
   </si>
   <si>
-    <t xml:space="preserve">3.18898916244507</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.1807279586792</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.24847340583801</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.21707916259766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.16750979423523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.1542911529541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.170814037323</t>
+    <t xml:space="preserve">3.18898940086365</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.18072748184204</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.24847316741943</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.21707963943481</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.16750931739807</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.15429067611694</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.17081427574158</t>
   </si>
   <si>
     <t xml:space="preserve">3.07663130760193</t>
@@ -788,25 +788,25 @@
     <t xml:space="preserve">3.07497882843018</t>
   </si>
   <si>
-    <t xml:space="preserve">2.98244857788086</t>
+    <t xml:space="preserve">2.98244881629944</t>
   </si>
   <si>
     <t xml:space="preserve">3.0584557056427</t>
   </si>
   <si>
-    <t xml:space="preserve">3.06506514549255</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.03367066383362</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.02540922164917</t>
+    <t xml:space="preserve">3.06506490707397</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.0336709022522</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.02540946006775</t>
   </si>
   <si>
     <t xml:space="preserve">2.99401521682739</t>
   </si>
   <si>
-    <t xml:space="preserve">2.99071025848389</t>
+    <t xml:space="preserve">2.99071049690247</t>
   </si>
   <si>
     <t xml:space="preserve">2.99897217750549</t>
@@ -815,91 +815,91 @@
     <t xml:space="preserve">2.93783617019653</t>
   </si>
   <si>
-    <t xml:space="preserve">2.95601153373718</t>
+    <t xml:space="preserve">2.95601177215576</t>
   </si>
   <si>
     <t xml:space="preserve">3.07993578910828</t>
   </si>
   <si>
-    <t xml:space="preserve">3.08819770812988</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.08654570579529</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.10802531242371</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.11133003234863</t>
+    <t xml:space="preserve">3.08819723129272</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.08654546737671</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.10802578926086</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.11133027076721</t>
   </si>
   <si>
     <t xml:space="preserve">3.14768147468567</t>
   </si>
   <si>
-    <t xml:space="preserve">3.16420483589172</t>
+    <t xml:space="preserve">3.16420459747314</t>
   </si>
   <si>
     <t xml:space="preserve">3.2055127620697</t>
   </si>
   <si>
-    <t xml:space="preserve">3.21377491950989</t>
+    <t xml:space="preserve">3.21377420425415</t>
   </si>
   <si>
     <t xml:space="preserve">3.23029804229736</t>
   </si>
   <si>
-    <t xml:space="preserve">3.23360252380371</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.25343012809753</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.29473829269409</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.30795741081238</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.27160549163818</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.29639101028442</t>
+    <t xml:space="preserve">3.23360204696655</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.25343036651611</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.29473853111267</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.30795693397522</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.27160596847534</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.29639053344727</t>
   </si>
   <si>
     <t xml:space="preserve">3.22368836402893</t>
   </si>
   <si>
-    <t xml:space="preserve">3.25012588500977</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.19394636154175</t>
+    <t xml:space="preserve">3.25012540817261</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.19394659996033</t>
   </si>
   <si>
     <t xml:space="preserve">3.26334428787231</t>
   </si>
   <si>
-    <t xml:space="preserve">3.09811186790466</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.15924787521362</t>
+    <t xml:space="preserve">3.09811162948608</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.15924763679504</t>
   </si>
   <si>
     <t xml:space="preserve">3.17246627807617</t>
   </si>
   <si>
-    <t xml:space="preserve">3.17411851882935</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.1509861946106</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.05184626579285</t>
+    <t xml:space="preserve">3.1741189956665</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.15098595619202</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.05184674263</t>
   </si>
   <si>
     <t xml:space="preserve">3.05680346488953</t>
   </si>
   <si>
-    <t xml:space="preserve">3.08489298820496</t>
+    <t xml:space="preserve">3.08489322662354</t>
   </si>
   <si>
     <t xml:space="preserve">3.12785339355469</t>
@@ -908,34 +908,34 @@
     <t xml:space="preserve">3.03201866149902</t>
   </si>
   <si>
-    <t xml:space="preserve">3.09480690956116</t>
+    <t xml:space="preserve">3.09480738639832</t>
   </si>
   <si>
     <t xml:space="preserve">3.07332682609558</t>
   </si>
   <si>
-    <t xml:space="preserve">3.09150242805481</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.13115811347961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.10967779159546</t>
+    <t xml:space="preserve">3.09150266647339</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.13115763664246</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.10967803001404</t>
   </si>
   <si>
     <t xml:space="preserve">3.10472106933594</t>
   </si>
   <si>
-    <t xml:space="preserve">3.12124466896057</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.13611483573914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.14602899551392</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.12950587272644</t>
+    <t xml:space="preserve">3.12124419212341</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.13611507415771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.14602947235107</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.12950563430786</t>
   </si>
   <si>
     <t xml:space="preserve">3.14107203483582</t>
@@ -950,40 +950,40 @@
     <t xml:space="preserve">3.10637307167053</t>
   </si>
   <si>
-    <t xml:space="preserve">3.08158826828003</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.10141634941101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.10306859016418</t>
+    <t xml:space="preserve">3.08158850669861</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.10141611099243</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.10306882858276</t>
   </si>
   <si>
     <t xml:space="preserve">3.12289643287659</t>
   </si>
   <si>
-    <t xml:space="preserve">3.08985018730164</t>
+    <t xml:space="preserve">3.08984994888306</t>
   </si>
   <si>
     <t xml:space="preserve">2.94940233230591</t>
   </si>
   <si>
-    <t xml:space="preserve">2.93287920951843</t>
+    <t xml:space="preserve">2.93287897109985</t>
   </si>
   <si>
     <t xml:space="preserve">2.83704400062561</t>
   </si>
   <si>
-    <t xml:space="preserve">2.88165664672852</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.90809392929077</t>
+    <t xml:space="preserve">2.88165688514709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.90809416770935</t>
   </si>
   <si>
     <t xml:space="preserve">2.9113986492157</t>
   </si>
   <si>
-    <t xml:space="preserve">2.9460973739624</t>
+    <t xml:space="preserve">2.94609761238098</t>
   </si>
   <si>
     <t xml:space="preserve">2.94114065170288</t>
@@ -995,28 +995,28 @@
     <t xml:space="preserve">2.88496160507202</t>
   </si>
   <si>
-    <t xml:space="preserve">2.8403491973877</t>
+    <t xml:space="preserve">2.84034872055054</t>
   </si>
   <si>
     <t xml:space="preserve">2.82878255844116</t>
   </si>
   <si>
-    <t xml:space="preserve">2.81225919723511</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.88000416755676</t>
+    <t xml:space="preserve">2.81225943565369</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.88000464439392</t>
   </si>
   <si>
     <t xml:space="preserve">2.75112295150757</t>
   </si>
   <si>
-    <t xml:space="preserve">2.8089542388916</t>
+    <t xml:space="preserve">2.80895447731018</t>
   </si>
   <si>
     <t xml:space="preserve">2.79243135452271</t>
   </si>
   <si>
-    <t xml:space="preserve">2.81391143798828</t>
+    <t xml:space="preserve">2.81391096115112</t>
   </si>
   <si>
     <t xml:space="preserve">2.85852432250977</t>
@@ -1031,19 +1031,19 @@
     <t xml:space="preserve">3.01549530029297</t>
   </si>
   <si>
-    <t xml:space="preserve">3.05515122413635</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.04028010368347</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.07002210617065</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.06341242790222</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.02375721931458</t>
+    <t xml:space="preserve">3.05515098571777</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.04028034210205</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.07002186775208</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.06341290473938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.02375674247742</t>
   </si>
   <si>
     <t xml:space="preserve">3.03697562217712</t>
@@ -1052,10 +1052,10 @@
     <t xml:space="preserve">3.02871370315552</t>
   </si>
   <si>
-    <t xml:space="preserve">3.05349898338318</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.07828378677368</t>
+    <t xml:space="preserve">3.05349922180176</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.0782835483551</t>
   </si>
   <si>
     <t xml:space="preserve">3.11050391197205</t>
@@ -1064,16 +1064,16 @@
     <t xml:space="preserve">3.06919574737549</t>
   </si>
   <si>
-    <t xml:space="preserve">3.15594291687012</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.21790528297424</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.17659687995911</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.19312024116516</t>
+    <t xml:space="preserve">3.1559431552887</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.21790504455566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.17659711837769</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.19312047958374</t>
   </si>
   <si>
     <t xml:space="preserve">3.25508260726929</t>
@@ -1082,13 +1082,13 @@
     <t xml:space="preserve">3.22203636169434</t>
   </si>
   <si>
-    <t xml:space="preserve">2.96179437637329</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.97831773757935</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.92461705207825</t>
+    <t xml:space="preserve">2.96179485321045</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.97831797599792</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.92461776733398</t>
   </si>
   <si>
     <t xml:space="preserve">2.87504744529724</t>
@@ -1097,10 +1097,10 @@
     <t xml:space="preserve">3.13528919219971</t>
   </si>
   <si>
-    <t xml:space="preserve">3.07745742797852</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.05267262458801</t>
+    <t xml:space="preserve">3.07745766639709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.05267238616943</t>
   </si>
   <si>
     <t xml:space="preserve">3.03614926338196</t>
@@ -1109,7 +1109,7 @@
     <t xml:space="preserve">2.92048645019531</t>
   </si>
   <si>
-    <t xml:space="preserve">3.08571910858154</t>
+    <t xml:space="preserve">3.08571934700012</t>
   </si>
   <si>
     <t xml:space="preserve">3.01962614059448</t>
@@ -1124,7 +1124,7 @@
     <t xml:space="preserve">3.04441070556641</t>
   </si>
   <si>
-    <t xml:space="preserve">3.15181231498718</t>
+    <t xml:space="preserve">3.1518120765686</t>
   </si>
   <si>
     <t xml:space="preserve">3.3376989364624</t>
@@ -1133,10 +1133,10 @@
     <t xml:space="preserve">3.25095200538635</t>
   </si>
   <si>
-    <t xml:space="preserve">3.2757363319397</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.2839982509613</t>
+    <t xml:space="preserve">3.27573657035828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.28399801254272</t>
   </si>
   <si>
     <t xml:space="preserve">3.24682092666626</t>
@@ -1145,7 +1145,7 @@
     <t xml:space="preserve">3.18485879898071</t>
   </si>
   <si>
-    <t xml:space="preserve">3.24373769760132</t>
+    <t xml:space="preserve">3.2437379360199</t>
   </si>
   <si>
     <t xml:space="preserve">3.20177483558655</t>
@@ -1154,31 +1154,31 @@
     <t xml:space="preserve">3.2101674079895</t>
   </si>
   <si>
-    <t xml:space="preserve">3.18918609619141</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.22275614738464</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.16400814056396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.0884747505188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.12204551696777</t>
+    <t xml:space="preserve">3.18918585777283</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.22275638580322</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.16400837898254</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.08847498893738</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.12204527854919</t>
   </si>
   <si>
     <t xml:space="preserve">3.14302682876587</t>
   </si>
   <si>
-    <t xml:space="preserve">3.20597100257874</t>
+    <t xml:space="preserve">3.20597076416016</t>
   </si>
   <si>
     <t xml:space="preserve">3.25632691383362</t>
   </si>
   <si>
-    <t xml:space="preserve">3.24793410301208</t>
+    <t xml:space="preserve">3.24793386459351</t>
   </si>
   <si>
     <t xml:space="preserve">3.10526013374329</t>
@@ -1190,9 +1190,6 @@
     <t xml:space="preserve">3.18498992919922</t>
   </si>
   <si>
-    <t xml:space="preserve">3.17659711837769</t>
-  </si>
-  <si>
     <t xml:space="preserve">3.11365246772766</t>
   </si>
   <si>
@@ -1205,16 +1202,16 @@
     <t xml:space="preserve">3.14722299575806</t>
   </si>
   <si>
-    <t xml:space="preserve">3.15561580657959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.1724009513855</t>
+    <t xml:space="preserve">3.15561556816101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.17240071296692</t>
   </si>
   <si>
     <t xml:space="preserve">3.08427858352661</t>
   </si>
   <si>
-    <t xml:space="preserve">3.13463377952576</t>
+    <t xml:space="preserve">3.13463401794434</t>
   </si>
   <si>
     <t xml:space="preserve">3.16820454597473</t>
@@ -1226,82 +1223,82 @@
     <t xml:space="preserve">3.1598117351532</t>
   </si>
   <si>
-    <t xml:space="preserve">3.19338226318359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.21436357498169</t>
+    <t xml:space="preserve">3.19338250160217</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.21436381340027</t>
   </si>
   <si>
     <t xml:space="preserve">3.23534536361694</t>
   </si>
   <si>
-    <t xml:space="preserve">3.26471948623657</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.32346749305725</t>
+    <t xml:space="preserve">3.26471924781799</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.32346725463867</t>
   </si>
   <si>
     <t xml:space="preserve">3.31087827682495</t>
   </si>
   <si>
-    <t xml:space="preserve">3.27730822563171</t>
+    <t xml:space="preserve">3.27730798721313</t>
   </si>
   <si>
     <t xml:space="preserve">3.35703778266907</t>
   </si>
   <si>
-    <t xml:space="preserve">3.42417860031128</t>
+    <t xml:space="preserve">3.4241783618927</t>
   </si>
   <si>
     <t xml:space="preserve">3.49131941795349</t>
   </si>
   <si>
-    <t xml:space="preserve">3.43257141113281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.54167461395264</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.44935655593872</t>
+    <t xml:space="preserve">3.43257188796997</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.54167509078979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.4493567943573</t>
   </si>
   <si>
     <t xml:space="preserve">3.48292684555054</t>
   </si>
   <si>
-    <t xml:space="preserve">3.51649761199951</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.474534034729</t>
+    <t xml:space="preserve">3.51649737358093</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.47453427314758</t>
   </si>
   <si>
     <t xml:space="preserve">3.4577488899231</t>
   </si>
   <si>
-    <t xml:space="preserve">3.38641166687012</t>
+    <t xml:space="preserve">3.38641214370728</t>
   </si>
   <si>
     <t xml:space="preserve">3.37801957130432</t>
   </si>
   <si>
-    <t xml:space="preserve">3.47033786773682</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.30248618125916</t>
+    <t xml:space="preserve">3.4703381061554</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.30248594284058</t>
   </si>
   <si>
     <t xml:space="preserve">3.31927132606506</t>
   </si>
   <si>
-    <t xml:space="preserve">3.29828977584839</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.34025263786316</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.27311182022095</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.28150486946106</t>
+    <t xml:space="preserve">3.29828953742981</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.34025287628174</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.27311229705811</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.28150463104248</t>
   </si>
   <si>
     <t xml:space="preserve">3.399001121521</t>
@@ -1310,31 +1307,31 @@
     <t xml:space="preserve">3.57524561882019</t>
   </si>
   <si>
-    <t xml:space="preserve">3.58783483505249</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.55006694793701</t>
+    <t xml:space="preserve">3.58783411979675</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.55006742477417</t>
   </si>
   <si>
     <t xml:space="preserve">3.5794415473938</t>
   </si>
   <si>
-    <t xml:space="preserve">3.58363747596741</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.6633677482605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.55846047401428</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.56685256958008</t>
+    <t xml:space="preserve">3.58363795280457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.66336727142334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.55845975875854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.5668523311615</t>
   </si>
   <si>
     <t xml:space="preserve">3.62140464782715</t>
   </si>
   <si>
-    <t xml:space="preserve">3.78086400032043</t>
+    <t xml:space="preserve">3.78086376190186</t>
   </si>
   <si>
     <t xml:space="preserve">3.88577127456665</t>
@@ -1343,28 +1340,28 @@
     <t xml:space="preserve">3.72211527824402</t>
   </si>
   <si>
-    <t xml:space="preserve">3.76407885551453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.68434906005859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.79764938354492</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.82702326774597</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.80184531211853</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.83961224555969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.91934204101562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.91094899177551</t>
+    <t xml:space="preserve">3.76407837867737</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.68434882164001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.79764914512634</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.82702279090881</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.80184578895569</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.83961200714111</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.91934132575989</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.91094923019409</t>
   </si>
   <si>
     <t xml:space="preserve">3.94451951980591</t>
@@ -1376,37 +1373,37 @@
     <t xml:space="preserve">4.02005290985107</t>
   </si>
   <si>
-    <t xml:space="preserve">3.92773389816284</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.86898612976074</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.8186309337616</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.86059355735779</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.793452501297</t>
+    <t xml:space="preserve">3.927734375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.86898636817932</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.81863045692444</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.86059331893921</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.79345297813416</t>
   </si>
   <si>
     <t xml:space="preserve">3.8647894859314</t>
   </si>
   <si>
-    <t xml:space="preserve">3.8773787021637</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.73470497131348</t>
+    <t xml:space="preserve">3.87737846374512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.7347047328949</t>
   </si>
   <si>
     <t xml:space="preserve">3.84380841255188</t>
   </si>
   <si>
-    <t xml:space="preserve">3.69274187088013</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.90255665779114</t>
+    <t xml:space="preserve">3.69274210929871</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.90255641937256</t>
   </si>
   <si>
     <t xml:space="preserve">3.95291233062744</t>
@@ -1415,85 +1412,85 @@
     <t xml:space="preserve">3.99067902565002</t>
   </si>
   <si>
-    <t xml:space="preserve">4.00326776504517</t>
+    <t xml:space="preserve">4.00326728820801</t>
   </si>
   <si>
     <t xml:space="preserve">3.91514539718628</t>
   </si>
   <si>
-    <t xml:space="preserve">3.87318277359009</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.85220122337341</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.66756367683411</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.67595672607422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.5920307636261</t>
+    <t xml:space="preserve">3.87318229675293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.85220098495483</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.66756391525269</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.67595648765564</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.59203028678894</t>
   </si>
   <si>
     <t xml:space="preserve">3.53328251838684</t>
   </si>
   <si>
-    <t xml:space="preserve">3.70533108711243</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.64238619804382</t>
+    <t xml:space="preserve">3.70533037185669</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.64238595962524</t>
   </si>
   <si>
     <t xml:space="preserve">3.77666783332825</t>
   </si>
   <si>
-    <t xml:space="preserve">3.71791887283325</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.64658212661743</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.70113372802734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.68015241622925</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.8060417175293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.78506064414978</t>
+    <t xml:space="preserve">3.71791958808899</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.64658188819885</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.7011342048645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.68015289306641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.80604147911072</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.78505992889404</t>
   </si>
   <si>
     <t xml:space="preserve">3.69693803787231</t>
   </si>
   <si>
-    <t xml:space="preserve">3.73050832748413</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.74729371070862</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.6507785320282</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.65917134284973</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.85639715194702</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.89416360855103</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.9361264705658</t>
+    <t xml:space="preserve">3.73050808906555</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.74729323387146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.65077829360962</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.65917181968689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.8563973903656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.89416408538818</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.93612694740295</t>
   </si>
   <si>
     <t xml:space="preserve">4.00746440887451</t>
   </si>
   <si>
-    <t xml:space="preserve">4.08719396591187</t>
+    <t xml:space="preserve">4.08719348907471</t>
   </si>
   <si>
     <t xml:space="preserve">4.11237144470215</t>
@@ -1502,13 +1499,13 @@
     <t xml:space="preserve">4.17111921310425</t>
   </si>
   <si>
-    <t xml:space="preserve">4.19629716873169</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.23826122283936</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.18790435791016</t>
+    <t xml:space="preserve">4.19629764556885</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.2382607460022</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.18790483474731</t>
   </si>
   <si>
     <t xml:space="preserve">4.09978294372559</t>
@@ -1517,7 +1514,7 @@
     <t xml:space="preserve">4.09558629989624</t>
   </si>
   <si>
-    <t xml:space="preserve">4.07880115509033</t>
+    <t xml:space="preserve">4.07880067825317</t>
   </si>
   <si>
     <t xml:space="preserve">4.14594173431396</t>
@@ -1526,10 +1523,10 @@
     <t xml:space="preserve">4.09139013290405</t>
   </si>
   <si>
-    <t xml:space="preserve">4.08299684524536</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.06201601028442</t>
+    <t xml:space="preserve">4.08299732208252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.06201648712158</t>
   </si>
   <si>
     <t xml:space="preserve">4.26343822479248</t>
@@ -1538,37 +1535,37 @@
     <t xml:space="preserve">4.39771938323975</t>
   </si>
   <si>
-    <t xml:space="preserve">4.52360820770264</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.49843072891235</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.58235692977905</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.48164558410645</t>
+    <t xml:space="preserve">4.52360773086548</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.49843120574951</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.58235645294189</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.48164510726929</t>
   </si>
   <si>
     <t xml:space="preserve">4.62431955337524</t>
   </si>
   <si>
-    <t xml:space="preserve">4.67467498779297</t>
+    <t xml:space="preserve">4.67467546463013</t>
   </si>
   <si>
     <t xml:space="preserve">4.69985294342041</t>
   </si>
   <si>
-    <t xml:space="preserve">4.6830677986145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.66628313064575</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.63271284103394</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.44807529449463</t>
+    <t xml:space="preserve">4.68306827545166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.66628217697144</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.63271236419678</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.44807577133179</t>
   </si>
   <si>
     <t xml:space="preserve">4.4396824836731</t>
@@ -1577,13 +1574,13 @@
     <t xml:space="preserve">4.47325277328491</t>
   </si>
   <si>
-    <t xml:space="preserve">4.49003791809082</t>
+    <t xml:space="preserve">4.49003839492798</t>
   </si>
   <si>
     <t xml:space="preserve">4.54878664016724</t>
   </si>
   <si>
-    <t xml:space="preserve">4.59914255142212</t>
+    <t xml:space="preserve">4.5991415977478</t>
   </si>
   <si>
     <t xml:space="preserve">4.61592674255371</t>
@@ -1595,34 +1592,34 @@
     <t xml:space="preserve">4.40611219406128</t>
   </si>
   <si>
-    <t xml:space="preserve">4.53200054168701</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.75860166549683</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.80895662307739</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.7418155670166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.69146108627319</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.65789031982422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.50682401657104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.54039430618286</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.46486043930054</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.41450500488281</t>
+    <t xml:space="preserve">4.53200101852417</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.75860118865967</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.80895709991455</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.74181604385376</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.69146013259888</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.65788984298706</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.50682353973389</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.5403938293457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.4648609161377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.41450548171997</t>
   </si>
   <si>
     <t xml:space="preserve">4.38932704925537</t>
@@ -1634,10 +1631,10 @@
     <t xml:space="preserve">4.34736394882202</t>
   </si>
   <si>
-    <t xml:space="preserve">4.46764707565308</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.51919651031494</t>
+    <t xml:space="preserve">4.46764659881592</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.5191969871521</t>
   </si>
   <si>
     <t xml:space="preserve">4.39891386032104</t>
@@ -1652,7 +1649,7 @@
     <t xml:space="preserve">4.27003908157349</t>
   </si>
   <si>
-    <t xml:space="preserve">4.33018064498901</t>
+    <t xml:space="preserve">4.33018112182617</t>
   </si>
   <si>
     <t xml:space="preserve">4.31299734115601</t>
@@ -1661,73 +1658,76 @@
     <t xml:space="preserve">4.38173055648804</t>
   </si>
   <si>
-    <t xml:space="preserve">4.44187211990356</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.45905494689941</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.35595512390137</t>
+    <t xml:space="preserve">4.34736347198486</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.44187164306641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.45905542373657</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.35595607757568</t>
   </si>
   <si>
     <t xml:space="preserve">4.39032220840454</t>
   </si>
   <si>
-    <t xml:space="preserve">4.45046377182007</t>
+    <t xml:space="preserve">4.45046329498291</t>
   </si>
   <si>
     <t xml:space="preserve">4.41609716415405</t>
   </si>
   <si>
-    <t xml:space="preserve">4.23137760162354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.26574373245239</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.13257312774658</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.04665756225586</t>
+    <t xml:space="preserve">4.23137712478638</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.26574325561523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.13257265090942</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.0466570854187</t>
   </si>
   <si>
     <t xml:space="preserve">4.08531951904297</t>
   </si>
   <si>
-    <t xml:space="preserve">3.9822199344635</t>
+    <t xml:space="preserve">3.98222041130066</t>
   </si>
   <si>
     <t xml:space="preserve">4.03376960754395</t>
   </si>
   <si>
-    <t xml:space="preserve">3.94785284996033</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.99081110954285</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.98651552200317</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.94355773925781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.96503663063049</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.96074056625366</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.01229095458984</t>
+    <t xml:space="preserve">3.94785332679749</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.99081134796143</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.98651576042175</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.94355750083923</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.96503639221191</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.96074080467224</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.01229000091553</t>
   </si>
   <si>
     <t xml:space="preserve">3.9263744354248</t>
   </si>
   <si>
-    <t xml:space="preserve">4.07243204116821</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.08961486816406</t>
+    <t xml:space="preserve">4.07243156433105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.08961534500122</t>
   </si>
   <si>
     <t xml:space="preserve">4.11109399795532</t>
@@ -1736,19 +1736,19 @@
     <t xml:space="preserve">4.26144790649414</t>
   </si>
   <si>
-    <t xml:space="preserve">4.32158851623535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.295814037323</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.02947330474854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.84045767784119</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.87482476234436</t>
+    <t xml:space="preserve">4.32158946990967</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.29581451416016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.02947378158569</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.84045815467834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.87482404708862</t>
   </si>
   <si>
     <t xml:space="preserve">3.88771200180054</t>
@@ -1757,34 +1757,34 @@
     <t xml:space="preserve">4.00369882583618</t>
   </si>
   <si>
-    <t xml:space="preserve">4.02088165283203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.93496561050415</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.86623311042786</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.77172493934631</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.71587944030762</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.70299172401428</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.67721724510193</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.68580889701843</t>
+    <t xml:space="preserve">4.02088212966919</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.93496584892273</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.86623287200928</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.77172470092773</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.71587896347046</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.70299196243286</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.67721676826477</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.68580842018127</t>
   </si>
   <si>
     <t xml:space="preserve">3.70728778839111</t>
   </si>
   <si>
-    <t xml:space="preserve">3.66432952880859</t>
+    <t xml:space="preserve">3.66432929039001</t>
   </si>
   <si>
     <t xml:space="preserve">3.66003394126892</t>
@@ -1793,55 +1793,55 @@
     <t xml:space="preserve">3.72017502784729</t>
   </si>
   <si>
-    <t xml:space="preserve">3.81468319892883</t>
+    <t xml:space="preserve">3.81468296051025</t>
   </si>
   <si>
     <t xml:space="preserve">3.95214891433716</t>
   </si>
   <si>
-    <t xml:space="preserve">3.85764122009277</t>
+    <t xml:space="preserve">3.85764050483704</t>
   </si>
   <si>
     <t xml:space="preserve">3.78461241722107</t>
   </si>
   <si>
-    <t xml:space="preserve">3.84475350379944</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.78031659126282</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.69440054893494</t>
+    <t xml:space="preserve">3.84475374221802</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.7803168296814</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.69440031051636</t>
   </si>
   <si>
     <t xml:space="preserve">3.73306202888489</t>
   </si>
   <si>
-    <t xml:space="preserve">3.71158385276794</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.59989285469055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.75454139709473</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.65144181251526</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.72447037696838</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.78890776634216</t>
+    <t xml:space="preserve">3.71158361434937</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.59989237785339</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.75454163551331</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.65144157409668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.72447085380554</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.78890800476074</t>
   </si>
   <si>
     <t xml:space="preserve">3.64714622497559</t>
   </si>
   <si>
-    <t xml:space="preserve">3.66862487792969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.67292165756226</t>
+    <t xml:space="preserve">3.66862535476685</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.67292094230652</t>
   </si>
   <si>
     <t xml:space="preserve">3.6170756816864</t>
@@ -1850,22 +1850,22 @@
     <t xml:space="preserve">3.57411742210388</t>
   </si>
   <si>
-    <t xml:space="preserve">3.64285063743591</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.65573787689209</t>
+    <t xml:space="preserve">3.64284992218018</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.65573811531067</t>
   </si>
   <si>
     <t xml:space="preserve">3.629962682724</t>
   </si>
   <si>
-    <t xml:space="preserve">3.96933221817017</t>
+    <t xml:space="preserve">3.96933197975159</t>
   </si>
   <si>
     <t xml:space="preserve">3.95644450187683</t>
   </si>
   <si>
-    <t xml:space="preserve">3.90059971809387</t>
+    <t xml:space="preserve">3.90059947967529</t>
   </si>
   <si>
     <t xml:space="preserve">3.93067002296448</t>
@@ -1877,43 +1877,43 @@
     <t xml:space="preserve">4.09820652008057</t>
   </si>
   <si>
-    <t xml:space="preserve">4.14116477966309</t>
+    <t xml:space="preserve">4.14116525650024</t>
   </si>
   <si>
     <t xml:space="preserve">4.24426460266113</t>
   </si>
   <si>
-    <t xml:space="preserve">4.24855947494507</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.43328046798706</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.42468881607056</t>
+    <t xml:space="preserve">4.24856042861938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.4332799911499</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.42468929290771</t>
   </si>
   <si>
     <t xml:space="preserve">4.58792924880981</t>
   </si>
   <si>
-    <t xml:space="preserve">4.57933807373047</t>
+    <t xml:space="preserve">4.57933759689331</t>
   </si>
   <si>
     <t xml:space="preserve">4.49342155456543</t>
   </si>
   <si>
-    <t xml:space="preserve">4.5535626411438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.48482990264893</t>
+    <t xml:space="preserve">4.55356359481812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.48482942581177</t>
   </si>
   <si>
     <t xml:space="preserve">4.53637981414795</t>
   </si>
   <si>
-    <t xml:space="preserve">4.59652090072632</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.7769455909729</t>
+    <t xml:space="preserve">4.59652137756348</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.77694511413574</t>
   </si>
   <si>
     <t xml:space="preserve">4.81131172180176</t>
@@ -1922,7 +1922,7 @@
     <t xml:space="preserve">4.69962072372437</t>
   </si>
   <si>
-    <t xml:space="preserve">4.6480712890625</t>
+    <t xml:space="preserve">4.64807081222534</t>
   </si>
   <si>
     <t xml:space="preserve">4.72539520263672</t>
@@ -1931,13 +1931,13 @@
     <t xml:space="preserve">4.71680355072021</t>
   </si>
   <si>
-    <t xml:space="preserve">4.69102954864502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.68243741989136</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.70821285247803</t>
+    <t xml:space="preserve">4.69102907180786</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.6824369430542</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.70821189880371</t>
   </si>
   <si>
     <t xml:space="preserve">4.67384576797485</t>
@@ -1958,7 +1958,7 @@
     <t xml:space="preserve">4.52778768539429</t>
   </si>
   <si>
-    <t xml:space="preserve">4.7683539390564</t>
+    <t xml:space="preserve">4.76835346221924</t>
   </si>
   <si>
     <t xml:space="preserve">4.66525411605835</t>
@@ -1973,10 +1973,10 @@
     <t xml:space="preserve">4.63947916030884</t>
   </si>
   <si>
-    <t xml:space="preserve">4.23567247390747</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.15834808349609</t>
+    <t xml:space="preserve">4.23567295074463</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.15834856033325</t>
   </si>
   <si>
     <t xml:space="preserve">4.20130586624146</t>
@@ -1991,7 +1991,7 @@
     <t xml:space="preserve">4.11538982391357</t>
   </si>
   <si>
-    <t xml:space="preserve">3.75024580955505</t>
+    <t xml:space="preserve">3.75024557113647</t>
   </si>
   <si>
     <t xml:space="preserve">3.47101783752441</t>
@@ -2003,34 +2003,34 @@
     <t xml:space="preserve">3.31207275390625</t>
   </si>
   <si>
-    <t xml:space="preserve">3.16601514816284</t>
+    <t xml:space="preserve">3.16601490974426</t>
   </si>
   <si>
     <t xml:space="preserve">3.22186064720154</t>
   </si>
   <si>
-    <t xml:space="preserve">2.80516672134399</t>
+    <t xml:space="preserve">2.80516695976257</t>
   </si>
   <si>
     <t xml:space="preserve">2.91685771942139</t>
   </si>
   <si>
-    <t xml:space="preserve">2.86530804634094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.88678693771362</t>
+    <t xml:space="preserve">2.86530828475952</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.8867871761322</t>
   </si>
   <si>
     <t xml:space="preserve">2.73213791847229</t>
   </si>
   <si>
-    <t xml:space="preserve">2.66770052909851</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.80087065696716</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.61185479164124</t>
+    <t xml:space="preserve">2.66770029067993</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.80087089538574</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.61185503005981</t>
   </si>
   <si>
     <t xml:space="preserve">2.72354626655579</t>
@@ -2042,25 +2042,25 @@
     <t xml:space="preserve">2.8137583732605</t>
   </si>
   <si>
-    <t xml:space="preserve">2.70206713676453</t>
+    <t xml:space="preserve">2.70206689834595</t>
   </si>
   <si>
     <t xml:space="preserve">2.65910911560059</t>
   </si>
   <si>
-    <t xml:space="preserve">2.8438286781311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.76650452613831</t>
+    <t xml:space="preserve">2.84382915496826</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.76650428771973</t>
   </si>
   <si>
     <t xml:space="preserve">2.78798317909241</t>
   </si>
   <si>
-    <t xml:space="preserve">2.70636296272278</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.71065855026245</t>
+    <t xml:space="preserve">2.70636320114136</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.71065878868103</t>
   </si>
   <si>
     <t xml:space="preserve">2.85242080688477</t>
@@ -2075,7 +2075,7 @@
     <t xml:space="preserve">3.0070698261261</t>
   </si>
   <si>
-    <t xml:space="preserve">2.96411204338074</t>
+    <t xml:space="preserve">2.96411180496216</t>
   </si>
   <si>
     <t xml:space="preserve">2.93833684921265</t>
@@ -2084,34 +2084,34 @@
     <t xml:space="preserve">2.9426326751709</t>
   </si>
   <si>
-    <t xml:space="preserve">2.98129534721375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.01136565208435</t>
+    <t xml:space="preserve">2.98129510879517</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.01136589050293</t>
   </si>
   <si>
     <t xml:space="preserve">2.94692873954773</t>
   </si>
   <si>
-    <t xml:space="preserve">2.97699952125549</t>
+    <t xml:space="preserve">2.97699904441833</t>
   </si>
   <si>
     <t xml:space="preserve">2.9512243270874</t>
   </si>
   <si>
-    <t xml:space="preserve">3.10587358474731</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.04143619537354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.0500283241272</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.08439469337463</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.13164854049683</t>
+    <t xml:space="preserve">3.10587382316589</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.04143643379211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.05002784729004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.08439445495605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.13164877891541</t>
   </si>
   <si>
     <t xml:space="preserve">3.03284478187561</t>
@@ -2123,7 +2123,7 @@
     <t xml:space="preserve">3.19178986549377</t>
   </si>
   <si>
-    <t xml:space="preserve">3.24763560295105</t>
+    <t xml:space="preserve">3.24763536453247</t>
   </si>
   <si>
     <t xml:space="preserve">3.16171932220459</t>
@@ -2135,7 +2135,7 @@
     <t xml:space="preserve">3.18319845199585</t>
   </si>
   <si>
-    <t xml:space="preserve">3.13594436645508</t>
+    <t xml:space="preserve">3.13594460487366</t>
   </si>
   <si>
     <t xml:space="preserve">3.11876106262207</t>
@@ -2153,64 +2153,64 @@
     <t xml:space="preserve">3.48390531539917</t>
   </si>
   <si>
-    <t xml:space="preserve">3.46242642402649</t>
+    <t xml:space="preserve">3.46242666244507</t>
   </si>
   <si>
     <t xml:space="preserve">3.4796097278595</t>
   </si>
   <si>
-    <t xml:space="preserve">3.3163685798645</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.29488968849182</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.19608592987061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.38080596923828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.37651014328003</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.35073494911194</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.3722140789032</t>
+    <t xml:space="preserve">3.31636834144592</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.29488945007324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.19608569145203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.3808057308197</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.37650966644287</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.3507354259491</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.37221431732178</t>
   </si>
   <si>
     <t xml:space="preserve">3.42805981636047</t>
   </si>
   <si>
-    <t xml:space="preserve">3.44094729423523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.44524312019348</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.75857472419739</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.71435594558716</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.63034129142761</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.58170104026794</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.51979470252991</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.50210738182068</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.43135786056519</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.44904494285583</t>
+    <t xml:space="preserve">3.44094753265381</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.44524335861206</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.75857424736023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.71435618400574</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.63034105300903</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.58170080184937</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.51979494094849</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.5021071434021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.43135762214661</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.44904541969299</t>
   </si>
   <si>
     <t xml:space="preserve">3.36060786247253</t>
@@ -2219,7 +2219,7 @@
     <t xml:space="preserve">3.38713908195496</t>
   </si>
   <si>
-    <t xml:space="preserve">3.41809225082397</t>
+    <t xml:space="preserve">3.4180920124054</t>
   </si>
   <si>
     <t xml:space="preserve">3.32081151008606</t>
@@ -2231,7 +2231,7 @@
     <t xml:space="preserve">3.31638956069946</t>
   </si>
   <si>
-    <t xml:space="preserve">3.27217125892639</t>
+    <t xml:space="preserve">3.27217102050781</t>
   </si>
   <si>
     <t xml:space="preserve">3.28101444244385</t>
@@ -2243,7 +2243,7 @@
     <t xml:space="preserve">3.09529662132263</t>
   </si>
   <si>
-    <t xml:space="preserve">3.18373394012451</t>
+    <t xml:space="preserve">3.18373370170593</t>
   </si>
   <si>
     <t xml:space="preserve">3.25448369979858</t>
@@ -2252,10 +2252,10 @@
     <t xml:space="preserve">3.20584321022034</t>
   </si>
   <si>
-    <t xml:space="preserve">3.1660463809967</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.15720224380493</t>
+    <t xml:space="preserve">3.16604614257812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.15720272064209</t>
   </si>
   <si>
     <t xml:space="preserve">3.13951516151428</t>
@@ -2264,13 +2264,13 @@
     <t xml:space="preserve">3.10414052009583</t>
   </si>
   <si>
-    <t xml:space="preserve">3.09971857070923</t>
+    <t xml:space="preserve">3.09971880912781</t>
   </si>
   <si>
     <t xml:space="preserve">3.04223465919495</t>
   </si>
   <si>
-    <t xml:space="preserve">3.04665660858154</t>
+    <t xml:space="preserve">3.04665613174438</t>
   </si>
   <si>
     <t xml:space="preserve">3.0776093006134</t>
@@ -2288,22 +2288,22 @@
     <t xml:space="preserve">2.94495368003845</t>
   </si>
   <si>
-    <t xml:space="preserve">2.93611001968384</t>
+    <t xml:space="preserve">2.93611025810242</t>
   </si>
   <si>
     <t xml:space="preserve">3.09087491035461</t>
   </si>
   <si>
-    <t xml:space="preserve">3.06876611709595</t>
+    <t xml:space="preserve">3.06876587867737</t>
   </si>
   <si>
     <t xml:space="preserve">3.05550003051758</t>
   </si>
   <si>
-    <t xml:space="preserve">2.98475074768066</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.9051570892334</t>
+    <t xml:space="preserve">2.98475050926208</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.90515756607056</t>
   </si>
   <si>
     <t xml:space="preserve">2.83440756797791</t>
@@ -2312,31 +2312,31 @@
     <t xml:space="preserve">2.86978220939636</t>
   </si>
   <si>
-    <t xml:space="preserve">2.80345439910889</t>
+    <t xml:space="preserve">2.80345463752747</t>
   </si>
   <si>
     <t xml:space="preserve">2.77692341804504</t>
   </si>
   <si>
-    <t xml:space="preserve">2.81229853630066</t>
+    <t xml:space="preserve">2.81229829788208</t>
   </si>
   <si>
     <t xml:space="preserve">2.84767293930054</t>
   </si>
   <si>
-    <t xml:space="preserve">2.82998585700989</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.79461121559143</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.91842269897461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.82114219665527</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.79903268814087</t>
+    <t xml:space="preserve">2.82998561859131</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.79461073875427</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.91842293739319</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.82114171981812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.79903244972229</t>
   </si>
   <si>
     <t xml:space="preserve">2.80787634849548</t>
@@ -2354,22 +2354,22 @@
     <t xml:space="preserve">2.68406462669373</t>
   </si>
   <si>
-    <t xml:space="preserve">2.63542437553406</t>
+    <t xml:space="preserve">2.63542413711548</t>
   </si>
   <si>
     <t xml:space="preserve">2.61773681640625</t>
   </si>
   <si>
-    <t xml:space="preserve">2.58236193656921</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.54698705673218</t>
+    <t xml:space="preserve">2.58236217498779</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.54698729515076</t>
   </si>
   <si>
     <t xml:space="preserve">2.56467461585999</t>
   </si>
   <si>
-    <t xml:space="preserve">2.5514087677002</t>
+    <t xml:space="preserve">2.55140900611877</t>
   </si>
   <si>
     <t xml:space="preserve">2.49392461776733</t>
@@ -2378,22 +2378,22 @@
     <t xml:space="preserve">2.5735182762146</t>
   </si>
   <si>
-    <t xml:space="preserve">2.97148466110229</t>
+    <t xml:space="preserve">2.97148489952087</t>
   </si>
   <si>
     <t xml:space="preserve">2.95379734039307</t>
   </si>
   <si>
-    <t xml:space="preserve">3.00243806838989</t>
+    <t xml:space="preserve">3.00243782997131</t>
   </si>
   <si>
     <t xml:space="preserve">3.17931199073792</t>
   </si>
   <si>
-    <t xml:space="preserve">3.17046856880188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.19257783889771</t>
+    <t xml:space="preserve">3.1704683303833</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.19257760047913</t>
   </si>
   <si>
     <t xml:space="preserve">3.28985834121704</t>
@@ -2402,13 +2402,13 @@
     <t xml:space="preserve">3.29870223999023</t>
   </si>
   <si>
-    <t xml:space="preserve">3.47999811172485</t>
+    <t xml:space="preserve">3.47999787330627</t>
   </si>
   <si>
     <t xml:space="preserve">3.4136700630188</t>
   </si>
   <si>
-    <t xml:space="preserve">3.48442006111145</t>
+    <t xml:space="preserve">3.48441982269287</t>
   </si>
   <si>
     <t xml:space="preserve">3.45788884162903</t>
@@ -2420,13 +2420,13 @@
     <t xml:space="preserve">3.51095080375671</t>
   </si>
   <si>
-    <t xml:space="preserve">3.44462323188782</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.42693567276001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.55516910552979</t>
+    <t xml:space="preserve">3.44462299346924</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.42693591117859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.55516934394836</t>
   </si>
   <si>
     <t xml:space="preserve">3.6789813041687</t>
@@ -2435,25 +2435,25 @@
     <t xml:space="preserve">3.72320008277893</t>
   </si>
   <si>
-    <t xml:space="preserve">3.74973082542419</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.80279350280762</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.65687203407288</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.66129422187805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.65245056152344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.62591910362244</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.60823178291321</t>
+    <t xml:space="preserve">3.74973058700562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.80279326438904</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.65687227249146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.66129398345947</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.65245032310486</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.62591886520386</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.60823154449463</t>
   </si>
   <si>
     <t xml:space="preserve">3.54632616043091</t>
@@ -2465,10 +2465,10 @@
     <t xml:space="preserve">3.57285690307617</t>
   </si>
   <si>
-    <t xml:space="preserve">3.5065290927887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.59054446220398</t>
+    <t xml:space="preserve">3.50652885437012</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.59054470062256</t>
   </si>
   <si>
     <t xml:space="preserve">3.57727885246277</t>
@@ -2477,7 +2477,7 @@
     <t xml:space="preserve">3.74530911445618</t>
   </si>
   <si>
-    <t xml:space="preserve">3.74088764190674</t>
+    <t xml:space="preserve">3.74088716506958</t>
   </si>
   <si>
     <t xml:space="preserve">3.73204374313354</t>
@@ -2486,58 +2486,61 @@
     <t xml:space="preserve">3.70551252365112</t>
   </si>
   <si>
-    <t xml:space="preserve">3.77626252174377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.83816838264465</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.68340301513672</t>
+    <t xml:space="preserve">3.7762622833252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.83816814422607</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.68340349197388</t>
   </si>
   <si>
     <t xml:space="preserve">3.76741862297058</t>
   </si>
   <si>
-    <t xml:space="preserve">3.78068399429321</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.76299667358398</t>
+    <t xml:space="preserve">3.78068375587463</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.76299691200256</t>
   </si>
   <si>
     <t xml:space="preserve">3.77184009552002</t>
   </si>
   <si>
-    <t xml:space="preserve">3.71877813339233</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.68782544136047</t>
+    <t xml:space="preserve">3.71877789497375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.68782496452332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.61707592010498</t>
   </si>
   <si>
     <t xml:space="preserve">3.59938812255859</t>
   </si>
   <si>
-    <t xml:space="preserve">3.66571569442749</t>
+    <t xml:space="preserve">3.66571545600891</t>
   </si>
   <si>
     <t xml:space="preserve">3.70993447303772</t>
   </si>
   <si>
-    <t xml:space="preserve">3.78510642051697</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.92660522460938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.93987083435059</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.99735474586487</t>
+    <t xml:space="preserve">3.78510570526123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.9266049861908</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.93987035751343</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.99735498428345</t>
   </si>
   <si>
     <t xml:space="preserve">4.01079893112183</t>
   </si>
   <si>
-    <t xml:space="preserve">4.09594392776489</t>
+    <t xml:space="preserve">4.09594440460205</t>
   </si>
   <si>
     <t xml:space="preserve">4.17212724685669</t>
@@ -2546,16 +2549,16 @@
     <t xml:space="preserve">4.16316413879395</t>
   </si>
   <si>
-    <t xml:space="preserve">4.13627576828003</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.19901466369629</t>
+    <t xml:space="preserve">4.13627624511719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.19901514053345</t>
   </si>
   <si>
     <t xml:space="preserve">4.14075756072998</t>
   </si>
   <si>
-    <t xml:space="preserve">4.10490655899048</t>
+    <t xml:space="preserve">4.10490703582764</t>
   </si>
   <si>
     <t xml:space="preserve">4.06905603408813</t>
@@ -2564,13 +2567,13 @@
     <t xml:space="preserve">4.03320550918579</t>
   </si>
   <si>
-    <t xml:space="preserve">3.9794294834137</t>
+    <t xml:space="preserve">3.97942924499512</t>
   </si>
   <si>
     <t xml:space="preserve">4.02872371673584</t>
   </si>
   <si>
-    <t xml:space="preserve">4.05561208724976</t>
+    <t xml:space="preserve">4.05561256408691</t>
   </si>
   <si>
     <t xml:space="preserve">4.08698177337646</t>
@@ -2585,16 +2588,16 @@
     <t xml:space="preserve">4.01528024673462</t>
   </si>
   <si>
-    <t xml:space="preserve">3.96150398254395</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.98839211463928</t>
+    <t xml:space="preserve">3.9615044593811</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.9883918762207</t>
   </si>
   <si>
     <t xml:space="preserve">3.95254135131836</t>
   </si>
   <si>
-    <t xml:space="preserve">3.96598529815674</t>
+    <t xml:space="preserve">3.9659857749939</t>
   </si>
   <si>
     <t xml:space="preserve">4.04216861724854</t>
@@ -2612,85 +2615,82 @@
     <t xml:space="preserve">4.11386966705322</t>
   </si>
   <si>
-    <t xml:space="preserve">4.10938787460327</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.06009340286255</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.1945333480835</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.21245861053467</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.14972019195557</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.12283182144165</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.03768634796143</t>
+    <t xml:space="preserve">4.10938835144043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.06009387969971</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.19453382492065</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.21245908737183</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.14972066879272</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.12283229827881</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.03768682479858</t>
   </si>
   <si>
     <t xml:space="preserve">4.01976156234741</t>
   </si>
   <si>
-    <t xml:space="preserve">4.06457471847534</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.20797729492188</t>
+    <t xml:space="preserve">4.0645751953125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.20797777175903</t>
   </si>
   <si>
     <t xml:space="preserve">4.230384349823</t>
   </si>
   <si>
-    <t xml:space="preserve">4.25727224349976</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.20349645614624</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.92565321922302</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.90772795677185</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.88083982467651</t>
+    <t xml:space="preserve">4.2572717666626</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.2034969329834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.9256534576416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.90772819519043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.88083934783936</t>
   </si>
   <si>
     <t xml:space="preserve">3.87635850906372</t>
   </si>
   <si>
-    <t xml:space="preserve">3.80913853645325</t>
+    <t xml:space="preserve">3.80913829803467</t>
   </si>
   <si>
     <t xml:space="preserve">3.71503019332886</t>
   </si>
   <si>
-    <t xml:space="preserve">3.66573596000671</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.83154487609863</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.93461537361145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.99735522270203</t>
+    <t xml:space="preserve">3.66573572158813</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.83154511451721</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.93461561203003</t>
   </si>
   <si>
     <t xml:space="preserve">3.94357872009277</t>
   </si>
   <si>
-    <t xml:space="preserve">4.04664897918701</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.99287295341492</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.98391079902649</t>
+    <t xml:space="preserve">4.04664945602417</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.9928731918335</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.98391056060791</t>
   </si>
   <si>
     <t xml:space="preserve">4.02424240112305</t>
@@ -2699,7 +2699,7 @@
     <t xml:space="preserve">3.85395193099976</t>
   </si>
   <si>
-    <t xml:space="preserve">3.93013501167297</t>
+    <t xml:space="preserve">3.93013477325439</t>
   </si>
   <si>
     <t xml:space="preserve">3.97046661376953</t>
@@ -2708,7 +2708,7 @@
     <t xml:space="preserve">4.10042572021484</t>
   </si>
   <si>
-    <t xml:space="preserve">4.15420150756836</t>
+    <t xml:space="preserve">4.15420198440552</t>
   </si>
   <si>
     <t xml:space="preserve">4.09146308898926</t>
@@ -2723,7 +2723,7 @@
     <t xml:space="preserve">4.24382829666138</t>
   </si>
   <si>
-    <t xml:space="preserve">4.13179445266724</t>
+    <t xml:space="preserve">4.13179492950439</t>
   </si>
   <si>
     <t xml:space="preserve">4.1273136138916</t>
@@ -2732,7 +2732,7 @@
     <t xml:space="preserve">4.24830961227417</t>
   </si>
   <si>
-    <t xml:space="preserve">4.19005250930786</t>
+    <t xml:space="preserve">4.19005298614502</t>
   </si>
   <si>
     <t xml:space="preserve">4.29312324523926</t>
@@ -2744,10 +2744,10 @@
     <t xml:space="preserve">4.43652582168579</t>
   </si>
   <si>
-    <t xml:space="preserve">4.48133897781372</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.53511571884155</t>
+    <t xml:space="preserve">4.48133945465088</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.53511524200439</t>
   </si>
   <si>
     <t xml:space="preserve">4.55304050445557</t>
@@ -2765,7 +2765,7 @@
     <t xml:space="preserve">4.43204498291016</t>
   </si>
   <si>
-    <t xml:space="preserve">4.49926424026489</t>
+    <t xml:space="preserve">4.49926471710205</t>
   </si>
   <si>
     <t xml:space="preserve">4.49030208587646</t>
@@ -2783,25 +2783,25 @@
     <t xml:space="preserve">4.47685813903809</t>
   </si>
   <si>
-    <t xml:space="preserve">4.57096576690674</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.61577939987183</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.64266681671143</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.39171266555786</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.44997024536133</t>
+    <t xml:space="preserve">4.5709662437439</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.61577987670898</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.64266729354858</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.3917121887207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.44996976852417</t>
   </si>
   <si>
     <t xml:space="preserve">4.27519750595093</t>
   </si>
   <si>
-    <t xml:space="preserve">4.58889198303223</t>
+    <t xml:space="preserve">4.58889150619507</t>
   </si>
   <si>
     <t xml:space="preserve">4.66059303283691</t>
@@ -2810,10 +2810,10 @@
     <t xml:space="preserve">4.65163040161133</t>
   </si>
   <si>
-    <t xml:space="preserve">4.71436882019043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.75918245315552</t>
+    <t xml:space="preserve">4.71436977386475</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.75918292999268</t>
   </si>
   <si>
     <t xml:space="preserve">4.7681450843811</t>
@@ -2822,25 +2822,25 @@
     <t xml:space="preserve">4.89362287521362</t>
   </si>
   <si>
-    <t xml:space="preserve">4.92051029205322</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.88465976715088</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.05495023727417</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.01909971237183</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.14457702636719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.31486845016479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.37760734558105</t>
+    <t xml:space="preserve">4.92051076889038</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.88466024398804</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.05495071411133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.01910018920898</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.14457750320435</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.31486797332764</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.3776068687439</t>
   </si>
   <si>
     <t xml:space="preserve">5.35968160629272</t>
@@ -2849,58 +2849,58 @@
     <t xml:space="preserve">5.16250324249268</t>
   </si>
   <si>
-    <t xml:space="preserve">5.04598808288574</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.15354061126709</t>
+    <t xml:space="preserve">5.0459885597229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.15354013442993</t>
   </si>
   <si>
     <t xml:space="preserve">5.26109218597412</t>
   </si>
   <si>
-    <t xml:space="preserve">5.27901744842529</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.51204776763916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.47619676589966</t>
+    <t xml:space="preserve">5.27901697158813</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.512047290802</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.4761962890625</t>
   </si>
   <si>
     <t xml:space="preserve">5.50308465957642</t>
   </si>
   <si>
-    <t xml:space="preserve">5.29694366455078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.19835376739502</t>
+    <t xml:space="preserve">5.29694271087646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.19835329055786</t>
   </si>
   <si>
     <t xml:space="preserve">5.18042802810669</t>
   </si>
   <si>
-    <t xml:space="preserve">5.07287549972534</t>
+    <t xml:space="preserve">5.07287645339966</t>
   </si>
   <si>
     <t xml:space="preserve">5.09080171585083</t>
   </si>
   <si>
-    <t xml:space="preserve">4.99221181869507</t>
+    <t xml:space="preserve">4.99221277236938</t>
   </si>
   <si>
     <t xml:space="preserve">4.75022029876709</t>
   </si>
   <si>
-    <t xml:space="preserve">4.80399560928345</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.92947292327881</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.83984661102295</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.9742865562439</t>
+    <t xml:space="preserve">4.80399608612061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.92947340011597</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.83984708786011</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.97428703308105</t>
   </si>
   <si>
     <t xml:space="preserve">4.90258502960205</t>
@@ -2909,7 +2909,7 @@
     <t xml:space="preserve">4.86673450469971</t>
   </si>
   <si>
-    <t xml:space="preserve">5.03702545166016</t>
+    <t xml:space="preserve">5.03702592849731</t>
   </si>
   <si>
     <t xml:space="preserve">4.95636177062988</t>
@@ -2921,22 +2921,22 @@
     <t xml:space="preserve">4.74125719070435</t>
   </si>
   <si>
-    <t xml:space="preserve">4.70540618896484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.52615261077881</t>
+    <t xml:space="preserve">4.705406665802</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.52615308761597</t>
   </si>
   <si>
     <t xml:space="preserve">4.41860055923462</t>
   </si>
   <si>
-    <t xml:space="preserve">4.3648247718811</t>
+    <t xml:space="preserve">4.36482429504395</t>
   </si>
   <si>
     <t xml:space="preserve">4.23934698104858</t>
   </si>
   <si>
-    <t xml:space="preserve">4.85777139663696</t>
+    <t xml:space="preserve">4.85777187347412</t>
   </si>
   <si>
     <t xml:space="preserve">4.91154813766479</t>
@@ -2948,28 +2948,28 @@
     <t xml:space="preserve">5.11768960952759</t>
   </si>
   <si>
-    <t xml:space="preserve">5.22524166107178</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.30590581893921</t>
+    <t xml:space="preserve">5.22524118423462</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.30590534210205</t>
   </si>
   <si>
     <t xml:space="preserve">5.42242050170898</t>
   </si>
   <si>
-    <t xml:space="preserve">5.28798055648804</t>
+    <t xml:space="preserve">5.28798007965088</t>
   </si>
   <si>
     <t xml:space="preserve">5.43138265609741</t>
   </si>
   <si>
-    <t xml:space="preserve">5.55686044692993</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.62856197357178</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.52100992202759</t>
+    <t xml:space="preserve">5.55685997009277</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.62856245040894</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.52100944519043</t>
   </si>
   <si>
     <t xml:space="preserve">5.61959934234619</t>
@@ -2987,10 +2987,10 @@
     <t xml:space="preserve">5.46581411361694</t>
   </si>
   <si>
-    <t xml:space="preserve">5.48409414291382</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.63947725296021</t>
+    <t xml:space="preserve">5.48409461975098</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.63947677612305</t>
   </si>
   <si>
     <t xml:space="preserve">5.75829935073853</t>
@@ -3008,28 +3008,28 @@
     <t xml:space="preserve">5.410973072052</t>
   </si>
   <si>
-    <t xml:space="preserve">5.40183305740356</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.63033628463745</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.61205673217773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.8222804069519</t>
+    <t xml:space="preserve">5.40183258056641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.63033676147461</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.61205625534058</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.82227993011475</t>
   </si>
   <si>
     <t xml:space="preserve">5.84056043624878</t>
   </si>
   <si>
-    <t xml:space="preserve">5.88626146316528</t>
+    <t xml:space="preserve">5.88626098632812</t>
   </si>
   <si>
     <t xml:space="preserve">5.93196201324463</t>
   </si>
   <si>
-    <t xml:space="preserve">5.90454196929932</t>
+    <t xml:space="preserve">5.90454149246216</t>
   </si>
   <si>
     <t xml:space="preserve">5.97766304016113</t>
@@ -3038,7 +3038,7 @@
     <t xml:space="preserve">5.9593825340271</t>
   </si>
   <si>
-    <t xml:space="preserve">6.04164361953735</t>
+    <t xml:space="preserve">6.04164409637451</t>
   </si>
   <si>
     <t xml:space="preserve">5.87712097167969</t>
@@ -3047,10 +3047,10 @@
     <t xml:space="preserve">6.07820463180542</t>
   </si>
   <si>
-    <t xml:space="preserve">5.91368198394775</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.68517780303955</t>
+    <t xml:space="preserve">5.91368103027344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.68517732620239</t>
   </si>
   <si>
     <t xml:space="preserve">5.785719871521</t>
@@ -3059,16 +3059,16 @@
     <t xml:space="preserve">5.7308783531189</t>
   </si>
   <si>
-    <t xml:space="preserve">5.67603778839111</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.69431829452515</t>
+    <t xml:space="preserve">5.67603731155396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.69431781768799</t>
   </si>
   <si>
     <t xml:space="preserve">5.66689729690552</t>
   </si>
   <si>
-    <t xml:space="preserve">5.42925357818604</t>
+    <t xml:space="preserve">5.42925310134888</t>
   </si>
   <si>
     <t xml:space="preserve">5.42011308670044</t>
@@ -3077,7 +3077,7 @@
     <t xml:space="preserve">5.33785200119019</t>
   </si>
   <si>
-    <t xml:space="preserve">5.20988988876343</t>
+    <t xml:space="preserve">5.20988941192627</t>
   </si>
   <si>
     <t xml:space="preserve">5.34699201583862</t>
@@ -3089,7 +3089,7 @@
     <t xml:space="preserve">5.39269304275513</t>
   </si>
   <si>
-    <t xml:space="preserve">5.3652720451355</t>
+    <t xml:space="preserve">5.36527252197266</t>
   </si>
   <si>
     <t xml:space="preserve">5.2830114364624</t>
@@ -3101,43 +3101,43 @@
     <t xml:space="preserve">5.21902942657471</t>
   </si>
   <si>
-    <t xml:space="preserve">5.15504884719849</t>
+    <t xml:space="preserve">5.15504837036133</t>
   </si>
   <si>
     <t xml:space="preserve">5.10020780563354</t>
   </si>
   <si>
-    <t xml:space="preserve">5.10934829711914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.08192777633667</t>
+    <t xml:space="preserve">5.10934782028198</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.08192729949951</t>
   </si>
   <si>
     <t xml:space="preserve">5.03622674942017</t>
   </si>
   <si>
-    <t xml:space="preserve">5.01794576644897</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.11848783493042</t>
+    <t xml:space="preserve">5.01794624328613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.11848831176758</t>
   </si>
   <si>
     <t xml:space="preserve">5.13676834106445</t>
   </si>
   <si>
-    <t xml:space="preserve">5.07278728485107</t>
+    <t xml:space="preserve">5.07278776168823</t>
   </si>
   <si>
     <t xml:space="preserve">5.02708625793457</t>
   </si>
   <si>
-    <t xml:space="preserve">5.0453667640686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.99052619934082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.00880670547485</t>
+    <t xml:space="preserve">5.04536724090576</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.99052572250366</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.00880575180054</t>
   </si>
   <si>
     <t xml:space="preserve">5.0545072555542</t>
@@ -3149,7 +3149,7 @@
     <t xml:space="preserve">5.16418886184692</t>
   </si>
   <si>
-    <t xml:space="preserve">5.14590835571289</t>
+    <t xml:space="preserve">5.14590883255005</t>
   </si>
   <si>
     <t xml:space="preserve">4.94482469558716</t>
@@ -3158,16 +3158,16 @@
     <t xml:space="preserve">4.93568515777588</t>
   </si>
   <si>
-    <t xml:space="preserve">4.89912462234497</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.88084411621094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.85342311859131</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.826003074646</t>
+    <t xml:space="preserve">4.89912414550781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.8808445930481</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.85342359542847</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.82600355148315</t>
   </si>
   <si>
     <t xml:space="preserve">4.73460102081299</t>
@@ -3194,16 +3194,16 @@
     <t xml:space="preserve">4.80772304534912</t>
   </si>
   <si>
-    <t xml:space="preserve">4.57007884979248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.72546100616455</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.6889009475708</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.67062091827393</t>
+    <t xml:space="preserve">4.57007837295532</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.72546148300171</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.68890047073364</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.67062044143677</t>
   </si>
   <si>
     <t xml:space="preserve">4.6431999206543</t>
@@ -3215,16 +3215,16 @@
     <t xml:space="preserve">4.56093835830688</t>
   </si>
   <si>
-    <t xml:space="preserve">4.58835887908936</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.55179834365845</t>
+    <t xml:space="preserve">4.58835935592651</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.55179786682129</t>
   </si>
   <si>
     <t xml:space="preserve">4.48781728744507</t>
   </si>
   <si>
-    <t xml:space="preserve">4.53808832168579</t>
+    <t xml:space="preserve">4.53808784484863</t>
   </si>
   <si>
     <t xml:space="preserve">4.46953678131104</t>
@@ -3233,10 +3233,10 @@
     <t xml:space="preserve">4.50152778625488</t>
   </si>
   <si>
-    <t xml:space="preserve">4.49695777893066</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.40555572509766</t>
+    <t xml:space="preserve">4.49695730209351</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.40555620193481</t>
   </si>
   <si>
     <t xml:space="preserve">4.43297624588013</t>
@@ -3248,7 +3248,7 @@
     <t xml:space="preserve">4.36899518966675</t>
   </si>
   <si>
-    <t xml:space="preserve">4.29130363464355</t>
+    <t xml:space="preserve">4.29130411148071</t>
   </si>
   <si>
     <t xml:space="preserve">4.20447206497192</t>
@@ -3266,7 +3266,7 @@
     <t xml:space="preserve">4.87170362472534</t>
   </si>
   <si>
-    <t xml:space="preserve">4.83514308929443</t>
+    <t xml:space="preserve">4.83514356613159</t>
   </si>
   <si>
     <t xml:space="preserve">5.17332887649536</t>
@@ -3275,10 +3275,10 @@
     <t xml:space="preserve">5.32871150970459</t>
   </si>
   <si>
-    <t xml:space="preserve">5.19160938262939</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.25559043884277</t>
+    <t xml:space="preserve">5.19160890579224</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.25559091567993</t>
   </si>
   <si>
     <t xml:space="preserve">5.38355255126953</t>
@@ -3302,10 +3302,10 @@
     <t xml:space="preserve">5.09106779098511</t>
   </si>
   <si>
-    <t xml:space="preserve">4.98138570785522</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.92654418945312</t>
+    <t xml:space="preserve">4.98138523101807</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.92654466629028</t>
   </si>
   <si>
     <t xml:space="preserve">5.06364727020264</t>
@@ -3314,7 +3314,7 @@
     <t xml:space="preserve">5.30129146575928</t>
   </si>
   <si>
-    <t xml:space="preserve">5.20074987411499</t>
+    <t xml:space="preserve">5.20074939727783</t>
   </si>
   <si>
     <t xml:space="preserve">5.12762832641602</t>
@@ -3326,10 +3326,10 @@
     <t xml:space="preserve">5.27387094497681</t>
   </si>
   <si>
-    <t xml:space="preserve">5.31957149505615</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.27241277694702</t>
+    <t xml:space="preserve">5.31957197189331</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.27241230010986</t>
   </si>
   <si>
     <t xml:space="preserve">5.23468494415283</t>
@@ -3341,13 +3341,13 @@
     <t xml:space="preserve">5.02718353271484</t>
   </si>
   <si>
-    <t xml:space="preserve">4.99888849258423</t>
+    <t xml:space="preserve">4.99888801574707</t>
   </si>
   <si>
     <t xml:space="preserve">5.01775217056274</t>
   </si>
   <si>
-    <t xml:space="preserve">5.16866207122803</t>
+    <t xml:space="preserve">5.16866159439087</t>
   </si>
   <si>
     <t xml:space="preserve">5.1403660774231</t>
@@ -3377,10 +3377,10 @@
     <t xml:space="preserve">5.26298046112061</t>
   </si>
   <si>
-    <t xml:space="preserve">5.37616300582886</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.17809295654297</t>
+    <t xml:space="preserve">5.3761625289917</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.17809343338013</t>
   </si>
   <si>
     <t xml:space="preserve">5.21582126617432</t>
@@ -3389,7 +3389,7 @@
     <t xml:space="preserve">5.10263824462891</t>
   </si>
   <si>
-    <t xml:space="preserve">5.14979839324951</t>
+    <t xml:space="preserve">5.14979791641235</t>
   </si>
   <si>
     <t xml:space="preserve">5.09320688247681</t>
@@ -3404,7 +3404,7 @@
     <t xml:space="preserve">5.03661584854126</t>
   </si>
   <si>
-    <t xml:space="preserve">5.06491136550903</t>
+    <t xml:space="preserve">5.06491088867188</t>
   </si>
   <si>
     <t xml:space="preserve">4.95172882080078</t>
@@ -3419,7 +3419,7 @@
     <t xml:space="preserve">4.91400146484375</t>
   </si>
   <si>
-    <t xml:space="preserve">4.90456914901733</t>
+    <t xml:space="preserve">4.90456962585449</t>
   </si>
   <si>
     <t xml:space="preserve">4.77252340316772</t>
@@ -3431,16 +3431,16 @@
     <t xml:space="preserve">4.72536420822144</t>
   </si>
   <si>
-    <t xml:space="preserve">4.9611611366272</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.8574104309082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.8008189201355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.51786327362061</t>
+    <t xml:space="preserve">4.96116065979004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.85740995407104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.80081939697266</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.51786279678345</t>
   </si>
   <si>
     <t xml:space="preserve">4.50843143463135</t>
@@ -3452,7 +3452,7 @@
     <t xml:space="preserve">4.54615879058838</t>
   </si>
   <si>
-    <t xml:space="preserve">4.6216139793396</t>
+    <t xml:space="preserve">4.62161350250244</t>
   </si>
   <si>
     <t xml:space="preserve">4.54144287109375</t>
@@ -3467,7 +3467,7 @@
     <t xml:space="preserve">4.56030654907227</t>
   </si>
   <si>
-    <t xml:space="preserve">4.47541952133179</t>
+    <t xml:space="preserve">4.47541999816895</t>
   </si>
   <si>
     <t xml:space="preserve">4.47070360183716</t>
@@ -3485,7 +3485,7 @@
     <t xml:space="preserve">4.50371503829956</t>
   </si>
   <si>
-    <t xml:space="preserve">4.51314687728882</t>
+    <t xml:space="preserve">4.51314735412598</t>
   </si>
   <si>
     <t xml:space="preserve">4.63576126098633</t>
@@ -3494,13 +3494,13 @@
     <t xml:space="preserve">4.65934085845947</t>
   </si>
   <si>
-    <t xml:space="preserve">4.62632942199707</t>
+    <t xml:space="preserve">4.62632989883423</t>
   </si>
   <si>
     <t xml:space="preserve">4.64519357681274</t>
   </si>
   <si>
-    <t xml:space="preserve">4.67820453643799</t>
+    <t xml:space="preserve">4.67820501327515</t>
   </si>
   <si>
     <t xml:space="preserve">4.71593236923218</t>
@@ -3518,7 +3518,7 @@
     <t xml:space="preserve">4.73479604721069</t>
   </si>
   <si>
-    <t xml:space="preserve">4.60274982452393</t>
+    <t xml:space="preserve">4.60275030136108</t>
   </si>
   <si>
     <t xml:space="preserve">4.57445430755615</t>
@@ -3533,7 +3533,7 @@
     <t xml:space="preserve">4.34337377548218</t>
   </si>
   <si>
-    <t xml:space="preserve">4.41411256790161</t>
+    <t xml:space="preserve">4.41411209106445</t>
   </si>
   <si>
     <t xml:space="preserve">4.3952488899231</t>
@@ -3575,31 +3575,31 @@
     <t xml:space="preserve">4.27263498306274</t>
   </si>
   <si>
-    <t xml:space="preserve">4.2349066734314</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.1122932434082</t>
+    <t xml:space="preserve">4.23490715026855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.11229276657104</t>
   </si>
   <si>
     <t xml:space="preserve">4.0887131690979</t>
   </si>
   <si>
-    <t xml:space="preserve">4.0557017326355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.10757684707642</t>
+    <t xml:space="preserve">4.05570220947266</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.10757732391357</t>
   </si>
   <si>
     <t xml:space="preserve">4.03683805465698</t>
   </si>
   <si>
-    <t xml:space="preserve">3.86234831809998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.00854253768921</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.99910998344421</t>
+    <t xml:space="preserve">3.86234855651855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.00854206085205</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.99911022186279</t>
   </si>
   <si>
     <t xml:space="preserve">4.07456541061401</t>
@@ -3617,7 +3617,7 @@
     <t xml:space="preserve">4.15473651885986</t>
   </si>
   <si>
-    <t xml:space="preserve">4.18303155899048</t>
+    <t xml:space="preserve">4.18303203582764</t>
   </si>
   <si>
     <t xml:space="preserve">4.27735042572021</t>
@@ -3635,7 +3635,7 @@
     <t xml:space="preserve">4.24905490875244</t>
   </si>
   <si>
-    <t xml:space="preserve">4.26791906356812</t>
+    <t xml:space="preserve">4.26791858673096</t>
   </si>
   <si>
     <t xml:space="preserve">4.39053297042847</t>
@@ -3644,7 +3644,7 @@
     <t xml:space="preserve">4.37166976928711</t>
   </si>
   <si>
-    <t xml:space="preserve">4.35752105712891</t>
+    <t xml:space="preserve">4.35752153396606</t>
   </si>
   <si>
     <t xml:space="preserve">4.35280513763428</t>
@@ -3680,19 +3680,19 @@
     <t xml:space="preserve">4.23962306976318</t>
   </si>
   <si>
-    <t xml:space="preserve">4.20189523696899</t>
+    <t xml:space="preserve">4.20189571380615</t>
   </si>
   <si>
     <t xml:space="preserve">4.12644052505493</t>
   </si>
   <si>
-    <t xml:space="preserve">4.0226902961731</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.15002012252808</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.92837142944336</t>
+    <t xml:space="preserve">4.02268981933594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.15002059936523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.92837166786194</t>
   </si>
   <si>
     <t xml:space="preserve">4.04626989364624</t>
@@ -3701,16 +3701,16 @@
     <t xml:space="preserve">3.96138286590576</t>
   </si>
   <si>
-    <t xml:space="preserve">4.06041765213013</t>
+    <t xml:space="preserve">4.06041717529297</t>
   </si>
   <si>
     <t xml:space="preserve">4.01797485351562</t>
   </si>
   <si>
-    <t xml:space="preserve">3.90007615089417</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.94251942634583</t>
+    <t xml:space="preserve">3.90007638931274</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.94251894950867</t>
   </si>
   <si>
     <t xml:space="preserve">3.89535999298096</t>
@@ -3728,7 +3728,7 @@
     <t xml:space="preserve">3.88121199607849</t>
   </si>
   <si>
-    <t xml:space="preserve">3.84348440170288</t>
+    <t xml:space="preserve">3.84348464012146</t>
   </si>
   <si>
     <t xml:space="preserve">3.81990528106689</t>
@@ -3746,10 +3746,10 @@
     <t xml:space="preserve">3.75388216972351</t>
   </si>
   <si>
-    <t xml:space="preserve">3.72558665275574</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.76331400871277</t>
+    <t xml:space="preserve">3.72558641433716</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.76331377029419</t>
   </si>
   <si>
     <t xml:space="preserve">3.735018491745</t>
@@ -3758,7 +3758,7 @@
     <t xml:space="preserve">3.71615481376648</t>
   </si>
   <si>
-    <t xml:space="preserve">3.58410835266113</t>
+    <t xml:space="preserve">3.58410859107971</t>
   </si>
   <si>
     <t xml:space="preserve">3.76442790031433</t>
@@ -21104,7 +21104,7 @@
         <v>3.78500008583069</v>
       </c>
       <c r="G625" t="s">
-        <v>392</v>
+        <v>352</v>
       </c>
       <c r="H625" t="s">
         <v>9</v>
@@ -21130,7 +21130,7 @@
         <v>3.71000003814697</v>
       </c>
       <c r="G626" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="H626" t="s">
         <v>9</v>
@@ -21156,7 +21156,7 @@
         <v>3.72499990463257</v>
       </c>
       <c r="G627" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="H627" t="s">
         <v>9</v>
@@ -21182,7 +21182,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G628" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="H628" t="s">
         <v>9</v>
@@ -21208,7 +21208,7 @@
         <v>3.75</v>
       </c>
       <c r="G629" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="H629" t="s">
         <v>9</v>
@@ -21234,7 +21234,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G630" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="H630" t="s">
         <v>9</v>
@@ -21260,7 +21260,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G631" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="H631" t="s">
         <v>9</v>
@@ -21286,7 +21286,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G632" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="H632" t="s">
         <v>9</v>
@@ -21312,7 +21312,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G633" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="H633" t="s">
         <v>9</v>
@@ -21364,7 +21364,7 @@
         <v>3.67499995231628</v>
       </c>
       <c r="G635" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="H635" t="s">
         <v>9</v>
@@ -21390,7 +21390,7 @@
         <v>3.73499989509583</v>
       </c>
       <c r="G636" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="H636" t="s">
         <v>9</v>
@@ -21416,7 +21416,7 @@
         <v>3.77500009536743</v>
       </c>
       <c r="G637" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="H637" t="s">
         <v>9</v>
@@ -21442,7 +21442,7 @@
         <v>3.70499992370605</v>
       </c>
       <c r="G638" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="H638" t="s">
         <v>9</v>
@@ -21468,7 +21468,7 @@
         <v>3.76500010490417</v>
       </c>
       <c r="G639" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="H639" t="s">
         <v>9</v>
@@ -21494,7 +21494,7 @@
         <v>3.8050000667572</v>
       </c>
       <c r="G640" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="H640" t="s">
         <v>9</v>
@@ -21520,7 +21520,7 @@
         <v>3.8050000667572</v>
       </c>
       <c r="G641" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="H641" t="s">
         <v>9</v>
@@ -21546,7 +21546,7 @@
         <v>3.8050000667572</v>
       </c>
       <c r="G642" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="H642" t="s">
         <v>9</v>
@@ -21572,7 +21572,7 @@
         <v>3.75</v>
       </c>
       <c r="G643" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="H643" t="s">
         <v>9</v>
@@ -21624,7 +21624,7 @@
         <v>3.82999992370605</v>
       </c>
       <c r="G645" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="H645" t="s">
         <v>9</v>
@@ -21650,7 +21650,7 @@
         <v>3.82999992370605</v>
       </c>
       <c r="G646" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="H646" t="s">
         <v>9</v>
@@ -21702,7 +21702,7 @@
         <v>3.8050000667572</v>
       </c>
       <c r="G648" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="H648" t="s">
         <v>9</v>
@@ -21754,7 +21754,7 @@
         <v>3.85500001907349</v>
       </c>
       <c r="G650" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="H650" t="s">
         <v>9</v>
@@ -21780,7 +21780,7 @@
         <v>3.89000010490417</v>
       </c>
       <c r="G651" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="H651" t="s">
         <v>9</v>
@@ -21806,7 +21806,7 @@
         <v>3.96000003814697</v>
       </c>
       <c r="G652" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="H652" t="s">
         <v>9</v>
@@ -21832,7 +21832,7 @@
         <v>3.9449999332428</v>
       </c>
       <c r="G653" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="H653" t="s">
         <v>9</v>
@@ -21858,7 +21858,7 @@
         <v>3.90499997138977</v>
       </c>
       <c r="G654" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="H654" t="s">
         <v>9</v>
@@ -21884,7 +21884,7 @@
         <v>4</v>
       </c>
       <c r="G655" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="H655" t="s">
         <v>9</v>
@@ -21910,7 +21910,7 @@
         <v>4.07999992370605</v>
       </c>
       <c r="G656" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="H656" t="s">
         <v>9</v>
@@ -21936,7 +21936,7 @@
         <v>4.15999984741211</v>
       </c>
       <c r="G657" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="H657" t="s">
         <v>9</v>
@@ -21962,7 +21962,7 @@
         <v>4.07999992370605</v>
       </c>
       <c r="G658" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="H658" t="s">
         <v>9</v>
@@ -21988,7 +21988,7 @@
         <v>4.09000015258789</v>
       </c>
       <c r="G659" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="H659" t="s">
         <v>9</v>
@@ -22014,7 +22014,7 @@
         <v>4.21999979019165</v>
       </c>
       <c r="G660" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="H660" t="s">
         <v>9</v>
@@ -22040,7 +22040,7 @@
         <v>4.1100001335144</v>
       </c>
       <c r="G661" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="H661" t="s">
         <v>9</v>
@@ -22066,7 +22066,7 @@
         <v>4.15000009536743</v>
       </c>
       <c r="G662" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="H662" t="s">
         <v>9</v>
@@ -22092,7 +22092,7 @@
         <v>4.19000005722046</v>
       </c>
       <c r="G663" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="H663" t="s">
         <v>9</v>
@@ -22118,7 +22118,7 @@
         <v>4.19000005722046</v>
       </c>
       <c r="G664" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="H664" t="s">
         <v>9</v>
@@ -22144,7 +22144,7 @@
         <v>4.1399998664856</v>
       </c>
       <c r="G665" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="H665" t="s">
         <v>9</v>
@@ -22170,7 +22170,7 @@
         <v>4.11999988555908</v>
       </c>
       <c r="G666" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="H666" t="s">
         <v>9</v>
@@ -22196,7 +22196,7 @@
         <v>4.03499984741211</v>
       </c>
       <c r="G667" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="H667" t="s">
         <v>9</v>
@@ -22222,7 +22222,7 @@
         <v>4</v>
       </c>
       <c r="G668" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="H668" t="s">
         <v>9</v>
@@ -22248,7 +22248,7 @@
         <v>4.02500009536743</v>
       </c>
       <c r="G669" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="H669" t="s">
         <v>9</v>
@@ -22274,7 +22274,7 @@
         <v>4.13500022888184</v>
       </c>
       <c r="G670" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="H670" t="s">
         <v>9</v>
@@ -22300,7 +22300,7 @@
         <v>4.09000015258789</v>
       </c>
       <c r="G671" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="H671" t="s">
         <v>9</v>
@@ -22326,7 +22326,7 @@
         <v>3.9449999332428</v>
       </c>
       <c r="G672" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="H672" t="s">
         <v>9</v>
@@ -22352,7 +22352,7 @@
         <v>3.93499994277954</v>
       </c>
       <c r="G673" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="H673" t="s">
         <v>9</v>
@@ -22378,7 +22378,7 @@
         <v>3.95499992370605</v>
       </c>
       <c r="G674" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="H674" t="s">
         <v>9</v>
@@ -22404,7 +22404,7 @@
         <v>3.9300000667572</v>
       </c>
       <c r="G675" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="H675" t="s">
         <v>9</v>
@@ -22430,7 +22430,7 @@
         <v>3.98000001907349</v>
       </c>
       <c r="G676" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="H676" t="s">
         <v>9</v>
@@ -22456,7 +22456,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G677" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="H677" t="s">
         <v>9</v>
@@ -22482,7 +22482,7 @@
         <v>3.95499992370605</v>
       </c>
       <c r="G678" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="H678" t="s">
         <v>9</v>
@@ -22508,7 +22508,7 @@
         <v>3.91000008583069</v>
       </c>
       <c r="G679" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="H679" t="s">
         <v>9</v>
@@ -22534,7 +22534,7 @@
         <v>3.9300000667572</v>
       </c>
       <c r="G680" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="H680" t="s">
         <v>9</v>
@@ -22560,7 +22560,7 @@
         <v>4</v>
       </c>
       <c r="G681" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="H681" t="s">
         <v>9</v>
@@ -22586,7 +22586,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G682" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="H682" t="s">
         <v>9</v>
@@ -22612,7 +22612,7 @@
         <v>4.26000022888184</v>
       </c>
       <c r="G683" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="H683" t="s">
         <v>9</v>
@@ -22638,7 +22638,7 @@
         <v>4.27500009536743</v>
       </c>
       <c r="G684" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="H684" t="s">
         <v>9</v>
@@ -22664,7 +22664,7 @@
         <v>4.23000001907349</v>
       </c>
       <c r="G685" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="H685" t="s">
         <v>9</v>
@@ -22690,7 +22690,7 @@
         <v>4.2649998664856</v>
       </c>
       <c r="G686" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="H686" t="s">
         <v>9</v>
@@ -22716,7 +22716,7 @@
         <v>4.26999998092651</v>
       </c>
       <c r="G687" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="H687" t="s">
         <v>9</v>
@@ -22742,7 +22742,7 @@
         <v>4.36499977111816</v>
       </c>
       <c r="G688" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="H688" t="s">
         <v>9</v>
@@ -22768,7 +22768,7 @@
         <v>4.23999977111816</v>
       </c>
       <c r="G689" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="H689" t="s">
         <v>9</v>
@@ -22794,7 +22794,7 @@
         <v>4.25</v>
       </c>
       <c r="G690" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="H690" t="s">
         <v>9</v>
@@ -22820,7 +22820,7 @@
         <v>4.31500005722046</v>
       </c>
       <c r="G691" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="H691" t="s">
         <v>9</v>
@@ -22846,7 +22846,7 @@
         <v>4.50500011444092</v>
       </c>
       <c r="G692" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="H692" t="s">
         <v>9</v>
@@ -22872,7 +22872,7 @@
         <v>4.63000011444092</v>
       </c>
       <c r="G693" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="H693" t="s">
         <v>9</v>
@@ -22898,7 +22898,7 @@
         <v>4.43499994277954</v>
       </c>
       <c r="G694" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="H694" t="s">
         <v>9</v>
@@ -22924,7 +22924,7 @@
         <v>4.4850001335144</v>
       </c>
       <c r="G695" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="H695" t="s">
         <v>9</v>
@@ -22950,7 +22950,7 @@
         <v>4.3899998664856</v>
       </c>
       <c r="G696" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="H696" t="s">
         <v>9</v>
@@ -22976,7 +22976,7 @@
         <v>4.52500009536743</v>
       </c>
       <c r="G697" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="H697" t="s">
         <v>9</v>
@@ -23002,7 +23002,7 @@
         <v>4.50500011444092</v>
       </c>
       <c r="G698" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="H698" t="s">
         <v>9</v>
@@ -23028,7 +23028,7 @@
         <v>4.55999994277954</v>
       </c>
       <c r="G699" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="H699" t="s">
         <v>9</v>
@@ -23054,7 +23054,7 @@
         <v>4.53000020980835</v>
       </c>
       <c r="G700" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="H700" t="s">
         <v>9</v>
@@ -23080,7 +23080,7 @@
         <v>4.57499980926514</v>
       </c>
       <c r="G701" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="H701" t="s">
         <v>9</v>
@@ -23106,7 +23106,7 @@
         <v>4.67000007629395</v>
       </c>
       <c r="G702" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="H702" t="s">
         <v>9</v>
@@ -23132,7 +23132,7 @@
         <v>4.65999984741211</v>
       </c>
       <c r="G703" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="H703" t="s">
         <v>9</v>
@@ -23158,7 +23158,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G704" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="H704" t="s">
         <v>9</v>
@@ -23184,7 +23184,7 @@
         <v>4.84499979019165</v>
       </c>
       <c r="G705" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="H705" t="s">
         <v>9</v>
@@ -23210,7 +23210,7 @@
         <v>4.78999996185303</v>
       </c>
       <c r="G706" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="H706" t="s">
         <v>9</v>
@@ -23236,7 +23236,7 @@
         <v>4.67999982833862</v>
       </c>
       <c r="G707" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="H707" t="s">
         <v>9</v>
@@ -23262,7 +23262,7 @@
         <v>4.63000011444092</v>
       </c>
       <c r="G708" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="H708" t="s">
         <v>9</v>
@@ -23288,7 +23288,7 @@
         <v>4.6100001335144</v>
       </c>
       <c r="G709" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="H709" t="s">
         <v>9</v>
@@ -23314,7 +23314,7 @@
         <v>4.55000019073486</v>
       </c>
       <c r="G710" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="H710" t="s">
         <v>9</v>
@@ -23340,7 +23340,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G711" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="H711" t="s">
         <v>9</v>
@@ -23366,7 +23366,7 @@
         <v>4.51999998092651</v>
       </c>
       <c r="G712" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="H712" t="s">
         <v>9</v>
@@ -23392,7 +23392,7 @@
         <v>4.60500001907349</v>
       </c>
       <c r="G713" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="H713" t="s">
         <v>9</v>
@@ -23418,7 +23418,7 @@
         <v>4.61999988555908</v>
       </c>
       <c r="G714" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="H714" t="s">
         <v>9</v>
@@ -23444,7 +23444,7 @@
         <v>4.57499980926514</v>
       </c>
       <c r="G715" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="H715" t="s">
         <v>9</v>
@@ -23470,7 +23470,7 @@
         <v>4.44999980926514</v>
       </c>
       <c r="G716" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="H716" t="s">
         <v>9</v>
@@ -23496,7 +23496,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G717" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="H717" t="s">
         <v>9</v>
@@ -23522,7 +23522,7 @@
         <v>4.57999992370605</v>
       </c>
       <c r="G718" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="H718" t="s">
         <v>9</v>
@@ -23548,7 +23548,7 @@
         <v>4.53000020980835</v>
       </c>
       <c r="G719" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="H719" t="s">
         <v>9</v>
@@ -23574,7 +23574,7 @@
         <v>4.4850001335144</v>
       </c>
       <c r="G720" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="H720" t="s">
         <v>9</v>
@@ -23600,7 +23600,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G721" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="H721" t="s">
         <v>9</v>
@@ -23626,7 +23626,7 @@
         <v>4.55000019073486</v>
       </c>
       <c r="G722" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="H722" t="s">
         <v>9</v>
@@ -23652,7 +23652,7 @@
         <v>4.65000009536743</v>
       </c>
       <c r="G723" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="H723" t="s">
         <v>9</v>
@@ -23678,7 +23678,7 @@
         <v>4.71000003814697</v>
       </c>
       <c r="G724" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="H724" t="s">
         <v>9</v>
@@ -23704,7 +23704,7 @@
         <v>4.75500011444092</v>
       </c>
       <c r="G725" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="H725" t="s">
         <v>9</v>
@@ -23730,7 +23730,7 @@
         <v>4.76999998092651</v>
       </c>
       <c r="G726" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="H726" t="s">
         <v>9</v>
@@ -23756,7 +23756,7 @@
         <v>4.76999998092651</v>
       </c>
       <c r="G727" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="H727" t="s">
         <v>9</v>
@@ -23782,7 +23782,7 @@
         <v>4.66499996185303</v>
       </c>
       <c r="G728" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="H728" t="s">
         <v>9</v>
@@ -23808,7 +23808,7 @@
         <v>4.61499977111816</v>
       </c>
       <c r="G729" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="H729" t="s">
         <v>9</v>
@@ -23834,7 +23834,7 @@
         <v>4.67000007629395</v>
       </c>
       <c r="G730" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="H730" t="s">
         <v>9</v>
@@ -23860,7 +23860,7 @@
         <v>4.59000015258789</v>
       </c>
       <c r="G731" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="H731" t="s">
         <v>9</v>
@@ -23886,7 +23886,7 @@
         <v>4.57999992370605</v>
       </c>
       <c r="G732" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="H732" t="s">
         <v>9</v>
@@ -23912,7 +23912,7 @@
         <v>4.57999992370605</v>
       </c>
       <c r="G733" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="H733" t="s">
         <v>9</v>
@@ -23938,7 +23938,7 @@
         <v>4.4850001335144</v>
       </c>
       <c r="G734" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="H734" t="s">
         <v>9</v>
@@ -23964,7 +23964,7 @@
         <v>4.43499994277954</v>
       </c>
       <c r="G735" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="H735" t="s">
         <v>9</v>
@@ -23990,7 +23990,7 @@
         <v>4.36999988555908</v>
       </c>
       <c r="G736" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="H736" t="s">
         <v>9</v>
@@ -24016,7 +24016,7 @@
         <v>4.38000011444092</v>
       </c>
       <c r="G737" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="H737" t="s">
         <v>9</v>
@@ -24042,7 +24042,7 @@
         <v>4.28000020980835</v>
       </c>
       <c r="G738" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="H738" t="s">
         <v>9</v>
@@ -24068,7 +24068,7 @@
         <v>4.25</v>
       </c>
       <c r="G739" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="H739" t="s">
         <v>9</v>
@@ -24094,7 +24094,7 @@
         <v>4.23999977111816</v>
       </c>
       <c r="G740" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="H740" t="s">
         <v>9</v>
@@ -24120,7 +24120,7 @@
         <v>4.21000003814697</v>
       </c>
       <c r="G741" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="H741" t="s">
         <v>9</v>
@@ -24146,7 +24146,7 @@
         <v>4.3899998664856</v>
       </c>
       <c r="G742" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="H742" t="s">
         <v>9</v>
@@ -24172,7 +24172,7 @@
         <v>4.41499996185303</v>
       </c>
       <c r="G743" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="H743" t="s">
         <v>9</v>
@@ -24198,7 +24198,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G744" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="H744" t="s">
         <v>9</v>
@@ -24224,7 +24224,7 @@
         <v>4.34000015258789</v>
       </c>
       <c r="G745" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="H745" t="s">
         <v>9</v>
@@ -24250,7 +24250,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G746" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="H746" t="s">
         <v>9</v>
@@ -24276,7 +24276,7 @@
         <v>4.55000019073486</v>
       </c>
       <c r="G747" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="H747" t="s">
         <v>9</v>
@@ -24302,7 +24302,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G748" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="H748" t="s">
         <v>9</v>
@@ -24328,7 +24328,7 @@
         <v>4.5</v>
       </c>
       <c r="G749" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="H749" t="s">
         <v>9</v>
@@ -24354,7 +24354,7 @@
         <v>4.42999982833862</v>
       </c>
       <c r="G750" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="H750" t="s">
         <v>9</v>
@@ -24380,7 +24380,7 @@
         <v>4.41499996185303</v>
       </c>
       <c r="G751" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="H751" t="s">
         <v>9</v>
@@ -24406,7 +24406,7 @@
         <v>4.34499979019165</v>
       </c>
       <c r="G752" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="H752" t="s">
         <v>9</v>
@@ -24432,7 +24432,7 @@
         <v>4.43499994277954</v>
       </c>
       <c r="G753" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="H753" t="s">
         <v>9</v>
@@ -24458,7 +24458,7 @@
         <v>4.42999982833862</v>
       </c>
       <c r="G754" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="H754" t="s">
         <v>9</v>
@@ -24484,7 +24484,7 @@
         <v>4.42999982833862</v>
       </c>
       <c r="G755" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="H755" t="s">
         <v>9</v>
@@ -24510,7 +24510,7 @@
         <v>4.40999984741211</v>
       </c>
       <c r="G756" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="H756" t="s">
         <v>9</v>
@@ -24536,7 +24536,7 @@
         <v>4.38500022888184</v>
       </c>
       <c r="G757" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="H757" t="s">
         <v>9</v>
@@ -24562,7 +24562,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G758" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="H758" t="s">
         <v>9</v>
@@ -24588,7 +24588,7 @@
         <v>4.44999980926514</v>
       </c>
       <c r="G759" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="H759" t="s">
         <v>9</v>
@@ -24614,7 +24614,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G760" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="H760" t="s">
         <v>9</v>
@@ -24640,7 +24640,7 @@
         <v>4.38000011444092</v>
       </c>
       <c r="G761" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="H761" t="s">
         <v>9</v>
@@ -24666,7 +24666,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G762" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="H762" t="s">
         <v>9</v>
@@ -24692,7 +24692,7 @@
         <v>4.42999982833862</v>
       </c>
       <c r="G763" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="H763" t="s">
         <v>9</v>
@@ -24718,7 +24718,7 @@
         <v>4.55000019073486</v>
       </c>
       <c r="G764" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="H764" t="s">
         <v>9</v>
@@ -24744,7 +24744,7 @@
         <v>4.53499984741211</v>
       </c>
       <c r="G765" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="H765" t="s">
         <v>9</v>
@@ -24770,7 +24770,7 @@
         <v>4.51000022888184</v>
       </c>
       <c r="G766" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="H766" t="s">
         <v>9</v>
@@ -24796,7 +24796,7 @@
         <v>4.40500020980835</v>
       </c>
       <c r="G767" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="H767" t="s">
         <v>9</v>
@@ -24822,7 +24822,7 @@
         <v>4.44999980926514</v>
       </c>
       <c r="G768" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="H768" t="s">
         <v>9</v>
@@ -24848,7 +24848,7 @@
         <v>4.44999980926514</v>
       </c>
       <c r="G769" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="H769" t="s">
         <v>9</v>
@@ -24874,7 +24874,7 @@
         <v>4.44500017166138</v>
       </c>
       <c r="G770" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="H770" t="s">
         <v>9</v>
@@ -24900,7 +24900,7 @@
         <v>4.46500015258789</v>
       </c>
       <c r="G771" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="H771" t="s">
         <v>9</v>
@@ -24926,7 +24926,7 @@
         <v>4.42999982833862</v>
       </c>
       <c r="G772" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="H772" t="s">
         <v>9</v>
@@ -24952,7 +24952,7 @@
         <v>4.34999990463257</v>
       </c>
       <c r="G773" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="H773" t="s">
         <v>9</v>
@@ -24978,7 +24978,7 @@
         <v>4.28000020980835</v>
       </c>
       <c r="G774" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="H774" t="s">
         <v>9</v>
@@ -25004,7 +25004,7 @@
         <v>4.3600001335144</v>
       </c>
       <c r="G775" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="H775" t="s">
         <v>9</v>
@@ -25030,7 +25030,7 @@
         <v>4.5</v>
       </c>
       <c r="G776" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="H776" t="s">
         <v>9</v>
@@ -25056,7 +25056,7 @@
         <v>4.63000011444092</v>
       </c>
       <c r="G777" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="H777" t="s">
         <v>9</v>
@@ -25082,7 +25082,7 @@
         <v>4.59499979019165</v>
       </c>
       <c r="G778" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="H778" t="s">
         <v>9</v>
@@ -25108,7 +25108,7 @@
         <v>4.65000009536743</v>
       </c>
       <c r="G779" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="H779" t="s">
         <v>9</v>
@@ -25134,7 +25134,7 @@
         <v>4.6399998664856</v>
       </c>
       <c r="G780" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="H780" t="s">
         <v>9</v>
@@ -25160,7 +25160,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G781" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="H781" t="s">
         <v>9</v>
@@ -25186,7 +25186,7 @@
         <v>4.69000005722046</v>
       </c>
       <c r="G782" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="H782" t="s">
         <v>9</v>
@@ -25212,7 +25212,7 @@
         <v>4.77500009536743</v>
       </c>
       <c r="G783" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="H783" t="s">
         <v>9</v>
@@ -25238,7 +25238,7 @@
         <v>4.78999996185303</v>
       </c>
       <c r="G784" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="H784" t="s">
         <v>9</v>
@@ -25264,7 +25264,7 @@
         <v>4.86999988555908</v>
       </c>
       <c r="G785" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="H785" t="s">
         <v>9</v>
@@ -25290,7 +25290,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G786" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="H786" t="s">
         <v>9</v>
@@ -25316,7 +25316,7 @@
         <v>4.96999979019165</v>
       </c>
       <c r="G787" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="H787" t="s">
         <v>9</v>
@@ -25342,7 +25342,7 @@
         <v>5</v>
       </c>
       <c r="G788" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="H788" t="s">
         <v>9</v>
@@ -25368,7 +25368,7 @@
         <v>5.05000019073486</v>
       </c>
       <c r="G789" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="H789" t="s">
         <v>9</v>
@@ -25394,7 +25394,7 @@
         <v>4.98999977111816</v>
       </c>
       <c r="G790" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="H790" t="s">
         <v>9</v>
@@ -25420,7 +25420,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G791" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="H791" t="s">
         <v>9</v>
@@ -25446,7 +25446,7 @@
         <v>4.88500022888184</v>
       </c>
       <c r="G792" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="H792" t="s">
         <v>9</v>
@@ -25472,7 +25472,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G793" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="H793" t="s">
         <v>9</v>
@@ -25498,7 +25498,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G794" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="H794" t="s">
         <v>9</v>
@@ -25524,7 +25524,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G795" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="H795" t="s">
         <v>9</v>
@@ -25550,7 +25550,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G796" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="H796" t="s">
         <v>9</v>
@@ -25576,7 +25576,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G797" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="H797" t="s">
         <v>9</v>
@@ -25602,7 +25602,7 @@
         <v>4.8600001335144</v>
       </c>
       <c r="G798" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="H798" t="s">
         <v>9</v>
@@ -25628,7 +25628,7 @@
         <v>4.88500022888184</v>
       </c>
       <c r="G799" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="H799" t="s">
         <v>9</v>
@@ -25654,7 +25654,7 @@
         <v>4.94000005722046</v>
       </c>
       <c r="G800" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="H800" t="s">
         <v>9</v>
@@ -25680,7 +25680,7 @@
         <v>4.875</v>
       </c>
       <c r="G801" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="H801" t="s">
         <v>9</v>
@@ -25706,7 +25706,7 @@
         <v>4.86499977111816</v>
       </c>
       <c r="G802" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="H802" t="s">
         <v>9</v>
@@ -25732,7 +25732,7 @@
         <v>4.8600001335144</v>
       </c>
       <c r="G803" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="H803" t="s">
         <v>9</v>
@@ -25758,7 +25758,7 @@
         <v>4.84000015258789</v>
       </c>
       <c r="G804" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="H804" t="s">
         <v>9</v>
@@ -25784,7 +25784,7 @@
         <v>4.8600001335144</v>
       </c>
       <c r="G805" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="H805" t="s">
         <v>9</v>
@@ -25810,7 +25810,7 @@
         <v>5.07999992370605</v>
       </c>
       <c r="G806" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="H806" t="s">
         <v>9</v>
@@ -25836,7 +25836,7 @@
         <v>5.23999977111816</v>
       </c>
       <c r="G807" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="H807" t="s">
         <v>9</v>
@@ -25862,7 +25862,7 @@
         <v>5.3899998664856</v>
       </c>
       <c r="G808" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="H808" t="s">
         <v>9</v>
@@ -25888,7 +25888,7 @@
         <v>5.3600001335144</v>
       </c>
       <c r="G809" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="H809" t="s">
         <v>9</v>
@@ -25914,7 +25914,7 @@
         <v>5.46000003814697</v>
       </c>
       <c r="G810" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="H810" t="s">
         <v>9</v>
@@ -25940,7 +25940,7 @@
         <v>5.34000015258789</v>
       </c>
       <c r="G811" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="H811" t="s">
         <v>9</v>
@@ -25966,7 +25966,7 @@
         <v>5.46000003814697</v>
       </c>
       <c r="G812" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="H812" t="s">
         <v>9</v>
@@ -25992,7 +25992,7 @@
         <v>5.51000022888184</v>
       </c>
       <c r="G813" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="H813" t="s">
         <v>9</v>
@@ -26018,7 +26018,7 @@
         <v>5.57000017166138</v>
       </c>
       <c r="G814" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="H814" t="s">
         <v>9</v>
@@ -26044,7 +26044,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G815" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="H815" t="s">
         <v>9</v>
@@ -26070,7 +26070,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G816" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="H816" t="s">
         <v>9</v>
@@ -26096,7 +26096,7 @@
         <v>5.57000017166138</v>
       </c>
       <c r="G817" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="H817" t="s">
         <v>9</v>
@@ -26122,7 +26122,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G818" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="H818" t="s">
         <v>9</v>
@@ -26148,7 +26148,7 @@
         <v>5.57999992370605</v>
       </c>
       <c r="G819" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="H819" t="s">
         <v>9</v>
@@ -26174,7 +26174,7 @@
         <v>5.55999994277954</v>
       </c>
       <c r="G820" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="H820" t="s">
         <v>9</v>
@@ -26200,7 +26200,7 @@
         <v>5.51999998092651</v>
       </c>
       <c r="G821" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="H821" t="s">
         <v>9</v>
@@ -26226,7 +26226,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G822" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="H822" t="s">
         <v>9</v>
@@ -26252,7 +26252,7 @@
         <v>5.28999996185303</v>
       </c>
       <c r="G823" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="H823" t="s">
         <v>9</v>
@@ -26278,7 +26278,7 @@
         <v>5.32999992370605</v>
       </c>
       <c r="G824" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="H824" t="s">
         <v>9</v>
@@ -26304,7 +26304,7 @@
         <v>5.34999990463257</v>
       </c>
       <c r="G825" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="H825" t="s">
         <v>9</v>
@@ -26330,7 +26330,7 @@
         <v>5.42000007629395</v>
       </c>
       <c r="G826" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="H826" t="s">
         <v>9</v>
@@ -26356,7 +26356,7 @@
         <v>5.42000007629395</v>
       </c>
       <c r="G827" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="H827" t="s">
         <v>9</v>
@@ -26382,7 +26382,7 @@
         <v>5.48000001907349</v>
       </c>
       <c r="G828" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="H828" t="s">
         <v>9</v>
@@ -26408,7 +26408,7 @@
         <v>5.5</v>
       </c>
       <c r="G829" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="H829" t="s">
         <v>9</v>
@@ -26434,7 +26434,7 @@
         <v>5.48999977111816</v>
       </c>
       <c r="G830" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="H830" t="s">
         <v>9</v>
@@ -26460,7 +26460,7 @@
         <v>5.5</v>
       </c>
       <c r="G831" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="H831" t="s">
         <v>9</v>
@@ -26486,7 +26486,7 @@
         <v>5.5</v>
       </c>
       <c r="G832" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="H832" t="s">
         <v>9</v>
@@ -26512,7 +26512,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G833" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="H833" t="s">
         <v>9</v>
@@ -26538,7 +26538,7 @@
         <v>5.25</v>
       </c>
       <c r="G834" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
       <c r="H834" t="s">
         <v>9</v>
@@ -26564,7 +26564,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G835" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="H835" t="s">
         <v>9</v>
@@ -26590,7 +26590,7 @@
         <v>5.46000003814697</v>
       </c>
       <c r="G836" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="H836" t="s">
         <v>9</v>
@@ -26616,7 +26616,7 @@
         <v>5.51000022888184</v>
       </c>
       <c r="G837" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="H837" t="s">
         <v>9</v>
@@ -26642,7 +26642,7 @@
         <v>5.67000007629395</v>
       </c>
       <c r="G838" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="H838" t="s">
         <v>9</v>
@@ -26668,7 +26668,7 @@
         <v>5.73000001907349</v>
       </c>
       <c r="G839" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="H839" t="s">
         <v>9</v>
@@ -26694,7 +26694,7 @@
         <v>5.65000009536743</v>
       </c>
       <c r="G840" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="H840" t="s">
         <v>9</v>
@@ -26720,7 +26720,7 @@
         <v>5.59000015258789</v>
       </c>
       <c r="G841" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="H841" t="s">
         <v>9</v>
@@ -26746,7 +26746,7 @@
         <v>5.55000019073486</v>
       </c>
       <c r="G842" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="H842" t="s">
         <v>9</v>
@@ -26772,7 +26772,7 @@
         <v>5.55000019073486</v>
       </c>
       <c r="G843" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="H843" t="s">
         <v>9</v>
@@ -26798,7 +26798,7 @@
         <v>5.46000003814697</v>
       </c>
       <c r="G844" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="H844" t="s">
         <v>9</v>
@@ -26824,7 +26824,7 @@
         <v>5.36999988555908</v>
       </c>
       <c r="G845" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="H845" t="s">
         <v>9</v>
@@ -26850,7 +26850,7 @@
         <v>5.46000003814697</v>
       </c>
       <c r="G846" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="H846" t="s">
         <v>9</v>
@@ -26876,7 +26876,7 @@
         <v>5.40999984741211</v>
       </c>
       <c r="G847" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="H847" t="s">
         <v>9</v>
@@ -26902,7 +26902,7 @@
         <v>5.48999977111816</v>
       </c>
       <c r="G848" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="H848" t="s">
         <v>9</v>
@@ -26928,7 +26928,7 @@
         <v>5.42000007629395</v>
       </c>
       <c r="G849" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="H849" t="s">
         <v>9</v>
@@ -26954,7 +26954,7 @@
         <v>5.32000017166138</v>
       </c>
       <c r="G850" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="H850" t="s">
         <v>9</v>
@@ -26980,7 +26980,7 @@
         <v>5.34000015258789</v>
       </c>
       <c r="G851" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="H851" t="s">
         <v>9</v>
@@ -27006,7 +27006,7 @@
         <v>5.32000017166138</v>
       </c>
       <c r="G852" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="H852" t="s">
         <v>9</v>
@@ -27032,7 +27032,7 @@
         <v>5.34999990463257</v>
       </c>
       <c r="G853" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="H853" t="s">
         <v>9</v>
@@ -27058,7 +27058,7 @@
         <v>5.26000022888184</v>
       </c>
       <c r="G854" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="H854" t="s">
         <v>9</v>
@@ -27084,7 +27084,7 @@
         <v>5.26000022888184</v>
       </c>
       <c r="G855" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="H855" t="s">
         <v>9</v>
@@ -27110,7 +27110,7 @@
         <v>5.23000001907349</v>
       </c>
       <c r="G856" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="H856" t="s">
         <v>9</v>
@@ -27136,7 +27136,7 @@
         <v>5.21999979019165</v>
       </c>
       <c r="G857" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="H857" t="s">
         <v>9</v>
@@ -27162,7 +27162,7 @@
         <v>5.17999982833862</v>
       </c>
       <c r="G858" t="s">
-        <v>539</v>
+        <v>538</v>
       </c>
       <c r="H858" t="s">
         <v>9</v>
@@ -27188,7 +27188,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G859" t="s">
-        <v>540</v>
+        <v>539</v>
       </c>
       <c r="H859" t="s">
         <v>9</v>
@@ -27214,7 +27214,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G860" t="s">
-        <v>540</v>
+        <v>539</v>
       </c>
       <c r="H860" t="s">
         <v>9</v>
@@ -27240,7 +27240,7 @@
         <v>5.26000022888184</v>
       </c>
       <c r="G861" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="H861" t="s">
         <v>9</v>
@@ -27266,7 +27266,7 @@
         <v>5.11999988555908</v>
       </c>
       <c r="G862" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="H862" t="s">
         <v>9</v>
@@ -27292,7 +27292,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G863" t="s">
-        <v>540</v>
+        <v>539</v>
       </c>
       <c r="H863" t="s">
         <v>9</v>
@@ -27318,7 +27318,7 @@
         <v>5.09000015258789</v>
       </c>
       <c r="G864" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="H864" t="s">
         <v>9</v>
@@ -27344,7 +27344,7 @@
         <v>5.01000022888184</v>
       </c>
       <c r="G865" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="H865" t="s">
         <v>9</v>
@@ -27370,7 +27370,7 @@
         <v>4.96999979019165</v>
       </c>
       <c r="G866" t="s">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="H866" t="s">
         <v>9</v>
@@ -27396,7 +27396,7 @@
         <v>5.03999996185303</v>
       </c>
       <c r="G867" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
       <c r="H867" t="s">
         <v>9</v>
@@ -27422,7 +27422,7 @@
         <v>5.01999998092651</v>
       </c>
       <c r="G868" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="H868" t="s">
         <v>9</v>
@@ -27448,7 +27448,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G869" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="H869" t="s">
         <v>9</v>
@@ -27474,7 +27474,7 @@
         <v>5.05999994277954</v>
       </c>
       <c r="G870" t="s">
-        <v>539</v>
+        <v>548</v>
       </c>
       <c r="H870" t="s">
         <v>9</v>
@@ -27552,7 +27552,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G873" t="s">
-        <v>540</v>
+        <v>539</v>
       </c>
       <c r="H873" t="s">
         <v>9</v>
@@ -27578,7 +27578,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G874" t="s">
-        <v>540</v>
+        <v>539</v>
       </c>
       <c r="H874" t="s">
         <v>9</v>
@@ -27604,7 +27604,7 @@
         <v>5.09000015258789</v>
       </c>
       <c r="G875" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="H875" t="s">
         <v>9</v>
@@ -27708,7 +27708,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G879" t="s">
-        <v>540</v>
+        <v>539</v>
       </c>
       <c r="H879" t="s">
         <v>9</v>
@@ -27786,7 +27786,7 @@
         <v>5.11999988555908</v>
       </c>
       <c r="G882" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="H882" t="s">
         <v>9</v>
@@ -27812,7 +27812,7 @@
         <v>5.05999994277954</v>
       </c>
       <c r="G883" t="s">
-        <v>539</v>
+        <v>548</v>
       </c>
       <c r="H883" t="s">
         <v>9</v>
@@ -28358,7 +28358,7 @@
         <v>4.96999979019165</v>
       </c>
       <c r="G904" t="s">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="H904" t="s">
         <v>9</v>
@@ -30334,7 +30334,7 @@
         <v>5.05999994277954</v>
       </c>
       <c r="G980" t="s">
-        <v>539</v>
+        <v>548</v>
       </c>
       <c r="H980" t="s">
         <v>9</v>
@@ -30360,7 +30360,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G981" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="H981" t="s">
         <v>9</v>
@@ -30412,7 +30412,7 @@
         <v>5.26000022888184</v>
       </c>
       <c r="G983" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="H983" t="s">
         <v>9</v>
@@ -30516,7 +30516,7 @@
         <v>5.26000022888184</v>
       </c>
       <c r="G987" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="H987" t="s">
         <v>9</v>
@@ -30542,7 +30542,7 @@
         <v>5.11999988555908</v>
       </c>
       <c r="G988" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="H988" t="s">
         <v>9</v>
@@ -31244,7 +31244,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G1015" t="s">
-        <v>540</v>
+        <v>539</v>
       </c>
       <c r="H1015" t="s">
         <v>9</v>
@@ -31374,7 +31374,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G1020" t="s">
-        <v>540</v>
+        <v>539</v>
       </c>
       <c r="H1020" t="s">
         <v>9</v>
@@ -31894,7 +31894,7 @@
         <v>5.01000022888184</v>
       </c>
       <c r="G1040" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="H1040" t="s">
         <v>9</v>
@@ -31998,7 +31998,7 @@
         <v>5.11999988555908</v>
       </c>
       <c r="G1044" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="H1044" t="s">
         <v>9</v>
@@ -39408,7 +39408,7 @@
         <v>4.09000015258789</v>
       </c>
       <c r="G1329" t="s">
-        <v>610</v>
+        <v>833</v>
       </c>
       <c r="H1329" t="s">
         <v>9</v>
@@ -39486,7 +39486,7 @@
         <v>4.07000017166138</v>
       </c>
       <c r="G1332" t="s">
-        <v>833</v>
+        <v>834</v>
       </c>
       <c r="H1332" t="s">
         <v>9</v>
@@ -39564,7 +39564,7 @@
         <v>4.14499998092651</v>
       </c>
       <c r="G1335" t="s">
-        <v>834</v>
+        <v>835</v>
       </c>
       <c r="H1335" t="s">
         <v>9</v>
@@ -39616,7 +39616,7 @@
         <v>4.19500017166138</v>
       </c>
       <c r="G1337" t="s">
-        <v>835</v>
+        <v>836</v>
       </c>
       <c r="H1337" t="s">
         <v>9</v>
@@ -39668,7 +39668,7 @@
         <v>4.28000020980835</v>
       </c>
       <c r="G1339" t="s">
-        <v>836</v>
+        <v>837</v>
       </c>
       <c r="H1339" t="s">
         <v>9</v>
@@ -39720,7 +39720,7 @@
         <v>4.44000005722046</v>
       </c>
       <c r="G1341" t="s">
-        <v>837</v>
+        <v>838</v>
       </c>
       <c r="H1341" t="s">
         <v>9</v>
@@ -39746,7 +39746,7 @@
         <v>4.45499992370605</v>
       </c>
       <c r="G1342" t="s">
-        <v>838</v>
+        <v>839</v>
       </c>
       <c r="H1342" t="s">
         <v>9</v>
@@ -39772,7 +39772,7 @@
         <v>4.51999998092651</v>
       </c>
       <c r="G1343" t="s">
-        <v>839</v>
+        <v>840</v>
       </c>
       <c r="H1343" t="s">
         <v>9</v>
@@ -39798,7 +39798,7 @@
         <v>4.47499990463257</v>
       </c>
       <c r="G1344" t="s">
-        <v>840</v>
+        <v>841</v>
       </c>
       <c r="H1344" t="s">
         <v>9</v>
@@ -39824,7 +39824,7 @@
         <v>4.57000017166138</v>
       </c>
       <c r="G1345" t="s">
-        <v>841</v>
+        <v>842</v>
       </c>
       <c r="H1345" t="s">
         <v>9</v>
@@ -39850,7 +39850,7 @@
         <v>4.65500020980835</v>
       </c>
       <c r="G1346" t="s">
-        <v>842</v>
+        <v>843</v>
       </c>
       <c r="H1346" t="s">
         <v>9</v>
@@ -39876,7 +39876,7 @@
         <v>4.64499998092651</v>
       </c>
       <c r="G1347" t="s">
-        <v>843</v>
+        <v>844</v>
       </c>
       <c r="H1347" t="s">
         <v>9</v>
@@ -39902,7 +39902,7 @@
         <v>4.61499977111816</v>
       </c>
       <c r="G1348" t="s">
-        <v>844</v>
+        <v>845</v>
       </c>
       <c r="H1348" t="s">
         <v>9</v>
@@ -39928,7 +39928,7 @@
         <v>4.68499994277954</v>
       </c>
       <c r="G1349" t="s">
-        <v>845</v>
+        <v>846</v>
       </c>
       <c r="H1349" t="s">
         <v>9</v>
@@ -39954,7 +39954,7 @@
         <v>4.61499977111816</v>
       </c>
       <c r="G1350" t="s">
-        <v>844</v>
+        <v>845</v>
       </c>
       <c r="H1350" t="s">
         <v>9</v>
@@ -39980,7 +39980,7 @@
         <v>4.61999988555908</v>
       </c>
       <c r="G1351" t="s">
-        <v>846</v>
+        <v>847</v>
       </c>
       <c r="H1351" t="s">
         <v>9</v>
@@ -40006,7 +40006,7 @@
         <v>4.57999992370605</v>
       </c>
       <c r="G1352" t="s">
-        <v>847</v>
+        <v>848</v>
       </c>
       <c r="H1352" t="s">
         <v>9</v>
@@ -40032,7 +40032,7 @@
         <v>4.57000017166138</v>
       </c>
       <c r="G1353" t="s">
-        <v>841</v>
+        <v>842</v>
       </c>
       <c r="H1353" t="s">
         <v>9</v>
@@ -40058,7 +40058,7 @@
         <v>4.53999996185303</v>
       </c>
       <c r="G1354" t="s">
-        <v>848</v>
+        <v>849</v>
       </c>
       <c r="H1354" t="s">
         <v>9</v>
@@ -40084,7 +40084,7 @@
         <v>4.5</v>
       </c>
       <c r="G1355" t="s">
-        <v>849</v>
+        <v>850</v>
       </c>
       <c r="H1355" t="s">
         <v>9</v>
@@ -40110,7 +40110,7 @@
         <v>4.44000005722046</v>
       </c>
       <c r="G1356" t="s">
-        <v>850</v>
+        <v>851</v>
       </c>
       <c r="H1356" t="s">
         <v>9</v>
@@ -40136,7 +40136,7 @@
         <v>4.49499988555908</v>
       </c>
       <c r="G1357" t="s">
-        <v>851</v>
+        <v>852</v>
       </c>
       <c r="H1357" t="s">
         <v>9</v>
@@ -40162,7 +40162,7 @@
         <v>4.52500009536743</v>
       </c>
       <c r="G1358" t="s">
-        <v>852</v>
+        <v>853</v>
       </c>
       <c r="H1358" t="s">
         <v>9</v>
@@ -40188,7 +40188,7 @@
         <v>4.55999994277954</v>
       </c>
       <c r="G1359" t="s">
-        <v>853</v>
+        <v>854</v>
       </c>
       <c r="H1359" t="s">
         <v>9</v>
@@ -40214,7 +40214,7 @@
         <v>4.5</v>
       </c>
       <c r="G1360" t="s">
-        <v>849</v>
+        <v>850</v>
       </c>
       <c r="H1360" t="s">
         <v>9</v>
@@ -40240,7 +40240,7 @@
         <v>4.5</v>
       </c>
       <c r="G1361" t="s">
-        <v>849</v>
+        <v>850</v>
       </c>
       <c r="H1361" t="s">
         <v>9</v>
@@ -40266,7 +40266,7 @@
         <v>4.5</v>
       </c>
       <c r="G1362" t="s">
-        <v>849</v>
+        <v>850</v>
       </c>
       <c r="H1362" t="s">
         <v>9</v>
@@ -40292,7 +40292,7 @@
         <v>4.43499994277954</v>
       </c>
       <c r="G1363" t="s">
-        <v>854</v>
+        <v>855</v>
       </c>
       <c r="H1363" t="s">
         <v>9</v>
@@ -40318,7 +40318,7 @@
         <v>4.46500015258789</v>
       </c>
       <c r="G1364" t="s">
-        <v>855</v>
+        <v>856</v>
       </c>
       <c r="H1364" t="s">
         <v>9</v>
@@ -40344,7 +40344,7 @@
         <v>4.48000001907349</v>
       </c>
       <c r="G1365" t="s">
-        <v>856</v>
+        <v>857</v>
       </c>
       <c r="H1365" t="s">
         <v>9</v>
@@ -40370,7 +40370,7 @@
         <v>4.44000005722046</v>
       </c>
       <c r="G1366" t="s">
-        <v>850</v>
+        <v>851</v>
       </c>
       <c r="H1366" t="s">
         <v>9</v>
@@ -40396,7 +40396,7 @@
         <v>4.42000007629395</v>
       </c>
       <c r="G1367" t="s">
-        <v>857</v>
+        <v>858</v>
       </c>
       <c r="H1367" t="s">
         <v>9</v>
@@ -40422,7 +40422,7 @@
         <v>4.44999980926514</v>
       </c>
       <c r="G1368" t="s">
-        <v>858</v>
+        <v>859</v>
       </c>
       <c r="H1368" t="s">
         <v>9</v>
@@ -40448,7 +40448,7 @@
         <v>4.40999984741211</v>
       </c>
       <c r="G1369" t="s">
-        <v>859</v>
+        <v>860</v>
       </c>
       <c r="H1369" t="s">
         <v>9</v>
@@ -40474,7 +40474,7 @@
         <v>4.42000007629395</v>
       </c>
       <c r="G1370" t="s">
-        <v>857</v>
+        <v>858</v>
       </c>
       <c r="H1370" t="s">
         <v>9</v>
@@ -40500,7 +40500,7 @@
         <v>4.42500019073486</v>
       </c>
       <c r="G1371" t="s">
-        <v>860</v>
+        <v>861</v>
       </c>
       <c r="H1371" t="s">
         <v>9</v>
@@ -40526,7 +40526,7 @@
         <v>4.42500019073486</v>
       </c>
       <c r="G1372" t="s">
-        <v>860</v>
+        <v>861</v>
       </c>
       <c r="H1372" t="s">
         <v>9</v>
@@ -40552,7 +40552,7 @@
         <v>4.47499990463257</v>
       </c>
       <c r="G1373" t="s">
-        <v>840</v>
+        <v>841</v>
       </c>
       <c r="H1373" t="s">
         <v>9</v>
@@ -40578,7 +40578,7 @@
         <v>4.51000022888184</v>
       </c>
       <c r="G1374" t="s">
-        <v>861</v>
+        <v>862</v>
       </c>
       <c r="H1374" t="s">
         <v>9</v>
@@ -40604,7 +40604,7 @@
         <v>4.55000019073486</v>
       </c>
       <c r="G1375" t="s">
-        <v>862</v>
+        <v>863</v>
       </c>
       <c r="H1375" t="s">
         <v>9</v>
@@ -40630,7 +40630,7 @@
         <v>4.59499979019165</v>
       </c>
       <c r="G1376" t="s">
-        <v>863</v>
+        <v>864</v>
       </c>
       <c r="H1376" t="s">
         <v>9</v>
@@ -40656,7 +40656,7 @@
         <v>4.65999984741211</v>
       </c>
       <c r="G1377" t="s">
-        <v>864</v>
+        <v>865</v>
       </c>
       <c r="H1377" t="s">
         <v>9</v>
@@ -40682,7 +40682,7 @@
         <v>4.57999992370605</v>
       </c>
       <c r="G1378" t="s">
-        <v>847</v>
+        <v>848</v>
       </c>
       <c r="H1378" t="s">
         <v>9</v>
@@ -40708,7 +40708,7 @@
         <v>4.57999992370605</v>
       </c>
       <c r="G1379" t="s">
-        <v>847</v>
+        <v>848</v>
       </c>
       <c r="H1379" t="s">
         <v>9</v>
@@ -40734,7 +40734,7 @@
         <v>4.59000015258789</v>
       </c>
       <c r="G1380" t="s">
-        <v>865</v>
+        <v>866</v>
       </c>
       <c r="H1380" t="s">
         <v>9</v>
@@ -40760,7 +40760,7 @@
         <v>4.58500003814697</v>
       </c>
       <c r="G1381" t="s">
-        <v>866</v>
+        <v>867</v>
       </c>
       <c r="H1381" t="s">
         <v>9</v>
@@ -40786,7 +40786,7 @@
         <v>4.53000020980835</v>
       </c>
       <c r="G1382" t="s">
-        <v>867</v>
+        <v>868</v>
       </c>
       <c r="H1382" t="s">
         <v>9</v>
@@ -40812,7 +40812,7 @@
         <v>4.59000015258789</v>
       </c>
       <c r="G1383" t="s">
-        <v>865</v>
+        <v>866</v>
       </c>
       <c r="H1383" t="s">
         <v>9</v>
@@ -40838,7 +40838,7 @@
         <v>4.67999982833862</v>
       </c>
       <c r="G1384" t="s">
-        <v>868</v>
+        <v>869</v>
       </c>
       <c r="H1384" t="s">
         <v>9</v>
@@ -40864,7 +40864,7 @@
         <v>4.67999982833862</v>
       </c>
       <c r="G1385" t="s">
-        <v>868</v>
+        <v>869</v>
       </c>
       <c r="H1385" t="s">
         <v>9</v>
@@ -40890,7 +40890,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G1386" t="s">
-        <v>869</v>
+        <v>870</v>
       </c>
       <c r="H1386" t="s">
         <v>9</v>
@@ -40916,7 +40916,7 @@
         <v>4.63000011444092</v>
       </c>
       <c r="G1387" t="s">
-        <v>870</v>
+        <v>871</v>
       </c>
       <c r="H1387" t="s">
         <v>9</v>
@@ -40942,7 +40942,7 @@
         <v>4.63000011444092</v>
       </c>
       <c r="G1388" t="s">
-        <v>870</v>
+        <v>871</v>
       </c>
       <c r="H1388" t="s">
         <v>9</v>
@@ -40968,7 +40968,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G1389" t="s">
-        <v>871</v>
+        <v>872</v>
       </c>
       <c r="H1389" t="s">
         <v>9</v>
@@ -40994,7 +40994,7 @@
         <v>4.59499979019165</v>
       </c>
       <c r="G1390" t="s">
-        <v>863</v>
+        <v>864</v>
       </c>
       <c r="H1390" t="s">
         <v>9</v>
@@ -41020,7 +41020,7 @@
         <v>4.50500011444092</v>
       </c>
       <c r="G1391" t="s">
-        <v>872</v>
+        <v>873</v>
       </c>
       <c r="H1391" t="s">
         <v>9</v>
@@ -41046,7 +41046,7 @@
         <v>4.4850001335144</v>
       </c>
       <c r="G1392" t="s">
-        <v>873</v>
+        <v>874</v>
       </c>
       <c r="H1392" t="s">
         <v>9</v>
@@ -41072,7 +41072,7 @@
         <v>4.53499984741211</v>
       </c>
       <c r="G1393" t="s">
-        <v>874</v>
+        <v>875</v>
       </c>
       <c r="H1393" t="s">
         <v>9</v>
@@ -41098,7 +41098,7 @@
         <v>4.67999982833862</v>
       </c>
       <c r="G1394" t="s">
-        <v>868</v>
+        <v>869</v>
       </c>
       <c r="H1394" t="s">
         <v>9</v>
@@ -41124,7 +41124,7 @@
         <v>4.69500017166138</v>
       </c>
       <c r="G1395" t="s">
-        <v>875</v>
+        <v>876</v>
       </c>
       <c r="H1395" t="s">
         <v>9</v>
@@ -41150,7 +41150,7 @@
         <v>4.71999979019165</v>
       </c>
       <c r="G1396" t="s">
-        <v>876</v>
+        <v>877</v>
       </c>
       <c r="H1396" t="s">
         <v>9</v>
@@ -41176,7 +41176,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G1397" t="s">
-        <v>869</v>
+        <v>870</v>
       </c>
       <c r="H1397" t="s">
         <v>9</v>
@@ -41202,7 +41202,7 @@
         <v>4.75</v>
       </c>
       <c r="G1398" t="s">
-        <v>877</v>
+        <v>878</v>
       </c>
       <c r="H1398" t="s">
         <v>9</v>
@@ -41228,7 +41228,7 @@
         <v>4.71999979019165</v>
       </c>
       <c r="G1399" t="s">
-        <v>876</v>
+        <v>877</v>
       </c>
       <c r="H1399" t="s">
         <v>9</v>
@@ -41254,7 +41254,7 @@
         <v>4.69000005722046</v>
       </c>
       <c r="G1400" t="s">
-        <v>878</v>
+        <v>879</v>
       </c>
       <c r="H1400" t="s">
         <v>9</v>
@@ -41280,7 +41280,7 @@
         <v>4.69500017166138</v>
       </c>
       <c r="G1401" t="s">
-        <v>875</v>
+        <v>876</v>
       </c>
       <c r="H1401" t="s">
         <v>9</v>
@@ -41306,7 +41306,7 @@
         <v>4.59000015258789</v>
       </c>
       <c r="G1402" t="s">
-        <v>865</v>
+        <v>866</v>
       </c>
       <c r="H1402" t="s">
         <v>9</v>
@@ -41332,7 +41332,7 @@
         <v>4.5</v>
       </c>
       <c r="G1403" t="s">
-        <v>849</v>
+        <v>850</v>
       </c>
       <c r="H1403" t="s">
         <v>9</v>
@@ -41358,7 +41358,7 @@
         <v>4.38000011444092</v>
       </c>
       <c r="G1404" t="s">
-        <v>879</v>
+        <v>880</v>
       </c>
       <c r="H1404" t="s">
         <v>9</v>
@@ -41384,7 +41384,7 @@
         <v>4.3600001335144</v>
       </c>
       <c r="G1405" t="s">
-        <v>880</v>
+        <v>881</v>
       </c>
       <c r="H1405" t="s">
         <v>9</v>
@@ -41410,7 +41410,7 @@
         <v>4.32999992370605</v>
       </c>
       <c r="G1406" t="s">
-        <v>881</v>
+        <v>882</v>
       </c>
       <c r="H1406" t="s">
         <v>9</v>
@@ -41436,7 +41436,7 @@
         <v>4.32499980926514</v>
       </c>
       <c r="G1407" t="s">
-        <v>882</v>
+        <v>883</v>
       </c>
       <c r="H1407" t="s">
         <v>9</v>
@@ -41462,7 +41462,7 @@
         <v>4.25</v>
       </c>
       <c r="G1408" t="s">
-        <v>883</v>
+        <v>884</v>
       </c>
       <c r="H1408" t="s">
         <v>9</v>
@@ -41488,7 +41488,7 @@
         <v>4.14499998092651</v>
       </c>
       <c r="G1409" t="s">
-        <v>884</v>
+        <v>885</v>
       </c>
       <c r="H1409" t="s">
         <v>9</v>
@@ -41514,7 +41514,7 @@
         <v>4.09000015258789</v>
       </c>
       <c r="G1410" t="s">
-        <v>885</v>
+        <v>886</v>
       </c>
       <c r="H1410" t="s">
         <v>9</v>
@@ -41540,7 +41540,7 @@
         <v>4.27500009536743</v>
       </c>
       <c r="G1411" t="s">
-        <v>886</v>
+        <v>887</v>
       </c>
       <c r="H1411" t="s">
         <v>9</v>
@@ -41566,7 +41566,7 @@
         <v>4.3899998664856</v>
       </c>
       <c r="G1412" t="s">
-        <v>887</v>
+        <v>888</v>
       </c>
       <c r="H1412" t="s">
         <v>9</v>
@@ -41592,7 +41592,7 @@
         <v>4.5</v>
       </c>
       <c r="G1413" t="s">
-        <v>849</v>
+        <v>850</v>
       </c>
       <c r="H1413" t="s">
         <v>9</v>
@@ -41618,7 +41618,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G1414" t="s">
-        <v>888</v>
+        <v>840</v>
       </c>
       <c r="H1414" t="s">
         <v>9</v>
@@ -41644,7 +41644,7 @@
         <v>4.32999992370605</v>
       </c>
       <c r="G1415" t="s">
-        <v>881</v>
+        <v>882</v>
       </c>
       <c r="H1415" t="s">
         <v>9</v>
@@ -41748,7 +41748,7 @@
         <v>4.5</v>
       </c>
       <c r="G1419" t="s">
-        <v>849</v>
+        <v>850</v>
       </c>
       <c r="H1419" t="s">
         <v>9</v>
@@ -41774,7 +41774,7 @@
         <v>4.50500011444092</v>
       </c>
       <c r="G1420" t="s">
-        <v>872</v>
+        <v>873</v>
       </c>
       <c r="H1420" t="s">
         <v>9</v>
@@ -41800,7 +41800,7 @@
         <v>4.44999980926514</v>
       </c>
       <c r="G1421" t="s">
-        <v>858</v>
+        <v>859</v>
       </c>
       <c r="H1421" t="s">
         <v>9</v>
@@ -41826,7 +41826,7 @@
         <v>4.44000005722046</v>
       </c>
       <c r="G1422" t="s">
-        <v>850</v>
+        <v>851</v>
       </c>
       <c r="H1422" t="s">
         <v>9</v>
@@ -41878,7 +41878,7 @@
         <v>4.5</v>
       </c>
       <c r="G1424" t="s">
-        <v>849</v>
+        <v>850</v>
       </c>
       <c r="H1424" t="s">
         <v>9</v>
@@ -41904,7 +41904,7 @@
         <v>4.46500015258789</v>
       </c>
       <c r="G1425" t="s">
-        <v>855</v>
+        <v>856</v>
       </c>
       <c r="H1425" t="s">
         <v>9</v>
@@ -41956,7 +41956,7 @@
         <v>4.51000022888184</v>
       </c>
       <c r="G1427" t="s">
-        <v>861</v>
+        <v>862</v>
       </c>
       <c r="H1427" t="s">
         <v>9</v>
@@ -41982,7 +41982,7 @@
         <v>4.5</v>
       </c>
       <c r="G1428" t="s">
-        <v>849</v>
+        <v>850</v>
       </c>
       <c r="H1428" t="s">
         <v>9</v>
@@ -42008,7 +42008,7 @@
         <v>4.43499994277954</v>
       </c>
       <c r="G1429" t="s">
-        <v>854</v>
+        <v>855</v>
       </c>
       <c r="H1429" t="s">
         <v>9</v>
@@ -42034,7 +42034,7 @@
         <v>4.3600001335144</v>
       </c>
       <c r="G1430" t="s">
-        <v>880</v>
+        <v>881</v>
       </c>
       <c r="H1430" t="s">
         <v>9</v>
@@ -42060,7 +42060,7 @@
         <v>4.42500019073486</v>
       </c>
       <c r="G1431" t="s">
-        <v>860</v>
+        <v>861</v>
       </c>
       <c r="H1431" t="s">
         <v>9</v>
@@ -42086,7 +42086,7 @@
         <v>4.38000011444092</v>
       </c>
       <c r="G1432" t="s">
-        <v>879</v>
+        <v>880</v>
       </c>
       <c r="H1432" t="s">
         <v>9</v>
@@ -42216,7 +42216,7 @@
         <v>4.49499988555908</v>
       </c>
       <c r="G1437" t="s">
-        <v>851</v>
+        <v>852</v>
       </c>
       <c r="H1437" t="s">
         <v>9</v>
@@ -42268,7 +42268,7 @@
         <v>4.44999980926514</v>
       </c>
       <c r="G1439" t="s">
-        <v>858</v>
+        <v>859</v>
       </c>
       <c r="H1439" t="s">
         <v>9</v>
@@ -42294,7 +42294,7 @@
         <v>4.48000001907349</v>
       </c>
       <c r="G1440" t="s">
-        <v>856</v>
+        <v>857</v>
       </c>
       <c r="H1440" t="s">
         <v>9</v>
@@ -42372,7 +42372,7 @@
         <v>4.44000005722046</v>
       </c>
       <c r="G1443" t="s">
-        <v>850</v>
+        <v>851</v>
       </c>
       <c r="H1443" t="s">
         <v>9</v>
@@ -42398,7 +42398,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G1444" t="s">
-        <v>871</v>
+        <v>872</v>
       </c>
       <c r="H1444" t="s">
         <v>9</v>
@@ -42424,7 +42424,7 @@
         <v>4.61499977111816</v>
       </c>
       <c r="G1445" t="s">
-        <v>844</v>
+        <v>845</v>
       </c>
       <c r="H1445" t="s">
         <v>9</v>
@@ -42450,7 +42450,7 @@
         <v>4.51000022888184</v>
       </c>
       <c r="G1446" t="s">
-        <v>861</v>
+        <v>862</v>
       </c>
       <c r="H1446" t="s">
         <v>9</v>
@@ -42476,7 +42476,7 @@
         <v>4.4850001335144</v>
       </c>
       <c r="G1447" t="s">
-        <v>873</v>
+        <v>874</v>
       </c>
       <c r="H1447" t="s">
         <v>9</v>
@@ -42502,7 +42502,7 @@
         <v>4.51000022888184</v>
       </c>
       <c r="G1448" t="s">
-        <v>861</v>
+        <v>862</v>
       </c>
       <c r="H1448" t="s">
         <v>9</v>
@@ -42528,7 +42528,7 @@
         <v>4.63000011444092</v>
       </c>
       <c r="G1449" t="s">
-        <v>870</v>
+        <v>871</v>
       </c>
       <c r="H1449" t="s">
         <v>9</v>
@@ -42580,7 +42580,7 @@
         <v>4.57000017166138</v>
       </c>
       <c r="G1451" t="s">
-        <v>841</v>
+        <v>842</v>
       </c>
       <c r="H1451" t="s">
         <v>9</v>
@@ -42632,7 +42632,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G1453" t="s">
-        <v>869</v>
+        <v>870</v>
       </c>
       <c r="H1453" t="s">
         <v>9</v>
@@ -42684,7 +42684,7 @@
         <v>4.58500003814697</v>
       </c>
       <c r="G1455" t="s">
-        <v>866</v>
+        <v>867</v>
       </c>
       <c r="H1455" t="s">
         <v>9</v>
@@ -42814,7 +42814,7 @@
         <v>4.57999992370605</v>
       </c>
       <c r="G1460" t="s">
-        <v>847</v>
+        <v>848</v>
       </c>
       <c r="H1460" t="s">
         <v>9</v>
@@ -42892,7 +42892,7 @@
         <v>4.55000019073486</v>
       </c>
       <c r="G1463" t="s">
-        <v>862</v>
+        <v>863</v>
       </c>
       <c r="H1463" t="s">
         <v>9</v>
@@ -42918,7 +42918,7 @@
         <v>4.58500003814697</v>
       </c>
       <c r="G1464" t="s">
-        <v>866</v>
+        <v>867</v>
       </c>
       <c r="H1464" t="s">
         <v>9</v>
@@ -42944,7 +42944,7 @@
         <v>4.69000005722046</v>
       </c>
       <c r="G1465" t="s">
-        <v>878</v>
+        <v>879</v>
       </c>
       <c r="H1465" t="s">
         <v>9</v>
@@ -42996,7 +42996,7 @@
         <v>4.69500017166138</v>
       </c>
       <c r="G1467" t="s">
-        <v>875</v>
+        <v>876</v>
       </c>
       <c r="H1467" t="s">
         <v>9</v>
@@ -43022,7 +43022,7 @@
         <v>4.68499994277954</v>
       </c>
       <c r="G1468" t="s">
-        <v>845</v>
+        <v>846</v>
       </c>
       <c r="H1468" t="s">
         <v>9</v>
@@ -43100,7 +43100,7 @@
         <v>4.71999979019165</v>
       </c>
       <c r="G1471" t="s">
-        <v>876</v>
+        <v>877</v>
       </c>
       <c r="H1471" t="s">
         <v>9</v>
@@ -43126,7 +43126,7 @@
         <v>4.71999979019165</v>
       </c>
       <c r="G1472" t="s">
-        <v>876</v>
+        <v>877</v>
       </c>
       <c r="H1472" t="s">
         <v>9</v>
@@ -45726,7 +45726,7 @@
         <v>4.71999979019165</v>
       </c>
       <c r="G1572" t="s">
-        <v>876</v>
+        <v>877</v>
       </c>
       <c r="H1572" t="s">
         <v>9</v>
@@ -71474,7 +71474,7 @@
     </row>
     <row r="2563">
       <c r="A2563" s="1" t="n">
-        <v>46055.6913078704</v>
+        <v>46055.3333333333</v>
       </c>
       <c r="B2563" t="n">
         <v>17930</v>
@@ -71495,6 +71495,32 @@
         <v>1503</v>
       </c>
       <c r="H2563" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2564">
+      <c r="A2564" s="1" t="n">
+        <v>46056.6911226852</v>
+      </c>
+      <c r="B2564" t="n">
+        <v>21099</v>
+      </c>
+      <c r="C2564" t="n">
+        <v>7.38000011444092</v>
+      </c>
+      <c r="D2564" t="n">
+        <v>7.19000005722046</v>
+      </c>
+      <c r="E2564" t="n">
+        <v>7.36999988555908</v>
+      </c>
+      <c r="F2564" t="n">
+        <v>7.19000005722046</v>
+      </c>
+      <c r="G2564" t="s">
+        <v>1490</v>
+      </c>
+      <c r="H2564" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/BAN.MI.xlsx
+++ b/data/BAN.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1512" uniqueCount="1512">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1513" uniqueCount="1513">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -47,31 +47,31 @@
     <t xml:space="preserve">3.68330240249634</t>
   </si>
   <si>
-    <t xml:space="preserve">3.59039306640625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.46283912658691</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.41874694824219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.35733246803284</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.44551801681519</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.46441459655762</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.45181608200073</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.43134498596191</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.38410258293152</t>
+    <t xml:space="preserve">3.59039258956909</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.46283960342407</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.41874718666077</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.35733270645142</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.44551753997803</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.46441435813904</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.45181632041931</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.43134474754333</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.38410305976868</t>
   </si>
   <si>
     <t xml:space="preserve">3.40929889678955</t>
@@ -80,31 +80,31 @@
     <t xml:space="preserve">3.11639857292175</t>
   </si>
   <si>
-    <t xml:space="preserve">3.24080228805542</t>
+    <t xml:space="preserve">3.240802526474</t>
   </si>
   <si>
     <t xml:space="preserve">3.29119348526001</t>
   </si>
   <si>
-    <t xml:space="preserve">3.21245741844177</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.26757287979126</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.19356036186218</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.13372015953064</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.22820425033569</t>
+    <t xml:space="preserve">3.21245670318604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.26757311820984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.19356060028076</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.1337206363678</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.22820448875427</t>
   </si>
   <si>
     <t xml:space="preserve">3.16678977012634</t>
   </si>
   <si>
-    <t xml:space="preserve">3.17308855056763</t>
+    <t xml:space="preserve">3.17308926582336</t>
   </si>
   <si>
     <t xml:space="preserve">3.0707311630249</t>
@@ -116,37 +116,37 @@
     <t xml:space="preserve">3.05025959014893</t>
   </si>
   <si>
-    <t xml:space="preserve">2.92900490760803</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.91325807571411</t>
+    <t xml:space="preserve">2.92900514602661</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.91325783729553</t>
   </si>
   <si>
     <t xml:space="preserve">2.8345205783844</t>
   </si>
   <si>
-    <t xml:space="preserve">2.82664704322815</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.75263428688049</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.75420951843262</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.75578427314758</t>
+    <t xml:space="preserve">2.82664752006531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.75263452529907</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.75420928001404</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.755784034729</t>
   </si>
   <si>
     <t xml:space="preserve">2.89436078071594</t>
   </si>
   <si>
-    <t xml:space="preserve">2.98254561424255</t>
+    <t xml:space="preserve">2.98254585266113</t>
   </si>
   <si>
     <t xml:space="preserve">2.96207451820374</t>
   </si>
   <si>
-    <t xml:space="preserve">2.99356937408447</t>
+    <t xml:space="preserve">2.99356913566589</t>
   </si>
   <si>
     <t xml:space="preserve">3.05970788002014</t>
@@ -155,22 +155,22 @@
     <t xml:space="preserve">3.11009931564331</t>
   </si>
   <si>
-    <t xml:space="preserve">3.06915616989136</t>
+    <t xml:space="preserve">3.06915640830994</t>
   </si>
   <si>
     <t xml:space="preserve">2.96364903450012</t>
   </si>
   <si>
-    <t xml:space="preserve">2.99199438095093</t>
+    <t xml:space="preserve">2.99199414253235</t>
   </si>
   <si>
     <t xml:space="preserve">3.00774168968201</t>
   </si>
   <si>
-    <t xml:space="preserve">2.97624731063843</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.06285738945007</t>
+    <t xml:space="preserve">2.97624683380127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.06285762786865</t>
   </si>
   <si>
     <t xml:space="preserve">3.11797308921814</t>
@@ -182,64 +182,64 @@
     <t xml:space="preserve">3.10222578048706</t>
   </si>
   <si>
-    <t xml:space="preserve">3.13686966896057</t>
+    <t xml:space="preserve">3.13687014579773</t>
   </si>
   <si>
     <t xml:space="preserve">3.23292851448059</t>
   </si>
   <si>
-    <t xml:space="preserve">3.33843588829041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.30694079399109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.24395203590393</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.24237751960754</t>
+    <t xml:space="preserve">3.33843564987183</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.30694103240967</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.24395179748535</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.24237704277039</t>
   </si>
   <si>
     <t xml:space="preserve">3.12584686279297</t>
   </si>
   <si>
-    <t xml:space="preserve">3.19670939445496</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.20300841331482</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.10380005836487</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.11324906349182</t>
+    <t xml:space="preserve">3.19670963287354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.2030086517334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.10380029678345</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.11324882507324</t>
   </si>
   <si>
     <t xml:space="preserve">3.14159417152405</t>
   </si>
   <si>
-    <t xml:space="preserve">3.04710960388184</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.99986791610718</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.96049952507019</t>
+    <t xml:space="preserve">3.04710984230042</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.99986815452576</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.96049904823303</t>
   </si>
   <si>
     <t xml:space="preserve">3.09435224533081</t>
   </si>
   <si>
-    <t xml:space="preserve">2.96837329864502</t>
+    <t xml:space="preserve">2.9683735370636</t>
   </si>
   <si>
     <t xml:space="preserve">2.86286592483521</t>
   </si>
   <si>
-    <t xml:space="preserve">2.87388968467712</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.91010856628418</t>
+    <t xml:space="preserve">2.87388920783997</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.91010808944702</t>
   </si>
   <si>
     <t xml:space="preserve">2.98569536209106</t>
@@ -248,7 +248,7 @@
     <t xml:space="preserve">3.00144290924072</t>
   </si>
   <si>
-    <t xml:space="preserve">3.01561570167542</t>
+    <t xml:space="preserve">3.01561522483826</t>
   </si>
   <si>
     <t xml:space="preserve">2.92743015289307</t>
@@ -260,28 +260,28 @@
     <t xml:space="preserve">2.85814213752747</t>
   </si>
   <si>
-    <t xml:space="preserve">2.814049243927</t>
+    <t xml:space="preserve">2.81404972076416</t>
   </si>
   <si>
     <t xml:space="preserve">2.84081983566284</t>
   </si>
   <si>
-    <t xml:space="preserve">2.80145144462585</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.72901368141174</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.65185213088989</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.68177175521851</t>
+    <t xml:space="preserve">2.80145168304443</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.7290141582489</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.65185165405273</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.68177151679993</t>
   </si>
   <si>
     <t xml:space="preserve">2.71484088897705</t>
   </si>
   <si>
-    <t xml:space="preserve">2.76365804672241</t>
+    <t xml:space="preserve">2.76365828514099</t>
   </si>
   <si>
     <t xml:space="preserve">2.77940511703491</t>
@@ -290,28 +290,28 @@
     <t xml:space="preserve">2.72428965568542</t>
   </si>
   <si>
-    <t xml:space="preserve">2.59043717384338</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.5353217124939</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.49437808990479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.48020577430725</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.51957440376282</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.60572695732117</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.58784627914429</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.5602126121521</t>
+    <t xml:space="preserve">2.5904369354248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.53532123565674</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.49437856674194</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.48020601272583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.51957392692566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.60572743415833</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.58784675598145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.56021285057068</t>
   </si>
   <si>
     <t xml:space="preserve">2.56183815002441</t>
@@ -323,46 +323,43 @@
     <t xml:space="preserve">2.59272336959839</t>
   </si>
   <si>
-    <t xml:space="preserve">2.58134436607361</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.60085082054138</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.72113990783691</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.82029747962952</t>
+    <t xml:space="preserve">2.58134460449219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.60085105895996</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.72113966941833</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.82029724121094</t>
   </si>
   <si>
     <t xml:space="preserve">2.80404210090637</t>
   </si>
   <si>
-    <t xml:space="preserve">2.68212723731995</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.71463751792908</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.44642519950867</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.39765954017639</t>
+    <t xml:space="preserve">2.6821277141571</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.71463775634766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.44642496109009</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.39765906333923</t>
   </si>
   <si>
     <t xml:space="preserve">2.50331878662109</t>
   </si>
   <si>
-    <t xml:space="preserve">2.47568464279175</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.51957416534424</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.52770209312439</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.50819540023804</t>
+    <t xml:space="preserve">2.47568488121033</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.52770185470581</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.50819563865662</t>
   </si>
   <si>
     <t xml:space="preserve">2.40578699111938</t>
@@ -371,22 +368,22 @@
     <t xml:space="preserve">2.19446778297424</t>
   </si>
   <si>
-    <t xml:space="preserve">2.2351062297821</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.29525065422058</t>
+    <t xml:space="preserve">2.23510599136353</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.29525089263916</t>
   </si>
   <si>
     <t xml:space="preserve">2.27411913871765</t>
   </si>
   <si>
-    <t xml:space="preserve">2.35702109336853</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.37327647209167</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.29199981689453</t>
+    <t xml:space="preserve">2.35702085494995</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.3732762336731</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.29200005531311</t>
   </si>
   <si>
     <t xml:space="preserve">2.19284248352051</t>
@@ -395,22 +392,22 @@
     <t xml:space="preserve">2.22535276412964</t>
   </si>
   <si>
-    <t xml:space="preserve">2.28387188911438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.30500388145447</t>
+    <t xml:space="preserve">2.2838716506958</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.30500411987305</t>
   </si>
   <si>
     <t xml:space="preserve">2.33101224899292</t>
   </si>
   <si>
-    <t xml:space="preserve">2.33588933944702</t>
+    <t xml:space="preserve">2.33588886260986</t>
   </si>
   <si>
     <t xml:space="preserve">2.33263802528381</t>
   </si>
   <si>
-    <t xml:space="preserve">2.31963396072388</t>
+    <t xml:space="preserve">2.3196337223053</t>
   </si>
   <si>
     <t xml:space="preserve">2.38140392303467</t>
@@ -419,28 +416,28 @@
     <t xml:space="preserve">2.53582954406738</t>
   </si>
   <si>
-    <t xml:space="preserve">2.54395723342896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.56834006309509</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.8966977596283</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.83817839622498</t>
+    <t xml:space="preserve">2.54395747184753</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.56834030151367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.89669728279114</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.83817863464355</t>
   </si>
   <si>
     <t xml:space="preserve">2.81216979026794</t>
   </si>
   <si>
-    <t xml:space="preserve">2.59597396850586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.57646775245667</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.57321667671204</t>
+    <t xml:space="preserve">2.59597420692444</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.57646799087524</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.57321643829346</t>
   </si>
   <si>
     <t xml:space="preserve">2.56671476364136</t>
@@ -455,10 +452,10 @@
     <t xml:space="preserve">2.6366126537323</t>
   </si>
   <si>
-    <t xml:space="preserve">2.63011074066162</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.64636564254761</t>
+    <t xml:space="preserve">2.63011050224304</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.64636540412903</t>
   </si>
   <si>
     <t xml:space="preserve">2.65286779403687</t>
@@ -467,55 +464,55 @@
     <t xml:space="preserve">2.63823795318604</t>
   </si>
   <si>
-    <t xml:space="preserve">2.64148926734924</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.69188094139099</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.75690197944641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.79266357421875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.76340413093567</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.73089337348938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.65449333190918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.65774440765381</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.74227237701416</t>
+    <t xml:space="preserve">2.64148902893066</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.69188070297241</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.75690150260925</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.79266381263733</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.76340389251709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.7308931350708</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.65449357032776</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.65774416923523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.74227213859558</t>
   </si>
   <si>
     <t xml:space="preserve">2.76828026771545</t>
   </si>
   <si>
-    <t xml:space="preserve">2.70651030540466</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.72764229774475</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.74064636230469</t>
+    <t xml:space="preserve">2.70651006698608</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.72764182090759</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.74064683914185</t>
   </si>
   <si>
     <t xml:space="preserve">2.76990604400635</t>
   </si>
   <si>
-    <t xml:space="preserve">2.8007915019989</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.69513177871704</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.66749739646912</t>
+    <t xml:space="preserve">2.80079102516174</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.69513154029846</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.6674976348877</t>
   </si>
   <si>
     <t xml:space="preserve">2.64799118041992</t>
@@ -524,19 +521,19 @@
     <t xml:space="preserve">2.62523365020752</t>
   </si>
   <si>
-    <t xml:space="preserve">2.59759974479675</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.61710619926453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.66587162017822</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.63336133956909</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.68862986564636</t>
+    <t xml:space="preserve">2.59759998321533</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.61710596084595</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.66587233543396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.63336157798767</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.68862962722778</t>
   </si>
   <si>
     <t xml:space="preserve">2.6024763584137</t>
@@ -554,19 +551,19 @@
     <t xml:space="preserve">2.72601675987244</t>
   </si>
   <si>
-    <t xml:space="preserve">2.72276544570923</t>
+    <t xml:space="preserve">2.72276568412781</t>
   </si>
   <si>
     <t xml:space="preserve">2.82842516899109</t>
   </si>
   <si>
-    <t xml:space="preserve">2.7438976764679</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.7617781162262</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.73902106285095</t>
+    <t xml:space="preserve">2.74389743804932</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.76177835464478</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.73902058601379</t>
   </si>
   <si>
     <t xml:space="preserve">2.70488476753235</t>
@@ -575,25 +572,25 @@
     <t xml:space="preserve">2.69025492668152</t>
   </si>
   <si>
-    <t xml:space="preserve">2.612229347229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.73251891136169</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.67562508583069</t>
+    <t xml:space="preserve">2.61222982406616</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.73251843452454</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.67562532424927</t>
   </si>
   <si>
     <t xml:space="preserve">2.62360835075378</t>
   </si>
   <si>
-    <t xml:space="preserve">2.59434866905212</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.55371022224426</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.55045914649963</t>
+    <t xml:space="preserve">2.5943489074707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.55371069908142</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.55045938491821</t>
   </si>
   <si>
     <t xml:space="preserve">2.51307201385498</t>
@@ -611,7 +608,7 @@
     <t xml:space="preserve">2.6317355632782</t>
   </si>
   <si>
-    <t xml:space="preserve">2.65611910820007</t>
+    <t xml:space="preserve">2.65611863136292</t>
   </si>
   <si>
     <t xml:space="preserve">2.66912293434143</t>
@@ -620,64 +617,64 @@
     <t xml:space="preserve">2.72439122200012</t>
   </si>
   <si>
-    <t xml:space="preserve">2.78291058540344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.77153158187866</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.77803373336792</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.70000839233398</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.77315664291382</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.76502919197083</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.71788883209229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.74552321434021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.77965927124023</t>
+    <t xml:space="preserve">2.78291034698486</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.77153182029724</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.77803349494934</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.70000815391541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.7731568813324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.7650294303894</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.71788907051086</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.74552297592163</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.77965903282166</t>
   </si>
   <si>
     <t xml:space="preserve">2.74714875221252</t>
   </si>
   <si>
-    <t xml:space="preserve">2.60410189628601</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.62685918807983</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.64961671829224</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.69350576400757</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.69838285446167</t>
+    <t xml:space="preserve">2.60410165786743</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.62685894966125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.64961695671082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.69350600242615</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.69838261604309</t>
   </si>
   <si>
     <t xml:space="preserve">2.92270588874817</t>
   </si>
   <si>
-    <t xml:space="preserve">2.88531851768494</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.99910616874695</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.97472286224365</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.96984624862671</t>
+    <t xml:space="preserve">2.88531875610352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.99910593032837</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.97472310066223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.96984648704529</t>
   </si>
   <si>
     <t xml:space="preserve">2.96334433555603</t>
@@ -689,31 +686,31 @@
     <t xml:space="preserve">2.93408465385437</t>
   </si>
   <si>
-    <t xml:space="preserve">2.89832305908203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.89182090759277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.87881636619568</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.87556552886963</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.84468078613281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.82192301750183</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.84955716133118</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.91945481300354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.92595672607422</t>
+    <t xml:space="preserve">2.89832353591919</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.89182114601135</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.87881660461426</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.87556576728821</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.84468054771423</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.82192277908325</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.8495569229126</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.91945505142212</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.9259569644928</t>
   </si>
   <si>
     <t xml:space="preserve">2.99097847938538</t>
@@ -722,16 +719,16 @@
     <t xml:space="preserve">2.91457843780518</t>
   </si>
   <si>
-    <t xml:space="preserve">2.91620397567749</t>
+    <t xml:space="preserve">2.91620421409607</t>
   </si>
   <si>
     <t xml:space="preserve">2.95846796035767</t>
   </si>
   <si>
-    <t xml:space="preserve">2.95684266090393</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.95196580886841</t>
+    <t xml:space="preserve">2.95684218406677</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.95196557044983</t>
   </si>
   <si>
     <t xml:space="preserve">3.04949760437012</t>
@@ -740,67 +737,67 @@
     <t xml:space="preserve">3.05599975585938</t>
   </si>
   <si>
-    <t xml:space="preserve">2.99585485458374</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.9795994758606</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.00723385810852</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.09645938873291</t>
+    <t xml:space="preserve">2.99585461616516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.97959971427917</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.00723361968994</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.09645891189575</t>
   </si>
   <si>
     <t xml:space="preserve">3.11628723144531</t>
   </si>
   <si>
-    <t xml:space="preserve">3.16916179656982</t>
+    <t xml:space="preserve">3.16916155815125</t>
   </si>
   <si>
     <t xml:space="preserve">3.13941979408264</t>
   </si>
   <si>
-    <t xml:space="preserve">3.14437699317932</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.18898940086365</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.18072772026062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.24847340583801</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.21707940101624</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.16750931739807</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.15429067611694</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.17081427574158</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.07663154602051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.07497906684875</t>
+    <t xml:space="preserve">3.14437651634216</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.18898963928223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.1807279586792</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.24847316741943</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.21707916259766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.16750955581665</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.1542911529541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.17081379890442</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.07663130760193</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.07497882843018</t>
   </si>
   <si>
     <t xml:space="preserve">2.98244857788086</t>
   </si>
   <si>
-    <t xml:space="preserve">3.05845594406128</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.06506514549255</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.03367066383362</t>
+    <t xml:space="preserve">3.0584557056427</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.06506538391113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.03367114067078</t>
   </si>
   <si>
     <t xml:space="preserve">3.02540946006775</t>
@@ -821,22 +818,22 @@
     <t xml:space="preserve">2.95601177215576</t>
   </si>
   <si>
-    <t xml:space="preserve">3.07993578910828</t>
+    <t xml:space="preserve">3.07993602752686</t>
   </si>
   <si>
     <t xml:space="preserve">3.08819770812988</t>
   </si>
   <si>
-    <t xml:space="preserve">3.08654522895813</t>
+    <t xml:space="preserve">3.08654546737671</t>
   </si>
   <si>
     <t xml:space="preserve">3.10802578926086</t>
   </si>
   <si>
-    <t xml:space="preserve">3.11133003234863</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.14768123626709</t>
+    <t xml:space="preserve">3.11133027076721</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.14768147468567</t>
   </si>
   <si>
     <t xml:space="preserve">3.16420459747314</t>
@@ -845,13 +842,13 @@
     <t xml:space="preserve">3.20551300048828</t>
   </si>
   <si>
-    <t xml:space="preserve">3.21377444267273</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.23029780387878</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.23360228538513</t>
+    <t xml:space="preserve">3.21377468109131</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.23029804229736</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.23360252380371</t>
   </si>
   <si>
     <t xml:space="preserve">3.25343036651611</t>
@@ -860,22 +857,22 @@
     <t xml:space="preserve">3.29473829269409</t>
   </si>
   <si>
-    <t xml:space="preserve">3.3079571723938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.27160596847534</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.29639077186584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.22368812561035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.25012540817261</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.19394659996033</t>
+    <t xml:space="preserve">3.30795741081238</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.27160573005676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.29639053344727</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.22368836402893</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.25012564659119</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.19394636154175</t>
   </si>
   <si>
     <t xml:space="preserve">3.26334428787231</t>
@@ -896,10 +893,10 @@
     <t xml:space="preserve">3.15098595619202</t>
   </si>
   <si>
-    <t xml:space="preserve">3.05184650421143</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.05680346488953</t>
+    <t xml:space="preserve">3.05184626579285</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.05680370330811</t>
   </si>
   <si>
     <t xml:space="preserve">3.08489298820496</t>
@@ -911,16 +908,16 @@
     <t xml:space="preserve">3.03201866149902</t>
   </si>
   <si>
-    <t xml:space="preserve">3.09480714797974</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.073326587677</t>
+    <t xml:space="preserve">3.09480690956116</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.07332682609558</t>
   </si>
   <si>
     <t xml:space="preserve">3.09150218963623</t>
   </si>
   <si>
-    <t xml:space="preserve">3.13115811347961</t>
+    <t xml:space="preserve">3.13115835189819</t>
   </si>
   <si>
     <t xml:space="preserve">3.10967779159546</t>
@@ -929,16 +926,16 @@
     <t xml:space="preserve">3.10472083091736</t>
   </si>
   <si>
-    <t xml:space="preserve">3.12124443054199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.13611483573914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.14602899551392</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.12950563430786</t>
+    <t xml:space="preserve">3.12124419212341</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.13611531257629</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.1460292339325</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.12950587272644</t>
   </si>
   <si>
     <t xml:space="preserve">3.14107203483582</t>
@@ -947,7 +944,7 @@
     <t xml:space="preserve">3.15759539604187</t>
   </si>
   <si>
-    <t xml:space="preserve">3.18403267860413</t>
+    <t xml:space="preserve">3.18403291702271</t>
   </si>
   <si>
     <t xml:space="preserve">3.10637331008911</t>
@@ -956,37 +953,37 @@
     <t xml:space="preserve">3.08158826828003</t>
   </si>
   <si>
-    <t xml:space="preserve">3.10141611099243</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.10306859016418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.12289643287659</t>
+    <t xml:space="preserve">3.10141634941101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.10306882858276</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.12289667129517</t>
   </si>
   <si>
     <t xml:space="preserve">3.08985018730164</t>
   </si>
   <si>
-    <t xml:space="preserve">2.94940233230591</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.93287873268127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.83704447746277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.88165688514709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.90809416770935</t>
+    <t xml:space="preserve">2.94940209388733</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.93287920951843</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.83704423904419</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.88165712356567</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.90809392929077</t>
   </si>
   <si>
     <t xml:space="preserve">2.91139888763428</t>
   </si>
   <si>
-    <t xml:space="preserve">2.9460973739624</t>
+    <t xml:space="preserve">2.94609785079956</t>
   </si>
   <si>
     <t xml:space="preserve">2.94114065170288</t>
@@ -995,34 +992,34 @@
     <t xml:space="preserve">2.96592545509338</t>
   </si>
   <si>
-    <t xml:space="preserve">2.8849618434906</t>
+    <t xml:space="preserve">2.88496160507202</t>
   </si>
   <si>
     <t xml:space="preserve">2.84034872055054</t>
   </si>
   <si>
-    <t xml:space="preserve">2.82878279685974</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.81225919723511</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.88000464439392</t>
+    <t xml:space="preserve">2.82878255844116</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.81225943565369</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.88000440597534</t>
   </si>
   <si>
     <t xml:space="preserve">2.75112271308899</t>
   </si>
   <si>
-    <t xml:space="preserve">2.80895495414734</t>
+    <t xml:space="preserve">2.80895447731018</t>
   </si>
   <si>
     <t xml:space="preserve">2.79243135452271</t>
   </si>
   <si>
-    <t xml:space="preserve">2.81391143798828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.85852456092834</t>
+    <t xml:space="preserve">2.81391167640686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.85852432250977</t>
   </si>
   <si>
     <t xml:space="preserve">2.97418713569641</t>
@@ -1031,31 +1028,31 @@
     <t xml:space="preserve">2.97088217735291</t>
   </si>
   <si>
-    <t xml:space="preserve">3.01549553871155</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.05515098571777</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.04028010368347</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.07002234458923</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.06341290473938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.02375721931458</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.03697538375854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.0287139415741</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.05349898338318</t>
+    <t xml:space="preserve">3.01549530029297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.05515146255493</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.04028034210205</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.07002186775208</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.0634126663208</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.023756980896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.03697562217712</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.02871370315552</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.0534987449646</t>
   </si>
   <si>
     <t xml:space="preserve">3.07828378677368</t>
@@ -1067,16 +1064,16 @@
     <t xml:space="preserve">3.06919574737549</t>
   </si>
   <si>
-    <t xml:space="preserve">3.15594291687012</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.21790552139282</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.17659687995911</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.19312024116516</t>
+    <t xml:space="preserve">3.15594244003296</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.21790504455566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.17659711837769</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.19312047958374</t>
   </si>
   <si>
     <t xml:space="preserve">3.25508260726929</t>
@@ -1085,52 +1082,52 @@
     <t xml:space="preserve">3.22203612327576</t>
   </si>
   <si>
-    <t xml:space="preserve">2.96179485321045</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.97831845283508</t>
+    <t xml:space="preserve">2.96179461479187</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.9783182144165</t>
   </si>
   <si>
     <t xml:space="preserve">2.92461729049683</t>
   </si>
   <si>
-    <t xml:space="preserve">2.87504768371582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.13528919219971</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.07745766639709</t>
+    <t xml:space="preserve">2.87504744529724</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.13528895378113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.07745742797852</t>
   </si>
   <si>
     <t xml:space="preserve">3.05267286300659</t>
   </si>
   <si>
-    <t xml:space="preserve">3.03614926338196</t>
+    <t xml:space="preserve">3.03614974021912</t>
   </si>
   <si>
     <t xml:space="preserve">2.92048668861389</t>
   </si>
   <si>
-    <t xml:space="preserve">3.08571887016296</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.0196259021759</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.02788805961609</t>
+    <t xml:space="preserve">3.08571910858154</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.01962614059448</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.02788758277893</t>
   </si>
   <si>
     <t xml:space="preserve">3.0485417842865</t>
   </si>
   <si>
-    <t xml:space="preserve">3.04441046714783</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.15181231498718</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.33769869804382</t>
+    <t xml:space="preserve">3.04441070556641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.1518120765686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.3376989364624</t>
   </si>
   <si>
     <t xml:space="preserve">3.25095176696777</t>
@@ -1142,22 +1139,22 @@
     <t xml:space="preserve">3.2839982509613</t>
   </si>
   <si>
-    <t xml:space="preserve">3.24682092666626</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.18485856056213</t>
+    <t xml:space="preserve">3.24682068824768</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.18485879898071</t>
   </si>
   <si>
     <t xml:space="preserve">3.24373769760132</t>
   </si>
   <si>
-    <t xml:space="preserve">3.20177507400513</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.21016716957092</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.18918561935425</t>
+    <t xml:space="preserve">3.20177483558655</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.21016788482666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.18918609619141</t>
   </si>
   <si>
     <t xml:space="preserve">3.22275614738464</t>
@@ -1175,7 +1172,7 @@
     <t xml:space="preserve">3.14302659034729</t>
   </si>
   <si>
-    <t xml:space="preserve">3.20597124099731</t>
+    <t xml:space="preserve">3.20597052574158</t>
   </si>
   <si>
     <t xml:space="preserve">3.25632691383362</t>
@@ -1184,61 +1181,64 @@
     <t xml:space="preserve">3.24793410301208</t>
   </si>
   <si>
-    <t xml:space="preserve">3.10526013374329</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.07168936729431</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.18498992919922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.11365270614624</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.12624144554138</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.1388304233551</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.14722299575806</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.15561532974243</t>
+    <t xml:space="preserve">3.10526037216187</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.07168960571289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.18498945236206</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.17659735679626</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.11365294456482</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.1262412071228</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.13883066177368</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.14722275733948</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.15561580657959</t>
   </si>
   <si>
     <t xml:space="preserve">3.1724009513855</t>
   </si>
   <si>
-    <t xml:space="preserve">3.08427858352661</t>
+    <t xml:space="preserve">3.08427882194519</t>
   </si>
   <si>
     <t xml:space="preserve">3.13463401794434</t>
   </si>
   <si>
-    <t xml:space="preserve">3.16820454597473</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.10945630073547</t>
+    <t xml:space="preserve">3.16820406913757</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.10945606231689</t>
   </si>
   <si>
     <t xml:space="preserve">3.15981197357178</t>
   </si>
   <si>
-    <t xml:space="preserve">3.19338226318359</t>
+    <t xml:space="preserve">3.19338250160217</t>
   </si>
   <si>
     <t xml:space="preserve">3.21436381340027</t>
   </si>
   <si>
-    <t xml:space="preserve">3.23534512519836</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.26471924781799</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.32346725463867</t>
+    <t xml:space="preserve">3.23534536361694</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.26471972465515</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.32346749305725</t>
   </si>
   <si>
     <t xml:space="preserve">3.31087851524353</t>
@@ -1247,34 +1247,34 @@
     <t xml:space="preserve">3.27730798721313</t>
   </si>
   <si>
-    <t xml:space="preserve">3.35703778266907</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.42417883872986</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.49131917953491</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.43257164955139</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.54167509078979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.44935703277588</t>
+    <t xml:space="preserve">3.35703802108765</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.4241783618927</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.49131965637207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.43257141113281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.54167485237122</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.44935655593872</t>
   </si>
   <si>
     <t xml:space="preserve">3.48292684555054</t>
   </si>
   <si>
-    <t xml:space="preserve">3.51649737358093</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.47453427314758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.4577488899231</t>
+    <t xml:space="preserve">3.51649761199951</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.474534034729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.45774912834167</t>
   </si>
   <si>
     <t xml:space="preserve">3.3864119052887</t>
@@ -1283,25 +1283,25 @@
     <t xml:space="preserve">3.37801957130432</t>
   </si>
   <si>
-    <t xml:space="preserve">3.47033834457397</t>
+    <t xml:space="preserve">3.4703381061554</t>
   </si>
   <si>
     <t xml:space="preserve">3.30248618125916</t>
   </si>
   <si>
-    <t xml:space="preserve">3.31927108764648</t>
+    <t xml:space="preserve">3.31927132606506</t>
   </si>
   <si>
     <t xml:space="preserve">3.29828953742981</t>
   </si>
   <si>
-    <t xml:space="preserve">3.34025287628174</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.27311182022095</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.28150486946106</t>
+    <t xml:space="preserve">3.34025311470032</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.27311205863953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.28150463104248</t>
   </si>
   <si>
     <t xml:space="preserve">3.399001121521</t>
@@ -1310,217 +1310,217 @@
     <t xml:space="preserve">3.57524561882019</t>
   </si>
   <si>
-    <t xml:space="preserve">3.58783411979675</t>
+    <t xml:space="preserve">3.58783459663391</t>
   </si>
   <si>
     <t xml:space="preserve">3.55006742477417</t>
   </si>
   <si>
-    <t xml:space="preserve">3.5794415473938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.58363819122314</t>
+    <t xml:space="preserve">3.57944130897522</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.58363747596741</t>
   </si>
   <si>
     <t xml:space="preserve">3.66336750984192</t>
   </si>
   <si>
-    <t xml:space="preserve">3.55845975875854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.56685304641724</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.62140464782715</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.78086376190186</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.88577127456665</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.72211575508118</t>
+    <t xml:space="preserve">3.55845999717712</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.56685280799866</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.62140440940857</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.78086423873901</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.88577151298523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.7221155166626</t>
   </si>
   <si>
     <t xml:space="preserve">3.76407861709595</t>
   </si>
   <si>
-    <t xml:space="preserve">3.68434858322144</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.79764938354492</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.82702326774597</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.80184555053711</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.83961200714111</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.91934180259705</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.91094923019409</t>
+    <t xml:space="preserve">3.68434882164001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.79764890670776</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.82702255249023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.80184578895569</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.83961224555969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.9193422794342</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.91094899177551</t>
   </si>
   <si>
     <t xml:space="preserve">3.94451928138733</t>
   </si>
   <si>
-    <t xml:space="preserve">4.06621265411377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.02005338668823</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.92773389816284</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.86898589134216</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.81863045692444</t>
+    <t xml:space="preserve">4.06621217727661</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.02005290985107</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.927734375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.86898636817932</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.8186309337616</t>
   </si>
   <si>
     <t xml:space="preserve">3.86059379577637</t>
   </si>
   <si>
-    <t xml:space="preserve">3.79345297813416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.86478996276855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.8773787021637</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.73470449447632</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.8438081741333</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.69274187088013</t>
+    <t xml:space="preserve">3.793452501297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.86478972434998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.87737822532654</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.73470425605774</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.84380865097046</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.69274139404297</t>
   </si>
   <si>
     <t xml:space="preserve">3.90255665779114</t>
   </si>
   <si>
-    <t xml:space="preserve">3.95291185379028</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.99067854881287</t>
+    <t xml:space="preserve">3.9529116153717</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.99067974090576</t>
   </si>
   <si>
     <t xml:space="preserve">4.00326776504517</t>
   </si>
   <si>
-    <t xml:space="preserve">3.91514587402344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.87318205833435</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.85220098495483</t>
+    <t xml:space="preserve">3.9151451587677</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.87318253517151</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.85220122337341</t>
   </si>
   <si>
     <t xml:space="preserve">3.66756391525269</t>
   </si>
   <si>
-    <t xml:space="preserve">3.67595648765564</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.59203052520752</t>
+    <t xml:space="preserve">3.67595672607422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.59203100204468</t>
   </si>
   <si>
     <t xml:space="preserve">3.53328251838684</t>
   </si>
   <si>
-    <t xml:space="preserve">3.70533037185669</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.64238595962524</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.77666759490967</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.71791934967041</t>
+    <t xml:space="preserve">3.70533084869385</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.64238619804382</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.77666783332825</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.71791911125183</t>
   </si>
   <si>
     <t xml:space="preserve">3.64658236503601</t>
   </si>
   <si>
-    <t xml:space="preserve">3.70113396644592</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.68015265464783</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.80604195594788</t>
+    <t xml:space="preserve">3.70113444328308</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.68015289306641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.80604147911072</t>
   </si>
   <si>
     <t xml:space="preserve">3.7850604057312</t>
   </si>
   <si>
-    <t xml:space="preserve">3.69693803787231</t>
+    <t xml:space="preserve">3.69693827629089</t>
   </si>
   <si>
     <t xml:space="preserve">3.73050832748413</t>
   </si>
   <si>
-    <t xml:space="preserve">3.74729371070862</t>
+    <t xml:space="preserve">3.7472939491272</t>
   </si>
   <si>
     <t xml:space="preserve">3.65077877044678</t>
   </si>
   <si>
-    <t xml:space="preserve">3.65917110443115</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.85639691352844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.89416360855103</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.93612718582153</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.00746297836304</t>
+    <t xml:space="preserve">3.65917134284973</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.85639667510986</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.8941638469696</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.9361264705658</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.0074634552002</t>
   </si>
   <si>
     <t xml:space="preserve">4.08719396591187</t>
   </si>
   <si>
-    <t xml:space="preserve">4.11237192153931</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.17111968994141</t>
+    <t xml:space="preserve">4.11237144470215</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.17111921310425</t>
   </si>
   <si>
     <t xml:space="preserve">4.19629716873169</t>
   </si>
   <si>
-    <t xml:space="preserve">4.2382607460022</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.18790435791016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.09978246688843</t>
+    <t xml:space="preserve">4.23826026916504</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.18790483474731</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.09978294372559</t>
   </si>
   <si>
     <t xml:space="preserve">4.09558582305908</t>
   </si>
   <si>
-    <t xml:space="preserve">4.07880115509033</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.14594173431396</t>
+    <t xml:space="preserve">4.07880067825317</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.14594221115112</t>
   </si>
   <si>
     <t xml:space="preserve">4.09139013290405</t>
@@ -1529,7 +1529,7 @@
     <t xml:space="preserve">4.08299732208252</t>
   </si>
   <si>
-    <t xml:space="preserve">4.06201601028442</t>
+    <t xml:space="preserve">4.06201553344727</t>
   </si>
   <si>
     <t xml:space="preserve">4.26343822479248</t>
@@ -1538,13 +1538,13 @@
     <t xml:space="preserve">4.39771938323975</t>
   </si>
   <si>
-    <t xml:space="preserve">4.52360820770264</t>
+    <t xml:space="preserve">4.52360916137695</t>
   </si>
   <si>
     <t xml:space="preserve">4.49843072891235</t>
   </si>
   <si>
-    <t xml:space="preserve">4.58235645294189</t>
+    <t xml:space="preserve">4.58235692977905</t>
   </si>
   <si>
     <t xml:space="preserve">4.4816460609436</t>
@@ -1553,13 +1553,13 @@
     <t xml:space="preserve">4.6243200302124</t>
   </si>
   <si>
-    <t xml:space="preserve">4.67467594146729</t>
+    <t xml:space="preserve">4.67467546463013</t>
   </si>
   <si>
     <t xml:space="preserve">4.69985246658325</t>
   </si>
   <si>
-    <t xml:space="preserve">4.6830677986145</t>
+    <t xml:space="preserve">4.68306827545166</t>
   </si>
   <si>
     <t xml:space="preserve">4.66628265380859</t>
@@ -1568,31 +1568,31 @@
     <t xml:space="preserve">4.63271236419678</t>
   </si>
   <si>
-    <t xml:space="preserve">4.44807577133179</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.43968296051025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.47325277328491</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.49003791809082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.54878664016724</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.59914112091064</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.61592769622803</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.60753440856934</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.40611219406128</t>
+    <t xml:space="preserve">4.44807529449463</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.4396824836731</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.47325325012207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.49003744125366</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.54878616333008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.59914207458496</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.61592721939087</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.60753393173218</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.40611267089844</t>
   </si>
   <si>
     <t xml:space="preserve">4.53200101852417</t>
@@ -1601,10 +1601,10 @@
     <t xml:space="preserve">4.75860166549683</t>
   </si>
   <si>
-    <t xml:space="preserve">4.80895757675171</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.74181652069092</t>
+    <t xml:space="preserve">4.80895662307739</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.74181604385376</t>
   </si>
   <si>
     <t xml:space="preserve">4.69146060943604</t>
@@ -1613,10 +1613,10 @@
     <t xml:space="preserve">4.65789031982422</t>
   </si>
   <si>
-    <t xml:space="preserve">4.50682401657104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.54039335250854</t>
+    <t xml:space="preserve">4.50682353973389</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.54039287567139</t>
   </si>
   <si>
     <t xml:space="preserve">4.46486043930054</t>
@@ -1625,55 +1625,55 @@
     <t xml:space="preserve">4.41450500488281</t>
   </si>
   <si>
-    <t xml:space="preserve">4.38932704925537</t>
+    <t xml:space="preserve">4.38932657241821</t>
   </si>
   <si>
     <t xml:space="preserve">4.38093423843384</t>
   </si>
   <si>
-    <t xml:space="preserve">4.34736347198486</t>
+    <t xml:space="preserve">4.34736394882202</t>
   </si>
   <si>
     <t xml:space="preserve">4.46764659881592</t>
   </si>
   <si>
-    <t xml:space="preserve">4.5191969871521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.39891386032104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.37313842773438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.30440616607666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.27003908157349</t>
+    <t xml:space="preserve">4.51919651031494</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.3989143371582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.37313938140869</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.3044056892395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.27003812789917</t>
   </si>
   <si>
     <t xml:space="preserve">4.33018064498901</t>
   </si>
   <si>
-    <t xml:space="preserve">4.31299781799316</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.38173055648804</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.44187116622925</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.45905494689941</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.35595607757568</t>
+    <t xml:space="preserve">4.31299734115601</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.38173007965088</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.44187259674072</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.45905447006226</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.35595512390137</t>
   </si>
   <si>
     <t xml:space="preserve">4.39032220840454</t>
   </si>
   <si>
-    <t xml:space="preserve">4.45046377182007</t>
+    <t xml:space="preserve">4.45046329498291</t>
   </si>
   <si>
     <t xml:space="preserve">4.41609668731689</t>
@@ -1685,64 +1685,64 @@
     <t xml:space="preserve">4.26574373245239</t>
   </si>
   <si>
-    <t xml:space="preserve">4.13257265090942</t>
+    <t xml:space="preserve">4.13257312774658</t>
   </si>
   <si>
     <t xml:space="preserve">4.0466570854187</t>
   </si>
   <si>
-    <t xml:space="preserve">4.08531904220581</t>
+    <t xml:space="preserve">4.08531999588013</t>
   </si>
   <si>
     <t xml:space="preserve">3.9822199344635</t>
   </si>
   <si>
-    <t xml:space="preserve">4.03376960754395</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.94785237312317</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.99081087112427</t>
+    <t xml:space="preserve">4.03376913070679</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.94785261154175</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.99081134796143</t>
   </si>
   <si>
     <t xml:space="preserve">3.98651576042175</t>
   </si>
   <si>
-    <t xml:space="preserve">3.94355702400208</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.96503591537476</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.9607412815094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.01229000091553</t>
+    <t xml:space="preserve">3.94355750083923</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.96503663063049</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.96074080467224</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.01229047775269</t>
   </si>
   <si>
     <t xml:space="preserve">3.9263744354248</t>
   </si>
   <si>
-    <t xml:space="preserve">4.07243204116821</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.08961534500122</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.11109447479248</t>
+    <t xml:space="preserve">4.07243156433105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.08961582183838</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.11109399795532</t>
   </si>
   <si>
     <t xml:space="preserve">4.26144790649414</t>
   </si>
   <si>
-    <t xml:space="preserve">4.32158946990967</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.29581356048584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.02947378158569</t>
+    <t xml:space="preserve">4.32158899307251</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.295814037323</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.02947330474854</t>
   </si>
   <si>
     <t xml:space="preserve">3.84045767784119</t>
@@ -1757,13 +1757,13 @@
     <t xml:space="preserve">4.00369882583618</t>
   </si>
   <si>
-    <t xml:space="preserve">4.02088212966919</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.93496584892273</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.86623287200928</t>
+    <t xml:space="preserve">4.02088260650635</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.93496632575989</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.86623311042786</t>
   </si>
   <si>
     <t xml:space="preserve">3.77172470092773</t>
@@ -1775,16 +1775,16 @@
     <t xml:space="preserve">3.70299196243286</t>
   </si>
   <si>
-    <t xml:space="preserve">3.67721700668335</t>
+    <t xml:space="preserve">3.67721724510193</t>
   </si>
   <si>
     <t xml:space="preserve">3.68580842018127</t>
   </si>
   <si>
-    <t xml:space="preserve">3.70728778839111</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.66432952880859</t>
+    <t xml:space="preserve">3.70728731155396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.66432929039001</t>
   </si>
   <si>
     <t xml:space="preserve">3.66003394126892</t>
@@ -1793,82 +1793,82 @@
     <t xml:space="preserve">3.72017478942871</t>
   </si>
   <si>
-    <t xml:space="preserve">3.81468319892883</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.95214939117432</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.85764098167419</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.78461289405823</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.84475350379944</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.7803168296814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.69440054893494</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.73306250572205</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.71158361434937</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.59989261627197</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.75454187393188</t>
+    <t xml:space="preserve">3.8146824836731</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.95214891433716</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.85764122009277</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.78461265563965</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.84475326538086</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.78031611442566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.69440007209778</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.73306226730347</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.71158385276794</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.59989237785339</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.75454163551331</t>
   </si>
   <si>
     <t xml:space="preserve">3.65144205093384</t>
   </si>
   <si>
-    <t xml:space="preserve">3.72447061538696</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.78890776634216</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.64714670181274</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.66862535476685</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.67292094230652</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.61707544326782</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.5741171836853</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.64284992218018</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.65573811531067</t>
+    <t xml:space="preserve">3.72447085380554</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.78890800476074</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.64714622497559</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.66862511634827</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.67292165756226</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.6170756816864</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.57411742210388</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.64285039901733</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.65573787689209</t>
   </si>
   <si>
     <t xml:space="preserve">3.629962682724</t>
   </si>
   <si>
-    <t xml:space="preserve">3.96933197975159</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.95644497871399</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.90059900283813</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.93067002296448</t>
+    <t xml:space="preserve">3.96933221817017</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.95644474029541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.90059971809387</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.9306697845459</t>
   </si>
   <si>
     <t xml:space="preserve">4.01658630371094</t>
@@ -1877,10 +1877,10 @@
     <t xml:space="preserve">4.09820652008057</t>
   </si>
   <si>
-    <t xml:space="preserve">4.14116525650024</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.24426412582397</t>
+    <t xml:space="preserve">4.14116430282593</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.24426460266113</t>
   </si>
   <si>
     <t xml:space="preserve">4.24855995178223</t>
@@ -1889,28 +1889,28 @@
     <t xml:space="preserve">4.4332799911499</t>
   </si>
   <si>
-    <t xml:space="preserve">4.42468929290771</t>
+    <t xml:space="preserve">4.42468881607056</t>
   </si>
   <si>
     <t xml:space="preserve">4.58793020248413</t>
   </si>
   <si>
-    <t xml:space="preserve">4.57933759689331</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.49342155456543</t>
+    <t xml:space="preserve">4.57933807373047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.49342107772827</t>
   </si>
   <si>
     <t xml:space="preserve">4.55356311798096</t>
   </si>
   <si>
-    <t xml:space="preserve">4.48482942581177</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.53637933731079</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.59652090072632</t>
+    <t xml:space="preserve">4.48482990264893</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.53637981414795</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.59652042388916</t>
   </si>
   <si>
     <t xml:space="preserve">4.7769455909729</t>
@@ -1919,22 +1919,22 @@
     <t xml:space="preserve">4.81131172180176</t>
   </si>
   <si>
-    <t xml:space="preserve">4.69962024688721</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.64807081222534</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.72539567947388</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.71680402755737</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.69102954864502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.68243789672852</t>
+    <t xml:space="preserve">4.69962120056152</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.64806985855103</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.72539615631104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.71680355072021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.69102907180786</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.6824369430542</t>
   </si>
   <si>
     <t xml:space="preserve">4.70821189880371</t>
@@ -1949,37 +1949,37 @@
     <t xml:space="preserve">4.50201320648193</t>
   </si>
   <si>
-    <t xml:space="preserve">4.54497194290161</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.51060438156128</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.52778768539429</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.7683539390564</t>
+    <t xml:space="preserve">4.54497146606445</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.51060485839844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.52778816223145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.76835441589355</t>
   </si>
   <si>
     <t xml:space="preserve">4.66525411605835</t>
   </si>
   <si>
-    <t xml:space="preserve">4.61370468139648</t>
+    <t xml:space="preserve">4.61370515823364</t>
   </si>
   <si>
     <t xml:space="preserve">4.73398733139038</t>
   </si>
   <si>
-    <t xml:space="preserve">4.63947916030884</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.23567247390747</t>
+    <t xml:space="preserve">4.639479637146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.23567295074463</t>
   </si>
   <si>
     <t xml:space="preserve">4.15834856033325</t>
   </si>
   <si>
-    <t xml:space="preserve">4.2013053894043</t>
+    <t xml:space="preserve">4.20130634307861</t>
   </si>
   <si>
     <t xml:space="preserve">4.36454725265503</t>
@@ -1991,7 +1991,7 @@
     <t xml:space="preserve">4.11539030075073</t>
   </si>
   <si>
-    <t xml:space="preserve">3.75024580955505</t>
+    <t xml:space="preserve">3.7502453327179</t>
   </si>
   <si>
     <t xml:space="preserve">3.47101783752441</t>
@@ -2000,7 +2000,7 @@
     <t xml:space="preserve">3.36362266540527</t>
   </si>
   <si>
-    <t xml:space="preserve">3.31207251548767</t>
+    <t xml:space="preserve">3.31207299232483</t>
   </si>
   <si>
     <t xml:space="preserve">3.16601490974426</t>
@@ -2012,7 +2012,7 @@
     <t xml:space="preserve">2.80516672134399</t>
   </si>
   <si>
-    <t xml:space="preserve">2.91685771942139</t>
+    <t xml:space="preserve">2.91685795783997</t>
   </si>
   <si>
     <t xml:space="preserve">2.86530804634094</t>
@@ -2021,7 +2021,7 @@
     <t xml:space="preserve">2.8867871761322</t>
   </si>
   <si>
-    <t xml:space="preserve">2.73213791847229</t>
+    <t xml:space="preserve">2.73213768005371</t>
   </si>
   <si>
     <t xml:space="preserve">2.66770052909851</t>
@@ -2033,28 +2033,28 @@
     <t xml:space="preserve">2.61185503005981</t>
   </si>
   <si>
-    <t xml:space="preserve">2.72354626655579</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.92115378379822</t>
+    <t xml:space="preserve">2.72354650497437</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.92115330696106</t>
   </si>
   <si>
     <t xml:space="preserve">2.81375813484192</t>
   </si>
   <si>
-    <t xml:space="preserve">2.70206689834595</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.65910911560059</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.84382915496826</t>
+    <t xml:space="preserve">2.70206713676453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.65910887718201</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.84382891654968</t>
   </si>
   <si>
     <t xml:space="preserve">2.76650452613831</t>
   </si>
   <si>
-    <t xml:space="preserve">2.78798317909241</t>
+    <t xml:space="preserve">2.78798341751099</t>
   </si>
   <si>
     <t xml:space="preserve">2.70636320114136</t>
@@ -2063,28 +2063,28 @@
     <t xml:space="preserve">2.71065878868103</t>
   </si>
   <si>
-    <t xml:space="preserve">2.85242056846619</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.89108324050903</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.92974519729614</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.00707006454468</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.96411180496216</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.93833708763123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.9426326751709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.98129487037659</t>
+    <t xml:space="preserve">2.85242080688477</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.89108300209045</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.9297456741333</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.0070698261261</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.96411156654358</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.93833684921265</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.94263243675232</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.98129510879517</t>
   </si>
   <si>
     <t xml:space="preserve">3.01136589050293</t>
@@ -2093,7 +2093,7 @@
     <t xml:space="preserve">2.94692873954773</t>
   </si>
   <si>
-    <t xml:space="preserve">2.97699904441833</t>
+    <t xml:space="preserve">2.97699928283691</t>
   </si>
   <si>
     <t xml:space="preserve">2.9512243270874</t>
@@ -2102,52 +2102,52 @@
     <t xml:space="preserve">3.10587382316589</t>
   </si>
   <si>
-    <t xml:space="preserve">3.04143619537354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.05002784729004</t>
+    <t xml:space="preserve">3.04143643379211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.0500283241272</t>
   </si>
   <si>
     <t xml:space="preserve">3.08439445495605</t>
   </si>
   <si>
-    <t xml:space="preserve">3.13164854049683</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.03284502029419</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.09298610687256</t>
+    <t xml:space="preserve">3.13164830207825</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.03284478187561</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.09298634529114</t>
   </si>
   <si>
     <t xml:space="preserve">3.19178986549377</t>
   </si>
   <si>
-    <t xml:space="preserve">3.24763536453247</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.16171908378601</t>
+    <t xml:space="preserve">3.24763560295105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.16171932220459</t>
   </si>
   <si>
     <t xml:space="preserve">3.14883184432983</t>
   </si>
   <si>
-    <t xml:space="preserve">3.18319821357727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.13594436645508</t>
+    <t xml:space="preserve">3.18319797515869</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.13594460487366</t>
   </si>
   <si>
     <t xml:space="preserve">3.11876106262207</t>
   </si>
   <si>
-    <t xml:space="preserve">3.30777668952942</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.38510179519653</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.43665146827698</t>
+    <t xml:space="preserve">3.307776927948</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.38510155677795</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.4366512298584</t>
   </si>
   <si>
     <t xml:space="preserve">3.48390531539917</t>
@@ -2156,10 +2156,10 @@
     <t xml:space="preserve">3.46242642402649</t>
   </si>
   <si>
-    <t xml:space="preserve">3.4796097278595</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.3163685798645</t>
+    <t xml:space="preserve">3.47960948944092</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.31636834144592</t>
   </si>
   <si>
     <t xml:space="preserve">3.29488945007324</t>
@@ -2171,16 +2171,16 @@
     <t xml:space="preserve">3.3808057308197</t>
   </si>
   <si>
-    <t xml:space="preserve">3.37650966644287</t>
+    <t xml:space="preserve">3.37651014328003</t>
   </si>
   <si>
     <t xml:space="preserve">3.35073518753052</t>
   </si>
   <si>
-    <t xml:space="preserve">3.37221431732178</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.42805933952332</t>
+    <t xml:space="preserve">3.37221384048462</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.42805981636047</t>
   </si>
   <si>
     <t xml:space="preserve">3.44094729423523</t>
@@ -2195,7 +2195,7 @@
     <t xml:space="preserve">3.71435594558716</t>
   </si>
   <si>
-    <t xml:space="preserve">3.63034081459045</t>
+    <t xml:space="preserve">3.63034105300903</t>
   </si>
   <si>
     <t xml:space="preserve">3.58170080184937</t>
@@ -2204,19 +2204,19 @@
     <t xml:space="preserve">3.51979494094849</t>
   </si>
   <si>
-    <t xml:space="preserve">3.5021071434021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.43135762214661</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.44904518127441</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.36060762405396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.38713932037354</t>
+    <t xml:space="preserve">3.50210762023926</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.43135786056519</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.44904541969299</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.36060786247253</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.38713908195496</t>
   </si>
   <si>
     <t xml:space="preserve">3.4180920124054</t>
@@ -2228,7 +2228,7 @@
     <t xml:space="preserve">3.33849883079529</t>
   </si>
   <si>
-    <t xml:space="preserve">3.31638956069946</t>
+    <t xml:space="preserve">3.31638932228088</t>
   </si>
   <si>
     <t xml:space="preserve">3.27217102050781</t>
@@ -2237,7 +2237,7 @@
     <t xml:space="preserve">3.28101468086243</t>
   </si>
   <si>
-    <t xml:space="preserve">3.22795248031616</t>
+    <t xml:space="preserve">3.22795224189758</t>
   </si>
   <si>
     <t xml:space="preserve">3.09529685974121</t>
@@ -2246,7 +2246,7 @@
     <t xml:space="preserve">3.18373370170593</t>
   </si>
   <si>
-    <t xml:space="preserve">3.25448346138</t>
+    <t xml:space="preserve">3.25448369979858</t>
   </si>
   <si>
     <t xml:space="preserve">3.20584321022034</t>
@@ -2255,13 +2255,13 @@
     <t xml:space="preserve">3.1660463809967</t>
   </si>
   <si>
-    <t xml:space="preserve">3.15720272064209</t>
+    <t xml:space="preserve">3.15720248222351</t>
   </si>
   <si>
     <t xml:space="preserve">3.13951516151428</t>
   </si>
   <si>
-    <t xml:space="preserve">3.10414028167725</t>
+    <t xml:space="preserve">3.10414052009583</t>
   </si>
   <si>
     <t xml:space="preserve">3.09971880912781</t>
@@ -2273,19 +2273,19 @@
     <t xml:space="preserve">3.04665637016296</t>
   </si>
   <si>
-    <t xml:space="preserve">3.07760953903198</t>
+    <t xml:space="preserve">3.0776093006134</t>
   </si>
   <si>
     <t xml:space="preserve">3.05992221832275</t>
   </si>
   <si>
-    <t xml:space="preserve">2.98032855987549</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.96264100074768</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.94495344161987</t>
+    <t xml:space="preserve">2.98032832145691</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.96264123916626</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.94495368003845</t>
   </si>
   <si>
     <t xml:space="preserve">2.93611001968384</t>
@@ -2297,13 +2297,13 @@
     <t xml:space="preserve">3.06876564025879</t>
   </si>
   <si>
-    <t xml:space="preserve">3.05550003051758</t>
+    <t xml:space="preserve">3.05550026893616</t>
   </si>
   <si>
     <t xml:space="preserve">2.98475050926208</t>
   </si>
   <si>
-    <t xml:space="preserve">2.90515756607056</t>
+    <t xml:space="preserve">2.90515732765198</t>
   </si>
   <si>
     <t xml:space="preserve">2.83440756797791</t>
@@ -2318,7 +2318,7 @@
     <t xml:space="preserve">2.77692365646362</t>
   </si>
   <si>
-    <t xml:space="preserve">2.81229829788208</t>
+    <t xml:space="preserve">2.81229853630066</t>
   </si>
   <si>
     <t xml:space="preserve">2.84767317771912</t>
@@ -2336,7 +2336,7 @@
     <t xml:space="preserve">2.82114219665527</t>
   </si>
   <si>
-    <t xml:space="preserve">2.79903268814087</t>
+    <t xml:space="preserve">2.79903292655945</t>
   </si>
   <si>
     <t xml:space="preserve">2.80787634849548</t>
@@ -2357,10 +2357,10 @@
     <t xml:space="preserve">2.63542413711548</t>
   </si>
   <si>
-    <t xml:space="preserve">2.61773705482483</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.58236217498779</t>
+    <t xml:space="preserve">2.61773681640625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.58236193656921</t>
   </si>
   <si>
     <t xml:space="preserve">2.54698729515076</t>
@@ -2369,37 +2369,37 @@
     <t xml:space="preserve">2.56467461585999</t>
   </si>
   <si>
-    <t xml:space="preserve">2.5514087677002</t>
+    <t xml:space="preserve">2.55140900611877</t>
   </si>
   <si>
     <t xml:space="preserve">2.49392485618591</t>
   </si>
   <si>
-    <t xml:space="preserve">2.57351803779602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.97148489952087</t>
+    <t xml:space="preserve">2.5735182762146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.97148466110229</t>
   </si>
   <si>
     <t xml:space="preserve">2.95379757881165</t>
   </si>
   <si>
-    <t xml:space="preserve">3.00243782997131</t>
+    <t xml:space="preserve">3.00243806838989</t>
   </si>
   <si>
     <t xml:space="preserve">3.17931199073792</t>
   </si>
   <si>
-    <t xml:space="preserve">3.17046856880188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.19257760047913</t>
+    <t xml:space="preserve">3.1704683303833</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.19257736206055</t>
   </si>
   <si>
     <t xml:space="preserve">3.28985834121704</t>
   </si>
   <si>
-    <t xml:space="preserve">3.29870223999023</t>
+    <t xml:space="preserve">3.29870200157166</t>
   </si>
   <si>
     <t xml:space="preserve">3.47999787330627</t>
@@ -2408,40 +2408,40 @@
     <t xml:space="preserve">3.41367030143738</t>
   </si>
   <si>
-    <t xml:space="preserve">3.48442006111145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.45788860321045</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.49326348304749</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.51095104217529</t>
+    <t xml:space="preserve">3.48442029953003</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.45788884162903</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.49326372146606</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.51095080375671</t>
   </si>
   <si>
     <t xml:space="preserve">3.44462299346924</t>
   </si>
   <si>
-    <t xml:space="preserve">3.42693591117859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.55516958236694</t>
+    <t xml:space="preserve">3.42693543434143</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.55516934394836</t>
   </si>
   <si>
     <t xml:space="preserve">3.67898106575012</t>
   </si>
   <si>
-    <t xml:space="preserve">3.72319984436035</t>
+    <t xml:space="preserve">3.72320032119751</t>
   </si>
   <si>
     <t xml:space="preserve">3.74973058700562</t>
   </si>
   <si>
-    <t xml:space="preserve">3.80279350280762</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.65687251091003</t>
+    <t xml:space="preserve">3.80279302597046</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.65687227249146</t>
   </si>
   <si>
     <t xml:space="preserve">3.66129398345947</t>
@@ -2450,237 +2450,237 @@
     <t xml:space="preserve">3.65245032310486</t>
   </si>
   <si>
-    <t xml:space="preserve">3.62591886520386</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.60823202133179</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.54632592201233</t>
+    <t xml:space="preserve">3.62591910362244</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.60823178291321</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.54632616043091</t>
   </si>
   <si>
     <t xml:space="preserve">3.53748226165771</t>
   </si>
   <si>
-    <t xml:space="preserve">3.57285690307617</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.50652933120728</t>
+    <t xml:space="preserve">3.57285714149475</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.5065290927887</t>
   </si>
   <si>
     <t xml:space="preserve">3.59054446220398</t>
   </si>
   <si>
-    <t xml:space="preserve">3.57727861404419</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.74530911445618</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.74088716506958</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.73204350471497</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.7055127620697</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.7762622833252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.8381679058075</t>
+    <t xml:space="preserve">3.57727885246277</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.74530959129333</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.74088764190674</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.73204326629639</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.70551252365112</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.77626180648804</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.83816838264465</t>
   </si>
   <si>
     <t xml:space="preserve">3.6834032535553</t>
   </si>
   <si>
-    <t xml:space="preserve">3.76741862297058</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.78068375587463</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.76299691200256</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.7718403339386</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.71877789497375</t>
+    <t xml:space="preserve">3.76741886138916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.78068399429321</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.76299667358398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.77184057235718</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.71877813339233</t>
   </si>
   <si>
     <t xml:space="preserve">3.68782520294189</t>
   </si>
   <si>
-    <t xml:space="preserve">3.61707592010498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.59938788414001</t>
+    <t xml:space="preserve">3.59938836097717</t>
   </si>
   <si>
     <t xml:space="preserve">3.66571569442749</t>
   </si>
   <si>
-    <t xml:space="preserve">3.7099347114563</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.78510594367981</t>
+    <t xml:space="preserve">3.70993423461914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.78510570526123</t>
   </si>
   <si>
     <t xml:space="preserve">3.92660522460938</t>
   </si>
   <si>
-    <t xml:space="preserve">3.93987083435059</t>
+    <t xml:space="preserve">3.93987011909485</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.99735474586487</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.01079893112183</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.09594440460205</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.17212677001953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.16316413879395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.13627576828003</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.19901466369629</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.14075756072998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.10490703582764</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.06905603408813</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.03320550918579</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.9794294834137</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.02872371673584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.05561256408691</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.08698129653931</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.97494769096375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.00183629989624</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.01528024673462</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.96150422096252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.9883918762207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.9525408744812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.96598553657532</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.04216814041138</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.07801914215088</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.11835050582886</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.17660856246948</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.11386966705322</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.10938787460327</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.06009340286255</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.19453382492065</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.21245861053467</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.14972019195557</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.12283182144165</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.03768682479858</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.01976108551025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.06457424163818</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.20797729492188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.23038387298584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.25727224349976</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.20349645614624</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.92565321922302</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.90772819519043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.88083982467651</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.87635803222656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.80913853645325</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.71503019332886</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.66573572158813</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.83154511451721</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.93461585044861</t>
   </si>
   <si>
     <t xml:space="preserve">3.99735498428345</t>
   </si>
   <si>
-    <t xml:space="preserve">4.01079893112183</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.09594440460205</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.17212677001953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.16316413879395</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.13627576828003</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.19901466369629</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.14075756072998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.10490703582764</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.06905603408813</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.03320550918579</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.9794294834137</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.02872371673584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.05561256408691</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.08698129653931</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.97494769096375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.00183629989624</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.01528024673462</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.96150422096252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.9883918762207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.9525408744812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.96598553657532</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.04216814041138</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.07801914215088</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.11835050582886</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.17660856246948</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.11386966705322</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.10938787460327</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.06009340286255</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.19453382492065</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.21245861053467</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.14972019195557</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.12283182144165</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.03768682479858</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.01976108551025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.06457424163818</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.20797729492188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.23038387298584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.25727224349976</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.20349645614624</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.92565321922302</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.90772819519043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.88083982467651</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.87635803222656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.80913853645325</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.71503019332886</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.66573572158813</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.83154511451721</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.93461585044861</t>
-  </si>
-  <si>
     <t xml:space="preserve">3.94357824325562</t>
   </si>
   <si>
@@ -4548,6 +4548,9 @@
   </si>
   <si>
     <t xml:space="preserve">6.21999979019165</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.30000019073486</t>
   </si>
 </sst>
 </file>
@@ -8024,7 +8027,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G121" t="s">
-        <v>114</v>
+        <v>96</v>
       </c>
       <c r="H121" t="s">
         <v>9</v>
@@ -8050,7 +8053,7 @@
         <v>3.10999989509583</v>
       </c>
       <c r="G122" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="H122" t="s">
         <v>9</v>
@@ -8076,7 +8079,7 @@
         <v>3.08599996566772</v>
       </c>
       <c r="G123" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="H123" t="s">
         <v>9</v>
@@ -8102,7 +8105,7 @@
         <v>2.96000003814697</v>
       </c>
       <c r="G124" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="H124" t="s">
         <v>9</v>
@@ -8128,7 +8131,7 @@
         <v>2.70000004768372</v>
       </c>
       <c r="G125" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="H125" t="s">
         <v>9</v>
@@ -8154,7 +8157,7 @@
         <v>2.75</v>
       </c>
       <c r="G126" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="H126" t="s">
         <v>9</v>
@@ -8180,7 +8183,7 @@
         <v>2.82399988174438</v>
       </c>
       <c r="G127" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="H127" t="s">
         <v>9</v>
@@ -8206,7 +8209,7 @@
         <v>2.79800009727478</v>
       </c>
       <c r="G128" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="H128" t="s">
         <v>9</v>
@@ -8232,7 +8235,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G129" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="H129" t="s">
         <v>9</v>
@@ -8258,7 +8261,7 @@
         <v>2.92000007629395</v>
       </c>
       <c r="G130" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="H130" t="s">
         <v>9</v>
@@ -8284,7 +8287,7 @@
         <v>2.8199999332428</v>
       </c>
       <c r="G131" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="H131" t="s">
         <v>9</v>
@@ -8310,7 +8313,7 @@
         <v>2.69799995422363</v>
       </c>
       <c r="G132" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="H132" t="s">
         <v>9</v>
@@ -8336,7 +8339,7 @@
         <v>2.73799991607666</v>
       </c>
       <c r="G133" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="H133" t="s">
         <v>9</v>
@@ -8362,7 +8365,7 @@
         <v>2.80999994277954</v>
       </c>
       <c r="G134" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="H134" t="s">
         <v>9</v>
@@ -8388,7 +8391,7 @@
         <v>2.83599996566772</v>
       </c>
       <c r="G135" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="H135" t="s">
         <v>9</v>
@@ -8414,7 +8417,7 @@
         <v>2.86800003051758</v>
       </c>
       <c r="G136" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="H136" t="s">
         <v>9</v>
@@ -8440,7 +8443,7 @@
         <v>2.87400007247925</v>
       </c>
       <c r="G137" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="H137" t="s">
         <v>9</v>
@@ -8466,7 +8469,7 @@
         <v>2.86999988555908</v>
       </c>
       <c r="G138" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="H138" t="s">
         <v>9</v>
@@ -8492,7 +8495,7 @@
         <v>2.85400009155273</v>
       </c>
       <c r="G139" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="H139" t="s">
         <v>9</v>
@@ -8518,7 +8521,7 @@
         <v>2.85400009155273</v>
       </c>
       <c r="G140" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="H140" t="s">
         <v>9</v>
@@ -8544,7 +8547,7 @@
         <v>2.9300000667572</v>
       </c>
       <c r="G141" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="H141" t="s">
         <v>9</v>
@@ -8570,7 +8573,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G142" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="H142" t="s">
         <v>9</v>
@@ -8596,7 +8599,7 @@
         <v>3.13000011444092</v>
       </c>
       <c r="G143" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="H143" t="s">
         <v>9</v>
@@ -8622,7 +8625,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G144" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="H144" t="s">
         <v>9</v>
@@ -8674,7 +8677,7 @@
         <v>3.56399989128113</v>
       </c>
       <c r="G146" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="H146" t="s">
         <v>9</v>
@@ -8700,7 +8703,7 @@
         <v>3.49200010299683</v>
       </c>
       <c r="G147" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="H147" t="s">
         <v>9</v>
@@ -8752,7 +8755,7 @@
         <v>3.46000003814697</v>
       </c>
       <c r="G149" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="H149" t="s">
         <v>9</v>
@@ -8778,7 +8781,7 @@
         <v>3.19400000572205</v>
       </c>
       <c r="G150" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="H150" t="s">
         <v>9</v>
@@ -8804,7 +8807,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G151" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="H151" t="s">
         <v>9</v>
@@ -8908,7 +8911,7 @@
         <v>3.17000007629395</v>
       </c>
       <c r="G155" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="H155" t="s">
         <v>9</v>
@@ -8934,7 +8937,7 @@
         <v>3.17000007629395</v>
       </c>
       <c r="G156" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="H156" t="s">
         <v>9</v>
@@ -8960,7 +8963,7 @@
         <v>3.16599988937378</v>
       </c>
       <c r="G157" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="H157" t="s">
         <v>9</v>
@@ -8986,7 +8989,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G158" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="H158" t="s">
         <v>9</v>
@@ -9012,7 +9015,7 @@
         <v>3.15799999237061</v>
       </c>
       <c r="G159" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="H159" t="s">
         <v>9</v>
@@ -9038,7 +9041,7 @@
         <v>3.1159999370575</v>
       </c>
       <c r="G160" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="H160" t="s">
         <v>9</v>
@@ -9064,7 +9067,7 @@
         <v>3.10999989509583</v>
       </c>
       <c r="G161" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="H161" t="s">
         <v>9</v>
@@ -9090,7 +9093,7 @@
         <v>3.12199997901917</v>
       </c>
       <c r="G162" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="H162" t="s">
         <v>9</v>
@@ -9116,7 +9119,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G163" t="s">
-        <v>114</v>
+        <v>96</v>
       </c>
       <c r="H163" t="s">
         <v>9</v>
@@ -9142,7 +9145,7 @@
         <v>3.10999989509583</v>
       </c>
       <c r="G164" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="H164" t="s">
         <v>9</v>
@@ -9168,7 +9171,7 @@
         <v>3.10999989509583</v>
       </c>
       <c r="G165" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="H165" t="s">
         <v>9</v>
@@ -9194,7 +9197,7 @@
         <v>3.24399995803833</v>
       </c>
       <c r="G166" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="H166" t="s">
         <v>9</v>
@@ -9220,7 +9223,7 @@
         <v>3.23600006103516</v>
       </c>
       <c r="G167" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="H167" t="s">
         <v>9</v>
@@ -9246,7 +9249,7 @@
         <v>3.24399995803833</v>
       </c>
       <c r="G168" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="H168" t="s">
         <v>9</v>
@@ -9272,7 +9275,7 @@
         <v>3.25600004196167</v>
       </c>
       <c r="G169" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="H169" t="s">
         <v>9</v>
@@ -9298,7 +9301,7 @@
         <v>3.26399993896484</v>
       </c>
       <c r="G170" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="H170" t="s">
         <v>9</v>
@@ -9324,7 +9327,7 @@
         <v>3.24600005149841</v>
       </c>
       <c r="G171" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="H171" t="s">
         <v>9</v>
@@ -9350,7 +9353,7 @@
         <v>3.25</v>
       </c>
       <c r="G172" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="H172" t="s">
         <v>9</v>
@@ -9376,7 +9379,7 @@
         <v>3.31200003623962</v>
       </c>
       <c r="G173" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="H173" t="s">
         <v>9</v>
@@ -9402,7 +9405,7 @@
         <v>3.39199995994568</v>
       </c>
       <c r="G174" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="H174" t="s">
         <v>9</v>
@@ -9428,7 +9431,7 @@
         <v>3.43600010871887</v>
       </c>
       <c r="G175" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="H175" t="s">
         <v>9</v>
@@ -9454,7 +9457,7 @@
         <v>3.43600010871887</v>
       </c>
       <c r="G176" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="H176" t="s">
         <v>9</v>
@@ -9506,7 +9509,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G178" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="H178" t="s">
         <v>9</v>
@@ -9532,7 +9535,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G179" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="H179" t="s">
         <v>9</v>
@@ -9558,7 +9561,7 @@
         <v>3.26600003242493</v>
       </c>
       <c r="G180" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="H180" t="s">
         <v>9</v>
@@ -9584,7 +9587,7 @@
         <v>3.26999998092651</v>
       </c>
       <c r="G181" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="H181" t="s">
         <v>9</v>
@@ -9610,7 +9613,7 @@
         <v>3.37400007247925</v>
       </c>
       <c r="G182" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="H182" t="s">
         <v>9</v>
@@ -9636,7 +9639,7 @@
         <v>3.40599989891052</v>
       </c>
       <c r="G183" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="H183" t="s">
         <v>9</v>
@@ -9662,7 +9665,7 @@
         <v>3.32999992370605</v>
       </c>
       <c r="G184" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="H184" t="s">
         <v>9</v>
@@ -9688,7 +9691,7 @@
         <v>3.35599994659424</v>
       </c>
       <c r="G185" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="H185" t="s">
         <v>9</v>
@@ -9714,7 +9717,7 @@
         <v>3.37199997901917</v>
       </c>
       <c r="G186" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="H186" t="s">
         <v>9</v>
@@ -9740,7 +9743,7 @@
         <v>3.40799999237061</v>
       </c>
       <c r="G187" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="H187" t="s">
         <v>9</v>
@@ -9766,7 +9769,7 @@
         <v>3.44600009918213</v>
       </c>
       <c r="G188" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="H188" t="s">
         <v>9</v>
@@ -9792,7 +9795,7 @@
         <v>3.32999992370605</v>
       </c>
       <c r="G189" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="H189" t="s">
         <v>9</v>
@@ -9818,7 +9821,7 @@
         <v>3.31599998474121</v>
       </c>
       <c r="G190" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="H190" t="s">
         <v>9</v>
@@ -9844,7 +9847,7 @@
         <v>3.28200006484985</v>
       </c>
       <c r="G191" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="H191" t="s">
         <v>9</v>
@@ -9870,7 +9873,7 @@
         <v>3.25799989700317</v>
       </c>
       <c r="G192" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="H192" t="s">
         <v>9</v>
@@ -9896,7 +9899,7 @@
         <v>3.23000001907349</v>
       </c>
       <c r="G193" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="H193" t="s">
         <v>9</v>
@@ -9922,7 +9925,7 @@
         <v>3.19600009918213</v>
       </c>
       <c r="G194" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="H194" t="s">
         <v>9</v>
@@ -9974,7 +9977,7 @@
         <v>3.22000002861023</v>
       </c>
       <c r="G196" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="H196" t="s">
         <v>9</v>
@@ -10052,7 +10055,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G199" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="H199" t="s">
         <v>9</v>
@@ -10078,7 +10081,7 @@
         <v>3.24000000953674</v>
       </c>
       <c r="G200" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="H200" t="s">
         <v>9</v>
@@ -10104,7 +10107,7 @@
         <v>3.30800008773804</v>
       </c>
       <c r="G201" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="H201" t="s">
         <v>9</v>
@@ -10130,7 +10133,7 @@
         <v>3.20199990272522</v>
       </c>
       <c r="G202" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="H202" t="s">
         <v>9</v>
@@ -10156,7 +10159,7 @@
         <v>3.26999998092651</v>
       </c>
       <c r="G203" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="H203" t="s">
         <v>9</v>
@@ -10182,7 +10185,7 @@
         <v>3.29399991035461</v>
       </c>
       <c r="G204" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="H204" t="s">
         <v>9</v>
@@ -10208,7 +10211,7 @@
         <v>3.33400011062622</v>
       </c>
       <c r="G205" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="H205" t="s">
         <v>9</v>
@@ -10234,7 +10237,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G206" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="H206" t="s">
         <v>9</v>
@@ -10260,7 +10263,7 @@
         <v>3.39000010490417</v>
       </c>
       <c r="G207" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="H207" t="s">
         <v>9</v>
@@ -10286,7 +10289,7 @@
         <v>3.35400009155273</v>
       </c>
       <c r="G208" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="H208" t="s">
         <v>9</v>
@@ -10312,7 +10315,7 @@
         <v>3.34999990463257</v>
       </c>
       <c r="G209" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="H209" t="s">
         <v>9</v>
@@ -10338,7 +10341,7 @@
         <v>3.48000001907349</v>
       </c>
       <c r="G210" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="H210" t="s">
         <v>9</v>
@@ -10364,7 +10367,7 @@
         <v>3.37599992752075</v>
       </c>
       <c r="G211" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="H211" t="s">
         <v>9</v>
@@ -10390,7 +10393,7 @@
         <v>3.37400007247925</v>
       </c>
       <c r="G212" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="H212" t="s">
         <v>9</v>
@@ -10416,7 +10419,7 @@
         <v>3.39800000190735</v>
       </c>
       <c r="G213" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="H213" t="s">
         <v>9</v>
@@ -10442,7 +10445,7 @@
         <v>3.36999988555908</v>
       </c>
       <c r="G214" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="H214" t="s">
         <v>9</v>
@@ -10468,7 +10471,7 @@
         <v>3.36999988555908</v>
       </c>
       <c r="G215" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="H215" t="s">
         <v>9</v>
@@ -10494,7 +10497,7 @@
         <v>3.32800006866455</v>
       </c>
       <c r="G216" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="H216" t="s">
         <v>9</v>
@@ -10520,7 +10523,7 @@
         <v>3.30999994277954</v>
       </c>
       <c r="G217" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="H217" t="s">
         <v>9</v>
@@ -10546,7 +10549,7 @@
         <v>3.25</v>
       </c>
       <c r="G218" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="H218" t="s">
         <v>9</v>
@@ -10572,7 +10575,7 @@
         <v>3.10999989509583</v>
       </c>
       <c r="G219" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="H219" t="s">
         <v>9</v>
@@ -10598,7 +10601,7 @@
         <v>3.21399998664856</v>
       </c>
       <c r="G220" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="H220" t="s">
         <v>9</v>
@@ -10624,7 +10627,7 @@
         <v>3.34999990463257</v>
       </c>
       <c r="G221" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="H221" t="s">
         <v>9</v>
@@ -10650,7 +10653,7 @@
         <v>3.36199998855591</v>
       </c>
       <c r="G222" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="H222" t="s">
         <v>9</v>
@@ -10702,7 +10705,7 @@
         <v>3.34999990463257</v>
       </c>
       <c r="G224" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="H224" t="s">
         <v>9</v>
@@ -10728,7 +10731,7 @@
         <v>3.29200005531311</v>
       </c>
       <c r="G225" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="H225" t="s">
         <v>9</v>
@@ -10754,7 +10757,7 @@
         <v>3.2279999256134</v>
       </c>
       <c r="G226" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="H226" t="s">
         <v>9</v>
@@ -10780,7 +10783,7 @@
         <v>3.23000001907349</v>
       </c>
       <c r="G227" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="H227" t="s">
         <v>9</v>
@@ -10806,7 +10809,7 @@
         <v>3.19199991226196</v>
       </c>
       <c r="G228" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="H228" t="s">
         <v>9</v>
@@ -10884,7 +10887,7 @@
         <v>3.14199995994568</v>
       </c>
       <c r="G231" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="H231" t="s">
         <v>9</v>
@@ -10910,7 +10913,7 @@
         <v>3.13000011444092</v>
       </c>
       <c r="G232" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="H232" t="s">
         <v>9</v>
@@ -10936,7 +10939,7 @@
         <v>3.13800001144409</v>
       </c>
       <c r="G233" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="H233" t="s">
         <v>9</v>
@@ -10962,7 +10965,7 @@
         <v>3.09200000762939</v>
       </c>
       <c r="G234" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="H234" t="s">
         <v>9</v>
@@ -10988,7 +10991,7 @@
         <v>3.03600001335144</v>
       </c>
       <c r="G235" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="H235" t="s">
         <v>9</v>
@@ -11014,7 +11017,7 @@
         <v>3.03600001335144</v>
       </c>
       <c r="G236" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="H236" t="s">
         <v>9</v>
@@ -11040,7 +11043,7 @@
         <v>2.96000003814697</v>
       </c>
       <c r="G237" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="H237" t="s">
         <v>9</v>
@@ -11066,7 +11069,7 @@
         <v>3.07800006866455</v>
       </c>
       <c r="G238" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="H238" t="s">
         <v>9</v>
@@ -11118,7 +11121,7 @@
         <v>3.23000001907349</v>
       </c>
       <c r="G240" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="H240" t="s">
         <v>9</v>
@@ -11170,7 +11173,7 @@
         <v>3.19199991226196</v>
       </c>
       <c r="G242" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="H242" t="s">
         <v>9</v>
@@ -11196,7 +11199,7 @@
         <v>3.19199991226196</v>
       </c>
       <c r="G243" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="H243" t="s">
         <v>9</v>
@@ -11222,7 +11225,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G244" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="H244" t="s">
         <v>9</v>
@@ -11248,7 +11251,7 @@
         <v>3.23799991607666</v>
       </c>
       <c r="G245" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="H245" t="s">
         <v>9</v>
@@ -11274,7 +11277,7 @@
         <v>3.17000007629395</v>
       </c>
       <c r="G246" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="H246" t="s">
         <v>9</v>
@@ -11300,7 +11303,7 @@
         <v>3.24000000953674</v>
       </c>
       <c r="G247" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="H247" t="s">
         <v>9</v>
@@ -11326,7 +11329,7 @@
         <v>3.24000000953674</v>
       </c>
       <c r="G248" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="H248" t="s">
         <v>9</v>
@@ -11352,7 +11355,7 @@
         <v>3.25</v>
       </c>
       <c r="G249" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="H249" t="s">
         <v>9</v>
@@ -11404,7 +11407,7 @@
         <v>3.24000000953674</v>
       </c>
       <c r="G251" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="H251" t="s">
         <v>9</v>
@@ -11430,7 +11433,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G252" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="H252" t="s">
         <v>9</v>
@@ -11456,7 +11459,7 @@
         <v>3.26799988746643</v>
       </c>
       <c r="G253" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="H253" t="s">
         <v>9</v>
@@ -11482,7 +11485,7 @@
         <v>3.28399991989136</v>
       </c>
       <c r="G254" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="H254" t="s">
         <v>9</v>
@@ -11508,7 +11511,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G255" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="H255" t="s">
         <v>9</v>
@@ -11534,7 +11537,7 @@
         <v>3.30999994277954</v>
       </c>
       <c r="G256" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="H256" t="s">
         <v>9</v>
@@ -11560,7 +11563,7 @@
         <v>3.35199999809265</v>
       </c>
       <c r="G257" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="H257" t="s">
         <v>9</v>
@@ -11586,7 +11589,7 @@
         <v>3.46000003814697</v>
       </c>
       <c r="G258" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="H258" t="s">
         <v>9</v>
@@ -11612,7 +11615,7 @@
         <v>3.46000003814697</v>
       </c>
       <c r="G259" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="H259" t="s">
         <v>9</v>
@@ -11638,7 +11641,7 @@
         <v>3.42400002479553</v>
       </c>
       <c r="G260" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="H260" t="s">
         <v>9</v>
@@ -11664,7 +11667,7 @@
         <v>3.41000008583069</v>
       </c>
       <c r="G261" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="H261" t="s">
         <v>9</v>
@@ -11690,7 +11693,7 @@
         <v>3.41799998283386</v>
       </c>
       <c r="G262" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="H262" t="s">
         <v>9</v>
@@ -11716,7 +11719,7 @@
         <v>3.32200002670288</v>
       </c>
       <c r="G263" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="H263" t="s">
         <v>9</v>
@@ -11742,7 +11745,7 @@
         <v>3.35199999809265</v>
       </c>
       <c r="G264" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="H264" t="s">
         <v>9</v>
@@ -11768,7 +11771,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G265" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="H265" t="s">
         <v>9</v>
@@ -11794,7 +11797,7 @@
         <v>3.36999988555908</v>
       </c>
       <c r="G266" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="H266" t="s">
         <v>9</v>
@@ -11820,7 +11823,7 @@
         <v>3.41199994087219</v>
       </c>
       <c r="G267" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="H267" t="s">
         <v>9</v>
@@ -11846,7 +11849,7 @@
         <v>3.40199995040894</v>
       </c>
       <c r="G268" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="H268" t="s">
         <v>9</v>
@@ -11872,7 +11875,7 @@
         <v>3.40199995040894</v>
       </c>
       <c r="G269" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="H269" t="s">
         <v>9</v>
@@ -11898,7 +11901,7 @@
         <v>3.34400010108948</v>
       </c>
       <c r="G270" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="H270" t="s">
         <v>9</v>
@@ -11950,7 +11953,7 @@
         <v>3.30800008773804</v>
       </c>
       <c r="G272" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="H272" t="s">
         <v>9</v>
@@ -12054,7 +12057,7 @@
         <v>3.26999998092651</v>
       </c>
       <c r="G276" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="H276" t="s">
         <v>9</v>
@@ -12080,7 +12083,7 @@
         <v>3.23600006103516</v>
       </c>
       <c r="G277" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="H277" t="s">
         <v>9</v>
@@ -12106,7 +12109,7 @@
         <v>3.25</v>
       </c>
       <c r="G278" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="H278" t="s">
         <v>9</v>
@@ -12132,7 +12135,7 @@
         <v>3.23000001907349</v>
       </c>
       <c r="G279" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="H279" t="s">
         <v>9</v>
@@ -12158,7 +12161,7 @@
         <v>3.25799989700317</v>
       </c>
       <c r="G280" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="H280" t="s">
         <v>9</v>
@@ -12236,7 +12239,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G283" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="H283" t="s">
         <v>9</v>
@@ -12262,7 +12265,7 @@
         <v>3.36999988555908</v>
       </c>
       <c r="G284" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="H284" t="s">
         <v>9</v>
@@ -12288,7 +12291,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G285" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="H285" t="s">
         <v>9</v>
@@ -12314,7 +12317,7 @@
         <v>3.37800002098083</v>
       </c>
       <c r="G286" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="H286" t="s">
         <v>9</v>
@@ -12340,7 +12343,7 @@
         <v>3.37400007247925</v>
       </c>
       <c r="G287" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="H287" t="s">
         <v>9</v>
@@ -12366,7 +12369,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G288" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="H288" t="s">
         <v>9</v>
@@ -12392,7 +12395,7 @@
         <v>3.42000007629395</v>
       </c>
       <c r="G289" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="H289" t="s">
         <v>9</v>
@@ -12418,7 +12421,7 @@
         <v>3.38000011444092</v>
       </c>
       <c r="G290" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="H290" t="s">
         <v>9</v>
@@ -12470,7 +12473,7 @@
         <v>3.30999994277954</v>
       </c>
       <c r="G292" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="H292" t="s">
         <v>9</v>
@@ -12496,7 +12499,7 @@
         <v>3.34999990463257</v>
       </c>
       <c r="G293" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="H293" t="s">
         <v>9</v>
@@ -12522,7 +12525,7 @@
         <v>3.34999990463257</v>
       </c>
       <c r="G294" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="H294" t="s">
         <v>9</v>
@@ -12548,7 +12551,7 @@
         <v>3.26999998092651</v>
       </c>
       <c r="G295" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="H295" t="s">
         <v>9</v>
@@ -12574,7 +12577,7 @@
         <v>3.29399991035461</v>
       </c>
       <c r="G296" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="H296" t="s">
         <v>9</v>
@@ -12626,7 +12629,7 @@
         <v>3.24600005149841</v>
       </c>
       <c r="G298" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="H298" t="s">
         <v>9</v>
@@ -12678,7 +12681,7 @@
         <v>3.2039999961853</v>
       </c>
       <c r="G300" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="H300" t="s">
         <v>9</v>
@@ -12704,7 +12707,7 @@
         <v>3.23200011253357</v>
       </c>
       <c r="G301" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="H301" t="s">
         <v>9</v>
@@ -12730,7 +12733,7 @@
         <v>3.25999999046326</v>
       </c>
       <c r="G302" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="H302" t="s">
         <v>9</v>
@@ -12756,7 +12759,7 @@
         <v>3.28200006484985</v>
       </c>
       <c r="G303" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="H303" t="s">
         <v>9</v>
@@ -12782,7 +12785,7 @@
         <v>3.25</v>
       </c>
       <c r="G304" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="H304" t="s">
         <v>9</v>
@@ -12808,7 +12811,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G305" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="H305" t="s">
         <v>9</v>
@@ -12834,7 +12837,7 @@
         <v>3.31399989128113</v>
       </c>
       <c r="G306" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="H306" t="s">
         <v>9</v>
@@ -12860,7 +12863,7 @@
         <v>3.31599998474121</v>
       </c>
       <c r="G307" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="H307" t="s">
         <v>9</v>
@@ -12886,7 +12889,7 @@
         <v>3.28399991989136</v>
       </c>
       <c r="G308" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="H308" t="s">
         <v>9</v>
@@ -12912,7 +12915,7 @@
         <v>3.29200005531311</v>
       </c>
       <c r="G309" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="H309" t="s">
         <v>9</v>
@@ -12938,7 +12941,7 @@
         <v>3.29399991035461</v>
       </c>
       <c r="G310" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="H310" t="s">
         <v>9</v>
@@ -12964,7 +12967,7 @@
         <v>3.3199999332428</v>
       </c>
       <c r="G311" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="H311" t="s">
         <v>9</v>
@@ -12990,7 +12993,7 @@
         <v>3.35400009155273</v>
       </c>
       <c r="G312" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="H312" t="s">
         <v>9</v>
@@ -13042,7 +13045,7 @@
         <v>3.59599995613098</v>
       </c>
       <c r="G314" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="H314" t="s">
         <v>9</v>
@@ -13068,7 +13071,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G315" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="H315" t="s">
         <v>9</v>
@@ -13094,7 +13097,7 @@
         <v>3.69000005722046</v>
       </c>
       <c r="G316" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="H316" t="s">
         <v>9</v>
@@ -13120,7 +13123,7 @@
         <v>3.66000008583069</v>
       </c>
       <c r="G317" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="H317" t="s">
         <v>9</v>
@@ -13146,7 +13149,7 @@
         <v>3.65400004386902</v>
       </c>
       <c r="G318" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="H318" t="s">
         <v>9</v>
@@ -13172,7 +13175,7 @@
         <v>3.66000008583069</v>
       </c>
       <c r="G319" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="H319" t="s">
         <v>9</v>
@@ -13198,7 +13201,7 @@
         <v>3.64599990844727</v>
       </c>
       <c r="G320" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="H320" t="s">
         <v>9</v>
@@ -13224,7 +13227,7 @@
         <v>3.61999988555908</v>
       </c>
       <c r="G321" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="H321" t="s">
         <v>9</v>
@@ -13250,7 +13253,7 @@
         <v>3.61999988555908</v>
       </c>
       <c r="G322" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="H322" t="s">
         <v>9</v>
@@ -13276,7 +13279,7 @@
         <v>3.60999989509583</v>
       </c>
       <c r="G323" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="H323" t="s">
         <v>9</v>
@@ -13302,7 +13305,7 @@
         <v>3.59599995613098</v>
       </c>
       <c r="G324" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="H324" t="s">
         <v>9</v>
@@ -13328,7 +13331,7 @@
         <v>3.56599998474121</v>
       </c>
       <c r="G325" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="H325" t="s">
         <v>9</v>
@@ -13354,7 +13357,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G326" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="H326" t="s">
         <v>9</v>
@@ -13380,7 +13383,7 @@
         <v>3.55800008773804</v>
       </c>
       <c r="G327" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="H327" t="s">
         <v>9</v>
@@ -13406,7 +13409,7 @@
         <v>3.55800008773804</v>
       </c>
       <c r="G328" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="H328" t="s">
         <v>9</v>
@@ -13432,7 +13435,7 @@
         <v>3.54200005531311</v>
       </c>
       <c r="G329" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="H329" t="s">
         <v>9</v>
@@ -13458,7 +13461,7 @@
         <v>3.53800010681152</v>
       </c>
       <c r="G330" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="H330" t="s">
         <v>9</v>
@@ -13484,7 +13487,7 @@
         <v>3.5</v>
       </c>
       <c r="G331" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="H331" t="s">
         <v>9</v>
@@ -13510,7 +13513,7 @@
         <v>3.47199988365173</v>
       </c>
       <c r="G332" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="H332" t="s">
         <v>9</v>
@@ -13536,7 +13539,7 @@
         <v>3.50600004196167</v>
       </c>
       <c r="G333" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="H333" t="s">
         <v>9</v>
@@ -13562,7 +13565,7 @@
         <v>3.59200000762939</v>
       </c>
       <c r="G334" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="H334" t="s">
         <v>9</v>
@@ -13588,7 +13591,7 @@
         <v>3.59200000762939</v>
       </c>
       <c r="G335" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="H335" t="s">
         <v>9</v>
@@ -13614,7 +13617,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G336" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="H336" t="s">
         <v>9</v>
@@ -13640,7 +13643,7 @@
         <v>3.61999988555908</v>
       </c>
       <c r="G337" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="H337" t="s">
         <v>9</v>
@@ -13666,7 +13669,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G338" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="H338" t="s">
         <v>9</v>
@@ -13692,7 +13695,7 @@
         <v>3.59200000762939</v>
       </c>
       <c r="G339" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="H339" t="s">
         <v>9</v>
@@ -13718,7 +13721,7 @@
         <v>3.58599996566772</v>
       </c>
       <c r="G340" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="H340" t="s">
         <v>9</v>
@@ -13744,7 +13747,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G341" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="H341" t="s">
         <v>9</v>
@@ -13770,7 +13773,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G342" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="H342" t="s">
         <v>9</v>
@@ -13796,7 +13799,7 @@
         <v>3.58800005912781</v>
       </c>
       <c r="G343" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="H343" t="s">
         <v>9</v>
@@ -13822,7 +13825,7 @@
         <v>3.61999988555908</v>
       </c>
       <c r="G344" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="H344" t="s">
         <v>9</v>
@@ -13848,7 +13851,7 @@
         <v>3.64000010490417</v>
       </c>
       <c r="G345" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="H345" t="s">
         <v>9</v>
@@ -13874,7 +13877,7 @@
         <v>3.63800001144409</v>
       </c>
       <c r="G346" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="H346" t="s">
         <v>9</v>
@@ -13900,7 +13903,7 @@
         <v>3.63199996948242</v>
       </c>
       <c r="G347" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="H347" t="s">
         <v>9</v>
@@ -13926,7 +13929,7 @@
         <v>3.61999988555908</v>
       </c>
       <c r="G348" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="H348" t="s">
         <v>9</v>
@@ -13952,7 +13955,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G349" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="H349" t="s">
         <v>9</v>
@@ -13978,7 +13981,7 @@
         <v>3.75200009346008</v>
       </c>
       <c r="G350" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="H350" t="s">
         <v>9</v>
@@ -14004,7 +14007,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G351" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="H351" t="s">
         <v>9</v>
@@ -14030,7 +14033,7 @@
         <v>3.68600010871887</v>
       </c>
       <c r="G352" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="H352" t="s">
         <v>9</v>
@@ -14056,7 +14059,7 @@
         <v>3.66599988937378</v>
       </c>
       <c r="G353" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="H353" t="s">
         <v>9</v>
@@ -14082,7 +14085,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G354" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="H354" t="s">
         <v>9</v>
@@ -14108,7 +14111,7 @@
         <v>3.74799990653992</v>
       </c>
       <c r="G355" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="H355" t="s">
         <v>9</v>
@@ -14134,7 +14137,7 @@
         <v>3.7720000743866</v>
       </c>
       <c r="G356" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="H356" t="s">
         <v>9</v>
@@ -14160,7 +14163,7 @@
         <v>3.83599996566772</v>
       </c>
       <c r="G357" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="H357" t="s">
         <v>9</v>
@@ -14186,7 +14189,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G358" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="H358" t="s">
         <v>9</v>
@@ -14212,7 +14215,7 @@
         <v>3.80599999427795</v>
       </c>
       <c r="G359" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="H359" t="s">
         <v>9</v>
@@ -14238,7 +14241,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G360" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="H360" t="s">
         <v>9</v>
@@ -14264,7 +14267,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G361" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="H361" t="s">
         <v>9</v>
@@ -14290,7 +14293,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G362" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="H362" t="s">
         <v>9</v>
@@ -14316,7 +14319,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G363" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="H363" t="s">
         <v>9</v>
@@ -14342,7 +14345,7 @@
         <v>3.84999990463257</v>
       </c>
       <c r="G364" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="H364" t="s">
         <v>9</v>
@@ -14368,7 +14371,7 @@
         <v>3.93199992179871</v>
       </c>
       <c r="G365" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="H365" t="s">
         <v>9</v>
@@ -14394,7 +14397,7 @@
         <v>3.89400005340576</v>
       </c>
       <c r="G366" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="H366" t="s">
         <v>9</v>
@@ -14420,7 +14423,7 @@
         <v>3.83400011062622</v>
       </c>
       <c r="G367" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="H367" t="s">
         <v>9</v>
@@ -14446,7 +14449,7 @@
         <v>3.83400011062622</v>
       </c>
       <c r="G368" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="H368" t="s">
         <v>9</v>
@@ -14472,7 +14475,7 @@
         <v>3.81800007820129</v>
       </c>
       <c r="G369" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="H369" t="s">
         <v>9</v>
@@ -14498,7 +14501,7 @@
         <v>3.83800005912781</v>
       </c>
       <c r="G370" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="H370" t="s">
         <v>9</v>
@@ -14524,7 +14527,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G371" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="H371" t="s">
         <v>9</v>
@@ -14550,7 +14553,7 @@
         <v>3.72399997711182</v>
       </c>
       <c r="G372" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="H372" t="s">
         <v>9</v>
@@ -14576,7 +14579,7 @@
         <v>3.72199988365173</v>
       </c>
       <c r="G373" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="H373" t="s">
         <v>9</v>
@@ -14602,7 +14605,7 @@
         <v>3.60999989509583</v>
       </c>
       <c r="G374" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="H374" t="s">
         <v>9</v>
@@ -14628,7 +14631,7 @@
         <v>3.70199990272522</v>
       </c>
       <c r="G375" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="H375" t="s">
         <v>9</v>
@@ -14654,7 +14657,7 @@
         <v>3.71000003814697</v>
       </c>
       <c r="G376" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="H376" t="s">
         <v>9</v>
@@ -14680,7 +14683,7 @@
         <v>3.67199993133545</v>
       </c>
       <c r="G377" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="H377" t="s">
         <v>9</v>
@@ -14706,7 +14709,7 @@
         <v>3.66199994087219</v>
       </c>
       <c r="G378" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="H378" t="s">
         <v>9</v>
@@ -14732,7 +14735,7 @@
         <v>3.62400007247925</v>
       </c>
       <c r="G379" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="H379" t="s">
         <v>9</v>
@@ -14758,7 +14761,7 @@
         <v>3.66199994087219</v>
       </c>
       <c r="G380" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="H380" t="s">
         <v>9</v>
@@ -14784,7 +14787,7 @@
         <v>3.61999988555908</v>
       </c>
       <c r="G381" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="H381" t="s">
         <v>9</v>
@@ -14810,7 +14813,7 @@
         <v>3.63000011444092</v>
       </c>
       <c r="G382" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="H382" t="s">
         <v>9</v>
@@ -14836,7 +14839,7 @@
         <v>3.55599999427795</v>
       </c>
       <c r="G383" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="H383" t="s">
         <v>9</v>
@@ -14862,7 +14865,7 @@
         <v>3.57800006866455</v>
       </c>
       <c r="G384" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="H384" t="s">
         <v>9</v>
@@ -14888,7 +14891,7 @@
         <v>3.7279999256134</v>
       </c>
       <c r="G385" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="H385" t="s">
         <v>9</v>
@@ -14914,7 +14917,7 @@
         <v>3.73799991607666</v>
       </c>
       <c r="G386" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="H386" t="s">
         <v>9</v>
@@ -14940,7 +14943,7 @@
         <v>3.73600006103516</v>
       </c>
       <c r="G387" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="H387" t="s">
         <v>9</v>
@@ -14966,7 +14969,7 @@
         <v>3.76200008392334</v>
       </c>
       <c r="G388" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="H388" t="s">
         <v>9</v>
@@ -14992,7 +14995,7 @@
         <v>3.76600003242493</v>
       </c>
       <c r="G389" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="H389" t="s">
         <v>9</v>
@@ -15018,7 +15021,7 @@
         <v>3.80999994277954</v>
       </c>
       <c r="G390" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="H390" t="s">
         <v>9</v>
@@ -15044,7 +15047,7 @@
         <v>3.82999992370605</v>
       </c>
       <c r="G391" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="H391" t="s">
         <v>9</v>
@@ -15070,7 +15073,7 @@
         <v>3.88000011444092</v>
       </c>
       <c r="G392" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="H392" t="s">
         <v>9</v>
@@ -15096,7 +15099,7 @@
         <v>3.89000010490417</v>
       </c>
       <c r="G393" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="H393" t="s">
         <v>9</v>
@@ -15122,7 +15125,7 @@
         <v>3.91000008583069</v>
       </c>
       <c r="G394" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="H394" t="s">
         <v>9</v>
@@ -15148,7 +15151,7 @@
         <v>3.91400003433228</v>
       </c>
       <c r="G395" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="H395" t="s">
         <v>9</v>
@@ -15174,7 +15177,7 @@
         <v>3.93799996376038</v>
       </c>
       <c r="G396" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="H396" t="s">
         <v>9</v>
@@ -15200,7 +15203,7 @@
         <v>3.98799991607666</v>
       </c>
       <c r="G397" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="H397" t="s">
         <v>9</v>
@@ -15226,7 +15229,7 @@
         <v>4.00400018692017</v>
       </c>
       <c r="G398" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="H398" t="s">
         <v>9</v>
@@ -15252,7 +15255,7 @@
         <v>3.96000003814697</v>
       </c>
       <c r="G399" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="H399" t="s">
         <v>9</v>
@@ -15278,7 +15281,7 @@
         <v>3.99000000953674</v>
       </c>
       <c r="G400" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="H400" t="s">
         <v>9</v>
@@ -15304,7 +15307,7 @@
         <v>3.90199995040894</v>
       </c>
       <c r="G401" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="H401" t="s">
         <v>9</v>
@@ -15330,7 +15333,7 @@
         <v>3.93400001525879</v>
       </c>
       <c r="G402" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="H402" t="s">
         <v>9</v>
@@ -15356,7 +15359,7 @@
         <v>3.8659999370575</v>
       </c>
       <c r="G403" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="H403" t="s">
         <v>9</v>
@@ -15382,7 +15385,7 @@
         <v>3.84999990463257</v>
       </c>
       <c r="G404" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="H404" t="s">
         <v>9</v>
@@ -15408,7 +15411,7 @@
         <v>3.95000004768372</v>
       </c>
       <c r="G405" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="H405" t="s">
         <v>9</v>
@@ -15434,7 +15437,7 @@
         <v>3.75</v>
       </c>
       <c r="G406" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="H406" t="s">
         <v>9</v>
@@ -15460,7 +15463,7 @@
         <v>3.82399988174438</v>
       </c>
       <c r="G407" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="H407" t="s">
         <v>9</v>
@@ -15486,7 +15489,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G408" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="H408" t="s">
         <v>9</v>
@@ -15512,7 +15515,7 @@
         <v>3.84200000762939</v>
       </c>
       <c r="G409" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="H409" t="s">
         <v>9</v>
@@ -15538,7 +15541,7 @@
         <v>3.81399989